--- a/BacklogGATEAutoCompleto.xlsx
+++ b/BacklogGATEAutoCompleto.xlsx
@@ -8289,7 +8289,7 @@
         <v>1385</v>
       </c>
       <c r="E2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="F2" t="s">
         <v>1604</v>
@@ -8324,7 +8324,7 @@
         <v>1386</v>
       </c>
       <c r="E3">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="F3" t="s">
         <v>1605</v>
@@ -8359,7 +8359,7 @@
         <v>1387</v>
       </c>
       <c r="E4">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="F4" t="s">
         <v>1605</v>
@@ -8394,7 +8394,7 @@
         <v>1388</v>
       </c>
       <c r="E5">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="F5" t="s">
         <v>1605</v>
@@ -8429,7 +8429,7 @@
         <v>1389</v>
       </c>
       <c r="E6">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="F6" t="s">
         <v>1605</v>
@@ -8464,7 +8464,7 @@
         <v>1390</v>
       </c>
       <c r="E7">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F7" t="s">
         <v>1605</v>
@@ -8499,7 +8499,7 @@
         <v>1391</v>
       </c>
       <c r="E8">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="F8" t="s">
         <v>1605</v>
@@ -8534,7 +8534,7 @@
         <v>1391</v>
       </c>
       <c r="E9">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="F9" t="s">
         <v>1605</v>
@@ -8569,7 +8569,7 @@
         <v>1392</v>
       </c>
       <c r="E10">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F10" t="s">
         <v>1605</v>
@@ -8604,7 +8604,7 @@
         <v>1393</v>
       </c>
       <c r="E11">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="F11" t="s">
         <v>1605</v>
@@ -8639,7 +8639,7 @@
         <v>1394</v>
       </c>
       <c r="E12">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="F12" t="s">
         <v>1605</v>
@@ -8674,7 +8674,7 @@
         <v>1395</v>
       </c>
       <c r="E13">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="F13" t="s">
         <v>1605</v>
@@ -8709,7 +8709,7 @@
         <v>1396</v>
       </c>
       <c r="E14">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F14" t="s">
         <v>1605</v>
@@ -8744,7 +8744,7 @@
         <v>1397</v>
       </c>
       <c r="E15">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="F15" t="s">
         <v>1605</v>
@@ -8779,7 +8779,7 @@
         <v>1398</v>
       </c>
       <c r="E16">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="F16" t="s">
         <v>1605</v>
@@ -8814,7 +8814,7 @@
         <v>1398</v>
       </c>
       <c r="E17">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="F17" t="s">
         <v>1605</v>
@@ -8849,7 +8849,7 @@
         <v>1399</v>
       </c>
       <c r="E18">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="F18" t="s">
         <v>1605</v>
@@ -8884,7 +8884,7 @@
         <v>1400</v>
       </c>
       <c r="E19">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="F19" t="s">
         <v>1605</v>
@@ -8919,7 +8919,7 @@
         <v>1401</v>
       </c>
       <c r="E20">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="F20" t="s">
         <v>1605</v>
@@ -8954,7 +8954,7 @@
         <v>1401</v>
       </c>
       <c r="E21">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="F21" t="s">
         <v>1605</v>
@@ -8989,7 +8989,7 @@
         <v>1402</v>
       </c>
       <c r="E22">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="F22" t="s">
         <v>1605</v>
@@ -9024,7 +9024,7 @@
         <v>1403</v>
       </c>
       <c r="E23">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="F23" t="s">
         <v>1605</v>
@@ -9059,7 +9059,7 @@
         <v>1404</v>
       </c>
       <c r="E24">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="F24" t="s">
         <v>1605</v>
@@ -9094,7 +9094,7 @@
         <v>1404</v>
       </c>
       <c r="E25">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="F25" t="s">
         <v>1605</v>
@@ -9129,7 +9129,7 @@
         <v>1405</v>
       </c>
       <c r="E26">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="F26" t="s">
         <v>1605</v>
@@ -9164,7 +9164,7 @@
         <v>1406</v>
       </c>
       <c r="E27">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F27" t="s">
         <v>1605</v>
@@ -9199,7 +9199,7 @@
         <v>1407</v>
       </c>
       <c r="E28">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F28" t="s">
         <v>1605</v>
@@ -9234,7 +9234,7 @@
         <v>1408</v>
       </c>
       <c r="E29">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F29" t="s">
         <v>1605</v>
@@ -9269,7 +9269,7 @@
         <v>1409</v>
       </c>
       <c r="E30">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F30" t="s">
         <v>1605</v>
@@ -9307,7 +9307,7 @@
         <v>1410</v>
       </c>
       <c r="E31">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F31" t="s">
         <v>1605</v>
@@ -9342,7 +9342,7 @@
         <v>1411</v>
       </c>
       <c r="E32">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F32" t="s">
         <v>1605</v>
@@ -9377,7 +9377,7 @@
         <v>1412</v>
       </c>
       <c r="E33">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F33" t="s">
         <v>1605</v>
@@ -9412,7 +9412,7 @@
         <v>1413</v>
       </c>
       <c r="E34">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F34" t="s">
         <v>1605</v>
@@ -9447,7 +9447,7 @@
         <v>1413</v>
       </c>
       <c r="E35">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F35" t="s">
         <v>1605</v>
@@ -9482,7 +9482,7 @@
         <v>1414</v>
       </c>
       <c r="E36">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F36" t="s">
         <v>1605</v>
@@ -9517,7 +9517,7 @@
         <v>1415</v>
       </c>
       <c r="E37">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="F37" t="s">
         <v>1605</v>
@@ -9552,7 +9552,7 @@
         <v>1416</v>
       </c>
       <c r="E38">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F38" t="s">
         <v>1605</v>
@@ -9587,7 +9587,7 @@
         <v>1417</v>
       </c>
       <c r="E39">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F39" t="s">
         <v>1605</v>
@@ -9622,7 +9622,7 @@
         <v>1418</v>
       </c>
       <c r="E40">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F40" t="s">
         <v>1605</v>
@@ -9657,7 +9657,7 @@
         <v>1419</v>
       </c>
       <c r="E41">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F41" t="s">
         <v>1605</v>
@@ -9692,7 +9692,7 @@
         <v>1420</v>
       </c>
       <c r="E42">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F42" t="s">
         <v>1605</v>
@@ -9727,7 +9727,7 @@
         <v>1421</v>
       </c>
       <c r="E43">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F43" t="s">
         <v>1605</v>
@@ -9762,7 +9762,7 @@
         <v>1421</v>
       </c>
       <c r="E44">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F44" t="s">
         <v>1605</v>
@@ -9797,7 +9797,7 @@
         <v>1422</v>
       </c>
       <c r="E45">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F45" t="s">
         <v>1605</v>
@@ -9832,7 +9832,7 @@
         <v>1422</v>
       </c>
       <c r="E46">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F46" t="s">
         <v>1605</v>
@@ -9867,7 +9867,7 @@
         <v>1423</v>
       </c>
       <c r="E47">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F47" t="s">
         <v>1605</v>
@@ -9902,7 +9902,7 @@
         <v>1424</v>
       </c>
       <c r="E48">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F48" t="s">
         <v>1605</v>
@@ -9937,7 +9937,7 @@
         <v>1425</v>
       </c>
       <c r="E49">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F49" t="s">
         <v>1605</v>
@@ -9972,7 +9972,7 @@
         <v>1426</v>
       </c>
       <c r="E50">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F50" t="s">
         <v>1605</v>
@@ -10007,7 +10007,7 @@
         <v>1427</v>
       </c>
       <c r="E51">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F51" t="s">
         <v>1605</v>
@@ -10042,7 +10042,7 @@
         <v>1427</v>
       </c>
       <c r="E52">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F52" t="s">
         <v>1605</v>
@@ -10077,7 +10077,7 @@
         <v>1428</v>
       </c>
       <c r="E53">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F53" t="s">
         <v>1605</v>
@@ -10112,7 +10112,7 @@
         <v>1429</v>
       </c>
       <c r="E54">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F54" t="s">
         <v>1605</v>
@@ -10147,7 +10147,7 @@
         <v>1430</v>
       </c>
       <c r="E55">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F55" t="s">
         <v>1605</v>
@@ -10182,7 +10182,7 @@
         <v>1430</v>
       </c>
       <c r="E56">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F56" t="s">
         <v>1605</v>
@@ -10217,7 +10217,7 @@
         <v>1431</v>
       </c>
       <c r="E57">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F57" t="s">
         <v>1605</v>
@@ -10252,7 +10252,7 @@
         <v>1431</v>
       </c>
       <c r="E58">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F58" t="s">
         <v>1605</v>
@@ -10287,7 +10287,7 @@
         <v>1432</v>
       </c>
       <c r="E59">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F59" t="s">
         <v>1605</v>
@@ -10322,7 +10322,7 @@
         <v>1433</v>
       </c>
       <c r="E60">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F60" t="s">
         <v>1605</v>
@@ -10357,7 +10357,7 @@
         <v>1434</v>
       </c>
       <c r="E61">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F61" t="s">
         <v>1605</v>
@@ -10392,7 +10392,7 @@
         <v>1435</v>
       </c>
       <c r="E62">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F62" t="s">
         <v>1605</v>
@@ -10427,7 +10427,7 @@
         <v>1436</v>
       </c>
       <c r="E63">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F63" t="s">
         <v>1605</v>
@@ -10462,7 +10462,7 @@
         <v>1436</v>
       </c>
       <c r="E64">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F64" t="s">
         <v>1605</v>
@@ -10497,7 +10497,7 @@
         <v>1437</v>
       </c>
       <c r="E65">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F65" t="s">
         <v>1605</v>
@@ -10532,7 +10532,7 @@
         <v>1437</v>
       </c>
       <c r="E66">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F66" t="s">
         <v>1605</v>
@@ -10567,7 +10567,7 @@
         <v>1438</v>
       </c>
       <c r="E67">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F67" t="s">
         <v>1605</v>
@@ -10602,7 +10602,7 @@
         <v>1439</v>
       </c>
       <c r="E68">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F68" t="s">
         <v>1605</v>
@@ -10637,7 +10637,7 @@
         <v>1440</v>
       </c>
       <c r="E69">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F69" t="s">
         <v>1605</v>
@@ -10672,7 +10672,7 @@
         <v>1441</v>
       </c>
       <c r="E70">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F70" t="s">
         <v>1605</v>
@@ -10707,7 +10707,7 @@
         <v>1442</v>
       </c>
       <c r="E71">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F71" t="s">
         <v>1605</v>
@@ -10742,7 +10742,7 @@
         <v>1443</v>
       </c>
       <c r="E72">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F72" t="s">
         <v>1605</v>
@@ -10777,7 +10777,7 @@
         <v>1444</v>
       </c>
       <c r="E73">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F73" t="s">
         <v>1605</v>
@@ -10812,7 +10812,7 @@
         <v>1445</v>
       </c>
       <c r="E74">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F74" t="s">
         <v>1605</v>
@@ -10847,7 +10847,7 @@
         <v>1446</v>
       </c>
       <c r="E75">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F75" t="s">
         <v>1605</v>
@@ -10882,7 +10882,7 @@
         <v>1447</v>
       </c>
       <c r="E76">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F76" t="s">
         <v>1605</v>
@@ -10917,7 +10917,7 @@
         <v>1448</v>
       </c>
       <c r="E77">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F77" t="s">
         <v>1605</v>
@@ -10952,7 +10952,7 @@
         <v>1449</v>
       </c>
       <c r="E78">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F78" t="s">
         <v>1605</v>
@@ -10987,7 +10987,7 @@
         <v>1450</v>
       </c>
       <c r="E79">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F79" t="s">
         <v>1605</v>
@@ -11022,7 +11022,7 @@
         <v>1450</v>
       </c>
       <c r="E80">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F80" t="s">
         <v>1605</v>
@@ -11057,7 +11057,7 @@
         <v>1450</v>
       </c>
       <c r="E81">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F81" t="s">
         <v>1605</v>
@@ -11092,7 +11092,7 @@
         <v>1451</v>
       </c>
       <c r="E82">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F82" t="s">
         <v>1605</v>
@@ -11127,7 +11127,7 @@
         <v>1452</v>
       </c>
       <c r="E83">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F83" t="s">
         <v>1605</v>
@@ -11162,7 +11162,7 @@
         <v>1453</v>
       </c>
       <c r="E84">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F84" t="s">
         <v>1605</v>
@@ -11197,7 +11197,7 @@
         <v>1453</v>
       </c>
       <c r="E85">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F85" t="s">
         <v>1605</v>
@@ -11232,7 +11232,7 @@
         <v>1453</v>
       </c>
       <c r="E86">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F86" t="s">
         <v>1605</v>
@@ -11267,7 +11267,7 @@
         <v>1454</v>
       </c>
       <c r="E87">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F87" t="s">
         <v>1605</v>
@@ -11302,7 +11302,7 @@
         <v>1455</v>
       </c>
       <c r="E88">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F88" t="s">
         <v>1605</v>
@@ -11337,7 +11337,7 @@
         <v>1456</v>
       </c>
       <c r="E89">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F89" t="s">
         <v>1605</v>
@@ -11372,7 +11372,7 @@
         <v>1457</v>
       </c>
       <c r="E90">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F90" t="s">
         <v>1605</v>
@@ -11407,7 +11407,7 @@
         <v>1457</v>
       </c>
       <c r="E91">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F91" t="s">
         <v>1605</v>
@@ -11442,7 +11442,7 @@
         <v>1457</v>
       </c>
       <c r="E92">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F92" t="s">
         <v>1605</v>
@@ -11477,7 +11477,7 @@
         <v>1458</v>
       </c>
       <c r="E93">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F93" t="s">
         <v>1605</v>
@@ -11512,7 +11512,7 @@
         <v>1459</v>
       </c>
       <c r="E94">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F94" t="s">
         <v>1605</v>
@@ -11547,7 +11547,7 @@
         <v>1459</v>
       </c>
       <c r="E95">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F95" t="s">
         <v>1605</v>
@@ -11582,7 +11582,7 @@
         <v>1459</v>
       </c>
       <c r="E96">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F96" t="s">
         <v>1606</v>
@@ -11617,7 +11617,7 @@
         <v>1459</v>
       </c>
       <c r="E97">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F97" t="s">
         <v>1605</v>
@@ -11652,7 +11652,7 @@
         <v>1460</v>
       </c>
       <c r="E98">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F98" t="s">
         <v>1605</v>
@@ -11687,7 +11687,7 @@
         <v>1461</v>
       </c>
       <c r="E99">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F99" t="s">
         <v>1605</v>
@@ -11722,7 +11722,7 @@
         <v>1462</v>
       </c>
       <c r="E100">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F100" t="s">
         <v>1605</v>
@@ -11757,7 +11757,7 @@
         <v>1462</v>
       </c>
       <c r="E101">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F101" t="s">
         <v>1605</v>
@@ -11792,7 +11792,7 @@
         <v>1462</v>
       </c>
       <c r="E102">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F102" t="s">
         <v>1605</v>
@@ -11827,7 +11827,7 @@
         <v>1463</v>
       </c>
       <c r="E103">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F103" t="s">
         <v>1605</v>
@@ -11862,7 +11862,7 @@
         <v>1464</v>
       </c>
       <c r="E104">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F104" t="s">
         <v>1605</v>
@@ -11897,7 +11897,7 @@
         <v>1465</v>
       </c>
       <c r="E105">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F105" t="s">
         <v>1605</v>
@@ -11932,7 +11932,7 @@
         <v>1466</v>
       </c>
       <c r="E106">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F106" t="s">
         <v>1605</v>
@@ -11967,7 +11967,7 @@
         <v>1467</v>
       </c>
       <c r="E107">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F107" t="s">
         <v>1605</v>
@@ -12002,7 +12002,7 @@
         <v>1467</v>
       </c>
       <c r="E108">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F108" t="s">
         <v>1605</v>
@@ -12037,7 +12037,7 @@
         <v>1467</v>
       </c>
       <c r="E109">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F109" t="s">
         <v>1605</v>
@@ -12072,7 +12072,7 @@
         <v>1467</v>
       </c>
       <c r="E110">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F110" t="s">
         <v>1605</v>
@@ -12107,7 +12107,7 @@
         <v>1467</v>
       </c>
       <c r="E111">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F111" t="s">
         <v>1605</v>
@@ -12142,7 +12142,7 @@
         <v>1467</v>
       </c>
       <c r="E112">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F112" t="s">
         <v>1605</v>
@@ -12177,7 +12177,7 @@
         <v>1467</v>
       </c>
       <c r="E113">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F113" t="s">
         <v>1605</v>
@@ -12212,7 +12212,7 @@
         <v>1468</v>
       </c>
       <c r="E114">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F114" t="s">
         <v>1605</v>
@@ -12247,7 +12247,7 @@
         <v>1468</v>
       </c>
       <c r="E115">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F115" t="s">
         <v>1605</v>
@@ -12282,7 +12282,7 @@
         <v>1469</v>
       </c>
       <c r="E116">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F116" t="s">
         <v>1605</v>
@@ -12317,7 +12317,7 @@
         <v>1470</v>
       </c>
       <c r="E117">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F117" t="s">
         <v>1605</v>
@@ -12352,7 +12352,7 @@
         <v>1470</v>
       </c>
       <c r="E118">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F118" t="s">
         <v>1605</v>
@@ -12387,7 +12387,7 @@
         <v>1471</v>
       </c>
       <c r="E119">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F119" t="s">
         <v>1605</v>
@@ -12422,7 +12422,7 @@
         <v>1471</v>
       </c>
       <c r="E120">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F120" t="s">
         <v>1607</v>
@@ -12457,7 +12457,7 @@
         <v>1472</v>
       </c>
       <c r="E121">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F121" t="s">
         <v>1605</v>
@@ -12492,7 +12492,7 @@
         <v>1473</v>
       </c>
       <c r="E122">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F122" t="s">
         <v>1605</v>
@@ -12527,7 +12527,7 @@
         <v>1474</v>
       </c>
       <c r="E123">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F123" t="s">
         <v>1605</v>
@@ -12562,7 +12562,7 @@
         <v>1474</v>
       </c>
       <c r="E124">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F124" t="s">
         <v>1605</v>
@@ -12597,7 +12597,7 @@
         <v>1475</v>
       </c>
       <c r="E125">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F125" t="s">
         <v>1605</v>
@@ -12632,7 +12632,7 @@
         <v>1476</v>
       </c>
       <c r="E126">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F126" t="s">
         <v>1605</v>
@@ -12667,7 +12667,7 @@
         <v>1477</v>
       </c>
       <c r="E127">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F127" t="s">
         <v>1605</v>
@@ -12702,7 +12702,7 @@
         <v>1477</v>
       </c>
       <c r="E128">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F128" t="s">
         <v>1605</v>
@@ -12737,7 +12737,7 @@
         <v>1478</v>
       </c>
       <c r="E129">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F129" t="s">
         <v>1605</v>
@@ -12772,7 +12772,7 @@
         <v>1479</v>
       </c>
       <c r="E130">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F130" t="s">
         <v>1605</v>
@@ -12807,7 +12807,7 @@
         <v>1479</v>
       </c>
       <c r="E131">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F131" t="s">
         <v>1605</v>
@@ -12842,7 +12842,7 @@
         <v>1480</v>
       </c>
       <c r="E132">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F132" t="s">
         <v>1605</v>
@@ -12877,7 +12877,7 @@
         <v>1480</v>
       </c>
       <c r="E133">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F133" t="s">
         <v>1605</v>
@@ -12912,7 +12912,7 @@
         <v>1480</v>
       </c>
       <c r="E134">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F134" t="s">
         <v>1605</v>
@@ -12947,7 +12947,7 @@
         <v>1480</v>
       </c>
       <c r="E135">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F135" t="s">
         <v>1605</v>
@@ -12982,7 +12982,7 @@
         <v>1481</v>
       </c>
       <c r="E136">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F136" t="s">
         <v>1605</v>
@@ -13017,7 +13017,7 @@
         <v>1481</v>
       </c>
       <c r="E137">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F137" t="s">
         <v>1605</v>
@@ -13052,7 +13052,7 @@
         <v>1481</v>
       </c>
       <c r="E138">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F138" t="s">
         <v>1605</v>
@@ -13087,7 +13087,7 @@
         <v>1481</v>
       </c>
       <c r="E139">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F139" t="s">
         <v>1605</v>
@@ -13122,7 +13122,7 @@
         <v>1481</v>
       </c>
       <c r="E140">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F140" t="s">
         <v>1605</v>
@@ -13157,7 +13157,7 @@
         <v>1481</v>
       </c>
       <c r="E141">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F141" t="s">
         <v>1605</v>
@@ -13192,7 +13192,7 @@
         <v>1482</v>
       </c>
       <c r="E142">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F142" t="s">
         <v>1605</v>
@@ -13227,7 +13227,7 @@
         <v>1482</v>
       </c>
       <c r="E143">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F143" t="s">
         <v>1605</v>
@@ -13262,7 +13262,7 @@
         <v>1483</v>
       </c>
       <c r="E144">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F144" t="s">
         <v>1605</v>
@@ -13297,7 +13297,7 @@
         <v>1483</v>
       </c>
       <c r="E145">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F145" t="s">
         <v>1605</v>
@@ -13332,7 +13332,7 @@
         <v>1484</v>
       </c>
       <c r="E146">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F146" t="s">
         <v>1605</v>
@@ -13367,7 +13367,7 @@
         <v>1485</v>
       </c>
       <c r="E147">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F147" t="s">
         <v>1605</v>
@@ -13402,7 +13402,7 @@
         <v>1485</v>
       </c>
       <c r="E148">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F148" t="s">
         <v>1605</v>
@@ -13437,7 +13437,7 @@
         <v>1485</v>
       </c>
       <c r="E149">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F149" t="s">
         <v>1605</v>
@@ -13472,7 +13472,7 @@
         <v>1486</v>
       </c>
       <c r="E150">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F150" t="s">
         <v>1605</v>
@@ -13507,7 +13507,7 @@
         <v>1486</v>
       </c>
       <c r="E151">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F151" t="s">
         <v>1605</v>
@@ -13542,7 +13542,7 @@
         <v>1486</v>
       </c>
       <c r="E152">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F152" t="s">
         <v>1605</v>
@@ -13577,7 +13577,7 @@
         <v>1487</v>
       </c>
       <c r="E153">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F153" t="s">
         <v>1605</v>
@@ -13612,7 +13612,7 @@
         <v>1487</v>
       </c>
       <c r="E154">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F154" t="s">
         <v>1605</v>
@@ -13647,7 +13647,7 @@
         <v>1487</v>
       </c>
       <c r="E155">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F155" t="s">
         <v>1605</v>
@@ -13682,7 +13682,7 @@
         <v>1488</v>
       </c>
       <c r="E156">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F156" t="s">
         <v>1605</v>
@@ -13717,7 +13717,7 @@
         <v>1488</v>
       </c>
       <c r="E157">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F157" t="s">
         <v>1605</v>
@@ -13752,7 +13752,7 @@
         <v>1489</v>
       </c>
       <c r="E158">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F158" t="s">
         <v>1605</v>
@@ -13787,7 +13787,7 @@
         <v>1490</v>
       </c>
       <c r="E159">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F159" t="s">
         <v>1605</v>
@@ -13822,7 +13822,7 @@
         <v>1490</v>
       </c>
       <c r="E160">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F160" t="s">
         <v>1605</v>
@@ -13857,7 +13857,7 @@
         <v>1490</v>
       </c>
       <c r="E161">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F161" t="s">
         <v>1605</v>
@@ -13892,7 +13892,7 @@
         <v>1491</v>
       </c>
       <c r="E162">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F162" t="s">
         <v>1605</v>
@@ -13927,7 +13927,7 @@
         <v>1491</v>
       </c>
       <c r="E163">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F163" t="s">
         <v>1605</v>
@@ -13962,7 +13962,7 @@
         <v>1492</v>
       </c>
       <c r="E164">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F164" t="s">
         <v>1605</v>
@@ -14000,7 +14000,7 @@
         <v>1492</v>
       </c>
       <c r="E165">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F165" t="s">
         <v>1605</v>
@@ -14035,7 +14035,7 @@
         <v>1492</v>
       </c>
       <c r="E166">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F166" t="s">
         <v>1605</v>
@@ -14070,7 +14070,7 @@
         <v>1492</v>
       </c>
       <c r="E167">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F167" t="s">
         <v>1605</v>
@@ -14105,7 +14105,7 @@
         <v>1492</v>
       </c>
       <c r="E168">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F168" t="s">
         <v>1605</v>
@@ -14140,7 +14140,7 @@
         <v>1492</v>
       </c>
       <c r="E169">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F169" t="s">
         <v>1605</v>
@@ -14175,7 +14175,7 @@
         <v>1493</v>
       </c>
       <c r="E170">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F170" t="s">
         <v>1605</v>
@@ -14210,7 +14210,7 @@
         <v>1494</v>
       </c>
       <c r="E171">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F171" t="s">
         <v>1605</v>
@@ -14245,7 +14245,7 @@
         <v>1494</v>
       </c>
       <c r="E172">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F172" t="s">
         <v>1605</v>
@@ -14280,7 +14280,7 @@
         <v>1495</v>
       </c>
       <c r="E173">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F173" t="s">
         <v>1606</v>
@@ -14315,7 +14315,7 @@
         <v>1496</v>
       </c>
       <c r="E174">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F174" t="s">
         <v>1605</v>
@@ -14350,7 +14350,7 @@
         <v>1496</v>
       </c>
       <c r="E175">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F175" t="s">
         <v>1605</v>
@@ -14385,7 +14385,7 @@
         <v>1496</v>
       </c>
       <c r="E176">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F176" t="s">
         <v>1605</v>
@@ -14420,7 +14420,7 @@
         <v>1496</v>
       </c>
       <c r="E177">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F177" t="s">
         <v>1605</v>
@@ -14455,7 +14455,7 @@
         <v>1496</v>
       </c>
       <c r="E178">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F178" t="s">
         <v>1605</v>
@@ -14490,7 +14490,7 @@
         <v>1497</v>
       </c>
       <c r="E179">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F179" t="s">
         <v>1605</v>
@@ -14525,7 +14525,7 @@
         <v>1497</v>
       </c>
       <c r="E180">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F180" t="s">
         <v>1605</v>
@@ -14560,7 +14560,7 @@
         <v>1497</v>
       </c>
       <c r="E181">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F181" t="s">
         <v>1605</v>
@@ -14595,7 +14595,7 @@
         <v>1497</v>
       </c>
       <c r="E182">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F182" t="s">
         <v>1605</v>
@@ -14630,7 +14630,7 @@
         <v>1497</v>
       </c>
       <c r="E183">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F183" t="s">
         <v>1605</v>
@@ -14665,7 +14665,7 @@
         <v>1497</v>
       </c>
       <c r="E184">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F184" t="s">
         <v>1605</v>
@@ -14700,7 +14700,7 @@
         <v>1497</v>
       </c>
       <c r="E185">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F185" t="s">
         <v>1605</v>
@@ -14735,7 +14735,7 @@
         <v>1498</v>
       </c>
       <c r="E186">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F186" t="s">
         <v>1605</v>
@@ -14770,7 +14770,7 @@
         <v>1498</v>
       </c>
       <c r="E187">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F187" t="s">
         <v>1605</v>
@@ -14805,7 +14805,7 @@
         <v>1499</v>
       </c>
       <c r="E188">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F188" t="s">
         <v>1605</v>
@@ -14840,7 +14840,7 @@
         <v>1499</v>
       </c>
       <c r="E189">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F189" t="s">
         <v>1605</v>
@@ -14875,7 +14875,7 @@
         <v>1499</v>
       </c>
       <c r="E190">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F190" t="s">
         <v>1605</v>
@@ -14910,7 +14910,7 @@
         <v>1500</v>
       </c>
       <c r="E191">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F191" t="s">
         <v>1605</v>
@@ -14945,7 +14945,7 @@
         <v>1500</v>
       </c>
       <c r="E192">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F192" t="s">
         <v>1605</v>
@@ -14980,7 +14980,7 @@
         <v>1500</v>
       </c>
       <c r="E193">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F193" t="s">
         <v>1605</v>
@@ -15015,7 +15015,7 @@
         <v>1500</v>
       </c>
       <c r="E194">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F194" t="s">
         <v>1605</v>
@@ -15050,7 +15050,7 @@
         <v>1501</v>
       </c>
       <c r="E195">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F195" t="s">
         <v>1605</v>
@@ -15085,7 +15085,7 @@
         <v>1501</v>
       </c>
       <c r="E196">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F196" t="s">
         <v>1605</v>
@@ -15120,7 +15120,7 @@
         <v>1501</v>
       </c>
       <c r="E197">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F197" t="s">
         <v>1605</v>
@@ -15155,7 +15155,7 @@
         <v>1501</v>
       </c>
       <c r="E198">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F198" t="s">
         <v>1605</v>
@@ -15190,7 +15190,7 @@
         <v>1501</v>
       </c>
       <c r="E199">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F199" t="s">
         <v>1605</v>
@@ -15225,7 +15225,7 @@
         <v>1501</v>
       </c>
       <c r="E200">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F200" t="s">
         <v>1605</v>
@@ -15260,7 +15260,7 @@
         <v>1501</v>
       </c>
       <c r="E201">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F201" t="s">
         <v>1605</v>
@@ -15295,7 +15295,7 @@
         <v>1501</v>
       </c>
       <c r="E202">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F202" t="s">
         <v>1605</v>
@@ -15330,7 +15330,7 @@
         <v>1501</v>
       </c>
       <c r="E203">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F203" t="s">
         <v>1605</v>
@@ -15365,7 +15365,7 @@
         <v>1501</v>
       </c>
       <c r="E204">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F204" t="s">
         <v>1605</v>
@@ -15400,7 +15400,7 @@
         <v>1502</v>
       </c>
       <c r="E205">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F205" t="s">
         <v>1605</v>
@@ -15435,7 +15435,7 @@
         <v>1502</v>
       </c>
       <c r="E206">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F206" t="s">
         <v>1605</v>
@@ -15470,7 +15470,7 @@
         <v>1502</v>
       </c>
       <c r="E207">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F207" t="s">
         <v>1605</v>
@@ -15505,7 +15505,7 @@
         <v>1502</v>
       </c>
       <c r="E208">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F208" t="s">
         <v>1608</v>
@@ -15540,7 +15540,7 @@
         <v>1503</v>
       </c>
       <c r="E209">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F209" t="s">
         <v>1605</v>
@@ -15575,7 +15575,7 @@
         <v>1503</v>
       </c>
       <c r="E210">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F210" t="s">
         <v>1606</v>
@@ -15610,7 +15610,7 @@
         <v>1503</v>
       </c>
       <c r="E211">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F211" t="s">
         <v>1605</v>
@@ -15645,7 +15645,7 @@
         <v>1504</v>
       </c>
       <c r="E212">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F212" t="s">
         <v>1605</v>
@@ -15680,7 +15680,7 @@
         <v>1504</v>
       </c>
       <c r="E213">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F213" t="s">
         <v>1605</v>
@@ -15715,7 +15715,7 @@
         <v>1505</v>
       </c>
       <c r="E214">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F214" t="s">
         <v>1605</v>
@@ -15750,7 +15750,7 @@
         <v>1505</v>
       </c>
       <c r="E215">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F215" t="s">
         <v>1605</v>
@@ -15785,7 +15785,7 @@
         <v>1506</v>
       </c>
       <c r="E216">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F216" t="s">
         <v>1605</v>
@@ -15820,7 +15820,7 @@
         <v>1506</v>
       </c>
       <c r="E217">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F217" t="s">
         <v>1605</v>
@@ -15855,7 +15855,7 @@
         <v>1506</v>
       </c>
       <c r="E218">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F218" t="s">
         <v>1605</v>
@@ -15890,7 +15890,7 @@
         <v>1507</v>
       </c>
       <c r="E219">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F219" t="s">
         <v>1605</v>
@@ -15925,7 +15925,7 @@
         <v>1507</v>
       </c>
       <c r="E220">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F220" t="s">
         <v>1605</v>
@@ -15960,7 +15960,7 @@
         <v>1507</v>
       </c>
       <c r="E221">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F221" t="s">
         <v>1605</v>
@@ -15995,7 +15995,7 @@
         <v>1507</v>
       </c>
       <c r="E222">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F222" t="s">
         <v>1605</v>
@@ -16030,7 +16030,7 @@
         <v>1507</v>
       </c>
       <c r="E223">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F223" t="s">
         <v>1605</v>
@@ -16065,7 +16065,7 @@
         <v>1507</v>
       </c>
       <c r="E224">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F224" t="s">
         <v>1605</v>
@@ -16100,7 +16100,7 @@
         <v>1508</v>
       </c>
       <c r="E225">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F225" t="s">
         <v>1605</v>
@@ -16135,7 +16135,7 @@
         <v>1508</v>
       </c>
       <c r="E226">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F226" t="s">
         <v>1605</v>
@@ -16170,7 +16170,7 @@
         <v>1509</v>
       </c>
       <c r="E227">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F227" t="s">
         <v>1605</v>
@@ -16205,7 +16205,7 @@
         <v>1510</v>
       </c>
       <c r="E228">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F228" t="s">
         <v>1605</v>
@@ -16240,7 +16240,7 @@
         <v>1510</v>
       </c>
       <c r="E229">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F229" t="s">
         <v>1605</v>
@@ -16275,7 +16275,7 @@
         <v>1510</v>
       </c>
       <c r="E230">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F230" t="s">
         <v>1605</v>
@@ -16310,7 +16310,7 @@
         <v>1510</v>
       </c>
       <c r="E231">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F231" t="s">
         <v>1605</v>
@@ -16345,7 +16345,7 @@
         <v>1511</v>
       </c>
       <c r="E232">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F232" t="s">
         <v>1605</v>
@@ -16380,7 +16380,7 @@
         <v>1512</v>
       </c>
       <c r="E233">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F233" t="s">
         <v>1605</v>
@@ -16415,7 +16415,7 @@
         <v>1512</v>
       </c>
       <c r="E234">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F234" t="s">
         <v>1605</v>
@@ -16450,7 +16450,7 @@
         <v>1512</v>
       </c>
       <c r="E235">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F235" t="s">
         <v>1605</v>
@@ -16485,7 +16485,7 @@
         <v>1512</v>
       </c>
       <c r="E236">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F236" t="s">
         <v>1605</v>
@@ -16520,7 +16520,7 @@
         <v>1512</v>
       </c>
       <c r="E237">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F237" t="s">
         <v>1605</v>
@@ -16555,7 +16555,7 @@
         <v>1513</v>
       </c>
       <c r="E238">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F238" t="s">
         <v>1605</v>
@@ -16590,7 +16590,7 @@
         <v>1513</v>
       </c>
       <c r="E239">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F239" t="s">
         <v>1605</v>
@@ -16625,7 +16625,7 @@
         <v>1513</v>
       </c>
       <c r="E240">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F240" t="s">
         <v>1605</v>
@@ -16660,7 +16660,7 @@
         <v>1513</v>
       </c>
       <c r="E241">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F241" t="s">
         <v>1605</v>
@@ -16695,7 +16695,7 @@
         <v>1513</v>
       </c>
       <c r="E242">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F242" t="s">
         <v>1605</v>
@@ -16730,7 +16730,7 @@
         <v>1513</v>
       </c>
       <c r="E243">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F243" t="s">
         <v>1605</v>
@@ -16765,7 +16765,7 @@
         <v>1513</v>
       </c>
       <c r="E244">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F244" t="s">
         <v>1605</v>
@@ -16800,7 +16800,7 @@
         <v>1514</v>
       </c>
       <c r="E245">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F245" t="s">
         <v>1605</v>
@@ -16835,7 +16835,7 @@
         <v>1514</v>
       </c>
       <c r="E246">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F246" t="s">
         <v>1605</v>
@@ -16870,7 +16870,7 @@
         <v>1514</v>
       </c>
       <c r="E247">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F247" t="s">
         <v>1605</v>
@@ -16905,7 +16905,7 @@
         <v>1514</v>
       </c>
       <c r="E248">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F248" t="s">
         <v>1605</v>
@@ -16940,7 +16940,7 @@
         <v>1515</v>
       </c>
       <c r="E249">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F249" t="s">
         <v>1605</v>
@@ -16975,7 +16975,7 @@
         <v>1515</v>
       </c>
       <c r="E250">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F250" t="s">
         <v>1605</v>
@@ -17010,7 +17010,7 @@
         <v>1515</v>
       </c>
       <c r="E251">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F251" t="s">
         <v>1605</v>
@@ -17045,7 +17045,7 @@
         <v>1516</v>
       </c>
       <c r="E252">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F252" t="s">
         <v>1605</v>
@@ -17080,7 +17080,7 @@
         <v>1516</v>
       </c>
       <c r="E253">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F253" t="s">
         <v>1605</v>
@@ -17115,7 +17115,7 @@
         <v>1517</v>
       </c>
       <c r="E254">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F254" t="s">
         <v>1605</v>
@@ -17150,7 +17150,7 @@
         <v>1517</v>
       </c>
       <c r="E255">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F255" t="s">
         <v>1605</v>
@@ -17185,7 +17185,7 @@
         <v>1518</v>
       </c>
       <c r="E256">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F256" t="s">
         <v>1605</v>
@@ -17220,7 +17220,7 @@
         <v>1518</v>
       </c>
       <c r="E257">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F257" t="s">
         <v>1605</v>
@@ -17255,7 +17255,7 @@
         <v>1519</v>
       </c>
       <c r="E258">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F258" t="s">
         <v>1605</v>
@@ -17290,7 +17290,7 @@
         <v>1519</v>
       </c>
       <c r="E259">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F259" t="s">
         <v>1605</v>
@@ -17325,7 +17325,7 @@
         <v>1520</v>
       </c>
       <c r="E260">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F260" t="s">
         <v>1605</v>
@@ -17360,7 +17360,7 @@
         <v>1520</v>
       </c>
       <c r="E261">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F261" t="s">
         <v>1605</v>
@@ -17395,7 +17395,7 @@
         <v>1521</v>
       </c>
       <c r="E262">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F262" t="s">
         <v>1605</v>
@@ -17430,7 +17430,7 @@
         <v>1521</v>
       </c>
       <c r="E263">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F263" t="s">
         <v>1605</v>
@@ -17465,7 +17465,7 @@
         <v>1522</v>
       </c>
       <c r="E264">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F264" t="s">
         <v>1605</v>
@@ -17500,7 +17500,7 @@
         <v>1522</v>
       </c>
       <c r="E265">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F265" t="s">
         <v>1605</v>
@@ -17535,7 +17535,7 @@
         <v>1522</v>
       </c>
       <c r="E266">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F266" t="s">
         <v>1605</v>
@@ -17570,7 +17570,7 @@
         <v>1523</v>
       </c>
       <c r="E267">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F267" t="s">
         <v>1605</v>
@@ -17605,7 +17605,7 @@
         <v>1523</v>
       </c>
       <c r="E268">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F268" t="s">
         <v>1605</v>
@@ -17640,7 +17640,7 @@
         <v>1523</v>
       </c>
       <c r="E269">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F269" t="s">
         <v>1605</v>
@@ -17675,7 +17675,7 @@
         <v>1524</v>
       </c>
       <c r="E270">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F270" t="s">
         <v>1605</v>
@@ -17710,7 +17710,7 @@
         <v>1525</v>
       </c>
       <c r="E271">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F271" t="s">
         <v>1605</v>
@@ -17745,7 +17745,7 @@
         <v>1525</v>
       </c>
       <c r="E272">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F272" t="s">
         <v>1605</v>
@@ -17780,7 +17780,7 @@
         <v>1525</v>
       </c>
       <c r="E273">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F273" t="s">
         <v>1605</v>
@@ -17815,7 +17815,7 @@
         <v>1526</v>
       </c>
       <c r="E274">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F274" t="s">
         <v>1605</v>
@@ -17850,7 +17850,7 @@
         <v>1526</v>
       </c>
       <c r="E275">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F275" t="s">
         <v>1605</v>
@@ -17885,7 +17885,7 @@
         <v>1526</v>
       </c>
       <c r="E276">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F276" t="s">
         <v>1605</v>
@@ -17920,7 +17920,7 @@
         <v>1527</v>
       </c>
       <c r="E277">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F277" t="s">
         <v>1605</v>
@@ -17955,7 +17955,7 @@
         <v>1527</v>
       </c>
       <c r="E278">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F278" t="s">
         <v>1605</v>
@@ -17990,7 +17990,7 @@
         <v>1527</v>
       </c>
       <c r="E279">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F279" t="s">
         <v>1607</v>
@@ -18025,7 +18025,7 @@
         <v>1527</v>
       </c>
       <c r="E280">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F280" t="s">
         <v>1605</v>
@@ -18060,7 +18060,7 @@
         <v>1527</v>
       </c>
       <c r="E281">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F281" t="s">
         <v>1605</v>
@@ -18095,7 +18095,7 @@
         <v>1528</v>
       </c>
       <c r="E282">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F282" t="s">
         <v>1605</v>
@@ -18130,7 +18130,7 @@
         <v>1528</v>
       </c>
       <c r="E283">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F283" t="s">
         <v>1605</v>
@@ -18165,7 +18165,7 @@
         <v>1528</v>
       </c>
       <c r="E284">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F284" t="s">
         <v>1605</v>
@@ -18203,7 +18203,7 @@
         <v>1528</v>
       </c>
       <c r="E285">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F285" t="s">
         <v>1605</v>
@@ -18238,7 +18238,7 @@
         <v>1528</v>
       </c>
       <c r="E286">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F286" t="s">
         <v>1605</v>
@@ -18273,7 +18273,7 @@
         <v>1528</v>
       </c>
       <c r="E287">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F287" t="s">
         <v>1605</v>
@@ -18308,7 +18308,7 @@
         <v>1528</v>
       </c>
       <c r="E288">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F288" t="s">
         <v>1605</v>
@@ -18343,7 +18343,7 @@
         <v>1529</v>
       </c>
       <c r="E289">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F289" t="s">
         <v>1605</v>
@@ -18378,7 +18378,7 @@
         <v>1529</v>
       </c>
       <c r="E290">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F290" t="s">
         <v>1605</v>
@@ -18413,7 +18413,7 @@
         <v>1529</v>
       </c>
       <c r="E291">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F291" t="s">
         <v>1605</v>
@@ -18448,7 +18448,7 @@
         <v>1529</v>
       </c>
       <c r="E292">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F292" t="s">
         <v>1605</v>
@@ -18483,7 +18483,7 @@
         <v>1530</v>
       </c>
       <c r="E293">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F293" t="s">
         <v>1605</v>
@@ -18518,7 +18518,7 @@
         <v>1530</v>
       </c>
       <c r="E294">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F294" t="s">
         <v>1605</v>
@@ -18553,7 +18553,7 @@
         <v>1530</v>
       </c>
       <c r="E295">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F295" t="s">
         <v>1605</v>
@@ -18588,7 +18588,7 @@
         <v>1530</v>
       </c>
       <c r="E296">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F296" t="s">
         <v>1605</v>
@@ -18623,7 +18623,7 @@
         <v>1530</v>
       </c>
       <c r="E297">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F297" t="s">
         <v>1605</v>
@@ -18658,7 +18658,7 @@
         <v>1531</v>
       </c>
       <c r="E298">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F298" t="s">
         <v>1605</v>
@@ -18693,7 +18693,7 @@
         <v>1531</v>
       </c>
       <c r="E299">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F299" t="s">
         <v>1605</v>
@@ -18728,7 +18728,7 @@
         <v>1531</v>
       </c>
       <c r="E300">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F300" t="s">
         <v>1605</v>
@@ -18763,7 +18763,7 @@
         <v>1531</v>
       </c>
       <c r="E301">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F301" t="s">
         <v>1605</v>
@@ -18798,7 +18798,7 @@
         <v>1531</v>
       </c>
       <c r="E302">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F302" t="s">
         <v>1605</v>
@@ -18833,7 +18833,7 @@
         <v>1531</v>
       </c>
       <c r="E303">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F303" t="s">
         <v>1605</v>
@@ -18868,7 +18868,7 @@
         <v>1532</v>
       </c>
       <c r="E304">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F304" t="s">
         <v>1605</v>
@@ -18903,7 +18903,7 @@
         <v>1532</v>
       </c>
       <c r="E305">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F305" t="s">
         <v>1605</v>
@@ -18938,7 +18938,7 @@
         <v>1532</v>
       </c>
       <c r="E306">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F306" t="s">
         <v>1605</v>
@@ -18973,7 +18973,7 @@
         <v>1532</v>
       </c>
       <c r="E307">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F307" t="s">
         <v>1605</v>
@@ -19008,7 +19008,7 @@
         <v>1532</v>
       </c>
       <c r="E308">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F308" t="s">
         <v>1605</v>
@@ -19043,7 +19043,7 @@
         <v>1532</v>
       </c>
       <c r="E309">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F309" t="s">
         <v>1605</v>
@@ -19078,7 +19078,7 @@
         <v>1533</v>
       </c>
       <c r="E310">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F310" t="s">
         <v>1605</v>
@@ -19113,7 +19113,7 @@
         <v>1533</v>
       </c>
       <c r="E311">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F311" t="s">
         <v>1605</v>
@@ -19148,7 +19148,7 @@
         <v>1534</v>
       </c>
       <c r="E312">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F312" t="s">
         <v>1606</v>
@@ -19183,7 +19183,7 @@
         <v>1534</v>
       </c>
       <c r="E313">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F313" t="s">
         <v>1605</v>
@@ -19218,7 +19218,7 @@
         <v>1534</v>
       </c>
       <c r="E314">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F314" t="s">
         <v>1605</v>
@@ -19253,7 +19253,7 @@
         <v>1534</v>
       </c>
       <c r="E315">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F315" t="s">
         <v>1608</v>
@@ -19288,7 +19288,7 @@
         <v>1534</v>
       </c>
       <c r="E316">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F316" t="s">
         <v>1605</v>
@@ -19323,7 +19323,7 @@
         <v>1534</v>
       </c>
       <c r="E317">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F317" t="s">
         <v>1605</v>
@@ -19358,7 +19358,7 @@
         <v>1534</v>
       </c>
       <c r="E318">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F318" t="s">
         <v>1605</v>
@@ -19393,7 +19393,7 @@
         <v>1534</v>
       </c>
       <c r="E319">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F319" t="s">
         <v>1605</v>
@@ -19428,7 +19428,7 @@
         <v>1535</v>
       </c>
       <c r="E320">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F320" t="s">
         <v>1605</v>
@@ -19463,7 +19463,7 @@
         <v>1535</v>
       </c>
       <c r="E321">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F321" t="s">
         <v>1605</v>
@@ -19498,7 +19498,7 @@
         <v>1535</v>
       </c>
       <c r="E322">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F322" t="s">
         <v>1605</v>
@@ -19533,7 +19533,7 @@
         <v>1535</v>
       </c>
       <c r="E323">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F323" t="s">
         <v>1605</v>
@@ -19568,7 +19568,7 @@
         <v>1536</v>
       </c>
       <c r="E324">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F324" t="s">
         <v>1605</v>
@@ -19603,7 +19603,7 @@
         <v>1536</v>
       </c>
       <c r="E325">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F325" t="s">
         <v>1605</v>
@@ -19638,7 +19638,7 @@
         <v>1537</v>
       </c>
       <c r="E326">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F326" t="s">
         <v>1605</v>
@@ -19676,7 +19676,7 @@
         <v>1537</v>
       </c>
       <c r="E327">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F327" t="s">
         <v>1605</v>
@@ -19711,7 +19711,7 @@
         <v>1538</v>
       </c>
       <c r="E328">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F328" t="s">
         <v>1605</v>
@@ -19746,7 +19746,7 @@
         <v>1538</v>
       </c>
       <c r="E329">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F329" t="s">
         <v>1605</v>
@@ -19781,7 +19781,7 @@
         <v>1538</v>
       </c>
       <c r="E330">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F330" t="s">
         <v>1605</v>
@@ -19816,7 +19816,7 @@
         <v>1538</v>
       </c>
       <c r="E331">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F331" t="s">
         <v>1605</v>
@@ -19854,7 +19854,7 @@
         <v>1538</v>
       </c>
       <c r="E332">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F332" t="s">
         <v>1605</v>
@@ -19889,7 +19889,7 @@
         <v>1538</v>
       </c>
       <c r="E333">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F333" t="s">
         <v>1605</v>
@@ -19924,7 +19924,7 @@
         <v>1539</v>
       </c>
       <c r="E334">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F334" t="s">
         <v>1605</v>
@@ -19959,7 +19959,7 @@
         <v>1539</v>
       </c>
       <c r="E335">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F335" t="s">
         <v>1605</v>
@@ -19994,7 +19994,7 @@
         <v>1540</v>
       </c>
       <c r="E336">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F336" t="s">
         <v>1605</v>
@@ -20029,7 +20029,7 @@
         <v>1540</v>
       </c>
       <c r="E337">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F337" t="s">
         <v>1605</v>
@@ -20064,7 +20064,7 @@
         <v>1541</v>
       </c>
       <c r="E338">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F338" t="s">
         <v>1605</v>
@@ -20099,7 +20099,7 @@
         <v>1541</v>
       </c>
       <c r="E339">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F339" t="s">
         <v>1605</v>
@@ -20134,7 +20134,7 @@
         <v>1541</v>
       </c>
       <c r="E340">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F340" t="s">
         <v>1605</v>
@@ -20169,7 +20169,7 @@
         <v>1541</v>
       </c>
       <c r="E341">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F341" t="s">
         <v>1605</v>
@@ -20204,7 +20204,7 @@
         <v>1541</v>
       </c>
       <c r="E342">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F342" t="s">
         <v>1605</v>
@@ -20239,7 +20239,7 @@
         <v>1542</v>
       </c>
       <c r="E343">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F343" t="s">
         <v>1605</v>
@@ -20274,7 +20274,7 @@
         <v>1542</v>
       </c>
       <c r="E344">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F344" t="s">
         <v>1605</v>
@@ -20309,7 +20309,7 @@
         <v>1542</v>
       </c>
       <c r="E345">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F345" t="s">
         <v>1605</v>
@@ -20344,7 +20344,7 @@
         <v>1542</v>
       </c>
       <c r="E346">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F346" t="s">
         <v>1605</v>
@@ -20379,7 +20379,7 @@
         <v>1543</v>
       </c>
       <c r="E347">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F347" t="s">
         <v>1605</v>
@@ -20414,7 +20414,7 @@
         <v>1543</v>
       </c>
       <c r="E348">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F348" t="s">
         <v>1605</v>
@@ -20449,7 +20449,7 @@
         <v>1544</v>
       </c>
       <c r="E349">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F349" t="s">
         <v>1605</v>
@@ -20484,7 +20484,7 @@
         <v>1544</v>
       </c>
       <c r="E350">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F350" t="s">
         <v>1605</v>
@@ -20519,7 +20519,7 @@
         <v>1544</v>
       </c>
       <c r="E351">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F351" t="s">
         <v>1605</v>
@@ -20554,7 +20554,7 @@
         <v>1544</v>
       </c>
       <c r="E352">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F352" t="s">
         <v>1605</v>
@@ -20589,7 +20589,7 @@
         <v>1544</v>
       </c>
       <c r="E353">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F353" t="s">
         <v>1605</v>
@@ -20624,7 +20624,7 @@
         <v>1545</v>
       </c>
       <c r="E354">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F354" t="s">
         <v>1605</v>
@@ -20659,7 +20659,7 @@
         <v>1545</v>
       </c>
       <c r="E355">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F355" t="s">
         <v>1605</v>
@@ -20694,7 +20694,7 @@
         <v>1545</v>
       </c>
       <c r="E356">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F356" t="s">
         <v>1605</v>
@@ -20729,7 +20729,7 @@
         <v>1545</v>
       </c>
       <c r="E357">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F357" t="s">
         <v>1605</v>
@@ -20764,7 +20764,7 @@
         <v>1546</v>
       </c>
       <c r="E358">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F358" t="s">
         <v>1605</v>
@@ -20799,7 +20799,7 @@
         <v>1546</v>
       </c>
       <c r="E359">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F359" t="s">
         <v>1605</v>
@@ -20834,7 +20834,7 @@
         <v>1547</v>
       </c>
       <c r="E360">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F360" t="s">
         <v>1605</v>
@@ -20869,7 +20869,7 @@
         <v>1547</v>
       </c>
       <c r="E361">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F361" t="s">
         <v>1605</v>
@@ -20904,7 +20904,7 @@
         <v>1547</v>
       </c>
       <c r="E362">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F362" t="s">
         <v>1605</v>
@@ -20939,7 +20939,7 @@
         <v>1547</v>
       </c>
       <c r="E363">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F363" t="s">
         <v>1605</v>
@@ -20974,7 +20974,7 @@
         <v>1547</v>
       </c>
       <c r="E364">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F364" t="s">
         <v>1605</v>
@@ -21009,7 +21009,7 @@
         <v>1547</v>
       </c>
       <c r="E365">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F365" t="s">
         <v>1605</v>
@@ -21044,7 +21044,7 @@
         <v>1547</v>
       </c>
       <c r="E366">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F366" t="s">
         <v>1605</v>
@@ -21079,7 +21079,7 @@
         <v>1547</v>
       </c>
       <c r="E367">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F367" t="s">
         <v>1605</v>
@@ -21114,7 +21114,7 @@
         <v>1548</v>
       </c>
       <c r="E368">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F368" t="s">
         <v>1605</v>
@@ -21149,7 +21149,7 @@
         <v>1548</v>
       </c>
       <c r="E369">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F369" t="s">
         <v>1605</v>
@@ -21184,7 +21184,7 @@
         <v>1548</v>
       </c>
       <c r="E370">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F370" t="s">
         <v>1605</v>
@@ -21219,7 +21219,7 @@
         <v>1549</v>
       </c>
       <c r="E371">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F371" t="s">
         <v>1605</v>
@@ -21254,7 +21254,7 @@
         <v>1549</v>
       </c>
       <c r="E372">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F372" t="s">
         <v>1605</v>
@@ -21289,7 +21289,7 @@
         <v>1550</v>
       </c>
       <c r="E373">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F373" t="s">
         <v>1605</v>
@@ -21324,7 +21324,7 @@
         <v>1551</v>
       </c>
       <c r="E374">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F374" t="s">
         <v>1607</v>
@@ -21359,7 +21359,7 @@
         <v>1551</v>
       </c>
       <c r="E375">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F375" t="s">
         <v>1605</v>
@@ -21394,7 +21394,7 @@
         <v>1551</v>
       </c>
       <c r="E376">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F376" t="s">
         <v>1605</v>
@@ -21429,7 +21429,7 @@
         <v>1551</v>
       </c>
       <c r="E377">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F377" t="s">
         <v>1605</v>
@@ -21464,7 +21464,7 @@
         <v>1551</v>
       </c>
       <c r="E378">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F378" t="s">
         <v>1605</v>
@@ -21499,7 +21499,7 @@
         <v>1551</v>
       </c>
       <c r="E379">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F379" t="s">
         <v>1605</v>
@@ -21534,7 +21534,7 @@
         <v>1552</v>
       </c>
       <c r="E380">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F380" t="s">
         <v>1605</v>
@@ -21569,7 +21569,7 @@
         <v>1552</v>
       </c>
       <c r="E381">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F381" t="s">
         <v>1605</v>
@@ -21604,7 +21604,7 @@
         <v>1553</v>
       </c>
       <c r="E382">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F382" t="s">
         <v>1605</v>
@@ -21639,7 +21639,7 @@
         <v>1553</v>
       </c>
       <c r="E383">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F383" t="s">
         <v>1605</v>
@@ -21674,7 +21674,7 @@
         <v>1553</v>
       </c>
       <c r="E384">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F384" t="s">
         <v>1605</v>
@@ -21709,7 +21709,7 @@
         <v>1554</v>
       </c>
       <c r="E385">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F385" t="s">
         <v>1605</v>
@@ -21744,7 +21744,7 @@
         <v>1555</v>
       </c>
       <c r="E386">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F386" t="s">
         <v>1605</v>
@@ -21779,7 +21779,7 @@
         <v>1556</v>
       </c>
       <c r="E387">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F387" t="s">
         <v>1605</v>
@@ -21814,7 +21814,7 @@
         <v>1556</v>
       </c>
       <c r="E388">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F388" t="s">
         <v>1605</v>
@@ -21849,7 +21849,7 @@
         <v>1557</v>
       </c>
       <c r="E389">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F389" t="s">
         <v>1605</v>
@@ -21884,7 +21884,7 @@
         <v>1557</v>
       </c>
       <c r="E390">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F390" t="s">
         <v>1605</v>
@@ -21919,7 +21919,7 @@
         <v>1557</v>
       </c>
       <c r="E391">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F391" t="s">
         <v>1605</v>
@@ -21954,7 +21954,7 @@
         <v>1558</v>
       </c>
       <c r="E392">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F392" t="s">
         <v>1605</v>
@@ -21989,7 +21989,7 @@
         <v>1558</v>
       </c>
       <c r="E393">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F393" t="s">
         <v>1605</v>
@@ -22024,7 +22024,7 @@
         <v>1558</v>
       </c>
       <c r="E394">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F394" t="s">
         <v>1605</v>
@@ -22059,7 +22059,7 @@
         <v>1558</v>
       </c>
       <c r="E395">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F395" t="s">
         <v>1605</v>
@@ -22094,7 +22094,7 @@
         <v>1558</v>
       </c>
       <c r="E396">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F396" t="s">
         <v>1605</v>
@@ -22129,7 +22129,7 @@
         <v>1558</v>
       </c>
       <c r="E397">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F397" t="s">
         <v>1605</v>
@@ -22164,7 +22164,7 @@
         <v>1558</v>
       </c>
       <c r="E398">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F398" t="s">
         <v>1605</v>
@@ -22199,7 +22199,7 @@
         <v>1558</v>
       </c>
       <c r="E399">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F399" t="s">
         <v>1605</v>
@@ -22234,7 +22234,7 @@
         <v>1558</v>
       </c>
       <c r="E400">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F400" t="s">
         <v>1605</v>
@@ -22269,7 +22269,7 @@
         <v>1558</v>
       </c>
       <c r="E401">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F401" t="s">
         <v>1605</v>
@@ -22304,7 +22304,7 @@
         <v>1559</v>
       </c>
       <c r="E402">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F402" t="s">
         <v>1605</v>
@@ -22339,7 +22339,7 @@
         <v>1559</v>
       </c>
       <c r="E403">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F403" t="s">
         <v>1605</v>
@@ -22374,7 +22374,7 @@
         <v>1559</v>
       </c>
       <c r="E404">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F404" t="s">
         <v>1605</v>
@@ -22409,7 +22409,7 @@
         <v>1559</v>
       </c>
       <c r="E405">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F405" t="s">
         <v>1605</v>
@@ -22444,7 +22444,7 @@
         <v>1559</v>
       </c>
       <c r="E406">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F406" t="s">
         <v>1605</v>
@@ -22479,7 +22479,7 @@
         <v>1560</v>
       </c>
       <c r="E407">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F407" t="s">
         <v>1608</v>
@@ -22514,7 +22514,7 @@
         <v>1560</v>
       </c>
       <c r="E408">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F408" t="s">
         <v>1605</v>
@@ -22549,7 +22549,7 @@
         <v>1561</v>
       </c>
       <c r="E409">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F409" t="s">
         <v>1605</v>
@@ -22584,7 +22584,7 @@
         <v>1561</v>
       </c>
       <c r="E410">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F410" t="s">
         <v>1605</v>
@@ -22619,7 +22619,7 @@
         <v>1561</v>
       </c>
       <c r="E411">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F411" t="s">
         <v>1605</v>
@@ -22654,7 +22654,7 @@
         <v>1561</v>
       </c>
       <c r="E412">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F412" t="s">
         <v>1605</v>
@@ -22689,7 +22689,7 @@
         <v>1561</v>
       </c>
       <c r="E413">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F413" t="s">
         <v>1605</v>
@@ -22724,7 +22724,7 @@
         <v>1561</v>
       </c>
       <c r="E414">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F414" t="s">
         <v>1604</v>
@@ -22762,7 +22762,7 @@
         <v>1561</v>
       </c>
       <c r="E415">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F415" t="s">
         <v>1605</v>
@@ -22797,7 +22797,7 @@
         <v>1561</v>
       </c>
       <c r="E416">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F416" t="s">
         <v>1605</v>
@@ -22832,7 +22832,7 @@
         <v>1562</v>
       </c>
       <c r="E417">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F417" t="s">
         <v>1605</v>
@@ -22867,7 +22867,7 @@
         <v>1562</v>
       </c>
       <c r="E418">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F418" t="s">
         <v>1605</v>
@@ -22902,7 +22902,7 @@
         <v>1562</v>
       </c>
       <c r="E419">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F419" t="s">
         <v>1605</v>
@@ -22937,7 +22937,7 @@
         <v>1562</v>
       </c>
       <c r="E420">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F420" t="s">
         <v>1605</v>
@@ -22975,7 +22975,7 @@
         <v>1562</v>
       </c>
       <c r="E421">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F421" t="s">
         <v>1605</v>
@@ -23010,7 +23010,7 @@
         <v>1562</v>
       </c>
       <c r="E422">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F422" t="s">
         <v>1605</v>
@@ -23045,7 +23045,7 @@
         <v>1562</v>
       </c>
       <c r="E423">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F423" t="s">
         <v>1605</v>
@@ -23080,7 +23080,7 @@
         <v>1562</v>
       </c>
       <c r="E424">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F424" t="s">
         <v>1605</v>
@@ -23115,7 +23115,7 @@
         <v>1562</v>
       </c>
       <c r="E425">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F425" t="s">
         <v>1605</v>
@@ -23150,7 +23150,7 @@
         <v>1563</v>
       </c>
       <c r="E426">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F426" t="s">
         <v>1606</v>
@@ -23185,7 +23185,7 @@
         <v>1564</v>
       </c>
       <c r="E427">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F427" t="s">
         <v>1607</v>
@@ -23220,7 +23220,7 @@
         <v>1564</v>
       </c>
       <c r="E428">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F428" t="s">
         <v>1604</v>
@@ -23255,7 +23255,7 @@
         <v>1565</v>
       </c>
       <c r="E429">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F429" t="s">
         <v>1605</v>
@@ -23290,7 +23290,7 @@
         <v>1566</v>
       </c>
       <c r="E430">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F430" t="s">
         <v>1605</v>
@@ -23325,7 +23325,7 @@
         <v>1566</v>
       </c>
       <c r="E431">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F431" t="s">
         <v>1605</v>
@@ -23360,7 +23360,7 @@
         <v>1567</v>
       </c>
       <c r="E432">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F432" t="s">
         <v>1605</v>
@@ -23395,7 +23395,7 @@
         <v>1568</v>
       </c>
       <c r="E433">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F433" t="s">
         <v>1608</v>
@@ -23430,7 +23430,7 @@
         <v>1568</v>
       </c>
       <c r="E434">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F434" t="s">
         <v>1605</v>
@@ -23465,7 +23465,7 @@
         <v>1568</v>
       </c>
       <c r="E435">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F435" t="s">
         <v>1605</v>
@@ -23500,7 +23500,7 @@
         <v>1568</v>
       </c>
       <c r="E436">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F436" t="s">
         <v>1605</v>
@@ -23535,7 +23535,7 @@
         <v>1568</v>
       </c>
       <c r="E437">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F437" t="s">
         <v>1605</v>
@@ -23570,7 +23570,7 @@
         <v>1568</v>
       </c>
       <c r="E438">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F438" t="s">
         <v>1605</v>
@@ -23605,7 +23605,7 @@
         <v>1569</v>
       </c>
       <c r="E439">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F439" t="s">
         <v>1605</v>
@@ -23640,7 +23640,7 @@
         <v>1569</v>
       </c>
       <c r="E440">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F440" t="s">
         <v>1605</v>
@@ -23675,7 +23675,7 @@
         <v>1569</v>
       </c>
       <c r="E441">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F441" t="s">
         <v>1605</v>
@@ -23710,7 +23710,7 @@
         <v>1569</v>
       </c>
       <c r="E442">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F442" t="s">
         <v>1605</v>
@@ -23745,7 +23745,7 @@
         <v>1570</v>
       </c>
       <c r="E443">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F443" t="s">
         <v>1605</v>
@@ -23780,7 +23780,7 @@
         <v>1570</v>
       </c>
       <c r="E444">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F444" t="s">
         <v>1605</v>
@@ -23815,7 +23815,7 @@
         <v>1570</v>
       </c>
       <c r="E445">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F445" t="s">
         <v>1605</v>
@@ -23853,7 +23853,7 @@
         <v>1570</v>
       </c>
       <c r="E446">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F446" t="s">
         <v>1605</v>
@@ -23888,7 +23888,7 @@
         <v>1571</v>
       </c>
       <c r="E447">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F447" t="s">
         <v>1605</v>
@@ -23923,7 +23923,7 @@
         <v>1571</v>
       </c>
       <c r="E448">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F448" t="s">
         <v>1605</v>
@@ -23958,7 +23958,7 @@
         <v>1571</v>
       </c>
       <c r="E449">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F449" t="s">
         <v>1605</v>
@@ -23993,7 +23993,7 @@
         <v>1571</v>
       </c>
       <c r="E450">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F450" t="s">
         <v>1605</v>
@@ -24028,7 +24028,7 @@
         <v>1571</v>
       </c>
       <c r="E451">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F451" t="s">
         <v>1605</v>
@@ -24063,7 +24063,7 @@
         <v>1572</v>
       </c>
       <c r="E452">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F452" t="s">
         <v>1605</v>
@@ -24098,7 +24098,7 @@
         <v>1572</v>
       </c>
       <c r="E453">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F453" t="s">
         <v>1605</v>
@@ -24133,7 +24133,7 @@
         <v>1572</v>
       </c>
       <c r="E454">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F454" t="s">
         <v>1605</v>
@@ -24168,7 +24168,7 @@
         <v>1572</v>
       </c>
       <c r="E455">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F455" t="s">
         <v>1605</v>
@@ -24203,7 +24203,7 @@
         <v>1573</v>
       </c>
       <c r="E456">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F456" t="s">
         <v>1605</v>
@@ -24238,7 +24238,7 @@
         <v>1573</v>
       </c>
       <c r="E457">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F457" t="s">
         <v>1605</v>
@@ -24273,7 +24273,7 @@
         <v>1573</v>
       </c>
       <c r="E458">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F458" t="s">
         <v>1605</v>
@@ -24308,7 +24308,7 @@
         <v>1573</v>
       </c>
       <c r="E459">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F459" t="s">
         <v>1605</v>
@@ -24343,7 +24343,7 @@
         <v>1573</v>
       </c>
       <c r="E460">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F460" t="s">
         <v>1605</v>
@@ -24378,7 +24378,7 @@
         <v>1573</v>
       </c>
       <c r="E461">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F461" t="s">
         <v>1605</v>
@@ -24413,7 +24413,7 @@
         <v>1573</v>
       </c>
       <c r="E462">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F462" t="s">
         <v>1605</v>
@@ -24448,7 +24448,7 @@
         <v>1573</v>
       </c>
       <c r="E463">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F463" t="s">
         <v>1605</v>
@@ -24483,7 +24483,7 @@
         <v>1573</v>
       </c>
       <c r="E464">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F464" t="s">
         <v>1605</v>
@@ -24518,7 +24518,7 @@
         <v>1573</v>
       </c>
       <c r="E465">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F465" t="s">
         <v>1605</v>
@@ -24553,7 +24553,7 @@
         <v>1573</v>
       </c>
       <c r="E466">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F466" t="s">
         <v>1605</v>
@@ -24588,7 +24588,7 @@
         <v>1574</v>
       </c>
       <c r="E467">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F467" t="s">
         <v>1605</v>
@@ -24623,7 +24623,7 @@
         <v>1574</v>
       </c>
       <c r="E468">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F468" t="s">
         <v>1605</v>
@@ -24658,7 +24658,7 @@
         <v>1574</v>
       </c>
       <c r="E469">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F469" t="s">
         <v>1606</v>
@@ -24693,7 +24693,7 @@
         <v>1575</v>
       </c>
       <c r="E470">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F470" t="s">
         <v>1605</v>
@@ -24728,7 +24728,7 @@
         <v>1575</v>
       </c>
       <c r="E471">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F471" t="s">
         <v>1605</v>
@@ -24763,7 +24763,7 @@
         <v>1575</v>
       </c>
       <c r="E472">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F472" t="s">
         <v>1605</v>
@@ -24798,7 +24798,7 @@
         <v>1575</v>
       </c>
       <c r="E473">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F473" t="s">
         <v>1605</v>
@@ -24833,7 +24833,7 @@
         <v>1575</v>
       </c>
       <c r="E474">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F474" t="s">
         <v>1605</v>
@@ -24868,7 +24868,7 @@
         <v>1575</v>
       </c>
       <c r="E475">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F475" t="s">
         <v>1605</v>
@@ -24903,7 +24903,7 @@
         <v>1575</v>
       </c>
       <c r="E476">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F476" t="s">
         <v>1608</v>
@@ -24938,7 +24938,7 @@
         <v>1576</v>
       </c>
       <c r="E477">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F477" t="s">
         <v>1605</v>
@@ -24973,7 +24973,7 @@
         <v>1576</v>
       </c>
       <c r="E478">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F478" t="s">
         <v>1605</v>
@@ -25008,7 +25008,7 @@
         <v>1576</v>
       </c>
       <c r="E479">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F479" t="s">
         <v>1605</v>
@@ -25043,7 +25043,7 @@
         <v>1576</v>
       </c>
       <c r="E480">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F480" t="s">
         <v>1605</v>
@@ -25078,7 +25078,7 @@
         <v>1577</v>
       </c>
       <c r="E481">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F481" t="s">
         <v>1605</v>
@@ -25113,7 +25113,7 @@
         <v>1577</v>
       </c>
       <c r="E482">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F482" t="s">
         <v>1608</v>
@@ -25148,7 +25148,7 @@
         <v>1577</v>
       </c>
       <c r="E483">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F483" t="s">
         <v>1605</v>
@@ -25183,7 +25183,7 @@
         <v>1577</v>
       </c>
       <c r="E484">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F484" t="s">
         <v>1605</v>
@@ -25218,7 +25218,7 @@
         <v>1577</v>
       </c>
       <c r="E485">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F485" t="s">
         <v>1605</v>
@@ -25253,7 +25253,7 @@
         <v>1577</v>
       </c>
       <c r="E486">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F486" t="s">
         <v>1607</v>
@@ -25291,7 +25291,7 @@
         <v>1577</v>
       </c>
       <c r="E487">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F487" t="s">
         <v>1605</v>
@@ -25326,7 +25326,7 @@
         <v>1577</v>
       </c>
       <c r="E488">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F488" t="s">
         <v>1604</v>
@@ -25361,7 +25361,7 @@
         <v>1577</v>
       </c>
       <c r="E489">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F489" t="s">
         <v>1605</v>
@@ -25396,7 +25396,7 @@
         <v>1577</v>
       </c>
       <c r="E490">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F490" t="s">
         <v>1605</v>
@@ -25431,7 +25431,7 @@
         <v>1578</v>
       </c>
       <c r="E491">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F491" t="s">
         <v>1605</v>
@@ -25466,7 +25466,7 @@
         <v>1578</v>
       </c>
       <c r="E492">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F492" t="s">
         <v>1605</v>
@@ -25501,7 +25501,7 @@
         <v>1578</v>
       </c>
       <c r="E493">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F493" t="s">
         <v>1605</v>
@@ -25536,7 +25536,7 @@
         <v>1578</v>
       </c>
       <c r="E494">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F494" t="s">
         <v>1605</v>
@@ -25571,7 +25571,7 @@
         <v>1578</v>
       </c>
       <c r="E495">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F495" t="s">
         <v>1605</v>
@@ -25606,7 +25606,7 @@
         <v>1578</v>
       </c>
       <c r="E496">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F496" t="s">
         <v>1607</v>
@@ -25641,7 +25641,7 @@
         <v>1578</v>
       </c>
       <c r="E497">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F497" t="s">
         <v>1605</v>
@@ -25676,7 +25676,7 @@
         <v>1578</v>
       </c>
       <c r="E498">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F498" t="s">
         <v>1605</v>
@@ -25711,7 +25711,7 @@
         <v>1579</v>
       </c>
       <c r="E499">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F499" t="s">
         <v>1605</v>
@@ -25746,7 +25746,7 @@
         <v>1579</v>
       </c>
       <c r="E500">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F500" t="s">
         <v>1605</v>
@@ -25781,7 +25781,7 @@
         <v>1579</v>
       </c>
       <c r="E501">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F501" t="s">
         <v>1605</v>
@@ -25816,7 +25816,7 @@
         <v>1579</v>
       </c>
       <c r="E502">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F502" t="s">
         <v>1605</v>
@@ -25851,7 +25851,7 @@
         <v>1579</v>
       </c>
       <c r="E503">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F503" t="s">
         <v>1605</v>
@@ -25886,7 +25886,7 @@
         <v>1580</v>
       </c>
       <c r="E504">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F504" t="s">
         <v>1605</v>
@@ -25921,7 +25921,7 @@
         <v>1580</v>
       </c>
       <c r="E505">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F505" t="s">
         <v>1605</v>
@@ -25956,7 +25956,7 @@
         <v>1580</v>
       </c>
       <c r="E506">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F506" t="s">
         <v>1605</v>
@@ -25991,7 +25991,7 @@
         <v>1580</v>
       </c>
       <c r="E507">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F507" t="s">
         <v>1605</v>
@@ -26026,7 +26026,7 @@
         <v>1580</v>
       </c>
       <c r="E508">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F508" t="s">
         <v>1605</v>
@@ -26061,7 +26061,7 @@
         <v>1580</v>
       </c>
       <c r="E509">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F509" t="s">
         <v>1605</v>
@@ -26099,7 +26099,7 @@
         <v>1581</v>
       </c>
       <c r="E510">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F510" t="s">
         <v>1605</v>
@@ -26134,7 +26134,7 @@
         <v>1581</v>
       </c>
       <c r="E511">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F511" t="s">
         <v>1605</v>
@@ -26169,7 +26169,7 @@
         <v>1581</v>
       </c>
       <c r="E512">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F512" t="s">
         <v>1605</v>
@@ -26204,7 +26204,7 @@
         <v>1581</v>
       </c>
       <c r="E513">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F513" t="s">
         <v>1605</v>
@@ -26239,7 +26239,7 @@
         <v>1581</v>
       </c>
       <c r="E514">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F514" t="s">
         <v>1605</v>
@@ -26274,7 +26274,7 @@
         <v>1581</v>
       </c>
       <c r="E515">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F515" t="s">
         <v>1605</v>
@@ -26309,7 +26309,7 @@
         <v>1581</v>
       </c>
       <c r="E516">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F516" t="s">
         <v>1605</v>
@@ -26344,7 +26344,7 @@
         <v>1582</v>
       </c>
       <c r="E517">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F517" t="s">
         <v>1605</v>
@@ -26379,7 +26379,7 @@
         <v>1582</v>
       </c>
       <c r="E518">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F518" t="s">
         <v>1605</v>
@@ -26414,7 +26414,7 @@
         <v>1582</v>
       </c>
       <c r="E519">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F519" t="s">
         <v>1605</v>
@@ -26449,7 +26449,7 @@
         <v>1583</v>
       </c>
       <c r="E520">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F520" t="s">
         <v>1605</v>
@@ -26484,7 +26484,7 @@
         <v>1583</v>
       </c>
       <c r="E521">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F521" t="s">
         <v>1605</v>
@@ -26519,7 +26519,7 @@
         <v>1584</v>
       </c>
       <c r="E522">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F522" t="s">
         <v>1605</v>
@@ -26554,7 +26554,7 @@
         <v>1584</v>
       </c>
       <c r="E523">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F523" t="s">
         <v>1605</v>
@@ -26589,7 +26589,7 @@
         <v>1584</v>
       </c>
       <c r="E524">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F524" t="s">
         <v>1607</v>
@@ -26627,7 +26627,7 @@
         <v>1584</v>
       </c>
       <c r="E525">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F525" t="s">
         <v>1605</v>
@@ -26662,7 +26662,7 @@
         <v>1584</v>
       </c>
       <c r="E526">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F526" t="s">
         <v>1605</v>
@@ -26697,7 +26697,7 @@
         <v>1585</v>
       </c>
       <c r="E527">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F527" t="s">
         <v>1605</v>
@@ -26732,7 +26732,7 @@
         <v>1585</v>
       </c>
       <c r="E528">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F528" t="s">
         <v>1605</v>
@@ -26767,7 +26767,7 @@
         <v>1585</v>
       </c>
       <c r="E529">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F529" t="s">
         <v>1605</v>
@@ -26802,7 +26802,7 @@
         <v>1585</v>
       </c>
       <c r="E530">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F530" t="s">
         <v>1605</v>
@@ -26837,7 +26837,7 @@
         <v>1585</v>
       </c>
       <c r="E531">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F531" t="s">
         <v>1605</v>
@@ -26872,7 +26872,7 @@
         <v>1586</v>
       </c>
       <c r="E532">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F532" t="s">
         <v>1605</v>
@@ -26907,7 +26907,7 @@
         <v>1586</v>
       </c>
       <c r="E533">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F533" t="s">
         <v>1605</v>
@@ -26942,7 +26942,7 @@
         <v>1586</v>
       </c>
       <c r="E534">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F534" t="s">
         <v>1605</v>
@@ -26977,7 +26977,7 @@
         <v>1586</v>
       </c>
       <c r="E535">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F535" t="s">
         <v>1605</v>
@@ -27012,7 +27012,7 @@
         <v>1586</v>
       </c>
       <c r="E536">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F536" t="s">
         <v>1605</v>
@@ -27047,7 +27047,7 @@
         <v>1586</v>
       </c>
       <c r="E537">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F537" t="s">
         <v>1605</v>
@@ -27082,7 +27082,7 @@
         <v>1586</v>
       </c>
       <c r="E538">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F538" t="s">
         <v>1605</v>
@@ -27117,7 +27117,7 @@
         <v>1586</v>
       </c>
       <c r="E539">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F539" t="s">
         <v>1605</v>
@@ -27152,7 +27152,7 @@
         <v>1587</v>
       </c>
       <c r="E540">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F540" t="s">
         <v>1605</v>
@@ -27187,7 +27187,7 @@
         <v>1587</v>
       </c>
       <c r="E541">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F541" t="s">
         <v>1605</v>
@@ -27222,7 +27222,7 @@
         <v>1588</v>
       </c>
       <c r="E542">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F542" t="s">
         <v>1605</v>
@@ -27257,7 +27257,7 @@
         <v>1588</v>
       </c>
       <c r="E543">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F543" t="s">
         <v>1605</v>
@@ -27292,7 +27292,7 @@
         <v>1588</v>
       </c>
       <c r="E544">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F544" t="s">
         <v>1605</v>
@@ -27327,7 +27327,7 @@
         <v>1588</v>
       </c>
       <c r="E545">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F545" t="s">
         <v>1604</v>
@@ -27365,7 +27365,7 @@
         <v>1588</v>
       </c>
       <c r="E546">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F546" t="s">
         <v>1605</v>
@@ -27400,7 +27400,7 @@
         <v>1588</v>
       </c>
       <c r="E547">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F547" t="s">
         <v>1604</v>
@@ -27435,7 +27435,7 @@
         <v>1589</v>
       </c>
       <c r="E548">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F548" t="s">
         <v>1605</v>
@@ -27470,7 +27470,7 @@
         <v>1590</v>
       </c>
       <c r="E549">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F549" t="s">
         <v>1605</v>
@@ -27505,7 +27505,7 @@
         <v>1590</v>
       </c>
       <c r="E550">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F550" t="s">
         <v>1605</v>
@@ -27540,7 +27540,7 @@
         <v>1590</v>
       </c>
       <c r="E551">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F551" t="s">
         <v>1605</v>
@@ -27575,7 +27575,7 @@
         <v>1590</v>
       </c>
       <c r="E552">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F552" t="s">
         <v>1605</v>
@@ -27610,7 +27610,7 @@
         <v>1591</v>
       </c>
       <c r="E553">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F553" t="s">
         <v>1605</v>
@@ -27645,7 +27645,7 @@
         <v>1591</v>
       </c>
       <c r="E554">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F554" t="s">
         <v>1604</v>
@@ -27680,7 +27680,7 @@
         <v>1591</v>
       </c>
       <c r="E555">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F555" t="s">
         <v>1605</v>
@@ -27715,7 +27715,7 @@
         <v>1591</v>
       </c>
       <c r="E556">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F556" t="s">
         <v>1605</v>
@@ -27750,7 +27750,7 @@
         <v>1591</v>
       </c>
       <c r="E557">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F557" t="s">
         <v>1605</v>
@@ -27785,7 +27785,7 @@
         <v>1591</v>
       </c>
       <c r="E558">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F558" t="s">
         <v>1605</v>
@@ -27820,7 +27820,7 @@
         <v>1592</v>
       </c>
       <c r="E559">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F559" t="s">
         <v>1605</v>
@@ -27855,7 +27855,7 @@
         <v>1592</v>
       </c>
       <c r="E560">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F560" t="s">
         <v>1604</v>
@@ -27890,7 +27890,7 @@
         <v>1592</v>
       </c>
       <c r="E561">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F561" t="s">
         <v>1607</v>
@@ -27925,7 +27925,7 @@
         <v>1592</v>
       </c>
       <c r="E562">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F562" t="s">
         <v>1605</v>
@@ -27960,7 +27960,7 @@
         <v>1592</v>
       </c>
       <c r="E563">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F563" t="s">
         <v>1605</v>
@@ -27995,7 +27995,7 @@
         <v>1593</v>
       </c>
       <c r="E564">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F564" t="s">
         <v>1605</v>
@@ -28030,7 +28030,7 @@
         <v>1593</v>
       </c>
       <c r="E565">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F565" t="s">
         <v>1605</v>
@@ -28065,7 +28065,7 @@
         <v>1593</v>
       </c>
       <c r="E566">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F566" t="s">
         <v>1605</v>
@@ -28100,7 +28100,7 @@
         <v>1593</v>
       </c>
       <c r="E567">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F567" t="s">
         <v>1605</v>
@@ -28135,7 +28135,7 @@
         <v>1593</v>
       </c>
       <c r="E568">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F568" t="s">
         <v>1605</v>
@@ -28170,7 +28170,7 @@
         <v>1593</v>
       </c>
       <c r="E569">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F569" t="s">
         <v>1605</v>
@@ -28205,7 +28205,7 @@
         <v>1593</v>
       </c>
       <c r="E570">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F570" t="s">
         <v>1605</v>
@@ -28240,7 +28240,7 @@
         <v>1594</v>
       </c>
       <c r="E571">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F571" t="s">
         <v>1605</v>
@@ -28275,7 +28275,7 @@
         <v>1594</v>
       </c>
       <c r="E572">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F572" t="s">
         <v>1605</v>
@@ -28310,7 +28310,7 @@
         <v>1594</v>
       </c>
       <c r="E573">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F573" t="s">
         <v>1605</v>
@@ -28345,7 +28345,7 @@
         <v>1594</v>
       </c>
       <c r="E574">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F574" t="s">
         <v>1605</v>
@@ -28380,7 +28380,7 @@
         <v>1594</v>
       </c>
       <c r="E575">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F575" t="s">
         <v>1605</v>
@@ -28415,7 +28415,7 @@
         <v>1594</v>
       </c>
       <c r="E576">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F576" t="s">
         <v>1605</v>
@@ -28450,7 +28450,7 @@
         <v>1594</v>
       </c>
       <c r="E577">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F577" t="s">
         <v>1605</v>
@@ -28485,7 +28485,7 @@
         <v>1594</v>
       </c>
       <c r="E578">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F578" t="s">
         <v>1605</v>
@@ -28520,7 +28520,7 @@
         <v>1594</v>
       </c>
       <c r="E579">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F579" t="s">
         <v>1605</v>
@@ -28555,7 +28555,7 @@
         <v>1594</v>
       </c>
       <c r="E580">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F580" t="s">
         <v>1605</v>
@@ -28590,7 +28590,7 @@
         <v>1594</v>
       </c>
       <c r="E581">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F581" t="s">
         <v>1605</v>
@@ -28625,7 +28625,7 @@
         <v>1594</v>
       </c>
       <c r="E582">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F582" t="s">
         <v>1605</v>
@@ -28660,7 +28660,7 @@
         <v>1594</v>
       </c>
       <c r="E583">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F583" t="s">
         <v>1605</v>
@@ -28695,7 +28695,7 @@
         <v>1594</v>
       </c>
       <c r="E584">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F584" t="s">
         <v>1605</v>
@@ -28730,7 +28730,7 @@
         <v>1594</v>
       </c>
       <c r="E585">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F585" t="s">
         <v>1605</v>
@@ -28765,7 +28765,7 @@
         <v>1594</v>
       </c>
       <c r="E586">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F586" t="s">
         <v>1605</v>
@@ -28800,7 +28800,7 @@
         <v>1594</v>
       </c>
       <c r="E587">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F587" t="s">
         <v>1605</v>
@@ -28835,7 +28835,7 @@
         <v>1594</v>
       </c>
       <c r="E588">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F588" t="s">
         <v>1605</v>
@@ -28870,7 +28870,7 @@
         <v>1594</v>
       </c>
       <c r="E589">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F589" t="s">
         <v>1605</v>
@@ -28905,7 +28905,7 @@
         <v>1594</v>
       </c>
       <c r="E590">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F590" t="s">
         <v>1605</v>
@@ -28940,7 +28940,7 @@
         <v>1594</v>
       </c>
       <c r="E591">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F591" t="s">
         <v>1605</v>
@@ -28975,7 +28975,7 @@
         <v>1594</v>
       </c>
       <c r="E592">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F592" t="s">
         <v>1605</v>
@@ -29010,7 +29010,7 @@
         <v>1594</v>
       </c>
       <c r="E593">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F593" t="s">
         <v>1605</v>
@@ -29045,7 +29045,7 @@
         <v>1594</v>
       </c>
       <c r="E594">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F594" t="s">
         <v>1605</v>
@@ -29080,7 +29080,7 @@
         <v>1594</v>
       </c>
       <c r="E595">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F595" t="s">
         <v>1605</v>
@@ -29115,7 +29115,7 @@
         <v>1594</v>
       </c>
       <c r="E596">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F596" t="s">
         <v>1605</v>
@@ -29150,7 +29150,7 @@
         <v>1594</v>
       </c>
       <c r="E597">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F597" t="s">
         <v>1605</v>
@@ -29185,7 +29185,7 @@
         <v>1594</v>
       </c>
       <c r="E598">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F598" t="s">
         <v>1607</v>
@@ -29223,7 +29223,7 @@
         <v>1595</v>
       </c>
       <c r="E599">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F599" t="s">
         <v>1605</v>
@@ -29258,7 +29258,7 @@
         <v>1595</v>
       </c>
       <c r="E600">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F600" t="s">
         <v>1605</v>
@@ -29293,7 +29293,7 @@
         <v>1595</v>
       </c>
       <c r="E601">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F601" t="s">
         <v>1607</v>
@@ -29328,7 +29328,7 @@
         <v>1595</v>
       </c>
       <c r="E602">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F602" t="s">
         <v>1605</v>
@@ -29363,7 +29363,7 @@
         <v>1595</v>
       </c>
       <c r="E603">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F603" t="s">
         <v>1605</v>
@@ -29398,7 +29398,7 @@
         <v>1595</v>
       </c>
       <c r="E604">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F604" t="s">
         <v>1605</v>
@@ -29433,7 +29433,7 @@
         <v>1595</v>
       </c>
       <c r="E605">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F605" t="s">
         <v>1605</v>
@@ -29468,7 +29468,7 @@
         <v>1595</v>
       </c>
       <c r="E606">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F606" t="s">
         <v>1605</v>
@@ -29503,7 +29503,7 @@
         <v>1596</v>
       </c>
       <c r="E607">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F607" t="s">
         <v>1605</v>
@@ -29538,7 +29538,7 @@
         <v>1596</v>
       </c>
       <c r="E608">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F608" t="s">
         <v>1605</v>
@@ -29573,7 +29573,7 @@
         <v>1597</v>
       </c>
       <c r="E609">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F609" t="s">
         <v>1605</v>
@@ -29608,7 +29608,7 @@
         <v>1597</v>
       </c>
       <c r="E610">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F610" t="s">
         <v>1607</v>
@@ -29646,7 +29646,7 @@
         <v>1597</v>
       </c>
       <c r="E611">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F611" t="s">
         <v>1607</v>
@@ -29684,7 +29684,7 @@
         <v>1598</v>
       </c>
       <c r="E612">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F612" t="s">
         <v>1607</v>
@@ -29722,7 +29722,7 @@
         <v>1598</v>
       </c>
       <c r="E613">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F613" t="s">
         <v>1605</v>
@@ -29757,7 +29757,7 @@
         <v>1598</v>
       </c>
       <c r="E614">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F614" t="s">
         <v>1605</v>
@@ -29792,7 +29792,7 @@
         <v>1598</v>
       </c>
       <c r="E615">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F615" t="s">
         <v>1605</v>
@@ -29830,7 +29830,7 @@
         <v>1598</v>
       </c>
       <c r="E616">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F616" t="s">
         <v>1605</v>
@@ -29865,7 +29865,7 @@
         <v>1598</v>
       </c>
       <c r="E617">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F617" t="s">
         <v>1605</v>
@@ -29900,7 +29900,7 @@
         <v>1598</v>
       </c>
       <c r="E618">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F618" t="s">
         <v>1607</v>
@@ -29938,7 +29938,7 @@
         <v>1598</v>
       </c>
       <c r="E619">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F619" t="s">
         <v>1607</v>
@@ -29976,7 +29976,7 @@
         <v>1598</v>
       </c>
       <c r="E620">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F620" t="s">
         <v>1605</v>
@@ -30011,7 +30011,7 @@
         <v>1598</v>
       </c>
       <c r="E621">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F621" t="s">
         <v>1605</v>
@@ -30049,7 +30049,7 @@
         <v>1598</v>
       </c>
       <c r="E622">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F622" t="s">
         <v>1607</v>
@@ -30084,7 +30084,7 @@
         <v>1598</v>
       </c>
       <c r="E623">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F623" t="s">
         <v>1605</v>
@@ -30119,7 +30119,7 @@
         <v>1598</v>
       </c>
       <c r="E624">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F624" t="s">
         <v>1605</v>
@@ -30154,7 +30154,7 @@
         <v>1598</v>
       </c>
       <c r="E625">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F625" t="s">
         <v>1605</v>
@@ -30189,7 +30189,7 @@
         <v>1599</v>
       </c>
       <c r="E626">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F626" t="s">
         <v>1605</v>
@@ -30227,7 +30227,7 @@
         <v>1599</v>
       </c>
       <c r="E627">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F627" t="s">
         <v>1604</v>
@@ -30262,7 +30262,7 @@
         <v>1599</v>
       </c>
       <c r="E628">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F628" t="s">
         <v>1605</v>
@@ -30297,7 +30297,7 @@
         <v>1599</v>
       </c>
       <c r="E629">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F629" t="s">
         <v>1605</v>
@@ -30332,7 +30332,7 @@
         <v>1599</v>
       </c>
       <c r="E630">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F630" t="s">
         <v>1607</v>
@@ -30370,7 +30370,7 @@
         <v>1599</v>
       </c>
       <c r="E631">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F631" t="s">
         <v>1605</v>
@@ -30405,7 +30405,7 @@
         <v>1599</v>
       </c>
       <c r="E632">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F632" t="s">
         <v>1605</v>
@@ -30440,7 +30440,7 @@
         <v>1599</v>
       </c>
       <c r="E633">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F633" t="s">
         <v>1605</v>
@@ -30475,7 +30475,7 @@
         <v>1599</v>
       </c>
       <c r="E634">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F634" t="s">
         <v>1605</v>
@@ -30510,7 +30510,7 @@
         <v>1599</v>
       </c>
       <c r="E635">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F635" t="s">
         <v>1605</v>
@@ -30545,7 +30545,7 @@
         <v>1600</v>
       </c>
       <c r="E636">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F636" t="s">
         <v>1605</v>
@@ -30580,7 +30580,7 @@
         <v>1600</v>
       </c>
       <c r="E637">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F637" t="s">
         <v>1605</v>
@@ -30618,7 +30618,7 @@
         <v>1600</v>
       </c>
       <c r="E638">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F638" t="s">
         <v>1605</v>
@@ -30653,7 +30653,7 @@
         <v>1601</v>
       </c>
       <c r="E639">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F639" t="s">
         <v>1605</v>
@@ -30688,7 +30688,7 @@
         <v>1601</v>
       </c>
       <c r="E640">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F640" t="s">
         <v>1605</v>
@@ -30726,7 +30726,7 @@
         <v>1601</v>
       </c>
       <c r="E641">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F641" t="s">
         <v>1605</v>
@@ -30761,7 +30761,7 @@
         <v>1601</v>
       </c>
       <c r="E642">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F642" t="s">
         <v>1605</v>
@@ -30796,7 +30796,7 @@
         <v>1601</v>
       </c>
       <c r="E643">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F643" t="s">
         <v>1605</v>
@@ -30831,7 +30831,7 @@
         <v>1601</v>
       </c>
       <c r="E644">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F644" t="s">
         <v>1605</v>
@@ -30866,7 +30866,7 @@
         <v>1601</v>
       </c>
       <c r="E645">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F645" t="s">
         <v>1605</v>
@@ -30901,7 +30901,7 @@
         <v>1601</v>
       </c>
       <c r="E646">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F646" t="s">
         <v>1605</v>
@@ -30936,7 +30936,7 @@
         <v>1601</v>
       </c>
       <c r="E647">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F647" t="s">
         <v>1605</v>
@@ -30971,7 +30971,7 @@
         <v>1601</v>
       </c>
       <c r="E648">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F648" t="s">
         <v>1605</v>
@@ -31006,7 +31006,7 @@
         <v>1602</v>
       </c>
       <c r="E649">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F649" t="s">
         <v>1605</v>
@@ -31041,7 +31041,7 @@
         <v>1602</v>
       </c>
       <c r="E650">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F650" t="s">
         <v>1605</v>
@@ -31076,7 +31076,7 @@
         <v>1602</v>
       </c>
       <c r="E651">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F651" t="s">
         <v>1605</v>
@@ -31111,7 +31111,7 @@
         <v>1602</v>
       </c>
       <c r="E652">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F652" t="s">
         <v>1605</v>
@@ -31146,7 +31146,7 @@
         <v>1602</v>
       </c>
       <c r="E653">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F653" t="s">
         <v>1605</v>
@@ -31184,7 +31184,7 @@
         <v>1602</v>
       </c>
       <c r="E654">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F654" t="s">
         <v>1605</v>
@@ -31219,7 +31219,7 @@
         <v>1602</v>
       </c>
       <c r="E655">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F655" t="s">
         <v>1605</v>
@@ -31254,7 +31254,7 @@
         <v>1602</v>
       </c>
       <c r="E656">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F656" t="s">
         <v>1605</v>
@@ -31289,7 +31289,7 @@
         <v>1602</v>
       </c>
       <c r="E657">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F657" t="s">
         <v>1605</v>
@@ -31324,7 +31324,7 @@
         <v>1602</v>
       </c>
       <c r="E658">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F658" t="s">
         <v>1605</v>
@@ -31359,7 +31359,7 @@
         <v>1602</v>
       </c>
       <c r="E659">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F659" t="s">
         <v>1604</v>
@@ -31394,7 +31394,7 @@
         <v>1602</v>
       </c>
       <c r="E660">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F660" t="s">
         <v>1605</v>
@@ -31429,7 +31429,7 @@
         <v>1603</v>
       </c>
       <c r="E661">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F661" t="s">
         <v>1605</v>
@@ -31467,7 +31467,7 @@
         <v>1603</v>
       </c>
       <c r="E662">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F662" t="s">
         <v>1605</v>
@@ -31502,7 +31502,7 @@
         <v>1603</v>
       </c>
       <c r="E663">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F663" t="s">
         <v>1605</v>
@@ -31537,7 +31537,7 @@
         <v>1603</v>
       </c>
       <c r="E664">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F664" t="s">
         <v>1605</v>
@@ -31572,7 +31572,7 @@
         <v>1603</v>
       </c>
       <c r="E665">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F665" t="s">
         <v>1605</v>
@@ -31607,7 +31607,7 @@
         <v>1603</v>
       </c>
       <c r="E666">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F666" t="s">
         <v>1605</v>
@@ -31642,7 +31642,7 @@
         <v>1603</v>
       </c>
       <c r="E667">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F667" t="s">
         <v>1605</v>
@@ -31677,7 +31677,7 @@
         <v>1603</v>
       </c>
       <c r="E668">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F668" t="s">
         <v>1605</v>
@@ -31712,7 +31712,7 @@
         <v>1603</v>
       </c>
       <c r="E669">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F669" t="s">
         <v>1605</v>
@@ -31750,7 +31750,7 @@
         <v>1603</v>
       </c>
       <c r="E670">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F670" t="s">
         <v>1605</v>
@@ -31785,7 +31785,7 @@
         <v>1603</v>
       </c>
       <c r="E671">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F671" t="s">
         <v>1605</v>
@@ -31820,7 +31820,7 @@
         <v>1603</v>
       </c>
       <c r="E672">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F672" t="s">
         <v>1605</v>
@@ -31855,7 +31855,7 @@
         <v>1603</v>
       </c>
       <c r="E673">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F673" t="s">
         <v>1605</v>

--- a/BacklogGATEAutoCompleto.xlsx
+++ b/BacklogGATEAutoCompleto.xlsx
@@ -8328,7 +8328,7 @@
         <v>1391</v>
       </c>
       <c r="E2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="F2" t="s">
         <v>1608</v>
@@ -8363,7 +8363,7 @@
         <v>1392</v>
       </c>
       <c r="E3">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="F3" t="s">
         <v>1609</v>
@@ -8398,7 +8398,7 @@
         <v>1393</v>
       </c>
       <c r="E4">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="F4" t="s">
         <v>1609</v>
@@ -8433,7 +8433,7 @@
         <v>1394</v>
       </c>
       <c r="E5">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="F5" t="s">
         <v>1609</v>
@@ -8468,7 +8468,7 @@
         <v>1395</v>
       </c>
       <c r="E6">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="F6" t="s">
         <v>1609</v>
@@ -8503,7 +8503,7 @@
         <v>1396</v>
       </c>
       <c r="E7">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="F7" t="s">
         <v>1609</v>
@@ -8538,7 +8538,7 @@
         <v>1396</v>
       </c>
       <c r="E8">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="F8" t="s">
         <v>1609</v>
@@ -8573,7 +8573,7 @@
         <v>1397</v>
       </c>
       <c r="E9">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="F9" t="s">
         <v>1609</v>
@@ -8608,7 +8608,7 @@
         <v>1398</v>
       </c>
       <c r="E10">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F10" t="s">
         <v>1609</v>
@@ -8643,7 +8643,7 @@
         <v>1399</v>
       </c>
       <c r="E11">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="F11" t="s">
         <v>1609</v>
@@ -8678,7 +8678,7 @@
         <v>1400</v>
       </c>
       <c r="E12">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="F12" t="s">
         <v>1609</v>
@@ -8713,7 +8713,7 @@
         <v>1401</v>
       </c>
       <c r="E13">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="F13" t="s">
         <v>1609</v>
@@ -8748,7 +8748,7 @@
         <v>1402</v>
       </c>
       <c r="E14">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F14" t="s">
         <v>1609</v>
@@ -8783,7 +8783,7 @@
         <v>1403</v>
       </c>
       <c r="E15">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="F15" t="s">
         <v>1609</v>
@@ -8818,7 +8818,7 @@
         <v>1403</v>
       </c>
       <c r="E16">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="F16" t="s">
         <v>1609</v>
@@ -8853,7 +8853,7 @@
         <v>1404</v>
       </c>
       <c r="E17">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="F17" t="s">
         <v>1609</v>
@@ -8888,7 +8888,7 @@
         <v>1405</v>
       </c>
       <c r="E18">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="F18" t="s">
         <v>1609</v>
@@ -8923,7 +8923,7 @@
         <v>1406</v>
       </c>
       <c r="E19">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="F19" t="s">
         <v>1609</v>
@@ -8958,7 +8958,7 @@
         <v>1406</v>
       </c>
       <c r="E20">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="F20" t="s">
         <v>1609</v>
@@ -8993,7 +8993,7 @@
         <v>1407</v>
       </c>
       <c r="E21">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="F21" t="s">
         <v>1609</v>
@@ -9028,7 +9028,7 @@
         <v>1408</v>
       </c>
       <c r="E22">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="F22" t="s">
         <v>1609</v>
@@ -9063,7 +9063,7 @@
         <v>1409</v>
       </c>
       <c r="E23">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="F23" t="s">
         <v>1609</v>
@@ -9098,7 +9098,7 @@
         <v>1409</v>
       </c>
       <c r="E24">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="F24" t="s">
         <v>1609</v>
@@ -9133,7 +9133,7 @@
         <v>1410</v>
       </c>
       <c r="E25">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="F25" t="s">
         <v>1609</v>
@@ -9168,7 +9168,7 @@
         <v>1411</v>
       </c>
       <c r="E26">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="F26" t="s">
         <v>1609</v>
@@ -9203,7 +9203,7 @@
         <v>1412</v>
       </c>
       <c r="E27">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F27" t="s">
         <v>1609</v>
@@ -9238,7 +9238,7 @@
         <v>1413</v>
       </c>
       <c r="E28">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F28" t="s">
         <v>1609</v>
@@ -9273,7 +9273,7 @@
         <v>1414</v>
       </c>
       <c r="E29">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F29" t="s">
         <v>1609</v>
@@ -9311,7 +9311,7 @@
         <v>1415</v>
       </c>
       <c r="E30">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F30" t="s">
         <v>1609</v>
@@ -9346,7 +9346,7 @@
         <v>1416</v>
       </c>
       <c r="E31">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F31" t="s">
         <v>1609</v>
@@ -9381,7 +9381,7 @@
         <v>1417</v>
       </c>
       <c r="E32">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F32" t="s">
         <v>1609</v>
@@ -9416,7 +9416,7 @@
         <v>1418</v>
       </c>
       <c r="E33">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F33" t="s">
         <v>1609</v>
@@ -9451,7 +9451,7 @@
         <v>1418</v>
       </c>
       <c r="E34">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F34" t="s">
         <v>1609</v>
@@ -9486,7 +9486,7 @@
         <v>1419</v>
       </c>
       <c r="E35">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="F35" t="s">
         <v>1609</v>
@@ -9521,7 +9521,7 @@
         <v>1420</v>
       </c>
       <c r="E36">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F36" t="s">
         <v>1609</v>
@@ -9556,7 +9556,7 @@
         <v>1421</v>
       </c>
       <c r="E37">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F37" t="s">
         <v>1609</v>
@@ -9591,7 +9591,7 @@
         <v>1422</v>
       </c>
       <c r="E38">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F38" t="s">
         <v>1609</v>
@@ -9626,7 +9626,7 @@
         <v>1423</v>
       </c>
       <c r="E39">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F39" t="s">
         <v>1609</v>
@@ -9661,7 +9661,7 @@
         <v>1424</v>
       </c>
       <c r="E40">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F40" t="s">
         <v>1609</v>
@@ -9696,7 +9696,7 @@
         <v>1425</v>
       </c>
       <c r="E41">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F41" t="s">
         <v>1609</v>
@@ -9731,7 +9731,7 @@
         <v>1426</v>
       </c>
       <c r="E42">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F42" t="s">
         <v>1609</v>
@@ -9766,7 +9766,7 @@
         <v>1426</v>
       </c>
       <c r="E43">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F43" t="s">
         <v>1609</v>
@@ -9801,7 +9801,7 @@
         <v>1427</v>
       </c>
       <c r="E44">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F44" t="s">
         <v>1609</v>
@@ -9836,7 +9836,7 @@
         <v>1427</v>
       </c>
       <c r="E45">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F45" t="s">
         <v>1609</v>
@@ -9871,7 +9871,7 @@
         <v>1428</v>
       </c>
       <c r="E46">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F46" t="s">
         <v>1609</v>
@@ -9906,7 +9906,7 @@
         <v>1429</v>
       </c>
       <c r="E47">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F47" t="s">
         <v>1609</v>
@@ -9941,7 +9941,7 @@
         <v>1430</v>
       </c>
       <c r="E48">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F48" t="s">
         <v>1609</v>
@@ -9976,7 +9976,7 @@
         <v>1431</v>
       </c>
       <c r="E49">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F49" t="s">
         <v>1609</v>
@@ -10011,7 +10011,7 @@
         <v>1432</v>
       </c>
       <c r="E50">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F50" t="s">
         <v>1609</v>
@@ -10046,7 +10046,7 @@
         <v>1432</v>
       </c>
       <c r="E51">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F51" t="s">
         <v>1609</v>
@@ -10081,7 +10081,7 @@
         <v>1433</v>
       </c>
       <c r="E52">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F52" t="s">
         <v>1609</v>
@@ -10116,7 +10116,7 @@
         <v>1434</v>
       </c>
       <c r="E53">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F53" t="s">
         <v>1609</v>
@@ -10151,7 +10151,7 @@
         <v>1435</v>
       </c>
       <c r="E54">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F54" t="s">
         <v>1609</v>
@@ -10186,7 +10186,7 @@
         <v>1435</v>
       </c>
       <c r="E55">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F55" t="s">
         <v>1609</v>
@@ -10221,7 +10221,7 @@
         <v>1436</v>
       </c>
       <c r="E56">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F56" t="s">
         <v>1609</v>
@@ -10256,7 +10256,7 @@
         <v>1436</v>
       </c>
       <c r="E57">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F57" t="s">
         <v>1609</v>
@@ -10291,7 +10291,7 @@
         <v>1437</v>
       </c>
       <c r="E58">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F58" t="s">
         <v>1609</v>
@@ -10326,7 +10326,7 @@
         <v>1438</v>
       </c>
       <c r="E59">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F59" t="s">
         <v>1609</v>
@@ -10361,7 +10361,7 @@
         <v>1439</v>
       </c>
       <c r="E60">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F60" t="s">
         <v>1609</v>
@@ -10396,7 +10396,7 @@
         <v>1440</v>
       </c>
       <c r="E61">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F61" t="s">
         <v>1609</v>
@@ -10431,7 +10431,7 @@
         <v>1441</v>
       </c>
       <c r="E62">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F62" t="s">
         <v>1609</v>
@@ -10466,7 +10466,7 @@
         <v>1441</v>
       </c>
       <c r="E63">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F63" t="s">
         <v>1609</v>
@@ -10501,7 +10501,7 @@
         <v>1442</v>
       </c>
       <c r="E64">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F64" t="s">
         <v>1609</v>
@@ -10536,7 +10536,7 @@
         <v>1442</v>
       </c>
       <c r="E65">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F65" t="s">
         <v>1609</v>
@@ -10571,7 +10571,7 @@
         <v>1443</v>
       </c>
       <c r="E66">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F66" t="s">
         <v>1609</v>
@@ -10606,7 +10606,7 @@
         <v>1444</v>
       </c>
       <c r="E67">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F67" t="s">
         <v>1609</v>
@@ -10641,7 +10641,7 @@
         <v>1445</v>
       </c>
       <c r="E68">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F68" t="s">
         <v>1609</v>
@@ -10676,7 +10676,7 @@
         <v>1446</v>
       </c>
       <c r="E69">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F69" t="s">
         <v>1609</v>
@@ -10711,7 +10711,7 @@
         <v>1447</v>
       </c>
       <c r="E70">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F70" t="s">
         <v>1609</v>
@@ -10746,7 +10746,7 @@
         <v>1448</v>
       </c>
       <c r="E71">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F71" t="s">
         <v>1609</v>
@@ -10781,7 +10781,7 @@
         <v>1449</v>
       </c>
       <c r="E72">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F72" t="s">
         <v>1609</v>
@@ -10816,7 +10816,7 @@
         <v>1450</v>
       </c>
       <c r="E73">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F73" t="s">
         <v>1609</v>
@@ -10851,7 +10851,7 @@
         <v>1451</v>
       </c>
       <c r="E74">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F74" t="s">
         <v>1609</v>
@@ -10886,7 +10886,7 @@
         <v>1452</v>
       </c>
       <c r="E75">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F75" t="s">
         <v>1609</v>
@@ -10921,7 +10921,7 @@
         <v>1453</v>
       </c>
       <c r="E76">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F76" t="s">
         <v>1609</v>
@@ -10956,7 +10956,7 @@
         <v>1454</v>
       </c>
       <c r="E77">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F77" t="s">
         <v>1609</v>
@@ -10991,7 +10991,7 @@
         <v>1454</v>
       </c>
       <c r="E78">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F78" t="s">
         <v>1609</v>
@@ -11026,7 +11026,7 @@
         <v>1454</v>
       </c>
       <c r="E79">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F79" t="s">
         <v>1609</v>
@@ -11061,7 +11061,7 @@
         <v>1455</v>
       </c>
       <c r="E80">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F80" t="s">
         <v>1609</v>
@@ -11096,7 +11096,7 @@
         <v>1456</v>
       </c>
       <c r="E81">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F81" t="s">
         <v>1609</v>
@@ -11131,7 +11131,7 @@
         <v>1457</v>
       </c>
       <c r="E82">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F82" t="s">
         <v>1609</v>
@@ -11166,7 +11166,7 @@
         <v>1457</v>
       </c>
       <c r="E83">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F83" t="s">
         <v>1609</v>
@@ -11201,7 +11201,7 @@
         <v>1457</v>
       </c>
       <c r="E84">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F84" t="s">
         <v>1609</v>
@@ -11236,7 +11236,7 @@
         <v>1458</v>
       </c>
       <c r="E85">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F85" t="s">
         <v>1609</v>
@@ -11271,7 +11271,7 @@
         <v>1459</v>
       </c>
       <c r="E86">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F86" t="s">
         <v>1609</v>
@@ -11306,7 +11306,7 @@
         <v>1460</v>
       </c>
       <c r="E87">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F87" t="s">
         <v>1609</v>
@@ -11341,7 +11341,7 @@
         <v>1460</v>
       </c>
       <c r="E88">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F88" t="s">
         <v>1609</v>
@@ -11376,7 +11376,7 @@
         <v>1460</v>
       </c>
       <c r="E89">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F89" t="s">
         <v>1609</v>
@@ -11411,7 +11411,7 @@
         <v>1461</v>
       </c>
       <c r="E90">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F90" t="s">
         <v>1609</v>
@@ -11446,7 +11446,7 @@
         <v>1462</v>
       </c>
       <c r="E91">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F91" t="s">
         <v>1609</v>
@@ -11481,7 +11481,7 @@
         <v>1462</v>
       </c>
       <c r="E92">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F92" t="s">
         <v>1609</v>
@@ -11516,7 +11516,7 @@
         <v>1462</v>
       </c>
       <c r="E93">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F93" t="s">
         <v>1610</v>
@@ -11551,7 +11551,7 @@
         <v>1462</v>
       </c>
       <c r="E94">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F94" t="s">
         <v>1609</v>
@@ -11586,7 +11586,7 @@
         <v>1463</v>
       </c>
       <c r="E95">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F95" t="s">
         <v>1609</v>
@@ -11621,7 +11621,7 @@
         <v>1464</v>
       </c>
       <c r="E96">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F96" t="s">
         <v>1609</v>
@@ -11656,7 +11656,7 @@
         <v>1465</v>
       </c>
       <c r="E97">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F97" t="s">
         <v>1609</v>
@@ -11691,7 +11691,7 @@
         <v>1465</v>
       </c>
       <c r="E98">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F98" t="s">
         <v>1609</v>
@@ -11726,7 +11726,7 @@
         <v>1465</v>
       </c>
       <c r="E99">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F99" t="s">
         <v>1609</v>
@@ -11761,7 +11761,7 @@
         <v>1466</v>
       </c>
       <c r="E100">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F100" t="s">
         <v>1609</v>
@@ -11796,7 +11796,7 @@
         <v>1467</v>
       </c>
       <c r="E101">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F101" t="s">
         <v>1609</v>
@@ -11831,7 +11831,7 @@
         <v>1468</v>
       </c>
       <c r="E102">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F102" t="s">
         <v>1609</v>
@@ -11866,7 +11866,7 @@
         <v>1469</v>
       </c>
       <c r="E103">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F103" t="s">
         <v>1609</v>
@@ -11901,7 +11901,7 @@
         <v>1470</v>
       </c>
       <c r="E104">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F104" t="s">
         <v>1609</v>
@@ -11936,7 +11936,7 @@
         <v>1470</v>
       </c>
       <c r="E105">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F105" t="s">
         <v>1609</v>
@@ -11971,7 +11971,7 @@
         <v>1470</v>
       </c>
       <c r="E106">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F106" t="s">
         <v>1609</v>
@@ -12006,7 +12006,7 @@
         <v>1470</v>
       </c>
       <c r="E107">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F107" t="s">
         <v>1609</v>
@@ -12041,7 +12041,7 @@
         <v>1470</v>
       </c>
       <c r="E108">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F108" t="s">
         <v>1609</v>
@@ -12076,7 +12076,7 @@
         <v>1470</v>
       </c>
       <c r="E109">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F109" t="s">
         <v>1609</v>
@@ -12111,7 +12111,7 @@
         <v>1470</v>
       </c>
       <c r="E110">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F110" t="s">
         <v>1609</v>
@@ -12146,7 +12146,7 @@
         <v>1471</v>
       </c>
       <c r="E111">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F111" t="s">
         <v>1609</v>
@@ -12181,7 +12181,7 @@
         <v>1471</v>
       </c>
       <c r="E112">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F112" t="s">
         <v>1609</v>
@@ -12216,7 +12216,7 @@
         <v>1472</v>
       </c>
       <c r="E113">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F113" t="s">
         <v>1609</v>
@@ -12251,7 +12251,7 @@
         <v>1473</v>
       </c>
       <c r="E114">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F114" t="s">
         <v>1609</v>
@@ -12286,7 +12286,7 @@
         <v>1473</v>
       </c>
       <c r="E115">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F115" t="s">
         <v>1609</v>
@@ -12321,7 +12321,7 @@
         <v>1474</v>
       </c>
       <c r="E116">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F116" t="s">
         <v>1609</v>
@@ -12356,7 +12356,7 @@
         <v>1474</v>
       </c>
       <c r="E117">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F117" t="s">
         <v>1611</v>
@@ -12391,7 +12391,7 @@
         <v>1475</v>
       </c>
       <c r="E118">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F118" t="s">
         <v>1609</v>
@@ -12426,7 +12426,7 @@
         <v>1476</v>
       </c>
       <c r="E119">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F119" t="s">
         <v>1609</v>
@@ -12461,7 +12461,7 @@
         <v>1477</v>
       </c>
       <c r="E120">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F120" t="s">
         <v>1609</v>
@@ -12496,7 +12496,7 @@
         <v>1477</v>
       </c>
       <c r="E121">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F121" t="s">
         <v>1609</v>
@@ -12531,7 +12531,7 @@
         <v>1478</v>
       </c>
       <c r="E122">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F122" t="s">
         <v>1609</v>
@@ -12566,7 +12566,7 @@
         <v>1479</v>
       </c>
       <c r="E123">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F123" t="s">
         <v>1609</v>
@@ -12601,7 +12601,7 @@
         <v>1480</v>
       </c>
       <c r="E124">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F124" t="s">
         <v>1609</v>
@@ -12636,7 +12636,7 @@
         <v>1480</v>
       </c>
       <c r="E125">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F125" t="s">
         <v>1609</v>
@@ -12671,7 +12671,7 @@
         <v>1481</v>
       </c>
       <c r="E126">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F126" t="s">
         <v>1609</v>
@@ -12706,7 +12706,7 @@
         <v>1482</v>
       </c>
       <c r="E127">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F127" t="s">
         <v>1609</v>
@@ -12741,7 +12741,7 @@
         <v>1482</v>
       </c>
       <c r="E128">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F128" t="s">
         <v>1609</v>
@@ -12776,7 +12776,7 @@
         <v>1483</v>
       </c>
       <c r="E129">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F129" t="s">
         <v>1609</v>
@@ -12811,7 +12811,7 @@
         <v>1483</v>
       </c>
       <c r="E130">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F130" t="s">
         <v>1609</v>
@@ -12846,7 +12846,7 @@
         <v>1483</v>
       </c>
       <c r="E131">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F131" t="s">
         <v>1609</v>
@@ -12881,7 +12881,7 @@
         <v>1483</v>
       </c>
       <c r="E132">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F132" t="s">
         <v>1609</v>
@@ -12916,7 +12916,7 @@
         <v>1484</v>
       </c>
       <c r="E133">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F133" t="s">
         <v>1609</v>
@@ -12951,7 +12951,7 @@
         <v>1484</v>
       </c>
       <c r="E134">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F134" t="s">
         <v>1609</v>
@@ -12986,7 +12986,7 @@
         <v>1484</v>
       </c>
       <c r="E135">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F135" t="s">
         <v>1609</v>
@@ -13021,7 +13021,7 @@
         <v>1484</v>
       </c>
       <c r="E136">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F136" t="s">
         <v>1609</v>
@@ -13056,7 +13056,7 @@
         <v>1484</v>
       </c>
       <c r="E137">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F137" t="s">
         <v>1609</v>
@@ -13091,7 +13091,7 @@
         <v>1484</v>
       </c>
       <c r="E138">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F138" t="s">
         <v>1609</v>
@@ -13126,7 +13126,7 @@
         <v>1485</v>
       </c>
       <c r="E139">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F139" t="s">
         <v>1609</v>
@@ -13161,7 +13161,7 @@
         <v>1485</v>
       </c>
       <c r="E140">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F140" t="s">
         <v>1609</v>
@@ -13196,7 +13196,7 @@
         <v>1486</v>
       </c>
       <c r="E141">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F141" t="s">
         <v>1609</v>
@@ -13231,7 +13231,7 @@
         <v>1486</v>
       </c>
       <c r="E142">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F142" t="s">
         <v>1609</v>
@@ -13266,7 +13266,7 @@
         <v>1487</v>
       </c>
       <c r="E143">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F143" t="s">
         <v>1609</v>
@@ -13301,7 +13301,7 @@
         <v>1488</v>
       </c>
       <c r="E144">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F144" t="s">
         <v>1609</v>
@@ -13336,7 +13336,7 @@
         <v>1488</v>
       </c>
       <c r="E145">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F145" t="s">
         <v>1609</v>
@@ -13371,7 +13371,7 @@
         <v>1488</v>
       </c>
       <c r="E146">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F146" t="s">
         <v>1609</v>
@@ -13406,7 +13406,7 @@
         <v>1489</v>
       </c>
       <c r="E147">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F147" t="s">
         <v>1609</v>
@@ -13441,7 +13441,7 @@
         <v>1489</v>
       </c>
       <c r="E148">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F148" t="s">
         <v>1609</v>
@@ -13476,7 +13476,7 @@
         <v>1489</v>
       </c>
       <c r="E149">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F149" t="s">
         <v>1609</v>
@@ -13511,7 +13511,7 @@
         <v>1490</v>
       </c>
       <c r="E150">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F150" t="s">
         <v>1609</v>
@@ -13546,7 +13546,7 @@
         <v>1490</v>
       </c>
       <c r="E151">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F151" t="s">
         <v>1609</v>
@@ -13581,7 +13581,7 @@
         <v>1490</v>
       </c>
       <c r="E152">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F152" t="s">
         <v>1609</v>
@@ -13616,7 +13616,7 @@
         <v>1491</v>
       </c>
       <c r="E153">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F153" t="s">
         <v>1609</v>
@@ -13651,7 +13651,7 @@
         <v>1491</v>
       </c>
       <c r="E154">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F154" t="s">
         <v>1609</v>
@@ -13686,7 +13686,7 @@
         <v>1492</v>
       </c>
       <c r="E155">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F155" t="s">
         <v>1609</v>
@@ -13721,7 +13721,7 @@
         <v>1493</v>
       </c>
       <c r="E156">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F156" t="s">
         <v>1609</v>
@@ -13756,7 +13756,7 @@
         <v>1493</v>
       </c>
       <c r="E157">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F157" t="s">
         <v>1609</v>
@@ -13791,7 +13791,7 @@
         <v>1493</v>
       </c>
       <c r="E158">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F158" t="s">
         <v>1609</v>
@@ -13826,7 +13826,7 @@
         <v>1494</v>
       </c>
       <c r="E159">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F159" t="s">
         <v>1609</v>
@@ -13861,7 +13861,7 @@
         <v>1494</v>
       </c>
       <c r="E160">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F160" t="s">
         <v>1609</v>
@@ -13896,7 +13896,7 @@
         <v>1495</v>
       </c>
       <c r="E161">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F161" t="s">
         <v>1609</v>
@@ -13934,7 +13934,7 @@
         <v>1495</v>
       </c>
       <c r="E162">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F162" t="s">
         <v>1609</v>
@@ -13969,7 +13969,7 @@
         <v>1495</v>
       </c>
       <c r="E163">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F163" t="s">
         <v>1609</v>
@@ -14004,7 +14004,7 @@
         <v>1495</v>
       </c>
       <c r="E164">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F164" t="s">
         <v>1609</v>
@@ -14039,7 +14039,7 @@
         <v>1495</v>
       </c>
       <c r="E165">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F165" t="s">
         <v>1609</v>
@@ -14074,7 +14074,7 @@
         <v>1495</v>
       </c>
       <c r="E166">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F166" t="s">
         <v>1609</v>
@@ -14109,7 +14109,7 @@
         <v>1496</v>
       </c>
       <c r="E167">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F167" t="s">
         <v>1609</v>
@@ -14144,7 +14144,7 @@
         <v>1497</v>
       </c>
       <c r="E168">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F168" t="s">
         <v>1609</v>
@@ -14179,7 +14179,7 @@
         <v>1498</v>
       </c>
       <c r="E169">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F169" t="s">
         <v>1610</v>
@@ -14214,7 +14214,7 @@
         <v>1499</v>
       </c>
       <c r="E170">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F170" t="s">
         <v>1609</v>
@@ -14249,7 +14249,7 @@
         <v>1499</v>
       </c>
       <c r="E171">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F171" t="s">
         <v>1609</v>
@@ -14284,7 +14284,7 @@
         <v>1499</v>
       </c>
       <c r="E172">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F172" t="s">
         <v>1609</v>
@@ -14319,7 +14319,7 @@
         <v>1499</v>
       </c>
       <c r="E173">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F173" t="s">
         <v>1609</v>
@@ -14354,7 +14354,7 @@
         <v>1500</v>
       </c>
       <c r="E174">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F174" t="s">
         <v>1609</v>
@@ -14389,7 +14389,7 @@
         <v>1500</v>
       </c>
       <c r="E175">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F175" t="s">
         <v>1609</v>
@@ -14424,7 +14424,7 @@
         <v>1500</v>
       </c>
       <c r="E176">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F176" t="s">
         <v>1609</v>
@@ -14459,7 +14459,7 @@
         <v>1500</v>
       </c>
       <c r="E177">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F177" t="s">
         <v>1609</v>
@@ -14494,7 +14494,7 @@
         <v>1500</v>
       </c>
       <c r="E178">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F178" t="s">
         <v>1609</v>
@@ -14529,7 +14529,7 @@
         <v>1500</v>
       </c>
       <c r="E179">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F179" t="s">
         <v>1609</v>
@@ -14564,7 +14564,7 @@
         <v>1500</v>
       </c>
       <c r="E180">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F180" t="s">
         <v>1609</v>
@@ -14599,7 +14599,7 @@
         <v>1501</v>
       </c>
       <c r="E181">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F181" t="s">
         <v>1609</v>
@@ -14634,7 +14634,7 @@
         <v>1501</v>
       </c>
       <c r="E182">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F182" t="s">
         <v>1609</v>
@@ -14669,7 +14669,7 @@
         <v>1502</v>
       </c>
       <c r="E183">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F183" t="s">
         <v>1609</v>
@@ -14704,7 +14704,7 @@
         <v>1502</v>
       </c>
       <c r="E184">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F184" t="s">
         <v>1609</v>
@@ -14739,7 +14739,7 @@
         <v>1502</v>
       </c>
       <c r="E185">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F185" t="s">
         <v>1609</v>
@@ -14774,7 +14774,7 @@
         <v>1503</v>
       </c>
       <c r="E186">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F186" t="s">
         <v>1609</v>
@@ -14809,7 +14809,7 @@
         <v>1503</v>
       </c>
       <c r="E187">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F187" t="s">
         <v>1609</v>
@@ -14844,7 +14844,7 @@
         <v>1503</v>
       </c>
       <c r="E188">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F188" t="s">
         <v>1609</v>
@@ -14879,7 +14879,7 @@
         <v>1503</v>
       </c>
       <c r="E189">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F189" t="s">
         <v>1609</v>
@@ -14914,7 +14914,7 @@
         <v>1504</v>
       </c>
       <c r="E190">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F190" t="s">
         <v>1609</v>
@@ -14949,7 +14949,7 @@
         <v>1504</v>
       </c>
       <c r="E191">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F191" t="s">
         <v>1609</v>
@@ -14984,7 +14984,7 @@
         <v>1504</v>
       </c>
       <c r="E192">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F192" t="s">
         <v>1609</v>
@@ -15019,7 +15019,7 @@
         <v>1504</v>
       </c>
       <c r="E193">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F193" t="s">
         <v>1609</v>
@@ -15054,7 +15054,7 @@
         <v>1504</v>
       </c>
       <c r="E194">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F194" t="s">
         <v>1609</v>
@@ -15089,7 +15089,7 @@
         <v>1504</v>
       </c>
       <c r="E195">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F195" t="s">
         <v>1609</v>
@@ -15124,7 +15124,7 @@
         <v>1504</v>
       </c>
       <c r="E196">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F196" t="s">
         <v>1609</v>
@@ -15159,7 +15159,7 @@
         <v>1504</v>
       </c>
       <c r="E197">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F197" t="s">
         <v>1609</v>
@@ -15194,7 +15194,7 @@
         <v>1504</v>
       </c>
       <c r="E198">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F198" t="s">
         <v>1609</v>
@@ -15229,7 +15229,7 @@
         <v>1504</v>
       </c>
       <c r="E199">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F199" t="s">
         <v>1609</v>
@@ -15264,7 +15264,7 @@
         <v>1505</v>
       </c>
       <c r="E200">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F200" t="s">
         <v>1609</v>
@@ -15299,7 +15299,7 @@
         <v>1505</v>
       </c>
       <c r="E201">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F201" t="s">
         <v>1609</v>
@@ -15334,7 +15334,7 @@
         <v>1505</v>
       </c>
       <c r="E202">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F202" t="s">
         <v>1609</v>
@@ -15369,7 +15369,7 @@
         <v>1505</v>
       </c>
       <c r="E203">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F203" t="s">
         <v>1612</v>
@@ -15404,7 +15404,7 @@
         <v>1506</v>
       </c>
       <c r="E204">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F204" t="s">
         <v>1609</v>
@@ -15439,7 +15439,7 @@
         <v>1506</v>
       </c>
       <c r="E205">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F205" t="s">
         <v>1610</v>
@@ -15474,7 +15474,7 @@
         <v>1506</v>
       </c>
       <c r="E206">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F206" t="s">
         <v>1609</v>
@@ -15509,7 +15509,7 @@
         <v>1507</v>
       </c>
       <c r="E207">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F207" t="s">
         <v>1609</v>
@@ -15544,7 +15544,7 @@
         <v>1507</v>
       </c>
       <c r="E208">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F208" t="s">
         <v>1609</v>
@@ -15579,7 +15579,7 @@
         <v>1508</v>
       </c>
       <c r="E209">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F209" t="s">
         <v>1609</v>
@@ -15614,7 +15614,7 @@
         <v>1508</v>
       </c>
       <c r="E210">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F210" t="s">
         <v>1609</v>
@@ -15649,7 +15649,7 @@
         <v>1509</v>
       </c>
       <c r="E211">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F211" t="s">
         <v>1609</v>
@@ -15684,7 +15684,7 @@
         <v>1509</v>
       </c>
       <c r="E212">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F212" t="s">
         <v>1609</v>
@@ -15719,7 +15719,7 @@
         <v>1509</v>
       </c>
       <c r="E213">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F213" t="s">
         <v>1609</v>
@@ -15754,7 +15754,7 @@
         <v>1510</v>
       </c>
       <c r="E214">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F214" t="s">
         <v>1609</v>
@@ -15789,7 +15789,7 @@
         <v>1510</v>
       </c>
       <c r="E215">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F215" t="s">
         <v>1609</v>
@@ -15824,7 +15824,7 @@
         <v>1510</v>
       </c>
       <c r="E216">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F216" t="s">
         <v>1609</v>
@@ -15859,7 +15859,7 @@
         <v>1510</v>
       </c>
       <c r="E217">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F217" t="s">
         <v>1609</v>
@@ -15894,7 +15894,7 @@
         <v>1510</v>
       </c>
       <c r="E218">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F218" t="s">
         <v>1609</v>
@@ -15929,7 +15929,7 @@
         <v>1510</v>
       </c>
       <c r="E219">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F219" t="s">
         <v>1609</v>
@@ -15964,7 +15964,7 @@
         <v>1511</v>
       </c>
       <c r="E220">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F220" t="s">
         <v>1609</v>
@@ -15999,7 +15999,7 @@
         <v>1511</v>
       </c>
       <c r="E221">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F221" t="s">
         <v>1609</v>
@@ -16034,7 +16034,7 @@
         <v>1512</v>
       </c>
       <c r="E222">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F222" t="s">
         <v>1609</v>
@@ -16069,7 +16069,7 @@
         <v>1513</v>
       </c>
       <c r="E223">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F223" t="s">
         <v>1609</v>
@@ -16104,7 +16104,7 @@
         <v>1513</v>
       </c>
       <c r="E224">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F224" t="s">
         <v>1609</v>
@@ -16139,7 +16139,7 @@
         <v>1513</v>
       </c>
       <c r="E225">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F225" t="s">
         <v>1609</v>
@@ -16174,7 +16174,7 @@
         <v>1513</v>
       </c>
       <c r="E226">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F226" t="s">
         <v>1609</v>
@@ -16209,7 +16209,7 @@
         <v>1514</v>
       </c>
       <c r="E227">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F227" t="s">
         <v>1609</v>
@@ -16244,7 +16244,7 @@
         <v>1515</v>
       </c>
       <c r="E228">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F228" t="s">
         <v>1609</v>
@@ -16279,7 +16279,7 @@
         <v>1515</v>
       </c>
       <c r="E229">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F229" t="s">
         <v>1609</v>
@@ -16314,7 +16314,7 @@
         <v>1515</v>
       </c>
       <c r="E230">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F230" t="s">
         <v>1609</v>
@@ -16349,7 +16349,7 @@
         <v>1515</v>
       </c>
       <c r="E231">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F231" t="s">
         <v>1609</v>
@@ -16384,7 +16384,7 @@
         <v>1515</v>
       </c>
       <c r="E232">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F232" t="s">
         <v>1609</v>
@@ -16419,7 +16419,7 @@
         <v>1516</v>
       </c>
       <c r="E233">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F233" t="s">
         <v>1609</v>
@@ -16454,7 +16454,7 @@
         <v>1516</v>
       </c>
       <c r="E234">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F234" t="s">
         <v>1609</v>
@@ -16489,7 +16489,7 @@
         <v>1516</v>
       </c>
       <c r="E235">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F235" t="s">
         <v>1609</v>
@@ -16524,7 +16524,7 @@
         <v>1516</v>
       </c>
       <c r="E236">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F236" t="s">
         <v>1609</v>
@@ -16559,7 +16559,7 @@
         <v>1516</v>
       </c>
       <c r="E237">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F237" t="s">
         <v>1609</v>
@@ -16594,7 +16594,7 @@
         <v>1516</v>
       </c>
       <c r="E238">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F238" t="s">
         <v>1609</v>
@@ -16629,7 +16629,7 @@
         <v>1516</v>
       </c>
       <c r="E239">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F239" t="s">
         <v>1609</v>
@@ -16664,7 +16664,7 @@
         <v>1517</v>
       </c>
       <c r="E240">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F240" t="s">
         <v>1609</v>
@@ -16699,7 +16699,7 @@
         <v>1517</v>
       </c>
       <c r="E241">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F241" t="s">
         <v>1609</v>
@@ -16734,7 +16734,7 @@
         <v>1517</v>
       </c>
       <c r="E242">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F242" t="s">
         <v>1609</v>
@@ -16769,7 +16769,7 @@
         <v>1517</v>
       </c>
       <c r="E243">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F243" t="s">
         <v>1609</v>
@@ -16804,7 +16804,7 @@
         <v>1518</v>
       </c>
       <c r="E244">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F244" t="s">
         <v>1609</v>
@@ -16839,7 +16839,7 @@
         <v>1518</v>
       </c>
       <c r="E245">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F245" t="s">
         <v>1609</v>
@@ -16874,7 +16874,7 @@
         <v>1518</v>
       </c>
       <c r="E246">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F246" t="s">
         <v>1609</v>
@@ -16909,7 +16909,7 @@
         <v>1519</v>
       </c>
       <c r="E247">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F247" t="s">
         <v>1609</v>
@@ -16944,7 +16944,7 @@
         <v>1519</v>
       </c>
       <c r="E248">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F248" t="s">
         <v>1609</v>
@@ -16979,7 +16979,7 @@
         <v>1520</v>
       </c>
       <c r="E249">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F249" t="s">
         <v>1609</v>
@@ -17014,7 +17014,7 @@
         <v>1520</v>
       </c>
       <c r="E250">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F250" t="s">
         <v>1609</v>
@@ -17049,7 +17049,7 @@
         <v>1521</v>
       </c>
       <c r="E251">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F251" t="s">
         <v>1609</v>
@@ -17084,7 +17084,7 @@
         <v>1521</v>
       </c>
       <c r="E252">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F252" t="s">
         <v>1609</v>
@@ -17119,7 +17119,7 @@
         <v>1522</v>
       </c>
       <c r="E253">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F253" t="s">
         <v>1609</v>
@@ -17154,7 +17154,7 @@
         <v>1522</v>
       </c>
       <c r="E254">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F254" t="s">
         <v>1609</v>
@@ -17189,7 +17189,7 @@
         <v>1523</v>
       </c>
       <c r="E255">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F255" t="s">
         <v>1609</v>
@@ -17224,7 +17224,7 @@
         <v>1523</v>
       </c>
       <c r="E256">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F256" t="s">
         <v>1609</v>
@@ -17259,7 +17259,7 @@
         <v>1524</v>
       </c>
       <c r="E257">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F257" t="s">
         <v>1609</v>
@@ -17294,7 +17294,7 @@
         <v>1524</v>
       </c>
       <c r="E258">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F258" t="s">
         <v>1609</v>
@@ -17329,7 +17329,7 @@
         <v>1525</v>
       </c>
       <c r="E259">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F259" t="s">
         <v>1609</v>
@@ -17364,7 +17364,7 @@
         <v>1525</v>
       </c>
       <c r="E260">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F260" t="s">
         <v>1609</v>
@@ -17399,7 +17399,7 @@
         <v>1525</v>
       </c>
       <c r="E261">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F261" t="s">
         <v>1609</v>
@@ -17434,7 +17434,7 @@
         <v>1526</v>
       </c>
       <c r="E262">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F262" t="s">
         <v>1609</v>
@@ -17469,7 +17469,7 @@
         <v>1526</v>
       </c>
       <c r="E263">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F263" t="s">
         <v>1609</v>
@@ -17504,7 +17504,7 @@
         <v>1526</v>
       </c>
       <c r="E264">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F264" t="s">
         <v>1609</v>
@@ -17539,7 +17539,7 @@
         <v>1527</v>
       </c>
       <c r="E265">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F265" t="s">
         <v>1609</v>
@@ -17574,7 +17574,7 @@
         <v>1528</v>
       </c>
       <c r="E266">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F266" t="s">
         <v>1609</v>
@@ -17609,7 +17609,7 @@
         <v>1528</v>
       </c>
       <c r="E267">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F267" t="s">
         <v>1609</v>
@@ -17644,7 +17644,7 @@
         <v>1528</v>
       </c>
       <c r="E268">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F268" t="s">
         <v>1609</v>
@@ -17679,7 +17679,7 @@
         <v>1529</v>
       </c>
       <c r="E269">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F269" t="s">
         <v>1609</v>
@@ -17714,7 +17714,7 @@
         <v>1529</v>
       </c>
       <c r="E270">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F270" t="s">
         <v>1609</v>
@@ -17749,7 +17749,7 @@
         <v>1530</v>
       </c>
       <c r="E271">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F271" t="s">
         <v>1609</v>
@@ -17784,7 +17784,7 @@
         <v>1530</v>
       </c>
       <c r="E272">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F272" t="s">
         <v>1609</v>
@@ -17819,7 +17819,7 @@
         <v>1530</v>
       </c>
       <c r="E273">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F273" t="s">
         <v>1611</v>
@@ -17854,7 +17854,7 @@
         <v>1530</v>
       </c>
       <c r="E274">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F274" t="s">
         <v>1609</v>
@@ -17889,7 +17889,7 @@
         <v>1530</v>
       </c>
       <c r="E275">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F275" t="s">
         <v>1609</v>
@@ -17924,7 +17924,7 @@
         <v>1531</v>
       </c>
       <c r="E276">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F276" t="s">
         <v>1609</v>
@@ -17959,7 +17959,7 @@
         <v>1531</v>
       </c>
       <c r="E277">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F277" t="s">
         <v>1609</v>
@@ -17994,7 +17994,7 @@
         <v>1531</v>
       </c>
       <c r="E278">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F278" t="s">
         <v>1609</v>
@@ -18032,7 +18032,7 @@
         <v>1531</v>
       </c>
       <c r="E279">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F279" t="s">
         <v>1609</v>
@@ -18067,7 +18067,7 @@
         <v>1531</v>
       </c>
       <c r="E280">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F280" t="s">
         <v>1609</v>
@@ -18102,7 +18102,7 @@
         <v>1531</v>
       </c>
       <c r="E281">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F281" t="s">
         <v>1609</v>
@@ -18137,7 +18137,7 @@
         <v>1531</v>
       </c>
       <c r="E282">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F282" t="s">
         <v>1609</v>
@@ -18172,7 +18172,7 @@
         <v>1532</v>
       </c>
       <c r="E283">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F283" t="s">
         <v>1609</v>
@@ -18207,7 +18207,7 @@
         <v>1532</v>
       </c>
       <c r="E284">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F284" t="s">
         <v>1609</v>
@@ -18242,7 +18242,7 @@
         <v>1532</v>
       </c>
       <c r="E285">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F285" t="s">
         <v>1609</v>
@@ -18277,7 +18277,7 @@
         <v>1532</v>
       </c>
       <c r="E286">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F286" t="s">
         <v>1609</v>
@@ -18312,7 +18312,7 @@
         <v>1533</v>
       </c>
       <c r="E287">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F287" t="s">
         <v>1609</v>
@@ -18347,7 +18347,7 @@
         <v>1533</v>
       </c>
       <c r="E288">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F288" t="s">
         <v>1609</v>
@@ -18382,7 +18382,7 @@
         <v>1533</v>
       </c>
       <c r="E289">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F289" t="s">
         <v>1609</v>
@@ -18417,7 +18417,7 @@
         <v>1533</v>
       </c>
       <c r="E290">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F290" t="s">
         <v>1609</v>
@@ -18452,7 +18452,7 @@
         <v>1533</v>
       </c>
       <c r="E291">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F291" t="s">
         <v>1609</v>
@@ -18487,7 +18487,7 @@
         <v>1534</v>
       </c>
       <c r="E292">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F292" t="s">
         <v>1609</v>
@@ -18522,7 +18522,7 @@
         <v>1534</v>
       </c>
       <c r="E293">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F293" t="s">
         <v>1609</v>
@@ -18557,7 +18557,7 @@
         <v>1534</v>
       </c>
       <c r="E294">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F294" t="s">
         <v>1609</v>
@@ -18592,7 +18592,7 @@
         <v>1534</v>
       </c>
       <c r="E295">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F295" t="s">
         <v>1609</v>
@@ -18627,7 +18627,7 @@
         <v>1534</v>
       </c>
       <c r="E296">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F296" t="s">
         <v>1609</v>
@@ -18662,7 +18662,7 @@
         <v>1534</v>
       </c>
       <c r="E297">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F297" t="s">
         <v>1609</v>
@@ -18697,7 +18697,7 @@
         <v>1535</v>
       </c>
       <c r="E298">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F298" t="s">
         <v>1609</v>
@@ -18732,7 +18732,7 @@
         <v>1535</v>
       </c>
       <c r="E299">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F299" t="s">
         <v>1609</v>
@@ -18767,7 +18767,7 @@
         <v>1535</v>
       </c>
       <c r="E300">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F300" t="s">
         <v>1609</v>
@@ -18802,7 +18802,7 @@
         <v>1535</v>
       </c>
       <c r="E301">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F301" t="s">
         <v>1609</v>
@@ -18837,7 +18837,7 @@
         <v>1535</v>
       </c>
       <c r="E302">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F302" t="s">
         <v>1609</v>
@@ -18872,7 +18872,7 @@
         <v>1535</v>
       </c>
       <c r="E303">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F303" t="s">
         <v>1609</v>
@@ -18907,7 +18907,7 @@
         <v>1536</v>
       </c>
       <c r="E304">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F304" t="s">
         <v>1609</v>
@@ -18942,7 +18942,7 @@
         <v>1536</v>
       </c>
       <c r="E305">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F305" t="s">
         <v>1609</v>
@@ -18977,7 +18977,7 @@
         <v>1537</v>
       </c>
       <c r="E306">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F306" t="s">
         <v>1610</v>
@@ -19012,7 +19012,7 @@
         <v>1537</v>
       </c>
       <c r="E307">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F307" t="s">
         <v>1609</v>
@@ -19047,7 +19047,7 @@
         <v>1537</v>
       </c>
       <c r="E308">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F308" t="s">
         <v>1609</v>
@@ -19082,7 +19082,7 @@
         <v>1537</v>
       </c>
       <c r="E309">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F309" t="s">
         <v>1612</v>
@@ -19117,7 +19117,7 @@
         <v>1537</v>
       </c>
       <c r="E310">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F310" t="s">
         <v>1609</v>
@@ -19152,7 +19152,7 @@
         <v>1537</v>
       </c>
       <c r="E311">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F311" t="s">
         <v>1609</v>
@@ -19187,7 +19187,7 @@
         <v>1537</v>
       </c>
       <c r="E312">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F312" t="s">
         <v>1609</v>
@@ -19222,7 +19222,7 @@
         <v>1537</v>
       </c>
       <c r="E313">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F313" t="s">
         <v>1609</v>
@@ -19257,7 +19257,7 @@
         <v>1538</v>
       </c>
       <c r="E314">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F314" t="s">
         <v>1609</v>
@@ -19292,7 +19292,7 @@
         <v>1538</v>
       </c>
       <c r="E315">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F315" t="s">
         <v>1609</v>
@@ -19327,7 +19327,7 @@
         <v>1538</v>
       </c>
       <c r="E316">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F316" t="s">
         <v>1609</v>
@@ -19362,7 +19362,7 @@
         <v>1538</v>
       </c>
       <c r="E317">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F317" t="s">
         <v>1609</v>
@@ -19397,7 +19397,7 @@
         <v>1539</v>
       </c>
       <c r="E318">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F318" t="s">
         <v>1609</v>
@@ -19432,7 +19432,7 @@
         <v>1539</v>
       </c>
       <c r="E319">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F319" t="s">
         <v>1609</v>
@@ -19467,7 +19467,7 @@
         <v>1540</v>
       </c>
       <c r="E320">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F320" t="s">
         <v>1609</v>
@@ -19505,7 +19505,7 @@
         <v>1540</v>
       </c>
       <c r="E321">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F321" t="s">
         <v>1609</v>
@@ -19540,7 +19540,7 @@
         <v>1541</v>
       </c>
       <c r="E322">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F322" t="s">
         <v>1609</v>
@@ -19575,7 +19575,7 @@
         <v>1541</v>
       </c>
       <c r="E323">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F323" t="s">
         <v>1609</v>
@@ -19610,7 +19610,7 @@
         <v>1541</v>
       </c>
       <c r="E324">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F324" t="s">
         <v>1609</v>
@@ -19645,7 +19645,7 @@
         <v>1541</v>
       </c>
       <c r="E325">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F325" t="s">
         <v>1609</v>
@@ -19683,7 +19683,7 @@
         <v>1541</v>
       </c>
       <c r="E326">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F326" t="s">
         <v>1609</v>
@@ -19718,7 +19718,7 @@
         <v>1541</v>
       </c>
       <c r="E327">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F327" t="s">
         <v>1609</v>
@@ -19753,7 +19753,7 @@
         <v>1542</v>
       </c>
       <c r="E328">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F328" t="s">
         <v>1609</v>
@@ -19788,7 +19788,7 @@
         <v>1542</v>
       </c>
       <c r="E329">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F329" t="s">
         <v>1609</v>
@@ -19823,7 +19823,7 @@
         <v>1543</v>
       </c>
       <c r="E330">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F330" t="s">
         <v>1609</v>
@@ -19858,7 +19858,7 @@
         <v>1543</v>
       </c>
       <c r="E331">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F331" t="s">
         <v>1609</v>
@@ -19893,7 +19893,7 @@
         <v>1544</v>
       </c>
       <c r="E332">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F332" t="s">
         <v>1609</v>
@@ -19928,7 +19928,7 @@
         <v>1544</v>
       </c>
       <c r="E333">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F333" t="s">
         <v>1609</v>
@@ -19963,7 +19963,7 @@
         <v>1544</v>
       </c>
       <c r="E334">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F334" t="s">
         <v>1609</v>
@@ -19998,7 +19998,7 @@
         <v>1544</v>
       </c>
       <c r="E335">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F335" t="s">
         <v>1609</v>
@@ -20033,7 +20033,7 @@
         <v>1544</v>
       </c>
       <c r="E336">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F336" t="s">
         <v>1609</v>
@@ -20068,7 +20068,7 @@
         <v>1545</v>
       </c>
       <c r="E337">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F337" t="s">
         <v>1609</v>
@@ -20103,7 +20103,7 @@
         <v>1545</v>
       </c>
       <c r="E338">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F338" t="s">
         <v>1609</v>
@@ -20138,7 +20138,7 @@
         <v>1545</v>
       </c>
       <c r="E339">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F339" t="s">
         <v>1609</v>
@@ -20173,7 +20173,7 @@
         <v>1545</v>
       </c>
       <c r="E340">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F340" t="s">
         <v>1609</v>
@@ -20208,7 +20208,7 @@
         <v>1546</v>
       </c>
       <c r="E341">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F341" t="s">
         <v>1609</v>
@@ -20243,7 +20243,7 @@
         <v>1546</v>
       </c>
       <c r="E342">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F342" t="s">
         <v>1609</v>
@@ -20278,7 +20278,7 @@
         <v>1547</v>
       </c>
       <c r="E343">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F343" t="s">
         <v>1609</v>
@@ -20313,7 +20313,7 @@
         <v>1547</v>
       </c>
       <c r="E344">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F344" t="s">
         <v>1609</v>
@@ -20348,7 +20348,7 @@
         <v>1547</v>
       </c>
       <c r="E345">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F345" t="s">
         <v>1609</v>
@@ -20383,7 +20383,7 @@
         <v>1547</v>
       </c>
       <c r="E346">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F346" t="s">
         <v>1609</v>
@@ -20418,7 +20418,7 @@
         <v>1547</v>
       </c>
       <c r="E347">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F347" t="s">
         <v>1609</v>
@@ -20453,7 +20453,7 @@
         <v>1548</v>
       </c>
       <c r="E348">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F348" t="s">
         <v>1609</v>
@@ -20488,7 +20488,7 @@
         <v>1548</v>
       </c>
       <c r="E349">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F349" t="s">
         <v>1609</v>
@@ -20523,7 +20523,7 @@
         <v>1548</v>
       </c>
       <c r="E350">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F350" t="s">
         <v>1609</v>
@@ -20558,7 +20558,7 @@
         <v>1548</v>
       </c>
       <c r="E351">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F351" t="s">
         <v>1609</v>
@@ -20593,7 +20593,7 @@
         <v>1549</v>
       </c>
       <c r="E352">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F352" t="s">
         <v>1609</v>
@@ -20628,7 +20628,7 @@
         <v>1549</v>
       </c>
       <c r="E353">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F353" t="s">
         <v>1609</v>
@@ -20663,7 +20663,7 @@
         <v>1550</v>
       </c>
       <c r="E354">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F354" t="s">
         <v>1609</v>
@@ -20698,7 +20698,7 @@
         <v>1550</v>
       </c>
       <c r="E355">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F355" t="s">
         <v>1609</v>
@@ -20733,7 +20733,7 @@
         <v>1550</v>
       </c>
       <c r="E356">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F356" t="s">
         <v>1609</v>
@@ -20768,7 +20768,7 @@
         <v>1550</v>
       </c>
       <c r="E357">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F357" t="s">
         <v>1609</v>
@@ -20803,7 +20803,7 @@
         <v>1550</v>
       </c>
       <c r="E358">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F358" t="s">
         <v>1609</v>
@@ -20838,7 +20838,7 @@
         <v>1550</v>
       </c>
       <c r="E359">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F359" t="s">
         <v>1609</v>
@@ -20873,7 +20873,7 @@
         <v>1550</v>
       </c>
       <c r="E360">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F360" t="s">
         <v>1609</v>
@@ -20908,7 +20908,7 @@
         <v>1550</v>
       </c>
       <c r="E361">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F361" t="s">
         <v>1609</v>
@@ -20943,7 +20943,7 @@
         <v>1551</v>
       </c>
       <c r="E362">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F362" t="s">
         <v>1609</v>
@@ -20978,7 +20978,7 @@
         <v>1551</v>
       </c>
       <c r="E363">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F363" t="s">
         <v>1609</v>
@@ -21013,7 +21013,7 @@
         <v>1551</v>
       </c>
       <c r="E364">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F364" t="s">
         <v>1609</v>
@@ -21048,7 +21048,7 @@
         <v>1552</v>
       </c>
       <c r="E365">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F365" t="s">
         <v>1609</v>
@@ -21083,7 +21083,7 @@
         <v>1552</v>
       </c>
       <c r="E366">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F366" t="s">
         <v>1609</v>
@@ -21118,7 +21118,7 @@
         <v>1553</v>
       </c>
       <c r="E367">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F367" t="s">
         <v>1609</v>
@@ -21153,7 +21153,7 @@
         <v>1554</v>
       </c>
       <c r="E368">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F368" t="s">
         <v>1611</v>
@@ -21188,7 +21188,7 @@
         <v>1554</v>
       </c>
       <c r="E369">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F369" t="s">
         <v>1609</v>
@@ -21223,7 +21223,7 @@
         <v>1554</v>
       </c>
       <c r="E370">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F370" t="s">
         <v>1609</v>
@@ -21258,7 +21258,7 @@
         <v>1554</v>
       </c>
       <c r="E371">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F371" t="s">
         <v>1609</v>
@@ -21293,7 +21293,7 @@
         <v>1554</v>
       </c>
       <c r="E372">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F372" t="s">
         <v>1609</v>
@@ -21328,7 +21328,7 @@
         <v>1554</v>
       </c>
       <c r="E373">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F373" t="s">
         <v>1609</v>
@@ -21363,7 +21363,7 @@
         <v>1555</v>
       </c>
       <c r="E374">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F374" t="s">
         <v>1609</v>
@@ -21398,7 +21398,7 @@
         <v>1555</v>
       </c>
       <c r="E375">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F375" t="s">
         <v>1609</v>
@@ -21433,7 +21433,7 @@
         <v>1556</v>
       </c>
       <c r="E376">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F376" t="s">
         <v>1609</v>
@@ -21468,7 +21468,7 @@
         <v>1556</v>
       </c>
       <c r="E377">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F377" t="s">
         <v>1609</v>
@@ -21503,7 +21503,7 @@
         <v>1556</v>
       </c>
       <c r="E378">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F378" t="s">
         <v>1609</v>
@@ -21538,7 +21538,7 @@
         <v>1557</v>
       </c>
       <c r="E379">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F379" t="s">
         <v>1609</v>
@@ -21573,7 +21573,7 @@
         <v>1558</v>
       </c>
       <c r="E380">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F380" t="s">
         <v>1609</v>
@@ -21608,7 +21608,7 @@
         <v>1559</v>
       </c>
       <c r="E381">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F381" t="s">
         <v>1609</v>
@@ -21643,7 +21643,7 @@
         <v>1559</v>
       </c>
       <c r="E382">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F382" t="s">
         <v>1609</v>
@@ -21678,7 +21678,7 @@
         <v>1560</v>
       </c>
       <c r="E383">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F383" t="s">
         <v>1609</v>
@@ -21713,7 +21713,7 @@
         <v>1560</v>
       </c>
       <c r="E384">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F384" t="s">
         <v>1609</v>
@@ -21748,7 +21748,7 @@
         <v>1560</v>
       </c>
       <c r="E385">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F385" t="s">
         <v>1609</v>
@@ -21783,7 +21783,7 @@
         <v>1561</v>
       </c>
       <c r="E386">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F386" t="s">
         <v>1609</v>
@@ -21818,7 +21818,7 @@
         <v>1561</v>
       </c>
       <c r="E387">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F387" t="s">
         <v>1609</v>
@@ -21853,7 +21853,7 @@
         <v>1561</v>
       </c>
       <c r="E388">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F388" t="s">
         <v>1609</v>
@@ -21888,7 +21888,7 @@
         <v>1561</v>
       </c>
       <c r="E389">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F389" t="s">
         <v>1609</v>
@@ -21923,7 +21923,7 @@
         <v>1561</v>
       </c>
       <c r="E390">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F390" t="s">
         <v>1609</v>
@@ -21958,7 +21958,7 @@
         <v>1561</v>
       </c>
       <c r="E391">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F391" t="s">
         <v>1609</v>
@@ -21993,7 +21993,7 @@
         <v>1561</v>
       </c>
       <c r="E392">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F392" t="s">
         <v>1609</v>
@@ -22028,7 +22028,7 @@
         <v>1561</v>
       </c>
       <c r="E393">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F393" t="s">
         <v>1609</v>
@@ -22063,7 +22063,7 @@
         <v>1561</v>
       </c>
       <c r="E394">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F394" t="s">
         <v>1609</v>
@@ -22098,7 +22098,7 @@
         <v>1561</v>
       </c>
       <c r="E395">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F395" t="s">
         <v>1609</v>
@@ -22133,7 +22133,7 @@
         <v>1562</v>
       </c>
       <c r="E396">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F396" t="s">
         <v>1609</v>
@@ -22168,7 +22168,7 @@
         <v>1562</v>
       </c>
       <c r="E397">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F397" t="s">
         <v>1609</v>
@@ -22203,7 +22203,7 @@
         <v>1562</v>
       </c>
       <c r="E398">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F398" t="s">
         <v>1609</v>
@@ -22238,7 +22238,7 @@
         <v>1562</v>
       </c>
       <c r="E399">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F399" t="s">
         <v>1609</v>
@@ -22273,7 +22273,7 @@
         <v>1562</v>
       </c>
       <c r="E400">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F400" t="s">
         <v>1609</v>
@@ -22308,7 +22308,7 @@
         <v>1563</v>
       </c>
       <c r="E401">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F401" t="s">
         <v>1612</v>
@@ -22343,7 +22343,7 @@
         <v>1563</v>
       </c>
       <c r="E402">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F402" t="s">
         <v>1609</v>
@@ -22378,7 +22378,7 @@
         <v>1564</v>
       </c>
       <c r="E403">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F403" t="s">
         <v>1609</v>
@@ -22413,7 +22413,7 @@
         <v>1564</v>
       </c>
       <c r="E404">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F404" t="s">
         <v>1609</v>
@@ -22448,7 +22448,7 @@
         <v>1564</v>
       </c>
       <c r="E405">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F405" t="s">
         <v>1609</v>
@@ -22483,7 +22483,7 @@
         <v>1564</v>
       </c>
       <c r="E406">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F406" t="s">
         <v>1609</v>
@@ -22518,7 +22518,7 @@
         <v>1564</v>
       </c>
       <c r="E407">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F407" t="s">
         <v>1609</v>
@@ -22553,7 +22553,7 @@
         <v>1564</v>
       </c>
       <c r="E408">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F408" t="s">
         <v>1608</v>
@@ -22591,7 +22591,7 @@
         <v>1564</v>
       </c>
       <c r="E409">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F409" t="s">
         <v>1609</v>
@@ -22626,7 +22626,7 @@
         <v>1564</v>
       </c>
       <c r="E410">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F410" t="s">
         <v>1609</v>
@@ -22661,7 +22661,7 @@
         <v>1565</v>
       </c>
       <c r="E411">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F411" t="s">
         <v>1609</v>
@@ -22696,7 +22696,7 @@
         <v>1565</v>
       </c>
       <c r="E412">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F412" t="s">
         <v>1609</v>
@@ -22731,7 +22731,7 @@
         <v>1565</v>
       </c>
       <c r="E413">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F413" t="s">
         <v>1609</v>
@@ -22766,7 +22766,7 @@
         <v>1565</v>
       </c>
       <c r="E414">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F414" t="s">
         <v>1609</v>
@@ -22804,7 +22804,7 @@
         <v>1565</v>
       </c>
       <c r="E415">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F415" t="s">
         <v>1609</v>
@@ -22839,7 +22839,7 @@
         <v>1565</v>
       </c>
       <c r="E416">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F416" t="s">
         <v>1609</v>
@@ -22874,7 +22874,7 @@
         <v>1565</v>
       </c>
       <c r="E417">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F417" t="s">
         <v>1609</v>
@@ -22909,7 +22909,7 @@
         <v>1565</v>
       </c>
       <c r="E418">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F418" t="s">
         <v>1609</v>
@@ -22944,7 +22944,7 @@
         <v>1565</v>
       </c>
       <c r="E419">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F419" t="s">
         <v>1609</v>
@@ -22979,7 +22979,7 @@
         <v>1566</v>
       </c>
       <c r="E420">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F420" t="s">
         <v>1610</v>
@@ -23014,7 +23014,7 @@
         <v>1567</v>
       </c>
       <c r="E421">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F421" t="s">
         <v>1611</v>
@@ -23049,7 +23049,7 @@
         <v>1567</v>
       </c>
       <c r="E422">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F422" t="s">
         <v>1608</v>
@@ -23084,7 +23084,7 @@
         <v>1568</v>
       </c>
       <c r="E423">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F423" t="s">
         <v>1609</v>
@@ -23119,7 +23119,7 @@
         <v>1569</v>
       </c>
       <c r="E424">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F424" t="s">
         <v>1609</v>
@@ -23154,7 +23154,7 @@
         <v>1569</v>
       </c>
       <c r="E425">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F425" t="s">
         <v>1609</v>
@@ -23189,7 +23189,7 @@
         <v>1570</v>
       </c>
       <c r="E426">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F426" t="s">
         <v>1609</v>
@@ -23224,7 +23224,7 @@
         <v>1571</v>
       </c>
       <c r="E427">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F427" t="s">
         <v>1612</v>
@@ -23259,7 +23259,7 @@
         <v>1571</v>
       </c>
       <c r="E428">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F428" t="s">
         <v>1609</v>
@@ -23294,7 +23294,7 @@
         <v>1571</v>
       </c>
       <c r="E429">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F429" t="s">
         <v>1609</v>
@@ -23329,7 +23329,7 @@
         <v>1571</v>
       </c>
       <c r="E430">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F430" t="s">
         <v>1609</v>
@@ -23364,7 +23364,7 @@
         <v>1571</v>
       </c>
       <c r="E431">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F431" t="s">
         <v>1609</v>
@@ -23399,7 +23399,7 @@
         <v>1571</v>
       </c>
       <c r="E432">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F432" t="s">
         <v>1609</v>
@@ -23434,7 +23434,7 @@
         <v>1572</v>
       </c>
       <c r="E433">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F433" t="s">
         <v>1609</v>
@@ -23469,7 +23469,7 @@
         <v>1572</v>
       </c>
       <c r="E434">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F434" t="s">
         <v>1609</v>
@@ -23504,7 +23504,7 @@
         <v>1572</v>
       </c>
       <c r="E435">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F435" t="s">
         <v>1609</v>
@@ -23539,7 +23539,7 @@
         <v>1572</v>
       </c>
       <c r="E436">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F436" t="s">
         <v>1609</v>
@@ -23574,7 +23574,7 @@
         <v>1573</v>
       </c>
       <c r="E437">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F437" t="s">
         <v>1609</v>
@@ -23609,7 +23609,7 @@
         <v>1573</v>
       </c>
       <c r="E438">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F438" t="s">
         <v>1609</v>
@@ -23644,7 +23644,7 @@
         <v>1573</v>
       </c>
       <c r="E439">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F439" t="s">
         <v>1609</v>
@@ -23682,7 +23682,7 @@
         <v>1573</v>
       </c>
       <c r="E440">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F440" t="s">
         <v>1609</v>
@@ -23717,7 +23717,7 @@
         <v>1574</v>
       </c>
       <c r="E441">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F441" t="s">
         <v>1609</v>
@@ -23752,7 +23752,7 @@
         <v>1574</v>
       </c>
       <c r="E442">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F442" t="s">
         <v>1609</v>
@@ -23787,7 +23787,7 @@
         <v>1574</v>
       </c>
       <c r="E443">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F443" t="s">
         <v>1609</v>
@@ -23822,7 +23822,7 @@
         <v>1574</v>
       </c>
       <c r="E444">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F444" t="s">
         <v>1609</v>
@@ -23857,7 +23857,7 @@
         <v>1574</v>
       </c>
       <c r="E445">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F445" t="s">
         <v>1609</v>
@@ -23892,7 +23892,7 @@
         <v>1575</v>
       </c>
       <c r="E446">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F446" t="s">
         <v>1609</v>
@@ -23927,7 +23927,7 @@
         <v>1575</v>
       </c>
       <c r="E447">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F447" t="s">
         <v>1609</v>
@@ -23962,7 +23962,7 @@
         <v>1575</v>
       </c>
       <c r="E448">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F448" t="s">
         <v>1609</v>
@@ -23997,7 +23997,7 @@
         <v>1575</v>
       </c>
       <c r="E449">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F449" t="s">
         <v>1609</v>
@@ -24032,7 +24032,7 @@
         <v>1576</v>
       </c>
       <c r="E450">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F450" t="s">
         <v>1609</v>
@@ -24067,7 +24067,7 @@
         <v>1576</v>
       </c>
       <c r="E451">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F451" t="s">
         <v>1609</v>
@@ -24102,7 +24102,7 @@
         <v>1576</v>
       </c>
       <c r="E452">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F452" t="s">
         <v>1609</v>
@@ -24137,7 +24137,7 @@
         <v>1576</v>
       </c>
       <c r="E453">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F453" t="s">
         <v>1609</v>
@@ -24172,7 +24172,7 @@
         <v>1576</v>
       </c>
       <c r="E454">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F454" t="s">
         <v>1609</v>
@@ -24207,7 +24207,7 @@
         <v>1576</v>
       </c>
       <c r="E455">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F455" t="s">
         <v>1609</v>
@@ -24242,7 +24242,7 @@
         <v>1576</v>
       </c>
       <c r="E456">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F456" t="s">
         <v>1609</v>
@@ -24277,7 +24277,7 @@
         <v>1576</v>
       </c>
       <c r="E457">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F457" t="s">
         <v>1609</v>
@@ -24312,7 +24312,7 @@
         <v>1576</v>
       </c>
       <c r="E458">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F458" t="s">
         <v>1609</v>
@@ -24347,7 +24347,7 @@
         <v>1576</v>
       </c>
       <c r="E459">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F459" t="s">
         <v>1609</v>
@@ -24382,7 +24382,7 @@
         <v>1576</v>
       </c>
       <c r="E460">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F460" t="s">
         <v>1609</v>
@@ -24417,7 +24417,7 @@
         <v>1577</v>
       </c>
       <c r="E461">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F461" t="s">
         <v>1609</v>
@@ -24452,7 +24452,7 @@
         <v>1577</v>
       </c>
       <c r="E462">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F462" t="s">
         <v>1609</v>
@@ -24487,7 +24487,7 @@
         <v>1577</v>
       </c>
       <c r="E463">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F463" t="s">
         <v>1610</v>
@@ -24522,7 +24522,7 @@
         <v>1578</v>
       </c>
       <c r="E464">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F464" t="s">
         <v>1609</v>
@@ -24557,7 +24557,7 @@
         <v>1578</v>
       </c>
       <c r="E465">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F465" t="s">
         <v>1609</v>
@@ -24592,7 +24592,7 @@
         <v>1578</v>
       </c>
       <c r="E466">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F466" t="s">
         <v>1609</v>
@@ -24627,7 +24627,7 @@
         <v>1578</v>
       </c>
       <c r="E467">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F467" t="s">
         <v>1609</v>
@@ -24662,7 +24662,7 @@
         <v>1578</v>
       </c>
       <c r="E468">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F468" t="s">
         <v>1609</v>
@@ -24697,7 +24697,7 @@
         <v>1578</v>
       </c>
       <c r="E469">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F469" t="s">
         <v>1609</v>
@@ -24732,7 +24732,7 @@
         <v>1578</v>
       </c>
       <c r="E470">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F470" t="s">
         <v>1612</v>
@@ -24767,7 +24767,7 @@
         <v>1579</v>
       </c>
       <c r="E471">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F471" t="s">
         <v>1609</v>
@@ -24802,7 +24802,7 @@
         <v>1579</v>
       </c>
       <c r="E472">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F472" t="s">
         <v>1609</v>
@@ -24837,7 +24837,7 @@
         <v>1579</v>
       </c>
       <c r="E473">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F473" t="s">
         <v>1609</v>
@@ -24872,7 +24872,7 @@
         <v>1579</v>
       </c>
       <c r="E474">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F474" t="s">
         <v>1609</v>
@@ -24907,7 +24907,7 @@
         <v>1580</v>
       </c>
       <c r="E475">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F475" t="s">
         <v>1609</v>
@@ -24942,7 +24942,7 @@
         <v>1580</v>
       </c>
       <c r="E476">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F476" t="s">
         <v>1612</v>
@@ -24977,7 +24977,7 @@
         <v>1580</v>
       </c>
       <c r="E477">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F477" t="s">
         <v>1609</v>
@@ -25012,7 +25012,7 @@
         <v>1580</v>
       </c>
       <c r="E478">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F478" t="s">
         <v>1609</v>
@@ -25047,7 +25047,7 @@
         <v>1580</v>
       </c>
       <c r="E479">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F479" t="s">
         <v>1609</v>
@@ -25082,7 +25082,7 @@
         <v>1580</v>
       </c>
       <c r="E480">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F480" t="s">
         <v>1611</v>
@@ -25120,7 +25120,7 @@
         <v>1580</v>
       </c>
       <c r="E481">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F481" t="s">
         <v>1609</v>
@@ -25155,7 +25155,7 @@
         <v>1580</v>
       </c>
       <c r="E482">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F482" t="s">
         <v>1608</v>
@@ -25190,7 +25190,7 @@
         <v>1580</v>
       </c>
       <c r="E483">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F483" t="s">
         <v>1609</v>
@@ -25225,7 +25225,7 @@
         <v>1580</v>
       </c>
       <c r="E484">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F484" t="s">
         <v>1609</v>
@@ -25260,7 +25260,7 @@
         <v>1581</v>
       </c>
       <c r="E485">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F485" t="s">
         <v>1609</v>
@@ -25295,7 +25295,7 @@
         <v>1581</v>
       </c>
       <c r="E486">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F486" t="s">
         <v>1609</v>
@@ -25330,7 +25330,7 @@
         <v>1581</v>
       </c>
       <c r="E487">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F487" t="s">
         <v>1609</v>
@@ -25365,7 +25365,7 @@
         <v>1581</v>
       </c>
       <c r="E488">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F488" t="s">
         <v>1609</v>
@@ -25400,7 +25400,7 @@
         <v>1581</v>
       </c>
       <c r="E489">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F489" t="s">
         <v>1609</v>
@@ -25435,7 +25435,7 @@
         <v>1581</v>
       </c>
       <c r="E490">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F490" t="s">
         <v>1609</v>
@@ -25470,7 +25470,7 @@
         <v>1581</v>
       </c>
       <c r="E491">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F491" t="s">
         <v>1611</v>
@@ -25505,7 +25505,7 @@
         <v>1581</v>
       </c>
       <c r="E492">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F492" t="s">
         <v>1609</v>
@@ -25540,7 +25540,7 @@
         <v>1581</v>
       </c>
       <c r="E493">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F493" t="s">
         <v>1609</v>
@@ -25575,7 +25575,7 @@
         <v>1582</v>
       </c>
       <c r="E494">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F494" t="s">
         <v>1609</v>
@@ -25610,7 +25610,7 @@
         <v>1582</v>
       </c>
       <c r="E495">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F495" t="s">
         <v>1609</v>
@@ -25645,7 +25645,7 @@
         <v>1582</v>
       </c>
       <c r="E496">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F496" t="s">
         <v>1609</v>
@@ -25680,7 +25680,7 @@
         <v>1582</v>
       </c>
       <c r="E497">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F497" t="s">
         <v>1609</v>
@@ -25715,7 +25715,7 @@
         <v>1582</v>
       </c>
       <c r="E498">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F498" t="s">
         <v>1609</v>
@@ -25750,7 +25750,7 @@
         <v>1583</v>
       </c>
       <c r="E499">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F499" t="s">
         <v>1609</v>
@@ -25785,7 +25785,7 @@
         <v>1583</v>
       </c>
       <c r="E500">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F500" t="s">
         <v>1609</v>
@@ -25820,7 +25820,7 @@
         <v>1583</v>
       </c>
       <c r="E501">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F501" t="s">
         <v>1609</v>
@@ -25855,7 +25855,7 @@
         <v>1583</v>
       </c>
       <c r="E502">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F502" t="s">
         <v>1609</v>
@@ -25890,7 +25890,7 @@
         <v>1583</v>
       </c>
       <c r="E503">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F503" t="s">
         <v>1609</v>
@@ -25928,7 +25928,7 @@
         <v>1584</v>
       </c>
       <c r="E504">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F504" t="s">
         <v>1609</v>
@@ -25963,7 +25963,7 @@
         <v>1584</v>
       </c>
       <c r="E505">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F505" t="s">
         <v>1609</v>
@@ -25998,7 +25998,7 @@
         <v>1584</v>
       </c>
       <c r="E506">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F506" t="s">
         <v>1609</v>
@@ -26033,7 +26033,7 @@
         <v>1584</v>
       </c>
       <c r="E507">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F507" t="s">
         <v>1609</v>
@@ -26068,7 +26068,7 @@
         <v>1584</v>
       </c>
       <c r="E508">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F508" t="s">
         <v>1609</v>
@@ -26103,7 +26103,7 @@
         <v>1584</v>
       </c>
       <c r="E509">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F509" t="s">
         <v>1609</v>
@@ -26138,7 +26138,7 @@
         <v>1584</v>
       </c>
       <c r="E510">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F510" t="s">
         <v>1609</v>
@@ -26173,7 +26173,7 @@
         <v>1585</v>
       </c>
       <c r="E511">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F511" t="s">
         <v>1609</v>
@@ -26208,7 +26208,7 @@
         <v>1585</v>
       </c>
       <c r="E512">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F512" t="s">
         <v>1609</v>
@@ -26243,7 +26243,7 @@
         <v>1585</v>
       </c>
       <c r="E513">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F513" t="s">
         <v>1609</v>
@@ -26278,7 +26278,7 @@
         <v>1586</v>
       </c>
       <c r="E514">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F514" t="s">
         <v>1609</v>
@@ -26313,7 +26313,7 @@
         <v>1586</v>
       </c>
       <c r="E515">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F515" t="s">
         <v>1609</v>
@@ -26348,7 +26348,7 @@
         <v>1587</v>
       </c>
       <c r="E516">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F516" t="s">
         <v>1609</v>
@@ -26383,7 +26383,7 @@
         <v>1587</v>
       </c>
       <c r="E517">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F517" t="s">
         <v>1609</v>
@@ -26418,7 +26418,7 @@
         <v>1587</v>
       </c>
       <c r="E518">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F518" t="s">
         <v>1611</v>
@@ -26456,7 +26456,7 @@
         <v>1587</v>
       </c>
       <c r="E519">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F519" t="s">
         <v>1609</v>
@@ -26491,7 +26491,7 @@
         <v>1587</v>
       </c>
       <c r="E520">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F520" t="s">
         <v>1609</v>
@@ -26526,7 +26526,7 @@
         <v>1588</v>
       </c>
       <c r="E521">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F521" t="s">
         <v>1609</v>
@@ -26561,7 +26561,7 @@
         <v>1588</v>
       </c>
       <c r="E522">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F522" t="s">
         <v>1609</v>
@@ -26596,7 +26596,7 @@
         <v>1588</v>
       </c>
       <c r="E523">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F523" t="s">
         <v>1609</v>
@@ -26631,7 +26631,7 @@
         <v>1588</v>
       </c>
       <c r="E524">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F524" t="s">
         <v>1609</v>
@@ -26666,7 +26666,7 @@
         <v>1588</v>
       </c>
       <c r="E525">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F525" t="s">
         <v>1609</v>
@@ -26701,7 +26701,7 @@
         <v>1589</v>
       </c>
       <c r="E526">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F526" t="s">
         <v>1609</v>
@@ -26736,7 +26736,7 @@
         <v>1589</v>
       </c>
       <c r="E527">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F527" t="s">
         <v>1609</v>
@@ -26771,7 +26771,7 @@
         <v>1589</v>
       </c>
       <c r="E528">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F528" t="s">
         <v>1609</v>
@@ -26806,7 +26806,7 @@
         <v>1589</v>
       </c>
       <c r="E529">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F529" t="s">
         <v>1609</v>
@@ -26841,7 +26841,7 @@
         <v>1589</v>
       </c>
       <c r="E530">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F530" t="s">
         <v>1609</v>
@@ -26876,7 +26876,7 @@
         <v>1589</v>
       </c>
       <c r="E531">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F531" t="s">
         <v>1609</v>
@@ -26911,7 +26911,7 @@
         <v>1589</v>
       </c>
       <c r="E532">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F532" t="s">
         <v>1609</v>
@@ -26946,7 +26946,7 @@
         <v>1589</v>
       </c>
       <c r="E533">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F533" t="s">
         <v>1609</v>
@@ -26981,7 +26981,7 @@
         <v>1590</v>
       </c>
       <c r="E534">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F534" t="s">
         <v>1609</v>
@@ -27016,7 +27016,7 @@
         <v>1590</v>
       </c>
       <c r="E535">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F535" t="s">
         <v>1609</v>
@@ -27051,7 +27051,7 @@
         <v>1591</v>
       </c>
       <c r="E536">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F536" t="s">
         <v>1609</v>
@@ -27086,7 +27086,7 @@
         <v>1591</v>
       </c>
       <c r="E537">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F537" t="s">
         <v>1609</v>
@@ -27121,7 +27121,7 @@
         <v>1591</v>
       </c>
       <c r="E538">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F538" t="s">
         <v>1609</v>
@@ -27156,7 +27156,7 @@
         <v>1591</v>
       </c>
       <c r="E539">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F539" t="s">
         <v>1608</v>
@@ -27194,7 +27194,7 @@
         <v>1591</v>
       </c>
       <c r="E540">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F540" t="s">
         <v>1609</v>
@@ -27229,7 +27229,7 @@
         <v>1591</v>
       </c>
       <c r="E541">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F541" t="s">
         <v>1608</v>
@@ -27264,7 +27264,7 @@
         <v>1592</v>
       </c>
       <c r="E542">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F542" t="s">
         <v>1609</v>
@@ -27299,7 +27299,7 @@
         <v>1593</v>
       </c>
       <c r="E543">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F543" t="s">
         <v>1609</v>
@@ -27334,7 +27334,7 @@
         <v>1593</v>
       </c>
       <c r="E544">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F544" t="s">
         <v>1609</v>
@@ -27369,7 +27369,7 @@
         <v>1593</v>
       </c>
       <c r="E545">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F545" t="s">
         <v>1609</v>
@@ -27404,7 +27404,7 @@
         <v>1593</v>
       </c>
       <c r="E546">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F546" t="s">
         <v>1609</v>
@@ -27439,7 +27439,7 @@
         <v>1594</v>
       </c>
       <c r="E547">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F547" t="s">
         <v>1609</v>
@@ -27474,7 +27474,7 @@
         <v>1594</v>
       </c>
       <c r="E548">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F548" t="s">
         <v>1608</v>
@@ -27509,7 +27509,7 @@
         <v>1594</v>
       </c>
       <c r="E549">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F549" t="s">
         <v>1609</v>
@@ -27544,7 +27544,7 @@
         <v>1594</v>
       </c>
       <c r="E550">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F550" t="s">
         <v>1609</v>
@@ -27579,7 +27579,7 @@
         <v>1594</v>
       </c>
       <c r="E551">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F551" t="s">
         <v>1609</v>
@@ -27614,7 +27614,7 @@
         <v>1594</v>
       </c>
       <c r="E552">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F552" t="s">
         <v>1609</v>
@@ -27649,7 +27649,7 @@
         <v>1595</v>
       </c>
       <c r="E553">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F553" t="s">
         <v>1609</v>
@@ -27684,7 +27684,7 @@
         <v>1595</v>
       </c>
       <c r="E554">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F554" t="s">
         <v>1608</v>
@@ -27719,7 +27719,7 @@
         <v>1595</v>
       </c>
       <c r="E555">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F555" t="s">
         <v>1611</v>
@@ -27754,7 +27754,7 @@
         <v>1595</v>
       </c>
       <c r="E556">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F556" t="s">
         <v>1609</v>
@@ -27789,7 +27789,7 @@
         <v>1595</v>
       </c>
       <c r="E557">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F557" t="s">
         <v>1609</v>
@@ -27824,7 +27824,7 @@
         <v>1596</v>
       </c>
       <c r="E558">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F558" t="s">
         <v>1609</v>
@@ -27859,7 +27859,7 @@
         <v>1596</v>
       </c>
       <c r="E559">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F559" t="s">
         <v>1609</v>
@@ -27894,7 +27894,7 @@
         <v>1596</v>
       </c>
       <c r="E560">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F560" t="s">
         <v>1609</v>
@@ -27929,7 +27929,7 @@
         <v>1596</v>
       </c>
       <c r="E561">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F561" t="s">
         <v>1609</v>
@@ -27964,7 +27964,7 @@
         <v>1596</v>
       </c>
       <c r="E562">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F562" t="s">
         <v>1609</v>
@@ -27999,7 +27999,7 @@
         <v>1596</v>
       </c>
       <c r="E563">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F563" t="s">
         <v>1609</v>
@@ -28034,7 +28034,7 @@
         <v>1596</v>
       </c>
       <c r="E564">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F564" t="s">
         <v>1609</v>
@@ -28069,7 +28069,7 @@
         <v>1597</v>
       </c>
       <c r="E565">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F565" t="s">
         <v>1609</v>
@@ -28104,7 +28104,7 @@
         <v>1597</v>
       </c>
       <c r="E566">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F566" t="s">
         <v>1609</v>
@@ -28139,7 +28139,7 @@
         <v>1597</v>
       </c>
       <c r="E567">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F567" t="s">
         <v>1609</v>
@@ -28174,7 +28174,7 @@
         <v>1597</v>
       </c>
       <c r="E568">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F568" t="s">
         <v>1609</v>
@@ -28209,7 +28209,7 @@
         <v>1597</v>
       </c>
       <c r="E569">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F569" t="s">
         <v>1609</v>
@@ -28244,7 +28244,7 @@
         <v>1597</v>
       </c>
       <c r="E570">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F570" t="s">
         <v>1609</v>
@@ -28279,7 +28279,7 @@
         <v>1597</v>
       </c>
       <c r="E571">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F571" t="s">
         <v>1609</v>
@@ -28314,7 +28314,7 @@
         <v>1597</v>
       </c>
       <c r="E572">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F572" t="s">
         <v>1609</v>
@@ -28349,7 +28349,7 @@
         <v>1597</v>
       </c>
       <c r="E573">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F573" t="s">
         <v>1609</v>
@@ -28384,7 +28384,7 @@
         <v>1597</v>
       </c>
       <c r="E574">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F574" t="s">
         <v>1609</v>
@@ -28419,7 +28419,7 @@
         <v>1597</v>
       </c>
       <c r="E575">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F575" t="s">
         <v>1609</v>
@@ -28454,7 +28454,7 @@
         <v>1597</v>
       </c>
       <c r="E576">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F576" t="s">
         <v>1609</v>
@@ -28489,7 +28489,7 @@
         <v>1597</v>
       </c>
       <c r="E577">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F577" t="s">
         <v>1609</v>
@@ -28524,7 +28524,7 @@
         <v>1597</v>
       </c>
       <c r="E578">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F578" t="s">
         <v>1609</v>
@@ -28559,7 +28559,7 @@
         <v>1597</v>
       </c>
       <c r="E579">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F579" t="s">
         <v>1609</v>
@@ -28594,7 +28594,7 @@
         <v>1597</v>
       </c>
       <c r="E580">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F580" t="s">
         <v>1609</v>
@@ -28629,7 +28629,7 @@
         <v>1597</v>
       </c>
       <c r="E581">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F581" t="s">
         <v>1609</v>
@@ -28664,7 +28664,7 @@
         <v>1597</v>
       </c>
       <c r="E582">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F582" t="s">
         <v>1609</v>
@@ -28699,7 +28699,7 @@
         <v>1597</v>
       </c>
       <c r="E583">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F583" t="s">
         <v>1609</v>
@@ -28734,7 +28734,7 @@
         <v>1597</v>
       </c>
       <c r="E584">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F584" t="s">
         <v>1609</v>
@@ -28769,7 +28769,7 @@
         <v>1597</v>
       </c>
       <c r="E585">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F585" t="s">
         <v>1609</v>
@@ -28804,7 +28804,7 @@
         <v>1597</v>
       </c>
       <c r="E586">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F586" t="s">
         <v>1609</v>
@@ -28839,7 +28839,7 @@
         <v>1597</v>
       </c>
       <c r="E587">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F587" t="s">
         <v>1609</v>
@@ -28874,7 +28874,7 @@
         <v>1597</v>
       </c>
       <c r="E588">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F588" t="s">
         <v>1609</v>
@@ -28909,7 +28909,7 @@
         <v>1597</v>
       </c>
       <c r="E589">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F589" t="s">
         <v>1609</v>
@@ -28944,7 +28944,7 @@
         <v>1597</v>
       </c>
       <c r="E590">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F590" t="s">
         <v>1609</v>
@@ -28979,7 +28979,7 @@
         <v>1597</v>
       </c>
       <c r="E591">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F591" t="s">
         <v>1609</v>
@@ -29014,7 +29014,7 @@
         <v>1597</v>
       </c>
       <c r="E592">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F592" t="s">
         <v>1611</v>
@@ -29052,7 +29052,7 @@
         <v>1598</v>
       </c>
       <c r="E593">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F593" t="s">
         <v>1609</v>
@@ -29087,7 +29087,7 @@
         <v>1598</v>
       </c>
       <c r="E594">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F594" t="s">
         <v>1609</v>
@@ -29122,7 +29122,7 @@
         <v>1598</v>
       </c>
       <c r="E595">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F595" t="s">
         <v>1611</v>
@@ -29157,7 +29157,7 @@
         <v>1598</v>
       </c>
       <c r="E596">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F596" t="s">
         <v>1609</v>
@@ -29192,7 +29192,7 @@
         <v>1598</v>
       </c>
       <c r="E597">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F597" t="s">
         <v>1609</v>
@@ -29227,7 +29227,7 @@
         <v>1598</v>
       </c>
       <c r="E598">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F598" t="s">
         <v>1609</v>
@@ -29262,7 +29262,7 @@
         <v>1598</v>
       </c>
       <c r="E599">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F599" t="s">
         <v>1609</v>
@@ -29297,7 +29297,7 @@
         <v>1598</v>
       </c>
       <c r="E600">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F600" t="s">
         <v>1609</v>
@@ -29332,7 +29332,7 @@
         <v>1599</v>
       </c>
       <c r="E601">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F601" t="s">
         <v>1609</v>
@@ -29367,7 +29367,7 @@
         <v>1599</v>
       </c>
       <c r="E602">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F602" t="s">
         <v>1609</v>
@@ -29402,7 +29402,7 @@
         <v>1600</v>
       </c>
       <c r="E603">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F603" t="s">
         <v>1609</v>
@@ -29437,7 +29437,7 @@
         <v>1600</v>
       </c>
       <c r="E604">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F604" t="s">
         <v>1611</v>
@@ -29475,7 +29475,7 @@
         <v>1600</v>
       </c>
       <c r="E605">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F605" t="s">
         <v>1611</v>
@@ -29513,7 +29513,7 @@
         <v>1601</v>
       </c>
       <c r="E606">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F606" t="s">
         <v>1611</v>
@@ -29551,7 +29551,7 @@
         <v>1601</v>
       </c>
       <c r="E607">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F607" t="s">
         <v>1609</v>
@@ -29586,7 +29586,7 @@
         <v>1601</v>
       </c>
       <c r="E608">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F608" t="s">
         <v>1609</v>
@@ -29621,7 +29621,7 @@
         <v>1601</v>
       </c>
       <c r="E609">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F609" t="s">
         <v>1611</v>
@@ -29659,7 +29659,7 @@
         <v>1601</v>
       </c>
       <c r="E610">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F610" t="s">
         <v>1609</v>
@@ -29694,7 +29694,7 @@
         <v>1601</v>
       </c>
       <c r="E611">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F611" t="s">
         <v>1609</v>
@@ -29729,7 +29729,7 @@
         <v>1601</v>
       </c>
       <c r="E612">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F612" t="s">
         <v>1611</v>
@@ -29767,7 +29767,7 @@
         <v>1601</v>
       </c>
       <c r="E613">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F613" t="s">
         <v>1609</v>
@@ -29802,7 +29802,7 @@
         <v>1601</v>
       </c>
       <c r="E614">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F614" t="s">
         <v>1609</v>
@@ -29840,7 +29840,7 @@
         <v>1601</v>
       </c>
       <c r="E615">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F615" t="s">
         <v>1611</v>
@@ -29875,7 +29875,7 @@
         <v>1601</v>
       </c>
       <c r="E616">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F616" t="s">
         <v>1609</v>
@@ -29910,7 +29910,7 @@
         <v>1601</v>
       </c>
       <c r="E617">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F617" t="s">
         <v>1609</v>
@@ -29945,7 +29945,7 @@
         <v>1602</v>
       </c>
       <c r="E618">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F618" t="s">
         <v>1609</v>
@@ -29983,7 +29983,7 @@
         <v>1602</v>
       </c>
       <c r="E619">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F619" t="s">
         <v>1608</v>
@@ -30018,7 +30018,7 @@
         <v>1602</v>
       </c>
       <c r="E620">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F620" t="s">
         <v>1611</v>
@@ -30053,7 +30053,7 @@
         <v>1602</v>
       </c>
       <c r="E621">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F621" t="s">
         <v>1609</v>
@@ -30088,7 +30088,7 @@
         <v>1602</v>
       </c>
       <c r="E622">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F622" t="s">
         <v>1611</v>
@@ -30126,7 +30126,7 @@
         <v>1602</v>
       </c>
       <c r="E623">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F623" t="s">
         <v>1609</v>
@@ -30161,7 +30161,7 @@
         <v>1602</v>
       </c>
       <c r="E624">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F624" t="s">
         <v>1609</v>
@@ -30196,7 +30196,7 @@
         <v>1602</v>
       </c>
       <c r="E625">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F625" t="s">
         <v>1609</v>
@@ -30231,7 +30231,7 @@
         <v>1602</v>
       </c>
       <c r="E626">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F626" t="s">
         <v>1609</v>
@@ -30266,7 +30266,7 @@
         <v>1602</v>
       </c>
       <c r="E627">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F627" t="s">
         <v>1609</v>
@@ -30301,7 +30301,7 @@
         <v>1603</v>
       </c>
       <c r="E628">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F628" t="s">
         <v>1609</v>
@@ -30336,7 +30336,7 @@
         <v>1603</v>
       </c>
       <c r="E629">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F629" t="s">
         <v>1609</v>
@@ -30374,7 +30374,7 @@
         <v>1603</v>
       </c>
       <c r="E630">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F630" t="s">
         <v>1609</v>
@@ -30409,7 +30409,7 @@
         <v>1604</v>
       </c>
       <c r="E631">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F631" t="s">
         <v>1609</v>
@@ -30444,7 +30444,7 @@
         <v>1604</v>
       </c>
       <c r="E632">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F632" t="s">
         <v>1611</v>
@@ -30482,7 +30482,7 @@
         <v>1604</v>
       </c>
       <c r="E633">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F633" t="s">
         <v>1609</v>
@@ -30517,7 +30517,7 @@
         <v>1604</v>
       </c>
       <c r="E634">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F634" t="s">
         <v>1609</v>
@@ -30552,7 +30552,7 @@
         <v>1604</v>
       </c>
       <c r="E635">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F635" t="s">
         <v>1609</v>
@@ -30587,7 +30587,7 @@
         <v>1604</v>
       </c>
       <c r="E636">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F636" t="s">
         <v>1609</v>
@@ -30622,7 +30622,7 @@
         <v>1604</v>
       </c>
       <c r="E637">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F637" t="s">
         <v>1609</v>
@@ -30657,7 +30657,7 @@
         <v>1604</v>
       </c>
       <c r="E638">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F638" t="s">
         <v>1609</v>
@@ -30692,7 +30692,7 @@
         <v>1604</v>
       </c>
       <c r="E639">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F639" t="s">
         <v>1609</v>
@@ -30727,7 +30727,7 @@
         <v>1604</v>
       </c>
       <c r="E640">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F640" t="s">
         <v>1609</v>
@@ -30762,7 +30762,7 @@
         <v>1605</v>
       </c>
       <c r="E641">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F641" t="s">
         <v>1609</v>
@@ -30797,7 +30797,7 @@
         <v>1605</v>
       </c>
       <c r="E642">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F642" t="s">
         <v>1609</v>
@@ -30832,7 +30832,7 @@
         <v>1605</v>
       </c>
       <c r="E643">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F643" t="s">
         <v>1609</v>
@@ -30867,7 +30867,7 @@
         <v>1605</v>
       </c>
       <c r="E644">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F644" t="s">
         <v>1609</v>
@@ -30902,7 +30902,7 @@
         <v>1605</v>
       </c>
       <c r="E645">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F645" t="s">
         <v>1611</v>
@@ -30940,7 +30940,7 @@
         <v>1605</v>
       </c>
       <c r="E646">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F646" t="s">
         <v>1609</v>
@@ -30975,7 +30975,7 @@
         <v>1605</v>
       </c>
       <c r="E647">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F647" t="s">
         <v>1609</v>
@@ -31010,7 +31010,7 @@
         <v>1605</v>
       </c>
       <c r="E648">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F648" t="s">
         <v>1609</v>
@@ -31045,7 +31045,7 @@
         <v>1605</v>
       </c>
       <c r="E649">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F649" t="s">
         <v>1609</v>
@@ -31080,7 +31080,7 @@
         <v>1605</v>
       </c>
       <c r="E650">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F650" t="s">
         <v>1609</v>
@@ -31115,7 +31115,7 @@
         <v>1605</v>
       </c>
       <c r="E651">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F651" t="s">
         <v>1608</v>
@@ -31150,7 +31150,7 @@
         <v>1605</v>
       </c>
       <c r="E652">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F652" t="s">
         <v>1609</v>
@@ -31185,7 +31185,7 @@
         <v>1606</v>
       </c>
       <c r="E653">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F653" t="s">
         <v>1611</v>
@@ -31223,7 +31223,7 @@
         <v>1606</v>
       </c>
       <c r="E654">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F654" t="s">
         <v>1609</v>
@@ -31258,7 +31258,7 @@
         <v>1606</v>
       </c>
       <c r="E655">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F655" t="s">
         <v>1609</v>
@@ -31293,7 +31293,7 @@
         <v>1606</v>
       </c>
       <c r="E656">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F656" t="s">
         <v>1609</v>
@@ -31328,7 +31328,7 @@
         <v>1606</v>
       </c>
       <c r="E657">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F657" t="s">
         <v>1609</v>
@@ -31363,7 +31363,7 @@
         <v>1606</v>
       </c>
       <c r="E658">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F658" t="s">
         <v>1609</v>
@@ -31398,7 +31398,7 @@
         <v>1606</v>
       </c>
       <c r="E659">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F659" t="s">
         <v>1609</v>
@@ -31433,7 +31433,7 @@
         <v>1606</v>
       </c>
       <c r="E660">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F660" t="s">
         <v>1609</v>
@@ -31468,7 +31468,7 @@
         <v>1606</v>
       </c>
       <c r="E661">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F661" t="s">
         <v>1609</v>
@@ -31506,7 +31506,7 @@
         <v>1606</v>
       </c>
       <c r="E662">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F662" t="s">
         <v>1609</v>
@@ -31541,7 +31541,7 @@
         <v>1606</v>
       </c>
       <c r="E663">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F663" t="s">
         <v>1611</v>
@@ -31576,7 +31576,7 @@
         <v>1606</v>
       </c>
       <c r="E664">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F664" t="s">
         <v>1609</v>
@@ -31611,7 +31611,7 @@
         <v>1606</v>
       </c>
       <c r="E665">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F665" t="s">
         <v>1609</v>
@@ -31646,7 +31646,7 @@
         <v>1607</v>
       </c>
       <c r="E666">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F666" t="s">
         <v>1609</v>
@@ -31681,7 +31681,7 @@
         <v>1607</v>
       </c>
       <c r="E667">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F667" t="s">
         <v>1609</v>
@@ -31716,7 +31716,7 @@
         <v>1607</v>
       </c>
       <c r="E668">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F668" t="s">
         <v>1609</v>
@@ -31751,7 +31751,7 @@
         <v>1607</v>
       </c>
       <c r="E669">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F669" t="s">
         <v>1609</v>
@@ -31786,7 +31786,7 @@
         <v>1607</v>
       </c>
       <c r="E670">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F670" t="s">
         <v>1609</v>
@@ -31821,7 +31821,7 @@
         <v>1607</v>
       </c>
       <c r="E671">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F671" t="s">
         <v>1609</v>
@@ -31856,7 +31856,7 @@
         <v>1607</v>
       </c>
       <c r="E672">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F672" t="s">
         <v>1609</v>
@@ -31891,7 +31891,7 @@
         <v>1607</v>
       </c>
       <c r="E673">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F673" t="s">
         <v>1609</v>
@@ -31929,7 +31929,7 @@
         <v>1607</v>
       </c>
       <c r="E674">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F674" t="s">
         <v>1609</v>
@@ -31964,7 +31964,7 @@
         <v>1607</v>
       </c>
       <c r="E675">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F675" t="s">
         <v>1609</v>
@@ -31999,7 +31999,7 @@
         <v>1607</v>
       </c>
       <c r="E676">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F676" t="s">
         <v>1609</v>

--- a/BacklogGATEAutoCompleto.xlsx
+++ b/BacklogGATEAutoCompleto.xlsx
@@ -8328,7 +8328,7 @@
         <v>1391</v>
       </c>
       <c r="E2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="F2" t="s">
         <v>1608</v>
@@ -8363,7 +8363,7 @@
         <v>1392</v>
       </c>
       <c r="E3">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="F3" t="s">
         <v>1609</v>
@@ -8398,7 +8398,7 @@
         <v>1393</v>
       </c>
       <c r="E4">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="F4" t="s">
         <v>1609</v>
@@ -8433,7 +8433,7 @@
         <v>1394</v>
       </c>
       <c r="E5">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="F5" t="s">
         <v>1609</v>
@@ -8468,7 +8468,7 @@
         <v>1395</v>
       </c>
       <c r="E6">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="F6" t="s">
         <v>1609</v>
@@ -8503,7 +8503,7 @@
         <v>1396</v>
       </c>
       <c r="E7">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="F7" t="s">
         <v>1609</v>
@@ -8538,7 +8538,7 @@
         <v>1396</v>
       </c>
       <c r="E8">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="F8" t="s">
         <v>1609</v>
@@ -8573,7 +8573,7 @@
         <v>1397</v>
       </c>
       <c r="E9">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="F9" t="s">
         <v>1609</v>
@@ -8608,7 +8608,7 @@
         <v>1398</v>
       </c>
       <c r="E10">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="F10" t="s">
         <v>1609</v>
@@ -8643,7 +8643,7 @@
         <v>1399</v>
       </c>
       <c r="E11">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="F11" t="s">
         <v>1609</v>
@@ -8678,7 +8678,7 @@
         <v>1400</v>
       </c>
       <c r="E12">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="F12" t="s">
         <v>1609</v>
@@ -8713,7 +8713,7 @@
         <v>1401</v>
       </c>
       <c r="E13">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="F13" t="s">
         <v>1609</v>
@@ -8748,7 +8748,7 @@
         <v>1402</v>
       </c>
       <c r="E14">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="F14" t="s">
         <v>1609</v>
@@ -8783,7 +8783,7 @@
         <v>1403</v>
       </c>
       <c r="E15">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F15" t="s">
         <v>1609</v>
@@ -8818,7 +8818,7 @@
         <v>1403</v>
       </c>
       <c r="E16">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F16" t="s">
         <v>1609</v>
@@ -8853,7 +8853,7 @@
         <v>1404</v>
       </c>
       <c r="E17">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="F17" t="s">
         <v>1609</v>
@@ -8888,7 +8888,7 @@
         <v>1405</v>
       </c>
       <c r="E18">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="F18" t="s">
         <v>1609</v>
@@ -8923,7 +8923,7 @@
         <v>1406</v>
       </c>
       <c r="E19">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="F19" t="s">
         <v>1609</v>
@@ -8958,7 +8958,7 @@
         <v>1406</v>
       </c>
       <c r="E20">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="F20" t="s">
         <v>1609</v>
@@ -8993,7 +8993,7 @@
         <v>1407</v>
       </c>
       <c r="E21">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="F21" t="s">
         <v>1609</v>
@@ -9028,7 +9028,7 @@
         <v>1408</v>
       </c>
       <c r="E22">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="F22" t="s">
         <v>1609</v>
@@ -9063,7 +9063,7 @@
         <v>1409</v>
       </c>
       <c r="E23">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="F23" t="s">
         <v>1609</v>
@@ -9098,7 +9098,7 @@
         <v>1409</v>
       </c>
       <c r="E24">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="F24" t="s">
         <v>1609</v>
@@ -9133,7 +9133,7 @@
         <v>1410</v>
       </c>
       <c r="E25">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="F25" t="s">
         <v>1609</v>
@@ -9168,7 +9168,7 @@
         <v>1411</v>
       </c>
       <c r="E26">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="F26" t="s">
         <v>1609</v>
@@ -9203,7 +9203,7 @@
         <v>1412</v>
       </c>
       <c r="E27">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="F27" t="s">
         <v>1609</v>
@@ -9238,7 +9238,7 @@
         <v>1413</v>
       </c>
       <c r="E28">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="F28" t="s">
         <v>1609</v>
@@ -9273,7 +9273,7 @@
         <v>1414</v>
       </c>
       <c r="E29">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F29" t="s">
         <v>1609</v>
@@ -9311,7 +9311,7 @@
         <v>1415</v>
       </c>
       <c r="E30">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="F30" t="s">
         <v>1609</v>
@@ -9346,7 +9346,7 @@
         <v>1416</v>
       </c>
       <c r="E31">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F31" t="s">
         <v>1609</v>
@@ -9381,7 +9381,7 @@
         <v>1417</v>
       </c>
       <c r="E32">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F32" t="s">
         <v>1609</v>
@@ -9416,7 +9416,7 @@
         <v>1418</v>
       </c>
       <c r="E33">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F33" t="s">
         <v>1609</v>
@@ -9451,7 +9451,7 @@
         <v>1418</v>
       </c>
       <c r="E34">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F34" t="s">
         <v>1609</v>
@@ -9486,7 +9486,7 @@
         <v>1419</v>
       </c>
       <c r="E35">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F35" t="s">
         <v>1609</v>
@@ -9521,7 +9521,7 @@
         <v>1420</v>
       </c>
       <c r="E36">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F36" t="s">
         <v>1609</v>
@@ -9556,7 +9556,7 @@
         <v>1421</v>
       </c>
       <c r="E37">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F37" t="s">
         <v>1609</v>
@@ -9591,7 +9591,7 @@
         <v>1422</v>
       </c>
       <c r="E38">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F38" t="s">
         <v>1609</v>
@@ -9626,7 +9626,7 @@
         <v>1423</v>
       </c>
       <c r="E39">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F39" t="s">
         <v>1609</v>
@@ -9661,7 +9661,7 @@
         <v>1424</v>
       </c>
       <c r="E40">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F40" t="s">
         <v>1609</v>
@@ -9696,7 +9696,7 @@
         <v>1425</v>
       </c>
       <c r="E41">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F41" t="s">
         <v>1609</v>
@@ -9731,7 +9731,7 @@
         <v>1426</v>
       </c>
       <c r="E42">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F42" t="s">
         <v>1609</v>
@@ -9766,7 +9766,7 @@
         <v>1426</v>
       </c>
       <c r="E43">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F43" t="s">
         <v>1609</v>
@@ -9801,7 +9801,7 @@
         <v>1427</v>
       </c>
       <c r="E44">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F44" t="s">
         <v>1609</v>
@@ -9836,7 +9836,7 @@
         <v>1427</v>
       </c>
       <c r="E45">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F45" t="s">
         <v>1609</v>
@@ -9871,7 +9871,7 @@
         <v>1428</v>
       </c>
       <c r="E46">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F46" t="s">
         <v>1609</v>
@@ -9906,7 +9906,7 @@
         <v>1429</v>
       </c>
       <c r="E47">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F47" t="s">
         <v>1609</v>
@@ -9941,7 +9941,7 @@
         <v>1430</v>
       </c>
       <c r="E48">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F48" t="s">
         <v>1609</v>
@@ -9976,7 +9976,7 @@
         <v>1431</v>
       </c>
       <c r="E49">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F49" t="s">
         <v>1609</v>
@@ -10011,7 +10011,7 @@
         <v>1432</v>
       </c>
       <c r="E50">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F50" t="s">
         <v>1609</v>
@@ -10046,7 +10046,7 @@
         <v>1432</v>
       </c>
       <c r="E51">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F51" t="s">
         <v>1609</v>
@@ -10081,7 +10081,7 @@
         <v>1433</v>
       </c>
       <c r="E52">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F52" t="s">
         <v>1609</v>
@@ -10116,7 +10116,7 @@
         <v>1434</v>
       </c>
       <c r="E53">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F53" t="s">
         <v>1609</v>
@@ -10151,7 +10151,7 @@
         <v>1435</v>
       </c>
       <c r="E54">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F54" t="s">
         <v>1609</v>
@@ -10186,7 +10186,7 @@
         <v>1435</v>
       </c>
       <c r="E55">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F55" t="s">
         <v>1609</v>
@@ -10221,7 +10221,7 @@
         <v>1436</v>
       </c>
       <c r="E56">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F56" t="s">
         <v>1609</v>
@@ -10256,7 +10256,7 @@
         <v>1436</v>
       </c>
       <c r="E57">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F57" t="s">
         <v>1609</v>
@@ -10291,7 +10291,7 @@
         <v>1437</v>
       </c>
       <c r="E58">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F58" t="s">
         <v>1609</v>
@@ -10326,7 +10326,7 @@
         <v>1438</v>
       </c>
       <c r="E59">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F59" t="s">
         <v>1609</v>
@@ -10361,7 +10361,7 @@
         <v>1439</v>
       </c>
       <c r="E60">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F60" t="s">
         <v>1609</v>
@@ -10396,7 +10396,7 @@
         <v>1440</v>
       </c>
       <c r="E61">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F61" t="s">
         <v>1609</v>
@@ -10431,7 +10431,7 @@
         <v>1441</v>
       </c>
       <c r="E62">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F62" t="s">
         <v>1609</v>
@@ -10466,7 +10466,7 @@
         <v>1441</v>
       </c>
       <c r="E63">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F63" t="s">
         <v>1609</v>
@@ -10501,7 +10501,7 @@
         <v>1442</v>
       </c>
       <c r="E64">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F64" t="s">
         <v>1609</v>
@@ -10536,7 +10536,7 @@
         <v>1442</v>
       </c>
       <c r="E65">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F65" t="s">
         <v>1609</v>
@@ -10571,7 +10571,7 @@
         <v>1443</v>
       </c>
       <c r="E66">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F66" t="s">
         <v>1609</v>
@@ -10606,7 +10606,7 @@
         <v>1444</v>
       </c>
       <c r="E67">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F67" t="s">
         <v>1609</v>
@@ -10641,7 +10641,7 @@
         <v>1445</v>
       </c>
       <c r="E68">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F68" t="s">
         <v>1609</v>
@@ -10676,7 +10676,7 @@
         <v>1446</v>
       </c>
       <c r="E69">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F69" t="s">
         <v>1609</v>
@@ -10711,7 +10711,7 @@
         <v>1447</v>
       </c>
       <c r="E70">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F70" t="s">
         <v>1609</v>
@@ -10746,7 +10746,7 @@
         <v>1448</v>
       </c>
       <c r="E71">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F71" t="s">
         <v>1609</v>
@@ -10781,7 +10781,7 @@
         <v>1449</v>
       </c>
       <c r="E72">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F72" t="s">
         <v>1609</v>
@@ -10816,7 +10816,7 @@
         <v>1450</v>
       </c>
       <c r="E73">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F73" t="s">
         <v>1609</v>
@@ -10851,7 +10851,7 @@
         <v>1451</v>
       </c>
       <c r="E74">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F74" t="s">
         <v>1609</v>
@@ -10886,7 +10886,7 @@
         <v>1452</v>
       </c>
       <c r="E75">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F75" t="s">
         <v>1609</v>
@@ -10921,7 +10921,7 @@
         <v>1453</v>
       </c>
       <c r="E76">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F76" t="s">
         <v>1609</v>
@@ -10956,7 +10956,7 @@
         <v>1454</v>
       </c>
       <c r="E77">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F77" t="s">
         <v>1609</v>
@@ -10991,7 +10991,7 @@
         <v>1454</v>
       </c>
       <c r="E78">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F78" t="s">
         <v>1609</v>
@@ -11026,7 +11026,7 @@
         <v>1454</v>
       </c>
       <c r="E79">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F79" t="s">
         <v>1609</v>
@@ -11061,7 +11061,7 @@
         <v>1455</v>
       </c>
       <c r="E80">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F80" t="s">
         <v>1609</v>
@@ -11096,7 +11096,7 @@
         <v>1456</v>
       </c>
       <c r="E81">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F81" t="s">
         <v>1609</v>
@@ -11131,7 +11131,7 @@
         <v>1457</v>
       </c>
       <c r="E82">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F82" t="s">
         <v>1609</v>
@@ -11166,7 +11166,7 @@
         <v>1457</v>
       </c>
       <c r="E83">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F83" t="s">
         <v>1609</v>
@@ -11201,7 +11201,7 @@
         <v>1457</v>
       </c>
       <c r="E84">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F84" t="s">
         <v>1609</v>
@@ -11236,7 +11236,7 @@
         <v>1458</v>
       </c>
       <c r="E85">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F85" t="s">
         <v>1609</v>
@@ -11271,7 +11271,7 @@
         <v>1459</v>
       </c>
       <c r="E86">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F86" t="s">
         <v>1609</v>
@@ -11306,7 +11306,7 @@
         <v>1460</v>
       </c>
       <c r="E87">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F87" t="s">
         <v>1609</v>
@@ -11341,7 +11341,7 @@
         <v>1460</v>
       </c>
       <c r="E88">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F88" t="s">
         <v>1609</v>
@@ -11376,7 +11376,7 @@
         <v>1460</v>
       </c>
       <c r="E89">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F89" t="s">
         <v>1609</v>
@@ -11411,7 +11411,7 @@
         <v>1461</v>
       </c>
       <c r="E90">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F90" t="s">
         <v>1609</v>
@@ -11446,7 +11446,7 @@
         <v>1462</v>
       </c>
       <c r="E91">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F91" t="s">
         <v>1609</v>
@@ -11481,7 +11481,7 @@
         <v>1462</v>
       </c>
       <c r="E92">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F92" t="s">
         <v>1609</v>
@@ -11516,7 +11516,7 @@
         <v>1462</v>
       </c>
       <c r="E93">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F93" t="s">
         <v>1610</v>
@@ -11551,7 +11551,7 @@
         <v>1462</v>
       </c>
       <c r="E94">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F94" t="s">
         <v>1609</v>
@@ -11586,7 +11586,7 @@
         <v>1463</v>
       </c>
       <c r="E95">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F95" t="s">
         <v>1609</v>
@@ -11621,7 +11621,7 @@
         <v>1464</v>
       </c>
       <c r="E96">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F96" t="s">
         <v>1609</v>
@@ -11656,7 +11656,7 @@
         <v>1465</v>
       </c>
       <c r="E97">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F97" t="s">
         <v>1609</v>
@@ -11691,7 +11691,7 @@
         <v>1465</v>
       </c>
       <c r="E98">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F98" t="s">
         <v>1609</v>
@@ -11726,7 +11726,7 @@
         <v>1465</v>
       </c>
       <c r="E99">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F99" t="s">
         <v>1609</v>
@@ -11761,7 +11761,7 @@
         <v>1466</v>
       </c>
       <c r="E100">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F100" t="s">
         <v>1609</v>
@@ -11796,7 +11796,7 @@
         <v>1467</v>
       </c>
       <c r="E101">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F101" t="s">
         <v>1609</v>
@@ -11831,7 +11831,7 @@
         <v>1468</v>
       </c>
       <c r="E102">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F102" t="s">
         <v>1609</v>
@@ -11866,7 +11866,7 @@
         <v>1469</v>
       </c>
       <c r="E103">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F103" t="s">
         <v>1609</v>
@@ -11901,7 +11901,7 @@
         <v>1470</v>
       </c>
       <c r="E104">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F104" t="s">
         <v>1609</v>
@@ -11936,7 +11936,7 @@
         <v>1470</v>
       </c>
       <c r="E105">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F105" t="s">
         <v>1609</v>
@@ -11971,7 +11971,7 @@
         <v>1470</v>
       </c>
       <c r="E106">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F106" t="s">
         <v>1609</v>
@@ -12006,7 +12006,7 @@
         <v>1470</v>
       </c>
       <c r="E107">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F107" t="s">
         <v>1609</v>
@@ -12041,7 +12041,7 @@
         <v>1470</v>
       </c>
       <c r="E108">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F108" t="s">
         <v>1609</v>
@@ -12076,7 +12076,7 @@
         <v>1470</v>
       </c>
       <c r="E109">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F109" t="s">
         <v>1609</v>
@@ -12111,7 +12111,7 @@
         <v>1470</v>
       </c>
       <c r="E110">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F110" t="s">
         <v>1609</v>
@@ -12146,7 +12146,7 @@
         <v>1471</v>
       </c>
       <c r="E111">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F111" t="s">
         <v>1609</v>
@@ -12181,7 +12181,7 @@
         <v>1471</v>
       </c>
       <c r="E112">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F112" t="s">
         <v>1609</v>
@@ -12216,7 +12216,7 @@
         <v>1472</v>
       </c>
       <c r="E113">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F113" t="s">
         <v>1609</v>
@@ -12251,7 +12251,7 @@
         <v>1473</v>
       </c>
       <c r="E114">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F114" t="s">
         <v>1609</v>
@@ -12286,7 +12286,7 @@
         <v>1473</v>
       </c>
       <c r="E115">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F115" t="s">
         <v>1609</v>
@@ -12321,7 +12321,7 @@
         <v>1474</v>
       </c>
       <c r="E116">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F116" t="s">
         <v>1609</v>
@@ -12356,7 +12356,7 @@
         <v>1474</v>
       </c>
       <c r="E117">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F117" t="s">
         <v>1611</v>
@@ -12391,7 +12391,7 @@
         <v>1475</v>
       </c>
       <c r="E118">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F118" t="s">
         <v>1609</v>
@@ -12426,7 +12426,7 @@
         <v>1476</v>
       </c>
       <c r="E119">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F119" t="s">
         <v>1609</v>
@@ -12461,7 +12461,7 @@
         <v>1477</v>
       </c>
       <c r="E120">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F120" t="s">
         <v>1609</v>
@@ -12496,7 +12496,7 @@
         <v>1477</v>
       </c>
       <c r="E121">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F121" t="s">
         <v>1609</v>
@@ -12531,7 +12531,7 @@
         <v>1478</v>
       </c>
       <c r="E122">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F122" t="s">
         <v>1609</v>
@@ -12566,7 +12566,7 @@
         <v>1479</v>
       </c>
       <c r="E123">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F123" t="s">
         <v>1609</v>
@@ -12601,7 +12601,7 @@
         <v>1480</v>
       </c>
       <c r="E124">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F124" t="s">
         <v>1609</v>
@@ -12636,7 +12636,7 @@
         <v>1480</v>
       </c>
       <c r="E125">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F125" t="s">
         <v>1609</v>
@@ -12671,7 +12671,7 @@
         <v>1481</v>
       </c>
       <c r="E126">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F126" t="s">
         <v>1609</v>
@@ -12706,7 +12706,7 @@
         <v>1482</v>
       </c>
       <c r="E127">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F127" t="s">
         <v>1609</v>
@@ -12741,7 +12741,7 @@
         <v>1482</v>
       </c>
       <c r="E128">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F128" t="s">
         <v>1609</v>
@@ -12776,7 +12776,7 @@
         <v>1483</v>
       </c>
       <c r="E129">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F129" t="s">
         <v>1609</v>
@@ -12811,7 +12811,7 @@
         <v>1483</v>
       </c>
       <c r="E130">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F130" t="s">
         <v>1609</v>
@@ -12846,7 +12846,7 @@
         <v>1483</v>
       </c>
       <c r="E131">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F131" t="s">
         <v>1609</v>
@@ -12881,7 +12881,7 @@
         <v>1483</v>
       </c>
       <c r="E132">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F132" t="s">
         <v>1609</v>
@@ -12916,7 +12916,7 @@
         <v>1484</v>
       </c>
       <c r="E133">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F133" t="s">
         <v>1609</v>
@@ -12951,7 +12951,7 @@
         <v>1484</v>
       </c>
       <c r="E134">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F134" t="s">
         <v>1609</v>
@@ -12986,7 +12986,7 @@
         <v>1484</v>
       </c>
       <c r="E135">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F135" t="s">
         <v>1609</v>
@@ -13021,7 +13021,7 @@
         <v>1484</v>
       </c>
       <c r="E136">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F136" t="s">
         <v>1609</v>
@@ -13056,7 +13056,7 @@
         <v>1484</v>
       </c>
       <c r="E137">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F137" t="s">
         <v>1609</v>
@@ -13091,7 +13091,7 @@
         <v>1484</v>
       </c>
       <c r="E138">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F138" t="s">
         <v>1609</v>
@@ -13126,7 +13126,7 @@
         <v>1485</v>
       </c>
       <c r="E139">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F139" t="s">
         <v>1609</v>
@@ -13161,7 +13161,7 @@
         <v>1485</v>
       </c>
       <c r="E140">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F140" t="s">
         <v>1609</v>
@@ -13196,7 +13196,7 @@
         <v>1486</v>
       </c>
       <c r="E141">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F141" t="s">
         <v>1609</v>
@@ -13231,7 +13231,7 @@
         <v>1486</v>
       </c>
       <c r="E142">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F142" t="s">
         <v>1609</v>
@@ -13266,7 +13266,7 @@
         <v>1487</v>
       </c>
       <c r="E143">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F143" t="s">
         <v>1609</v>
@@ -13301,7 +13301,7 @@
         <v>1488</v>
       </c>
       <c r="E144">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F144" t="s">
         <v>1609</v>
@@ -13336,7 +13336,7 @@
         <v>1488</v>
       </c>
       <c r="E145">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F145" t="s">
         <v>1609</v>
@@ -13371,7 +13371,7 @@
         <v>1488</v>
       </c>
       <c r="E146">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F146" t="s">
         <v>1609</v>
@@ -13406,7 +13406,7 @@
         <v>1489</v>
       </c>
       <c r="E147">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F147" t="s">
         <v>1609</v>
@@ -13441,7 +13441,7 @@
         <v>1489</v>
       </c>
       <c r="E148">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F148" t="s">
         <v>1609</v>
@@ -13476,7 +13476,7 @@
         <v>1489</v>
       </c>
       <c r="E149">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F149" t="s">
         <v>1609</v>
@@ -13511,7 +13511,7 @@
         <v>1490</v>
       </c>
       <c r="E150">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F150" t="s">
         <v>1609</v>
@@ -13546,7 +13546,7 @@
         <v>1490</v>
       </c>
       <c r="E151">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F151" t="s">
         <v>1609</v>
@@ -13581,7 +13581,7 @@
         <v>1490</v>
       </c>
       <c r="E152">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F152" t="s">
         <v>1609</v>
@@ -13616,7 +13616,7 @@
         <v>1491</v>
       </c>
       <c r="E153">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F153" t="s">
         <v>1609</v>
@@ -13651,7 +13651,7 @@
         <v>1491</v>
       </c>
       <c r="E154">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F154" t="s">
         <v>1609</v>
@@ -13686,7 +13686,7 @@
         <v>1492</v>
       </c>
       <c r="E155">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F155" t="s">
         <v>1609</v>
@@ -13721,7 +13721,7 @@
         <v>1493</v>
       </c>
       <c r="E156">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F156" t="s">
         <v>1609</v>
@@ -13756,7 +13756,7 @@
         <v>1493</v>
       </c>
       <c r="E157">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F157" t="s">
         <v>1609</v>
@@ -13791,7 +13791,7 @@
         <v>1493</v>
       </c>
       <c r="E158">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F158" t="s">
         <v>1609</v>
@@ -13826,7 +13826,7 @@
         <v>1494</v>
       </c>
       <c r="E159">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F159" t="s">
         <v>1609</v>
@@ -13861,7 +13861,7 @@
         <v>1494</v>
       </c>
       <c r="E160">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F160" t="s">
         <v>1609</v>
@@ -13896,7 +13896,7 @@
         <v>1495</v>
       </c>
       <c r="E161">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F161" t="s">
         <v>1609</v>
@@ -13934,7 +13934,7 @@
         <v>1495</v>
       </c>
       <c r="E162">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F162" t="s">
         <v>1609</v>
@@ -13969,7 +13969,7 @@
         <v>1495</v>
       </c>
       <c r="E163">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F163" t="s">
         <v>1609</v>
@@ -14004,7 +14004,7 @@
         <v>1495</v>
       </c>
       <c r="E164">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F164" t="s">
         <v>1609</v>
@@ -14039,7 +14039,7 @@
         <v>1495</v>
       </c>
       <c r="E165">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F165" t="s">
         <v>1609</v>
@@ -14074,7 +14074,7 @@
         <v>1495</v>
       </c>
       <c r="E166">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F166" t="s">
         <v>1609</v>
@@ -14109,7 +14109,7 @@
         <v>1496</v>
       </c>
       <c r="E167">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F167" t="s">
         <v>1609</v>
@@ -14144,7 +14144,7 @@
         <v>1497</v>
       </c>
       <c r="E168">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F168" t="s">
         <v>1609</v>
@@ -14179,7 +14179,7 @@
         <v>1498</v>
       </c>
       <c r="E169">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F169" t="s">
         <v>1610</v>
@@ -14214,7 +14214,7 @@
         <v>1499</v>
       </c>
       <c r="E170">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F170" t="s">
         <v>1609</v>
@@ -14249,7 +14249,7 @@
         <v>1499</v>
       </c>
       <c r="E171">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F171" t="s">
         <v>1609</v>
@@ -14284,7 +14284,7 @@
         <v>1499</v>
       </c>
       <c r="E172">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F172" t="s">
         <v>1609</v>
@@ -14319,7 +14319,7 @@
         <v>1499</v>
       </c>
       <c r="E173">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F173" t="s">
         <v>1609</v>
@@ -14354,7 +14354,7 @@
         <v>1500</v>
       </c>
       <c r="E174">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F174" t="s">
         <v>1609</v>
@@ -14389,7 +14389,7 @@
         <v>1500</v>
       </c>
       <c r="E175">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F175" t="s">
         <v>1609</v>
@@ -14424,7 +14424,7 @@
         <v>1500</v>
       </c>
       <c r="E176">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F176" t="s">
         <v>1609</v>
@@ -14459,7 +14459,7 @@
         <v>1500</v>
       </c>
       <c r="E177">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F177" t="s">
         <v>1609</v>
@@ -14494,7 +14494,7 @@
         <v>1500</v>
       </c>
       <c r="E178">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F178" t="s">
         <v>1609</v>
@@ -14529,7 +14529,7 @@
         <v>1500</v>
       </c>
       <c r="E179">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F179" t="s">
         <v>1609</v>
@@ -14564,7 +14564,7 @@
         <v>1500</v>
       </c>
       <c r="E180">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F180" t="s">
         <v>1609</v>
@@ -14599,7 +14599,7 @@
         <v>1501</v>
       </c>
       <c r="E181">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F181" t="s">
         <v>1609</v>
@@ -14634,7 +14634,7 @@
         <v>1501</v>
       </c>
       <c r="E182">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F182" t="s">
         <v>1609</v>
@@ -14669,7 +14669,7 @@
         <v>1502</v>
       </c>
       <c r="E183">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F183" t="s">
         <v>1609</v>
@@ -14704,7 +14704,7 @@
         <v>1502</v>
       </c>
       <c r="E184">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F184" t="s">
         <v>1609</v>
@@ -14739,7 +14739,7 @@
         <v>1502</v>
       </c>
       <c r="E185">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F185" t="s">
         <v>1609</v>
@@ -14774,7 +14774,7 @@
         <v>1503</v>
       </c>
       <c r="E186">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F186" t="s">
         <v>1609</v>
@@ -14809,7 +14809,7 @@
         <v>1503</v>
       </c>
       <c r="E187">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F187" t="s">
         <v>1609</v>
@@ -14844,7 +14844,7 @@
         <v>1503</v>
       </c>
       <c r="E188">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F188" t="s">
         <v>1609</v>
@@ -14879,7 +14879,7 @@
         <v>1503</v>
       </c>
       <c r="E189">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F189" t="s">
         <v>1609</v>
@@ -14914,7 +14914,7 @@
         <v>1504</v>
       </c>
       <c r="E190">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F190" t="s">
         <v>1609</v>
@@ -14949,7 +14949,7 @@
         <v>1504</v>
       </c>
       <c r="E191">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F191" t="s">
         <v>1609</v>
@@ -14984,7 +14984,7 @@
         <v>1504</v>
       </c>
       <c r="E192">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F192" t="s">
         <v>1609</v>
@@ -15019,7 +15019,7 @@
         <v>1504</v>
       </c>
       <c r="E193">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F193" t="s">
         <v>1609</v>
@@ -15054,7 +15054,7 @@
         <v>1504</v>
       </c>
       <c r="E194">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F194" t="s">
         <v>1609</v>
@@ -15089,7 +15089,7 @@
         <v>1504</v>
       </c>
       <c r="E195">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F195" t="s">
         <v>1609</v>
@@ -15124,7 +15124,7 @@
         <v>1504</v>
       </c>
       <c r="E196">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F196" t="s">
         <v>1609</v>
@@ -15159,7 +15159,7 @@
         <v>1504</v>
       </c>
       <c r="E197">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F197" t="s">
         <v>1609</v>
@@ -15194,7 +15194,7 @@
         <v>1504</v>
       </c>
       <c r="E198">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F198" t="s">
         <v>1609</v>
@@ -15229,7 +15229,7 @@
         <v>1504</v>
       </c>
       <c r="E199">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F199" t="s">
         <v>1609</v>
@@ -15264,7 +15264,7 @@
         <v>1505</v>
       </c>
       <c r="E200">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F200" t="s">
         <v>1609</v>
@@ -15299,7 +15299,7 @@
         <v>1505</v>
       </c>
       <c r="E201">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F201" t="s">
         <v>1609</v>
@@ -15334,7 +15334,7 @@
         <v>1505</v>
       </c>
       <c r="E202">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F202" t="s">
         <v>1609</v>
@@ -15369,7 +15369,7 @@
         <v>1505</v>
       </c>
       <c r="E203">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F203" t="s">
         <v>1612</v>
@@ -15404,7 +15404,7 @@
         <v>1506</v>
       </c>
       <c r="E204">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F204" t="s">
         <v>1609</v>
@@ -15439,7 +15439,7 @@
         <v>1506</v>
       </c>
       <c r="E205">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F205" t="s">
         <v>1610</v>
@@ -15474,7 +15474,7 @@
         <v>1506</v>
       </c>
       <c r="E206">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F206" t="s">
         <v>1609</v>
@@ -15509,7 +15509,7 @@
         <v>1507</v>
       </c>
       <c r="E207">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F207" t="s">
         <v>1609</v>
@@ -15544,7 +15544,7 @@
         <v>1507</v>
       </c>
       <c r="E208">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F208" t="s">
         <v>1609</v>
@@ -15579,7 +15579,7 @@
         <v>1508</v>
       </c>
       <c r="E209">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F209" t="s">
         <v>1609</v>
@@ -15614,7 +15614,7 @@
         <v>1508</v>
       </c>
       <c r="E210">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F210" t="s">
         <v>1609</v>
@@ -15649,7 +15649,7 @@
         <v>1509</v>
       </c>
       <c r="E211">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F211" t="s">
         <v>1609</v>
@@ -15684,7 +15684,7 @@
         <v>1509</v>
       </c>
       <c r="E212">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F212" t="s">
         <v>1609</v>
@@ -15719,7 +15719,7 @@
         <v>1509</v>
       </c>
       <c r="E213">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F213" t="s">
         <v>1609</v>
@@ -15754,7 +15754,7 @@
         <v>1510</v>
       </c>
       <c r="E214">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F214" t="s">
         <v>1609</v>
@@ -15789,7 +15789,7 @@
         <v>1510</v>
       </c>
       <c r="E215">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F215" t="s">
         <v>1609</v>
@@ -15824,7 +15824,7 @@
         <v>1510</v>
       </c>
       <c r="E216">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F216" t="s">
         <v>1609</v>
@@ -15859,7 +15859,7 @@
         <v>1510</v>
       </c>
       <c r="E217">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F217" t="s">
         <v>1609</v>
@@ -15894,7 +15894,7 @@
         <v>1510</v>
       </c>
       <c r="E218">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F218" t="s">
         <v>1609</v>
@@ -15929,7 +15929,7 @@
         <v>1510</v>
       </c>
       <c r="E219">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F219" t="s">
         <v>1609</v>
@@ -15964,7 +15964,7 @@
         <v>1511</v>
       </c>
       <c r="E220">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F220" t="s">
         <v>1609</v>
@@ -15999,7 +15999,7 @@
         <v>1511</v>
       </c>
       <c r="E221">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F221" t="s">
         <v>1609</v>
@@ -16034,7 +16034,7 @@
         <v>1512</v>
       </c>
       <c r="E222">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F222" t="s">
         <v>1609</v>
@@ -16069,7 +16069,7 @@
         <v>1513</v>
       </c>
       <c r="E223">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F223" t="s">
         <v>1609</v>
@@ -16104,7 +16104,7 @@
         <v>1513</v>
       </c>
       <c r="E224">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F224" t="s">
         <v>1609</v>
@@ -16139,7 +16139,7 @@
         <v>1513</v>
       </c>
       <c r="E225">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F225" t="s">
         <v>1609</v>
@@ -16174,7 +16174,7 @@
         <v>1513</v>
       </c>
       <c r="E226">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F226" t="s">
         <v>1609</v>
@@ -16209,7 +16209,7 @@
         <v>1514</v>
       </c>
       <c r="E227">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F227" t="s">
         <v>1609</v>
@@ -16244,7 +16244,7 @@
         <v>1515</v>
       </c>
       <c r="E228">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F228" t="s">
         <v>1609</v>
@@ -16279,7 +16279,7 @@
         <v>1515</v>
       </c>
       <c r="E229">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F229" t="s">
         <v>1609</v>
@@ -16314,7 +16314,7 @@
         <v>1515</v>
       </c>
       <c r="E230">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F230" t="s">
         <v>1609</v>
@@ -16349,7 +16349,7 @@
         <v>1515</v>
       </c>
       <c r="E231">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F231" t="s">
         <v>1609</v>
@@ -16384,7 +16384,7 @@
         <v>1515</v>
       </c>
       <c r="E232">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F232" t="s">
         <v>1609</v>
@@ -16419,7 +16419,7 @@
         <v>1516</v>
       </c>
       <c r="E233">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F233" t="s">
         <v>1609</v>
@@ -16454,7 +16454,7 @@
         <v>1516</v>
       </c>
       <c r="E234">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F234" t="s">
         <v>1609</v>
@@ -16489,7 +16489,7 @@
         <v>1516</v>
       </c>
       <c r="E235">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F235" t="s">
         <v>1609</v>
@@ -16524,7 +16524,7 @@
         <v>1516</v>
       </c>
       <c r="E236">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F236" t="s">
         <v>1609</v>
@@ -16559,7 +16559,7 @@
         <v>1516</v>
       </c>
       <c r="E237">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F237" t="s">
         <v>1609</v>
@@ -16594,7 +16594,7 @@
         <v>1516</v>
       </c>
       <c r="E238">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F238" t="s">
         <v>1609</v>
@@ -16629,7 +16629,7 @@
         <v>1516</v>
       </c>
       <c r="E239">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F239" t="s">
         <v>1609</v>
@@ -16664,7 +16664,7 @@
         <v>1517</v>
       </c>
       <c r="E240">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F240" t="s">
         <v>1609</v>
@@ -16699,7 +16699,7 @@
         <v>1517</v>
       </c>
       <c r="E241">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F241" t="s">
         <v>1609</v>
@@ -16734,7 +16734,7 @@
         <v>1517</v>
       </c>
       <c r="E242">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F242" t="s">
         <v>1609</v>
@@ -16769,7 +16769,7 @@
         <v>1517</v>
       </c>
       <c r="E243">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F243" t="s">
         <v>1609</v>
@@ -16804,7 +16804,7 @@
         <v>1518</v>
       </c>
       <c r="E244">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F244" t="s">
         <v>1609</v>
@@ -16839,7 +16839,7 @@
         <v>1518</v>
       </c>
       <c r="E245">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F245" t="s">
         <v>1609</v>
@@ -16874,7 +16874,7 @@
         <v>1518</v>
       </c>
       <c r="E246">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F246" t="s">
         <v>1609</v>
@@ -16909,7 +16909,7 @@
         <v>1519</v>
       </c>
       <c r="E247">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F247" t="s">
         <v>1609</v>
@@ -16944,7 +16944,7 @@
         <v>1519</v>
       </c>
       <c r="E248">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F248" t="s">
         <v>1609</v>
@@ -16979,7 +16979,7 @@
         <v>1520</v>
       </c>
       <c r="E249">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F249" t="s">
         <v>1609</v>
@@ -17014,7 +17014,7 @@
         <v>1520</v>
       </c>
       <c r="E250">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F250" t="s">
         <v>1609</v>
@@ -17049,7 +17049,7 @@
         <v>1521</v>
       </c>
       <c r="E251">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F251" t="s">
         <v>1609</v>
@@ -17084,7 +17084,7 @@
         <v>1521</v>
       </c>
       <c r="E252">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F252" t="s">
         <v>1609</v>
@@ -17119,7 +17119,7 @@
         <v>1522</v>
       </c>
       <c r="E253">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F253" t="s">
         <v>1609</v>
@@ -17154,7 +17154,7 @@
         <v>1522</v>
       </c>
       <c r="E254">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F254" t="s">
         <v>1609</v>
@@ -17189,7 +17189,7 @@
         <v>1523</v>
       </c>
       <c r="E255">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F255" t="s">
         <v>1609</v>
@@ -17224,7 +17224,7 @@
         <v>1523</v>
       </c>
       <c r="E256">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F256" t="s">
         <v>1609</v>
@@ -17259,7 +17259,7 @@
         <v>1524</v>
       </c>
       <c r="E257">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F257" t="s">
         <v>1609</v>
@@ -17294,7 +17294,7 @@
         <v>1524</v>
       </c>
       <c r="E258">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F258" t="s">
         <v>1609</v>
@@ -17329,7 +17329,7 @@
         <v>1525</v>
       </c>
       <c r="E259">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F259" t="s">
         <v>1609</v>
@@ -17364,7 +17364,7 @@
         <v>1525</v>
       </c>
       <c r="E260">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F260" t="s">
         <v>1609</v>
@@ -17399,7 +17399,7 @@
         <v>1525</v>
       </c>
       <c r="E261">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F261" t="s">
         <v>1609</v>
@@ -17434,7 +17434,7 @@
         <v>1526</v>
       </c>
       <c r="E262">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F262" t="s">
         <v>1609</v>
@@ -17469,7 +17469,7 @@
         <v>1526</v>
       </c>
       <c r="E263">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F263" t="s">
         <v>1609</v>
@@ -17504,7 +17504,7 @@
         <v>1526</v>
       </c>
       <c r="E264">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F264" t="s">
         <v>1609</v>
@@ -17539,7 +17539,7 @@
         <v>1527</v>
       </c>
       <c r="E265">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F265" t="s">
         <v>1609</v>
@@ -17574,7 +17574,7 @@
         <v>1528</v>
       </c>
       <c r="E266">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F266" t="s">
         <v>1609</v>
@@ -17609,7 +17609,7 @@
         <v>1528</v>
       </c>
       <c r="E267">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F267" t="s">
         <v>1609</v>
@@ -17644,7 +17644,7 @@
         <v>1528</v>
       </c>
       <c r="E268">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F268" t="s">
         <v>1609</v>
@@ -17679,7 +17679,7 @@
         <v>1529</v>
       </c>
       <c r="E269">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F269" t="s">
         <v>1609</v>
@@ -17714,7 +17714,7 @@
         <v>1529</v>
       </c>
       <c r="E270">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F270" t="s">
         <v>1609</v>
@@ -17749,7 +17749,7 @@
         <v>1530</v>
       </c>
       <c r="E271">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F271" t="s">
         <v>1609</v>
@@ -17784,7 +17784,7 @@
         <v>1530</v>
       </c>
       <c r="E272">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F272" t="s">
         <v>1609</v>
@@ -17819,7 +17819,7 @@
         <v>1530</v>
       </c>
       <c r="E273">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F273" t="s">
         <v>1611</v>
@@ -17854,7 +17854,7 @@
         <v>1530</v>
       </c>
       <c r="E274">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F274" t="s">
         <v>1609</v>
@@ -17889,7 +17889,7 @@
         <v>1530</v>
       </c>
       <c r="E275">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F275" t="s">
         <v>1609</v>
@@ -17924,7 +17924,7 @@
         <v>1531</v>
       </c>
       <c r="E276">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F276" t="s">
         <v>1609</v>
@@ -17959,7 +17959,7 @@
         <v>1531</v>
       </c>
       <c r="E277">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F277" t="s">
         <v>1609</v>
@@ -17994,7 +17994,7 @@
         <v>1531</v>
       </c>
       <c r="E278">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F278" t="s">
         <v>1609</v>
@@ -18032,7 +18032,7 @@
         <v>1531</v>
       </c>
       <c r="E279">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F279" t="s">
         <v>1609</v>
@@ -18067,7 +18067,7 @@
         <v>1531</v>
       </c>
       <c r="E280">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F280" t="s">
         <v>1609</v>
@@ -18102,7 +18102,7 @@
         <v>1531</v>
       </c>
       <c r="E281">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F281" t="s">
         <v>1609</v>
@@ -18137,7 +18137,7 @@
         <v>1531</v>
       </c>
       <c r="E282">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F282" t="s">
         <v>1609</v>
@@ -18172,7 +18172,7 @@
         <v>1532</v>
       </c>
       <c r="E283">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F283" t="s">
         <v>1609</v>
@@ -18207,7 +18207,7 @@
         <v>1532</v>
       </c>
       <c r="E284">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F284" t="s">
         <v>1609</v>
@@ -18242,7 +18242,7 @@
         <v>1532</v>
       </c>
       <c r="E285">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F285" t="s">
         <v>1609</v>
@@ -18277,7 +18277,7 @@
         <v>1532</v>
       </c>
       <c r="E286">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F286" t="s">
         <v>1609</v>
@@ -18312,7 +18312,7 @@
         <v>1533</v>
       </c>
       <c r="E287">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F287" t="s">
         <v>1609</v>
@@ -18347,7 +18347,7 @@
         <v>1533</v>
       </c>
       <c r="E288">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F288" t="s">
         <v>1609</v>
@@ -18382,7 +18382,7 @@
         <v>1533</v>
       </c>
       <c r="E289">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F289" t="s">
         <v>1609</v>
@@ -18417,7 +18417,7 @@
         <v>1533</v>
       </c>
       <c r="E290">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F290" t="s">
         <v>1609</v>
@@ -18452,7 +18452,7 @@
         <v>1533</v>
       </c>
       <c r="E291">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F291" t="s">
         <v>1609</v>
@@ -18487,7 +18487,7 @@
         <v>1534</v>
       </c>
       <c r="E292">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F292" t="s">
         <v>1609</v>
@@ -18522,7 +18522,7 @@
         <v>1534</v>
       </c>
       <c r="E293">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F293" t="s">
         <v>1609</v>
@@ -18557,7 +18557,7 @@
         <v>1534</v>
       </c>
       <c r="E294">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F294" t="s">
         <v>1609</v>
@@ -18592,7 +18592,7 @@
         <v>1534</v>
       </c>
       <c r="E295">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F295" t="s">
         <v>1609</v>
@@ -18627,7 +18627,7 @@
         <v>1534</v>
       </c>
       <c r="E296">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F296" t="s">
         <v>1609</v>
@@ -18662,7 +18662,7 @@
         <v>1534</v>
       </c>
       <c r="E297">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F297" t="s">
         <v>1609</v>
@@ -18697,7 +18697,7 @@
         <v>1535</v>
       </c>
       <c r="E298">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F298" t="s">
         <v>1609</v>
@@ -18732,7 +18732,7 @@
         <v>1535</v>
       </c>
       <c r="E299">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F299" t="s">
         <v>1609</v>
@@ -18767,7 +18767,7 @@
         <v>1535</v>
       </c>
       <c r="E300">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F300" t="s">
         <v>1609</v>
@@ -18802,7 +18802,7 @@
         <v>1535</v>
       </c>
       <c r="E301">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F301" t="s">
         <v>1609</v>
@@ -18837,7 +18837,7 @@
         <v>1535</v>
       </c>
       <c r="E302">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F302" t="s">
         <v>1609</v>
@@ -18872,7 +18872,7 @@
         <v>1535</v>
       </c>
       <c r="E303">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F303" t="s">
         <v>1609</v>
@@ -18907,7 +18907,7 @@
         <v>1536</v>
       </c>
       <c r="E304">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F304" t="s">
         <v>1609</v>
@@ -18942,7 +18942,7 @@
         <v>1536</v>
       </c>
       <c r="E305">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F305" t="s">
         <v>1609</v>
@@ -18977,7 +18977,7 @@
         <v>1537</v>
       </c>
       <c r="E306">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F306" t="s">
         <v>1610</v>
@@ -19012,7 +19012,7 @@
         <v>1537</v>
       </c>
       <c r="E307">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F307" t="s">
         <v>1609</v>
@@ -19047,7 +19047,7 @@
         <v>1537</v>
       </c>
       <c r="E308">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F308" t="s">
         <v>1609</v>
@@ -19082,7 +19082,7 @@
         <v>1537</v>
       </c>
       <c r="E309">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F309" t="s">
         <v>1612</v>
@@ -19117,7 +19117,7 @@
         <v>1537</v>
       </c>
       <c r="E310">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F310" t="s">
         <v>1609</v>
@@ -19152,7 +19152,7 @@
         <v>1537</v>
       </c>
       <c r="E311">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F311" t="s">
         <v>1609</v>
@@ -19187,7 +19187,7 @@
         <v>1537</v>
       </c>
       <c r="E312">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F312" t="s">
         <v>1609</v>
@@ -19222,7 +19222,7 @@
         <v>1537</v>
       </c>
       <c r="E313">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F313" t="s">
         <v>1609</v>
@@ -19257,7 +19257,7 @@
         <v>1538</v>
       </c>
       <c r="E314">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F314" t="s">
         <v>1609</v>
@@ -19292,7 +19292,7 @@
         <v>1538</v>
       </c>
       <c r="E315">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F315" t="s">
         <v>1609</v>
@@ -19327,7 +19327,7 @@
         <v>1538</v>
       </c>
       <c r="E316">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F316" t="s">
         <v>1609</v>
@@ -19362,7 +19362,7 @@
         <v>1538</v>
       </c>
       <c r="E317">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F317" t="s">
         <v>1609</v>
@@ -19397,7 +19397,7 @@
         <v>1539</v>
       </c>
       <c r="E318">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F318" t="s">
         <v>1609</v>
@@ -19432,7 +19432,7 @@
         <v>1539</v>
       </c>
       <c r="E319">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F319" t="s">
         <v>1609</v>
@@ -19467,7 +19467,7 @@
         <v>1540</v>
       </c>
       <c r="E320">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F320" t="s">
         <v>1609</v>
@@ -19505,7 +19505,7 @@
         <v>1540</v>
       </c>
       <c r="E321">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F321" t="s">
         <v>1609</v>
@@ -19540,7 +19540,7 @@
         <v>1541</v>
       </c>
       <c r="E322">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F322" t="s">
         <v>1609</v>
@@ -19575,7 +19575,7 @@
         <v>1541</v>
       </c>
       <c r="E323">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F323" t="s">
         <v>1609</v>
@@ -19610,7 +19610,7 @@
         <v>1541</v>
       </c>
       <c r="E324">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F324" t="s">
         <v>1609</v>
@@ -19645,7 +19645,7 @@
         <v>1541</v>
       </c>
       <c r="E325">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F325" t="s">
         <v>1609</v>
@@ -19683,7 +19683,7 @@
         <v>1541</v>
       </c>
       <c r="E326">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F326" t="s">
         <v>1609</v>
@@ -19718,7 +19718,7 @@
         <v>1541</v>
       </c>
       <c r="E327">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F327" t="s">
         <v>1609</v>
@@ -19753,7 +19753,7 @@
         <v>1542</v>
       </c>
       <c r="E328">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F328" t="s">
         <v>1609</v>
@@ -19788,7 +19788,7 @@
         <v>1542</v>
       </c>
       <c r="E329">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F329" t="s">
         <v>1609</v>
@@ -19823,7 +19823,7 @@
         <v>1543</v>
       </c>
       <c r="E330">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F330" t="s">
         <v>1609</v>
@@ -19858,7 +19858,7 @@
         <v>1543</v>
       </c>
       <c r="E331">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F331" t="s">
         <v>1609</v>
@@ -19893,7 +19893,7 @@
         <v>1544</v>
       </c>
       <c r="E332">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F332" t="s">
         <v>1609</v>
@@ -19928,7 +19928,7 @@
         <v>1544</v>
       </c>
       <c r="E333">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F333" t="s">
         <v>1609</v>
@@ -19963,7 +19963,7 @@
         <v>1544</v>
       </c>
       <c r="E334">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F334" t="s">
         <v>1609</v>
@@ -19998,7 +19998,7 @@
         <v>1544</v>
       </c>
       <c r="E335">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F335" t="s">
         <v>1609</v>
@@ -20033,7 +20033,7 @@
         <v>1544</v>
       </c>
       <c r="E336">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F336" t="s">
         <v>1609</v>
@@ -20068,7 +20068,7 @@
         <v>1545</v>
       </c>
       <c r="E337">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F337" t="s">
         <v>1609</v>
@@ -20103,7 +20103,7 @@
         <v>1545</v>
       </c>
       <c r="E338">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F338" t="s">
         <v>1609</v>
@@ -20138,7 +20138,7 @@
         <v>1545</v>
       </c>
       <c r="E339">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F339" t="s">
         <v>1609</v>
@@ -20173,7 +20173,7 @@
         <v>1545</v>
       </c>
       <c r="E340">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F340" t="s">
         <v>1609</v>
@@ -20208,7 +20208,7 @@
         <v>1546</v>
       </c>
       <c r="E341">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F341" t="s">
         <v>1609</v>
@@ -20243,7 +20243,7 @@
         <v>1546</v>
       </c>
       <c r="E342">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F342" t="s">
         <v>1609</v>
@@ -20278,7 +20278,7 @@
         <v>1547</v>
       </c>
       <c r="E343">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F343" t="s">
         <v>1609</v>
@@ -20313,7 +20313,7 @@
         <v>1547</v>
       </c>
       <c r="E344">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F344" t="s">
         <v>1609</v>
@@ -20348,7 +20348,7 @@
         <v>1547</v>
       </c>
       <c r="E345">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F345" t="s">
         <v>1609</v>
@@ -20383,7 +20383,7 @@
         <v>1547</v>
       </c>
       <c r="E346">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F346" t="s">
         <v>1609</v>
@@ -20418,7 +20418,7 @@
         <v>1547</v>
       </c>
       <c r="E347">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F347" t="s">
         <v>1609</v>
@@ -20453,7 +20453,7 @@
         <v>1548</v>
       </c>
       <c r="E348">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F348" t="s">
         <v>1609</v>
@@ -20488,7 +20488,7 @@
         <v>1548</v>
       </c>
       <c r="E349">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F349" t="s">
         <v>1609</v>
@@ -20523,7 +20523,7 @@
         <v>1548</v>
       </c>
       <c r="E350">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F350" t="s">
         <v>1609</v>
@@ -20558,7 +20558,7 @@
         <v>1548</v>
       </c>
       <c r="E351">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F351" t="s">
         <v>1609</v>
@@ -20593,7 +20593,7 @@
         <v>1549</v>
       </c>
       <c r="E352">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F352" t="s">
         <v>1609</v>
@@ -20628,7 +20628,7 @@
         <v>1549</v>
       </c>
       <c r="E353">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F353" t="s">
         <v>1609</v>
@@ -20663,7 +20663,7 @@
         <v>1550</v>
       </c>
       <c r="E354">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F354" t="s">
         <v>1609</v>
@@ -20698,7 +20698,7 @@
         <v>1550</v>
       </c>
       <c r="E355">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F355" t="s">
         <v>1609</v>
@@ -20733,7 +20733,7 @@
         <v>1550</v>
       </c>
       <c r="E356">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F356" t="s">
         <v>1609</v>
@@ -20768,7 +20768,7 @@
         <v>1550</v>
       </c>
       <c r="E357">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F357" t="s">
         <v>1609</v>
@@ -20803,7 +20803,7 @@
         <v>1550</v>
       </c>
       <c r="E358">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F358" t="s">
         <v>1609</v>
@@ -20838,7 +20838,7 @@
         <v>1550</v>
       </c>
       <c r="E359">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F359" t="s">
         <v>1609</v>
@@ -20873,7 +20873,7 @@
         <v>1550</v>
       </c>
       <c r="E360">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F360" t="s">
         <v>1609</v>
@@ -20908,7 +20908,7 @@
         <v>1550</v>
       </c>
       <c r="E361">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F361" t="s">
         <v>1609</v>
@@ -20943,7 +20943,7 @@
         <v>1551</v>
       </c>
       <c r="E362">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F362" t="s">
         <v>1609</v>
@@ -20978,7 +20978,7 @@
         <v>1551</v>
       </c>
       <c r="E363">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F363" t="s">
         <v>1609</v>
@@ -21013,7 +21013,7 @@
         <v>1551</v>
       </c>
       <c r="E364">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F364" t="s">
         <v>1609</v>
@@ -21048,7 +21048,7 @@
         <v>1552</v>
       </c>
       <c r="E365">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F365" t="s">
         <v>1609</v>
@@ -21083,7 +21083,7 @@
         <v>1552</v>
       </c>
       <c r="E366">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F366" t="s">
         <v>1609</v>
@@ -21118,7 +21118,7 @@
         <v>1553</v>
       </c>
       <c r="E367">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F367" t="s">
         <v>1609</v>
@@ -21153,7 +21153,7 @@
         <v>1554</v>
       </c>
       <c r="E368">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F368" t="s">
         <v>1611</v>
@@ -21188,7 +21188,7 @@
         <v>1554</v>
       </c>
       <c r="E369">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F369" t="s">
         <v>1609</v>
@@ -21223,7 +21223,7 @@
         <v>1554</v>
       </c>
       <c r="E370">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F370" t="s">
         <v>1609</v>
@@ -21258,7 +21258,7 @@
         <v>1554</v>
       </c>
       <c r="E371">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F371" t="s">
         <v>1609</v>
@@ -21293,7 +21293,7 @@
         <v>1554</v>
       </c>
       <c r="E372">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F372" t="s">
         <v>1609</v>
@@ -21328,7 +21328,7 @@
         <v>1554</v>
       </c>
       <c r="E373">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F373" t="s">
         <v>1609</v>
@@ -21363,7 +21363,7 @@
         <v>1555</v>
       </c>
       <c r="E374">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F374" t="s">
         <v>1609</v>
@@ -21398,7 +21398,7 @@
         <v>1555</v>
       </c>
       <c r="E375">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F375" t="s">
         <v>1609</v>
@@ -21433,7 +21433,7 @@
         <v>1556</v>
       </c>
       <c r="E376">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F376" t="s">
         <v>1609</v>
@@ -21468,7 +21468,7 @@
         <v>1556</v>
       </c>
       <c r="E377">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F377" t="s">
         <v>1609</v>
@@ -21503,7 +21503,7 @@
         <v>1556</v>
       </c>
       <c r="E378">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F378" t="s">
         <v>1609</v>
@@ -21538,7 +21538,7 @@
         <v>1557</v>
       </c>
       <c r="E379">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F379" t="s">
         <v>1609</v>
@@ -21573,7 +21573,7 @@
         <v>1558</v>
       </c>
       <c r="E380">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F380" t="s">
         <v>1609</v>
@@ -21608,7 +21608,7 @@
         <v>1559</v>
       </c>
       <c r="E381">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F381" t="s">
         <v>1609</v>
@@ -21643,7 +21643,7 @@
         <v>1559</v>
       </c>
       <c r="E382">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F382" t="s">
         <v>1609</v>
@@ -21678,7 +21678,7 @@
         <v>1560</v>
       </c>
       <c r="E383">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F383" t="s">
         <v>1609</v>
@@ -21713,7 +21713,7 @@
         <v>1560</v>
       </c>
       <c r="E384">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F384" t="s">
         <v>1609</v>
@@ -21748,7 +21748,7 @@
         <v>1560</v>
       </c>
       <c r="E385">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F385" t="s">
         <v>1609</v>
@@ -21783,7 +21783,7 @@
         <v>1561</v>
       </c>
       <c r="E386">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F386" t="s">
         <v>1609</v>
@@ -21818,7 +21818,7 @@
         <v>1561</v>
       </c>
       <c r="E387">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F387" t="s">
         <v>1609</v>
@@ -21853,7 +21853,7 @@
         <v>1561</v>
       </c>
       <c r="E388">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F388" t="s">
         <v>1609</v>
@@ -21888,7 +21888,7 @@
         <v>1561</v>
       </c>
       <c r="E389">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F389" t="s">
         <v>1609</v>
@@ -21923,7 +21923,7 @@
         <v>1561</v>
       </c>
       <c r="E390">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F390" t="s">
         <v>1609</v>
@@ -21958,7 +21958,7 @@
         <v>1561</v>
       </c>
       <c r="E391">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F391" t="s">
         <v>1609</v>
@@ -21993,7 +21993,7 @@
         <v>1561</v>
       </c>
       <c r="E392">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F392" t="s">
         <v>1609</v>
@@ -22028,7 +22028,7 @@
         <v>1561</v>
       </c>
       <c r="E393">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F393" t="s">
         <v>1609</v>
@@ -22063,7 +22063,7 @@
         <v>1561</v>
       </c>
       <c r="E394">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F394" t="s">
         <v>1609</v>
@@ -22098,7 +22098,7 @@
         <v>1561</v>
       </c>
       <c r="E395">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F395" t="s">
         <v>1609</v>
@@ -22133,7 +22133,7 @@
         <v>1562</v>
       </c>
       <c r="E396">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F396" t="s">
         <v>1609</v>
@@ -22168,7 +22168,7 @@
         <v>1562</v>
       </c>
       <c r="E397">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F397" t="s">
         <v>1609</v>
@@ -22203,7 +22203,7 @@
         <v>1562</v>
       </c>
       <c r="E398">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F398" t="s">
         <v>1609</v>
@@ -22238,7 +22238,7 @@
         <v>1562</v>
       </c>
       <c r="E399">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F399" t="s">
         <v>1609</v>
@@ -22273,7 +22273,7 @@
         <v>1562</v>
       </c>
       <c r="E400">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F400" t="s">
         <v>1609</v>
@@ -22308,7 +22308,7 @@
         <v>1563</v>
       </c>
       <c r="E401">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F401" t="s">
         <v>1612</v>
@@ -22343,7 +22343,7 @@
         <v>1563</v>
       </c>
       <c r="E402">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F402" t="s">
         <v>1609</v>
@@ -22378,7 +22378,7 @@
         <v>1564</v>
       </c>
       <c r="E403">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F403" t="s">
         <v>1609</v>
@@ -22413,7 +22413,7 @@
         <v>1564</v>
       </c>
       <c r="E404">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F404" t="s">
         <v>1609</v>
@@ -22448,7 +22448,7 @@
         <v>1564</v>
       </c>
       <c r="E405">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F405" t="s">
         <v>1609</v>
@@ -22483,7 +22483,7 @@
         <v>1564</v>
       </c>
       <c r="E406">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F406" t="s">
         <v>1609</v>
@@ -22518,7 +22518,7 @@
         <v>1564</v>
       </c>
       <c r="E407">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F407" t="s">
         <v>1609</v>
@@ -22553,7 +22553,7 @@
         <v>1564</v>
       </c>
       <c r="E408">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F408" t="s">
         <v>1608</v>
@@ -22591,7 +22591,7 @@
         <v>1564</v>
       </c>
       <c r="E409">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F409" t="s">
         <v>1609</v>
@@ -22626,7 +22626,7 @@
         <v>1564</v>
       </c>
       <c r="E410">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F410" t="s">
         <v>1609</v>
@@ -22661,7 +22661,7 @@
         <v>1565</v>
       </c>
       <c r="E411">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F411" t="s">
         <v>1609</v>
@@ -22696,7 +22696,7 @@
         <v>1565</v>
       </c>
       <c r="E412">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F412" t="s">
         <v>1609</v>
@@ -22731,7 +22731,7 @@
         <v>1565</v>
       </c>
       <c r="E413">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F413" t="s">
         <v>1609</v>
@@ -22766,7 +22766,7 @@
         <v>1565</v>
       </c>
       <c r="E414">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F414" t="s">
         <v>1609</v>
@@ -22804,7 +22804,7 @@
         <v>1565</v>
       </c>
       <c r="E415">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F415" t="s">
         <v>1609</v>
@@ -22839,7 +22839,7 @@
         <v>1565</v>
       </c>
       <c r="E416">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F416" t="s">
         <v>1609</v>
@@ -22874,7 +22874,7 @@
         <v>1565</v>
       </c>
       <c r="E417">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F417" t="s">
         <v>1609</v>
@@ -22909,7 +22909,7 @@
         <v>1565</v>
       </c>
       <c r="E418">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F418" t="s">
         <v>1609</v>
@@ -22944,7 +22944,7 @@
         <v>1565</v>
       </c>
       <c r="E419">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F419" t="s">
         <v>1609</v>
@@ -22979,7 +22979,7 @@
         <v>1566</v>
       </c>
       <c r="E420">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F420" t="s">
         <v>1610</v>
@@ -23014,7 +23014,7 @@
         <v>1567</v>
       </c>
       <c r="E421">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F421" t="s">
         <v>1611</v>
@@ -23049,7 +23049,7 @@
         <v>1567</v>
       </c>
       <c r="E422">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F422" t="s">
         <v>1608</v>
@@ -23084,7 +23084,7 @@
         <v>1568</v>
       </c>
       <c r="E423">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F423" t="s">
         <v>1609</v>
@@ -23119,7 +23119,7 @@
         <v>1569</v>
       </c>
       <c r="E424">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F424" t="s">
         <v>1609</v>
@@ -23154,7 +23154,7 @@
         <v>1569</v>
       </c>
       <c r="E425">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F425" t="s">
         <v>1609</v>
@@ -23189,7 +23189,7 @@
         <v>1570</v>
       </c>
       <c r="E426">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F426" t="s">
         <v>1609</v>
@@ -23224,7 +23224,7 @@
         <v>1571</v>
       </c>
       <c r="E427">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F427" t="s">
         <v>1612</v>
@@ -23259,7 +23259,7 @@
         <v>1571</v>
       </c>
       <c r="E428">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F428" t="s">
         <v>1609</v>
@@ -23294,7 +23294,7 @@
         <v>1571</v>
       </c>
       <c r="E429">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F429" t="s">
         <v>1609</v>
@@ -23329,7 +23329,7 @@
         <v>1571</v>
       </c>
       <c r="E430">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F430" t="s">
         <v>1609</v>
@@ -23364,7 +23364,7 @@
         <v>1571</v>
       </c>
       <c r="E431">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F431" t="s">
         <v>1609</v>
@@ -23399,7 +23399,7 @@
         <v>1571</v>
       </c>
       <c r="E432">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F432" t="s">
         <v>1609</v>
@@ -23434,7 +23434,7 @@
         <v>1572</v>
       </c>
       <c r="E433">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F433" t="s">
         <v>1609</v>
@@ -23469,7 +23469,7 @@
         <v>1572</v>
       </c>
       <c r="E434">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F434" t="s">
         <v>1609</v>
@@ -23504,7 +23504,7 @@
         <v>1572</v>
       </c>
       <c r="E435">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F435" t="s">
         <v>1609</v>
@@ -23539,7 +23539,7 @@
         <v>1572</v>
       </c>
       <c r="E436">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F436" t="s">
         <v>1609</v>
@@ -23574,7 +23574,7 @@
         <v>1573</v>
       </c>
       <c r="E437">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F437" t="s">
         <v>1609</v>
@@ -23609,7 +23609,7 @@
         <v>1573</v>
       </c>
       <c r="E438">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F438" t="s">
         <v>1609</v>
@@ -23644,7 +23644,7 @@
         <v>1573</v>
       </c>
       <c r="E439">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F439" t="s">
         <v>1609</v>
@@ -23682,7 +23682,7 @@
         <v>1573</v>
       </c>
       <c r="E440">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F440" t="s">
         <v>1609</v>
@@ -23717,7 +23717,7 @@
         <v>1574</v>
       </c>
       <c r="E441">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F441" t="s">
         <v>1609</v>
@@ -23752,7 +23752,7 @@
         <v>1574</v>
       </c>
       <c r="E442">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F442" t="s">
         <v>1609</v>
@@ -23787,7 +23787,7 @@
         <v>1574</v>
       </c>
       <c r="E443">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F443" t="s">
         <v>1609</v>
@@ -23822,7 +23822,7 @@
         <v>1574</v>
       </c>
       <c r="E444">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F444" t="s">
         <v>1609</v>
@@ -23857,7 +23857,7 @@
         <v>1574</v>
       </c>
       <c r="E445">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F445" t="s">
         <v>1609</v>
@@ -23892,7 +23892,7 @@
         <v>1575</v>
       </c>
       <c r="E446">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F446" t="s">
         <v>1609</v>
@@ -23927,7 +23927,7 @@
         <v>1575</v>
       </c>
       <c r="E447">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F447" t="s">
         <v>1609</v>
@@ -23962,7 +23962,7 @@
         <v>1575</v>
       </c>
       <c r="E448">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F448" t="s">
         <v>1609</v>
@@ -23997,7 +23997,7 @@
         <v>1575</v>
       </c>
       <c r="E449">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F449" t="s">
         <v>1609</v>
@@ -24032,7 +24032,7 @@
         <v>1576</v>
       </c>
       <c r="E450">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F450" t="s">
         <v>1609</v>
@@ -24067,7 +24067,7 @@
         <v>1576</v>
       </c>
       <c r="E451">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F451" t="s">
         <v>1609</v>
@@ -24102,7 +24102,7 @@
         <v>1576</v>
       </c>
       <c r="E452">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F452" t="s">
         <v>1609</v>
@@ -24137,7 +24137,7 @@
         <v>1576</v>
       </c>
       <c r="E453">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F453" t="s">
         <v>1609</v>
@@ -24172,7 +24172,7 @@
         <v>1576</v>
       </c>
       <c r="E454">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F454" t="s">
         <v>1609</v>
@@ -24207,7 +24207,7 @@
         <v>1576</v>
       </c>
       <c r="E455">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F455" t="s">
         <v>1609</v>
@@ -24242,7 +24242,7 @@
         <v>1576</v>
       </c>
       <c r="E456">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F456" t="s">
         <v>1609</v>
@@ -24277,7 +24277,7 @@
         <v>1576</v>
       </c>
       <c r="E457">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F457" t="s">
         <v>1609</v>
@@ -24312,7 +24312,7 @@
         <v>1576</v>
       </c>
       <c r="E458">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F458" t="s">
         <v>1609</v>
@@ -24347,7 +24347,7 @@
         <v>1576</v>
       </c>
       <c r="E459">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F459" t="s">
         <v>1609</v>
@@ -24382,7 +24382,7 @@
         <v>1576</v>
       </c>
       <c r="E460">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F460" t="s">
         <v>1609</v>
@@ -24417,7 +24417,7 @@
         <v>1577</v>
       </c>
       <c r="E461">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F461" t="s">
         <v>1609</v>
@@ -24452,7 +24452,7 @@
         <v>1577</v>
       </c>
       <c r="E462">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F462" t="s">
         <v>1609</v>
@@ -24487,7 +24487,7 @@
         <v>1577</v>
       </c>
       <c r="E463">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F463" t="s">
         <v>1610</v>
@@ -24522,7 +24522,7 @@
         <v>1578</v>
       </c>
       <c r="E464">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F464" t="s">
         <v>1609</v>
@@ -24557,7 +24557,7 @@
         <v>1578</v>
       </c>
       <c r="E465">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F465" t="s">
         <v>1609</v>
@@ -24592,7 +24592,7 @@
         <v>1578</v>
       </c>
       <c r="E466">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F466" t="s">
         <v>1609</v>
@@ -24627,7 +24627,7 @@
         <v>1578</v>
       </c>
       <c r="E467">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F467" t="s">
         <v>1609</v>
@@ -24662,7 +24662,7 @@
         <v>1578</v>
       </c>
       <c r="E468">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F468" t="s">
         <v>1609</v>
@@ -24697,7 +24697,7 @@
         <v>1578</v>
       </c>
       <c r="E469">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F469" t="s">
         <v>1609</v>
@@ -24732,7 +24732,7 @@
         <v>1578</v>
       </c>
       <c r="E470">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F470" t="s">
         <v>1612</v>
@@ -24767,7 +24767,7 @@
         <v>1579</v>
       </c>
       <c r="E471">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F471" t="s">
         <v>1609</v>
@@ -24802,7 +24802,7 @@
         <v>1579</v>
       </c>
       <c r="E472">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F472" t="s">
         <v>1609</v>
@@ -24837,7 +24837,7 @@
         <v>1579</v>
       </c>
       <c r="E473">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F473" t="s">
         <v>1609</v>
@@ -24872,7 +24872,7 @@
         <v>1579</v>
       </c>
       <c r="E474">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F474" t="s">
         <v>1609</v>
@@ -24907,7 +24907,7 @@
         <v>1580</v>
       </c>
       <c r="E475">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F475" t="s">
         <v>1609</v>
@@ -24942,7 +24942,7 @@
         <v>1580</v>
       </c>
       <c r="E476">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F476" t="s">
         <v>1612</v>
@@ -24977,7 +24977,7 @@
         <v>1580</v>
       </c>
       <c r="E477">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F477" t="s">
         <v>1609</v>
@@ -25012,7 +25012,7 @@
         <v>1580</v>
       </c>
       <c r="E478">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F478" t="s">
         <v>1609</v>
@@ -25047,7 +25047,7 @@
         <v>1580</v>
       </c>
       <c r="E479">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F479" t="s">
         <v>1609</v>
@@ -25082,7 +25082,7 @@
         <v>1580</v>
       </c>
       <c r="E480">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F480" t="s">
         <v>1611</v>
@@ -25120,7 +25120,7 @@
         <v>1580</v>
       </c>
       <c r="E481">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F481" t="s">
         <v>1609</v>
@@ -25155,7 +25155,7 @@
         <v>1580</v>
       </c>
       <c r="E482">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F482" t="s">
         <v>1608</v>
@@ -25190,7 +25190,7 @@
         <v>1580</v>
       </c>
       <c r="E483">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F483" t="s">
         <v>1609</v>
@@ -25225,7 +25225,7 @@
         <v>1580</v>
       </c>
       <c r="E484">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F484" t="s">
         <v>1609</v>
@@ -25260,7 +25260,7 @@
         <v>1581</v>
       </c>
       <c r="E485">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F485" t="s">
         <v>1609</v>
@@ -25295,7 +25295,7 @@
         <v>1581</v>
       </c>
       <c r="E486">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F486" t="s">
         <v>1609</v>
@@ -25330,7 +25330,7 @@
         <v>1581</v>
       </c>
       <c r="E487">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F487" t="s">
         <v>1609</v>
@@ -25365,7 +25365,7 @@
         <v>1581</v>
       </c>
       <c r="E488">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F488" t="s">
         <v>1609</v>
@@ -25400,7 +25400,7 @@
         <v>1581</v>
       </c>
       <c r="E489">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F489" t="s">
         <v>1609</v>
@@ -25435,7 +25435,7 @@
         <v>1581</v>
       </c>
       <c r="E490">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F490" t="s">
         <v>1609</v>
@@ -25470,7 +25470,7 @@
         <v>1581</v>
       </c>
       <c r="E491">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F491" t="s">
         <v>1611</v>
@@ -25505,7 +25505,7 @@
         <v>1581</v>
       </c>
       <c r="E492">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F492" t="s">
         <v>1609</v>
@@ -25540,7 +25540,7 @@
         <v>1581</v>
       </c>
       <c r="E493">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F493" t="s">
         <v>1609</v>
@@ -25575,7 +25575,7 @@
         <v>1582</v>
       </c>
       <c r="E494">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F494" t="s">
         <v>1609</v>
@@ -25610,7 +25610,7 @@
         <v>1582</v>
       </c>
       <c r="E495">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F495" t="s">
         <v>1609</v>
@@ -25645,7 +25645,7 @@
         <v>1582</v>
       </c>
       <c r="E496">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F496" t="s">
         <v>1609</v>
@@ -25680,7 +25680,7 @@
         <v>1582</v>
       </c>
       <c r="E497">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F497" t="s">
         <v>1609</v>
@@ -25715,7 +25715,7 @@
         <v>1582</v>
       </c>
       <c r="E498">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F498" t="s">
         <v>1609</v>
@@ -25750,7 +25750,7 @@
         <v>1583</v>
       </c>
       <c r="E499">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F499" t="s">
         <v>1609</v>
@@ -25785,7 +25785,7 @@
         <v>1583</v>
       </c>
       <c r="E500">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F500" t="s">
         <v>1609</v>
@@ -25820,7 +25820,7 @@
         <v>1583</v>
       </c>
       <c r="E501">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F501" t="s">
         <v>1609</v>
@@ -25855,7 +25855,7 @@
         <v>1583</v>
       </c>
       <c r="E502">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F502" t="s">
         <v>1609</v>
@@ -25890,7 +25890,7 @@
         <v>1583</v>
       </c>
       <c r="E503">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F503" t="s">
         <v>1609</v>
@@ -25928,7 +25928,7 @@
         <v>1584</v>
       </c>
       <c r="E504">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F504" t="s">
         <v>1609</v>
@@ -25963,7 +25963,7 @@
         <v>1584</v>
       </c>
       <c r="E505">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F505" t="s">
         <v>1609</v>
@@ -25998,7 +25998,7 @@
         <v>1584</v>
       </c>
       <c r="E506">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F506" t="s">
         <v>1609</v>
@@ -26033,7 +26033,7 @@
         <v>1584</v>
       </c>
       <c r="E507">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F507" t="s">
         <v>1609</v>
@@ -26068,7 +26068,7 @@
         <v>1584</v>
       </c>
       <c r="E508">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F508" t="s">
         <v>1609</v>
@@ -26103,7 +26103,7 @@
         <v>1584</v>
       </c>
       <c r="E509">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F509" t="s">
         <v>1609</v>
@@ -26138,7 +26138,7 @@
         <v>1584</v>
       </c>
       <c r="E510">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F510" t="s">
         <v>1609</v>
@@ -26173,7 +26173,7 @@
         <v>1585</v>
       </c>
       <c r="E511">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F511" t="s">
         <v>1609</v>
@@ -26208,7 +26208,7 @@
         <v>1585</v>
       </c>
       <c r="E512">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F512" t="s">
         <v>1609</v>
@@ -26243,7 +26243,7 @@
         <v>1585</v>
       </c>
       <c r="E513">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F513" t="s">
         <v>1609</v>
@@ -26278,7 +26278,7 @@
         <v>1586</v>
       </c>
       <c r="E514">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F514" t="s">
         <v>1609</v>
@@ -26313,7 +26313,7 @@
         <v>1586</v>
       </c>
       <c r="E515">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F515" t="s">
         <v>1609</v>
@@ -26348,7 +26348,7 @@
         <v>1587</v>
       </c>
       <c r="E516">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F516" t="s">
         <v>1609</v>
@@ -26383,7 +26383,7 @@
         <v>1587</v>
       </c>
       <c r="E517">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F517" t="s">
         <v>1609</v>
@@ -26418,7 +26418,7 @@
         <v>1587</v>
       </c>
       <c r="E518">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F518" t="s">
         <v>1611</v>
@@ -26456,7 +26456,7 @@
         <v>1587</v>
       </c>
       <c r="E519">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F519" t="s">
         <v>1609</v>
@@ -26491,7 +26491,7 @@
         <v>1587</v>
       </c>
       <c r="E520">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F520" t="s">
         <v>1609</v>
@@ -26526,7 +26526,7 @@
         <v>1588</v>
       </c>
       <c r="E521">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F521" t="s">
         <v>1609</v>
@@ -26561,7 +26561,7 @@
         <v>1588</v>
       </c>
       <c r="E522">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F522" t="s">
         <v>1609</v>
@@ -26596,7 +26596,7 @@
         <v>1588</v>
       </c>
       <c r="E523">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F523" t="s">
         <v>1609</v>
@@ -26631,7 +26631,7 @@
         <v>1588</v>
       </c>
       <c r="E524">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F524" t="s">
         <v>1609</v>
@@ -26666,7 +26666,7 @@
         <v>1588</v>
       </c>
       <c r="E525">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F525" t="s">
         <v>1609</v>
@@ -26701,7 +26701,7 @@
         <v>1589</v>
       </c>
       <c r="E526">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F526" t="s">
         <v>1609</v>
@@ -26736,7 +26736,7 @@
         <v>1589</v>
       </c>
       <c r="E527">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F527" t="s">
         <v>1609</v>
@@ -26771,7 +26771,7 @@
         <v>1589</v>
       </c>
       <c r="E528">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F528" t="s">
         <v>1609</v>
@@ -26806,7 +26806,7 @@
         <v>1589</v>
       </c>
       <c r="E529">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F529" t="s">
         <v>1609</v>
@@ -26841,7 +26841,7 @@
         <v>1589</v>
       </c>
       <c r="E530">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F530" t="s">
         <v>1609</v>
@@ -26876,7 +26876,7 @@
         <v>1589</v>
       </c>
       <c r="E531">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F531" t="s">
         <v>1609</v>
@@ -26911,7 +26911,7 @@
         <v>1589</v>
       </c>
       <c r="E532">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F532" t="s">
         <v>1609</v>
@@ -26946,7 +26946,7 @@
         <v>1589</v>
       </c>
       <c r="E533">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F533" t="s">
         <v>1609</v>
@@ -26981,7 +26981,7 @@
         <v>1590</v>
       </c>
       <c r="E534">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F534" t="s">
         <v>1609</v>
@@ -27016,7 +27016,7 @@
         <v>1590</v>
       </c>
       <c r="E535">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F535" t="s">
         <v>1609</v>
@@ -27051,7 +27051,7 @@
         <v>1591</v>
       </c>
       <c r="E536">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F536" t="s">
         <v>1609</v>
@@ -27086,7 +27086,7 @@
         <v>1591</v>
       </c>
       <c r="E537">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F537" t="s">
         <v>1609</v>
@@ -27121,7 +27121,7 @@
         <v>1591</v>
       </c>
       <c r="E538">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F538" t="s">
         <v>1609</v>
@@ -27156,7 +27156,7 @@
         <v>1591</v>
       </c>
       <c r="E539">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F539" t="s">
         <v>1608</v>
@@ -27194,7 +27194,7 @@
         <v>1591</v>
       </c>
       <c r="E540">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F540" t="s">
         <v>1609</v>
@@ -27229,7 +27229,7 @@
         <v>1591</v>
       </c>
       <c r="E541">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F541" t="s">
         <v>1608</v>
@@ -27264,7 +27264,7 @@
         <v>1592</v>
       </c>
       <c r="E542">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F542" t="s">
         <v>1609</v>
@@ -27299,7 +27299,7 @@
         <v>1593</v>
       </c>
       <c r="E543">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F543" t="s">
         <v>1609</v>
@@ -27334,7 +27334,7 @@
         <v>1593</v>
       </c>
       <c r="E544">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F544" t="s">
         <v>1609</v>
@@ -27369,7 +27369,7 @@
         <v>1593</v>
       </c>
       <c r="E545">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F545" t="s">
         <v>1609</v>
@@ -27404,7 +27404,7 @@
         <v>1593</v>
       </c>
       <c r="E546">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F546" t="s">
         <v>1609</v>
@@ -27439,7 +27439,7 @@
         <v>1594</v>
       </c>
       <c r="E547">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F547" t="s">
         <v>1609</v>
@@ -27474,7 +27474,7 @@
         <v>1594</v>
       </c>
       <c r="E548">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F548" t="s">
         <v>1608</v>
@@ -27509,7 +27509,7 @@
         <v>1594</v>
       </c>
       <c r="E549">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F549" t="s">
         <v>1609</v>
@@ -27544,7 +27544,7 @@
         <v>1594</v>
       </c>
       <c r="E550">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F550" t="s">
         <v>1609</v>
@@ -27579,7 +27579,7 @@
         <v>1594</v>
       </c>
       <c r="E551">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F551" t="s">
         <v>1609</v>
@@ -27614,7 +27614,7 @@
         <v>1594</v>
       </c>
       <c r="E552">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F552" t="s">
         <v>1609</v>
@@ -27649,7 +27649,7 @@
         <v>1595</v>
       </c>
       <c r="E553">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F553" t="s">
         <v>1609</v>
@@ -27684,7 +27684,7 @@
         <v>1595</v>
       </c>
       <c r="E554">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F554" t="s">
         <v>1608</v>
@@ -27719,7 +27719,7 @@
         <v>1595</v>
       </c>
       <c r="E555">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F555" t="s">
         <v>1611</v>
@@ -27754,7 +27754,7 @@
         <v>1595</v>
       </c>
       <c r="E556">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F556" t="s">
         <v>1609</v>
@@ -27789,7 +27789,7 @@
         <v>1595</v>
       </c>
       <c r="E557">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F557" t="s">
         <v>1609</v>
@@ -27824,7 +27824,7 @@
         <v>1596</v>
       </c>
       <c r="E558">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F558" t="s">
         <v>1609</v>
@@ -27859,7 +27859,7 @@
         <v>1596</v>
       </c>
       <c r="E559">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F559" t="s">
         <v>1609</v>
@@ -27894,7 +27894,7 @@
         <v>1596</v>
       </c>
       <c r="E560">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F560" t="s">
         <v>1609</v>
@@ -27929,7 +27929,7 @@
         <v>1596</v>
       </c>
       <c r="E561">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F561" t="s">
         <v>1609</v>
@@ -27964,7 +27964,7 @@
         <v>1596</v>
       </c>
       <c r="E562">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F562" t="s">
         <v>1609</v>
@@ -27999,7 +27999,7 @@
         <v>1596</v>
       </c>
       <c r="E563">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F563" t="s">
         <v>1609</v>
@@ -28034,7 +28034,7 @@
         <v>1596</v>
       </c>
       <c r="E564">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F564" t="s">
         <v>1609</v>
@@ -28069,7 +28069,7 @@
         <v>1597</v>
       </c>
       <c r="E565">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F565" t="s">
         <v>1609</v>
@@ -28104,7 +28104,7 @@
         <v>1597</v>
       </c>
       <c r="E566">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F566" t="s">
         <v>1609</v>
@@ -28139,7 +28139,7 @@
         <v>1597</v>
       </c>
       <c r="E567">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F567" t="s">
         <v>1609</v>
@@ -28174,7 +28174,7 @@
         <v>1597</v>
       </c>
       <c r="E568">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F568" t="s">
         <v>1609</v>
@@ -28209,7 +28209,7 @@
         <v>1597</v>
       </c>
       <c r="E569">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F569" t="s">
         <v>1609</v>
@@ -28244,7 +28244,7 @@
         <v>1597</v>
       </c>
       <c r="E570">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F570" t="s">
         <v>1609</v>
@@ -28279,7 +28279,7 @@
         <v>1597</v>
       </c>
       <c r="E571">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F571" t="s">
         <v>1609</v>
@@ -28314,7 +28314,7 @@
         <v>1597</v>
       </c>
       <c r="E572">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F572" t="s">
         <v>1609</v>
@@ -28349,7 +28349,7 @@
         <v>1597</v>
       </c>
       <c r="E573">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F573" t="s">
         <v>1609</v>
@@ -28384,7 +28384,7 @@
         <v>1597</v>
       </c>
       <c r="E574">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F574" t="s">
         <v>1609</v>
@@ -28419,7 +28419,7 @@
         <v>1597</v>
       </c>
       <c r="E575">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F575" t="s">
         <v>1609</v>
@@ -28454,7 +28454,7 @@
         <v>1597</v>
       </c>
       <c r="E576">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F576" t="s">
         <v>1609</v>
@@ -28489,7 +28489,7 @@
         <v>1597</v>
       </c>
       <c r="E577">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F577" t="s">
         <v>1609</v>
@@ -28524,7 +28524,7 @@
         <v>1597</v>
       </c>
       <c r="E578">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F578" t="s">
         <v>1609</v>
@@ -28559,7 +28559,7 @@
         <v>1597</v>
       </c>
       <c r="E579">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F579" t="s">
         <v>1609</v>
@@ -28594,7 +28594,7 @@
         <v>1597</v>
       </c>
       <c r="E580">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F580" t="s">
         <v>1609</v>
@@ -28629,7 +28629,7 @@
         <v>1597</v>
       </c>
       <c r="E581">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F581" t="s">
         <v>1609</v>
@@ -28664,7 +28664,7 @@
         <v>1597</v>
       </c>
       <c r="E582">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F582" t="s">
         <v>1609</v>
@@ -28699,7 +28699,7 @@
         <v>1597</v>
       </c>
       <c r="E583">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F583" t="s">
         <v>1609</v>
@@ -28734,7 +28734,7 @@
         <v>1597</v>
       </c>
       <c r="E584">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F584" t="s">
         <v>1609</v>
@@ -28769,7 +28769,7 @@
         <v>1597</v>
       </c>
       <c r="E585">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F585" t="s">
         <v>1609</v>
@@ -28804,7 +28804,7 @@
         <v>1597</v>
       </c>
       <c r="E586">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F586" t="s">
         <v>1609</v>
@@ -28839,7 +28839,7 @@
         <v>1597</v>
       </c>
       <c r="E587">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F587" t="s">
         <v>1609</v>
@@ -28874,7 +28874,7 @@
         <v>1597</v>
       </c>
       <c r="E588">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F588" t="s">
         <v>1609</v>
@@ -28909,7 +28909,7 @@
         <v>1597</v>
       </c>
       <c r="E589">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F589" t="s">
         <v>1609</v>
@@ -28944,7 +28944,7 @@
         <v>1597</v>
       </c>
       <c r="E590">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F590" t="s">
         <v>1609</v>
@@ -28979,7 +28979,7 @@
         <v>1597</v>
       </c>
       <c r="E591">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F591" t="s">
         <v>1609</v>
@@ -29014,7 +29014,7 @@
         <v>1597</v>
       </c>
       <c r="E592">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F592" t="s">
         <v>1611</v>
@@ -29052,7 +29052,7 @@
         <v>1598</v>
       </c>
       <c r="E593">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F593" t="s">
         <v>1609</v>
@@ -29087,7 +29087,7 @@
         <v>1598</v>
       </c>
       <c r="E594">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F594" t="s">
         <v>1609</v>
@@ -29122,7 +29122,7 @@
         <v>1598</v>
       </c>
       <c r="E595">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F595" t="s">
         <v>1611</v>
@@ -29157,7 +29157,7 @@
         <v>1598</v>
       </c>
       <c r="E596">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F596" t="s">
         <v>1609</v>
@@ -29192,7 +29192,7 @@
         <v>1598</v>
       </c>
       <c r="E597">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F597" t="s">
         <v>1609</v>
@@ -29227,7 +29227,7 @@
         <v>1598</v>
       </c>
       <c r="E598">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F598" t="s">
         <v>1609</v>
@@ -29262,7 +29262,7 @@
         <v>1598</v>
       </c>
       <c r="E599">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F599" t="s">
         <v>1609</v>
@@ -29297,7 +29297,7 @@
         <v>1598</v>
       </c>
       <c r="E600">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F600" t="s">
         <v>1609</v>
@@ -29332,7 +29332,7 @@
         <v>1599</v>
       </c>
       <c r="E601">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F601" t="s">
         <v>1609</v>
@@ -29367,7 +29367,7 @@
         <v>1599</v>
       </c>
       <c r="E602">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F602" t="s">
         <v>1609</v>
@@ -29402,7 +29402,7 @@
         <v>1600</v>
       </c>
       <c r="E603">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F603" t="s">
         <v>1609</v>
@@ -29437,7 +29437,7 @@
         <v>1600</v>
       </c>
       <c r="E604">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F604" t="s">
         <v>1611</v>
@@ -29475,7 +29475,7 @@
         <v>1600</v>
       </c>
       <c r="E605">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F605" t="s">
         <v>1611</v>
@@ -29513,7 +29513,7 @@
         <v>1601</v>
       </c>
       <c r="E606">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F606" t="s">
         <v>1611</v>
@@ -29551,7 +29551,7 @@
         <v>1601</v>
       </c>
       <c r="E607">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F607" t="s">
         <v>1609</v>
@@ -29586,7 +29586,7 @@
         <v>1601</v>
       </c>
       <c r="E608">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F608" t="s">
         <v>1609</v>
@@ -29621,7 +29621,7 @@
         <v>1601</v>
       </c>
       <c r="E609">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F609" t="s">
         <v>1611</v>
@@ -29659,7 +29659,7 @@
         <v>1601</v>
       </c>
       <c r="E610">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F610" t="s">
         <v>1609</v>
@@ -29694,7 +29694,7 @@
         <v>1601</v>
       </c>
       <c r="E611">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F611" t="s">
         <v>1609</v>
@@ -29729,7 +29729,7 @@
         <v>1601</v>
       </c>
       <c r="E612">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F612" t="s">
         <v>1611</v>
@@ -29767,7 +29767,7 @@
         <v>1601</v>
       </c>
       <c r="E613">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F613" t="s">
         <v>1609</v>
@@ -29802,7 +29802,7 @@
         <v>1601</v>
       </c>
       <c r="E614">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F614" t="s">
         <v>1609</v>
@@ -29840,7 +29840,7 @@
         <v>1601</v>
       </c>
       <c r="E615">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F615" t="s">
         <v>1611</v>
@@ -29875,7 +29875,7 @@
         <v>1601</v>
       </c>
       <c r="E616">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F616" t="s">
         <v>1609</v>
@@ -29910,7 +29910,7 @@
         <v>1601</v>
       </c>
       <c r="E617">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F617" t="s">
         <v>1609</v>
@@ -29945,7 +29945,7 @@
         <v>1602</v>
       </c>
       <c r="E618">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F618" t="s">
         <v>1609</v>
@@ -29983,7 +29983,7 @@
         <v>1602</v>
       </c>
       <c r="E619">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F619" t="s">
         <v>1608</v>
@@ -30018,7 +30018,7 @@
         <v>1602</v>
       </c>
       <c r="E620">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F620" t="s">
         <v>1611</v>
@@ -30053,7 +30053,7 @@
         <v>1602</v>
       </c>
       <c r="E621">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F621" t="s">
         <v>1609</v>
@@ -30088,7 +30088,7 @@
         <v>1602</v>
       </c>
       <c r="E622">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F622" t="s">
         <v>1611</v>
@@ -30126,7 +30126,7 @@
         <v>1602</v>
       </c>
       <c r="E623">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F623" t="s">
         <v>1609</v>
@@ -30161,7 +30161,7 @@
         <v>1602</v>
       </c>
       <c r="E624">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F624" t="s">
         <v>1609</v>
@@ -30196,7 +30196,7 @@
         <v>1602</v>
       </c>
       <c r="E625">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F625" t="s">
         <v>1609</v>
@@ -30231,7 +30231,7 @@
         <v>1602</v>
       </c>
       <c r="E626">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F626" t="s">
         <v>1609</v>
@@ -30266,7 +30266,7 @@
         <v>1602</v>
       </c>
       <c r="E627">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F627" t="s">
         <v>1609</v>
@@ -30301,7 +30301,7 @@
         <v>1603</v>
       </c>
       <c r="E628">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F628" t="s">
         <v>1609</v>
@@ -30336,7 +30336,7 @@
         <v>1603</v>
       </c>
       <c r="E629">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F629" t="s">
         <v>1609</v>
@@ -30374,7 +30374,7 @@
         <v>1603</v>
       </c>
       <c r="E630">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F630" t="s">
         <v>1609</v>
@@ -30409,7 +30409,7 @@
         <v>1604</v>
       </c>
       <c r="E631">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F631" t="s">
         <v>1609</v>
@@ -30444,7 +30444,7 @@
         <v>1604</v>
       </c>
       <c r="E632">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F632" t="s">
         <v>1611</v>
@@ -30482,7 +30482,7 @@
         <v>1604</v>
       </c>
       <c r="E633">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F633" t="s">
         <v>1609</v>
@@ -30517,7 +30517,7 @@
         <v>1604</v>
       </c>
       <c r="E634">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F634" t="s">
         <v>1609</v>
@@ -30552,7 +30552,7 @@
         <v>1604</v>
       </c>
       <c r="E635">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F635" t="s">
         <v>1609</v>
@@ -30587,7 +30587,7 @@
         <v>1604</v>
       </c>
       <c r="E636">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F636" t="s">
         <v>1609</v>
@@ -30622,7 +30622,7 @@
         <v>1604</v>
       </c>
       <c r="E637">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F637" t="s">
         <v>1609</v>
@@ -30657,7 +30657,7 @@
         <v>1604</v>
       </c>
       <c r="E638">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F638" t="s">
         <v>1609</v>
@@ -30692,7 +30692,7 @@
         <v>1604</v>
       </c>
       <c r="E639">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F639" t="s">
         <v>1609</v>
@@ -30727,7 +30727,7 @@
         <v>1604</v>
       </c>
       <c r="E640">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F640" t="s">
         <v>1609</v>
@@ -30762,7 +30762,7 @@
         <v>1605</v>
       </c>
       <c r="E641">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F641" t="s">
         <v>1609</v>
@@ -30797,7 +30797,7 @@
         <v>1605</v>
       </c>
       <c r="E642">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F642" t="s">
         <v>1609</v>
@@ -30832,7 +30832,7 @@
         <v>1605</v>
       </c>
       <c r="E643">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F643" t="s">
         <v>1609</v>
@@ -30867,7 +30867,7 @@
         <v>1605</v>
       </c>
       <c r="E644">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F644" t="s">
         <v>1609</v>
@@ -30902,7 +30902,7 @@
         <v>1605</v>
       </c>
       <c r="E645">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F645" t="s">
         <v>1611</v>
@@ -30940,7 +30940,7 @@
         <v>1605</v>
       </c>
       <c r="E646">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F646" t="s">
         <v>1609</v>
@@ -30975,7 +30975,7 @@
         <v>1605</v>
       </c>
       <c r="E647">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F647" t="s">
         <v>1609</v>
@@ -31010,7 +31010,7 @@
         <v>1605</v>
       </c>
       <c r="E648">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F648" t="s">
         <v>1609</v>
@@ -31045,7 +31045,7 @@
         <v>1605</v>
       </c>
       <c r="E649">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F649" t="s">
         <v>1609</v>
@@ -31080,7 +31080,7 @@
         <v>1605</v>
       </c>
       <c r="E650">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F650" t="s">
         <v>1609</v>
@@ -31115,7 +31115,7 @@
         <v>1605</v>
       </c>
       <c r="E651">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F651" t="s">
         <v>1608</v>
@@ -31150,7 +31150,7 @@
         <v>1605</v>
       </c>
       <c r="E652">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F652" t="s">
         <v>1609</v>
@@ -31185,7 +31185,7 @@
         <v>1606</v>
       </c>
       <c r="E653">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F653" t="s">
         <v>1611</v>
@@ -31223,7 +31223,7 @@
         <v>1606</v>
       </c>
       <c r="E654">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F654" t="s">
         <v>1609</v>
@@ -31258,7 +31258,7 @@
         <v>1606</v>
       </c>
       <c r="E655">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F655" t="s">
         <v>1609</v>
@@ -31293,7 +31293,7 @@
         <v>1606</v>
       </c>
       <c r="E656">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F656" t="s">
         <v>1609</v>
@@ -31328,7 +31328,7 @@
         <v>1606</v>
       </c>
       <c r="E657">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F657" t="s">
         <v>1609</v>
@@ -31363,7 +31363,7 @@
         <v>1606</v>
       </c>
       <c r="E658">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F658" t="s">
         <v>1609</v>
@@ -31398,7 +31398,7 @@
         <v>1606</v>
       </c>
       <c r="E659">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F659" t="s">
         <v>1609</v>
@@ -31433,7 +31433,7 @@
         <v>1606</v>
       </c>
       <c r="E660">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F660" t="s">
         <v>1609</v>
@@ -31468,7 +31468,7 @@
         <v>1606</v>
       </c>
       <c r="E661">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F661" t="s">
         <v>1609</v>
@@ -31506,7 +31506,7 @@
         <v>1606</v>
       </c>
       <c r="E662">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F662" t="s">
         <v>1609</v>
@@ -31541,7 +31541,7 @@
         <v>1606</v>
       </c>
       <c r="E663">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F663" t="s">
         <v>1611</v>
@@ -31576,7 +31576,7 @@
         <v>1606</v>
       </c>
       <c r="E664">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F664" t="s">
         <v>1609</v>
@@ -31611,7 +31611,7 @@
         <v>1606</v>
       </c>
       <c r="E665">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F665" t="s">
         <v>1609</v>
@@ -31646,7 +31646,7 @@
         <v>1607</v>
       </c>
       <c r="E666">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F666" t="s">
         <v>1609</v>
@@ -31681,7 +31681,7 @@
         <v>1607</v>
       </c>
       <c r="E667">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F667" t="s">
         <v>1609</v>
@@ -31716,7 +31716,7 @@
         <v>1607</v>
       </c>
       <c r="E668">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F668" t="s">
         <v>1609</v>
@@ -31751,7 +31751,7 @@
         <v>1607</v>
       </c>
       <c r="E669">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F669" t="s">
         <v>1609</v>
@@ -31786,7 +31786,7 @@
         <v>1607</v>
       </c>
       <c r="E670">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F670" t="s">
         <v>1609</v>
@@ -31821,7 +31821,7 @@
         <v>1607</v>
       </c>
       <c r="E671">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F671" t="s">
         <v>1609</v>
@@ -31856,7 +31856,7 @@
         <v>1607</v>
       </c>
       <c r="E672">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F672" t="s">
         <v>1609</v>
@@ -31891,7 +31891,7 @@
         <v>1607</v>
       </c>
       <c r="E673">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F673" t="s">
         <v>1609</v>
@@ -31929,7 +31929,7 @@
         <v>1607</v>
       </c>
       <c r="E674">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F674" t="s">
         <v>1609</v>
@@ -31964,7 +31964,7 @@
         <v>1607</v>
       </c>
       <c r="E675">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F675" t="s">
         <v>1609</v>
@@ -31999,7 +31999,7 @@
         <v>1607</v>
       </c>
       <c r="E676">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F676" t="s">
         <v>1609</v>

--- a/BacklogGATEAutoCompleto.xlsx
+++ b/BacklogGATEAutoCompleto.xlsx
@@ -8328,7 +8328,7 @@
         <v>1391</v>
       </c>
       <c r="E2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="F2" t="s">
         <v>1608</v>
@@ -8363,7 +8363,7 @@
         <v>1392</v>
       </c>
       <c r="E3">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="F3" t="s">
         <v>1609</v>
@@ -8398,7 +8398,7 @@
         <v>1393</v>
       </c>
       <c r="E4">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="F4" t="s">
         <v>1609</v>
@@ -8433,7 +8433,7 @@
         <v>1394</v>
       </c>
       <c r="E5">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="F5" t="s">
         <v>1609</v>
@@ -8468,7 +8468,7 @@
         <v>1395</v>
       </c>
       <c r="E6">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="F6" t="s">
         <v>1609</v>
@@ -8503,7 +8503,7 @@
         <v>1396</v>
       </c>
       <c r="E7">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="F7" t="s">
         <v>1609</v>
@@ -8538,7 +8538,7 @@
         <v>1396</v>
       </c>
       <c r="E8">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="F8" t="s">
         <v>1609</v>
@@ -8573,7 +8573,7 @@
         <v>1397</v>
       </c>
       <c r="E9">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="F9" t="s">
         <v>1609</v>
@@ -8608,7 +8608,7 @@
         <v>1398</v>
       </c>
       <c r="E10">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="F10" t="s">
         <v>1609</v>
@@ -8643,7 +8643,7 @@
         <v>1399</v>
       </c>
       <c r="E11">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F11" t="s">
         <v>1609</v>
@@ -8678,7 +8678,7 @@
         <v>1400</v>
       </c>
       <c r="E12">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="F12" t="s">
         <v>1609</v>
@@ -8713,7 +8713,7 @@
         <v>1401</v>
       </c>
       <c r="E13">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F13" t="s">
         <v>1609</v>
@@ -8748,7 +8748,7 @@
         <v>1402</v>
       </c>
       <c r="E14">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="F14" t="s">
         <v>1609</v>
@@ -8783,7 +8783,7 @@
         <v>1403</v>
       </c>
       <c r="E15">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="F15" t="s">
         <v>1609</v>
@@ -8818,7 +8818,7 @@
         <v>1403</v>
       </c>
       <c r="E16">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="F16" t="s">
         <v>1609</v>
@@ -8853,7 +8853,7 @@
         <v>1404</v>
       </c>
       <c r="E17">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="F17" t="s">
         <v>1609</v>
@@ -8888,7 +8888,7 @@
         <v>1405</v>
       </c>
       <c r="E18">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="F18" t="s">
         <v>1609</v>
@@ -8923,7 +8923,7 @@
         <v>1406</v>
       </c>
       <c r="E19">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="F19" t="s">
         <v>1609</v>
@@ -8958,7 +8958,7 @@
         <v>1406</v>
       </c>
       <c r="E20">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="F20" t="s">
         <v>1609</v>
@@ -8993,7 +8993,7 @@
         <v>1407</v>
       </c>
       <c r="E21">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="F21" t="s">
         <v>1609</v>
@@ -9028,7 +9028,7 @@
         <v>1408</v>
       </c>
       <c r="E22">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="F22" t="s">
         <v>1609</v>
@@ -9063,7 +9063,7 @@
         <v>1409</v>
       </c>
       <c r="E23">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F23" t="s">
         <v>1609</v>
@@ -9098,7 +9098,7 @@
         <v>1409</v>
       </c>
       <c r="E24">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F24" t="s">
         <v>1609</v>
@@ -9133,7 +9133,7 @@
         <v>1410</v>
       </c>
       <c r="E25">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F25" t="s">
         <v>1609</v>
@@ -9168,7 +9168,7 @@
         <v>1411</v>
       </c>
       <c r="E26">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F26" t="s">
         <v>1609</v>
@@ -9203,7 +9203,7 @@
         <v>1412</v>
       </c>
       <c r="E27">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="F27" t="s">
         <v>1609</v>
@@ -9238,7 +9238,7 @@
         <v>1413</v>
       </c>
       <c r="E28">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F28" t="s">
         <v>1609</v>
@@ -9273,7 +9273,7 @@
         <v>1414</v>
       </c>
       <c r="E29">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F29" t="s">
         <v>1609</v>
@@ -9311,7 +9311,7 @@
         <v>1415</v>
       </c>
       <c r="E30">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F30" t="s">
         <v>1609</v>
@@ -9346,7 +9346,7 @@
         <v>1416</v>
       </c>
       <c r="E31">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F31" t="s">
         <v>1609</v>
@@ -9381,7 +9381,7 @@
         <v>1417</v>
       </c>
       <c r="E32">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F32" t="s">
         <v>1609</v>
@@ -9416,7 +9416,7 @@
         <v>1418</v>
       </c>
       <c r="E33">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F33" t="s">
         <v>1609</v>
@@ -9451,7 +9451,7 @@
         <v>1418</v>
       </c>
       <c r="E34">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F34" t="s">
         <v>1609</v>
@@ -9486,7 +9486,7 @@
         <v>1419</v>
       </c>
       <c r="E35">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="F35" t="s">
         <v>1609</v>
@@ -9521,7 +9521,7 @@
         <v>1420</v>
       </c>
       <c r="E36">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F36" t="s">
         <v>1609</v>
@@ -9556,7 +9556,7 @@
         <v>1421</v>
       </c>
       <c r="E37">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F37" t="s">
         <v>1609</v>
@@ -9591,7 +9591,7 @@
         <v>1422</v>
       </c>
       <c r="E38">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F38" t="s">
         <v>1609</v>
@@ -9626,7 +9626,7 @@
         <v>1423</v>
       </c>
       <c r="E39">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F39" t="s">
         <v>1609</v>
@@ -9661,7 +9661,7 @@
         <v>1424</v>
       </c>
       <c r="E40">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F40" t="s">
         <v>1609</v>
@@ -9696,7 +9696,7 @@
         <v>1425</v>
       </c>
       <c r="E41">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F41" t="s">
         <v>1609</v>
@@ -9731,7 +9731,7 @@
         <v>1426</v>
       </c>
       <c r="E42">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F42" t="s">
         <v>1609</v>
@@ -9766,7 +9766,7 @@
         <v>1426</v>
       </c>
       <c r="E43">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F43" t="s">
         <v>1609</v>
@@ -9801,7 +9801,7 @@
         <v>1427</v>
       </c>
       <c r="E44">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F44" t="s">
         <v>1609</v>
@@ -9836,7 +9836,7 @@
         <v>1427</v>
       </c>
       <c r="E45">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F45" t="s">
         <v>1609</v>
@@ -9871,7 +9871,7 @@
         <v>1428</v>
       </c>
       <c r="E46">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F46" t="s">
         <v>1609</v>
@@ -9906,7 +9906,7 @@
         <v>1429</v>
       </c>
       <c r="E47">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F47" t="s">
         <v>1609</v>
@@ -9941,7 +9941,7 @@
         <v>1430</v>
       </c>
       <c r="E48">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F48" t="s">
         <v>1609</v>
@@ -9976,7 +9976,7 @@
         <v>1431</v>
       </c>
       <c r="E49">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F49" t="s">
         <v>1609</v>
@@ -10011,7 +10011,7 @@
         <v>1432</v>
       </c>
       <c r="E50">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F50" t="s">
         <v>1609</v>
@@ -10046,7 +10046,7 @@
         <v>1432</v>
       </c>
       <c r="E51">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F51" t="s">
         <v>1609</v>
@@ -10081,7 +10081,7 @@
         <v>1433</v>
       </c>
       <c r="E52">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F52" t="s">
         <v>1609</v>
@@ -10116,7 +10116,7 @@
         <v>1434</v>
       </c>
       <c r="E53">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F53" t="s">
         <v>1609</v>
@@ -10151,7 +10151,7 @@
         <v>1435</v>
       </c>
       <c r="E54">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F54" t="s">
         <v>1609</v>
@@ -10186,7 +10186,7 @@
         <v>1435</v>
       </c>
       <c r="E55">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F55" t="s">
         <v>1609</v>
@@ -10221,7 +10221,7 @@
         <v>1436</v>
       </c>
       <c r="E56">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F56" t="s">
         <v>1609</v>
@@ -10256,7 +10256,7 @@
         <v>1436</v>
       </c>
       <c r="E57">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F57" t="s">
         <v>1609</v>
@@ -10291,7 +10291,7 @@
         <v>1437</v>
       </c>
       <c r="E58">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F58" t="s">
         <v>1609</v>
@@ -10326,7 +10326,7 @@
         <v>1438</v>
       </c>
       <c r="E59">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F59" t="s">
         <v>1609</v>
@@ -10361,7 +10361,7 @@
         <v>1439</v>
       </c>
       <c r="E60">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F60" t="s">
         <v>1609</v>
@@ -10396,7 +10396,7 @@
         <v>1440</v>
       </c>
       <c r="E61">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F61" t="s">
         <v>1609</v>
@@ -10431,7 +10431,7 @@
         <v>1441</v>
       </c>
       <c r="E62">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F62" t="s">
         <v>1609</v>
@@ -10466,7 +10466,7 @@
         <v>1441</v>
       </c>
       <c r="E63">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F63" t="s">
         <v>1609</v>
@@ -10501,7 +10501,7 @@
         <v>1442</v>
       </c>
       <c r="E64">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F64" t="s">
         <v>1609</v>
@@ -10536,7 +10536,7 @@
         <v>1442</v>
       </c>
       <c r="E65">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F65" t="s">
         <v>1609</v>
@@ -10571,7 +10571,7 @@
         <v>1443</v>
       </c>
       <c r="E66">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F66" t="s">
         <v>1609</v>
@@ -10606,7 +10606,7 @@
         <v>1444</v>
       </c>
       <c r="E67">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F67" t="s">
         <v>1609</v>
@@ -10641,7 +10641,7 @@
         <v>1445</v>
       </c>
       <c r="E68">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F68" t="s">
         <v>1609</v>
@@ -10676,7 +10676,7 @@
         <v>1446</v>
       </c>
       <c r="E69">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F69" t="s">
         <v>1609</v>
@@ -10711,7 +10711,7 @@
         <v>1447</v>
       </c>
       <c r="E70">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F70" t="s">
         <v>1609</v>
@@ -10746,7 +10746,7 @@
         <v>1448</v>
       </c>
       <c r="E71">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F71" t="s">
         <v>1609</v>
@@ -10781,7 +10781,7 @@
         <v>1449</v>
       </c>
       <c r="E72">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F72" t="s">
         <v>1609</v>
@@ -10816,7 +10816,7 @@
         <v>1450</v>
       </c>
       <c r="E73">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F73" t="s">
         <v>1609</v>
@@ -10851,7 +10851,7 @@
         <v>1451</v>
       </c>
       <c r="E74">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F74" t="s">
         <v>1609</v>
@@ -10886,7 +10886,7 @@
         <v>1452</v>
       </c>
       <c r="E75">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F75" t="s">
         <v>1609</v>
@@ -10921,7 +10921,7 @@
         <v>1453</v>
       </c>
       <c r="E76">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F76" t="s">
         <v>1609</v>
@@ -10956,7 +10956,7 @@
         <v>1454</v>
       </c>
       <c r="E77">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F77" t="s">
         <v>1609</v>
@@ -10991,7 +10991,7 @@
         <v>1454</v>
       </c>
       <c r="E78">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F78" t="s">
         <v>1609</v>
@@ -11026,7 +11026,7 @@
         <v>1454</v>
       </c>
       <c r="E79">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F79" t="s">
         <v>1609</v>
@@ -11061,7 +11061,7 @@
         <v>1455</v>
       </c>
       <c r="E80">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F80" t="s">
         <v>1609</v>
@@ -11096,7 +11096,7 @@
         <v>1456</v>
       </c>
       <c r="E81">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F81" t="s">
         <v>1609</v>
@@ -11131,7 +11131,7 @@
         <v>1457</v>
       </c>
       <c r="E82">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F82" t="s">
         <v>1609</v>
@@ -11166,7 +11166,7 @@
         <v>1457</v>
       </c>
       <c r="E83">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F83" t="s">
         <v>1609</v>
@@ -11201,7 +11201,7 @@
         <v>1457</v>
       </c>
       <c r="E84">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F84" t="s">
         <v>1609</v>
@@ -11236,7 +11236,7 @@
         <v>1458</v>
       </c>
       <c r="E85">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F85" t="s">
         <v>1609</v>
@@ -11271,7 +11271,7 @@
         <v>1459</v>
       </c>
       <c r="E86">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F86" t="s">
         <v>1609</v>
@@ -11306,7 +11306,7 @@
         <v>1460</v>
       </c>
       <c r="E87">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F87" t="s">
         <v>1609</v>
@@ -11341,7 +11341,7 @@
         <v>1460</v>
       </c>
       <c r="E88">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F88" t="s">
         <v>1609</v>
@@ -11376,7 +11376,7 @@
         <v>1460</v>
       </c>
       <c r="E89">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F89" t="s">
         <v>1609</v>
@@ -11411,7 +11411,7 @@
         <v>1461</v>
       </c>
       <c r="E90">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F90" t="s">
         <v>1609</v>
@@ -11446,7 +11446,7 @@
         <v>1462</v>
       </c>
       <c r="E91">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F91" t="s">
         <v>1609</v>
@@ -11481,7 +11481,7 @@
         <v>1462</v>
       </c>
       <c r="E92">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F92" t="s">
         <v>1609</v>
@@ -11516,7 +11516,7 @@
         <v>1462</v>
       </c>
       <c r="E93">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F93" t="s">
         <v>1610</v>
@@ -11551,7 +11551,7 @@
         <v>1462</v>
       </c>
       <c r="E94">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F94" t="s">
         <v>1609</v>
@@ -11586,7 +11586,7 @@
         <v>1463</v>
       </c>
       <c r="E95">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F95" t="s">
         <v>1609</v>
@@ -11621,7 +11621,7 @@
         <v>1464</v>
       </c>
       <c r="E96">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F96" t="s">
         <v>1609</v>
@@ -11656,7 +11656,7 @@
         <v>1465</v>
       </c>
       <c r="E97">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F97" t="s">
         <v>1609</v>
@@ -11691,7 +11691,7 @@
         <v>1465</v>
       </c>
       <c r="E98">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F98" t="s">
         <v>1609</v>
@@ -11726,7 +11726,7 @@
         <v>1465</v>
       </c>
       <c r="E99">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F99" t="s">
         <v>1609</v>
@@ -11761,7 +11761,7 @@
         <v>1466</v>
       </c>
       <c r="E100">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F100" t="s">
         <v>1609</v>
@@ -11796,7 +11796,7 @@
         <v>1467</v>
       </c>
       <c r="E101">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F101" t="s">
         <v>1609</v>
@@ -11831,7 +11831,7 @@
         <v>1468</v>
       </c>
       <c r="E102">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F102" t="s">
         <v>1609</v>
@@ -11866,7 +11866,7 @@
         <v>1469</v>
       </c>
       <c r="E103">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F103" t="s">
         <v>1609</v>
@@ -11901,7 +11901,7 @@
         <v>1470</v>
       </c>
       <c r="E104">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F104" t="s">
         <v>1609</v>
@@ -11936,7 +11936,7 @@
         <v>1470</v>
       </c>
       <c r="E105">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F105" t="s">
         <v>1609</v>
@@ -11971,7 +11971,7 @@
         <v>1470</v>
       </c>
       <c r="E106">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F106" t="s">
         <v>1609</v>
@@ -12006,7 +12006,7 @@
         <v>1470</v>
       </c>
       <c r="E107">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F107" t="s">
         <v>1609</v>
@@ -12041,7 +12041,7 @@
         <v>1470</v>
       </c>
       <c r="E108">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F108" t="s">
         <v>1609</v>
@@ -12076,7 +12076,7 @@
         <v>1470</v>
       </c>
       <c r="E109">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F109" t="s">
         <v>1609</v>
@@ -12111,7 +12111,7 @@
         <v>1470</v>
       </c>
       <c r="E110">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F110" t="s">
         <v>1609</v>
@@ -12146,7 +12146,7 @@
         <v>1471</v>
       </c>
       <c r="E111">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F111" t="s">
         <v>1609</v>
@@ -12181,7 +12181,7 @@
         <v>1471</v>
       </c>
       <c r="E112">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F112" t="s">
         <v>1609</v>
@@ -12216,7 +12216,7 @@
         <v>1472</v>
       </c>
       <c r="E113">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F113" t="s">
         <v>1609</v>
@@ -12251,7 +12251,7 @@
         <v>1473</v>
       </c>
       <c r="E114">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F114" t="s">
         <v>1609</v>
@@ -12286,7 +12286,7 @@
         <v>1473</v>
       </c>
       <c r="E115">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F115" t="s">
         <v>1609</v>
@@ -12321,7 +12321,7 @@
         <v>1474</v>
       </c>
       <c r="E116">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F116" t="s">
         <v>1609</v>
@@ -12356,7 +12356,7 @@
         <v>1474</v>
       </c>
       <c r="E117">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F117" t="s">
         <v>1611</v>
@@ -12391,7 +12391,7 @@
         <v>1475</v>
       </c>
       <c r="E118">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F118" t="s">
         <v>1609</v>
@@ -12426,7 +12426,7 @@
         <v>1476</v>
       </c>
       <c r="E119">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F119" t="s">
         <v>1609</v>
@@ -12461,7 +12461,7 @@
         <v>1477</v>
       </c>
       <c r="E120">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F120" t="s">
         <v>1609</v>
@@ -12496,7 +12496,7 @@
         <v>1477</v>
       </c>
       <c r="E121">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F121" t="s">
         <v>1609</v>
@@ -12531,7 +12531,7 @@
         <v>1478</v>
       </c>
       <c r="E122">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F122" t="s">
         <v>1609</v>
@@ -12566,7 +12566,7 @@
         <v>1479</v>
       </c>
       <c r="E123">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F123" t="s">
         <v>1609</v>
@@ -12601,7 +12601,7 @@
         <v>1480</v>
       </c>
       <c r="E124">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F124" t="s">
         <v>1609</v>
@@ -12636,7 +12636,7 @@
         <v>1480</v>
       </c>
       <c r="E125">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F125" t="s">
         <v>1609</v>
@@ -12671,7 +12671,7 @@
         <v>1481</v>
       </c>
       <c r="E126">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F126" t="s">
         <v>1609</v>
@@ -12706,7 +12706,7 @@
         <v>1482</v>
       </c>
       <c r="E127">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F127" t="s">
         <v>1609</v>
@@ -12741,7 +12741,7 @@
         <v>1482</v>
       </c>
       <c r="E128">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F128" t="s">
         <v>1609</v>
@@ -12776,7 +12776,7 @@
         <v>1483</v>
       </c>
       <c r="E129">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F129" t="s">
         <v>1609</v>
@@ -12811,7 +12811,7 @@
         <v>1483</v>
       </c>
       <c r="E130">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F130" t="s">
         <v>1609</v>
@@ -12846,7 +12846,7 @@
         <v>1483</v>
       </c>
       <c r="E131">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F131" t="s">
         <v>1609</v>
@@ -12881,7 +12881,7 @@
         <v>1483</v>
       </c>
       <c r="E132">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F132" t="s">
         <v>1609</v>
@@ -12916,7 +12916,7 @@
         <v>1484</v>
       </c>
       <c r="E133">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F133" t="s">
         <v>1609</v>
@@ -12951,7 +12951,7 @@
         <v>1484</v>
       </c>
       <c r="E134">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F134" t="s">
         <v>1609</v>
@@ -12986,7 +12986,7 @@
         <v>1484</v>
       </c>
       <c r="E135">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F135" t="s">
         <v>1609</v>
@@ -13021,7 +13021,7 @@
         <v>1484</v>
       </c>
       <c r="E136">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F136" t="s">
         <v>1609</v>
@@ -13056,7 +13056,7 @@
         <v>1484</v>
       </c>
       <c r="E137">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F137" t="s">
         <v>1609</v>
@@ -13091,7 +13091,7 @@
         <v>1484</v>
       </c>
       <c r="E138">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F138" t="s">
         <v>1609</v>
@@ -13126,7 +13126,7 @@
         <v>1485</v>
       </c>
       <c r="E139">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F139" t="s">
         <v>1609</v>
@@ -13161,7 +13161,7 @@
         <v>1485</v>
       </c>
       <c r="E140">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F140" t="s">
         <v>1609</v>
@@ -13196,7 +13196,7 @@
         <v>1486</v>
       </c>
       <c r="E141">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F141" t="s">
         <v>1609</v>
@@ -13231,7 +13231,7 @@
         <v>1486</v>
       </c>
       <c r="E142">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F142" t="s">
         <v>1609</v>
@@ -13266,7 +13266,7 @@
         <v>1487</v>
       </c>
       <c r="E143">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F143" t="s">
         <v>1609</v>
@@ -13301,7 +13301,7 @@
         <v>1488</v>
       </c>
       <c r="E144">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F144" t="s">
         <v>1609</v>
@@ -13336,7 +13336,7 @@
         <v>1488</v>
       </c>
       <c r="E145">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F145" t="s">
         <v>1609</v>
@@ -13371,7 +13371,7 @@
         <v>1488</v>
       </c>
       <c r="E146">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F146" t="s">
         <v>1609</v>
@@ -13406,7 +13406,7 @@
         <v>1489</v>
       </c>
       <c r="E147">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F147" t="s">
         <v>1609</v>
@@ -13441,7 +13441,7 @@
         <v>1489</v>
       </c>
       <c r="E148">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F148" t="s">
         <v>1609</v>
@@ -13476,7 +13476,7 @@
         <v>1489</v>
       </c>
       <c r="E149">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F149" t="s">
         <v>1609</v>
@@ -13511,7 +13511,7 @@
         <v>1490</v>
       </c>
       <c r="E150">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F150" t="s">
         <v>1609</v>
@@ -13546,7 +13546,7 @@
         <v>1490</v>
       </c>
       <c r="E151">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F151" t="s">
         <v>1609</v>
@@ -13581,7 +13581,7 @@
         <v>1490</v>
       </c>
       <c r="E152">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F152" t="s">
         <v>1609</v>
@@ -13616,7 +13616,7 @@
         <v>1491</v>
       </c>
       <c r="E153">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F153" t="s">
         <v>1609</v>
@@ -13651,7 +13651,7 @@
         <v>1491</v>
       </c>
       <c r="E154">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F154" t="s">
         <v>1609</v>
@@ -13686,7 +13686,7 @@
         <v>1492</v>
       </c>
       <c r="E155">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F155" t="s">
         <v>1609</v>
@@ -13721,7 +13721,7 @@
         <v>1493</v>
       </c>
       <c r="E156">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F156" t="s">
         <v>1609</v>
@@ -13756,7 +13756,7 @@
         <v>1493</v>
       </c>
       <c r="E157">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F157" t="s">
         <v>1609</v>
@@ -13791,7 +13791,7 @@
         <v>1493</v>
       </c>
       <c r="E158">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F158" t="s">
         <v>1609</v>
@@ -13826,7 +13826,7 @@
         <v>1494</v>
       </c>
       <c r="E159">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F159" t="s">
         <v>1609</v>
@@ -13861,7 +13861,7 @@
         <v>1494</v>
       </c>
       <c r="E160">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F160" t="s">
         <v>1609</v>
@@ -13896,7 +13896,7 @@
         <v>1495</v>
       </c>
       <c r="E161">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F161" t="s">
         <v>1609</v>
@@ -13934,7 +13934,7 @@
         <v>1495</v>
       </c>
       <c r="E162">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F162" t="s">
         <v>1609</v>
@@ -13969,7 +13969,7 @@
         <v>1495</v>
       </c>
       <c r="E163">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F163" t="s">
         <v>1609</v>
@@ -14004,7 +14004,7 @@
         <v>1495</v>
       </c>
       <c r="E164">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F164" t="s">
         <v>1609</v>
@@ -14039,7 +14039,7 @@
         <v>1495</v>
       </c>
       <c r="E165">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F165" t="s">
         <v>1609</v>
@@ -14074,7 +14074,7 @@
         <v>1495</v>
       </c>
       <c r="E166">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F166" t="s">
         <v>1609</v>
@@ -14109,7 +14109,7 @@
         <v>1496</v>
       </c>
       <c r="E167">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F167" t="s">
         <v>1609</v>
@@ -14144,7 +14144,7 @@
         <v>1497</v>
       </c>
       <c r="E168">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F168" t="s">
         <v>1609</v>
@@ -14179,7 +14179,7 @@
         <v>1498</v>
       </c>
       <c r="E169">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F169" t="s">
         <v>1610</v>
@@ -14214,7 +14214,7 @@
         <v>1499</v>
       </c>
       <c r="E170">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F170" t="s">
         <v>1609</v>
@@ -14249,7 +14249,7 @@
         <v>1499</v>
       </c>
       <c r="E171">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F171" t="s">
         <v>1609</v>
@@ -14284,7 +14284,7 @@
         <v>1499</v>
       </c>
       <c r="E172">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F172" t="s">
         <v>1609</v>
@@ -14319,7 +14319,7 @@
         <v>1499</v>
       </c>
       <c r="E173">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F173" t="s">
         <v>1609</v>
@@ -14354,7 +14354,7 @@
         <v>1500</v>
       </c>
       <c r="E174">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F174" t="s">
         <v>1609</v>
@@ -14389,7 +14389,7 @@
         <v>1500</v>
       </c>
       <c r="E175">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F175" t="s">
         <v>1609</v>
@@ -14424,7 +14424,7 @@
         <v>1500</v>
       </c>
       <c r="E176">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F176" t="s">
         <v>1609</v>
@@ -14459,7 +14459,7 @@
         <v>1500</v>
       </c>
       <c r="E177">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F177" t="s">
         <v>1609</v>
@@ -14494,7 +14494,7 @@
         <v>1500</v>
       </c>
       <c r="E178">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F178" t="s">
         <v>1609</v>
@@ -14529,7 +14529,7 @@
         <v>1500</v>
       </c>
       <c r="E179">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F179" t="s">
         <v>1609</v>
@@ -14564,7 +14564,7 @@
         <v>1500</v>
       </c>
       <c r="E180">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F180" t="s">
         <v>1609</v>
@@ -14599,7 +14599,7 @@
         <v>1501</v>
       </c>
       <c r="E181">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F181" t="s">
         <v>1609</v>
@@ -14634,7 +14634,7 @@
         <v>1501</v>
       </c>
       <c r="E182">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F182" t="s">
         <v>1609</v>
@@ -14669,7 +14669,7 @@
         <v>1502</v>
       </c>
       <c r="E183">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F183" t="s">
         <v>1609</v>
@@ -14704,7 +14704,7 @@
         <v>1502</v>
       </c>
       <c r="E184">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F184" t="s">
         <v>1609</v>
@@ -14739,7 +14739,7 @@
         <v>1502</v>
       </c>
       <c r="E185">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F185" t="s">
         <v>1609</v>
@@ -14774,7 +14774,7 @@
         <v>1503</v>
       </c>
       <c r="E186">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F186" t="s">
         <v>1609</v>
@@ -14809,7 +14809,7 @@
         <v>1503</v>
       </c>
       <c r="E187">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F187" t="s">
         <v>1609</v>
@@ -14844,7 +14844,7 @@
         <v>1503</v>
       </c>
       <c r="E188">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F188" t="s">
         <v>1609</v>
@@ -14879,7 +14879,7 @@
         <v>1503</v>
       </c>
       <c r="E189">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F189" t="s">
         <v>1609</v>
@@ -14914,7 +14914,7 @@
         <v>1504</v>
       </c>
       <c r="E190">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F190" t="s">
         <v>1609</v>
@@ -14949,7 +14949,7 @@
         <v>1504</v>
       </c>
       <c r="E191">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F191" t="s">
         <v>1609</v>
@@ -14984,7 +14984,7 @@
         <v>1504</v>
       </c>
       <c r="E192">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F192" t="s">
         <v>1609</v>
@@ -15019,7 +15019,7 @@
         <v>1504</v>
       </c>
       <c r="E193">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F193" t="s">
         <v>1609</v>
@@ -15054,7 +15054,7 @@
         <v>1504</v>
       </c>
       <c r="E194">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F194" t="s">
         <v>1609</v>
@@ -15089,7 +15089,7 @@
         <v>1504</v>
       </c>
       <c r="E195">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F195" t="s">
         <v>1609</v>
@@ -15124,7 +15124,7 @@
         <v>1504</v>
       </c>
       <c r="E196">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F196" t="s">
         <v>1609</v>
@@ -15159,7 +15159,7 @@
         <v>1504</v>
       </c>
       <c r="E197">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F197" t="s">
         <v>1609</v>
@@ -15194,7 +15194,7 @@
         <v>1504</v>
       </c>
       <c r="E198">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F198" t="s">
         <v>1609</v>
@@ -15229,7 +15229,7 @@
         <v>1504</v>
       </c>
       <c r="E199">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F199" t="s">
         <v>1609</v>
@@ -15264,7 +15264,7 @@
         <v>1505</v>
       </c>
       <c r="E200">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F200" t="s">
         <v>1609</v>
@@ -15299,7 +15299,7 @@
         <v>1505</v>
       </c>
       <c r="E201">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F201" t="s">
         <v>1609</v>
@@ -15334,7 +15334,7 @@
         <v>1505</v>
       </c>
       <c r="E202">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F202" t="s">
         <v>1609</v>
@@ -15369,7 +15369,7 @@
         <v>1505</v>
       </c>
       <c r="E203">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F203" t="s">
         <v>1612</v>
@@ -15404,7 +15404,7 @@
         <v>1506</v>
       </c>
       <c r="E204">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F204" t="s">
         <v>1609</v>
@@ -15439,7 +15439,7 @@
         <v>1506</v>
       </c>
       <c r="E205">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F205" t="s">
         <v>1610</v>
@@ -15474,7 +15474,7 @@
         <v>1506</v>
       </c>
       <c r="E206">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F206" t="s">
         <v>1609</v>
@@ -15509,7 +15509,7 @@
         <v>1507</v>
       </c>
       <c r="E207">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F207" t="s">
         <v>1609</v>
@@ -15544,7 +15544,7 @@
         <v>1507</v>
       </c>
       <c r="E208">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F208" t="s">
         <v>1609</v>
@@ -15579,7 +15579,7 @@
         <v>1508</v>
       </c>
       <c r="E209">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F209" t="s">
         <v>1609</v>
@@ -15614,7 +15614,7 @@
         <v>1508</v>
       </c>
       <c r="E210">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F210" t="s">
         <v>1609</v>
@@ -15649,7 +15649,7 @@
         <v>1509</v>
       </c>
       <c r="E211">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F211" t="s">
         <v>1609</v>
@@ -15684,7 +15684,7 @@
         <v>1509</v>
       </c>
       <c r="E212">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F212" t="s">
         <v>1609</v>
@@ -15719,7 +15719,7 @@
         <v>1509</v>
       </c>
       <c r="E213">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F213" t="s">
         <v>1609</v>
@@ -15754,7 +15754,7 @@
         <v>1510</v>
       </c>
       <c r="E214">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F214" t="s">
         <v>1609</v>
@@ -15789,7 +15789,7 @@
         <v>1510</v>
       </c>
       <c r="E215">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F215" t="s">
         <v>1609</v>
@@ -15824,7 +15824,7 @@
         <v>1510</v>
       </c>
       <c r="E216">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F216" t="s">
         <v>1609</v>
@@ -15859,7 +15859,7 @@
         <v>1510</v>
       </c>
       <c r="E217">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F217" t="s">
         <v>1609</v>
@@ -15894,7 +15894,7 @@
         <v>1510</v>
       </c>
       <c r="E218">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F218" t="s">
         <v>1609</v>
@@ -15929,7 +15929,7 @@
         <v>1510</v>
       </c>
       <c r="E219">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F219" t="s">
         <v>1609</v>
@@ -15964,7 +15964,7 @@
         <v>1511</v>
       </c>
       <c r="E220">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F220" t="s">
         <v>1609</v>
@@ -15999,7 +15999,7 @@
         <v>1511</v>
       </c>
       <c r="E221">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F221" t="s">
         <v>1609</v>
@@ -16034,7 +16034,7 @@
         <v>1512</v>
       </c>
       <c r="E222">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F222" t="s">
         <v>1609</v>
@@ -16069,7 +16069,7 @@
         <v>1513</v>
       </c>
       <c r="E223">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F223" t="s">
         <v>1609</v>
@@ -16104,7 +16104,7 @@
         <v>1513</v>
       </c>
       <c r="E224">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F224" t="s">
         <v>1609</v>
@@ -16139,7 +16139,7 @@
         <v>1513</v>
       </c>
       <c r="E225">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F225" t="s">
         <v>1609</v>
@@ -16174,7 +16174,7 @@
         <v>1513</v>
       </c>
       <c r="E226">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F226" t="s">
         <v>1609</v>
@@ -16209,7 +16209,7 @@
         <v>1514</v>
       </c>
       <c r="E227">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F227" t="s">
         <v>1609</v>
@@ -16244,7 +16244,7 @@
         <v>1515</v>
       </c>
       <c r="E228">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F228" t="s">
         <v>1609</v>
@@ -16279,7 +16279,7 @@
         <v>1515</v>
       </c>
       <c r="E229">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F229" t="s">
         <v>1609</v>
@@ -16314,7 +16314,7 @@
         <v>1515</v>
       </c>
       <c r="E230">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F230" t="s">
         <v>1609</v>
@@ -16349,7 +16349,7 @@
         <v>1515</v>
       </c>
       <c r="E231">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F231" t="s">
         <v>1609</v>
@@ -16384,7 +16384,7 @@
         <v>1515</v>
       </c>
       <c r="E232">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F232" t="s">
         <v>1609</v>
@@ -16419,7 +16419,7 @@
         <v>1516</v>
       </c>
       <c r="E233">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F233" t="s">
         <v>1609</v>
@@ -16454,7 +16454,7 @@
         <v>1516</v>
       </c>
       <c r="E234">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F234" t="s">
         <v>1609</v>
@@ -16489,7 +16489,7 @@
         <v>1516</v>
       </c>
       <c r="E235">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F235" t="s">
         <v>1609</v>
@@ -16524,7 +16524,7 @@
         <v>1516</v>
       </c>
       <c r="E236">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F236" t="s">
         <v>1609</v>
@@ -16559,7 +16559,7 @@
         <v>1516</v>
       </c>
       <c r="E237">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F237" t="s">
         <v>1609</v>
@@ -16594,7 +16594,7 @@
         <v>1516</v>
       </c>
       <c r="E238">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F238" t="s">
         <v>1609</v>
@@ -16629,7 +16629,7 @@
         <v>1516</v>
       </c>
       <c r="E239">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F239" t="s">
         <v>1609</v>
@@ -16664,7 +16664,7 @@
         <v>1517</v>
       </c>
       <c r="E240">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F240" t="s">
         <v>1609</v>
@@ -16699,7 +16699,7 @@
         <v>1517</v>
       </c>
       <c r="E241">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F241" t="s">
         <v>1609</v>
@@ -16734,7 +16734,7 @@
         <v>1517</v>
       </c>
       <c r="E242">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F242" t="s">
         <v>1609</v>
@@ -16769,7 +16769,7 @@
         <v>1517</v>
       </c>
       <c r="E243">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F243" t="s">
         <v>1609</v>
@@ -16804,7 +16804,7 @@
         <v>1518</v>
       </c>
       <c r="E244">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F244" t="s">
         <v>1609</v>
@@ -16839,7 +16839,7 @@
         <v>1518</v>
       </c>
       <c r="E245">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F245" t="s">
         <v>1609</v>
@@ -16874,7 +16874,7 @@
         <v>1518</v>
       </c>
       <c r="E246">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F246" t="s">
         <v>1609</v>
@@ -16909,7 +16909,7 @@
         <v>1519</v>
       </c>
       <c r="E247">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F247" t="s">
         <v>1609</v>
@@ -16944,7 +16944,7 @@
         <v>1519</v>
       </c>
       <c r="E248">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F248" t="s">
         <v>1609</v>
@@ -16979,7 +16979,7 @@
         <v>1520</v>
       </c>
       <c r="E249">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F249" t="s">
         <v>1609</v>
@@ -17014,7 +17014,7 @@
         <v>1520</v>
       </c>
       <c r="E250">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F250" t="s">
         <v>1609</v>
@@ -17049,7 +17049,7 @@
         <v>1521</v>
       </c>
       <c r="E251">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F251" t="s">
         <v>1609</v>
@@ -17084,7 +17084,7 @@
         <v>1521</v>
       </c>
       <c r="E252">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F252" t="s">
         <v>1609</v>
@@ -17119,7 +17119,7 @@
         <v>1522</v>
       </c>
       <c r="E253">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F253" t="s">
         <v>1609</v>
@@ -17154,7 +17154,7 @@
         <v>1522</v>
       </c>
       <c r="E254">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F254" t="s">
         <v>1609</v>
@@ -17189,7 +17189,7 @@
         <v>1523</v>
       </c>
       <c r="E255">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F255" t="s">
         <v>1609</v>
@@ -17224,7 +17224,7 @@
         <v>1523</v>
       </c>
       <c r="E256">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F256" t="s">
         <v>1609</v>
@@ -17259,7 +17259,7 @@
         <v>1524</v>
       </c>
       <c r="E257">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F257" t="s">
         <v>1609</v>
@@ -17294,7 +17294,7 @@
         <v>1524</v>
       </c>
       <c r="E258">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F258" t="s">
         <v>1609</v>
@@ -17329,7 +17329,7 @@
         <v>1525</v>
       </c>
       <c r="E259">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F259" t="s">
         <v>1609</v>
@@ -17364,7 +17364,7 @@
         <v>1525</v>
       </c>
       <c r="E260">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F260" t="s">
         <v>1609</v>
@@ -17399,7 +17399,7 @@
         <v>1525</v>
       </c>
       <c r="E261">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F261" t="s">
         <v>1609</v>
@@ -17434,7 +17434,7 @@
         <v>1526</v>
       </c>
       <c r="E262">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F262" t="s">
         <v>1609</v>
@@ -17469,7 +17469,7 @@
         <v>1526</v>
       </c>
       <c r="E263">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F263" t="s">
         <v>1609</v>
@@ -17504,7 +17504,7 @@
         <v>1526</v>
       </c>
       <c r="E264">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F264" t="s">
         <v>1609</v>
@@ -17539,7 +17539,7 @@
         <v>1527</v>
       </c>
       <c r="E265">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F265" t="s">
         <v>1609</v>
@@ -17574,7 +17574,7 @@
         <v>1528</v>
       </c>
       <c r="E266">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F266" t="s">
         <v>1609</v>
@@ -17609,7 +17609,7 @@
         <v>1528</v>
       </c>
       <c r="E267">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F267" t="s">
         <v>1609</v>
@@ -17644,7 +17644,7 @@
         <v>1528</v>
       </c>
       <c r="E268">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F268" t="s">
         <v>1609</v>
@@ -17679,7 +17679,7 @@
         <v>1529</v>
       </c>
       <c r="E269">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F269" t="s">
         <v>1609</v>
@@ -17714,7 +17714,7 @@
         <v>1529</v>
       </c>
       <c r="E270">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F270" t="s">
         <v>1609</v>
@@ -17749,7 +17749,7 @@
         <v>1530</v>
       </c>
       <c r="E271">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F271" t="s">
         <v>1609</v>
@@ -17784,7 +17784,7 @@
         <v>1530</v>
       </c>
       <c r="E272">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F272" t="s">
         <v>1609</v>
@@ -17819,7 +17819,7 @@
         <v>1530</v>
       </c>
       <c r="E273">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F273" t="s">
         <v>1611</v>
@@ -17854,7 +17854,7 @@
         <v>1530</v>
       </c>
       <c r="E274">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F274" t="s">
         <v>1609</v>
@@ -17889,7 +17889,7 @@
         <v>1530</v>
       </c>
       <c r="E275">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F275" t="s">
         <v>1609</v>
@@ -17924,7 +17924,7 @@
         <v>1531</v>
       </c>
       <c r="E276">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F276" t="s">
         <v>1609</v>
@@ -17959,7 +17959,7 @@
         <v>1531</v>
       </c>
       <c r="E277">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F277" t="s">
         <v>1609</v>
@@ -17994,7 +17994,7 @@
         <v>1531</v>
       </c>
       <c r="E278">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F278" t="s">
         <v>1609</v>
@@ -18032,7 +18032,7 @@
         <v>1531</v>
       </c>
       <c r="E279">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F279" t="s">
         <v>1609</v>
@@ -18067,7 +18067,7 @@
         <v>1531</v>
       </c>
       <c r="E280">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F280" t="s">
         <v>1609</v>
@@ -18102,7 +18102,7 @@
         <v>1531</v>
       </c>
       <c r="E281">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F281" t="s">
         <v>1609</v>
@@ -18137,7 +18137,7 @@
         <v>1531</v>
       </c>
       <c r="E282">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F282" t="s">
         <v>1609</v>
@@ -18172,7 +18172,7 @@
         <v>1532</v>
       </c>
       <c r="E283">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F283" t="s">
         <v>1609</v>
@@ -18207,7 +18207,7 @@
         <v>1532</v>
       </c>
       <c r="E284">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F284" t="s">
         <v>1609</v>
@@ -18242,7 +18242,7 @@
         <v>1532</v>
       </c>
       <c r="E285">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F285" t="s">
         <v>1609</v>
@@ -18277,7 +18277,7 @@
         <v>1532</v>
       </c>
       <c r="E286">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F286" t="s">
         <v>1609</v>
@@ -18312,7 +18312,7 @@
         <v>1533</v>
       </c>
       <c r="E287">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F287" t="s">
         <v>1609</v>
@@ -18347,7 +18347,7 @@
         <v>1533</v>
       </c>
       <c r="E288">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F288" t="s">
         <v>1609</v>
@@ -18382,7 +18382,7 @@
         <v>1533</v>
       </c>
       <c r="E289">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F289" t="s">
         <v>1609</v>
@@ -18417,7 +18417,7 @@
         <v>1533</v>
       </c>
       <c r="E290">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F290" t="s">
         <v>1609</v>
@@ -18452,7 +18452,7 @@
         <v>1533</v>
       </c>
       <c r="E291">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F291" t="s">
         <v>1609</v>
@@ -18487,7 +18487,7 @@
         <v>1534</v>
       </c>
       <c r="E292">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F292" t="s">
         <v>1609</v>
@@ -18522,7 +18522,7 @@
         <v>1534</v>
       </c>
       <c r="E293">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F293" t="s">
         <v>1609</v>
@@ -18557,7 +18557,7 @@
         <v>1534</v>
       </c>
       <c r="E294">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F294" t="s">
         <v>1609</v>
@@ -18592,7 +18592,7 @@
         <v>1534</v>
       </c>
       <c r="E295">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F295" t="s">
         <v>1609</v>
@@ -18627,7 +18627,7 @@
         <v>1534</v>
       </c>
       <c r="E296">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F296" t="s">
         <v>1609</v>
@@ -18662,7 +18662,7 @@
         <v>1534</v>
       </c>
       <c r="E297">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F297" t="s">
         <v>1609</v>
@@ -18697,7 +18697,7 @@
         <v>1535</v>
       </c>
       <c r="E298">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F298" t="s">
         <v>1609</v>
@@ -18732,7 +18732,7 @@
         <v>1535</v>
       </c>
       <c r="E299">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F299" t="s">
         <v>1609</v>
@@ -18767,7 +18767,7 @@
         <v>1535</v>
       </c>
       <c r="E300">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F300" t="s">
         <v>1609</v>
@@ -18802,7 +18802,7 @@
         <v>1535</v>
       </c>
       <c r="E301">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F301" t="s">
         <v>1609</v>
@@ -18837,7 +18837,7 @@
         <v>1535</v>
       </c>
       <c r="E302">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F302" t="s">
         <v>1609</v>
@@ -18872,7 +18872,7 @@
         <v>1535</v>
       </c>
       <c r="E303">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F303" t="s">
         <v>1609</v>
@@ -18907,7 +18907,7 @@
         <v>1536</v>
       </c>
       <c r="E304">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F304" t="s">
         <v>1609</v>
@@ -18942,7 +18942,7 @@
         <v>1536</v>
       </c>
       <c r="E305">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F305" t="s">
         <v>1609</v>
@@ -18977,7 +18977,7 @@
         <v>1537</v>
       </c>
       <c r="E306">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F306" t="s">
         <v>1610</v>
@@ -19012,7 +19012,7 @@
         <v>1537</v>
       </c>
       <c r="E307">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F307" t="s">
         <v>1609</v>
@@ -19047,7 +19047,7 @@
         <v>1537</v>
       </c>
       <c r="E308">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F308" t="s">
         <v>1609</v>
@@ -19082,7 +19082,7 @@
         <v>1537</v>
       </c>
       <c r="E309">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F309" t="s">
         <v>1612</v>
@@ -19117,7 +19117,7 @@
         <v>1537</v>
       </c>
       <c r="E310">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F310" t="s">
         <v>1609</v>
@@ -19152,7 +19152,7 @@
         <v>1537</v>
       </c>
       <c r="E311">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F311" t="s">
         <v>1609</v>
@@ -19187,7 +19187,7 @@
         <v>1537</v>
       </c>
       <c r="E312">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F312" t="s">
         <v>1609</v>
@@ -19222,7 +19222,7 @@
         <v>1537</v>
       </c>
       <c r="E313">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F313" t="s">
         <v>1609</v>
@@ -19257,7 +19257,7 @@
         <v>1538</v>
       </c>
       <c r="E314">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F314" t="s">
         <v>1609</v>
@@ -19292,7 +19292,7 @@
         <v>1538</v>
       </c>
       <c r="E315">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F315" t="s">
         <v>1609</v>
@@ -19327,7 +19327,7 @@
         <v>1538</v>
       </c>
       <c r="E316">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F316" t="s">
         <v>1609</v>
@@ -19362,7 +19362,7 @@
         <v>1538</v>
       </c>
       <c r="E317">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F317" t="s">
         <v>1609</v>
@@ -19397,7 +19397,7 @@
         <v>1539</v>
       </c>
       <c r="E318">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F318" t="s">
         <v>1609</v>
@@ -19432,7 +19432,7 @@
         <v>1539</v>
       </c>
       <c r="E319">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F319" t="s">
         <v>1609</v>
@@ -19467,7 +19467,7 @@
         <v>1540</v>
       </c>
       <c r="E320">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F320" t="s">
         <v>1609</v>
@@ -19505,7 +19505,7 @@
         <v>1540</v>
       </c>
       <c r="E321">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F321" t="s">
         <v>1609</v>
@@ -19540,7 +19540,7 @@
         <v>1541</v>
       </c>
       <c r="E322">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F322" t="s">
         <v>1609</v>
@@ -19575,7 +19575,7 @@
         <v>1541</v>
       </c>
       <c r="E323">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F323" t="s">
         <v>1609</v>
@@ -19610,7 +19610,7 @@
         <v>1541</v>
       </c>
       <c r="E324">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F324" t="s">
         <v>1609</v>
@@ -19645,7 +19645,7 @@
         <v>1541</v>
       </c>
       <c r="E325">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F325" t="s">
         <v>1609</v>
@@ -19683,7 +19683,7 @@
         <v>1541</v>
       </c>
       <c r="E326">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F326" t="s">
         <v>1609</v>
@@ -19718,7 +19718,7 @@
         <v>1541</v>
       </c>
       <c r="E327">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F327" t="s">
         <v>1609</v>
@@ -19753,7 +19753,7 @@
         <v>1542</v>
       </c>
       <c r="E328">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F328" t="s">
         <v>1609</v>
@@ -19788,7 +19788,7 @@
         <v>1542</v>
       </c>
       <c r="E329">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F329" t="s">
         <v>1609</v>
@@ -19823,7 +19823,7 @@
         <v>1543</v>
       </c>
       <c r="E330">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F330" t="s">
         <v>1609</v>
@@ -19858,7 +19858,7 @@
         <v>1543</v>
       </c>
       <c r="E331">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F331" t="s">
         <v>1609</v>
@@ -19893,7 +19893,7 @@
         <v>1544</v>
       </c>
       <c r="E332">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F332" t="s">
         <v>1609</v>
@@ -19928,7 +19928,7 @@
         <v>1544</v>
       </c>
       <c r="E333">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F333" t="s">
         <v>1609</v>
@@ -19963,7 +19963,7 @@
         <v>1544</v>
       </c>
       <c r="E334">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F334" t="s">
         <v>1609</v>
@@ -19998,7 +19998,7 @@
         <v>1544</v>
       </c>
       <c r="E335">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F335" t="s">
         <v>1609</v>
@@ -20033,7 +20033,7 @@
         <v>1544</v>
       </c>
       <c r="E336">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F336" t="s">
         <v>1609</v>
@@ -20068,7 +20068,7 @@
         <v>1545</v>
       </c>
       <c r="E337">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F337" t="s">
         <v>1609</v>
@@ -20103,7 +20103,7 @@
         <v>1545</v>
       </c>
       <c r="E338">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F338" t="s">
         <v>1609</v>
@@ -20138,7 +20138,7 @@
         <v>1545</v>
       </c>
       <c r="E339">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F339" t="s">
         <v>1609</v>
@@ -20173,7 +20173,7 @@
         <v>1545</v>
       </c>
       <c r="E340">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F340" t="s">
         <v>1609</v>
@@ -20208,7 +20208,7 @@
         <v>1546</v>
       </c>
       <c r="E341">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F341" t="s">
         <v>1609</v>
@@ -20243,7 +20243,7 @@
         <v>1546</v>
       </c>
       <c r="E342">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F342" t="s">
         <v>1609</v>
@@ -20278,7 +20278,7 @@
         <v>1547</v>
       </c>
       <c r="E343">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F343" t="s">
         <v>1609</v>
@@ -20313,7 +20313,7 @@
         <v>1547</v>
       </c>
       <c r="E344">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F344" t="s">
         <v>1609</v>
@@ -20348,7 +20348,7 @@
         <v>1547</v>
       </c>
       <c r="E345">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F345" t="s">
         <v>1609</v>
@@ -20383,7 +20383,7 @@
         <v>1547</v>
       </c>
       <c r="E346">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F346" t="s">
         <v>1609</v>
@@ -20418,7 +20418,7 @@
         <v>1547</v>
       </c>
       <c r="E347">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F347" t="s">
         <v>1609</v>
@@ -20453,7 +20453,7 @@
         <v>1548</v>
       </c>
       <c r="E348">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F348" t="s">
         <v>1609</v>
@@ -20488,7 +20488,7 @@
         <v>1548</v>
       </c>
       <c r="E349">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F349" t="s">
         <v>1609</v>
@@ -20523,7 +20523,7 @@
         <v>1548</v>
       </c>
       <c r="E350">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F350" t="s">
         <v>1609</v>
@@ -20558,7 +20558,7 @@
         <v>1548</v>
       </c>
       <c r="E351">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F351" t="s">
         <v>1609</v>
@@ -20593,7 +20593,7 @@
         <v>1549</v>
       </c>
       <c r="E352">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F352" t="s">
         <v>1609</v>
@@ -20628,7 +20628,7 @@
         <v>1549</v>
       </c>
       <c r="E353">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F353" t="s">
         <v>1609</v>
@@ -20663,7 +20663,7 @@
         <v>1550</v>
       </c>
       <c r="E354">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F354" t="s">
         <v>1609</v>
@@ -20698,7 +20698,7 @@
         <v>1550</v>
       </c>
       <c r="E355">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F355" t="s">
         <v>1609</v>
@@ -20733,7 +20733,7 @@
         <v>1550</v>
       </c>
       <c r="E356">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F356" t="s">
         <v>1609</v>
@@ -20768,7 +20768,7 @@
         <v>1550</v>
       </c>
       <c r="E357">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F357" t="s">
         <v>1609</v>
@@ -20803,7 +20803,7 @@
         <v>1550</v>
       </c>
       <c r="E358">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F358" t="s">
         <v>1609</v>
@@ -20838,7 +20838,7 @@
         <v>1550</v>
       </c>
       <c r="E359">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F359" t="s">
         <v>1609</v>
@@ -20873,7 +20873,7 @@
         <v>1550</v>
       </c>
       <c r="E360">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F360" t="s">
         <v>1609</v>
@@ -20908,7 +20908,7 @@
         <v>1550</v>
       </c>
       <c r="E361">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F361" t="s">
         <v>1609</v>
@@ -20943,7 +20943,7 @@
         <v>1551</v>
       </c>
       <c r="E362">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F362" t="s">
         <v>1609</v>
@@ -20978,7 +20978,7 @@
         <v>1551</v>
       </c>
       <c r="E363">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F363" t="s">
         <v>1609</v>
@@ -21013,7 +21013,7 @@
         <v>1551</v>
       </c>
       <c r="E364">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F364" t="s">
         <v>1609</v>
@@ -21048,7 +21048,7 @@
         <v>1552</v>
       </c>
       <c r="E365">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F365" t="s">
         <v>1609</v>
@@ -21083,7 +21083,7 @@
         <v>1552</v>
       </c>
       <c r="E366">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F366" t="s">
         <v>1609</v>
@@ -21118,7 +21118,7 @@
         <v>1553</v>
       </c>
       <c r="E367">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F367" t="s">
         <v>1609</v>
@@ -21153,7 +21153,7 @@
         <v>1554</v>
       </c>
       <c r="E368">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F368" t="s">
         <v>1611</v>
@@ -21188,7 +21188,7 @@
         <v>1554</v>
       </c>
       <c r="E369">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F369" t="s">
         <v>1609</v>
@@ -21223,7 +21223,7 @@
         <v>1554</v>
       </c>
       <c r="E370">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F370" t="s">
         <v>1609</v>
@@ -21258,7 +21258,7 @@
         <v>1554</v>
       </c>
       <c r="E371">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F371" t="s">
         <v>1609</v>
@@ -21293,7 +21293,7 @@
         <v>1554</v>
       </c>
       <c r="E372">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F372" t="s">
         <v>1609</v>
@@ -21328,7 +21328,7 @@
         <v>1554</v>
       </c>
       <c r="E373">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F373" t="s">
         <v>1609</v>
@@ -21363,7 +21363,7 @@
         <v>1555</v>
       </c>
       <c r="E374">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F374" t="s">
         <v>1609</v>
@@ -21398,7 +21398,7 @@
         <v>1555</v>
       </c>
       <c r="E375">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F375" t="s">
         <v>1609</v>
@@ -21433,7 +21433,7 @@
         <v>1556</v>
       </c>
       <c r="E376">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F376" t="s">
         <v>1609</v>
@@ -21468,7 +21468,7 @@
         <v>1556</v>
       </c>
       <c r="E377">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F377" t="s">
         <v>1609</v>
@@ -21503,7 +21503,7 @@
         <v>1556</v>
       </c>
       <c r="E378">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F378" t="s">
         <v>1609</v>
@@ -21538,7 +21538,7 @@
         <v>1557</v>
       </c>
       <c r="E379">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F379" t="s">
         <v>1609</v>
@@ -21573,7 +21573,7 @@
         <v>1558</v>
       </c>
       <c r="E380">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F380" t="s">
         <v>1609</v>
@@ -21608,7 +21608,7 @@
         <v>1559</v>
       </c>
       <c r="E381">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F381" t="s">
         <v>1609</v>
@@ -21643,7 +21643,7 @@
         <v>1559</v>
       </c>
       <c r="E382">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F382" t="s">
         <v>1609</v>
@@ -21678,7 +21678,7 @@
         <v>1560</v>
       </c>
       <c r="E383">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F383" t="s">
         <v>1609</v>
@@ -21713,7 +21713,7 @@
         <v>1560</v>
       </c>
       <c r="E384">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F384" t="s">
         <v>1609</v>
@@ -21748,7 +21748,7 @@
         <v>1560</v>
       </c>
       <c r="E385">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F385" t="s">
         <v>1609</v>
@@ -21783,7 +21783,7 @@
         <v>1561</v>
       </c>
       <c r="E386">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F386" t="s">
         <v>1609</v>
@@ -21818,7 +21818,7 @@
         <v>1561</v>
       </c>
       <c r="E387">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F387" t="s">
         <v>1609</v>
@@ -21853,7 +21853,7 @@
         <v>1561</v>
       </c>
       <c r="E388">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F388" t="s">
         <v>1609</v>
@@ -21888,7 +21888,7 @@
         <v>1561</v>
       </c>
       <c r="E389">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F389" t="s">
         <v>1609</v>
@@ -21923,7 +21923,7 @@
         <v>1561</v>
       </c>
       <c r="E390">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F390" t="s">
         <v>1609</v>
@@ -21958,7 +21958,7 @@
         <v>1561</v>
       </c>
       <c r="E391">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F391" t="s">
         <v>1609</v>
@@ -21993,7 +21993,7 @@
         <v>1561</v>
       </c>
       <c r="E392">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F392" t="s">
         <v>1609</v>
@@ -22028,7 +22028,7 @@
         <v>1561</v>
       </c>
       <c r="E393">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F393" t="s">
         <v>1609</v>
@@ -22063,7 +22063,7 @@
         <v>1561</v>
       </c>
       <c r="E394">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F394" t="s">
         <v>1609</v>
@@ -22098,7 +22098,7 @@
         <v>1561</v>
       </c>
       <c r="E395">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F395" t="s">
         <v>1609</v>
@@ -22133,7 +22133,7 @@
         <v>1562</v>
       </c>
       <c r="E396">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F396" t="s">
         <v>1609</v>
@@ -22168,7 +22168,7 @@
         <v>1562</v>
       </c>
       <c r="E397">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F397" t="s">
         <v>1609</v>
@@ -22203,7 +22203,7 @@
         <v>1562</v>
       </c>
       <c r="E398">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F398" t="s">
         <v>1609</v>
@@ -22238,7 +22238,7 @@
         <v>1562</v>
       </c>
       <c r="E399">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F399" t="s">
         <v>1609</v>
@@ -22273,7 +22273,7 @@
         <v>1562</v>
       </c>
       <c r="E400">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F400" t="s">
         <v>1609</v>
@@ -22308,7 +22308,7 @@
         <v>1563</v>
       </c>
       <c r="E401">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F401" t="s">
         <v>1612</v>
@@ -22343,7 +22343,7 @@
         <v>1563</v>
       </c>
       <c r="E402">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F402" t="s">
         <v>1609</v>
@@ -22378,7 +22378,7 @@
         <v>1564</v>
       </c>
       <c r="E403">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F403" t="s">
         <v>1609</v>
@@ -22413,7 +22413,7 @@
         <v>1564</v>
       </c>
       <c r="E404">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F404" t="s">
         <v>1609</v>
@@ -22448,7 +22448,7 @@
         <v>1564</v>
       </c>
       <c r="E405">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F405" t="s">
         <v>1609</v>
@@ -22483,7 +22483,7 @@
         <v>1564</v>
       </c>
       <c r="E406">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F406" t="s">
         <v>1609</v>
@@ -22518,7 +22518,7 @@
         <v>1564</v>
       </c>
       <c r="E407">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F407" t="s">
         <v>1609</v>
@@ -22553,7 +22553,7 @@
         <v>1564</v>
       </c>
       <c r="E408">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F408" t="s">
         <v>1608</v>
@@ -22591,7 +22591,7 @@
         <v>1564</v>
       </c>
       <c r="E409">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F409" t="s">
         <v>1609</v>
@@ -22626,7 +22626,7 @@
         <v>1564</v>
       </c>
       <c r="E410">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F410" t="s">
         <v>1609</v>
@@ -22661,7 +22661,7 @@
         <v>1565</v>
       </c>
       <c r="E411">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F411" t="s">
         <v>1609</v>
@@ -22696,7 +22696,7 @@
         <v>1565</v>
       </c>
       <c r="E412">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F412" t="s">
         <v>1609</v>
@@ -22731,7 +22731,7 @@
         <v>1565</v>
       </c>
       <c r="E413">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F413" t="s">
         <v>1609</v>
@@ -22766,7 +22766,7 @@
         <v>1565</v>
       </c>
       <c r="E414">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F414" t="s">
         <v>1609</v>
@@ -22804,7 +22804,7 @@
         <v>1565</v>
       </c>
       <c r="E415">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F415" t="s">
         <v>1609</v>
@@ -22839,7 +22839,7 @@
         <v>1565</v>
       </c>
       <c r="E416">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F416" t="s">
         <v>1609</v>
@@ -22874,7 +22874,7 @@
         <v>1565</v>
       </c>
       <c r="E417">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F417" t="s">
         <v>1609</v>
@@ -22909,7 +22909,7 @@
         <v>1565</v>
       </c>
       <c r="E418">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F418" t="s">
         <v>1609</v>
@@ -22944,7 +22944,7 @@
         <v>1565</v>
       </c>
       <c r="E419">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F419" t="s">
         <v>1609</v>
@@ -22979,7 +22979,7 @@
         <v>1566</v>
       </c>
       <c r="E420">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F420" t="s">
         <v>1610</v>
@@ -23014,7 +23014,7 @@
         <v>1567</v>
       </c>
       <c r="E421">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F421" t="s">
         <v>1611</v>
@@ -23049,7 +23049,7 @@
         <v>1567</v>
       </c>
       <c r="E422">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F422" t="s">
         <v>1608</v>
@@ -23084,7 +23084,7 @@
         <v>1568</v>
       </c>
       <c r="E423">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F423" t="s">
         <v>1609</v>
@@ -23119,7 +23119,7 @@
         <v>1569</v>
       </c>
       <c r="E424">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F424" t="s">
         <v>1609</v>
@@ -23154,7 +23154,7 @@
         <v>1569</v>
       </c>
       <c r="E425">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F425" t="s">
         <v>1609</v>
@@ -23189,7 +23189,7 @@
         <v>1570</v>
       </c>
       <c r="E426">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F426" t="s">
         <v>1609</v>
@@ -23224,7 +23224,7 @@
         <v>1571</v>
       </c>
       <c r="E427">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F427" t="s">
         <v>1612</v>
@@ -23259,7 +23259,7 @@
         <v>1571</v>
       </c>
       <c r="E428">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F428" t="s">
         <v>1609</v>
@@ -23294,7 +23294,7 @@
         <v>1571</v>
       </c>
       <c r="E429">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F429" t="s">
         <v>1609</v>
@@ -23329,7 +23329,7 @@
         <v>1571</v>
       </c>
       <c r="E430">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F430" t="s">
         <v>1609</v>
@@ -23364,7 +23364,7 @@
         <v>1571</v>
       </c>
       <c r="E431">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F431" t="s">
         <v>1609</v>
@@ -23399,7 +23399,7 @@
         <v>1571</v>
       </c>
       <c r="E432">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F432" t="s">
         <v>1609</v>
@@ -23434,7 +23434,7 @@
         <v>1572</v>
       </c>
       <c r="E433">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F433" t="s">
         <v>1609</v>
@@ -23469,7 +23469,7 @@
         <v>1572</v>
       </c>
       <c r="E434">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F434" t="s">
         <v>1609</v>
@@ -23504,7 +23504,7 @@
         <v>1572</v>
       </c>
       <c r="E435">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F435" t="s">
         <v>1609</v>
@@ -23539,7 +23539,7 @@
         <v>1572</v>
       </c>
       <c r="E436">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F436" t="s">
         <v>1609</v>
@@ -23574,7 +23574,7 @@
         <v>1573</v>
       </c>
       <c r="E437">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F437" t="s">
         <v>1609</v>
@@ -23609,7 +23609,7 @@
         <v>1573</v>
       </c>
       <c r="E438">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F438" t="s">
         <v>1609</v>
@@ -23644,7 +23644,7 @@
         <v>1573</v>
       </c>
       <c r="E439">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F439" t="s">
         <v>1609</v>
@@ -23682,7 +23682,7 @@
         <v>1573</v>
       </c>
       <c r="E440">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F440" t="s">
         <v>1609</v>
@@ -23717,7 +23717,7 @@
         <v>1574</v>
       </c>
       <c r="E441">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F441" t="s">
         <v>1609</v>
@@ -23752,7 +23752,7 @@
         <v>1574</v>
       </c>
       <c r="E442">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F442" t="s">
         <v>1609</v>
@@ -23787,7 +23787,7 @@
         <v>1574</v>
       </c>
       <c r="E443">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F443" t="s">
         <v>1609</v>
@@ -23822,7 +23822,7 @@
         <v>1574</v>
       </c>
       <c r="E444">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F444" t="s">
         <v>1609</v>
@@ -23857,7 +23857,7 @@
         <v>1574</v>
       </c>
       <c r="E445">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F445" t="s">
         <v>1609</v>
@@ -23892,7 +23892,7 @@
         <v>1575</v>
       </c>
       <c r="E446">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F446" t="s">
         <v>1609</v>
@@ -23927,7 +23927,7 @@
         <v>1575</v>
       </c>
       <c r="E447">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F447" t="s">
         <v>1609</v>
@@ -23962,7 +23962,7 @@
         <v>1575</v>
       </c>
       <c r="E448">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F448" t="s">
         <v>1609</v>
@@ -23997,7 +23997,7 @@
         <v>1575</v>
       </c>
       <c r="E449">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F449" t="s">
         <v>1609</v>
@@ -24032,7 +24032,7 @@
         <v>1576</v>
       </c>
       <c r="E450">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F450" t="s">
         <v>1609</v>
@@ -24067,7 +24067,7 @@
         <v>1576</v>
       </c>
       <c r="E451">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F451" t="s">
         <v>1609</v>
@@ -24102,7 +24102,7 @@
         <v>1576</v>
       </c>
       <c r="E452">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F452" t="s">
         <v>1609</v>
@@ -24137,7 +24137,7 @@
         <v>1576</v>
       </c>
       <c r="E453">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F453" t="s">
         <v>1609</v>
@@ -24172,7 +24172,7 @@
         <v>1576</v>
       </c>
       <c r="E454">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F454" t="s">
         <v>1609</v>
@@ -24207,7 +24207,7 @@
         <v>1576</v>
       </c>
       <c r="E455">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F455" t="s">
         <v>1609</v>
@@ -24242,7 +24242,7 @@
         <v>1576</v>
       </c>
       <c r="E456">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F456" t="s">
         <v>1609</v>
@@ -24277,7 +24277,7 @@
         <v>1576</v>
       </c>
       <c r="E457">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F457" t="s">
         <v>1609</v>
@@ -24312,7 +24312,7 @@
         <v>1576</v>
       </c>
       <c r="E458">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F458" t="s">
         <v>1609</v>
@@ -24347,7 +24347,7 @@
         <v>1576</v>
       </c>
       <c r="E459">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F459" t="s">
         <v>1609</v>
@@ -24382,7 +24382,7 @@
         <v>1576</v>
       </c>
       <c r="E460">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F460" t="s">
         <v>1609</v>
@@ -24417,7 +24417,7 @@
         <v>1577</v>
       </c>
       <c r="E461">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F461" t="s">
         <v>1609</v>
@@ -24452,7 +24452,7 @@
         <v>1577</v>
       </c>
       <c r="E462">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F462" t="s">
         <v>1609</v>
@@ -24487,7 +24487,7 @@
         <v>1577</v>
       </c>
       <c r="E463">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F463" t="s">
         <v>1610</v>
@@ -24522,7 +24522,7 @@
         <v>1578</v>
       </c>
       <c r="E464">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F464" t="s">
         <v>1609</v>
@@ -24557,7 +24557,7 @@
         <v>1578</v>
       </c>
       <c r="E465">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F465" t="s">
         <v>1609</v>
@@ -24592,7 +24592,7 @@
         <v>1578</v>
       </c>
       <c r="E466">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F466" t="s">
         <v>1609</v>
@@ -24627,7 +24627,7 @@
         <v>1578</v>
       </c>
       <c r="E467">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F467" t="s">
         <v>1609</v>
@@ -24662,7 +24662,7 @@
         <v>1578</v>
       </c>
       <c r="E468">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F468" t="s">
         <v>1609</v>
@@ -24697,7 +24697,7 @@
         <v>1578</v>
       </c>
       <c r="E469">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F469" t="s">
         <v>1609</v>
@@ -24732,7 +24732,7 @@
         <v>1578</v>
       </c>
       <c r="E470">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F470" t="s">
         <v>1612</v>
@@ -24767,7 +24767,7 @@
         <v>1579</v>
       </c>
       <c r="E471">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F471" t="s">
         <v>1609</v>
@@ -24802,7 +24802,7 @@
         <v>1579</v>
       </c>
       <c r="E472">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F472" t="s">
         <v>1609</v>
@@ -24837,7 +24837,7 @@
         <v>1579</v>
       </c>
       <c r="E473">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F473" t="s">
         <v>1609</v>
@@ -24872,7 +24872,7 @@
         <v>1579</v>
       </c>
       <c r="E474">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F474" t="s">
         <v>1609</v>
@@ -24907,7 +24907,7 @@
         <v>1580</v>
       </c>
       <c r="E475">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F475" t="s">
         <v>1609</v>
@@ -24942,7 +24942,7 @@
         <v>1580</v>
       </c>
       <c r="E476">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F476" t="s">
         <v>1612</v>
@@ -24977,7 +24977,7 @@
         <v>1580</v>
       </c>
       <c r="E477">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F477" t="s">
         <v>1609</v>
@@ -25012,7 +25012,7 @@
         <v>1580</v>
       </c>
       <c r="E478">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F478" t="s">
         <v>1609</v>
@@ -25047,7 +25047,7 @@
         <v>1580</v>
       </c>
       <c r="E479">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F479" t="s">
         <v>1609</v>
@@ -25082,7 +25082,7 @@
         <v>1580</v>
       </c>
       <c r="E480">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F480" t="s">
         <v>1611</v>
@@ -25120,7 +25120,7 @@
         <v>1580</v>
       </c>
       <c r="E481">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F481" t="s">
         <v>1609</v>
@@ -25155,7 +25155,7 @@
         <v>1580</v>
       </c>
       <c r="E482">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F482" t="s">
         <v>1608</v>
@@ -25190,7 +25190,7 @@
         <v>1580</v>
       </c>
       <c r="E483">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F483" t="s">
         <v>1609</v>
@@ -25225,7 +25225,7 @@
         <v>1580</v>
       </c>
       <c r="E484">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F484" t="s">
         <v>1609</v>
@@ -25260,7 +25260,7 @@
         <v>1581</v>
       </c>
       <c r="E485">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F485" t="s">
         <v>1609</v>
@@ -25295,7 +25295,7 @@
         <v>1581</v>
       </c>
       <c r="E486">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F486" t="s">
         <v>1609</v>
@@ -25330,7 +25330,7 @@
         <v>1581</v>
       </c>
       <c r="E487">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F487" t="s">
         <v>1609</v>
@@ -25365,7 +25365,7 @@
         <v>1581</v>
       </c>
       <c r="E488">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F488" t="s">
         <v>1609</v>
@@ -25400,7 +25400,7 @@
         <v>1581</v>
       </c>
       <c r="E489">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F489" t="s">
         <v>1609</v>
@@ -25435,7 +25435,7 @@
         <v>1581</v>
       </c>
       <c r="E490">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F490" t="s">
         <v>1609</v>
@@ -25470,7 +25470,7 @@
         <v>1581</v>
       </c>
       <c r="E491">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F491" t="s">
         <v>1611</v>
@@ -25505,7 +25505,7 @@
         <v>1581</v>
       </c>
       <c r="E492">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F492" t="s">
         <v>1609</v>
@@ -25540,7 +25540,7 @@
         <v>1581</v>
       </c>
       <c r="E493">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F493" t="s">
         <v>1609</v>
@@ -25575,7 +25575,7 @@
         <v>1582</v>
       </c>
       <c r="E494">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F494" t="s">
         <v>1609</v>
@@ -25610,7 +25610,7 @@
         <v>1582</v>
       </c>
       <c r="E495">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F495" t="s">
         <v>1609</v>
@@ -25645,7 +25645,7 @@
         <v>1582</v>
       </c>
       <c r="E496">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F496" t="s">
         <v>1609</v>
@@ -25680,7 +25680,7 @@
         <v>1582</v>
       </c>
       <c r="E497">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F497" t="s">
         <v>1609</v>
@@ -25715,7 +25715,7 @@
         <v>1582</v>
       </c>
       <c r="E498">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F498" t="s">
         <v>1609</v>
@@ -25750,7 +25750,7 @@
         <v>1583</v>
       </c>
       <c r="E499">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F499" t="s">
         <v>1609</v>
@@ -25785,7 +25785,7 @@
         <v>1583</v>
       </c>
       <c r="E500">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F500" t="s">
         <v>1609</v>
@@ -25820,7 +25820,7 @@
         <v>1583</v>
       </c>
       <c r="E501">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F501" t="s">
         <v>1609</v>
@@ -25855,7 +25855,7 @@
         <v>1583</v>
       </c>
       <c r="E502">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F502" t="s">
         <v>1609</v>
@@ -25890,7 +25890,7 @@
         <v>1583</v>
       </c>
       <c r="E503">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F503" t="s">
         <v>1609</v>
@@ -25928,7 +25928,7 @@
         <v>1584</v>
       </c>
       <c r="E504">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F504" t="s">
         <v>1609</v>
@@ -25963,7 +25963,7 @@
         <v>1584</v>
       </c>
       <c r="E505">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F505" t="s">
         <v>1609</v>
@@ -25998,7 +25998,7 @@
         <v>1584</v>
       </c>
       <c r="E506">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F506" t="s">
         <v>1609</v>
@@ -26033,7 +26033,7 @@
         <v>1584</v>
       </c>
       <c r="E507">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F507" t="s">
         <v>1609</v>
@@ -26068,7 +26068,7 @@
         <v>1584</v>
       </c>
       <c r="E508">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F508" t="s">
         <v>1609</v>
@@ -26103,7 +26103,7 @@
         <v>1584</v>
       </c>
       <c r="E509">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F509" t="s">
         <v>1609</v>
@@ -26138,7 +26138,7 @@
         <v>1584</v>
       </c>
       <c r="E510">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F510" t="s">
         <v>1609</v>
@@ -26173,7 +26173,7 @@
         <v>1585</v>
       </c>
       <c r="E511">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F511" t="s">
         <v>1609</v>
@@ -26208,7 +26208,7 @@
         <v>1585</v>
       </c>
       <c r="E512">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F512" t="s">
         <v>1609</v>
@@ -26243,7 +26243,7 @@
         <v>1585</v>
       </c>
       <c r="E513">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F513" t="s">
         <v>1609</v>
@@ -26278,7 +26278,7 @@
         <v>1586</v>
       </c>
       <c r="E514">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F514" t="s">
         <v>1609</v>
@@ -26313,7 +26313,7 @@
         <v>1586</v>
       </c>
       <c r="E515">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F515" t="s">
         <v>1609</v>
@@ -26348,7 +26348,7 @@
         <v>1587</v>
       </c>
       <c r="E516">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F516" t="s">
         <v>1609</v>
@@ -26383,7 +26383,7 @@
         <v>1587</v>
       </c>
       <c r="E517">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F517" t="s">
         <v>1609</v>
@@ -26418,7 +26418,7 @@
         <v>1587</v>
       </c>
       <c r="E518">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F518" t="s">
         <v>1611</v>
@@ -26456,7 +26456,7 @@
         <v>1587</v>
       </c>
       <c r="E519">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F519" t="s">
         <v>1609</v>
@@ -26491,7 +26491,7 @@
         <v>1587</v>
       </c>
       <c r="E520">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F520" t="s">
         <v>1609</v>
@@ -26526,7 +26526,7 @@
         <v>1588</v>
       </c>
       <c r="E521">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F521" t="s">
         <v>1609</v>
@@ -26561,7 +26561,7 @@
         <v>1588</v>
       </c>
       <c r="E522">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F522" t="s">
         <v>1609</v>
@@ -26596,7 +26596,7 @@
         <v>1588</v>
       </c>
       <c r="E523">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F523" t="s">
         <v>1609</v>
@@ -26631,7 +26631,7 @@
         <v>1588</v>
       </c>
       <c r="E524">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F524" t="s">
         <v>1609</v>
@@ -26666,7 +26666,7 @@
         <v>1588</v>
       </c>
       <c r="E525">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F525" t="s">
         <v>1609</v>
@@ -26701,7 +26701,7 @@
         <v>1589</v>
       </c>
       <c r="E526">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F526" t="s">
         <v>1609</v>
@@ -26736,7 +26736,7 @@
         <v>1589</v>
       </c>
       <c r="E527">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F527" t="s">
         <v>1609</v>
@@ -26771,7 +26771,7 @@
         <v>1589</v>
       </c>
       <c r="E528">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F528" t="s">
         <v>1609</v>
@@ -26806,7 +26806,7 @@
         <v>1589</v>
       </c>
       <c r="E529">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F529" t="s">
         <v>1609</v>
@@ -26841,7 +26841,7 @@
         <v>1589</v>
       </c>
       <c r="E530">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F530" t="s">
         <v>1609</v>
@@ -26876,7 +26876,7 @@
         <v>1589</v>
       </c>
       <c r="E531">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F531" t="s">
         <v>1609</v>
@@ -26911,7 +26911,7 @@
         <v>1589</v>
       </c>
       <c r="E532">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F532" t="s">
         <v>1609</v>
@@ -26946,7 +26946,7 @@
         <v>1589</v>
       </c>
       <c r="E533">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F533" t="s">
         <v>1609</v>
@@ -26981,7 +26981,7 @@
         <v>1590</v>
       </c>
       <c r="E534">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F534" t="s">
         <v>1609</v>
@@ -27016,7 +27016,7 @@
         <v>1590</v>
       </c>
       <c r="E535">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F535" t="s">
         <v>1609</v>
@@ -27051,7 +27051,7 @@
         <v>1591</v>
       </c>
       <c r="E536">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F536" t="s">
         <v>1609</v>
@@ -27086,7 +27086,7 @@
         <v>1591</v>
       </c>
       <c r="E537">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F537" t="s">
         <v>1609</v>
@@ -27121,7 +27121,7 @@
         <v>1591</v>
       </c>
       <c r="E538">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F538" t="s">
         <v>1609</v>
@@ -27156,7 +27156,7 @@
         <v>1591</v>
       </c>
       <c r="E539">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F539" t="s">
         <v>1608</v>
@@ -27194,7 +27194,7 @@
         <v>1591</v>
       </c>
       <c r="E540">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F540" t="s">
         <v>1609</v>
@@ -27229,7 +27229,7 @@
         <v>1591</v>
       </c>
       <c r="E541">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F541" t="s">
         <v>1608</v>
@@ -27264,7 +27264,7 @@
         <v>1592</v>
       </c>
       <c r="E542">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F542" t="s">
         <v>1609</v>
@@ -27299,7 +27299,7 @@
         <v>1593</v>
       </c>
       <c r="E543">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F543" t="s">
         <v>1609</v>
@@ -27334,7 +27334,7 @@
         <v>1593</v>
       </c>
       <c r="E544">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F544" t="s">
         <v>1609</v>
@@ -27369,7 +27369,7 @@
         <v>1593</v>
       </c>
       <c r="E545">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F545" t="s">
         <v>1609</v>
@@ -27404,7 +27404,7 @@
         <v>1593</v>
       </c>
       <c r="E546">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F546" t="s">
         <v>1609</v>
@@ -27439,7 +27439,7 @@
         <v>1594</v>
       </c>
       <c r="E547">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F547" t="s">
         <v>1609</v>
@@ -27474,7 +27474,7 @@
         <v>1594</v>
       </c>
       <c r="E548">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F548" t="s">
         <v>1608</v>
@@ -27509,7 +27509,7 @@
         <v>1594</v>
       </c>
       <c r="E549">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F549" t="s">
         <v>1609</v>
@@ -27544,7 +27544,7 @@
         <v>1594</v>
       </c>
       <c r="E550">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F550" t="s">
         <v>1609</v>
@@ -27579,7 +27579,7 @@
         <v>1594</v>
       </c>
       <c r="E551">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F551" t="s">
         <v>1609</v>
@@ -27614,7 +27614,7 @@
         <v>1594</v>
       </c>
       <c r="E552">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F552" t="s">
         <v>1609</v>
@@ -27649,7 +27649,7 @@
         <v>1595</v>
       </c>
       <c r="E553">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F553" t="s">
         <v>1609</v>
@@ -27684,7 +27684,7 @@
         <v>1595</v>
       </c>
       <c r="E554">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F554" t="s">
         <v>1608</v>
@@ -27719,7 +27719,7 @@
         <v>1595</v>
       </c>
       <c r="E555">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F555" t="s">
         <v>1611</v>
@@ -27754,7 +27754,7 @@
         <v>1595</v>
       </c>
       <c r="E556">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F556" t="s">
         <v>1609</v>
@@ -27789,7 +27789,7 @@
         <v>1595</v>
       </c>
       <c r="E557">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F557" t="s">
         <v>1609</v>
@@ -27824,7 +27824,7 @@
         <v>1596</v>
       </c>
       <c r="E558">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F558" t="s">
         <v>1609</v>
@@ -27859,7 +27859,7 @@
         <v>1596</v>
       </c>
       <c r="E559">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F559" t="s">
         <v>1609</v>
@@ -27894,7 +27894,7 @@
         <v>1596</v>
       </c>
       <c r="E560">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F560" t="s">
         <v>1609</v>
@@ -27929,7 +27929,7 @@
         <v>1596</v>
       </c>
       <c r="E561">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F561" t="s">
         <v>1609</v>
@@ -27964,7 +27964,7 @@
         <v>1596</v>
       </c>
       <c r="E562">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F562" t="s">
         <v>1609</v>
@@ -27999,7 +27999,7 @@
         <v>1596</v>
       </c>
       <c r="E563">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F563" t="s">
         <v>1609</v>
@@ -28034,7 +28034,7 @@
         <v>1596</v>
       </c>
       <c r="E564">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F564" t="s">
         <v>1609</v>
@@ -28069,7 +28069,7 @@
         <v>1597</v>
       </c>
       <c r="E565">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F565" t="s">
         <v>1609</v>
@@ -28104,7 +28104,7 @@
         <v>1597</v>
       </c>
       <c r="E566">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F566" t="s">
         <v>1609</v>
@@ -28139,7 +28139,7 @@
         <v>1597</v>
       </c>
       <c r="E567">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F567" t="s">
         <v>1609</v>
@@ -28174,7 +28174,7 @@
         <v>1597</v>
       </c>
       <c r="E568">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F568" t="s">
         <v>1609</v>
@@ -28209,7 +28209,7 @@
         <v>1597</v>
       </c>
       <c r="E569">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F569" t="s">
         <v>1609</v>
@@ -28244,7 +28244,7 @@
         <v>1597</v>
       </c>
       <c r="E570">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F570" t="s">
         <v>1609</v>
@@ -28279,7 +28279,7 @@
         <v>1597</v>
       </c>
       <c r="E571">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F571" t="s">
         <v>1609</v>
@@ -28314,7 +28314,7 @@
         <v>1597</v>
       </c>
       <c r="E572">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F572" t="s">
         <v>1609</v>
@@ -28349,7 +28349,7 @@
         <v>1597</v>
       </c>
       <c r="E573">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F573" t="s">
         <v>1609</v>
@@ -28384,7 +28384,7 @@
         <v>1597</v>
       </c>
       <c r="E574">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F574" t="s">
         <v>1609</v>
@@ -28419,7 +28419,7 @@
         <v>1597</v>
       </c>
       <c r="E575">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F575" t="s">
         <v>1609</v>
@@ -28454,7 +28454,7 @@
         <v>1597</v>
       </c>
       <c r="E576">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F576" t="s">
         <v>1609</v>
@@ -28489,7 +28489,7 @@
         <v>1597</v>
       </c>
       <c r="E577">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F577" t="s">
         <v>1609</v>
@@ -28524,7 +28524,7 @@
         <v>1597</v>
       </c>
       <c r="E578">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F578" t="s">
         <v>1609</v>
@@ -28559,7 +28559,7 @@
         <v>1597</v>
       </c>
       <c r="E579">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F579" t="s">
         <v>1609</v>
@@ -28594,7 +28594,7 @@
         <v>1597</v>
       </c>
       <c r="E580">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F580" t="s">
         <v>1609</v>
@@ -28629,7 +28629,7 @@
         <v>1597</v>
       </c>
       <c r="E581">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F581" t="s">
         <v>1609</v>
@@ -28664,7 +28664,7 @@
         <v>1597</v>
       </c>
       <c r="E582">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F582" t="s">
         <v>1609</v>
@@ -28699,7 +28699,7 @@
         <v>1597</v>
       </c>
       <c r="E583">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F583" t="s">
         <v>1609</v>
@@ -28734,7 +28734,7 @@
         <v>1597</v>
       </c>
       <c r="E584">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F584" t="s">
         <v>1609</v>
@@ -28769,7 +28769,7 @@
         <v>1597</v>
       </c>
       <c r="E585">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F585" t="s">
         <v>1609</v>
@@ -28804,7 +28804,7 @@
         <v>1597</v>
       </c>
       <c r="E586">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F586" t="s">
         <v>1609</v>
@@ -28839,7 +28839,7 @@
         <v>1597</v>
       </c>
       <c r="E587">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F587" t="s">
         <v>1609</v>
@@ -28874,7 +28874,7 @@
         <v>1597</v>
       </c>
       <c r="E588">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F588" t="s">
         <v>1609</v>
@@ -28909,7 +28909,7 @@
         <v>1597</v>
       </c>
       <c r="E589">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F589" t="s">
         <v>1609</v>
@@ -28944,7 +28944,7 @@
         <v>1597</v>
       </c>
       <c r="E590">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F590" t="s">
         <v>1609</v>
@@ -28979,7 +28979,7 @@
         <v>1597</v>
       </c>
       <c r="E591">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F591" t="s">
         <v>1609</v>
@@ -29014,7 +29014,7 @@
         <v>1597</v>
       </c>
       <c r="E592">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F592" t="s">
         <v>1611</v>
@@ -29052,7 +29052,7 @@
         <v>1598</v>
       </c>
       <c r="E593">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F593" t="s">
         <v>1609</v>
@@ -29087,7 +29087,7 @@
         <v>1598</v>
       </c>
       <c r="E594">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F594" t="s">
         <v>1609</v>
@@ -29122,7 +29122,7 @@
         <v>1598</v>
       </c>
       <c r="E595">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F595" t="s">
         <v>1611</v>
@@ -29157,7 +29157,7 @@
         <v>1598</v>
       </c>
       <c r="E596">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F596" t="s">
         <v>1609</v>
@@ -29192,7 +29192,7 @@
         <v>1598</v>
       </c>
       <c r="E597">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F597" t="s">
         <v>1609</v>
@@ -29227,7 +29227,7 @@
         <v>1598</v>
       </c>
       <c r="E598">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F598" t="s">
         <v>1609</v>
@@ -29262,7 +29262,7 @@
         <v>1598</v>
       </c>
       <c r="E599">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F599" t="s">
         <v>1609</v>
@@ -29297,7 +29297,7 @@
         <v>1598</v>
       </c>
       <c r="E600">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F600" t="s">
         <v>1609</v>
@@ -29332,7 +29332,7 @@
         <v>1599</v>
       </c>
       <c r="E601">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F601" t="s">
         <v>1609</v>
@@ -29367,7 +29367,7 @@
         <v>1599</v>
       </c>
       <c r="E602">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F602" t="s">
         <v>1609</v>
@@ -29402,7 +29402,7 @@
         <v>1600</v>
       </c>
       <c r="E603">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F603" t="s">
         <v>1609</v>
@@ -29437,7 +29437,7 @@
         <v>1600</v>
       </c>
       <c r="E604">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F604" t="s">
         <v>1611</v>
@@ -29475,7 +29475,7 @@
         <v>1600</v>
       </c>
       <c r="E605">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F605" t="s">
         <v>1611</v>
@@ -29513,7 +29513,7 @@
         <v>1601</v>
       </c>
       <c r="E606">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F606" t="s">
         <v>1611</v>
@@ -29551,7 +29551,7 @@
         <v>1601</v>
       </c>
       <c r="E607">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F607" t="s">
         <v>1609</v>
@@ -29586,7 +29586,7 @@
         <v>1601</v>
       </c>
       <c r="E608">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F608" t="s">
         <v>1609</v>
@@ -29621,7 +29621,7 @@
         <v>1601</v>
       </c>
       <c r="E609">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F609" t="s">
         <v>1611</v>
@@ -29659,7 +29659,7 @@
         <v>1601</v>
       </c>
       <c r="E610">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F610" t="s">
         <v>1609</v>
@@ -29694,7 +29694,7 @@
         <v>1601</v>
       </c>
       <c r="E611">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F611" t="s">
         <v>1609</v>
@@ -29729,7 +29729,7 @@
         <v>1601</v>
       </c>
       <c r="E612">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F612" t="s">
         <v>1611</v>
@@ -29767,7 +29767,7 @@
         <v>1601</v>
       </c>
       <c r="E613">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F613" t="s">
         <v>1609</v>
@@ -29802,7 +29802,7 @@
         <v>1601</v>
       </c>
       <c r="E614">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F614" t="s">
         <v>1609</v>
@@ -29840,7 +29840,7 @@
         <v>1601</v>
       </c>
       <c r="E615">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F615" t="s">
         <v>1611</v>
@@ -29875,7 +29875,7 @@
         <v>1601</v>
       </c>
       <c r="E616">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F616" t="s">
         <v>1609</v>
@@ -29910,7 +29910,7 @@
         <v>1601</v>
       </c>
       <c r="E617">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F617" t="s">
         <v>1609</v>
@@ -29945,7 +29945,7 @@
         <v>1602</v>
       </c>
       <c r="E618">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F618" t="s">
         <v>1609</v>
@@ -29983,7 +29983,7 @@
         <v>1602</v>
       </c>
       <c r="E619">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F619" t="s">
         <v>1608</v>
@@ -30018,7 +30018,7 @@
         <v>1602</v>
       </c>
       <c r="E620">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F620" t="s">
         <v>1611</v>
@@ -30053,7 +30053,7 @@
         <v>1602</v>
       </c>
       <c r="E621">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F621" t="s">
         <v>1609</v>
@@ -30088,7 +30088,7 @@
         <v>1602</v>
       </c>
       <c r="E622">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F622" t="s">
         <v>1611</v>
@@ -30126,7 +30126,7 @@
         <v>1602</v>
       </c>
       <c r="E623">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F623" t="s">
         <v>1609</v>
@@ -30161,7 +30161,7 @@
         <v>1602</v>
       </c>
       <c r="E624">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F624" t="s">
         <v>1609</v>
@@ -30196,7 +30196,7 @@
         <v>1602</v>
       </c>
       <c r="E625">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F625" t="s">
         <v>1609</v>
@@ -30231,7 +30231,7 @@
         <v>1602</v>
       </c>
       <c r="E626">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F626" t="s">
         <v>1609</v>
@@ -30266,7 +30266,7 @@
         <v>1602</v>
       </c>
       <c r="E627">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F627" t="s">
         <v>1609</v>
@@ -30301,7 +30301,7 @@
         <v>1603</v>
       </c>
       <c r="E628">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F628" t="s">
         <v>1609</v>
@@ -30336,7 +30336,7 @@
         <v>1603</v>
       </c>
       <c r="E629">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F629" t="s">
         <v>1609</v>
@@ -30374,7 +30374,7 @@
         <v>1603</v>
       </c>
       <c r="E630">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F630" t="s">
         <v>1609</v>
@@ -30409,7 +30409,7 @@
         <v>1604</v>
       </c>
       <c r="E631">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F631" t="s">
         <v>1609</v>
@@ -30444,7 +30444,7 @@
         <v>1604</v>
       </c>
       <c r="E632">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F632" t="s">
         <v>1611</v>
@@ -30482,7 +30482,7 @@
         <v>1604</v>
       </c>
       <c r="E633">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F633" t="s">
         <v>1609</v>
@@ -30517,7 +30517,7 @@
         <v>1604</v>
       </c>
       <c r="E634">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F634" t="s">
         <v>1609</v>
@@ -30552,7 +30552,7 @@
         <v>1604</v>
       </c>
       <c r="E635">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F635" t="s">
         <v>1609</v>
@@ -30587,7 +30587,7 @@
         <v>1604</v>
       </c>
       <c r="E636">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F636" t="s">
         <v>1609</v>
@@ -30622,7 +30622,7 @@
         <v>1604</v>
       </c>
       <c r="E637">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F637" t="s">
         <v>1609</v>
@@ -30657,7 +30657,7 @@
         <v>1604</v>
       </c>
       <c r="E638">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F638" t="s">
         <v>1609</v>
@@ -30692,7 +30692,7 @@
         <v>1604</v>
       </c>
       <c r="E639">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F639" t="s">
         <v>1609</v>
@@ -30727,7 +30727,7 @@
         <v>1604</v>
       </c>
       <c r="E640">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F640" t="s">
         <v>1609</v>
@@ -30762,7 +30762,7 @@
         <v>1605</v>
       </c>
       <c r="E641">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F641" t="s">
         <v>1609</v>
@@ -30797,7 +30797,7 @@
         <v>1605</v>
       </c>
       <c r="E642">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F642" t="s">
         <v>1609</v>
@@ -30832,7 +30832,7 @@
         <v>1605</v>
       </c>
       <c r="E643">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F643" t="s">
         <v>1609</v>
@@ -30867,7 +30867,7 @@
         <v>1605</v>
       </c>
       <c r="E644">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F644" t="s">
         <v>1609</v>
@@ -30902,7 +30902,7 @@
         <v>1605</v>
       </c>
       <c r="E645">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F645" t="s">
         <v>1611</v>
@@ -30940,7 +30940,7 @@
         <v>1605</v>
       </c>
       <c r="E646">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F646" t="s">
         <v>1609</v>
@@ -30975,7 +30975,7 @@
         <v>1605</v>
       </c>
       <c r="E647">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F647" t="s">
         <v>1609</v>
@@ -31010,7 +31010,7 @@
         <v>1605</v>
       </c>
       <c r="E648">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F648" t="s">
         <v>1609</v>
@@ -31045,7 +31045,7 @@
         <v>1605</v>
       </c>
       <c r="E649">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F649" t="s">
         <v>1609</v>
@@ -31080,7 +31080,7 @@
         <v>1605</v>
       </c>
       <c r="E650">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F650" t="s">
         <v>1609</v>
@@ -31115,7 +31115,7 @@
         <v>1605</v>
       </c>
       <c r="E651">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F651" t="s">
         <v>1608</v>
@@ -31150,7 +31150,7 @@
         <v>1605</v>
       </c>
       <c r="E652">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F652" t="s">
         <v>1609</v>
@@ -31185,7 +31185,7 @@
         <v>1606</v>
       </c>
       <c r="E653">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F653" t="s">
         <v>1611</v>
@@ -31223,7 +31223,7 @@
         <v>1606</v>
       </c>
       <c r="E654">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F654" t="s">
         <v>1609</v>
@@ -31258,7 +31258,7 @@
         <v>1606</v>
       </c>
       <c r="E655">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F655" t="s">
         <v>1609</v>
@@ -31293,7 +31293,7 @@
         <v>1606</v>
       </c>
       <c r="E656">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F656" t="s">
         <v>1609</v>
@@ -31328,7 +31328,7 @@
         <v>1606</v>
       </c>
       <c r="E657">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F657" t="s">
         <v>1609</v>
@@ -31363,7 +31363,7 @@
         <v>1606</v>
       </c>
       <c r="E658">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F658" t="s">
         <v>1609</v>
@@ -31398,7 +31398,7 @@
         <v>1606</v>
       </c>
       <c r="E659">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F659" t="s">
         <v>1609</v>
@@ -31433,7 +31433,7 @@
         <v>1606</v>
       </c>
       <c r="E660">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F660" t="s">
         <v>1609</v>
@@ -31468,7 +31468,7 @@
         <v>1606</v>
       </c>
       <c r="E661">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F661" t="s">
         <v>1609</v>
@@ -31506,7 +31506,7 @@
         <v>1606</v>
       </c>
       <c r="E662">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F662" t="s">
         <v>1609</v>
@@ -31541,7 +31541,7 @@
         <v>1606</v>
       </c>
       <c r="E663">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F663" t="s">
         <v>1611</v>
@@ -31576,7 +31576,7 @@
         <v>1606</v>
       </c>
       <c r="E664">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F664" t="s">
         <v>1609</v>
@@ -31611,7 +31611,7 @@
         <v>1606</v>
       </c>
       <c r="E665">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F665" t="s">
         <v>1609</v>
@@ -31646,7 +31646,7 @@
         <v>1607</v>
       </c>
       <c r="E666">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F666" t="s">
         <v>1609</v>
@@ -31681,7 +31681,7 @@
         <v>1607</v>
       </c>
       <c r="E667">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F667" t="s">
         <v>1609</v>
@@ -31716,7 +31716,7 @@
         <v>1607</v>
       </c>
       <c r="E668">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F668" t="s">
         <v>1609</v>
@@ -31751,7 +31751,7 @@
         <v>1607</v>
       </c>
       <c r="E669">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F669" t="s">
         <v>1609</v>
@@ -31786,7 +31786,7 @@
         <v>1607</v>
       </c>
       <c r="E670">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F670" t="s">
         <v>1609</v>
@@ -31821,7 +31821,7 @@
         <v>1607</v>
       </c>
       <c r="E671">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F671" t="s">
         <v>1609</v>
@@ -31856,7 +31856,7 @@
         <v>1607</v>
       </c>
       <c r="E672">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F672" t="s">
         <v>1609</v>
@@ -31891,7 +31891,7 @@
         <v>1607</v>
       </c>
       <c r="E673">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F673" t="s">
         <v>1609</v>
@@ -31929,7 +31929,7 @@
         <v>1607</v>
       </c>
       <c r="E674">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F674" t="s">
         <v>1609</v>
@@ -31964,7 +31964,7 @@
         <v>1607</v>
       </c>
       <c r="E675">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F675" t="s">
         <v>1609</v>
@@ -31999,7 +31999,7 @@
         <v>1607</v>
       </c>
       <c r="E676">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F676" t="s">
         <v>1609</v>

--- a/BacklogGATEAutoCompleto.xlsx
+++ b/BacklogGATEAutoCompleto.xlsx
@@ -7852,7 +7852,7 @@
     <t>BIOLOGIA,RESÍDUOS SÓLIDOS</t>
   </si>
   <si>
-    <t>ENGENHARIA CIVIL,ECONOMICIDADE OBRAS</t>
+    <t>ECONOMICIDADE OBRAS,ENGENHARIA CIVIL</t>
   </si>
   <si>
     <t>RECURSOS HÍDRICOS,URBANISMO</t>
@@ -7897,7 +7897,7 @@
     <t>BIOLOGIA,ENGENHARIA AMBIENTAL,RESÍDUOS SÓLIDOS</t>
   </si>
   <si>
-    <t>BIOLOGIA,RESÍDUOS SÓLIDOS,ENGENHARIA AMBIENTAL</t>
+    <t>RESÍDUOS SÓLIDOS,BIOLOGIA,ENGENHARIA AMBIENTAL</t>
   </si>
   <si>
     <t>MEDICINA LEGAL,SAÚDE</t>
@@ -7921,7 +7921,7 @@
     <t>ENGENHARIA CIVIL,FENOMENOS DE ENERGIA E INFORMAÇÃO</t>
   </si>
   <si>
-    <t>ENGENHARIA QUÍMICA,ENGENHARIA CIVIL,FENOMENOS DE ENERGIA E INFORMAÇÃO</t>
+    <t>ENGENHARIA CIVIL,ENGENHARIA QUÍMICA,FENOMENOS DE ENERGIA E INFORMAÇÃO</t>
   </si>
   <si>
     <t>ECONOMICIDADE CONTÁBIL,ECONOMICIDADE CONTÁBIL</t>
@@ -7930,13 +7930,13 @@
     <t>RECURSOS HÍDRICOS,VALORAÇÃO DANOS AMBIENTAIS</t>
   </si>
   <si>
-    <t>RECURSOS HÍDRICOS,BIOLOGIA</t>
-  </si>
-  <si>
     <t>ASSISTÊNCIA SOCIAL,EDIFICAÇÕES</t>
   </si>
   <si>
-    <t>PSICOLOGIA,ECONOMICIDADE CONTÁBIL,AVALIAÇÃO DE IMÓVEIS,SAÚDE,ORÇAMENTO,ASSISTÊNCIA SOCIAL,URBANISMO,SAÚDE MENTAL,ECONOMIA,MOBILIDADE E TRANSPORTE</t>
+    <t>GEOTECNIA,ENGENHARIA CIVIL</t>
+  </si>
+  <si>
+    <t>MOBILIDADE E TRANSPORTE,SAÚDE,ECONOMICIDADE CONTÁBIL,ECONOMIA,ASSISTÊNCIA SOCIAL,ORÇAMENTO,SAÚDE MENTAL,AVALIAÇÃO DE IMÓVEIS,PSICOLOGIA,URBANISMO</t>
   </si>
 </sst>
 </file>
@@ -15763,7 +15763,7 @@
     </row>
     <row r="214" spans="1:12">
       <c r="A214" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="B214" t="s">
         <v>253</v>
@@ -15784,7 +15784,7 @@
         <v>1618</v>
       </c>
       <c r="I214" t="s">
-        <v>1697</v>
+        <v>1643</v>
       </c>
       <c r="J214" t="s">
         <v>1971</v>
@@ -31615,7 +31615,7 @@
         <v>2440</v>
       </c>
       <c r="L664" t="s">
-        <v>2638</v>
+        <v>2597</v>
       </c>
     </row>
     <row r="665" spans="1:12">
@@ -31685,7 +31685,7 @@
         <v>2554</v>
       </c>
       <c r="L666" t="s">
-        <v>2615</v>
+        <v>2558</v>
       </c>
     </row>
     <row r="667" spans="1:12">
@@ -31755,7 +31755,7 @@
         <v>2449</v>
       </c>
       <c r="L668" t="s">
-        <v>2615</v>
+        <v>2558</v>
       </c>
     </row>
     <row r="669" spans="1:12">
@@ -31790,7 +31790,7 @@
         <v>2467</v>
       </c>
       <c r="L669" t="s">
-        <v>2615</v>
+        <v>2558</v>
       </c>
     </row>
     <row r="670" spans="1:12">
@@ -31825,7 +31825,7 @@
         <v>2503</v>
       </c>
       <c r="L670" t="s">
-        <v>2615</v>
+        <v>2559</v>
       </c>
     </row>
     <row r="671" spans="1:12">
@@ -31895,7 +31895,7 @@
         <v>2443</v>
       </c>
       <c r="L672" t="s">
-        <v>2615</v>
+        <v>2558</v>
       </c>
     </row>
     <row r="673" spans="1:12">
@@ -32041,7 +32041,7 @@
         <v>2555</v>
       </c>
       <c r="L676" t="s">
-        <v>2639</v>
+        <v>2638</v>
       </c>
     </row>
     <row r="677" spans="1:12">
@@ -32143,7 +32143,7 @@
         <v>2556</v>
       </c>
       <c r="L679" t="s">
-        <v>2617</v>
+        <v>2639</v>
       </c>
     </row>
     <row r="680" spans="1:12">

--- a/BacklogGATEAutoCompleto.xlsx
+++ b/BacklogGATEAutoCompleto.xlsx
@@ -8262,7 +8262,7 @@
         <v>1376</v>
       </c>
       <c r="E2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="F2" t="s">
         <v>1594</v>
@@ -8297,7 +8297,7 @@
         <v>1377</v>
       </c>
       <c r="E3">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="F3" t="s">
         <v>1594</v>
@@ -8332,7 +8332,7 @@
         <v>1378</v>
       </c>
       <c r="E4">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="F4" t="s">
         <v>1594</v>
@@ -8367,7 +8367,7 @@
         <v>1379</v>
       </c>
       <c r="E5">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="F5" t="s">
         <v>1594</v>
@@ -8402,7 +8402,7 @@
         <v>1380</v>
       </c>
       <c r="E6">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="F6" t="s">
         <v>1594</v>
@@ -8437,7 +8437,7 @@
         <v>1380</v>
       </c>
       <c r="E7">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="F7" t="s">
         <v>1594</v>
@@ -8472,7 +8472,7 @@
         <v>1381</v>
       </c>
       <c r="E8">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="F8" t="s">
         <v>1594</v>
@@ -8507,7 +8507,7 @@
         <v>1382</v>
       </c>
       <c r="E9">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="F9" t="s">
         <v>1594</v>
@@ -8542,7 +8542,7 @@
         <v>1383</v>
       </c>
       <c r="E10">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="F10" t="s">
         <v>1594</v>
@@ -8577,7 +8577,7 @@
         <v>1384</v>
       </c>
       <c r="E11">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="F11" t="s">
         <v>1594</v>
@@ -8612,7 +8612,7 @@
         <v>1385</v>
       </c>
       <c r="E12">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="F12" t="s">
         <v>1594</v>
@@ -8647,7 +8647,7 @@
         <v>1386</v>
       </c>
       <c r="E13">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F13" t="s">
         <v>1594</v>
@@ -8682,7 +8682,7 @@
         <v>1387</v>
       </c>
       <c r="E14">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="F14" t="s">
         <v>1594</v>
@@ -8717,7 +8717,7 @@
         <v>1387</v>
       </c>
       <c r="E15">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="F15" t="s">
         <v>1594</v>
@@ -8752,7 +8752,7 @@
         <v>1388</v>
       </c>
       <c r="E16">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="F16" t="s">
         <v>1594</v>
@@ -8787,7 +8787,7 @@
         <v>1389</v>
       </c>
       <c r="E17">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="F17" t="s">
         <v>1594</v>
@@ -8822,7 +8822,7 @@
         <v>1390</v>
       </c>
       <c r="E18">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="F18" t="s">
         <v>1594</v>
@@ -8857,7 +8857,7 @@
         <v>1390</v>
       </c>
       <c r="E19">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="F19" t="s">
         <v>1594</v>
@@ -8892,7 +8892,7 @@
         <v>1391</v>
       </c>
       <c r="E20">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="F20" t="s">
         <v>1594</v>
@@ -8927,7 +8927,7 @@
         <v>1392</v>
       </c>
       <c r="E21">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="F21" t="s">
         <v>1594</v>
@@ -8962,7 +8962,7 @@
         <v>1393</v>
       </c>
       <c r="E22">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="F22" t="s">
         <v>1594</v>
@@ -8997,7 +8997,7 @@
         <v>1393</v>
       </c>
       <c r="E23">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="F23" t="s">
         <v>1594</v>
@@ -9032,7 +9032,7 @@
         <v>1394</v>
       </c>
       <c r="E24">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="F24" t="s">
         <v>1594</v>
@@ -9067,7 +9067,7 @@
         <v>1395</v>
       </c>
       <c r="E25">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F25" t="s">
         <v>1594</v>
@@ -9102,7 +9102,7 @@
         <v>1396</v>
       </c>
       <c r="E26">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F26" t="s">
         <v>1594</v>
@@ -9137,7 +9137,7 @@
         <v>1397</v>
       </c>
       <c r="E27">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F27" t="s">
         <v>1594</v>
@@ -9172,7 +9172,7 @@
         <v>1398</v>
       </c>
       <c r="E28">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="F28" t="s">
         <v>1594</v>
@@ -9210,7 +9210,7 @@
         <v>1399</v>
       </c>
       <c r="E29">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F29" t="s">
         <v>1594</v>
@@ -9245,7 +9245,7 @@
         <v>1400</v>
       </c>
       <c r="E30">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="F30" t="s">
         <v>1594</v>
@@ -9280,7 +9280,7 @@
         <v>1401</v>
       </c>
       <c r="E31">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F31" t="s">
         <v>1594</v>
@@ -9315,7 +9315,7 @@
         <v>1402</v>
       </c>
       <c r="E32">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F32" t="s">
         <v>1594</v>
@@ -9350,7 +9350,7 @@
         <v>1402</v>
       </c>
       <c r="E33">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F33" t="s">
         <v>1594</v>
@@ -9385,7 +9385,7 @@
         <v>1403</v>
       </c>
       <c r="E34">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F34" t="s">
         <v>1594</v>
@@ -9420,7 +9420,7 @@
         <v>1404</v>
       </c>
       <c r="E35">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="F35" t="s">
         <v>1594</v>
@@ -9455,7 +9455,7 @@
         <v>1405</v>
       </c>
       <c r="E36">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="F36" t="s">
         <v>1594</v>
@@ -9490,7 +9490,7 @@
         <v>1406</v>
       </c>
       <c r="E37">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F37" t="s">
         <v>1594</v>
@@ -9525,7 +9525,7 @@
         <v>1407</v>
       </c>
       <c r="E38">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F38" t="s">
         <v>1594</v>
@@ -9560,7 +9560,7 @@
         <v>1408</v>
       </c>
       <c r="E39">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F39" t="s">
         <v>1594</v>
@@ -9595,7 +9595,7 @@
         <v>1409</v>
       </c>
       <c r="E40">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F40" t="s">
         <v>1594</v>
@@ -9630,7 +9630,7 @@
         <v>1410</v>
       </c>
       <c r="E41">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F41" t="s">
         <v>1594</v>
@@ -9665,7 +9665,7 @@
         <v>1410</v>
       </c>
       <c r="E42">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F42" t="s">
         <v>1594</v>
@@ -9700,7 +9700,7 @@
         <v>1411</v>
       </c>
       <c r="E43">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F43" t="s">
         <v>1594</v>
@@ -9735,7 +9735,7 @@
         <v>1411</v>
       </c>
       <c r="E44">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F44" t="s">
         <v>1594</v>
@@ -9770,7 +9770,7 @@
         <v>1412</v>
       </c>
       <c r="E45">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F45" t="s">
         <v>1594</v>
@@ -9805,7 +9805,7 @@
         <v>1413</v>
       </c>
       <c r="E46">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F46" t="s">
         <v>1594</v>
@@ -9840,7 +9840,7 @@
         <v>1414</v>
       </c>
       <c r="E47">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F47" t="s">
         <v>1594</v>
@@ -9875,7 +9875,7 @@
         <v>1415</v>
       </c>
       <c r="E48">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F48" t="s">
         <v>1594</v>
@@ -9910,7 +9910,7 @@
         <v>1416</v>
       </c>
       <c r="E49">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F49" t="s">
         <v>1594</v>
@@ -9945,7 +9945,7 @@
         <v>1416</v>
       </c>
       <c r="E50">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F50" t="s">
         <v>1594</v>
@@ -9980,7 +9980,7 @@
         <v>1417</v>
       </c>
       <c r="E51">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F51" t="s">
         <v>1594</v>
@@ -10015,7 +10015,7 @@
         <v>1418</v>
       </c>
       <c r="E52">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F52" t="s">
         <v>1594</v>
@@ -10050,7 +10050,7 @@
         <v>1419</v>
       </c>
       <c r="E53">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F53" t="s">
         <v>1594</v>
@@ -10085,7 +10085,7 @@
         <v>1419</v>
       </c>
       <c r="E54">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F54" t="s">
         <v>1594</v>
@@ -10120,7 +10120,7 @@
         <v>1420</v>
       </c>
       <c r="E55">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F55" t="s">
         <v>1594</v>
@@ -10155,7 +10155,7 @@
         <v>1420</v>
       </c>
       <c r="E56">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F56" t="s">
         <v>1594</v>
@@ -10190,7 +10190,7 @@
         <v>1421</v>
       </c>
       <c r="E57">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F57" t="s">
         <v>1594</v>
@@ -10225,7 +10225,7 @@
         <v>1422</v>
       </c>
       <c r="E58">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F58" t="s">
         <v>1594</v>
@@ -10260,7 +10260,7 @@
         <v>1423</v>
       </c>
       <c r="E59">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F59" t="s">
         <v>1594</v>
@@ -10295,7 +10295,7 @@
         <v>1424</v>
       </c>
       <c r="E60">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F60" t="s">
         <v>1594</v>
@@ -10330,7 +10330,7 @@
         <v>1425</v>
       </c>
       <c r="E61">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F61" t="s">
         <v>1594</v>
@@ -10365,7 +10365,7 @@
         <v>1425</v>
       </c>
       <c r="E62">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F62" t="s">
         <v>1594</v>
@@ -10400,7 +10400,7 @@
         <v>1426</v>
       </c>
       <c r="E63">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F63" t="s">
         <v>1594</v>
@@ -10435,7 +10435,7 @@
         <v>1426</v>
       </c>
       <c r="E64">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F64" t="s">
         <v>1594</v>
@@ -10470,7 +10470,7 @@
         <v>1427</v>
       </c>
       <c r="E65">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F65" t="s">
         <v>1594</v>
@@ -10505,7 +10505,7 @@
         <v>1428</v>
       </c>
       <c r="E66">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F66" t="s">
         <v>1594</v>
@@ -10540,7 +10540,7 @@
         <v>1429</v>
       </c>
       <c r="E67">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F67" t="s">
         <v>1594</v>
@@ -10575,7 +10575,7 @@
         <v>1430</v>
       </c>
       <c r="E68">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F68" t="s">
         <v>1594</v>
@@ -10610,7 +10610,7 @@
         <v>1431</v>
       </c>
       <c r="E69">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F69" t="s">
         <v>1594</v>
@@ -10645,7 +10645,7 @@
         <v>1432</v>
       </c>
       <c r="E70">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F70" t="s">
         <v>1594</v>
@@ -10680,7 +10680,7 @@
         <v>1433</v>
       </c>
       <c r="E71">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F71" t="s">
         <v>1594</v>
@@ -10715,7 +10715,7 @@
         <v>1434</v>
       </c>
       <c r="E72">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F72" t="s">
         <v>1594</v>
@@ -10750,7 +10750,7 @@
         <v>1435</v>
       </c>
       <c r="E73">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F73" t="s">
         <v>1594</v>
@@ -10785,7 +10785,7 @@
         <v>1436</v>
       </c>
       <c r="E74">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F74" t="s">
         <v>1594</v>
@@ -10820,7 +10820,7 @@
         <v>1437</v>
       </c>
       <c r="E75">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F75" t="s">
         <v>1594</v>
@@ -10855,7 +10855,7 @@
         <v>1438</v>
       </c>
       <c r="E76">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F76" t="s">
         <v>1594</v>
@@ -10890,7 +10890,7 @@
         <v>1438</v>
       </c>
       <c r="E77">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F77" t="s">
         <v>1594</v>
@@ -10925,7 +10925,7 @@
         <v>1438</v>
       </c>
       <c r="E78">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F78" t="s">
         <v>1594</v>
@@ -10960,7 +10960,7 @@
         <v>1439</v>
       </c>
       <c r="E79">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F79" t="s">
         <v>1594</v>
@@ -10995,7 +10995,7 @@
         <v>1440</v>
       </c>
       <c r="E80">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F80" t="s">
         <v>1594</v>
@@ -11030,7 +11030,7 @@
         <v>1441</v>
       </c>
       <c r="E81">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F81" t="s">
         <v>1594</v>
@@ -11065,7 +11065,7 @@
         <v>1441</v>
       </c>
       <c r="E82">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F82" t="s">
         <v>1594</v>
@@ -11100,7 +11100,7 @@
         <v>1441</v>
       </c>
       <c r="E83">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F83" t="s">
         <v>1594</v>
@@ -11135,7 +11135,7 @@
         <v>1442</v>
       </c>
       <c r="E84">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F84" t="s">
         <v>1594</v>
@@ -11170,7 +11170,7 @@
         <v>1443</v>
       </c>
       <c r="E85">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F85" t="s">
         <v>1594</v>
@@ -11205,7 +11205,7 @@
         <v>1444</v>
       </c>
       <c r="E86">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F86" t="s">
         <v>1594</v>
@@ -11240,7 +11240,7 @@
         <v>1444</v>
       </c>
       <c r="E87">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F87" t="s">
         <v>1594</v>
@@ -11275,7 +11275,7 @@
         <v>1444</v>
       </c>
       <c r="E88">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F88" t="s">
         <v>1594</v>
@@ -11310,7 +11310,7 @@
         <v>1445</v>
       </c>
       <c r="E89">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F89" t="s">
         <v>1594</v>
@@ -11345,7 +11345,7 @@
         <v>1446</v>
       </c>
       <c r="E90">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F90" t="s">
         <v>1594</v>
@@ -11380,7 +11380,7 @@
         <v>1446</v>
       </c>
       <c r="E91">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F91" t="s">
         <v>1594</v>
@@ -11415,7 +11415,7 @@
         <v>1446</v>
       </c>
       <c r="E92">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F92" t="s">
         <v>1595</v>
@@ -11450,7 +11450,7 @@
         <v>1446</v>
       </c>
       <c r="E93">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F93" t="s">
         <v>1594</v>
@@ -11485,7 +11485,7 @@
         <v>1447</v>
       </c>
       <c r="E94">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F94" t="s">
         <v>1594</v>
@@ -11520,7 +11520,7 @@
         <v>1448</v>
       </c>
       <c r="E95">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F95" t="s">
         <v>1594</v>
@@ -11555,7 +11555,7 @@
         <v>1449</v>
       </c>
       <c r="E96">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F96" t="s">
         <v>1594</v>
@@ -11590,7 +11590,7 @@
         <v>1449</v>
       </c>
       <c r="E97">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F97" t="s">
         <v>1594</v>
@@ -11625,7 +11625,7 @@
         <v>1449</v>
       </c>
       <c r="E98">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F98" t="s">
         <v>1594</v>
@@ -11660,7 +11660,7 @@
         <v>1450</v>
       </c>
       <c r="E99">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F99" t="s">
         <v>1594</v>
@@ -11695,7 +11695,7 @@
         <v>1451</v>
       </c>
       <c r="E100">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F100" t="s">
         <v>1594</v>
@@ -11730,7 +11730,7 @@
         <v>1452</v>
       </c>
       <c r="E101">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F101" t="s">
         <v>1594</v>
@@ -11765,7 +11765,7 @@
         <v>1453</v>
       </c>
       <c r="E102">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F102" t="s">
         <v>1594</v>
@@ -11800,7 +11800,7 @@
         <v>1454</v>
       </c>
       <c r="E103">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F103" t="s">
         <v>1594</v>
@@ -11835,7 +11835,7 @@
         <v>1454</v>
       </c>
       <c r="E104">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F104" t="s">
         <v>1594</v>
@@ -11870,7 +11870,7 @@
         <v>1454</v>
       </c>
       <c r="E105">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F105" t="s">
         <v>1594</v>
@@ -11905,7 +11905,7 @@
         <v>1454</v>
       </c>
       <c r="E106">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F106" t="s">
         <v>1594</v>
@@ -11940,7 +11940,7 @@
         <v>1454</v>
       </c>
       <c r="E107">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F107" t="s">
         <v>1594</v>
@@ -11975,7 +11975,7 @@
         <v>1454</v>
       </c>
       <c r="E108">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F108" t="s">
         <v>1594</v>
@@ -12010,7 +12010,7 @@
         <v>1454</v>
       </c>
       <c r="E109">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F109" t="s">
         <v>1594</v>
@@ -12045,7 +12045,7 @@
         <v>1455</v>
       </c>
       <c r="E110">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F110" t="s">
         <v>1594</v>
@@ -12080,7 +12080,7 @@
         <v>1455</v>
       </c>
       <c r="E111">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F111" t="s">
         <v>1594</v>
@@ -12115,7 +12115,7 @@
         <v>1456</v>
       </c>
       <c r="E112">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F112" t="s">
         <v>1594</v>
@@ -12150,7 +12150,7 @@
         <v>1457</v>
       </c>
       <c r="E113">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F113" t="s">
         <v>1594</v>
@@ -12185,7 +12185,7 @@
         <v>1457</v>
       </c>
       <c r="E114">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F114" t="s">
         <v>1594</v>
@@ -12220,7 +12220,7 @@
         <v>1458</v>
       </c>
       <c r="E115">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F115" t="s">
         <v>1594</v>
@@ -12255,7 +12255,7 @@
         <v>1458</v>
       </c>
       <c r="E116">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F116" t="s">
         <v>1596</v>
@@ -12290,7 +12290,7 @@
         <v>1459</v>
       </c>
       <c r="E117">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F117" t="s">
         <v>1594</v>
@@ -12325,7 +12325,7 @@
         <v>1460</v>
       </c>
       <c r="E118">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F118" t="s">
         <v>1594</v>
@@ -12360,7 +12360,7 @@
         <v>1461</v>
       </c>
       <c r="E119">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F119" t="s">
         <v>1594</v>
@@ -12395,7 +12395,7 @@
         <v>1461</v>
       </c>
       <c r="E120">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F120" t="s">
         <v>1594</v>
@@ -12430,7 +12430,7 @@
         <v>1462</v>
       </c>
       <c r="E121">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F121" t="s">
         <v>1594</v>
@@ -12465,7 +12465,7 @@
         <v>1463</v>
       </c>
       <c r="E122">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F122" t="s">
         <v>1594</v>
@@ -12500,7 +12500,7 @@
         <v>1464</v>
       </c>
       <c r="E123">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F123" t="s">
         <v>1594</v>
@@ -12535,7 +12535,7 @@
         <v>1464</v>
       </c>
       <c r="E124">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F124" t="s">
         <v>1594</v>
@@ -12570,7 +12570,7 @@
         <v>1465</v>
       </c>
       <c r="E125">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F125" t="s">
         <v>1594</v>
@@ -12605,7 +12605,7 @@
         <v>1466</v>
       </c>
       <c r="E126">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F126" t="s">
         <v>1594</v>
@@ -12640,7 +12640,7 @@
         <v>1466</v>
       </c>
       <c r="E127">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F127" t="s">
         <v>1594</v>
@@ -12675,7 +12675,7 @@
         <v>1467</v>
       </c>
       <c r="E128">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F128" t="s">
         <v>1594</v>
@@ -12710,7 +12710,7 @@
         <v>1467</v>
       </c>
       <c r="E129">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F129" t="s">
         <v>1594</v>
@@ -12745,7 +12745,7 @@
         <v>1467</v>
       </c>
       <c r="E130">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F130" t="s">
         <v>1594</v>
@@ -12780,7 +12780,7 @@
         <v>1467</v>
       </c>
       <c r="E131">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F131" t="s">
         <v>1594</v>
@@ -12815,7 +12815,7 @@
         <v>1468</v>
       </c>
       <c r="E132">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F132" t="s">
         <v>1594</v>
@@ -12850,7 +12850,7 @@
         <v>1468</v>
       </c>
       <c r="E133">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F133" t="s">
         <v>1594</v>
@@ -12885,7 +12885,7 @@
         <v>1468</v>
       </c>
       <c r="E134">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F134" t="s">
         <v>1594</v>
@@ -12920,7 +12920,7 @@
         <v>1468</v>
       </c>
       <c r="E135">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F135" t="s">
         <v>1594</v>
@@ -12955,7 +12955,7 @@
         <v>1468</v>
       </c>
       <c r="E136">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F136" t="s">
         <v>1594</v>
@@ -12990,7 +12990,7 @@
         <v>1468</v>
       </c>
       <c r="E137">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F137" t="s">
         <v>1594</v>
@@ -13025,7 +13025,7 @@
         <v>1469</v>
       </c>
       <c r="E138">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F138" t="s">
         <v>1594</v>
@@ -13060,7 +13060,7 @@
         <v>1470</v>
       </c>
       <c r="E139">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F139" t="s">
         <v>1594</v>
@@ -13095,7 +13095,7 @@
         <v>1470</v>
       </c>
       <c r="E140">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F140" t="s">
         <v>1594</v>
@@ -13130,7 +13130,7 @@
         <v>1471</v>
       </c>
       <c r="E141">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F141" t="s">
         <v>1594</v>
@@ -13165,7 +13165,7 @@
         <v>1472</v>
       </c>
       <c r="E142">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F142" t="s">
         <v>1594</v>
@@ -13200,7 +13200,7 @@
         <v>1472</v>
       </c>
       <c r="E143">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F143" t="s">
         <v>1594</v>
@@ -13235,7 +13235,7 @@
         <v>1472</v>
       </c>
       <c r="E144">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F144" t="s">
         <v>1594</v>
@@ -13270,7 +13270,7 @@
         <v>1473</v>
       </c>
       <c r="E145">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F145" t="s">
         <v>1594</v>
@@ -13305,7 +13305,7 @@
         <v>1473</v>
       </c>
       <c r="E146">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F146" t="s">
         <v>1594</v>
@@ -13340,7 +13340,7 @@
         <v>1473</v>
       </c>
       <c r="E147">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F147" t="s">
         <v>1594</v>
@@ -13375,7 +13375,7 @@
         <v>1474</v>
       </c>
       <c r="E148">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F148" t="s">
         <v>1594</v>
@@ -13410,7 +13410,7 @@
         <v>1474</v>
       </c>
       <c r="E149">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F149" t="s">
         <v>1594</v>
@@ -13445,7 +13445,7 @@
         <v>1474</v>
       </c>
       <c r="E150">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F150" t="s">
         <v>1594</v>
@@ -13480,7 +13480,7 @@
         <v>1475</v>
       </c>
       <c r="E151">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F151" t="s">
         <v>1594</v>
@@ -13515,7 +13515,7 @@
         <v>1475</v>
       </c>
       <c r="E152">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F152" t="s">
         <v>1594</v>
@@ -13550,7 +13550,7 @@
         <v>1476</v>
       </c>
       <c r="E153">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F153" t="s">
         <v>1594</v>
@@ -13585,7 +13585,7 @@
         <v>1477</v>
       </c>
       <c r="E154">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F154" t="s">
         <v>1594</v>
@@ -13620,7 +13620,7 @@
         <v>1477</v>
       </c>
       <c r="E155">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F155" t="s">
         <v>1594</v>
@@ -13655,7 +13655,7 @@
         <v>1477</v>
       </c>
       <c r="E156">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F156" t="s">
         <v>1594</v>
@@ -13690,7 +13690,7 @@
         <v>1478</v>
       </c>
       <c r="E157">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F157" t="s">
         <v>1594</v>
@@ -13725,7 +13725,7 @@
         <v>1478</v>
       </c>
       <c r="E158">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F158" t="s">
         <v>1594</v>
@@ -13760,7 +13760,7 @@
         <v>1479</v>
       </c>
       <c r="E159">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F159" t="s">
         <v>1594</v>
@@ -13798,7 +13798,7 @@
         <v>1479</v>
       </c>
       <c r="E160">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F160" t="s">
         <v>1594</v>
@@ -13833,7 +13833,7 @@
         <v>1479</v>
       </c>
       <c r="E161">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F161" t="s">
         <v>1594</v>
@@ -13868,7 +13868,7 @@
         <v>1479</v>
       </c>
       <c r="E162">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F162" t="s">
         <v>1594</v>
@@ -13903,7 +13903,7 @@
         <v>1479</v>
       </c>
       <c r="E163">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F163" t="s">
         <v>1594</v>
@@ -13938,7 +13938,7 @@
         <v>1479</v>
       </c>
       <c r="E164">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F164" t="s">
         <v>1594</v>
@@ -13973,7 +13973,7 @@
         <v>1480</v>
       </c>
       <c r="E165">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F165" t="s">
         <v>1594</v>
@@ -14008,7 +14008,7 @@
         <v>1481</v>
       </c>
       <c r="E166">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F166" t="s">
         <v>1594</v>
@@ -14043,7 +14043,7 @@
         <v>1482</v>
       </c>
       <c r="E167">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F167" t="s">
         <v>1595</v>
@@ -14078,7 +14078,7 @@
         <v>1483</v>
       </c>
       <c r="E168">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F168" t="s">
         <v>1594</v>
@@ -14113,7 +14113,7 @@
         <v>1483</v>
       </c>
       <c r="E169">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F169" t="s">
         <v>1594</v>
@@ -14148,7 +14148,7 @@
         <v>1483</v>
       </c>
       <c r="E170">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F170" t="s">
         <v>1594</v>
@@ -14183,7 +14183,7 @@
         <v>1483</v>
       </c>
       <c r="E171">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F171" t="s">
         <v>1594</v>
@@ -14218,7 +14218,7 @@
         <v>1484</v>
       </c>
       <c r="E172">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F172" t="s">
         <v>1594</v>
@@ -14253,7 +14253,7 @@
         <v>1484</v>
       </c>
       <c r="E173">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F173" t="s">
         <v>1594</v>
@@ -14288,7 +14288,7 @@
         <v>1484</v>
       </c>
       <c r="E174">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F174" t="s">
         <v>1594</v>
@@ -14323,7 +14323,7 @@
         <v>1484</v>
       </c>
       <c r="E175">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F175" t="s">
         <v>1594</v>
@@ -14358,7 +14358,7 @@
         <v>1484</v>
       </c>
       <c r="E176">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F176" t="s">
         <v>1594</v>
@@ -14393,7 +14393,7 @@
         <v>1484</v>
       </c>
       <c r="E177">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F177" t="s">
         <v>1594</v>
@@ -14428,7 +14428,7 @@
         <v>1484</v>
       </c>
       <c r="E178">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F178" t="s">
         <v>1594</v>
@@ -14463,7 +14463,7 @@
         <v>1485</v>
       </c>
       <c r="E179">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F179" t="s">
         <v>1594</v>
@@ -14498,7 +14498,7 @@
         <v>1485</v>
       </c>
       <c r="E180">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F180" t="s">
         <v>1594</v>
@@ -14533,7 +14533,7 @@
         <v>1486</v>
       </c>
       <c r="E181">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F181" t="s">
         <v>1594</v>
@@ -14568,7 +14568,7 @@
         <v>1486</v>
       </c>
       <c r="E182">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F182" t="s">
         <v>1594</v>
@@ -14603,7 +14603,7 @@
         <v>1486</v>
       </c>
       <c r="E183">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F183" t="s">
         <v>1594</v>
@@ -14638,7 +14638,7 @@
         <v>1487</v>
       </c>
       <c r="E184">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F184" t="s">
         <v>1594</v>
@@ -14673,7 +14673,7 @@
         <v>1487</v>
       </c>
       <c r="E185">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F185" t="s">
         <v>1594</v>
@@ -14708,7 +14708,7 @@
         <v>1487</v>
       </c>
       <c r="E186">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F186" t="s">
         <v>1594</v>
@@ -14743,7 +14743,7 @@
         <v>1487</v>
       </c>
       <c r="E187">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F187" t="s">
         <v>1594</v>
@@ -14778,7 +14778,7 @@
         <v>1488</v>
       </c>
       <c r="E188">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F188" t="s">
         <v>1594</v>
@@ -14813,7 +14813,7 @@
         <v>1488</v>
       </c>
       <c r="E189">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F189" t="s">
         <v>1594</v>
@@ -14848,7 +14848,7 @@
         <v>1488</v>
       </c>
       <c r="E190">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F190" t="s">
         <v>1594</v>
@@ -14883,7 +14883,7 @@
         <v>1488</v>
       </c>
       <c r="E191">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F191" t="s">
         <v>1594</v>
@@ -14918,7 +14918,7 @@
         <v>1488</v>
       </c>
       <c r="E192">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F192" t="s">
         <v>1594</v>
@@ -14953,7 +14953,7 @@
         <v>1488</v>
       </c>
       <c r="E193">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F193" t="s">
         <v>1594</v>
@@ -14988,7 +14988,7 @@
         <v>1488</v>
       </c>
       <c r="E194">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F194" t="s">
         <v>1594</v>
@@ -15023,7 +15023,7 @@
         <v>1488</v>
       </c>
       <c r="E195">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F195" t="s">
         <v>1594</v>
@@ -15058,7 +15058,7 @@
         <v>1488</v>
       </c>
       <c r="E196">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F196" t="s">
         <v>1594</v>
@@ -15093,7 +15093,7 @@
         <v>1488</v>
       </c>
       <c r="E197">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F197" t="s">
         <v>1594</v>
@@ -15128,7 +15128,7 @@
         <v>1489</v>
       </c>
       <c r="E198">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F198" t="s">
         <v>1594</v>
@@ -15163,7 +15163,7 @@
         <v>1489</v>
       </c>
       <c r="E199">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F199" t="s">
         <v>1594</v>
@@ -15198,7 +15198,7 @@
         <v>1489</v>
       </c>
       <c r="E200">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F200" t="s">
         <v>1594</v>
@@ -15233,7 +15233,7 @@
         <v>1489</v>
       </c>
       <c r="E201">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F201" t="s">
         <v>1597</v>
@@ -15268,7 +15268,7 @@
         <v>1490</v>
       </c>
       <c r="E202">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F202" t="s">
         <v>1594</v>
@@ -15303,7 +15303,7 @@
         <v>1490</v>
       </c>
       <c r="E203">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F203" t="s">
         <v>1595</v>
@@ -15338,7 +15338,7 @@
         <v>1490</v>
       </c>
       <c r="E204">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F204" t="s">
         <v>1594</v>
@@ -15373,7 +15373,7 @@
         <v>1491</v>
       </c>
       <c r="E205">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F205" t="s">
         <v>1594</v>
@@ -15408,7 +15408,7 @@
         <v>1491</v>
       </c>
       <c r="E206">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F206" t="s">
         <v>1594</v>
@@ -15443,7 +15443,7 @@
         <v>1492</v>
       </c>
       <c r="E207">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F207" t="s">
         <v>1594</v>
@@ -15478,7 +15478,7 @@
         <v>1492</v>
       </c>
       <c r="E208">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F208" t="s">
         <v>1594</v>
@@ -15513,7 +15513,7 @@
         <v>1493</v>
       </c>
       <c r="E209">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F209" t="s">
         <v>1594</v>
@@ -15548,7 +15548,7 @@
         <v>1493</v>
       </c>
       <c r="E210">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F210" t="s">
         <v>1594</v>
@@ -15583,7 +15583,7 @@
         <v>1493</v>
       </c>
       <c r="E211">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F211" t="s">
         <v>1594</v>
@@ -15618,7 +15618,7 @@
         <v>1494</v>
       </c>
       <c r="E212">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F212" t="s">
         <v>1594</v>
@@ -15653,7 +15653,7 @@
         <v>1494</v>
       </c>
       <c r="E213">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F213" t="s">
         <v>1594</v>
@@ -15688,7 +15688,7 @@
         <v>1494</v>
       </c>
       <c r="E214">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F214" t="s">
         <v>1594</v>
@@ -15723,7 +15723,7 @@
         <v>1494</v>
       </c>
       <c r="E215">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F215" t="s">
         <v>1594</v>
@@ -15758,7 +15758,7 @@
         <v>1494</v>
       </c>
       <c r="E216">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F216" t="s">
         <v>1594</v>
@@ -15793,7 +15793,7 @@
         <v>1495</v>
       </c>
       <c r="E217">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F217" t="s">
         <v>1594</v>
@@ -15828,7 +15828,7 @@
         <v>1495</v>
       </c>
       <c r="E218">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F218" t="s">
         <v>1594</v>
@@ -15863,7 +15863,7 @@
         <v>1496</v>
       </c>
       <c r="E219">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F219" t="s">
         <v>1594</v>
@@ -15898,7 +15898,7 @@
         <v>1497</v>
       </c>
       <c r="E220">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F220" t="s">
         <v>1594</v>
@@ -15933,7 +15933,7 @@
         <v>1497</v>
       </c>
       <c r="E221">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F221" t="s">
         <v>1594</v>
@@ -15968,7 +15968,7 @@
         <v>1497</v>
       </c>
       <c r="E222">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F222" t="s">
         <v>1594</v>
@@ -16003,7 +16003,7 @@
         <v>1497</v>
       </c>
       <c r="E223">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F223" t="s">
         <v>1594</v>
@@ -16038,7 +16038,7 @@
         <v>1498</v>
       </c>
       <c r="E224">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F224" t="s">
         <v>1594</v>
@@ -16073,7 +16073,7 @@
         <v>1499</v>
       </c>
       <c r="E225">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F225" t="s">
         <v>1594</v>
@@ -16108,7 +16108,7 @@
         <v>1499</v>
       </c>
       <c r="E226">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F226" t="s">
         <v>1594</v>
@@ -16143,7 +16143,7 @@
         <v>1499</v>
       </c>
       <c r="E227">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F227" t="s">
         <v>1594</v>
@@ -16178,7 +16178,7 @@
         <v>1499</v>
       </c>
       <c r="E228">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F228" t="s">
         <v>1594</v>
@@ -16213,7 +16213,7 @@
         <v>1499</v>
       </c>
       <c r="E229">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F229" t="s">
         <v>1594</v>
@@ -16248,7 +16248,7 @@
         <v>1500</v>
       </c>
       <c r="E230">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F230" t="s">
         <v>1594</v>
@@ -16283,7 +16283,7 @@
         <v>1500</v>
       </c>
       <c r="E231">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F231" t="s">
         <v>1594</v>
@@ -16318,7 +16318,7 @@
         <v>1500</v>
       </c>
       <c r="E232">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F232" t="s">
         <v>1594</v>
@@ -16353,7 +16353,7 @@
         <v>1500</v>
       </c>
       <c r="E233">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F233" t="s">
         <v>1594</v>
@@ -16388,7 +16388,7 @@
         <v>1500</v>
       </c>
       <c r="E234">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F234" t="s">
         <v>1594</v>
@@ -16423,7 +16423,7 @@
         <v>1500</v>
       </c>
       <c r="E235">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F235" t="s">
         <v>1594</v>
@@ -16458,7 +16458,7 @@
         <v>1500</v>
       </c>
       <c r="E236">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F236" t="s">
         <v>1594</v>
@@ -16493,7 +16493,7 @@
         <v>1501</v>
       </c>
       <c r="E237">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F237" t="s">
         <v>1594</v>
@@ -16528,7 +16528,7 @@
         <v>1501</v>
       </c>
       <c r="E238">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F238" t="s">
         <v>1594</v>
@@ -16563,7 +16563,7 @@
         <v>1501</v>
       </c>
       <c r="E239">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F239" t="s">
         <v>1594</v>
@@ -16598,7 +16598,7 @@
         <v>1501</v>
       </c>
       <c r="E240">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F240" t="s">
         <v>1594</v>
@@ -16633,7 +16633,7 @@
         <v>1502</v>
       </c>
       <c r="E241">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F241" t="s">
         <v>1594</v>
@@ -16668,7 +16668,7 @@
         <v>1502</v>
       </c>
       <c r="E242">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F242" t="s">
         <v>1594</v>
@@ -16703,7 +16703,7 @@
         <v>1502</v>
       </c>
       <c r="E243">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F243" t="s">
         <v>1594</v>
@@ -16738,7 +16738,7 @@
         <v>1503</v>
       </c>
       <c r="E244">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F244" t="s">
         <v>1594</v>
@@ -16773,7 +16773,7 @@
         <v>1503</v>
       </c>
       <c r="E245">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F245" t="s">
         <v>1594</v>
@@ -16808,7 +16808,7 @@
         <v>1504</v>
       </c>
       <c r="E246">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F246" t="s">
         <v>1594</v>
@@ -16843,7 +16843,7 @@
         <v>1504</v>
       </c>
       <c r="E247">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F247" t="s">
         <v>1594</v>
@@ -16878,7 +16878,7 @@
         <v>1505</v>
       </c>
       <c r="E248">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F248" t="s">
         <v>1594</v>
@@ -16913,7 +16913,7 @@
         <v>1505</v>
       </c>
       <c r="E249">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F249" t="s">
         <v>1594</v>
@@ -16948,7 +16948,7 @@
         <v>1506</v>
       </c>
       <c r="E250">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F250" t="s">
         <v>1594</v>
@@ -16983,7 +16983,7 @@
         <v>1506</v>
       </c>
       <c r="E251">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F251" t="s">
         <v>1594</v>
@@ -17018,7 +17018,7 @@
         <v>1507</v>
       </c>
       <c r="E252">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F252" t="s">
         <v>1594</v>
@@ -17053,7 +17053,7 @@
         <v>1507</v>
       </c>
       <c r="E253">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F253" t="s">
         <v>1594</v>
@@ -17088,7 +17088,7 @@
         <v>1508</v>
       </c>
       <c r="E254">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F254" t="s">
         <v>1594</v>
@@ -17123,7 +17123,7 @@
         <v>1508</v>
       </c>
       <c r="E255">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F255" t="s">
         <v>1594</v>
@@ -17158,7 +17158,7 @@
         <v>1509</v>
       </c>
       <c r="E256">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F256" t="s">
         <v>1594</v>
@@ -17193,7 +17193,7 @@
         <v>1509</v>
       </c>
       <c r="E257">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F257" t="s">
         <v>1594</v>
@@ -17228,7 +17228,7 @@
         <v>1509</v>
       </c>
       <c r="E258">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F258" t="s">
         <v>1594</v>
@@ -17263,7 +17263,7 @@
         <v>1510</v>
       </c>
       <c r="E259">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F259" t="s">
         <v>1594</v>
@@ -17298,7 +17298,7 @@
         <v>1510</v>
       </c>
       <c r="E260">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F260" t="s">
         <v>1594</v>
@@ -17333,7 +17333,7 @@
         <v>1510</v>
       </c>
       <c r="E261">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F261" t="s">
         <v>1594</v>
@@ -17368,7 +17368,7 @@
         <v>1511</v>
       </c>
       <c r="E262">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F262" t="s">
         <v>1594</v>
@@ -17403,7 +17403,7 @@
         <v>1512</v>
       </c>
       <c r="E263">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F263" t="s">
         <v>1594</v>
@@ -17438,7 +17438,7 @@
         <v>1512</v>
       </c>
       <c r="E264">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F264" t="s">
         <v>1594</v>
@@ -17473,7 +17473,7 @@
         <v>1512</v>
       </c>
       <c r="E265">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F265" t="s">
         <v>1594</v>
@@ -17508,7 +17508,7 @@
         <v>1513</v>
       </c>
       <c r="E266">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F266" t="s">
         <v>1594</v>
@@ -17543,7 +17543,7 @@
         <v>1513</v>
       </c>
       <c r="E267">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F267" t="s">
         <v>1594</v>
@@ -17578,7 +17578,7 @@
         <v>1514</v>
       </c>
       <c r="E268">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F268" t="s">
         <v>1594</v>
@@ -17613,7 +17613,7 @@
         <v>1514</v>
       </c>
       <c r="E269">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F269" t="s">
         <v>1594</v>
@@ -17648,7 +17648,7 @@
         <v>1514</v>
       </c>
       <c r="E270">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F270" t="s">
         <v>1596</v>
@@ -17683,7 +17683,7 @@
         <v>1514</v>
       </c>
       <c r="E271">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F271" t="s">
         <v>1594</v>
@@ -17718,7 +17718,7 @@
         <v>1514</v>
       </c>
       <c r="E272">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F272" t="s">
         <v>1594</v>
@@ -17753,7 +17753,7 @@
         <v>1515</v>
       </c>
       <c r="E273">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F273" t="s">
         <v>1594</v>
@@ -17788,7 +17788,7 @@
         <v>1515</v>
       </c>
       <c r="E274">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F274" t="s">
         <v>1594</v>
@@ -17823,7 +17823,7 @@
         <v>1515</v>
       </c>
       <c r="E275">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F275" t="s">
         <v>1594</v>
@@ -17861,7 +17861,7 @@
         <v>1515</v>
       </c>
       <c r="E276">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F276" t="s">
         <v>1594</v>
@@ -17896,7 +17896,7 @@
         <v>1515</v>
       </c>
       <c r="E277">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F277" t="s">
         <v>1594</v>
@@ -17931,7 +17931,7 @@
         <v>1515</v>
       </c>
       <c r="E278">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F278" t="s">
         <v>1594</v>
@@ -17966,7 +17966,7 @@
         <v>1515</v>
       </c>
       <c r="E279">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F279" t="s">
         <v>1594</v>
@@ -18001,7 +18001,7 @@
         <v>1516</v>
       </c>
       <c r="E280">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F280" t="s">
         <v>1594</v>
@@ -18036,7 +18036,7 @@
         <v>1516</v>
       </c>
       <c r="E281">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F281" t="s">
         <v>1594</v>
@@ -18071,7 +18071,7 @@
         <v>1516</v>
       </c>
       <c r="E282">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F282" t="s">
         <v>1594</v>
@@ -18106,7 +18106,7 @@
         <v>1517</v>
       </c>
       <c r="E283">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F283" t="s">
         <v>1594</v>
@@ -18141,7 +18141,7 @@
         <v>1517</v>
       </c>
       <c r="E284">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F284" t="s">
         <v>1594</v>
@@ -18176,7 +18176,7 @@
         <v>1517</v>
       </c>
       <c r="E285">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F285" t="s">
         <v>1594</v>
@@ -18211,7 +18211,7 @@
         <v>1517</v>
       </c>
       <c r="E286">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F286" t="s">
         <v>1594</v>
@@ -18246,7 +18246,7 @@
         <v>1517</v>
       </c>
       <c r="E287">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F287" t="s">
         <v>1594</v>
@@ -18281,7 +18281,7 @@
         <v>1518</v>
       </c>
       <c r="E288">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F288" t="s">
         <v>1594</v>
@@ -18316,7 +18316,7 @@
         <v>1518</v>
       </c>
       <c r="E289">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F289" t="s">
         <v>1594</v>
@@ -18351,7 +18351,7 @@
         <v>1518</v>
       </c>
       <c r="E290">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F290" t="s">
         <v>1594</v>
@@ -18386,7 +18386,7 @@
         <v>1518</v>
       </c>
       <c r="E291">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F291" t="s">
         <v>1594</v>
@@ -18421,7 +18421,7 @@
         <v>1518</v>
       </c>
       <c r="E292">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F292" t="s">
         <v>1594</v>
@@ -18456,7 +18456,7 @@
         <v>1518</v>
       </c>
       <c r="E293">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F293" t="s">
         <v>1594</v>
@@ -18491,7 +18491,7 @@
         <v>1519</v>
       </c>
       <c r="E294">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F294" t="s">
         <v>1594</v>
@@ -18526,7 +18526,7 @@
         <v>1519</v>
       </c>
       <c r="E295">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F295" t="s">
         <v>1594</v>
@@ -18561,7 +18561,7 @@
         <v>1519</v>
       </c>
       <c r="E296">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F296" t="s">
         <v>1594</v>
@@ -18596,7 +18596,7 @@
         <v>1519</v>
       </c>
       <c r="E297">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F297" t="s">
         <v>1594</v>
@@ -18631,7 +18631,7 @@
         <v>1519</v>
       </c>
       <c r="E298">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F298" t="s">
         <v>1594</v>
@@ -18666,7 +18666,7 @@
         <v>1519</v>
       </c>
       <c r="E299">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F299" t="s">
         <v>1594</v>
@@ -18701,7 +18701,7 @@
         <v>1520</v>
       </c>
       <c r="E300">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F300" t="s">
         <v>1594</v>
@@ -18736,7 +18736,7 @@
         <v>1521</v>
       </c>
       <c r="E301">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F301" t="s">
         <v>1595</v>
@@ -18771,7 +18771,7 @@
         <v>1521</v>
       </c>
       <c r="E302">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F302" t="s">
         <v>1594</v>
@@ -18806,7 +18806,7 @@
         <v>1521</v>
       </c>
       <c r="E303">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F303" t="s">
         <v>1594</v>
@@ -18841,7 +18841,7 @@
         <v>1521</v>
       </c>
       <c r="E304">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F304" t="s">
         <v>1597</v>
@@ -18876,7 +18876,7 @@
         <v>1521</v>
       </c>
       <c r="E305">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F305" t="s">
         <v>1594</v>
@@ -18911,7 +18911,7 @@
         <v>1521</v>
       </c>
       <c r="E306">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F306" t="s">
         <v>1594</v>
@@ -18946,7 +18946,7 @@
         <v>1521</v>
       </c>
       <c r="E307">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F307" t="s">
         <v>1594</v>
@@ -18981,7 +18981,7 @@
         <v>1521</v>
       </c>
       <c r="E308">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F308" t="s">
         <v>1594</v>
@@ -19016,7 +19016,7 @@
         <v>1522</v>
       </c>
       <c r="E309">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F309" t="s">
         <v>1594</v>
@@ -19051,7 +19051,7 @@
         <v>1522</v>
       </c>
       <c r="E310">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F310" t="s">
         <v>1594</v>
@@ -19086,7 +19086,7 @@
         <v>1522</v>
       </c>
       <c r="E311">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F311" t="s">
         <v>1594</v>
@@ -19121,7 +19121,7 @@
         <v>1522</v>
       </c>
       <c r="E312">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F312" t="s">
         <v>1594</v>
@@ -19156,7 +19156,7 @@
         <v>1523</v>
       </c>
       <c r="E313">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F313" t="s">
         <v>1594</v>
@@ -19191,7 +19191,7 @@
         <v>1523</v>
       </c>
       <c r="E314">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F314" t="s">
         <v>1594</v>
@@ -19226,7 +19226,7 @@
         <v>1524</v>
       </c>
       <c r="E315">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F315" t="s">
         <v>1594</v>
@@ -19264,7 +19264,7 @@
         <v>1524</v>
       </c>
       <c r="E316">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F316" t="s">
         <v>1594</v>
@@ -19299,7 +19299,7 @@
         <v>1525</v>
       </c>
       <c r="E317">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F317" t="s">
         <v>1594</v>
@@ -19334,7 +19334,7 @@
         <v>1525</v>
       </c>
       <c r="E318">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F318" t="s">
         <v>1594</v>
@@ -19369,7 +19369,7 @@
         <v>1525</v>
       </c>
       <c r="E319">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F319" t="s">
         <v>1594</v>
@@ -19404,7 +19404,7 @@
         <v>1525</v>
       </c>
       <c r="E320">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F320" t="s">
         <v>1594</v>
@@ -19442,7 +19442,7 @@
         <v>1525</v>
       </c>
       <c r="E321">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F321" t="s">
         <v>1594</v>
@@ -19477,7 +19477,7 @@
         <v>1525</v>
       </c>
       <c r="E322">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F322" t="s">
         <v>1594</v>
@@ -19512,7 +19512,7 @@
         <v>1526</v>
       </c>
       <c r="E323">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F323" t="s">
         <v>1594</v>
@@ -19547,7 +19547,7 @@
         <v>1526</v>
       </c>
       <c r="E324">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F324" t="s">
         <v>1594</v>
@@ -19582,7 +19582,7 @@
         <v>1527</v>
       </c>
       <c r="E325">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F325" t="s">
         <v>1594</v>
@@ -19617,7 +19617,7 @@
         <v>1527</v>
       </c>
       <c r="E326">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F326" t="s">
         <v>1594</v>
@@ -19652,7 +19652,7 @@
         <v>1528</v>
       </c>
       <c r="E327">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F327" t="s">
         <v>1594</v>
@@ -19687,7 +19687,7 @@
         <v>1528</v>
       </c>
       <c r="E328">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F328" t="s">
         <v>1594</v>
@@ -19722,7 +19722,7 @@
         <v>1528</v>
       </c>
       <c r="E329">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F329" t="s">
         <v>1594</v>
@@ -19757,7 +19757,7 @@
         <v>1528</v>
       </c>
       <c r="E330">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F330" t="s">
         <v>1594</v>
@@ -19792,7 +19792,7 @@
         <v>1529</v>
       </c>
       <c r="E331">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F331" t="s">
         <v>1594</v>
@@ -19827,7 +19827,7 @@
         <v>1529</v>
       </c>
       <c r="E332">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F332" t="s">
         <v>1594</v>
@@ -19862,7 +19862,7 @@
         <v>1529</v>
       </c>
       <c r="E333">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F333" t="s">
         <v>1594</v>
@@ -19897,7 +19897,7 @@
         <v>1529</v>
       </c>
       <c r="E334">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F334" t="s">
         <v>1594</v>
@@ -19932,7 +19932,7 @@
         <v>1530</v>
       </c>
       <c r="E335">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F335" t="s">
         <v>1594</v>
@@ -19967,7 +19967,7 @@
         <v>1530</v>
       </c>
       <c r="E336">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F336" t="s">
         <v>1594</v>
@@ -20002,7 +20002,7 @@
         <v>1531</v>
       </c>
       <c r="E337">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F337" t="s">
         <v>1594</v>
@@ -20037,7 +20037,7 @@
         <v>1531</v>
       </c>
       <c r="E338">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F338" t="s">
         <v>1594</v>
@@ -20072,7 +20072,7 @@
         <v>1531</v>
       </c>
       <c r="E339">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F339" t="s">
         <v>1594</v>
@@ -20107,7 +20107,7 @@
         <v>1531</v>
       </c>
       <c r="E340">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F340" t="s">
         <v>1594</v>
@@ -20142,7 +20142,7 @@
         <v>1531</v>
       </c>
       <c r="E341">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F341" t="s">
         <v>1594</v>
@@ -20177,7 +20177,7 @@
         <v>1532</v>
       </c>
       <c r="E342">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F342" t="s">
         <v>1594</v>
@@ -20212,7 +20212,7 @@
         <v>1532</v>
       </c>
       <c r="E343">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F343" t="s">
         <v>1594</v>
@@ -20247,7 +20247,7 @@
         <v>1532</v>
       </c>
       <c r="E344">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F344" t="s">
         <v>1594</v>
@@ -20282,7 +20282,7 @@
         <v>1533</v>
       </c>
       <c r="E345">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F345" t="s">
         <v>1594</v>
@@ -20317,7 +20317,7 @@
         <v>1533</v>
       </c>
       <c r="E346">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F346" t="s">
         <v>1594</v>
@@ -20352,7 +20352,7 @@
         <v>1534</v>
       </c>
       <c r="E347">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F347" t="s">
         <v>1594</v>
@@ -20387,7 +20387,7 @@
         <v>1534</v>
       </c>
       <c r="E348">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F348" t="s">
         <v>1594</v>
@@ -20422,7 +20422,7 @@
         <v>1534</v>
       </c>
       <c r="E349">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F349" t="s">
         <v>1594</v>
@@ -20457,7 +20457,7 @@
         <v>1534</v>
       </c>
       <c r="E350">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F350" t="s">
         <v>1594</v>
@@ -20492,7 +20492,7 @@
         <v>1534</v>
       </c>
       <c r="E351">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F351" t="s">
         <v>1594</v>
@@ -20527,7 +20527,7 @@
         <v>1534</v>
       </c>
       <c r="E352">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F352" t="s">
         <v>1594</v>
@@ -20562,7 +20562,7 @@
         <v>1534</v>
       </c>
       <c r="E353">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F353" t="s">
         <v>1594</v>
@@ -20597,7 +20597,7 @@
         <v>1534</v>
       </c>
       <c r="E354">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F354" t="s">
         <v>1594</v>
@@ -20632,7 +20632,7 @@
         <v>1535</v>
       </c>
       <c r="E355">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F355" t="s">
         <v>1594</v>
@@ -20667,7 +20667,7 @@
         <v>1535</v>
       </c>
       <c r="E356">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F356" t="s">
         <v>1594</v>
@@ -20702,7 +20702,7 @@
         <v>1535</v>
       </c>
       <c r="E357">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F357" t="s">
         <v>1594</v>
@@ -20737,7 +20737,7 @@
         <v>1536</v>
       </c>
       <c r="E358">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F358" t="s">
         <v>1594</v>
@@ -20772,7 +20772,7 @@
         <v>1536</v>
       </c>
       <c r="E359">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F359" t="s">
         <v>1594</v>
@@ -20807,7 +20807,7 @@
         <v>1537</v>
       </c>
       <c r="E360">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F360" t="s">
         <v>1594</v>
@@ -20842,7 +20842,7 @@
         <v>1538</v>
       </c>
       <c r="E361">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F361" t="s">
         <v>1596</v>
@@ -20877,7 +20877,7 @@
         <v>1538</v>
       </c>
       <c r="E362">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F362" t="s">
         <v>1594</v>
@@ -20912,7 +20912,7 @@
         <v>1538</v>
       </c>
       <c r="E363">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F363" t="s">
         <v>1594</v>
@@ -20947,7 +20947,7 @@
         <v>1538</v>
       </c>
       <c r="E364">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F364" t="s">
         <v>1594</v>
@@ -20982,7 +20982,7 @@
         <v>1538</v>
       </c>
       <c r="E365">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F365" t="s">
         <v>1594</v>
@@ -21017,7 +21017,7 @@
         <v>1538</v>
       </c>
       <c r="E366">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F366" t="s">
         <v>1594</v>
@@ -21052,7 +21052,7 @@
         <v>1539</v>
       </c>
       <c r="E367">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F367" t="s">
         <v>1594</v>
@@ -21087,7 +21087,7 @@
         <v>1539</v>
       </c>
       <c r="E368">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F368" t="s">
         <v>1594</v>
@@ -21122,7 +21122,7 @@
         <v>1540</v>
       </c>
       <c r="E369">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F369" t="s">
         <v>1594</v>
@@ -21157,7 +21157,7 @@
         <v>1540</v>
       </c>
       <c r="E370">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F370" t="s">
         <v>1594</v>
@@ -21192,7 +21192,7 @@
         <v>1540</v>
       </c>
       <c r="E371">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F371" t="s">
         <v>1594</v>
@@ -21227,7 +21227,7 @@
         <v>1541</v>
       </c>
       <c r="E372">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F372" t="s">
         <v>1594</v>
@@ -21262,7 +21262,7 @@
         <v>1542</v>
       </c>
       <c r="E373">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F373" t="s">
         <v>1594</v>
@@ -21297,7 +21297,7 @@
         <v>1543</v>
       </c>
       <c r="E374">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F374" t="s">
         <v>1594</v>
@@ -21332,7 +21332,7 @@
         <v>1543</v>
       </c>
       <c r="E375">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F375" t="s">
         <v>1594</v>
@@ -21367,7 +21367,7 @@
         <v>1544</v>
       </c>
       <c r="E376">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F376" t="s">
         <v>1594</v>
@@ -21402,7 +21402,7 @@
         <v>1544</v>
       </c>
       <c r="E377">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F377" t="s">
         <v>1594</v>
@@ -21437,7 +21437,7 @@
         <v>1544</v>
       </c>
       <c r="E378">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F378" t="s">
         <v>1594</v>
@@ -21472,7 +21472,7 @@
         <v>1545</v>
       </c>
       <c r="E379">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F379" t="s">
         <v>1594</v>
@@ -21507,7 +21507,7 @@
         <v>1545</v>
       </c>
       <c r="E380">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F380" t="s">
         <v>1594</v>
@@ -21542,7 +21542,7 @@
         <v>1545</v>
       </c>
       <c r="E381">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F381" t="s">
         <v>1594</v>
@@ -21577,7 +21577,7 @@
         <v>1545</v>
       </c>
       <c r="E382">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F382" t="s">
         <v>1594</v>
@@ -21612,7 +21612,7 @@
         <v>1545</v>
       </c>
       <c r="E383">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F383" t="s">
         <v>1594</v>
@@ -21647,7 +21647,7 @@
         <v>1545</v>
       </c>
       <c r="E384">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F384" t="s">
         <v>1594</v>
@@ -21682,7 +21682,7 @@
         <v>1545</v>
       </c>
       <c r="E385">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F385" t="s">
         <v>1594</v>
@@ -21717,7 +21717,7 @@
         <v>1545</v>
       </c>
       <c r="E386">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F386" t="s">
         <v>1594</v>
@@ -21752,7 +21752,7 @@
         <v>1545</v>
       </c>
       <c r="E387">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F387" t="s">
         <v>1594</v>
@@ -21787,7 +21787,7 @@
         <v>1545</v>
       </c>
       <c r="E388">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F388" t="s">
         <v>1594</v>
@@ -21822,7 +21822,7 @@
         <v>1546</v>
       </c>
       <c r="E389">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F389" t="s">
         <v>1594</v>
@@ -21857,7 +21857,7 @@
         <v>1546</v>
       </c>
       <c r="E390">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F390" t="s">
         <v>1594</v>
@@ -21892,7 +21892,7 @@
         <v>1546</v>
       </c>
       <c r="E391">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F391" t="s">
         <v>1594</v>
@@ -21927,7 +21927,7 @@
         <v>1546</v>
       </c>
       <c r="E392">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F392" t="s">
         <v>1594</v>
@@ -21962,7 +21962,7 @@
         <v>1547</v>
       </c>
       <c r="E393">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F393" t="s">
         <v>1597</v>
@@ -21997,7 +21997,7 @@
         <v>1547</v>
       </c>
       <c r="E394">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F394" t="s">
         <v>1594</v>
@@ -22032,7 +22032,7 @@
         <v>1548</v>
       </c>
       <c r="E395">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F395" t="s">
         <v>1594</v>
@@ -22067,7 +22067,7 @@
         <v>1548</v>
       </c>
       <c r="E396">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F396" t="s">
         <v>1594</v>
@@ -22102,7 +22102,7 @@
         <v>1548</v>
       </c>
       <c r="E397">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F397" t="s">
         <v>1594</v>
@@ -22137,7 +22137,7 @@
         <v>1548</v>
       </c>
       <c r="E398">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F398" t="s">
         <v>1594</v>
@@ -22172,7 +22172,7 @@
         <v>1548</v>
       </c>
       <c r="E399">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F399" t="s">
         <v>1598</v>
@@ -22210,7 +22210,7 @@
         <v>1548</v>
       </c>
       <c r="E400">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F400" t="s">
         <v>1594</v>
@@ -22245,7 +22245,7 @@
         <v>1548</v>
       </c>
       <c r="E401">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F401" t="s">
         <v>1594</v>
@@ -22280,7 +22280,7 @@
         <v>1549</v>
       </c>
       <c r="E402">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F402" t="s">
         <v>1594</v>
@@ -22315,7 +22315,7 @@
         <v>1549</v>
       </c>
       <c r="E403">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F403" t="s">
         <v>1594</v>
@@ -22350,7 +22350,7 @@
         <v>1549</v>
       </c>
       <c r="E404">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F404" t="s">
         <v>1594</v>
@@ -22385,7 +22385,7 @@
         <v>1549</v>
       </c>
       <c r="E405">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F405" t="s">
         <v>1594</v>
@@ -22423,7 +22423,7 @@
         <v>1549</v>
       </c>
       <c r="E406">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F406" t="s">
         <v>1594</v>
@@ -22458,7 +22458,7 @@
         <v>1549</v>
       </c>
       <c r="E407">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F407" t="s">
         <v>1594</v>
@@ -22493,7 +22493,7 @@
         <v>1549</v>
       </c>
       <c r="E408">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F408" t="s">
         <v>1594</v>
@@ -22528,7 +22528,7 @@
         <v>1549</v>
       </c>
       <c r="E409">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F409" t="s">
         <v>1594</v>
@@ -22563,7 +22563,7 @@
         <v>1549</v>
       </c>
       <c r="E410">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F410" t="s">
         <v>1594</v>
@@ -22598,7 +22598,7 @@
         <v>1550</v>
       </c>
       <c r="E411">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F411" t="s">
         <v>1595</v>
@@ -22633,7 +22633,7 @@
         <v>1551</v>
       </c>
       <c r="E412">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F412" t="s">
         <v>1596</v>
@@ -22668,7 +22668,7 @@
         <v>1551</v>
       </c>
       <c r="E413">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F413" t="s">
         <v>1598</v>
@@ -22703,7 +22703,7 @@
         <v>1552</v>
       </c>
       <c r="E414">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F414" t="s">
         <v>1594</v>
@@ -22738,7 +22738,7 @@
         <v>1553</v>
       </c>
       <c r="E415">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F415" t="s">
         <v>1594</v>
@@ -22773,7 +22773,7 @@
         <v>1553</v>
       </c>
       <c r="E416">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F416" t="s">
         <v>1594</v>
@@ -22808,7 +22808,7 @@
         <v>1554</v>
       </c>
       <c r="E417">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F417" t="s">
         <v>1594</v>
@@ -22843,7 +22843,7 @@
         <v>1555</v>
       </c>
       <c r="E418">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F418" t="s">
         <v>1597</v>
@@ -22878,7 +22878,7 @@
         <v>1555</v>
       </c>
       <c r="E419">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F419" t="s">
         <v>1594</v>
@@ -22913,7 +22913,7 @@
         <v>1555</v>
       </c>
       <c r="E420">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F420" t="s">
         <v>1594</v>
@@ -22948,7 +22948,7 @@
         <v>1555</v>
       </c>
       <c r="E421">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F421" t="s">
         <v>1594</v>
@@ -22983,7 +22983,7 @@
         <v>1555</v>
       </c>
       <c r="E422">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F422" t="s">
         <v>1594</v>
@@ -23018,7 +23018,7 @@
         <v>1555</v>
       </c>
       <c r="E423">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F423" t="s">
         <v>1594</v>
@@ -23053,7 +23053,7 @@
         <v>1556</v>
       </c>
       <c r="E424">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F424" t="s">
         <v>1594</v>
@@ -23088,7 +23088,7 @@
         <v>1556</v>
       </c>
       <c r="E425">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F425" t="s">
         <v>1594</v>
@@ -23123,7 +23123,7 @@
         <v>1556</v>
       </c>
       <c r="E426">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F426" t="s">
         <v>1594</v>
@@ -23158,7 +23158,7 @@
         <v>1556</v>
       </c>
       <c r="E427">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F427" t="s">
         <v>1594</v>
@@ -23193,7 +23193,7 @@
         <v>1557</v>
       </c>
       <c r="E428">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F428" t="s">
         <v>1594</v>
@@ -23228,7 +23228,7 @@
         <v>1557</v>
       </c>
       <c r="E429">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F429" t="s">
         <v>1594</v>
@@ -23263,7 +23263,7 @@
         <v>1557</v>
       </c>
       <c r="E430">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F430" t="s">
         <v>1594</v>
@@ -23301,7 +23301,7 @@
         <v>1557</v>
       </c>
       <c r="E431">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F431" t="s">
         <v>1594</v>
@@ -23336,7 +23336,7 @@
         <v>1558</v>
       </c>
       <c r="E432">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F432" t="s">
         <v>1594</v>
@@ -23371,7 +23371,7 @@
         <v>1558</v>
       </c>
       <c r="E433">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F433" t="s">
         <v>1594</v>
@@ -23406,7 +23406,7 @@
         <v>1558</v>
       </c>
       <c r="E434">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F434" t="s">
         <v>1594</v>
@@ -23441,7 +23441,7 @@
         <v>1558</v>
       </c>
       <c r="E435">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F435" t="s">
         <v>1594</v>
@@ -23476,7 +23476,7 @@
         <v>1558</v>
       </c>
       <c r="E436">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F436" t="s">
         <v>1594</v>
@@ -23511,7 +23511,7 @@
         <v>1559</v>
       </c>
       <c r="E437">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F437" t="s">
         <v>1594</v>
@@ -23546,7 +23546,7 @@
         <v>1559</v>
       </c>
       <c r="E438">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F438" t="s">
         <v>1594</v>
@@ -23581,7 +23581,7 @@
         <v>1560</v>
       </c>
       <c r="E439">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F439" t="s">
         <v>1594</v>
@@ -23616,7 +23616,7 @@
         <v>1560</v>
       </c>
       <c r="E440">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F440" t="s">
         <v>1594</v>
@@ -23651,7 +23651,7 @@
         <v>1560</v>
       </c>
       <c r="E441">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F441" t="s">
         <v>1594</v>
@@ -23686,7 +23686,7 @@
         <v>1560</v>
       </c>
       <c r="E442">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F442" t="s">
         <v>1594</v>
@@ -23721,7 +23721,7 @@
         <v>1560</v>
       </c>
       <c r="E443">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F443" t="s">
         <v>1594</v>
@@ -23756,7 +23756,7 @@
         <v>1560</v>
       </c>
       <c r="E444">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F444" t="s">
         <v>1594</v>
@@ -23791,7 +23791,7 @@
         <v>1560</v>
       </c>
       <c r="E445">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F445" t="s">
         <v>1594</v>
@@ -23826,7 +23826,7 @@
         <v>1560</v>
       </c>
       <c r="E446">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F446" t="s">
         <v>1594</v>
@@ -23861,7 +23861,7 @@
         <v>1560</v>
       </c>
       <c r="E447">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F447" t="s">
         <v>1594</v>
@@ -23896,7 +23896,7 @@
         <v>1560</v>
       </c>
       <c r="E448">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F448" t="s">
         <v>1594</v>
@@ -23931,7 +23931,7 @@
         <v>1560</v>
       </c>
       <c r="E449">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F449" t="s">
         <v>1594</v>
@@ -23966,7 +23966,7 @@
         <v>1561</v>
       </c>
       <c r="E450">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F450" t="s">
         <v>1594</v>
@@ -24001,7 +24001,7 @@
         <v>1561</v>
       </c>
       <c r="E451">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F451" t="s">
         <v>1594</v>
@@ -24036,7 +24036,7 @@
         <v>1561</v>
       </c>
       <c r="E452">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F452" t="s">
         <v>1595</v>
@@ -24071,7 +24071,7 @@
         <v>1562</v>
       </c>
       <c r="E453">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F453" t="s">
         <v>1594</v>
@@ -24106,7 +24106,7 @@
         <v>1562</v>
       </c>
       <c r="E454">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F454" t="s">
         <v>1594</v>
@@ -24141,7 +24141,7 @@
         <v>1562</v>
       </c>
       <c r="E455">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F455" t="s">
         <v>1594</v>
@@ -24176,7 +24176,7 @@
         <v>1562</v>
       </c>
       <c r="E456">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F456" t="s">
         <v>1594</v>
@@ -24211,7 +24211,7 @@
         <v>1562</v>
       </c>
       <c r="E457">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F457" t="s">
         <v>1594</v>
@@ -24246,7 +24246,7 @@
         <v>1562</v>
       </c>
       <c r="E458">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F458" t="s">
         <v>1594</v>
@@ -24281,7 +24281,7 @@
         <v>1562</v>
       </c>
       <c r="E459">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F459" t="s">
         <v>1597</v>
@@ -24316,7 +24316,7 @@
         <v>1563</v>
       </c>
       <c r="E460">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F460" t="s">
         <v>1594</v>
@@ -24351,7 +24351,7 @@
         <v>1563</v>
       </c>
       <c r="E461">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F461" t="s">
         <v>1594</v>
@@ -24386,7 +24386,7 @@
         <v>1563</v>
       </c>
       <c r="E462">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F462" t="s">
         <v>1594</v>
@@ -24421,7 +24421,7 @@
         <v>1563</v>
       </c>
       <c r="E463">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F463" t="s">
         <v>1594</v>
@@ -24456,7 +24456,7 @@
         <v>1564</v>
       </c>
       <c r="E464">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F464" t="s">
         <v>1594</v>
@@ -24491,7 +24491,7 @@
         <v>1564</v>
       </c>
       <c r="E465">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F465" t="s">
         <v>1597</v>
@@ -24526,7 +24526,7 @@
         <v>1564</v>
       </c>
       <c r="E466">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F466" t="s">
         <v>1594</v>
@@ -24561,7 +24561,7 @@
         <v>1564</v>
       </c>
       <c r="E467">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F467" t="s">
         <v>1594</v>
@@ -24596,7 +24596,7 @@
         <v>1564</v>
       </c>
       <c r="E468">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F468" t="s">
         <v>1594</v>
@@ -24631,7 +24631,7 @@
         <v>1564</v>
       </c>
       <c r="E469">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F469" t="s">
         <v>1596</v>
@@ -24669,7 +24669,7 @@
         <v>1564</v>
       </c>
       <c r="E470">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F470" t="s">
         <v>1594</v>
@@ -24704,7 +24704,7 @@
         <v>1564</v>
       </c>
       <c r="E471">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F471" t="s">
         <v>1598</v>
@@ -24739,7 +24739,7 @@
         <v>1564</v>
       </c>
       <c r="E472">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F472" t="s">
         <v>1594</v>
@@ -24774,7 +24774,7 @@
         <v>1564</v>
       </c>
       <c r="E473">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F473" t="s">
         <v>1594</v>
@@ -24809,7 +24809,7 @@
         <v>1565</v>
       </c>
       <c r="E474">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F474" t="s">
         <v>1594</v>
@@ -24844,7 +24844,7 @@
         <v>1565</v>
       </c>
       <c r="E475">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F475" t="s">
         <v>1594</v>
@@ -24879,7 +24879,7 @@
         <v>1565</v>
       </c>
       <c r="E476">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F476" t="s">
         <v>1594</v>
@@ -24914,7 +24914,7 @@
         <v>1565</v>
       </c>
       <c r="E477">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F477" t="s">
         <v>1594</v>
@@ -24949,7 +24949,7 @@
         <v>1565</v>
       </c>
       <c r="E478">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F478" t="s">
         <v>1594</v>
@@ -24984,7 +24984,7 @@
         <v>1565</v>
       </c>
       <c r="E479">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F479" t="s">
         <v>1594</v>
@@ -25019,7 +25019,7 @@
         <v>1565</v>
       </c>
       <c r="E480">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F480" t="s">
         <v>1596</v>
@@ -25054,7 +25054,7 @@
         <v>1565</v>
       </c>
       <c r="E481">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F481" t="s">
         <v>1594</v>
@@ -25089,7 +25089,7 @@
         <v>1565</v>
       </c>
       <c r="E482">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F482" t="s">
         <v>1594</v>
@@ -25124,7 +25124,7 @@
         <v>1566</v>
       </c>
       <c r="E483">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F483" t="s">
         <v>1594</v>
@@ -25159,7 +25159,7 @@
         <v>1566</v>
       </c>
       <c r="E484">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F484" t="s">
         <v>1594</v>
@@ -25194,7 +25194,7 @@
         <v>1566</v>
       </c>
       <c r="E485">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F485" t="s">
         <v>1594</v>
@@ -25229,7 +25229,7 @@
         <v>1566</v>
       </c>
       <c r="E486">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F486" t="s">
         <v>1594</v>
@@ -25264,7 +25264,7 @@
         <v>1566</v>
       </c>
       <c r="E487">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F487" t="s">
         <v>1594</v>
@@ -25299,7 +25299,7 @@
         <v>1567</v>
       </c>
       <c r="E488">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F488" t="s">
         <v>1594</v>
@@ -25334,7 +25334,7 @@
         <v>1567</v>
       </c>
       <c r="E489">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F489" t="s">
         <v>1594</v>
@@ -25369,7 +25369,7 @@
         <v>1567</v>
       </c>
       <c r="E490">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F490" t="s">
         <v>1594</v>
@@ -25404,7 +25404,7 @@
         <v>1567</v>
       </c>
       <c r="E491">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F491" t="s">
         <v>1594</v>
@@ -25439,7 +25439,7 @@
         <v>1567</v>
       </c>
       <c r="E492">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F492" t="s">
         <v>1594</v>
@@ -25477,7 +25477,7 @@
         <v>1568</v>
       </c>
       <c r="E493">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F493" t="s">
         <v>1594</v>
@@ -25512,7 +25512,7 @@
         <v>1568</v>
       </c>
       <c r="E494">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F494" t="s">
         <v>1594</v>
@@ -25547,7 +25547,7 @@
         <v>1568</v>
       </c>
       <c r="E495">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F495" t="s">
         <v>1594</v>
@@ -25582,7 +25582,7 @@
         <v>1568</v>
       </c>
       <c r="E496">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F496" t="s">
         <v>1594</v>
@@ -25617,7 +25617,7 @@
         <v>1568</v>
       </c>
       <c r="E497">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F497" t="s">
         <v>1594</v>
@@ -25652,7 +25652,7 @@
         <v>1568</v>
       </c>
       <c r="E498">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F498" t="s">
         <v>1594</v>
@@ -25687,7 +25687,7 @@
         <v>1568</v>
       </c>
       <c r="E499">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F499" t="s">
         <v>1594</v>
@@ -25722,7 +25722,7 @@
         <v>1569</v>
       </c>
       <c r="E500">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F500" t="s">
         <v>1594</v>
@@ -25757,7 +25757,7 @@
         <v>1569</v>
       </c>
       <c r="E501">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F501" t="s">
         <v>1594</v>
@@ -25792,7 +25792,7 @@
         <v>1569</v>
       </c>
       <c r="E502">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F502" t="s">
         <v>1594</v>
@@ -25827,7 +25827,7 @@
         <v>1570</v>
       </c>
       <c r="E503">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F503" t="s">
         <v>1594</v>
@@ -25862,7 +25862,7 @@
         <v>1571</v>
       </c>
       <c r="E504">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F504" t="s">
         <v>1594</v>
@@ -25897,7 +25897,7 @@
         <v>1571</v>
       </c>
       <c r="E505">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F505" t="s">
         <v>1594</v>
@@ -25932,7 +25932,7 @@
         <v>1571</v>
       </c>
       <c r="E506">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F506" t="s">
         <v>1596</v>
@@ -25970,7 +25970,7 @@
         <v>1571</v>
       </c>
       <c r="E507">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F507" t="s">
         <v>1594</v>
@@ -26005,7 +26005,7 @@
         <v>1571</v>
       </c>
       <c r="E508">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F508" t="s">
         <v>1594</v>
@@ -26040,7 +26040,7 @@
         <v>1572</v>
       </c>
       <c r="E509">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F509" t="s">
         <v>1594</v>
@@ -26075,7 +26075,7 @@
         <v>1572</v>
       </c>
       <c r="E510">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F510" t="s">
         <v>1594</v>
@@ -26110,7 +26110,7 @@
         <v>1572</v>
       </c>
       <c r="E511">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F511" t="s">
         <v>1594</v>
@@ -26145,7 +26145,7 @@
         <v>1572</v>
       </c>
       <c r="E512">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F512" t="s">
         <v>1594</v>
@@ -26180,7 +26180,7 @@
         <v>1572</v>
       </c>
       <c r="E513">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F513" t="s">
         <v>1594</v>
@@ -26215,7 +26215,7 @@
         <v>1573</v>
       </c>
       <c r="E514">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F514" t="s">
         <v>1594</v>
@@ -26250,7 +26250,7 @@
         <v>1573</v>
       </c>
       <c r="E515">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F515" t="s">
         <v>1594</v>
@@ -26285,7 +26285,7 @@
         <v>1573</v>
       </c>
       <c r="E516">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F516" t="s">
         <v>1594</v>
@@ -26320,7 +26320,7 @@
         <v>1573</v>
       </c>
       <c r="E517">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F517" t="s">
         <v>1594</v>
@@ -26355,7 +26355,7 @@
         <v>1573</v>
       </c>
       <c r="E518">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F518" t="s">
         <v>1594</v>
@@ -26390,7 +26390,7 @@
         <v>1573</v>
       </c>
       <c r="E519">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F519" t="s">
         <v>1594</v>
@@ -26425,7 +26425,7 @@
         <v>1573</v>
       </c>
       <c r="E520">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F520" t="s">
         <v>1594</v>
@@ -26460,7 +26460,7 @@
         <v>1573</v>
       </c>
       <c r="E521">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F521" t="s">
         <v>1594</v>
@@ -26495,7 +26495,7 @@
         <v>1574</v>
       </c>
       <c r="E522">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F522" t="s">
         <v>1594</v>
@@ -26530,7 +26530,7 @@
         <v>1574</v>
       </c>
       <c r="E523">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F523" t="s">
         <v>1594</v>
@@ -26565,7 +26565,7 @@
         <v>1575</v>
       </c>
       <c r="E524">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F524" t="s">
         <v>1594</v>
@@ -26600,7 +26600,7 @@
         <v>1575</v>
       </c>
       <c r="E525">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F525" t="s">
         <v>1594</v>
@@ -26635,7 +26635,7 @@
         <v>1575</v>
       </c>
       <c r="E526">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F526" t="s">
         <v>1594</v>
@@ -26670,7 +26670,7 @@
         <v>1575</v>
       </c>
       <c r="E527">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F527" t="s">
         <v>1598</v>
@@ -26708,7 +26708,7 @@
         <v>1575</v>
       </c>
       <c r="E528">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F528" t="s">
         <v>1594</v>
@@ -26743,7 +26743,7 @@
         <v>1575</v>
       </c>
       <c r="E529">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F529" t="s">
         <v>1598</v>
@@ -26778,7 +26778,7 @@
         <v>1576</v>
       </c>
       <c r="E530">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F530" t="s">
         <v>1594</v>
@@ -26813,7 +26813,7 @@
         <v>1577</v>
       </c>
       <c r="E531">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F531" t="s">
         <v>1594</v>
@@ -26848,7 +26848,7 @@
         <v>1577</v>
       </c>
       <c r="E532">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F532" t="s">
         <v>1594</v>
@@ -26883,7 +26883,7 @@
         <v>1577</v>
       </c>
       <c r="E533">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F533" t="s">
         <v>1594</v>
@@ -26918,7 +26918,7 @@
         <v>1577</v>
       </c>
       <c r="E534">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F534" t="s">
         <v>1594</v>
@@ -26953,7 +26953,7 @@
         <v>1578</v>
       </c>
       <c r="E535">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F535" t="s">
         <v>1594</v>
@@ -26988,7 +26988,7 @@
         <v>1578</v>
       </c>
       <c r="E536">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F536" t="s">
         <v>1598</v>
@@ -27023,7 +27023,7 @@
         <v>1578</v>
       </c>
       <c r="E537">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F537" t="s">
         <v>1594</v>
@@ -27058,7 +27058,7 @@
         <v>1578</v>
       </c>
       <c r="E538">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F538" t="s">
         <v>1594</v>
@@ -27093,7 +27093,7 @@
         <v>1578</v>
       </c>
       <c r="E539">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F539" t="s">
         <v>1594</v>
@@ -27128,7 +27128,7 @@
         <v>1579</v>
       </c>
       <c r="E540">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F540" t="s">
         <v>1594</v>
@@ -27163,7 +27163,7 @@
         <v>1579</v>
       </c>
       <c r="E541">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F541" t="s">
         <v>1598</v>
@@ -27198,7 +27198,7 @@
         <v>1579</v>
       </c>
       <c r="E542">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F542" t="s">
         <v>1596</v>
@@ -27233,7 +27233,7 @@
         <v>1579</v>
       </c>
       <c r="E543">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F543" t="s">
         <v>1594</v>
@@ -27268,7 +27268,7 @@
         <v>1579</v>
       </c>
       <c r="E544">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F544" t="s">
         <v>1594</v>
@@ -27303,7 +27303,7 @@
         <v>1580</v>
       </c>
       <c r="E545">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F545" t="s">
         <v>1594</v>
@@ -27338,7 +27338,7 @@
         <v>1580</v>
       </c>
       <c r="E546">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F546" t="s">
         <v>1594</v>
@@ -27373,7 +27373,7 @@
         <v>1580</v>
       </c>
       <c r="E547">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F547" t="s">
         <v>1594</v>
@@ -27408,7 +27408,7 @@
         <v>1580</v>
       </c>
       <c r="E548">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F548" t="s">
         <v>1594</v>
@@ -27443,7 +27443,7 @@
         <v>1580</v>
       </c>
       <c r="E549">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F549" t="s">
         <v>1594</v>
@@ -27478,7 +27478,7 @@
         <v>1580</v>
       </c>
       <c r="E550">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F550" t="s">
         <v>1594</v>
@@ -27513,7 +27513,7 @@
         <v>1581</v>
       </c>
       <c r="E551">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F551" t="s">
         <v>1594</v>
@@ -27548,7 +27548,7 @@
         <v>1581</v>
       </c>
       <c r="E552">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F552" t="s">
         <v>1594</v>
@@ -27583,7 +27583,7 @@
         <v>1581</v>
       </c>
       <c r="E553">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F553" t="s">
         <v>1594</v>
@@ -27618,7 +27618,7 @@
         <v>1581</v>
       </c>
       <c r="E554">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F554" t="s">
         <v>1594</v>
@@ -27653,7 +27653,7 @@
         <v>1581</v>
       </c>
       <c r="E555">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F555" t="s">
         <v>1594</v>
@@ -27688,7 +27688,7 @@
         <v>1581</v>
       </c>
       <c r="E556">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F556" t="s">
         <v>1594</v>
@@ -27723,7 +27723,7 @@
         <v>1581</v>
       </c>
       <c r="E557">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F557" t="s">
         <v>1594</v>
@@ -27758,7 +27758,7 @@
         <v>1581</v>
       </c>
       <c r="E558">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F558" t="s">
         <v>1594</v>
@@ -27793,7 +27793,7 @@
         <v>1581</v>
       </c>
       <c r="E559">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F559" t="s">
         <v>1594</v>
@@ -27828,7 +27828,7 @@
         <v>1581</v>
       </c>
       <c r="E560">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F560" t="s">
         <v>1594</v>
@@ -27863,7 +27863,7 @@
         <v>1581</v>
       </c>
       <c r="E561">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F561" t="s">
         <v>1594</v>
@@ -27898,7 +27898,7 @@
         <v>1581</v>
       </c>
       <c r="E562">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F562" t="s">
         <v>1594</v>
@@ -27933,7 +27933,7 @@
         <v>1581</v>
       </c>
       <c r="E563">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F563" t="s">
         <v>1594</v>
@@ -27968,7 +27968,7 @@
         <v>1581</v>
       </c>
       <c r="E564">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F564" t="s">
         <v>1594</v>
@@ -28003,7 +28003,7 @@
         <v>1581</v>
       </c>
       <c r="E565">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F565" t="s">
         <v>1594</v>
@@ -28038,7 +28038,7 @@
         <v>1581</v>
       </c>
       <c r="E566">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F566" t="s">
         <v>1594</v>
@@ -28073,7 +28073,7 @@
         <v>1581</v>
       </c>
       <c r="E567">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F567" t="s">
         <v>1594</v>
@@ -28108,7 +28108,7 @@
         <v>1581</v>
       </c>
       <c r="E568">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F568" t="s">
         <v>1594</v>
@@ -28143,7 +28143,7 @@
         <v>1581</v>
       </c>
       <c r="E569">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F569" t="s">
         <v>1594</v>
@@ -28178,7 +28178,7 @@
         <v>1581</v>
       </c>
       <c r="E570">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F570" t="s">
         <v>1594</v>
@@ -28213,7 +28213,7 @@
         <v>1581</v>
       </c>
       <c r="E571">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F571" t="s">
         <v>1594</v>
@@ -28248,7 +28248,7 @@
         <v>1581</v>
       </c>
       <c r="E572">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F572" t="s">
         <v>1594</v>
@@ -28283,7 +28283,7 @@
         <v>1581</v>
       </c>
       <c r="E573">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F573" t="s">
         <v>1594</v>
@@ -28318,7 +28318,7 @@
         <v>1581</v>
       </c>
       <c r="E574">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F574" t="s">
         <v>1594</v>
@@ -28353,7 +28353,7 @@
         <v>1581</v>
       </c>
       <c r="E575">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F575" t="s">
         <v>1594</v>
@@ -28388,7 +28388,7 @@
         <v>1581</v>
       </c>
       <c r="E576">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F576" t="s">
         <v>1594</v>
@@ -28423,7 +28423,7 @@
         <v>1581</v>
       </c>
       <c r="E577">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F577" t="s">
         <v>1596</v>
@@ -28461,7 +28461,7 @@
         <v>1582</v>
       </c>
       <c r="E578">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F578" t="s">
         <v>1594</v>
@@ -28496,7 +28496,7 @@
         <v>1582</v>
       </c>
       <c r="E579">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F579" t="s">
         <v>1594</v>
@@ -28531,7 +28531,7 @@
         <v>1582</v>
       </c>
       <c r="E580">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F580" t="s">
         <v>1596</v>
@@ -28566,7 +28566,7 @@
         <v>1582</v>
       </c>
       <c r="E581">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F581" t="s">
         <v>1594</v>
@@ -28601,7 +28601,7 @@
         <v>1582</v>
       </c>
       <c r="E582">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F582" t="s">
         <v>1594</v>
@@ -28636,7 +28636,7 @@
         <v>1582</v>
       </c>
       <c r="E583">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F583" t="s">
         <v>1594</v>
@@ -28671,7 +28671,7 @@
         <v>1582</v>
       </c>
       <c r="E584">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F584" t="s">
         <v>1594</v>
@@ -28706,7 +28706,7 @@
         <v>1582</v>
       </c>
       <c r="E585">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F585" t="s">
         <v>1594</v>
@@ -28741,7 +28741,7 @@
         <v>1583</v>
       </c>
       <c r="E586">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F586" t="s">
         <v>1594</v>
@@ -28776,7 +28776,7 @@
         <v>1583</v>
       </c>
       <c r="E587">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F587" t="s">
         <v>1594</v>
@@ -28811,7 +28811,7 @@
         <v>1584</v>
       </c>
       <c r="E588">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F588" t="s">
         <v>1594</v>
@@ -28846,7 +28846,7 @@
         <v>1584</v>
       </c>
       <c r="E589">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F589" t="s">
         <v>1596</v>
@@ -28884,7 +28884,7 @@
         <v>1584</v>
       </c>
       <c r="E590">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F590" t="s">
         <v>1596</v>
@@ -28922,7 +28922,7 @@
         <v>1585</v>
       </c>
       <c r="E591">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F591" t="s">
         <v>1596</v>
@@ -28960,7 +28960,7 @@
         <v>1585</v>
       </c>
       <c r="E592">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F592" t="s">
         <v>1594</v>
@@ -28995,7 +28995,7 @@
         <v>1585</v>
       </c>
       <c r="E593">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F593" t="s">
         <v>1594</v>
@@ -29030,7 +29030,7 @@
         <v>1585</v>
       </c>
       <c r="E594">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F594" t="s">
         <v>1596</v>
@@ -29068,7 +29068,7 @@
         <v>1585</v>
       </c>
       <c r="E595">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F595" t="s">
         <v>1594</v>
@@ -29103,7 +29103,7 @@
         <v>1585</v>
       </c>
       <c r="E596">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F596" t="s">
         <v>1594</v>
@@ -29138,7 +29138,7 @@
         <v>1585</v>
       </c>
       <c r="E597">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F597" t="s">
         <v>1596</v>
@@ -29176,7 +29176,7 @@
         <v>1585</v>
       </c>
       <c r="E598">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F598" t="s">
         <v>1594</v>
@@ -29211,7 +29211,7 @@
         <v>1585</v>
       </c>
       <c r="E599">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F599" t="s">
         <v>1594</v>
@@ -29249,7 +29249,7 @@
         <v>1585</v>
       </c>
       <c r="E600">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F600" t="s">
         <v>1596</v>
@@ -29284,7 +29284,7 @@
         <v>1585</v>
       </c>
       <c r="E601">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F601" t="s">
         <v>1594</v>
@@ -29319,7 +29319,7 @@
         <v>1585</v>
       </c>
       <c r="E602">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F602" t="s">
         <v>1594</v>
@@ -29354,7 +29354,7 @@
         <v>1586</v>
       </c>
       <c r="E603">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F603" t="s">
         <v>1594</v>
@@ -29392,7 +29392,7 @@
         <v>1586</v>
       </c>
       <c r="E604">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F604" t="s">
         <v>1598</v>
@@ -29427,7 +29427,7 @@
         <v>1586</v>
       </c>
       <c r="E605">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F605" t="s">
         <v>1596</v>
@@ -29462,7 +29462,7 @@
         <v>1586</v>
       </c>
       <c r="E606">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F606" t="s">
         <v>1594</v>
@@ -29497,7 +29497,7 @@
         <v>1586</v>
       </c>
       <c r="E607">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F607" t="s">
         <v>1596</v>
@@ -29535,7 +29535,7 @@
         <v>1586</v>
       </c>
       <c r="E608">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F608" t="s">
         <v>1594</v>
@@ -29570,7 +29570,7 @@
         <v>1586</v>
       </c>
       <c r="E609">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F609" t="s">
         <v>1594</v>
@@ -29605,7 +29605,7 @@
         <v>1586</v>
       </c>
       <c r="E610">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F610" t="s">
         <v>1594</v>
@@ -29640,7 +29640,7 @@
         <v>1586</v>
       </c>
       <c r="E611">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F611" t="s">
         <v>1594</v>
@@ -29675,7 +29675,7 @@
         <v>1586</v>
       </c>
       <c r="E612">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F612" t="s">
         <v>1594</v>
@@ -29710,7 +29710,7 @@
         <v>1587</v>
       </c>
       <c r="E613">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F613" t="s">
         <v>1594</v>
@@ -29748,7 +29748,7 @@
         <v>1587</v>
       </c>
       <c r="E614">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F614" t="s">
         <v>1594</v>
@@ -29783,7 +29783,7 @@
         <v>1588</v>
       </c>
       <c r="E615">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F615" t="s">
         <v>1594</v>
@@ -29818,7 +29818,7 @@
         <v>1588</v>
       </c>
       <c r="E616">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F616" t="s">
         <v>1596</v>
@@ -29856,7 +29856,7 @@
         <v>1588</v>
       </c>
       <c r="E617">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F617" t="s">
         <v>1594</v>
@@ -29891,7 +29891,7 @@
         <v>1588</v>
       </c>
       <c r="E618">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F618" t="s">
         <v>1594</v>
@@ -29926,7 +29926,7 @@
         <v>1588</v>
       </c>
       <c r="E619">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F619" t="s">
         <v>1594</v>
@@ -29961,7 +29961,7 @@
         <v>1588</v>
       </c>
       <c r="E620">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F620" t="s">
         <v>1594</v>
@@ -29996,7 +29996,7 @@
         <v>1588</v>
       </c>
       <c r="E621">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F621" t="s">
         <v>1594</v>
@@ -30031,7 +30031,7 @@
         <v>1588</v>
       </c>
       <c r="E622">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F622" t="s">
         <v>1596</v>
@@ -30066,7 +30066,7 @@
         <v>1588</v>
       </c>
       <c r="E623">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F623" t="s">
         <v>1594</v>
@@ -30101,7 +30101,7 @@
         <v>1588</v>
       </c>
       <c r="E624">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F624" t="s">
         <v>1594</v>
@@ -30136,7 +30136,7 @@
         <v>1589</v>
       </c>
       <c r="E625">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F625" t="s">
         <v>1594</v>
@@ -30171,7 +30171,7 @@
         <v>1589</v>
       </c>
       <c r="E626">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F626" t="s">
         <v>1594</v>
@@ -30206,7 +30206,7 @@
         <v>1589</v>
       </c>
       <c r="E627">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F627" t="s">
         <v>1594</v>
@@ -30241,7 +30241,7 @@
         <v>1589</v>
       </c>
       <c r="E628">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F628" t="s">
         <v>1594</v>
@@ -30276,7 +30276,7 @@
         <v>1589</v>
       </c>
       <c r="E629">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F629" t="s">
         <v>1596</v>
@@ -30314,7 +30314,7 @@
         <v>1589</v>
       </c>
       <c r="E630">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F630" t="s">
         <v>1594</v>
@@ -30349,7 +30349,7 @@
         <v>1589</v>
       </c>
       <c r="E631">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F631" t="s">
         <v>1594</v>
@@ -30384,7 +30384,7 @@
         <v>1589</v>
       </c>
       <c r="E632">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F632" t="s">
         <v>1594</v>
@@ -30419,7 +30419,7 @@
         <v>1589</v>
       </c>
       <c r="E633">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F633" t="s">
         <v>1594</v>
@@ -30454,7 +30454,7 @@
         <v>1589</v>
       </c>
       <c r="E634">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F634" t="s">
         <v>1594</v>
@@ -30489,7 +30489,7 @@
         <v>1589</v>
       </c>
       <c r="E635">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F635" t="s">
         <v>1598</v>
@@ -30524,7 +30524,7 @@
         <v>1589</v>
       </c>
       <c r="E636">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F636" t="s">
         <v>1594</v>
@@ -30559,7 +30559,7 @@
         <v>1590</v>
       </c>
       <c r="E637">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F637" t="s">
         <v>1596</v>
@@ -30597,7 +30597,7 @@
         <v>1590</v>
       </c>
       <c r="E638">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F638" t="s">
         <v>1594</v>
@@ -30632,7 +30632,7 @@
         <v>1590</v>
       </c>
       <c r="E639">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F639" t="s">
         <v>1594</v>
@@ -30667,7 +30667,7 @@
         <v>1590</v>
       </c>
       <c r="E640">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F640" t="s">
         <v>1594</v>
@@ -30702,7 +30702,7 @@
         <v>1590</v>
       </c>
       <c r="E641">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F641" t="s">
         <v>1594</v>
@@ -30737,7 +30737,7 @@
         <v>1590</v>
       </c>
       <c r="E642">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F642" t="s">
         <v>1594</v>
@@ -30772,7 +30772,7 @@
         <v>1590</v>
       </c>
       <c r="E643">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F643" t="s">
         <v>1594</v>
@@ -30807,7 +30807,7 @@
         <v>1590</v>
       </c>
       <c r="E644">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F644" t="s">
         <v>1594</v>
@@ -30842,7 +30842,7 @@
         <v>1590</v>
       </c>
       <c r="E645">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F645" t="s">
         <v>1594</v>
@@ -30880,7 +30880,7 @@
         <v>1590</v>
       </c>
       <c r="E646">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F646" t="s">
         <v>1594</v>
@@ -30915,7 +30915,7 @@
         <v>1590</v>
       </c>
       <c r="E647">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F647" t="s">
         <v>1596</v>
@@ -30950,7 +30950,7 @@
         <v>1590</v>
       </c>
       <c r="E648">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F648" t="s">
         <v>1594</v>
@@ -30985,7 +30985,7 @@
         <v>1590</v>
       </c>
       <c r="E649">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F649" t="s">
         <v>1594</v>
@@ -31020,7 +31020,7 @@
         <v>1591</v>
       </c>
       <c r="E650">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F650" t="s">
         <v>1594</v>
@@ -31055,7 +31055,7 @@
         <v>1591</v>
       </c>
       <c r="E651">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F651" t="s">
         <v>1594</v>
@@ -31090,7 +31090,7 @@
         <v>1591</v>
       </c>
       <c r="E652">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F652" t="s">
         <v>1594</v>
@@ -31125,7 +31125,7 @@
         <v>1591</v>
       </c>
       <c r="E653">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F653" t="s">
         <v>1594</v>
@@ -31160,7 +31160,7 @@
         <v>1591</v>
       </c>
       <c r="E654">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F654" t="s">
         <v>1594</v>
@@ -31195,7 +31195,7 @@
         <v>1591</v>
       </c>
       <c r="E655">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F655" t="s">
         <v>1594</v>
@@ -31230,7 +31230,7 @@
         <v>1591</v>
       </c>
       <c r="E656">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F656" t="s">
         <v>1594</v>
@@ -31265,7 +31265,7 @@
         <v>1591</v>
       </c>
       <c r="E657">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F657" t="s">
         <v>1594</v>
@@ -31300,7 +31300,7 @@
         <v>1591</v>
       </c>
       <c r="E658">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F658" t="s">
         <v>1594</v>
@@ -31335,7 +31335,7 @@
         <v>1591</v>
       </c>
       <c r="E659">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F659" t="s">
         <v>1594</v>
@@ -31373,7 +31373,7 @@
         <v>1592</v>
       </c>
       <c r="E660">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F660" t="s">
         <v>1594</v>
@@ -31408,7 +31408,7 @@
         <v>1592</v>
       </c>
       <c r="E661">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F661" t="s">
         <v>1594</v>
@@ -31443,7 +31443,7 @@
         <v>1593</v>
       </c>
       <c r="E662">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F662" t="s">
         <v>1594</v>
@@ -31481,7 +31481,7 @@
         <v>1593</v>
       </c>
       <c r="E663">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F663" t="s">
         <v>1594</v>
@@ -31516,7 +31516,7 @@
         <v>1593</v>
       </c>
       <c r="E664">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F664" t="s">
         <v>1594</v>
@@ -31551,7 +31551,7 @@
         <v>1593</v>
       </c>
       <c r="E665">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F665" t="s">
         <v>1594</v>
@@ -31589,7 +31589,7 @@
         <v>1593</v>
       </c>
       <c r="E666">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F666" t="s">
         <v>1594</v>
@@ -31627,7 +31627,7 @@
         <v>1593</v>
       </c>
       <c r="E667">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F667" t="s">
         <v>1594</v>
@@ -31662,7 +31662,7 @@
         <v>1593</v>
       </c>
       <c r="E668">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F668" t="s">
         <v>1594</v>
@@ -31697,7 +31697,7 @@
         <v>1593</v>
       </c>
       <c r="E669">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F669" t="s">
         <v>1594</v>

--- a/BacklogGATEAutoCompleto.xlsx
+++ b/BacklogGATEAutoCompleto.xlsx
@@ -29126,7 +29126,7 @@
     </row>
     <row r="597" spans="1:12">
       <c r="A597" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B597" t="s">
         <v>633</v>
@@ -29150,7 +29150,7 @@
         <v>1612</v>
       </c>
       <c r="I597" t="s">
-        <v>1684</v>
+        <v>1626</v>
       </c>
       <c r="J597" t="s">
         <v>2330</v>

--- a/BacklogGATEAutoCompleto.xlsx
+++ b/BacklogGATEAutoCompleto.xlsx
@@ -5278,13 +5278,13 @@
     <t>IZABEL REGINA BENITE AGUIAR DA SILVA,THIAGO JOSÉ DUPRAT FORTES</t>
   </si>
   <si>
+    <t>REINALDO DE SOUZA MACHADO,RONALDO PEIXOTO VELLOSO</t>
+  </si>
+  <si>
+    <t>EDIWAN SOUSA DA SILVA,THIAGO JOSÉ DUPRAT FORTES,VANESSA TRINDADE CAMPOS DA SILVA</t>
+  </si>
+  <si>
     <t>VÍTOR MENDONÇA CELANE PINHEIRO</t>
-  </si>
-  <si>
-    <t>REINALDO DE SOUZA MACHADO,RONALDO PEIXOTO VELLOSO</t>
-  </si>
-  <si>
-    <t>EDIWAN SOUSA DA SILVA,THIAGO JOSÉ DUPRAT FORTES,VANESSA TRINDADE CAMPOS DA SILVA</t>
   </si>
   <si>
     <t>JULIANA MARTINS BAHIENSE,RODRIGO VALENTE SERRA</t>
@@ -11464,7 +11464,7 @@
         <v>1612</v>
       </c>
       <c r="I91" t="s">
-        <v>1639</v>
+        <v>1644</v>
       </c>
       <c r="J91" t="s">
         <v>1848</v>
@@ -27002,7 +27002,7 @@
         <v>1612</v>
       </c>
       <c r="I534" t="s">
-        <v>1639</v>
+        <v>1644</v>
       </c>
       <c r="J534" t="s">
         <v>2284</v>
@@ -29916,7 +29916,7 @@
     </row>
     <row r="617" spans="1:12">
       <c r="A617" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="B617" t="s">
         <v>653</v>
@@ -29937,7 +29937,7 @@
         <v>1612</v>
       </c>
       <c r="I617" t="s">
-        <v>1754</v>
+        <v>1639</v>
       </c>
       <c r="J617" t="s">
         <v>2364</v>
@@ -30045,7 +30045,7 @@
         <v>1631</v>
       </c>
       <c r="I620" t="s">
-        <v>1755</v>
+        <v>1754</v>
       </c>
       <c r="J620" t="s">
         <v>2367</v>
@@ -30185,7 +30185,7 @@
         <v>1612</v>
       </c>
       <c r="I624" t="s">
-        <v>1756</v>
+        <v>1755</v>
       </c>
       <c r="J624" t="s">
         <v>2371</v>
@@ -30220,7 +30220,7 @@
         <v>1612</v>
       </c>
       <c r="I625" t="s">
-        <v>1756</v>
+        <v>1755</v>
       </c>
       <c r="J625" t="s">
         <v>2371</v>
@@ -30255,7 +30255,7 @@
         <v>1612</v>
       </c>
       <c r="I626" t="s">
-        <v>1754</v>
+        <v>1756</v>
       </c>
       <c r="J626" t="s">
         <v>2372</v>
@@ -30573,7 +30573,7 @@
         <v>1612</v>
       </c>
       <c r="I635" t="s">
-        <v>1754</v>
+        <v>1756</v>
       </c>
       <c r="J635" t="s">
         <v>2381</v>
@@ -31177,7 +31177,7 @@
         <v>1633</v>
       </c>
       <c r="I652" t="s">
-        <v>1754</v>
+        <v>1756</v>
       </c>
       <c r="J652" t="s">
         <v>1792</v>
@@ -31959,7 +31959,7 @@
         <v>1631</v>
       </c>
       <c r="I674" t="s">
-        <v>1754</v>
+        <v>1756</v>
       </c>
       <c r="J674" t="s">
         <v>2415</v>
@@ -32035,7 +32035,7 @@
         <v>1624</v>
       </c>
       <c r="I676" t="s">
-        <v>1754</v>
+        <v>1756</v>
       </c>
       <c r="J676" t="s">
         <v>2417</v>

--- a/BacklogGATEAutoCompleto.xlsx
+++ b/BacklogGATEAutoCompleto.xlsx
@@ -2152,15 +2152,15 @@
     <t>20.22.0001.0059924.2026-19</t>
   </si>
   <si>
+    <t>20.22.0001.0005233.2026-45</t>
+  </si>
+  <si>
     <t>20.22.0001.0010728.2022-05</t>
   </si>
   <si>
     <t>20.22.0001.0006163.2021-73</t>
   </si>
   <si>
-    <t>20.22.0001.0005233.2026-45</t>
-  </si>
-  <si>
     <t>2926282</t>
   </si>
   <si>
@@ -4177,15 +4177,15 @@
     <t>2026.1035</t>
   </si>
   <si>
+    <t>2026.0075</t>
+  </si>
+  <si>
     <t>1427672</t>
   </si>
   <si>
     <t>1695198</t>
   </si>
   <si>
-    <t>2026.0075</t>
-  </si>
-  <si>
     <t>12/02/2025</t>
   </si>
   <si>
@@ -7273,13 +7273,13 @@
     <t>202400775938</t>
   </si>
   <si>
+    <t>202401101474</t>
+  </si>
+  <si>
     <t>202200161771</t>
   </si>
   <si>
     <t>0000000000000</t>
-  </si>
-  <si>
-    <t>202401101474</t>
   </si>
   <si>
     <t>1ª PROMOTORIA DE JUSTIÇA DE TUTELA COLETIVA DO NÚCLEO MACAÉ</t>
@@ -8337,7 +8337,7 @@
         <v>1390</v>
       </c>
       <c r="E2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="F2" t="s">
         <v>1607</v>
@@ -8372,7 +8372,7 @@
         <v>1391</v>
       </c>
       <c r="E3">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="F3" t="s">
         <v>1607</v>
@@ -8407,7 +8407,7 @@
         <v>1392</v>
       </c>
       <c r="E4">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="F4" t="s">
         <v>1607</v>
@@ -8442,7 +8442,7 @@
         <v>1393</v>
       </c>
       <c r="E5">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="F5" t="s">
         <v>1607</v>
@@ -8477,7 +8477,7 @@
         <v>1393</v>
       </c>
       <c r="E6">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="F6" t="s">
         <v>1607</v>
@@ -8512,7 +8512,7 @@
         <v>1394</v>
       </c>
       <c r="E7">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="F7" t="s">
         <v>1607</v>
@@ -8547,7 +8547,7 @@
         <v>1395</v>
       </c>
       <c r="E8">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="F8" t="s">
         <v>1607</v>
@@ -8582,7 +8582,7 @@
         <v>1396</v>
       </c>
       <c r="E9">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="F9" t="s">
         <v>1607</v>
@@ -8617,7 +8617,7 @@
         <v>1397</v>
       </c>
       <c r="E10">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="F10" t="s">
         <v>1607</v>
@@ -8652,7 +8652,7 @@
         <v>1398</v>
       </c>
       <c r="E11">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F11" t="s">
         <v>1607</v>
@@ -8687,7 +8687,7 @@
         <v>1399</v>
       </c>
       <c r="E12">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="F12" t="s">
         <v>1607</v>
@@ -8722,7 +8722,7 @@
         <v>1400</v>
       </c>
       <c r="E13">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F13" t="s">
         <v>1607</v>
@@ -8757,7 +8757,7 @@
         <v>1400</v>
       </c>
       <c r="E14">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F14" t="s">
         <v>1607</v>
@@ -8792,7 +8792,7 @@
         <v>1401</v>
       </c>
       <c r="E15">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F15" t="s">
         <v>1607</v>
@@ -8827,7 +8827,7 @@
         <v>1402</v>
       </c>
       <c r="E16">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="F16" t="s">
         <v>1607</v>
@@ -8862,7 +8862,7 @@
         <v>1403</v>
       </c>
       <c r="E17">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="F17" t="s">
         <v>1607</v>
@@ -8897,7 +8897,7 @@
         <v>1403</v>
       </c>
       <c r="E18">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="F18" t="s">
         <v>1607</v>
@@ -8932,7 +8932,7 @@
         <v>1404</v>
       </c>
       <c r="E19">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F19" t="s">
         <v>1607</v>
@@ -8967,7 +8967,7 @@
         <v>1405</v>
       </c>
       <c r="E20">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="F20" t="s">
         <v>1607</v>
@@ -9002,7 +9002,7 @@
         <v>1406</v>
       </c>
       <c r="E21">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="F21" t="s">
         <v>1607</v>
@@ -9037,7 +9037,7 @@
         <v>1406</v>
       </c>
       <c r="E22">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="F22" t="s">
         <v>1607</v>
@@ -9072,7 +9072,7 @@
         <v>1407</v>
       </c>
       <c r="E23">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="F23" t="s">
         <v>1607</v>
@@ -9107,7 +9107,7 @@
         <v>1408</v>
       </c>
       <c r="E24">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="F24" t="s">
         <v>1607</v>
@@ -9142,7 +9142,7 @@
         <v>1409</v>
       </c>
       <c r="E25">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F25" t="s">
         <v>1607</v>
@@ -9177,7 +9177,7 @@
         <v>1410</v>
       </c>
       <c r="E26">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="F26" t="s">
         <v>1607</v>
@@ -9212,7 +9212,7 @@
         <v>1411</v>
       </c>
       <c r="E27">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F27" t="s">
         <v>1607</v>
@@ -9250,7 +9250,7 @@
         <v>1412</v>
       </c>
       <c r="E28">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F28" t="s">
         <v>1607</v>
@@ -9285,7 +9285,7 @@
         <v>1413</v>
       </c>
       <c r="E29">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F29" t="s">
         <v>1607</v>
@@ -9320,7 +9320,7 @@
         <v>1414</v>
       </c>
       <c r="E30">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F30" t="s">
         <v>1607</v>
@@ -9355,7 +9355,7 @@
         <v>1415</v>
       </c>
       <c r="E31">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F31" t="s">
         <v>1607</v>
@@ -9390,7 +9390,7 @@
         <v>1415</v>
       </c>
       <c r="E32">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F32" t="s">
         <v>1607</v>
@@ -9425,7 +9425,7 @@
         <v>1416</v>
       </c>
       <c r="E33">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F33" t="s">
         <v>1607</v>
@@ -9460,7 +9460,7 @@
         <v>1417</v>
       </c>
       <c r="E34">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F34" t="s">
         <v>1607</v>
@@ -9495,7 +9495,7 @@
         <v>1418</v>
       </c>
       <c r="E35">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F35" t="s">
         <v>1607</v>
@@ -9530,7 +9530,7 @@
         <v>1419</v>
       </c>
       <c r="E36">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="F36" t="s">
         <v>1607</v>
@@ -9565,7 +9565,7 @@
         <v>1420</v>
       </c>
       <c r="E37">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F37" t="s">
         <v>1607</v>
@@ -9600,7 +9600,7 @@
         <v>1421</v>
       </c>
       <c r="E38">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F38" t="s">
         <v>1607</v>
@@ -9635,7 +9635,7 @@
         <v>1422</v>
       </c>
       <c r="E39">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F39" t="s">
         <v>1607</v>
@@ -9670,7 +9670,7 @@
         <v>1423</v>
       </c>
       <c r="E40">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F40" t="s">
         <v>1607</v>
@@ -9705,7 +9705,7 @@
         <v>1423</v>
       </c>
       <c r="E41">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F41" t="s">
         <v>1607</v>
@@ -9740,7 +9740,7 @@
         <v>1424</v>
       </c>
       <c r="E42">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F42" t="s">
         <v>1607</v>
@@ -9775,7 +9775,7 @@
         <v>1424</v>
       </c>
       <c r="E43">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F43" t="s">
         <v>1607</v>
@@ -9810,7 +9810,7 @@
         <v>1425</v>
       </c>
       <c r="E44">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F44" t="s">
         <v>1607</v>
@@ -9845,7 +9845,7 @@
         <v>1426</v>
       </c>
       <c r="E45">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F45" t="s">
         <v>1607</v>
@@ -9880,7 +9880,7 @@
         <v>1427</v>
       </c>
       <c r="E46">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F46" t="s">
         <v>1607</v>
@@ -9915,7 +9915,7 @@
         <v>1428</v>
       </c>
       <c r="E47">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F47" t="s">
         <v>1607</v>
@@ -9950,7 +9950,7 @@
         <v>1428</v>
       </c>
       <c r="E48">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F48" t="s">
         <v>1607</v>
@@ -9985,7 +9985,7 @@
         <v>1429</v>
       </c>
       <c r="E49">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F49" t="s">
         <v>1607</v>
@@ -10020,7 +10020,7 @@
         <v>1430</v>
       </c>
       <c r="E50">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F50" t="s">
         <v>1607</v>
@@ -10055,7 +10055,7 @@
         <v>1431</v>
       </c>
       <c r="E51">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F51" t="s">
         <v>1607</v>
@@ -10090,7 +10090,7 @@
         <v>1431</v>
       </c>
       <c r="E52">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F52" t="s">
         <v>1607</v>
@@ -10125,7 +10125,7 @@
         <v>1432</v>
       </c>
       <c r="E53">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F53" t="s">
         <v>1607</v>
@@ -10160,7 +10160,7 @@
         <v>1432</v>
       </c>
       <c r="E54">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F54" t="s">
         <v>1607</v>
@@ -10195,7 +10195,7 @@
         <v>1433</v>
       </c>
       <c r="E55">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F55" t="s">
         <v>1607</v>
@@ -10230,7 +10230,7 @@
         <v>1434</v>
       </c>
       <c r="E56">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F56" t="s">
         <v>1607</v>
@@ -10265,7 +10265,7 @@
         <v>1435</v>
       </c>
       <c r="E57">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F57" t="s">
         <v>1607</v>
@@ -10300,7 +10300,7 @@
         <v>1436</v>
       </c>
       <c r="E58">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F58" t="s">
         <v>1607</v>
@@ -10335,7 +10335,7 @@
         <v>1437</v>
       </c>
       <c r="E59">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F59" t="s">
         <v>1607</v>
@@ -10370,7 +10370,7 @@
         <v>1438</v>
       </c>
       <c r="E60">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F60" t="s">
         <v>1607</v>
@@ -10405,7 +10405,7 @@
         <v>1438</v>
       </c>
       <c r="E61">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F61" t="s">
         <v>1607</v>
@@ -10440,7 +10440,7 @@
         <v>1439</v>
       </c>
       <c r="E62">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F62" t="s">
         <v>1607</v>
@@ -10475,7 +10475,7 @@
         <v>1440</v>
       </c>
       <c r="E63">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F63" t="s">
         <v>1607</v>
@@ -10510,7 +10510,7 @@
         <v>1441</v>
       </c>
       <c r="E64">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F64" t="s">
         <v>1607</v>
@@ -10545,7 +10545,7 @@
         <v>1442</v>
       </c>
       <c r="E65">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F65" t="s">
         <v>1607</v>
@@ -10580,7 +10580,7 @@
         <v>1443</v>
       </c>
       <c r="E66">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F66" t="s">
         <v>1607</v>
@@ -10615,7 +10615,7 @@
         <v>1444</v>
       </c>
       <c r="E67">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F67" t="s">
         <v>1607</v>
@@ -10650,7 +10650,7 @@
         <v>1445</v>
       </c>
       <c r="E68">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F68" t="s">
         <v>1607</v>
@@ -10685,7 +10685,7 @@
         <v>1446</v>
       </c>
       <c r="E69">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F69" t="s">
         <v>1607</v>
@@ -10720,7 +10720,7 @@
         <v>1447</v>
       </c>
       <c r="E70">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F70" t="s">
         <v>1607</v>
@@ -10755,7 +10755,7 @@
         <v>1448</v>
       </c>
       <c r="E71">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F71" t="s">
         <v>1607</v>
@@ -10790,7 +10790,7 @@
         <v>1449</v>
       </c>
       <c r="E72">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F72" t="s">
         <v>1607</v>
@@ -10825,7 +10825,7 @@
         <v>1450</v>
       </c>
       <c r="E73">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F73" t="s">
         <v>1607</v>
@@ -10860,7 +10860,7 @@
         <v>1450</v>
       </c>
       <c r="E74">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F74" t="s">
         <v>1607</v>
@@ -10895,7 +10895,7 @@
         <v>1450</v>
       </c>
       <c r="E75">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F75" t="s">
         <v>1607</v>
@@ -10930,7 +10930,7 @@
         <v>1451</v>
       </c>
       <c r="E76">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F76" t="s">
         <v>1607</v>
@@ -10965,7 +10965,7 @@
         <v>1452</v>
       </c>
       <c r="E77">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F77" t="s">
         <v>1607</v>
@@ -11000,7 +11000,7 @@
         <v>1453</v>
       </c>
       <c r="E78">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F78" t="s">
         <v>1607</v>
@@ -11035,7 +11035,7 @@
         <v>1453</v>
       </c>
       <c r="E79">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F79" t="s">
         <v>1607</v>
@@ -11070,7 +11070,7 @@
         <v>1453</v>
       </c>
       <c r="E80">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F80" t="s">
         <v>1607</v>
@@ -11105,7 +11105,7 @@
         <v>1454</v>
       </c>
       <c r="E81">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F81" t="s">
         <v>1607</v>
@@ -11140,7 +11140,7 @@
         <v>1455</v>
       </c>
       <c r="E82">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F82" t="s">
         <v>1607</v>
@@ -11175,7 +11175,7 @@
         <v>1456</v>
       </c>
       <c r="E83">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F83" t="s">
         <v>1607</v>
@@ -11210,7 +11210,7 @@
         <v>1456</v>
       </c>
       <c r="E84">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F84" t="s">
         <v>1607</v>
@@ -11245,7 +11245,7 @@
         <v>1456</v>
       </c>
       <c r="E85">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F85" t="s">
         <v>1607</v>
@@ -11280,7 +11280,7 @@
         <v>1457</v>
       </c>
       <c r="E86">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F86" t="s">
         <v>1607</v>
@@ -11315,7 +11315,7 @@
         <v>1458</v>
       </c>
       <c r="E87">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F87" t="s">
         <v>1607</v>
@@ -11350,7 +11350,7 @@
         <v>1458</v>
       </c>
       <c r="E88">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F88" t="s">
         <v>1607</v>
@@ -11385,7 +11385,7 @@
         <v>1458</v>
       </c>
       <c r="E89">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F89" t="s">
         <v>1608</v>
@@ -11420,7 +11420,7 @@
         <v>1458</v>
       </c>
       <c r="E90">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F90" t="s">
         <v>1607</v>
@@ -11455,7 +11455,7 @@
         <v>1459</v>
       </c>
       <c r="E91">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F91" t="s">
         <v>1607</v>
@@ -11490,7 +11490,7 @@
         <v>1460</v>
       </c>
       <c r="E92">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F92" t="s">
         <v>1607</v>
@@ -11525,7 +11525,7 @@
         <v>1461</v>
       </c>
       <c r="E93">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F93" t="s">
         <v>1607</v>
@@ -11560,7 +11560,7 @@
         <v>1461</v>
       </c>
       <c r="E94">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F94" t="s">
         <v>1607</v>
@@ -11595,7 +11595,7 @@
         <v>1461</v>
       </c>
       <c r="E95">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F95" t="s">
         <v>1607</v>
@@ -11630,7 +11630,7 @@
         <v>1462</v>
       </c>
       <c r="E96">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F96" t="s">
         <v>1607</v>
@@ -11665,7 +11665,7 @@
         <v>1463</v>
       </c>
       <c r="E97">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F97" t="s">
         <v>1607</v>
@@ -11700,7 +11700,7 @@
         <v>1464</v>
       </c>
       <c r="E98">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F98" t="s">
         <v>1607</v>
@@ -11735,7 +11735,7 @@
         <v>1465</v>
       </c>
       <c r="E99">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F99" t="s">
         <v>1607</v>
@@ -11770,7 +11770,7 @@
         <v>1466</v>
       </c>
       <c r="E100">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F100" t="s">
         <v>1607</v>
@@ -11805,7 +11805,7 @@
         <v>1466</v>
       </c>
       <c r="E101">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F101" t="s">
         <v>1607</v>
@@ -11840,7 +11840,7 @@
         <v>1466</v>
       </c>
       <c r="E102">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F102" t="s">
         <v>1607</v>
@@ -11875,7 +11875,7 @@
         <v>1466</v>
       </c>
       <c r="E103">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F103" t="s">
         <v>1607</v>
@@ -11910,7 +11910,7 @@
         <v>1466</v>
       </c>
       <c r="E104">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F104" t="s">
         <v>1607</v>
@@ -11945,7 +11945,7 @@
         <v>1466</v>
       </c>
       <c r="E105">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F105" t="s">
         <v>1607</v>
@@ -11980,7 +11980,7 @@
         <v>1466</v>
       </c>
       <c r="E106">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F106" t="s">
         <v>1607</v>
@@ -12015,7 +12015,7 @@
         <v>1467</v>
       </c>
       <c r="E107">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F107" t="s">
         <v>1607</v>
@@ -12050,7 +12050,7 @@
         <v>1467</v>
       </c>
       <c r="E108">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F108" t="s">
         <v>1607</v>
@@ -12085,7 +12085,7 @@
         <v>1468</v>
       </c>
       <c r="E109">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F109" t="s">
         <v>1607</v>
@@ -12120,7 +12120,7 @@
         <v>1469</v>
       </c>
       <c r="E110">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F110" t="s">
         <v>1607</v>
@@ -12155,7 +12155,7 @@
         <v>1469</v>
       </c>
       <c r="E111">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F111" t="s">
         <v>1607</v>
@@ -12190,7 +12190,7 @@
         <v>1470</v>
       </c>
       <c r="E112">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F112" t="s">
         <v>1607</v>
@@ -12225,7 +12225,7 @@
         <v>1470</v>
       </c>
       <c r="E113">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F113" t="s">
         <v>1609</v>
@@ -12260,7 +12260,7 @@
         <v>1471</v>
       </c>
       <c r="E114">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F114" t="s">
         <v>1607</v>
@@ -12295,7 +12295,7 @@
         <v>1472</v>
       </c>
       <c r="E115">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F115" t="s">
         <v>1607</v>
@@ -12330,7 +12330,7 @@
         <v>1473</v>
       </c>
       <c r="E116">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F116" t="s">
         <v>1607</v>
@@ -12365,7 +12365,7 @@
         <v>1473</v>
       </c>
       <c r="E117">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F117" t="s">
         <v>1607</v>
@@ -12400,7 +12400,7 @@
         <v>1474</v>
       </c>
       <c r="E118">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F118" t="s">
         <v>1607</v>
@@ -12435,7 +12435,7 @@
         <v>1475</v>
       </c>
       <c r="E119">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F119" t="s">
         <v>1607</v>
@@ -12470,7 +12470,7 @@
         <v>1476</v>
       </c>
       <c r="E120">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F120" t="s">
         <v>1607</v>
@@ -12505,7 +12505,7 @@
         <v>1476</v>
       </c>
       <c r="E121">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F121" t="s">
         <v>1607</v>
@@ -12540,7 +12540,7 @@
         <v>1477</v>
       </c>
       <c r="E122">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F122" t="s">
         <v>1607</v>
@@ -12575,7 +12575,7 @@
         <v>1478</v>
       </c>
       <c r="E123">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F123" t="s">
         <v>1607</v>
@@ -12610,7 +12610,7 @@
         <v>1478</v>
       </c>
       <c r="E124">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F124" t="s">
         <v>1607</v>
@@ -12645,7 +12645,7 @@
         <v>1479</v>
       </c>
       <c r="E125">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F125" t="s">
         <v>1607</v>
@@ -12680,7 +12680,7 @@
         <v>1479</v>
       </c>
       <c r="E126">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F126" t="s">
         <v>1607</v>
@@ -12715,7 +12715,7 @@
         <v>1479</v>
       </c>
       <c r="E127">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F127" t="s">
         <v>1607</v>
@@ -12750,7 +12750,7 @@
         <v>1479</v>
       </c>
       <c r="E128">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F128" t="s">
         <v>1607</v>
@@ -12785,7 +12785,7 @@
         <v>1480</v>
       </c>
       <c r="E129">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F129" t="s">
         <v>1607</v>
@@ -12820,7 +12820,7 @@
         <v>1480</v>
       </c>
       <c r="E130">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F130" t="s">
         <v>1607</v>
@@ -12855,7 +12855,7 @@
         <v>1480</v>
       </c>
       <c r="E131">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F131" t="s">
         <v>1607</v>
@@ -12890,7 +12890,7 @@
         <v>1480</v>
       </c>
       <c r="E132">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F132" t="s">
         <v>1607</v>
@@ -12925,7 +12925,7 @@
         <v>1480</v>
       </c>
       <c r="E133">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F133" t="s">
         <v>1607</v>
@@ -12960,7 +12960,7 @@
         <v>1480</v>
       </c>
       <c r="E134">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F134" t="s">
         <v>1607</v>
@@ -12995,7 +12995,7 @@
         <v>1481</v>
       </c>
       <c r="E135">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F135" t="s">
         <v>1607</v>
@@ -13030,7 +13030,7 @@
         <v>1482</v>
       </c>
       <c r="E136">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F136" t="s">
         <v>1607</v>
@@ -13065,7 +13065,7 @@
         <v>1482</v>
       </c>
       <c r="E137">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F137" t="s">
         <v>1607</v>
@@ -13100,7 +13100,7 @@
         <v>1483</v>
       </c>
       <c r="E138">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F138" t="s">
         <v>1607</v>
@@ -13135,7 +13135,7 @@
         <v>1484</v>
       </c>
       <c r="E139">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F139" t="s">
         <v>1607</v>
@@ -13170,7 +13170,7 @@
         <v>1484</v>
       </c>
       <c r="E140">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F140" t="s">
         <v>1607</v>
@@ -13205,7 +13205,7 @@
         <v>1484</v>
       </c>
       <c r="E141">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F141" t="s">
         <v>1607</v>
@@ -13240,7 +13240,7 @@
         <v>1485</v>
       </c>
       <c r="E142">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F142" t="s">
         <v>1607</v>
@@ -13275,7 +13275,7 @@
         <v>1485</v>
       </c>
       <c r="E143">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F143" t="s">
         <v>1607</v>
@@ -13310,7 +13310,7 @@
         <v>1485</v>
       </c>
       <c r="E144">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F144" t="s">
         <v>1607</v>
@@ -13345,7 +13345,7 @@
         <v>1486</v>
       </c>
       <c r="E145">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F145" t="s">
         <v>1607</v>
@@ -13380,7 +13380,7 @@
         <v>1486</v>
       </c>
       <c r="E146">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F146" t="s">
         <v>1607</v>
@@ -13415,7 +13415,7 @@
         <v>1486</v>
       </c>
       <c r="E147">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F147" t="s">
         <v>1607</v>
@@ -13450,7 +13450,7 @@
         <v>1487</v>
       </c>
       <c r="E148">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F148" t="s">
         <v>1607</v>
@@ -13485,7 +13485,7 @@
         <v>1487</v>
       </c>
       <c r="E149">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F149" t="s">
         <v>1607</v>
@@ -13520,7 +13520,7 @@
         <v>1488</v>
       </c>
       <c r="E150">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F150" t="s">
         <v>1607</v>
@@ -13555,7 +13555,7 @@
         <v>1489</v>
       </c>
       <c r="E151">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F151" t="s">
         <v>1607</v>
@@ -13590,7 +13590,7 @@
         <v>1489</v>
       </c>
       <c r="E152">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F152" t="s">
         <v>1607</v>
@@ -13625,7 +13625,7 @@
         <v>1489</v>
       </c>
       <c r="E153">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F153" t="s">
         <v>1607</v>
@@ -13660,7 +13660,7 @@
         <v>1490</v>
       </c>
       <c r="E154">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F154" t="s">
         <v>1607</v>
@@ -13695,7 +13695,7 @@
         <v>1490</v>
       </c>
       <c r="E155">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F155" t="s">
         <v>1607</v>
@@ -13730,7 +13730,7 @@
         <v>1491</v>
       </c>
       <c r="E156">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F156" t="s">
         <v>1607</v>
@@ -13768,7 +13768,7 @@
         <v>1491</v>
       </c>
       <c r="E157">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F157" t="s">
         <v>1607</v>
@@ -13803,7 +13803,7 @@
         <v>1491</v>
       </c>
       <c r="E158">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F158" t="s">
         <v>1607</v>
@@ -13838,7 +13838,7 @@
         <v>1491</v>
       </c>
       <c r="E159">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F159" t="s">
         <v>1607</v>
@@ -13873,7 +13873,7 @@
         <v>1491</v>
       </c>
       <c r="E160">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F160" t="s">
         <v>1607</v>
@@ -13908,7 +13908,7 @@
         <v>1491</v>
       </c>
       <c r="E161">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F161" t="s">
         <v>1607</v>
@@ -13943,7 +13943,7 @@
         <v>1492</v>
       </c>
       <c r="E162">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F162" t="s">
         <v>1607</v>
@@ -13978,7 +13978,7 @@
         <v>1493</v>
       </c>
       <c r="E163">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F163" t="s">
         <v>1607</v>
@@ -14013,7 +14013,7 @@
         <v>1494</v>
       </c>
       <c r="E164">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F164" t="s">
         <v>1608</v>
@@ -14048,7 +14048,7 @@
         <v>1495</v>
       </c>
       <c r="E165">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F165" t="s">
         <v>1607</v>
@@ -14083,7 +14083,7 @@
         <v>1495</v>
       </c>
       <c r="E166">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F166" t="s">
         <v>1607</v>
@@ -14118,7 +14118,7 @@
         <v>1495</v>
       </c>
       <c r="E167">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F167" t="s">
         <v>1607</v>
@@ -14153,7 +14153,7 @@
         <v>1495</v>
       </c>
       <c r="E168">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F168" t="s">
         <v>1607</v>
@@ -14188,7 +14188,7 @@
         <v>1496</v>
       </c>
       <c r="E169">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F169" t="s">
         <v>1607</v>
@@ -14223,7 +14223,7 @@
         <v>1496</v>
       </c>
       <c r="E170">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F170" t="s">
         <v>1607</v>
@@ -14258,7 +14258,7 @@
         <v>1496</v>
       </c>
       <c r="E171">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F171" t="s">
         <v>1607</v>
@@ -14293,7 +14293,7 @@
         <v>1496</v>
       </c>
       <c r="E172">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F172" t="s">
         <v>1607</v>
@@ -14328,7 +14328,7 @@
         <v>1496</v>
       </c>
       <c r="E173">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F173" t="s">
         <v>1607</v>
@@ -14363,7 +14363,7 @@
         <v>1496</v>
       </c>
       <c r="E174">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F174" t="s">
         <v>1607</v>
@@ -14398,7 +14398,7 @@
         <v>1496</v>
       </c>
       <c r="E175">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F175" t="s">
         <v>1607</v>
@@ -14433,7 +14433,7 @@
         <v>1497</v>
       </c>
       <c r="E176">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F176" t="s">
         <v>1607</v>
@@ -14468,7 +14468,7 @@
         <v>1497</v>
       </c>
       <c r="E177">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F177" t="s">
         <v>1607</v>
@@ -14503,7 +14503,7 @@
         <v>1498</v>
       </c>
       <c r="E178">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F178" t="s">
         <v>1607</v>
@@ -14538,7 +14538,7 @@
         <v>1498</v>
       </c>
       <c r="E179">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F179" t="s">
         <v>1607</v>
@@ -14573,7 +14573,7 @@
         <v>1498</v>
       </c>
       <c r="E180">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F180" t="s">
         <v>1607</v>
@@ -14608,7 +14608,7 @@
         <v>1499</v>
       </c>
       <c r="E181">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F181" t="s">
         <v>1607</v>
@@ -14643,7 +14643,7 @@
         <v>1499</v>
       </c>
       <c r="E182">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F182" t="s">
         <v>1607</v>
@@ -14678,7 +14678,7 @@
         <v>1499</v>
       </c>
       <c r="E183">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F183" t="s">
         <v>1607</v>
@@ -14713,7 +14713,7 @@
         <v>1499</v>
       </c>
       <c r="E184">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F184" t="s">
         <v>1607</v>
@@ -14748,7 +14748,7 @@
         <v>1500</v>
       </c>
       <c r="E185">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F185" t="s">
         <v>1607</v>
@@ -14783,7 +14783,7 @@
         <v>1500</v>
       </c>
       <c r="E186">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F186" t="s">
         <v>1607</v>
@@ -14818,7 +14818,7 @@
         <v>1500</v>
       </c>
       <c r="E187">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F187" t="s">
         <v>1607</v>
@@ -14853,7 +14853,7 @@
         <v>1500</v>
       </c>
       <c r="E188">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F188" t="s">
         <v>1607</v>
@@ -14888,7 +14888,7 @@
         <v>1500</v>
       </c>
       <c r="E189">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F189" t="s">
         <v>1607</v>
@@ -14923,7 +14923,7 @@
         <v>1500</v>
       </c>
       <c r="E190">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F190" t="s">
         <v>1607</v>
@@ -14958,7 +14958,7 @@
         <v>1500</v>
       </c>
       <c r="E191">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F191" t="s">
         <v>1607</v>
@@ -14993,7 +14993,7 @@
         <v>1500</v>
       </c>
       <c r="E192">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F192" t="s">
         <v>1607</v>
@@ -15028,7 +15028,7 @@
         <v>1500</v>
       </c>
       <c r="E193">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F193" t="s">
         <v>1607</v>
@@ -15063,7 +15063,7 @@
         <v>1500</v>
       </c>
       <c r="E194">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F194" t="s">
         <v>1607</v>
@@ -15098,7 +15098,7 @@
         <v>1501</v>
       </c>
       <c r="E195">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F195" t="s">
         <v>1607</v>
@@ -15133,7 +15133,7 @@
         <v>1501</v>
       </c>
       <c r="E196">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F196" t="s">
         <v>1607</v>
@@ -15168,7 +15168,7 @@
         <v>1501</v>
       </c>
       <c r="E197">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F197" t="s">
         <v>1607</v>
@@ -15203,7 +15203,7 @@
         <v>1501</v>
       </c>
       <c r="E198">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F198" t="s">
         <v>1610</v>
@@ -15238,7 +15238,7 @@
         <v>1502</v>
       </c>
       <c r="E199">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F199" t="s">
         <v>1607</v>
@@ -15273,7 +15273,7 @@
         <v>1502</v>
       </c>
       <c r="E200">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F200" t="s">
         <v>1608</v>
@@ -15308,7 +15308,7 @@
         <v>1502</v>
       </c>
       <c r="E201">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F201" t="s">
         <v>1607</v>
@@ -15343,7 +15343,7 @@
         <v>1503</v>
       </c>
       <c r="E202">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F202" t="s">
         <v>1607</v>
@@ -15378,7 +15378,7 @@
         <v>1503</v>
       </c>
       <c r="E203">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F203" t="s">
         <v>1607</v>
@@ -15413,7 +15413,7 @@
         <v>1504</v>
       </c>
       <c r="E204">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F204" t="s">
         <v>1607</v>
@@ -15448,7 +15448,7 @@
         <v>1504</v>
       </c>
       <c r="E205">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F205" t="s">
         <v>1607</v>
@@ -15483,7 +15483,7 @@
         <v>1505</v>
       </c>
       <c r="E206">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F206" t="s">
         <v>1607</v>
@@ -15518,7 +15518,7 @@
         <v>1505</v>
       </c>
       <c r="E207">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F207" t="s">
         <v>1607</v>
@@ -15553,7 +15553,7 @@
         <v>1505</v>
       </c>
       <c r="E208">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F208" t="s">
         <v>1607</v>
@@ -15588,7 +15588,7 @@
         <v>1506</v>
       </c>
       <c r="E209">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F209" t="s">
         <v>1607</v>
@@ -15623,7 +15623,7 @@
         <v>1506</v>
       </c>
       <c r="E210">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F210" t="s">
         <v>1607</v>
@@ -15658,7 +15658,7 @@
         <v>1506</v>
       </c>
       <c r="E211">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F211" t="s">
         <v>1607</v>
@@ -15693,7 +15693,7 @@
         <v>1506</v>
       </c>
       <c r="E212">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F212" t="s">
         <v>1607</v>
@@ -15728,7 +15728,7 @@
         <v>1506</v>
       </c>
       <c r="E213">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F213" t="s">
         <v>1607</v>
@@ -15763,7 +15763,7 @@
         <v>1507</v>
       </c>
       <c r="E214">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F214" t="s">
         <v>1607</v>
@@ -15798,7 +15798,7 @@
         <v>1507</v>
       </c>
       <c r="E215">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F215" t="s">
         <v>1607</v>
@@ -15833,7 +15833,7 @@
         <v>1508</v>
       </c>
       <c r="E216">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F216" t="s">
         <v>1607</v>
@@ -15868,7 +15868,7 @@
         <v>1509</v>
       </c>
       <c r="E217">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F217" t="s">
         <v>1607</v>
@@ -15903,7 +15903,7 @@
         <v>1509</v>
       </c>
       <c r="E218">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F218" t="s">
         <v>1607</v>
@@ -15938,7 +15938,7 @@
         <v>1509</v>
       </c>
       <c r="E219">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F219" t="s">
         <v>1607</v>
@@ -15973,7 +15973,7 @@
         <v>1509</v>
       </c>
       <c r="E220">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F220" t="s">
         <v>1607</v>
@@ -16008,7 +16008,7 @@
         <v>1510</v>
       </c>
       <c r="E221">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F221" t="s">
         <v>1607</v>
@@ -16043,7 +16043,7 @@
         <v>1511</v>
       </c>
       <c r="E222">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F222" t="s">
         <v>1607</v>
@@ -16078,7 +16078,7 @@
         <v>1511</v>
       </c>
       <c r="E223">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F223" t="s">
         <v>1607</v>
@@ -16113,7 +16113,7 @@
         <v>1511</v>
       </c>
       <c r="E224">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F224" t="s">
         <v>1607</v>
@@ -16148,7 +16148,7 @@
         <v>1511</v>
       </c>
       <c r="E225">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F225" t="s">
         <v>1607</v>
@@ -16183,7 +16183,7 @@
         <v>1511</v>
       </c>
       <c r="E226">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F226" t="s">
         <v>1607</v>
@@ -16218,7 +16218,7 @@
         <v>1512</v>
       </c>
       <c r="E227">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F227" t="s">
         <v>1607</v>
@@ -16253,7 +16253,7 @@
         <v>1512</v>
       </c>
       <c r="E228">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F228" t="s">
         <v>1607</v>
@@ -16288,7 +16288,7 @@
         <v>1512</v>
       </c>
       <c r="E229">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F229" t="s">
         <v>1607</v>
@@ -16323,7 +16323,7 @@
         <v>1512</v>
       </c>
       <c r="E230">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F230" t="s">
         <v>1607</v>
@@ -16358,7 +16358,7 @@
         <v>1512</v>
       </c>
       <c r="E231">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F231" t="s">
         <v>1607</v>
@@ -16393,7 +16393,7 @@
         <v>1512</v>
       </c>
       <c r="E232">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F232" t="s">
         <v>1607</v>
@@ -16428,7 +16428,7 @@
         <v>1512</v>
       </c>
       <c r="E233">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F233" t="s">
         <v>1607</v>
@@ -16463,7 +16463,7 @@
         <v>1513</v>
       </c>
       <c r="E234">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F234" t="s">
         <v>1607</v>
@@ -16498,7 +16498,7 @@
         <v>1513</v>
       </c>
       <c r="E235">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F235" t="s">
         <v>1607</v>
@@ -16533,7 +16533,7 @@
         <v>1513</v>
       </c>
       <c r="E236">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F236" t="s">
         <v>1607</v>
@@ -16568,7 +16568,7 @@
         <v>1513</v>
       </c>
       <c r="E237">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F237" t="s">
         <v>1607</v>
@@ -16603,7 +16603,7 @@
         <v>1514</v>
       </c>
       <c r="E238">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F238" t="s">
         <v>1607</v>
@@ -16638,7 +16638,7 @@
         <v>1514</v>
       </c>
       <c r="E239">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F239" t="s">
         <v>1607</v>
@@ -16673,7 +16673,7 @@
         <v>1514</v>
       </c>
       <c r="E240">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F240" t="s">
         <v>1607</v>
@@ -16708,7 +16708,7 @@
         <v>1515</v>
       </c>
       <c r="E241">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F241" t="s">
         <v>1607</v>
@@ -16743,7 +16743,7 @@
         <v>1515</v>
       </c>
       <c r="E242">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F242" t="s">
         <v>1607</v>
@@ -16778,7 +16778,7 @@
         <v>1516</v>
       </c>
       <c r="E243">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F243" t="s">
         <v>1607</v>
@@ -16813,7 +16813,7 @@
         <v>1516</v>
       </c>
       <c r="E244">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F244" t="s">
         <v>1607</v>
@@ -16848,7 +16848,7 @@
         <v>1517</v>
       </c>
       <c r="E245">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F245" t="s">
         <v>1607</v>
@@ -16883,7 +16883,7 @@
         <v>1517</v>
       </c>
       <c r="E246">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F246" t="s">
         <v>1607</v>
@@ -16918,7 +16918,7 @@
         <v>1518</v>
       </c>
       <c r="E247">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F247" t="s">
         <v>1607</v>
@@ -16953,7 +16953,7 @@
         <v>1518</v>
       </c>
       <c r="E248">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F248" t="s">
         <v>1607</v>
@@ -16988,7 +16988,7 @@
         <v>1519</v>
       </c>
       <c r="E249">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F249" t="s">
         <v>1607</v>
@@ -17023,7 +17023,7 @@
         <v>1519</v>
       </c>
       <c r="E250">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F250" t="s">
         <v>1607</v>
@@ -17058,7 +17058,7 @@
         <v>1520</v>
       </c>
       <c r="E251">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F251" t="s">
         <v>1607</v>
@@ -17093,7 +17093,7 @@
         <v>1520</v>
       </c>
       <c r="E252">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F252" t="s">
         <v>1607</v>
@@ -17128,7 +17128,7 @@
         <v>1521</v>
       </c>
       <c r="E253">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F253" t="s">
         <v>1607</v>
@@ -17163,7 +17163,7 @@
         <v>1521</v>
       </c>
       <c r="E254">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F254" t="s">
         <v>1607</v>
@@ -17198,7 +17198,7 @@
         <v>1521</v>
       </c>
       <c r="E255">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F255" t="s">
         <v>1607</v>
@@ -17233,7 +17233,7 @@
         <v>1522</v>
       </c>
       <c r="E256">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F256" t="s">
         <v>1607</v>
@@ -17268,7 +17268,7 @@
         <v>1522</v>
       </c>
       <c r="E257">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F257" t="s">
         <v>1607</v>
@@ -17303,7 +17303,7 @@
         <v>1523</v>
       </c>
       <c r="E258">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F258" t="s">
         <v>1607</v>
@@ -17338,7 +17338,7 @@
         <v>1524</v>
       </c>
       <c r="E259">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F259" t="s">
         <v>1607</v>
@@ -17373,7 +17373,7 @@
         <v>1524</v>
       </c>
       <c r="E260">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F260" t="s">
         <v>1607</v>
@@ -17408,7 +17408,7 @@
         <v>1524</v>
       </c>
       <c r="E261">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F261" t="s">
         <v>1607</v>
@@ -17443,7 +17443,7 @@
         <v>1525</v>
       </c>
       <c r="E262">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F262" t="s">
         <v>1607</v>
@@ -17478,7 +17478,7 @@
         <v>1525</v>
       </c>
       <c r="E263">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F263" t="s">
         <v>1607</v>
@@ -17513,7 +17513,7 @@
         <v>1526</v>
       </c>
       <c r="E264">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F264" t="s">
         <v>1607</v>
@@ -17548,7 +17548,7 @@
         <v>1526</v>
       </c>
       <c r="E265">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F265" t="s">
         <v>1607</v>
@@ -17583,7 +17583,7 @@
         <v>1526</v>
       </c>
       <c r="E266">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F266" t="s">
         <v>1609</v>
@@ -17618,7 +17618,7 @@
         <v>1526</v>
       </c>
       <c r="E267">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F267" t="s">
         <v>1607</v>
@@ -17653,7 +17653,7 @@
         <v>1526</v>
       </c>
       <c r="E268">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F268" t="s">
         <v>1607</v>
@@ -17688,7 +17688,7 @@
         <v>1527</v>
       </c>
       <c r="E269">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F269" t="s">
         <v>1607</v>
@@ -17723,7 +17723,7 @@
         <v>1527</v>
       </c>
       <c r="E270">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F270" t="s">
         <v>1607</v>
@@ -17758,7 +17758,7 @@
         <v>1527</v>
       </c>
       <c r="E271">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F271" t="s">
         <v>1607</v>
@@ -17796,7 +17796,7 @@
         <v>1527</v>
       </c>
       <c r="E272">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F272" t="s">
         <v>1607</v>
@@ -17831,7 +17831,7 @@
         <v>1527</v>
       </c>
       <c r="E273">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F273" t="s">
         <v>1607</v>
@@ -17866,7 +17866,7 @@
         <v>1527</v>
       </c>
       <c r="E274">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F274" t="s">
         <v>1607</v>
@@ -17901,7 +17901,7 @@
         <v>1527</v>
       </c>
       <c r="E275">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F275" t="s">
         <v>1607</v>
@@ -17936,7 +17936,7 @@
         <v>1528</v>
       </c>
       <c r="E276">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F276" t="s">
         <v>1607</v>
@@ -17971,7 +17971,7 @@
         <v>1528</v>
       </c>
       <c r="E277">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F277" t="s">
         <v>1607</v>
@@ -18006,7 +18006,7 @@
         <v>1528</v>
       </c>
       <c r="E278">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F278" t="s">
         <v>1607</v>
@@ -18041,7 +18041,7 @@
         <v>1529</v>
       </c>
       <c r="E279">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F279" t="s">
         <v>1607</v>
@@ -18076,7 +18076,7 @@
         <v>1529</v>
       </c>
       <c r="E280">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F280" t="s">
         <v>1607</v>
@@ -18111,7 +18111,7 @@
         <v>1529</v>
       </c>
       <c r="E281">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F281" t="s">
         <v>1607</v>
@@ -18146,7 +18146,7 @@
         <v>1529</v>
       </c>
       <c r="E282">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F282" t="s">
         <v>1607</v>
@@ -18181,7 +18181,7 @@
         <v>1530</v>
       </c>
       <c r="E283">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F283" t="s">
         <v>1607</v>
@@ -18216,7 +18216,7 @@
         <v>1530</v>
       </c>
       <c r="E284">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F284" t="s">
         <v>1607</v>
@@ -18251,7 +18251,7 @@
         <v>1530</v>
       </c>
       <c r="E285">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F285" t="s">
         <v>1607</v>
@@ -18286,7 +18286,7 @@
         <v>1530</v>
       </c>
       <c r="E286">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F286" t="s">
         <v>1607</v>
@@ -18321,7 +18321,7 @@
         <v>1530</v>
       </c>
       <c r="E287">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F287" t="s">
         <v>1607</v>
@@ -18356,7 +18356,7 @@
         <v>1530</v>
       </c>
       <c r="E288">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F288" t="s">
         <v>1607</v>
@@ -18391,7 +18391,7 @@
         <v>1531</v>
       </c>
       <c r="E289">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F289" t="s">
         <v>1607</v>
@@ -18426,7 +18426,7 @@
         <v>1531</v>
       </c>
       <c r="E290">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F290" t="s">
         <v>1607</v>
@@ -18461,7 +18461,7 @@
         <v>1531</v>
       </c>
       <c r="E291">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F291" t="s">
         <v>1607</v>
@@ -18496,7 +18496,7 @@
         <v>1531</v>
       </c>
       <c r="E292">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F292" t="s">
         <v>1607</v>
@@ -18531,7 +18531,7 @@
         <v>1531</v>
       </c>
       <c r="E293">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F293" t="s">
         <v>1607</v>
@@ -18566,7 +18566,7 @@
         <v>1531</v>
       </c>
       <c r="E294">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F294" t="s">
         <v>1607</v>
@@ -18601,7 +18601,7 @@
         <v>1532</v>
       </c>
       <c r="E295">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F295" t="s">
         <v>1607</v>
@@ -18636,7 +18636,7 @@
         <v>1533</v>
       </c>
       <c r="E296">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F296" t="s">
         <v>1608</v>
@@ -18671,7 +18671,7 @@
         <v>1533</v>
       </c>
       <c r="E297">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F297" t="s">
         <v>1607</v>
@@ -18706,7 +18706,7 @@
         <v>1533</v>
       </c>
       <c r="E298">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F298" t="s">
         <v>1607</v>
@@ -18741,7 +18741,7 @@
         <v>1533</v>
       </c>
       <c r="E299">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F299" t="s">
         <v>1610</v>
@@ -18776,7 +18776,7 @@
         <v>1533</v>
       </c>
       <c r="E300">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F300" t="s">
         <v>1607</v>
@@ -18811,7 +18811,7 @@
         <v>1533</v>
       </c>
       <c r="E301">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F301" t="s">
         <v>1607</v>
@@ -18846,7 +18846,7 @@
         <v>1533</v>
       </c>
       <c r="E302">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F302" t="s">
         <v>1607</v>
@@ -18881,7 +18881,7 @@
         <v>1533</v>
       </c>
       <c r="E303">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F303" t="s">
         <v>1607</v>
@@ -18916,7 +18916,7 @@
         <v>1534</v>
       </c>
       <c r="E304">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F304" t="s">
         <v>1607</v>
@@ -18951,7 +18951,7 @@
         <v>1534</v>
       </c>
       <c r="E305">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F305" t="s">
         <v>1607</v>
@@ -18986,7 +18986,7 @@
         <v>1534</v>
       </c>
       <c r="E306">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F306" t="s">
         <v>1607</v>
@@ -19021,7 +19021,7 @@
         <v>1534</v>
       </c>
       <c r="E307">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F307" t="s">
         <v>1607</v>
@@ -19056,7 +19056,7 @@
         <v>1535</v>
       </c>
       <c r="E308">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F308" t="s">
         <v>1607</v>
@@ -19091,7 +19091,7 @@
         <v>1535</v>
       </c>
       <c r="E309">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F309" t="s">
         <v>1607</v>
@@ -19126,7 +19126,7 @@
         <v>1536</v>
       </c>
       <c r="E310">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F310" t="s">
         <v>1607</v>
@@ -19164,7 +19164,7 @@
         <v>1536</v>
       </c>
       <c r="E311">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F311" t="s">
         <v>1607</v>
@@ -19199,7 +19199,7 @@
         <v>1537</v>
       </c>
       <c r="E312">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F312" t="s">
         <v>1607</v>
@@ -19234,7 +19234,7 @@
         <v>1537</v>
       </c>
       <c r="E313">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F313" t="s">
         <v>1607</v>
@@ -19269,7 +19269,7 @@
         <v>1537</v>
       </c>
       <c r="E314">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F314" t="s">
         <v>1607</v>
@@ -19304,7 +19304,7 @@
         <v>1537</v>
       </c>
       <c r="E315">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F315" t="s">
         <v>1607</v>
@@ -19342,7 +19342,7 @@
         <v>1537</v>
       </c>
       <c r="E316">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F316" t="s">
         <v>1607</v>
@@ -19377,7 +19377,7 @@
         <v>1537</v>
       </c>
       <c r="E317">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F317" t="s">
         <v>1607</v>
@@ -19412,7 +19412,7 @@
         <v>1538</v>
       </c>
       <c r="E318">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F318" t="s">
         <v>1607</v>
@@ -19447,7 +19447,7 @@
         <v>1538</v>
       </c>
       <c r="E319">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F319" t="s">
         <v>1607</v>
@@ -19482,7 +19482,7 @@
         <v>1539</v>
       </c>
       <c r="E320">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F320" t="s">
         <v>1607</v>
@@ -19517,7 +19517,7 @@
         <v>1539</v>
       </c>
       <c r="E321">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F321" t="s">
         <v>1607</v>
@@ -19552,7 +19552,7 @@
         <v>1540</v>
       </c>
       <c r="E322">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F322" t="s">
         <v>1607</v>
@@ -19587,7 +19587,7 @@
         <v>1540</v>
       </c>
       <c r="E323">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F323" t="s">
         <v>1607</v>
@@ -19622,7 +19622,7 @@
         <v>1540</v>
       </c>
       <c r="E324">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F324" t="s">
         <v>1607</v>
@@ -19657,7 +19657,7 @@
         <v>1540</v>
       </c>
       <c r="E325">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F325" t="s">
         <v>1607</v>
@@ -19692,7 +19692,7 @@
         <v>1541</v>
       </c>
       <c r="E326">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F326" t="s">
         <v>1607</v>
@@ -19727,7 +19727,7 @@
         <v>1541</v>
       </c>
       <c r="E327">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F327" t="s">
         <v>1607</v>
@@ -19762,7 +19762,7 @@
         <v>1541</v>
       </c>
       <c r="E328">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F328" t="s">
         <v>1607</v>
@@ -19797,7 +19797,7 @@
         <v>1541</v>
       </c>
       <c r="E329">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F329" t="s">
         <v>1607</v>
@@ -19832,7 +19832,7 @@
         <v>1542</v>
       </c>
       <c r="E330">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F330" t="s">
         <v>1607</v>
@@ -19867,7 +19867,7 @@
         <v>1542</v>
       </c>
       <c r="E331">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F331" t="s">
         <v>1607</v>
@@ -19902,7 +19902,7 @@
         <v>1543</v>
       </c>
       <c r="E332">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F332" t="s">
         <v>1607</v>
@@ -19937,7 +19937,7 @@
         <v>1543</v>
       </c>
       <c r="E333">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F333" t="s">
         <v>1607</v>
@@ -19972,7 +19972,7 @@
         <v>1543</v>
       </c>
       <c r="E334">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F334" t="s">
         <v>1607</v>
@@ -20007,7 +20007,7 @@
         <v>1543</v>
       </c>
       <c r="E335">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F335" t="s">
         <v>1607</v>
@@ -20042,7 +20042,7 @@
         <v>1543</v>
       </c>
       <c r="E336">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F336" t="s">
         <v>1607</v>
@@ -20077,7 +20077,7 @@
         <v>1544</v>
       </c>
       <c r="E337">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F337" t="s">
         <v>1607</v>
@@ -20112,7 +20112,7 @@
         <v>1544</v>
       </c>
       <c r="E338">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F338" t="s">
         <v>1607</v>
@@ -20147,7 +20147,7 @@
         <v>1544</v>
       </c>
       <c r="E339">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F339" t="s">
         <v>1607</v>
@@ -20182,7 +20182,7 @@
         <v>1545</v>
       </c>
       <c r="E340">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F340" t="s">
         <v>1607</v>
@@ -20217,7 +20217,7 @@
         <v>1545</v>
       </c>
       <c r="E341">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F341" t="s">
         <v>1607</v>
@@ -20252,7 +20252,7 @@
         <v>1546</v>
       </c>
       <c r="E342">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F342" t="s">
         <v>1607</v>
@@ -20287,7 +20287,7 @@
         <v>1546</v>
       </c>
       <c r="E343">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F343" t="s">
         <v>1607</v>
@@ -20322,7 +20322,7 @@
         <v>1546</v>
       </c>
       <c r="E344">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F344" t="s">
         <v>1607</v>
@@ -20357,7 +20357,7 @@
         <v>1546</v>
       </c>
       <c r="E345">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F345" t="s">
         <v>1607</v>
@@ -20392,7 +20392,7 @@
         <v>1546</v>
       </c>
       <c r="E346">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F346" t="s">
         <v>1607</v>
@@ -20427,7 +20427,7 @@
         <v>1546</v>
       </c>
       <c r="E347">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F347" t="s">
         <v>1607</v>
@@ -20462,7 +20462,7 @@
         <v>1546</v>
       </c>
       <c r="E348">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F348" t="s">
         <v>1607</v>
@@ -20497,7 +20497,7 @@
         <v>1546</v>
       </c>
       <c r="E349">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F349" t="s">
         <v>1607</v>
@@ -20532,7 +20532,7 @@
         <v>1547</v>
       </c>
       <c r="E350">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F350" t="s">
         <v>1607</v>
@@ -20567,7 +20567,7 @@
         <v>1547</v>
       </c>
       <c r="E351">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F351" t="s">
         <v>1607</v>
@@ -20602,7 +20602,7 @@
         <v>1547</v>
       </c>
       <c r="E352">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F352" t="s">
         <v>1607</v>
@@ -20637,7 +20637,7 @@
         <v>1548</v>
       </c>
       <c r="E353">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F353" t="s">
         <v>1607</v>
@@ -20672,7 +20672,7 @@
         <v>1548</v>
       </c>
       <c r="E354">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F354" t="s">
         <v>1607</v>
@@ -20707,7 +20707,7 @@
         <v>1549</v>
       </c>
       <c r="E355">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F355" t="s">
         <v>1607</v>
@@ -20742,7 +20742,7 @@
         <v>1550</v>
       </c>
       <c r="E356">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F356" t="s">
         <v>1609</v>
@@ -20777,7 +20777,7 @@
         <v>1550</v>
       </c>
       <c r="E357">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F357" t="s">
         <v>1607</v>
@@ -20812,7 +20812,7 @@
         <v>1550</v>
       </c>
       <c r="E358">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F358" t="s">
         <v>1607</v>
@@ -20847,7 +20847,7 @@
         <v>1550</v>
       </c>
       <c r="E359">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F359" t="s">
         <v>1607</v>
@@ -20882,7 +20882,7 @@
         <v>1550</v>
       </c>
       <c r="E360">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F360" t="s">
         <v>1607</v>
@@ -20917,7 +20917,7 @@
         <v>1550</v>
       </c>
       <c r="E361">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F361" t="s">
         <v>1607</v>
@@ -20952,7 +20952,7 @@
         <v>1551</v>
       </c>
       <c r="E362">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F362" t="s">
         <v>1607</v>
@@ -20987,7 +20987,7 @@
         <v>1551</v>
       </c>
       <c r="E363">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F363" t="s">
         <v>1607</v>
@@ -21022,7 +21022,7 @@
         <v>1552</v>
       </c>
       <c r="E364">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F364" t="s">
         <v>1607</v>
@@ -21057,7 +21057,7 @@
         <v>1552</v>
       </c>
       <c r="E365">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F365" t="s">
         <v>1607</v>
@@ -21092,7 +21092,7 @@
         <v>1552</v>
       </c>
       <c r="E366">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F366" t="s">
         <v>1607</v>
@@ -21127,7 +21127,7 @@
         <v>1553</v>
       </c>
       <c r="E367">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F367" t="s">
         <v>1607</v>
@@ -21162,7 +21162,7 @@
         <v>1554</v>
       </c>
       <c r="E368">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F368" t="s">
         <v>1607</v>
@@ -21197,7 +21197,7 @@
         <v>1555</v>
       </c>
       <c r="E369">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F369" t="s">
         <v>1607</v>
@@ -21232,7 +21232,7 @@
         <v>1555</v>
       </c>
       <c r="E370">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F370" t="s">
         <v>1607</v>
@@ -21267,7 +21267,7 @@
         <v>1556</v>
       </c>
       <c r="E371">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F371" t="s">
         <v>1607</v>
@@ -21302,7 +21302,7 @@
         <v>1556</v>
       </c>
       <c r="E372">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F372" t="s">
         <v>1607</v>
@@ -21337,7 +21337,7 @@
         <v>1556</v>
       </c>
       <c r="E373">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F373" t="s">
         <v>1607</v>
@@ -21372,7 +21372,7 @@
         <v>1557</v>
       </c>
       <c r="E374">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F374" t="s">
         <v>1607</v>
@@ -21407,7 +21407,7 @@
         <v>1557</v>
       </c>
       <c r="E375">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F375" t="s">
         <v>1607</v>
@@ -21442,7 +21442,7 @@
         <v>1557</v>
       </c>
       <c r="E376">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F376" t="s">
         <v>1607</v>
@@ -21477,7 +21477,7 @@
         <v>1557</v>
       </c>
       <c r="E377">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F377" t="s">
         <v>1607</v>
@@ -21512,7 +21512,7 @@
         <v>1557</v>
       </c>
       <c r="E378">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F378" t="s">
         <v>1607</v>
@@ -21547,7 +21547,7 @@
         <v>1557</v>
       </c>
       <c r="E379">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F379" t="s">
         <v>1607</v>
@@ -21582,7 +21582,7 @@
         <v>1557</v>
       </c>
       <c r="E380">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F380" t="s">
         <v>1607</v>
@@ -21617,7 +21617,7 @@
         <v>1557</v>
       </c>
       <c r="E381">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F381" t="s">
         <v>1607</v>
@@ -21652,7 +21652,7 @@
         <v>1557</v>
       </c>
       <c r="E382">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F382" t="s">
         <v>1607</v>
@@ -21687,7 +21687,7 @@
         <v>1557</v>
       </c>
       <c r="E383">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F383" t="s">
         <v>1607</v>
@@ -21722,7 +21722,7 @@
         <v>1558</v>
       </c>
       <c r="E384">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F384" t="s">
         <v>1607</v>
@@ -21757,7 +21757,7 @@
         <v>1558</v>
       </c>
       <c r="E385">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F385" t="s">
         <v>1607</v>
@@ -21792,7 +21792,7 @@
         <v>1558</v>
       </c>
       <c r="E386">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F386" t="s">
         <v>1607</v>
@@ -21827,7 +21827,7 @@
         <v>1558</v>
       </c>
       <c r="E387">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F387" t="s">
         <v>1607</v>
@@ -21862,7 +21862,7 @@
         <v>1559</v>
       </c>
       <c r="E388">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F388" t="s">
         <v>1610</v>
@@ -21897,7 +21897,7 @@
         <v>1559</v>
       </c>
       <c r="E389">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F389" t="s">
         <v>1607</v>
@@ -21932,7 +21932,7 @@
         <v>1560</v>
       </c>
       <c r="E390">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F390" t="s">
         <v>1607</v>
@@ -21967,7 +21967,7 @@
         <v>1560</v>
       </c>
       <c r="E391">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F391" t="s">
         <v>1607</v>
@@ -22002,7 +22002,7 @@
         <v>1560</v>
       </c>
       <c r="E392">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F392" t="s">
         <v>1607</v>
@@ -22037,7 +22037,7 @@
         <v>1560</v>
       </c>
       <c r="E393">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F393" t="s">
         <v>1607</v>
@@ -22072,7 +22072,7 @@
         <v>1560</v>
       </c>
       <c r="E394">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F394" t="s">
         <v>1611</v>
@@ -22110,7 +22110,7 @@
         <v>1560</v>
       </c>
       <c r="E395">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F395" t="s">
         <v>1607</v>
@@ -22145,7 +22145,7 @@
         <v>1560</v>
       </c>
       <c r="E396">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F396" t="s">
         <v>1607</v>
@@ -22180,7 +22180,7 @@
         <v>1561</v>
       </c>
       <c r="E397">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F397" t="s">
         <v>1607</v>
@@ -22215,7 +22215,7 @@
         <v>1561</v>
       </c>
       <c r="E398">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F398" t="s">
         <v>1607</v>
@@ -22250,7 +22250,7 @@
         <v>1561</v>
       </c>
       <c r="E399">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F399" t="s">
         <v>1607</v>
@@ -22285,7 +22285,7 @@
         <v>1561</v>
       </c>
       <c r="E400">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F400" t="s">
         <v>1607</v>
@@ -22323,7 +22323,7 @@
         <v>1561</v>
       </c>
       <c r="E401">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F401" t="s">
         <v>1607</v>
@@ -22358,7 +22358,7 @@
         <v>1561</v>
       </c>
       <c r="E402">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F402" t="s">
         <v>1607</v>
@@ -22393,7 +22393,7 @@
         <v>1561</v>
       </c>
       <c r="E403">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F403" t="s">
         <v>1607</v>
@@ -22428,7 +22428,7 @@
         <v>1561</v>
       </c>
       <c r="E404">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F404" t="s">
         <v>1607</v>
@@ -22463,7 +22463,7 @@
         <v>1561</v>
       </c>
       <c r="E405">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F405" t="s">
         <v>1607</v>
@@ -22498,7 +22498,7 @@
         <v>1562</v>
       </c>
       <c r="E406">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F406" t="s">
         <v>1608</v>
@@ -22533,7 +22533,7 @@
         <v>1563</v>
       </c>
       <c r="E407">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F407" t="s">
         <v>1609</v>
@@ -22568,7 +22568,7 @@
         <v>1563</v>
       </c>
       <c r="E408">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F408" t="s">
         <v>1611</v>
@@ -22603,7 +22603,7 @@
         <v>1564</v>
       </c>
       <c r="E409">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F409" t="s">
         <v>1607</v>
@@ -22638,7 +22638,7 @@
         <v>1565</v>
       </c>
       <c r="E410">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F410" t="s">
         <v>1607</v>
@@ -22673,7 +22673,7 @@
         <v>1565</v>
       </c>
       <c r="E411">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F411" t="s">
         <v>1607</v>
@@ -22708,7 +22708,7 @@
         <v>1566</v>
       </c>
       <c r="E412">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F412" t="s">
         <v>1607</v>
@@ -22743,7 +22743,7 @@
         <v>1567</v>
       </c>
       <c r="E413">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F413" t="s">
         <v>1610</v>
@@ -22778,7 +22778,7 @@
         <v>1567</v>
       </c>
       <c r="E414">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F414" t="s">
         <v>1607</v>
@@ -22813,7 +22813,7 @@
         <v>1567</v>
       </c>
       <c r="E415">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F415" t="s">
         <v>1607</v>
@@ -22848,7 +22848,7 @@
         <v>1567</v>
       </c>
       <c r="E416">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F416" t="s">
         <v>1607</v>
@@ -22883,7 +22883,7 @@
         <v>1567</v>
       </c>
       <c r="E417">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F417" t="s">
         <v>1607</v>
@@ -22918,7 +22918,7 @@
         <v>1567</v>
       </c>
       <c r="E418">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F418" t="s">
         <v>1607</v>
@@ -22953,7 +22953,7 @@
         <v>1568</v>
       </c>
       <c r="E419">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F419" t="s">
         <v>1607</v>
@@ -22988,7 +22988,7 @@
         <v>1568</v>
       </c>
       <c r="E420">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F420" t="s">
         <v>1607</v>
@@ -23023,7 +23023,7 @@
         <v>1568</v>
       </c>
       <c r="E421">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F421" t="s">
         <v>1607</v>
@@ -23058,7 +23058,7 @@
         <v>1568</v>
       </c>
       <c r="E422">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F422" t="s">
         <v>1607</v>
@@ -23093,7 +23093,7 @@
         <v>1569</v>
       </c>
       <c r="E423">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F423" t="s">
         <v>1607</v>
@@ -23128,7 +23128,7 @@
         <v>1569</v>
       </c>
       <c r="E424">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F424" t="s">
         <v>1607</v>
@@ -23163,7 +23163,7 @@
         <v>1569</v>
       </c>
       <c r="E425">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F425" t="s">
         <v>1607</v>
@@ -23201,7 +23201,7 @@
         <v>1569</v>
       </c>
       <c r="E426">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F426" t="s">
         <v>1607</v>
@@ -23236,7 +23236,7 @@
         <v>1570</v>
       </c>
       <c r="E427">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F427" t="s">
         <v>1607</v>
@@ -23271,7 +23271,7 @@
         <v>1570</v>
       </c>
       <c r="E428">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F428" t="s">
         <v>1607</v>
@@ -23306,7 +23306,7 @@
         <v>1570</v>
       </c>
       <c r="E429">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F429" t="s">
         <v>1607</v>
@@ -23341,7 +23341,7 @@
         <v>1570</v>
       </c>
       <c r="E430">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F430" t="s">
         <v>1607</v>
@@ -23376,7 +23376,7 @@
         <v>1570</v>
       </c>
       <c r="E431">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F431" t="s">
         <v>1607</v>
@@ -23411,7 +23411,7 @@
         <v>1571</v>
       </c>
       <c r="E432">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F432" t="s">
         <v>1607</v>
@@ -23446,7 +23446,7 @@
         <v>1571</v>
       </c>
       <c r="E433">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F433" t="s">
         <v>1607</v>
@@ -23481,7 +23481,7 @@
         <v>1572</v>
       </c>
       <c r="E434">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F434" t="s">
         <v>1607</v>
@@ -23516,7 +23516,7 @@
         <v>1572</v>
       </c>
       <c r="E435">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F435" t="s">
         <v>1607</v>
@@ -23551,7 +23551,7 @@
         <v>1572</v>
       </c>
       <c r="E436">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F436" t="s">
         <v>1607</v>
@@ -23586,7 +23586,7 @@
         <v>1572</v>
       </c>
       <c r="E437">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F437" t="s">
         <v>1607</v>
@@ -23621,7 +23621,7 @@
         <v>1572</v>
       </c>
       <c r="E438">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F438" t="s">
         <v>1607</v>
@@ -23656,7 +23656,7 @@
         <v>1572</v>
       </c>
       <c r="E439">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F439" t="s">
         <v>1607</v>
@@ -23691,7 +23691,7 @@
         <v>1572</v>
       </c>
       <c r="E440">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F440" t="s">
         <v>1607</v>
@@ -23726,7 +23726,7 @@
         <v>1572</v>
       </c>
       <c r="E441">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F441" t="s">
         <v>1607</v>
@@ -23761,7 +23761,7 @@
         <v>1572</v>
       </c>
       <c r="E442">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F442" t="s">
         <v>1607</v>
@@ -23796,7 +23796,7 @@
         <v>1572</v>
       </c>
       <c r="E443">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F443" t="s">
         <v>1607</v>
@@ -23831,7 +23831,7 @@
         <v>1573</v>
       </c>
       <c r="E444">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F444" t="s">
         <v>1607</v>
@@ -23866,7 +23866,7 @@
         <v>1573</v>
       </c>
       <c r="E445">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F445" t="s">
         <v>1607</v>
@@ -23901,7 +23901,7 @@
         <v>1573</v>
       </c>
       <c r="E446">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F446" t="s">
         <v>1608</v>
@@ -23936,7 +23936,7 @@
         <v>1574</v>
       </c>
       <c r="E447">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F447" t="s">
         <v>1607</v>
@@ -23971,7 +23971,7 @@
         <v>1574</v>
       </c>
       <c r="E448">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F448" t="s">
         <v>1607</v>
@@ -24006,7 +24006,7 @@
         <v>1574</v>
       </c>
       <c r="E449">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F449" t="s">
         <v>1607</v>
@@ -24041,7 +24041,7 @@
         <v>1574</v>
       </c>
       <c r="E450">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F450" t="s">
         <v>1607</v>
@@ -24076,7 +24076,7 @@
         <v>1574</v>
       </c>
       <c r="E451">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F451" t="s">
         <v>1607</v>
@@ -24111,7 +24111,7 @@
         <v>1574</v>
       </c>
       <c r="E452">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F452" t="s">
         <v>1607</v>
@@ -24146,7 +24146,7 @@
         <v>1574</v>
       </c>
       <c r="E453">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F453" t="s">
         <v>1610</v>
@@ -24181,7 +24181,7 @@
         <v>1575</v>
       </c>
       <c r="E454">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F454" t="s">
         <v>1607</v>
@@ -24216,7 +24216,7 @@
         <v>1575</v>
       </c>
       <c r="E455">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F455" t="s">
         <v>1607</v>
@@ -24251,7 +24251,7 @@
         <v>1575</v>
       </c>
       <c r="E456">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F456" t="s">
         <v>1607</v>
@@ -24286,7 +24286,7 @@
         <v>1575</v>
       </c>
       <c r="E457">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F457" t="s">
         <v>1607</v>
@@ -24321,7 +24321,7 @@
         <v>1576</v>
       </c>
       <c r="E458">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F458" t="s">
         <v>1607</v>
@@ -24356,7 +24356,7 @@
         <v>1576</v>
       </c>
       <c r="E459">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F459" t="s">
         <v>1610</v>
@@ -24391,7 +24391,7 @@
         <v>1576</v>
       </c>
       <c r="E460">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F460" t="s">
         <v>1607</v>
@@ -24426,7 +24426,7 @@
         <v>1576</v>
       </c>
       <c r="E461">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F461" t="s">
         <v>1607</v>
@@ -24461,7 +24461,7 @@
         <v>1576</v>
       </c>
       <c r="E462">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F462" t="s">
         <v>1607</v>
@@ -24496,7 +24496,7 @@
         <v>1576</v>
       </c>
       <c r="E463">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F463" t="s">
         <v>1609</v>
@@ -24534,7 +24534,7 @@
         <v>1576</v>
       </c>
       <c r="E464">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F464" t="s">
         <v>1607</v>
@@ -24569,7 +24569,7 @@
         <v>1576</v>
       </c>
       <c r="E465">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F465" t="s">
         <v>1611</v>
@@ -24604,7 +24604,7 @@
         <v>1576</v>
       </c>
       <c r="E466">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F466" t="s">
         <v>1607</v>
@@ -24639,7 +24639,7 @@
         <v>1576</v>
       </c>
       <c r="E467">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F467" t="s">
         <v>1607</v>
@@ -24674,7 +24674,7 @@
         <v>1577</v>
       </c>
       <c r="E468">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F468" t="s">
         <v>1607</v>
@@ -24709,7 +24709,7 @@
         <v>1577</v>
       </c>
       <c r="E469">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F469" t="s">
         <v>1607</v>
@@ -24744,7 +24744,7 @@
         <v>1577</v>
       </c>
       <c r="E470">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F470" t="s">
         <v>1607</v>
@@ -24779,7 +24779,7 @@
         <v>1577</v>
       </c>
       <c r="E471">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F471" t="s">
         <v>1607</v>
@@ -24814,7 +24814,7 @@
         <v>1577</v>
       </c>
       <c r="E472">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F472" t="s">
         <v>1607</v>
@@ -24849,7 +24849,7 @@
         <v>1577</v>
       </c>
       <c r="E473">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F473" t="s">
         <v>1607</v>
@@ -24884,7 +24884,7 @@
         <v>1577</v>
       </c>
       <c r="E474">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F474" t="s">
         <v>1609</v>
@@ -24919,7 +24919,7 @@
         <v>1577</v>
       </c>
       <c r="E475">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F475" t="s">
         <v>1607</v>
@@ -24954,7 +24954,7 @@
         <v>1577</v>
       </c>
       <c r="E476">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F476" t="s">
         <v>1607</v>
@@ -24989,7 +24989,7 @@
         <v>1578</v>
       </c>
       <c r="E477">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F477" t="s">
         <v>1607</v>
@@ -25024,7 +25024,7 @@
         <v>1578</v>
       </c>
       <c r="E478">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F478" t="s">
         <v>1607</v>
@@ -25059,7 +25059,7 @@
         <v>1578</v>
       </c>
       <c r="E479">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F479" t="s">
         <v>1607</v>
@@ -25094,7 +25094,7 @@
         <v>1578</v>
       </c>
       <c r="E480">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F480" t="s">
         <v>1607</v>
@@ -25129,7 +25129,7 @@
         <v>1578</v>
       </c>
       <c r="E481">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F481" t="s">
         <v>1607</v>
@@ -25164,7 +25164,7 @@
         <v>1579</v>
       </c>
       <c r="E482">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F482" t="s">
         <v>1607</v>
@@ -25199,7 +25199,7 @@
         <v>1579</v>
       </c>
       <c r="E483">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F483" t="s">
         <v>1607</v>
@@ -25234,7 +25234,7 @@
         <v>1579</v>
       </c>
       <c r="E484">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F484" t="s">
         <v>1607</v>
@@ -25269,7 +25269,7 @@
         <v>1579</v>
       </c>
       <c r="E485">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F485" t="s">
         <v>1607</v>
@@ -25304,7 +25304,7 @@
         <v>1579</v>
       </c>
       <c r="E486">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F486" t="s">
         <v>1607</v>
@@ -25342,7 +25342,7 @@
         <v>1580</v>
       </c>
       <c r="E487">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F487" t="s">
         <v>1607</v>
@@ -25377,7 +25377,7 @@
         <v>1580</v>
       </c>
       <c r="E488">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F488" t="s">
         <v>1607</v>
@@ -25412,7 +25412,7 @@
         <v>1580</v>
       </c>
       <c r="E489">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F489" t="s">
         <v>1607</v>
@@ -25447,7 +25447,7 @@
         <v>1580</v>
       </c>
       <c r="E490">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F490" t="s">
         <v>1607</v>
@@ -25482,7 +25482,7 @@
         <v>1580</v>
       </c>
       <c r="E491">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F491" t="s">
         <v>1607</v>
@@ -25517,7 +25517,7 @@
         <v>1580</v>
       </c>
       <c r="E492">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F492" t="s">
         <v>1607</v>
@@ -25552,7 +25552,7 @@
         <v>1581</v>
       </c>
       <c r="E493">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F493" t="s">
         <v>1607</v>
@@ -25587,7 +25587,7 @@
         <v>1581</v>
       </c>
       <c r="E494">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F494" t="s">
         <v>1607</v>
@@ -25622,7 +25622,7 @@
         <v>1581</v>
       </c>
       <c r="E495">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F495" t="s">
         <v>1607</v>
@@ -25657,7 +25657,7 @@
         <v>1582</v>
       </c>
       <c r="E496">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F496" t="s">
         <v>1607</v>
@@ -25692,7 +25692,7 @@
         <v>1583</v>
       </c>
       <c r="E497">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F497" t="s">
         <v>1607</v>
@@ -25727,7 +25727,7 @@
         <v>1583</v>
       </c>
       <c r="E498">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F498" t="s">
         <v>1607</v>
@@ -25762,7 +25762,7 @@
         <v>1583</v>
       </c>
       <c r="E499">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F499" t="s">
         <v>1609</v>
@@ -25800,7 +25800,7 @@
         <v>1583</v>
       </c>
       <c r="E500">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F500" t="s">
         <v>1607</v>
@@ -25835,7 +25835,7 @@
         <v>1583</v>
       </c>
       <c r="E501">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F501" t="s">
         <v>1607</v>
@@ -25870,7 +25870,7 @@
         <v>1584</v>
       </c>
       <c r="E502">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F502" t="s">
         <v>1607</v>
@@ -25905,7 +25905,7 @@
         <v>1584</v>
       </c>
       <c r="E503">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F503" t="s">
         <v>1607</v>
@@ -25940,7 +25940,7 @@
         <v>1584</v>
       </c>
       <c r="E504">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F504" t="s">
         <v>1607</v>
@@ -25975,7 +25975,7 @@
         <v>1584</v>
       </c>
       <c r="E505">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F505" t="s">
         <v>1607</v>
@@ -26010,7 +26010,7 @@
         <v>1584</v>
       </c>
       <c r="E506">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F506" t="s">
         <v>1607</v>
@@ -26045,7 +26045,7 @@
         <v>1585</v>
       </c>
       <c r="E507">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F507" t="s">
         <v>1607</v>
@@ -26080,7 +26080,7 @@
         <v>1585</v>
       </c>
       <c r="E508">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F508" t="s">
         <v>1607</v>
@@ -26115,7 +26115,7 @@
         <v>1585</v>
       </c>
       <c r="E509">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F509" t="s">
         <v>1607</v>
@@ -26150,7 +26150,7 @@
         <v>1585</v>
       </c>
       <c r="E510">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F510" t="s">
         <v>1607</v>
@@ -26185,7 +26185,7 @@
         <v>1585</v>
       </c>
       <c r="E511">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F511" t="s">
         <v>1607</v>
@@ -26220,7 +26220,7 @@
         <v>1585</v>
       </c>
       <c r="E512">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F512" t="s">
         <v>1607</v>
@@ -26255,7 +26255,7 @@
         <v>1585</v>
       </c>
       <c r="E513">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F513" t="s">
         <v>1607</v>
@@ -26290,7 +26290,7 @@
         <v>1585</v>
       </c>
       <c r="E514">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F514" t="s">
         <v>1607</v>
@@ -26325,7 +26325,7 @@
         <v>1586</v>
       </c>
       <c r="E515">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F515" t="s">
         <v>1607</v>
@@ -26360,7 +26360,7 @@
         <v>1586</v>
       </c>
       <c r="E516">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F516" t="s">
         <v>1607</v>
@@ -26395,7 +26395,7 @@
         <v>1587</v>
       </c>
       <c r="E517">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F517" t="s">
         <v>1607</v>
@@ -26430,7 +26430,7 @@
         <v>1587</v>
       </c>
       <c r="E518">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F518" t="s">
         <v>1607</v>
@@ -26465,7 +26465,7 @@
         <v>1587</v>
       </c>
       <c r="E519">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F519" t="s">
         <v>1607</v>
@@ -26500,7 +26500,7 @@
         <v>1587</v>
       </c>
       <c r="E520">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F520" t="s">
         <v>1611</v>
@@ -26538,7 +26538,7 @@
         <v>1587</v>
       </c>
       <c r="E521">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F521" t="s">
         <v>1607</v>
@@ -26573,7 +26573,7 @@
         <v>1587</v>
       </c>
       <c r="E522">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F522" t="s">
         <v>1611</v>
@@ -26608,7 +26608,7 @@
         <v>1588</v>
       </c>
       <c r="E523">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F523" t="s">
         <v>1607</v>
@@ -26643,7 +26643,7 @@
         <v>1589</v>
       </c>
       <c r="E524">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F524" t="s">
         <v>1607</v>
@@ -26678,7 +26678,7 @@
         <v>1589</v>
       </c>
       <c r="E525">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F525" t="s">
         <v>1607</v>
@@ -26713,7 +26713,7 @@
         <v>1589</v>
       </c>
       <c r="E526">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F526" t="s">
         <v>1607</v>
@@ -26748,7 +26748,7 @@
         <v>1589</v>
       </c>
       <c r="E527">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F527" t="s">
         <v>1607</v>
@@ -26783,7 +26783,7 @@
         <v>1590</v>
       </c>
       <c r="E528">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F528" t="s">
         <v>1607</v>
@@ -26818,7 +26818,7 @@
         <v>1590</v>
       </c>
       <c r="E529">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F529" t="s">
         <v>1611</v>
@@ -26853,7 +26853,7 @@
         <v>1590</v>
       </c>
       <c r="E530">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F530" t="s">
         <v>1607</v>
@@ -26888,7 +26888,7 @@
         <v>1590</v>
       </c>
       <c r="E531">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F531" t="s">
         <v>1607</v>
@@ -26923,7 +26923,7 @@
         <v>1590</v>
       </c>
       <c r="E532">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F532" t="s">
         <v>1607</v>
@@ -26958,7 +26958,7 @@
         <v>1591</v>
       </c>
       <c r="E533">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F533" t="s">
         <v>1607</v>
@@ -26993,7 +26993,7 @@
         <v>1591</v>
       </c>
       <c r="E534">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F534" t="s">
         <v>1611</v>
@@ -27028,7 +27028,7 @@
         <v>1591</v>
       </c>
       <c r="E535">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F535" t="s">
         <v>1609</v>
@@ -27063,7 +27063,7 @@
         <v>1591</v>
       </c>
       <c r="E536">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F536" t="s">
         <v>1607</v>
@@ -27098,7 +27098,7 @@
         <v>1591</v>
       </c>
       <c r="E537">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F537" t="s">
         <v>1607</v>
@@ -27133,7 +27133,7 @@
         <v>1592</v>
       </c>
       <c r="E538">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F538" t="s">
         <v>1607</v>
@@ -27168,7 +27168,7 @@
         <v>1592</v>
       </c>
       <c r="E539">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F539" t="s">
         <v>1607</v>
@@ -27203,7 +27203,7 @@
         <v>1592</v>
       </c>
       <c r="E540">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F540" t="s">
         <v>1607</v>
@@ -27238,7 +27238,7 @@
         <v>1592</v>
       </c>
       <c r="E541">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F541" t="s">
         <v>1607</v>
@@ -27273,7 +27273,7 @@
         <v>1592</v>
       </c>
       <c r="E542">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F542" t="s">
         <v>1607</v>
@@ -27308,7 +27308,7 @@
         <v>1592</v>
       </c>
       <c r="E543">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F543" t="s">
         <v>1607</v>
@@ -27343,7 +27343,7 @@
         <v>1593</v>
       </c>
       <c r="E544">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F544" t="s">
         <v>1607</v>
@@ -27378,7 +27378,7 @@
         <v>1593</v>
       </c>
       <c r="E545">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F545" t="s">
         <v>1607</v>
@@ -27413,7 +27413,7 @@
         <v>1593</v>
       </c>
       <c r="E546">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F546" t="s">
         <v>1607</v>
@@ -27448,7 +27448,7 @@
         <v>1593</v>
       </c>
       <c r="E547">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F547" t="s">
         <v>1607</v>
@@ -27483,7 +27483,7 @@
         <v>1593</v>
       </c>
       <c r="E548">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F548" t="s">
         <v>1607</v>
@@ -27518,7 +27518,7 @@
         <v>1593</v>
       </c>
       <c r="E549">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F549" t="s">
         <v>1607</v>
@@ -27553,7 +27553,7 @@
         <v>1593</v>
       </c>
       <c r="E550">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F550" t="s">
         <v>1607</v>
@@ -27588,7 +27588,7 @@
         <v>1593</v>
       </c>
       <c r="E551">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F551" t="s">
         <v>1607</v>
@@ -27623,7 +27623,7 @@
         <v>1593</v>
       </c>
       <c r="E552">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F552" t="s">
         <v>1607</v>
@@ -27658,7 +27658,7 @@
         <v>1593</v>
       </c>
       <c r="E553">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F553" t="s">
         <v>1607</v>
@@ -27693,7 +27693,7 @@
         <v>1593</v>
       </c>
       <c r="E554">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F554" t="s">
         <v>1607</v>
@@ -27728,7 +27728,7 @@
         <v>1593</v>
       </c>
       <c r="E555">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F555" t="s">
         <v>1607</v>
@@ -27763,7 +27763,7 @@
         <v>1593</v>
       </c>
       <c r="E556">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F556" t="s">
         <v>1607</v>
@@ -27798,7 +27798,7 @@
         <v>1593</v>
       </c>
       <c r="E557">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F557" t="s">
         <v>1607</v>
@@ -27833,7 +27833,7 @@
         <v>1593</v>
       </c>
       <c r="E558">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F558" t="s">
         <v>1607</v>
@@ -27868,7 +27868,7 @@
         <v>1593</v>
       </c>
       <c r="E559">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F559" t="s">
         <v>1607</v>
@@ -27903,7 +27903,7 @@
         <v>1593</v>
       </c>
       <c r="E560">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F560" t="s">
         <v>1607</v>
@@ -27938,7 +27938,7 @@
         <v>1593</v>
       </c>
       <c r="E561">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F561" t="s">
         <v>1607</v>
@@ -27973,7 +27973,7 @@
         <v>1593</v>
       </c>
       <c r="E562">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F562" t="s">
         <v>1607</v>
@@ -28008,7 +28008,7 @@
         <v>1593</v>
       </c>
       <c r="E563">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F563" t="s">
         <v>1607</v>
@@ -28043,7 +28043,7 @@
         <v>1593</v>
       </c>
       <c r="E564">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F564" t="s">
         <v>1607</v>
@@ -28078,7 +28078,7 @@
         <v>1593</v>
       </c>
       <c r="E565">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F565" t="s">
         <v>1607</v>
@@ -28113,7 +28113,7 @@
         <v>1593</v>
       </c>
       <c r="E566">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F566" t="s">
         <v>1607</v>
@@ -28148,7 +28148,7 @@
         <v>1593</v>
       </c>
       <c r="E567">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F567" t="s">
         <v>1607</v>
@@ -28183,7 +28183,7 @@
         <v>1593</v>
       </c>
       <c r="E568">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F568" t="s">
         <v>1607</v>
@@ -28218,7 +28218,7 @@
         <v>1593</v>
       </c>
       <c r="E569">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F569" t="s">
         <v>1607</v>
@@ -28253,7 +28253,7 @@
         <v>1593</v>
       </c>
       <c r="E570">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F570" t="s">
         <v>1609</v>
@@ -28291,7 +28291,7 @@
         <v>1594</v>
       </c>
       <c r="E571">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F571" t="s">
         <v>1607</v>
@@ -28326,7 +28326,7 @@
         <v>1594</v>
       </c>
       <c r="E572">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F572" t="s">
         <v>1607</v>
@@ -28361,7 +28361,7 @@
         <v>1594</v>
       </c>
       <c r="E573">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F573" t="s">
         <v>1607</v>
@@ -28396,7 +28396,7 @@
         <v>1594</v>
       </c>
       <c r="E574">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F574" t="s">
         <v>1607</v>
@@ -28431,7 +28431,7 @@
         <v>1594</v>
       </c>
       <c r="E575">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F575" t="s">
         <v>1607</v>
@@ -28466,7 +28466,7 @@
         <v>1594</v>
       </c>
       <c r="E576">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F576" t="s">
         <v>1607</v>
@@ -28501,7 +28501,7 @@
         <v>1594</v>
       </c>
       <c r="E577">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F577" t="s">
         <v>1607</v>
@@ -28536,7 +28536,7 @@
         <v>1595</v>
       </c>
       <c r="E578">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F578" t="s">
         <v>1607</v>
@@ -28571,7 +28571,7 @@
         <v>1595</v>
       </c>
       <c r="E579">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F579" t="s">
         <v>1607</v>
@@ -28606,7 +28606,7 @@
         <v>1596</v>
       </c>
       <c r="E580">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F580" t="s">
         <v>1607</v>
@@ -28641,7 +28641,7 @@
         <v>1596</v>
       </c>
       <c r="E581">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F581" t="s">
         <v>1609</v>
@@ -28679,7 +28679,7 @@
         <v>1596</v>
       </c>
       <c r="E582">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F582" t="s">
         <v>1609</v>
@@ -28717,7 +28717,7 @@
         <v>1597</v>
       </c>
       <c r="E583">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F583" t="s">
         <v>1609</v>
@@ -28755,7 +28755,7 @@
         <v>1597</v>
       </c>
       <c r="E584">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F584" t="s">
         <v>1607</v>
@@ -28790,7 +28790,7 @@
         <v>1597</v>
       </c>
       <c r="E585">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F585" t="s">
         <v>1607</v>
@@ -28825,7 +28825,7 @@
         <v>1597</v>
       </c>
       <c r="E586">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F586" t="s">
         <v>1609</v>
@@ -28863,7 +28863,7 @@
         <v>1597</v>
       </c>
       <c r="E587">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F587" t="s">
         <v>1607</v>
@@ -28898,7 +28898,7 @@
         <v>1597</v>
       </c>
       <c r="E588">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F588" t="s">
         <v>1607</v>
@@ -28933,7 +28933,7 @@
         <v>1597</v>
       </c>
       <c r="E589">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F589" t="s">
         <v>1607</v>
@@ -28968,7 +28968,7 @@
         <v>1597</v>
       </c>
       <c r="E590">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F590" t="s">
         <v>1607</v>
@@ -29006,7 +29006,7 @@
         <v>1597</v>
       </c>
       <c r="E591">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F591" t="s">
         <v>1609</v>
@@ -29041,7 +29041,7 @@
         <v>1597</v>
       </c>
       <c r="E592">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F592" t="s">
         <v>1607</v>
@@ -29076,7 +29076,7 @@
         <v>1597</v>
       </c>
       <c r="E593">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F593" t="s">
         <v>1607</v>
@@ -29111,7 +29111,7 @@
         <v>1598</v>
       </c>
       <c r="E594">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F594" t="s">
         <v>1607</v>
@@ -29149,7 +29149,7 @@
         <v>1598</v>
       </c>
       <c r="E595">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F595" t="s">
         <v>1611</v>
@@ -29184,7 +29184,7 @@
         <v>1598</v>
       </c>
       <c r="E596">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F596" t="s">
         <v>1609</v>
@@ -29219,7 +29219,7 @@
         <v>1598</v>
       </c>
       <c r="E597">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F597" t="s">
         <v>1607</v>
@@ -29254,7 +29254,7 @@
         <v>1598</v>
       </c>
       <c r="E598">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F598" t="s">
         <v>1609</v>
@@ -29292,7 +29292,7 @@
         <v>1598</v>
       </c>
       <c r="E599">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F599" t="s">
         <v>1607</v>
@@ -29327,7 +29327,7 @@
         <v>1598</v>
       </c>
       <c r="E600">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F600" t="s">
         <v>1607</v>
@@ -29362,7 +29362,7 @@
         <v>1598</v>
       </c>
       <c r="E601">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F601" t="s">
         <v>1607</v>
@@ -29397,7 +29397,7 @@
         <v>1598</v>
       </c>
       <c r="E602">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F602" t="s">
         <v>1607</v>
@@ -29432,7 +29432,7 @@
         <v>1598</v>
       </c>
       <c r="E603">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F603" t="s">
         <v>1607</v>
@@ -29467,7 +29467,7 @@
         <v>1599</v>
       </c>
       <c r="E604">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F604" t="s">
         <v>1607</v>
@@ -29505,7 +29505,7 @@
         <v>1599</v>
       </c>
       <c r="E605">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F605" t="s">
         <v>1607</v>
@@ -29540,7 +29540,7 @@
         <v>1600</v>
       </c>
       <c r="E606">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F606" t="s">
         <v>1607</v>
@@ -29575,7 +29575,7 @@
         <v>1600</v>
       </c>
       <c r="E607">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F607" t="s">
         <v>1609</v>
@@ -29613,7 +29613,7 @@
         <v>1600</v>
       </c>
       <c r="E608">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F608" t="s">
         <v>1607</v>
@@ -29648,7 +29648,7 @@
         <v>1600</v>
       </c>
       <c r="E609">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F609" t="s">
         <v>1607</v>
@@ -29683,7 +29683,7 @@
         <v>1600</v>
       </c>
       <c r="E610">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F610" t="s">
         <v>1607</v>
@@ -29718,7 +29718,7 @@
         <v>1600</v>
       </c>
       <c r="E611">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F611" t="s">
         <v>1607</v>
@@ -29753,7 +29753,7 @@
         <v>1600</v>
       </c>
       <c r="E612">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F612" t="s">
         <v>1607</v>
@@ -29788,7 +29788,7 @@
         <v>1600</v>
       </c>
       <c r="E613">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F613" t="s">
         <v>1609</v>
@@ -29823,7 +29823,7 @@
         <v>1600</v>
       </c>
       <c r="E614">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F614" t="s">
         <v>1607</v>
@@ -29858,7 +29858,7 @@
         <v>1600</v>
       </c>
       <c r="E615">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F615" t="s">
         <v>1607</v>
@@ -29893,7 +29893,7 @@
         <v>1601</v>
       </c>
       <c r="E616">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F616" t="s">
         <v>1607</v>
@@ -29928,7 +29928,7 @@
         <v>1601</v>
       </c>
       <c r="E617">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F617" t="s">
         <v>1607</v>
@@ -29963,7 +29963,7 @@
         <v>1601</v>
       </c>
       <c r="E618">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F618" t="s">
         <v>1607</v>
@@ -29998,7 +29998,7 @@
         <v>1601</v>
       </c>
       <c r="E619">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F619" t="s">
         <v>1607</v>
@@ -30033,7 +30033,7 @@
         <v>1601</v>
       </c>
       <c r="E620">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F620" t="s">
         <v>1609</v>
@@ -30071,7 +30071,7 @@
         <v>1601</v>
       </c>
       <c r="E621">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F621" t="s">
         <v>1607</v>
@@ -30106,7 +30106,7 @@
         <v>1601</v>
       </c>
       <c r="E622">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F622" t="s">
         <v>1607</v>
@@ -30141,7 +30141,7 @@
         <v>1601</v>
       </c>
       <c r="E623">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F623" t="s">
         <v>1607</v>
@@ -30176,7 +30176,7 @@
         <v>1601</v>
       </c>
       <c r="E624">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F624" t="s">
         <v>1607</v>
@@ -30211,7 +30211,7 @@
         <v>1601</v>
       </c>
       <c r="E625">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F625" t="s">
         <v>1609</v>
@@ -30246,7 +30246,7 @@
         <v>1601</v>
       </c>
       <c r="E626">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F626" t="s">
         <v>1607</v>
@@ -30281,7 +30281,7 @@
         <v>1601</v>
       </c>
       <c r="E627">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F627" t="s">
         <v>1611</v>
@@ -30316,7 +30316,7 @@
         <v>1601</v>
       </c>
       <c r="E628">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F628" t="s">
         <v>1607</v>
@@ -30351,7 +30351,7 @@
         <v>1602</v>
       </c>
       <c r="E629">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F629" t="s">
         <v>1609</v>
@@ -30389,7 +30389,7 @@
         <v>1602</v>
       </c>
       <c r="E630">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F630" t="s">
         <v>1607</v>
@@ -30424,7 +30424,7 @@
         <v>1602</v>
       </c>
       <c r="E631">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F631" t="s">
         <v>1607</v>
@@ -30459,7 +30459,7 @@
         <v>1602</v>
       </c>
       <c r="E632">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F632" t="s">
         <v>1607</v>
@@ -30494,7 +30494,7 @@
         <v>1602</v>
       </c>
       <c r="E633">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F633" t="s">
         <v>1607</v>
@@ -30529,7 +30529,7 @@
         <v>1602</v>
       </c>
       <c r="E634">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F634" t="s">
         <v>1607</v>
@@ -30564,7 +30564,7 @@
         <v>1602</v>
       </c>
       <c r="E635">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F635" t="s">
         <v>1607</v>
@@ -30599,7 +30599,7 @@
         <v>1602</v>
       </c>
       <c r="E636">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F636" t="s">
         <v>1607</v>
@@ -30634,7 +30634,7 @@
         <v>1602</v>
       </c>
       <c r="E637">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F637" t="s">
         <v>1607</v>
@@ -30672,7 +30672,7 @@
         <v>1602</v>
       </c>
       <c r="E638">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F638" t="s">
         <v>1609</v>
@@ -30710,7 +30710,7 @@
         <v>1602</v>
       </c>
       <c r="E639">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F639" t="s">
         <v>1607</v>
@@ -30745,7 +30745,7 @@
         <v>1602</v>
       </c>
       <c r="E640">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F640" t="s">
         <v>1609</v>
@@ -30780,7 +30780,7 @@
         <v>1602</v>
       </c>
       <c r="E641">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F641" t="s">
         <v>1609</v>
@@ -30815,7 +30815,7 @@
         <v>1602</v>
       </c>
       <c r="E642">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F642" t="s">
         <v>1607</v>
@@ -30850,7 +30850,7 @@
         <v>1603</v>
       </c>
       <c r="E643">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F643" t="s">
         <v>1607</v>
@@ -30885,7 +30885,7 @@
         <v>1603</v>
       </c>
       <c r="E644">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F644" t="s">
         <v>1607</v>
@@ -30920,7 +30920,7 @@
         <v>1603</v>
       </c>
       <c r="E645">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F645" t="s">
         <v>1607</v>
@@ -30955,7 +30955,7 @@
         <v>1603</v>
       </c>
       <c r="E646">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F646" t="s">
         <v>1607</v>
@@ -30990,7 +30990,7 @@
         <v>1603</v>
       </c>
       <c r="E647">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F647" t="s">
         <v>1607</v>
@@ -31025,7 +31025,7 @@
         <v>1603</v>
       </c>
       <c r="E648">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F648" t="s">
         <v>1607</v>
@@ -31060,7 +31060,7 @@
         <v>1603</v>
       </c>
       <c r="E649">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F649" t="s">
         <v>1607</v>
@@ -31095,7 +31095,7 @@
         <v>1603</v>
       </c>
       <c r="E650">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F650" t="s">
         <v>1607</v>
@@ -31130,7 +31130,7 @@
         <v>1603</v>
       </c>
       <c r="E651">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F651" t="s">
         <v>1607</v>
@@ -31165,7 +31165,7 @@
         <v>1603</v>
       </c>
       <c r="E652">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F652" t="s">
         <v>1607</v>
@@ -31203,7 +31203,7 @@
         <v>1604</v>
       </c>
       <c r="E653">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F653" t="s">
         <v>1607</v>
@@ -31238,7 +31238,7 @@
         <v>1604</v>
       </c>
       <c r="E654">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F654" t="s">
         <v>1607</v>
@@ -31273,7 +31273,7 @@
         <v>1605</v>
       </c>
       <c r="E655">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F655" t="s">
         <v>1607</v>
@@ -31311,7 +31311,7 @@
         <v>1605</v>
       </c>
       <c r="E656">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F656" t="s">
         <v>1607</v>
@@ -31346,7 +31346,7 @@
         <v>1605</v>
       </c>
       <c r="E657">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F657" t="s">
         <v>1607</v>
@@ -31381,7 +31381,7 @@
         <v>1605</v>
       </c>
       <c r="E658">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F658" t="s">
         <v>1607</v>
@@ -31419,7 +31419,7 @@
         <v>1605</v>
       </c>
       <c r="E659">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F659" t="s">
         <v>1607</v>
@@ -31457,7 +31457,7 @@
         <v>1605</v>
       </c>
       <c r="E660">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F660" t="s">
         <v>1607</v>
@@ -31492,7 +31492,7 @@
         <v>1605</v>
       </c>
       <c r="E661">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F661" t="s">
         <v>1607</v>
@@ -31527,7 +31527,7 @@
         <v>1605</v>
       </c>
       <c r="E662">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F662" t="s">
         <v>1607</v>
@@ -31562,7 +31562,7 @@
         <v>1606</v>
       </c>
       <c r="E663">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F663" t="s">
         <v>1607</v>
@@ -31597,7 +31597,7 @@
         <v>1606</v>
       </c>
       <c r="E664">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F664" t="s">
         <v>1607</v>
@@ -31632,7 +31632,7 @@
         <v>1606</v>
       </c>
       <c r="E665">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F665" t="s">
         <v>1607</v>
@@ -31667,7 +31667,7 @@
         <v>1606</v>
       </c>
       <c r="E666">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F666" t="s">
         <v>1607</v>
@@ -31702,7 +31702,7 @@
         <v>1606</v>
       </c>
       <c r="E667">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F667" t="s">
         <v>1607</v>
@@ -31737,7 +31737,7 @@
         <v>1606</v>
       </c>
       <c r="E668">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F668" t="s">
         <v>1607</v>
@@ -31772,7 +31772,7 @@
         <v>1606</v>
       </c>
       <c r="E669">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F669" t="s">
         <v>1607</v>
@@ -31807,7 +31807,7 @@
         <v>1606</v>
       </c>
       <c r="E670">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F670" t="s">
         <v>1607</v>
@@ -31842,7 +31842,7 @@
         <v>1606</v>
       </c>
       <c r="E671">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F671" t="s">
         <v>1607</v>
@@ -31877,7 +31877,7 @@
         <v>1606</v>
       </c>
       <c r="E672">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F672" t="s">
         <v>1607</v>
@@ -31912,7 +31912,7 @@
         <v>1606</v>
       </c>
       <c r="E673">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F673" t="s">
         <v>1607</v>
@@ -31947,7 +31947,7 @@
         <v>1606</v>
       </c>
       <c r="E674">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F674" t="s">
         <v>1607</v>
@@ -31985,7 +31985,7 @@
         <v>1606</v>
       </c>
       <c r="E675">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F675" t="s">
         <v>1607</v>
@@ -32023,7 +32023,7 @@
         <v>1606</v>
       </c>
       <c r="E676">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F676" t="s">
         <v>1607</v>
@@ -32061,7 +32061,7 @@
         <v>1606</v>
       </c>
       <c r="E677">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F677" t="s">
         <v>1607</v>
@@ -32084,7 +32084,7 @@
     </row>
     <row r="678" spans="1:12">
       <c r="A678" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B678" t="s">
         <v>712</v>
@@ -32092,26 +32092,32 @@
       <c r="C678" t="s">
         <v>1387</v>
       </c>
+      <c r="D678" t="s">
+        <v>1606</v>
+      </c>
       <c r="E678">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F678" t="s">
         <v>1607</v>
       </c>
       <c r="G678" t="s">
-        <v>1612</v>
+        <v>1614</v>
+      </c>
+      <c r="H678" t="s">
+        <v>1637</v>
       </c>
       <c r="I678" t="s">
-        <v>1747</v>
+        <v>1759</v>
       </c>
       <c r="J678" t="s">
         <v>2419</v>
       </c>
       <c r="K678" t="s">
-        <v>2546</v>
+        <v>2525</v>
       </c>
       <c r="L678" t="s">
-        <v>2635</v>
+        <v>2583</v>
       </c>
     </row>
     <row r="679" spans="1:12">
@@ -32143,12 +32149,12 @@
         <v>2546</v>
       </c>
       <c r="L679" t="s">
-        <v>2636</v>
+        <v>2635</v>
       </c>
     </row>
     <row r="680" spans="1:12">
       <c r="A680" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="B680" t="s">
         <v>714</v>
@@ -32156,9 +32162,6 @@
       <c r="C680" t="s">
         <v>1389</v>
       </c>
-      <c r="D680" t="s">
-        <v>1606</v>
-      </c>
       <c r="E680">
         <v>0</v>
       </c>
@@ -32166,22 +32169,19 @@
         <v>1607</v>
       </c>
       <c r="G680" t="s">
-        <v>1614</v>
-      </c>
-      <c r="H680" t="s">
-        <v>1637</v>
+        <v>1612</v>
       </c>
       <c r="I680" t="s">
-        <v>1759</v>
+        <v>1747</v>
       </c>
       <c r="J680" t="s">
         <v>2421</v>
       </c>
       <c r="K680" t="s">
-        <v>2525</v>
+        <v>2546</v>
       </c>
       <c r="L680" t="s">
-        <v>2583</v>
+        <v>2636</v>
       </c>
     </row>
   </sheetData>

--- a/BacklogGATEAutoCompleto.xlsx
+++ b/BacklogGATEAutoCompleto.xlsx
@@ -7834,7 +7834,7 @@
     <t>BIOLOGIA,RESÍDUOS SÓLIDOS</t>
   </si>
   <si>
-    <t>ENGENHARIA CIVIL,ECONOMICIDADE OBRAS</t>
+    <t>ECONOMICIDADE OBRAS,ENGENHARIA CIVIL</t>
   </si>
   <si>
     <t>RECURSOS HÍDRICOS,URBANISMO</t>
@@ -7888,7 +7888,7 @@
     <t>AVALIAÇÃO DE IMÓVEIS,ECONOMICIDADE CONTÁBIL</t>
   </si>
   <si>
-    <t>ECONOMICIDADE CONTÁBIL,ECONOMICIDADE OBRAS</t>
+    <t>ECONOMICIDADE OBRAS,ECONOMICIDADE CONTÁBIL</t>
   </si>
   <si>
     <t>ENGENHARIA CIVIL,MOBILIDADE E TRANSPORTE</t>
@@ -7909,21 +7909,21 @@
     <t>ECONOMICIDADE CONTÁBIL,ECONOMICIDADE CONTÁBIL</t>
   </si>
   <si>
+    <t>PATRIMÔNIO HISTÓRICO E CULTURAL,FENOMENOS DE ENERGIA E INFORMAÇÃO</t>
+  </si>
+  <si>
     <t>RECURSOS HÍDRICOS,VALORAÇÃO DANOS AMBIENTAIS</t>
   </si>
   <si>
-    <t>ASSISTÊNCIA SOCIAL,EDIFICAÇÕES</t>
-  </si>
-  <si>
-    <t>ECONOMICIDADE OBRAS,AVALIAÇÃO DE IMÓVEIS</t>
+    <t>EDIFICAÇÕES,ASSISTÊNCIA SOCIAL</t>
+  </si>
+  <si>
+    <t>AVALIAÇÃO DE IMÓVEIS,ECONOMICIDADE OBRAS</t>
   </si>
   <si>
     <t>ENGENHARIA FLORESTAL,BIOLOGIA</t>
   </si>
   <si>
-    <t>URBANISMO,BIOLOGIA</t>
-  </si>
-  <si>
     <t>FENOMENOS DE ENERGIA E INFORMAÇÃO,ENGENHARIA CIVIL</t>
   </si>
   <si>
@@ -7933,7 +7933,7 @@
     <t>GEOTECNIA,ENGENHARIA CIVIL</t>
   </si>
   <si>
-    <t>ASSISTÊNCIA SOCIAL,AVALIAÇÃO DE IMÓVEIS,SAÚDE MENTAL,MOBILIDADE E TRANSPORTE,PSICOLOGIA,ORÇAMENTO,ECONOMICIDADE CONTÁBIL,URBANISMO,SAÚDE,ECONOMIA</t>
+    <t>AVALIAÇÃO DE IMÓVEIS,MOBILIDADE E TRANSPORTE,ORÇAMENTO,SAÚDE MENTAL,ECONOMIA,ECONOMICIDADE CONTÁBIL,URBANISMO,ASSISTÊNCIA SOCIAL,SAÚDE,PSICOLOGIA</t>
   </si>
 </sst>
 </file>
@@ -30591,7 +30591,7 @@
         <v>2544</v>
       </c>
       <c r="L635" t="s">
-        <v>2613</v>
+        <v>2631</v>
       </c>
     </row>
     <row r="636" spans="1:12">
@@ -30772,7 +30772,7 @@
         <v>2436</v>
       </c>
       <c r="L640" t="s">
-        <v>2631</v>
+        <v>2632</v>
       </c>
     </row>
     <row r="641" spans="1:12">
@@ -31195,7 +31195,7 @@
         <v>2547</v>
       </c>
       <c r="L652" t="s">
-        <v>2632</v>
+        <v>2633</v>
       </c>
     </row>
     <row r="653" spans="1:12">
@@ -31230,7 +31230,7 @@
         <v>2452</v>
       </c>
       <c r="L653" t="s">
-        <v>2609</v>
+        <v>2588</v>
       </c>
     </row>
     <row r="654" spans="1:12">
@@ -31338,7 +31338,7 @@
         <v>2467</v>
       </c>
       <c r="L656" t="s">
-        <v>2633</v>
+        <v>2634</v>
       </c>
     </row>
     <row r="657" spans="1:12">
@@ -31411,7 +31411,7 @@
         <v>2430</v>
       </c>
       <c r="L658" t="s">
-        <v>2634</v>
+        <v>2635</v>
       </c>
     </row>
     <row r="659" spans="1:12">
@@ -31449,7 +31449,7 @@
         <v>2441</v>
       </c>
       <c r="L659" t="s">
-        <v>2635</v>
+        <v>2552</v>
       </c>
     </row>
     <row r="660" spans="1:12">

--- a/BacklogGATEAutoCompleto.xlsx
+++ b/BacklogGATEAutoCompleto.xlsx
@@ -8310,7 +8310,7 @@
         <v>1386</v>
       </c>
       <c r="E2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="F2" t="s">
         <v>1603</v>
@@ -8345,7 +8345,7 @@
         <v>1387</v>
       </c>
       <c r="E3">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="F3" t="s">
         <v>1603</v>
@@ -8380,7 +8380,7 @@
         <v>1388</v>
       </c>
       <c r="E4">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="F4" t="s">
         <v>1603</v>
@@ -8415,7 +8415,7 @@
         <v>1389</v>
       </c>
       <c r="E5">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F5" t="s">
         <v>1603</v>
@@ -8450,7 +8450,7 @@
         <v>1389</v>
       </c>
       <c r="E6">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F6" t="s">
         <v>1603</v>
@@ -8485,7 +8485,7 @@
         <v>1390</v>
       </c>
       <c r="E7">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="F7" t="s">
         <v>1603</v>
@@ -8520,7 +8520,7 @@
         <v>1391</v>
       </c>
       <c r="E8">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="F8" t="s">
         <v>1603</v>
@@ -8555,7 +8555,7 @@
         <v>1392</v>
       </c>
       <c r="E9">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="F9" t="s">
         <v>1603</v>
@@ -8590,7 +8590,7 @@
         <v>1393</v>
       </c>
       <c r="E10">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="F10" t="s">
         <v>1603</v>
@@ -8625,7 +8625,7 @@
         <v>1394</v>
       </c>
       <c r="E11">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="F11" t="s">
         <v>1603</v>
@@ -8660,7 +8660,7 @@
         <v>1395</v>
       </c>
       <c r="E12">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F12" t="s">
         <v>1603</v>
@@ -8695,7 +8695,7 @@
         <v>1396</v>
       </c>
       <c r="E13">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="F13" t="s">
         <v>1603</v>
@@ -8730,7 +8730,7 @@
         <v>1397</v>
       </c>
       <c r="E14">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="F14" t="s">
         <v>1603</v>
@@ -8765,7 +8765,7 @@
         <v>1398</v>
       </c>
       <c r="E15">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="F15" t="s">
         <v>1603</v>
@@ -8800,7 +8800,7 @@
         <v>1399</v>
       </c>
       <c r="E16">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="F16" t="s">
         <v>1603</v>
@@ -8835,7 +8835,7 @@
         <v>1399</v>
       </c>
       <c r="E17">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="F17" t="s">
         <v>1603</v>
@@ -8870,7 +8870,7 @@
         <v>1400</v>
       </c>
       <c r="E18">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F18" t="s">
         <v>1603</v>
@@ -8905,7 +8905,7 @@
         <v>1401</v>
       </c>
       <c r="E19">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="F19" t="s">
         <v>1603</v>
@@ -8940,7 +8940,7 @@
         <v>1402</v>
       </c>
       <c r="E20">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="F20" t="s">
         <v>1603</v>
@@ -8975,7 +8975,7 @@
         <v>1402</v>
       </c>
       <c r="E21">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="F21" t="s">
         <v>1603</v>
@@ -9010,7 +9010,7 @@
         <v>1403</v>
       </c>
       <c r="E22">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="F22" t="s">
         <v>1603</v>
@@ -9045,7 +9045,7 @@
         <v>1404</v>
       </c>
       <c r="E23">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="F23" t="s">
         <v>1603</v>
@@ -9080,7 +9080,7 @@
         <v>1405</v>
       </c>
       <c r="E24">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="F24" t="s">
         <v>1603</v>
@@ -9115,7 +9115,7 @@
         <v>1406</v>
       </c>
       <c r="E25">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="F25" t="s">
         <v>1603</v>
@@ -9150,7 +9150,7 @@
         <v>1407</v>
       </c>
       <c r="E26">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F26" t="s">
         <v>1603</v>
@@ -9188,7 +9188,7 @@
         <v>1408</v>
       </c>
       <c r="E27">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F27" t="s">
         <v>1603</v>
@@ -9223,7 +9223,7 @@
         <v>1409</v>
       </c>
       <c r="E28">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F28" t="s">
         <v>1603</v>
@@ -9258,7 +9258,7 @@
         <v>1410</v>
       </c>
       <c r="E29">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F29" t="s">
         <v>1603</v>
@@ -9293,7 +9293,7 @@
         <v>1411</v>
       </c>
       <c r="E30">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F30" t="s">
         <v>1603</v>
@@ -9328,7 +9328,7 @@
         <v>1411</v>
       </c>
       <c r="E31">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F31" t="s">
         <v>1603</v>
@@ -9363,7 +9363,7 @@
         <v>1412</v>
       </c>
       <c r="E32">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F32" t="s">
         <v>1603</v>
@@ -9398,7 +9398,7 @@
         <v>1413</v>
       </c>
       <c r="E33">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="F33" t="s">
         <v>1603</v>
@@ -9433,7 +9433,7 @@
         <v>1414</v>
       </c>
       <c r="E34">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F34" t="s">
         <v>1603</v>
@@ -9468,7 +9468,7 @@
         <v>1415</v>
       </c>
       <c r="E35">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F35" t="s">
         <v>1603</v>
@@ -9503,7 +9503,7 @@
         <v>1416</v>
       </c>
       <c r="E36">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="F36" t="s">
         <v>1603</v>
@@ -9538,7 +9538,7 @@
         <v>1417</v>
       </c>
       <c r="E37">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F37" t="s">
         <v>1603</v>
@@ -9573,7 +9573,7 @@
         <v>1418</v>
       </c>
       <c r="E38">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F38" t="s">
         <v>1603</v>
@@ -9608,7 +9608,7 @@
         <v>1419</v>
       </c>
       <c r="E39">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F39" t="s">
         <v>1603</v>
@@ -9643,7 +9643,7 @@
         <v>1419</v>
       </c>
       <c r="E40">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F40" t="s">
         <v>1603</v>
@@ -9678,7 +9678,7 @@
         <v>1420</v>
       </c>
       <c r="E41">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F41" t="s">
         <v>1603</v>
@@ -9713,7 +9713,7 @@
         <v>1420</v>
       </c>
       <c r="E42">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F42" t="s">
         <v>1603</v>
@@ -9748,7 +9748,7 @@
         <v>1421</v>
       </c>
       <c r="E43">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F43" t="s">
         <v>1603</v>
@@ -9783,7 +9783,7 @@
         <v>1422</v>
       </c>
       <c r="E44">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F44" t="s">
         <v>1603</v>
@@ -9818,7 +9818,7 @@
         <v>1423</v>
       </c>
       <c r="E45">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F45" t="s">
         <v>1603</v>
@@ -9853,7 +9853,7 @@
         <v>1424</v>
       </c>
       <c r="E46">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F46" t="s">
         <v>1603</v>
@@ -9888,7 +9888,7 @@
         <v>1424</v>
       </c>
       <c r="E47">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F47" t="s">
         <v>1603</v>
@@ -9923,7 +9923,7 @@
         <v>1425</v>
       </c>
       <c r="E48">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F48" t="s">
         <v>1603</v>
@@ -9958,7 +9958,7 @@
         <v>1426</v>
       </c>
       <c r="E49">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F49" t="s">
         <v>1603</v>
@@ -9993,7 +9993,7 @@
         <v>1427</v>
       </c>
       <c r="E50">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F50" t="s">
         <v>1603</v>
@@ -10028,7 +10028,7 @@
         <v>1427</v>
       </c>
       <c r="E51">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F51" t="s">
         <v>1603</v>
@@ -10063,7 +10063,7 @@
         <v>1428</v>
       </c>
       <c r="E52">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F52" t="s">
         <v>1603</v>
@@ -10098,7 +10098,7 @@
         <v>1428</v>
       </c>
       <c r="E53">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F53" t="s">
         <v>1603</v>
@@ -10133,7 +10133,7 @@
         <v>1429</v>
       </c>
       <c r="E54">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F54" t="s">
         <v>1603</v>
@@ -10168,7 +10168,7 @@
         <v>1430</v>
       </c>
       <c r="E55">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F55" t="s">
         <v>1603</v>
@@ -10203,7 +10203,7 @@
         <v>1431</v>
       </c>
       <c r="E56">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F56" t="s">
         <v>1603</v>
@@ -10238,7 +10238,7 @@
         <v>1432</v>
       </c>
       <c r="E57">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F57" t="s">
         <v>1603</v>
@@ -10273,7 +10273,7 @@
         <v>1433</v>
       </c>
       <c r="E58">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F58" t="s">
         <v>1603</v>
@@ -10308,7 +10308,7 @@
         <v>1434</v>
       </c>
       <c r="E59">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F59" t="s">
         <v>1603</v>
@@ -10343,7 +10343,7 @@
         <v>1435</v>
       </c>
       <c r="E60">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F60" t="s">
         <v>1603</v>
@@ -10378,7 +10378,7 @@
         <v>1436</v>
       </c>
       <c r="E61">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F61" t="s">
         <v>1603</v>
@@ -10413,7 +10413,7 @@
         <v>1437</v>
       </c>
       <c r="E62">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F62" t="s">
         <v>1603</v>
@@ -10448,7 +10448,7 @@
         <v>1438</v>
       </c>
       <c r="E63">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F63" t="s">
         <v>1603</v>
@@ -10483,7 +10483,7 @@
         <v>1439</v>
       </c>
       <c r="E64">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F64" t="s">
         <v>1603</v>
@@ -10518,7 +10518,7 @@
         <v>1440</v>
       </c>
       <c r="E65">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F65" t="s">
         <v>1603</v>
@@ -10553,7 +10553,7 @@
         <v>1441</v>
       </c>
       <c r="E66">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F66" t="s">
         <v>1603</v>
@@ -10588,7 +10588,7 @@
         <v>1442</v>
       </c>
       <c r="E67">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F67" t="s">
         <v>1603</v>
@@ -10623,7 +10623,7 @@
         <v>1443</v>
       </c>
       <c r="E68">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F68" t="s">
         <v>1603</v>
@@ -10658,7 +10658,7 @@
         <v>1444</v>
       </c>
       <c r="E69">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F69" t="s">
         <v>1603</v>
@@ -10693,7 +10693,7 @@
         <v>1445</v>
       </c>
       <c r="E70">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F70" t="s">
         <v>1603</v>
@@ -10728,7 +10728,7 @@
         <v>1446</v>
       </c>
       <c r="E71">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F71" t="s">
         <v>1603</v>
@@ -10763,7 +10763,7 @@
         <v>1446</v>
       </c>
       <c r="E72">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F72" t="s">
         <v>1603</v>
@@ -10798,7 +10798,7 @@
         <v>1446</v>
       </c>
       <c r="E73">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F73" t="s">
         <v>1603</v>
@@ -10833,7 +10833,7 @@
         <v>1447</v>
       </c>
       <c r="E74">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F74" t="s">
         <v>1603</v>
@@ -10868,7 +10868,7 @@
         <v>1448</v>
       </c>
       <c r="E75">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F75" t="s">
         <v>1603</v>
@@ -10903,7 +10903,7 @@
         <v>1449</v>
       </c>
       <c r="E76">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F76" t="s">
         <v>1603</v>
@@ -10938,7 +10938,7 @@
         <v>1449</v>
       </c>
       <c r="E77">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F77" t="s">
         <v>1603</v>
@@ -10973,7 +10973,7 @@
         <v>1449</v>
       </c>
       <c r="E78">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F78" t="s">
         <v>1603</v>
@@ -11008,7 +11008,7 @@
         <v>1450</v>
       </c>
       <c r="E79">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F79" t="s">
         <v>1603</v>
@@ -11043,7 +11043,7 @@
         <v>1451</v>
       </c>
       <c r="E80">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F80" t="s">
         <v>1603</v>
@@ -11078,7 +11078,7 @@
         <v>1452</v>
       </c>
       <c r="E81">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F81" t="s">
         <v>1603</v>
@@ -11113,7 +11113,7 @@
         <v>1452</v>
       </c>
       <c r="E82">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F82" t="s">
         <v>1603</v>
@@ -11148,7 +11148,7 @@
         <v>1452</v>
       </c>
       <c r="E83">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F83" t="s">
         <v>1603</v>
@@ -11183,7 +11183,7 @@
         <v>1453</v>
       </c>
       <c r="E84">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F84" t="s">
         <v>1603</v>
@@ -11218,7 +11218,7 @@
         <v>1454</v>
       </c>
       <c r="E85">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F85" t="s">
         <v>1603</v>
@@ -11253,7 +11253,7 @@
         <v>1454</v>
       </c>
       <c r="E86">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F86" t="s">
         <v>1603</v>
@@ -11288,7 +11288,7 @@
         <v>1454</v>
       </c>
       <c r="E87">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F87" t="s">
         <v>1604</v>
@@ -11323,7 +11323,7 @@
         <v>1454</v>
       </c>
       <c r="E88">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F88" t="s">
         <v>1603</v>
@@ -11358,7 +11358,7 @@
         <v>1455</v>
       </c>
       <c r="E89">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F89" t="s">
         <v>1603</v>
@@ -11393,7 +11393,7 @@
         <v>1456</v>
       </c>
       <c r="E90">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F90" t="s">
         <v>1603</v>
@@ -11428,7 +11428,7 @@
         <v>1456</v>
       </c>
       <c r="E91">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F91" t="s">
         <v>1603</v>
@@ -11463,7 +11463,7 @@
         <v>1456</v>
       </c>
       <c r="E92">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F92" t="s">
         <v>1603</v>
@@ -11498,7 +11498,7 @@
         <v>1457</v>
       </c>
       <c r="E93">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F93" t="s">
         <v>1603</v>
@@ -11533,7 +11533,7 @@
         <v>1458</v>
       </c>
       <c r="E94">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F94" t="s">
         <v>1603</v>
@@ -11568,7 +11568,7 @@
         <v>1459</v>
       </c>
       <c r="E95">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F95" t="s">
         <v>1603</v>
@@ -11603,7 +11603,7 @@
         <v>1460</v>
       </c>
       <c r="E96">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F96" t="s">
         <v>1603</v>
@@ -11638,7 +11638,7 @@
         <v>1461</v>
       </c>
       <c r="E97">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F97" t="s">
         <v>1603</v>
@@ -11673,7 +11673,7 @@
         <v>1461</v>
       </c>
       <c r="E98">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F98" t="s">
         <v>1603</v>
@@ -11708,7 +11708,7 @@
         <v>1461</v>
       </c>
       <c r="E99">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F99" t="s">
         <v>1603</v>
@@ -11743,7 +11743,7 @@
         <v>1461</v>
       </c>
       <c r="E100">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F100" t="s">
         <v>1603</v>
@@ -11778,7 +11778,7 @@
         <v>1461</v>
       </c>
       <c r="E101">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F101" t="s">
         <v>1603</v>
@@ -11813,7 +11813,7 @@
         <v>1461</v>
       </c>
       <c r="E102">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F102" t="s">
         <v>1603</v>
@@ -11848,7 +11848,7 @@
         <v>1461</v>
       </c>
       <c r="E103">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F103" t="s">
         <v>1603</v>
@@ -11883,7 +11883,7 @@
         <v>1462</v>
       </c>
       <c r="E104">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F104" t="s">
         <v>1603</v>
@@ -11918,7 +11918,7 @@
         <v>1462</v>
       </c>
       <c r="E105">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F105" t="s">
         <v>1603</v>
@@ -11953,7 +11953,7 @@
         <v>1463</v>
       </c>
       <c r="E106">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F106" t="s">
         <v>1603</v>
@@ -11988,7 +11988,7 @@
         <v>1464</v>
       </c>
       <c r="E107">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F107" t="s">
         <v>1603</v>
@@ -12023,7 +12023,7 @@
         <v>1464</v>
       </c>
       <c r="E108">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F108" t="s">
         <v>1603</v>
@@ -12058,7 +12058,7 @@
         <v>1465</v>
       </c>
       <c r="E109">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F109" t="s">
         <v>1603</v>
@@ -12093,7 +12093,7 @@
         <v>1465</v>
       </c>
       <c r="E110">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F110" t="s">
         <v>1605</v>
@@ -12128,7 +12128,7 @@
         <v>1466</v>
       </c>
       <c r="E111">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F111" t="s">
         <v>1603</v>
@@ -12163,7 +12163,7 @@
         <v>1467</v>
       </c>
       <c r="E112">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F112" t="s">
         <v>1603</v>
@@ -12198,7 +12198,7 @@
         <v>1468</v>
       </c>
       <c r="E113">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F113" t="s">
         <v>1603</v>
@@ -12233,7 +12233,7 @@
         <v>1468</v>
       </c>
       <c r="E114">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F114" t="s">
         <v>1603</v>
@@ -12268,7 +12268,7 @@
         <v>1469</v>
       </c>
       <c r="E115">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F115" t="s">
         <v>1603</v>
@@ -12303,7 +12303,7 @@
         <v>1470</v>
       </c>
       <c r="E116">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F116" t="s">
         <v>1603</v>
@@ -12338,7 +12338,7 @@
         <v>1471</v>
       </c>
       <c r="E117">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F117" t="s">
         <v>1603</v>
@@ -12373,7 +12373,7 @@
         <v>1472</v>
       </c>
       <c r="E118">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F118" t="s">
         <v>1603</v>
@@ -12408,7 +12408,7 @@
         <v>1473</v>
       </c>
       <c r="E119">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F119" t="s">
         <v>1603</v>
@@ -12443,7 +12443,7 @@
         <v>1473</v>
       </c>
       <c r="E120">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F120" t="s">
         <v>1603</v>
@@ -12478,7 +12478,7 @@
         <v>1474</v>
       </c>
       <c r="E121">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F121" t="s">
         <v>1603</v>
@@ -12513,7 +12513,7 @@
         <v>1474</v>
       </c>
       <c r="E122">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F122" t="s">
         <v>1603</v>
@@ -12548,7 +12548,7 @@
         <v>1474</v>
       </c>
       <c r="E123">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F123" t="s">
         <v>1603</v>
@@ -12583,7 +12583,7 @@
         <v>1474</v>
       </c>
       <c r="E124">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F124" t="s">
         <v>1603</v>
@@ -12618,7 +12618,7 @@
         <v>1475</v>
       </c>
       <c r="E125">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F125" t="s">
         <v>1603</v>
@@ -12653,7 +12653,7 @@
         <v>1475</v>
       </c>
       <c r="E126">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F126" t="s">
         <v>1603</v>
@@ -12688,7 +12688,7 @@
         <v>1475</v>
       </c>
       <c r="E127">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F127" t="s">
         <v>1603</v>
@@ -12723,7 +12723,7 @@
         <v>1475</v>
       </c>
       <c r="E128">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F128" t="s">
         <v>1603</v>
@@ -12758,7 +12758,7 @@
         <v>1475</v>
       </c>
       <c r="E129">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F129" t="s">
         <v>1603</v>
@@ -12793,7 +12793,7 @@
         <v>1475</v>
       </c>
       <c r="E130">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F130" t="s">
         <v>1603</v>
@@ -12828,7 +12828,7 @@
         <v>1476</v>
       </c>
       <c r="E131">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F131" t="s">
         <v>1603</v>
@@ -12863,7 +12863,7 @@
         <v>1477</v>
       </c>
       <c r="E132">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F132" t="s">
         <v>1603</v>
@@ -12898,7 +12898,7 @@
         <v>1477</v>
       </c>
       <c r="E133">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F133" t="s">
         <v>1603</v>
@@ -12933,7 +12933,7 @@
         <v>1478</v>
       </c>
       <c r="E134">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F134" t="s">
         <v>1603</v>
@@ -12968,7 +12968,7 @@
         <v>1479</v>
       </c>
       <c r="E135">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F135" t="s">
         <v>1603</v>
@@ -13003,7 +13003,7 @@
         <v>1479</v>
       </c>
       <c r="E136">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F136" t="s">
         <v>1603</v>
@@ -13038,7 +13038,7 @@
         <v>1479</v>
       </c>
       <c r="E137">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F137" t="s">
         <v>1603</v>
@@ -13073,7 +13073,7 @@
         <v>1480</v>
       </c>
       <c r="E138">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F138" t="s">
         <v>1603</v>
@@ -13108,7 +13108,7 @@
         <v>1480</v>
       </c>
       <c r="E139">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F139" t="s">
         <v>1603</v>
@@ -13143,7 +13143,7 @@
         <v>1480</v>
       </c>
       <c r="E140">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F140" t="s">
         <v>1603</v>
@@ -13178,7 +13178,7 @@
         <v>1481</v>
       </c>
       <c r="E141">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F141" t="s">
         <v>1603</v>
@@ -13213,7 +13213,7 @@
         <v>1481</v>
       </c>
       <c r="E142">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F142" t="s">
         <v>1603</v>
@@ -13248,7 +13248,7 @@
         <v>1481</v>
       </c>
       <c r="E143">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F143" t="s">
         <v>1603</v>
@@ -13283,7 +13283,7 @@
         <v>1482</v>
       </c>
       <c r="E144">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F144" t="s">
         <v>1603</v>
@@ -13318,7 +13318,7 @@
         <v>1482</v>
       </c>
       <c r="E145">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F145" t="s">
         <v>1603</v>
@@ -13353,7 +13353,7 @@
         <v>1483</v>
       </c>
       <c r="E146">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F146" t="s">
         <v>1603</v>
@@ -13388,7 +13388,7 @@
         <v>1484</v>
       </c>
       <c r="E147">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F147" t="s">
         <v>1603</v>
@@ -13423,7 +13423,7 @@
         <v>1484</v>
       </c>
       <c r="E148">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F148" t="s">
         <v>1603</v>
@@ -13458,7 +13458,7 @@
         <v>1484</v>
       </c>
       <c r="E149">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F149" t="s">
         <v>1603</v>
@@ -13493,7 +13493,7 @@
         <v>1485</v>
       </c>
       <c r="E150">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F150" t="s">
         <v>1603</v>
@@ -13528,7 +13528,7 @@
         <v>1485</v>
       </c>
       <c r="E151">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F151" t="s">
         <v>1603</v>
@@ -13563,7 +13563,7 @@
         <v>1486</v>
       </c>
       <c r="E152">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F152" t="s">
         <v>1603</v>
@@ -13601,7 +13601,7 @@
         <v>1486</v>
       </c>
       <c r="E153">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F153" t="s">
         <v>1603</v>
@@ -13636,7 +13636,7 @@
         <v>1486</v>
       </c>
       <c r="E154">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F154" t="s">
         <v>1603</v>
@@ -13671,7 +13671,7 @@
         <v>1486</v>
       </c>
       <c r="E155">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F155" t="s">
         <v>1603</v>
@@ -13706,7 +13706,7 @@
         <v>1486</v>
       </c>
       <c r="E156">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F156" t="s">
         <v>1603</v>
@@ -13741,7 +13741,7 @@
         <v>1486</v>
       </c>
       <c r="E157">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F157" t="s">
         <v>1603</v>
@@ -13776,7 +13776,7 @@
         <v>1487</v>
       </c>
       <c r="E158">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F158" t="s">
         <v>1603</v>
@@ -13811,7 +13811,7 @@
         <v>1488</v>
       </c>
       <c r="E159">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F159" t="s">
         <v>1603</v>
@@ -13846,7 +13846,7 @@
         <v>1489</v>
       </c>
       <c r="E160">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F160" t="s">
         <v>1604</v>
@@ -13881,7 +13881,7 @@
         <v>1490</v>
       </c>
       <c r="E161">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F161" t="s">
         <v>1603</v>
@@ -13916,7 +13916,7 @@
         <v>1490</v>
       </c>
       <c r="E162">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F162" t="s">
         <v>1603</v>
@@ -13951,7 +13951,7 @@
         <v>1490</v>
       </c>
       <c r="E163">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F163" t="s">
         <v>1603</v>
@@ -13986,7 +13986,7 @@
         <v>1490</v>
       </c>
       <c r="E164">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F164" t="s">
         <v>1603</v>
@@ -14021,7 +14021,7 @@
         <v>1491</v>
       </c>
       <c r="E165">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F165" t="s">
         <v>1603</v>
@@ -14056,7 +14056,7 @@
         <v>1491</v>
       </c>
       <c r="E166">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F166" t="s">
         <v>1603</v>
@@ -14091,7 +14091,7 @@
         <v>1491</v>
       </c>
       <c r="E167">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F167" t="s">
         <v>1603</v>
@@ -14126,7 +14126,7 @@
         <v>1491</v>
       </c>
       <c r="E168">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F168" t="s">
         <v>1603</v>
@@ -14161,7 +14161,7 @@
         <v>1491</v>
       </c>
       <c r="E169">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F169" t="s">
         <v>1603</v>
@@ -14196,7 +14196,7 @@
         <v>1491</v>
       </c>
       <c r="E170">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F170" t="s">
         <v>1603</v>
@@ -14231,7 +14231,7 @@
         <v>1491</v>
       </c>
       <c r="E171">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F171" t="s">
         <v>1603</v>
@@ -14266,7 +14266,7 @@
         <v>1492</v>
       </c>
       <c r="E172">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F172" t="s">
         <v>1603</v>
@@ -14301,7 +14301,7 @@
         <v>1492</v>
       </c>
       <c r="E173">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F173" t="s">
         <v>1603</v>
@@ -14336,7 +14336,7 @@
         <v>1493</v>
       </c>
       <c r="E174">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F174" t="s">
         <v>1603</v>
@@ -14371,7 +14371,7 @@
         <v>1493</v>
       </c>
       <c r="E175">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F175" t="s">
         <v>1603</v>
@@ -14406,7 +14406,7 @@
         <v>1493</v>
       </c>
       <c r="E176">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F176" t="s">
         <v>1603</v>
@@ -14441,7 +14441,7 @@
         <v>1494</v>
       </c>
       <c r="E177">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F177" t="s">
         <v>1603</v>
@@ -14476,7 +14476,7 @@
         <v>1494</v>
       </c>
       <c r="E178">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F178" t="s">
         <v>1603</v>
@@ -14511,7 +14511,7 @@
         <v>1494</v>
       </c>
       <c r="E179">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F179" t="s">
         <v>1603</v>
@@ -14546,7 +14546,7 @@
         <v>1494</v>
       </c>
       <c r="E180">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F180" t="s">
         <v>1603</v>
@@ -14581,7 +14581,7 @@
         <v>1495</v>
       </c>
       <c r="E181">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F181" t="s">
         <v>1603</v>
@@ -14616,7 +14616,7 @@
         <v>1495</v>
       </c>
       <c r="E182">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F182" t="s">
         <v>1603</v>
@@ -14651,7 +14651,7 @@
         <v>1495</v>
       </c>
       <c r="E183">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F183" t="s">
         <v>1603</v>
@@ -14686,7 +14686,7 @@
         <v>1495</v>
       </c>
       <c r="E184">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F184" t="s">
         <v>1603</v>
@@ -14721,7 +14721,7 @@
         <v>1495</v>
       </c>
       <c r="E185">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F185" t="s">
         <v>1603</v>
@@ -14756,7 +14756,7 @@
         <v>1495</v>
       </c>
       <c r="E186">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F186" t="s">
         <v>1603</v>
@@ -14791,7 +14791,7 @@
         <v>1495</v>
       </c>
       <c r="E187">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F187" t="s">
         <v>1603</v>
@@ -14826,7 +14826,7 @@
         <v>1495</v>
       </c>
       <c r="E188">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F188" t="s">
         <v>1603</v>
@@ -14861,7 +14861,7 @@
         <v>1495</v>
       </c>
       <c r="E189">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F189" t="s">
         <v>1603</v>
@@ -14896,7 +14896,7 @@
         <v>1495</v>
       </c>
       <c r="E190">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F190" t="s">
         <v>1603</v>
@@ -14931,7 +14931,7 @@
         <v>1496</v>
       </c>
       <c r="E191">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F191" t="s">
         <v>1603</v>
@@ -14966,7 +14966,7 @@
         <v>1496</v>
       </c>
       <c r="E192">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F192" t="s">
         <v>1603</v>
@@ -15001,7 +15001,7 @@
         <v>1496</v>
       </c>
       <c r="E193">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F193" t="s">
         <v>1603</v>
@@ -15036,7 +15036,7 @@
         <v>1496</v>
       </c>
       <c r="E194">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F194" t="s">
         <v>1606</v>
@@ -15071,7 +15071,7 @@
         <v>1497</v>
       </c>
       <c r="E195">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F195" t="s">
         <v>1603</v>
@@ -15106,7 +15106,7 @@
         <v>1497</v>
       </c>
       <c r="E196">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F196" t="s">
         <v>1604</v>
@@ -15141,7 +15141,7 @@
         <v>1497</v>
       </c>
       <c r="E197">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F197" t="s">
         <v>1603</v>
@@ -15176,7 +15176,7 @@
         <v>1498</v>
       </c>
       <c r="E198">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F198" t="s">
         <v>1603</v>
@@ -15211,7 +15211,7 @@
         <v>1498</v>
       </c>
       <c r="E199">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F199" t="s">
         <v>1603</v>
@@ -15246,7 +15246,7 @@
         <v>1499</v>
       </c>
       <c r="E200">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F200" t="s">
         <v>1603</v>
@@ -15281,7 +15281,7 @@
         <v>1499</v>
       </c>
       <c r="E201">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F201" t="s">
         <v>1603</v>
@@ -15316,7 +15316,7 @@
         <v>1500</v>
       </c>
       <c r="E202">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F202" t="s">
         <v>1603</v>
@@ -15351,7 +15351,7 @@
         <v>1500</v>
       </c>
       <c r="E203">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F203" t="s">
         <v>1603</v>
@@ -15386,7 +15386,7 @@
         <v>1500</v>
       </c>
       <c r="E204">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F204" t="s">
         <v>1603</v>
@@ -15421,7 +15421,7 @@
         <v>1501</v>
       </c>
       <c r="E205">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F205" t="s">
         <v>1603</v>
@@ -15456,7 +15456,7 @@
         <v>1501</v>
       </c>
       <c r="E206">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F206" t="s">
         <v>1603</v>
@@ -15491,7 +15491,7 @@
         <v>1501</v>
       </c>
       <c r="E207">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F207" t="s">
         <v>1603</v>
@@ -15526,7 +15526,7 @@
         <v>1501</v>
       </c>
       <c r="E208">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F208" t="s">
         <v>1603</v>
@@ -15561,7 +15561,7 @@
         <v>1501</v>
       </c>
       <c r="E209">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F209" t="s">
         <v>1603</v>
@@ -15596,7 +15596,7 @@
         <v>1502</v>
       </c>
       <c r="E210">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F210" t="s">
         <v>1603</v>
@@ -15631,7 +15631,7 @@
         <v>1502</v>
       </c>
       <c r="E211">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F211" t="s">
         <v>1603</v>
@@ -15666,7 +15666,7 @@
         <v>1503</v>
       </c>
       <c r="E212">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F212" t="s">
         <v>1603</v>
@@ -15701,7 +15701,7 @@
         <v>1504</v>
       </c>
       <c r="E213">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F213" t="s">
         <v>1603</v>
@@ -15736,7 +15736,7 @@
         <v>1504</v>
       </c>
       <c r="E214">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F214" t="s">
         <v>1603</v>
@@ -15771,7 +15771,7 @@
         <v>1504</v>
       </c>
       <c r="E215">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F215" t="s">
         <v>1603</v>
@@ -15806,7 +15806,7 @@
         <v>1504</v>
       </c>
       <c r="E216">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F216" t="s">
         <v>1603</v>
@@ -15841,7 +15841,7 @@
         <v>1505</v>
       </c>
       <c r="E217">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F217" t="s">
         <v>1603</v>
@@ -15876,7 +15876,7 @@
         <v>1506</v>
       </c>
       <c r="E218">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F218" t="s">
         <v>1603</v>
@@ -15911,7 +15911,7 @@
         <v>1506</v>
       </c>
       <c r="E219">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F219" t="s">
         <v>1603</v>
@@ -15946,7 +15946,7 @@
         <v>1506</v>
       </c>
       <c r="E220">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F220" t="s">
         <v>1603</v>
@@ -15981,7 +15981,7 @@
         <v>1506</v>
       </c>
       <c r="E221">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F221" t="s">
         <v>1603</v>
@@ -16016,7 +16016,7 @@
         <v>1506</v>
       </c>
       <c r="E222">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F222" t="s">
         <v>1603</v>
@@ -16051,7 +16051,7 @@
         <v>1507</v>
       </c>
       <c r="E223">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F223" t="s">
         <v>1603</v>
@@ -16086,7 +16086,7 @@
         <v>1507</v>
       </c>
       <c r="E224">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F224" t="s">
         <v>1603</v>
@@ -16121,7 +16121,7 @@
         <v>1507</v>
       </c>
       <c r="E225">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F225" t="s">
         <v>1603</v>
@@ -16156,7 +16156,7 @@
         <v>1507</v>
       </c>
       <c r="E226">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F226" t="s">
         <v>1603</v>
@@ -16191,7 +16191,7 @@
         <v>1507</v>
       </c>
       <c r="E227">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F227" t="s">
         <v>1603</v>
@@ -16226,7 +16226,7 @@
         <v>1507</v>
       </c>
       <c r="E228">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F228" t="s">
         <v>1603</v>
@@ -16261,7 +16261,7 @@
         <v>1507</v>
       </c>
       <c r="E229">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F229" t="s">
         <v>1603</v>
@@ -16296,7 +16296,7 @@
         <v>1508</v>
       </c>
       <c r="E230">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F230" t="s">
         <v>1603</v>
@@ -16331,7 +16331,7 @@
         <v>1508</v>
       </c>
       <c r="E231">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F231" t="s">
         <v>1603</v>
@@ -16366,7 +16366,7 @@
         <v>1508</v>
       </c>
       <c r="E232">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F232" t="s">
         <v>1603</v>
@@ -16401,7 +16401,7 @@
         <v>1508</v>
       </c>
       <c r="E233">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F233" t="s">
         <v>1603</v>
@@ -16436,7 +16436,7 @@
         <v>1509</v>
       </c>
       <c r="E234">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F234" t="s">
         <v>1603</v>
@@ -16471,7 +16471,7 @@
         <v>1509</v>
       </c>
       <c r="E235">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F235" t="s">
         <v>1603</v>
@@ -16506,7 +16506,7 @@
         <v>1509</v>
       </c>
       <c r="E236">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F236" t="s">
         <v>1603</v>
@@ -16541,7 +16541,7 @@
         <v>1510</v>
       </c>
       <c r="E237">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F237" t="s">
         <v>1603</v>
@@ -16576,7 +16576,7 @@
         <v>1510</v>
       </c>
       <c r="E238">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F238" t="s">
         <v>1603</v>
@@ -16611,7 +16611,7 @@
         <v>1511</v>
       </c>
       <c r="E239">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F239" t="s">
         <v>1603</v>
@@ -16646,7 +16646,7 @@
         <v>1511</v>
       </c>
       <c r="E240">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F240" t="s">
         <v>1603</v>
@@ -16681,7 +16681,7 @@
         <v>1512</v>
       </c>
       <c r="E241">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F241" t="s">
         <v>1603</v>
@@ -16716,7 +16716,7 @@
         <v>1512</v>
       </c>
       <c r="E242">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F242" t="s">
         <v>1603</v>
@@ -16751,7 +16751,7 @@
         <v>1513</v>
       </c>
       <c r="E243">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F243" t="s">
         <v>1603</v>
@@ -16786,7 +16786,7 @@
         <v>1513</v>
       </c>
       <c r="E244">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F244" t="s">
         <v>1603</v>
@@ -16821,7 +16821,7 @@
         <v>1514</v>
       </c>
       <c r="E245">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F245" t="s">
         <v>1603</v>
@@ -16856,7 +16856,7 @@
         <v>1514</v>
       </c>
       <c r="E246">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F246" t="s">
         <v>1603</v>
@@ -16891,7 +16891,7 @@
         <v>1515</v>
       </c>
       <c r="E247">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F247" t="s">
         <v>1603</v>
@@ -16926,7 +16926,7 @@
         <v>1515</v>
       </c>
       <c r="E248">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F248" t="s">
         <v>1603</v>
@@ -16961,7 +16961,7 @@
         <v>1516</v>
       </c>
       <c r="E249">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F249" t="s">
         <v>1603</v>
@@ -16996,7 +16996,7 @@
         <v>1516</v>
       </c>
       <c r="E250">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F250" t="s">
         <v>1603</v>
@@ -17031,7 +17031,7 @@
         <v>1516</v>
       </c>
       <c r="E251">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F251" t="s">
         <v>1603</v>
@@ -17066,7 +17066,7 @@
         <v>1517</v>
       </c>
       <c r="E252">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F252" t="s">
         <v>1603</v>
@@ -17101,7 +17101,7 @@
         <v>1517</v>
       </c>
       <c r="E253">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F253" t="s">
         <v>1603</v>
@@ -17136,7 +17136,7 @@
         <v>1518</v>
       </c>
       <c r="E254">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F254" t="s">
         <v>1603</v>
@@ -17171,7 +17171,7 @@
         <v>1519</v>
       </c>
       <c r="E255">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F255" t="s">
         <v>1603</v>
@@ -17206,7 +17206,7 @@
         <v>1519</v>
       </c>
       <c r="E256">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F256" t="s">
         <v>1603</v>
@@ -17241,7 +17241,7 @@
         <v>1519</v>
       </c>
       <c r="E257">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F257" t="s">
         <v>1603</v>
@@ -17276,7 +17276,7 @@
         <v>1520</v>
       </c>
       <c r="E258">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F258" t="s">
         <v>1603</v>
@@ -17311,7 +17311,7 @@
         <v>1520</v>
       </c>
       <c r="E259">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F259" t="s">
         <v>1603</v>
@@ -17346,7 +17346,7 @@
         <v>1521</v>
       </c>
       <c r="E260">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F260" t="s">
         <v>1603</v>
@@ -17381,7 +17381,7 @@
         <v>1521</v>
       </c>
       <c r="E261">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F261" t="s">
         <v>1603</v>
@@ -17416,7 +17416,7 @@
         <v>1521</v>
       </c>
       <c r="E262">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F262" t="s">
         <v>1605</v>
@@ -17451,7 +17451,7 @@
         <v>1521</v>
       </c>
       <c r="E263">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F263" t="s">
         <v>1603</v>
@@ -17486,7 +17486,7 @@
         <v>1521</v>
       </c>
       <c r="E264">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F264" t="s">
         <v>1603</v>
@@ -17521,7 +17521,7 @@
         <v>1522</v>
       </c>
       <c r="E265">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F265" t="s">
         <v>1603</v>
@@ -17556,7 +17556,7 @@
         <v>1522</v>
       </c>
       <c r="E266">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F266" t="s">
         <v>1603</v>
@@ -17591,7 +17591,7 @@
         <v>1522</v>
       </c>
       <c r="E267">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F267" t="s">
         <v>1603</v>
@@ -17629,7 +17629,7 @@
         <v>1522</v>
       </c>
       <c r="E268">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F268" t="s">
         <v>1603</v>
@@ -17664,7 +17664,7 @@
         <v>1522</v>
       </c>
       <c r="E269">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F269" t="s">
         <v>1603</v>
@@ -17699,7 +17699,7 @@
         <v>1522</v>
       </c>
       <c r="E270">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F270" t="s">
         <v>1603</v>
@@ -17734,7 +17734,7 @@
         <v>1522</v>
       </c>
       <c r="E271">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F271" t="s">
         <v>1603</v>
@@ -17769,7 +17769,7 @@
         <v>1523</v>
       </c>
       <c r="E272">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F272" t="s">
         <v>1603</v>
@@ -17804,7 +17804,7 @@
         <v>1523</v>
       </c>
       <c r="E273">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F273" t="s">
         <v>1603</v>
@@ -17839,7 +17839,7 @@
         <v>1523</v>
       </c>
       <c r="E274">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F274" t="s">
         <v>1603</v>
@@ -17874,7 +17874,7 @@
         <v>1524</v>
       </c>
       <c r="E275">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F275" t="s">
         <v>1603</v>
@@ -17909,7 +17909,7 @@
         <v>1524</v>
       </c>
       <c r="E276">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F276" t="s">
         <v>1603</v>
@@ -17944,7 +17944,7 @@
         <v>1524</v>
       </c>
       <c r="E277">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F277" t="s">
         <v>1603</v>
@@ -17979,7 +17979,7 @@
         <v>1524</v>
       </c>
       <c r="E278">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F278" t="s">
         <v>1603</v>
@@ -18014,7 +18014,7 @@
         <v>1525</v>
       </c>
       <c r="E279">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F279" t="s">
         <v>1603</v>
@@ -18049,7 +18049,7 @@
         <v>1525</v>
       </c>
       <c r="E280">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F280" t="s">
         <v>1603</v>
@@ -18084,7 +18084,7 @@
         <v>1525</v>
       </c>
       <c r="E281">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F281" t="s">
         <v>1603</v>
@@ -18119,7 +18119,7 @@
         <v>1525</v>
       </c>
       <c r="E282">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F282" t="s">
         <v>1603</v>
@@ -18154,7 +18154,7 @@
         <v>1525</v>
       </c>
       <c r="E283">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F283" t="s">
         <v>1603</v>
@@ -18189,7 +18189,7 @@
         <v>1525</v>
       </c>
       <c r="E284">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F284" t="s">
         <v>1603</v>
@@ -18224,7 +18224,7 @@
         <v>1526</v>
       </c>
       <c r="E285">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F285" t="s">
         <v>1603</v>
@@ -18259,7 +18259,7 @@
         <v>1526</v>
       </c>
       <c r="E286">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F286" t="s">
         <v>1603</v>
@@ -18294,7 +18294,7 @@
         <v>1526</v>
       </c>
       <c r="E287">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F287" t="s">
         <v>1603</v>
@@ -18329,7 +18329,7 @@
         <v>1526</v>
       </c>
       <c r="E288">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F288" t="s">
         <v>1603</v>
@@ -18364,7 +18364,7 @@
         <v>1526</v>
       </c>
       <c r="E289">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F289" t="s">
         <v>1603</v>
@@ -18399,7 +18399,7 @@
         <v>1526</v>
       </c>
       <c r="E290">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F290" t="s">
         <v>1603</v>
@@ -18434,7 +18434,7 @@
         <v>1527</v>
       </c>
       <c r="E291">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F291" t="s">
         <v>1603</v>
@@ -18469,7 +18469,7 @@
         <v>1528</v>
       </c>
       <c r="E292">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F292" t="s">
         <v>1604</v>
@@ -18504,7 +18504,7 @@
         <v>1528</v>
       </c>
       <c r="E293">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F293" t="s">
         <v>1603</v>
@@ -18539,7 +18539,7 @@
         <v>1528</v>
       </c>
       <c r="E294">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F294" t="s">
         <v>1603</v>
@@ -18574,7 +18574,7 @@
         <v>1528</v>
       </c>
       <c r="E295">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F295" t="s">
         <v>1606</v>
@@ -18609,7 +18609,7 @@
         <v>1528</v>
       </c>
       <c r="E296">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F296" t="s">
         <v>1603</v>
@@ -18644,7 +18644,7 @@
         <v>1528</v>
       </c>
       <c r="E297">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F297" t="s">
         <v>1603</v>
@@ -18679,7 +18679,7 @@
         <v>1528</v>
       </c>
       <c r="E298">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F298" t="s">
         <v>1603</v>
@@ -18714,7 +18714,7 @@
         <v>1528</v>
       </c>
       <c r="E299">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F299" t="s">
         <v>1603</v>
@@ -18749,7 +18749,7 @@
         <v>1529</v>
       </c>
       <c r="E300">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F300" t="s">
         <v>1603</v>
@@ -18784,7 +18784,7 @@
         <v>1529</v>
       </c>
       <c r="E301">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F301" t="s">
         <v>1603</v>
@@ -18819,7 +18819,7 @@
         <v>1529</v>
       </c>
       <c r="E302">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F302" t="s">
         <v>1603</v>
@@ -18854,7 +18854,7 @@
         <v>1529</v>
       </c>
       <c r="E303">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F303" t="s">
         <v>1603</v>
@@ -18889,7 +18889,7 @@
         <v>1530</v>
       </c>
       <c r="E304">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F304" t="s">
         <v>1603</v>
@@ -18924,7 +18924,7 @@
         <v>1530</v>
       </c>
       <c r="E305">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F305" t="s">
         <v>1603</v>
@@ -18959,7 +18959,7 @@
         <v>1531</v>
       </c>
       <c r="E306">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F306" t="s">
         <v>1603</v>
@@ -18997,7 +18997,7 @@
         <v>1531</v>
       </c>
       <c r="E307">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F307" t="s">
         <v>1603</v>
@@ -19032,7 +19032,7 @@
         <v>1532</v>
       </c>
       <c r="E308">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F308" t="s">
         <v>1603</v>
@@ -19067,7 +19067,7 @@
         <v>1532</v>
       </c>
       <c r="E309">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F309" t="s">
         <v>1603</v>
@@ -19102,7 +19102,7 @@
         <v>1532</v>
       </c>
       <c r="E310">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F310" t="s">
         <v>1603</v>
@@ -19137,7 +19137,7 @@
         <v>1532</v>
       </c>
       <c r="E311">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F311" t="s">
         <v>1603</v>
@@ -19175,7 +19175,7 @@
         <v>1532</v>
       </c>
       <c r="E312">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F312" t="s">
         <v>1603</v>
@@ -19210,7 +19210,7 @@
         <v>1532</v>
       </c>
       <c r="E313">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F313" t="s">
         <v>1603</v>
@@ -19245,7 +19245,7 @@
         <v>1533</v>
       </c>
       <c r="E314">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F314" t="s">
         <v>1603</v>
@@ -19280,7 +19280,7 @@
         <v>1533</v>
       </c>
       <c r="E315">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F315" t="s">
         <v>1603</v>
@@ -19315,7 +19315,7 @@
         <v>1534</v>
       </c>
       <c r="E316">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F316" t="s">
         <v>1603</v>
@@ -19350,7 +19350,7 @@
         <v>1534</v>
       </c>
       <c r="E317">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F317" t="s">
         <v>1603</v>
@@ -19385,7 +19385,7 @@
         <v>1535</v>
       </c>
       <c r="E318">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F318" t="s">
         <v>1603</v>
@@ -19420,7 +19420,7 @@
         <v>1535</v>
       </c>
       <c r="E319">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F319" t="s">
         <v>1603</v>
@@ -19455,7 +19455,7 @@
         <v>1535</v>
       </c>
       <c r="E320">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F320" t="s">
         <v>1603</v>
@@ -19490,7 +19490,7 @@
         <v>1535</v>
       </c>
       <c r="E321">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F321" t="s">
         <v>1603</v>
@@ -19525,7 +19525,7 @@
         <v>1536</v>
       </c>
       <c r="E322">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F322" t="s">
         <v>1603</v>
@@ -19560,7 +19560,7 @@
         <v>1536</v>
       </c>
       <c r="E323">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F323" t="s">
         <v>1603</v>
@@ -19595,7 +19595,7 @@
         <v>1536</v>
       </c>
       <c r="E324">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F324" t="s">
         <v>1603</v>
@@ -19630,7 +19630,7 @@
         <v>1536</v>
       </c>
       <c r="E325">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F325" t="s">
         <v>1603</v>
@@ -19665,7 +19665,7 @@
         <v>1537</v>
       </c>
       <c r="E326">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F326" t="s">
         <v>1603</v>
@@ -19700,7 +19700,7 @@
         <v>1537</v>
       </c>
       <c r="E327">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F327" t="s">
         <v>1603</v>
@@ -19735,7 +19735,7 @@
         <v>1538</v>
       </c>
       <c r="E328">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F328" t="s">
         <v>1603</v>
@@ -19770,7 +19770,7 @@
         <v>1538</v>
       </c>
       <c r="E329">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F329" t="s">
         <v>1603</v>
@@ -19805,7 +19805,7 @@
         <v>1538</v>
       </c>
       <c r="E330">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F330" t="s">
         <v>1603</v>
@@ -19840,7 +19840,7 @@
         <v>1538</v>
       </c>
       <c r="E331">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F331" t="s">
         <v>1603</v>
@@ -19875,7 +19875,7 @@
         <v>1538</v>
       </c>
       <c r="E332">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F332" t="s">
         <v>1603</v>
@@ -19910,7 +19910,7 @@
         <v>1539</v>
       </c>
       <c r="E333">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F333" t="s">
         <v>1603</v>
@@ -19945,7 +19945,7 @@
         <v>1539</v>
       </c>
       <c r="E334">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F334" t="s">
         <v>1603</v>
@@ -19980,7 +19980,7 @@
         <v>1539</v>
       </c>
       <c r="E335">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F335" t="s">
         <v>1603</v>
@@ -20015,7 +20015,7 @@
         <v>1540</v>
       </c>
       <c r="E336">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F336" t="s">
         <v>1603</v>
@@ -20050,7 +20050,7 @@
         <v>1540</v>
       </c>
       <c r="E337">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F337" t="s">
         <v>1603</v>
@@ -20085,7 +20085,7 @@
         <v>1541</v>
       </c>
       <c r="E338">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F338" t="s">
         <v>1603</v>
@@ -20120,7 +20120,7 @@
         <v>1541</v>
       </c>
       <c r="E339">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F339" t="s">
         <v>1603</v>
@@ -20155,7 +20155,7 @@
         <v>1541</v>
       </c>
       <c r="E340">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F340" t="s">
         <v>1603</v>
@@ -20190,7 +20190,7 @@
         <v>1541</v>
       </c>
       <c r="E341">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F341" t="s">
         <v>1603</v>
@@ -20225,7 +20225,7 @@
         <v>1541</v>
       </c>
       <c r="E342">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F342" t="s">
         <v>1603</v>
@@ -20260,7 +20260,7 @@
         <v>1541</v>
       </c>
       <c r="E343">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F343" t="s">
         <v>1603</v>
@@ -20295,7 +20295,7 @@
         <v>1541</v>
       </c>
       <c r="E344">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F344" t="s">
         <v>1603</v>
@@ -20330,7 +20330,7 @@
         <v>1541</v>
       </c>
       <c r="E345">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F345" t="s">
         <v>1603</v>
@@ -20365,7 +20365,7 @@
         <v>1542</v>
       </c>
       <c r="E346">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F346" t="s">
         <v>1603</v>
@@ -20400,7 +20400,7 @@
         <v>1542</v>
       </c>
       <c r="E347">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F347" t="s">
         <v>1603</v>
@@ -20435,7 +20435,7 @@
         <v>1542</v>
       </c>
       <c r="E348">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F348" t="s">
         <v>1603</v>
@@ -20470,7 +20470,7 @@
         <v>1543</v>
       </c>
       <c r="E349">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F349" t="s">
         <v>1603</v>
@@ -20505,7 +20505,7 @@
         <v>1543</v>
       </c>
       <c r="E350">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F350" t="s">
         <v>1603</v>
@@ -20540,7 +20540,7 @@
         <v>1544</v>
       </c>
       <c r="E351">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F351" t="s">
         <v>1603</v>
@@ -20575,7 +20575,7 @@
         <v>1545</v>
       </c>
       <c r="E352">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F352" t="s">
         <v>1605</v>
@@ -20610,7 +20610,7 @@
         <v>1545</v>
       </c>
       <c r="E353">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F353" t="s">
         <v>1603</v>
@@ -20645,7 +20645,7 @@
         <v>1545</v>
       </c>
       <c r="E354">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F354" t="s">
         <v>1603</v>
@@ -20680,7 +20680,7 @@
         <v>1545</v>
       </c>
       <c r="E355">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F355" t="s">
         <v>1603</v>
@@ -20715,7 +20715,7 @@
         <v>1545</v>
       </c>
       <c r="E356">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F356" t="s">
         <v>1603</v>
@@ -20750,7 +20750,7 @@
         <v>1545</v>
       </c>
       <c r="E357">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F357" t="s">
         <v>1603</v>
@@ -20785,7 +20785,7 @@
         <v>1546</v>
       </c>
       <c r="E358">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F358" t="s">
         <v>1603</v>
@@ -20820,7 +20820,7 @@
         <v>1546</v>
       </c>
       <c r="E359">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F359" t="s">
         <v>1603</v>
@@ -20855,7 +20855,7 @@
         <v>1547</v>
       </c>
       <c r="E360">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F360" t="s">
         <v>1603</v>
@@ -20890,7 +20890,7 @@
         <v>1547</v>
       </c>
       <c r="E361">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F361" t="s">
         <v>1603</v>
@@ -20925,7 +20925,7 @@
         <v>1547</v>
       </c>
       <c r="E362">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F362" t="s">
         <v>1603</v>
@@ -20960,7 +20960,7 @@
         <v>1548</v>
       </c>
       <c r="E363">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F363" t="s">
         <v>1603</v>
@@ -20995,7 +20995,7 @@
         <v>1549</v>
       </c>
       <c r="E364">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F364" t="s">
         <v>1603</v>
@@ -21030,7 +21030,7 @@
         <v>1550</v>
       </c>
       <c r="E365">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F365" t="s">
         <v>1603</v>
@@ -21065,7 +21065,7 @@
         <v>1550</v>
       </c>
       <c r="E366">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F366" t="s">
         <v>1603</v>
@@ -21100,7 +21100,7 @@
         <v>1551</v>
       </c>
       <c r="E367">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F367" t="s">
         <v>1603</v>
@@ -21135,7 +21135,7 @@
         <v>1551</v>
       </c>
       <c r="E368">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F368" t="s">
         <v>1603</v>
@@ -21170,7 +21170,7 @@
         <v>1551</v>
       </c>
       <c r="E369">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F369" t="s">
         <v>1603</v>
@@ -21205,7 +21205,7 @@
         <v>1552</v>
       </c>
       <c r="E370">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F370" t="s">
         <v>1603</v>
@@ -21240,7 +21240,7 @@
         <v>1552</v>
       </c>
       <c r="E371">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F371" t="s">
         <v>1603</v>
@@ -21275,7 +21275,7 @@
         <v>1552</v>
       </c>
       <c r="E372">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F372" t="s">
         <v>1603</v>
@@ -21310,7 +21310,7 @@
         <v>1552</v>
       </c>
       <c r="E373">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F373" t="s">
         <v>1603</v>
@@ -21345,7 +21345,7 @@
         <v>1552</v>
       </c>
       <c r="E374">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F374" t="s">
         <v>1603</v>
@@ -21380,7 +21380,7 @@
         <v>1552</v>
       </c>
       <c r="E375">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F375" t="s">
         <v>1603</v>
@@ -21415,7 +21415,7 @@
         <v>1552</v>
       </c>
       <c r="E376">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F376" t="s">
         <v>1603</v>
@@ -21450,7 +21450,7 @@
         <v>1552</v>
       </c>
       <c r="E377">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F377" t="s">
         <v>1603</v>
@@ -21485,7 +21485,7 @@
         <v>1552</v>
       </c>
       <c r="E378">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F378" t="s">
         <v>1603</v>
@@ -21520,7 +21520,7 @@
         <v>1553</v>
       </c>
       <c r="E379">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F379" t="s">
         <v>1603</v>
@@ -21555,7 +21555,7 @@
         <v>1553</v>
       </c>
       <c r="E380">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F380" t="s">
         <v>1603</v>
@@ -21590,7 +21590,7 @@
         <v>1553</v>
       </c>
       <c r="E381">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F381" t="s">
         <v>1603</v>
@@ -21625,7 +21625,7 @@
         <v>1553</v>
       </c>
       <c r="E382">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F382" t="s">
         <v>1603</v>
@@ -21660,7 +21660,7 @@
         <v>1554</v>
       </c>
       <c r="E383">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F383" t="s">
         <v>1606</v>
@@ -21695,7 +21695,7 @@
         <v>1554</v>
       </c>
       <c r="E384">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F384" t="s">
         <v>1603</v>
@@ -21730,7 +21730,7 @@
         <v>1555</v>
       </c>
       <c r="E385">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F385" t="s">
         <v>1603</v>
@@ -21765,7 +21765,7 @@
         <v>1555</v>
       </c>
       <c r="E386">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F386" t="s">
         <v>1603</v>
@@ -21800,7 +21800,7 @@
         <v>1555</v>
       </c>
       <c r="E387">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F387" t="s">
         <v>1603</v>
@@ -21835,7 +21835,7 @@
         <v>1555</v>
       </c>
       <c r="E388">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F388" t="s">
         <v>1603</v>
@@ -21870,7 +21870,7 @@
         <v>1555</v>
       </c>
       <c r="E389">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F389" t="s">
         <v>1607</v>
@@ -21908,7 +21908,7 @@
         <v>1555</v>
       </c>
       <c r="E390">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F390" t="s">
         <v>1603</v>
@@ -21943,7 +21943,7 @@
         <v>1555</v>
       </c>
       <c r="E391">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F391" t="s">
         <v>1603</v>
@@ -21978,7 +21978,7 @@
         <v>1556</v>
       </c>
       <c r="E392">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F392" t="s">
         <v>1603</v>
@@ -22013,7 +22013,7 @@
         <v>1556</v>
       </c>
       <c r="E393">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F393" t="s">
         <v>1603</v>
@@ -22048,7 +22048,7 @@
         <v>1556</v>
       </c>
       <c r="E394">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F394" t="s">
         <v>1603</v>
@@ -22083,7 +22083,7 @@
         <v>1556</v>
       </c>
       <c r="E395">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F395" t="s">
         <v>1603</v>
@@ -22121,7 +22121,7 @@
         <v>1556</v>
       </c>
       <c r="E396">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F396" t="s">
         <v>1603</v>
@@ -22156,7 +22156,7 @@
         <v>1556</v>
       </c>
       <c r="E397">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F397" t="s">
         <v>1603</v>
@@ -22191,7 +22191,7 @@
         <v>1556</v>
       </c>
       <c r="E398">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F398" t="s">
         <v>1603</v>
@@ -22226,7 +22226,7 @@
         <v>1556</v>
       </c>
       <c r="E399">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F399" t="s">
         <v>1603</v>
@@ -22261,7 +22261,7 @@
         <v>1556</v>
       </c>
       <c r="E400">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F400" t="s">
         <v>1603</v>
@@ -22296,7 +22296,7 @@
         <v>1557</v>
       </c>
       <c r="E401">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F401" t="s">
         <v>1604</v>
@@ -22331,7 +22331,7 @@
         <v>1558</v>
       </c>
       <c r="E402">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F402" t="s">
         <v>1607</v>
@@ -22366,7 +22366,7 @@
         <v>1559</v>
       </c>
       <c r="E403">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F403" t="s">
         <v>1603</v>
@@ -22401,7 +22401,7 @@
         <v>1560</v>
       </c>
       <c r="E404">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F404" t="s">
         <v>1603</v>
@@ -22436,7 +22436,7 @@
         <v>1560</v>
       </c>
       <c r="E405">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F405" t="s">
         <v>1603</v>
@@ -22471,7 +22471,7 @@
         <v>1561</v>
       </c>
       <c r="E406">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F406" t="s">
         <v>1603</v>
@@ -22506,7 +22506,7 @@
         <v>1562</v>
       </c>
       <c r="E407">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F407" t="s">
         <v>1606</v>
@@ -22541,7 +22541,7 @@
         <v>1562</v>
       </c>
       <c r="E408">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F408" t="s">
         <v>1603</v>
@@ -22576,7 +22576,7 @@
         <v>1562</v>
       </c>
       <c r="E409">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F409" t="s">
         <v>1603</v>
@@ -22611,7 +22611,7 @@
         <v>1562</v>
       </c>
       <c r="E410">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F410" t="s">
         <v>1603</v>
@@ -22646,7 +22646,7 @@
         <v>1562</v>
       </c>
       <c r="E411">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F411" t="s">
         <v>1603</v>
@@ -22681,7 +22681,7 @@
         <v>1562</v>
       </c>
       <c r="E412">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F412" t="s">
         <v>1603</v>
@@ -22716,7 +22716,7 @@
         <v>1563</v>
       </c>
       <c r="E413">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F413" t="s">
         <v>1603</v>
@@ -22751,7 +22751,7 @@
         <v>1563</v>
       </c>
       <c r="E414">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F414" t="s">
         <v>1603</v>
@@ -22786,7 +22786,7 @@
         <v>1563</v>
       </c>
       <c r="E415">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F415" t="s">
         <v>1603</v>
@@ -22821,7 +22821,7 @@
         <v>1563</v>
       </c>
       <c r="E416">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F416" t="s">
         <v>1603</v>
@@ -22856,7 +22856,7 @@
         <v>1564</v>
       </c>
       <c r="E417">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F417" t="s">
         <v>1603</v>
@@ -22891,7 +22891,7 @@
         <v>1564</v>
       </c>
       <c r="E418">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F418" t="s">
         <v>1603</v>
@@ -22926,7 +22926,7 @@
         <v>1564</v>
       </c>
       <c r="E419">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F419" t="s">
         <v>1603</v>
@@ -22964,7 +22964,7 @@
         <v>1564</v>
       </c>
       <c r="E420">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F420" t="s">
         <v>1603</v>
@@ -22999,7 +22999,7 @@
         <v>1565</v>
       </c>
       <c r="E421">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F421" t="s">
         <v>1603</v>
@@ -23034,7 +23034,7 @@
         <v>1565</v>
       </c>
       <c r="E422">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F422" t="s">
         <v>1603</v>
@@ -23069,7 +23069,7 @@
         <v>1565</v>
       </c>
       <c r="E423">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F423" t="s">
         <v>1603</v>
@@ -23104,7 +23104,7 @@
         <v>1565</v>
       </c>
       <c r="E424">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F424" t="s">
         <v>1603</v>
@@ -23139,7 +23139,7 @@
         <v>1565</v>
       </c>
       <c r="E425">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F425" t="s">
         <v>1603</v>
@@ -23174,7 +23174,7 @@
         <v>1566</v>
       </c>
       <c r="E426">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F426" t="s">
         <v>1603</v>
@@ -23209,7 +23209,7 @@
         <v>1566</v>
       </c>
       <c r="E427">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F427" t="s">
         <v>1603</v>
@@ -23244,7 +23244,7 @@
         <v>1567</v>
       </c>
       <c r="E428">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F428" t="s">
         <v>1603</v>
@@ -23279,7 +23279,7 @@
         <v>1567</v>
       </c>
       <c r="E429">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F429" t="s">
         <v>1603</v>
@@ -23314,7 +23314,7 @@
         <v>1567</v>
       </c>
       <c r="E430">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F430" t="s">
         <v>1603</v>
@@ -23349,7 +23349,7 @@
         <v>1567</v>
       </c>
       <c r="E431">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F431" t="s">
         <v>1603</v>
@@ -23384,7 +23384,7 @@
         <v>1567</v>
       </c>
       <c r="E432">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F432" t="s">
         <v>1603</v>
@@ -23419,7 +23419,7 @@
         <v>1567</v>
       </c>
       <c r="E433">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F433" t="s">
         <v>1603</v>
@@ -23454,7 +23454,7 @@
         <v>1567</v>
       </c>
       <c r="E434">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F434" t="s">
         <v>1603</v>
@@ -23489,7 +23489,7 @@
         <v>1567</v>
       </c>
       <c r="E435">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F435" t="s">
         <v>1603</v>
@@ -23524,7 +23524,7 @@
         <v>1567</v>
       </c>
       <c r="E436">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F436" t="s">
         <v>1603</v>
@@ -23559,7 +23559,7 @@
         <v>1567</v>
       </c>
       <c r="E437">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F437" t="s">
         <v>1603</v>
@@ -23594,7 +23594,7 @@
         <v>1568</v>
       </c>
       <c r="E438">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F438" t="s">
         <v>1603</v>
@@ -23629,7 +23629,7 @@
         <v>1568</v>
       </c>
       <c r="E439">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F439" t="s">
         <v>1603</v>
@@ -23664,7 +23664,7 @@
         <v>1568</v>
       </c>
       <c r="E440">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F440" t="s">
         <v>1604</v>
@@ -23699,7 +23699,7 @@
         <v>1569</v>
       </c>
       <c r="E441">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F441" t="s">
         <v>1603</v>
@@ -23734,7 +23734,7 @@
         <v>1569</v>
       </c>
       <c r="E442">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F442" t="s">
         <v>1603</v>
@@ -23769,7 +23769,7 @@
         <v>1569</v>
       </c>
       <c r="E443">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F443" t="s">
         <v>1603</v>
@@ -23804,7 +23804,7 @@
         <v>1569</v>
       </c>
       <c r="E444">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F444" t="s">
         <v>1603</v>
@@ -23839,7 +23839,7 @@
         <v>1569</v>
       </c>
       <c r="E445">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F445" t="s">
         <v>1603</v>
@@ -23874,7 +23874,7 @@
         <v>1569</v>
       </c>
       <c r="E446">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F446" t="s">
         <v>1603</v>
@@ -23909,7 +23909,7 @@
         <v>1569</v>
       </c>
       <c r="E447">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F447" t="s">
         <v>1606</v>
@@ -23944,7 +23944,7 @@
         <v>1570</v>
       </c>
       <c r="E448">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F448" t="s">
         <v>1603</v>
@@ -23979,7 +23979,7 @@
         <v>1570</v>
       </c>
       <c r="E449">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F449" t="s">
         <v>1603</v>
@@ -24014,7 +24014,7 @@
         <v>1570</v>
       </c>
       <c r="E450">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F450" t="s">
         <v>1603</v>
@@ -24049,7 +24049,7 @@
         <v>1570</v>
       </c>
       <c r="E451">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F451" t="s">
         <v>1603</v>
@@ -24084,7 +24084,7 @@
         <v>1571</v>
       </c>
       <c r="E452">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F452" t="s">
         <v>1603</v>
@@ -24119,7 +24119,7 @@
         <v>1571</v>
       </c>
       <c r="E453">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F453" t="s">
         <v>1606</v>
@@ -24154,7 +24154,7 @@
         <v>1571</v>
       </c>
       <c r="E454">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F454" t="s">
         <v>1603</v>
@@ -24189,7 +24189,7 @@
         <v>1571</v>
       </c>
       <c r="E455">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F455" t="s">
         <v>1603</v>
@@ -24224,7 +24224,7 @@
         <v>1571</v>
       </c>
       <c r="E456">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F456" t="s">
         <v>1603</v>
@@ -24259,7 +24259,7 @@
         <v>1571</v>
       </c>
       <c r="E457">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F457" t="s">
         <v>1605</v>
@@ -24297,7 +24297,7 @@
         <v>1571</v>
       </c>
       <c r="E458">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F458" t="s">
         <v>1603</v>
@@ -24332,7 +24332,7 @@
         <v>1571</v>
       </c>
       <c r="E459">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F459" t="s">
         <v>1607</v>
@@ -24367,7 +24367,7 @@
         <v>1571</v>
       </c>
       <c r="E460">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F460" t="s">
         <v>1603</v>
@@ -24402,7 +24402,7 @@
         <v>1571</v>
       </c>
       <c r="E461">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F461" t="s">
         <v>1603</v>
@@ -24437,7 +24437,7 @@
         <v>1572</v>
       </c>
       <c r="E462">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F462" t="s">
         <v>1603</v>
@@ -24472,7 +24472,7 @@
         <v>1572</v>
       </c>
       <c r="E463">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F463" t="s">
         <v>1603</v>
@@ -24507,7 +24507,7 @@
         <v>1572</v>
       </c>
       <c r="E464">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F464" t="s">
         <v>1603</v>
@@ -24542,7 +24542,7 @@
         <v>1572</v>
       </c>
       <c r="E465">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F465" t="s">
         <v>1603</v>
@@ -24577,7 +24577,7 @@
         <v>1572</v>
       </c>
       <c r="E466">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F466" t="s">
         <v>1603</v>
@@ -24612,7 +24612,7 @@
         <v>1572</v>
       </c>
       <c r="E467">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F467" t="s">
         <v>1605</v>
@@ -24647,7 +24647,7 @@
         <v>1572</v>
       </c>
       <c r="E468">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F468" t="s">
         <v>1603</v>
@@ -24682,7 +24682,7 @@
         <v>1572</v>
       </c>
       <c r="E469">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F469" t="s">
         <v>1603</v>
@@ -24717,7 +24717,7 @@
         <v>1573</v>
       </c>
       <c r="E470">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F470" t="s">
         <v>1603</v>
@@ -24752,7 +24752,7 @@
         <v>1573</v>
       </c>
       <c r="E471">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F471" t="s">
         <v>1603</v>
@@ -24787,7 +24787,7 @@
         <v>1573</v>
       </c>
       <c r="E472">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F472" t="s">
         <v>1603</v>
@@ -24822,7 +24822,7 @@
         <v>1573</v>
       </c>
       <c r="E473">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F473" t="s">
         <v>1603</v>
@@ -24857,7 +24857,7 @@
         <v>1573</v>
       </c>
       <c r="E474">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F474" t="s">
         <v>1603</v>
@@ -24892,7 +24892,7 @@
         <v>1574</v>
       </c>
       <c r="E475">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F475" t="s">
         <v>1603</v>
@@ -24927,7 +24927,7 @@
         <v>1574</v>
       </c>
       <c r="E476">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F476" t="s">
         <v>1603</v>
@@ -24962,7 +24962,7 @@
         <v>1574</v>
       </c>
       <c r="E477">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F477" t="s">
         <v>1603</v>
@@ -24997,7 +24997,7 @@
         <v>1574</v>
       </c>
       <c r="E478">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F478" t="s">
         <v>1603</v>
@@ -25032,7 +25032,7 @@
         <v>1574</v>
       </c>
       <c r="E479">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F479" t="s">
         <v>1603</v>
@@ -25070,7 +25070,7 @@
         <v>1575</v>
       </c>
       <c r="E480">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F480" t="s">
         <v>1603</v>
@@ -25105,7 +25105,7 @@
         <v>1575</v>
       </c>
       <c r="E481">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F481" t="s">
         <v>1603</v>
@@ -25140,7 +25140,7 @@
         <v>1575</v>
       </c>
       <c r="E482">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F482" t="s">
         <v>1603</v>
@@ -25175,7 +25175,7 @@
         <v>1575</v>
       </c>
       <c r="E483">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F483" t="s">
         <v>1603</v>
@@ -25210,7 +25210,7 @@
         <v>1575</v>
       </c>
       <c r="E484">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F484" t="s">
         <v>1603</v>
@@ -25245,7 +25245,7 @@
         <v>1575</v>
       </c>
       <c r="E485">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F485" t="s">
         <v>1603</v>
@@ -25280,7 +25280,7 @@
         <v>1576</v>
       </c>
       <c r="E486">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F486" t="s">
         <v>1603</v>
@@ -25315,7 +25315,7 @@
         <v>1576</v>
       </c>
       <c r="E487">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F487" t="s">
         <v>1603</v>
@@ -25350,7 +25350,7 @@
         <v>1576</v>
       </c>
       <c r="E488">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F488" t="s">
         <v>1603</v>
@@ -25385,7 +25385,7 @@
         <v>1577</v>
       </c>
       <c r="E489">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F489" t="s">
         <v>1603</v>
@@ -25420,7 +25420,7 @@
         <v>1578</v>
       </c>
       <c r="E490">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F490" t="s">
         <v>1603</v>
@@ -25455,7 +25455,7 @@
         <v>1578</v>
       </c>
       <c r="E491">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F491" t="s">
         <v>1603</v>
@@ -25490,7 +25490,7 @@
         <v>1578</v>
       </c>
       <c r="E492">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F492" t="s">
         <v>1605</v>
@@ -25528,7 +25528,7 @@
         <v>1578</v>
       </c>
       <c r="E493">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F493" t="s">
         <v>1603</v>
@@ -25563,7 +25563,7 @@
         <v>1578</v>
       </c>
       <c r="E494">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F494" t="s">
         <v>1603</v>
@@ -25598,7 +25598,7 @@
         <v>1579</v>
       </c>
       <c r="E495">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F495" t="s">
         <v>1603</v>
@@ -25633,7 +25633,7 @@
         <v>1579</v>
       </c>
       <c r="E496">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F496" t="s">
         <v>1603</v>
@@ -25668,7 +25668,7 @@
         <v>1579</v>
       </c>
       <c r="E497">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F497" t="s">
         <v>1603</v>
@@ -25703,7 +25703,7 @@
         <v>1579</v>
       </c>
       <c r="E498">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F498" t="s">
         <v>1603</v>
@@ -25738,7 +25738,7 @@
         <v>1579</v>
       </c>
       <c r="E499">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F499" t="s">
         <v>1603</v>
@@ -25773,7 +25773,7 @@
         <v>1580</v>
       </c>
       <c r="E500">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F500" t="s">
         <v>1603</v>
@@ -25808,7 +25808,7 @@
         <v>1580</v>
       </c>
       <c r="E501">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F501" t="s">
         <v>1603</v>
@@ -25843,7 +25843,7 @@
         <v>1580</v>
       </c>
       <c r="E502">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F502" t="s">
         <v>1603</v>
@@ -25878,7 +25878,7 @@
         <v>1580</v>
       </c>
       <c r="E503">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F503" t="s">
         <v>1603</v>
@@ -25913,7 +25913,7 @@
         <v>1580</v>
       </c>
       <c r="E504">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F504" t="s">
         <v>1603</v>
@@ -25948,7 +25948,7 @@
         <v>1580</v>
       </c>
       <c r="E505">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F505" t="s">
         <v>1603</v>
@@ -25983,7 +25983,7 @@
         <v>1580</v>
       </c>
       <c r="E506">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F506" t="s">
         <v>1603</v>
@@ -26018,7 +26018,7 @@
         <v>1580</v>
       </c>
       <c r="E507">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F507" t="s">
         <v>1603</v>
@@ -26053,7 +26053,7 @@
         <v>1581</v>
       </c>
       <c r="E508">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F508" t="s">
         <v>1603</v>
@@ -26088,7 +26088,7 @@
         <v>1581</v>
       </c>
       <c r="E509">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F509" t="s">
         <v>1603</v>
@@ -26123,7 +26123,7 @@
         <v>1582</v>
       </c>
       <c r="E510">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F510" t="s">
         <v>1603</v>
@@ -26158,7 +26158,7 @@
         <v>1582</v>
       </c>
       <c r="E511">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F511" t="s">
         <v>1603</v>
@@ -26193,7 +26193,7 @@
         <v>1582</v>
       </c>
       <c r="E512">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F512" t="s">
         <v>1603</v>
@@ -26228,7 +26228,7 @@
         <v>1582</v>
       </c>
       <c r="E513">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F513" t="s">
         <v>1607</v>
@@ -26266,7 +26266,7 @@
         <v>1582</v>
       </c>
       <c r="E514">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F514" t="s">
         <v>1603</v>
@@ -26301,7 +26301,7 @@
         <v>1582</v>
       </c>
       <c r="E515">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F515" t="s">
         <v>1607</v>
@@ -26336,7 +26336,7 @@
         <v>1583</v>
       </c>
       <c r="E516">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F516" t="s">
         <v>1603</v>
@@ -26371,7 +26371,7 @@
         <v>1584</v>
       </c>
       <c r="E517">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F517" t="s">
         <v>1603</v>
@@ -26406,7 +26406,7 @@
         <v>1584</v>
       </c>
       <c r="E518">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F518" t="s">
         <v>1603</v>
@@ -26441,7 +26441,7 @@
         <v>1584</v>
       </c>
       <c r="E519">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F519" t="s">
         <v>1603</v>
@@ -26476,7 +26476,7 @@
         <v>1584</v>
       </c>
       <c r="E520">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F520" t="s">
         <v>1603</v>
@@ -26511,7 +26511,7 @@
         <v>1585</v>
       </c>
       <c r="E521">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F521" t="s">
         <v>1603</v>
@@ -26546,7 +26546,7 @@
         <v>1585</v>
       </c>
       <c r="E522">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F522" t="s">
         <v>1607</v>
@@ -26581,7 +26581,7 @@
         <v>1585</v>
       </c>
       <c r="E523">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F523" t="s">
         <v>1603</v>
@@ -26616,7 +26616,7 @@
         <v>1585</v>
       </c>
       <c r="E524">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F524" t="s">
         <v>1603</v>
@@ -26651,7 +26651,7 @@
         <v>1585</v>
       </c>
       <c r="E525">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F525" t="s">
         <v>1603</v>
@@ -26686,7 +26686,7 @@
         <v>1586</v>
       </c>
       <c r="E526">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F526" t="s">
         <v>1603</v>
@@ -26721,7 +26721,7 @@
         <v>1586</v>
       </c>
       <c r="E527">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F527" t="s">
         <v>1605</v>
@@ -26756,7 +26756,7 @@
         <v>1586</v>
       </c>
       <c r="E528">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F528" t="s">
         <v>1603</v>
@@ -26791,7 +26791,7 @@
         <v>1586</v>
       </c>
       <c r="E529">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F529" t="s">
         <v>1603</v>
@@ -26826,7 +26826,7 @@
         <v>1587</v>
       </c>
       <c r="E530">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F530" t="s">
         <v>1603</v>
@@ -26861,7 +26861,7 @@
         <v>1587</v>
       </c>
       <c r="E531">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F531" t="s">
         <v>1603</v>
@@ -26896,7 +26896,7 @@
         <v>1587</v>
       </c>
       <c r="E532">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F532" t="s">
         <v>1603</v>
@@ -26931,7 +26931,7 @@
         <v>1587</v>
       </c>
       <c r="E533">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F533" t="s">
         <v>1603</v>
@@ -26966,7 +26966,7 @@
         <v>1587</v>
       </c>
       <c r="E534">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F534" t="s">
         <v>1603</v>
@@ -27001,7 +27001,7 @@
         <v>1587</v>
       </c>
       <c r="E535">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F535" t="s">
         <v>1603</v>
@@ -27036,7 +27036,7 @@
         <v>1588</v>
       </c>
       <c r="E536">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F536" t="s">
         <v>1603</v>
@@ -27071,7 +27071,7 @@
         <v>1588</v>
       </c>
       <c r="E537">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F537" t="s">
         <v>1603</v>
@@ -27106,7 +27106,7 @@
         <v>1588</v>
       </c>
       <c r="E538">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F538" t="s">
         <v>1603</v>
@@ -27141,7 +27141,7 @@
         <v>1588</v>
       </c>
       <c r="E539">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F539" t="s">
         <v>1603</v>
@@ -27176,7 +27176,7 @@
         <v>1588</v>
       </c>
       <c r="E540">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F540" t="s">
         <v>1603</v>
@@ -27211,7 +27211,7 @@
         <v>1588</v>
       </c>
       <c r="E541">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F541" t="s">
         <v>1603</v>
@@ -27246,7 +27246,7 @@
         <v>1588</v>
       </c>
       <c r="E542">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F542" t="s">
         <v>1603</v>
@@ -27281,7 +27281,7 @@
         <v>1588</v>
       </c>
       <c r="E543">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F543" t="s">
         <v>1603</v>
@@ -27316,7 +27316,7 @@
         <v>1588</v>
       </c>
       <c r="E544">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F544" t="s">
         <v>1603</v>
@@ -27351,7 +27351,7 @@
         <v>1588</v>
       </c>
       <c r="E545">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F545" t="s">
         <v>1603</v>
@@ -27386,7 +27386,7 @@
         <v>1588</v>
       </c>
       <c r="E546">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F546" t="s">
         <v>1603</v>
@@ -27421,7 +27421,7 @@
         <v>1588</v>
       </c>
       <c r="E547">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F547" t="s">
         <v>1603</v>
@@ -27456,7 +27456,7 @@
         <v>1588</v>
       </c>
       <c r="E548">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F548" t="s">
         <v>1603</v>
@@ -27491,7 +27491,7 @@
         <v>1588</v>
       </c>
       <c r="E549">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F549" t="s">
         <v>1603</v>
@@ -27526,7 +27526,7 @@
         <v>1588</v>
       </c>
       <c r="E550">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F550" t="s">
         <v>1603</v>
@@ -27561,7 +27561,7 @@
         <v>1588</v>
       </c>
       <c r="E551">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F551" t="s">
         <v>1603</v>
@@ -27596,7 +27596,7 @@
         <v>1588</v>
       </c>
       <c r="E552">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F552" t="s">
         <v>1603</v>
@@ -27631,7 +27631,7 @@
         <v>1588</v>
       </c>
       <c r="E553">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F553" t="s">
         <v>1603</v>
@@ -27666,7 +27666,7 @@
         <v>1588</v>
       </c>
       <c r="E554">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F554" t="s">
         <v>1603</v>
@@ -27701,7 +27701,7 @@
         <v>1588</v>
       </c>
       <c r="E555">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F555" t="s">
         <v>1603</v>
@@ -27736,7 +27736,7 @@
         <v>1588</v>
       </c>
       <c r="E556">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F556" t="s">
         <v>1603</v>
@@ -27771,7 +27771,7 @@
         <v>1588</v>
       </c>
       <c r="E557">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F557" t="s">
         <v>1603</v>
@@ -27806,7 +27806,7 @@
         <v>1588</v>
       </c>
       <c r="E558">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F558" t="s">
         <v>1603</v>
@@ -27841,7 +27841,7 @@
         <v>1588</v>
       </c>
       <c r="E559">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F559" t="s">
         <v>1603</v>
@@ -27876,7 +27876,7 @@
         <v>1588</v>
       </c>
       <c r="E560">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F560" t="s">
         <v>1603</v>
@@ -27911,7 +27911,7 @@
         <v>1588</v>
       </c>
       <c r="E561">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F561" t="s">
         <v>1603</v>
@@ -27946,7 +27946,7 @@
         <v>1588</v>
       </c>
       <c r="E562">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F562" t="s">
         <v>1605</v>
@@ -27984,7 +27984,7 @@
         <v>1589</v>
       </c>
       <c r="E563">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F563" t="s">
         <v>1603</v>
@@ -28019,7 +28019,7 @@
         <v>1589</v>
       </c>
       <c r="E564">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F564" t="s">
         <v>1603</v>
@@ -28054,7 +28054,7 @@
         <v>1589</v>
       </c>
       <c r="E565">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F565" t="s">
         <v>1603</v>
@@ -28089,7 +28089,7 @@
         <v>1589</v>
       </c>
       <c r="E566">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F566" t="s">
         <v>1603</v>
@@ -28124,7 +28124,7 @@
         <v>1589</v>
       </c>
       <c r="E567">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F567" t="s">
         <v>1603</v>
@@ -28159,7 +28159,7 @@
         <v>1589</v>
       </c>
       <c r="E568">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F568" t="s">
         <v>1603</v>
@@ -28194,7 +28194,7 @@
         <v>1589</v>
       </c>
       <c r="E569">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F569" t="s">
         <v>1607</v>
@@ -28229,7 +28229,7 @@
         <v>1589</v>
       </c>
       <c r="E570">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F570" t="s">
         <v>1603</v>
@@ -28264,7 +28264,7 @@
         <v>1590</v>
       </c>
       <c r="E571">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F571" t="s">
         <v>1603</v>
@@ -28299,7 +28299,7 @@
         <v>1590</v>
       </c>
       <c r="E572">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F572" t="s">
         <v>1603</v>
@@ -28334,7 +28334,7 @@
         <v>1591</v>
       </c>
       <c r="E573">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F573" t="s">
         <v>1603</v>
@@ -28369,7 +28369,7 @@
         <v>1591</v>
       </c>
       <c r="E574">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F574" t="s">
         <v>1605</v>
@@ -28407,7 +28407,7 @@
         <v>1591</v>
       </c>
       <c r="E575">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F575" t="s">
         <v>1605</v>
@@ -28445,7 +28445,7 @@
         <v>1592</v>
       </c>
       <c r="E576">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F576" t="s">
         <v>1605</v>
@@ -28483,7 +28483,7 @@
         <v>1592</v>
       </c>
       <c r="E577">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F577" t="s">
         <v>1603</v>
@@ -28518,7 +28518,7 @@
         <v>1592</v>
       </c>
       <c r="E578">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F578" t="s">
         <v>1603</v>
@@ -28553,7 +28553,7 @@
         <v>1592</v>
       </c>
       <c r="E579">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F579" t="s">
         <v>1605</v>
@@ -28591,7 +28591,7 @@
         <v>1592</v>
       </c>
       <c r="E580">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F580" t="s">
         <v>1603</v>
@@ -28626,7 +28626,7 @@
         <v>1592</v>
       </c>
       <c r="E581">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F581" t="s">
         <v>1603</v>
@@ -28661,7 +28661,7 @@
         <v>1592</v>
       </c>
       <c r="E582">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F582" t="s">
         <v>1603</v>
@@ -28696,7 +28696,7 @@
         <v>1592</v>
       </c>
       <c r="E583">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F583" t="s">
         <v>1603</v>
@@ -28734,7 +28734,7 @@
         <v>1592</v>
       </c>
       <c r="E584">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F584" t="s">
         <v>1603</v>
@@ -28769,7 +28769,7 @@
         <v>1592</v>
       </c>
       <c r="E585">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F585" t="s">
         <v>1603</v>
@@ -28804,7 +28804,7 @@
         <v>1593</v>
       </c>
       <c r="E586">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F586" t="s">
         <v>1603</v>
@@ -28842,7 +28842,7 @@
         <v>1593</v>
       </c>
       <c r="E587">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F587" t="s">
         <v>1607</v>
@@ -28877,7 +28877,7 @@
         <v>1593</v>
       </c>
       <c r="E588">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F588" t="s">
         <v>1605</v>
@@ -28912,7 +28912,7 @@
         <v>1593</v>
       </c>
       <c r="E589">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F589" t="s">
         <v>1603</v>
@@ -28947,7 +28947,7 @@
         <v>1593</v>
       </c>
       <c r="E590">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F590" t="s">
         <v>1605</v>
@@ -28985,7 +28985,7 @@
         <v>1593</v>
       </c>
       <c r="E591">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F591" t="s">
         <v>1603</v>
@@ -29020,7 +29020,7 @@
         <v>1593</v>
       </c>
       <c r="E592">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F592" t="s">
         <v>1603</v>
@@ -29055,7 +29055,7 @@
         <v>1593</v>
       </c>
       <c r="E593">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F593" t="s">
         <v>1603</v>
@@ -29090,7 +29090,7 @@
         <v>1593</v>
       </c>
       <c r="E594">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F594" t="s">
         <v>1603</v>
@@ -29125,7 +29125,7 @@
         <v>1593</v>
       </c>
       <c r="E595">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F595" t="s">
         <v>1603</v>
@@ -29160,7 +29160,7 @@
         <v>1594</v>
       </c>
       <c r="E596">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F596" t="s">
         <v>1603</v>
@@ -29198,7 +29198,7 @@
         <v>1594</v>
       </c>
       <c r="E597">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F597" t="s">
         <v>1603</v>
@@ -29233,7 +29233,7 @@
         <v>1595</v>
       </c>
       <c r="E598">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F598" t="s">
         <v>1603</v>
@@ -29268,7 +29268,7 @@
         <v>1595</v>
       </c>
       <c r="E599">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F599" t="s">
         <v>1605</v>
@@ -29306,7 +29306,7 @@
         <v>1595</v>
       </c>
       <c r="E600">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F600" t="s">
         <v>1603</v>
@@ -29341,7 +29341,7 @@
         <v>1595</v>
       </c>
       <c r="E601">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F601" t="s">
         <v>1603</v>
@@ -29376,7 +29376,7 @@
         <v>1595</v>
       </c>
       <c r="E602">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F602" t="s">
         <v>1603</v>
@@ -29411,7 +29411,7 @@
         <v>1595</v>
       </c>
       <c r="E603">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F603" t="s">
         <v>1603</v>
@@ -29446,7 +29446,7 @@
         <v>1595</v>
       </c>
       <c r="E604">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F604" t="s">
         <v>1603</v>
@@ -29481,7 +29481,7 @@
         <v>1595</v>
       </c>
       <c r="E605">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F605" t="s">
         <v>1605</v>
@@ -29516,7 +29516,7 @@
         <v>1595</v>
       </c>
       <c r="E606">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F606" t="s">
         <v>1603</v>
@@ -29551,7 +29551,7 @@
         <v>1595</v>
       </c>
       <c r="E607">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F607" t="s">
         <v>1603</v>
@@ -29586,7 +29586,7 @@
         <v>1596</v>
       </c>
       <c r="E608">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F608" t="s">
         <v>1603</v>
@@ -29621,7 +29621,7 @@
         <v>1596</v>
       </c>
       <c r="E609">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F609" t="s">
         <v>1603</v>
@@ -29656,7 +29656,7 @@
         <v>1596</v>
       </c>
       <c r="E610">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F610" t="s">
         <v>1603</v>
@@ -29691,7 +29691,7 @@
         <v>1596</v>
       </c>
       <c r="E611">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F611" t="s">
         <v>1603</v>
@@ -29726,7 +29726,7 @@
         <v>1596</v>
       </c>
       <c r="E612">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F612" t="s">
         <v>1605</v>
@@ -29764,7 +29764,7 @@
         <v>1596</v>
       </c>
       <c r="E613">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F613" t="s">
         <v>1603</v>
@@ -29799,7 +29799,7 @@
         <v>1596</v>
       </c>
       <c r="E614">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F614" t="s">
         <v>1603</v>
@@ -29834,7 +29834,7 @@
         <v>1596</v>
       </c>
       <c r="E615">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F615" t="s">
         <v>1603</v>
@@ -29869,7 +29869,7 @@
         <v>1596</v>
       </c>
       <c r="E616">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F616" t="s">
         <v>1603</v>
@@ -29904,7 +29904,7 @@
         <v>1596</v>
       </c>
       <c r="E617">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F617" t="s">
         <v>1605</v>
@@ -29939,7 +29939,7 @@
         <v>1596</v>
       </c>
       <c r="E618">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F618" t="s">
         <v>1603</v>
@@ -29974,7 +29974,7 @@
         <v>1596</v>
       </c>
       <c r="E619">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F619" t="s">
         <v>1607</v>
@@ -30009,7 +30009,7 @@
         <v>1596</v>
       </c>
       <c r="E620">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F620" t="s">
         <v>1603</v>
@@ -30044,7 +30044,7 @@
         <v>1597</v>
       </c>
       <c r="E621">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F621" t="s">
         <v>1605</v>
@@ -30082,7 +30082,7 @@
         <v>1597</v>
       </c>
       <c r="E622">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F622" t="s">
         <v>1603</v>
@@ -30117,7 +30117,7 @@
         <v>1597</v>
       </c>
       <c r="E623">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F623" t="s">
         <v>1603</v>
@@ -30152,7 +30152,7 @@
         <v>1597</v>
       </c>
       <c r="E624">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F624" t="s">
         <v>1603</v>
@@ -30187,7 +30187,7 @@
         <v>1597</v>
       </c>
       <c r="E625">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F625" t="s">
         <v>1603</v>
@@ -30222,7 +30222,7 @@
         <v>1597</v>
       </c>
       <c r="E626">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F626" t="s">
         <v>1603</v>
@@ -30257,7 +30257,7 @@
         <v>1597</v>
       </c>
       <c r="E627">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F627" t="s">
         <v>1603</v>
@@ -30292,7 +30292,7 @@
         <v>1597</v>
       </c>
       <c r="E628">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F628" t="s">
         <v>1603</v>
@@ -30327,7 +30327,7 @@
         <v>1597</v>
       </c>
       <c r="E629">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F629" t="s">
         <v>1603</v>
@@ -30362,7 +30362,7 @@
         <v>1597</v>
       </c>
       <c r="E630">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F630" t="s">
         <v>1603</v>
@@ -30400,7 +30400,7 @@
         <v>1597</v>
       </c>
       <c r="E631">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F631" t="s">
         <v>1605</v>
@@ -30438,7 +30438,7 @@
         <v>1597</v>
       </c>
       <c r="E632">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F632" t="s">
         <v>1603</v>
@@ -30473,7 +30473,7 @@
         <v>1597</v>
       </c>
       <c r="E633">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F633" t="s">
         <v>1605</v>
@@ -30508,7 +30508,7 @@
         <v>1597</v>
       </c>
       <c r="E634">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F634" t="s">
         <v>1605</v>
@@ -30543,7 +30543,7 @@
         <v>1597</v>
       </c>
       <c r="E635">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F635" t="s">
         <v>1603</v>
@@ -30578,7 +30578,7 @@
         <v>1598</v>
       </c>
       <c r="E636">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F636" t="s">
         <v>1603</v>
@@ -30613,7 +30613,7 @@
         <v>1598</v>
       </c>
       <c r="E637">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F637" t="s">
         <v>1603</v>
@@ -30648,7 +30648,7 @@
         <v>1598</v>
       </c>
       <c r="E638">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F638" t="s">
         <v>1603</v>
@@ -30683,7 +30683,7 @@
         <v>1598</v>
       </c>
       <c r="E639">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F639" t="s">
         <v>1603</v>
@@ -30718,7 +30718,7 @@
         <v>1598</v>
       </c>
       <c r="E640">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F640" t="s">
         <v>1603</v>
@@ -30753,7 +30753,7 @@
         <v>1598</v>
       </c>
       <c r="E641">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F641" t="s">
         <v>1603</v>
@@ -30788,7 +30788,7 @@
         <v>1598</v>
       </c>
       <c r="E642">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F642" t="s">
         <v>1603</v>
@@ -30823,7 +30823,7 @@
         <v>1598</v>
       </c>
       <c r="E643">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F643" t="s">
         <v>1603</v>
@@ -30858,7 +30858,7 @@
         <v>1598</v>
       </c>
       <c r="E644">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F644" t="s">
         <v>1603</v>
@@ -30893,7 +30893,7 @@
         <v>1598</v>
       </c>
       <c r="E645">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F645" t="s">
         <v>1603</v>
@@ -30931,7 +30931,7 @@
         <v>1599</v>
       </c>
       <c r="E646">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F646" t="s">
         <v>1603</v>
@@ -30966,7 +30966,7 @@
         <v>1599</v>
       </c>
       <c r="E647">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F647" t="s">
         <v>1603</v>
@@ -31001,7 +31001,7 @@
         <v>1600</v>
       </c>
       <c r="E648">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F648" t="s">
         <v>1603</v>
@@ -31039,7 +31039,7 @@
         <v>1600</v>
       </c>
       <c r="E649">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F649" t="s">
         <v>1603</v>
@@ -31074,7 +31074,7 @@
         <v>1600</v>
       </c>
       <c r="E650">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F650" t="s">
         <v>1603</v>
@@ -31109,7 +31109,7 @@
         <v>1600</v>
       </c>
       <c r="E651">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F651" t="s">
         <v>1605</v>
@@ -31147,7 +31147,7 @@
         <v>1600</v>
       </c>
       <c r="E652">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F652" t="s">
         <v>1603</v>
@@ -31185,7 +31185,7 @@
         <v>1600</v>
       </c>
       <c r="E653">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F653" t="s">
         <v>1603</v>
@@ -31220,7 +31220,7 @@
         <v>1600</v>
       </c>
       <c r="E654">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F654" t="s">
         <v>1603</v>
@@ -31255,7 +31255,7 @@
         <v>1600</v>
       </c>
       <c r="E655">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F655" t="s">
         <v>1603</v>
@@ -31290,7 +31290,7 @@
         <v>1601</v>
       </c>
       <c r="E656">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F656" t="s">
         <v>1603</v>
@@ -31325,7 +31325,7 @@
         <v>1601</v>
       </c>
       <c r="E657">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F657" t="s">
         <v>1603</v>
@@ -31360,7 +31360,7 @@
         <v>1601</v>
       </c>
       <c r="E658">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F658" t="s">
         <v>1603</v>
@@ -31395,7 +31395,7 @@
         <v>1601</v>
       </c>
       <c r="E659">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F659" t="s">
         <v>1603</v>
@@ -31430,7 +31430,7 @@
         <v>1601</v>
       </c>
       <c r="E660">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F660" t="s">
         <v>1603</v>
@@ -31465,7 +31465,7 @@
         <v>1601</v>
       </c>
       <c r="E661">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F661" t="s">
         <v>1603</v>
@@ -31500,7 +31500,7 @@
         <v>1601</v>
       </c>
       <c r="E662">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F662" t="s">
         <v>1603</v>
@@ -31535,7 +31535,7 @@
         <v>1601</v>
       </c>
       <c r="E663">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F663" t="s">
         <v>1603</v>
@@ -31570,7 +31570,7 @@
         <v>1601</v>
       </c>
       <c r="E664">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F664" t="s">
         <v>1603</v>
@@ -31605,7 +31605,7 @@
         <v>1601</v>
       </c>
       <c r="E665">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F665" t="s">
         <v>1603</v>
@@ -31640,7 +31640,7 @@
         <v>1601</v>
       </c>
       <c r="E666">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F666" t="s">
         <v>1603</v>
@@ -31675,7 +31675,7 @@
         <v>1601</v>
       </c>
       <c r="E667">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F667" t="s">
         <v>1603</v>
@@ -31710,7 +31710,7 @@
         <v>1601</v>
       </c>
       <c r="E668">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F668" t="s">
         <v>1603</v>
@@ -31748,7 +31748,7 @@
         <v>1601</v>
       </c>
       <c r="E669">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F669" t="s">
         <v>1603</v>
@@ -31786,7 +31786,7 @@
         <v>1601</v>
       </c>
       <c r="E670">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F670" t="s">
         <v>1603</v>
@@ -31824,7 +31824,7 @@
         <v>1601</v>
       </c>
       <c r="E671">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F671" t="s">
         <v>1603</v>
@@ -31859,7 +31859,7 @@
         <v>1601</v>
       </c>
       <c r="E672">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F672" t="s">
         <v>1603</v>
@@ -31897,7 +31897,7 @@
         <v>1602</v>
       </c>
       <c r="E673">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F673" t="s">
         <v>1603</v>
@@ -31932,7 +31932,7 @@
         <v>1602</v>
       </c>
       <c r="E674">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F674" t="s">
         <v>1603</v>
@@ -31970,7 +31970,7 @@
         <v>1602</v>
       </c>
       <c r="E675">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F675" t="s">
         <v>1603</v>
@@ -32005,7 +32005,7 @@
         <v>1602</v>
       </c>
       <c r="E676">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F676" t="s">
         <v>1603</v>
@@ -32040,7 +32040,7 @@
         <v>1602</v>
       </c>
       <c r="E677">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F677" t="s">
         <v>1603</v>

--- a/BacklogGATEAutoCompleto.xlsx
+++ b/BacklogGATEAutoCompleto.xlsx
@@ -4975,129 +4975,129 @@
     <t>LILIAN ALVES DE ARAUJO</t>
   </si>
   <si>
+    <t>ANDRÉA SILVA ARAUJO DE MELLO</t>
+  </si>
+  <si>
+    <t>CAIO EDUARDO BARBOSA DOS SANTOS FERREIRA,EDIWAN SOUSA DA SILVA</t>
+  </si>
+  <si>
+    <t>FERNANDA FERREIRA FONTES,SIMONE MANNHEIMER DE ALVARENGA</t>
+  </si>
+  <si>
+    <t>REGINA SILBERSTEIN RACHEVSKY</t>
+  </si>
+  <si>
+    <t>ANDRÉA ALVARENGA D´ALMEIDA MORAIS,CELSO SOARES BELFORT GARCIA</t>
+  </si>
+  <si>
+    <t>ROSEMARY PROVENZANO THAMI</t>
+  </si>
+  <si>
+    <t>MANOELA DE MORAES SILVA</t>
+  </si>
+  <si>
+    <t>LILIAN ALVES DE ARAUJO,SIMONE MANNHEIMER DE ALVARENGA</t>
+  </si>
+  <si>
+    <t>CELSO BARBOSA MONTENEGRO,PATRICIA PASSARO DA SILVA TOLEDO</t>
+  </si>
+  <si>
+    <t>MARINA DE AQUINO PARREIRA XAVIER,SERGIO PEDRO LOPES</t>
+  </si>
+  <si>
+    <t>LUZIA LAMOSA ARANTES</t>
+  </si>
+  <si>
+    <t>RODRIGO VENTURA MARRA</t>
+  </si>
+  <si>
+    <t>PABLO GINIO VIMERCATI SIMAS</t>
+  </si>
+  <si>
+    <t>MARIA JOSÉ LOPES DE ARAUJO SAROLDI</t>
+  </si>
+  <si>
+    <t>VICTOR AUGUSTO LOURO BERBARA</t>
+  </si>
+  <si>
+    <t>ALESSANDRA ALMEIDA DIAS DA SILVA,THIAGO JOSÉ DUPRAT FORTES, _SEM USUARIO ATRIBUIDO</t>
+  </si>
+  <si>
+    <t>ALESSANDRA ALMEIDA DIAS DA SILVA,DANIEL FONTANA OBERLING,JORGE LUIS DANTAS BATISTA</t>
+  </si>
+  <si>
+    <t>PEDRO MARCELO ROCHA GOMES</t>
+  </si>
+  <si>
+    <t>ELIANA MIRANDA ARAUJO DA SILVA SOARES,RODRIGO VENTURA MARRA</t>
+  </si>
+  <si>
+    <t>CLAUDIA DA SILVA LUNARDI,RENATA PASCOAL FREIRE</t>
+  </si>
+  <si>
+    <t>CASSIA CRISTINA DA SILVA</t>
+  </si>
+  <si>
+    <t>ITAMAR COSTA KALIL</t>
+  </si>
+  <si>
+    <t>FERNANDA FERREIRA FONTES</t>
+  </si>
+  <si>
+    <t>EDIWAN SOUSA DA SILVA,MAYRA LIMA VERISSIMO RAMOS MUNIVE</t>
+  </si>
+  <si>
+    <t>MARINA DE AQUINO PARREIRA XAVIER</t>
+  </si>
+  <si>
+    <t>HIAN GOMES DE OLIVEIRA DA COSTA</t>
+  </si>
+  <si>
+    <t>MOEMA BELLONI SCHMIDT,RENATA DE ARAUJO RIOS</t>
+  </si>
+  <si>
+    <t>LUIZ FRANCISCO PERALTA BRAGA,MARCELO SILVA DE AZEVEDO,ROMULO LUCIANO INOCENCIO</t>
+  </si>
+  <si>
+    <t>ALEXANDER MAGNO BORGES GOMES DA SILVA</t>
+  </si>
+  <si>
+    <t>PEDRO HENRIQUE DE MESQUITA MAGALHÃES</t>
+  </si>
+  <si>
+    <t>CARLOS FELIPE DA GRAÇA SILVA,MARCELO TEIXEIRA SANTANA,MARIA JOSÉ LOPES DE ARAUJO SAROLDI</t>
+  </si>
+  <si>
+    <t>EDUARDO COUTO SOLEDADE</t>
+  </si>
+  <si>
+    <t>ERIKA SILVEIRA PAES BARRETO ALVES</t>
+  </si>
+  <si>
+    <t>DAGER SALLES AMARAL</t>
+  </si>
+  <si>
+    <t>GIULIANA DE ANDRADE CERVAI</t>
+  </si>
+  <si>
+    <t>MARCELO TEIXEIRA SANTANA,MARIA JOSÉ LOPES DE ARAUJO SAROLDI,SIMONE MANNHEIMER DE ALVARENGA</t>
+  </si>
+  <si>
+    <t>JULIANA MARTINS BAHIENSE,RODRIGO VENTURA MARRA</t>
+  </si>
+  <si>
+    <t>IZABEL REGINA BENITE AGUIAR DA SILVA,VANESSA FERNANDES LEÃO</t>
+  </si>
+  <si>
+    <t>LUIZ FRANCISCO PERALTA BRAGA,MARCELO SILVA DE AZEVEDO</t>
+  </si>
+  <si>
+    <t>CARLOS FELIPE DA GRAÇA SILVA</t>
+  </si>
+  <si>
     <t>JORGE LUIS DANTAS BATISTA</t>
   </si>
   <si>
-    <t>CAIO EDUARDO BARBOSA DOS SANTOS FERREIRA,EDIWAN SOUSA DA SILVA</t>
-  </si>
-  <si>
-    <t>FERNANDA FERREIRA FONTES,SIMONE MANNHEIMER DE ALVARENGA</t>
-  </si>
-  <si>
-    <t>REGINA SILBERSTEIN RACHEVSKY</t>
-  </si>
-  <si>
-    <t>ANDRÉA ALVARENGA D´ALMEIDA MORAIS,CELSO SOARES BELFORT GARCIA</t>
-  </si>
-  <si>
-    <t>ROSEMARY PROVENZANO THAMI</t>
-  </si>
-  <si>
-    <t>MANOELA DE MORAES SILVA</t>
-  </si>
-  <si>
-    <t>LILIAN ALVES DE ARAUJO,SIMONE MANNHEIMER DE ALVARENGA</t>
-  </si>
-  <si>
-    <t>CELSO BARBOSA MONTENEGRO,PATRICIA PASSARO DA SILVA TOLEDO</t>
-  </si>
-  <si>
-    <t>MARINA DE AQUINO PARREIRA XAVIER,SERGIO PEDRO LOPES</t>
-  </si>
-  <si>
-    <t>LUZIA LAMOSA ARANTES</t>
-  </si>
-  <si>
-    <t>RODRIGO VENTURA MARRA</t>
-  </si>
-  <si>
-    <t>PABLO GINIO VIMERCATI SIMAS</t>
-  </si>
-  <si>
-    <t>MARIA JOSÉ LOPES DE ARAUJO SAROLDI</t>
-  </si>
-  <si>
-    <t>VICTOR AUGUSTO LOURO BERBARA</t>
-  </si>
-  <si>
-    <t>ALESSANDRA ALMEIDA DIAS DA SILVA,THIAGO JOSÉ DUPRAT FORTES, _SEM USUARIO ATRIBUIDO</t>
-  </si>
-  <si>
-    <t>ALESSANDRA ALMEIDA DIAS DA SILVA,DANIEL FONTANA OBERLING,JORGE LUIS DANTAS BATISTA</t>
-  </si>
-  <si>
-    <t>PEDRO MARCELO ROCHA GOMES</t>
-  </si>
-  <si>
-    <t>ELIANA MIRANDA ARAUJO DA SILVA SOARES,RODRIGO VENTURA MARRA</t>
-  </si>
-  <si>
-    <t>CLAUDIA DA SILVA LUNARDI,RENATA PASCOAL FREIRE</t>
-  </si>
-  <si>
-    <t>CASSIA CRISTINA DA SILVA</t>
-  </si>
-  <si>
-    <t>ANDRÉA SILVA ARAUJO DE MELLO</t>
-  </si>
-  <si>
-    <t>ITAMAR COSTA KALIL</t>
-  </si>
-  <si>
-    <t>FERNANDA FERREIRA FONTES</t>
-  </si>
-  <si>
-    <t>EDIWAN SOUSA DA SILVA,MAYRA LIMA VERISSIMO RAMOS MUNIVE</t>
-  </si>
-  <si>
-    <t>MARINA DE AQUINO PARREIRA XAVIER</t>
-  </si>
-  <si>
-    <t>HIAN GOMES DE OLIVEIRA DA COSTA</t>
-  </si>
-  <si>
-    <t>MOEMA BELLONI SCHMIDT,RENATA DE ARAUJO RIOS</t>
-  </si>
-  <si>
-    <t>LUIZ FRANCISCO PERALTA BRAGA,MARCELO SILVA DE AZEVEDO,ROMULO LUCIANO INOCENCIO</t>
-  </si>
-  <si>
-    <t>ALEXANDER MAGNO BORGES GOMES DA SILVA</t>
-  </si>
-  <si>
-    <t>PEDRO HENRIQUE DE MESQUITA MAGALHÃES</t>
-  </si>
-  <si>
-    <t>CARLOS FELIPE DA GRAÇA SILVA,MARCELO TEIXEIRA SANTANA,MARIA JOSÉ LOPES DE ARAUJO SAROLDI</t>
-  </si>
-  <si>
-    <t>EDUARDO COUTO SOLEDADE</t>
-  </si>
-  <si>
-    <t>ERIKA SILVEIRA PAES BARRETO ALVES</t>
-  </si>
-  <si>
-    <t>DAGER SALLES AMARAL</t>
-  </si>
-  <si>
-    <t>GIULIANA DE ANDRADE CERVAI</t>
-  </si>
-  <si>
-    <t>MARCELO TEIXEIRA SANTANA,MARIA JOSÉ LOPES DE ARAUJO SAROLDI,SIMONE MANNHEIMER DE ALVARENGA</t>
-  </si>
-  <si>
-    <t>JULIANA MARTINS BAHIENSE,RODRIGO VENTURA MARRA</t>
-  </si>
-  <si>
-    <t>IZABEL REGINA BENITE AGUIAR DA SILVA,VANESSA FERNANDES LEÃO</t>
-  </si>
-  <si>
-    <t>LUIZ FRANCISCO PERALTA BRAGA,MARCELO SILVA DE AZEVEDO</t>
-  </si>
-  <si>
-    <t>CARLOS FELIPE DA GRAÇA SILVA</t>
-  </si>
-  <si>
     <t>DANIEL FONTANA OBERLING</t>
   </si>
   <si>
@@ -5176,33 +5176,33 @@
     <t>HELENA FERREIRA DE LIMA</t>
   </si>
   <si>
+    <t>LUIZ FRANCISCO PERALTA BRAGA,MARCELO SILVA DE AZEVEDO, _SEM USUARIO ATRIBUIDO</t>
+  </si>
+  <si>
+    <t>SERGIO PEDRO LOPES</t>
+  </si>
+  <si>
+    <t>HEITOR DE FÁTIMA BARBOSA DA SILVA</t>
+  </si>
+  <si>
+    <t>ROMULO LUCIANO INOCENCIO</t>
+  </si>
+  <si>
+    <t>RENATA DE ARAUJO RIOS</t>
+  </si>
+  <si>
+    <t>LEONARDO ARAÚJO DE SOUZA,MOEMA BELLONI SCHMIDT</t>
+  </si>
+  <si>
+    <t>MARCELO KOLBLINGER DE GODOY</t>
+  </si>
+  <si>
+    <t>SEZISNANDO JOSE PRIMO PAES</t>
+  </si>
+  <si>
     <t>FERNANDA TEIXEIRA ROSALBA</t>
   </si>
   <si>
-    <t>LUIZ FRANCISCO PERALTA BRAGA,MARCELO SILVA DE AZEVEDO, _SEM USUARIO ATRIBUIDO</t>
-  </si>
-  <si>
-    <t>SERGIO PEDRO LOPES</t>
-  </si>
-  <si>
-    <t>HEITOR DE FÁTIMA BARBOSA DA SILVA</t>
-  </si>
-  <si>
-    <t>ROMULO LUCIANO INOCENCIO</t>
-  </si>
-  <si>
-    <t>RENATA DE ARAUJO RIOS</t>
-  </si>
-  <si>
-    <t>LEONARDO ARAÚJO DE SOUZA,MOEMA BELLONI SCHMIDT</t>
-  </si>
-  <si>
-    <t>MARCELO KOLBLINGER DE GODOY</t>
-  </si>
-  <si>
-    <t>SEZISNANDO JOSE PRIMO PAES</t>
-  </si>
-  <si>
     <t>MOEMA BELLONI SCHMIDT</t>
   </si>
   <si>
@@ -7822,7 +7822,7 @@
     <t>BIOLOGIA,RESÍDUOS SÓLIDOS</t>
   </si>
   <si>
-    <t>ECONOMICIDADE OBRAS,ENGENHARIA CIVIL</t>
+    <t>ENGENHARIA CIVIL,ECONOMICIDADE OBRAS</t>
   </si>
   <si>
     <t>RECURSOS HÍDRICOS,URBANISMO</t>
@@ -7855,7 +7855,7 @@
     <t>ECONOMICIDADE CONTÁBIL,RECURSOS HÍDRICOS</t>
   </si>
   <si>
-    <t>ECONOMICIDADE OBRAS,MOBILIDADE E TRANSPORTE</t>
+    <t>MOBILIDADE E TRANSPORTE,ECONOMICIDADE OBRAS</t>
   </si>
   <si>
     <t>ECONOMICIDADE OBRAS,RECURSOS HÍDRICOS</t>
@@ -7894,19 +7894,19 @@
     <t>RECURSOS HÍDRICOS,VALORAÇÃO DANOS AMBIENTAIS</t>
   </si>
   <si>
-    <t>ASSISTÊNCIA SOCIAL,EDIFICAÇÕES</t>
+    <t>EDIFICAÇÕES,ASSISTÊNCIA SOCIAL</t>
   </si>
   <si>
     <t>AVALIAÇÃO DE IMÓVEIS,ECONOMICIDADE OBRAS</t>
   </si>
   <si>
-    <t>FENOMENOS DE ENERGIA E INFORMAÇÃO,ENGENHARIA CIVIL</t>
+    <t>URBANISMO,BIOLOGIA</t>
   </si>
   <si>
     <t>GEOTECNIA,ENGENHARIA CIVIL</t>
   </si>
   <si>
-    <t>SAÚDE MENTAL,ORÇAMENTO,AVALIAÇÃO DE IMÓVEIS,MOBILIDADE E TRANSPORTE,URBANISMO,PSICOLOGIA,ECONOMICIDADE CONTÁBIL,SAÚDE,ASSISTÊNCIA SOCIAL,ECONOMIA</t>
+    <t>URBANISMO,ECONOMICIDADE CONTÁBIL,ORÇAMENTO,SAÚDE MENTAL,PSICOLOGIA,ECONOMIA,MOBILIDADE E TRANSPORTE,AVALIAÇÃO DE IMÓVEIS,ASSISTÊNCIA SOCIAL,SAÚDE</t>
   </si>
 </sst>
 </file>
@@ -10165,7 +10165,7 @@
     </row>
     <row r="55" spans="1:12">
       <c r="A55" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="B55" t="s">
         <v>94</v>
@@ -10361,7 +10361,7 @@
         <v>1612</v>
       </c>
       <c r="I60" t="s">
-        <v>1638</v>
+        <v>1653</v>
       </c>
       <c r="J60" t="s">
         <v>1818</v>
@@ -12636,7 +12636,7 @@
         <v>1612</v>
       </c>
       <c r="I125" t="s">
-        <v>1674</v>
+        <v>1653</v>
       </c>
       <c r="J125" t="s">
         <v>1882</v>
@@ -12671,7 +12671,7 @@
         <v>1612</v>
       </c>
       <c r="I126" t="s">
-        <v>1675</v>
+        <v>1674</v>
       </c>
       <c r="J126" t="s">
         <v>1883</v>
@@ -12741,7 +12741,7 @@
         <v>1612</v>
       </c>
       <c r="I128" t="s">
-        <v>1676</v>
+        <v>1675</v>
       </c>
       <c r="J128" t="s">
         <v>1885</v>
@@ -12951,7 +12951,7 @@
         <v>1612</v>
       </c>
       <c r="I134" t="s">
-        <v>1677</v>
+        <v>1676</v>
       </c>
       <c r="J134" t="s">
         <v>1891</v>
@@ -13021,7 +13021,7 @@
         <v>1612</v>
       </c>
       <c r="I136" t="s">
-        <v>1678</v>
+        <v>1677</v>
       </c>
       <c r="J136" t="s">
         <v>1893</v>
@@ -13091,7 +13091,7 @@
         <v>1612</v>
       </c>
       <c r="I138" t="s">
-        <v>1679</v>
+        <v>1678</v>
       </c>
       <c r="J138" t="s">
         <v>1895</v>
@@ -13126,7 +13126,7 @@
         <v>1612</v>
       </c>
       <c r="I139" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
       <c r="J139" t="s">
         <v>1896</v>
@@ -13161,7 +13161,7 @@
         <v>1612</v>
       </c>
       <c r="I140" t="s">
-        <v>1681</v>
+        <v>1680</v>
       </c>
       <c r="J140" t="s">
         <v>1897</v>
@@ -13231,7 +13231,7 @@
         <v>1612</v>
       </c>
       <c r="I142" t="s">
-        <v>1682</v>
+        <v>1681</v>
       </c>
       <c r="J142" t="s">
         <v>1899</v>
@@ -13406,7 +13406,7 @@
         <v>1612</v>
       </c>
       <c r="I147" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="J147" t="s">
         <v>1904</v>
@@ -13546,7 +13546,7 @@
         <v>1612</v>
       </c>
       <c r="I151" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="J151" t="s">
         <v>1908</v>
@@ -13654,7 +13654,7 @@
         <v>1612</v>
       </c>
       <c r="I154" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
       <c r="J154" t="s">
         <v>1911</v>
@@ -13794,7 +13794,7 @@
         <v>1612</v>
       </c>
       <c r="I158" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
       <c r="J158" t="s">
         <v>1915</v>
@@ -13829,7 +13829,7 @@
         <v>1612</v>
       </c>
       <c r="I159" t="s">
-        <v>1687</v>
+        <v>1686</v>
       </c>
       <c r="J159" t="s">
         <v>1916</v>
@@ -13899,7 +13899,7 @@
         <v>1612</v>
       </c>
       <c r="I161" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
       <c r="J161" t="s">
         <v>1918</v>
@@ -13969,7 +13969,7 @@
         <v>1612</v>
       </c>
       <c r="I163" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="J163" t="s">
         <v>1920</v>
@@ -14109,7 +14109,7 @@
         <v>1612</v>
       </c>
       <c r="I167" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="J167" t="s">
         <v>1924</v>
@@ -14144,7 +14144,7 @@
         <v>1612</v>
       </c>
       <c r="I168" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
       <c r="J168" t="s">
         <v>1925</v>
@@ -14284,7 +14284,7 @@
         <v>1612</v>
       </c>
       <c r="I172" t="s">
-        <v>1682</v>
+        <v>1681</v>
       </c>
       <c r="J172" t="s">
         <v>1929</v>
@@ -14354,7 +14354,7 @@
         <v>1612</v>
       </c>
       <c r="I174" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="J174" t="s">
         <v>1931</v>
@@ -14389,7 +14389,7 @@
         <v>1612</v>
       </c>
       <c r="I175" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="J175" t="s">
         <v>1932</v>
@@ -14459,7 +14459,7 @@
         <v>1612</v>
       </c>
       <c r="I177" t="s">
-        <v>1678</v>
+        <v>1677</v>
       </c>
       <c r="J177" t="s">
         <v>1934</v>
@@ -14739,7 +14739,7 @@
         <v>1612</v>
       </c>
       <c r="I185" t="s">
-        <v>1653</v>
+        <v>1693</v>
       </c>
       <c r="J185" t="s">
         <v>1941</v>
@@ -14949,7 +14949,7 @@
         <v>1612</v>
       </c>
       <c r="I191" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
       <c r="J191" t="s">
         <v>1947</v>
@@ -15544,7 +15544,7 @@
         <v>1612</v>
       </c>
       <c r="I208" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="J208" t="s">
         <v>1963</v>
@@ -15614,7 +15614,7 @@
         <v>1612</v>
       </c>
       <c r="I210" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="J210" t="s">
         <v>1965</v>
@@ -16559,7 +16559,7 @@
         <v>1612</v>
       </c>
       <c r="I237" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="J237" t="s">
         <v>1992</v>
@@ -16734,7 +16734,7 @@
         <v>1612</v>
       </c>
       <c r="I242" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="J242" t="s">
         <v>1997</v>
@@ -17364,7 +17364,7 @@
         <v>1612</v>
       </c>
       <c r="I260" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="J260" t="s">
         <v>2015</v>
@@ -17612,7 +17612,7 @@
         <v>1617</v>
       </c>
       <c r="I267" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="J267" t="s">
         <v>2022</v>
@@ -18207,7 +18207,7 @@
         <v>1612</v>
       </c>
       <c r="I284" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="J284" t="s">
         <v>2039</v>
@@ -18242,7 +18242,7 @@
         <v>1612</v>
       </c>
       <c r="I285" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
       <c r="J285" t="s">
         <v>2040</v>
@@ -18417,7 +18417,7 @@
         <v>1612</v>
       </c>
       <c r="I290" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="J290" t="s">
         <v>2045</v>
@@ -18606,7 +18606,7 @@
     </row>
     <row r="296" spans="1:12">
       <c r="A296" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="B296" t="s">
         <v>335</v>
@@ -18627,7 +18627,7 @@
         <v>1612</v>
       </c>
       <c r="I296" t="s">
-        <v>1720</v>
+        <v>1638</v>
       </c>
       <c r="J296" t="s">
         <v>2051</v>
@@ -18697,7 +18697,7 @@
         <v>1612</v>
       </c>
       <c r="I298" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="J298" t="s">
         <v>2053</v>
@@ -18732,7 +18732,7 @@
         <v>1612</v>
       </c>
       <c r="I299" t="s">
-        <v>1721</v>
+        <v>1720</v>
       </c>
       <c r="J299" t="s">
         <v>2054</v>
@@ -18907,7 +18907,7 @@
         <v>1612</v>
       </c>
       <c r="I304" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="J304" t="s">
         <v>2059</v>
@@ -18942,7 +18942,7 @@
         <v>1612</v>
       </c>
       <c r="I305" t="s">
-        <v>1722</v>
+        <v>1721</v>
       </c>
       <c r="J305" t="s">
         <v>2060</v>
@@ -19158,7 +19158,7 @@
         <v>1618</v>
       </c>
       <c r="I311" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="J311" t="s">
         <v>2066</v>
@@ -19193,7 +19193,7 @@
         <v>1612</v>
       </c>
       <c r="I312" t="s">
-        <v>1723</v>
+        <v>1722</v>
       </c>
       <c r="J312" t="s">
         <v>2067</v>
@@ -19368,7 +19368,7 @@
         <v>1612</v>
       </c>
       <c r="I317" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="J317" t="s">
         <v>2072</v>
@@ -19438,7 +19438,7 @@
         <v>1612</v>
       </c>
       <c r="I319" t="s">
-        <v>1724</v>
+        <v>1723</v>
       </c>
       <c r="J319" t="s">
         <v>2074</v>
@@ -19543,7 +19543,7 @@
         <v>1612</v>
       </c>
       <c r="I322" t="s">
-        <v>1725</v>
+        <v>1724</v>
       </c>
       <c r="J322" t="s">
         <v>2077</v>
@@ -19578,7 +19578,7 @@
         <v>1612</v>
       </c>
       <c r="I323" t="s">
-        <v>1726</v>
+        <v>1725</v>
       </c>
       <c r="J323" t="s">
         <v>2078</v>
@@ -19613,7 +19613,7 @@
         <v>1612</v>
       </c>
       <c r="I324" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="J324" t="s">
         <v>2079</v>
@@ -19648,7 +19648,7 @@
         <v>1612</v>
       </c>
       <c r="I325" t="s">
-        <v>1727</v>
+        <v>1726</v>
       </c>
       <c r="J325" t="s">
         <v>2080</v>
@@ -19718,7 +19718,7 @@
         <v>1612</v>
       </c>
       <c r="I327" t="s">
-        <v>1728</v>
+        <v>1727</v>
       </c>
       <c r="J327" t="s">
         <v>2082</v>
@@ -19858,7 +19858,7 @@
         <v>1612</v>
       </c>
       <c r="I331" t="s">
-        <v>1720</v>
+        <v>1728</v>
       </c>
       <c r="J331" t="s">
         <v>2086</v>
@@ -20033,7 +20033,7 @@
         <v>1612</v>
       </c>
       <c r="I336" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="J336" t="s">
         <v>2091</v>
@@ -20278,7 +20278,7 @@
         <v>1612</v>
       </c>
       <c r="I343" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="J343" t="s">
         <v>2098</v>
@@ -20733,7 +20733,7 @@
         <v>1612</v>
       </c>
       <c r="I356" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="J356" t="s">
         <v>2111</v>
@@ -21328,7 +21328,7 @@
         <v>1612</v>
       </c>
       <c r="I373" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="J373" t="s">
         <v>2128</v>
@@ -21678,7 +21678,7 @@
         <v>1612</v>
       </c>
       <c r="I383" t="s">
-        <v>1727</v>
+        <v>1726</v>
       </c>
       <c r="J383" t="s">
         <v>2138</v>
@@ -21996,7 +21996,7 @@
         <v>1612</v>
       </c>
       <c r="I392" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="J392" t="s">
         <v>2147</v>
@@ -22384,7 +22384,7 @@
         <v>1612</v>
       </c>
       <c r="I403" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="J403" t="s">
         <v>2158</v>
@@ -22982,7 +22982,7 @@
         <v>1612</v>
       </c>
       <c r="I420" t="s">
-        <v>1725</v>
+        <v>1724</v>
       </c>
       <c r="J420" t="s">
         <v>2175</v>
@@ -23017,7 +23017,7 @@
         <v>1612</v>
       </c>
       <c r="I421" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="J421" t="s">
         <v>2176</v>
@@ -23052,7 +23052,7 @@
         <v>1612</v>
       </c>
       <c r="I422" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="J422" t="s">
         <v>2177</v>
@@ -23157,7 +23157,7 @@
         <v>1612</v>
       </c>
       <c r="I425" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="J425" t="s">
         <v>2180</v>
@@ -23332,7 +23332,7 @@
         <v>1612</v>
       </c>
       <c r="I430" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="J430" t="s">
         <v>2185</v>
@@ -23437,7 +23437,7 @@
         <v>1612</v>
       </c>
       <c r="I433" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="J433" t="s">
         <v>2188</v>
@@ -24315,7 +24315,7 @@
         <v>1612</v>
       </c>
       <c r="I458" t="s">
-        <v>1676</v>
+        <v>1675</v>
       </c>
       <c r="J458" t="s">
         <v>2212</v>
@@ -24350,7 +24350,7 @@
         <v>1612</v>
       </c>
       <c r="I459" t="s">
-        <v>1676</v>
+        <v>1675</v>
       </c>
       <c r="J459" t="s">
         <v>2212</v>
@@ -24420,7 +24420,7 @@
         <v>1612</v>
       </c>
       <c r="I461" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="J461" t="s">
         <v>2214</v>
@@ -26036,7 +26036,7 @@
         <v>1612</v>
       </c>
       <c r="I507" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="J507" t="s">
         <v>2260</v>
@@ -26141,7 +26141,7 @@
         <v>1612</v>
       </c>
       <c r="I510" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="J510" t="s">
         <v>2263</v>
@@ -26249,7 +26249,7 @@
         <v>1623</v>
       </c>
       <c r="I513" t="s">
-        <v>1679</v>
+        <v>1678</v>
       </c>
       <c r="J513" t="s">
         <v>2265</v>
@@ -26459,7 +26459,7 @@
         <v>1612</v>
       </c>
       <c r="I519" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="J519" t="s">
         <v>2271</v>
@@ -26704,7 +26704,7 @@
         <v>1612</v>
       </c>
       <c r="I526" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="J526" t="s">
         <v>2278</v>
@@ -26774,7 +26774,7 @@
         <v>1612</v>
       </c>
       <c r="I528" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="J528" t="s">
         <v>2280</v>
@@ -28002,7 +28002,7 @@
         <v>1612</v>
       </c>
       <c r="I563" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="J563" t="s">
         <v>2315</v>
@@ -28037,7 +28037,7 @@
         <v>1612</v>
       </c>
       <c r="I564" t="s">
-        <v>1674</v>
+        <v>1653</v>
       </c>
       <c r="J564" t="s">
         <v>2316</v>
@@ -28787,7 +28787,7 @@
         <v>1612</v>
       </c>
       <c r="I585" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="J585" t="s">
         <v>2333</v>
@@ -28895,7 +28895,7 @@
         <v>1612</v>
       </c>
       <c r="I588" t="s">
-        <v>1726</v>
+        <v>1725</v>
       </c>
       <c r="J588" t="s">
         <v>2336</v>
@@ -28930,7 +28930,7 @@
         <v>1612</v>
       </c>
       <c r="I589" t="s">
-        <v>1674</v>
+        <v>1653</v>
       </c>
       <c r="J589" t="s">
         <v>2337</v>
@@ -28968,7 +28968,7 @@
         <v>1606</v>
       </c>
       <c r="I590" t="s">
-        <v>1638</v>
+        <v>1653</v>
       </c>
       <c r="J590" t="s">
         <v>2338</v>
@@ -29324,7 +29324,7 @@
         <v>1612</v>
       </c>
       <c r="I600" t="s">
-        <v>1674</v>
+        <v>1653</v>
       </c>
       <c r="J600" t="s">
         <v>2348</v>
@@ -29359,7 +29359,7 @@
         <v>1612</v>
       </c>
       <c r="I601" t="s">
-        <v>1675</v>
+        <v>1674</v>
       </c>
       <c r="J601" t="s">
         <v>2349</v>
@@ -29709,7 +29709,7 @@
         <v>1612</v>
       </c>
       <c r="I611" t="s">
-        <v>1674</v>
+        <v>1653</v>
       </c>
       <c r="J611" t="s">
         <v>2359</v>
@@ -30027,7 +30027,7 @@
         <v>1612</v>
       </c>
       <c r="I620" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="J620" t="s">
         <v>2367</v>
@@ -30100,7 +30100,7 @@
         <v>1612</v>
       </c>
       <c r="I622" t="s">
-        <v>1674</v>
+        <v>1653</v>
       </c>
       <c r="J622" t="s">
         <v>2369</v>
@@ -30348,7 +30348,7 @@
         <v>1624</v>
       </c>
       <c r="I629" t="s">
-        <v>1681</v>
+        <v>1680</v>
       </c>
       <c r="J629" t="s">
         <v>2376</v>
@@ -30386,7 +30386,7 @@
         <v>1624</v>
       </c>
       <c r="I630" t="s">
-        <v>1681</v>
+        <v>1680</v>
       </c>
       <c r="J630" t="s">
         <v>2376</v>
@@ -30491,7 +30491,7 @@
         <v>1612</v>
       </c>
       <c r="I633" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
       <c r="J633" t="s">
         <v>2379</v>
@@ -31142,7 +31142,7 @@
         <v>2437</v>
       </c>
       <c r="L651" t="s">
-        <v>2549</v>
+        <v>2628</v>
       </c>
     </row>
     <row r="652" spans="1:12">
@@ -31483,7 +31483,7 @@
         <v>1612</v>
       </c>
       <c r="I661" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="J661" t="s">
         <v>2404</v>
@@ -31597,7 +31597,7 @@
         <v>2537</v>
       </c>
       <c r="L664" t="s">
-        <v>2628</v>
+        <v>2622</v>
       </c>
     </row>
     <row r="665" spans="1:12">
@@ -31927,7 +31927,7 @@
         <v>2465</v>
       </c>
       <c r="L673" t="s">
-        <v>2605</v>
+        <v>2570</v>
       </c>
     </row>
     <row r="674" spans="1:12">
@@ -32002,7 +32002,7 @@
     </row>
     <row r="676" spans="1:12">
       <c r="A676" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B676" t="s">
         <v>711</v>
@@ -32023,7 +32023,7 @@
         <v>1612</v>
       </c>
       <c r="I676" t="s">
-        <v>1638</v>
+        <v>1732</v>
       </c>
       <c r="J676" t="s">
         <v>2418</v>
@@ -32037,7 +32037,7 @@
     </row>
     <row r="677" spans="1:12">
       <c r="A677" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B677" t="s">
         <v>712</v>
@@ -32058,7 +32058,7 @@
         <v>1612</v>
       </c>
       <c r="I677" t="s">
-        <v>1638</v>
+        <v>1759</v>
       </c>
       <c r="J677" t="s">
         <v>2419</v>

--- a/BacklogGATEAutoCompleto.xlsx
+++ b/BacklogGATEAutoCompleto.xlsx
@@ -2176,12 +2176,12 @@
     <t>20.22.0001.0022126.2021-43</t>
   </si>
   <si>
+    <t>20.22.0001.0006465.2026-52</t>
+  </si>
+  <si>
     <t>20.22.0001.0010728.2022-05</t>
   </si>
   <si>
-    <t>20.22.0001.0006465.2026-52</t>
-  </si>
-  <si>
     <t>20.22.0001.0006163.2021-73</t>
   </si>
   <si>
@@ -4222,12 +4222,12 @@
     <t>2051234</t>
   </si>
   <si>
+    <t>2026.0095</t>
+  </si>
+  <si>
     <t>1427672</t>
   </si>
   <si>
-    <t>2026.0095</t>
-  </si>
-  <si>
     <t>1695198</t>
   </si>
   <si>
@@ -7333,10 +7333,10 @@
     <t>201800611246</t>
   </si>
   <si>
+    <t>202400093563</t>
+  </si>
+  <si>
     <t>202200161771</t>
-  </si>
-  <si>
-    <t>202400093563</t>
   </si>
   <si>
     <t>0000000000000</t>
@@ -8382,7 +8382,7 @@
         <v>1405</v>
       </c>
       <c r="E2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="F2" t="s">
         <v>1622</v>
@@ -8417,7 +8417,7 @@
         <v>1406</v>
       </c>
       <c r="E3">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="F3" t="s">
         <v>1622</v>
@@ -8452,7 +8452,7 @@
         <v>1407</v>
       </c>
       <c r="E4">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="F4" t="s">
         <v>1622</v>
@@ -8487,7 +8487,7 @@
         <v>1408</v>
       </c>
       <c r="E5">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="F5" t="s">
         <v>1622</v>
@@ -8522,7 +8522,7 @@
         <v>1408</v>
       </c>
       <c r="E6">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="F6" t="s">
         <v>1622</v>
@@ -8557,7 +8557,7 @@
         <v>1409</v>
       </c>
       <c r="E7">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F7" t="s">
         <v>1622</v>
@@ -8592,7 +8592,7 @@
         <v>1410</v>
       </c>
       <c r="E8">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="F8" t="s">
         <v>1622</v>
@@ -8627,7 +8627,7 @@
         <v>1411</v>
       </c>
       <c r="E9">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F9" t="s">
         <v>1622</v>
@@ -8662,7 +8662,7 @@
         <v>1412</v>
       </c>
       <c r="E10">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="F10" t="s">
         <v>1622</v>
@@ -8697,7 +8697,7 @@
         <v>1413</v>
       </c>
       <c r="E11">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="F11" t="s">
         <v>1622</v>
@@ -8732,7 +8732,7 @@
         <v>1414</v>
       </c>
       <c r="E12">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="F12" t="s">
         <v>1622</v>
@@ -8767,7 +8767,7 @@
         <v>1415</v>
       </c>
       <c r="E13">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F13" t="s">
         <v>1622</v>
@@ -8802,7 +8802,7 @@
         <v>1416</v>
       </c>
       <c r="E14">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="F14" t="s">
         <v>1622</v>
@@ -8837,7 +8837,7 @@
         <v>1417</v>
       </c>
       <c r="E15">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="F15" t="s">
         <v>1622</v>
@@ -8872,7 +8872,7 @@
         <v>1418</v>
       </c>
       <c r="E16">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="F16" t="s">
         <v>1622</v>
@@ -8907,7 +8907,7 @@
         <v>1418</v>
       </c>
       <c r="E17">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="F17" t="s">
         <v>1622</v>
@@ -8942,7 +8942,7 @@
         <v>1419</v>
       </c>
       <c r="E18">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="F18" t="s">
         <v>1622</v>
@@ -8977,7 +8977,7 @@
         <v>1420</v>
       </c>
       <c r="E19">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="F19" t="s">
         <v>1622</v>
@@ -9012,7 +9012,7 @@
         <v>1421</v>
       </c>
       <c r="E20">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="F20" t="s">
         <v>1622</v>
@@ -9047,7 +9047,7 @@
         <v>1421</v>
       </c>
       <c r="E21">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="F21" t="s">
         <v>1622</v>
@@ -9082,7 +9082,7 @@
         <v>1422</v>
       </c>
       <c r="E22">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F22" t="s">
         <v>1622</v>
@@ -9117,7 +9117,7 @@
         <v>1423</v>
       </c>
       <c r="E23">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="F23" t="s">
         <v>1622</v>
@@ -9152,7 +9152,7 @@
         <v>1424</v>
       </c>
       <c r="E24">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="F24" t="s">
         <v>1622</v>
@@ -9187,7 +9187,7 @@
         <v>1425</v>
       </c>
       <c r="E25">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="F25" t="s">
         <v>1622</v>
@@ -9222,7 +9222,7 @@
         <v>1426</v>
       </c>
       <c r="E26">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F26" t="s">
         <v>1622</v>
@@ -9260,7 +9260,7 @@
         <v>1427</v>
       </c>
       <c r="E27">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="F27" t="s">
         <v>1622</v>
@@ -9295,7 +9295,7 @@
         <v>1428</v>
       </c>
       <c r="E28">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F28" t="s">
         <v>1622</v>
@@ -9330,7 +9330,7 @@
         <v>1429</v>
       </c>
       <c r="E29">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F29" t="s">
         <v>1622</v>
@@ -9365,7 +9365,7 @@
         <v>1430</v>
       </c>
       <c r="E30">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F30" t="s">
         <v>1622</v>
@@ -9400,7 +9400,7 @@
         <v>1430</v>
       </c>
       <c r="E31">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F31" t="s">
         <v>1622</v>
@@ -9435,7 +9435,7 @@
         <v>1431</v>
       </c>
       <c r="E32">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F32" t="s">
         <v>1622</v>
@@ -9470,7 +9470,7 @@
         <v>1432</v>
       </c>
       <c r="E33">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F33" t="s">
         <v>1622</v>
@@ -9505,7 +9505,7 @@
         <v>1433</v>
       </c>
       <c r="E34">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F34" t="s">
         <v>1622</v>
@@ -9540,7 +9540,7 @@
         <v>1434</v>
       </c>
       <c r="E35">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F35" t="s">
         <v>1622</v>
@@ -9575,7 +9575,7 @@
         <v>1435</v>
       </c>
       <c r="E36">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F36" t="s">
         <v>1622</v>
@@ -9610,7 +9610,7 @@
         <v>1436</v>
       </c>
       <c r="E37">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F37" t="s">
         <v>1622</v>
@@ -9645,7 +9645,7 @@
         <v>1437</v>
       </c>
       <c r="E38">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F38" t="s">
         <v>1622</v>
@@ -9680,7 +9680,7 @@
         <v>1438</v>
       </c>
       <c r="E39">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F39" t="s">
         <v>1622</v>
@@ -9715,7 +9715,7 @@
         <v>1438</v>
       </c>
       <c r="E40">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F40" t="s">
         <v>1622</v>
@@ -9750,7 +9750,7 @@
         <v>1439</v>
       </c>
       <c r="E41">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F41" t="s">
         <v>1622</v>
@@ -9785,7 +9785,7 @@
         <v>1439</v>
       </c>
       <c r="E42">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F42" t="s">
         <v>1622</v>
@@ -9820,7 +9820,7 @@
         <v>1440</v>
       </c>
       <c r="E43">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F43" t="s">
         <v>1622</v>
@@ -9855,7 +9855,7 @@
         <v>1441</v>
       </c>
       <c r="E44">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F44" t="s">
         <v>1622</v>
@@ -9890,7 +9890,7 @@
         <v>1442</v>
       </c>
       <c r="E45">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F45" t="s">
         <v>1622</v>
@@ -9925,7 +9925,7 @@
         <v>1443</v>
       </c>
       <c r="E46">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F46" t="s">
         <v>1622</v>
@@ -9960,7 +9960,7 @@
         <v>1443</v>
       </c>
       <c r="E47">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F47" t="s">
         <v>1622</v>
@@ -9995,7 +9995,7 @@
         <v>1444</v>
       </c>
       <c r="E48">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F48" t="s">
         <v>1622</v>
@@ -10030,7 +10030,7 @@
         <v>1445</v>
       </c>
       <c r="E49">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F49" t="s">
         <v>1622</v>
@@ -10065,7 +10065,7 @@
         <v>1446</v>
       </c>
       <c r="E50">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F50" t="s">
         <v>1622</v>
@@ -10100,7 +10100,7 @@
         <v>1446</v>
       </c>
       <c r="E51">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F51" t="s">
         <v>1622</v>
@@ -10135,7 +10135,7 @@
         <v>1447</v>
       </c>
       <c r="E52">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F52" t="s">
         <v>1622</v>
@@ -10170,7 +10170,7 @@
         <v>1447</v>
       </c>
       <c r="E53">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F53" t="s">
         <v>1622</v>
@@ -10205,7 +10205,7 @@
         <v>1448</v>
       </c>
       <c r="E54">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F54" t="s">
         <v>1622</v>
@@ -10240,7 +10240,7 @@
         <v>1449</v>
       </c>
       <c r="E55">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F55" t="s">
         <v>1622</v>
@@ -10275,7 +10275,7 @@
         <v>1450</v>
       </c>
       <c r="E56">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F56" t="s">
         <v>1622</v>
@@ -10310,7 +10310,7 @@
         <v>1451</v>
       </c>
       <c r="E57">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F57" t="s">
         <v>1622</v>
@@ -10345,7 +10345,7 @@
         <v>1452</v>
       </c>
       <c r="E58">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F58" t="s">
         <v>1622</v>
@@ -10380,7 +10380,7 @@
         <v>1453</v>
       </c>
       <c r="E59">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F59" t="s">
         <v>1622</v>
@@ -10415,7 +10415,7 @@
         <v>1454</v>
       </c>
       <c r="E60">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F60" t="s">
         <v>1622</v>
@@ -10450,7 +10450,7 @@
         <v>1455</v>
       </c>
       <c r="E61">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F61" t="s">
         <v>1622</v>
@@ -10485,7 +10485,7 @@
         <v>1456</v>
       </c>
       <c r="E62">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F62" t="s">
         <v>1622</v>
@@ -10520,7 +10520,7 @@
         <v>1457</v>
       </c>
       <c r="E63">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F63" t="s">
         <v>1622</v>
@@ -10555,7 +10555,7 @@
         <v>1458</v>
       </c>
       <c r="E64">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F64" t="s">
         <v>1622</v>
@@ -10590,7 +10590,7 @@
         <v>1459</v>
       </c>
       <c r="E65">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F65" t="s">
         <v>1622</v>
@@ -10625,7 +10625,7 @@
         <v>1460</v>
       </c>
       <c r="E66">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F66" t="s">
         <v>1622</v>
@@ -10660,7 +10660,7 @@
         <v>1461</v>
       </c>
       <c r="E67">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F67" t="s">
         <v>1622</v>
@@ -10695,7 +10695,7 @@
         <v>1462</v>
       </c>
       <c r="E68">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F68" t="s">
         <v>1622</v>
@@ -10730,7 +10730,7 @@
         <v>1463</v>
       </c>
       <c r="E69">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F69" t="s">
         <v>1622</v>
@@ -10765,7 +10765,7 @@
         <v>1464</v>
       </c>
       <c r="E70">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F70" t="s">
         <v>1622</v>
@@ -10800,7 +10800,7 @@
         <v>1464</v>
       </c>
       <c r="E71">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F71" t="s">
         <v>1622</v>
@@ -10835,7 +10835,7 @@
         <v>1464</v>
       </c>
       <c r="E72">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F72" t="s">
         <v>1622</v>
@@ -10870,7 +10870,7 @@
         <v>1465</v>
       </c>
       <c r="E73">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F73" t="s">
         <v>1622</v>
@@ -10905,7 +10905,7 @@
         <v>1466</v>
       </c>
       <c r="E74">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F74" t="s">
         <v>1622</v>
@@ -10940,7 +10940,7 @@
         <v>1467</v>
       </c>
       <c r="E75">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F75" t="s">
         <v>1622</v>
@@ -10975,7 +10975,7 @@
         <v>1467</v>
       </c>
       <c r="E76">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F76" t="s">
         <v>1622</v>
@@ -11010,7 +11010,7 @@
         <v>1467</v>
       </c>
       <c r="E77">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F77" t="s">
         <v>1622</v>
@@ -11045,7 +11045,7 @@
         <v>1468</v>
       </c>
       <c r="E78">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F78" t="s">
         <v>1622</v>
@@ -11080,7 +11080,7 @@
         <v>1469</v>
       </c>
       <c r="E79">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F79" t="s">
         <v>1622</v>
@@ -11115,7 +11115,7 @@
         <v>1470</v>
       </c>
       <c r="E80">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F80" t="s">
         <v>1622</v>
@@ -11150,7 +11150,7 @@
         <v>1470</v>
       </c>
       <c r="E81">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F81" t="s">
         <v>1622</v>
@@ -11185,7 +11185,7 @@
         <v>1470</v>
       </c>
       <c r="E82">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F82" t="s">
         <v>1622</v>
@@ -11220,7 +11220,7 @@
         <v>1471</v>
       </c>
       <c r="E83">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F83" t="s">
         <v>1622</v>
@@ -11255,7 +11255,7 @@
         <v>1472</v>
       </c>
       <c r="E84">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F84" t="s">
         <v>1622</v>
@@ -11290,7 +11290,7 @@
         <v>1472</v>
       </c>
       <c r="E85">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F85" t="s">
         <v>1622</v>
@@ -11325,7 +11325,7 @@
         <v>1472</v>
       </c>
       <c r="E86">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F86" t="s">
         <v>1623</v>
@@ -11360,7 +11360,7 @@
         <v>1472</v>
       </c>
       <c r="E87">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F87" t="s">
         <v>1622</v>
@@ -11395,7 +11395,7 @@
         <v>1473</v>
       </c>
       <c r="E88">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F88" t="s">
         <v>1622</v>
@@ -11430,7 +11430,7 @@
         <v>1474</v>
       </c>
       <c r="E89">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F89" t="s">
         <v>1622</v>
@@ -11465,7 +11465,7 @@
         <v>1474</v>
       </c>
       <c r="E90">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F90" t="s">
         <v>1622</v>
@@ -11500,7 +11500,7 @@
         <v>1474</v>
       </c>
       <c r="E91">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F91" t="s">
         <v>1622</v>
@@ -11535,7 +11535,7 @@
         <v>1475</v>
       </c>
       <c r="E92">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F92" t="s">
         <v>1622</v>
@@ -11570,7 +11570,7 @@
         <v>1476</v>
       </c>
       <c r="E93">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F93" t="s">
         <v>1622</v>
@@ -11605,7 +11605,7 @@
         <v>1477</v>
       </c>
       <c r="E94">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F94" t="s">
         <v>1622</v>
@@ -11640,7 +11640,7 @@
         <v>1478</v>
       </c>
       <c r="E95">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F95" t="s">
         <v>1622</v>
@@ -11675,7 +11675,7 @@
         <v>1479</v>
       </c>
       <c r="E96">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F96" t="s">
         <v>1622</v>
@@ -11710,7 +11710,7 @@
         <v>1479</v>
       </c>
       <c r="E97">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F97" t="s">
         <v>1622</v>
@@ -11745,7 +11745,7 @@
         <v>1479</v>
       </c>
       <c r="E98">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F98" t="s">
         <v>1622</v>
@@ -11780,7 +11780,7 @@
         <v>1479</v>
       </c>
       <c r="E99">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F99" t="s">
         <v>1622</v>
@@ -11815,7 +11815,7 @@
         <v>1479</v>
       </c>
       <c r="E100">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F100" t="s">
         <v>1622</v>
@@ -11850,7 +11850,7 @@
         <v>1479</v>
       </c>
       <c r="E101">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F101" t="s">
         <v>1622</v>
@@ -11885,7 +11885,7 @@
         <v>1479</v>
       </c>
       <c r="E102">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F102" t="s">
         <v>1622</v>
@@ -11920,7 +11920,7 @@
         <v>1480</v>
       </c>
       <c r="E103">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F103" t="s">
         <v>1622</v>
@@ -11955,7 +11955,7 @@
         <v>1480</v>
       </c>
       <c r="E104">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F104" t="s">
         <v>1622</v>
@@ -11990,7 +11990,7 @@
         <v>1481</v>
       </c>
       <c r="E105">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F105" t="s">
         <v>1622</v>
@@ -12025,7 +12025,7 @@
         <v>1482</v>
       </c>
       <c r="E106">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F106" t="s">
         <v>1622</v>
@@ -12060,7 +12060,7 @@
         <v>1482</v>
       </c>
       <c r="E107">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F107" t="s">
         <v>1622</v>
@@ -12095,7 +12095,7 @@
         <v>1483</v>
       </c>
       <c r="E108">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F108" t="s">
         <v>1622</v>
@@ -12130,7 +12130,7 @@
         <v>1483</v>
       </c>
       <c r="E109">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F109" t="s">
         <v>1624</v>
@@ -12165,7 +12165,7 @@
         <v>1484</v>
       </c>
       <c r="E110">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F110" t="s">
         <v>1622</v>
@@ -12200,7 +12200,7 @@
         <v>1485</v>
       </c>
       <c r="E111">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F111" t="s">
         <v>1622</v>
@@ -12235,7 +12235,7 @@
         <v>1486</v>
       </c>
       <c r="E112">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F112" t="s">
         <v>1622</v>
@@ -12270,7 +12270,7 @@
         <v>1486</v>
       </c>
       <c r="E113">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F113" t="s">
         <v>1622</v>
@@ -12305,7 +12305,7 @@
         <v>1487</v>
       </c>
       <c r="E114">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F114" t="s">
         <v>1622</v>
@@ -12340,7 +12340,7 @@
         <v>1488</v>
       </c>
       <c r="E115">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F115" t="s">
         <v>1622</v>
@@ -12375,7 +12375,7 @@
         <v>1489</v>
       </c>
       <c r="E116">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F116" t="s">
         <v>1622</v>
@@ -12410,7 +12410,7 @@
         <v>1490</v>
       </c>
       <c r="E117">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F117" t="s">
         <v>1622</v>
@@ -12445,7 +12445,7 @@
         <v>1491</v>
       </c>
       <c r="E118">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F118" t="s">
         <v>1622</v>
@@ -12480,7 +12480,7 @@
         <v>1491</v>
       </c>
       <c r="E119">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F119" t="s">
         <v>1622</v>
@@ -12515,7 +12515,7 @@
         <v>1492</v>
       </c>
       <c r="E120">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F120" t="s">
         <v>1622</v>
@@ -12550,7 +12550,7 @@
         <v>1492</v>
       </c>
       <c r="E121">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F121" t="s">
         <v>1622</v>
@@ -12585,7 +12585,7 @@
         <v>1492</v>
       </c>
       <c r="E122">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F122" t="s">
         <v>1622</v>
@@ -12620,7 +12620,7 @@
         <v>1492</v>
       </c>
       <c r="E123">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F123" t="s">
         <v>1622</v>
@@ -12655,7 +12655,7 @@
         <v>1493</v>
       </c>
       <c r="E124">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F124" t="s">
         <v>1622</v>
@@ -12690,7 +12690,7 @@
         <v>1493</v>
       </c>
       <c r="E125">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F125" t="s">
         <v>1622</v>
@@ -12725,7 +12725,7 @@
         <v>1493</v>
       </c>
       <c r="E126">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F126" t="s">
         <v>1622</v>
@@ -12760,7 +12760,7 @@
         <v>1493</v>
       </c>
       <c r="E127">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F127" t="s">
         <v>1622</v>
@@ -12795,7 +12795,7 @@
         <v>1493</v>
       </c>
       <c r="E128">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F128" t="s">
         <v>1622</v>
@@ -12830,7 +12830,7 @@
         <v>1493</v>
       </c>
       <c r="E129">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F129" t="s">
         <v>1622</v>
@@ -12865,7 +12865,7 @@
         <v>1494</v>
       </c>
       <c r="E130">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F130" t="s">
         <v>1622</v>
@@ -12900,7 +12900,7 @@
         <v>1495</v>
       </c>
       <c r="E131">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F131" t="s">
         <v>1622</v>
@@ -12935,7 +12935,7 @@
         <v>1495</v>
       </c>
       <c r="E132">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F132" t="s">
         <v>1622</v>
@@ -12970,7 +12970,7 @@
         <v>1496</v>
       </c>
       <c r="E133">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F133" t="s">
         <v>1622</v>
@@ -13005,7 +13005,7 @@
         <v>1497</v>
       </c>
       <c r="E134">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F134" t="s">
         <v>1622</v>
@@ -13040,7 +13040,7 @@
         <v>1497</v>
       </c>
       <c r="E135">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F135" t="s">
         <v>1622</v>
@@ -13075,7 +13075,7 @@
         <v>1497</v>
       </c>
       <c r="E136">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F136" t="s">
         <v>1622</v>
@@ -13110,7 +13110,7 @@
         <v>1498</v>
       </c>
       <c r="E137">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F137" t="s">
         <v>1622</v>
@@ -13145,7 +13145,7 @@
         <v>1498</v>
       </c>
       <c r="E138">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F138" t="s">
         <v>1622</v>
@@ -13180,7 +13180,7 @@
         <v>1498</v>
       </c>
       <c r="E139">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F139" t="s">
         <v>1622</v>
@@ -13215,7 +13215,7 @@
         <v>1499</v>
       </c>
       <c r="E140">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F140" t="s">
         <v>1622</v>
@@ -13250,7 +13250,7 @@
         <v>1499</v>
       </c>
       <c r="E141">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F141" t="s">
         <v>1622</v>
@@ -13285,7 +13285,7 @@
         <v>1499</v>
       </c>
       <c r="E142">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F142" t="s">
         <v>1622</v>
@@ -13320,7 +13320,7 @@
         <v>1500</v>
       </c>
       <c r="E143">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F143" t="s">
         <v>1622</v>
@@ -13355,7 +13355,7 @@
         <v>1500</v>
       </c>
       <c r="E144">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F144" t="s">
         <v>1622</v>
@@ -13390,7 +13390,7 @@
         <v>1501</v>
       </c>
       <c r="E145">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F145" t="s">
         <v>1622</v>
@@ -13425,7 +13425,7 @@
         <v>1502</v>
       </c>
       <c r="E146">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F146" t="s">
         <v>1622</v>
@@ -13460,7 +13460,7 @@
         <v>1502</v>
       </c>
       <c r="E147">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F147" t="s">
         <v>1622</v>
@@ -13495,7 +13495,7 @@
         <v>1502</v>
       </c>
       <c r="E148">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F148" t="s">
         <v>1622</v>
@@ -13530,7 +13530,7 @@
         <v>1503</v>
       </c>
       <c r="E149">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F149" t="s">
         <v>1622</v>
@@ -13565,7 +13565,7 @@
         <v>1503</v>
       </c>
       <c r="E150">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F150" t="s">
         <v>1622</v>
@@ -13600,7 +13600,7 @@
         <v>1504</v>
       </c>
       <c r="E151">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F151" t="s">
         <v>1622</v>
@@ -13638,7 +13638,7 @@
         <v>1504</v>
       </c>
       <c r="E152">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F152" t="s">
         <v>1622</v>
@@ -13673,7 +13673,7 @@
         <v>1504</v>
       </c>
       <c r="E153">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F153" t="s">
         <v>1622</v>
@@ -13708,7 +13708,7 @@
         <v>1504</v>
       </c>
       <c r="E154">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F154" t="s">
         <v>1622</v>
@@ -13743,7 +13743,7 @@
         <v>1504</v>
       </c>
       <c r="E155">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F155" t="s">
         <v>1622</v>
@@ -13778,7 +13778,7 @@
         <v>1504</v>
       </c>
       <c r="E156">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F156" t="s">
         <v>1622</v>
@@ -13813,7 +13813,7 @@
         <v>1505</v>
       </c>
       <c r="E157">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F157" t="s">
         <v>1622</v>
@@ -13848,7 +13848,7 @@
         <v>1506</v>
       </c>
       <c r="E158">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F158" t="s">
         <v>1622</v>
@@ -13883,7 +13883,7 @@
         <v>1507</v>
       </c>
       <c r="E159">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F159" t="s">
         <v>1623</v>
@@ -13918,7 +13918,7 @@
         <v>1508</v>
       </c>
       <c r="E160">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F160" t="s">
         <v>1622</v>
@@ -13953,7 +13953,7 @@
         <v>1508</v>
       </c>
       <c r="E161">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F161" t="s">
         <v>1622</v>
@@ -13988,7 +13988,7 @@
         <v>1508</v>
       </c>
       <c r="E162">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F162" t="s">
         <v>1622</v>
@@ -14023,7 +14023,7 @@
         <v>1508</v>
       </c>
       <c r="E163">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F163" t="s">
         <v>1622</v>
@@ -14058,7 +14058,7 @@
         <v>1509</v>
       </c>
       <c r="E164">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F164" t="s">
         <v>1622</v>
@@ -14093,7 +14093,7 @@
         <v>1509</v>
       </c>
       <c r="E165">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F165" t="s">
         <v>1622</v>
@@ -14128,7 +14128,7 @@
         <v>1509</v>
       </c>
       <c r="E166">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F166" t="s">
         <v>1622</v>
@@ -14163,7 +14163,7 @@
         <v>1509</v>
       </c>
       <c r="E167">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F167" t="s">
         <v>1622</v>
@@ -14198,7 +14198,7 @@
         <v>1509</v>
       </c>
       <c r="E168">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F168" t="s">
         <v>1622</v>
@@ -14233,7 +14233,7 @@
         <v>1509</v>
       </c>
       <c r="E169">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F169" t="s">
         <v>1622</v>
@@ -14268,7 +14268,7 @@
         <v>1509</v>
       </c>
       <c r="E170">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F170" t="s">
         <v>1622</v>
@@ -14303,7 +14303,7 @@
         <v>1510</v>
       </c>
       <c r="E171">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F171" t="s">
         <v>1622</v>
@@ -14338,7 +14338,7 @@
         <v>1510</v>
       </c>
       <c r="E172">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F172" t="s">
         <v>1622</v>
@@ -14373,7 +14373,7 @@
         <v>1511</v>
       </c>
       <c r="E173">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F173" t="s">
         <v>1622</v>
@@ -14408,7 +14408,7 @@
         <v>1511</v>
       </c>
       <c r="E174">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F174" t="s">
         <v>1622</v>
@@ -14443,7 +14443,7 @@
         <v>1511</v>
       </c>
       <c r="E175">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F175" t="s">
         <v>1622</v>
@@ -14478,7 +14478,7 @@
         <v>1512</v>
       </c>
       <c r="E176">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F176" t="s">
         <v>1622</v>
@@ -14513,7 +14513,7 @@
         <v>1512</v>
       </c>
       <c r="E177">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F177" t="s">
         <v>1622</v>
@@ -14548,7 +14548,7 @@
         <v>1512</v>
       </c>
       <c r="E178">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F178" t="s">
         <v>1622</v>
@@ -14583,7 +14583,7 @@
         <v>1512</v>
       </c>
       <c r="E179">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F179" t="s">
         <v>1622</v>
@@ -14618,7 +14618,7 @@
         <v>1513</v>
       </c>
       <c r="E180">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F180" t="s">
         <v>1622</v>
@@ -14653,7 +14653,7 @@
         <v>1513</v>
       </c>
       <c r="E181">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F181" t="s">
         <v>1622</v>
@@ -14688,7 +14688,7 @@
         <v>1513</v>
       </c>
       <c r="E182">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F182" t="s">
         <v>1622</v>
@@ -14723,7 +14723,7 @@
         <v>1513</v>
       </c>
       <c r="E183">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F183" t="s">
         <v>1622</v>
@@ -14758,7 +14758,7 @@
         <v>1513</v>
       </c>
       <c r="E184">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F184" t="s">
         <v>1622</v>
@@ -14793,7 +14793,7 @@
         <v>1513</v>
       </c>
       <c r="E185">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F185" t="s">
         <v>1622</v>
@@ -14828,7 +14828,7 @@
         <v>1513</v>
       </c>
       <c r="E186">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F186" t="s">
         <v>1622</v>
@@ -14863,7 +14863,7 @@
         <v>1513</v>
       </c>
       <c r="E187">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F187" t="s">
         <v>1622</v>
@@ -14898,7 +14898,7 @@
         <v>1513</v>
       </c>
       <c r="E188">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F188" t="s">
         <v>1622</v>
@@ -14933,7 +14933,7 @@
         <v>1513</v>
       </c>
       <c r="E189">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F189" t="s">
         <v>1622</v>
@@ -14968,7 +14968,7 @@
         <v>1514</v>
       </c>
       <c r="E190">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F190" t="s">
         <v>1622</v>
@@ -15003,7 +15003,7 @@
         <v>1514</v>
       </c>
       <c r="E191">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F191" t="s">
         <v>1622</v>
@@ -15038,7 +15038,7 @@
         <v>1514</v>
       </c>
       <c r="E192">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F192" t="s">
         <v>1622</v>
@@ -15073,7 +15073,7 @@
         <v>1514</v>
       </c>
       <c r="E193">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F193" t="s">
         <v>1625</v>
@@ -15108,7 +15108,7 @@
         <v>1515</v>
       </c>
       <c r="E194">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F194" t="s">
         <v>1622</v>
@@ -15143,7 +15143,7 @@
         <v>1515</v>
       </c>
       <c r="E195">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F195" t="s">
         <v>1623</v>
@@ -15178,7 +15178,7 @@
         <v>1515</v>
       </c>
       <c r="E196">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F196" t="s">
         <v>1622</v>
@@ -15213,7 +15213,7 @@
         <v>1516</v>
       </c>
       <c r="E197">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F197" t="s">
         <v>1622</v>
@@ -15248,7 +15248,7 @@
         <v>1516</v>
       </c>
       <c r="E198">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F198" t="s">
         <v>1622</v>
@@ -15283,7 +15283,7 @@
         <v>1517</v>
       </c>
       <c r="E199">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F199" t="s">
         <v>1622</v>
@@ -15318,7 +15318,7 @@
         <v>1517</v>
       </c>
       <c r="E200">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F200" t="s">
         <v>1622</v>
@@ -15353,7 +15353,7 @@
         <v>1518</v>
       </c>
       <c r="E201">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F201" t="s">
         <v>1622</v>
@@ -15388,7 +15388,7 @@
         <v>1518</v>
       </c>
       <c r="E202">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F202" t="s">
         <v>1622</v>
@@ -15423,7 +15423,7 @@
         <v>1518</v>
       </c>
       <c r="E203">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F203" t="s">
         <v>1622</v>
@@ -15458,7 +15458,7 @@
         <v>1519</v>
       </c>
       <c r="E204">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F204" t="s">
         <v>1622</v>
@@ -15493,7 +15493,7 @@
         <v>1519</v>
       </c>
       <c r="E205">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F205" t="s">
         <v>1622</v>
@@ -15528,7 +15528,7 @@
         <v>1519</v>
       </c>
       <c r="E206">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F206" t="s">
         <v>1622</v>
@@ -15563,7 +15563,7 @@
         <v>1519</v>
       </c>
       <c r="E207">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F207" t="s">
         <v>1622</v>
@@ -15598,7 +15598,7 @@
         <v>1519</v>
       </c>
       <c r="E208">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F208" t="s">
         <v>1622</v>
@@ -15633,7 +15633,7 @@
         <v>1520</v>
       </c>
       <c r="E209">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F209" t="s">
         <v>1622</v>
@@ -15668,7 +15668,7 @@
         <v>1520</v>
       </c>
       <c r="E210">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F210" t="s">
         <v>1622</v>
@@ -15703,7 +15703,7 @@
         <v>1521</v>
       </c>
       <c r="E211">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F211" t="s">
         <v>1622</v>
@@ -15738,7 +15738,7 @@
         <v>1522</v>
       </c>
       <c r="E212">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F212" t="s">
         <v>1622</v>
@@ -15773,7 +15773,7 @@
         <v>1522</v>
       </c>
       <c r="E213">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F213" t="s">
         <v>1622</v>
@@ -15808,7 +15808,7 @@
         <v>1522</v>
       </c>
       <c r="E214">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F214" t="s">
         <v>1622</v>
@@ -15843,7 +15843,7 @@
         <v>1522</v>
       </c>
       <c r="E215">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F215" t="s">
         <v>1622</v>
@@ -15878,7 +15878,7 @@
         <v>1523</v>
       </c>
       <c r="E216">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F216" t="s">
         <v>1622</v>
@@ -15913,7 +15913,7 @@
         <v>1524</v>
       </c>
       <c r="E217">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F217" t="s">
         <v>1622</v>
@@ -15948,7 +15948,7 @@
         <v>1524</v>
       </c>
       <c r="E218">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F218" t="s">
         <v>1622</v>
@@ -15983,7 +15983,7 @@
         <v>1524</v>
       </c>
       <c r="E219">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F219" t="s">
         <v>1622</v>
@@ -16018,7 +16018,7 @@
         <v>1524</v>
       </c>
       <c r="E220">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F220" t="s">
         <v>1622</v>
@@ -16053,7 +16053,7 @@
         <v>1524</v>
       </c>
       <c r="E221">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F221" t="s">
         <v>1622</v>
@@ -16088,7 +16088,7 @@
         <v>1525</v>
       </c>
       <c r="E222">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F222" t="s">
         <v>1622</v>
@@ -16123,7 +16123,7 @@
         <v>1525</v>
       </c>
       <c r="E223">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F223" t="s">
         <v>1622</v>
@@ -16158,7 +16158,7 @@
         <v>1525</v>
       </c>
       <c r="E224">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F224" t="s">
         <v>1622</v>
@@ -16193,7 +16193,7 @@
         <v>1525</v>
       </c>
       <c r="E225">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F225" t="s">
         <v>1622</v>
@@ -16228,7 +16228,7 @@
         <v>1525</v>
       </c>
       <c r="E226">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F226" t="s">
         <v>1622</v>
@@ -16263,7 +16263,7 @@
         <v>1525</v>
       </c>
       <c r="E227">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F227" t="s">
         <v>1622</v>
@@ -16298,7 +16298,7 @@
         <v>1525</v>
       </c>
       <c r="E228">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F228" t="s">
         <v>1622</v>
@@ -16333,7 +16333,7 @@
         <v>1526</v>
       </c>
       <c r="E229">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F229" t="s">
         <v>1622</v>
@@ -16368,7 +16368,7 @@
         <v>1526</v>
       </c>
       <c r="E230">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F230" t="s">
         <v>1622</v>
@@ -16403,7 +16403,7 @@
         <v>1526</v>
       </c>
       <c r="E231">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F231" t="s">
         <v>1622</v>
@@ -16438,7 +16438,7 @@
         <v>1526</v>
       </c>
       <c r="E232">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F232" t="s">
         <v>1622</v>
@@ -16473,7 +16473,7 @@
         <v>1527</v>
       </c>
       <c r="E233">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F233" t="s">
         <v>1622</v>
@@ -16508,7 +16508,7 @@
         <v>1527</v>
       </c>
       <c r="E234">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F234" t="s">
         <v>1622</v>
@@ -16543,7 +16543,7 @@
         <v>1527</v>
       </c>
       <c r="E235">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F235" t="s">
         <v>1622</v>
@@ -16578,7 +16578,7 @@
         <v>1528</v>
       </c>
       <c r="E236">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F236" t="s">
         <v>1622</v>
@@ -16613,7 +16613,7 @@
         <v>1528</v>
       </c>
       <c r="E237">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F237" t="s">
         <v>1622</v>
@@ -16648,7 +16648,7 @@
         <v>1529</v>
       </c>
       <c r="E238">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F238" t="s">
         <v>1622</v>
@@ -16683,7 +16683,7 @@
         <v>1529</v>
       </c>
       <c r="E239">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F239" t="s">
         <v>1622</v>
@@ -16718,7 +16718,7 @@
         <v>1530</v>
       </c>
       <c r="E240">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F240" t="s">
         <v>1622</v>
@@ -16753,7 +16753,7 @@
         <v>1530</v>
       </c>
       <c r="E241">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F241" t="s">
         <v>1622</v>
@@ -16788,7 +16788,7 @@
         <v>1531</v>
       </c>
       <c r="E242">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F242" t="s">
         <v>1622</v>
@@ -16823,7 +16823,7 @@
         <v>1531</v>
       </c>
       <c r="E243">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F243" t="s">
         <v>1622</v>
@@ -16858,7 +16858,7 @@
         <v>1532</v>
       </c>
       <c r="E244">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F244" t="s">
         <v>1622</v>
@@ -16893,7 +16893,7 @@
         <v>1532</v>
       </c>
       <c r="E245">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F245" t="s">
         <v>1622</v>
@@ -16928,7 +16928,7 @@
         <v>1533</v>
       </c>
       <c r="E246">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F246" t="s">
         <v>1622</v>
@@ -16963,7 +16963,7 @@
         <v>1533</v>
       </c>
       <c r="E247">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F247" t="s">
         <v>1622</v>
@@ -16998,7 +16998,7 @@
         <v>1534</v>
       </c>
       <c r="E248">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F248" t="s">
         <v>1622</v>
@@ -17033,7 +17033,7 @@
         <v>1534</v>
       </c>
       <c r="E249">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F249" t="s">
         <v>1622</v>
@@ -17068,7 +17068,7 @@
         <v>1534</v>
       </c>
       <c r="E250">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F250" t="s">
         <v>1622</v>
@@ -17103,7 +17103,7 @@
         <v>1535</v>
       </c>
       <c r="E251">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F251" t="s">
         <v>1622</v>
@@ -17138,7 +17138,7 @@
         <v>1535</v>
       </c>
       <c r="E252">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F252" t="s">
         <v>1622</v>
@@ -17173,7 +17173,7 @@
         <v>1536</v>
       </c>
       <c r="E253">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F253" t="s">
         <v>1622</v>
@@ -17208,7 +17208,7 @@
         <v>1537</v>
       </c>
       <c r="E254">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F254" t="s">
         <v>1622</v>
@@ -17243,7 +17243,7 @@
         <v>1537</v>
       </c>
       <c r="E255">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F255" t="s">
         <v>1622</v>
@@ -17278,7 +17278,7 @@
         <v>1537</v>
       </c>
       <c r="E256">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F256" t="s">
         <v>1622</v>
@@ -17313,7 +17313,7 @@
         <v>1538</v>
       </c>
       <c r="E257">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F257" t="s">
         <v>1622</v>
@@ -17348,7 +17348,7 @@
         <v>1538</v>
       </c>
       <c r="E258">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F258" t="s">
         <v>1622</v>
@@ -17383,7 +17383,7 @@
         <v>1539</v>
       </c>
       <c r="E259">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F259" t="s">
         <v>1622</v>
@@ -17418,7 +17418,7 @@
         <v>1539</v>
       </c>
       <c r="E260">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F260" t="s">
         <v>1622</v>
@@ -17453,7 +17453,7 @@
         <v>1539</v>
       </c>
       <c r="E261">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F261" t="s">
         <v>1624</v>
@@ -17488,7 +17488,7 @@
         <v>1539</v>
       </c>
       <c r="E262">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F262" t="s">
         <v>1622</v>
@@ -17523,7 +17523,7 @@
         <v>1539</v>
       </c>
       <c r="E263">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F263" t="s">
         <v>1622</v>
@@ -17558,7 +17558,7 @@
         <v>1540</v>
       </c>
       <c r="E264">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F264" t="s">
         <v>1622</v>
@@ -17593,7 +17593,7 @@
         <v>1540</v>
       </c>
       <c r="E265">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F265" t="s">
         <v>1622</v>
@@ -17628,7 +17628,7 @@
         <v>1540</v>
       </c>
       <c r="E266">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F266" t="s">
         <v>1622</v>
@@ -17666,7 +17666,7 @@
         <v>1540</v>
       </c>
       <c r="E267">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F267" t="s">
         <v>1622</v>
@@ -17701,7 +17701,7 @@
         <v>1540</v>
       </c>
       <c r="E268">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F268" t="s">
         <v>1622</v>
@@ -17736,7 +17736,7 @@
         <v>1540</v>
       </c>
       <c r="E269">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F269" t="s">
         <v>1622</v>
@@ -17771,7 +17771,7 @@
         <v>1540</v>
       </c>
       <c r="E270">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F270" t="s">
         <v>1622</v>
@@ -17806,7 +17806,7 @@
         <v>1541</v>
       </c>
       <c r="E271">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F271" t="s">
         <v>1622</v>
@@ -17841,7 +17841,7 @@
         <v>1541</v>
       </c>
       <c r="E272">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F272" t="s">
         <v>1622</v>
@@ -17876,7 +17876,7 @@
         <v>1541</v>
       </c>
       <c r="E273">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F273" t="s">
         <v>1622</v>
@@ -17911,7 +17911,7 @@
         <v>1542</v>
       </c>
       <c r="E274">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F274" t="s">
         <v>1622</v>
@@ -17946,7 +17946,7 @@
         <v>1542</v>
       </c>
       <c r="E275">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F275" t="s">
         <v>1622</v>
@@ -17981,7 +17981,7 @@
         <v>1542</v>
       </c>
       <c r="E276">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F276" t="s">
         <v>1622</v>
@@ -18016,7 +18016,7 @@
         <v>1542</v>
       </c>
       <c r="E277">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F277" t="s">
         <v>1622</v>
@@ -18051,7 +18051,7 @@
         <v>1543</v>
       </c>
       <c r="E278">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F278" t="s">
         <v>1622</v>
@@ -18086,7 +18086,7 @@
         <v>1543</v>
       </c>
       <c r="E279">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F279" t="s">
         <v>1622</v>
@@ -18121,7 +18121,7 @@
         <v>1543</v>
       </c>
       <c r="E280">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F280" t="s">
         <v>1622</v>
@@ -18156,7 +18156,7 @@
         <v>1543</v>
       </c>
       <c r="E281">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F281" t="s">
         <v>1622</v>
@@ -18191,7 +18191,7 @@
         <v>1543</v>
       </c>
       <c r="E282">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F282" t="s">
         <v>1622</v>
@@ -18226,7 +18226,7 @@
         <v>1543</v>
       </c>
       <c r="E283">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F283" t="s">
         <v>1622</v>
@@ -18261,7 +18261,7 @@
         <v>1544</v>
       </c>
       <c r="E284">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F284" t="s">
         <v>1622</v>
@@ -18296,7 +18296,7 @@
         <v>1544</v>
       </c>
       <c r="E285">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F285" t="s">
         <v>1622</v>
@@ -18331,7 +18331,7 @@
         <v>1544</v>
       </c>
       <c r="E286">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F286" t="s">
         <v>1622</v>
@@ -18366,7 +18366,7 @@
         <v>1544</v>
       </c>
       <c r="E287">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F287" t="s">
         <v>1622</v>
@@ -18401,7 +18401,7 @@
         <v>1544</v>
       </c>
       <c r="E288">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F288" t="s">
         <v>1622</v>
@@ -18436,7 +18436,7 @@
         <v>1544</v>
       </c>
       <c r="E289">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F289" t="s">
         <v>1622</v>
@@ -18471,7 +18471,7 @@
         <v>1545</v>
       </c>
       <c r="E290">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F290" t="s">
         <v>1622</v>
@@ -18506,7 +18506,7 @@
         <v>1546</v>
       </c>
       <c r="E291">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F291" t="s">
         <v>1623</v>
@@ -18541,7 +18541,7 @@
         <v>1546</v>
       </c>
       <c r="E292">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F292" t="s">
         <v>1622</v>
@@ -18576,7 +18576,7 @@
         <v>1546</v>
       </c>
       <c r="E293">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F293" t="s">
         <v>1622</v>
@@ -18611,7 +18611,7 @@
         <v>1546</v>
       </c>
       <c r="E294">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F294" t="s">
         <v>1625</v>
@@ -18646,7 +18646,7 @@
         <v>1546</v>
       </c>
       <c r="E295">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F295" t="s">
         <v>1622</v>
@@ -18681,7 +18681,7 @@
         <v>1546</v>
       </c>
       <c r="E296">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F296" t="s">
         <v>1622</v>
@@ -18716,7 +18716,7 @@
         <v>1546</v>
       </c>
       <c r="E297">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F297" t="s">
         <v>1622</v>
@@ -18751,7 +18751,7 @@
         <v>1546</v>
       </c>
       <c r="E298">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F298" t="s">
         <v>1622</v>
@@ -18786,7 +18786,7 @@
         <v>1547</v>
       </c>
       <c r="E299">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F299" t="s">
         <v>1622</v>
@@ -18821,7 +18821,7 @@
         <v>1547</v>
       </c>
       <c r="E300">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F300" t="s">
         <v>1622</v>
@@ -18856,7 +18856,7 @@
         <v>1547</v>
       </c>
       <c r="E301">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F301" t="s">
         <v>1622</v>
@@ -18891,7 +18891,7 @@
         <v>1547</v>
       </c>
       <c r="E302">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F302" t="s">
         <v>1622</v>
@@ -18926,7 +18926,7 @@
         <v>1548</v>
       </c>
       <c r="E303">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F303" t="s">
         <v>1622</v>
@@ -18961,7 +18961,7 @@
         <v>1548</v>
       </c>
       <c r="E304">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F304" t="s">
         <v>1622</v>
@@ -18996,7 +18996,7 @@
         <v>1549</v>
       </c>
       <c r="E305">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F305" t="s">
         <v>1622</v>
@@ -19034,7 +19034,7 @@
         <v>1549</v>
       </c>
       <c r="E306">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F306" t="s">
         <v>1622</v>
@@ -19069,7 +19069,7 @@
         <v>1550</v>
       </c>
       <c r="E307">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F307" t="s">
         <v>1622</v>
@@ -19104,7 +19104,7 @@
         <v>1550</v>
       </c>
       <c r="E308">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F308" t="s">
         <v>1622</v>
@@ -19139,7 +19139,7 @@
         <v>1550</v>
       </c>
       <c r="E309">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F309" t="s">
         <v>1622</v>
@@ -19174,7 +19174,7 @@
         <v>1550</v>
       </c>
       <c r="E310">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F310" t="s">
         <v>1622</v>
@@ -19212,7 +19212,7 @@
         <v>1550</v>
       </c>
       <c r="E311">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F311" t="s">
         <v>1622</v>
@@ -19247,7 +19247,7 @@
         <v>1550</v>
       </c>
       <c r="E312">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F312" t="s">
         <v>1622</v>
@@ -19282,7 +19282,7 @@
         <v>1551</v>
       </c>
       <c r="E313">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F313" t="s">
         <v>1622</v>
@@ -19317,7 +19317,7 @@
         <v>1551</v>
       </c>
       <c r="E314">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F314" t="s">
         <v>1622</v>
@@ -19352,7 +19352,7 @@
         <v>1552</v>
       </c>
       <c r="E315">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F315" t="s">
         <v>1622</v>
@@ -19387,7 +19387,7 @@
         <v>1552</v>
       </c>
       <c r="E316">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F316" t="s">
         <v>1622</v>
@@ -19422,7 +19422,7 @@
         <v>1553</v>
       </c>
       <c r="E317">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F317" t="s">
         <v>1622</v>
@@ -19457,7 +19457,7 @@
         <v>1553</v>
       </c>
       <c r="E318">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F318" t="s">
         <v>1622</v>
@@ -19492,7 +19492,7 @@
         <v>1553</v>
       </c>
       <c r="E319">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F319" t="s">
         <v>1622</v>
@@ -19527,7 +19527,7 @@
         <v>1553</v>
       </c>
       <c r="E320">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F320" t="s">
         <v>1622</v>
@@ -19562,7 +19562,7 @@
         <v>1554</v>
       </c>
       <c r="E321">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F321" t="s">
         <v>1622</v>
@@ -19597,7 +19597,7 @@
         <v>1554</v>
       </c>
       <c r="E322">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F322" t="s">
         <v>1622</v>
@@ -19632,7 +19632,7 @@
         <v>1554</v>
       </c>
       <c r="E323">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F323" t="s">
         <v>1622</v>
@@ -19667,7 +19667,7 @@
         <v>1554</v>
       </c>
       <c r="E324">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F324" t="s">
         <v>1622</v>
@@ -19702,7 +19702,7 @@
         <v>1555</v>
       </c>
       <c r="E325">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F325" t="s">
         <v>1622</v>
@@ -19737,7 +19737,7 @@
         <v>1555</v>
       </c>
       <c r="E326">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F326" t="s">
         <v>1622</v>
@@ -19772,7 +19772,7 @@
         <v>1556</v>
       </c>
       <c r="E327">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F327" t="s">
         <v>1622</v>
@@ -19807,7 +19807,7 @@
         <v>1556</v>
       </c>
       <c r="E328">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F328" t="s">
         <v>1622</v>
@@ -19842,7 +19842,7 @@
         <v>1556</v>
       </c>
       <c r="E329">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F329" t="s">
         <v>1622</v>
@@ -19877,7 +19877,7 @@
         <v>1556</v>
       </c>
       <c r="E330">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F330" t="s">
         <v>1622</v>
@@ -19912,7 +19912,7 @@
         <v>1556</v>
       </c>
       <c r="E331">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F331" t="s">
         <v>1622</v>
@@ -19947,7 +19947,7 @@
         <v>1557</v>
       </c>
       <c r="E332">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F332" t="s">
         <v>1622</v>
@@ -19982,7 +19982,7 @@
         <v>1557</v>
       </c>
       <c r="E333">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F333" t="s">
         <v>1622</v>
@@ -20017,7 +20017,7 @@
         <v>1557</v>
       </c>
       <c r="E334">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F334" t="s">
         <v>1622</v>
@@ -20052,7 +20052,7 @@
         <v>1558</v>
       </c>
       <c r="E335">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F335" t="s">
         <v>1622</v>
@@ -20087,7 +20087,7 @@
         <v>1558</v>
       </c>
       <c r="E336">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F336" t="s">
         <v>1622</v>
@@ -20122,7 +20122,7 @@
         <v>1559</v>
       </c>
       <c r="E337">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F337" t="s">
         <v>1622</v>
@@ -20157,7 +20157,7 @@
         <v>1559</v>
       </c>
       <c r="E338">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F338" t="s">
         <v>1622</v>
@@ -20192,7 +20192,7 @@
         <v>1559</v>
       </c>
       <c r="E339">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F339" t="s">
         <v>1622</v>
@@ -20227,7 +20227,7 @@
         <v>1559</v>
       </c>
       <c r="E340">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F340" t="s">
         <v>1622</v>
@@ -20262,7 +20262,7 @@
         <v>1559</v>
       </c>
       <c r="E341">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F341" t="s">
         <v>1622</v>
@@ -20297,7 +20297,7 @@
         <v>1559</v>
       </c>
       <c r="E342">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F342" t="s">
         <v>1622</v>
@@ -20332,7 +20332,7 @@
         <v>1559</v>
       </c>
       <c r="E343">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F343" t="s">
         <v>1622</v>
@@ -20367,7 +20367,7 @@
         <v>1559</v>
       </c>
       <c r="E344">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F344" t="s">
         <v>1622</v>
@@ -20402,7 +20402,7 @@
         <v>1560</v>
       </c>
       <c r="E345">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F345" t="s">
         <v>1622</v>
@@ -20437,7 +20437,7 @@
         <v>1560</v>
       </c>
       <c r="E346">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F346" t="s">
         <v>1622</v>
@@ -20472,7 +20472,7 @@
         <v>1560</v>
       </c>
       <c r="E347">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F347" t="s">
         <v>1622</v>
@@ -20507,7 +20507,7 @@
         <v>1561</v>
       </c>
       <c r="E348">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F348" t="s">
         <v>1622</v>
@@ -20542,7 +20542,7 @@
         <v>1561</v>
       </c>
       <c r="E349">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F349" t="s">
         <v>1622</v>
@@ -20577,7 +20577,7 @@
         <v>1562</v>
       </c>
       <c r="E350">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F350" t="s">
         <v>1622</v>
@@ -20612,7 +20612,7 @@
         <v>1563</v>
       </c>
       <c r="E351">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F351" t="s">
         <v>1624</v>
@@ -20647,7 +20647,7 @@
         <v>1563</v>
       </c>
       <c r="E352">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F352" t="s">
         <v>1622</v>
@@ -20682,7 +20682,7 @@
         <v>1563</v>
       </c>
       <c r="E353">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F353" t="s">
         <v>1622</v>
@@ -20717,7 +20717,7 @@
         <v>1563</v>
       </c>
       <c r="E354">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F354" t="s">
         <v>1622</v>
@@ -20752,7 +20752,7 @@
         <v>1563</v>
       </c>
       <c r="E355">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F355" t="s">
         <v>1622</v>
@@ -20787,7 +20787,7 @@
         <v>1563</v>
       </c>
       <c r="E356">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F356" t="s">
         <v>1622</v>
@@ -20822,7 +20822,7 @@
         <v>1564</v>
       </c>
       <c r="E357">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F357" t="s">
         <v>1622</v>
@@ -20857,7 +20857,7 @@
         <v>1564</v>
       </c>
       <c r="E358">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F358" t="s">
         <v>1622</v>
@@ -20892,7 +20892,7 @@
         <v>1565</v>
       </c>
       <c r="E359">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F359" t="s">
         <v>1622</v>
@@ -20927,7 +20927,7 @@
         <v>1565</v>
       </c>
       <c r="E360">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F360" t="s">
         <v>1622</v>
@@ -20962,7 +20962,7 @@
         <v>1565</v>
       </c>
       <c r="E361">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F361" t="s">
         <v>1622</v>
@@ -20997,7 +20997,7 @@
         <v>1566</v>
       </c>
       <c r="E362">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F362" t="s">
         <v>1622</v>
@@ -21032,7 +21032,7 @@
         <v>1567</v>
       </c>
       <c r="E363">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F363" t="s">
         <v>1622</v>
@@ -21067,7 +21067,7 @@
         <v>1568</v>
       </c>
       <c r="E364">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F364" t="s">
         <v>1622</v>
@@ -21102,7 +21102,7 @@
         <v>1568</v>
       </c>
       <c r="E365">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F365" t="s">
         <v>1622</v>
@@ -21137,7 +21137,7 @@
         <v>1569</v>
       </c>
       <c r="E366">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F366" t="s">
         <v>1622</v>
@@ -21172,7 +21172,7 @@
         <v>1569</v>
       </c>
       <c r="E367">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F367" t="s">
         <v>1622</v>
@@ -21207,7 +21207,7 @@
         <v>1569</v>
       </c>
       <c r="E368">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F368" t="s">
         <v>1622</v>
@@ -21242,7 +21242,7 @@
         <v>1570</v>
       </c>
       <c r="E369">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F369" t="s">
         <v>1622</v>
@@ -21277,7 +21277,7 @@
         <v>1570</v>
       </c>
       <c r="E370">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F370" t="s">
         <v>1622</v>
@@ -21312,7 +21312,7 @@
         <v>1570</v>
       </c>
       <c r="E371">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F371" t="s">
         <v>1622</v>
@@ -21347,7 +21347,7 @@
         <v>1570</v>
       </c>
       <c r="E372">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F372" t="s">
         <v>1622</v>
@@ -21382,7 +21382,7 @@
         <v>1570</v>
       </c>
       <c r="E373">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F373" t="s">
         <v>1622</v>
@@ -21417,7 +21417,7 @@
         <v>1570</v>
       </c>
       <c r="E374">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F374" t="s">
         <v>1622</v>
@@ -21452,7 +21452,7 @@
         <v>1570</v>
       </c>
       <c r="E375">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F375" t="s">
         <v>1622</v>
@@ -21487,7 +21487,7 @@
         <v>1570</v>
       </c>
       <c r="E376">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F376" t="s">
         <v>1622</v>
@@ -21522,7 +21522,7 @@
         <v>1570</v>
       </c>
       <c r="E377">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F377" t="s">
         <v>1622</v>
@@ -21557,7 +21557,7 @@
         <v>1571</v>
       </c>
       <c r="E378">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F378" t="s">
         <v>1622</v>
@@ -21592,7 +21592,7 @@
         <v>1571</v>
       </c>
       <c r="E379">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F379" t="s">
         <v>1622</v>
@@ -21627,7 +21627,7 @@
         <v>1571</v>
       </c>
       <c r="E380">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F380" t="s">
         <v>1622</v>
@@ -21662,7 +21662,7 @@
         <v>1571</v>
       </c>
       <c r="E381">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F381" t="s">
         <v>1622</v>
@@ -21697,7 +21697,7 @@
         <v>1572</v>
       </c>
       <c r="E382">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F382" t="s">
         <v>1625</v>
@@ -21732,7 +21732,7 @@
         <v>1572</v>
       </c>
       <c r="E383">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F383" t="s">
         <v>1622</v>
@@ -21767,7 +21767,7 @@
         <v>1573</v>
       </c>
       <c r="E384">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F384" t="s">
         <v>1622</v>
@@ -21802,7 +21802,7 @@
         <v>1573</v>
       </c>
       <c r="E385">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F385" t="s">
         <v>1622</v>
@@ -21837,7 +21837,7 @@
         <v>1573</v>
       </c>
       <c r="E386">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F386" t="s">
         <v>1622</v>
@@ -21872,7 +21872,7 @@
         <v>1573</v>
       </c>
       <c r="E387">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F387" t="s">
         <v>1622</v>
@@ -21907,7 +21907,7 @@
         <v>1573</v>
       </c>
       <c r="E388">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F388" t="s">
         <v>1626</v>
@@ -21945,7 +21945,7 @@
         <v>1573</v>
       </c>
       <c r="E389">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F389" t="s">
         <v>1622</v>
@@ -21980,7 +21980,7 @@
         <v>1573</v>
       </c>
       <c r="E390">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F390" t="s">
         <v>1622</v>
@@ -22015,7 +22015,7 @@
         <v>1574</v>
       </c>
       <c r="E391">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F391" t="s">
         <v>1622</v>
@@ -22050,7 +22050,7 @@
         <v>1574</v>
       </c>
       <c r="E392">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F392" t="s">
         <v>1622</v>
@@ -22085,7 +22085,7 @@
         <v>1574</v>
       </c>
       <c r="E393">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F393" t="s">
         <v>1622</v>
@@ -22120,7 +22120,7 @@
         <v>1574</v>
       </c>
       <c r="E394">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F394" t="s">
         <v>1622</v>
@@ -22158,7 +22158,7 @@
         <v>1574</v>
       </c>
       <c r="E395">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F395" t="s">
         <v>1622</v>
@@ -22193,7 +22193,7 @@
         <v>1574</v>
       </c>
       <c r="E396">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F396" t="s">
         <v>1622</v>
@@ -22228,7 +22228,7 @@
         <v>1574</v>
       </c>
       <c r="E397">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F397" t="s">
         <v>1622</v>
@@ -22263,7 +22263,7 @@
         <v>1574</v>
       </c>
       <c r="E398">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F398" t="s">
         <v>1622</v>
@@ -22298,7 +22298,7 @@
         <v>1574</v>
       </c>
       <c r="E399">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F399" t="s">
         <v>1622</v>
@@ -22333,7 +22333,7 @@
         <v>1575</v>
       </c>
       <c r="E400">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F400" t="s">
         <v>1623</v>
@@ -22368,7 +22368,7 @@
         <v>1576</v>
       </c>
       <c r="E401">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F401" t="s">
         <v>1626</v>
@@ -22403,7 +22403,7 @@
         <v>1577</v>
       </c>
       <c r="E402">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F402" t="s">
         <v>1622</v>
@@ -22438,7 +22438,7 @@
         <v>1578</v>
       </c>
       <c r="E403">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F403" t="s">
         <v>1622</v>
@@ -22473,7 +22473,7 @@
         <v>1578</v>
       </c>
       <c r="E404">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F404" t="s">
         <v>1622</v>
@@ -22508,7 +22508,7 @@
         <v>1579</v>
       </c>
       <c r="E405">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F405" t="s">
         <v>1622</v>
@@ -22543,7 +22543,7 @@
         <v>1580</v>
       </c>
       <c r="E406">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F406" t="s">
         <v>1625</v>
@@ -22578,7 +22578,7 @@
         <v>1580</v>
       </c>
       <c r="E407">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F407" t="s">
         <v>1622</v>
@@ -22613,7 +22613,7 @@
         <v>1580</v>
       </c>
       <c r="E408">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F408" t="s">
         <v>1622</v>
@@ -22648,7 +22648,7 @@
         <v>1580</v>
       </c>
       <c r="E409">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F409" t="s">
         <v>1622</v>
@@ -22683,7 +22683,7 @@
         <v>1580</v>
       </c>
       <c r="E410">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F410" t="s">
         <v>1622</v>
@@ -22718,7 +22718,7 @@
         <v>1580</v>
       </c>
       <c r="E411">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F411" t="s">
         <v>1622</v>
@@ -22753,7 +22753,7 @@
         <v>1581</v>
       </c>
       <c r="E412">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F412" t="s">
         <v>1622</v>
@@ -22788,7 +22788,7 @@
         <v>1581</v>
       </c>
       <c r="E413">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F413" t="s">
         <v>1622</v>
@@ -22823,7 +22823,7 @@
         <v>1581</v>
       </c>
       <c r="E414">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F414" t="s">
         <v>1622</v>
@@ -22858,7 +22858,7 @@
         <v>1581</v>
       </c>
       <c r="E415">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F415" t="s">
         <v>1622</v>
@@ -22893,7 +22893,7 @@
         <v>1582</v>
       </c>
       <c r="E416">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F416" t="s">
         <v>1622</v>
@@ -22928,7 +22928,7 @@
         <v>1582</v>
       </c>
       <c r="E417">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F417" t="s">
         <v>1622</v>
@@ -22963,7 +22963,7 @@
         <v>1582</v>
       </c>
       <c r="E418">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F418" t="s">
         <v>1622</v>
@@ -23001,7 +23001,7 @@
         <v>1582</v>
       </c>
       <c r="E419">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F419" t="s">
         <v>1622</v>
@@ -23036,7 +23036,7 @@
         <v>1583</v>
       </c>
       <c r="E420">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F420" t="s">
         <v>1622</v>
@@ -23071,7 +23071,7 @@
         <v>1583</v>
       </c>
       <c r="E421">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F421" t="s">
         <v>1622</v>
@@ -23106,7 +23106,7 @@
         <v>1583</v>
       </c>
       <c r="E422">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F422" t="s">
         <v>1622</v>
@@ -23141,7 +23141,7 @@
         <v>1583</v>
       </c>
       <c r="E423">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F423" t="s">
         <v>1622</v>
@@ -23176,7 +23176,7 @@
         <v>1583</v>
       </c>
       <c r="E424">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F424" t="s">
         <v>1622</v>
@@ -23211,7 +23211,7 @@
         <v>1584</v>
       </c>
       <c r="E425">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F425" t="s">
         <v>1622</v>
@@ -23246,7 +23246,7 @@
         <v>1584</v>
       </c>
       <c r="E426">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F426" t="s">
         <v>1622</v>
@@ -23281,7 +23281,7 @@
         <v>1585</v>
       </c>
       <c r="E427">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F427" t="s">
         <v>1622</v>
@@ -23316,7 +23316,7 @@
         <v>1585</v>
       </c>
       <c r="E428">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F428" t="s">
         <v>1622</v>
@@ -23351,7 +23351,7 @@
         <v>1585</v>
       </c>
       <c r="E429">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F429" t="s">
         <v>1622</v>
@@ -23386,7 +23386,7 @@
         <v>1585</v>
       </c>
       <c r="E430">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F430" t="s">
         <v>1622</v>
@@ -23421,7 +23421,7 @@
         <v>1585</v>
       </c>
       <c r="E431">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F431" t="s">
         <v>1622</v>
@@ -23456,7 +23456,7 @@
         <v>1585</v>
       </c>
       <c r="E432">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F432" t="s">
         <v>1622</v>
@@ -23491,7 +23491,7 @@
         <v>1585</v>
       </c>
       <c r="E433">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F433" t="s">
         <v>1622</v>
@@ -23526,7 +23526,7 @@
         <v>1585</v>
       </c>
       <c r="E434">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F434" t="s">
         <v>1622</v>
@@ -23561,7 +23561,7 @@
         <v>1585</v>
       </c>
       <c r="E435">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F435" t="s">
         <v>1622</v>
@@ -23596,7 +23596,7 @@
         <v>1585</v>
       </c>
       <c r="E436">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F436" t="s">
         <v>1622</v>
@@ -23631,7 +23631,7 @@
         <v>1586</v>
       </c>
       <c r="E437">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F437" t="s">
         <v>1622</v>
@@ -23666,7 +23666,7 @@
         <v>1586</v>
       </c>
       <c r="E438">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F438" t="s">
         <v>1622</v>
@@ -23701,7 +23701,7 @@
         <v>1586</v>
       </c>
       <c r="E439">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F439" t="s">
         <v>1623</v>
@@ -23736,7 +23736,7 @@
         <v>1587</v>
       </c>
       <c r="E440">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F440" t="s">
         <v>1622</v>
@@ -23771,7 +23771,7 @@
         <v>1587</v>
       </c>
       <c r="E441">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F441" t="s">
         <v>1622</v>
@@ -23806,7 +23806,7 @@
         <v>1587</v>
       </c>
       <c r="E442">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F442" t="s">
         <v>1622</v>
@@ -23841,7 +23841,7 @@
         <v>1587</v>
       </c>
       <c r="E443">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F443" t="s">
         <v>1622</v>
@@ -23876,7 +23876,7 @@
         <v>1587</v>
       </c>
       <c r="E444">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F444" t="s">
         <v>1622</v>
@@ -23911,7 +23911,7 @@
         <v>1587</v>
       </c>
       <c r="E445">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F445" t="s">
         <v>1622</v>
@@ -23946,7 +23946,7 @@
         <v>1587</v>
       </c>
       <c r="E446">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F446" t="s">
         <v>1625</v>
@@ -23981,7 +23981,7 @@
         <v>1588</v>
       </c>
       <c r="E447">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F447" t="s">
         <v>1622</v>
@@ -24016,7 +24016,7 @@
         <v>1588</v>
       </c>
       <c r="E448">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F448" t="s">
         <v>1622</v>
@@ -24051,7 +24051,7 @@
         <v>1588</v>
       </c>
       <c r="E449">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F449" t="s">
         <v>1622</v>
@@ -24086,7 +24086,7 @@
         <v>1588</v>
       </c>
       <c r="E450">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F450" t="s">
         <v>1622</v>
@@ -24121,7 +24121,7 @@
         <v>1589</v>
       </c>
       <c r="E451">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F451" t="s">
         <v>1622</v>
@@ -24156,7 +24156,7 @@
         <v>1589</v>
       </c>
       <c r="E452">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F452" t="s">
         <v>1625</v>
@@ -24191,7 +24191,7 @@
         <v>1589</v>
       </c>
       <c r="E453">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F453" t="s">
         <v>1622</v>
@@ -24226,7 +24226,7 @@
         <v>1589</v>
       </c>
       <c r="E454">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F454" t="s">
         <v>1622</v>
@@ -24261,7 +24261,7 @@
         <v>1589</v>
       </c>
       <c r="E455">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F455" t="s">
         <v>1622</v>
@@ -24296,7 +24296,7 @@
         <v>1589</v>
       </c>
       <c r="E456">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F456" t="s">
         <v>1622</v>
@@ -24331,7 +24331,7 @@
         <v>1589</v>
       </c>
       <c r="E457">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F457" t="s">
         <v>1626</v>
@@ -24366,7 +24366,7 @@
         <v>1589</v>
       </c>
       <c r="E458">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F458" t="s">
         <v>1622</v>
@@ -24401,7 +24401,7 @@
         <v>1589</v>
       </c>
       <c r="E459">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F459" t="s">
         <v>1622</v>
@@ -24436,7 +24436,7 @@
         <v>1590</v>
       </c>
       <c r="E460">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F460" t="s">
         <v>1622</v>
@@ -24471,7 +24471,7 @@
         <v>1590</v>
       </c>
       <c r="E461">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F461" t="s">
         <v>1622</v>
@@ -24506,7 +24506,7 @@
         <v>1590</v>
       </c>
       <c r="E462">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F462" t="s">
         <v>1622</v>
@@ -24541,7 +24541,7 @@
         <v>1590</v>
       </c>
       <c r="E463">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F463" t="s">
         <v>1622</v>
@@ -24576,7 +24576,7 @@
         <v>1590</v>
       </c>
       <c r="E464">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F464" t="s">
         <v>1622</v>
@@ -24611,7 +24611,7 @@
         <v>1590</v>
       </c>
       <c r="E465">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F465" t="s">
         <v>1624</v>
@@ -24646,7 +24646,7 @@
         <v>1590</v>
       </c>
       <c r="E466">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F466" t="s">
         <v>1622</v>
@@ -24681,7 +24681,7 @@
         <v>1590</v>
       </c>
       <c r="E467">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F467" t="s">
         <v>1622</v>
@@ -24716,7 +24716,7 @@
         <v>1591</v>
       </c>
       <c r="E468">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F468" t="s">
         <v>1622</v>
@@ -24751,7 +24751,7 @@
         <v>1591</v>
       </c>
       <c r="E469">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F469" t="s">
         <v>1622</v>
@@ -24786,7 +24786,7 @@
         <v>1591</v>
       </c>
       <c r="E470">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F470" t="s">
         <v>1622</v>
@@ -24821,7 +24821,7 @@
         <v>1591</v>
       </c>
       <c r="E471">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F471" t="s">
         <v>1622</v>
@@ -24856,7 +24856,7 @@
         <v>1591</v>
       </c>
       <c r="E472">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F472" t="s">
         <v>1622</v>
@@ -24891,7 +24891,7 @@
         <v>1592</v>
       </c>
       <c r="E473">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F473" t="s">
         <v>1622</v>
@@ -24926,7 +24926,7 @@
         <v>1592</v>
       </c>
       <c r="E474">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F474" t="s">
         <v>1622</v>
@@ -24961,7 +24961,7 @@
         <v>1592</v>
       </c>
       <c r="E475">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F475" t="s">
         <v>1622</v>
@@ -24996,7 +24996,7 @@
         <v>1592</v>
       </c>
       <c r="E476">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F476" t="s">
         <v>1622</v>
@@ -25031,7 +25031,7 @@
         <v>1592</v>
       </c>
       <c r="E477">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F477" t="s">
         <v>1622</v>
@@ -25069,7 +25069,7 @@
         <v>1593</v>
       </c>
       <c r="E478">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F478" t="s">
         <v>1622</v>
@@ -25104,7 +25104,7 @@
         <v>1593</v>
       </c>
       <c r="E479">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F479" t="s">
         <v>1622</v>
@@ -25139,7 +25139,7 @@
         <v>1593</v>
       </c>
       <c r="E480">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F480" t="s">
         <v>1622</v>
@@ -25174,7 +25174,7 @@
         <v>1593</v>
       </c>
       <c r="E481">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F481" t="s">
         <v>1622</v>
@@ -25209,7 +25209,7 @@
         <v>1593</v>
       </c>
       <c r="E482">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F482" t="s">
         <v>1622</v>
@@ -25244,7 +25244,7 @@
         <v>1593</v>
       </c>
       <c r="E483">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F483" t="s">
         <v>1622</v>
@@ -25279,7 +25279,7 @@
         <v>1594</v>
       </c>
       <c r="E484">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F484" t="s">
         <v>1622</v>
@@ -25314,7 +25314,7 @@
         <v>1594</v>
       </c>
       <c r="E485">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F485" t="s">
         <v>1622</v>
@@ -25349,7 +25349,7 @@
         <v>1594</v>
       </c>
       <c r="E486">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F486" t="s">
         <v>1622</v>
@@ -25384,7 +25384,7 @@
         <v>1595</v>
       </c>
       <c r="E487">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F487" t="s">
         <v>1622</v>
@@ -25419,7 +25419,7 @@
         <v>1596</v>
       </c>
       <c r="E488">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F488" t="s">
         <v>1622</v>
@@ -25454,7 +25454,7 @@
         <v>1596</v>
       </c>
       <c r="E489">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F489" t="s">
         <v>1622</v>
@@ -25489,7 +25489,7 @@
         <v>1596</v>
       </c>
       <c r="E490">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F490" t="s">
         <v>1624</v>
@@ -25527,7 +25527,7 @@
         <v>1596</v>
       </c>
       <c r="E491">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F491" t="s">
         <v>1622</v>
@@ -25562,7 +25562,7 @@
         <v>1596</v>
       </c>
       <c r="E492">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F492" t="s">
         <v>1622</v>
@@ -25597,7 +25597,7 @@
         <v>1597</v>
       </c>
       <c r="E493">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F493" t="s">
         <v>1622</v>
@@ -25632,7 +25632,7 @@
         <v>1597</v>
       </c>
       <c r="E494">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F494" t="s">
         <v>1622</v>
@@ -25667,7 +25667,7 @@
         <v>1597</v>
       </c>
       <c r="E495">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F495" t="s">
         <v>1622</v>
@@ -25702,7 +25702,7 @@
         <v>1597</v>
       </c>
       <c r="E496">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F496" t="s">
         <v>1622</v>
@@ -25737,7 +25737,7 @@
         <v>1597</v>
       </c>
       <c r="E497">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F497" t="s">
         <v>1622</v>
@@ -25772,7 +25772,7 @@
         <v>1598</v>
       </c>
       <c r="E498">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F498" t="s">
         <v>1622</v>
@@ -25807,7 +25807,7 @@
         <v>1598</v>
       </c>
       <c r="E499">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F499" t="s">
         <v>1622</v>
@@ -25842,7 +25842,7 @@
         <v>1598</v>
       </c>
       <c r="E500">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F500" t="s">
         <v>1622</v>
@@ -25877,7 +25877,7 @@
         <v>1598</v>
       </c>
       <c r="E501">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F501" t="s">
         <v>1622</v>
@@ -25912,7 +25912,7 @@
         <v>1598</v>
       </c>
       <c r="E502">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F502" t="s">
         <v>1622</v>
@@ -25947,7 +25947,7 @@
         <v>1598</v>
       </c>
       <c r="E503">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F503" t="s">
         <v>1622</v>
@@ -25982,7 +25982,7 @@
         <v>1598</v>
       </c>
       <c r="E504">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F504" t="s">
         <v>1622</v>
@@ -26017,7 +26017,7 @@
         <v>1598</v>
       </c>
       <c r="E505">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F505" t="s">
         <v>1622</v>
@@ -26052,7 +26052,7 @@
         <v>1599</v>
       </c>
       <c r="E506">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F506" t="s">
         <v>1622</v>
@@ -26087,7 +26087,7 @@
         <v>1599</v>
       </c>
       <c r="E507">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F507" t="s">
         <v>1622</v>
@@ -26122,7 +26122,7 @@
         <v>1600</v>
       </c>
       <c r="E508">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F508" t="s">
         <v>1622</v>
@@ -26157,7 +26157,7 @@
         <v>1600</v>
       </c>
       <c r="E509">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F509" t="s">
         <v>1622</v>
@@ -26192,7 +26192,7 @@
         <v>1600</v>
       </c>
       <c r="E510">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F510" t="s">
         <v>1622</v>
@@ -26227,7 +26227,7 @@
         <v>1600</v>
       </c>
       <c r="E511">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F511" t="s">
         <v>1626</v>
@@ -26265,7 +26265,7 @@
         <v>1600</v>
       </c>
       <c r="E512">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F512" t="s">
         <v>1622</v>
@@ -26300,7 +26300,7 @@
         <v>1600</v>
       </c>
       <c r="E513">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F513" t="s">
         <v>1626</v>
@@ -26335,7 +26335,7 @@
         <v>1601</v>
       </c>
       <c r="E514">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F514" t="s">
         <v>1622</v>
@@ -26370,7 +26370,7 @@
         <v>1602</v>
       </c>
       <c r="E515">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F515" t="s">
         <v>1622</v>
@@ -26405,7 +26405,7 @@
         <v>1602</v>
       </c>
       <c r="E516">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F516" t="s">
         <v>1622</v>
@@ -26440,7 +26440,7 @@
         <v>1602</v>
       </c>
       <c r="E517">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F517" t="s">
         <v>1622</v>
@@ -26475,7 +26475,7 @@
         <v>1602</v>
       </c>
       <c r="E518">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F518" t="s">
         <v>1622</v>
@@ -26510,7 +26510,7 @@
         <v>1603</v>
       </c>
       <c r="E519">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F519" t="s">
         <v>1622</v>
@@ -26545,7 +26545,7 @@
         <v>1603</v>
       </c>
       <c r="E520">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F520" t="s">
         <v>1626</v>
@@ -26580,7 +26580,7 @@
         <v>1603</v>
       </c>
       <c r="E521">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F521" t="s">
         <v>1622</v>
@@ -26615,7 +26615,7 @@
         <v>1603</v>
       </c>
       <c r="E522">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F522" t="s">
         <v>1622</v>
@@ -26650,7 +26650,7 @@
         <v>1603</v>
       </c>
       <c r="E523">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F523" t="s">
         <v>1622</v>
@@ -26685,7 +26685,7 @@
         <v>1604</v>
       </c>
       <c r="E524">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F524" t="s">
         <v>1622</v>
@@ -26720,7 +26720,7 @@
         <v>1604</v>
       </c>
       <c r="E525">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F525" t="s">
         <v>1624</v>
@@ -26755,7 +26755,7 @@
         <v>1604</v>
       </c>
       <c r="E526">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F526" t="s">
         <v>1622</v>
@@ -26790,7 +26790,7 @@
         <v>1604</v>
       </c>
       <c r="E527">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F527" t="s">
         <v>1622</v>
@@ -26825,7 +26825,7 @@
         <v>1605</v>
       </c>
       <c r="E528">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F528" t="s">
         <v>1622</v>
@@ -26860,7 +26860,7 @@
         <v>1605</v>
       </c>
       <c r="E529">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F529" t="s">
         <v>1622</v>
@@ -26895,7 +26895,7 @@
         <v>1605</v>
       </c>
       <c r="E530">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F530" t="s">
         <v>1622</v>
@@ -26930,7 +26930,7 @@
         <v>1605</v>
       </c>
       <c r="E531">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F531" t="s">
         <v>1622</v>
@@ -26965,7 +26965,7 @@
         <v>1605</v>
       </c>
       <c r="E532">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F532" t="s">
         <v>1622</v>
@@ -27000,7 +27000,7 @@
         <v>1605</v>
       </c>
       <c r="E533">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F533" t="s">
         <v>1622</v>
@@ -27035,7 +27035,7 @@
         <v>1606</v>
       </c>
       <c r="E534">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F534" t="s">
         <v>1622</v>
@@ -27070,7 +27070,7 @@
         <v>1606</v>
       </c>
       <c r="E535">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F535" t="s">
         <v>1622</v>
@@ -27105,7 +27105,7 @@
         <v>1606</v>
       </c>
       <c r="E536">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F536" t="s">
         <v>1622</v>
@@ -27140,7 +27140,7 @@
         <v>1606</v>
       </c>
       <c r="E537">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F537" t="s">
         <v>1622</v>
@@ -27175,7 +27175,7 @@
         <v>1606</v>
       </c>
       <c r="E538">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F538" t="s">
         <v>1622</v>
@@ -27210,7 +27210,7 @@
         <v>1606</v>
       </c>
       <c r="E539">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F539" t="s">
         <v>1622</v>
@@ -27245,7 +27245,7 @@
         <v>1606</v>
       </c>
       <c r="E540">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F540" t="s">
         <v>1622</v>
@@ -27280,7 +27280,7 @@
         <v>1606</v>
       </c>
       <c r="E541">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F541" t="s">
         <v>1622</v>
@@ -27315,7 +27315,7 @@
         <v>1606</v>
       </c>
       <c r="E542">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F542" t="s">
         <v>1622</v>
@@ -27350,7 +27350,7 @@
         <v>1606</v>
       </c>
       <c r="E543">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F543" t="s">
         <v>1622</v>
@@ -27385,7 +27385,7 @@
         <v>1606</v>
       </c>
       <c r="E544">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F544" t="s">
         <v>1622</v>
@@ -27420,7 +27420,7 @@
         <v>1606</v>
       </c>
       <c r="E545">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F545" t="s">
         <v>1622</v>
@@ -27455,7 +27455,7 @@
         <v>1606</v>
       </c>
       <c r="E546">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F546" t="s">
         <v>1622</v>
@@ -27490,7 +27490,7 @@
         <v>1606</v>
       </c>
       <c r="E547">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F547" t="s">
         <v>1622</v>
@@ -27525,7 +27525,7 @@
         <v>1606</v>
       </c>
       <c r="E548">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F548" t="s">
         <v>1622</v>
@@ -27560,7 +27560,7 @@
         <v>1606</v>
       </c>
       <c r="E549">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F549" t="s">
         <v>1622</v>
@@ -27595,7 +27595,7 @@
         <v>1606</v>
       </c>
       <c r="E550">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F550" t="s">
         <v>1622</v>
@@ -27630,7 +27630,7 @@
         <v>1606</v>
       </c>
       <c r="E551">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F551" t="s">
         <v>1622</v>
@@ -27665,7 +27665,7 @@
         <v>1606</v>
       </c>
       <c r="E552">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F552" t="s">
         <v>1622</v>
@@ -27700,7 +27700,7 @@
         <v>1606</v>
       </c>
       <c r="E553">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F553" t="s">
         <v>1622</v>
@@ -27735,7 +27735,7 @@
         <v>1606</v>
       </c>
       <c r="E554">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F554" t="s">
         <v>1622</v>
@@ -27770,7 +27770,7 @@
         <v>1606</v>
       </c>
       <c r="E555">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F555" t="s">
         <v>1622</v>
@@ -27805,7 +27805,7 @@
         <v>1606</v>
       </c>
       <c r="E556">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F556" t="s">
         <v>1622</v>
@@ -27840,7 +27840,7 @@
         <v>1606</v>
       </c>
       <c r="E557">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F557" t="s">
         <v>1622</v>
@@ -27875,7 +27875,7 @@
         <v>1606</v>
       </c>
       <c r="E558">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F558" t="s">
         <v>1622</v>
@@ -27910,7 +27910,7 @@
         <v>1606</v>
       </c>
       <c r="E559">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F559" t="s">
         <v>1622</v>
@@ -27945,7 +27945,7 @@
         <v>1606</v>
       </c>
       <c r="E560">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F560" t="s">
         <v>1624</v>
@@ -27983,7 +27983,7 @@
         <v>1607</v>
       </c>
       <c r="E561">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F561" t="s">
         <v>1622</v>
@@ -28018,7 +28018,7 @@
         <v>1607</v>
       </c>
       <c r="E562">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F562" t="s">
         <v>1622</v>
@@ -28053,7 +28053,7 @@
         <v>1607</v>
       </c>
       <c r="E563">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F563" t="s">
         <v>1622</v>
@@ -28088,7 +28088,7 @@
         <v>1607</v>
       </c>
       <c r="E564">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F564" t="s">
         <v>1622</v>
@@ -28123,7 +28123,7 @@
         <v>1607</v>
       </c>
       <c r="E565">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F565" t="s">
         <v>1622</v>
@@ -28158,7 +28158,7 @@
         <v>1607</v>
       </c>
       <c r="E566">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F566" t="s">
         <v>1622</v>
@@ -28193,7 +28193,7 @@
         <v>1607</v>
       </c>
       <c r="E567">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F567" t="s">
         <v>1626</v>
@@ -28228,7 +28228,7 @@
         <v>1607</v>
       </c>
       <c r="E568">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F568" t="s">
         <v>1622</v>
@@ -28263,7 +28263,7 @@
         <v>1608</v>
       </c>
       <c r="E569">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F569" t="s">
         <v>1622</v>
@@ -28298,7 +28298,7 @@
         <v>1608</v>
       </c>
       <c r="E570">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F570" t="s">
         <v>1622</v>
@@ -28333,7 +28333,7 @@
         <v>1609</v>
       </c>
       <c r="E571">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F571" t="s">
         <v>1622</v>
@@ -28368,7 +28368,7 @@
         <v>1609</v>
       </c>
       <c r="E572">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F572" t="s">
         <v>1624</v>
@@ -28406,7 +28406,7 @@
         <v>1609</v>
       </c>
       <c r="E573">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F573" t="s">
         <v>1624</v>
@@ -28444,7 +28444,7 @@
         <v>1610</v>
       </c>
       <c r="E574">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F574" t="s">
         <v>1624</v>
@@ -28482,7 +28482,7 @@
         <v>1610</v>
       </c>
       <c r="E575">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F575" t="s">
         <v>1622</v>
@@ -28517,7 +28517,7 @@
         <v>1610</v>
       </c>
       <c r="E576">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F576" t="s">
         <v>1622</v>
@@ -28552,7 +28552,7 @@
         <v>1610</v>
       </c>
       <c r="E577">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F577" t="s">
         <v>1624</v>
@@ -28590,7 +28590,7 @@
         <v>1610</v>
       </c>
       <c r="E578">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F578" t="s">
         <v>1622</v>
@@ -28625,7 +28625,7 @@
         <v>1610</v>
       </c>
       <c r="E579">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F579" t="s">
         <v>1622</v>
@@ -28660,7 +28660,7 @@
         <v>1610</v>
       </c>
       <c r="E580">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F580" t="s">
         <v>1622</v>
@@ -28695,7 +28695,7 @@
         <v>1610</v>
       </c>
       <c r="E581">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F581" t="s">
         <v>1622</v>
@@ -28733,7 +28733,7 @@
         <v>1610</v>
       </c>
       <c r="E582">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F582" t="s">
         <v>1622</v>
@@ -28768,7 +28768,7 @@
         <v>1610</v>
       </c>
       <c r="E583">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F583" t="s">
         <v>1622</v>
@@ -28803,7 +28803,7 @@
         <v>1611</v>
       </c>
       <c r="E584">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F584" t="s">
         <v>1622</v>
@@ -28841,7 +28841,7 @@
         <v>1611</v>
       </c>
       <c r="E585">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F585" t="s">
         <v>1626</v>
@@ -28876,7 +28876,7 @@
         <v>1611</v>
       </c>
       <c r="E586">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F586" t="s">
         <v>1624</v>
@@ -28911,7 +28911,7 @@
         <v>1611</v>
       </c>
       <c r="E587">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F587" t="s">
         <v>1622</v>
@@ -28946,7 +28946,7 @@
         <v>1611</v>
       </c>
       <c r="E588">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F588" t="s">
         <v>1622</v>
@@ -28981,7 +28981,7 @@
         <v>1611</v>
       </c>
       <c r="E589">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F589" t="s">
         <v>1622</v>
@@ -29016,7 +29016,7 @@
         <v>1611</v>
       </c>
       <c r="E590">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F590" t="s">
         <v>1622</v>
@@ -29051,7 +29051,7 @@
         <v>1611</v>
       </c>
       <c r="E591">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F591" t="s">
         <v>1622</v>
@@ -29086,7 +29086,7 @@
         <v>1611</v>
       </c>
       <c r="E592">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F592" t="s">
         <v>1622</v>
@@ -29121,7 +29121,7 @@
         <v>1612</v>
       </c>
       <c r="E593">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F593" t="s">
         <v>1622</v>
@@ -29159,7 +29159,7 @@
         <v>1612</v>
       </c>
       <c r="E594">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F594" t="s">
         <v>1622</v>
@@ -29194,7 +29194,7 @@
         <v>1613</v>
       </c>
       <c r="E595">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F595" t="s">
         <v>1622</v>
@@ -29229,7 +29229,7 @@
         <v>1613</v>
       </c>
       <c r="E596">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F596" t="s">
         <v>1624</v>
@@ -29267,7 +29267,7 @@
         <v>1613</v>
       </c>
       <c r="E597">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F597" t="s">
         <v>1622</v>
@@ -29302,7 +29302,7 @@
         <v>1613</v>
       </c>
       <c r="E598">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F598" t="s">
         <v>1622</v>
@@ -29337,7 +29337,7 @@
         <v>1613</v>
       </c>
       <c r="E599">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F599" t="s">
         <v>1622</v>
@@ -29372,7 +29372,7 @@
         <v>1613</v>
       </c>
       <c r="E600">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F600" t="s">
         <v>1622</v>
@@ -29407,7 +29407,7 @@
         <v>1613</v>
       </c>
       <c r="E601">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F601" t="s">
         <v>1622</v>
@@ -29442,7 +29442,7 @@
         <v>1613</v>
       </c>
       <c r="E602">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F602" t="s">
         <v>1624</v>
@@ -29477,7 +29477,7 @@
         <v>1613</v>
       </c>
       <c r="E603">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F603" t="s">
         <v>1622</v>
@@ -29512,7 +29512,7 @@
         <v>1613</v>
       </c>
       <c r="E604">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F604" t="s">
         <v>1622</v>
@@ -29547,7 +29547,7 @@
         <v>1614</v>
       </c>
       <c r="E605">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F605" t="s">
         <v>1622</v>
@@ -29582,7 +29582,7 @@
         <v>1614</v>
       </c>
       <c r="E606">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F606" t="s">
         <v>1622</v>
@@ -29617,7 +29617,7 @@
         <v>1614</v>
       </c>
       <c r="E607">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F607" t="s">
         <v>1622</v>
@@ -29652,7 +29652,7 @@
         <v>1614</v>
       </c>
       <c r="E608">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F608" t="s">
         <v>1622</v>
@@ -29687,7 +29687,7 @@
         <v>1614</v>
       </c>
       <c r="E609">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F609" t="s">
         <v>1624</v>
@@ -29725,7 +29725,7 @@
         <v>1614</v>
       </c>
       <c r="E610">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F610" t="s">
         <v>1622</v>
@@ -29760,7 +29760,7 @@
         <v>1614</v>
       </c>
       <c r="E611">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F611" t="s">
         <v>1622</v>
@@ -29795,7 +29795,7 @@
         <v>1614</v>
       </c>
       <c r="E612">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F612" t="s">
         <v>1622</v>
@@ -29830,7 +29830,7 @@
         <v>1614</v>
       </c>
       <c r="E613">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F613" t="s">
         <v>1622</v>
@@ -29865,7 +29865,7 @@
         <v>1614</v>
       </c>
       <c r="E614">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F614" t="s">
         <v>1624</v>
@@ -29900,7 +29900,7 @@
         <v>1614</v>
       </c>
       <c r="E615">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F615" t="s">
         <v>1622</v>
@@ -29935,7 +29935,7 @@
         <v>1614</v>
       </c>
       <c r="E616">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F616" t="s">
         <v>1626</v>
@@ -29970,7 +29970,7 @@
         <v>1614</v>
       </c>
       <c r="E617">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F617" t="s">
         <v>1622</v>
@@ -30005,7 +30005,7 @@
         <v>1615</v>
       </c>
       <c r="E618">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F618" t="s">
         <v>1624</v>
@@ -30043,7 +30043,7 @@
         <v>1615</v>
       </c>
       <c r="E619">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F619" t="s">
         <v>1622</v>
@@ -30078,7 +30078,7 @@
         <v>1615</v>
       </c>
       <c r="E620">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F620" t="s">
         <v>1622</v>
@@ -30113,7 +30113,7 @@
         <v>1615</v>
       </c>
       <c r="E621">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F621" t="s">
         <v>1622</v>
@@ -30148,7 +30148,7 @@
         <v>1615</v>
       </c>
       <c r="E622">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F622" t="s">
         <v>1622</v>
@@ -30183,7 +30183,7 @@
         <v>1615</v>
       </c>
       <c r="E623">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F623" t="s">
         <v>1622</v>
@@ -30218,7 +30218,7 @@
         <v>1615</v>
       </c>
       <c r="E624">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F624" t="s">
         <v>1622</v>
@@ -30253,7 +30253,7 @@
         <v>1615</v>
       </c>
       <c r="E625">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F625" t="s">
         <v>1622</v>
@@ -30288,7 +30288,7 @@
         <v>1615</v>
       </c>
       <c r="E626">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F626" t="s">
         <v>1622</v>
@@ -30326,7 +30326,7 @@
         <v>1615</v>
       </c>
       <c r="E627">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F627" t="s">
         <v>1624</v>
@@ -30364,7 +30364,7 @@
         <v>1615</v>
       </c>
       <c r="E628">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F628" t="s">
         <v>1622</v>
@@ -30399,7 +30399,7 @@
         <v>1615</v>
       </c>
       <c r="E629">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F629" t="s">
         <v>1624</v>
@@ -30434,7 +30434,7 @@
         <v>1615</v>
       </c>
       <c r="E630">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F630" t="s">
         <v>1624</v>
@@ -30469,7 +30469,7 @@
         <v>1615</v>
       </c>
       <c r="E631">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F631" t="s">
         <v>1622</v>
@@ -30504,7 +30504,7 @@
         <v>1616</v>
       </c>
       <c r="E632">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F632" t="s">
         <v>1622</v>
@@ -30539,7 +30539,7 @@
         <v>1616</v>
       </c>
       <c r="E633">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F633" t="s">
         <v>1622</v>
@@ -30574,7 +30574,7 @@
         <v>1616</v>
       </c>
       <c r="E634">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F634" t="s">
         <v>1622</v>
@@ -30609,7 +30609,7 @@
         <v>1616</v>
       </c>
       <c r="E635">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F635" t="s">
         <v>1622</v>
@@ -30644,7 +30644,7 @@
         <v>1616</v>
       </c>
       <c r="E636">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F636" t="s">
         <v>1622</v>
@@ -30679,7 +30679,7 @@
         <v>1616</v>
       </c>
       <c r="E637">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F637" t="s">
         <v>1622</v>
@@ -30714,7 +30714,7 @@
         <v>1616</v>
       </c>
       <c r="E638">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F638" t="s">
         <v>1622</v>
@@ -30749,7 +30749,7 @@
         <v>1616</v>
       </c>
       <c r="E639">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F639" t="s">
         <v>1622</v>
@@ -30784,7 +30784,7 @@
         <v>1616</v>
       </c>
       <c r="E640">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F640" t="s">
         <v>1622</v>
@@ -30819,7 +30819,7 @@
         <v>1616</v>
       </c>
       <c r="E641">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F641" t="s">
         <v>1622</v>
@@ -30857,7 +30857,7 @@
         <v>1617</v>
       </c>
       <c r="E642">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F642" t="s">
         <v>1622</v>
@@ -30892,7 +30892,7 @@
         <v>1617</v>
       </c>
       <c r="E643">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F643" t="s">
         <v>1622</v>
@@ -30927,7 +30927,7 @@
         <v>1618</v>
       </c>
       <c r="E644">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F644" t="s">
         <v>1622</v>
@@ -30965,7 +30965,7 @@
         <v>1618</v>
       </c>
       <c r="E645">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F645" t="s">
         <v>1622</v>
@@ -31000,7 +31000,7 @@
         <v>1618</v>
       </c>
       <c r="E646">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F646" t="s">
         <v>1622</v>
@@ -31035,7 +31035,7 @@
         <v>1618</v>
       </c>
       <c r="E647">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F647" t="s">
         <v>1624</v>
@@ -31073,7 +31073,7 @@
         <v>1618</v>
       </c>
       <c r="E648">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F648" t="s">
         <v>1622</v>
@@ -31111,7 +31111,7 @@
         <v>1618</v>
       </c>
       <c r="E649">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F649" t="s">
         <v>1622</v>
@@ -31146,7 +31146,7 @@
         <v>1618</v>
       </c>
       <c r="E650">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F650" t="s">
         <v>1622</v>
@@ -31181,7 +31181,7 @@
         <v>1618</v>
       </c>
       <c r="E651">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F651" t="s">
         <v>1622</v>
@@ -31216,7 +31216,7 @@
         <v>1619</v>
       </c>
       <c r="E652">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F652" t="s">
         <v>1622</v>
@@ -31251,7 +31251,7 @@
         <v>1619</v>
       </c>
       <c r="E653">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F653" t="s">
         <v>1622</v>
@@ -31286,7 +31286,7 @@
         <v>1619</v>
       </c>
       <c r="E654">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F654" t="s">
         <v>1622</v>
@@ -31321,7 +31321,7 @@
         <v>1619</v>
       </c>
       <c r="E655">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F655" t="s">
         <v>1622</v>
@@ -31356,7 +31356,7 @@
         <v>1619</v>
       </c>
       <c r="E656">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F656" t="s">
         <v>1622</v>
@@ -31391,7 +31391,7 @@
         <v>1619</v>
       </c>
       <c r="E657">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F657" t="s">
         <v>1622</v>
@@ -31426,7 +31426,7 @@
         <v>1619</v>
       </c>
       <c r="E658">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F658" t="s">
         <v>1622</v>
@@ -31461,7 +31461,7 @@
         <v>1619</v>
       </c>
       <c r="E659">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F659" t="s">
         <v>1622</v>
@@ -31496,7 +31496,7 @@
         <v>1619</v>
       </c>
       <c r="E660">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F660" t="s">
         <v>1622</v>
@@ -31531,7 +31531,7 @@
         <v>1619</v>
       </c>
       <c r="E661">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F661" t="s">
         <v>1622</v>
@@ -31566,7 +31566,7 @@
         <v>1619</v>
       </c>
       <c r="E662">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F662" t="s">
         <v>1622</v>
@@ -31601,7 +31601,7 @@
         <v>1619</v>
       </c>
       <c r="E663">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F663" t="s">
         <v>1622</v>
@@ -31636,7 +31636,7 @@
         <v>1619</v>
       </c>
       <c r="E664">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F664" t="s">
         <v>1622</v>
@@ -31674,7 +31674,7 @@
         <v>1619</v>
       </c>
       <c r="E665">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F665" t="s">
         <v>1622</v>
@@ -31712,7 +31712,7 @@
         <v>1619</v>
       </c>
       <c r="E666">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F666" t="s">
         <v>1622</v>
@@ -31750,7 +31750,7 @@
         <v>1619</v>
       </c>
       <c r="E667">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F667" t="s">
         <v>1622</v>
@@ -31785,7 +31785,7 @@
         <v>1619</v>
       </c>
       <c r="E668">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F668" t="s">
         <v>1622</v>
@@ -31823,7 +31823,7 @@
         <v>1620</v>
       </c>
       <c r="E669">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F669" t="s">
         <v>1622</v>
@@ -31858,7 +31858,7 @@
         <v>1620</v>
       </c>
       <c r="E670">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F670" t="s">
         <v>1622</v>
@@ -31896,7 +31896,7 @@
         <v>1620</v>
       </c>
       <c r="E671">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F671" t="s">
         <v>1622</v>
@@ -31931,7 +31931,7 @@
         <v>1620</v>
       </c>
       <c r="E672">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F672" t="s">
         <v>1622</v>
@@ -31966,7 +31966,7 @@
         <v>1620</v>
       </c>
       <c r="E673">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F673" t="s">
         <v>1622</v>
@@ -32001,7 +32001,7 @@
         <v>1621</v>
       </c>
       <c r="E674">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F674" t="s">
         <v>1622</v>
@@ -32036,7 +32036,7 @@
         <v>1621</v>
       </c>
       <c r="E675">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F675" t="s">
         <v>1622</v>
@@ -32071,7 +32071,7 @@
         <v>1621</v>
       </c>
       <c r="E676">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F676" t="s">
         <v>1622</v>
@@ -32106,7 +32106,7 @@
         <v>1621</v>
       </c>
       <c r="E677">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F677" t="s">
         <v>1622</v>
@@ -32144,7 +32144,7 @@
         <v>1621</v>
       </c>
       <c r="E678">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F678" t="s">
         <v>1622</v>
@@ -32182,7 +32182,7 @@
         <v>1621</v>
       </c>
       <c r="E679">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F679" t="s">
         <v>1622</v>
@@ -32217,7 +32217,7 @@
         <v>1621</v>
       </c>
       <c r="E680">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F680" t="s">
         <v>1622</v>
@@ -32252,7 +32252,7 @@
         <v>1621</v>
       </c>
       <c r="E681">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F681" t="s">
         <v>1622</v>
@@ -32287,7 +32287,7 @@
         <v>1621</v>
       </c>
       <c r="E682">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F682" t="s">
         <v>1622</v>
@@ -32322,7 +32322,7 @@
         <v>1621</v>
       </c>
       <c r="E683">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F683" t="s">
         <v>1622</v>
@@ -32357,7 +32357,7 @@
         <v>1621</v>
       </c>
       <c r="E684">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F684" t="s">
         <v>1622</v>
@@ -32380,7 +32380,7 @@
     </row>
     <row r="685" spans="1:12">
       <c r="A685" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B685" t="s">
         <v>720</v>
@@ -32388,8 +32388,11 @@
       <c r="C685" t="s">
         <v>1402</v>
       </c>
+      <c r="D685" t="s">
+        <v>1621</v>
+      </c>
       <c r="E685">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F685" t="s">
         <v>1622</v>
@@ -32398,21 +32401,21 @@
         <v>1627</v>
       </c>
       <c r="I685" t="s">
-        <v>1758</v>
+        <v>1747</v>
       </c>
       <c r="J685" t="s">
         <v>2439</v>
       </c>
       <c r="K685" t="s">
-        <v>2567</v>
+        <v>2470</v>
       </c>
       <c r="L685" t="s">
-        <v>2650</v>
+        <v>2602</v>
       </c>
     </row>
     <row r="686" spans="1:12">
       <c r="A686" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B686" t="s">
         <v>721</v>
@@ -32420,9 +32423,6 @@
       <c r="C686" t="s">
         <v>1403</v>
       </c>
-      <c r="D686" t="s">
-        <v>1621</v>
-      </c>
       <c r="E686">
         <v>0</v>
       </c>
@@ -32433,16 +32433,16 @@
         <v>1627</v>
       </c>
       <c r="I686" t="s">
-        <v>1747</v>
+        <v>1758</v>
       </c>
       <c r="J686" t="s">
         <v>2440</v>
       </c>
       <c r="K686" t="s">
-        <v>2470</v>
+        <v>2567</v>
       </c>
       <c r="L686" t="s">
-        <v>2602</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="687" spans="1:12">

--- a/BacklogGATEAutoCompleto.xlsx
+++ b/BacklogGATEAutoCompleto.xlsx
@@ -8349,7 +8349,7 @@
         <v>1397</v>
       </c>
       <c r="E2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="F2" t="s">
         <v>1613</v>
@@ -8384,7 +8384,7 @@
         <v>1398</v>
       </c>
       <c r="E3">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="F3" t="s">
         <v>1613</v>
@@ -8419,7 +8419,7 @@
         <v>1399</v>
       </c>
       <c r="E4">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="F4" t="s">
         <v>1613</v>
@@ -8454,7 +8454,7 @@
         <v>1400</v>
       </c>
       <c r="E5">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="F5" t="s">
         <v>1613</v>
@@ -8489,7 +8489,7 @@
         <v>1400</v>
       </c>
       <c r="E6">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="F6" t="s">
         <v>1613</v>
@@ -8524,7 +8524,7 @@
         <v>1401</v>
       </c>
       <c r="E7">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="F7" t="s">
         <v>1613</v>
@@ -8559,7 +8559,7 @@
         <v>1402</v>
       </c>
       <c r="E8">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F8" t="s">
         <v>1613</v>
@@ -8594,7 +8594,7 @@
         <v>1403</v>
       </c>
       <c r="E9">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="F9" t="s">
         <v>1613</v>
@@ -8629,7 +8629,7 @@
         <v>1404</v>
       </c>
       <c r="E10">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F10" t="s">
         <v>1613</v>
@@ -8664,7 +8664,7 @@
         <v>1405</v>
       </c>
       <c r="E11">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="F11" t="s">
         <v>1613</v>
@@ -8699,7 +8699,7 @@
         <v>1406</v>
       </c>
       <c r="E12">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="F12" t="s">
         <v>1613</v>
@@ -8734,7 +8734,7 @@
         <v>1407</v>
       </c>
       <c r="E13">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="F13" t="s">
         <v>1613</v>
@@ -8769,7 +8769,7 @@
         <v>1407</v>
       </c>
       <c r="E14">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="F14" t="s">
         <v>1613</v>
@@ -8804,7 +8804,7 @@
         <v>1408</v>
       </c>
       <c r="E15">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F15" t="s">
         <v>1613</v>
@@ -8839,7 +8839,7 @@
         <v>1409</v>
       </c>
       <c r="E16">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="F16" t="s">
         <v>1613</v>
@@ -8874,7 +8874,7 @@
         <v>1410</v>
       </c>
       <c r="E17">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F17" t="s">
         <v>1613</v>
@@ -8909,7 +8909,7 @@
         <v>1410</v>
       </c>
       <c r="E18">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F18" t="s">
         <v>1613</v>
@@ -8944,7 +8944,7 @@
         <v>1411</v>
       </c>
       <c r="E19">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="F19" t="s">
         <v>1613</v>
@@ -8979,7 +8979,7 @@
         <v>1412</v>
       </c>
       <c r="E20">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="F20" t="s">
         <v>1613</v>
@@ -9014,7 +9014,7 @@
         <v>1413</v>
       </c>
       <c r="E21">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="F21" t="s">
         <v>1613</v>
@@ -9049,7 +9049,7 @@
         <v>1413</v>
       </c>
       <c r="E22">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="F22" t="s">
         <v>1613</v>
@@ -9084,7 +9084,7 @@
         <v>1414</v>
       </c>
       <c r="E23">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="F23" t="s">
         <v>1613</v>
@@ -9119,7 +9119,7 @@
         <v>1415</v>
       </c>
       <c r="E24">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="F24" t="s">
         <v>1613</v>
@@ -9154,7 +9154,7 @@
         <v>1416</v>
       </c>
       <c r="E25">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="F25" t="s">
         <v>1613</v>
@@ -9189,7 +9189,7 @@
         <v>1417</v>
       </c>
       <c r="E26">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F26" t="s">
         <v>1613</v>
@@ -9224,7 +9224,7 @@
         <v>1418</v>
       </c>
       <c r="E27">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F27" t="s">
         <v>1613</v>
@@ -9262,7 +9262,7 @@
         <v>1419</v>
       </c>
       <c r="E28">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F28" t="s">
         <v>1613</v>
@@ -9297,7 +9297,7 @@
         <v>1420</v>
       </c>
       <c r="E29">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F29" t="s">
         <v>1613</v>
@@ -9332,7 +9332,7 @@
         <v>1421</v>
       </c>
       <c r="E30">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F30" t="s">
         <v>1613</v>
@@ -9367,7 +9367,7 @@
         <v>1422</v>
       </c>
       <c r="E31">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F31" t="s">
         <v>1613</v>
@@ -9402,7 +9402,7 @@
         <v>1423</v>
       </c>
       <c r="E32">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F32" t="s">
         <v>1613</v>
@@ -9437,7 +9437,7 @@
         <v>1424</v>
       </c>
       <c r="E33">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F33" t="s">
         <v>1613</v>
@@ -9472,7 +9472,7 @@
         <v>1425</v>
       </c>
       <c r="E34">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="F34" t="s">
         <v>1613</v>
@@ -9507,7 +9507,7 @@
         <v>1426</v>
       </c>
       <c r="E35">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F35" t="s">
         <v>1613</v>
@@ -9542,7 +9542,7 @@
         <v>1427</v>
       </c>
       <c r="E36">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F36" t="s">
         <v>1613</v>
@@ -9577,7 +9577,7 @@
         <v>1428</v>
       </c>
       <c r="E37">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F37" t="s">
         <v>1613</v>
@@ -9612,7 +9612,7 @@
         <v>1429</v>
       </c>
       <c r="E38">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F38" t="s">
         <v>1613</v>
@@ -9647,7 +9647,7 @@
         <v>1430</v>
       </c>
       <c r="E39">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F39" t="s">
         <v>1613</v>
@@ -9682,7 +9682,7 @@
         <v>1430</v>
       </c>
       <c r="E40">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F40" t="s">
         <v>1613</v>
@@ -9717,7 +9717,7 @@
         <v>1431</v>
       </c>
       <c r="E41">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F41" t="s">
         <v>1613</v>
@@ -9752,7 +9752,7 @@
         <v>1431</v>
       </c>
       <c r="E42">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F42" t="s">
         <v>1613</v>
@@ -9787,7 +9787,7 @@
         <v>1432</v>
       </c>
       <c r="E43">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F43" t="s">
         <v>1613</v>
@@ -9822,7 +9822,7 @@
         <v>1433</v>
       </c>
       <c r="E44">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F44" t="s">
         <v>1613</v>
@@ -9857,7 +9857,7 @@
         <v>1434</v>
       </c>
       <c r="E45">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F45" t="s">
         <v>1613</v>
@@ -9892,7 +9892,7 @@
         <v>1435</v>
       </c>
       <c r="E46">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F46" t="s">
         <v>1613</v>
@@ -9927,7 +9927,7 @@
         <v>1435</v>
       </c>
       <c r="E47">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F47" t="s">
         <v>1613</v>
@@ -9962,7 +9962,7 @@
         <v>1436</v>
       </c>
       <c r="E48">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F48" t="s">
         <v>1613</v>
@@ -9997,7 +9997,7 @@
         <v>1437</v>
       </c>
       <c r="E49">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F49" t="s">
         <v>1613</v>
@@ -10032,7 +10032,7 @@
         <v>1437</v>
       </c>
       <c r="E50">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F50" t="s">
         <v>1613</v>
@@ -10067,7 +10067,7 @@
         <v>1438</v>
       </c>
       <c r="E51">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F51" t="s">
         <v>1613</v>
@@ -10102,7 +10102,7 @@
         <v>1438</v>
       </c>
       <c r="E52">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F52" t="s">
         <v>1613</v>
@@ -10137,7 +10137,7 @@
         <v>1439</v>
       </c>
       <c r="E53">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F53" t="s">
         <v>1613</v>
@@ -10172,7 +10172,7 @@
         <v>1440</v>
       </c>
       <c r="E54">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F54" t="s">
         <v>1613</v>
@@ -10207,7 +10207,7 @@
         <v>1441</v>
       </c>
       <c r="E55">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F55" t="s">
         <v>1613</v>
@@ -10242,7 +10242,7 @@
         <v>1442</v>
       </c>
       <c r="E56">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F56" t="s">
         <v>1613</v>
@@ -10277,7 +10277,7 @@
         <v>1443</v>
       </c>
       <c r="E57">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F57" t="s">
         <v>1613</v>
@@ -10312,7 +10312,7 @@
         <v>1444</v>
       </c>
       <c r="E58">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F58" t="s">
         <v>1613</v>
@@ -10347,7 +10347,7 @@
         <v>1445</v>
       </c>
       <c r="E59">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F59" t="s">
         <v>1613</v>
@@ -10382,7 +10382,7 @@
         <v>1446</v>
       </c>
       <c r="E60">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F60" t="s">
         <v>1613</v>
@@ -10417,7 +10417,7 @@
         <v>1447</v>
       </c>
       <c r="E61">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F61" t="s">
         <v>1613</v>
@@ -10452,7 +10452,7 @@
         <v>1448</v>
       </c>
       <c r="E62">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F62" t="s">
         <v>1613</v>
@@ -10487,7 +10487,7 @@
         <v>1449</v>
       </c>
       <c r="E63">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F63" t="s">
         <v>1613</v>
@@ -10522,7 +10522,7 @@
         <v>1450</v>
       </c>
       <c r="E64">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F64" t="s">
         <v>1613</v>
@@ -10557,7 +10557,7 @@
         <v>1451</v>
       </c>
       <c r="E65">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F65" t="s">
         <v>1613</v>
@@ -10592,7 +10592,7 @@
         <v>1452</v>
       </c>
       <c r="E66">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F66" t="s">
         <v>1613</v>
@@ -10627,7 +10627,7 @@
         <v>1453</v>
       </c>
       <c r="E67">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F67" t="s">
         <v>1613</v>
@@ -10662,7 +10662,7 @@
         <v>1454</v>
       </c>
       <c r="E68">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F68" t="s">
         <v>1613</v>
@@ -10697,7 +10697,7 @@
         <v>1454</v>
       </c>
       <c r="E69">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F69" t="s">
         <v>1613</v>
@@ -10732,7 +10732,7 @@
         <v>1454</v>
       </c>
       <c r="E70">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F70" t="s">
         <v>1613</v>
@@ -10767,7 +10767,7 @@
         <v>1455</v>
       </c>
       <c r="E71">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F71" t="s">
         <v>1613</v>
@@ -10802,7 +10802,7 @@
         <v>1456</v>
       </c>
       <c r="E72">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F72" t="s">
         <v>1613</v>
@@ -10837,7 +10837,7 @@
         <v>1457</v>
       </c>
       <c r="E73">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F73" t="s">
         <v>1613</v>
@@ -10872,7 +10872,7 @@
         <v>1458</v>
       </c>
       <c r="E74">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F74" t="s">
         <v>1613</v>
@@ -10907,7 +10907,7 @@
         <v>1458</v>
       </c>
       <c r="E75">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F75" t="s">
         <v>1613</v>
@@ -10942,7 +10942,7 @@
         <v>1458</v>
       </c>
       <c r="E76">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F76" t="s">
         <v>1613</v>
@@ -10977,7 +10977,7 @@
         <v>1459</v>
       </c>
       <c r="E77">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F77" t="s">
         <v>1613</v>
@@ -11012,7 +11012,7 @@
         <v>1460</v>
       </c>
       <c r="E78">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F78" t="s">
         <v>1613</v>
@@ -11047,7 +11047,7 @@
         <v>1461</v>
       </c>
       <c r="E79">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F79" t="s">
         <v>1613</v>
@@ -11082,7 +11082,7 @@
         <v>1461</v>
       </c>
       <c r="E80">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F80" t="s">
         <v>1613</v>
@@ -11117,7 +11117,7 @@
         <v>1461</v>
       </c>
       <c r="E81">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F81" t="s">
         <v>1613</v>
@@ -11152,7 +11152,7 @@
         <v>1462</v>
       </c>
       <c r="E82">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F82" t="s">
         <v>1613</v>
@@ -11187,7 +11187,7 @@
         <v>1463</v>
       </c>
       <c r="E83">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F83" t="s">
         <v>1613</v>
@@ -11222,7 +11222,7 @@
         <v>1463</v>
       </c>
       <c r="E84">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F84" t="s">
         <v>1613</v>
@@ -11257,7 +11257,7 @@
         <v>1463</v>
       </c>
       <c r="E85">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F85" t="s">
         <v>1614</v>
@@ -11292,7 +11292,7 @@
         <v>1463</v>
       </c>
       <c r="E86">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F86" t="s">
         <v>1613</v>
@@ -11327,7 +11327,7 @@
         <v>1464</v>
       </c>
       <c r="E87">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F87" t="s">
         <v>1613</v>
@@ -11362,7 +11362,7 @@
         <v>1465</v>
       </c>
       <c r="E88">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F88" t="s">
         <v>1613</v>
@@ -11397,7 +11397,7 @@
         <v>1465</v>
       </c>
       <c r="E89">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F89" t="s">
         <v>1613</v>
@@ -11432,7 +11432,7 @@
         <v>1466</v>
       </c>
       <c r="E90">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F90" t="s">
         <v>1613</v>
@@ -11467,7 +11467,7 @@
         <v>1467</v>
       </c>
       <c r="E91">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F91" t="s">
         <v>1613</v>
@@ -11502,7 +11502,7 @@
         <v>1468</v>
       </c>
       <c r="E92">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F92" t="s">
         <v>1613</v>
@@ -11537,7 +11537,7 @@
         <v>1469</v>
       </c>
       <c r="E93">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F93" t="s">
         <v>1613</v>
@@ -11572,7 +11572,7 @@
         <v>1470</v>
       </c>
       <c r="E94">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F94" t="s">
         <v>1613</v>
@@ -11607,7 +11607,7 @@
         <v>1470</v>
       </c>
       <c r="E95">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F95" t="s">
         <v>1613</v>
@@ -11642,7 +11642,7 @@
         <v>1470</v>
       </c>
       <c r="E96">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F96" t="s">
         <v>1613</v>
@@ -11677,7 +11677,7 @@
         <v>1470</v>
       </c>
       <c r="E97">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F97" t="s">
         <v>1613</v>
@@ -11712,7 +11712,7 @@
         <v>1470</v>
       </c>
       <c r="E98">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F98" t="s">
         <v>1613</v>
@@ -11747,7 +11747,7 @@
         <v>1470</v>
       </c>
       <c r="E99">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F99" t="s">
         <v>1613</v>
@@ -11782,7 +11782,7 @@
         <v>1470</v>
       </c>
       <c r="E100">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F100" t="s">
         <v>1613</v>
@@ -11817,7 +11817,7 @@
         <v>1471</v>
       </c>
       <c r="E101">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F101" t="s">
         <v>1613</v>
@@ -11852,7 +11852,7 @@
         <v>1471</v>
       </c>
       <c r="E102">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F102" t="s">
         <v>1613</v>
@@ -11887,7 +11887,7 @@
         <v>1472</v>
       </c>
       <c r="E103">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F103" t="s">
         <v>1613</v>
@@ -11922,7 +11922,7 @@
         <v>1473</v>
       </c>
       <c r="E104">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F104" t="s">
         <v>1613</v>
@@ -11957,7 +11957,7 @@
         <v>1473</v>
       </c>
       <c r="E105">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F105" t="s">
         <v>1613</v>
@@ -11992,7 +11992,7 @@
         <v>1474</v>
       </c>
       <c r="E106">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F106" t="s">
         <v>1613</v>
@@ -12027,7 +12027,7 @@
         <v>1474</v>
       </c>
       <c r="E107">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F107" t="s">
         <v>1615</v>
@@ -12062,7 +12062,7 @@
         <v>1475</v>
       </c>
       <c r="E108">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F108" t="s">
         <v>1613</v>
@@ -12097,7 +12097,7 @@
         <v>1476</v>
       </c>
       <c r="E109">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F109" t="s">
         <v>1613</v>
@@ -12132,7 +12132,7 @@
         <v>1477</v>
       </c>
       <c r="E110">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F110" t="s">
         <v>1613</v>
@@ -12167,7 +12167,7 @@
         <v>1477</v>
       </c>
       <c r="E111">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F111" t="s">
         <v>1613</v>
@@ -12202,7 +12202,7 @@
         <v>1478</v>
       </c>
       <c r="E112">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F112" t="s">
         <v>1613</v>
@@ -12237,7 +12237,7 @@
         <v>1479</v>
       </c>
       <c r="E113">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F113" t="s">
         <v>1613</v>
@@ -12272,7 +12272,7 @@
         <v>1480</v>
       </c>
       <c r="E114">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F114" t="s">
         <v>1613</v>
@@ -12307,7 +12307,7 @@
         <v>1481</v>
       </c>
       <c r="E115">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F115" t="s">
         <v>1613</v>
@@ -12342,7 +12342,7 @@
         <v>1482</v>
       </c>
       <c r="E116">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F116" t="s">
         <v>1613</v>
@@ -12377,7 +12377,7 @@
         <v>1482</v>
       </c>
       <c r="E117">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F117" t="s">
         <v>1613</v>
@@ -12412,7 +12412,7 @@
         <v>1483</v>
       </c>
       <c r="E118">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F118" t="s">
         <v>1613</v>
@@ -12447,7 +12447,7 @@
         <v>1483</v>
       </c>
       <c r="E119">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F119" t="s">
         <v>1613</v>
@@ -12482,7 +12482,7 @@
         <v>1483</v>
       </c>
       <c r="E120">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F120" t="s">
         <v>1613</v>
@@ -12517,7 +12517,7 @@
         <v>1483</v>
       </c>
       <c r="E121">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F121" t="s">
         <v>1613</v>
@@ -12552,7 +12552,7 @@
         <v>1484</v>
       </c>
       <c r="E122">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F122" t="s">
         <v>1613</v>
@@ -12587,7 +12587,7 @@
         <v>1484</v>
       </c>
       <c r="E123">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F123" t="s">
         <v>1613</v>
@@ -12622,7 +12622,7 @@
         <v>1484</v>
       </c>
       <c r="E124">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F124" t="s">
         <v>1613</v>
@@ -12657,7 +12657,7 @@
         <v>1484</v>
       </c>
       <c r="E125">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F125" t="s">
         <v>1613</v>
@@ -12692,7 +12692,7 @@
         <v>1484</v>
       </c>
       <c r="E126">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F126" t="s">
         <v>1613</v>
@@ -12727,7 +12727,7 @@
         <v>1485</v>
       </c>
       <c r="E127">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F127" t="s">
         <v>1613</v>
@@ -12762,7 +12762,7 @@
         <v>1486</v>
       </c>
       <c r="E128">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F128" t="s">
         <v>1613</v>
@@ -12797,7 +12797,7 @@
         <v>1486</v>
       </c>
       <c r="E129">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F129" t="s">
         <v>1613</v>
@@ -12832,7 +12832,7 @@
         <v>1487</v>
       </c>
       <c r="E130">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F130" t="s">
         <v>1613</v>
@@ -12867,7 +12867,7 @@
         <v>1488</v>
       </c>
       <c r="E131">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F131" t="s">
         <v>1613</v>
@@ -12902,7 +12902,7 @@
         <v>1488</v>
       </c>
       <c r="E132">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F132" t="s">
         <v>1613</v>
@@ -12937,7 +12937,7 @@
         <v>1488</v>
       </c>
       <c r="E133">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F133" t="s">
         <v>1613</v>
@@ -12972,7 +12972,7 @@
         <v>1489</v>
       </c>
       <c r="E134">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F134" t="s">
         <v>1613</v>
@@ -13007,7 +13007,7 @@
         <v>1489</v>
       </c>
       <c r="E135">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F135" t="s">
         <v>1613</v>
@@ -13042,7 +13042,7 @@
         <v>1489</v>
       </c>
       <c r="E136">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F136" t="s">
         <v>1613</v>
@@ -13077,7 +13077,7 @@
         <v>1490</v>
       </c>
       <c r="E137">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F137" t="s">
         <v>1613</v>
@@ -13112,7 +13112,7 @@
         <v>1490</v>
       </c>
       <c r="E138">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F138" t="s">
         <v>1613</v>
@@ -13147,7 +13147,7 @@
         <v>1490</v>
       </c>
       <c r="E139">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F139" t="s">
         <v>1613</v>
@@ -13182,7 +13182,7 @@
         <v>1491</v>
       </c>
       <c r="E140">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F140" t="s">
         <v>1613</v>
@@ -13217,7 +13217,7 @@
         <v>1491</v>
       </c>
       <c r="E141">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F141" t="s">
         <v>1613</v>
@@ -13252,7 +13252,7 @@
         <v>1492</v>
       </c>
       <c r="E142">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F142" t="s">
         <v>1613</v>
@@ -13287,7 +13287,7 @@
         <v>1493</v>
       </c>
       <c r="E143">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F143" t="s">
         <v>1613</v>
@@ -13322,7 +13322,7 @@
         <v>1493</v>
       </c>
       <c r="E144">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F144" t="s">
         <v>1613</v>
@@ -13357,7 +13357,7 @@
         <v>1493</v>
       </c>
       <c r="E145">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F145" t="s">
         <v>1613</v>
@@ -13392,7 +13392,7 @@
         <v>1494</v>
       </c>
       <c r="E146">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F146" t="s">
         <v>1613</v>
@@ -13427,7 +13427,7 @@
         <v>1494</v>
       </c>
       <c r="E147">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F147" t="s">
         <v>1613</v>
@@ -13462,7 +13462,7 @@
         <v>1495</v>
       </c>
       <c r="E148">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F148" t="s">
         <v>1613</v>
@@ -13500,7 +13500,7 @@
         <v>1495</v>
       </c>
       <c r="E149">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F149" t="s">
         <v>1613</v>
@@ -13535,7 +13535,7 @@
         <v>1495</v>
       </c>
       <c r="E150">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F150" t="s">
         <v>1613</v>
@@ -13570,7 +13570,7 @@
         <v>1495</v>
       </c>
       <c r="E151">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F151" t="s">
         <v>1613</v>
@@ -13605,7 +13605,7 @@
         <v>1495</v>
       </c>
       <c r="E152">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F152" t="s">
         <v>1613</v>
@@ -13640,7 +13640,7 @@
         <v>1496</v>
       </c>
       <c r="E153">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F153" t="s">
         <v>1613</v>
@@ -13675,7 +13675,7 @@
         <v>1497</v>
       </c>
       <c r="E154">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F154" t="s">
         <v>1614</v>
@@ -13710,7 +13710,7 @@
         <v>1498</v>
       </c>
       <c r="E155">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F155" t="s">
         <v>1613</v>
@@ -13745,7 +13745,7 @@
         <v>1498</v>
       </c>
       <c r="E156">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F156" t="s">
         <v>1613</v>
@@ -13780,7 +13780,7 @@
         <v>1498</v>
       </c>
       <c r="E157">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F157" t="s">
         <v>1613</v>
@@ -13815,7 +13815,7 @@
         <v>1498</v>
       </c>
       <c r="E158">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F158" t="s">
         <v>1613</v>
@@ -13850,7 +13850,7 @@
         <v>1499</v>
       </c>
       <c r="E159">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F159" t="s">
         <v>1613</v>
@@ -13885,7 +13885,7 @@
         <v>1499</v>
       </c>
       <c r="E160">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F160" t="s">
         <v>1613</v>
@@ -13920,7 +13920,7 @@
         <v>1499</v>
       </c>
       <c r="E161">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F161" t="s">
         <v>1613</v>
@@ -13955,7 +13955,7 @@
         <v>1499</v>
       </c>
       <c r="E162">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F162" t="s">
         <v>1613</v>
@@ -13990,7 +13990,7 @@
         <v>1499</v>
       </c>
       <c r="E163">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F163" t="s">
         <v>1613</v>
@@ -14025,7 +14025,7 @@
         <v>1499</v>
       </c>
       <c r="E164">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F164" t="s">
         <v>1613</v>
@@ -14060,7 +14060,7 @@
         <v>1499</v>
       </c>
       <c r="E165">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F165" t="s">
         <v>1613</v>
@@ -14095,7 +14095,7 @@
         <v>1500</v>
       </c>
       <c r="E166">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F166" t="s">
         <v>1613</v>
@@ -14130,7 +14130,7 @@
         <v>1500</v>
       </c>
       <c r="E167">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F167" t="s">
         <v>1613</v>
@@ -14165,7 +14165,7 @@
         <v>1501</v>
       </c>
       <c r="E168">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F168" t="s">
         <v>1613</v>
@@ -14200,7 +14200,7 @@
         <v>1501</v>
       </c>
       <c r="E169">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F169" t="s">
         <v>1613</v>
@@ -14235,7 +14235,7 @@
         <v>1501</v>
       </c>
       <c r="E170">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F170" t="s">
         <v>1613</v>
@@ -14270,7 +14270,7 @@
         <v>1502</v>
       </c>
       <c r="E171">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F171" t="s">
         <v>1613</v>
@@ -14305,7 +14305,7 @@
         <v>1502</v>
       </c>
       <c r="E172">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F172" t="s">
         <v>1613</v>
@@ -14340,7 +14340,7 @@
         <v>1502</v>
       </c>
       <c r="E173">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F173" t="s">
         <v>1613</v>
@@ -14375,7 +14375,7 @@
         <v>1502</v>
       </c>
       <c r="E174">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F174" t="s">
         <v>1613</v>
@@ -14410,7 +14410,7 @@
         <v>1503</v>
       </c>
       <c r="E175">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F175" t="s">
         <v>1613</v>
@@ -14445,7 +14445,7 @@
         <v>1503</v>
       </c>
       <c r="E176">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F176" t="s">
         <v>1613</v>
@@ -14480,7 +14480,7 @@
         <v>1503</v>
       </c>
       <c r="E177">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F177" t="s">
         <v>1613</v>
@@ -14515,7 +14515,7 @@
         <v>1503</v>
       </c>
       <c r="E178">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F178" t="s">
         <v>1613</v>
@@ -14550,7 +14550,7 @@
         <v>1503</v>
       </c>
       <c r="E179">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F179" t="s">
         <v>1613</v>
@@ -14585,7 +14585,7 @@
         <v>1503</v>
       </c>
       <c r="E180">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F180" t="s">
         <v>1613</v>
@@ -14620,7 +14620,7 @@
         <v>1503</v>
       </c>
       <c r="E181">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F181" t="s">
         <v>1613</v>
@@ -14655,7 +14655,7 @@
         <v>1503</v>
       </c>
       <c r="E182">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F182" t="s">
         <v>1613</v>
@@ -14690,7 +14690,7 @@
         <v>1503</v>
       </c>
       <c r="E183">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F183" t="s">
         <v>1613</v>
@@ -14725,7 +14725,7 @@
         <v>1503</v>
       </c>
       <c r="E184">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F184" t="s">
         <v>1613</v>
@@ -14760,7 +14760,7 @@
         <v>1504</v>
       </c>
       <c r="E185">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F185" t="s">
         <v>1613</v>
@@ -14795,7 +14795,7 @@
         <v>1504</v>
       </c>
       <c r="E186">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F186" t="s">
         <v>1613</v>
@@ -14830,7 +14830,7 @@
         <v>1504</v>
       </c>
       <c r="E187">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F187" t="s">
         <v>1613</v>
@@ -14865,7 +14865,7 @@
         <v>1504</v>
       </c>
       <c r="E188">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F188" t="s">
         <v>1616</v>
@@ -14900,7 +14900,7 @@
         <v>1505</v>
       </c>
       <c r="E189">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F189" t="s">
         <v>1613</v>
@@ -14935,7 +14935,7 @@
         <v>1505</v>
       </c>
       <c r="E190">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F190" t="s">
         <v>1614</v>
@@ -14970,7 +14970,7 @@
         <v>1505</v>
       </c>
       <c r="E191">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F191" t="s">
         <v>1613</v>
@@ -15005,7 +15005,7 @@
         <v>1506</v>
       </c>
       <c r="E192">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F192" t="s">
         <v>1613</v>
@@ -15040,7 +15040,7 @@
         <v>1506</v>
       </c>
       <c r="E193">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F193" t="s">
         <v>1613</v>
@@ -15075,7 +15075,7 @@
         <v>1507</v>
       </c>
       <c r="E194">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F194" t="s">
         <v>1613</v>
@@ -15110,7 +15110,7 @@
         <v>1507</v>
       </c>
       <c r="E195">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F195" t="s">
         <v>1613</v>
@@ -15145,7 +15145,7 @@
         <v>1508</v>
       </c>
       <c r="E196">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F196" t="s">
         <v>1613</v>
@@ -15180,7 +15180,7 @@
         <v>1508</v>
       </c>
       <c r="E197">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F197" t="s">
         <v>1613</v>
@@ -15215,7 +15215,7 @@
         <v>1508</v>
       </c>
       <c r="E198">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F198" t="s">
         <v>1613</v>
@@ -15250,7 +15250,7 @@
         <v>1509</v>
       </c>
       <c r="E199">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F199" t="s">
         <v>1613</v>
@@ -15285,7 +15285,7 @@
         <v>1509</v>
       </c>
       <c r="E200">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F200" t="s">
         <v>1613</v>
@@ -15320,7 +15320,7 @@
         <v>1509</v>
       </c>
       <c r="E201">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F201" t="s">
         <v>1613</v>
@@ -15355,7 +15355,7 @@
         <v>1509</v>
       </c>
       <c r="E202">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F202" t="s">
         <v>1613</v>
@@ -15390,7 +15390,7 @@
         <v>1509</v>
       </c>
       <c r="E203">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F203" t="s">
         <v>1613</v>
@@ -15425,7 +15425,7 @@
         <v>1510</v>
       </c>
       <c r="E204">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F204" t="s">
         <v>1613</v>
@@ -15460,7 +15460,7 @@
         <v>1510</v>
       </c>
       <c r="E205">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F205" t="s">
         <v>1613</v>
@@ -15495,7 +15495,7 @@
         <v>1511</v>
       </c>
       <c r="E206">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F206" t="s">
         <v>1613</v>
@@ -15530,7 +15530,7 @@
         <v>1512</v>
       </c>
       <c r="E207">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F207" t="s">
         <v>1613</v>
@@ -15565,7 +15565,7 @@
         <v>1512</v>
       </c>
       <c r="E208">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F208" t="s">
         <v>1613</v>
@@ -15600,7 +15600,7 @@
         <v>1512</v>
       </c>
       <c r="E209">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F209" t="s">
         <v>1613</v>
@@ -15635,7 +15635,7 @@
         <v>1512</v>
       </c>
       <c r="E210">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F210" t="s">
         <v>1613</v>
@@ -15670,7 +15670,7 @@
         <v>1513</v>
       </c>
       <c r="E211">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F211" t="s">
         <v>1613</v>
@@ -15705,7 +15705,7 @@
         <v>1514</v>
       </c>
       <c r="E212">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F212" t="s">
         <v>1613</v>
@@ -15740,7 +15740,7 @@
         <v>1514</v>
       </c>
       <c r="E213">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F213" t="s">
         <v>1613</v>
@@ -15775,7 +15775,7 @@
         <v>1514</v>
       </c>
       <c r="E214">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F214" t="s">
         <v>1613</v>
@@ -15810,7 +15810,7 @@
         <v>1514</v>
       </c>
       <c r="E215">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F215" t="s">
         <v>1613</v>
@@ -15845,7 +15845,7 @@
         <v>1514</v>
       </c>
       <c r="E216">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F216" t="s">
         <v>1613</v>
@@ -15880,7 +15880,7 @@
         <v>1515</v>
       </c>
       <c r="E217">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F217" t="s">
         <v>1613</v>
@@ -15915,7 +15915,7 @@
         <v>1515</v>
       </c>
       <c r="E218">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F218" t="s">
         <v>1613</v>
@@ -15950,7 +15950,7 @@
         <v>1515</v>
       </c>
       <c r="E219">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F219" t="s">
         <v>1613</v>
@@ -15985,7 +15985,7 @@
         <v>1515</v>
       </c>
       <c r="E220">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F220" t="s">
         <v>1613</v>
@@ -16020,7 +16020,7 @@
         <v>1515</v>
       </c>
       <c r="E221">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F221" t="s">
         <v>1613</v>
@@ -16055,7 +16055,7 @@
         <v>1515</v>
       </c>
       <c r="E222">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F222" t="s">
         <v>1613</v>
@@ -16090,7 +16090,7 @@
         <v>1515</v>
       </c>
       <c r="E223">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F223" t="s">
         <v>1613</v>
@@ -16125,7 +16125,7 @@
         <v>1516</v>
       </c>
       <c r="E224">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F224" t="s">
         <v>1613</v>
@@ -16160,7 +16160,7 @@
         <v>1516</v>
       </c>
       <c r="E225">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F225" t="s">
         <v>1613</v>
@@ -16195,7 +16195,7 @@
         <v>1516</v>
       </c>
       <c r="E226">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F226" t="s">
         <v>1613</v>
@@ -16230,7 +16230,7 @@
         <v>1516</v>
       </c>
       <c r="E227">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F227" t="s">
         <v>1613</v>
@@ -16265,7 +16265,7 @@
         <v>1517</v>
       </c>
       <c r="E228">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F228" t="s">
         <v>1613</v>
@@ -16300,7 +16300,7 @@
         <v>1517</v>
       </c>
       <c r="E229">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F229" t="s">
         <v>1613</v>
@@ -16335,7 +16335,7 @@
         <v>1517</v>
       </c>
       <c r="E230">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F230" t="s">
         <v>1613</v>
@@ -16370,7 +16370,7 @@
         <v>1518</v>
       </c>
       <c r="E231">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F231" t="s">
         <v>1613</v>
@@ -16405,7 +16405,7 @@
         <v>1518</v>
       </c>
       <c r="E232">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F232" t="s">
         <v>1613</v>
@@ -16440,7 +16440,7 @@
         <v>1519</v>
       </c>
       <c r="E233">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F233" t="s">
         <v>1613</v>
@@ -16475,7 +16475,7 @@
         <v>1519</v>
       </c>
       <c r="E234">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F234" t="s">
         <v>1613</v>
@@ -16510,7 +16510,7 @@
         <v>1520</v>
       </c>
       <c r="E235">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F235" t="s">
         <v>1613</v>
@@ -16545,7 +16545,7 @@
         <v>1520</v>
       </c>
       <c r="E236">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F236" t="s">
         <v>1613</v>
@@ -16580,7 +16580,7 @@
         <v>1521</v>
       </c>
       <c r="E237">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F237" t="s">
         <v>1613</v>
@@ -16615,7 +16615,7 @@
         <v>1521</v>
       </c>
       <c r="E238">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F238" t="s">
         <v>1613</v>
@@ -16650,7 +16650,7 @@
         <v>1522</v>
       </c>
       <c r="E239">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F239" t="s">
         <v>1613</v>
@@ -16685,7 +16685,7 @@
         <v>1522</v>
       </c>
       <c r="E240">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F240" t="s">
         <v>1613</v>
@@ -16720,7 +16720,7 @@
         <v>1523</v>
       </c>
       <c r="E241">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F241" t="s">
         <v>1613</v>
@@ -16755,7 +16755,7 @@
         <v>1524</v>
       </c>
       <c r="E242">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F242" t="s">
         <v>1613</v>
@@ -16790,7 +16790,7 @@
         <v>1524</v>
       </c>
       <c r="E243">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F243" t="s">
         <v>1613</v>
@@ -16825,7 +16825,7 @@
         <v>1524</v>
       </c>
       <c r="E244">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F244" t="s">
         <v>1613</v>
@@ -16860,7 +16860,7 @@
         <v>1525</v>
       </c>
       <c r="E245">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F245" t="s">
         <v>1613</v>
@@ -16895,7 +16895,7 @@
         <v>1525</v>
       </c>
       <c r="E246">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F246" t="s">
         <v>1613</v>
@@ -16930,7 +16930,7 @@
         <v>1526</v>
       </c>
       <c r="E247">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F247" t="s">
         <v>1613</v>
@@ -16965,7 +16965,7 @@
         <v>1527</v>
       </c>
       <c r="E248">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F248" t="s">
         <v>1613</v>
@@ -17000,7 +17000,7 @@
         <v>1527</v>
       </c>
       <c r="E249">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F249" t="s">
         <v>1613</v>
@@ -17035,7 +17035,7 @@
         <v>1527</v>
       </c>
       <c r="E250">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F250" t="s">
         <v>1613</v>
@@ -17070,7 +17070,7 @@
         <v>1528</v>
       </c>
       <c r="E251">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F251" t="s">
         <v>1613</v>
@@ -17105,7 +17105,7 @@
         <v>1528</v>
       </c>
       <c r="E252">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F252" t="s">
         <v>1613</v>
@@ -17140,7 +17140,7 @@
         <v>1529</v>
       </c>
       <c r="E253">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F253" t="s">
         <v>1613</v>
@@ -17175,7 +17175,7 @@
         <v>1529</v>
       </c>
       <c r="E254">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F254" t="s">
         <v>1613</v>
@@ -17210,7 +17210,7 @@
         <v>1529</v>
       </c>
       <c r="E255">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F255" t="s">
         <v>1615</v>
@@ -17245,7 +17245,7 @@
         <v>1529</v>
       </c>
       <c r="E256">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F256" t="s">
         <v>1613</v>
@@ -17280,7 +17280,7 @@
         <v>1529</v>
       </c>
       <c r="E257">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F257" t="s">
         <v>1613</v>
@@ -17315,7 +17315,7 @@
         <v>1530</v>
       </c>
       <c r="E258">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F258" t="s">
         <v>1613</v>
@@ -17350,7 +17350,7 @@
         <v>1530</v>
       </c>
       <c r="E259">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F259" t="s">
         <v>1613</v>
@@ -17385,7 +17385,7 @@
         <v>1530</v>
       </c>
       <c r="E260">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F260" t="s">
         <v>1613</v>
@@ -17423,7 +17423,7 @@
         <v>1530</v>
       </c>
       <c r="E261">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F261" t="s">
         <v>1613</v>
@@ -17458,7 +17458,7 @@
         <v>1530</v>
       </c>
       <c r="E262">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F262" t="s">
         <v>1613</v>
@@ -17493,7 +17493,7 @@
         <v>1530</v>
       </c>
       <c r="E263">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F263" t="s">
         <v>1613</v>
@@ -17528,7 +17528,7 @@
         <v>1530</v>
       </c>
       <c r="E264">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F264" t="s">
         <v>1613</v>
@@ -17563,7 +17563,7 @@
         <v>1531</v>
       </c>
       <c r="E265">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F265" t="s">
         <v>1613</v>
@@ -17598,7 +17598,7 @@
         <v>1531</v>
       </c>
       <c r="E266">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F266" t="s">
         <v>1613</v>
@@ -17633,7 +17633,7 @@
         <v>1531</v>
       </c>
       <c r="E267">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F267" t="s">
         <v>1613</v>
@@ -17668,7 +17668,7 @@
         <v>1532</v>
       </c>
       <c r="E268">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F268" t="s">
         <v>1613</v>
@@ -17703,7 +17703,7 @@
         <v>1532</v>
       </c>
       <c r="E269">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F269" t="s">
         <v>1613</v>
@@ -17738,7 +17738,7 @@
         <v>1532</v>
       </c>
       <c r="E270">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F270" t="s">
         <v>1613</v>
@@ -17773,7 +17773,7 @@
         <v>1532</v>
       </c>
       <c r="E271">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F271" t="s">
         <v>1613</v>
@@ -17808,7 +17808,7 @@
         <v>1533</v>
       </c>
       <c r="E272">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F272" t="s">
         <v>1613</v>
@@ -17843,7 +17843,7 @@
         <v>1533</v>
       </c>
       <c r="E273">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F273" t="s">
         <v>1613</v>
@@ -17878,7 +17878,7 @@
         <v>1533</v>
       </c>
       <c r="E274">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F274" t="s">
         <v>1613</v>
@@ -17913,7 +17913,7 @@
         <v>1533</v>
       </c>
       <c r="E275">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F275" t="s">
         <v>1613</v>
@@ -17948,7 +17948,7 @@
         <v>1533</v>
       </c>
       <c r="E276">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F276" t="s">
         <v>1613</v>
@@ -17983,7 +17983,7 @@
         <v>1533</v>
       </c>
       <c r="E277">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F277" t="s">
         <v>1613</v>
@@ -18018,7 +18018,7 @@
         <v>1534</v>
       </c>
       <c r="E278">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F278" t="s">
         <v>1613</v>
@@ -18053,7 +18053,7 @@
         <v>1534</v>
       </c>
       <c r="E279">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F279" t="s">
         <v>1613</v>
@@ -18088,7 +18088,7 @@
         <v>1534</v>
       </c>
       <c r="E280">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F280" t="s">
         <v>1613</v>
@@ -18123,7 +18123,7 @@
         <v>1534</v>
       </c>
       <c r="E281">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F281" t="s">
         <v>1613</v>
@@ -18158,7 +18158,7 @@
         <v>1534</v>
       </c>
       <c r="E282">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F282" t="s">
         <v>1613</v>
@@ -18193,7 +18193,7 @@
         <v>1534</v>
       </c>
       <c r="E283">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F283" t="s">
         <v>1613</v>
@@ -18228,7 +18228,7 @@
         <v>1535</v>
       </c>
       <c r="E284">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F284" t="s">
         <v>1613</v>
@@ -18263,7 +18263,7 @@
         <v>1536</v>
       </c>
       <c r="E285">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F285" t="s">
         <v>1614</v>
@@ -18298,7 +18298,7 @@
         <v>1536</v>
       </c>
       <c r="E286">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F286" t="s">
         <v>1613</v>
@@ -18333,7 +18333,7 @@
         <v>1536</v>
       </c>
       <c r="E287">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F287" t="s">
         <v>1613</v>
@@ -18368,7 +18368,7 @@
         <v>1536</v>
       </c>
       <c r="E288">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F288" t="s">
         <v>1616</v>
@@ -18403,7 +18403,7 @@
         <v>1536</v>
       </c>
       <c r="E289">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F289" t="s">
         <v>1613</v>
@@ -18438,7 +18438,7 @@
         <v>1536</v>
       </c>
       <c r="E290">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F290" t="s">
         <v>1613</v>
@@ -18473,7 +18473,7 @@
         <v>1536</v>
       </c>
       <c r="E291">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F291" t="s">
         <v>1613</v>
@@ -18508,7 +18508,7 @@
         <v>1537</v>
       </c>
       <c r="E292">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F292" t="s">
         <v>1613</v>
@@ -18543,7 +18543,7 @@
         <v>1537</v>
       </c>
       <c r="E293">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F293" t="s">
         <v>1613</v>
@@ -18578,7 +18578,7 @@
         <v>1537</v>
       </c>
       <c r="E294">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F294" t="s">
         <v>1613</v>
@@ -18613,7 +18613,7 @@
         <v>1537</v>
       </c>
       <c r="E295">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F295" t="s">
         <v>1613</v>
@@ -18648,7 +18648,7 @@
         <v>1538</v>
       </c>
       <c r="E296">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F296" t="s">
         <v>1613</v>
@@ -18683,7 +18683,7 @@
         <v>1538</v>
       </c>
       <c r="E297">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F297" t="s">
         <v>1613</v>
@@ -18718,7 +18718,7 @@
         <v>1539</v>
       </c>
       <c r="E298">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F298" t="s">
         <v>1613</v>
@@ -18756,7 +18756,7 @@
         <v>1539</v>
       </c>
       <c r="E299">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F299" t="s">
         <v>1613</v>
@@ -18791,7 +18791,7 @@
         <v>1540</v>
       </c>
       <c r="E300">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F300" t="s">
         <v>1613</v>
@@ -18826,7 +18826,7 @@
         <v>1540</v>
       </c>
       <c r="E301">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F301" t="s">
         <v>1613</v>
@@ -18861,7 +18861,7 @@
         <v>1540</v>
       </c>
       <c r="E302">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F302" t="s">
         <v>1613</v>
@@ -18896,7 +18896,7 @@
         <v>1540</v>
       </c>
       <c r="E303">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F303" t="s">
         <v>1613</v>
@@ -18934,7 +18934,7 @@
         <v>1540</v>
       </c>
       <c r="E304">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F304" t="s">
         <v>1613</v>
@@ -18969,7 +18969,7 @@
         <v>1540</v>
       </c>
       <c r="E305">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F305" t="s">
         <v>1613</v>
@@ -19004,7 +19004,7 @@
         <v>1541</v>
       </c>
       <c r="E306">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F306" t="s">
         <v>1613</v>
@@ -19039,7 +19039,7 @@
         <v>1541</v>
       </c>
       <c r="E307">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F307" t="s">
         <v>1613</v>
@@ -19074,7 +19074,7 @@
         <v>1542</v>
       </c>
       <c r="E308">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F308" t="s">
         <v>1613</v>
@@ -19109,7 +19109,7 @@
         <v>1542</v>
       </c>
       <c r="E309">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F309" t="s">
         <v>1613</v>
@@ -19144,7 +19144,7 @@
         <v>1543</v>
       </c>
       <c r="E310">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F310" t="s">
         <v>1613</v>
@@ -19179,7 +19179,7 @@
         <v>1543</v>
       </c>
       <c r="E311">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F311" t="s">
         <v>1613</v>
@@ -19214,7 +19214,7 @@
         <v>1543</v>
       </c>
       <c r="E312">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F312" t="s">
         <v>1613</v>
@@ -19249,7 +19249,7 @@
         <v>1543</v>
       </c>
       <c r="E313">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F313" t="s">
         <v>1613</v>
@@ -19284,7 +19284,7 @@
         <v>1544</v>
       </c>
       <c r="E314">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F314" t="s">
         <v>1613</v>
@@ -19319,7 +19319,7 @@
         <v>1544</v>
       </c>
       <c r="E315">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F315" t="s">
         <v>1613</v>
@@ -19354,7 +19354,7 @@
         <v>1544</v>
       </c>
       <c r="E316">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F316" t="s">
         <v>1613</v>
@@ -19389,7 +19389,7 @@
         <v>1544</v>
       </c>
       <c r="E317">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F317" t="s">
         <v>1613</v>
@@ -19424,7 +19424,7 @@
         <v>1545</v>
       </c>
       <c r="E318">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F318" t="s">
         <v>1613</v>
@@ -19459,7 +19459,7 @@
         <v>1545</v>
       </c>
       <c r="E319">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F319" t="s">
         <v>1613</v>
@@ -19494,7 +19494,7 @@
         <v>1546</v>
       </c>
       <c r="E320">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F320" t="s">
         <v>1613</v>
@@ -19529,7 +19529,7 @@
         <v>1546</v>
       </c>
       <c r="E321">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F321" t="s">
         <v>1613</v>
@@ -19564,7 +19564,7 @@
         <v>1546</v>
       </c>
       <c r="E322">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F322" t="s">
         <v>1613</v>
@@ -19599,7 +19599,7 @@
         <v>1546</v>
       </c>
       <c r="E323">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F323" t="s">
         <v>1613</v>
@@ -19634,7 +19634,7 @@
         <v>1546</v>
       </c>
       <c r="E324">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F324" t="s">
         <v>1613</v>
@@ -19669,7 +19669,7 @@
         <v>1547</v>
       </c>
       <c r="E325">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F325" t="s">
         <v>1613</v>
@@ -19704,7 +19704,7 @@
         <v>1547</v>
       </c>
       <c r="E326">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F326" t="s">
         <v>1613</v>
@@ -19739,7 +19739,7 @@
         <v>1547</v>
       </c>
       <c r="E327">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F327" t="s">
         <v>1613</v>
@@ -19774,7 +19774,7 @@
         <v>1548</v>
       </c>
       <c r="E328">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F328" t="s">
         <v>1613</v>
@@ -19809,7 +19809,7 @@
         <v>1548</v>
       </c>
       <c r="E329">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F329" t="s">
         <v>1613</v>
@@ -19844,7 +19844,7 @@
         <v>1549</v>
       </c>
       <c r="E330">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F330" t="s">
         <v>1613</v>
@@ -19879,7 +19879,7 @@
         <v>1549</v>
       </c>
       <c r="E331">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F331" t="s">
         <v>1613</v>
@@ -19914,7 +19914,7 @@
         <v>1549</v>
       </c>
       <c r="E332">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F332" t="s">
         <v>1613</v>
@@ -19949,7 +19949,7 @@
         <v>1549</v>
       </c>
       <c r="E333">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F333" t="s">
         <v>1613</v>
@@ -19984,7 +19984,7 @@
         <v>1549</v>
       </c>
       <c r="E334">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F334" t="s">
         <v>1613</v>
@@ -20019,7 +20019,7 @@
         <v>1549</v>
       </c>
       <c r="E335">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F335" t="s">
         <v>1613</v>
@@ -20054,7 +20054,7 @@
         <v>1549</v>
       </c>
       <c r="E336">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F336" t="s">
         <v>1613</v>
@@ -20089,7 +20089,7 @@
         <v>1549</v>
       </c>
       <c r="E337">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F337" t="s">
         <v>1613</v>
@@ -20124,7 +20124,7 @@
         <v>1550</v>
       </c>
       <c r="E338">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F338" t="s">
         <v>1613</v>
@@ -20159,7 +20159,7 @@
         <v>1550</v>
       </c>
       <c r="E339">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F339" t="s">
         <v>1613</v>
@@ -20194,7 +20194,7 @@
         <v>1550</v>
       </c>
       <c r="E340">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F340" t="s">
         <v>1613</v>
@@ -20229,7 +20229,7 @@
         <v>1551</v>
       </c>
       <c r="E341">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F341" t="s">
         <v>1613</v>
@@ -20264,7 +20264,7 @@
         <v>1551</v>
       </c>
       <c r="E342">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F342" t="s">
         <v>1613</v>
@@ -20299,7 +20299,7 @@
         <v>1552</v>
       </c>
       <c r="E343">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F343" t="s">
         <v>1613</v>
@@ -20334,7 +20334,7 @@
         <v>1553</v>
       </c>
       <c r="E344">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F344" t="s">
         <v>1615</v>
@@ -20369,7 +20369,7 @@
         <v>1553</v>
       </c>
       <c r="E345">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F345" t="s">
         <v>1613</v>
@@ -20404,7 +20404,7 @@
         <v>1553</v>
       </c>
       <c r="E346">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F346" t="s">
         <v>1613</v>
@@ -20439,7 +20439,7 @@
         <v>1553</v>
       </c>
       <c r="E347">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F347" t="s">
         <v>1613</v>
@@ -20474,7 +20474,7 @@
         <v>1553</v>
       </c>
       <c r="E348">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F348" t="s">
         <v>1613</v>
@@ -20509,7 +20509,7 @@
         <v>1553</v>
       </c>
       <c r="E349">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F349" t="s">
         <v>1613</v>
@@ -20544,7 +20544,7 @@
         <v>1554</v>
       </c>
       <c r="E350">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F350" t="s">
         <v>1613</v>
@@ -20579,7 +20579,7 @@
         <v>1554</v>
       </c>
       <c r="E351">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F351" t="s">
         <v>1613</v>
@@ -20614,7 +20614,7 @@
         <v>1555</v>
       </c>
       <c r="E352">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F352" t="s">
         <v>1613</v>
@@ -20649,7 +20649,7 @@
         <v>1555</v>
       </c>
       <c r="E353">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F353" t="s">
         <v>1613</v>
@@ -20684,7 +20684,7 @@
         <v>1555</v>
       </c>
       <c r="E354">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F354" t="s">
         <v>1613</v>
@@ -20719,7 +20719,7 @@
         <v>1556</v>
       </c>
       <c r="E355">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F355" t="s">
         <v>1613</v>
@@ -20754,7 +20754,7 @@
         <v>1557</v>
       </c>
       <c r="E356">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F356" t="s">
         <v>1613</v>
@@ -20789,7 +20789,7 @@
         <v>1558</v>
       </c>
       <c r="E357">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F357" t="s">
         <v>1613</v>
@@ -20824,7 +20824,7 @@
         <v>1558</v>
       </c>
       <c r="E358">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F358" t="s">
         <v>1613</v>
@@ -20859,7 +20859,7 @@
         <v>1559</v>
       </c>
       <c r="E359">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F359" t="s">
         <v>1613</v>
@@ -20894,7 +20894,7 @@
         <v>1559</v>
       </c>
       <c r="E360">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F360" t="s">
         <v>1613</v>
@@ -20929,7 +20929,7 @@
         <v>1559</v>
       </c>
       <c r="E361">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F361" t="s">
         <v>1613</v>
@@ -20964,7 +20964,7 @@
         <v>1560</v>
       </c>
       <c r="E362">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F362" t="s">
         <v>1613</v>
@@ -20999,7 +20999,7 @@
         <v>1560</v>
       </c>
       <c r="E363">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F363" t="s">
         <v>1613</v>
@@ -21034,7 +21034,7 @@
         <v>1560</v>
       </c>
       <c r="E364">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F364" t="s">
         <v>1613</v>
@@ -21069,7 +21069,7 @@
         <v>1560</v>
       </c>
       <c r="E365">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F365" t="s">
         <v>1613</v>
@@ -21104,7 +21104,7 @@
         <v>1560</v>
       </c>
       <c r="E366">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F366" t="s">
         <v>1613</v>
@@ -21139,7 +21139,7 @@
         <v>1560</v>
       </c>
       <c r="E367">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F367" t="s">
         <v>1613</v>
@@ -21174,7 +21174,7 @@
         <v>1560</v>
       </c>
       <c r="E368">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F368" t="s">
         <v>1613</v>
@@ -21209,7 +21209,7 @@
         <v>1560</v>
       </c>
       <c r="E369">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F369" t="s">
         <v>1613</v>
@@ -21244,7 +21244,7 @@
         <v>1560</v>
       </c>
       <c r="E370">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F370" t="s">
         <v>1613</v>
@@ -21279,7 +21279,7 @@
         <v>1561</v>
       </c>
       <c r="E371">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F371" t="s">
         <v>1613</v>
@@ -21314,7 +21314,7 @@
         <v>1561</v>
       </c>
       <c r="E372">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F372" t="s">
         <v>1613</v>
@@ -21349,7 +21349,7 @@
         <v>1561</v>
       </c>
       <c r="E373">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F373" t="s">
         <v>1613</v>
@@ -21384,7 +21384,7 @@
         <v>1561</v>
       </c>
       <c r="E374">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F374" t="s">
         <v>1613</v>
@@ -21419,7 +21419,7 @@
         <v>1562</v>
       </c>
       <c r="E375">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F375" t="s">
         <v>1616</v>
@@ -21454,7 +21454,7 @@
         <v>1562</v>
       </c>
       <c r="E376">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F376" t="s">
         <v>1613</v>
@@ -21489,7 +21489,7 @@
         <v>1563</v>
       </c>
       <c r="E377">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F377" t="s">
         <v>1613</v>
@@ -21524,7 +21524,7 @@
         <v>1563</v>
       </c>
       <c r="E378">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F378" t="s">
         <v>1613</v>
@@ -21559,7 +21559,7 @@
         <v>1563</v>
       </c>
       <c r="E379">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F379" t="s">
         <v>1613</v>
@@ -21594,7 +21594,7 @@
         <v>1563</v>
       </c>
       <c r="E380">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F380" t="s">
         <v>1613</v>
@@ -21629,7 +21629,7 @@
         <v>1563</v>
       </c>
       <c r="E381">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F381" t="s">
         <v>1617</v>
@@ -21667,7 +21667,7 @@
         <v>1563</v>
       </c>
       <c r="E382">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F382" t="s">
         <v>1613</v>
@@ -21702,7 +21702,7 @@
         <v>1563</v>
       </c>
       <c r="E383">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F383" t="s">
         <v>1613</v>
@@ -21737,7 +21737,7 @@
         <v>1564</v>
       </c>
       <c r="E384">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F384" t="s">
         <v>1613</v>
@@ -21772,7 +21772,7 @@
         <v>1564</v>
       </c>
       <c r="E385">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F385" t="s">
         <v>1613</v>
@@ -21807,7 +21807,7 @@
         <v>1564</v>
       </c>
       <c r="E386">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F386" t="s">
         <v>1613</v>
@@ -21842,7 +21842,7 @@
         <v>1564</v>
       </c>
       <c r="E387">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F387" t="s">
         <v>1613</v>
@@ -21880,7 +21880,7 @@
         <v>1564</v>
       </c>
       <c r="E388">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F388" t="s">
         <v>1613</v>
@@ -21915,7 +21915,7 @@
         <v>1564</v>
       </c>
       <c r="E389">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F389" t="s">
         <v>1613</v>
@@ -21950,7 +21950,7 @@
         <v>1564</v>
       </c>
       <c r="E390">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F390" t="s">
         <v>1613</v>
@@ -21985,7 +21985,7 @@
         <v>1564</v>
       </c>
       <c r="E391">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F391" t="s">
         <v>1613</v>
@@ -22020,7 +22020,7 @@
         <v>1564</v>
       </c>
       <c r="E392">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F392" t="s">
         <v>1613</v>
@@ -22055,7 +22055,7 @@
         <v>1565</v>
       </c>
       <c r="E393">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F393" t="s">
         <v>1614</v>
@@ -22090,7 +22090,7 @@
         <v>1566</v>
       </c>
       <c r="E394">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F394" t="s">
         <v>1617</v>
@@ -22125,7 +22125,7 @@
         <v>1567</v>
       </c>
       <c r="E395">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F395" t="s">
         <v>1613</v>
@@ -22160,7 +22160,7 @@
         <v>1568</v>
       </c>
       <c r="E396">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F396" t="s">
         <v>1613</v>
@@ -22195,7 +22195,7 @@
         <v>1568</v>
       </c>
       <c r="E397">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F397" t="s">
         <v>1613</v>
@@ -22230,7 +22230,7 @@
         <v>1569</v>
       </c>
       <c r="E398">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F398" t="s">
         <v>1613</v>
@@ -22265,7 +22265,7 @@
         <v>1570</v>
       </c>
       <c r="E399">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F399" t="s">
         <v>1616</v>
@@ -22300,7 +22300,7 @@
         <v>1570</v>
       </c>
       <c r="E400">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F400" t="s">
         <v>1613</v>
@@ -22335,7 +22335,7 @@
         <v>1570</v>
       </c>
       <c r="E401">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F401" t="s">
         <v>1613</v>
@@ -22370,7 +22370,7 @@
         <v>1570</v>
       </c>
       <c r="E402">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F402" t="s">
         <v>1613</v>
@@ -22405,7 +22405,7 @@
         <v>1570</v>
       </c>
       <c r="E403">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F403" t="s">
         <v>1613</v>
@@ -22440,7 +22440,7 @@
         <v>1570</v>
       </c>
       <c r="E404">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F404" t="s">
         <v>1613</v>
@@ -22475,7 +22475,7 @@
         <v>1571</v>
       </c>
       <c r="E405">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F405" t="s">
         <v>1613</v>
@@ -22510,7 +22510,7 @@
         <v>1571</v>
       </c>
       <c r="E406">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F406" t="s">
         <v>1613</v>
@@ -22545,7 +22545,7 @@
         <v>1571</v>
       </c>
       <c r="E407">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F407" t="s">
         <v>1613</v>
@@ -22580,7 +22580,7 @@
         <v>1572</v>
       </c>
       <c r="E408">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F408" t="s">
         <v>1613</v>
@@ -22615,7 +22615,7 @@
         <v>1572</v>
       </c>
       <c r="E409">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F409" t="s">
         <v>1613</v>
@@ -22650,7 +22650,7 @@
         <v>1572</v>
       </c>
       <c r="E410">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F410" t="s">
         <v>1613</v>
@@ -22688,7 +22688,7 @@
         <v>1572</v>
       </c>
       <c r="E411">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F411" t="s">
         <v>1613</v>
@@ -22723,7 +22723,7 @@
         <v>1573</v>
       </c>
       <c r="E412">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F412" t="s">
         <v>1613</v>
@@ -22758,7 +22758,7 @@
         <v>1573</v>
       </c>
       <c r="E413">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F413" t="s">
         <v>1613</v>
@@ -22793,7 +22793,7 @@
         <v>1573</v>
       </c>
       <c r="E414">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F414" t="s">
         <v>1613</v>
@@ -22828,7 +22828,7 @@
         <v>1573</v>
       </c>
       <c r="E415">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F415" t="s">
         <v>1613</v>
@@ -22863,7 +22863,7 @@
         <v>1573</v>
       </c>
       <c r="E416">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F416" t="s">
         <v>1613</v>
@@ -22898,7 +22898,7 @@
         <v>1574</v>
       </c>
       <c r="E417">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F417" t="s">
         <v>1613</v>
@@ -22933,7 +22933,7 @@
         <v>1574</v>
       </c>
       <c r="E418">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F418" t="s">
         <v>1613</v>
@@ -22968,7 +22968,7 @@
         <v>1575</v>
       </c>
       <c r="E419">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F419" t="s">
         <v>1613</v>
@@ -23003,7 +23003,7 @@
         <v>1575</v>
       </c>
       <c r="E420">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F420" t="s">
         <v>1613</v>
@@ -23038,7 +23038,7 @@
         <v>1575</v>
       </c>
       <c r="E421">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F421" t="s">
         <v>1613</v>
@@ -23073,7 +23073,7 @@
         <v>1575</v>
       </c>
       <c r="E422">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F422" t="s">
         <v>1613</v>
@@ -23108,7 +23108,7 @@
         <v>1575</v>
       </c>
       <c r="E423">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F423" t="s">
         <v>1613</v>
@@ -23143,7 +23143,7 @@
         <v>1575</v>
       </c>
       <c r="E424">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F424" t="s">
         <v>1613</v>
@@ -23178,7 +23178,7 @@
         <v>1575</v>
       </c>
       <c r="E425">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F425" t="s">
         <v>1613</v>
@@ -23213,7 +23213,7 @@
         <v>1575</v>
       </c>
       <c r="E426">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F426" t="s">
         <v>1613</v>
@@ -23248,7 +23248,7 @@
         <v>1575</v>
       </c>
       <c r="E427">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F427" t="s">
         <v>1613</v>
@@ -23283,7 +23283,7 @@
         <v>1575</v>
       </c>
       <c r="E428">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F428" t="s">
         <v>1613</v>
@@ -23318,7 +23318,7 @@
         <v>1576</v>
       </c>
       <c r="E429">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F429" t="s">
         <v>1613</v>
@@ -23353,7 +23353,7 @@
         <v>1576</v>
       </c>
       <c r="E430">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F430" t="s">
         <v>1613</v>
@@ -23388,7 +23388,7 @@
         <v>1576</v>
       </c>
       <c r="E431">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F431" t="s">
         <v>1614</v>
@@ -23423,7 +23423,7 @@
         <v>1577</v>
       </c>
       <c r="E432">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F432" t="s">
         <v>1613</v>
@@ -23458,7 +23458,7 @@
         <v>1577</v>
       </c>
       <c r="E433">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F433" t="s">
         <v>1613</v>
@@ -23493,7 +23493,7 @@
         <v>1577</v>
       </c>
       <c r="E434">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F434" t="s">
         <v>1613</v>
@@ -23528,7 +23528,7 @@
         <v>1577</v>
       </c>
       <c r="E435">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F435" t="s">
         <v>1613</v>
@@ -23563,7 +23563,7 @@
         <v>1577</v>
       </c>
       <c r="E436">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F436" t="s">
         <v>1613</v>
@@ -23598,7 +23598,7 @@
         <v>1577</v>
       </c>
       <c r="E437">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F437" t="s">
         <v>1613</v>
@@ -23633,7 +23633,7 @@
         <v>1577</v>
       </c>
       <c r="E438">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F438" t="s">
         <v>1616</v>
@@ -23668,7 +23668,7 @@
         <v>1578</v>
       </c>
       <c r="E439">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F439" t="s">
         <v>1613</v>
@@ -23703,7 +23703,7 @@
         <v>1578</v>
       </c>
       <c r="E440">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F440" t="s">
         <v>1613</v>
@@ -23738,7 +23738,7 @@
         <v>1578</v>
       </c>
       <c r="E441">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F441" t="s">
         <v>1613</v>
@@ -23773,7 +23773,7 @@
         <v>1578</v>
       </c>
       <c r="E442">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F442" t="s">
         <v>1613</v>
@@ -23808,7 +23808,7 @@
         <v>1579</v>
       </c>
       <c r="E443">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F443" t="s">
         <v>1613</v>
@@ -23843,7 +23843,7 @@
         <v>1579</v>
       </c>
       <c r="E444">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F444" t="s">
         <v>1616</v>
@@ -23878,7 +23878,7 @@
         <v>1579</v>
       </c>
       <c r="E445">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F445" t="s">
         <v>1613</v>
@@ -23913,7 +23913,7 @@
         <v>1579</v>
       </c>
       <c r="E446">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F446" t="s">
         <v>1613</v>
@@ -23948,7 +23948,7 @@
         <v>1579</v>
       </c>
       <c r="E447">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F447" t="s">
         <v>1613</v>
@@ -23983,7 +23983,7 @@
         <v>1579</v>
       </c>
       <c r="E448">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F448" t="s">
         <v>1613</v>
@@ -24018,7 +24018,7 @@
         <v>1579</v>
       </c>
       <c r="E449">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F449" t="s">
         <v>1617</v>
@@ -24053,7 +24053,7 @@
         <v>1579</v>
       </c>
       <c r="E450">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F450" t="s">
         <v>1613</v>
@@ -24088,7 +24088,7 @@
         <v>1579</v>
       </c>
       <c r="E451">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F451" t="s">
         <v>1613</v>
@@ -24123,7 +24123,7 @@
         <v>1580</v>
       </c>
       <c r="E452">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F452" t="s">
         <v>1613</v>
@@ -24158,7 +24158,7 @@
         <v>1580</v>
       </c>
       <c r="E453">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F453" t="s">
         <v>1613</v>
@@ -24193,7 +24193,7 @@
         <v>1580</v>
       </c>
       <c r="E454">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F454" t="s">
         <v>1613</v>
@@ -24228,7 +24228,7 @@
         <v>1580</v>
       </c>
       <c r="E455">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F455" t="s">
         <v>1613</v>
@@ -24263,7 +24263,7 @@
         <v>1580</v>
       </c>
       <c r="E456">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F456" t="s">
         <v>1613</v>
@@ -24298,7 +24298,7 @@
         <v>1580</v>
       </c>
       <c r="E457">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F457" t="s">
         <v>1615</v>
@@ -24333,7 +24333,7 @@
         <v>1580</v>
       </c>
       <c r="E458">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F458" t="s">
         <v>1613</v>
@@ -24368,7 +24368,7 @@
         <v>1580</v>
       </c>
       <c r="E459">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F459" t="s">
         <v>1613</v>
@@ -24403,7 +24403,7 @@
         <v>1581</v>
       </c>
       <c r="E460">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F460" t="s">
         <v>1613</v>
@@ -24438,7 +24438,7 @@
         <v>1581</v>
       </c>
       <c r="E461">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F461" t="s">
         <v>1613</v>
@@ -24473,7 +24473,7 @@
         <v>1581</v>
       </c>
       <c r="E462">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F462" t="s">
         <v>1613</v>
@@ -24508,7 +24508,7 @@
         <v>1581</v>
       </c>
       <c r="E463">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F463" t="s">
         <v>1613</v>
@@ -24543,7 +24543,7 @@
         <v>1581</v>
       </c>
       <c r="E464">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F464" t="s">
         <v>1613</v>
@@ -24578,7 +24578,7 @@
         <v>1582</v>
       </c>
       <c r="E465">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F465" t="s">
         <v>1613</v>
@@ -24613,7 +24613,7 @@
         <v>1582</v>
       </c>
       <c r="E466">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F466" t="s">
         <v>1613</v>
@@ -24648,7 +24648,7 @@
         <v>1582</v>
       </c>
       <c r="E467">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F467" t="s">
         <v>1613</v>
@@ -24683,7 +24683,7 @@
         <v>1582</v>
       </c>
       <c r="E468">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F468" t="s">
         <v>1613</v>
@@ -24718,7 +24718,7 @@
         <v>1582</v>
       </c>
       <c r="E469">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F469" t="s">
         <v>1613</v>
@@ -24756,7 +24756,7 @@
         <v>1583</v>
       </c>
       <c r="E470">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F470" t="s">
         <v>1613</v>
@@ -24791,7 +24791,7 @@
         <v>1583</v>
       </c>
       <c r="E471">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F471" t="s">
         <v>1613</v>
@@ -24826,7 +24826,7 @@
         <v>1583</v>
       </c>
       <c r="E472">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F472" t="s">
         <v>1613</v>
@@ -24861,7 +24861,7 @@
         <v>1583</v>
       </c>
       <c r="E473">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F473" t="s">
         <v>1613</v>
@@ -24896,7 +24896,7 @@
         <v>1583</v>
       </c>
       <c r="E474">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F474" t="s">
         <v>1613</v>
@@ -24931,7 +24931,7 @@
         <v>1583</v>
       </c>
       <c r="E475">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F475" t="s">
         <v>1613</v>
@@ -24966,7 +24966,7 @@
         <v>1584</v>
       </c>
       <c r="E476">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F476" t="s">
         <v>1613</v>
@@ -25001,7 +25001,7 @@
         <v>1584</v>
       </c>
       <c r="E477">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F477" t="s">
         <v>1613</v>
@@ -25036,7 +25036,7 @@
         <v>1584</v>
       </c>
       <c r="E478">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F478" t="s">
         <v>1613</v>
@@ -25071,7 +25071,7 @@
         <v>1585</v>
       </c>
       <c r="E479">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F479" t="s">
         <v>1613</v>
@@ -25106,7 +25106,7 @@
         <v>1586</v>
       </c>
       <c r="E480">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F480" t="s">
         <v>1613</v>
@@ -25141,7 +25141,7 @@
         <v>1586</v>
       </c>
       <c r="E481">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F481" t="s">
         <v>1613</v>
@@ -25176,7 +25176,7 @@
         <v>1586</v>
       </c>
       <c r="E482">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F482" t="s">
         <v>1615</v>
@@ -25214,7 +25214,7 @@
         <v>1586</v>
       </c>
       <c r="E483">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F483" t="s">
         <v>1613</v>
@@ -25249,7 +25249,7 @@
         <v>1586</v>
       </c>
       <c r="E484">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F484" t="s">
         <v>1613</v>
@@ -25284,7 +25284,7 @@
         <v>1587</v>
       </c>
       <c r="E485">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F485" t="s">
         <v>1613</v>
@@ -25319,7 +25319,7 @@
         <v>1587</v>
       </c>
       <c r="E486">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F486" t="s">
         <v>1613</v>
@@ -25354,7 +25354,7 @@
         <v>1587</v>
       </c>
       <c r="E487">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F487" t="s">
         <v>1613</v>
@@ -25389,7 +25389,7 @@
         <v>1587</v>
       </c>
       <c r="E488">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F488" t="s">
         <v>1613</v>
@@ -25424,7 +25424,7 @@
         <v>1587</v>
       </c>
       <c r="E489">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F489" t="s">
         <v>1613</v>
@@ -25459,7 +25459,7 @@
         <v>1588</v>
       </c>
       <c r="E490">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F490" t="s">
         <v>1613</v>
@@ -25494,7 +25494,7 @@
         <v>1588</v>
       </c>
       <c r="E491">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F491" t="s">
         <v>1613</v>
@@ -25529,7 +25529,7 @@
         <v>1588</v>
       </c>
       <c r="E492">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F492" t="s">
         <v>1613</v>
@@ -25564,7 +25564,7 @@
         <v>1588</v>
       </c>
       <c r="E493">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F493" t="s">
         <v>1613</v>
@@ -25599,7 +25599,7 @@
         <v>1588</v>
       </c>
       <c r="E494">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F494" t="s">
         <v>1613</v>
@@ -25634,7 +25634,7 @@
         <v>1588</v>
       </c>
       <c r="E495">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F495" t="s">
         <v>1613</v>
@@ -25669,7 +25669,7 @@
         <v>1588</v>
       </c>
       <c r="E496">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F496" t="s">
         <v>1613</v>
@@ -25704,7 +25704,7 @@
         <v>1588</v>
       </c>
       <c r="E497">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F497" t="s">
         <v>1613</v>
@@ -25739,7 +25739,7 @@
         <v>1589</v>
       </c>
       <c r="E498">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F498" t="s">
         <v>1613</v>
@@ -25774,7 +25774,7 @@
         <v>1589</v>
       </c>
       <c r="E499">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F499" t="s">
         <v>1613</v>
@@ -25809,7 +25809,7 @@
         <v>1590</v>
       </c>
       <c r="E500">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F500" t="s">
         <v>1613</v>
@@ -25844,7 +25844,7 @@
         <v>1590</v>
       </c>
       <c r="E501">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F501" t="s">
         <v>1613</v>
@@ -25879,7 +25879,7 @@
         <v>1590</v>
       </c>
       <c r="E502">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F502" t="s">
         <v>1613</v>
@@ -25914,7 +25914,7 @@
         <v>1590</v>
       </c>
       <c r="E503">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F503" t="s">
         <v>1617</v>
@@ -25952,7 +25952,7 @@
         <v>1590</v>
       </c>
       <c r="E504">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F504" t="s">
         <v>1613</v>
@@ -25987,7 +25987,7 @@
         <v>1590</v>
       </c>
       <c r="E505">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F505" t="s">
         <v>1617</v>
@@ -26022,7 +26022,7 @@
         <v>1591</v>
       </c>
       <c r="E506">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F506" t="s">
         <v>1613</v>
@@ -26057,7 +26057,7 @@
         <v>1592</v>
       </c>
       <c r="E507">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F507" t="s">
         <v>1613</v>
@@ -26092,7 +26092,7 @@
         <v>1592</v>
       </c>
       <c r="E508">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F508" t="s">
         <v>1613</v>
@@ -26127,7 +26127,7 @@
         <v>1592</v>
       </c>
       <c r="E509">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F509" t="s">
         <v>1613</v>
@@ -26162,7 +26162,7 @@
         <v>1592</v>
       </c>
       <c r="E510">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F510" t="s">
         <v>1613</v>
@@ -26197,7 +26197,7 @@
         <v>1593</v>
       </c>
       <c r="E511">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F511" t="s">
         <v>1613</v>
@@ -26232,7 +26232,7 @@
         <v>1593</v>
       </c>
       <c r="E512">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F512" t="s">
         <v>1617</v>
@@ -26267,7 +26267,7 @@
         <v>1593</v>
       </c>
       <c r="E513">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F513" t="s">
         <v>1613</v>
@@ -26302,7 +26302,7 @@
         <v>1593</v>
       </c>
       <c r="E514">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F514" t="s">
         <v>1613</v>
@@ -26337,7 +26337,7 @@
         <v>1593</v>
       </c>
       <c r="E515">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F515" t="s">
         <v>1613</v>
@@ -26372,7 +26372,7 @@
         <v>1594</v>
       </c>
       <c r="E516">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F516" t="s">
         <v>1613</v>
@@ -26407,7 +26407,7 @@
         <v>1594</v>
       </c>
       <c r="E517">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F517" t="s">
         <v>1615</v>
@@ -26442,7 +26442,7 @@
         <v>1594</v>
       </c>
       <c r="E518">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F518" t="s">
         <v>1613</v>
@@ -26477,7 +26477,7 @@
         <v>1594</v>
       </c>
       <c r="E519">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F519" t="s">
         <v>1613</v>
@@ -26512,7 +26512,7 @@
         <v>1595</v>
       </c>
       <c r="E520">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F520" t="s">
         <v>1613</v>
@@ -26547,7 +26547,7 @@
         <v>1595</v>
       </c>
       <c r="E521">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F521" t="s">
         <v>1613</v>
@@ -26582,7 +26582,7 @@
         <v>1595</v>
       </c>
       <c r="E522">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F522" t="s">
         <v>1613</v>
@@ -26617,7 +26617,7 @@
         <v>1595</v>
       </c>
       <c r="E523">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F523" t="s">
         <v>1613</v>
@@ -26652,7 +26652,7 @@
         <v>1595</v>
       </c>
       <c r="E524">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F524" t="s">
         <v>1613</v>
@@ -26687,7 +26687,7 @@
         <v>1595</v>
       </c>
       <c r="E525">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F525" t="s">
         <v>1613</v>
@@ -26722,7 +26722,7 @@
         <v>1596</v>
       </c>
       <c r="E526">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F526" t="s">
         <v>1613</v>
@@ -26757,7 +26757,7 @@
         <v>1596</v>
       </c>
       <c r="E527">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F527" t="s">
         <v>1613</v>
@@ -26792,7 +26792,7 @@
         <v>1596</v>
       </c>
       <c r="E528">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F528" t="s">
         <v>1613</v>
@@ -26827,7 +26827,7 @@
         <v>1596</v>
       </c>
       <c r="E529">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F529" t="s">
         <v>1613</v>
@@ -26862,7 +26862,7 @@
         <v>1596</v>
       </c>
       <c r="E530">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F530" t="s">
         <v>1613</v>
@@ -26897,7 +26897,7 @@
         <v>1596</v>
       </c>
       <c r="E531">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F531" t="s">
         <v>1613</v>
@@ -26932,7 +26932,7 @@
         <v>1596</v>
       </c>
       <c r="E532">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F532" t="s">
         <v>1613</v>
@@ -26967,7 +26967,7 @@
         <v>1596</v>
       </c>
       <c r="E533">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F533" t="s">
         <v>1613</v>
@@ -27002,7 +27002,7 @@
         <v>1596</v>
       </c>
       <c r="E534">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F534" t="s">
         <v>1613</v>
@@ -27037,7 +27037,7 @@
         <v>1596</v>
       </c>
       <c r="E535">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F535" t="s">
         <v>1613</v>
@@ -27072,7 +27072,7 @@
         <v>1596</v>
       </c>
       <c r="E536">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F536" t="s">
         <v>1613</v>
@@ -27107,7 +27107,7 @@
         <v>1596</v>
       </c>
       <c r="E537">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F537" t="s">
         <v>1613</v>
@@ -27142,7 +27142,7 @@
         <v>1596</v>
       </c>
       <c r="E538">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F538" t="s">
         <v>1613</v>
@@ -27177,7 +27177,7 @@
         <v>1596</v>
       </c>
       <c r="E539">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F539" t="s">
         <v>1613</v>
@@ -27212,7 +27212,7 @@
         <v>1596</v>
       </c>
       <c r="E540">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F540" t="s">
         <v>1613</v>
@@ -27247,7 +27247,7 @@
         <v>1596</v>
       </c>
       <c r="E541">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F541" t="s">
         <v>1613</v>
@@ -27282,7 +27282,7 @@
         <v>1596</v>
       </c>
       <c r="E542">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F542" t="s">
         <v>1613</v>
@@ -27317,7 +27317,7 @@
         <v>1596</v>
       </c>
       <c r="E543">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F543" t="s">
         <v>1613</v>
@@ -27352,7 +27352,7 @@
         <v>1596</v>
       </c>
       <c r="E544">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F544" t="s">
         <v>1613</v>
@@ -27387,7 +27387,7 @@
         <v>1596</v>
       </c>
       <c r="E545">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F545" t="s">
         <v>1613</v>
@@ -27422,7 +27422,7 @@
         <v>1596</v>
       </c>
       <c r="E546">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F546" t="s">
         <v>1613</v>
@@ -27457,7 +27457,7 @@
         <v>1596</v>
       </c>
       <c r="E547">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F547" t="s">
         <v>1613</v>
@@ -27492,7 +27492,7 @@
         <v>1596</v>
       </c>
       <c r="E548">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F548" t="s">
         <v>1613</v>
@@ -27527,7 +27527,7 @@
         <v>1596</v>
       </c>
       <c r="E549">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F549" t="s">
         <v>1613</v>
@@ -27562,7 +27562,7 @@
         <v>1596</v>
       </c>
       <c r="E550">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F550" t="s">
         <v>1613</v>
@@ -27597,7 +27597,7 @@
         <v>1596</v>
       </c>
       <c r="E551">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F551" t="s">
         <v>1613</v>
@@ -27632,7 +27632,7 @@
         <v>1596</v>
       </c>
       <c r="E552">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F552" t="s">
         <v>1615</v>
@@ -27670,7 +27670,7 @@
         <v>1597</v>
       </c>
       <c r="E553">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F553" t="s">
         <v>1613</v>
@@ -27705,7 +27705,7 @@
         <v>1597</v>
       </c>
       <c r="E554">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F554" t="s">
         <v>1613</v>
@@ -27740,7 +27740,7 @@
         <v>1597</v>
       </c>
       <c r="E555">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F555" t="s">
         <v>1613</v>
@@ -27775,7 +27775,7 @@
         <v>1597</v>
       </c>
       <c r="E556">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F556" t="s">
         <v>1613</v>
@@ -27810,7 +27810,7 @@
         <v>1597</v>
       </c>
       <c r="E557">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F557" t="s">
         <v>1613</v>
@@ -27845,7 +27845,7 @@
         <v>1597</v>
       </c>
       <c r="E558">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F558" t="s">
         <v>1613</v>
@@ -27880,7 +27880,7 @@
         <v>1597</v>
       </c>
       <c r="E559">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F559" t="s">
         <v>1617</v>
@@ -27915,7 +27915,7 @@
         <v>1597</v>
       </c>
       <c r="E560">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F560" t="s">
         <v>1613</v>
@@ -27950,7 +27950,7 @@
         <v>1598</v>
       </c>
       <c r="E561">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F561" t="s">
         <v>1613</v>
@@ -27985,7 +27985,7 @@
         <v>1598</v>
       </c>
       <c r="E562">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F562" t="s">
         <v>1613</v>
@@ -28020,7 +28020,7 @@
         <v>1599</v>
       </c>
       <c r="E563">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F563" t="s">
         <v>1613</v>
@@ -28055,7 +28055,7 @@
         <v>1599</v>
       </c>
       <c r="E564">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F564" t="s">
         <v>1615</v>
@@ -28093,7 +28093,7 @@
         <v>1600</v>
       </c>
       <c r="E565">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F565" t="s">
         <v>1615</v>
@@ -28131,7 +28131,7 @@
         <v>1600</v>
       </c>
       <c r="E566">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F566" t="s">
         <v>1613</v>
@@ -28166,7 +28166,7 @@
         <v>1600</v>
       </c>
       <c r="E567">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F567" t="s">
         <v>1613</v>
@@ -28201,7 +28201,7 @@
         <v>1600</v>
       </c>
       <c r="E568">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F568" t="s">
         <v>1615</v>
@@ -28239,7 +28239,7 @@
         <v>1600</v>
       </c>
       <c r="E569">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F569" t="s">
         <v>1613</v>
@@ -28274,7 +28274,7 @@
         <v>1600</v>
       </c>
       <c r="E570">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F570" t="s">
         <v>1613</v>
@@ -28309,7 +28309,7 @@
         <v>1600</v>
       </c>
       <c r="E571">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F571" t="s">
         <v>1613</v>
@@ -28344,7 +28344,7 @@
         <v>1600</v>
       </c>
       <c r="E572">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F572" t="s">
         <v>1613</v>
@@ -28382,7 +28382,7 @@
         <v>1600</v>
       </c>
       <c r="E573">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F573" t="s">
         <v>1613</v>
@@ -28417,7 +28417,7 @@
         <v>1600</v>
       </c>
       <c r="E574">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F574" t="s">
         <v>1613</v>
@@ -28452,7 +28452,7 @@
         <v>1601</v>
       </c>
       <c r="E575">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F575" t="s">
         <v>1613</v>
@@ -28490,7 +28490,7 @@
         <v>1601</v>
       </c>
       <c r="E576">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F576" t="s">
         <v>1617</v>
@@ -28525,7 +28525,7 @@
         <v>1601</v>
       </c>
       <c r="E577">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F577" t="s">
         <v>1615</v>
@@ -28560,7 +28560,7 @@
         <v>1601</v>
       </c>
       <c r="E578">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F578" t="s">
         <v>1613</v>
@@ -28595,7 +28595,7 @@
         <v>1601</v>
       </c>
       <c r="E579">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F579" t="s">
         <v>1613</v>
@@ -28630,7 +28630,7 @@
         <v>1601</v>
       </c>
       <c r="E580">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F580" t="s">
         <v>1613</v>
@@ -28665,7 +28665,7 @@
         <v>1601</v>
       </c>
       <c r="E581">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F581" t="s">
         <v>1613</v>
@@ -28700,7 +28700,7 @@
         <v>1601</v>
       </c>
       <c r="E582">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F582" t="s">
         <v>1613</v>
@@ -28735,7 +28735,7 @@
         <v>1601</v>
       </c>
       <c r="E583">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F583" t="s">
         <v>1613</v>
@@ -28770,7 +28770,7 @@
         <v>1602</v>
       </c>
       <c r="E584">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F584" t="s">
         <v>1613</v>
@@ -28808,7 +28808,7 @@
         <v>1602</v>
       </c>
       <c r="E585">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F585" t="s">
         <v>1613</v>
@@ -28843,7 +28843,7 @@
         <v>1603</v>
       </c>
       <c r="E586">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F586" t="s">
         <v>1613</v>
@@ -28878,7 +28878,7 @@
         <v>1603</v>
       </c>
       <c r="E587">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F587" t="s">
         <v>1615</v>
@@ -28916,7 +28916,7 @@
         <v>1603</v>
       </c>
       <c r="E588">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F588" t="s">
         <v>1613</v>
@@ -28951,7 +28951,7 @@
         <v>1603</v>
       </c>
       <c r="E589">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F589" t="s">
         <v>1613</v>
@@ -28986,7 +28986,7 @@
         <v>1603</v>
       </c>
       <c r="E590">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F590" t="s">
         <v>1613</v>
@@ -29021,7 +29021,7 @@
         <v>1603</v>
       </c>
       <c r="E591">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F591" t="s">
         <v>1613</v>
@@ -29056,7 +29056,7 @@
         <v>1603</v>
       </c>
       <c r="E592">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F592" t="s">
         <v>1613</v>
@@ -29091,7 +29091,7 @@
         <v>1603</v>
       </c>
       <c r="E593">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F593" t="s">
         <v>1615</v>
@@ -29126,7 +29126,7 @@
         <v>1603</v>
       </c>
       <c r="E594">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F594" t="s">
         <v>1613</v>
@@ -29161,7 +29161,7 @@
         <v>1603</v>
       </c>
       <c r="E595">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F595" t="s">
         <v>1613</v>
@@ -29196,7 +29196,7 @@
         <v>1604</v>
       </c>
       <c r="E596">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F596" t="s">
         <v>1613</v>
@@ -29231,7 +29231,7 @@
         <v>1604</v>
       </c>
       <c r="E597">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F597" t="s">
         <v>1613</v>
@@ -29266,7 +29266,7 @@
         <v>1604</v>
       </c>
       <c r="E598">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F598" t="s">
         <v>1613</v>
@@ -29301,7 +29301,7 @@
         <v>1604</v>
       </c>
       <c r="E599">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F599" t="s">
         <v>1613</v>
@@ -29336,7 +29336,7 @@
         <v>1604</v>
       </c>
       <c r="E600">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F600" t="s">
         <v>1615</v>
@@ -29374,7 +29374,7 @@
         <v>1604</v>
       </c>
       <c r="E601">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F601" t="s">
         <v>1613</v>
@@ -29409,7 +29409,7 @@
         <v>1604</v>
       </c>
       <c r="E602">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F602" t="s">
         <v>1613</v>
@@ -29444,7 +29444,7 @@
         <v>1604</v>
       </c>
       <c r="E603">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F603" t="s">
         <v>1613</v>
@@ -29479,7 +29479,7 @@
         <v>1604</v>
       </c>
       <c r="E604">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F604" t="s">
         <v>1613</v>
@@ -29514,7 +29514,7 @@
         <v>1604</v>
       </c>
       <c r="E605">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F605" t="s">
         <v>1615</v>
@@ -29549,7 +29549,7 @@
         <v>1604</v>
       </c>
       <c r="E606">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F606" t="s">
         <v>1613</v>
@@ -29584,7 +29584,7 @@
         <v>1604</v>
       </c>
       <c r="E607">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F607" t="s">
         <v>1617</v>
@@ -29619,7 +29619,7 @@
         <v>1604</v>
       </c>
       <c r="E608">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F608" t="s">
         <v>1613</v>
@@ -29654,7 +29654,7 @@
         <v>1605</v>
       </c>
       <c r="E609">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F609" t="s">
         <v>1613</v>
@@ -29689,7 +29689,7 @@
         <v>1605</v>
       </c>
       <c r="E610">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F610" t="s">
         <v>1613</v>
@@ -29724,7 +29724,7 @@
         <v>1605</v>
       </c>
       <c r="E611">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F611" t="s">
         <v>1613</v>
@@ -29759,7 +29759,7 @@
         <v>1605</v>
       </c>
       <c r="E612">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F612" t="s">
         <v>1613</v>
@@ -29794,7 +29794,7 @@
         <v>1605</v>
       </c>
       <c r="E613">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F613" t="s">
         <v>1613</v>
@@ -29829,7 +29829,7 @@
         <v>1605</v>
       </c>
       <c r="E614">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F614" t="s">
         <v>1613</v>
@@ -29864,7 +29864,7 @@
         <v>1605</v>
       </c>
       <c r="E615">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F615" t="s">
         <v>1613</v>
@@ -29899,7 +29899,7 @@
         <v>1605</v>
       </c>
       <c r="E616">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F616" t="s">
         <v>1613</v>
@@ -29934,7 +29934,7 @@
         <v>1605</v>
       </c>
       <c r="E617">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F617" t="s">
         <v>1613</v>
@@ -29972,7 +29972,7 @@
         <v>1605</v>
       </c>
       <c r="E618">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F618" t="s">
         <v>1615</v>
@@ -30010,7 +30010,7 @@
         <v>1605</v>
       </c>
       <c r="E619">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F619" t="s">
         <v>1613</v>
@@ -30045,7 +30045,7 @@
         <v>1605</v>
       </c>
       <c r="E620">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F620" t="s">
         <v>1615</v>
@@ -30080,7 +30080,7 @@
         <v>1605</v>
       </c>
       <c r="E621">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F621" t="s">
         <v>1615</v>
@@ -30115,7 +30115,7 @@
         <v>1605</v>
       </c>
       <c r="E622">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F622" t="s">
         <v>1613</v>
@@ -30150,7 +30150,7 @@
         <v>1606</v>
       </c>
       <c r="E623">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F623" t="s">
         <v>1613</v>
@@ -30185,7 +30185,7 @@
         <v>1606</v>
       </c>
       <c r="E624">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F624" t="s">
         <v>1613</v>
@@ -30220,7 +30220,7 @@
         <v>1606</v>
       </c>
       <c r="E625">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F625" t="s">
         <v>1613</v>
@@ -30255,7 +30255,7 @@
         <v>1606</v>
       </c>
       <c r="E626">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F626" t="s">
         <v>1613</v>
@@ -30290,7 +30290,7 @@
         <v>1606</v>
       </c>
       <c r="E627">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F627" t="s">
         <v>1613</v>
@@ -30325,7 +30325,7 @@
         <v>1606</v>
       </c>
       <c r="E628">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F628" t="s">
         <v>1613</v>
@@ -30360,7 +30360,7 @@
         <v>1606</v>
       </c>
       <c r="E629">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F629" t="s">
         <v>1613</v>
@@ -30395,7 +30395,7 @@
         <v>1606</v>
       </c>
       <c r="E630">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F630" t="s">
         <v>1613</v>
@@ -30430,7 +30430,7 @@
         <v>1606</v>
       </c>
       <c r="E631">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F631" t="s">
         <v>1613</v>
@@ -30465,7 +30465,7 @@
         <v>1606</v>
       </c>
       <c r="E632">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F632" t="s">
         <v>1613</v>
@@ -30503,7 +30503,7 @@
         <v>1607</v>
       </c>
       <c r="E633">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F633" t="s">
         <v>1613</v>
@@ -30538,7 +30538,7 @@
         <v>1607</v>
       </c>
       <c r="E634">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F634" t="s">
         <v>1613</v>
@@ -30573,7 +30573,7 @@
         <v>1608</v>
       </c>
       <c r="E635">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F635" t="s">
         <v>1613</v>
@@ -30611,7 +30611,7 @@
         <v>1608</v>
       </c>
       <c r="E636">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F636" t="s">
         <v>1613</v>
@@ -30646,7 +30646,7 @@
         <v>1608</v>
       </c>
       <c r="E637">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F637" t="s">
         <v>1613</v>
@@ -30681,7 +30681,7 @@
         <v>1608</v>
       </c>
       <c r="E638">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F638" t="s">
         <v>1615</v>
@@ -30719,7 +30719,7 @@
         <v>1608</v>
       </c>
       <c r="E639">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F639" t="s">
         <v>1615</v>
@@ -30757,7 +30757,7 @@
         <v>1608</v>
       </c>
       <c r="E640">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F640" t="s">
         <v>1613</v>
@@ -30792,7 +30792,7 @@
         <v>1608</v>
       </c>
       <c r="E641">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F641" t="s">
         <v>1613</v>
@@ -30827,7 +30827,7 @@
         <v>1608</v>
       </c>
       <c r="E642">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F642" t="s">
         <v>1613</v>
@@ -30862,7 +30862,7 @@
         <v>1609</v>
       </c>
       <c r="E643">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F643" t="s">
         <v>1613</v>
@@ -30897,7 +30897,7 @@
         <v>1609</v>
       </c>
       <c r="E644">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F644" t="s">
         <v>1613</v>
@@ -30932,7 +30932,7 @@
         <v>1609</v>
       </c>
       <c r="E645">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F645" t="s">
         <v>1613</v>
@@ -30967,7 +30967,7 @@
         <v>1609</v>
       </c>
       <c r="E646">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F646" t="s">
         <v>1613</v>
@@ -31002,7 +31002,7 @@
         <v>1609</v>
       </c>
       <c r="E647">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F647" t="s">
         <v>1613</v>
@@ -31037,7 +31037,7 @@
         <v>1609</v>
       </c>
       <c r="E648">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F648" t="s">
         <v>1613</v>
@@ -31072,7 +31072,7 @@
         <v>1609</v>
       </c>
       <c r="E649">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F649" t="s">
         <v>1613</v>
@@ -31107,7 +31107,7 @@
         <v>1609</v>
       </c>
       <c r="E650">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F650" t="s">
         <v>1613</v>
@@ -31142,7 +31142,7 @@
         <v>1609</v>
       </c>
       <c r="E651">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F651" t="s">
         <v>1613</v>
@@ -31177,7 +31177,7 @@
         <v>1609</v>
       </c>
       <c r="E652">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F652" t="s">
         <v>1613</v>
@@ -31212,7 +31212,7 @@
         <v>1609</v>
       </c>
       <c r="E653">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F653" t="s">
         <v>1613</v>
@@ -31247,7 +31247,7 @@
         <v>1609</v>
       </c>
       <c r="E654">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F654" t="s">
         <v>1613</v>
@@ -31282,7 +31282,7 @@
         <v>1609</v>
       </c>
       <c r="E655">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F655" t="s">
         <v>1613</v>
@@ -31320,7 +31320,7 @@
         <v>1609</v>
       </c>
       <c r="E656">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F656" t="s">
         <v>1613</v>
@@ -31358,7 +31358,7 @@
         <v>1609</v>
       </c>
       <c r="E657">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F657" t="s">
         <v>1613</v>
@@ -31393,7 +31393,7 @@
         <v>1610</v>
       </c>
       <c r="E658">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F658" t="s">
         <v>1613</v>
@@ -31428,7 +31428,7 @@
         <v>1610</v>
       </c>
       <c r="E659">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F659" t="s">
         <v>1615</v>
@@ -31466,7 +31466,7 @@
         <v>1610</v>
       </c>
       <c r="E660">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F660" t="s">
         <v>1613</v>
@@ -31501,7 +31501,7 @@
         <v>1610</v>
       </c>
       <c r="E661">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F661" t="s">
         <v>1613</v>
@@ -31536,7 +31536,7 @@
         <v>1611</v>
       </c>
       <c r="E662">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F662" t="s">
         <v>1613</v>
@@ -31571,7 +31571,7 @@
         <v>1611</v>
       </c>
       <c r="E663">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F663" t="s">
         <v>1613</v>
@@ -31606,7 +31606,7 @@
         <v>1611</v>
       </c>
       <c r="E664">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F664" t="s">
         <v>1613</v>
@@ -31641,7 +31641,7 @@
         <v>1611</v>
       </c>
       <c r="E665">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F665" t="s">
         <v>1613</v>
@@ -31676,7 +31676,7 @@
         <v>1611</v>
       </c>
       <c r="E666">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F666" t="s">
         <v>1615</v>
@@ -31714,7 +31714,7 @@
         <v>1611</v>
       </c>
       <c r="E667">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F667" t="s">
         <v>1615</v>
@@ -31752,7 +31752,7 @@
         <v>1611</v>
       </c>
       <c r="E668">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F668" t="s">
         <v>1613</v>
@@ -31787,7 +31787,7 @@
         <v>1611</v>
       </c>
       <c r="E669">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F669" t="s">
         <v>1613</v>
@@ -31822,7 +31822,7 @@
         <v>1611</v>
       </c>
       <c r="E670">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F670" t="s">
         <v>1613</v>
@@ -31857,7 +31857,7 @@
         <v>1611</v>
       </c>
       <c r="E671">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F671" t="s">
         <v>1613</v>
@@ -31892,7 +31892,7 @@
         <v>1611</v>
       </c>
       <c r="E672">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F672" t="s">
         <v>1613</v>
@@ -31927,7 +31927,7 @@
         <v>1611</v>
       </c>
       <c r="E673">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F673" t="s">
         <v>1613</v>
@@ -31962,7 +31962,7 @@
         <v>1612</v>
       </c>
       <c r="E674">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F674" t="s">
         <v>1617</v>
@@ -31997,7 +31997,7 @@
         <v>1612</v>
       </c>
       <c r="E675">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F675" t="s">
         <v>1613</v>
@@ -32032,7 +32032,7 @@
         <v>1612</v>
       </c>
       <c r="E676">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F676" t="s">
         <v>1613</v>
@@ -32067,7 +32067,7 @@
         <v>1612</v>
       </c>
       <c r="E677">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F677" t="s">
         <v>1613</v>
@@ -32102,7 +32102,7 @@
         <v>1612</v>
       </c>
       <c r="E678">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F678" t="s">
         <v>1613</v>
@@ -32137,7 +32137,7 @@
         <v>1612</v>
       </c>
       <c r="E679">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F679" t="s">
         <v>1613</v>
@@ -32172,7 +32172,7 @@
         <v>1612</v>
       </c>
       <c r="E680">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F680" t="s">
         <v>1613</v>
@@ -32207,7 +32207,7 @@
         <v>1612</v>
       </c>
       <c r="E681">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F681" t="s">
         <v>1613</v>
@@ -32242,7 +32242,7 @@
         <v>1612</v>
       </c>
       <c r="E682">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F682" t="s">
         <v>1613</v>

--- a/BacklogGATEAutoCompleto.xlsx
+++ b/BacklogGATEAutoCompleto.xlsx
@@ -8349,7 +8349,7 @@
         <v>1397</v>
       </c>
       <c r="E2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="F2" t="s">
         <v>1613</v>
@@ -8384,7 +8384,7 @@
         <v>1398</v>
       </c>
       <c r="E3">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="F3" t="s">
         <v>1613</v>
@@ -8419,7 +8419,7 @@
         <v>1399</v>
       </c>
       <c r="E4">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="F4" t="s">
         <v>1613</v>
@@ -8454,7 +8454,7 @@
         <v>1400</v>
       </c>
       <c r="E5">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="F5" t="s">
         <v>1613</v>
@@ -8489,7 +8489,7 @@
         <v>1400</v>
       </c>
       <c r="E6">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="F6" t="s">
         <v>1613</v>
@@ -8524,7 +8524,7 @@
         <v>1401</v>
       </c>
       <c r="E7">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="F7" t="s">
         <v>1613</v>
@@ -8559,7 +8559,7 @@
         <v>1402</v>
       </c>
       <c r="E8">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="F8" t="s">
         <v>1613</v>
@@ -8594,7 +8594,7 @@
         <v>1403</v>
       </c>
       <c r="E9">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="F9" t="s">
         <v>1613</v>
@@ -8629,7 +8629,7 @@
         <v>1404</v>
       </c>
       <c r="E10">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="F10" t="s">
         <v>1613</v>
@@ -8664,7 +8664,7 @@
         <v>1405</v>
       </c>
       <c r="E11">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="F11" t="s">
         <v>1613</v>
@@ -8699,7 +8699,7 @@
         <v>1406</v>
       </c>
       <c r="E12">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="F12" t="s">
         <v>1613</v>
@@ -8734,7 +8734,7 @@
         <v>1407</v>
       </c>
       <c r="E13">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="F13" t="s">
         <v>1613</v>
@@ -8769,7 +8769,7 @@
         <v>1407</v>
       </c>
       <c r="E14">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="F14" t="s">
         <v>1613</v>
@@ -8804,7 +8804,7 @@
         <v>1408</v>
       </c>
       <c r="E15">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="F15" t="s">
         <v>1613</v>
@@ -8839,7 +8839,7 @@
         <v>1409</v>
       </c>
       <c r="E16">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="F16" t="s">
         <v>1613</v>
@@ -8874,7 +8874,7 @@
         <v>1410</v>
       </c>
       <c r="E17">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="F17" t="s">
         <v>1613</v>
@@ -8909,7 +8909,7 @@
         <v>1410</v>
       </c>
       <c r="E18">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="F18" t="s">
         <v>1613</v>
@@ -8944,7 +8944,7 @@
         <v>1411</v>
       </c>
       <c r="E19">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="F19" t="s">
         <v>1613</v>
@@ -8979,7 +8979,7 @@
         <v>1412</v>
       </c>
       <c r="E20">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="F20" t="s">
         <v>1613</v>
@@ -9014,7 +9014,7 @@
         <v>1413</v>
       </c>
       <c r="E21">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="F21" t="s">
         <v>1613</v>
@@ -9049,7 +9049,7 @@
         <v>1413</v>
       </c>
       <c r="E22">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="F22" t="s">
         <v>1613</v>
@@ -9084,7 +9084,7 @@
         <v>1414</v>
       </c>
       <c r="E23">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="F23" t="s">
         <v>1613</v>
@@ -9119,7 +9119,7 @@
         <v>1415</v>
       </c>
       <c r="E24">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="F24" t="s">
         <v>1613</v>
@@ -9154,7 +9154,7 @@
         <v>1416</v>
       </c>
       <c r="E25">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="F25" t="s">
         <v>1613</v>
@@ -9189,7 +9189,7 @@
         <v>1417</v>
       </c>
       <c r="E26">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F26" t="s">
         <v>1613</v>
@@ -9224,7 +9224,7 @@
         <v>1418</v>
       </c>
       <c r="E27">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="F27" t="s">
         <v>1613</v>
@@ -9262,7 +9262,7 @@
         <v>1419</v>
       </c>
       <c r="E28">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F28" t="s">
         <v>1613</v>
@@ -9297,7 +9297,7 @@
         <v>1420</v>
       </c>
       <c r="E29">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="F29" t="s">
         <v>1613</v>
@@ -9332,7 +9332,7 @@
         <v>1421</v>
       </c>
       <c r="E30">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="F30" t="s">
         <v>1613</v>
@@ -9367,7 +9367,7 @@
         <v>1422</v>
       </c>
       <c r="E31">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F31" t="s">
         <v>1613</v>
@@ -9402,7 +9402,7 @@
         <v>1423</v>
       </c>
       <c r="E32">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F32" t="s">
         <v>1613</v>
@@ -9437,7 +9437,7 @@
         <v>1424</v>
       </c>
       <c r="E33">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F33" t="s">
         <v>1613</v>
@@ -9472,7 +9472,7 @@
         <v>1425</v>
       </c>
       <c r="E34">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F34" t="s">
         <v>1613</v>
@@ -9507,7 +9507,7 @@
         <v>1426</v>
       </c>
       <c r="E35">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="F35" t="s">
         <v>1613</v>
@@ -9542,7 +9542,7 @@
         <v>1427</v>
       </c>
       <c r="E36">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F36" t="s">
         <v>1613</v>
@@ -9577,7 +9577,7 @@
         <v>1428</v>
       </c>
       <c r="E37">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F37" t="s">
         <v>1613</v>
@@ -9612,7 +9612,7 @@
         <v>1429</v>
       </c>
       <c r="E38">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F38" t="s">
         <v>1613</v>
@@ -9647,7 +9647,7 @@
         <v>1430</v>
       </c>
       <c r="E39">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F39" t="s">
         <v>1613</v>
@@ -9682,7 +9682,7 @@
         <v>1430</v>
       </c>
       <c r="E40">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F40" t="s">
         <v>1613</v>
@@ -9717,7 +9717,7 @@
         <v>1431</v>
       </c>
       <c r="E41">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F41" t="s">
         <v>1613</v>
@@ -9752,7 +9752,7 @@
         <v>1431</v>
       </c>
       <c r="E42">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F42" t="s">
         <v>1613</v>
@@ -9787,7 +9787,7 @@
         <v>1432</v>
       </c>
       <c r="E43">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F43" t="s">
         <v>1613</v>
@@ -9822,7 +9822,7 @@
         <v>1433</v>
       </c>
       <c r="E44">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F44" t="s">
         <v>1613</v>
@@ -9857,7 +9857,7 @@
         <v>1434</v>
       </c>
       <c r="E45">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F45" t="s">
         <v>1613</v>
@@ -9892,7 +9892,7 @@
         <v>1435</v>
       </c>
       <c r="E46">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F46" t="s">
         <v>1613</v>
@@ -9927,7 +9927,7 @@
         <v>1435</v>
       </c>
       <c r="E47">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F47" t="s">
         <v>1613</v>
@@ -9962,7 +9962,7 @@
         <v>1436</v>
       </c>
       <c r="E48">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F48" t="s">
         <v>1613</v>
@@ -9997,7 +9997,7 @@
         <v>1437</v>
       </c>
       <c r="E49">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F49" t="s">
         <v>1613</v>
@@ -10032,7 +10032,7 @@
         <v>1437</v>
       </c>
       <c r="E50">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F50" t="s">
         <v>1613</v>
@@ -10067,7 +10067,7 @@
         <v>1438</v>
       </c>
       <c r="E51">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F51" t="s">
         <v>1613</v>
@@ -10102,7 +10102,7 @@
         <v>1438</v>
       </c>
       <c r="E52">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F52" t="s">
         <v>1613</v>
@@ -10137,7 +10137,7 @@
         <v>1439</v>
       </c>
       <c r="E53">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F53" t="s">
         <v>1613</v>
@@ -10172,7 +10172,7 @@
         <v>1440</v>
       </c>
       <c r="E54">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F54" t="s">
         <v>1613</v>
@@ -10207,7 +10207,7 @@
         <v>1441</v>
       </c>
       <c r="E55">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F55" t="s">
         <v>1613</v>
@@ -10242,7 +10242,7 @@
         <v>1442</v>
       </c>
       <c r="E56">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F56" t="s">
         <v>1613</v>
@@ -10277,7 +10277,7 @@
         <v>1443</v>
       </c>
       <c r="E57">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F57" t="s">
         <v>1613</v>
@@ -10312,7 +10312,7 @@
         <v>1444</v>
       </c>
       <c r="E58">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F58" t="s">
         <v>1613</v>
@@ -10347,7 +10347,7 @@
         <v>1445</v>
       </c>
       <c r="E59">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F59" t="s">
         <v>1613</v>
@@ -10382,7 +10382,7 @@
         <v>1446</v>
       </c>
       <c r="E60">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F60" t="s">
         <v>1613</v>
@@ -10417,7 +10417,7 @@
         <v>1447</v>
       </c>
       <c r="E61">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F61" t="s">
         <v>1613</v>
@@ -10452,7 +10452,7 @@
         <v>1448</v>
       </c>
       <c r="E62">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F62" t="s">
         <v>1613</v>
@@ -10487,7 +10487,7 @@
         <v>1449</v>
       </c>
       <c r="E63">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F63" t="s">
         <v>1613</v>
@@ -10522,7 +10522,7 @@
         <v>1450</v>
       </c>
       <c r="E64">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F64" t="s">
         <v>1613</v>
@@ -10557,7 +10557,7 @@
         <v>1451</v>
       </c>
       <c r="E65">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F65" t="s">
         <v>1613</v>
@@ -10592,7 +10592,7 @@
         <v>1452</v>
       </c>
       <c r="E66">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F66" t="s">
         <v>1613</v>
@@ -10627,7 +10627,7 @@
         <v>1453</v>
       </c>
       <c r="E67">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F67" t="s">
         <v>1613</v>
@@ -10662,7 +10662,7 @@
         <v>1454</v>
       </c>
       <c r="E68">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F68" t="s">
         <v>1613</v>
@@ -10697,7 +10697,7 @@
         <v>1454</v>
       </c>
       <c r="E69">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F69" t="s">
         <v>1613</v>
@@ -10732,7 +10732,7 @@
         <v>1454</v>
       </c>
       <c r="E70">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F70" t="s">
         <v>1613</v>
@@ -10767,7 +10767,7 @@
         <v>1455</v>
       </c>
       <c r="E71">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F71" t="s">
         <v>1613</v>
@@ -10802,7 +10802,7 @@
         <v>1456</v>
       </c>
       <c r="E72">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F72" t="s">
         <v>1613</v>
@@ -10837,7 +10837,7 @@
         <v>1457</v>
       </c>
       <c r="E73">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F73" t="s">
         <v>1613</v>
@@ -10872,7 +10872,7 @@
         <v>1458</v>
       </c>
       <c r="E74">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F74" t="s">
         <v>1613</v>
@@ -10907,7 +10907,7 @@
         <v>1458</v>
       </c>
       <c r="E75">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F75" t="s">
         <v>1613</v>
@@ -10942,7 +10942,7 @@
         <v>1458</v>
       </c>
       <c r="E76">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F76" t="s">
         <v>1613</v>
@@ -10977,7 +10977,7 @@
         <v>1459</v>
       </c>
       <c r="E77">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F77" t="s">
         <v>1613</v>
@@ -11012,7 +11012,7 @@
         <v>1460</v>
       </c>
       <c r="E78">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F78" t="s">
         <v>1613</v>
@@ -11047,7 +11047,7 @@
         <v>1461</v>
       </c>
       <c r="E79">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F79" t="s">
         <v>1613</v>
@@ -11082,7 +11082,7 @@
         <v>1461</v>
       </c>
       <c r="E80">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F80" t="s">
         <v>1613</v>
@@ -11117,7 +11117,7 @@
         <v>1461</v>
       </c>
       <c r="E81">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F81" t="s">
         <v>1613</v>
@@ -11152,7 +11152,7 @@
         <v>1462</v>
       </c>
       <c r="E82">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F82" t="s">
         <v>1613</v>
@@ -11187,7 +11187,7 @@
         <v>1463</v>
       </c>
       <c r="E83">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F83" t="s">
         <v>1613</v>
@@ -11222,7 +11222,7 @@
         <v>1463</v>
       </c>
       <c r="E84">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F84" t="s">
         <v>1613</v>
@@ -11257,7 +11257,7 @@
         <v>1463</v>
       </c>
       <c r="E85">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F85" t="s">
         <v>1614</v>
@@ -11292,7 +11292,7 @@
         <v>1463</v>
       </c>
       <c r="E86">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F86" t="s">
         <v>1613</v>
@@ -11327,7 +11327,7 @@
         <v>1464</v>
       </c>
       <c r="E87">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F87" t="s">
         <v>1613</v>
@@ -11362,7 +11362,7 @@
         <v>1465</v>
       </c>
       <c r="E88">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F88" t="s">
         <v>1613</v>
@@ -11397,7 +11397,7 @@
         <v>1465</v>
       </c>
       <c r="E89">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F89" t="s">
         <v>1613</v>
@@ -11432,7 +11432,7 @@
         <v>1466</v>
       </c>
       <c r="E90">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F90" t="s">
         <v>1613</v>
@@ -11467,7 +11467,7 @@
         <v>1467</v>
       </c>
       <c r="E91">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F91" t="s">
         <v>1613</v>
@@ -11502,7 +11502,7 @@
         <v>1468</v>
       </c>
       <c r="E92">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F92" t="s">
         <v>1613</v>
@@ -11537,7 +11537,7 @@
         <v>1469</v>
       </c>
       <c r="E93">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F93" t="s">
         <v>1613</v>
@@ -11572,7 +11572,7 @@
         <v>1470</v>
       </c>
       <c r="E94">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F94" t="s">
         <v>1613</v>
@@ -11607,7 +11607,7 @@
         <v>1470</v>
       </c>
       <c r="E95">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F95" t="s">
         <v>1613</v>
@@ -11642,7 +11642,7 @@
         <v>1470</v>
       </c>
       <c r="E96">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F96" t="s">
         <v>1613</v>
@@ -11677,7 +11677,7 @@
         <v>1470</v>
       </c>
       <c r="E97">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F97" t="s">
         <v>1613</v>
@@ -11712,7 +11712,7 @@
         <v>1470</v>
       </c>
       <c r="E98">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F98" t="s">
         <v>1613</v>
@@ -11747,7 +11747,7 @@
         <v>1470</v>
       </c>
       <c r="E99">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F99" t="s">
         <v>1613</v>
@@ -11782,7 +11782,7 @@
         <v>1470</v>
       </c>
       <c r="E100">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F100" t="s">
         <v>1613</v>
@@ -11817,7 +11817,7 @@
         <v>1471</v>
       </c>
       <c r="E101">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F101" t="s">
         <v>1613</v>
@@ -11852,7 +11852,7 @@
         <v>1471</v>
       </c>
       <c r="E102">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F102" t="s">
         <v>1613</v>
@@ -11887,7 +11887,7 @@
         <v>1472</v>
       </c>
       <c r="E103">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F103" t="s">
         <v>1613</v>
@@ -11922,7 +11922,7 @@
         <v>1473</v>
       </c>
       <c r="E104">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F104" t="s">
         <v>1613</v>
@@ -11957,7 +11957,7 @@
         <v>1473</v>
       </c>
       <c r="E105">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F105" t="s">
         <v>1613</v>
@@ -11992,7 +11992,7 @@
         <v>1474</v>
       </c>
       <c r="E106">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F106" t="s">
         <v>1613</v>
@@ -12027,7 +12027,7 @@
         <v>1474</v>
       </c>
       <c r="E107">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F107" t="s">
         <v>1615</v>
@@ -12062,7 +12062,7 @@
         <v>1475</v>
       </c>
       <c r="E108">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F108" t="s">
         <v>1613</v>
@@ -12097,7 +12097,7 @@
         <v>1476</v>
       </c>
       <c r="E109">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F109" t="s">
         <v>1613</v>
@@ -12132,7 +12132,7 @@
         <v>1477</v>
       </c>
       <c r="E110">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F110" t="s">
         <v>1613</v>
@@ -12167,7 +12167,7 @@
         <v>1477</v>
       </c>
       <c r="E111">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F111" t="s">
         <v>1613</v>
@@ -12202,7 +12202,7 @@
         <v>1478</v>
       </c>
       <c r="E112">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F112" t="s">
         <v>1613</v>
@@ -12237,7 +12237,7 @@
         <v>1479</v>
       </c>
       <c r="E113">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F113" t="s">
         <v>1613</v>
@@ -12272,7 +12272,7 @@
         <v>1480</v>
       </c>
       <c r="E114">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F114" t="s">
         <v>1613</v>
@@ -12307,7 +12307,7 @@
         <v>1481</v>
       </c>
       <c r="E115">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F115" t="s">
         <v>1613</v>
@@ -12342,7 +12342,7 @@
         <v>1482</v>
       </c>
       <c r="E116">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F116" t="s">
         <v>1613</v>
@@ -12377,7 +12377,7 @@
         <v>1482</v>
       </c>
       <c r="E117">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F117" t="s">
         <v>1613</v>
@@ -12412,7 +12412,7 @@
         <v>1483</v>
       </c>
       <c r="E118">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F118" t="s">
         <v>1613</v>
@@ -12447,7 +12447,7 @@
         <v>1483</v>
       </c>
       <c r="E119">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F119" t="s">
         <v>1613</v>
@@ -12482,7 +12482,7 @@
         <v>1483</v>
       </c>
       <c r="E120">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F120" t="s">
         <v>1613</v>
@@ -12517,7 +12517,7 @@
         <v>1483</v>
       </c>
       <c r="E121">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F121" t="s">
         <v>1613</v>
@@ -12552,7 +12552,7 @@
         <v>1484</v>
       </c>
       <c r="E122">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F122" t="s">
         <v>1613</v>
@@ -12587,7 +12587,7 @@
         <v>1484</v>
       </c>
       <c r="E123">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F123" t="s">
         <v>1613</v>
@@ -12622,7 +12622,7 @@
         <v>1484</v>
       </c>
       <c r="E124">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F124" t="s">
         <v>1613</v>
@@ -12657,7 +12657,7 @@
         <v>1484</v>
       </c>
       <c r="E125">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F125" t="s">
         <v>1613</v>
@@ -12692,7 +12692,7 @@
         <v>1484</v>
       </c>
       <c r="E126">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F126" t="s">
         <v>1613</v>
@@ -12727,7 +12727,7 @@
         <v>1485</v>
       </c>
       <c r="E127">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F127" t="s">
         <v>1613</v>
@@ -12762,7 +12762,7 @@
         <v>1486</v>
       </c>
       <c r="E128">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F128" t="s">
         <v>1613</v>
@@ -12797,7 +12797,7 @@
         <v>1486</v>
       </c>
       <c r="E129">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F129" t="s">
         <v>1613</v>
@@ -12832,7 +12832,7 @@
         <v>1487</v>
       </c>
       <c r="E130">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F130" t="s">
         <v>1613</v>
@@ -12867,7 +12867,7 @@
         <v>1488</v>
       </c>
       <c r="E131">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F131" t="s">
         <v>1613</v>
@@ -12902,7 +12902,7 @@
         <v>1488</v>
       </c>
       <c r="E132">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F132" t="s">
         <v>1613</v>
@@ -12937,7 +12937,7 @@
         <v>1488</v>
       </c>
       <c r="E133">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F133" t="s">
         <v>1613</v>
@@ -12972,7 +12972,7 @@
         <v>1489</v>
       </c>
       <c r="E134">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F134" t="s">
         <v>1613</v>
@@ -13007,7 +13007,7 @@
         <v>1489</v>
       </c>
       <c r="E135">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F135" t="s">
         <v>1613</v>
@@ -13042,7 +13042,7 @@
         <v>1489</v>
       </c>
       <c r="E136">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F136" t="s">
         <v>1613</v>
@@ -13077,7 +13077,7 @@
         <v>1490</v>
       </c>
       <c r="E137">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F137" t="s">
         <v>1613</v>
@@ -13112,7 +13112,7 @@
         <v>1490</v>
       </c>
       <c r="E138">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F138" t="s">
         <v>1613</v>
@@ -13147,7 +13147,7 @@
         <v>1490</v>
       </c>
       <c r="E139">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F139" t="s">
         <v>1613</v>
@@ -13182,7 +13182,7 @@
         <v>1491</v>
       </c>
       <c r="E140">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F140" t="s">
         <v>1613</v>
@@ -13217,7 +13217,7 @@
         <v>1491</v>
       </c>
       <c r="E141">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F141" t="s">
         <v>1613</v>
@@ -13252,7 +13252,7 @@
         <v>1492</v>
       </c>
       <c r="E142">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F142" t="s">
         <v>1613</v>
@@ -13287,7 +13287,7 @@
         <v>1493</v>
       </c>
       <c r="E143">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F143" t="s">
         <v>1613</v>
@@ -13322,7 +13322,7 @@
         <v>1493</v>
       </c>
       <c r="E144">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F144" t="s">
         <v>1613</v>
@@ -13357,7 +13357,7 @@
         <v>1493</v>
       </c>
       <c r="E145">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F145" t="s">
         <v>1613</v>
@@ -13392,7 +13392,7 @@
         <v>1494</v>
       </c>
       <c r="E146">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F146" t="s">
         <v>1613</v>
@@ -13427,7 +13427,7 @@
         <v>1494</v>
       </c>
       <c r="E147">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F147" t="s">
         <v>1613</v>
@@ -13462,7 +13462,7 @@
         <v>1495</v>
       </c>
       <c r="E148">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F148" t="s">
         <v>1613</v>
@@ -13500,7 +13500,7 @@
         <v>1495</v>
       </c>
       <c r="E149">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F149" t="s">
         <v>1613</v>
@@ -13535,7 +13535,7 @@
         <v>1495</v>
       </c>
       <c r="E150">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F150" t="s">
         <v>1613</v>
@@ -13570,7 +13570,7 @@
         <v>1495</v>
       </c>
       <c r="E151">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F151" t="s">
         <v>1613</v>
@@ -13605,7 +13605,7 @@
         <v>1495</v>
       </c>
       <c r="E152">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F152" t="s">
         <v>1613</v>
@@ -13640,7 +13640,7 @@
         <v>1496</v>
       </c>
       <c r="E153">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F153" t="s">
         <v>1613</v>
@@ -13675,7 +13675,7 @@
         <v>1497</v>
       </c>
       <c r="E154">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F154" t="s">
         <v>1614</v>
@@ -13710,7 +13710,7 @@
         <v>1498</v>
       </c>
       <c r="E155">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F155" t="s">
         <v>1613</v>
@@ -13745,7 +13745,7 @@
         <v>1498</v>
       </c>
       <c r="E156">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F156" t="s">
         <v>1613</v>
@@ -13780,7 +13780,7 @@
         <v>1498</v>
       </c>
       <c r="E157">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F157" t="s">
         <v>1613</v>
@@ -13815,7 +13815,7 @@
         <v>1498</v>
       </c>
       <c r="E158">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F158" t="s">
         <v>1613</v>
@@ -13850,7 +13850,7 @@
         <v>1499</v>
       </c>
       <c r="E159">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F159" t="s">
         <v>1613</v>
@@ -13885,7 +13885,7 @@
         <v>1499</v>
       </c>
       <c r="E160">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F160" t="s">
         <v>1613</v>
@@ -13920,7 +13920,7 @@
         <v>1499</v>
       </c>
       <c r="E161">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F161" t="s">
         <v>1613</v>
@@ -13955,7 +13955,7 @@
         <v>1499</v>
       </c>
       <c r="E162">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F162" t="s">
         <v>1613</v>
@@ -13990,7 +13990,7 @@
         <v>1499</v>
       </c>
       <c r="E163">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F163" t="s">
         <v>1613</v>
@@ -14025,7 +14025,7 @@
         <v>1499</v>
       </c>
       <c r="E164">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F164" t="s">
         <v>1613</v>
@@ -14060,7 +14060,7 @@
         <v>1499</v>
       </c>
       <c r="E165">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F165" t="s">
         <v>1613</v>
@@ -14095,7 +14095,7 @@
         <v>1500</v>
       </c>
       <c r="E166">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F166" t="s">
         <v>1613</v>
@@ -14130,7 +14130,7 @@
         <v>1500</v>
       </c>
       <c r="E167">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F167" t="s">
         <v>1613</v>
@@ -14165,7 +14165,7 @@
         <v>1501</v>
       </c>
       <c r="E168">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F168" t="s">
         <v>1613</v>
@@ -14200,7 +14200,7 @@
         <v>1501</v>
       </c>
       <c r="E169">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F169" t="s">
         <v>1613</v>
@@ -14235,7 +14235,7 @@
         <v>1501</v>
       </c>
       <c r="E170">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F170" t="s">
         <v>1613</v>
@@ -14270,7 +14270,7 @@
         <v>1502</v>
       </c>
       <c r="E171">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F171" t="s">
         <v>1613</v>
@@ -14305,7 +14305,7 @@
         <v>1502</v>
       </c>
       <c r="E172">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F172" t="s">
         <v>1613</v>
@@ -14340,7 +14340,7 @@
         <v>1502</v>
       </c>
       <c r="E173">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F173" t="s">
         <v>1613</v>
@@ -14375,7 +14375,7 @@
         <v>1502</v>
       </c>
       <c r="E174">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F174" t="s">
         <v>1613</v>
@@ -14410,7 +14410,7 @@
         <v>1503</v>
       </c>
       <c r="E175">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F175" t="s">
         <v>1613</v>
@@ -14445,7 +14445,7 @@
         <v>1503</v>
       </c>
       <c r="E176">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F176" t="s">
         <v>1613</v>
@@ -14480,7 +14480,7 @@
         <v>1503</v>
       </c>
       <c r="E177">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F177" t="s">
         <v>1613</v>
@@ -14515,7 +14515,7 @@
         <v>1503</v>
       </c>
       <c r="E178">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F178" t="s">
         <v>1613</v>
@@ -14550,7 +14550,7 @@
         <v>1503</v>
       </c>
       <c r="E179">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F179" t="s">
         <v>1613</v>
@@ -14585,7 +14585,7 @@
         <v>1503</v>
       </c>
       <c r="E180">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F180" t="s">
         <v>1613</v>
@@ -14620,7 +14620,7 @@
         <v>1503</v>
       </c>
       <c r="E181">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F181" t="s">
         <v>1613</v>
@@ -14655,7 +14655,7 @@
         <v>1503</v>
       </c>
       <c r="E182">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F182" t="s">
         <v>1613</v>
@@ -14690,7 +14690,7 @@
         <v>1503</v>
       </c>
       <c r="E183">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F183" t="s">
         <v>1613</v>
@@ -14725,7 +14725,7 @@
         <v>1503</v>
       </c>
       <c r="E184">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F184" t="s">
         <v>1613</v>
@@ -14760,7 +14760,7 @@
         <v>1504</v>
       </c>
       <c r="E185">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F185" t="s">
         <v>1613</v>
@@ -14795,7 +14795,7 @@
         <v>1504</v>
       </c>
       <c r="E186">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F186" t="s">
         <v>1613</v>
@@ -14830,7 +14830,7 @@
         <v>1504</v>
       </c>
       <c r="E187">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F187" t="s">
         <v>1613</v>
@@ -14865,7 +14865,7 @@
         <v>1504</v>
       </c>
       <c r="E188">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F188" t="s">
         <v>1616</v>
@@ -14900,7 +14900,7 @@
         <v>1505</v>
       </c>
       <c r="E189">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F189" t="s">
         <v>1613</v>
@@ -14935,7 +14935,7 @@
         <v>1505</v>
       </c>
       <c r="E190">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F190" t="s">
         <v>1614</v>
@@ -14970,7 +14970,7 @@
         <v>1505</v>
       </c>
       <c r="E191">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F191" t="s">
         <v>1613</v>
@@ -15005,7 +15005,7 @@
         <v>1506</v>
       </c>
       <c r="E192">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F192" t="s">
         <v>1613</v>
@@ -15040,7 +15040,7 @@
         <v>1506</v>
       </c>
       <c r="E193">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F193" t="s">
         <v>1613</v>
@@ -15075,7 +15075,7 @@
         <v>1507</v>
       </c>
       <c r="E194">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F194" t="s">
         <v>1613</v>
@@ -15110,7 +15110,7 @@
         <v>1507</v>
       </c>
       <c r="E195">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F195" t="s">
         <v>1613</v>
@@ -15145,7 +15145,7 @@
         <v>1508</v>
       </c>
       <c r="E196">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F196" t="s">
         <v>1613</v>
@@ -15180,7 +15180,7 @@
         <v>1508</v>
       </c>
       <c r="E197">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F197" t="s">
         <v>1613</v>
@@ -15215,7 +15215,7 @@
         <v>1508</v>
       </c>
       <c r="E198">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F198" t="s">
         <v>1613</v>
@@ -15250,7 +15250,7 @@
         <v>1509</v>
       </c>
       <c r="E199">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F199" t="s">
         <v>1613</v>
@@ -15285,7 +15285,7 @@
         <v>1509</v>
       </c>
       <c r="E200">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F200" t="s">
         <v>1613</v>
@@ -15320,7 +15320,7 @@
         <v>1509</v>
       </c>
       <c r="E201">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F201" t="s">
         <v>1613</v>
@@ -15355,7 +15355,7 @@
         <v>1509</v>
       </c>
       <c r="E202">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F202" t="s">
         <v>1613</v>
@@ -15390,7 +15390,7 @@
         <v>1509</v>
       </c>
       <c r="E203">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F203" t="s">
         <v>1613</v>
@@ -15425,7 +15425,7 @@
         <v>1510</v>
       </c>
       <c r="E204">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F204" t="s">
         <v>1613</v>
@@ -15460,7 +15460,7 @@
         <v>1510</v>
       </c>
       <c r="E205">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F205" t="s">
         <v>1613</v>
@@ -15495,7 +15495,7 @@
         <v>1511</v>
       </c>
       <c r="E206">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F206" t="s">
         <v>1613</v>
@@ -15530,7 +15530,7 @@
         <v>1512</v>
       </c>
       <c r="E207">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F207" t="s">
         <v>1613</v>
@@ -15565,7 +15565,7 @@
         <v>1512</v>
       </c>
       <c r="E208">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F208" t="s">
         <v>1613</v>
@@ -15600,7 +15600,7 @@
         <v>1512</v>
       </c>
       <c r="E209">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F209" t="s">
         <v>1613</v>
@@ -15635,7 +15635,7 @@
         <v>1512</v>
       </c>
       <c r="E210">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F210" t="s">
         <v>1613</v>
@@ -15670,7 +15670,7 @@
         <v>1513</v>
       </c>
       <c r="E211">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F211" t="s">
         <v>1613</v>
@@ -15705,7 +15705,7 @@
         <v>1514</v>
       </c>
       <c r="E212">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F212" t="s">
         <v>1613</v>
@@ -15740,7 +15740,7 @@
         <v>1514</v>
       </c>
       <c r="E213">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F213" t="s">
         <v>1613</v>
@@ -15775,7 +15775,7 @@
         <v>1514</v>
       </c>
       <c r="E214">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F214" t="s">
         <v>1613</v>
@@ -15810,7 +15810,7 @@
         <v>1514</v>
       </c>
       <c r="E215">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F215" t="s">
         <v>1613</v>
@@ -15845,7 +15845,7 @@
         <v>1514</v>
       </c>
       <c r="E216">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F216" t="s">
         <v>1613</v>
@@ -15880,7 +15880,7 @@
         <v>1515</v>
       </c>
       <c r="E217">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F217" t="s">
         <v>1613</v>
@@ -15915,7 +15915,7 @@
         <v>1515</v>
       </c>
       <c r="E218">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F218" t="s">
         <v>1613</v>
@@ -15950,7 +15950,7 @@
         <v>1515</v>
       </c>
       <c r="E219">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F219" t="s">
         <v>1613</v>
@@ -15985,7 +15985,7 @@
         <v>1515</v>
       </c>
       <c r="E220">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F220" t="s">
         <v>1613</v>
@@ -16020,7 +16020,7 @@
         <v>1515</v>
       </c>
       <c r="E221">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F221" t="s">
         <v>1613</v>
@@ -16055,7 +16055,7 @@
         <v>1515</v>
       </c>
       <c r="E222">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F222" t="s">
         <v>1613</v>
@@ -16090,7 +16090,7 @@
         <v>1515</v>
       </c>
       <c r="E223">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F223" t="s">
         <v>1613</v>
@@ -16125,7 +16125,7 @@
         <v>1516</v>
       </c>
       <c r="E224">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F224" t="s">
         <v>1613</v>
@@ -16160,7 +16160,7 @@
         <v>1516</v>
       </c>
       <c r="E225">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F225" t="s">
         <v>1613</v>
@@ -16195,7 +16195,7 @@
         <v>1516</v>
       </c>
       <c r="E226">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F226" t="s">
         <v>1613</v>
@@ -16230,7 +16230,7 @@
         <v>1516</v>
       </c>
       <c r="E227">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F227" t="s">
         <v>1613</v>
@@ -16265,7 +16265,7 @@
         <v>1517</v>
       </c>
       <c r="E228">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F228" t="s">
         <v>1613</v>
@@ -16300,7 +16300,7 @@
         <v>1517</v>
       </c>
       <c r="E229">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F229" t="s">
         <v>1613</v>
@@ -16335,7 +16335,7 @@
         <v>1517</v>
       </c>
       <c r="E230">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F230" t="s">
         <v>1613</v>
@@ -16370,7 +16370,7 @@
         <v>1518</v>
       </c>
       <c r="E231">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F231" t="s">
         <v>1613</v>
@@ -16405,7 +16405,7 @@
         <v>1518</v>
       </c>
       <c r="E232">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F232" t="s">
         <v>1613</v>
@@ -16440,7 +16440,7 @@
         <v>1519</v>
       </c>
       <c r="E233">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F233" t="s">
         <v>1613</v>
@@ -16475,7 +16475,7 @@
         <v>1519</v>
       </c>
       <c r="E234">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F234" t="s">
         <v>1613</v>
@@ -16510,7 +16510,7 @@
         <v>1520</v>
       </c>
       <c r="E235">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F235" t="s">
         <v>1613</v>
@@ -16545,7 +16545,7 @@
         <v>1520</v>
       </c>
       <c r="E236">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F236" t="s">
         <v>1613</v>
@@ -16580,7 +16580,7 @@
         <v>1521</v>
       </c>
       <c r="E237">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F237" t="s">
         <v>1613</v>
@@ -16615,7 +16615,7 @@
         <v>1521</v>
       </c>
       <c r="E238">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F238" t="s">
         <v>1613</v>
@@ -16650,7 +16650,7 @@
         <v>1522</v>
       </c>
       <c r="E239">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F239" t="s">
         <v>1613</v>
@@ -16685,7 +16685,7 @@
         <v>1522</v>
       </c>
       <c r="E240">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F240" t="s">
         <v>1613</v>
@@ -16720,7 +16720,7 @@
         <v>1523</v>
       </c>
       <c r="E241">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F241" t="s">
         <v>1613</v>
@@ -16755,7 +16755,7 @@
         <v>1524</v>
       </c>
       <c r="E242">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F242" t="s">
         <v>1613</v>
@@ -16790,7 +16790,7 @@
         <v>1524</v>
       </c>
       <c r="E243">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F243" t="s">
         <v>1613</v>
@@ -16825,7 +16825,7 @@
         <v>1524</v>
       </c>
       <c r="E244">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F244" t="s">
         <v>1613</v>
@@ -16860,7 +16860,7 @@
         <v>1525</v>
       </c>
       <c r="E245">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F245" t="s">
         <v>1613</v>
@@ -16895,7 +16895,7 @@
         <v>1525</v>
       </c>
       <c r="E246">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F246" t="s">
         <v>1613</v>
@@ -16930,7 +16930,7 @@
         <v>1526</v>
       </c>
       <c r="E247">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F247" t="s">
         <v>1613</v>
@@ -16965,7 +16965,7 @@
         <v>1527</v>
       </c>
       <c r="E248">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F248" t="s">
         <v>1613</v>
@@ -17000,7 +17000,7 @@
         <v>1527</v>
       </c>
       <c r="E249">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F249" t="s">
         <v>1613</v>
@@ -17035,7 +17035,7 @@
         <v>1527</v>
       </c>
       <c r="E250">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F250" t="s">
         <v>1613</v>
@@ -17070,7 +17070,7 @@
         <v>1528</v>
       </c>
       <c r="E251">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F251" t="s">
         <v>1613</v>
@@ -17105,7 +17105,7 @@
         <v>1528</v>
       </c>
       <c r="E252">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F252" t="s">
         <v>1613</v>
@@ -17140,7 +17140,7 @@
         <v>1529</v>
       </c>
       <c r="E253">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F253" t="s">
         <v>1613</v>
@@ -17175,7 +17175,7 @@
         <v>1529</v>
       </c>
       <c r="E254">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F254" t="s">
         <v>1613</v>
@@ -17210,7 +17210,7 @@
         <v>1529</v>
       </c>
       <c r="E255">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F255" t="s">
         <v>1615</v>
@@ -17245,7 +17245,7 @@
         <v>1529</v>
       </c>
       <c r="E256">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F256" t="s">
         <v>1613</v>
@@ -17280,7 +17280,7 @@
         <v>1529</v>
       </c>
       <c r="E257">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F257" t="s">
         <v>1613</v>
@@ -17315,7 +17315,7 @@
         <v>1530</v>
       </c>
       <c r="E258">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F258" t="s">
         <v>1613</v>
@@ -17350,7 +17350,7 @@
         <v>1530</v>
       </c>
       <c r="E259">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F259" t="s">
         <v>1613</v>
@@ -17385,7 +17385,7 @@
         <v>1530</v>
       </c>
       <c r="E260">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F260" t="s">
         <v>1613</v>
@@ -17423,7 +17423,7 @@
         <v>1530</v>
       </c>
       <c r="E261">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F261" t="s">
         <v>1613</v>
@@ -17458,7 +17458,7 @@
         <v>1530</v>
       </c>
       <c r="E262">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F262" t="s">
         <v>1613</v>
@@ -17493,7 +17493,7 @@
         <v>1530</v>
       </c>
       <c r="E263">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F263" t="s">
         <v>1613</v>
@@ -17528,7 +17528,7 @@
         <v>1530</v>
       </c>
       <c r="E264">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F264" t="s">
         <v>1613</v>
@@ -17563,7 +17563,7 @@
         <v>1531</v>
       </c>
       <c r="E265">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F265" t="s">
         <v>1613</v>
@@ -17598,7 +17598,7 @@
         <v>1531</v>
       </c>
       <c r="E266">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F266" t="s">
         <v>1613</v>
@@ -17633,7 +17633,7 @@
         <v>1531</v>
       </c>
       <c r="E267">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F267" t="s">
         <v>1613</v>
@@ -17668,7 +17668,7 @@
         <v>1532</v>
       </c>
       <c r="E268">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F268" t="s">
         <v>1613</v>
@@ -17703,7 +17703,7 @@
         <v>1532</v>
       </c>
       <c r="E269">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F269" t="s">
         <v>1613</v>
@@ -17738,7 +17738,7 @@
         <v>1532</v>
       </c>
       <c r="E270">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F270" t="s">
         <v>1613</v>
@@ -17773,7 +17773,7 @@
         <v>1532</v>
       </c>
       <c r="E271">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F271" t="s">
         <v>1613</v>
@@ -17808,7 +17808,7 @@
         <v>1533</v>
       </c>
       <c r="E272">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F272" t="s">
         <v>1613</v>
@@ -17843,7 +17843,7 @@
         <v>1533</v>
       </c>
       <c r="E273">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F273" t="s">
         <v>1613</v>
@@ -17878,7 +17878,7 @@
         <v>1533</v>
       </c>
       <c r="E274">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F274" t="s">
         <v>1613</v>
@@ -17913,7 +17913,7 @@
         <v>1533</v>
       </c>
       <c r="E275">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F275" t="s">
         <v>1613</v>
@@ -17948,7 +17948,7 @@
         <v>1533</v>
       </c>
       <c r="E276">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F276" t="s">
         <v>1613</v>
@@ -17983,7 +17983,7 @@
         <v>1533</v>
       </c>
       <c r="E277">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F277" t="s">
         <v>1613</v>
@@ -18018,7 +18018,7 @@
         <v>1534</v>
       </c>
       <c r="E278">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F278" t="s">
         <v>1613</v>
@@ -18053,7 +18053,7 @@
         <v>1534</v>
       </c>
       <c r="E279">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F279" t="s">
         <v>1613</v>
@@ -18088,7 +18088,7 @@
         <v>1534</v>
       </c>
       <c r="E280">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F280" t="s">
         <v>1613</v>
@@ -18123,7 +18123,7 @@
         <v>1534</v>
       </c>
       <c r="E281">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F281" t="s">
         <v>1613</v>
@@ -18158,7 +18158,7 @@
         <v>1534</v>
       </c>
       <c r="E282">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F282" t="s">
         <v>1613</v>
@@ -18193,7 +18193,7 @@
         <v>1534</v>
       </c>
       <c r="E283">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F283" t="s">
         <v>1613</v>
@@ -18228,7 +18228,7 @@
         <v>1535</v>
       </c>
       <c r="E284">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F284" t="s">
         <v>1613</v>
@@ -18263,7 +18263,7 @@
         <v>1536</v>
       </c>
       <c r="E285">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F285" t="s">
         <v>1614</v>
@@ -18298,7 +18298,7 @@
         <v>1536</v>
       </c>
       <c r="E286">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F286" t="s">
         <v>1613</v>
@@ -18333,7 +18333,7 @@
         <v>1536</v>
       </c>
       <c r="E287">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F287" t="s">
         <v>1613</v>
@@ -18368,7 +18368,7 @@
         <v>1536</v>
       </c>
       <c r="E288">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F288" t="s">
         <v>1616</v>
@@ -18403,7 +18403,7 @@
         <v>1536</v>
       </c>
       <c r="E289">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F289" t="s">
         <v>1613</v>
@@ -18438,7 +18438,7 @@
         <v>1536</v>
       </c>
       <c r="E290">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F290" t="s">
         <v>1613</v>
@@ -18473,7 +18473,7 @@
         <v>1536</v>
       </c>
       <c r="E291">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F291" t="s">
         <v>1613</v>
@@ -18508,7 +18508,7 @@
         <v>1537</v>
       </c>
       <c r="E292">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F292" t="s">
         <v>1613</v>
@@ -18543,7 +18543,7 @@
         <v>1537</v>
       </c>
       <c r="E293">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F293" t="s">
         <v>1613</v>
@@ -18578,7 +18578,7 @@
         <v>1537</v>
       </c>
       <c r="E294">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F294" t="s">
         <v>1613</v>
@@ -18613,7 +18613,7 @@
         <v>1537</v>
       </c>
       <c r="E295">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F295" t="s">
         <v>1613</v>
@@ -18648,7 +18648,7 @@
         <v>1538</v>
       </c>
       <c r="E296">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F296" t="s">
         <v>1613</v>
@@ -18683,7 +18683,7 @@
         <v>1538</v>
       </c>
       <c r="E297">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F297" t="s">
         <v>1613</v>
@@ -18718,7 +18718,7 @@
         <v>1539</v>
       </c>
       <c r="E298">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F298" t="s">
         <v>1613</v>
@@ -18756,7 +18756,7 @@
         <v>1539</v>
       </c>
       <c r="E299">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F299" t="s">
         <v>1613</v>
@@ -18791,7 +18791,7 @@
         <v>1540</v>
       </c>
       <c r="E300">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F300" t="s">
         <v>1613</v>
@@ -18826,7 +18826,7 @@
         <v>1540</v>
       </c>
       <c r="E301">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F301" t="s">
         <v>1613</v>
@@ -18861,7 +18861,7 @@
         <v>1540</v>
       </c>
       <c r="E302">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F302" t="s">
         <v>1613</v>
@@ -18896,7 +18896,7 @@
         <v>1540</v>
       </c>
       <c r="E303">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F303" t="s">
         <v>1613</v>
@@ -18934,7 +18934,7 @@
         <v>1540</v>
       </c>
       <c r="E304">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F304" t="s">
         <v>1613</v>
@@ -18969,7 +18969,7 @@
         <v>1540</v>
       </c>
       <c r="E305">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F305" t="s">
         <v>1613</v>
@@ -19004,7 +19004,7 @@
         <v>1541</v>
       </c>
       <c r="E306">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F306" t="s">
         <v>1613</v>
@@ -19039,7 +19039,7 @@
         <v>1541</v>
       </c>
       <c r="E307">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F307" t="s">
         <v>1613</v>
@@ -19074,7 +19074,7 @@
         <v>1542</v>
       </c>
       <c r="E308">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F308" t="s">
         <v>1613</v>
@@ -19109,7 +19109,7 @@
         <v>1542</v>
       </c>
       <c r="E309">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F309" t="s">
         <v>1613</v>
@@ -19144,7 +19144,7 @@
         <v>1543</v>
       </c>
       <c r="E310">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F310" t="s">
         <v>1613</v>
@@ -19179,7 +19179,7 @@
         <v>1543</v>
       </c>
       <c r="E311">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F311" t="s">
         <v>1613</v>
@@ -19214,7 +19214,7 @@
         <v>1543</v>
       </c>
       <c r="E312">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F312" t="s">
         <v>1613</v>
@@ -19249,7 +19249,7 @@
         <v>1543</v>
       </c>
       <c r="E313">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F313" t="s">
         <v>1613</v>
@@ -19284,7 +19284,7 @@
         <v>1544</v>
       </c>
       <c r="E314">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F314" t="s">
         <v>1613</v>
@@ -19319,7 +19319,7 @@
         <v>1544</v>
       </c>
       <c r="E315">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F315" t="s">
         <v>1613</v>
@@ -19354,7 +19354,7 @@
         <v>1544</v>
       </c>
       <c r="E316">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F316" t="s">
         <v>1613</v>
@@ -19389,7 +19389,7 @@
         <v>1544</v>
       </c>
       <c r="E317">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F317" t="s">
         <v>1613</v>
@@ -19424,7 +19424,7 @@
         <v>1545</v>
       </c>
       <c r="E318">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F318" t="s">
         <v>1613</v>
@@ -19459,7 +19459,7 @@
         <v>1545</v>
       </c>
       <c r="E319">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F319" t="s">
         <v>1613</v>
@@ -19494,7 +19494,7 @@
         <v>1546</v>
       </c>
       <c r="E320">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F320" t="s">
         <v>1613</v>
@@ -19529,7 +19529,7 @@
         <v>1546</v>
       </c>
       <c r="E321">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F321" t="s">
         <v>1613</v>
@@ -19564,7 +19564,7 @@
         <v>1546</v>
       </c>
       <c r="E322">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F322" t="s">
         <v>1613</v>
@@ -19599,7 +19599,7 @@
         <v>1546</v>
       </c>
       <c r="E323">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F323" t="s">
         <v>1613</v>
@@ -19634,7 +19634,7 @@
         <v>1546</v>
       </c>
       <c r="E324">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F324" t="s">
         <v>1613</v>
@@ -19669,7 +19669,7 @@
         <v>1547</v>
       </c>
       <c r="E325">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F325" t="s">
         <v>1613</v>
@@ -19704,7 +19704,7 @@
         <v>1547</v>
       </c>
       <c r="E326">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F326" t="s">
         <v>1613</v>
@@ -19739,7 +19739,7 @@
         <v>1547</v>
       </c>
       <c r="E327">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F327" t="s">
         <v>1613</v>
@@ -19774,7 +19774,7 @@
         <v>1548</v>
       </c>
       <c r="E328">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F328" t="s">
         <v>1613</v>
@@ -19809,7 +19809,7 @@
         <v>1548</v>
       </c>
       <c r="E329">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F329" t="s">
         <v>1613</v>
@@ -19844,7 +19844,7 @@
         <v>1549</v>
       </c>
       <c r="E330">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F330" t="s">
         <v>1613</v>
@@ -19879,7 +19879,7 @@
         <v>1549</v>
       </c>
       <c r="E331">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F331" t="s">
         <v>1613</v>
@@ -19914,7 +19914,7 @@
         <v>1549</v>
       </c>
       <c r="E332">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F332" t="s">
         <v>1613</v>
@@ -19949,7 +19949,7 @@
         <v>1549</v>
       </c>
       <c r="E333">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F333" t="s">
         <v>1613</v>
@@ -19984,7 +19984,7 @@
         <v>1549</v>
       </c>
       <c r="E334">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F334" t="s">
         <v>1613</v>
@@ -20019,7 +20019,7 @@
         <v>1549</v>
       </c>
       <c r="E335">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F335" t="s">
         <v>1613</v>
@@ -20054,7 +20054,7 @@
         <v>1549</v>
       </c>
       <c r="E336">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F336" t="s">
         <v>1613</v>
@@ -20089,7 +20089,7 @@
         <v>1549</v>
       </c>
       <c r="E337">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F337" t="s">
         <v>1613</v>
@@ -20124,7 +20124,7 @@
         <v>1550</v>
       </c>
       <c r="E338">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F338" t="s">
         <v>1613</v>
@@ -20159,7 +20159,7 @@
         <v>1550</v>
       </c>
       <c r="E339">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F339" t="s">
         <v>1613</v>
@@ -20194,7 +20194,7 @@
         <v>1550</v>
       </c>
       <c r="E340">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F340" t="s">
         <v>1613</v>
@@ -20229,7 +20229,7 @@
         <v>1551</v>
       </c>
       <c r="E341">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F341" t="s">
         <v>1613</v>
@@ -20264,7 +20264,7 @@
         <v>1551</v>
       </c>
       <c r="E342">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F342" t="s">
         <v>1613</v>
@@ -20299,7 +20299,7 @@
         <v>1552</v>
       </c>
       <c r="E343">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F343" t="s">
         <v>1613</v>
@@ -20334,7 +20334,7 @@
         <v>1553</v>
       </c>
       <c r="E344">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F344" t="s">
         <v>1615</v>
@@ -20369,7 +20369,7 @@
         <v>1553</v>
       </c>
       <c r="E345">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F345" t="s">
         <v>1613</v>
@@ -20404,7 +20404,7 @@
         <v>1553</v>
       </c>
       <c r="E346">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F346" t="s">
         <v>1613</v>
@@ -20439,7 +20439,7 @@
         <v>1553</v>
       </c>
       <c r="E347">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F347" t="s">
         <v>1613</v>
@@ -20474,7 +20474,7 @@
         <v>1553</v>
       </c>
       <c r="E348">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F348" t="s">
         <v>1613</v>
@@ -20509,7 +20509,7 @@
         <v>1553</v>
       </c>
       <c r="E349">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F349" t="s">
         <v>1613</v>
@@ -20544,7 +20544,7 @@
         <v>1554</v>
       </c>
       <c r="E350">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F350" t="s">
         <v>1613</v>
@@ -20579,7 +20579,7 @@
         <v>1554</v>
       </c>
       <c r="E351">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F351" t="s">
         <v>1613</v>
@@ -20614,7 +20614,7 @@
         <v>1555</v>
       </c>
       <c r="E352">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F352" t="s">
         <v>1613</v>
@@ -20649,7 +20649,7 @@
         <v>1555</v>
       </c>
       <c r="E353">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F353" t="s">
         <v>1613</v>
@@ -20684,7 +20684,7 @@
         <v>1555</v>
       </c>
       <c r="E354">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F354" t="s">
         <v>1613</v>
@@ -20719,7 +20719,7 @@
         <v>1556</v>
       </c>
       <c r="E355">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F355" t="s">
         <v>1613</v>
@@ -20754,7 +20754,7 @@
         <v>1557</v>
       </c>
       <c r="E356">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F356" t="s">
         <v>1613</v>
@@ -20789,7 +20789,7 @@
         <v>1558</v>
       </c>
       <c r="E357">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F357" t="s">
         <v>1613</v>
@@ -20824,7 +20824,7 @@
         <v>1558</v>
       </c>
       <c r="E358">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F358" t="s">
         <v>1613</v>
@@ -20859,7 +20859,7 @@
         <v>1559</v>
       </c>
       <c r="E359">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F359" t="s">
         <v>1613</v>
@@ -20894,7 +20894,7 @@
         <v>1559</v>
       </c>
       <c r="E360">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F360" t="s">
         <v>1613</v>
@@ -20929,7 +20929,7 @@
         <v>1559</v>
       </c>
       <c r="E361">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F361" t="s">
         <v>1613</v>
@@ -20964,7 +20964,7 @@
         <v>1560</v>
       </c>
       <c r="E362">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F362" t="s">
         <v>1613</v>
@@ -20999,7 +20999,7 @@
         <v>1560</v>
       </c>
       <c r="E363">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F363" t="s">
         <v>1613</v>
@@ -21034,7 +21034,7 @@
         <v>1560</v>
       </c>
       <c r="E364">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F364" t="s">
         <v>1613</v>
@@ -21069,7 +21069,7 @@
         <v>1560</v>
       </c>
       <c r="E365">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F365" t="s">
         <v>1613</v>
@@ -21104,7 +21104,7 @@
         <v>1560</v>
       </c>
       <c r="E366">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F366" t="s">
         <v>1613</v>
@@ -21139,7 +21139,7 @@
         <v>1560</v>
       </c>
       <c r="E367">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F367" t="s">
         <v>1613</v>
@@ -21174,7 +21174,7 @@
         <v>1560</v>
       </c>
       <c r="E368">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F368" t="s">
         <v>1613</v>
@@ -21209,7 +21209,7 @@
         <v>1560</v>
       </c>
       <c r="E369">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F369" t="s">
         <v>1613</v>
@@ -21244,7 +21244,7 @@
         <v>1560</v>
       </c>
       <c r="E370">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F370" t="s">
         <v>1613</v>
@@ -21279,7 +21279,7 @@
         <v>1561</v>
       </c>
       <c r="E371">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F371" t="s">
         <v>1613</v>
@@ -21314,7 +21314,7 @@
         <v>1561</v>
       </c>
       <c r="E372">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F372" t="s">
         <v>1613</v>
@@ -21349,7 +21349,7 @@
         <v>1561</v>
       </c>
       <c r="E373">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F373" t="s">
         <v>1613</v>
@@ -21384,7 +21384,7 @@
         <v>1561</v>
       </c>
       <c r="E374">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F374" t="s">
         <v>1613</v>
@@ -21419,7 +21419,7 @@
         <v>1562</v>
       </c>
       <c r="E375">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F375" t="s">
         <v>1616</v>
@@ -21454,7 +21454,7 @@
         <v>1562</v>
       </c>
       <c r="E376">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F376" t="s">
         <v>1613</v>
@@ -21489,7 +21489,7 @@
         <v>1563</v>
       </c>
       <c r="E377">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F377" t="s">
         <v>1613</v>
@@ -21524,7 +21524,7 @@
         <v>1563</v>
       </c>
       <c r="E378">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F378" t="s">
         <v>1613</v>
@@ -21559,7 +21559,7 @@
         <v>1563</v>
       </c>
       <c r="E379">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F379" t="s">
         <v>1613</v>
@@ -21594,7 +21594,7 @@
         <v>1563</v>
       </c>
       <c r="E380">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F380" t="s">
         <v>1613</v>
@@ -21629,7 +21629,7 @@
         <v>1563</v>
       </c>
       <c r="E381">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F381" t="s">
         <v>1617</v>
@@ -21667,7 +21667,7 @@
         <v>1563</v>
       </c>
       <c r="E382">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F382" t="s">
         <v>1613</v>
@@ -21702,7 +21702,7 @@
         <v>1563</v>
       </c>
       <c r="E383">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F383" t="s">
         <v>1613</v>
@@ -21737,7 +21737,7 @@
         <v>1564</v>
       </c>
       <c r="E384">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F384" t="s">
         <v>1613</v>
@@ -21772,7 +21772,7 @@
         <v>1564</v>
       </c>
       <c r="E385">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F385" t="s">
         <v>1613</v>
@@ -21807,7 +21807,7 @@
         <v>1564</v>
       </c>
       <c r="E386">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F386" t="s">
         <v>1613</v>
@@ -21842,7 +21842,7 @@
         <v>1564</v>
       </c>
       <c r="E387">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F387" t="s">
         <v>1613</v>
@@ -21880,7 +21880,7 @@
         <v>1564</v>
       </c>
       <c r="E388">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F388" t="s">
         <v>1613</v>
@@ -21915,7 +21915,7 @@
         <v>1564</v>
       </c>
       <c r="E389">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F389" t="s">
         <v>1613</v>
@@ -21950,7 +21950,7 @@
         <v>1564</v>
       </c>
       <c r="E390">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F390" t="s">
         <v>1613</v>
@@ -21985,7 +21985,7 @@
         <v>1564</v>
       </c>
       <c r="E391">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F391" t="s">
         <v>1613</v>
@@ -22020,7 +22020,7 @@
         <v>1564</v>
       </c>
       <c r="E392">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F392" t="s">
         <v>1613</v>
@@ -22055,7 +22055,7 @@
         <v>1565</v>
       </c>
       <c r="E393">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F393" t="s">
         <v>1614</v>
@@ -22090,7 +22090,7 @@
         <v>1566</v>
       </c>
       <c r="E394">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F394" t="s">
         <v>1617</v>
@@ -22125,7 +22125,7 @@
         <v>1567</v>
       </c>
       <c r="E395">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F395" t="s">
         <v>1613</v>
@@ -22160,7 +22160,7 @@
         <v>1568</v>
       </c>
       <c r="E396">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F396" t="s">
         <v>1613</v>
@@ -22195,7 +22195,7 @@
         <v>1568</v>
       </c>
       <c r="E397">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F397" t="s">
         <v>1613</v>
@@ -22230,7 +22230,7 @@
         <v>1569</v>
       </c>
       <c r="E398">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F398" t="s">
         <v>1613</v>
@@ -22265,7 +22265,7 @@
         <v>1570</v>
       </c>
       <c r="E399">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F399" t="s">
         <v>1616</v>
@@ -22300,7 +22300,7 @@
         <v>1570</v>
       </c>
       <c r="E400">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F400" t="s">
         <v>1613</v>
@@ -22335,7 +22335,7 @@
         <v>1570</v>
       </c>
       <c r="E401">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F401" t="s">
         <v>1613</v>
@@ -22370,7 +22370,7 @@
         <v>1570</v>
       </c>
       <c r="E402">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F402" t="s">
         <v>1613</v>
@@ -22405,7 +22405,7 @@
         <v>1570</v>
       </c>
       <c r="E403">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F403" t="s">
         <v>1613</v>
@@ -22440,7 +22440,7 @@
         <v>1570</v>
       </c>
       <c r="E404">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F404" t="s">
         <v>1613</v>
@@ -22475,7 +22475,7 @@
         <v>1571</v>
       </c>
       <c r="E405">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F405" t="s">
         <v>1613</v>
@@ -22510,7 +22510,7 @@
         <v>1571</v>
       </c>
       <c r="E406">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F406" t="s">
         <v>1613</v>
@@ -22545,7 +22545,7 @@
         <v>1571</v>
       </c>
       <c r="E407">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F407" t="s">
         <v>1613</v>
@@ -22580,7 +22580,7 @@
         <v>1572</v>
       </c>
       <c r="E408">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F408" t="s">
         <v>1613</v>
@@ -22615,7 +22615,7 @@
         <v>1572</v>
       </c>
       <c r="E409">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F409" t="s">
         <v>1613</v>
@@ -22650,7 +22650,7 @@
         <v>1572</v>
       </c>
       <c r="E410">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F410" t="s">
         <v>1613</v>
@@ -22688,7 +22688,7 @@
         <v>1572</v>
       </c>
       <c r="E411">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F411" t="s">
         <v>1613</v>
@@ -22723,7 +22723,7 @@
         <v>1573</v>
       </c>
       <c r="E412">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F412" t="s">
         <v>1613</v>
@@ -22758,7 +22758,7 @@
         <v>1573</v>
       </c>
       <c r="E413">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F413" t="s">
         <v>1613</v>
@@ -22793,7 +22793,7 @@
         <v>1573</v>
       </c>
       <c r="E414">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F414" t="s">
         <v>1613</v>
@@ -22828,7 +22828,7 @@
         <v>1573</v>
       </c>
       <c r="E415">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F415" t="s">
         <v>1613</v>
@@ -22863,7 +22863,7 @@
         <v>1573</v>
       </c>
       <c r="E416">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F416" t="s">
         <v>1613</v>
@@ -22898,7 +22898,7 @@
         <v>1574</v>
       </c>
       <c r="E417">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F417" t="s">
         <v>1613</v>
@@ -22933,7 +22933,7 @@
         <v>1574</v>
       </c>
       <c r="E418">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F418" t="s">
         <v>1613</v>
@@ -22968,7 +22968,7 @@
         <v>1575</v>
       </c>
       <c r="E419">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F419" t="s">
         <v>1613</v>
@@ -23003,7 +23003,7 @@
         <v>1575</v>
       </c>
       <c r="E420">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F420" t="s">
         <v>1613</v>
@@ -23038,7 +23038,7 @@
         <v>1575</v>
       </c>
       <c r="E421">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F421" t="s">
         <v>1613</v>
@@ -23073,7 +23073,7 @@
         <v>1575</v>
       </c>
       <c r="E422">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F422" t="s">
         <v>1613</v>
@@ -23108,7 +23108,7 @@
         <v>1575</v>
       </c>
       <c r="E423">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F423" t="s">
         <v>1613</v>
@@ -23143,7 +23143,7 @@
         <v>1575</v>
       </c>
       <c r="E424">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F424" t="s">
         <v>1613</v>
@@ -23178,7 +23178,7 @@
         <v>1575</v>
       </c>
       <c r="E425">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F425" t="s">
         <v>1613</v>
@@ -23213,7 +23213,7 @@
         <v>1575</v>
       </c>
       <c r="E426">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F426" t="s">
         <v>1613</v>
@@ -23248,7 +23248,7 @@
         <v>1575</v>
       </c>
       <c r="E427">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F427" t="s">
         <v>1613</v>
@@ -23283,7 +23283,7 @@
         <v>1575</v>
       </c>
       <c r="E428">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F428" t="s">
         <v>1613</v>
@@ -23318,7 +23318,7 @@
         <v>1576</v>
       </c>
       <c r="E429">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F429" t="s">
         <v>1613</v>
@@ -23353,7 +23353,7 @@
         <v>1576</v>
       </c>
       <c r="E430">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F430" t="s">
         <v>1613</v>
@@ -23388,7 +23388,7 @@
         <v>1576</v>
       </c>
       <c r="E431">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F431" t="s">
         <v>1614</v>
@@ -23423,7 +23423,7 @@
         <v>1577</v>
       </c>
       <c r="E432">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F432" t="s">
         <v>1613</v>
@@ -23458,7 +23458,7 @@
         <v>1577</v>
       </c>
       <c r="E433">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F433" t="s">
         <v>1613</v>
@@ -23493,7 +23493,7 @@
         <v>1577</v>
       </c>
       <c r="E434">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F434" t="s">
         <v>1613</v>
@@ -23528,7 +23528,7 @@
         <v>1577</v>
       </c>
       <c r="E435">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F435" t="s">
         <v>1613</v>
@@ -23563,7 +23563,7 @@
         <v>1577</v>
       </c>
       <c r="E436">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F436" t="s">
         <v>1613</v>
@@ -23598,7 +23598,7 @@
         <v>1577</v>
       </c>
       <c r="E437">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F437" t="s">
         <v>1613</v>
@@ -23633,7 +23633,7 @@
         <v>1577</v>
       </c>
       <c r="E438">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F438" t="s">
         <v>1616</v>
@@ -23668,7 +23668,7 @@
         <v>1578</v>
       </c>
       <c r="E439">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F439" t="s">
         <v>1613</v>
@@ -23703,7 +23703,7 @@
         <v>1578</v>
       </c>
       <c r="E440">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F440" t="s">
         <v>1613</v>
@@ -23738,7 +23738,7 @@
         <v>1578</v>
       </c>
       <c r="E441">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F441" t="s">
         <v>1613</v>
@@ -23773,7 +23773,7 @@
         <v>1578</v>
       </c>
       <c r="E442">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F442" t="s">
         <v>1613</v>
@@ -23808,7 +23808,7 @@
         <v>1579</v>
       </c>
       <c r="E443">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F443" t="s">
         <v>1613</v>
@@ -23843,7 +23843,7 @@
         <v>1579</v>
       </c>
       <c r="E444">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F444" t="s">
         <v>1616</v>
@@ -23878,7 +23878,7 @@
         <v>1579</v>
       </c>
       <c r="E445">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F445" t="s">
         <v>1613</v>
@@ -23913,7 +23913,7 @@
         <v>1579</v>
       </c>
       <c r="E446">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F446" t="s">
         <v>1613</v>
@@ -23948,7 +23948,7 @@
         <v>1579</v>
       </c>
       <c r="E447">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F447" t="s">
         <v>1613</v>
@@ -23983,7 +23983,7 @@
         <v>1579</v>
       </c>
       <c r="E448">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F448" t="s">
         <v>1613</v>
@@ -24018,7 +24018,7 @@
         <v>1579</v>
       </c>
       <c r="E449">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F449" t="s">
         <v>1617</v>
@@ -24053,7 +24053,7 @@
         <v>1579</v>
       </c>
       <c r="E450">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F450" t="s">
         <v>1613</v>
@@ -24088,7 +24088,7 @@
         <v>1579</v>
       </c>
       <c r="E451">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F451" t="s">
         <v>1613</v>
@@ -24123,7 +24123,7 @@
         <v>1580</v>
       </c>
       <c r="E452">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F452" t="s">
         <v>1613</v>
@@ -24158,7 +24158,7 @@
         <v>1580</v>
       </c>
       <c r="E453">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F453" t="s">
         <v>1613</v>
@@ -24193,7 +24193,7 @@
         <v>1580</v>
       </c>
       <c r="E454">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F454" t="s">
         <v>1613</v>
@@ -24228,7 +24228,7 @@
         <v>1580</v>
       </c>
       <c r="E455">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F455" t="s">
         <v>1613</v>
@@ -24263,7 +24263,7 @@
         <v>1580</v>
       </c>
       <c r="E456">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F456" t="s">
         <v>1613</v>
@@ -24298,7 +24298,7 @@
         <v>1580</v>
       </c>
       <c r="E457">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F457" t="s">
         <v>1615</v>
@@ -24333,7 +24333,7 @@
         <v>1580</v>
       </c>
       <c r="E458">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F458" t="s">
         <v>1613</v>
@@ -24368,7 +24368,7 @@
         <v>1580</v>
       </c>
       <c r="E459">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F459" t="s">
         <v>1613</v>
@@ -24403,7 +24403,7 @@
         <v>1581</v>
       </c>
       <c r="E460">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F460" t="s">
         <v>1613</v>
@@ -24438,7 +24438,7 @@
         <v>1581</v>
       </c>
       <c r="E461">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F461" t="s">
         <v>1613</v>
@@ -24473,7 +24473,7 @@
         <v>1581</v>
       </c>
       <c r="E462">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F462" t="s">
         <v>1613</v>
@@ -24508,7 +24508,7 @@
         <v>1581</v>
       </c>
       <c r="E463">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F463" t="s">
         <v>1613</v>
@@ -24543,7 +24543,7 @@
         <v>1581</v>
       </c>
       <c r="E464">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F464" t="s">
         <v>1613</v>
@@ -24578,7 +24578,7 @@
         <v>1582</v>
       </c>
       <c r="E465">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F465" t="s">
         <v>1613</v>
@@ -24613,7 +24613,7 @@
         <v>1582</v>
       </c>
       <c r="E466">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F466" t="s">
         <v>1613</v>
@@ -24648,7 +24648,7 @@
         <v>1582</v>
       </c>
       <c r="E467">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F467" t="s">
         <v>1613</v>
@@ -24683,7 +24683,7 @@
         <v>1582</v>
       </c>
       <c r="E468">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F468" t="s">
         <v>1613</v>
@@ -24718,7 +24718,7 @@
         <v>1582</v>
       </c>
       <c r="E469">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F469" t="s">
         <v>1613</v>
@@ -24756,7 +24756,7 @@
         <v>1583</v>
       </c>
       <c r="E470">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F470" t="s">
         <v>1613</v>
@@ -24791,7 +24791,7 @@
         <v>1583</v>
       </c>
       <c r="E471">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F471" t="s">
         <v>1613</v>
@@ -24826,7 +24826,7 @@
         <v>1583</v>
       </c>
       <c r="E472">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F472" t="s">
         <v>1613</v>
@@ -24861,7 +24861,7 @@
         <v>1583</v>
       </c>
       <c r="E473">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F473" t="s">
         <v>1613</v>
@@ -24896,7 +24896,7 @@
         <v>1583</v>
       </c>
       <c r="E474">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F474" t="s">
         <v>1613</v>
@@ -24931,7 +24931,7 @@
         <v>1583</v>
       </c>
       <c r="E475">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F475" t="s">
         <v>1613</v>
@@ -24966,7 +24966,7 @@
         <v>1584</v>
       </c>
       <c r="E476">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F476" t="s">
         <v>1613</v>
@@ -25001,7 +25001,7 @@
         <v>1584</v>
       </c>
       <c r="E477">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F477" t="s">
         <v>1613</v>
@@ -25036,7 +25036,7 @@
         <v>1584</v>
       </c>
       <c r="E478">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F478" t="s">
         <v>1613</v>
@@ -25071,7 +25071,7 @@
         <v>1585</v>
       </c>
       <c r="E479">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F479" t="s">
         <v>1613</v>
@@ -25106,7 +25106,7 @@
         <v>1586</v>
       </c>
       <c r="E480">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F480" t="s">
         <v>1613</v>
@@ -25141,7 +25141,7 @@
         <v>1586</v>
       </c>
       <c r="E481">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F481" t="s">
         <v>1613</v>
@@ -25176,7 +25176,7 @@
         <v>1586</v>
       </c>
       <c r="E482">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F482" t="s">
         <v>1615</v>
@@ -25214,7 +25214,7 @@
         <v>1586</v>
       </c>
       <c r="E483">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F483" t="s">
         <v>1613</v>
@@ -25249,7 +25249,7 @@
         <v>1586</v>
       </c>
       <c r="E484">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F484" t="s">
         <v>1613</v>
@@ -25284,7 +25284,7 @@
         <v>1587</v>
       </c>
       <c r="E485">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F485" t="s">
         <v>1613</v>
@@ -25319,7 +25319,7 @@
         <v>1587</v>
       </c>
       <c r="E486">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F486" t="s">
         <v>1613</v>
@@ -25354,7 +25354,7 @@
         <v>1587</v>
       </c>
       <c r="E487">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F487" t="s">
         <v>1613</v>
@@ -25389,7 +25389,7 @@
         <v>1587</v>
       </c>
       <c r="E488">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F488" t="s">
         <v>1613</v>
@@ -25424,7 +25424,7 @@
         <v>1587</v>
       </c>
       <c r="E489">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F489" t="s">
         <v>1613</v>
@@ -25459,7 +25459,7 @@
         <v>1588</v>
       </c>
       <c r="E490">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F490" t="s">
         <v>1613</v>
@@ -25494,7 +25494,7 @@
         <v>1588</v>
       </c>
       <c r="E491">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F491" t="s">
         <v>1613</v>
@@ -25529,7 +25529,7 @@
         <v>1588</v>
       </c>
       <c r="E492">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F492" t="s">
         <v>1613</v>
@@ -25564,7 +25564,7 @@
         <v>1588</v>
       </c>
       <c r="E493">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F493" t="s">
         <v>1613</v>
@@ -25599,7 +25599,7 @@
         <v>1588</v>
       </c>
       <c r="E494">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F494" t="s">
         <v>1613</v>
@@ -25634,7 +25634,7 @@
         <v>1588</v>
       </c>
       <c r="E495">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F495" t="s">
         <v>1613</v>
@@ -25669,7 +25669,7 @@
         <v>1588</v>
       </c>
       <c r="E496">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F496" t="s">
         <v>1613</v>
@@ -25704,7 +25704,7 @@
         <v>1588</v>
       </c>
       <c r="E497">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F497" t="s">
         <v>1613</v>
@@ -25739,7 +25739,7 @@
         <v>1589</v>
       </c>
       <c r="E498">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F498" t="s">
         <v>1613</v>
@@ -25774,7 +25774,7 @@
         <v>1589</v>
       </c>
       <c r="E499">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F499" t="s">
         <v>1613</v>
@@ -25809,7 +25809,7 @@
         <v>1590</v>
       </c>
       <c r="E500">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F500" t="s">
         <v>1613</v>
@@ -25844,7 +25844,7 @@
         <v>1590</v>
       </c>
       <c r="E501">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F501" t="s">
         <v>1613</v>
@@ -25879,7 +25879,7 @@
         <v>1590</v>
       </c>
       <c r="E502">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F502" t="s">
         <v>1613</v>
@@ -25914,7 +25914,7 @@
         <v>1590</v>
       </c>
       <c r="E503">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F503" t="s">
         <v>1617</v>
@@ -25952,7 +25952,7 @@
         <v>1590</v>
       </c>
       <c r="E504">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F504" t="s">
         <v>1613</v>
@@ -25987,7 +25987,7 @@
         <v>1590</v>
       </c>
       <c r="E505">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F505" t="s">
         <v>1617</v>
@@ -26022,7 +26022,7 @@
         <v>1591</v>
       </c>
       <c r="E506">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F506" t="s">
         <v>1613</v>
@@ -26057,7 +26057,7 @@
         <v>1592</v>
       </c>
       <c r="E507">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F507" t="s">
         <v>1613</v>
@@ -26092,7 +26092,7 @@
         <v>1592</v>
       </c>
       <c r="E508">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F508" t="s">
         <v>1613</v>
@@ -26127,7 +26127,7 @@
         <v>1592</v>
       </c>
       <c r="E509">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F509" t="s">
         <v>1613</v>
@@ -26162,7 +26162,7 @@
         <v>1592</v>
       </c>
       <c r="E510">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F510" t="s">
         <v>1613</v>
@@ -26197,7 +26197,7 @@
         <v>1593</v>
       </c>
       <c r="E511">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F511" t="s">
         <v>1613</v>
@@ -26232,7 +26232,7 @@
         <v>1593</v>
       </c>
       <c r="E512">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F512" t="s">
         <v>1617</v>
@@ -26267,7 +26267,7 @@
         <v>1593</v>
       </c>
       <c r="E513">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F513" t="s">
         <v>1613</v>
@@ -26302,7 +26302,7 @@
         <v>1593</v>
       </c>
       <c r="E514">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F514" t="s">
         <v>1613</v>
@@ -26337,7 +26337,7 @@
         <v>1593</v>
       </c>
       <c r="E515">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F515" t="s">
         <v>1613</v>
@@ -26372,7 +26372,7 @@
         <v>1594</v>
       </c>
       <c r="E516">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F516" t="s">
         <v>1613</v>
@@ -26407,7 +26407,7 @@
         <v>1594</v>
       </c>
       <c r="E517">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F517" t="s">
         <v>1615</v>
@@ -26442,7 +26442,7 @@
         <v>1594</v>
       </c>
       <c r="E518">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F518" t="s">
         <v>1613</v>
@@ -26477,7 +26477,7 @@
         <v>1594</v>
       </c>
       <c r="E519">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F519" t="s">
         <v>1613</v>
@@ -26512,7 +26512,7 @@
         <v>1595</v>
       </c>
       <c r="E520">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F520" t="s">
         <v>1613</v>
@@ -26547,7 +26547,7 @@
         <v>1595</v>
       </c>
       <c r="E521">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F521" t="s">
         <v>1613</v>
@@ -26582,7 +26582,7 @@
         <v>1595</v>
       </c>
       <c r="E522">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F522" t="s">
         <v>1613</v>
@@ -26617,7 +26617,7 @@
         <v>1595</v>
       </c>
       <c r="E523">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F523" t="s">
         <v>1613</v>
@@ -26652,7 +26652,7 @@
         <v>1595</v>
       </c>
       <c r="E524">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F524" t="s">
         <v>1613</v>
@@ -26687,7 +26687,7 @@
         <v>1595</v>
       </c>
       <c r="E525">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F525" t="s">
         <v>1613</v>
@@ -26722,7 +26722,7 @@
         <v>1596</v>
       </c>
       <c r="E526">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F526" t="s">
         <v>1613</v>
@@ -26757,7 +26757,7 @@
         <v>1596</v>
       </c>
       <c r="E527">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F527" t="s">
         <v>1613</v>
@@ -26792,7 +26792,7 @@
         <v>1596</v>
       </c>
       <c r="E528">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F528" t="s">
         <v>1613</v>
@@ -26827,7 +26827,7 @@
         <v>1596</v>
       </c>
       <c r="E529">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F529" t="s">
         <v>1613</v>
@@ -26862,7 +26862,7 @@
         <v>1596</v>
       </c>
       <c r="E530">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F530" t="s">
         <v>1613</v>
@@ -26897,7 +26897,7 @@
         <v>1596</v>
       </c>
       <c r="E531">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F531" t="s">
         <v>1613</v>
@@ -26932,7 +26932,7 @@
         <v>1596</v>
       </c>
       <c r="E532">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F532" t="s">
         <v>1613</v>
@@ -26967,7 +26967,7 @@
         <v>1596</v>
       </c>
       <c r="E533">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F533" t="s">
         <v>1613</v>
@@ -27002,7 +27002,7 @@
         <v>1596</v>
       </c>
       <c r="E534">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F534" t="s">
         <v>1613</v>
@@ -27037,7 +27037,7 @@
         <v>1596</v>
       </c>
       <c r="E535">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F535" t="s">
         <v>1613</v>
@@ -27072,7 +27072,7 @@
         <v>1596</v>
       </c>
       <c r="E536">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F536" t="s">
         <v>1613</v>
@@ -27107,7 +27107,7 @@
         <v>1596</v>
       </c>
       <c r="E537">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F537" t="s">
         <v>1613</v>
@@ -27142,7 +27142,7 @@
         <v>1596</v>
       </c>
       <c r="E538">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F538" t="s">
         <v>1613</v>
@@ -27177,7 +27177,7 @@
         <v>1596</v>
       </c>
       <c r="E539">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F539" t="s">
         <v>1613</v>
@@ -27212,7 +27212,7 @@
         <v>1596</v>
       </c>
       <c r="E540">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F540" t="s">
         <v>1613</v>
@@ -27247,7 +27247,7 @@
         <v>1596</v>
       </c>
       <c r="E541">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F541" t="s">
         <v>1613</v>
@@ -27282,7 +27282,7 @@
         <v>1596</v>
       </c>
       <c r="E542">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F542" t="s">
         <v>1613</v>
@@ -27317,7 +27317,7 @@
         <v>1596</v>
       </c>
       <c r="E543">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F543" t="s">
         <v>1613</v>
@@ -27352,7 +27352,7 @@
         <v>1596</v>
       </c>
       <c r="E544">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F544" t="s">
         <v>1613</v>
@@ -27387,7 +27387,7 @@
         <v>1596</v>
       </c>
       <c r="E545">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F545" t="s">
         <v>1613</v>
@@ -27422,7 +27422,7 @@
         <v>1596</v>
       </c>
       <c r="E546">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F546" t="s">
         <v>1613</v>
@@ -27457,7 +27457,7 @@
         <v>1596</v>
       </c>
       <c r="E547">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F547" t="s">
         <v>1613</v>
@@ -27492,7 +27492,7 @@
         <v>1596</v>
       </c>
       <c r="E548">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F548" t="s">
         <v>1613</v>
@@ -27527,7 +27527,7 @@
         <v>1596</v>
       </c>
       <c r="E549">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F549" t="s">
         <v>1613</v>
@@ -27562,7 +27562,7 @@
         <v>1596</v>
       </c>
       <c r="E550">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F550" t="s">
         <v>1613</v>
@@ -27597,7 +27597,7 @@
         <v>1596</v>
       </c>
       <c r="E551">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F551" t="s">
         <v>1613</v>
@@ -27632,7 +27632,7 @@
         <v>1596</v>
       </c>
       <c r="E552">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F552" t="s">
         <v>1615</v>
@@ -27670,7 +27670,7 @@
         <v>1597</v>
       </c>
       <c r="E553">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F553" t="s">
         <v>1613</v>
@@ -27705,7 +27705,7 @@
         <v>1597</v>
       </c>
       <c r="E554">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F554" t="s">
         <v>1613</v>
@@ -27740,7 +27740,7 @@
         <v>1597</v>
       </c>
       <c r="E555">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F555" t="s">
         <v>1613</v>
@@ -27775,7 +27775,7 @@
         <v>1597</v>
       </c>
       <c r="E556">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F556" t="s">
         <v>1613</v>
@@ -27810,7 +27810,7 @@
         <v>1597</v>
       </c>
       <c r="E557">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F557" t="s">
         <v>1613</v>
@@ -27845,7 +27845,7 @@
         <v>1597</v>
       </c>
       <c r="E558">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F558" t="s">
         <v>1613</v>
@@ -27880,7 +27880,7 @@
         <v>1597</v>
       </c>
       <c r="E559">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F559" t="s">
         <v>1617</v>
@@ -27915,7 +27915,7 @@
         <v>1597</v>
       </c>
       <c r="E560">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F560" t="s">
         <v>1613</v>
@@ -27950,7 +27950,7 @@
         <v>1598</v>
       </c>
       <c r="E561">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F561" t="s">
         <v>1613</v>
@@ -27985,7 +27985,7 @@
         <v>1598</v>
       </c>
       <c r="E562">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F562" t="s">
         <v>1613</v>
@@ -28020,7 +28020,7 @@
         <v>1599</v>
       </c>
       <c r="E563">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F563" t="s">
         <v>1613</v>
@@ -28055,7 +28055,7 @@
         <v>1599</v>
       </c>
       <c r="E564">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F564" t="s">
         <v>1615</v>
@@ -28093,7 +28093,7 @@
         <v>1600</v>
       </c>
       <c r="E565">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F565" t="s">
         <v>1615</v>
@@ -28131,7 +28131,7 @@
         <v>1600</v>
       </c>
       <c r="E566">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F566" t="s">
         <v>1613</v>
@@ -28166,7 +28166,7 @@
         <v>1600</v>
       </c>
       <c r="E567">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F567" t="s">
         <v>1613</v>
@@ -28201,7 +28201,7 @@
         <v>1600</v>
       </c>
       <c r="E568">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F568" t="s">
         <v>1615</v>
@@ -28239,7 +28239,7 @@
         <v>1600</v>
       </c>
       <c r="E569">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F569" t="s">
         <v>1613</v>
@@ -28274,7 +28274,7 @@
         <v>1600</v>
       </c>
       <c r="E570">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F570" t="s">
         <v>1613</v>
@@ -28309,7 +28309,7 @@
         <v>1600</v>
       </c>
       <c r="E571">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F571" t="s">
         <v>1613</v>
@@ -28344,7 +28344,7 @@
         <v>1600</v>
       </c>
       <c r="E572">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F572" t="s">
         <v>1613</v>
@@ -28382,7 +28382,7 @@
         <v>1600</v>
       </c>
       <c r="E573">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F573" t="s">
         <v>1613</v>
@@ -28417,7 +28417,7 @@
         <v>1600</v>
       </c>
       <c r="E574">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F574" t="s">
         <v>1613</v>
@@ -28452,7 +28452,7 @@
         <v>1601</v>
       </c>
       <c r="E575">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F575" t="s">
         <v>1613</v>
@@ -28490,7 +28490,7 @@
         <v>1601</v>
       </c>
       <c r="E576">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F576" t="s">
         <v>1617</v>
@@ -28525,7 +28525,7 @@
         <v>1601</v>
       </c>
       <c r="E577">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F577" t="s">
         <v>1615</v>
@@ -28560,7 +28560,7 @@
         <v>1601</v>
       </c>
       <c r="E578">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F578" t="s">
         <v>1613</v>
@@ -28595,7 +28595,7 @@
         <v>1601</v>
       </c>
       <c r="E579">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F579" t="s">
         <v>1613</v>
@@ -28630,7 +28630,7 @@
         <v>1601</v>
       </c>
       <c r="E580">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F580" t="s">
         <v>1613</v>
@@ -28665,7 +28665,7 @@
         <v>1601</v>
       </c>
       <c r="E581">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F581" t="s">
         <v>1613</v>
@@ -28700,7 +28700,7 @@
         <v>1601</v>
       </c>
       <c r="E582">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F582" t="s">
         <v>1613</v>
@@ -28735,7 +28735,7 @@
         <v>1601</v>
       </c>
       <c r="E583">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F583" t="s">
         <v>1613</v>
@@ -28770,7 +28770,7 @@
         <v>1602</v>
       </c>
       <c r="E584">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F584" t="s">
         <v>1613</v>
@@ -28808,7 +28808,7 @@
         <v>1602</v>
       </c>
       <c r="E585">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F585" t="s">
         <v>1613</v>
@@ -28843,7 +28843,7 @@
         <v>1603</v>
       </c>
       <c r="E586">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F586" t="s">
         <v>1613</v>
@@ -28878,7 +28878,7 @@
         <v>1603</v>
       </c>
       <c r="E587">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F587" t="s">
         <v>1615</v>
@@ -28916,7 +28916,7 @@
         <v>1603</v>
       </c>
       <c r="E588">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F588" t="s">
         <v>1613</v>
@@ -28951,7 +28951,7 @@
         <v>1603</v>
       </c>
       <c r="E589">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F589" t="s">
         <v>1613</v>
@@ -28986,7 +28986,7 @@
         <v>1603</v>
       </c>
       <c r="E590">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F590" t="s">
         <v>1613</v>
@@ -29021,7 +29021,7 @@
         <v>1603</v>
       </c>
       <c r="E591">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F591" t="s">
         <v>1613</v>
@@ -29056,7 +29056,7 @@
         <v>1603</v>
       </c>
       <c r="E592">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F592" t="s">
         <v>1613</v>
@@ -29091,7 +29091,7 @@
         <v>1603</v>
       </c>
       <c r="E593">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F593" t="s">
         <v>1615</v>
@@ -29126,7 +29126,7 @@
         <v>1603</v>
       </c>
       <c r="E594">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F594" t="s">
         <v>1613</v>
@@ -29161,7 +29161,7 @@
         <v>1603</v>
       </c>
       <c r="E595">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F595" t="s">
         <v>1613</v>
@@ -29196,7 +29196,7 @@
         <v>1604</v>
       </c>
       <c r="E596">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F596" t="s">
         <v>1613</v>
@@ -29231,7 +29231,7 @@
         <v>1604</v>
       </c>
       <c r="E597">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F597" t="s">
         <v>1613</v>
@@ -29266,7 +29266,7 @@
         <v>1604</v>
       </c>
       <c r="E598">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F598" t="s">
         <v>1613</v>
@@ -29301,7 +29301,7 @@
         <v>1604</v>
       </c>
       <c r="E599">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F599" t="s">
         <v>1613</v>
@@ -29336,7 +29336,7 @@
         <v>1604</v>
       </c>
       <c r="E600">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F600" t="s">
         <v>1615</v>
@@ -29374,7 +29374,7 @@
         <v>1604</v>
       </c>
       <c r="E601">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F601" t="s">
         <v>1613</v>
@@ -29409,7 +29409,7 @@
         <v>1604</v>
       </c>
       <c r="E602">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F602" t="s">
         <v>1613</v>
@@ -29444,7 +29444,7 @@
         <v>1604</v>
       </c>
       <c r="E603">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F603" t="s">
         <v>1613</v>
@@ -29479,7 +29479,7 @@
         <v>1604</v>
       </c>
       <c r="E604">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F604" t="s">
         <v>1613</v>
@@ -29514,7 +29514,7 @@
         <v>1604</v>
       </c>
       <c r="E605">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F605" t="s">
         <v>1615</v>
@@ -29549,7 +29549,7 @@
         <v>1604</v>
       </c>
       <c r="E606">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F606" t="s">
         <v>1613</v>
@@ -29584,7 +29584,7 @@
         <v>1604</v>
       </c>
       <c r="E607">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F607" t="s">
         <v>1617</v>
@@ -29619,7 +29619,7 @@
         <v>1604</v>
       </c>
       <c r="E608">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F608" t="s">
         <v>1613</v>
@@ -29654,7 +29654,7 @@
         <v>1605</v>
       </c>
       <c r="E609">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F609" t="s">
         <v>1613</v>
@@ -29689,7 +29689,7 @@
         <v>1605</v>
       </c>
       <c r="E610">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F610" t="s">
         <v>1613</v>
@@ -29724,7 +29724,7 @@
         <v>1605</v>
       </c>
       <c r="E611">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F611" t="s">
         <v>1613</v>
@@ -29759,7 +29759,7 @@
         <v>1605</v>
       </c>
       <c r="E612">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F612" t="s">
         <v>1613</v>
@@ -29794,7 +29794,7 @@
         <v>1605</v>
       </c>
       <c r="E613">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F613" t="s">
         <v>1613</v>
@@ -29829,7 +29829,7 @@
         <v>1605</v>
       </c>
       <c r="E614">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F614" t="s">
         <v>1613</v>
@@ -29864,7 +29864,7 @@
         <v>1605</v>
       </c>
       <c r="E615">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F615" t="s">
         <v>1613</v>
@@ -29899,7 +29899,7 @@
         <v>1605</v>
       </c>
       <c r="E616">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F616" t="s">
         <v>1613</v>
@@ -29934,7 +29934,7 @@
         <v>1605</v>
       </c>
       <c r="E617">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F617" t="s">
         <v>1613</v>
@@ -29972,7 +29972,7 @@
         <v>1605</v>
       </c>
       <c r="E618">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F618" t="s">
         <v>1615</v>
@@ -30010,7 +30010,7 @@
         <v>1605</v>
       </c>
       <c r="E619">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F619" t="s">
         <v>1613</v>
@@ -30045,7 +30045,7 @@
         <v>1605</v>
       </c>
       <c r="E620">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F620" t="s">
         <v>1615</v>
@@ -30080,7 +30080,7 @@
         <v>1605</v>
       </c>
       <c r="E621">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F621" t="s">
         <v>1615</v>
@@ -30115,7 +30115,7 @@
         <v>1605</v>
       </c>
       <c r="E622">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F622" t="s">
         <v>1613</v>
@@ -30150,7 +30150,7 @@
         <v>1606</v>
       </c>
       <c r="E623">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F623" t="s">
         <v>1613</v>
@@ -30185,7 +30185,7 @@
         <v>1606</v>
       </c>
       <c r="E624">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F624" t="s">
         <v>1613</v>
@@ -30220,7 +30220,7 @@
         <v>1606</v>
       </c>
       <c r="E625">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F625" t="s">
         <v>1613</v>
@@ -30255,7 +30255,7 @@
         <v>1606</v>
       </c>
       <c r="E626">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F626" t="s">
         <v>1613</v>
@@ -30290,7 +30290,7 @@
         <v>1606</v>
       </c>
       <c r="E627">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F627" t="s">
         <v>1613</v>
@@ -30325,7 +30325,7 @@
         <v>1606</v>
       </c>
       <c r="E628">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F628" t="s">
         <v>1613</v>
@@ -30360,7 +30360,7 @@
         <v>1606</v>
       </c>
       <c r="E629">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F629" t="s">
         <v>1613</v>
@@ -30395,7 +30395,7 @@
         <v>1606</v>
       </c>
       <c r="E630">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F630" t="s">
         <v>1613</v>
@@ -30430,7 +30430,7 @@
         <v>1606</v>
       </c>
       <c r="E631">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F631" t="s">
         <v>1613</v>
@@ -30465,7 +30465,7 @@
         <v>1606</v>
       </c>
       <c r="E632">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F632" t="s">
         <v>1613</v>
@@ -30503,7 +30503,7 @@
         <v>1607</v>
       </c>
       <c r="E633">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F633" t="s">
         <v>1613</v>
@@ -30538,7 +30538,7 @@
         <v>1607</v>
       </c>
       <c r="E634">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F634" t="s">
         <v>1613</v>
@@ -30573,7 +30573,7 @@
         <v>1608</v>
       </c>
       <c r="E635">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F635" t="s">
         <v>1613</v>
@@ -30611,7 +30611,7 @@
         <v>1608</v>
       </c>
       <c r="E636">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F636" t="s">
         <v>1613</v>
@@ -30646,7 +30646,7 @@
         <v>1608</v>
       </c>
       <c r="E637">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F637" t="s">
         <v>1613</v>
@@ -30681,7 +30681,7 @@
         <v>1608</v>
       </c>
       <c r="E638">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F638" t="s">
         <v>1615</v>
@@ -30719,7 +30719,7 @@
         <v>1608</v>
       </c>
       <c r="E639">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F639" t="s">
         <v>1615</v>
@@ -30757,7 +30757,7 @@
         <v>1608</v>
       </c>
       <c r="E640">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F640" t="s">
         <v>1613</v>
@@ -30792,7 +30792,7 @@
         <v>1608</v>
       </c>
       <c r="E641">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F641" t="s">
         <v>1613</v>
@@ -30827,7 +30827,7 @@
         <v>1608</v>
       </c>
       <c r="E642">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F642" t="s">
         <v>1613</v>
@@ -30862,7 +30862,7 @@
         <v>1609</v>
       </c>
       <c r="E643">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F643" t="s">
         <v>1613</v>
@@ -30897,7 +30897,7 @@
         <v>1609</v>
       </c>
       <c r="E644">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F644" t="s">
         <v>1613</v>
@@ -30932,7 +30932,7 @@
         <v>1609</v>
       </c>
       <c r="E645">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F645" t="s">
         <v>1613</v>
@@ -30967,7 +30967,7 @@
         <v>1609</v>
       </c>
       <c r="E646">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F646" t="s">
         <v>1613</v>
@@ -31002,7 +31002,7 @@
         <v>1609</v>
       </c>
       <c r="E647">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F647" t="s">
         <v>1613</v>
@@ -31037,7 +31037,7 @@
         <v>1609</v>
       </c>
       <c r="E648">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F648" t="s">
         <v>1613</v>
@@ -31072,7 +31072,7 @@
         <v>1609</v>
       </c>
       <c r="E649">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F649" t="s">
         <v>1613</v>
@@ -31107,7 +31107,7 @@
         <v>1609</v>
       </c>
       <c r="E650">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F650" t="s">
         <v>1613</v>
@@ -31142,7 +31142,7 @@
         <v>1609</v>
       </c>
       <c r="E651">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F651" t="s">
         <v>1613</v>
@@ -31177,7 +31177,7 @@
         <v>1609</v>
       </c>
       <c r="E652">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F652" t="s">
         <v>1613</v>
@@ -31212,7 +31212,7 @@
         <v>1609</v>
       </c>
       <c r="E653">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F653" t="s">
         <v>1613</v>
@@ -31247,7 +31247,7 @@
         <v>1609</v>
       </c>
       <c r="E654">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F654" t="s">
         <v>1613</v>
@@ -31282,7 +31282,7 @@
         <v>1609</v>
       </c>
       <c r="E655">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F655" t="s">
         <v>1613</v>
@@ -31320,7 +31320,7 @@
         <v>1609</v>
       </c>
       <c r="E656">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F656" t="s">
         <v>1613</v>
@@ -31358,7 +31358,7 @@
         <v>1609</v>
       </c>
       <c r="E657">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F657" t="s">
         <v>1613</v>
@@ -31393,7 +31393,7 @@
         <v>1610</v>
       </c>
       <c r="E658">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F658" t="s">
         <v>1613</v>
@@ -31428,7 +31428,7 @@
         <v>1610</v>
       </c>
       <c r="E659">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F659" t="s">
         <v>1615</v>
@@ -31466,7 +31466,7 @@
         <v>1610</v>
       </c>
       <c r="E660">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F660" t="s">
         <v>1613</v>
@@ -31501,7 +31501,7 @@
         <v>1610</v>
       </c>
       <c r="E661">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F661" t="s">
         <v>1613</v>
@@ -31536,7 +31536,7 @@
         <v>1611</v>
       </c>
       <c r="E662">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F662" t="s">
         <v>1613</v>
@@ -31571,7 +31571,7 @@
         <v>1611</v>
       </c>
       <c r="E663">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F663" t="s">
         <v>1613</v>
@@ -31606,7 +31606,7 @@
         <v>1611</v>
       </c>
       <c r="E664">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F664" t="s">
         <v>1613</v>
@@ -31641,7 +31641,7 @@
         <v>1611</v>
       </c>
       <c r="E665">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F665" t="s">
         <v>1613</v>
@@ -31676,7 +31676,7 @@
         <v>1611</v>
       </c>
       <c r="E666">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F666" t="s">
         <v>1615</v>
@@ -31714,7 +31714,7 @@
         <v>1611</v>
       </c>
       <c r="E667">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F667" t="s">
         <v>1615</v>
@@ -31752,7 +31752,7 @@
         <v>1611</v>
       </c>
       <c r="E668">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F668" t="s">
         <v>1613</v>
@@ -31787,7 +31787,7 @@
         <v>1611</v>
       </c>
       <c r="E669">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F669" t="s">
         <v>1613</v>
@@ -31822,7 +31822,7 @@
         <v>1611</v>
       </c>
       <c r="E670">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F670" t="s">
         <v>1613</v>
@@ -31857,7 +31857,7 @@
         <v>1611</v>
       </c>
       <c r="E671">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F671" t="s">
         <v>1613</v>
@@ -31892,7 +31892,7 @@
         <v>1611</v>
       </c>
       <c r="E672">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F672" t="s">
         <v>1613</v>
@@ -31927,7 +31927,7 @@
         <v>1611</v>
       </c>
       <c r="E673">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F673" t="s">
         <v>1613</v>
@@ -31962,7 +31962,7 @@
         <v>1612</v>
       </c>
       <c r="E674">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F674" t="s">
         <v>1617</v>
@@ -31997,7 +31997,7 @@
         <v>1612</v>
       </c>
       <c r="E675">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F675" t="s">
         <v>1613</v>
@@ -32032,7 +32032,7 @@
         <v>1612</v>
       </c>
       <c r="E676">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F676" t="s">
         <v>1613</v>
@@ -32067,7 +32067,7 @@
         <v>1612</v>
       </c>
       <c r="E677">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F677" t="s">
         <v>1613</v>
@@ -32102,7 +32102,7 @@
         <v>1612</v>
       </c>
       <c r="E678">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F678" t="s">
         <v>1613</v>
@@ -32137,7 +32137,7 @@
         <v>1612</v>
       </c>
       <c r="E679">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F679" t="s">
         <v>1613</v>
@@ -32172,7 +32172,7 @@
         <v>1612</v>
       </c>
       <c r="E680">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F680" t="s">
         <v>1613</v>
@@ -32207,7 +32207,7 @@
         <v>1612</v>
       </c>
       <c r="E681">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F681" t="s">
         <v>1613</v>
@@ -32242,7 +32242,7 @@
         <v>1612</v>
       </c>
       <c r="E682">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F682" t="s">
         <v>1613</v>

--- a/BacklogGATEAutoCompleto.xlsx
+++ b/BacklogGATEAutoCompleto.xlsx
@@ -8349,7 +8349,7 @@
         <v>1397</v>
       </c>
       <c r="E2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="F2" t="s">
         <v>1613</v>
@@ -8384,7 +8384,7 @@
         <v>1398</v>
       </c>
       <c r="E3">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="F3" t="s">
         <v>1613</v>
@@ -8419,7 +8419,7 @@
         <v>1399</v>
       </c>
       <c r="E4">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="F4" t="s">
         <v>1613</v>
@@ -8454,7 +8454,7 @@
         <v>1400</v>
       </c>
       <c r="E5">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="F5" t="s">
         <v>1613</v>
@@ -8489,7 +8489,7 @@
         <v>1400</v>
       </c>
       <c r="E6">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="F6" t="s">
         <v>1613</v>
@@ -8524,7 +8524,7 @@
         <v>1401</v>
       </c>
       <c r="E7">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="F7" t="s">
         <v>1613</v>
@@ -8559,7 +8559,7 @@
         <v>1402</v>
       </c>
       <c r="E8">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="F8" t="s">
         <v>1613</v>
@@ -8594,7 +8594,7 @@
         <v>1403</v>
       </c>
       <c r="E9">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="F9" t="s">
         <v>1613</v>
@@ -8629,7 +8629,7 @@
         <v>1404</v>
       </c>
       <c r="E10">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="F10" t="s">
         <v>1613</v>
@@ -8664,7 +8664,7 @@
         <v>1405</v>
       </c>
       <c r="E11">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="F11" t="s">
         <v>1613</v>
@@ -8699,7 +8699,7 @@
         <v>1406</v>
       </c>
       <c r="E12">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="F12" t="s">
         <v>1613</v>
@@ -8734,7 +8734,7 @@
         <v>1407</v>
       </c>
       <c r="E13">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="F13" t="s">
         <v>1613</v>
@@ -8769,7 +8769,7 @@
         <v>1407</v>
       </c>
       <c r="E14">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="F14" t="s">
         <v>1613</v>
@@ -8804,7 +8804,7 @@
         <v>1408</v>
       </c>
       <c r="E15">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F15" t="s">
         <v>1613</v>
@@ -8839,7 +8839,7 @@
         <v>1409</v>
       </c>
       <c r="E16">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="F16" t="s">
         <v>1613</v>
@@ -8874,7 +8874,7 @@
         <v>1410</v>
       </c>
       <c r="E17">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="F17" t="s">
         <v>1613</v>
@@ -8909,7 +8909,7 @@
         <v>1410</v>
       </c>
       <c r="E18">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="F18" t="s">
         <v>1613</v>
@@ -8944,7 +8944,7 @@
         <v>1411</v>
       </c>
       <c r="E19">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F19" t="s">
         <v>1613</v>
@@ -8979,7 +8979,7 @@
         <v>1412</v>
       </c>
       <c r="E20">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="F20" t="s">
         <v>1613</v>
@@ -9014,7 +9014,7 @@
         <v>1413</v>
       </c>
       <c r="E21">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="F21" t="s">
         <v>1613</v>
@@ -9049,7 +9049,7 @@
         <v>1413</v>
       </c>
       <c r="E22">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="F22" t="s">
         <v>1613</v>
@@ -9084,7 +9084,7 @@
         <v>1414</v>
       </c>
       <c r="E23">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="F23" t="s">
         <v>1613</v>
@@ -9119,7 +9119,7 @@
         <v>1415</v>
       </c>
       <c r="E24">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="F24" t="s">
         <v>1613</v>
@@ -9154,7 +9154,7 @@
         <v>1416</v>
       </c>
       <c r="E25">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="F25" t="s">
         <v>1613</v>
@@ -9189,7 +9189,7 @@
         <v>1417</v>
       </c>
       <c r="E26">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F26" t="s">
         <v>1613</v>
@@ -9224,7 +9224,7 @@
         <v>1418</v>
       </c>
       <c r="E27">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F27" t="s">
         <v>1613</v>
@@ -9262,7 +9262,7 @@
         <v>1419</v>
       </c>
       <c r="E28">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F28" t="s">
         <v>1613</v>
@@ -9297,7 +9297,7 @@
         <v>1420</v>
       </c>
       <c r="E29">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F29" t="s">
         <v>1613</v>
@@ -9332,7 +9332,7 @@
         <v>1421</v>
       </c>
       <c r="E30">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F30" t="s">
         <v>1613</v>
@@ -9367,7 +9367,7 @@
         <v>1422</v>
       </c>
       <c r="E31">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="F31" t="s">
         <v>1613</v>
@@ -9402,7 +9402,7 @@
         <v>1423</v>
       </c>
       <c r="E32">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F32" t="s">
         <v>1613</v>
@@ -9437,7 +9437,7 @@
         <v>1424</v>
       </c>
       <c r="E33">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F33" t="s">
         <v>1613</v>
@@ -9472,7 +9472,7 @@
         <v>1425</v>
       </c>
       <c r="E34">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="F34" t="s">
         <v>1613</v>
@@ -9507,7 +9507,7 @@
         <v>1426</v>
       </c>
       <c r="E35">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F35" t="s">
         <v>1613</v>
@@ -9542,7 +9542,7 @@
         <v>1427</v>
       </c>
       <c r="E36">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="F36" t="s">
         <v>1613</v>
@@ -9577,7 +9577,7 @@
         <v>1428</v>
       </c>
       <c r="E37">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="F37" t="s">
         <v>1613</v>
@@ -9612,7 +9612,7 @@
         <v>1429</v>
       </c>
       <c r="E38">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F38" t="s">
         <v>1613</v>
@@ -9647,7 +9647,7 @@
         <v>1430</v>
       </c>
       <c r="E39">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F39" t="s">
         <v>1613</v>
@@ -9682,7 +9682,7 @@
         <v>1430</v>
       </c>
       <c r="E40">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F40" t="s">
         <v>1613</v>
@@ -9717,7 +9717,7 @@
         <v>1431</v>
       </c>
       <c r="E41">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F41" t="s">
         <v>1613</v>
@@ -9752,7 +9752,7 @@
         <v>1431</v>
       </c>
       <c r="E42">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F42" t="s">
         <v>1613</v>
@@ -9787,7 +9787,7 @@
         <v>1432</v>
       </c>
       <c r="E43">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F43" t="s">
         <v>1613</v>
@@ -9822,7 +9822,7 @@
         <v>1433</v>
       </c>
       <c r="E44">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F44" t="s">
         <v>1613</v>
@@ -9857,7 +9857,7 @@
         <v>1434</v>
       </c>
       <c r="E45">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F45" t="s">
         <v>1613</v>
@@ -9892,7 +9892,7 @@
         <v>1435</v>
       </c>
       <c r="E46">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F46" t="s">
         <v>1613</v>
@@ -9927,7 +9927,7 @@
         <v>1435</v>
       </c>
       <c r="E47">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F47" t="s">
         <v>1613</v>
@@ -9962,7 +9962,7 @@
         <v>1436</v>
       </c>
       <c r="E48">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F48" t="s">
         <v>1613</v>
@@ -9997,7 +9997,7 @@
         <v>1437</v>
       </c>
       <c r="E49">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F49" t="s">
         <v>1613</v>
@@ -10032,7 +10032,7 @@
         <v>1437</v>
       </c>
       <c r="E50">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F50" t="s">
         <v>1613</v>
@@ -10067,7 +10067,7 @@
         <v>1438</v>
       </c>
       <c r="E51">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F51" t="s">
         <v>1613</v>
@@ -10102,7 +10102,7 @@
         <v>1438</v>
       </c>
       <c r="E52">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F52" t="s">
         <v>1613</v>
@@ -10137,7 +10137,7 @@
         <v>1439</v>
       </c>
       <c r="E53">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F53" t="s">
         <v>1613</v>
@@ -10172,7 +10172,7 @@
         <v>1440</v>
       </c>
       <c r="E54">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F54" t="s">
         <v>1613</v>
@@ -10207,7 +10207,7 @@
         <v>1441</v>
       </c>
       <c r="E55">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F55" t="s">
         <v>1613</v>
@@ -10242,7 +10242,7 @@
         <v>1442</v>
       </c>
       <c r="E56">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F56" t="s">
         <v>1613</v>
@@ -10277,7 +10277,7 @@
         <v>1443</v>
       </c>
       <c r="E57">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F57" t="s">
         <v>1613</v>
@@ -10312,7 +10312,7 @@
         <v>1444</v>
       </c>
       <c r="E58">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F58" t="s">
         <v>1613</v>
@@ -10347,7 +10347,7 @@
         <v>1445</v>
       </c>
       <c r="E59">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F59" t="s">
         <v>1613</v>
@@ -10382,7 +10382,7 @@
         <v>1446</v>
       </c>
       <c r="E60">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F60" t="s">
         <v>1613</v>
@@ -10417,7 +10417,7 @@
         <v>1447</v>
       </c>
       <c r="E61">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F61" t="s">
         <v>1613</v>
@@ -10452,7 +10452,7 @@
         <v>1448</v>
       </c>
       <c r="E62">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F62" t="s">
         <v>1613</v>
@@ -10487,7 +10487,7 @@
         <v>1449</v>
       </c>
       <c r="E63">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F63" t="s">
         <v>1613</v>
@@ -10522,7 +10522,7 @@
         <v>1450</v>
       </c>
       <c r="E64">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F64" t="s">
         <v>1613</v>
@@ -10557,7 +10557,7 @@
         <v>1451</v>
       </c>
       <c r="E65">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F65" t="s">
         <v>1613</v>
@@ -10592,7 +10592,7 @@
         <v>1452</v>
       </c>
       <c r="E66">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F66" t="s">
         <v>1613</v>
@@ -10627,7 +10627,7 @@
         <v>1453</v>
       </c>
       <c r="E67">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F67" t="s">
         <v>1613</v>
@@ -10662,7 +10662,7 @@
         <v>1454</v>
       </c>
       <c r="E68">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F68" t="s">
         <v>1613</v>
@@ -10697,7 +10697,7 @@
         <v>1454</v>
       </c>
       <c r="E69">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F69" t="s">
         <v>1613</v>
@@ -10732,7 +10732,7 @@
         <v>1454</v>
       </c>
       <c r="E70">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F70" t="s">
         <v>1613</v>
@@ -10767,7 +10767,7 @@
         <v>1455</v>
       </c>
       <c r="E71">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F71" t="s">
         <v>1613</v>
@@ -10802,7 +10802,7 @@
         <v>1456</v>
       </c>
       <c r="E72">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F72" t="s">
         <v>1613</v>
@@ -10837,7 +10837,7 @@
         <v>1457</v>
       </c>
       <c r="E73">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F73" t="s">
         <v>1613</v>
@@ -10872,7 +10872,7 @@
         <v>1458</v>
       </c>
       <c r="E74">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F74" t="s">
         <v>1613</v>
@@ -10907,7 +10907,7 @@
         <v>1458</v>
       </c>
       <c r="E75">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F75" t="s">
         <v>1613</v>
@@ -10942,7 +10942,7 @@
         <v>1458</v>
       </c>
       <c r="E76">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F76" t="s">
         <v>1613</v>
@@ -10977,7 +10977,7 @@
         <v>1459</v>
       </c>
       <c r="E77">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F77" t="s">
         <v>1613</v>
@@ -11012,7 +11012,7 @@
         <v>1460</v>
       </c>
       <c r="E78">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F78" t="s">
         <v>1613</v>
@@ -11047,7 +11047,7 @@
         <v>1461</v>
       </c>
       <c r="E79">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F79" t="s">
         <v>1613</v>
@@ -11082,7 +11082,7 @@
         <v>1461</v>
       </c>
       <c r="E80">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F80" t="s">
         <v>1613</v>
@@ -11117,7 +11117,7 @@
         <v>1461</v>
       </c>
       <c r="E81">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F81" t="s">
         <v>1613</v>
@@ -11152,7 +11152,7 @@
         <v>1462</v>
       </c>
       <c r="E82">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F82" t="s">
         <v>1613</v>
@@ -11187,7 +11187,7 @@
         <v>1463</v>
       </c>
       <c r="E83">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F83" t="s">
         <v>1613</v>
@@ -11222,7 +11222,7 @@
         <v>1463</v>
       </c>
       <c r="E84">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F84" t="s">
         <v>1613</v>
@@ -11257,7 +11257,7 @@
         <v>1463</v>
       </c>
       <c r="E85">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F85" t="s">
         <v>1614</v>
@@ -11292,7 +11292,7 @@
         <v>1463</v>
       </c>
       <c r="E86">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F86" t="s">
         <v>1613</v>
@@ -11327,7 +11327,7 @@
         <v>1464</v>
       </c>
       <c r="E87">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F87" t="s">
         <v>1613</v>
@@ -11362,7 +11362,7 @@
         <v>1465</v>
       </c>
       <c r="E88">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F88" t="s">
         <v>1613</v>
@@ -11397,7 +11397,7 @@
         <v>1465</v>
       </c>
       <c r="E89">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F89" t="s">
         <v>1613</v>
@@ -11432,7 +11432,7 @@
         <v>1466</v>
       </c>
       <c r="E90">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F90" t="s">
         <v>1613</v>
@@ -11467,7 +11467,7 @@
         <v>1467</v>
       </c>
       <c r="E91">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F91" t="s">
         <v>1613</v>
@@ -11502,7 +11502,7 @@
         <v>1468</v>
       </c>
       <c r="E92">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F92" t="s">
         <v>1613</v>
@@ -11537,7 +11537,7 @@
         <v>1469</v>
       </c>
       <c r="E93">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F93" t="s">
         <v>1613</v>
@@ -11572,7 +11572,7 @@
         <v>1470</v>
       </c>
       <c r="E94">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F94" t="s">
         <v>1613</v>
@@ -11607,7 +11607,7 @@
         <v>1470</v>
       </c>
       <c r="E95">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F95" t="s">
         <v>1613</v>
@@ -11642,7 +11642,7 @@
         <v>1470</v>
       </c>
       <c r="E96">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F96" t="s">
         <v>1613</v>
@@ -11677,7 +11677,7 @@
         <v>1470</v>
       </c>
       <c r="E97">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F97" t="s">
         <v>1613</v>
@@ -11712,7 +11712,7 @@
         <v>1470</v>
       </c>
       <c r="E98">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F98" t="s">
         <v>1613</v>
@@ -11747,7 +11747,7 @@
         <v>1470</v>
       </c>
       <c r="E99">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F99" t="s">
         <v>1613</v>
@@ -11782,7 +11782,7 @@
         <v>1470</v>
       </c>
       <c r="E100">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F100" t="s">
         <v>1613</v>
@@ -11817,7 +11817,7 @@
         <v>1471</v>
       </c>
       <c r="E101">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F101" t="s">
         <v>1613</v>
@@ -11852,7 +11852,7 @@
         <v>1471</v>
       </c>
       <c r="E102">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F102" t="s">
         <v>1613</v>
@@ -11887,7 +11887,7 @@
         <v>1472</v>
       </c>
       <c r="E103">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F103" t="s">
         <v>1613</v>
@@ -11922,7 +11922,7 @@
         <v>1473</v>
       </c>
       <c r="E104">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F104" t="s">
         <v>1613</v>
@@ -11957,7 +11957,7 @@
         <v>1473</v>
       </c>
       <c r="E105">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F105" t="s">
         <v>1613</v>
@@ -11992,7 +11992,7 @@
         <v>1474</v>
       </c>
       <c r="E106">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F106" t="s">
         <v>1613</v>
@@ -12027,7 +12027,7 @@
         <v>1474</v>
       </c>
       <c r="E107">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F107" t="s">
         <v>1615</v>
@@ -12062,7 +12062,7 @@
         <v>1475</v>
       </c>
       <c r="E108">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F108" t="s">
         <v>1613</v>
@@ -12097,7 +12097,7 @@
         <v>1476</v>
       </c>
       <c r="E109">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F109" t="s">
         <v>1613</v>
@@ -12132,7 +12132,7 @@
         <v>1477</v>
       </c>
       <c r="E110">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F110" t="s">
         <v>1613</v>
@@ -12167,7 +12167,7 @@
         <v>1477</v>
       </c>
       <c r="E111">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F111" t="s">
         <v>1613</v>
@@ -12202,7 +12202,7 @@
         <v>1478</v>
       </c>
       <c r="E112">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F112" t="s">
         <v>1613</v>
@@ -12237,7 +12237,7 @@
         <v>1479</v>
       </c>
       <c r="E113">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F113" t="s">
         <v>1613</v>
@@ -12272,7 +12272,7 @@
         <v>1480</v>
       </c>
       <c r="E114">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F114" t="s">
         <v>1613</v>
@@ -12307,7 +12307,7 @@
         <v>1481</v>
       </c>
       <c r="E115">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F115" t="s">
         <v>1613</v>
@@ -12342,7 +12342,7 @@
         <v>1482</v>
       </c>
       <c r="E116">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F116" t="s">
         <v>1613</v>
@@ -12377,7 +12377,7 @@
         <v>1482</v>
       </c>
       <c r="E117">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F117" t="s">
         <v>1613</v>
@@ -12412,7 +12412,7 @@
         <v>1483</v>
       </c>
       <c r="E118">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F118" t="s">
         <v>1613</v>
@@ -12447,7 +12447,7 @@
         <v>1483</v>
       </c>
       <c r="E119">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F119" t="s">
         <v>1613</v>
@@ -12482,7 +12482,7 @@
         <v>1483</v>
       </c>
       <c r="E120">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F120" t="s">
         <v>1613</v>
@@ -12517,7 +12517,7 @@
         <v>1483</v>
       </c>
       <c r="E121">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F121" t="s">
         <v>1613</v>
@@ -12552,7 +12552,7 @@
         <v>1484</v>
       </c>
       <c r="E122">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F122" t="s">
         <v>1613</v>
@@ -12587,7 +12587,7 @@
         <v>1484</v>
       </c>
       <c r="E123">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F123" t="s">
         <v>1613</v>
@@ -12622,7 +12622,7 @@
         <v>1484</v>
       </c>
       <c r="E124">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F124" t="s">
         <v>1613</v>
@@ -12657,7 +12657,7 @@
         <v>1484</v>
       </c>
       <c r="E125">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F125" t="s">
         <v>1613</v>
@@ -12692,7 +12692,7 @@
         <v>1484</v>
       </c>
       <c r="E126">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F126" t="s">
         <v>1613</v>
@@ -12727,7 +12727,7 @@
         <v>1485</v>
       </c>
       <c r="E127">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F127" t="s">
         <v>1613</v>
@@ -12762,7 +12762,7 @@
         <v>1486</v>
       </c>
       <c r="E128">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F128" t="s">
         <v>1613</v>
@@ -12797,7 +12797,7 @@
         <v>1486</v>
       </c>
       <c r="E129">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F129" t="s">
         <v>1613</v>
@@ -12832,7 +12832,7 @@
         <v>1487</v>
       </c>
       <c r="E130">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F130" t="s">
         <v>1613</v>
@@ -12867,7 +12867,7 @@
         <v>1488</v>
       </c>
       <c r="E131">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F131" t="s">
         <v>1613</v>
@@ -12902,7 +12902,7 @@
         <v>1488</v>
       </c>
       <c r="E132">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F132" t="s">
         <v>1613</v>
@@ -12937,7 +12937,7 @@
         <v>1488</v>
       </c>
       <c r="E133">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F133" t="s">
         <v>1613</v>
@@ -12972,7 +12972,7 @@
         <v>1489</v>
       </c>
       <c r="E134">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F134" t="s">
         <v>1613</v>
@@ -13007,7 +13007,7 @@
         <v>1489</v>
       </c>
       <c r="E135">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F135" t="s">
         <v>1613</v>
@@ -13042,7 +13042,7 @@
         <v>1489</v>
       </c>
       <c r="E136">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F136" t="s">
         <v>1613</v>
@@ -13077,7 +13077,7 @@
         <v>1490</v>
       </c>
       <c r="E137">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F137" t="s">
         <v>1613</v>
@@ -13112,7 +13112,7 @@
         <v>1490</v>
       </c>
       <c r="E138">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F138" t="s">
         <v>1613</v>
@@ -13147,7 +13147,7 @@
         <v>1490</v>
       </c>
       <c r="E139">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F139" t="s">
         <v>1613</v>
@@ -13182,7 +13182,7 @@
         <v>1491</v>
       </c>
       <c r="E140">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F140" t="s">
         <v>1613</v>
@@ -13217,7 +13217,7 @@
         <v>1491</v>
       </c>
       <c r="E141">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F141" t="s">
         <v>1613</v>
@@ -13252,7 +13252,7 @@
         <v>1492</v>
       </c>
       <c r="E142">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F142" t="s">
         <v>1613</v>
@@ -13287,7 +13287,7 @@
         <v>1493</v>
       </c>
       <c r="E143">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F143" t="s">
         <v>1613</v>
@@ -13322,7 +13322,7 @@
         <v>1493</v>
       </c>
       <c r="E144">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F144" t="s">
         <v>1613</v>
@@ -13357,7 +13357,7 @@
         <v>1493</v>
       </c>
       <c r="E145">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F145" t="s">
         <v>1613</v>
@@ -13392,7 +13392,7 @@
         <v>1494</v>
       </c>
       <c r="E146">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F146" t="s">
         <v>1613</v>
@@ -13427,7 +13427,7 @@
         <v>1494</v>
       </c>
       <c r="E147">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F147" t="s">
         <v>1613</v>
@@ -13462,7 +13462,7 @@
         <v>1495</v>
       </c>
       <c r="E148">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F148" t="s">
         <v>1613</v>
@@ -13500,7 +13500,7 @@
         <v>1495</v>
       </c>
       <c r="E149">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F149" t="s">
         <v>1613</v>
@@ -13535,7 +13535,7 @@
         <v>1495</v>
       </c>
       <c r="E150">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F150" t="s">
         <v>1613</v>
@@ -13570,7 +13570,7 @@
         <v>1495</v>
       </c>
       <c r="E151">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F151" t="s">
         <v>1613</v>
@@ -13605,7 +13605,7 @@
         <v>1495</v>
       </c>
       <c r="E152">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F152" t="s">
         <v>1613</v>
@@ -13640,7 +13640,7 @@
         <v>1496</v>
       </c>
       <c r="E153">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F153" t="s">
         <v>1613</v>
@@ -13675,7 +13675,7 @@
         <v>1497</v>
       </c>
       <c r="E154">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F154" t="s">
         <v>1614</v>
@@ -13710,7 +13710,7 @@
         <v>1498</v>
       </c>
       <c r="E155">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F155" t="s">
         <v>1613</v>
@@ -13745,7 +13745,7 @@
         <v>1498</v>
       </c>
       <c r="E156">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F156" t="s">
         <v>1613</v>
@@ -13780,7 +13780,7 @@
         <v>1498</v>
       </c>
       <c r="E157">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F157" t="s">
         <v>1613</v>
@@ -13815,7 +13815,7 @@
         <v>1498</v>
       </c>
       <c r="E158">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F158" t="s">
         <v>1613</v>
@@ -13850,7 +13850,7 @@
         <v>1499</v>
       </c>
       <c r="E159">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F159" t="s">
         <v>1613</v>
@@ -13885,7 +13885,7 @@
         <v>1499</v>
       </c>
       <c r="E160">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F160" t="s">
         <v>1613</v>
@@ -13920,7 +13920,7 @@
         <v>1499</v>
       </c>
       <c r="E161">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F161" t="s">
         <v>1613</v>
@@ -13955,7 +13955,7 @@
         <v>1499</v>
       </c>
       <c r="E162">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F162" t="s">
         <v>1613</v>
@@ -13990,7 +13990,7 @@
         <v>1499</v>
       </c>
       <c r="E163">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F163" t="s">
         <v>1613</v>
@@ -14025,7 +14025,7 @@
         <v>1499</v>
       </c>
       <c r="E164">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F164" t="s">
         <v>1613</v>
@@ -14060,7 +14060,7 @@
         <v>1499</v>
       </c>
       <c r="E165">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F165" t="s">
         <v>1613</v>
@@ -14095,7 +14095,7 @@
         <v>1500</v>
       </c>
       <c r="E166">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F166" t="s">
         <v>1613</v>
@@ -14130,7 +14130,7 @@
         <v>1500</v>
       </c>
       <c r="E167">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F167" t="s">
         <v>1613</v>
@@ -14165,7 +14165,7 @@
         <v>1501</v>
       </c>
       <c r="E168">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F168" t="s">
         <v>1613</v>
@@ -14200,7 +14200,7 @@
         <v>1501</v>
       </c>
       <c r="E169">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F169" t="s">
         <v>1613</v>
@@ -14235,7 +14235,7 @@
         <v>1501</v>
       </c>
       <c r="E170">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F170" t="s">
         <v>1613</v>
@@ -14270,7 +14270,7 @@
         <v>1502</v>
       </c>
       <c r="E171">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F171" t="s">
         <v>1613</v>
@@ -14305,7 +14305,7 @@
         <v>1502</v>
       </c>
       <c r="E172">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F172" t="s">
         <v>1613</v>
@@ -14340,7 +14340,7 @@
         <v>1502</v>
       </c>
       <c r="E173">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F173" t="s">
         <v>1613</v>
@@ -14375,7 +14375,7 @@
         <v>1502</v>
       </c>
       <c r="E174">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F174" t="s">
         <v>1613</v>
@@ -14410,7 +14410,7 @@
         <v>1503</v>
       </c>
       <c r="E175">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F175" t="s">
         <v>1613</v>
@@ -14445,7 +14445,7 @@
         <v>1503</v>
       </c>
       <c r="E176">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F176" t="s">
         <v>1613</v>
@@ -14480,7 +14480,7 @@
         <v>1503</v>
       </c>
       <c r="E177">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F177" t="s">
         <v>1613</v>
@@ -14515,7 +14515,7 @@
         <v>1503</v>
       </c>
       <c r="E178">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F178" t="s">
         <v>1613</v>
@@ -14550,7 +14550,7 @@
         <v>1503</v>
       </c>
       <c r="E179">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F179" t="s">
         <v>1613</v>
@@ -14585,7 +14585,7 @@
         <v>1503</v>
       </c>
       <c r="E180">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F180" t="s">
         <v>1613</v>
@@ -14620,7 +14620,7 @@
         <v>1503</v>
       </c>
       <c r="E181">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F181" t="s">
         <v>1613</v>
@@ -14655,7 +14655,7 @@
         <v>1503</v>
       </c>
       <c r="E182">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F182" t="s">
         <v>1613</v>
@@ -14690,7 +14690,7 @@
         <v>1503</v>
       </c>
       <c r="E183">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F183" t="s">
         <v>1613</v>
@@ -14725,7 +14725,7 @@
         <v>1503</v>
       </c>
       <c r="E184">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F184" t="s">
         <v>1613</v>
@@ -14760,7 +14760,7 @@
         <v>1504</v>
       </c>
       <c r="E185">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F185" t="s">
         <v>1613</v>
@@ -14795,7 +14795,7 @@
         <v>1504</v>
       </c>
       <c r="E186">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F186" t="s">
         <v>1613</v>
@@ -14830,7 +14830,7 @@
         <v>1504</v>
       </c>
       <c r="E187">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F187" t="s">
         <v>1613</v>
@@ -14865,7 +14865,7 @@
         <v>1504</v>
       </c>
       <c r="E188">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F188" t="s">
         <v>1616</v>
@@ -14900,7 +14900,7 @@
         <v>1505</v>
       </c>
       <c r="E189">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F189" t="s">
         <v>1613</v>
@@ -14935,7 +14935,7 @@
         <v>1505</v>
       </c>
       <c r="E190">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F190" t="s">
         <v>1614</v>
@@ -14970,7 +14970,7 @@
         <v>1505</v>
       </c>
       <c r="E191">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F191" t="s">
         <v>1613</v>
@@ -15005,7 +15005,7 @@
         <v>1506</v>
       </c>
       <c r="E192">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F192" t="s">
         <v>1613</v>
@@ -15040,7 +15040,7 @@
         <v>1506</v>
       </c>
       <c r="E193">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F193" t="s">
         <v>1613</v>
@@ -15075,7 +15075,7 @@
         <v>1507</v>
       </c>
       <c r="E194">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F194" t="s">
         <v>1613</v>
@@ -15110,7 +15110,7 @@
         <v>1507</v>
       </c>
       <c r="E195">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F195" t="s">
         <v>1613</v>
@@ -15145,7 +15145,7 @@
         <v>1508</v>
       </c>
       <c r="E196">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F196" t="s">
         <v>1613</v>
@@ -15180,7 +15180,7 @@
         <v>1508</v>
       </c>
       <c r="E197">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F197" t="s">
         <v>1613</v>
@@ -15215,7 +15215,7 @@
         <v>1508</v>
       </c>
       <c r="E198">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F198" t="s">
         <v>1613</v>
@@ -15250,7 +15250,7 @@
         <v>1509</v>
       </c>
       <c r="E199">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F199" t="s">
         <v>1613</v>
@@ -15285,7 +15285,7 @@
         <v>1509</v>
       </c>
       <c r="E200">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F200" t="s">
         <v>1613</v>
@@ -15320,7 +15320,7 @@
         <v>1509</v>
       </c>
       <c r="E201">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F201" t="s">
         <v>1613</v>
@@ -15355,7 +15355,7 @@
         <v>1509</v>
       </c>
       <c r="E202">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F202" t="s">
         <v>1613</v>
@@ -15390,7 +15390,7 @@
         <v>1509</v>
       </c>
       <c r="E203">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F203" t="s">
         <v>1613</v>
@@ -15425,7 +15425,7 @@
         <v>1510</v>
       </c>
       <c r="E204">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F204" t="s">
         <v>1613</v>
@@ -15460,7 +15460,7 @@
         <v>1510</v>
       </c>
       <c r="E205">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F205" t="s">
         <v>1613</v>
@@ -15495,7 +15495,7 @@
         <v>1511</v>
       </c>
       <c r="E206">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F206" t="s">
         <v>1613</v>
@@ -15530,7 +15530,7 @@
         <v>1512</v>
       </c>
       <c r="E207">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F207" t="s">
         <v>1613</v>
@@ -15565,7 +15565,7 @@
         <v>1512</v>
       </c>
       <c r="E208">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F208" t="s">
         <v>1613</v>
@@ -15600,7 +15600,7 @@
         <v>1512</v>
       </c>
       <c r="E209">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F209" t="s">
         <v>1613</v>
@@ -15635,7 +15635,7 @@
         <v>1512</v>
       </c>
       <c r="E210">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F210" t="s">
         <v>1613</v>
@@ -15670,7 +15670,7 @@
         <v>1513</v>
       </c>
       <c r="E211">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F211" t="s">
         <v>1613</v>
@@ -15705,7 +15705,7 @@
         <v>1514</v>
       </c>
       <c r="E212">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F212" t="s">
         <v>1613</v>
@@ -15740,7 +15740,7 @@
         <v>1514</v>
       </c>
       <c r="E213">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F213" t="s">
         <v>1613</v>
@@ -15775,7 +15775,7 @@
         <v>1514</v>
       </c>
       <c r="E214">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F214" t="s">
         <v>1613</v>
@@ -15810,7 +15810,7 @@
         <v>1514</v>
       </c>
       <c r="E215">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F215" t="s">
         <v>1613</v>
@@ -15845,7 +15845,7 @@
         <v>1514</v>
       </c>
       <c r="E216">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F216" t="s">
         <v>1613</v>
@@ -15880,7 +15880,7 @@
         <v>1515</v>
       </c>
       <c r="E217">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F217" t="s">
         <v>1613</v>
@@ -15915,7 +15915,7 @@
         <v>1515</v>
       </c>
       <c r="E218">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F218" t="s">
         <v>1613</v>
@@ -15950,7 +15950,7 @@
         <v>1515</v>
       </c>
       <c r="E219">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F219" t="s">
         <v>1613</v>
@@ -15985,7 +15985,7 @@
         <v>1515</v>
       </c>
       <c r="E220">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F220" t="s">
         <v>1613</v>
@@ -16020,7 +16020,7 @@
         <v>1515</v>
       </c>
       <c r="E221">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F221" t="s">
         <v>1613</v>
@@ -16055,7 +16055,7 @@
         <v>1515</v>
       </c>
       <c r="E222">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F222" t="s">
         <v>1613</v>
@@ -16090,7 +16090,7 @@
         <v>1515</v>
       </c>
       <c r="E223">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F223" t="s">
         <v>1613</v>
@@ -16125,7 +16125,7 @@
         <v>1516</v>
       </c>
       <c r="E224">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F224" t="s">
         <v>1613</v>
@@ -16160,7 +16160,7 @@
         <v>1516</v>
       </c>
       <c r="E225">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F225" t="s">
         <v>1613</v>
@@ -16195,7 +16195,7 @@
         <v>1516</v>
       </c>
       <c r="E226">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F226" t="s">
         <v>1613</v>
@@ -16230,7 +16230,7 @@
         <v>1516</v>
       </c>
       <c r="E227">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F227" t="s">
         <v>1613</v>
@@ -16265,7 +16265,7 @@
         <v>1517</v>
       </c>
       <c r="E228">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F228" t="s">
         <v>1613</v>
@@ -16300,7 +16300,7 @@
         <v>1517</v>
       </c>
       <c r="E229">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F229" t="s">
         <v>1613</v>
@@ -16335,7 +16335,7 @@
         <v>1517</v>
       </c>
       <c r="E230">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F230" t="s">
         <v>1613</v>
@@ -16370,7 +16370,7 @@
         <v>1518</v>
       </c>
       <c r="E231">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F231" t="s">
         <v>1613</v>
@@ -16405,7 +16405,7 @@
         <v>1518</v>
       </c>
       <c r="E232">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F232" t="s">
         <v>1613</v>
@@ -16440,7 +16440,7 @@
         <v>1519</v>
       </c>
       <c r="E233">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F233" t="s">
         <v>1613</v>
@@ -16475,7 +16475,7 @@
         <v>1519</v>
       </c>
       <c r="E234">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F234" t="s">
         <v>1613</v>
@@ -16510,7 +16510,7 @@
         <v>1520</v>
       </c>
       <c r="E235">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F235" t="s">
         <v>1613</v>
@@ -16545,7 +16545,7 @@
         <v>1520</v>
       </c>
       <c r="E236">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F236" t="s">
         <v>1613</v>
@@ -16580,7 +16580,7 @@
         <v>1521</v>
       </c>
       <c r="E237">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F237" t="s">
         <v>1613</v>
@@ -16615,7 +16615,7 @@
         <v>1521</v>
       </c>
       <c r="E238">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F238" t="s">
         <v>1613</v>
@@ -16650,7 +16650,7 @@
         <v>1522</v>
       </c>
       <c r="E239">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F239" t="s">
         <v>1613</v>
@@ -16685,7 +16685,7 @@
         <v>1522</v>
       </c>
       <c r="E240">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F240" t="s">
         <v>1613</v>
@@ -16720,7 +16720,7 @@
         <v>1523</v>
       </c>
       <c r="E241">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F241" t="s">
         <v>1613</v>
@@ -16755,7 +16755,7 @@
         <v>1524</v>
       </c>
       <c r="E242">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F242" t="s">
         <v>1613</v>
@@ -16790,7 +16790,7 @@
         <v>1524</v>
       </c>
       <c r="E243">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F243" t="s">
         <v>1613</v>
@@ -16825,7 +16825,7 @@
         <v>1524</v>
       </c>
       <c r="E244">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F244" t="s">
         <v>1613</v>
@@ -16860,7 +16860,7 @@
         <v>1525</v>
       </c>
       <c r="E245">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F245" t="s">
         <v>1613</v>
@@ -16895,7 +16895,7 @@
         <v>1525</v>
       </c>
       <c r="E246">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F246" t="s">
         <v>1613</v>
@@ -16930,7 +16930,7 @@
         <v>1526</v>
       </c>
       <c r="E247">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F247" t="s">
         <v>1613</v>
@@ -16965,7 +16965,7 @@
         <v>1527</v>
       </c>
       <c r="E248">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F248" t="s">
         <v>1613</v>
@@ -17000,7 +17000,7 @@
         <v>1527</v>
       </c>
       <c r="E249">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F249" t="s">
         <v>1613</v>
@@ -17035,7 +17035,7 @@
         <v>1527</v>
       </c>
       <c r="E250">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F250" t="s">
         <v>1613</v>
@@ -17070,7 +17070,7 @@
         <v>1528</v>
       </c>
       <c r="E251">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F251" t="s">
         <v>1613</v>
@@ -17105,7 +17105,7 @@
         <v>1528</v>
       </c>
       <c r="E252">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F252" t="s">
         <v>1613</v>
@@ -17140,7 +17140,7 @@
         <v>1529</v>
       </c>
       <c r="E253">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F253" t="s">
         <v>1613</v>
@@ -17175,7 +17175,7 @@
         <v>1529</v>
       </c>
       <c r="E254">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F254" t="s">
         <v>1613</v>
@@ -17210,7 +17210,7 @@
         <v>1529</v>
       </c>
       <c r="E255">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F255" t="s">
         <v>1615</v>
@@ -17245,7 +17245,7 @@
         <v>1529</v>
       </c>
       <c r="E256">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F256" t="s">
         <v>1613</v>
@@ -17280,7 +17280,7 @@
         <v>1529</v>
       </c>
       <c r="E257">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F257" t="s">
         <v>1613</v>
@@ -17315,7 +17315,7 @@
         <v>1530</v>
       </c>
       <c r="E258">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F258" t="s">
         <v>1613</v>
@@ -17350,7 +17350,7 @@
         <v>1530</v>
       </c>
       <c r="E259">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F259" t="s">
         <v>1613</v>
@@ -17385,7 +17385,7 @@
         <v>1530</v>
       </c>
       <c r="E260">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F260" t="s">
         <v>1613</v>
@@ -17423,7 +17423,7 @@
         <v>1530</v>
       </c>
       <c r="E261">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F261" t="s">
         <v>1613</v>
@@ -17458,7 +17458,7 @@
         <v>1530</v>
       </c>
       <c r="E262">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F262" t="s">
         <v>1613</v>
@@ -17493,7 +17493,7 @@
         <v>1530</v>
       </c>
       <c r="E263">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F263" t="s">
         <v>1613</v>
@@ -17528,7 +17528,7 @@
         <v>1530</v>
       </c>
       <c r="E264">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F264" t="s">
         <v>1613</v>
@@ -17563,7 +17563,7 @@
         <v>1531</v>
       </c>
       <c r="E265">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F265" t="s">
         <v>1613</v>
@@ -17598,7 +17598,7 @@
         <v>1531</v>
       </c>
       <c r="E266">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F266" t="s">
         <v>1613</v>
@@ -17633,7 +17633,7 @@
         <v>1531</v>
       </c>
       <c r="E267">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F267" t="s">
         <v>1613</v>
@@ -17668,7 +17668,7 @@
         <v>1532</v>
       </c>
       <c r="E268">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F268" t="s">
         <v>1613</v>
@@ -17703,7 +17703,7 @@
         <v>1532</v>
       </c>
       <c r="E269">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F269" t="s">
         <v>1613</v>
@@ -17738,7 +17738,7 @@
         <v>1532</v>
       </c>
       <c r="E270">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F270" t="s">
         <v>1613</v>
@@ -17773,7 +17773,7 @@
         <v>1532</v>
       </c>
       <c r="E271">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F271" t="s">
         <v>1613</v>
@@ -17808,7 +17808,7 @@
         <v>1533</v>
       </c>
       <c r="E272">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F272" t="s">
         <v>1613</v>
@@ -17843,7 +17843,7 @@
         <v>1533</v>
       </c>
       <c r="E273">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F273" t="s">
         <v>1613</v>
@@ -17878,7 +17878,7 @@
         <v>1533</v>
       </c>
       <c r="E274">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F274" t="s">
         <v>1613</v>
@@ -17913,7 +17913,7 @@
         <v>1533</v>
       </c>
       <c r="E275">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F275" t="s">
         <v>1613</v>
@@ -17948,7 +17948,7 @@
         <v>1533</v>
       </c>
       <c r="E276">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F276" t="s">
         <v>1613</v>
@@ -17983,7 +17983,7 @@
         <v>1533</v>
       </c>
       <c r="E277">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F277" t="s">
         <v>1613</v>
@@ -18018,7 +18018,7 @@
         <v>1534</v>
       </c>
       <c r="E278">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F278" t="s">
         <v>1613</v>
@@ -18053,7 +18053,7 @@
         <v>1534</v>
       </c>
       <c r="E279">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F279" t="s">
         <v>1613</v>
@@ -18088,7 +18088,7 @@
         <v>1534</v>
       </c>
       <c r="E280">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F280" t="s">
         <v>1613</v>
@@ -18123,7 +18123,7 @@
         <v>1534</v>
       </c>
       <c r="E281">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F281" t="s">
         <v>1613</v>
@@ -18158,7 +18158,7 @@
         <v>1534</v>
       </c>
       <c r="E282">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F282" t="s">
         <v>1613</v>
@@ -18193,7 +18193,7 @@
         <v>1534</v>
       </c>
       <c r="E283">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F283" t="s">
         <v>1613</v>
@@ -18228,7 +18228,7 @@
         <v>1535</v>
       </c>
       <c r="E284">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F284" t="s">
         <v>1613</v>
@@ -18263,7 +18263,7 @@
         <v>1536</v>
       </c>
       <c r="E285">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F285" t="s">
         <v>1614</v>
@@ -18298,7 +18298,7 @@
         <v>1536</v>
       </c>
       <c r="E286">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F286" t="s">
         <v>1613</v>
@@ -18333,7 +18333,7 @@
         <v>1536</v>
       </c>
       <c r="E287">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F287" t="s">
         <v>1613</v>
@@ -18368,7 +18368,7 @@
         <v>1536</v>
       </c>
       <c r="E288">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F288" t="s">
         <v>1616</v>
@@ -18403,7 +18403,7 @@
         <v>1536</v>
       </c>
       <c r="E289">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F289" t="s">
         <v>1613</v>
@@ -18438,7 +18438,7 @@
         <v>1536</v>
       </c>
       <c r="E290">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F290" t="s">
         <v>1613</v>
@@ -18473,7 +18473,7 @@
         <v>1536</v>
       </c>
       <c r="E291">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F291" t="s">
         <v>1613</v>
@@ -18508,7 +18508,7 @@
         <v>1537</v>
       </c>
       <c r="E292">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F292" t="s">
         <v>1613</v>
@@ -18543,7 +18543,7 @@
         <v>1537</v>
       </c>
       <c r="E293">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F293" t="s">
         <v>1613</v>
@@ -18578,7 +18578,7 @@
         <v>1537</v>
       </c>
       <c r="E294">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F294" t="s">
         <v>1613</v>
@@ -18613,7 +18613,7 @@
         <v>1537</v>
       </c>
       <c r="E295">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F295" t="s">
         <v>1613</v>
@@ -18648,7 +18648,7 @@
         <v>1538</v>
       </c>
       <c r="E296">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F296" t="s">
         <v>1613</v>
@@ -18683,7 +18683,7 @@
         <v>1538</v>
       </c>
       <c r="E297">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F297" t="s">
         <v>1613</v>
@@ -18718,7 +18718,7 @@
         <v>1539</v>
       </c>
       <c r="E298">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F298" t="s">
         <v>1613</v>
@@ -18756,7 +18756,7 @@
         <v>1539</v>
       </c>
       <c r="E299">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F299" t="s">
         <v>1613</v>
@@ -18791,7 +18791,7 @@
         <v>1540</v>
       </c>
       <c r="E300">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F300" t="s">
         <v>1613</v>
@@ -18826,7 +18826,7 @@
         <v>1540</v>
       </c>
       <c r="E301">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F301" t="s">
         <v>1613</v>
@@ -18861,7 +18861,7 @@
         <v>1540</v>
       </c>
       <c r="E302">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F302" t="s">
         <v>1613</v>
@@ -18896,7 +18896,7 @@
         <v>1540</v>
       </c>
       <c r="E303">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F303" t="s">
         <v>1613</v>
@@ -18934,7 +18934,7 @@
         <v>1540</v>
       </c>
       <c r="E304">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F304" t="s">
         <v>1613</v>
@@ -18969,7 +18969,7 @@
         <v>1540</v>
       </c>
       <c r="E305">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F305" t="s">
         <v>1613</v>
@@ -19004,7 +19004,7 @@
         <v>1541</v>
       </c>
       <c r="E306">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F306" t="s">
         <v>1613</v>
@@ -19039,7 +19039,7 @@
         <v>1541</v>
       </c>
       <c r="E307">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F307" t="s">
         <v>1613</v>
@@ -19074,7 +19074,7 @@
         <v>1542</v>
       </c>
       <c r="E308">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F308" t="s">
         <v>1613</v>
@@ -19109,7 +19109,7 @@
         <v>1542</v>
       </c>
       <c r="E309">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F309" t="s">
         <v>1613</v>
@@ -19144,7 +19144,7 @@
         <v>1543</v>
       </c>
       <c r="E310">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F310" t="s">
         <v>1613</v>
@@ -19179,7 +19179,7 @@
         <v>1543</v>
       </c>
       <c r="E311">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F311" t="s">
         <v>1613</v>
@@ -19214,7 +19214,7 @@
         <v>1543</v>
       </c>
       <c r="E312">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F312" t="s">
         <v>1613</v>
@@ -19249,7 +19249,7 @@
         <v>1543</v>
       </c>
       <c r="E313">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F313" t="s">
         <v>1613</v>
@@ -19284,7 +19284,7 @@
         <v>1544</v>
       </c>
       <c r="E314">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F314" t="s">
         <v>1613</v>
@@ -19319,7 +19319,7 @@
         <v>1544</v>
       </c>
       <c r="E315">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F315" t="s">
         <v>1613</v>
@@ -19354,7 +19354,7 @@
         <v>1544</v>
       </c>
       <c r="E316">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F316" t="s">
         <v>1613</v>
@@ -19389,7 +19389,7 @@
         <v>1544</v>
       </c>
       <c r="E317">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F317" t="s">
         <v>1613</v>
@@ -19424,7 +19424,7 @@
         <v>1545</v>
       </c>
       <c r="E318">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F318" t="s">
         <v>1613</v>
@@ -19459,7 +19459,7 @@
         <v>1545</v>
       </c>
       <c r="E319">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F319" t="s">
         <v>1613</v>
@@ -19494,7 +19494,7 @@
         <v>1546</v>
       </c>
       <c r="E320">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F320" t="s">
         <v>1613</v>
@@ -19529,7 +19529,7 @@
         <v>1546</v>
       </c>
       <c r="E321">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F321" t="s">
         <v>1613</v>
@@ -19564,7 +19564,7 @@
         <v>1546</v>
       </c>
       <c r="E322">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F322" t="s">
         <v>1613</v>
@@ -19599,7 +19599,7 @@
         <v>1546</v>
       </c>
       <c r="E323">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F323" t="s">
         <v>1613</v>
@@ -19634,7 +19634,7 @@
         <v>1546</v>
       </c>
       <c r="E324">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F324" t="s">
         <v>1613</v>
@@ -19669,7 +19669,7 @@
         <v>1547</v>
       </c>
       <c r="E325">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F325" t="s">
         <v>1613</v>
@@ -19704,7 +19704,7 @@
         <v>1547</v>
       </c>
       <c r="E326">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F326" t="s">
         <v>1613</v>
@@ -19739,7 +19739,7 @@
         <v>1547</v>
       </c>
       <c r="E327">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F327" t="s">
         <v>1613</v>
@@ -19774,7 +19774,7 @@
         <v>1548</v>
       </c>
       <c r="E328">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F328" t="s">
         <v>1613</v>
@@ -19809,7 +19809,7 @@
         <v>1548</v>
       </c>
       <c r="E329">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F329" t="s">
         <v>1613</v>
@@ -19844,7 +19844,7 @@
         <v>1549</v>
       </c>
       <c r="E330">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F330" t="s">
         <v>1613</v>
@@ -19879,7 +19879,7 @@
         <v>1549</v>
       </c>
       <c r="E331">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F331" t="s">
         <v>1613</v>
@@ -19914,7 +19914,7 @@
         <v>1549</v>
       </c>
       <c r="E332">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F332" t="s">
         <v>1613</v>
@@ -19949,7 +19949,7 @@
         <v>1549</v>
       </c>
       <c r="E333">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F333" t="s">
         <v>1613</v>
@@ -19984,7 +19984,7 @@
         <v>1549</v>
       </c>
       <c r="E334">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F334" t="s">
         <v>1613</v>
@@ -20019,7 +20019,7 @@
         <v>1549</v>
       </c>
       <c r="E335">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F335" t="s">
         <v>1613</v>
@@ -20054,7 +20054,7 @@
         <v>1549</v>
       </c>
       <c r="E336">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F336" t="s">
         <v>1613</v>
@@ -20089,7 +20089,7 @@
         <v>1549</v>
       </c>
       <c r="E337">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F337" t="s">
         <v>1613</v>
@@ -20124,7 +20124,7 @@
         <v>1550</v>
       </c>
       <c r="E338">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F338" t="s">
         <v>1613</v>
@@ -20159,7 +20159,7 @@
         <v>1550</v>
       </c>
       <c r="E339">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F339" t="s">
         <v>1613</v>
@@ -20194,7 +20194,7 @@
         <v>1550</v>
       </c>
       <c r="E340">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F340" t="s">
         <v>1613</v>
@@ -20229,7 +20229,7 @@
         <v>1551</v>
       </c>
       <c r="E341">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F341" t="s">
         <v>1613</v>
@@ -20264,7 +20264,7 @@
         <v>1551</v>
       </c>
       <c r="E342">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F342" t="s">
         <v>1613</v>
@@ -20299,7 +20299,7 @@
         <v>1552</v>
       </c>
       <c r="E343">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F343" t="s">
         <v>1613</v>
@@ -20334,7 +20334,7 @@
         <v>1553</v>
       </c>
       <c r="E344">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F344" t="s">
         <v>1615</v>
@@ -20369,7 +20369,7 @@
         <v>1553</v>
       </c>
       <c r="E345">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F345" t="s">
         <v>1613</v>
@@ -20404,7 +20404,7 @@
         <v>1553</v>
       </c>
       <c r="E346">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F346" t="s">
         <v>1613</v>
@@ -20439,7 +20439,7 @@
         <v>1553</v>
       </c>
       <c r="E347">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F347" t="s">
         <v>1613</v>
@@ -20474,7 +20474,7 @@
         <v>1553</v>
       </c>
       <c r="E348">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F348" t="s">
         <v>1613</v>
@@ -20509,7 +20509,7 @@
         <v>1553</v>
       </c>
       <c r="E349">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F349" t="s">
         <v>1613</v>
@@ -20544,7 +20544,7 @@
         <v>1554</v>
       </c>
       <c r="E350">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F350" t="s">
         <v>1613</v>
@@ -20579,7 +20579,7 @@
         <v>1554</v>
       </c>
       <c r="E351">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F351" t="s">
         <v>1613</v>
@@ -20614,7 +20614,7 @@
         <v>1555</v>
       </c>
       <c r="E352">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F352" t="s">
         <v>1613</v>
@@ -20649,7 +20649,7 @@
         <v>1555</v>
       </c>
       <c r="E353">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F353" t="s">
         <v>1613</v>
@@ -20684,7 +20684,7 @@
         <v>1555</v>
       </c>
       <c r="E354">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F354" t="s">
         <v>1613</v>
@@ -20719,7 +20719,7 @@
         <v>1556</v>
       </c>
       <c r="E355">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F355" t="s">
         <v>1613</v>
@@ -20754,7 +20754,7 @@
         <v>1557</v>
       </c>
       <c r="E356">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F356" t="s">
         <v>1613</v>
@@ -20789,7 +20789,7 @@
         <v>1558</v>
       </c>
       <c r="E357">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F357" t="s">
         <v>1613</v>
@@ -20824,7 +20824,7 @@
         <v>1558</v>
       </c>
       <c r="E358">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F358" t="s">
         <v>1613</v>
@@ -20859,7 +20859,7 @@
         <v>1559</v>
       </c>
       <c r="E359">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F359" t="s">
         <v>1613</v>
@@ -20894,7 +20894,7 @@
         <v>1559</v>
       </c>
       <c r="E360">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F360" t="s">
         <v>1613</v>
@@ -20929,7 +20929,7 @@
         <v>1559</v>
       </c>
       <c r="E361">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F361" t="s">
         <v>1613</v>
@@ -20964,7 +20964,7 @@
         <v>1560</v>
       </c>
       <c r="E362">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F362" t="s">
         <v>1613</v>
@@ -20999,7 +20999,7 @@
         <v>1560</v>
       </c>
       <c r="E363">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F363" t="s">
         <v>1613</v>
@@ -21034,7 +21034,7 @@
         <v>1560</v>
       </c>
       <c r="E364">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F364" t="s">
         <v>1613</v>
@@ -21069,7 +21069,7 @@
         <v>1560</v>
       </c>
       <c r="E365">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F365" t="s">
         <v>1613</v>
@@ -21104,7 +21104,7 @@
         <v>1560</v>
       </c>
       <c r="E366">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F366" t="s">
         <v>1613</v>
@@ -21139,7 +21139,7 @@
         <v>1560</v>
       </c>
       <c r="E367">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F367" t="s">
         <v>1613</v>
@@ -21174,7 +21174,7 @@
         <v>1560</v>
       </c>
       <c r="E368">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F368" t="s">
         <v>1613</v>
@@ -21209,7 +21209,7 @@
         <v>1560</v>
       </c>
       <c r="E369">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F369" t="s">
         <v>1613</v>
@@ -21244,7 +21244,7 @@
         <v>1560</v>
       </c>
       <c r="E370">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F370" t="s">
         <v>1613</v>
@@ -21279,7 +21279,7 @@
         <v>1561</v>
       </c>
       <c r="E371">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F371" t="s">
         <v>1613</v>
@@ -21314,7 +21314,7 @@
         <v>1561</v>
       </c>
       <c r="E372">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F372" t="s">
         <v>1613</v>
@@ -21349,7 +21349,7 @@
         <v>1561</v>
       </c>
       <c r="E373">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F373" t="s">
         <v>1613</v>
@@ -21384,7 +21384,7 @@
         <v>1561</v>
       </c>
       <c r="E374">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F374" t="s">
         <v>1613</v>
@@ -21419,7 +21419,7 @@
         <v>1562</v>
       </c>
       <c r="E375">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F375" t="s">
         <v>1616</v>
@@ -21454,7 +21454,7 @@
         <v>1562</v>
       </c>
       <c r="E376">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F376" t="s">
         <v>1613</v>
@@ -21489,7 +21489,7 @@
         <v>1563</v>
       </c>
       <c r="E377">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F377" t="s">
         <v>1613</v>
@@ -21524,7 +21524,7 @@
         <v>1563</v>
       </c>
       <c r="E378">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F378" t="s">
         <v>1613</v>
@@ -21559,7 +21559,7 @@
         <v>1563</v>
       </c>
       <c r="E379">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F379" t="s">
         <v>1613</v>
@@ -21594,7 +21594,7 @@
         <v>1563</v>
       </c>
       <c r="E380">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F380" t="s">
         <v>1613</v>
@@ -21629,7 +21629,7 @@
         <v>1563</v>
       </c>
       <c r="E381">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F381" t="s">
         <v>1617</v>
@@ -21667,7 +21667,7 @@
         <v>1563</v>
       </c>
       <c r="E382">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F382" t="s">
         <v>1613</v>
@@ -21702,7 +21702,7 @@
         <v>1563</v>
       </c>
       <c r="E383">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F383" t="s">
         <v>1613</v>
@@ -21737,7 +21737,7 @@
         <v>1564</v>
       </c>
       <c r="E384">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F384" t="s">
         <v>1613</v>
@@ -21772,7 +21772,7 @@
         <v>1564</v>
       </c>
       <c r="E385">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F385" t="s">
         <v>1613</v>
@@ -21807,7 +21807,7 @@
         <v>1564</v>
       </c>
       <c r="E386">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F386" t="s">
         <v>1613</v>
@@ -21842,7 +21842,7 @@
         <v>1564</v>
       </c>
       <c r="E387">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F387" t="s">
         <v>1613</v>
@@ -21880,7 +21880,7 @@
         <v>1564</v>
       </c>
       <c r="E388">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F388" t="s">
         <v>1613</v>
@@ -21915,7 +21915,7 @@
         <v>1564</v>
       </c>
       <c r="E389">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F389" t="s">
         <v>1613</v>
@@ -21950,7 +21950,7 @@
         <v>1564</v>
       </c>
       <c r="E390">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F390" t="s">
         <v>1613</v>
@@ -21985,7 +21985,7 @@
         <v>1564</v>
       </c>
       <c r="E391">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F391" t="s">
         <v>1613</v>
@@ -22020,7 +22020,7 @@
         <v>1564</v>
       </c>
       <c r="E392">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F392" t="s">
         <v>1613</v>
@@ -22055,7 +22055,7 @@
         <v>1565</v>
       </c>
       <c r="E393">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F393" t="s">
         <v>1614</v>
@@ -22090,7 +22090,7 @@
         <v>1566</v>
       </c>
       <c r="E394">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F394" t="s">
         <v>1617</v>
@@ -22125,7 +22125,7 @@
         <v>1567</v>
       </c>
       <c r="E395">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F395" t="s">
         <v>1613</v>
@@ -22160,7 +22160,7 @@
         <v>1568</v>
       </c>
       <c r="E396">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F396" t="s">
         <v>1613</v>
@@ -22195,7 +22195,7 @@
         <v>1568</v>
       </c>
       <c r="E397">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F397" t="s">
         <v>1613</v>
@@ -22230,7 +22230,7 @@
         <v>1569</v>
       </c>
       <c r="E398">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F398" t="s">
         <v>1613</v>
@@ -22265,7 +22265,7 @@
         <v>1570</v>
       </c>
       <c r="E399">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F399" t="s">
         <v>1616</v>
@@ -22300,7 +22300,7 @@
         <v>1570</v>
       </c>
       <c r="E400">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F400" t="s">
         <v>1613</v>
@@ -22335,7 +22335,7 @@
         <v>1570</v>
       </c>
       <c r="E401">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F401" t="s">
         <v>1613</v>
@@ -22370,7 +22370,7 @@
         <v>1570</v>
       </c>
       <c r="E402">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F402" t="s">
         <v>1613</v>
@@ -22405,7 +22405,7 @@
         <v>1570</v>
       </c>
       <c r="E403">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F403" t="s">
         <v>1613</v>
@@ -22440,7 +22440,7 @@
         <v>1570</v>
       </c>
       <c r="E404">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F404" t="s">
         <v>1613</v>
@@ -22475,7 +22475,7 @@
         <v>1571</v>
       </c>
       <c r="E405">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F405" t="s">
         <v>1613</v>
@@ -22510,7 +22510,7 @@
         <v>1571</v>
       </c>
       <c r="E406">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F406" t="s">
         <v>1613</v>
@@ -22545,7 +22545,7 @@
         <v>1571</v>
       </c>
       <c r="E407">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F407" t="s">
         <v>1613</v>
@@ -22580,7 +22580,7 @@
         <v>1572</v>
       </c>
       <c r="E408">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F408" t="s">
         <v>1613</v>
@@ -22615,7 +22615,7 @@
         <v>1572</v>
       </c>
       <c r="E409">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F409" t="s">
         <v>1613</v>
@@ -22650,7 +22650,7 @@
         <v>1572</v>
       </c>
       <c r="E410">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F410" t="s">
         <v>1613</v>
@@ -22688,7 +22688,7 @@
         <v>1572</v>
       </c>
       <c r="E411">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F411" t="s">
         <v>1613</v>
@@ -22723,7 +22723,7 @@
         <v>1573</v>
       </c>
       <c r="E412">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F412" t="s">
         <v>1613</v>
@@ -22758,7 +22758,7 @@
         <v>1573</v>
       </c>
       <c r="E413">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F413" t="s">
         <v>1613</v>
@@ -22793,7 +22793,7 @@
         <v>1573</v>
       </c>
       <c r="E414">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F414" t="s">
         <v>1613</v>
@@ -22828,7 +22828,7 @@
         <v>1573</v>
       </c>
       <c r="E415">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F415" t="s">
         <v>1613</v>
@@ -22863,7 +22863,7 @@
         <v>1573</v>
       </c>
       <c r="E416">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F416" t="s">
         <v>1613</v>
@@ -22898,7 +22898,7 @@
         <v>1574</v>
       </c>
       <c r="E417">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F417" t="s">
         <v>1613</v>
@@ -22933,7 +22933,7 @@
         <v>1574</v>
       </c>
       <c r="E418">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F418" t="s">
         <v>1613</v>
@@ -22968,7 +22968,7 @@
         <v>1575</v>
       </c>
       <c r="E419">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F419" t="s">
         <v>1613</v>
@@ -23003,7 +23003,7 @@
         <v>1575</v>
       </c>
       <c r="E420">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F420" t="s">
         <v>1613</v>
@@ -23038,7 +23038,7 @@
         <v>1575</v>
       </c>
       <c r="E421">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F421" t="s">
         <v>1613</v>
@@ -23073,7 +23073,7 @@
         <v>1575</v>
       </c>
       <c r="E422">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F422" t="s">
         <v>1613</v>
@@ -23108,7 +23108,7 @@
         <v>1575</v>
       </c>
       <c r="E423">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F423" t="s">
         <v>1613</v>
@@ -23143,7 +23143,7 @@
         <v>1575</v>
       </c>
       <c r="E424">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F424" t="s">
         <v>1613</v>
@@ -23178,7 +23178,7 @@
         <v>1575</v>
       </c>
       <c r="E425">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F425" t="s">
         <v>1613</v>
@@ -23213,7 +23213,7 @@
         <v>1575</v>
       </c>
       <c r="E426">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F426" t="s">
         <v>1613</v>
@@ -23248,7 +23248,7 @@
         <v>1575</v>
       </c>
       <c r="E427">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F427" t="s">
         <v>1613</v>
@@ -23283,7 +23283,7 @@
         <v>1575</v>
       </c>
       <c r="E428">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F428" t="s">
         <v>1613</v>
@@ -23318,7 +23318,7 @@
         <v>1576</v>
       </c>
       <c r="E429">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F429" t="s">
         <v>1613</v>
@@ -23353,7 +23353,7 @@
         <v>1576</v>
       </c>
       <c r="E430">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F430" t="s">
         <v>1613</v>
@@ -23388,7 +23388,7 @@
         <v>1576</v>
       </c>
       <c r="E431">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F431" t="s">
         <v>1614</v>
@@ -23423,7 +23423,7 @@
         <v>1577</v>
       </c>
       <c r="E432">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F432" t="s">
         <v>1613</v>
@@ -23458,7 +23458,7 @@
         <v>1577</v>
       </c>
       <c r="E433">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F433" t="s">
         <v>1613</v>
@@ -23493,7 +23493,7 @@
         <v>1577</v>
       </c>
       <c r="E434">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F434" t="s">
         <v>1613</v>
@@ -23528,7 +23528,7 @@
         <v>1577</v>
       </c>
       <c r="E435">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F435" t="s">
         <v>1613</v>
@@ -23563,7 +23563,7 @@
         <v>1577</v>
       </c>
       <c r="E436">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F436" t="s">
         <v>1613</v>
@@ -23598,7 +23598,7 @@
         <v>1577</v>
       </c>
       <c r="E437">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F437" t="s">
         <v>1613</v>
@@ -23633,7 +23633,7 @@
         <v>1577</v>
       </c>
       <c r="E438">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F438" t="s">
         <v>1616</v>
@@ -23668,7 +23668,7 @@
         <v>1578</v>
       </c>
       <c r="E439">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F439" t="s">
         <v>1613</v>
@@ -23703,7 +23703,7 @@
         <v>1578</v>
       </c>
       <c r="E440">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F440" t="s">
         <v>1613</v>
@@ -23738,7 +23738,7 @@
         <v>1578</v>
       </c>
       <c r="E441">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F441" t="s">
         <v>1613</v>
@@ -23773,7 +23773,7 @@
         <v>1578</v>
       </c>
       <c r="E442">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F442" t="s">
         <v>1613</v>
@@ -23808,7 +23808,7 @@
         <v>1579</v>
       </c>
       <c r="E443">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F443" t="s">
         <v>1613</v>
@@ -23843,7 +23843,7 @@
         <v>1579</v>
       </c>
       <c r="E444">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F444" t="s">
         <v>1616</v>
@@ -23878,7 +23878,7 @@
         <v>1579</v>
       </c>
       <c r="E445">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F445" t="s">
         <v>1613</v>
@@ -23913,7 +23913,7 @@
         <v>1579</v>
       </c>
       <c r="E446">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F446" t="s">
         <v>1613</v>
@@ -23948,7 +23948,7 @@
         <v>1579</v>
       </c>
       <c r="E447">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F447" t="s">
         <v>1613</v>
@@ -23983,7 +23983,7 @@
         <v>1579</v>
       </c>
       <c r="E448">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F448" t="s">
         <v>1613</v>
@@ -24018,7 +24018,7 @@
         <v>1579</v>
       </c>
       <c r="E449">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F449" t="s">
         <v>1617</v>
@@ -24053,7 +24053,7 @@
         <v>1579</v>
       </c>
       <c r="E450">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F450" t="s">
         <v>1613</v>
@@ -24088,7 +24088,7 @@
         <v>1579</v>
       </c>
       <c r="E451">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F451" t="s">
         <v>1613</v>
@@ -24123,7 +24123,7 @@
         <v>1580</v>
       </c>
       <c r="E452">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F452" t="s">
         <v>1613</v>
@@ -24158,7 +24158,7 @@
         <v>1580</v>
       </c>
       <c r="E453">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F453" t="s">
         <v>1613</v>
@@ -24193,7 +24193,7 @@
         <v>1580</v>
       </c>
       <c r="E454">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F454" t="s">
         <v>1613</v>
@@ -24228,7 +24228,7 @@
         <v>1580</v>
       </c>
       <c r="E455">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F455" t="s">
         <v>1613</v>
@@ -24263,7 +24263,7 @@
         <v>1580</v>
       </c>
       <c r="E456">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F456" t="s">
         <v>1613</v>
@@ -24298,7 +24298,7 @@
         <v>1580</v>
       </c>
       <c r="E457">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F457" t="s">
         <v>1615</v>
@@ -24333,7 +24333,7 @@
         <v>1580</v>
       </c>
       <c r="E458">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F458" t="s">
         <v>1613</v>
@@ -24368,7 +24368,7 @@
         <v>1580</v>
       </c>
       <c r="E459">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F459" t="s">
         <v>1613</v>
@@ -24403,7 +24403,7 @@
         <v>1581</v>
       </c>
       <c r="E460">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F460" t="s">
         <v>1613</v>
@@ -24438,7 +24438,7 @@
         <v>1581</v>
       </c>
       <c r="E461">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F461" t="s">
         <v>1613</v>
@@ -24473,7 +24473,7 @@
         <v>1581</v>
       </c>
       <c r="E462">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F462" t="s">
         <v>1613</v>
@@ -24508,7 +24508,7 @@
         <v>1581</v>
       </c>
       <c r="E463">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F463" t="s">
         <v>1613</v>
@@ -24543,7 +24543,7 @@
         <v>1581</v>
       </c>
       <c r="E464">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F464" t="s">
         <v>1613</v>
@@ -24578,7 +24578,7 @@
         <v>1582</v>
       </c>
       <c r="E465">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F465" t="s">
         <v>1613</v>
@@ -24613,7 +24613,7 @@
         <v>1582</v>
       </c>
       <c r="E466">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F466" t="s">
         <v>1613</v>
@@ -24648,7 +24648,7 @@
         <v>1582</v>
       </c>
       <c r="E467">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F467" t="s">
         <v>1613</v>
@@ -24683,7 +24683,7 @@
         <v>1582</v>
       </c>
       <c r="E468">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F468" t="s">
         <v>1613</v>
@@ -24718,7 +24718,7 @@
         <v>1582</v>
       </c>
       <c r="E469">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F469" t="s">
         <v>1613</v>
@@ -24756,7 +24756,7 @@
         <v>1583</v>
       </c>
       <c r="E470">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F470" t="s">
         <v>1613</v>
@@ -24791,7 +24791,7 @@
         <v>1583</v>
       </c>
       <c r="E471">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F471" t="s">
         <v>1613</v>
@@ -24826,7 +24826,7 @@
         <v>1583</v>
       </c>
       <c r="E472">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F472" t="s">
         <v>1613</v>
@@ -24861,7 +24861,7 @@
         <v>1583</v>
       </c>
       <c r="E473">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F473" t="s">
         <v>1613</v>
@@ -24896,7 +24896,7 @@
         <v>1583</v>
       </c>
       <c r="E474">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F474" t="s">
         <v>1613</v>
@@ -24931,7 +24931,7 @@
         <v>1583</v>
       </c>
       <c r="E475">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F475" t="s">
         <v>1613</v>
@@ -24966,7 +24966,7 @@
         <v>1584</v>
       </c>
       <c r="E476">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F476" t="s">
         <v>1613</v>
@@ -25001,7 +25001,7 @@
         <v>1584</v>
       </c>
       <c r="E477">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F477" t="s">
         <v>1613</v>
@@ -25036,7 +25036,7 @@
         <v>1584</v>
       </c>
       <c r="E478">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F478" t="s">
         <v>1613</v>
@@ -25071,7 +25071,7 @@
         <v>1585</v>
       </c>
       <c r="E479">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F479" t="s">
         <v>1613</v>
@@ -25106,7 +25106,7 @@
         <v>1586</v>
       </c>
       <c r="E480">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F480" t="s">
         <v>1613</v>
@@ -25141,7 +25141,7 @@
         <v>1586</v>
       </c>
       <c r="E481">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F481" t="s">
         <v>1613</v>
@@ -25176,7 +25176,7 @@
         <v>1586</v>
       </c>
       <c r="E482">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F482" t="s">
         <v>1615</v>
@@ -25214,7 +25214,7 @@
         <v>1586</v>
       </c>
       <c r="E483">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F483" t="s">
         <v>1613</v>
@@ -25249,7 +25249,7 @@
         <v>1586</v>
       </c>
       <c r="E484">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F484" t="s">
         <v>1613</v>
@@ -25284,7 +25284,7 @@
         <v>1587</v>
       </c>
       <c r="E485">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F485" t="s">
         <v>1613</v>
@@ -25319,7 +25319,7 @@
         <v>1587</v>
       </c>
       <c r="E486">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F486" t="s">
         <v>1613</v>
@@ -25354,7 +25354,7 @@
         <v>1587</v>
       </c>
       <c r="E487">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F487" t="s">
         <v>1613</v>
@@ -25389,7 +25389,7 @@
         <v>1587</v>
       </c>
       <c r="E488">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F488" t="s">
         <v>1613</v>
@@ -25424,7 +25424,7 @@
         <v>1587</v>
       </c>
       <c r="E489">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F489" t="s">
         <v>1613</v>
@@ -25459,7 +25459,7 @@
         <v>1588</v>
       </c>
       <c r="E490">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F490" t="s">
         <v>1613</v>
@@ -25494,7 +25494,7 @@
         <v>1588</v>
       </c>
       <c r="E491">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F491" t="s">
         <v>1613</v>
@@ -25529,7 +25529,7 @@
         <v>1588</v>
       </c>
       <c r="E492">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F492" t="s">
         <v>1613</v>
@@ -25564,7 +25564,7 @@
         <v>1588</v>
       </c>
       <c r="E493">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F493" t="s">
         <v>1613</v>
@@ -25599,7 +25599,7 @@
         <v>1588</v>
       </c>
       <c r="E494">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F494" t="s">
         <v>1613</v>
@@ -25634,7 +25634,7 @@
         <v>1588</v>
       </c>
       <c r="E495">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F495" t="s">
         <v>1613</v>
@@ -25669,7 +25669,7 @@
         <v>1588</v>
       </c>
       <c r="E496">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F496" t="s">
         <v>1613</v>
@@ -25704,7 +25704,7 @@
         <v>1588</v>
       </c>
       <c r="E497">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F497" t="s">
         <v>1613</v>
@@ -25739,7 +25739,7 @@
         <v>1589</v>
       </c>
       <c r="E498">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F498" t="s">
         <v>1613</v>
@@ -25774,7 +25774,7 @@
         <v>1589</v>
       </c>
       <c r="E499">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F499" t="s">
         <v>1613</v>
@@ -25809,7 +25809,7 @@
         <v>1590</v>
       </c>
       <c r="E500">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F500" t="s">
         <v>1613</v>
@@ -25844,7 +25844,7 @@
         <v>1590</v>
       </c>
       <c r="E501">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F501" t="s">
         <v>1613</v>
@@ -25879,7 +25879,7 @@
         <v>1590</v>
       </c>
       <c r="E502">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F502" t="s">
         <v>1613</v>
@@ -25914,7 +25914,7 @@
         <v>1590</v>
       </c>
       <c r="E503">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F503" t="s">
         <v>1617</v>
@@ -25952,7 +25952,7 @@
         <v>1590</v>
       </c>
       <c r="E504">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F504" t="s">
         <v>1613</v>
@@ -25987,7 +25987,7 @@
         <v>1590</v>
       </c>
       <c r="E505">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F505" t="s">
         <v>1617</v>
@@ -26022,7 +26022,7 @@
         <v>1591</v>
       </c>
       <c r="E506">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F506" t="s">
         <v>1613</v>
@@ -26057,7 +26057,7 @@
         <v>1592</v>
       </c>
       <c r="E507">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F507" t="s">
         <v>1613</v>
@@ -26092,7 +26092,7 @@
         <v>1592</v>
       </c>
       <c r="E508">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F508" t="s">
         <v>1613</v>
@@ -26127,7 +26127,7 @@
         <v>1592</v>
       </c>
       <c r="E509">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F509" t="s">
         <v>1613</v>
@@ -26162,7 +26162,7 @@
         <v>1592</v>
       </c>
       <c r="E510">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F510" t="s">
         <v>1613</v>
@@ -26197,7 +26197,7 @@
         <v>1593</v>
       </c>
       <c r="E511">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F511" t="s">
         <v>1613</v>
@@ -26232,7 +26232,7 @@
         <v>1593</v>
       </c>
       <c r="E512">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F512" t="s">
         <v>1617</v>
@@ -26267,7 +26267,7 @@
         <v>1593</v>
       </c>
       <c r="E513">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F513" t="s">
         <v>1613</v>
@@ -26302,7 +26302,7 @@
         <v>1593</v>
       </c>
       <c r="E514">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F514" t="s">
         <v>1613</v>
@@ -26337,7 +26337,7 @@
         <v>1593</v>
       </c>
       <c r="E515">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F515" t="s">
         <v>1613</v>
@@ -26372,7 +26372,7 @@
         <v>1594</v>
       </c>
       <c r="E516">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F516" t="s">
         <v>1613</v>
@@ -26407,7 +26407,7 @@
         <v>1594</v>
       </c>
       <c r="E517">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F517" t="s">
         <v>1615</v>
@@ -26442,7 +26442,7 @@
         <v>1594</v>
       </c>
       <c r="E518">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F518" t="s">
         <v>1613</v>
@@ -26477,7 +26477,7 @@
         <v>1594</v>
       </c>
       <c r="E519">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F519" t="s">
         <v>1613</v>
@@ -26512,7 +26512,7 @@
         <v>1595</v>
       </c>
       <c r="E520">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F520" t="s">
         <v>1613</v>
@@ -26547,7 +26547,7 @@
         <v>1595</v>
       </c>
       <c r="E521">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F521" t="s">
         <v>1613</v>
@@ -26582,7 +26582,7 @@
         <v>1595</v>
       </c>
       <c r="E522">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F522" t="s">
         <v>1613</v>
@@ -26617,7 +26617,7 @@
         <v>1595</v>
       </c>
       <c r="E523">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F523" t="s">
         <v>1613</v>
@@ -26652,7 +26652,7 @@
         <v>1595</v>
       </c>
       <c r="E524">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F524" t="s">
         <v>1613</v>
@@ -26687,7 +26687,7 @@
         <v>1595</v>
       </c>
       <c r="E525">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F525" t="s">
         <v>1613</v>
@@ -26722,7 +26722,7 @@
         <v>1596</v>
       </c>
       <c r="E526">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F526" t="s">
         <v>1613</v>
@@ -26757,7 +26757,7 @@
         <v>1596</v>
       </c>
       <c r="E527">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F527" t="s">
         <v>1613</v>
@@ -26792,7 +26792,7 @@
         <v>1596</v>
       </c>
       <c r="E528">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F528" t="s">
         <v>1613</v>
@@ -26827,7 +26827,7 @@
         <v>1596</v>
       </c>
       <c r="E529">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F529" t="s">
         <v>1613</v>
@@ -26862,7 +26862,7 @@
         <v>1596</v>
       </c>
       <c r="E530">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F530" t="s">
         <v>1613</v>
@@ -26897,7 +26897,7 @@
         <v>1596</v>
       </c>
       <c r="E531">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F531" t="s">
         <v>1613</v>
@@ -26932,7 +26932,7 @@
         <v>1596</v>
       </c>
       <c r="E532">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F532" t="s">
         <v>1613</v>
@@ -26967,7 +26967,7 @@
         <v>1596</v>
       </c>
       <c r="E533">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F533" t="s">
         <v>1613</v>
@@ -27002,7 +27002,7 @@
         <v>1596</v>
       </c>
       <c r="E534">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F534" t="s">
         <v>1613</v>
@@ -27037,7 +27037,7 @@
         <v>1596</v>
       </c>
       <c r="E535">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F535" t="s">
         <v>1613</v>
@@ -27072,7 +27072,7 @@
         <v>1596</v>
       </c>
       <c r="E536">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F536" t="s">
         <v>1613</v>
@@ -27107,7 +27107,7 @@
         <v>1596</v>
       </c>
       <c r="E537">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F537" t="s">
         <v>1613</v>
@@ -27142,7 +27142,7 @@
         <v>1596</v>
       </c>
       <c r="E538">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F538" t="s">
         <v>1613</v>
@@ -27177,7 +27177,7 @@
         <v>1596</v>
       </c>
       <c r="E539">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F539" t="s">
         <v>1613</v>
@@ -27212,7 +27212,7 @@
         <v>1596</v>
       </c>
       <c r="E540">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F540" t="s">
         <v>1613</v>
@@ -27247,7 +27247,7 @@
         <v>1596</v>
       </c>
       <c r="E541">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F541" t="s">
         <v>1613</v>
@@ -27282,7 +27282,7 @@
         <v>1596</v>
       </c>
       <c r="E542">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F542" t="s">
         <v>1613</v>
@@ -27317,7 +27317,7 @@
         <v>1596</v>
       </c>
       <c r="E543">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F543" t="s">
         <v>1613</v>
@@ -27352,7 +27352,7 @@
         <v>1596</v>
       </c>
       <c r="E544">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F544" t="s">
         <v>1613</v>
@@ -27387,7 +27387,7 @@
         <v>1596</v>
       </c>
       <c r="E545">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F545" t="s">
         <v>1613</v>
@@ -27422,7 +27422,7 @@
         <v>1596</v>
       </c>
       <c r="E546">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F546" t="s">
         <v>1613</v>
@@ -27457,7 +27457,7 @@
         <v>1596</v>
       </c>
       <c r="E547">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F547" t="s">
         <v>1613</v>
@@ -27492,7 +27492,7 @@
         <v>1596</v>
       </c>
       <c r="E548">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F548" t="s">
         <v>1613</v>
@@ -27527,7 +27527,7 @@
         <v>1596</v>
       </c>
       <c r="E549">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F549" t="s">
         <v>1613</v>
@@ -27562,7 +27562,7 @@
         <v>1596</v>
       </c>
       <c r="E550">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F550" t="s">
         <v>1613</v>
@@ -27597,7 +27597,7 @@
         <v>1596</v>
       </c>
       <c r="E551">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F551" t="s">
         <v>1613</v>
@@ -27632,7 +27632,7 @@
         <v>1596</v>
       </c>
       <c r="E552">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F552" t="s">
         <v>1615</v>
@@ -27670,7 +27670,7 @@
         <v>1597</v>
       </c>
       <c r="E553">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F553" t="s">
         <v>1613</v>
@@ -27705,7 +27705,7 @@
         <v>1597</v>
       </c>
       <c r="E554">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F554" t="s">
         <v>1613</v>
@@ -27740,7 +27740,7 @@
         <v>1597</v>
       </c>
       <c r="E555">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F555" t="s">
         <v>1613</v>
@@ -27775,7 +27775,7 @@
         <v>1597</v>
       </c>
       <c r="E556">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F556" t="s">
         <v>1613</v>
@@ -27810,7 +27810,7 @@
         <v>1597</v>
       </c>
       <c r="E557">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F557" t="s">
         <v>1613</v>
@@ -27845,7 +27845,7 @@
         <v>1597</v>
       </c>
       <c r="E558">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F558" t="s">
         <v>1613</v>
@@ -27880,7 +27880,7 @@
         <v>1597</v>
       </c>
       <c r="E559">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F559" t="s">
         <v>1617</v>
@@ -27915,7 +27915,7 @@
         <v>1597</v>
       </c>
       <c r="E560">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F560" t="s">
         <v>1613</v>
@@ -27950,7 +27950,7 @@
         <v>1598</v>
       </c>
       <c r="E561">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F561" t="s">
         <v>1613</v>
@@ -27985,7 +27985,7 @@
         <v>1598</v>
       </c>
       <c r="E562">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F562" t="s">
         <v>1613</v>
@@ -28020,7 +28020,7 @@
         <v>1599</v>
       </c>
       <c r="E563">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F563" t="s">
         <v>1613</v>
@@ -28055,7 +28055,7 @@
         <v>1599</v>
       </c>
       <c r="E564">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F564" t="s">
         <v>1615</v>
@@ -28093,7 +28093,7 @@
         <v>1600</v>
       </c>
       <c r="E565">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F565" t="s">
         <v>1615</v>
@@ -28131,7 +28131,7 @@
         <v>1600</v>
       </c>
       <c r="E566">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F566" t="s">
         <v>1613</v>
@@ -28166,7 +28166,7 @@
         <v>1600</v>
       </c>
       <c r="E567">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F567" t="s">
         <v>1613</v>
@@ -28201,7 +28201,7 @@
         <v>1600</v>
       </c>
       <c r="E568">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F568" t="s">
         <v>1615</v>
@@ -28239,7 +28239,7 @@
         <v>1600</v>
       </c>
       <c r="E569">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F569" t="s">
         <v>1613</v>
@@ -28274,7 +28274,7 @@
         <v>1600</v>
       </c>
       <c r="E570">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F570" t="s">
         <v>1613</v>
@@ -28309,7 +28309,7 @@
         <v>1600</v>
       </c>
       <c r="E571">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F571" t="s">
         <v>1613</v>
@@ -28344,7 +28344,7 @@
         <v>1600</v>
       </c>
       <c r="E572">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F572" t="s">
         <v>1613</v>
@@ -28382,7 +28382,7 @@
         <v>1600</v>
       </c>
       <c r="E573">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F573" t="s">
         <v>1613</v>
@@ -28417,7 +28417,7 @@
         <v>1600</v>
       </c>
       <c r="E574">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F574" t="s">
         <v>1613</v>
@@ -28452,7 +28452,7 @@
         <v>1601</v>
       </c>
       <c r="E575">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F575" t="s">
         <v>1613</v>
@@ -28490,7 +28490,7 @@
         <v>1601</v>
       </c>
       <c r="E576">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F576" t="s">
         <v>1617</v>
@@ -28525,7 +28525,7 @@
         <v>1601</v>
       </c>
       <c r="E577">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F577" t="s">
         <v>1615</v>
@@ -28560,7 +28560,7 @@
         <v>1601</v>
       </c>
       <c r="E578">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F578" t="s">
         <v>1613</v>
@@ -28595,7 +28595,7 @@
         <v>1601</v>
       </c>
       <c r="E579">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F579" t="s">
         <v>1613</v>
@@ -28630,7 +28630,7 @@
         <v>1601</v>
       </c>
       <c r="E580">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F580" t="s">
         <v>1613</v>
@@ -28665,7 +28665,7 @@
         <v>1601</v>
       </c>
       <c r="E581">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F581" t="s">
         <v>1613</v>
@@ -28700,7 +28700,7 @@
         <v>1601</v>
       </c>
       <c r="E582">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F582" t="s">
         <v>1613</v>
@@ -28735,7 +28735,7 @@
         <v>1601</v>
       </c>
       <c r="E583">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F583" t="s">
         <v>1613</v>
@@ -28770,7 +28770,7 @@
         <v>1602</v>
       </c>
       <c r="E584">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F584" t="s">
         <v>1613</v>
@@ -28808,7 +28808,7 @@
         <v>1602</v>
       </c>
       <c r="E585">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F585" t="s">
         <v>1613</v>
@@ -28843,7 +28843,7 @@
         <v>1603</v>
       </c>
       <c r="E586">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F586" t="s">
         <v>1613</v>
@@ -28878,7 +28878,7 @@
         <v>1603</v>
       </c>
       <c r="E587">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F587" t="s">
         <v>1615</v>
@@ -28916,7 +28916,7 @@
         <v>1603</v>
       </c>
       <c r="E588">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F588" t="s">
         <v>1613</v>
@@ -28951,7 +28951,7 @@
         <v>1603</v>
       </c>
       <c r="E589">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F589" t="s">
         <v>1613</v>
@@ -28986,7 +28986,7 @@
         <v>1603</v>
       </c>
       <c r="E590">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F590" t="s">
         <v>1613</v>
@@ -29021,7 +29021,7 @@
         <v>1603</v>
       </c>
       <c r="E591">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F591" t="s">
         <v>1613</v>
@@ -29056,7 +29056,7 @@
         <v>1603</v>
       </c>
       <c r="E592">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F592" t="s">
         <v>1613</v>
@@ -29091,7 +29091,7 @@
         <v>1603</v>
       </c>
       <c r="E593">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F593" t="s">
         <v>1615</v>
@@ -29126,7 +29126,7 @@
         <v>1603</v>
       </c>
       <c r="E594">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F594" t="s">
         <v>1613</v>
@@ -29161,7 +29161,7 @@
         <v>1603</v>
       </c>
       <c r="E595">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F595" t="s">
         <v>1613</v>
@@ -29196,7 +29196,7 @@
         <v>1604</v>
       </c>
       <c r="E596">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F596" t="s">
         <v>1613</v>
@@ -29231,7 +29231,7 @@
         <v>1604</v>
       </c>
       <c r="E597">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F597" t="s">
         <v>1613</v>
@@ -29266,7 +29266,7 @@
         <v>1604</v>
       </c>
       <c r="E598">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F598" t="s">
         <v>1613</v>
@@ -29301,7 +29301,7 @@
         <v>1604</v>
       </c>
       <c r="E599">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F599" t="s">
         <v>1613</v>
@@ -29336,7 +29336,7 @@
         <v>1604</v>
       </c>
       <c r="E600">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F600" t="s">
         <v>1615</v>
@@ -29374,7 +29374,7 @@
         <v>1604</v>
       </c>
       <c r="E601">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F601" t="s">
         <v>1613</v>
@@ -29409,7 +29409,7 @@
         <v>1604</v>
       </c>
       <c r="E602">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F602" t="s">
         <v>1613</v>
@@ -29444,7 +29444,7 @@
         <v>1604</v>
       </c>
       <c r="E603">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F603" t="s">
         <v>1613</v>
@@ -29479,7 +29479,7 @@
         <v>1604</v>
       </c>
       <c r="E604">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F604" t="s">
         <v>1613</v>
@@ -29514,7 +29514,7 @@
         <v>1604</v>
       </c>
       <c r="E605">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F605" t="s">
         <v>1615</v>
@@ -29549,7 +29549,7 @@
         <v>1604</v>
       </c>
       <c r="E606">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F606" t="s">
         <v>1613</v>
@@ -29584,7 +29584,7 @@
         <v>1604</v>
       </c>
       <c r="E607">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F607" t="s">
         <v>1617</v>
@@ -29619,7 +29619,7 @@
         <v>1604</v>
       </c>
       <c r="E608">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F608" t="s">
         <v>1613</v>
@@ -29654,7 +29654,7 @@
         <v>1605</v>
       </c>
       <c r="E609">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F609" t="s">
         <v>1613</v>
@@ -29689,7 +29689,7 @@
         <v>1605</v>
       </c>
       <c r="E610">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F610" t="s">
         <v>1613</v>
@@ -29724,7 +29724,7 @@
         <v>1605</v>
       </c>
       <c r="E611">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F611" t="s">
         <v>1613</v>
@@ -29759,7 +29759,7 @@
         <v>1605</v>
       </c>
       <c r="E612">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F612" t="s">
         <v>1613</v>
@@ -29794,7 +29794,7 @@
         <v>1605</v>
       </c>
       <c r="E613">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F613" t="s">
         <v>1613</v>
@@ -29829,7 +29829,7 @@
         <v>1605</v>
       </c>
       <c r="E614">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F614" t="s">
         <v>1613</v>
@@ -29864,7 +29864,7 @@
         <v>1605</v>
       </c>
       <c r="E615">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F615" t="s">
         <v>1613</v>
@@ -29899,7 +29899,7 @@
         <v>1605</v>
       </c>
       <c r="E616">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F616" t="s">
         <v>1613</v>
@@ -29934,7 +29934,7 @@
         <v>1605</v>
       </c>
       <c r="E617">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F617" t="s">
         <v>1613</v>
@@ -29972,7 +29972,7 @@
         <v>1605</v>
       </c>
       <c r="E618">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F618" t="s">
         <v>1615</v>
@@ -30010,7 +30010,7 @@
         <v>1605</v>
       </c>
       <c r="E619">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F619" t="s">
         <v>1613</v>
@@ -30045,7 +30045,7 @@
         <v>1605</v>
       </c>
       <c r="E620">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F620" t="s">
         <v>1615</v>
@@ -30080,7 +30080,7 @@
         <v>1605</v>
       </c>
       <c r="E621">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F621" t="s">
         <v>1615</v>
@@ -30115,7 +30115,7 @@
         <v>1605</v>
       </c>
       <c r="E622">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F622" t="s">
         <v>1613</v>
@@ -30150,7 +30150,7 @@
         <v>1606</v>
       </c>
       <c r="E623">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F623" t="s">
         <v>1613</v>
@@ -30185,7 +30185,7 @@
         <v>1606</v>
       </c>
       <c r="E624">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F624" t="s">
         <v>1613</v>
@@ -30220,7 +30220,7 @@
         <v>1606</v>
       </c>
       <c r="E625">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F625" t="s">
         <v>1613</v>
@@ -30255,7 +30255,7 @@
         <v>1606</v>
       </c>
       <c r="E626">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F626" t="s">
         <v>1613</v>
@@ -30290,7 +30290,7 @@
         <v>1606</v>
       </c>
       <c r="E627">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F627" t="s">
         <v>1613</v>
@@ -30325,7 +30325,7 @@
         <v>1606</v>
       </c>
       <c r="E628">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F628" t="s">
         <v>1613</v>
@@ -30360,7 +30360,7 @@
         <v>1606</v>
       </c>
       <c r="E629">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F629" t="s">
         <v>1613</v>
@@ -30395,7 +30395,7 @@
         <v>1606</v>
       </c>
       <c r="E630">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F630" t="s">
         <v>1613</v>
@@ -30430,7 +30430,7 @@
         <v>1606</v>
       </c>
       <c r="E631">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F631" t="s">
         <v>1613</v>
@@ -30465,7 +30465,7 @@
         <v>1606</v>
       </c>
       <c r="E632">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F632" t="s">
         <v>1613</v>
@@ -30503,7 +30503,7 @@
         <v>1607</v>
       </c>
       <c r="E633">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F633" t="s">
         <v>1613</v>
@@ -30538,7 +30538,7 @@
         <v>1607</v>
       </c>
       <c r="E634">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F634" t="s">
         <v>1613</v>
@@ -30573,7 +30573,7 @@
         <v>1608</v>
       </c>
       <c r="E635">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F635" t="s">
         <v>1613</v>
@@ -30611,7 +30611,7 @@
         <v>1608</v>
       </c>
       <c r="E636">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F636" t="s">
         <v>1613</v>
@@ -30646,7 +30646,7 @@
         <v>1608</v>
       </c>
       <c r="E637">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F637" t="s">
         <v>1613</v>
@@ -30681,7 +30681,7 @@
         <v>1608</v>
       </c>
       <c r="E638">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F638" t="s">
         <v>1615</v>
@@ -30719,7 +30719,7 @@
         <v>1608</v>
       </c>
       <c r="E639">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F639" t="s">
         <v>1615</v>
@@ -30757,7 +30757,7 @@
         <v>1608</v>
       </c>
       <c r="E640">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F640" t="s">
         <v>1613</v>
@@ -30792,7 +30792,7 @@
         <v>1608</v>
       </c>
       <c r="E641">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F641" t="s">
         <v>1613</v>
@@ -30827,7 +30827,7 @@
         <v>1608</v>
       </c>
       <c r="E642">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F642" t="s">
         <v>1613</v>
@@ -30862,7 +30862,7 @@
         <v>1609</v>
       </c>
       <c r="E643">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F643" t="s">
         <v>1613</v>
@@ -30897,7 +30897,7 @@
         <v>1609</v>
       </c>
       <c r="E644">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F644" t="s">
         <v>1613</v>
@@ -30932,7 +30932,7 @@
         <v>1609</v>
       </c>
       <c r="E645">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F645" t="s">
         <v>1613</v>
@@ -30967,7 +30967,7 @@
         <v>1609</v>
       </c>
       <c r="E646">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F646" t="s">
         <v>1613</v>
@@ -31002,7 +31002,7 @@
         <v>1609</v>
       </c>
       <c r="E647">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F647" t="s">
         <v>1613</v>
@@ -31037,7 +31037,7 @@
         <v>1609</v>
       </c>
       <c r="E648">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F648" t="s">
         <v>1613</v>
@@ -31072,7 +31072,7 @@
         <v>1609</v>
       </c>
       <c r="E649">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F649" t="s">
         <v>1613</v>
@@ -31107,7 +31107,7 @@
         <v>1609</v>
       </c>
       <c r="E650">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F650" t="s">
         <v>1613</v>
@@ -31142,7 +31142,7 @@
         <v>1609</v>
       </c>
       <c r="E651">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F651" t="s">
         <v>1613</v>
@@ -31177,7 +31177,7 @@
         <v>1609</v>
       </c>
       <c r="E652">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F652" t="s">
         <v>1613</v>
@@ -31212,7 +31212,7 @@
         <v>1609</v>
       </c>
       <c r="E653">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F653" t="s">
         <v>1613</v>
@@ -31247,7 +31247,7 @@
         <v>1609</v>
       </c>
       <c r="E654">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F654" t="s">
         <v>1613</v>
@@ -31282,7 +31282,7 @@
         <v>1609</v>
       </c>
       <c r="E655">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F655" t="s">
         <v>1613</v>
@@ -31320,7 +31320,7 @@
         <v>1609</v>
       </c>
       <c r="E656">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F656" t="s">
         <v>1613</v>
@@ -31358,7 +31358,7 @@
         <v>1609</v>
       </c>
       <c r="E657">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F657" t="s">
         <v>1613</v>
@@ -31393,7 +31393,7 @@
         <v>1610</v>
       </c>
       <c r="E658">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F658" t="s">
         <v>1613</v>
@@ -31428,7 +31428,7 @@
         <v>1610</v>
       </c>
       <c r="E659">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F659" t="s">
         <v>1615</v>
@@ -31466,7 +31466,7 @@
         <v>1610</v>
       </c>
       <c r="E660">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F660" t="s">
         <v>1613</v>
@@ -31501,7 +31501,7 @@
         <v>1610</v>
       </c>
       <c r="E661">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F661" t="s">
         <v>1613</v>
@@ -31536,7 +31536,7 @@
         <v>1611</v>
       </c>
       <c r="E662">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F662" t="s">
         <v>1613</v>
@@ -31571,7 +31571,7 @@
         <v>1611</v>
       </c>
       <c r="E663">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F663" t="s">
         <v>1613</v>
@@ -31606,7 +31606,7 @@
         <v>1611</v>
       </c>
       <c r="E664">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F664" t="s">
         <v>1613</v>
@@ -31641,7 +31641,7 @@
         <v>1611</v>
       </c>
       <c r="E665">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F665" t="s">
         <v>1613</v>
@@ -31676,7 +31676,7 @@
         <v>1611</v>
       </c>
       <c r="E666">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F666" t="s">
         <v>1615</v>
@@ -31714,7 +31714,7 @@
         <v>1611</v>
       </c>
       <c r="E667">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F667" t="s">
         <v>1615</v>
@@ -31752,7 +31752,7 @@
         <v>1611</v>
       </c>
       <c r="E668">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F668" t="s">
         <v>1613</v>
@@ -31787,7 +31787,7 @@
         <v>1611</v>
       </c>
       <c r="E669">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F669" t="s">
         <v>1613</v>
@@ -31822,7 +31822,7 @@
         <v>1611</v>
       </c>
       <c r="E670">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F670" t="s">
         <v>1613</v>
@@ -31857,7 +31857,7 @@
         <v>1611</v>
       </c>
       <c r="E671">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F671" t="s">
         <v>1613</v>
@@ -31892,7 +31892,7 @@
         <v>1611</v>
       </c>
       <c r="E672">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F672" t="s">
         <v>1613</v>
@@ -31927,7 +31927,7 @@
         <v>1611</v>
       </c>
       <c r="E673">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F673" t="s">
         <v>1613</v>
@@ -31962,7 +31962,7 @@
         <v>1612</v>
       </c>
       <c r="E674">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F674" t="s">
         <v>1617</v>
@@ -31997,7 +31997,7 @@
         <v>1612</v>
       </c>
       <c r="E675">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F675" t="s">
         <v>1613</v>
@@ -32032,7 +32032,7 @@
         <v>1612</v>
       </c>
       <c r="E676">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F676" t="s">
         <v>1613</v>
@@ -32067,7 +32067,7 @@
         <v>1612</v>
       </c>
       <c r="E677">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F677" t="s">
         <v>1613</v>
@@ -32102,7 +32102,7 @@
         <v>1612</v>
       </c>
       <c r="E678">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F678" t="s">
         <v>1613</v>
@@ -32137,7 +32137,7 @@
         <v>1612</v>
       </c>
       <c r="E679">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F679" t="s">
         <v>1613</v>
@@ -32172,7 +32172,7 @@
         <v>1612</v>
       </c>
       <c r="E680">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F680" t="s">
         <v>1613</v>
@@ -32207,7 +32207,7 @@
         <v>1612</v>
       </c>
       <c r="E681">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F681" t="s">
         <v>1613</v>
@@ -32242,7 +32242,7 @@
         <v>1612</v>
       </c>
       <c r="E682">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F682" t="s">
         <v>1613</v>

--- a/BacklogGATEAutoCompleto.xlsx
+++ b/BacklogGATEAutoCompleto.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6791" uniqueCount="2612">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6781" uniqueCount="2611">
   <si>
     <t>NUCLEO</t>
   </si>
@@ -7826,9 +7826,6 @@
   </si>
   <si>
     <t>ECONOMICIDADE CONTÁBIL,ECONOMICIDADE CONTÁBIL</t>
-  </si>
-  <si>
-    <t>PATRIMÔNIO HISTÓRICO E CULTURAL,FENOMENOS DE ENERGIA E INFORMAÇÃO</t>
   </si>
   <si>
     <t>RECURSOS HÍDRICOS,VALORAÇÃO DANOS AMBIENTAIS</t>
@@ -8207,7 +8204,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L676"/>
+  <dimension ref="A1:L675"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
@@ -17464,7 +17461,7 @@
     </row>
     <row r="265" spans="1:12">
       <c r="A265" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="B265" t="s">
         <v>306</v>
@@ -17485,7 +17482,7 @@
         <v>1601</v>
       </c>
       <c r="I265" t="s">
-        <v>1649</v>
+        <v>1625</v>
       </c>
       <c r="J265" t="s">
         <v>2004</v>
@@ -29304,13 +29301,13 @@
     </row>
     <row r="602" spans="1:12">
       <c r="A602" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B602" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="C602" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="D602" t="s">
         <v>1587</v>
@@ -29325,27 +29322,27 @@
         <v>1601</v>
       </c>
       <c r="I602" t="s">
-        <v>1734</v>
+        <v>1703</v>
       </c>
       <c r="J602" t="s">
-        <v>2333</v>
+        <v>2334</v>
       </c>
       <c r="K602" t="s">
-        <v>2518</v>
+        <v>2473</v>
       </c>
       <c r="L602" t="s">
-        <v>2604</v>
+        <v>2558</v>
       </c>
     </row>
     <row r="603" spans="1:12">
       <c r="A603" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="B603" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C603" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="D603" t="s">
         <v>1587</v>
@@ -29357,16 +29354,19 @@
         <v>1596</v>
       </c>
       <c r="G603" t="s">
-        <v>1601</v>
+        <v>1602</v>
+      </c>
+      <c r="H603" t="s">
+        <v>1616</v>
       </c>
       <c r="I603" t="s">
-        <v>1703</v>
+        <v>1667</v>
       </c>
       <c r="J603" t="s">
-        <v>2334</v>
+        <v>2335</v>
       </c>
       <c r="K603" t="s">
-        <v>2473</v>
+        <v>2416</v>
       </c>
       <c r="L603" t="s">
         <v>2558</v>
@@ -29389,7 +29389,7 @@
         <v>11</v>
       </c>
       <c r="F604" t="s">
-        <v>1596</v>
+        <v>1598</v>
       </c>
       <c r="G604" t="s">
         <v>1602</v>
@@ -29412,13 +29412,13 @@
     </row>
     <row r="605" spans="1:12">
       <c r="A605" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="B605" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C605" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="D605" t="s">
         <v>1587</v>
@@ -29430,33 +29430,30 @@
         <v>1598</v>
       </c>
       <c r="G605" t="s">
-        <v>1602</v>
-      </c>
-      <c r="H605" t="s">
-        <v>1616</v>
+        <v>1601</v>
       </c>
       <c r="I605" t="s">
-        <v>1667</v>
+        <v>1736</v>
       </c>
       <c r="J605" t="s">
-        <v>2335</v>
+        <v>2336</v>
       </c>
       <c r="K605" t="s">
-        <v>2416</v>
+        <v>2413</v>
       </c>
       <c r="L605" t="s">
-        <v>2558</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="606" spans="1:12">
       <c r="A606" t="s">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="B606" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C606" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="D606" t="s">
         <v>1587</v>
@@ -29471,27 +29468,27 @@
         <v>1601</v>
       </c>
       <c r="I606" t="s">
-        <v>1736</v>
+        <v>1676</v>
       </c>
       <c r="J606" t="s">
-        <v>2336</v>
+        <v>2337</v>
       </c>
       <c r="K606" t="s">
         <v>2413</v>
       </c>
       <c r="L606" t="s">
-        <v>2605</v>
+        <v>2563</v>
       </c>
     </row>
     <row r="607" spans="1:12">
       <c r="A607" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="B607" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="C607" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="D607" t="s">
         <v>1587</v>
@@ -29500,22 +29497,22 @@
         <v>11</v>
       </c>
       <c r="F607" t="s">
-        <v>1598</v>
+        <v>1596</v>
       </c>
       <c r="G607" t="s">
         <v>1601</v>
       </c>
       <c r="I607" t="s">
-        <v>1676</v>
+        <v>1649</v>
       </c>
       <c r="J607" t="s">
-        <v>2337</v>
+        <v>2338</v>
       </c>
       <c r="K607" t="s">
-        <v>2413</v>
+        <v>2440</v>
       </c>
       <c r="L607" t="s">
-        <v>2563</v>
+        <v>2526</v>
       </c>
     </row>
     <row r="608" spans="1:12">
@@ -29523,16 +29520,16 @@
         <v>23</v>
       </c>
       <c r="B608" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="C608" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="D608" t="s">
-        <v>1587</v>
+        <v>1588</v>
       </c>
       <c r="E608">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F608" t="s">
         <v>1596</v>
@@ -29541,27 +29538,27 @@
         <v>1601</v>
       </c>
       <c r="I608" t="s">
-        <v>1649</v>
+        <v>1715</v>
       </c>
       <c r="J608" t="s">
-        <v>2338</v>
+        <v>2339</v>
       </c>
       <c r="K608" t="s">
-        <v>2440</v>
+        <v>2519</v>
       </c>
       <c r="L608" t="s">
-        <v>2526</v>
+        <v>2558</v>
       </c>
     </row>
     <row r="609" spans="1:12">
       <c r="A609" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B609" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C609" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="D609" t="s">
         <v>1588</v>
@@ -29576,27 +29573,27 @@
         <v>1601</v>
       </c>
       <c r="I609" t="s">
-        <v>1715</v>
+        <v>1735</v>
       </c>
       <c r="J609" t="s">
-        <v>2339</v>
+        <v>2048</v>
       </c>
       <c r="K609" t="s">
-        <v>2519</v>
+        <v>2414</v>
       </c>
       <c r="L609" t="s">
-        <v>2558</v>
+        <v>2582</v>
       </c>
     </row>
     <row r="610" spans="1:12">
       <c r="A610" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B610" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="C610" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="D610" t="s">
         <v>1588</v>
@@ -29611,16 +29608,16 @@
         <v>1601</v>
       </c>
       <c r="I610" t="s">
-        <v>1735</v>
+        <v>1715</v>
       </c>
       <c r="J610" t="s">
-        <v>2048</v>
+        <v>2340</v>
       </c>
       <c r="K610" t="s">
-        <v>2414</v>
+        <v>2422</v>
       </c>
       <c r="L610" t="s">
-        <v>2582</v>
+        <v>2558</v>
       </c>
     </row>
     <row r="611" spans="1:12">
@@ -29628,10 +29625,10 @@
         <v>23</v>
       </c>
       <c r="B611" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C611" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="D611" t="s">
         <v>1588</v>
@@ -29646,13 +29643,13 @@
         <v>1601</v>
       </c>
       <c r="I611" t="s">
-        <v>1715</v>
+        <v>1703</v>
       </c>
       <c r="J611" t="s">
-        <v>2340</v>
+        <v>2341</v>
       </c>
       <c r="K611" t="s">
-        <v>2422</v>
+        <v>2436</v>
       </c>
       <c r="L611" t="s">
         <v>2558</v>
@@ -29663,10 +29660,10 @@
         <v>23</v>
       </c>
       <c r="B612" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="C612" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="D612" t="s">
         <v>1588</v>
@@ -29681,27 +29678,27 @@
         <v>1601</v>
       </c>
       <c r="I612" t="s">
-        <v>1703</v>
+        <v>1694</v>
       </c>
       <c r="J612" t="s">
-        <v>2341</v>
+        <v>2342</v>
       </c>
       <c r="K612" t="s">
-        <v>2436</v>
+        <v>2473</v>
       </c>
       <c r="L612" t="s">
-        <v>2558</v>
+        <v>2526</v>
       </c>
     </row>
     <row r="613" spans="1:12">
       <c r="A613" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B613" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C613" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="D613" t="s">
         <v>1588</v>
@@ -29716,27 +29713,27 @@
         <v>1601</v>
       </c>
       <c r="I613" t="s">
-        <v>1694</v>
+        <v>1735</v>
       </c>
       <c r="J613" t="s">
-        <v>2342</v>
+        <v>2343</v>
       </c>
       <c r="K613" t="s">
-        <v>2473</v>
+        <v>2458</v>
       </c>
       <c r="L613" t="s">
-        <v>2526</v>
+        <v>2537</v>
       </c>
     </row>
     <row r="614" spans="1:12">
       <c r="A614" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B614" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C614" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="D614" t="s">
         <v>1588</v>
@@ -29751,27 +29748,27 @@
         <v>1601</v>
       </c>
       <c r="I614" t="s">
-        <v>1735</v>
+        <v>1703</v>
       </c>
       <c r="J614" t="s">
-        <v>2343</v>
+        <v>2344</v>
       </c>
       <c r="K614" t="s">
-        <v>2458</v>
+        <v>2416</v>
       </c>
       <c r="L614" t="s">
-        <v>2537</v>
+        <v>2558</v>
       </c>
     </row>
     <row r="615" spans="1:12">
       <c r="A615" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B615" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C615" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="D615" t="s">
         <v>1588</v>
@@ -29786,27 +29783,27 @@
         <v>1601</v>
       </c>
       <c r="I615" t="s">
-        <v>1703</v>
+        <v>1735</v>
       </c>
       <c r="J615" t="s">
-        <v>2344</v>
+        <v>2345</v>
       </c>
       <c r="K615" t="s">
-        <v>2416</v>
+        <v>2480</v>
       </c>
       <c r="L615" t="s">
-        <v>2558</v>
+        <v>2537</v>
       </c>
     </row>
     <row r="616" spans="1:12">
       <c r="A616" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B616" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C616" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="D616" t="s">
         <v>1588</v>
@@ -29821,27 +29818,27 @@
         <v>1601</v>
       </c>
       <c r="I616" t="s">
-        <v>1735</v>
+        <v>1703</v>
       </c>
       <c r="J616" t="s">
-        <v>2345</v>
+        <v>2346</v>
       </c>
       <c r="K616" t="s">
         <v>2480</v>
       </c>
       <c r="L616" t="s">
-        <v>2537</v>
+        <v>2558</v>
       </c>
     </row>
     <row r="617" spans="1:12">
       <c r="A617" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B617" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C617" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="D617" t="s">
         <v>1588</v>
@@ -29853,19 +29850,22 @@
         <v>1596</v>
       </c>
       <c r="G617" t="s">
-        <v>1601</v>
+        <v>1604</v>
+      </c>
+      <c r="H617" t="s">
+        <v>1617</v>
       </c>
       <c r="I617" t="s">
-        <v>1703</v>
+        <v>1734</v>
       </c>
       <c r="J617" t="s">
-        <v>2346</v>
+        <v>1777</v>
       </c>
       <c r="K617" t="s">
-        <v>2480</v>
+        <v>2520</v>
       </c>
       <c r="L617" t="s">
-        <v>2558</v>
+        <v>2605</v>
       </c>
     </row>
     <row r="618" spans="1:12">
@@ -29873,48 +29873,45 @@
         <v>24</v>
       </c>
       <c r="B618" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C618" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="D618" t="s">
-        <v>1588</v>
+        <v>1589</v>
       </c>
       <c r="E618">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F618" t="s">
         <v>1596</v>
       </c>
       <c r="G618" t="s">
-        <v>1604</v>
-      </c>
-      <c r="H618" t="s">
-        <v>1617</v>
+        <v>1601</v>
       </c>
       <c r="I618" t="s">
-        <v>1734</v>
+        <v>1735</v>
       </c>
       <c r="J618" t="s">
-        <v>1777</v>
+        <v>2347</v>
       </c>
       <c r="K618" t="s">
-        <v>2520</v>
+        <v>2429</v>
       </c>
       <c r="L618" t="s">
-        <v>2606</v>
+        <v>2560</v>
       </c>
     </row>
     <row r="619" spans="1:12">
       <c r="A619" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B619" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C619" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="D619" t="s">
         <v>1589</v>
@@ -29929,16 +29926,16 @@
         <v>1601</v>
       </c>
       <c r="I619" t="s">
-        <v>1735</v>
+        <v>1715</v>
       </c>
       <c r="J619" t="s">
-        <v>2347</v>
+        <v>2348</v>
       </c>
       <c r="K619" t="s">
         <v>2429</v>
       </c>
       <c r="L619" t="s">
-        <v>2560</v>
+        <v>2558</v>
       </c>
     </row>
     <row r="620" spans="1:12">
@@ -29946,34 +29943,37 @@
         <v>23</v>
       </c>
       <c r="B620" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="C620" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="D620" t="s">
-        <v>1589</v>
+        <v>1590</v>
       </c>
       <c r="E620">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F620" t="s">
         <v>1596</v>
       </c>
       <c r="G620" t="s">
-        <v>1601</v>
+        <v>1603</v>
+      </c>
+      <c r="H620" t="s">
+        <v>1618</v>
       </c>
       <c r="I620" t="s">
-        <v>1715</v>
+        <v>1694</v>
       </c>
       <c r="J620" t="s">
-        <v>2348</v>
+        <v>2349</v>
       </c>
       <c r="K620" t="s">
-        <v>2429</v>
+        <v>2504</v>
       </c>
       <c r="L620" t="s">
-        <v>2558</v>
+        <v>2526</v>
       </c>
     </row>
     <row r="621" spans="1:12">
@@ -29981,10 +29981,10 @@
         <v>23</v>
       </c>
       <c r="B621" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C621" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="D621" t="s">
         <v>1590</v>
@@ -29996,22 +29996,19 @@
         <v>1596</v>
       </c>
       <c r="G621" t="s">
-        <v>1603</v>
-      </c>
-      <c r="H621" t="s">
-        <v>1618</v>
+        <v>1601</v>
       </c>
       <c r="I621" t="s">
         <v>1694</v>
       </c>
       <c r="J621" t="s">
-        <v>2349</v>
+        <v>2350</v>
       </c>
       <c r="K621" t="s">
-        <v>2504</v>
+        <v>2440</v>
       </c>
       <c r="L621" t="s">
-        <v>2526</v>
+        <v>2606</v>
       </c>
     </row>
     <row r="622" spans="1:12">
@@ -30019,10 +30016,10 @@
         <v>23</v>
       </c>
       <c r="B622" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="C622" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="D622" t="s">
         <v>1590</v>
@@ -30037,27 +30034,27 @@
         <v>1601</v>
       </c>
       <c r="I622" t="s">
-        <v>1694</v>
+        <v>1714</v>
       </c>
       <c r="J622" t="s">
-        <v>2350</v>
+        <v>2351</v>
       </c>
       <c r="K622" t="s">
-        <v>2440</v>
+        <v>2443</v>
       </c>
       <c r="L622" t="s">
-        <v>2607</v>
+        <v>2582</v>
       </c>
     </row>
     <row r="623" spans="1:12">
       <c r="A623" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="B623" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="C623" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="D623" t="s">
         <v>1590</v>
@@ -30066,33 +30063,36 @@
         <v>7</v>
       </c>
       <c r="F623" t="s">
-        <v>1596</v>
+        <v>1598</v>
       </c>
       <c r="G623" t="s">
-        <v>1601</v>
+        <v>1602</v>
+      </c>
+      <c r="H623" t="s">
+        <v>1612</v>
       </c>
       <c r="I623" t="s">
-        <v>1714</v>
+        <v>1737</v>
       </c>
       <c r="J623" t="s">
-        <v>2351</v>
+        <v>2352</v>
       </c>
       <c r="K623" t="s">
-        <v>2443</v>
+        <v>2407</v>
       </c>
       <c r="L623" t="s">
-        <v>2582</v>
+        <v>2589</v>
       </c>
     </row>
     <row r="624" spans="1:12">
       <c r="A624" t="s">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="B624" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="C624" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="D624" t="s">
         <v>1590</v>
@@ -30107,30 +30107,30 @@
         <v>1602</v>
       </c>
       <c r="H624" t="s">
-        <v>1612</v>
+        <v>1619</v>
       </c>
       <c r="I624" t="s">
-        <v>1737</v>
+        <v>1738</v>
       </c>
       <c r="J624" t="s">
-        <v>2352</v>
+        <v>2353</v>
       </c>
       <c r="K624" t="s">
-        <v>2407</v>
+        <v>2418</v>
       </c>
       <c r="L624" t="s">
-        <v>2589</v>
+        <v>2528</v>
       </c>
     </row>
     <row r="625" spans="1:12">
       <c r="A625" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="B625" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="C625" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="D625" t="s">
         <v>1590</v>
@@ -30139,25 +30139,22 @@
         <v>7</v>
       </c>
       <c r="F625" t="s">
-        <v>1598</v>
+        <v>1596</v>
       </c>
       <c r="G625" t="s">
-        <v>1602</v>
-      </c>
-      <c r="H625" t="s">
-        <v>1619</v>
+        <v>1601</v>
       </c>
       <c r="I625" t="s">
-        <v>1738</v>
+        <v>1715</v>
       </c>
       <c r="J625" t="s">
-        <v>2353</v>
+        <v>2354</v>
       </c>
       <c r="K625" t="s">
-        <v>2418</v>
+        <v>2483</v>
       </c>
       <c r="L625" t="s">
-        <v>2528</v>
+        <v>2558</v>
       </c>
     </row>
     <row r="626" spans="1:12">
@@ -30165,10 +30162,10 @@
         <v>23</v>
       </c>
       <c r="B626" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="C626" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="D626" t="s">
         <v>1590</v>
@@ -30183,16 +30180,16 @@
         <v>1601</v>
       </c>
       <c r="I626" t="s">
-        <v>1715</v>
+        <v>1731</v>
       </c>
       <c r="J626" t="s">
-        <v>2354</v>
+        <v>2355</v>
       </c>
       <c r="K626" t="s">
-        <v>2483</v>
+        <v>2452</v>
       </c>
       <c r="L626" t="s">
-        <v>2558</v>
+        <v>2527</v>
       </c>
     </row>
     <row r="627" spans="1:12">
@@ -30200,10 +30197,10 @@
         <v>23</v>
       </c>
       <c r="B627" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C627" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="D627" t="s">
         <v>1590</v>
@@ -30218,16 +30215,16 @@
         <v>1601</v>
       </c>
       <c r="I627" t="s">
-        <v>1731</v>
+        <v>1649</v>
       </c>
       <c r="J627" t="s">
-        <v>2355</v>
+        <v>2356</v>
       </c>
       <c r="K627" t="s">
-        <v>2452</v>
+        <v>2448</v>
       </c>
       <c r="L627" t="s">
-        <v>2527</v>
+        <v>2526</v>
       </c>
     </row>
     <row r="628" spans="1:12">
@@ -30235,16 +30232,16 @@
         <v>23</v>
       </c>
       <c r="B628" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C628" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="D628" t="s">
-        <v>1590</v>
+        <v>1591</v>
       </c>
       <c r="E628">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F628" t="s">
         <v>1596</v>
@@ -30253,16 +30250,16 @@
         <v>1601</v>
       </c>
       <c r="I628" t="s">
-        <v>1649</v>
+        <v>1714</v>
       </c>
       <c r="J628" t="s">
-        <v>2356</v>
+        <v>2357</v>
       </c>
       <c r="K628" t="s">
-        <v>2448</v>
+        <v>2442</v>
       </c>
       <c r="L628" t="s">
-        <v>2526</v>
+        <v>2582</v>
       </c>
     </row>
     <row r="629" spans="1:12">
@@ -30270,10 +30267,10 @@
         <v>23</v>
       </c>
       <c r="B629" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="C629" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="D629" t="s">
         <v>1591</v>
@@ -30288,16 +30285,16 @@
         <v>1601</v>
       </c>
       <c r="I629" t="s">
-        <v>1714</v>
+        <v>1731</v>
       </c>
       <c r="J629" t="s">
-        <v>2357</v>
+        <v>2358</v>
       </c>
       <c r="K629" t="s">
-        <v>2442</v>
+        <v>2435</v>
       </c>
       <c r="L629" t="s">
-        <v>2582</v>
+        <v>2527</v>
       </c>
     </row>
     <row r="630" spans="1:12">
@@ -30305,10 +30302,10 @@
         <v>23</v>
       </c>
       <c r="B630" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="C630" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="D630" t="s">
         <v>1591</v>
@@ -30323,27 +30320,27 @@
         <v>1601</v>
       </c>
       <c r="I630" t="s">
-        <v>1731</v>
+        <v>1649</v>
       </c>
       <c r="J630" t="s">
-        <v>2358</v>
+        <v>2359</v>
       </c>
       <c r="K630" t="s">
-        <v>2435</v>
+        <v>2416</v>
       </c>
       <c r="L630" t="s">
-        <v>2527</v>
+        <v>2526</v>
       </c>
     </row>
     <row r="631" spans="1:12">
       <c r="A631" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B631" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="C631" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="D631" t="s">
         <v>1591</v>
@@ -30358,27 +30355,27 @@
         <v>1601</v>
       </c>
       <c r="I631" t="s">
-        <v>1649</v>
+        <v>1734</v>
       </c>
       <c r="J631" t="s">
-        <v>2359</v>
+        <v>1762</v>
       </c>
       <c r="K631" t="s">
         <v>2416</v>
       </c>
       <c r="L631" t="s">
-        <v>2526</v>
+        <v>2533</v>
       </c>
     </row>
     <row r="632" spans="1:12">
       <c r="A632" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B632" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="C632" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="D632" t="s">
         <v>1591</v>
@@ -30393,16 +30390,16 @@
         <v>1601</v>
       </c>
       <c r="I632" t="s">
-        <v>1734</v>
+        <v>1714</v>
       </c>
       <c r="J632" t="s">
-        <v>1762</v>
+        <v>2360</v>
       </c>
       <c r="K632" t="s">
-        <v>2416</v>
+        <v>2521</v>
       </c>
       <c r="L632" t="s">
-        <v>2533</v>
+        <v>2582</v>
       </c>
     </row>
     <row r="633" spans="1:12">
@@ -30410,10 +30407,10 @@
         <v>23</v>
       </c>
       <c r="B633" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C633" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="D633" t="s">
         <v>1591</v>
@@ -30428,16 +30425,16 @@
         <v>1601</v>
       </c>
       <c r="I633" t="s">
-        <v>1714</v>
+        <v>1739</v>
       </c>
       <c r="J633" t="s">
-        <v>2360</v>
+        <v>2361</v>
       </c>
       <c r="K633" t="s">
-        <v>2521</v>
+        <v>2420</v>
       </c>
       <c r="L633" t="s">
-        <v>2582</v>
+        <v>2526</v>
       </c>
     </row>
     <row r="634" spans="1:12">
@@ -30445,10 +30442,10 @@
         <v>23</v>
       </c>
       <c r="B634" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="C634" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="D634" t="s">
         <v>1591</v>
@@ -30463,10 +30460,10 @@
         <v>1601</v>
       </c>
       <c r="I634" t="s">
-        <v>1739</v>
+        <v>1669</v>
       </c>
       <c r="J634" t="s">
-        <v>2361</v>
+        <v>2362</v>
       </c>
       <c r="K634" t="s">
         <v>2420</v>
@@ -30480,10 +30477,10 @@
         <v>23</v>
       </c>
       <c r="B635" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="C635" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="D635" t="s">
         <v>1591</v>
@@ -30498,16 +30495,16 @@
         <v>1601</v>
       </c>
       <c r="I635" t="s">
-        <v>1669</v>
+        <v>1703</v>
       </c>
       <c r="J635" t="s">
-        <v>2362</v>
+        <v>2363</v>
       </c>
       <c r="K635" t="s">
         <v>2420</v>
       </c>
       <c r="L635" t="s">
-        <v>2526</v>
+        <v>2558</v>
       </c>
     </row>
     <row r="636" spans="1:12">
@@ -30515,10 +30512,10 @@
         <v>23</v>
       </c>
       <c r="B636" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="C636" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="D636" t="s">
         <v>1591</v>
@@ -30536,10 +30533,10 @@
         <v>1703</v>
       </c>
       <c r="J636" t="s">
-        <v>2363</v>
+        <v>2364</v>
       </c>
       <c r="K636" t="s">
-        <v>2420</v>
+        <v>2496</v>
       </c>
       <c r="L636" t="s">
         <v>2558</v>
@@ -30547,13 +30544,13 @@
     </row>
     <row r="637" spans="1:12">
       <c r="A637" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B637" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C637" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="D637" t="s">
         <v>1591</v>
@@ -30568,16 +30565,16 @@
         <v>1601</v>
       </c>
       <c r="I637" t="s">
-        <v>1703</v>
+        <v>1740</v>
       </c>
       <c r="J637" t="s">
-        <v>2364</v>
+        <v>2365</v>
       </c>
       <c r="K637" t="s">
-        <v>2496</v>
+        <v>2515</v>
       </c>
       <c r="L637" t="s">
-        <v>2558</v>
+        <v>2602</v>
       </c>
     </row>
     <row r="638" spans="1:12">
@@ -30585,10 +30582,10 @@
         <v>24</v>
       </c>
       <c r="B638" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C638" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="D638" t="s">
         <v>1591</v>
@@ -30603,27 +30600,27 @@
         <v>1601</v>
       </c>
       <c r="I638" t="s">
-        <v>1740</v>
+        <v>1735</v>
       </c>
       <c r="J638" t="s">
-        <v>2365</v>
+        <v>2366</v>
       </c>
       <c r="K638" t="s">
-        <v>2515</v>
+        <v>2446</v>
       </c>
       <c r="L638" t="s">
-        <v>2602</v>
+        <v>2607</v>
       </c>
     </row>
     <row r="639" spans="1:12">
       <c r="A639" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B639" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="C639" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="D639" t="s">
         <v>1591</v>
@@ -30638,27 +30635,27 @@
         <v>1601</v>
       </c>
       <c r="I639" t="s">
-        <v>1735</v>
+        <v>1649</v>
       </c>
       <c r="J639" t="s">
-        <v>2366</v>
+        <v>2232</v>
       </c>
       <c r="K639" t="s">
-        <v>2446</v>
+        <v>2407</v>
       </c>
       <c r="L639" t="s">
-        <v>2608</v>
+        <v>2526</v>
       </c>
     </row>
     <row r="640" spans="1:12">
       <c r="A640" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="B640" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="C640" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="D640" t="s">
         <v>1591</v>
@@ -30670,30 +30667,33 @@
         <v>1596</v>
       </c>
       <c r="G640" t="s">
-        <v>1601</v>
+        <v>1602</v>
+      </c>
+      <c r="H640" t="s">
+        <v>1615</v>
       </c>
       <c r="I640" t="s">
-        <v>1649</v>
+        <v>1741</v>
       </c>
       <c r="J640" t="s">
-        <v>2232</v>
+        <v>2367</v>
       </c>
       <c r="K640" t="s">
-        <v>2407</v>
+        <v>2489</v>
       </c>
       <c r="L640" t="s">
-        <v>2526</v>
+        <v>2540</v>
       </c>
     </row>
     <row r="641" spans="1:12">
       <c r="A641" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="B641" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="C641" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="D641" t="s">
         <v>1591</v>
@@ -30705,33 +30705,33 @@
         <v>1596</v>
       </c>
       <c r="G641" t="s">
-        <v>1602</v>
+        <v>1603</v>
       </c>
       <c r="H641" t="s">
-        <v>1615</v>
+        <v>1620</v>
       </c>
       <c r="I641" t="s">
-        <v>1741</v>
+        <v>1714</v>
       </c>
       <c r="J641" t="s">
-        <v>2367</v>
+        <v>2368</v>
       </c>
       <c r="K641" t="s">
-        <v>2489</v>
+        <v>2480</v>
       </c>
       <c r="L641" t="s">
-        <v>2540</v>
+        <v>2582</v>
       </c>
     </row>
     <row r="642" spans="1:12">
       <c r="A642" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="B642" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="C642" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
       <c r="D642" t="s">
         <v>1591</v>
@@ -30740,36 +30740,36 @@
         <v>6</v>
       </c>
       <c r="F642" t="s">
-        <v>1596</v>
+        <v>1598</v>
       </c>
       <c r="G642" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
       <c r="H642" t="s">
-        <v>1620</v>
+        <v>1616</v>
       </c>
       <c r="I642" t="s">
-        <v>1714</v>
+        <v>1690</v>
       </c>
       <c r="J642" t="s">
-        <v>2368</v>
+        <v>2369</v>
       </c>
       <c r="K642" t="s">
-        <v>2480</v>
+        <v>2456</v>
       </c>
       <c r="L642" t="s">
-        <v>2582</v>
+        <v>2571</v>
       </c>
     </row>
     <row r="643" spans="1:12">
       <c r="A643" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="B643" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="C643" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="D643" t="s">
         <v>1591</v>
@@ -30778,42 +30778,39 @@
         <v>6</v>
       </c>
       <c r="F643" t="s">
-        <v>1598</v>
+        <v>1596</v>
       </c>
       <c r="G643" t="s">
-        <v>1602</v>
-      </c>
-      <c r="H643" t="s">
-        <v>1616</v>
+        <v>1601</v>
       </c>
       <c r="I643" t="s">
-        <v>1690</v>
+        <v>1735</v>
       </c>
       <c r="J643" t="s">
-        <v>2369</v>
+        <v>2370</v>
       </c>
       <c r="K643" t="s">
-        <v>2456</v>
+        <v>2491</v>
       </c>
       <c r="L643" t="s">
-        <v>2571</v>
+        <v>2548</v>
       </c>
     </row>
     <row r="644" spans="1:12">
       <c r="A644" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B644" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="C644" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="D644" t="s">
-        <v>1591</v>
+        <v>1592</v>
       </c>
       <c r="E644">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F644" t="s">
         <v>1596</v>
@@ -30822,27 +30819,27 @@
         <v>1601</v>
       </c>
       <c r="I644" t="s">
-        <v>1735</v>
+        <v>1714</v>
       </c>
       <c r="J644" t="s">
-        <v>2370</v>
+        <v>2371</v>
       </c>
       <c r="K644" t="s">
-        <v>2491</v>
+        <v>2437</v>
       </c>
       <c r="L644" t="s">
-        <v>2548</v>
+        <v>2582</v>
       </c>
     </row>
     <row r="645" spans="1:12">
       <c r="A645" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="B645" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="C645" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
       <c r="D645" t="s">
         <v>1592</v>
@@ -30851,33 +30848,36 @@
         <v>5</v>
       </c>
       <c r="F645" t="s">
-        <v>1596</v>
+        <v>1598</v>
       </c>
       <c r="G645" t="s">
-        <v>1601</v>
+        <v>1602</v>
+      </c>
+      <c r="H645" t="s">
+        <v>1621</v>
       </c>
       <c r="I645" t="s">
-        <v>1714</v>
+        <v>1742</v>
       </c>
       <c r="J645" t="s">
-        <v>2371</v>
+        <v>2372</v>
       </c>
       <c r="K645" t="s">
-        <v>2437</v>
+        <v>2442</v>
       </c>
       <c r="L645" t="s">
-        <v>2582</v>
+        <v>2547</v>
       </c>
     </row>
     <row r="646" spans="1:12">
       <c r="A646" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="B646" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="C646" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="D646" t="s">
         <v>1592</v>
@@ -30886,36 +30886,33 @@
         <v>5</v>
       </c>
       <c r="F646" t="s">
-        <v>1598</v>
+        <v>1596</v>
       </c>
       <c r="G646" t="s">
-        <v>1602</v>
-      </c>
-      <c r="H646" t="s">
-        <v>1621</v>
+        <v>1601</v>
       </c>
       <c r="I646" t="s">
-        <v>1742</v>
+        <v>1735</v>
       </c>
       <c r="J646" t="s">
-        <v>2372</v>
+        <v>2373</v>
       </c>
       <c r="K646" t="s">
-        <v>2442</v>
+        <v>2478</v>
       </c>
       <c r="L646" t="s">
-        <v>2547</v>
+        <v>2608</v>
       </c>
     </row>
     <row r="647" spans="1:12">
       <c r="A647" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B647" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="C647" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="D647" t="s">
         <v>1592</v>
@@ -30930,16 +30927,16 @@
         <v>1601</v>
       </c>
       <c r="I647" t="s">
-        <v>1735</v>
+        <v>1714</v>
       </c>
       <c r="J647" t="s">
-        <v>2373</v>
+        <v>2374</v>
       </c>
       <c r="K647" t="s">
-        <v>2478</v>
+        <v>2442</v>
       </c>
       <c r="L647" t="s">
-        <v>2609</v>
+        <v>2582</v>
       </c>
     </row>
     <row r="648" spans="1:12">
@@ -30947,16 +30944,16 @@
         <v>23</v>
       </c>
       <c r="B648" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C648" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="D648" t="s">
-        <v>1592</v>
+        <v>1593</v>
       </c>
       <c r="E648">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F648" t="s">
         <v>1596</v>
@@ -30965,16 +30962,16 @@
         <v>1601</v>
       </c>
       <c r="I648" t="s">
-        <v>1714</v>
+        <v>1669</v>
       </c>
       <c r="J648" t="s">
-        <v>2374</v>
+        <v>2375</v>
       </c>
       <c r="K648" t="s">
-        <v>2442</v>
+        <v>2438</v>
       </c>
       <c r="L648" t="s">
-        <v>2582</v>
+        <v>2526</v>
       </c>
     </row>
     <row r="649" spans="1:12">
@@ -30982,10 +30979,10 @@
         <v>23</v>
       </c>
       <c r="B649" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="C649" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
       <c r="D649" t="s">
         <v>1593</v>
@@ -31003,10 +31000,10 @@
         <v>1669</v>
       </c>
       <c r="J649" t="s">
-        <v>2375</v>
+        <v>2376</v>
       </c>
       <c r="K649" t="s">
-        <v>2438</v>
+        <v>2450</v>
       </c>
       <c r="L649" t="s">
         <v>2526</v>
@@ -31017,10 +31014,10 @@
         <v>23</v>
       </c>
       <c r="B650" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C650" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
       <c r="D650" t="s">
         <v>1593</v>
@@ -31035,16 +31032,16 @@
         <v>1601</v>
       </c>
       <c r="I650" t="s">
-        <v>1669</v>
+        <v>1703</v>
       </c>
       <c r="J650" t="s">
-        <v>2376</v>
+        <v>2377</v>
       </c>
       <c r="K650" t="s">
-        <v>2450</v>
+        <v>2473</v>
       </c>
       <c r="L650" t="s">
-        <v>2526</v>
+        <v>2558</v>
       </c>
     </row>
     <row r="651" spans="1:12">
@@ -31052,10 +31049,10 @@
         <v>23</v>
       </c>
       <c r="B651" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="C651" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
       <c r="D651" t="s">
         <v>1593</v>
@@ -31070,27 +31067,27 @@
         <v>1601</v>
       </c>
       <c r="I651" t="s">
-        <v>1703</v>
+        <v>1694</v>
       </c>
       <c r="J651" t="s">
-        <v>2377</v>
+        <v>2378</v>
       </c>
       <c r="K651" t="s">
-        <v>2473</v>
+        <v>2483</v>
       </c>
       <c r="L651" t="s">
-        <v>2558</v>
+        <v>2526</v>
       </c>
     </row>
     <row r="652" spans="1:12">
       <c r="A652" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B652" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C652" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="D652" t="s">
         <v>1593</v>
@@ -31099,33 +31096,36 @@
         <v>4</v>
       </c>
       <c r="F652" t="s">
-        <v>1596</v>
+        <v>1598</v>
       </c>
       <c r="G652" t="s">
-        <v>1601</v>
+        <v>1602</v>
+      </c>
+      <c r="H652" t="s">
+        <v>1619</v>
       </c>
       <c r="I652" t="s">
-        <v>1694</v>
+        <v>1630</v>
       </c>
       <c r="J652" t="s">
-        <v>2378</v>
+        <v>2379</v>
       </c>
       <c r="K652" t="s">
-        <v>2483</v>
+        <v>2443</v>
       </c>
       <c r="L652" t="s">
-        <v>2526</v>
+        <v>2532</v>
       </c>
     </row>
     <row r="653" spans="1:12">
       <c r="A653" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B653" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="C653" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="D653" t="s">
         <v>1593</v>
@@ -31140,30 +31140,30 @@
         <v>1602</v>
       </c>
       <c r="H653" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="I653" t="s">
-        <v>1630</v>
+        <v>1743</v>
       </c>
       <c r="J653" t="s">
-        <v>2379</v>
+        <v>2380</v>
       </c>
       <c r="K653" t="s">
         <v>2443</v>
       </c>
       <c r="L653" t="s">
-        <v>2532</v>
+        <v>2546</v>
       </c>
     </row>
     <row r="654" spans="1:12">
       <c r="A654" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B654" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="C654" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="D654" t="s">
         <v>1593</v>
@@ -31172,36 +31172,33 @@
         <v>4</v>
       </c>
       <c r="F654" t="s">
-        <v>1598</v>
+        <v>1596</v>
       </c>
       <c r="G654" t="s">
-        <v>1602</v>
-      </c>
-      <c r="H654" t="s">
-        <v>1622</v>
+        <v>1601</v>
       </c>
       <c r="I654" t="s">
-        <v>1743</v>
+        <v>1723</v>
       </c>
       <c r="J654" t="s">
-        <v>2380</v>
+        <v>2381</v>
       </c>
       <c r="K654" t="s">
-        <v>2443</v>
+        <v>2522</v>
       </c>
       <c r="L654" t="s">
-        <v>2546</v>
+        <v>2548</v>
       </c>
     </row>
     <row r="655" spans="1:12">
       <c r="A655" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B655" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C655" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="D655" t="s">
         <v>1593</v>
@@ -31216,27 +31213,27 @@
         <v>1601</v>
       </c>
       <c r="I655" t="s">
-        <v>1723</v>
+        <v>1735</v>
       </c>
       <c r="J655" t="s">
-        <v>2381</v>
+        <v>2382</v>
       </c>
       <c r="K655" t="s">
-        <v>2522</v>
+        <v>2465</v>
       </c>
       <c r="L655" t="s">
-        <v>2548</v>
+        <v>2537</v>
       </c>
     </row>
     <row r="656" spans="1:12">
       <c r="A656" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B656" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="C656" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="D656" t="s">
         <v>1593</v>
@@ -31251,16 +31248,16 @@
         <v>1601</v>
       </c>
       <c r="I656" t="s">
-        <v>1735</v>
+        <v>1714</v>
       </c>
       <c r="J656" t="s">
-        <v>2382</v>
+        <v>2383</v>
       </c>
       <c r="K656" t="s">
-        <v>2465</v>
+        <v>2409</v>
       </c>
       <c r="L656" t="s">
-        <v>2537</v>
+        <v>2582</v>
       </c>
     </row>
     <row r="657" spans="1:12">
@@ -31268,10 +31265,10 @@
         <v>23</v>
       </c>
       <c r="B657" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="C657" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="D657" t="s">
         <v>1593</v>
@@ -31289,7 +31286,7 @@
         <v>1714</v>
       </c>
       <c r="J657" t="s">
-        <v>2383</v>
+        <v>2384</v>
       </c>
       <c r="K657" t="s">
         <v>2409</v>
@@ -31303,10 +31300,10 @@
         <v>23</v>
       </c>
       <c r="B658" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="C658" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="D658" t="s">
         <v>1593</v>
@@ -31324,7 +31321,7 @@
         <v>1714</v>
       </c>
       <c r="J658" t="s">
-        <v>2384</v>
+        <v>2385</v>
       </c>
       <c r="K658" t="s">
         <v>2409</v>
@@ -31338,10 +31335,10 @@
         <v>23</v>
       </c>
       <c r="B659" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="C659" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="D659" t="s">
         <v>1593</v>
@@ -31356,16 +31353,16 @@
         <v>1601</v>
       </c>
       <c r="I659" t="s">
-        <v>1714</v>
+        <v>1694</v>
       </c>
       <c r="J659" t="s">
-        <v>2385</v>
+        <v>2386</v>
       </c>
       <c r="K659" t="s">
-        <v>2409</v>
+        <v>2497</v>
       </c>
       <c r="L659" t="s">
-        <v>2582</v>
+        <v>2526</v>
       </c>
     </row>
     <row r="660" spans="1:12">
@@ -31373,10 +31370,10 @@
         <v>23</v>
       </c>
       <c r="B660" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="C660" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
       <c r="D660" t="s">
         <v>1593</v>
@@ -31391,62 +31388,62 @@
         <v>1601</v>
       </c>
       <c r="I660" t="s">
-        <v>1694</v>
+        <v>1715</v>
       </c>
       <c r="J660" t="s">
-        <v>2386</v>
+        <v>2387</v>
       </c>
       <c r="K660" t="s">
-        <v>2497</v>
+        <v>2431</v>
       </c>
       <c r="L660" t="s">
-        <v>2526</v>
+        <v>2558</v>
       </c>
     </row>
     <row r="661" spans="1:12">
       <c r="A661" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="B661" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="C661" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
       <c r="D661" t="s">
-        <v>1593</v>
+        <v>1594</v>
       </c>
       <c r="E661">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F661" t="s">
-        <v>1596</v>
+        <v>1600</v>
       </c>
       <c r="G661" t="s">
         <v>1601</v>
       </c>
       <c r="I661" t="s">
-        <v>1715</v>
+        <v>1744</v>
       </c>
       <c r="J661" t="s">
-        <v>2387</v>
+        <v>2388</v>
       </c>
       <c r="K661" t="s">
-        <v>2431</v>
+        <v>2406</v>
       </c>
       <c r="L661" t="s">
-        <v>2558</v>
+        <v>2567</v>
       </c>
     </row>
     <row r="662" spans="1:12">
       <c r="A662" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="B662" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="C662" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
       <c r="D662" t="s">
         <v>1594</v>
@@ -31455,33 +31452,33 @@
         <v>3</v>
       </c>
       <c r="F662" t="s">
-        <v>1600</v>
+        <v>1596</v>
       </c>
       <c r="G662" t="s">
         <v>1601</v>
       </c>
       <c r="I662" t="s">
-        <v>1744</v>
+        <v>1729</v>
       </c>
       <c r="J662" t="s">
-        <v>2388</v>
+        <v>2113</v>
       </c>
       <c r="K662" t="s">
-        <v>2406</v>
+        <v>2430</v>
       </c>
       <c r="L662" t="s">
-        <v>2567</v>
+        <v>2582</v>
       </c>
     </row>
     <row r="663" spans="1:12">
       <c r="A663" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="B663" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="C663" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
       <c r="D663" t="s">
         <v>1594</v>
@@ -31496,16 +31493,16 @@
         <v>1601</v>
       </c>
       <c r="I663" t="s">
-        <v>1729</v>
+        <v>1735</v>
       </c>
       <c r="J663" t="s">
-        <v>2113</v>
+        <v>2389</v>
       </c>
       <c r="K663" t="s">
         <v>2430</v>
       </c>
       <c r="L663" t="s">
-        <v>2582</v>
+        <v>2557</v>
       </c>
     </row>
     <row r="664" spans="1:12">
@@ -31513,10 +31510,10 @@
         <v>24</v>
       </c>
       <c r="B664" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="C664" t="s">
-        <v>1370</v>
+        <v>1371</v>
       </c>
       <c r="D664" t="s">
         <v>1594</v>
@@ -31531,27 +31528,27 @@
         <v>1601</v>
       </c>
       <c r="I664" t="s">
-        <v>1735</v>
+        <v>1734</v>
       </c>
       <c r="J664" t="s">
-        <v>2389</v>
+        <v>2390</v>
       </c>
       <c r="K664" t="s">
         <v>2430</v>
       </c>
       <c r="L664" t="s">
-        <v>2557</v>
+        <v>2582</v>
       </c>
     </row>
     <row r="665" spans="1:12">
       <c r="A665" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B665" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="C665" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
       <c r="D665" t="s">
         <v>1594</v>
@@ -31566,13 +31563,13 @@
         <v>1601</v>
       </c>
       <c r="I665" t="s">
-        <v>1734</v>
+        <v>1714</v>
       </c>
       <c r="J665" t="s">
-        <v>2390</v>
+        <v>2391</v>
       </c>
       <c r="K665" t="s">
-        <v>2430</v>
+        <v>2513</v>
       </c>
       <c r="L665" t="s">
         <v>2582</v>
@@ -31583,10 +31580,10 @@
         <v>23</v>
       </c>
       <c r="B666" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C666" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
       <c r="D666" t="s">
         <v>1594</v>
@@ -31601,16 +31598,16 @@
         <v>1601</v>
       </c>
       <c r="I666" t="s">
-        <v>1714</v>
+        <v>1731</v>
       </c>
       <c r="J666" t="s">
-        <v>2391</v>
+        <v>2392</v>
       </c>
       <c r="K666" t="s">
-        <v>2513</v>
+        <v>2420</v>
       </c>
       <c r="L666" t="s">
-        <v>2582</v>
+        <v>2527</v>
       </c>
     </row>
     <row r="667" spans="1:12">
@@ -31618,10 +31615,10 @@
         <v>23</v>
       </c>
       <c r="B667" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="C667" t="s">
-        <v>1373</v>
+        <v>1374</v>
       </c>
       <c r="D667" t="s">
         <v>1594</v>
@@ -31636,16 +31633,16 @@
         <v>1601</v>
       </c>
       <c r="I667" t="s">
-        <v>1731</v>
+        <v>1715</v>
       </c>
       <c r="J667" t="s">
-        <v>2392</v>
+        <v>2393</v>
       </c>
       <c r="K667" t="s">
-        <v>2420</v>
+        <v>2483</v>
       </c>
       <c r="L667" t="s">
-        <v>2527</v>
+        <v>2558</v>
       </c>
     </row>
     <row r="668" spans="1:12">
@@ -31653,10 +31650,10 @@
         <v>23</v>
       </c>
       <c r="B668" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="C668" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
       <c r="D668" t="s">
         <v>1594</v>
@@ -31671,16 +31668,16 @@
         <v>1601</v>
       </c>
       <c r="I668" t="s">
-        <v>1715</v>
+        <v>1714</v>
       </c>
       <c r="J668" t="s">
-        <v>2393</v>
+        <v>2394</v>
       </c>
       <c r="K668" t="s">
-        <v>2483</v>
+        <v>2457</v>
       </c>
       <c r="L668" t="s">
-        <v>2558</v>
+        <v>2582</v>
       </c>
     </row>
     <row r="669" spans="1:12">
@@ -31688,16 +31685,16 @@
         <v>23</v>
       </c>
       <c r="B669" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="C669" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
       <c r="D669" t="s">
-        <v>1594</v>
+        <v>1595</v>
       </c>
       <c r="E669">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F669" t="s">
         <v>1596</v>
@@ -31706,27 +31703,27 @@
         <v>1601</v>
       </c>
       <c r="I669" t="s">
-        <v>1714</v>
+        <v>1694</v>
       </c>
       <c r="J669" t="s">
-        <v>2394</v>
+        <v>2395</v>
       </c>
       <c r="K669" t="s">
-        <v>2457</v>
+        <v>2423</v>
       </c>
       <c r="L669" t="s">
-        <v>2582</v>
+        <v>2526</v>
       </c>
     </row>
     <row r="670" spans="1:12">
       <c r="A670" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B670" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="C670" t="s">
-        <v>1376</v>
+        <v>1377</v>
       </c>
       <c r="D670" t="s">
         <v>1595</v>
@@ -31741,27 +31738,27 @@
         <v>1601</v>
       </c>
       <c r="I670" t="s">
-        <v>1694</v>
+        <v>1625</v>
       </c>
       <c r="J670" t="s">
-        <v>2395</v>
+        <v>2396</v>
       </c>
       <c r="K670" t="s">
-        <v>2423</v>
+        <v>2464</v>
       </c>
       <c r="L670" t="s">
-        <v>2526</v>
+        <v>2582</v>
       </c>
     </row>
     <row r="671" spans="1:12">
       <c r="A671" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B671" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="C671" t="s">
-        <v>1377</v>
+        <v>1378</v>
       </c>
       <c r="D671" t="s">
         <v>1595</v>
@@ -31776,13 +31773,13 @@
         <v>1601</v>
       </c>
       <c r="I671" t="s">
-        <v>1625</v>
+        <v>1739</v>
       </c>
       <c r="J671" t="s">
-        <v>2396</v>
+        <v>2397</v>
       </c>
       <c r="K671" t="s">
-        <v>2464</v>
+        <v>2523</v>
       </c>
       <c r="L671" t="s">
         <v>2582</v>
@@ -31793,10 +31790,10 @@
         <v>23</v>
       </c>
       <c r="B672" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="C672" t="s">
-        <v>1378</v>
+        <v>1379</v>
       </c>
       <c r="D672" t="s">
         <v>1595</v>
@@ -31814,10 +31811,10 @@
         <v>1739</v>
       </c>
       <c r="J672" t="s">
-        <v>2397</v>
+        <v>2398</v>
       </c>
       <c r="K672" t="s">
-        <v>2523</v>
+        <v>2524</v>
       </c>
       <c r="L672" t="s">
         <v>2582</v>
@@ -31828,10 +31825,10 @@
         <v>23</v>
       </c>
       <c r="B673" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="C673" t="s">
-        <v>1379</v>
+        <v>1380</v>
       </c>
       <c r="D673" t="s">
         <v>1595</v>
@@ -31843,33 +31840,33 @@
         <v>1596</v>
       </c>
       <c r="G673" t="s">
-        <v>1601</v>
+        <v>1602</v>
+      </c>
+      <c r="H673" t="s">
+        <v>1623</v>
       </c>
       <c r="I673" t="s">
-        <v>1739</v>
+        <v>1731</v>
       </c>
       <c r="J673" t="s">
-        <v>2398</v>
+        <v>2399</v>
       </c>
       <c r="K673" t="s">
-        <v>2524</v>
+        <v>2419</v>
       </c>
       <c r="L673" t="s">
-        <v>2582</v>
+        <v>2527</v>
       </c>
     </row>
     <row r="674" spans="1:12">
       <c r="A674" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B674" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="C674" t="s">
-        <v>1380</v>
-      </c>
-      <c r="D674" t="s">
-        <v>1595</v>
+        <v>1381</v>
       </c>
       <c r="E674">
         <v>0</v>
@@ -31878,22 +31875,19 @@
         <v>1596</v>
       </c>
       <c r="G674" t="s">
-        <v>1602</v>
-      </c>
-      <c r="H674" t="s">
-        <v>1623</v>
+        <v>1601</v>
       </c>
       <c r="I674" t="s">
-        <v>1731</v>
+        <v>1735</v>
       </c>
       <c r="J674" t="s">
-        <v>2399</v>
+        <v>2400</v>
       </c>
       <c r="K674" t="s">
-        <v>2419</v>
+        <v>2525</v>
       </c>
       <c r="L674" t="s">
-        <v>2527</v>
+        <v>2609</v>
       </c>
     </row>
     <row r="675" spans="1:12">
@@ -31901,10 +31895,10 @@
         <v>24</v>
       </c>
       <c r="B675" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="C675" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="E675">
         <v>0</v>
@@ -31919,45 +31913,13 @@
         <v>1735</v>
       </c>
       <c r="J675" t="s">
-        <v>2400</v>
+        <v>2401</v>
       </c>
       <c r="K675" t="s">
         <v>2525</v>
       </c>
       <c r="L675" t="s">
         <v>2610</v>
-      </c>
-    </row>
-    <row r="676" spans="1:12">
-      <c r="A676" t="s">
-        <v>24</v>
-      </c>
-      <c r="B676" t="s">
-        <v>712</v>
-      </c>
-      <c r="C676" t="s">
-        <v>1382</v>
-      </c>
-      <c r="E676">
-        <v>0</v>
-      </c>
-      <c r="F676" t="s">
-        <v>1596</v>
-      </c>
-      <c r="G676" t="s">
-        <v>1601</v>
-      </c>
-      <c r="I676" t="s">
-        <v>1735</v>
-      </c>
-      <c r="J676" t="s">
-        <v>2401</v>
-      </c>
-      <c r="K676" t="s">
-        <v>2525</v>
-      </c>
-      <c r="L676" t="s">
-        <v>2611</v>
       </c>
     </row>
   </sheetData>

--- a/BacklogGATEAutoCompleto.xlsx
+++ b/BacklogGATEAutoCompleto.xlsx
@@ -8259,7 +8259,7 @@
         <v>1383</v>
       </c>
       <c r="E2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="F2" t="s">
         <v>1596</v>
@@ -8294,7 +8294,7 @@
         <v>1384</v>
       </c>
       <c r="E3">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="F3" t="s">
         <v>1596</v>
@@ -8329,7 +8329,7 @@
         <v>1385</v>
       </c>
       <c r="E4">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="F4" t="s">
         <v>1596</v>
@@ -8364,7 +8364,7 @@
         <v>1386</v>
       </c>
       <c r="E5">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="F5" t="s">
         <v>1596</v>
@@ -8399,7 +8399,7 @@
         <v>1386</v>
       </c>
       <c r="E6">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="F6" t="s">
         <v>1596</v>
@@ -8434,7 +8434,7 @@
         <v>1387</v>
       </c>
       <c r="E7">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="F7" t="s">
         <v>1596</v>
@@ -8469,7 +8469,7 @@
         <v>1388</v>
       </c>
       <c r="E8">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="F8" t="s">
         <v>1596</v>
@@ -8504,7 +8504,7 @@
         <v>1389</v>
       </c>
       <c r="E9">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="F9" t="s">
         <v>1596</v>
@@ -8539,7 +8539,7 @@
         <v>1390</v>
       </c>
       <c r="E10">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="F10" t="s">
         <v>1596</v>
@@ -8574,7 +8574,7 @@
         <v>1391</v>
       </c>
       <c r="E11">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="F11" t="s">
         <v>1596</v>
@@ -8609,7 +8609,7 @@
         <v>1392</v>
       </c>
       <c r="E12">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="F12" t="s">
         <v>1596</v>
@@ -8644,7 +8644,7 @@
         <v>1393</v>
       </c>
       <c r="E13">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="F13" t="s">
         <v>1596</v>
@@ -8679,7 +8679,7 @@
         <v>1393</v>
       </c>
       <c r="E14">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="F14" t="s">
         <v>1596</v>
@@ -8714,7 +8714,7 @@
         <v>1394</v>
       </c>
       <c r="E15">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="F15" t="s">
         <v>1596</v>
@@ -8749,7 +8749,7 @@
         <v>1395</v>
       </c>
       <c r="E16">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="F16" t="s">
         <v>1596</v>
@@ -8784,7 +8784,7 @@
         <v>1396</v>
       </c>
       <c r="E17">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="F17" t="s">
         <v>1596</v>
@@ -8819,7 +8819,7 @@
         <v>1396</v>
       </c>
       <c r="E18">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="F18" t="s">
         <v>1596</v>
@@ -8854,7 +8854,7 @@
         <v>1397</v>
       </c>
       <c r="E19">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="F19" t="s">
         <v>1596</v>
@@ -8889,7 +8889,7 @@
         <v>1398</v>
       </c>
       <c r="E20">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F20" t="s">
         <v>1596</v>
@@ -8924,7 +8924,7 @@
         <v>1399</v>
       </c>
       <c r="E21">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="F21" t="s">
         <v>1596</v>
@@ -8959,7 +8959,7 @@
         <v>1399</v>
       </c>
       <c r="E22">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="F22" t="s">
         <v>1596</v>
@@ -8994,7 +8994,7 @@
         <v>1400</v>
       </c>
       <c r="E23">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F23" t="s">
         <v>1596</v>
@@ -9029,7 +9029,7 @@
         <v>1401</v>
       </c>
       <c r="E24">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="F24" t="s">
         <v>1596</v>
@@ -9064,7 +9064,7 @@
         <v>1402</v>
       </c>
       <c r="E25">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="F25" t="s">
         <v>1596</v>
@@ -9099,7 +9099,7 @@
         <v>1403</v>
       </c>
       <c r="E26">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F26" t="s">
         <v>1596</v>
@@ -9134,7 +9134,7 @@
         <v>1404</v>
       </c>
       <c r="E27">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F27" t="s">
         <v>1596</v>
@@ -9172,7 +9172,7 @@
         <v>1405</v>
       </c>
       <c r="E28">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F28" t="s">
         <v>1596</v>
@@ -9207,7 +9207,7 @@
         <v>1406</v>
       </c>
       <c r="E29">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F29" t="s">
         <v>1596</v>
@@ -9242,7 +9242,7 @@
         <v>1407</v>
       </c>
       <c r="E30">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F30" t="s">
         <v>1596</v>
@@ -9277,7 +9277,7 @@
         <v>1408</v>
       </c>
       <c r="E31">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F31" t="s">
         <v>1596</v>
@@ -9312,7 +9312,7 @@
         <v>1408</v>
       </c>
       <c r="E32">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F32" t="s">
         <v>1596</v>
@@ -9347,7 +9347,7 @@
         <v>1409</v>
       </c>
       <c r="E33">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F33" t="s">
         <v>1596</v>
@@ -9382,7 +9382,7 @@
         <v>1410</v>
       </c>
       <c r="E34">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F34" t="s">
         <v>1596</v>
@@ -9417,7 +9417,7 @@
         <v>1411</v>
       </c>
       <c r="E35">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F35" t="s">
         <v>1596</v>
@@ -9452,7 +9452,7 @@
         <v>1412</v>
       </c>
       <c r="E36">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="F36" t="s">
         <v>1596</v>
@@ -9487,7 +9487,7 @@
         <v>1413</v>
       </c>
       <c r="E37">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F37" t="s">
         <v>1596</v>
@@ -9522,7 +9522,7 @@
         <v>1414</v>
       </c>
       <c r="E38">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F38" t="s">
         <v>1596</v>
@@ -9557,7 +9557,7 @@
         <v>1415</v>
       </c>
       <c r="E39">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="F39" t="s">
         <v>1596</v>
@@ -9592,7 +9592,7 @@
         <v>1416</v>
       </c>
       <c r="E40">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F40" t="s">
         <v>1596</v>
@@ -9627,7 +9627,7 @@
         <v>1416</v>
       </c>
       <c r="E41">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F41" t="s">
         <v>1596</v>
@@ -9662,7 +9662,7 @@
         <v>1417</v>
       </c>
       <c r="E42">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F42" t="s">
         <v>1596</v>
@@ -9697,7 +9697,7 @@
         <v>1417</v>
       </c>
       <c r="E43">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F43" t="s">
         <v>1596</v>
@@ -9732,7 +9732,7 @@
         <v>1418</v>
       </c>
       <c r="E44">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F44" t="s">
         <v>1596</v>
@@ -9767,7 +9767,7 @@
         <v>1419</v>
       </c>
       <c r="E45">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F45" t="s">
         <v>1596</v>
@@ -9802,7 +9802,7 @@
         <v>1420</v>
       </c>
       <c r="E46">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F46" t="s">
         <v>1596</v>
@@ -9837,7 +9837,7 @@
         <v>1421</v>
       </c>
       <c r="E47">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F47" t="s">
         <v>1596</v>
@@ -9872,7 +9872,7 @@
         <v>1421</v>
       </c>
       <c r="E48">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F48" t="s">
         <v>1596</v>
@@ -9907,7 +9907,7 @@
         <v>1422</v>
       </c>
       <c r="E49">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F49" t="s">
         <v>1596</v>
@@ -9942,7 +9942,7 @@
         <v>1423</v>
       </c>
       <c r="E50">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F50" t="s">
         <v>1596</v>
@@ -9977,7 +9977,7 @@
         <v>1423</v>
       </c>
       <c r="E51">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F51" t="s">
         <v>1596</v>
@@ -10012,7 +10012,7 @@
         <v>1424</v>
       </c>
       <c r="E52">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F52" t="s">
         <v>1596</v>
@@ -10047,7 +10047,7 @@
         <v>1424</v>
       </c>
       <c r="E53">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F53" t="s">
         <v>1596</v>
@@ -10082,7 +10082,7 @@
         <v>1425</v>
       </c>
       <c r="E54">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F54" t="s">
         <v>1596</v>
@@ -10117,7 +10117,7 @@
         <v>1426</v>
       </c>
       <c r="E55">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F55" t="s">
         <v>1596</v>
@@ -10152,7 +10152,7 @@
         <v>1427</v>
       </c>
       <c r="E56">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F56" t="s">
         <v>1596</v>
@@ -10187,7 +10187,7 @@
         <v>1428</v>
       </c>
       <c r="E57">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F57" t="s">
         <v>1596</v>
@@ -10222,7 +10222,7 @@
         <v>1429</v>
       </c>
       <c r="E58">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F58" t="s">
         <v>1596</v>
@@ -10257,7 +10257,7 @@
         <v>1430</v>
       </c>
       <c r="E59">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F59" t="s">
         <v>1596</v>
@@ -10292,7 +10292,7 @@
         <v>1431</v>
       </c>
       <c r="E60">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F60" t="s">
         <v>1596</v>
@@ -10327,7 +10327,7 @@
         <v>1432</v>
       </c>
       <c r="E61">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F61" t="s">
         <v>1596</v>
@@ -10362,7 +10362,7 @@
         <v>1433</v>
       </c>
       <c r="E62">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F62" t="s">
         <v>1596</v>
@@ -10397,7 +10397,7 @@
         <v>1434</v>
       </c>
       <c r="E63">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F63" t="s">
         <v>1596</v>
@@ -10432,7 +10432,7 @@
         <v>1435</v>
       </c>
       <c r="E64">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F64" t="s">
         <v>1596</v>
@@ -10467,7 +10467,7 @@
         <v>1436</v>
       </c>
       <c r="E65">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F65" t="s">
         <v>1596</v>
@@ -10502,7 +10502,7 @@
         <v>1437</v>
       </c>
       <c r="E66">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F66" t="s">
         <v>1596</v>
@@ -10537,7 +10537,7 @@
         <v>1437</v>
       </c>
       <c r="E67">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F67" t="s">
         <v>1596</v>
@@ -10572,7 +10572,7 @@
         <v>1437</v>
       </c>
       <c r="E68">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F68" t="s">
         <v>1596</v>
@@ -10607,7 +10607,7 @@
         <v>1438</v>
       </c>
       <c r="E69">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F69" t="s">
         <v>1596</v>
@@ -10642,7 +10642,7 @@
         <v>1439</v>
       </c>
       <c r="E70">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F70" t="s">
         <v>1596</v>
@@ -10677,7 +10677,7 @@
         <v>1440</v>
       </c>
       <c r="E71">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F71" t="s">
         <v>1596</v>
@@ -10712,7 +10712,7 @@
         <v>1440</v>
       </c>
       <c r="E72">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F72" t="s">
         <v>1596</v>
@@ -10747,7 +10747,7 @@
         <v>1440</v>
       </c>
       <c r="E73">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F73" t="s">
         <v>1596</v>
@@ -10782,7 +10782,7 @@
         <v>1441</v>
       </c>
       <c r="E74">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F74" t="s">
         <v>1596</v>
@@ -10817,7 +10817,7 @@
         <v>1442</v>
       </c>
       <c r="E75">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F75" t="s">
         <v>1596</v>
@@ -10852,7 +10852,7 @@
         <v>1443</v>
       </c>
       <c r="E76">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F76" t="s">
         <v>1596</v>
@@ -10887,7 +10887,7 @@
         <v>1443</v>
       </c>
       <c r="E77">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F77" t="s">
         <v>1596</v>
@@ -10922,7 +10922,7 @@
         <v>1443</v>
       </c>
       <c r="E78">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F78" t="s">
         <v>1596</v>
@@ -10957,7 +10957,7 @@
         <v>1444</v>
       </c>
       <c r="E79">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F79" t="s">
         <v>1596</v>
@@ -10992,7 +10992,7 @@
         <v>1445</v>
       </c>
       <c r="E80">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F80" t="s">
         <v>1596</v>
@@ -11027,7 +11027,7 @@
         <v>1445</v>
       </c>
       <c r="E81">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F81" t="s">
         <v>1596</v>
@@ -11062,7 +11062,7 @@
         <v>1445</v>
       </c>
       <c r="E82">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F82" t="s">
         <v>1597</v>
@@ -11097,7 +11097,7 @@
         <v>1445</v>
       </c>
       <c r="E83">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F83" t="s">
         <v>1596</v>
@@ -11132,7 +11132,7 @@
         <v>1446</v>
       </c>
       <c r="E84">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F84" t="s">
         <v>1596</v>
@@ -11167,7 +11167,7 @@
         <v>1447</v>
       </c>
       <c r="E85">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F85" t="s">
         <v>1596</v>
@@ -11202,7 +11202,7 @@
         <v>1447</v>
       </c>
       <c r="E86">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F86" t="s">
         <v>1596</v>
@@ -11237,7 +11237,7 @@
         <v>1447</v>
       </c>
       <c r="E87">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F87" t="s">
         <v>1596</v>
@@ -11272,7 +11272,7 @@
         <v>1448</v>
       </c>
       <c r="E88">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F88" t="s">
         <v>1596</v>
@@ -11307,7 +11307,7 @@
         <v>1449</v>
       </c>
       <c r="E89">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F89" t="s">
         <v>1596</v>
@@ -11342,7 +11342,7 @@
         <v>1450</v>
       </c>
       <c r="E90">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F90" t="s">
         <v>1596</v>
@@ -11377,7 +11377,7 @@
         <v>1451</v>
       </c>
       <c r="E91">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F91" t="s">
         <v>1596</v>
@@ -11412,7 +11412,7 @@
         <v>1452</v>
       </c>
       <c r="E92">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F92" t="s">
         <v>1596</v>
@@ -11447,7 +11447,7 @@
         <v>1452</v>
       </c>
       <c r="E93">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F93" t="s">
         <v>1596</v>
@@ -11482,7 +11482,7 @@
         <v>1452</v>
       </c>
       <c r="E94">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F94" t="s">
         <v>1596</v>
@@ -11517,7 +11517,7 @@
         <v>1452</v>
       </c>
       <c r="E95">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F95" t="s">
         <v>1596</v>
@@ -11552,7 +11552,7 @@
         <v>1452</v>
       </c>
       <c r="E96">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F96" t="s">
         <v>1596</v>
@@ -11587,7 +11587,7 @@
         <v>1452</v>
       </c>
       <c r="E97">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F97" t="s">
         <v>1596</v>
@@ -11622,7 +11622,7 @@
         <v>1452</v>
       </c>
       <c r="E98">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F98" t="s">
         <v>1596</v>
@@ -11657,7 +11657,7 @@
         <v>1453</v>
       </c>
       <c r="E99">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F99" t="s">
         <v>1596</v>
@@ -11692,7 +11692,7 @@
         <v>1453</v>
       </c>
       <c r="E100">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F100" t="s">
         <v>1596</v>
@@ -11727,7 +11727,7 @@
         <v>1454</v>
       </c>
       <c r="E101">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F101" t="s">
         <v>1596</v>
@@ -11762,7 +11762,7 @@
         <v>1455</v>
       </c>
       <c r="E102">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F102" t="s">
         <v>1596</v>
@@ -11797,7 +11797,7 @@
         <v>1455</v>
       </c>
       <c r="E103">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F103" t="s">
         <v>1596</v>
@@ -11832,7 +11832,7 @@
         <v>1456</v>
       </c>
       <c r="E104">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F104" t="s">
         <v>1596</v>
@@ -11867,7 +11867,7 @@
         <v>1456</v>
       </c>
       <c r="E105">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F105" t="s">
         <v>1598</v>
@@ -11902,7 +11902,7 @@
         <v>1457</v>
       </c>
       <c r="E106">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F106" t="s">
         <v>1596</v>
@@ -11937,7 +11937,7 @@
         <v>1458</v>
       </c>
       <c r="E107">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F107" t="s">
         <v>1596</v>
@@ -11972,7 +11972,7 @@
         <v>1459</v>
       </c>
       <c r="E108">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F108" t="s">
         <v>1596</v>
@@ -12007,7 +12007,7 @@
         <v>1459</v>
       </c>
       <c r="E109">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F109" t="s">
         <v>1596</v>
@@ -12042,7 +12042,7 @@
         <v>1460</v>
       </c>
       <c r="E110">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F110" t="s">
         <v>1596</v>
@@ -12077,7 +12077,7 @@
         <v>1461</v>
       </c>
       <c r="E111">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F111" t="s">
         <v>1596</v>
@@ -12112,7 +12112,7 @@
         <v>1462</v>
       </c>
       <c r="E112">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F112" t="s">
         <v>1596</v>
@@ -12147,7 +12147,7 @@
         <v>1463</v>
       </c>
       <c r="E113">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F113" t="s">
         <v>1596</v>
@@ -12182,7 +12182,7 @@
         <v>1464</v>
       </c>
       <c r="E114">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F114" t="s">
         <v>1596</v>
@@ -12217,7 +12217,7 @@
         <v>1464</v>
       </c>
       <c r="E115">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F115" t="s">
         <v>1596</v>
@@ -12252,7 +12252,7 @@
         <v>1465</v>
       </c>
       <c r="E116">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F116" t="s">
         <v>1596</v>
@@ -12287,7 +12287,7 @@
         <v>1465</v>
       </c>
       <c r="E117">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F117" t="s">
         <v>1596</v>
@@ -12322,7 +12322,7 @@
         <v>1465</v>
       </c>
       <c r="E118">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F118" t="s">
         <v>1596</v>
@@ -12357,7 +12357,7 @@
         <v>1465</v>
       </c>
       <c r="E119">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F119" t="s">
         <v>1596</v>
@@ -12392,7 +12392,7 @@
         <v>1466</v>
       </c>
       <c r="E120">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F120" t="s">
         <v>1596</v>
@@ -12427,7 +12427,7 @@
         <v>1466</v>
       </c>
       <c r="E121">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F121" t="s">
         <v>1596</v>
@@ -12462,7 +12462,7 @@
         <v>1466</v>
       </c>
       <c r="E122">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F122" t="s">
         <v>1596</v>
@@ -12497,7 +12497,7 @@
         <v>1466</v>
       </c>
       <c r="E123">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F123" t="s">
         <v>1596</v>
@@ -12532,7 +12532,7 @@
         <v>1466</v>
       </c>
       <c r="E124">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F124" t="s">
         <v>1596</v>
@@ -12567,7 +12567,7 @@
         <v>1467</v>
       </c>
       <c r="E125">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F125" t="s">
         <v>1596</v>
@@ -12602,7 +12602,7 @@
         <v>1468</v>
       </c>
       <c r="E126">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F126" t="s">
         <v>1596</v>
@@ -12637,7 +12637,7 @@
         <v>1468</v>
       </c>
       <c r="E127">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F127" t="s">
         <v>1596</v>
@@ -12672,7 +12672,7 @@
         <v>1469</v>
       </c>
       <c r="E128">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F128" t="s">
         <v>1596</v>
@@ -12707,7 +12707,7 @@
         <v>1470</v>
       </c>
       <c r="E129">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F129" t="s">
         <v>1596</v>
@@ -12742,7 +12742,7 @@
         <v>1470</v>
       </c>
       <c r="E130">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F130" t="s">
         <v>1596</v>
@@ -12777,7 +12777,7 @@
         <v>1470</v>
       </c>
       <c r="E131">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F131" t="s">
         <v>1596</v>
@@ -12812,7 +12812,7 @@
         <v>1471</v>
       </c>
       <c r="E132">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F132" t="s">
         <v>1596</v>
@@ -12847,7 +12847,7 @@
         <v>1471</v>
       </c>
       <c r="E133">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F133" t="s">
         <v>1596</v>
@@ -12882,7 +12882,7 @@
         <v>1471</v>
       </c>
       <c r="E134">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F134" t="s">
         <v>1596</v>
@@ -12917,7 +12917,7 @@
         <v>1472</v>
       </c>
       <c r="E135">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F135" t="s">
         <v>1596</v>
@@ -12952,7 +12952,7 @@
         <v>1472</v>
       </c>
       <c r="E136">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F136" t="s">
         <v>1596</v>
@@ -12987,7 +12987,7 @@
         <v>1472</v>
       </c>
       <c r="E137">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F137" t="s">
         <v>1596</v>
@@ -13022,7 +13022,7 @@
         <v>1473</v>
       </c>
       <c r="E138">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F138" t="s">
         <v>1596</v>
@@ -13057,7 +13057,7 @@
         <v>1473</v>
       </c>
       <c r="E139">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F139" t="s">
         <v>1596</v>
@@ -13092,7 +13092,7 @@
         <v>1474</v>
       </c>
       <c r="E140">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F140" t="s">
         <v>1596</v>
@@ -13127,7 +13127,7 @@
         <v>1475</v>
       </c>
       <c r="E141">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F141" t="s">
         <v>1596</v>
@@ -13162,7 +13162,7 @@
         <v>1475</v>
       </c>
       <c r="E142">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F142" t="s">
         <v>1596</v>
@@ -13197,7 +13197,7 @@
         <v>1475</v>
       </c>
       <c r="E143">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F143" t="s">
         <v>1596</v>
@@ -13232,7 +13232,7 @@
         <v>1476</v>
       </c>
       <c r="E144">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F144" t="s">
         <v>1596</v>
@@ -13267,7 +13267,7 @@
         <v>1476</v>
       </c>
       <c r="E145">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F145" t="s">
         <v>1596</v>
@@ -13302,7 +13302,7 @@
         <v>1477</v>
       </c>
       <c r="E146">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F146" t="s">
         <v>1596</v>
@@ -13340,7 +13340,7 @@
         <v>1477</v>
       </c>
       <c r="E147">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F147" t="s">
         <v>1596</v>
@@ -13375,7 +13375,7 @@
         <v>1477</v>
       </c>
       <c r="E148">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F148" t="s">
         <v>1596</v>
@@ -13410,7 +13410,7 @@
         <v>1477</v>
       </c>
       <c r="E149">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F149" t="s">
         <v>1596</v>
@@ -13445,7 +13445,7 @@
         <v>1477</v>
       </c>
       <c r="E150">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F150" t="s">
         <v>1596</v>
@@ -13480,7 +13480,7 @@
         <v>1478</v>
       </c>
       <c r="E151">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F151" t="s">
         <v>1596</v>
@@ -13515,7 +13515,7 @@
         <v>1479</v>
       </c>
       <c r="E152">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F152" t="s">
         <v>1597</v>
@@ -13550,7 +13550,7 @@
         <v>1480</v>
       </c>
       <c r="E153">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F153" t="s">
         <v>1596</v>
@@ -13585,7 +13585,7 @@
         <v>1480</v>
       </c>
       <c r="E154">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F154" t="s">
         <v>1596</v>
@@ -13620,7 +13620,7 @@
         <v>1480</v>
       </c>
       <c r="E155">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F155" t="s">
         <v>1596</v>
@@ -13655,7 +13655,7 @@
         <v>1480</v>
       </c>
       <c r="E156">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F156" t="s">
         <v>1596</v>
@@ -13690,7 +13690,7 @@
         <v>1481</v>
       </c>
       <c r="E157">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F157" t="s">
         <v>1596</v>
@@ -13725,7 +13725,7 @@
         <v>1481</v>
       </c>
       <c r="E158">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F158" t="s">
         <v>1596</v>
@@ -13760,7 +13760,7 @@
         <v>1481</v>
       </c>
       <c r="E159">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F159" t="s">
         <v>1596</v>
@@ -13795,7 +13795,7 @@
         <v>1481</v>
       </c>
       <c r="E160">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F160" t="s">
         <v>1596</v>
@@ -13830,7 +13830,7 @@
         <v>1481</v>
       </c>
       <c r="E161">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F161" t="s">
         <v>1596</v>
@@ -13865,7 +13865,7 @@
         <v>1481</v>
       </c>
       <c r="E162">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F162" t="s">
         <v>1596</v>
@@ -13900,7 +13900,7 @@
         <v>1481</v>
       </c>
       <c r="E163">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F163" t="s">
         <v>1596</v>
@@ -13935,7 +13935,7 @@
         <v>1482</v>
       </c>
       <c r="E164">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F164" t="s">
         <v>1596</v>
@@ -13970,7 +13970,7 @@
         <v>1482</v>
       </c>
       <c r="E165">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F165" t="s">
         <v>1596</v>
@@ -14005,7 +14005,7 @@
         <v>1483</v>
       </c>
       <c r="E166">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F166" t="s">
         <v>1596</v>
@@ -14040,7 +14040,7 @@
         <v>1483</v>
       </c>
       <c r="E167">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F167" t="s">
         <v>1596</v>
@@ -14075,7 +14075,7 @@
         <v>1483</v>
       </c>
       <c r="E168">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F168" t="s">
         <v>1596</v>
@@ -14110,7 +14110,7 @@
         <v>1484</v>
       </c>
       <c r="E169">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F169" t="s">
         <v>1596</v>
@@ -14145,7 +14145,7 @@
         <v>1484</v>
       </c>
       <c r="E170">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F170" t="s">
         <v>1596</v>
@@ -14180,7 +14180,7 @@
         <v>1484</v>
       </c>
       <c r="E171">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F171" t="s">
         <v>1596</v>
@@ -14215,7 +14215,7 @@
         <v>1484</v>
       </c>
       <c r="E172">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F172" t="s">
         <v>1596</v>
@@ -14250,7 +14250,7 @@
         <v>1485</v>
       </c>
       <c r="E173">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F173" t="s">
         <v>1596</v>
@@ -14285,7 +14285,7 @@
         <v>1485</v>
       </c>
       <c r="E174">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F174" t="s">
         <v>1596</v>
@@ -14320,7 +14320,7 @@
         <v>1485</v>
       </c>
       <c r="E175">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F175" t="s">
         <v>1596</v>
@@ -14355,7 +14355,7 @@
         <v>1485</v>
       </c>
       <c r="E176">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F176" t="s">
         <v>1596</v>
@@ -14390,7 +14390,7 @@
         <v>1485</v>
       </c>
       <c r="E177">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F177" t="s">
         <v>1596</v>
@@ -14425,7 +14425,7 @@
         <v>1485</v>
       </c>
       <c r="E178">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F178" t="s">
         <v>1596</v>
@@ -14460,7 +14460,7 @@
         <v>1485</v>
       </c>
       <c r="E179">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F179" t="s">
         <v>1596</v>
@@ -14495,7 +14495,7 @@
         <v>1485</v>
       </c>
       <c r="E180">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F180" t="s">
         <v>1596</v>
@@ -14530,7 +14530,7 @@
         <v>1485</v>
       </c>
       <c r="E181">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F181" t="s">
         <v>1596</v>
@@ -14565,7 +14565,7 @@
         <v>1485</v>
       </c>
       <c r="E182">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F182" t="s">
         <v>1596</v>
@@ -14600,7 +14600,7 @@
         <v>1486</v>
       </c>
       <c r="E183">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F183" t="s">
         <v>1596</v>
@@ -14635,7 +14635,7 @@
         <v>1486</v>
       </c>
       <c r="E184">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F184" t="s">
         <v>1596</v>
@@ -14670,7 +14670,7 @@
         <v>1486</v>
       </c>
       <c r="E185">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F185" t="s">
         <v>1596</v>
@@ -14705,7 +14705,7 @@
         <v>1486</v>
       </c>
       <c r="E186">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F186" t="s">
         <v>1599</v>
@@ -14740,7 +14740,7 @@
         <v>1487</v>
       </c>
       <c r="E187">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F187" t="s">
         <v>1596</v>
@@ -14775,7 +14775,7 @@
         <v>1487</v>
       </c>
       <c r="E188">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F188" t="s">
         <v>1597</v>
@@ -14810,7 +14810,7 @@
         <v>1487</v>
       </c>
       <c r="E189">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F189" t="s">
         <v>1596</v>
@@ -14845,7 +14845,7 @@
         <v>1488</v>
       </c>
       <c r="E190">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F190" t="s">
         <v>1596</v>
@@ -14880,7 +14880,7 @@
         <v>1488</v>
       </c>
       <c r="E191">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F191" t="s">
         <v>1596</v>
@@ -14915,7 +14915,7 @@
         <v>1489</v>
       </c>
       <c r="E192">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F192" t="s">
         <v>1596</v>
@@ -14950,7 +14950,7 @@
         <v>1489</v>
       </c>
       <c r="E193">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F193" t="s">
         <v>1596</v>
@@ -14985,7 +14985,7 @@
         <v>1490</v>
       </c>
       <c r="E194">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F194" t="s">
         <v>1596</v>
@@ -15020,7 +15020,7 @@
         <v>1490</v>
       </c>
       <c r="E195">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F195" t="s">
         <v>1596</v>
@@ -15055,7 +15055,7 @@
         <v>1490</v>
       </c>
       <c r="E196">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F196" t="s">
         <v>1596</v>
@@ -15090,7 +15090,7 @@
         <v>1491</v>
       </c>
       <c r="E197">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F197" t="s">
         <v>1596</v>
@@ -15125,7 +15125,7 @@
         <v>1491</v>
       </c>
       <c r="E198">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F198" t="s">
         <v>1596</v>
@@ -15160,7 +15160,7 @@
         <v>1491</v>
       </c>
       <c r="E199">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F199" t="s">
         <v>1596</v>
@@ -15195,7 +15195,7 @@
         <v>1491</v>
       </c>
       <c r="E200">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F200" t="s">
         <v>1596</v>
@@ -15230,7 +15230,7 @@
         <v>1491</v>
       </c>
       <c r="E201">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F201" t="s">
         <v>1596</v>
@@ -15265,7 +15265,7 @@
         <v>1492</v>
       </c>
       <c r="E202">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F202" t="s">
         <v>1596</v>
@@ -15300,7 +15300,7 @@
         <v>1492</v>
       </c>
       <c r="E203">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F203" t="s">
         <v>1596</v>
@@ -15335,7 +15335,7 @@
         <v>1493</v>
       </c>
       <c r="E204">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F204" t="s">
         <v>1596</v>
@@ -15370,7 +15370,7 @@
         <v>1494</v>
       </c>
       <c r="E205">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F205" t="s">
         <v>1596</v>
@@ -15405,7 +15405,7 @@
         <v>1494</v>
       </c>
       <c r="E206">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F206" t="s">
         <v>1596</v>
@@ -15440,7 +15440,7 @@
         <v>1494</v>
       </c>
       <c r="E207">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F207" t="s">
         <v>1596</v>
@@ -15475,7 +15475,7 @@
         <v>1494</v>
       </c>
       <c r="E208">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F208" t="s">
         <v>1596</v>
@@ -15510,7 +15510,7 @@
         <v>1495</v>
       </c>
       <c r="E209">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F209" t="s">
         <v>1596</v>
@@ -15545,7 +15545,7 @@
         <v>1496</v>
       </c>
       <c r="E210">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F210" t="s">
         <v>1596</v>
@@ -15580,7 +15580,7 @@
         <v>1496</v>
       </c>
       <c r="E211">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F211" t="s">
         <v>1596</v>
@@ -15615,7 +15615,7 @@
         <v>1496</v>
       </c>
       <c r="E212">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F212" t="s">
         <v>1596</v>
@@ -15650,7 +15650,7 @@
         <v>1496</v>
       </c>
       <c r="E213">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F213" t="s">
         <v>1596</v>
@@ -15685,7 +15685,7 @@
         <v>1496</v>
       </c>
       <c r="E214">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F214" t="s">
         <v>1596</v>
@@ -15720,7 +15720,7 @@
         <v>1497</v>
       </c>
       <c r="E215">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F215" t="s">
         <v>1596</v>
@@ -15755,7 +15755,7 @@
         <v>1497</v>
       </c>
       <c r="E216">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F216" t="s">
         <v>1596</v>
@@ -15790,7 +15790,7 @@
         <v>1497</v>
       </c>
       <c r="E217">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F217" t="s">
         <v>1596</v>
@@ -15825,7 +15825,7 @@
         <v>1497</v>
       </c>
       <c r="E218">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F218" t="s">
         <v>1596</v>
@@ -15860,7 +15860,7 @@
         <v>1497</v>
       </c>
       <c r="E219">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F219" t="s">
         <v>1596</v>
@@ -15895,7 +15895,7 @@
         <v>1497</v>
       </c>
       <c r="E220">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F220" t="s">
         <v>1596</v>
@@ -15930,7 +15930,7 @@
         <v>1497</v>
       </c>
       <c r="E221">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F221" t="s">
         <v>1596</v>
@@ -15965,7 +15965,7 @@
         <v>1498</v>
       </c>
       <c r="E222">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F222" t="s">
         <v>1596</v>
@@ -16000,7 +16000,7 @@
         <v>1498</v>
       </c>
       <c r="E223">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F223" t="s">
         <v>1596</v>
@@ -16035,7 +16035,7 @@
         <v>1498</v>
       </c>
       <c r="E224">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F224" t="s">
         <v>1596</v>
@@ -16070,7 +16070,7 @@
         <v>1498</v>
       </c>
       <c r="E225">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F225" t="s">
         <v>1596</v>
@@ -16105,7 +16105,7 @@
         <v>1499</v>
       </c>
       <c r="E226">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F226" t="s">
         <v>1596</v>
@@ -16140,7 +16140,7 @@
         <v>1499</v>
       </c>
       <c r="E227">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F227" t="s">
         <v>1596</v>
@@ -16175,7 +16175,7 @@
         <v>1499</v>
       </c>
       <c r="E228">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F228" t="s">
         <v>1596</v>
@@ -16210,7 +16210,7 @@
         <v>1500</v>
       </c>
       <c r="E229">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F229" t="s">
         <v>1596</v>
@@ -16245,7 +16245,7 @@
         <v>1500</v>
       </c>
       <c r="E230">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F230" t="s">
         <v>1596</v>
@@ -16280,7 +16280,7 @@
         <v>1501</v>
       </c>
       <c r="E231">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F231" t="s">
         <v>1596</v>
@@ -16315,7 +16315,7 @@
         <v>1501</v>
       </c>
       <c r="E232">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F232" t="s">
         <v>1596</v>
@@ -16350,7 +16350,7 @@
         <v>1502</v>
       </c>
       <c r="E233">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F233" t="s">
         <v>1596</v>
@@ -16385,7 +16385,7 @@
         <v>1502</v>
       </c>
       <c r="E234">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F234" t="s">
         <v>1596</v>
@@ -16420,7 +16420,7 @@
         <v>1503</v>
       </c>
       <c r="E235">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F235" t="s">
         <v>1596</v>
@@ -16455,7 +16455,7 @@
         <v>1503</v>
       </c>
       <c r="E236">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F236" t="s">
         <v>1596</v>
@@ -16490,7 +16490,7 @@
         <v>1504</v>
       </c>
       <c r="E237">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F237" t="s">
         <v>1596</v>
@@ -16525,7 +16525,7 @@
         <v>1504</v>
       </c>
       <c r="E238">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F238" t="s">
         <v>1596</v>
@@ -16560,7 +16560,7 @@
         <v>1505</v>
       </c>
       <c r="E239">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F239" t="s">
         <v>1596</v>
@@ -16595,7 +16595,7 @@
         <v>1506</v>
       </c>
       <c r="E240">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F240" t="s">
         <v>1596</v>
@@ -16630,7 +16630,7 @@
         <v>1506</v>
       </c>
       <c r="E241">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F241" t="s">
         <v>1596</v>
@@ -16665,7 +16665,7 @@
         <v>1506</v>
       </c>
       <c r="E242">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F242" t="s">
         <v>1596</v>
@@ -16700,7 +16700,7 @@
         <v>1507</v>
       </c>
       <c r="E243">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F243" t="s">
         <v>1596</v>
@@ -16735,7 +16735,7 @@
         <v>1507</v>
       </c>
       <c r="E244">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F244" t="s">
         <v>1596</v>
@@ -16770,7 +16770,7 @@
         <v>1508</v>
       </c>
       <c r="E245">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F245" t="s">
         <v>1596</v>
@@ -16805,7 +16805,7 @@
         <v>1509</v>
       </c>
       <c r="E246">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F246" t="s">
         <v>1596</v>
@@ -16840,7 +16840,7 @@
         <v>1509</v>
       </c>
       <c r="E247">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F247" t="s">
         <v>1596</v>
@@ -16875,7 +16875,7 @@
         <v>1509</v>
       </c>
       <c r="E248">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F248" t="s">
         <v>1596</v>
@@ -16910,7 +16910,7 @@
         <v>1510</v>
       </c>
       <c r="E249">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F249" t="s">
         <v>1596</v>
@@ -16945,7 +16945,7 @@
         <v>1510</v>
       </c>
       <c r="E250">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F250" t="s">
         <v>1596</v>
@@ -16980,7 +16980,7 @@
         <v>1511</v>
       </c>
       <c r="E251">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F251" t="s">
         <v>1596</v>
@@ -17015,7 +17015,7 @@
         <v>1511</v>
       </c>
       <c r="E252">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F252" t="s">
         <v>1596</v>
@@ -17050,7 +17050,7 @@
         <v>1511</v>
       </c>
       <c r="E253">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F253" t="s">
         <v>1598</v>
@@ -17085,7 +17085,7 @@
         <v>1511</v>
       </c>
       <c r="E254">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F254" t="s">
         <v>1596</v>
@@ -17120,7 +17120,7 @@
         <v>1512</v>
       </c>
       <c r="E255">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F255" t="s">
         <v>1596</v>
@@ -17155,7 +17155,7 @@
         <v>1512</v>
       </c>
       <c r="E256">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F256" t="s">
         <v>1596</v>
@@ -17193,7 +17193,7 @@
         <v>1512</v>
       </c>
       <c r="E257">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F257" t="s">
         <v>1596</v>
@@ -17228,7 +17228,7 @@
         <v>1512</v>
       </c>
       <c r="E258">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F258" t="s">
         <v>1596</v>
@@ -17263,7 +17263,7 @@
         <v>1512</v>
       </c>
       <c r="E259">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F259" t="s">
         <v>1596</v>
@@ -17298,7 +17298,7 @@
         <v>1512</v>
       </c>
       <c r="E260">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F260" t="s">
         <v>1596</v>
@@ -17333,7 +17333,7 @@
         <v>1513</v>
       </c>
       <c r="E261">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F261" t="s">
         <v>1596</v>
@@ -17368,7 +17368,7 @@
         <v>1513</v>
       </c>
       <c r="E262">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F262" t="s">
         <v>1596</v>
@@ -17403,7 +17403,7 @@
         <v>1513</v>
       </c>
       <c r="E263">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F263" t="s">
         <v>1596</v>
@@ -17438,7 +17438,7 @@
         <v>1514</v>
       </c>
       <c r="E264">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F264" t="s">
         <v>1596</v>
@@ -17473,7 +17473,7 @@
         <v>1514</v>
       </c>
       <c r="E265">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F265" t="s">
         <v>1596</v>
@@ -17508,7 +17508,7 @@
         <v>1514</v>
       </c>
       <c r="E266">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F266" t="s">
         <v>1596</v>
@@ -17543,7 +17543,7 @@
         <v>1514</v>
       </c>
       <c r="E267">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F267" t="s">
         <v>1596</v>
@@ -17578,7 +17578,7 @@
         <v>1515</v>
       </c>
       <c r="E268">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F268" t="s">
         <v>1596</v>
@@ -17613,7 +17613,7 @@
         <v>1515</v>
       </c>
       <c r="E269">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F269" t="s">
         <v>1596</v>
@@ -17648,7 +17648,7 @@
         <v>1515</v>
       </c>
       <c r="E270">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F270" t="s">
         <v>1596</v>
@@ -17683,7 +17683,7 @@
         <v>1515</v>
       </c>
       <c r="E271">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F271" t="s">
         <v>1596</v>
@@ -17718,7 +17718,7 @@
         <v>1515</v>
       </c>
       <c r="E272">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F272" t="s">
         <v>1596</v>
@@ -17753,7 +17753,7 @@
         <v>1516</v>
       </c>
       <c r="E273">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F273" t="s">
         <v>1596</v>
@@ -17788,7 +17788,7 @@
         <v>1516</v>
       </c>
       <c r="E274">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F274" t="s">
         <v>1596</v>
@@ -17823,7 +17823,7 @@
         <v>1516</v>
       </c>
       <c r="E275">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F275" t="s">
         <v>1596</v>
@@ -17858,7 +17858,7 @@
         <v>1516</v>
       </c>
       <c r="E276">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F276" t="s">
         <v>1596</v>
@@ -17893,7 +17893,7 @@
         <v>1516</v>
       </c>
       <c r="E277">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F277" t="s">
         <v>1596</v>
@@ -17928,7 +17928,7 @@
         <v>1516</v>
       </c>
       <c r="E278">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F278" t="s">
         <v>1596</v>
@@ -17963,7 +17963,7 @@
         <v>1517</v>
       </c>
       <c r="E279">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F279" t="s">
         <v>1596</v>
@@ -17998,7 +17998,7 @@
         <v>1518</v>
       </c>
       <c r="E280">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F280" t="s">
         <v>1597</v>
@@ -18033,7 +18033,7 @@
         <v>1518</v>
       </c>
       <c r="E281">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F281" t="s">
         <v>1596</v>
@@ -18068,7 +18068,7 @@
         <v>1518</v>
       </c>
       <c r="E282">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F282" t="s">
         <v>1596</v>
@@ -18103,7 +18103,7 @@
         <v>1518</v>
       </c>
       <c r="E283">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F283" t="s">
         <v>1599</v>
@@ -18138,7 +18138,7 @@
         <v>1518</v>
       </c>
       <c r="E284">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F284" t="s">
         <v>1596</v>
@@ -18173,7 +18173,7 @@
         <v>1518</v>
       </c>
       <c r="E285">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F285" t="s">
         <v>1596</v>
@@ -18208,7 +18208,7 @@
         <v>1518</v>
       </c>
       <c r="E286">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F286" t="s">
         <v>1596</v>
@@ -18243,7 +18243,7 @@
         <v>1519</v>
       </c>
       <c r="E287">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F287" t="s">
         <v>1596</v>
@@ -18278,7 +18278,7 @@
         <v>1519</v>
       </c>
       <c r="E288">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F288" t="s">
         <v>1596</v>
@@ -18313,7 +18313,7 @@
         <v>1519</v>
       </c>
       <c r="E289">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F289" t="s">
         <v>1596</v>
@@ -18348,7 +18348,7 @@
         <v>1519</v>
       </c>
       <c r="E290">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F290" t="s">
         <v>1596</v>
@@ -18383,7 +18383,7 @@
         <v>1520</v>
       </c>
       <c r="E291">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F291" t="s">
         <v>1596</v>
@@ -18418,7 +18418,7 @@
         <v>1520</v>
       </c>
       <c r="E292">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F292" t="s">
         <v>1596</v>
@@ -18453,7 +18453,7 @@
         <v>1521</v>
       </c>
       <c r="E293">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F293" t="s">
         <v>1596</v>
@@ -18491,7 +18491,7 @@
         <v>1521</v>
       </c>
       <c r="E294">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F294" t="s">
         <v>1596</v>
@@ -18526,7 +18526,7 @@
         <v>1522</v>
       </c>
       <c r="E295">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F295" t="s">
         <v>1596</v>
@@ -18561,7 +18561,7 @@
         <v>1522</v>
       </c>
       <c r="E296">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F296" t="s">
         <v>1596</v>
@@ -18596,7 +18596,7 @@
         <v>1522</v>
       </c>
       <c r="E297">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F297" t="s">
         <v>1596</v>
@@ -18631,7 +18631,7 @@
         <v>1522</v>
       </c>
       <c r="E298">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F298" t="s">
         <v>1596</v>
@@ -18669,7 +18669,7 @@
         <v>1522</v>
       </c>
       <c r="E299">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F299" t="s">
         <v>1596</v>
@@ -18704,7 +18704,7 @@
         <v>1522</v>
       </c>
       <c r="E300">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F300" t="s">
         <v>1596</v>
@@ -18739,7 +18739,7 @@
         <v>1523</v>
       </c>
       <c r="E301">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F301" t="s">
         <v>1596</v>
@@ -18774,7 +18774,7 @@
         <v>1523</v>
       </c>
       <c r="E302">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F302" t="s">
         <v>1596</v>
@@ -18809,7 +18809,7 @@
         <v>1524</v>
       </c>
       <c r="E303">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F303" t="s">
         <v>1596</v>
@@ -18844,7 +18844,7 @@
         <v>1524</v>
       </c>
       <c r="E304">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F304" t="s">
         <v>1596</v>
@@ -18879,7 +18879,7 @@
         <v>1525</v>
       </c>
       <c r="E305">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F305" t="s">
         <v>1596</v>
@@ -18914,7 +18914,7 @@
         <v>1525</v>
       </c>
       <c r="E306">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F306" t="s">
         <v>1596</v>
@@ -18949,7 +18949,7 @@
         <v>1525</v>
       </c>
       <c r="E307">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F307" t="s">
         <v>1596</v>
@@ -18984,7 +18984,7 @@
         <v>1525</v>
       </c>
       <c r="E308">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F308" t="s">
         <v>1596</v>
@@ -19019,7 +19019,7 @@
         <v>1526</v>
       </c>
       <c r="E309">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F309" t="s">
         <v>1596</v>
@@ -19054,7 +19054,7 @@
         <v>1526</v>
       </c>
       <c r="E310">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F310" t="s">
         <v>1596</v>
@@ -19089,7 +19089,7 @@
         <v>1526</v>
       </c>
       <c r="E311">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F311" t="s">
         <v>1596</v>
@@ -19124,7 +19124,7 @@
         <v>1526</v>
       </c>
       <c r="E312">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F312" t="s">
         <v>1596</v>
@@ -19159,7 +19159,7 @@
         <v>1527</v>
       </c>
       <c r="E313">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F313" t="s">
         <v>1596</v>
@@ -19194,7 +19194,7 @@
         <v>1527</v>
       </c>
       <c r="E314">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F314" t="s">
         <v>1596</v>
@@ -19229,7 +19229,7 @@
         <v>1528</v>
       </c>
       <c r="E315">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F315" t="s">
         <v>1596</v>
@@ -19264,7 +19264,7 @@
         <v>1528</v>
       </c>
       <c r="E316">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F316" t="s">
         <v>1596</v>
@@ -19299,7 +19299,7 @@
         <v>1528</v>
       </c>
       <c r="E317">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F317" t="s">
         <v>1596</v>
@@ -19334,7 +19334,7 @@
         <v>1528</v>
       </c>
       <c r="E318">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F318" t="s">
         <v>1596</v>
@@ -19369,7 +19369,7 @@
         <v>1528</v>
       </c>
       <c r="E319">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F319" t="s">
         <v>1596</v>
@@ -19404,7 +19404,7 @@
         <v>1529</v>
       </c>
       <c r="E320">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F320" t="s">
         <v>1596</v>
@@ -19439,7 +19439,7 @@
         <v>1529</v>
       </c>
       <c r="E321">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F321" t="s">
         <v>1596</v>
@@ -19474,7 +19474,7 @@
         <v>1529</v>
       </c>
       <c r="E322">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F322" t="s">
         <v>1596</v>
@@ -19509,7 +19509,7 @@
         <v>1530</v>
       </c>
       <c r="E323">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F323" t="s">
         <v>1596</v>
@@ -19544,7 +19544,7 @@
         <v>1530</v>
       </c>
       <c r="E324">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F324" t="s">
         <v>1596</v>
@@ -19579,7 +19579,7 @@
         <v>1531</v>
       </c>
       <c r="E325">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F325" t="s">
         <v>1596</v>
@@ -19614,7 +19614,7 @@
         <v>1531</v>
       </c>
       <c r="E326">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F326" t="s">
         <v>1596</v>
@@ -19649,7 +19649,7 @@
         <v>1531</v>
       </c>
       <c r="E327">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F327" t="s">
         <v>1596</v>
@@ -19684,7 +19684,7 @@
         <v>1531</v>
       </c>
       <c r="E328">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F328" t="s">
         <v>1596</v>
@@ -19719,7 +19719,7 @@
         <v>1531</v>
       </c>
       <c r="E329">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F329" t="s">
         <v>1596</v>
@@ -19754,7 +19754,7 @@
         <v>1531</v>
       </c>
       <c r="E330">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F330" t="s">
         <v>1596</v>
@@ -19789,7 +19789,7 @@
         <v>1531</v>
       </c>
       <c r="E331">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F331" t="s">
         <v>1596</v>
@@ -19824,7 +19824,7 @@
         <v>1531</v>
       </c>
       <c r="E332">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F332" t="s">
         <v>1596</v>
@@ -19859,7 +19859,7 @@
         <v>1532</v>
       </c>
       <c r="E333">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F333" t="s">
         <v>1596</v>
@@ -19894,7 +19894,7 @@
         <v>1532</v>
       </c>
       <c r="E334">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F334" t="s">
         <v>1596</v>
@@ -19929,7 +19929,7 @@
         <v>1532</v>
       </c>
       <c r="E335">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F335" t="s">
         <v>1596</v>
@@ -19964,7 +19964,7 @@
         <v>1533</v>
       </c>
       <c r="E336">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F336" t="s">
         <v>1596</v>
@@ -19999,7 +19999,7 @@
         <v>1534</v>
       </c>
       <c r="E337">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F337" t="s">
         <v>1596</v>
@@ -20034,7 +20034,7 @@
         <v>1535</v>
       </c>
       <c r="E338">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F338" t="s">
         <v>1598</v>
@@ -20069,7 +20069,7 @@
         <v>1535</v>
       </c>
       <c r="E339">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F339" t="s">
         <v>1596</v>
@@ -20104,7 +20104,7 @@
         <v>1535</v>
       </c>
       <c r="E340">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F340" t="s">
         <v>1596</v>
@@ -20139,7 +20139,7 @@
         <v>1535</v>
       </c>
       <c r="E341">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F341" t="s">
         <v>1596</v>
@@ -20174,7 +20174,7 @@
         <v>1535</v>
       </c>
       <c r="E342">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F342" t="s">
         <v>1596</v>
@@ -20209,7 +20209,7 @@
         <v>1535</v>
       </c>
       <c r="E343">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F343" t="s">
         <v>1596</v>
@@ -20244,7 +20244,7 @@
         <v>1536</v>
       </c>
       <c r="E344">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F344" t="s">
         <v>1596</v>
@@ -20279,7 +20279,7 @@
         <v>1536</v>
       </c>
       <c r="E345">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F345" t="s">
         <v>1596</v>
@@ -20314,7 +20314,7 @@
         <v>1537</v>
       </c>
       <c r="E346">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F346" t="s">
         <v>1596</v>
@@ -20349,7 +20349,7 @@
         <v>1537</v>
       </c>
       <c r="E347">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F347" t="s">
         <v>1596</v>
@@ -20384,7 +20384,7 @@
         <v>1537</v>
       </c>
       <c r="E348">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F348" t="s">
         <v>1596</v>
@@ -20419,7 +20419,7 @@
         <v>1538</v>
       </c>
       <c r="E349">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F349" t="s">
         <v>1596</v>
@@ -20454,7 +20454,7 @@
         <v>1539</v>
       </c>
       <c r="E350">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F350" t="s">
         <v>1596</v>
@@ -20489,7 +20489,7 @@
         <v>1540</v>
       </c>
       <c r="E351">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F351" t="s">
         <v>1596</v>
@@ -20524,7 +20524,7 @@
         <v>1540</v>
       </c>
       <c r="E352">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F352" t="s">
         <v>1596</v>
@@ -20559,7 +20559,7 @@
         <v>1541</v>
       </c>
       <c r="E353">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F353" t="s">
         <v>1596</v>
@@ -20594,7 +20594,7 @@
         <v>1541</v>
       </c>
       <c r="E354">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F354" t="s">
         <v>1596</v>
@@ -20629,7 +20629,7 @@
         <v>1541</v>
       </c>
       <c r="E355">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F355" t="s">
         <v>1596</v>
@@ -20664,7 +20664,7 @@
         <v>1542</v>
       </c>
       <c r="E356">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F356" t="s">
         <v>1596</v>
@@ -20699,7 +20699,7 @@
         <v>1542</v>
       </c>
       <c r="E357">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F357" t="s">
         <v>1596</v>
@@ -20734,7 +20734,7 @@
         <v>1542</v>
       </c>
       <c r="E358">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F358" t="s">
         <v>1596</v>
@@ -20769,7 +20769,7 @@
         <v>1542</v>
       </c>
       <c r="E359">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F359" t="s">
         <v>1596</v>
@@ -20804,7 +20804,7 @@
         <v>1542</v>
       </c>
       <c r="E360">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F360" t="s">
         <v>1596</v>
@@ -20839,7 +20839,7 @@
         <v>1542</v>
       </c>
       <c r="E361">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F361" t="s">
         <v>1596</v>
@@ -20874,7 +20874,7 @@
         <v>1542</v>
       </c>
       <c r="E362">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F362" t="s">
         <v>1596</v>
@@ -20909,7 +20909,7 @@
         <v>1542</v>
       </c>
       <c r="E363">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F363" t="s">
         <v>1596</v>
@@ -20944,7 +20944,7 @@
         <v>1542</v>
       </c>
       <c r="E364">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F364" t="s">
         <v>1596</v>
@@ -20979,7 +20979,7 @@
         <v>1543</v>
       </c>
       <c r="E365">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F365" t="s">
         <v>1596</v>
@@ -21014,7 +21014,7 @@
         <v>1543</v>
       </c>
       <c r="E366">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F366" t="s">
         <v>1596</v>
@@ -21049,7 +21049,7 @@
         <v>1543</v>
       </c>
       <c r="E367">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F367" t="s">
         <v>1596</v>
@@ -21084,7 +21084,7 @@
         <v>1543</v>
       </c>
       <c r="E368">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F368" t="s">
         <v>1596</v>
@@ -21119,7 +21119,7 @@
         <v>1544</v>
       </c>
       <c r="E369">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F369" t="s">
         <v>1596</v>
@@ -21154,7 +21154,7 @@
         <v>1545</v>
       </c>
       <c r="E370">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F370" t="s">
         <v>1596</v>
@@ -21189,7 +21189,7 @@
         <v>1545</v>
       </c>
       <c r="E371">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F371" t="s">
         <v>1596</v>
@@ -21224,7 +21224,7 @@
         <v>1545</v>
       </c>
       <c r="E372">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F372" t="s">
         <v>1596</v>
@@ -21259,7 +21259,7 @@
         <v>1545</v>
       </c>
       <c r="E373">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F373" t="s">
         <v>1596</v>
@@ -21294,7 +21294,7 @@
         <v>1545</v>
       </c>
       <c r="E374">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F374" t="s">
         <v>1600</v>
@@ -21332,7 +21332,7 @@
         <v>1545</v>
       </c>
       <c r="E375">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F375" t="s">
         <v>1596</v>
@@ -21367,7 +21367,7 @@
         <v>1545</v>
       </c>
       <c r="E376">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F376" t="s">
         <v>1596</v>
@@ -21402,7 +21402,7 @@
         <v>1546</v>
       </c>
       <c r="E377">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F377" t="s">
         <v>1596</v>
@@ -21437,7 +21437,7 @@
         <v>1546</v>
       </c>
       <c r="E378">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F378" t="s">
         <v>1596</v>
@@ -21472,7 +21472,7 @@
         <v>1546</v>
       </c>
       <c r="E379">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F379" t="s">
         <v>1596</v>
@@ -21507,7 +21507,7 @@
         <v>1546</v>
       </c>
       <c r="E380">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F380" t="s">
         <v>1596</v>
@@ -21545,7 +21545,7 @@
         <v>1546</v>
       </c>
       <c r="E381">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F381" t="s">
         <v>1596</v>
@@ -21580,7 +21580,7 @@
         <v>1546</v>
       </c>
       <c r="E382">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F382" t="s">
         <v>1596</v>
@@ -21615,7 +21615,7 @@
         <v>1546</v>
       </c>
       <c r="E383">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F383" t="s">
         <v>1596</v>
@@ -21650,7 +21650,7 @@
         <v>1546</v>
       </c>
       <c r="E384">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F384" t="s">
         <v>1596</v>
@@ -21685,7 +21685,7 @@
         <v>1546</v>
       </c>
       <c r="E385">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F385" t="s">
         <v>1596</v>
@@ -21720,7 +21720,7 @@
         <v>1547</v>
       </c>
       <c r="E386">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F386" t="s">
         <v>1597</v>
@@ -21755,7 +21755,7 @@
         <v>1548</v>
       </c>
       <c r="E387">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F387" t="s">
         <v>1600</v>
@@ -21790,7 +21790,7 @@
         <v>1549</v>
       </c>
       <c r="E388">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F388" t="s">
         <v>1596</v>
@@ -21825,7 +21825,7 @@
         <v>1550</v>
       </c>
       <c r="E389">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F389" t="s">
         <v>1596</v>
@@ -21860,7 +21860,7 @@
         <v>1550</v>
       </c>
       <c r="E390">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F390" t="s">
         <v>1596</v>
@@ -21895,7 +21895,7 @@
         <v>1551</v>
       </c>
       <c r="E391">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F391" t="s">
         <v>1596</v>
@@ -21930,7 +21930,7 @@
         <v>1552</v>
       </c>
       <c r="E392">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F392" t="s">
         <v>1599</v>
@@ -21965,7 +21965,7 @@
         <v>1552</v>
       </c>
       <c r="E393">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F393" t="s">
         <v>1596</v>
@@ -22000,7 +22000,7 @@
         <v>1552</v>
       </c>
       <c r="E394">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F394" t="s">
         <v>1596</v>
@@ -22035,7 +22035,7 @@
         <v>1552</v>
       </c>
       <c r="E395">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F395" t="s">
         <v>1596</v>
@@ -22070,7 +22070,7 @@
         <v>1552</v>
       </c>
       <c r="E396">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F396" t="s">
         <v>1596</v>
@@ -22105,7 +22105,7 @@
         <v>1552</v>
       </c>
       <c r="E397">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F397" t="s">
         <v>1596</v>
@@ -22140,7 +22140,7 @@
         <v>1553</v>
       </c>
       <c r="E398">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F398" t="s">
         <v>1596</v>
@@ -22175,7 +22175,7 @@
         <v>1553</v>
       </c>
       <c r="E399">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F399" t="s">
         <v>1596</v>
@@ -22210,7 +22210,7 @@
         <v>1553</v>
       </c>
       <c r="E400">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F400" t="s">
         <v>1596</v>
@@ -22245,7 +22245,7 @@
         <v>1554</v>
       </c>
       <c r="E401">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F401" t="s">
         <v>1596</v>
@@ -22280,7 +22280,7 @@
         <v>1554</v>
       </c>
       <c r="E402">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F402" t="s">
         <v>1596</v>
@@ -22315,7 +22315,7 @@
         <v>1554</v>
       </c>
       <c r="E403">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F403" t="s">
         <v>1596</v>
@@ -22353,7 +22353,7 @@
         <v>1554</v>
       </c>
       <c r="E404">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F404" t="s">
         <v>1596</v>
@@ -22388,7 +22388,7 @@
         <v>1555</v>
       </c>
       <c r="E405">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F405" t="s">
         <v>1596</v>
@@ -22423,7 +22423,7 @@
         <v>1555</v>
       </c>
       <c r="E406">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F406" t="s">
         <v>1596</v>
@@ -22458,7 +22458,7 @@
         <v>1555</v>
       </c>
       <c r="E407">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F407" t="s">
         <v>1596</v>
@@ -22493,7 +22493,7 @@
         <v>1555</v>
       </c>
       <c r="E408">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F408" t="s">
         <v>1596</v>
@@ -22528,7 +22528,7 @@
         <v>1555</v>
       </c>
       <c r="E409">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F409" t="s">
         <v>1596</v>
@@ -22563,7 +22563,7 @@
         <v>1556</v>
       </c>
       <c r="E410">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F410" t="s">
         <v>1596</v>
@@ -22598,7 +22598,7 @@
         <v>1556</v>
       </c>
       <c r="E411">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F411" t="s">
         <v>1596</v>
@@ -22633,7 +22633,7 @@
         <v>1557</v>
       </c>
       <c r="E412">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F412" t="s">
         <v>1596</v>
@@ -22668,7 +22668,7 @@
         <v>1557</v>
       </c>
       <c r="E413">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F413" t="s">
         <v>1596</v>
@@ -22703,7 +22703,7 @@
         <v>1557</v>
       </c>
       <c r="E414">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F414" t="s">
         <v>1596</v>
@@ -22738,7 +22738,7 @@
         <v>1557</v>
       </c>
       <c r="E415">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F415" t="s">
         <v>1596</v>
@@ -22773,7 +22773,7 @@
         <v>1557</v>
       </c>
       <c r="E416">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F416" t="s">
         <v>1596</v>
@@ -22808,7 +22808,7 @@
         <v>1557</v>
       </c>
       <c r="E417">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F417" t="s">
         <v>1596</v>
@@ -22843,7 +22843,7 @@
         <v>1557</v>
       </c>
       <c r="E418">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F418" t="s">
         <v>1596</v>
@@ -22878,7 +22878,7 @@
         <v>1557</v>
       </c>
       <c r="E419">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F419" t="s">
         <v>1596</v>
@@ -22913,7 +22913,7 @@
         <v>1557</v>
       </c>
       <c r="E420">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F420" t="s">
         <v>1596</v>
@@ -22948,7 +22948,7 @@
         <v>1557</v>
       </c>
       <c r="E421">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F421" t="s">
         <v>1596</v>
@@ -22983,7 +22983,7 @@
         <v>1558</v>
       </c>
       <c r="E422">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F422" t="s">
         <v>1596</v>
@@ -23018,7 +23018,7 @@
         <v>1558</v>
       </c>
       <c r="E423">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F423" t="s">
         <v>1596</v>
@@ -23053,7 +23053,7 @@
         <v>1558</v>
       </c>
       <c r="E424">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F424" t="s">
         <v>1597</v>
@@ -23088,7 +23088,7 @@
         <v>1559</v>
       </c>
       <c r="E425">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F425" t="s">
         <v>1596</v>
@@ -23123,7 +23123,7 @@
         <v>1559</v>
       </c>
       <c r="E426">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F426" t="s">
         <v>1596</v>
@@ -23158,7 +23158,7 @@
         <v>1559</v>
       </c>
       <c r="E427">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F427" t="s">
         <v>1596</v>
@@ -23193,7 +23193,7 @@
         <v>1559</v>
       </c>
       <c r="E428">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F428" t="s">
         <v>1596</v>
@@ -23228,7 +23228,7 @@
         <v>1559</v>
       </c>
       <c r="E429">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F429" t="s">
         <v>1596</v>
@@ -23263,7 +23263,7 @@
         <v>1559</v>
       </c>
       <c r="E430">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F430" t="s">
         <v>1596</v>
@@ -23298,7 +23298,7 @@
         <v>1559</v>
       </c>
       <c r="E431">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F431" t="s">
         <v>1599</v>
@@ -23333,7 +23333,7 @@
         <v>1560</v>
       </c>
       <c r="E432">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F432" t="s">
         <v>1596</v>
@@ -23368,7 +23368,7 @@
         <v>1560</v>
       </c>
       <c r="E433">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F433" t="s">
         <v>1596</v>
@@ -23403,7 +23403,7 @@
         <v>1560</v>
       </c>
       <c r="E434">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F434" t="s">
         <v>1596</v>
@@ -23438,7 +23438,7 @@
         <v>1560</v>
       </c>
       <c r="E435">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F435" t="s">
         <v>1596</v>
@@ -23473,7 +23473,7 @@
         <v>1561</v>
       </c>
       <c r="E436">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F436" t="s">
         <v>1596</v>
@@ -23508,7 +23508,7 @@
         <v>1561</v>
       </c>
       <c r="E437">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F437" t="s">
         <v>1599</v>
@@ -23543,7 +23543,7 @@
         <v>1561</v>
       </c>
       <c r="E438">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F438" t="s">
         <v>1596</v>
@@ -23578,7 +23578,7 @@
         <v>1561</v>
       </c>
       <c r="E439">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F439" t="s">
         <v>1596</v>
@@ -23613,7 +23613,7 @@
         <v>1561</v>
       </c>
       <c r="E440">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F440" t="s">
         <v>1596</v>
@@ -23648,7 +23648,7 @@
         <v>1561</v>
       </c>
       <c r="E441">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F441" t="s">
         <v>1596</v>
@@ -23683,7 +23683,7 @@
         <v>1561</v>
       </c>
       <c r="E442">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F442" t="s">
         <v>1600</v>
@@ -23718,7 +23718,7 @@
         <v>1561</v>
       </c>
       <c r="E443">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F443" t="s">
         <v>1596</v>
@@ -23753,7 +23753,7 @@
         <v>1561</v>
       </c>
       <c r="E444">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F444" t="s">
         <v>1596</v>
@@ -23788,7 +23788,7 @@
         <v>1562</v>
       </c>
       <c r="E445">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F445" t="s">
         <v>1596</v>
@@ -23823,7 +23823,7 @@
         <v>1562</v>
       </c>
       <c r="E446">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F446" t="s">
         <v>1596</v>
@@ -23858,7 +23858,7 @@
         <v>1562</v>
       </c>
       <c r="E447">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F447" t="s">
         <v>1596</v>
@@ -23893,7 +23893,7 @@
         <v>1562</v>
       </c>
       <c r="E448">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F448" t="s">
         <v>1596</v>
@@ -23928,7 +23928,7 @@
         <v>1562</v>
       </c>
       <c r="E449">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F449" t="s">
         <v>1598</v>
@@ -23963,7 +23963,7 @@
         <v>1562</v>
       </c>
       <c r="E450">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F450" t="s">
         <v>1596</v>
@@ -23998,7 +23998,7 @@
         <v>1562</v>
       </c>
       <c r="E451">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F451" t="s">
         <v>1596</v>
@@ -24033,7 +24033,7 @@
         <v>1563</v>
       </c>
       <c r="E452">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F452" t="s">
         <v>1596</v>
@@ -24068,7 +24068,7 @@
         <v>1563</v>
       </c>
       <c r="E453">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F453" t="s">
         <v>1596</v>
@@ -24103,7 +24103,7 @@
         <v>1563</v>
       </c>
       <c r="E454">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F454" t="s">
         <v>1596</v>
@@ -24138,7 +24138,7 @@
         <v>1563</v>
       </c>
       <c r="E455">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F455" t="s">
         <v>1596</v>
@@ -24173,7 +24173,7 @@
         <v>1563</v>
       </c>
       <c r="E456">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F456" t="s">
         <v>1596</v>
@@ -24208,7 +24208,7 @@
         <v>1564</v>
       </c>
       <c r="E457">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F457" t="s">
         <v>1596</v>
@@ -24243,7 +24243,7 @@
         <v>1564</v>
       </c>
       <c r="E458">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F458" t="s">
         <v>1596</v>
@@ -24278,7 +24278,7 @@
         <v>1564</v>
       </c>
       <c r="E459">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F459" t="s">
         <v>1596</v>
@@ -24313,7 +24313,7 @@
         <v>1564</v>
       </c>
       <c r="E460">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F460" t="s">
         <v>1596</v>
@@ -24348,7 +24348,7 @@
         <v>1564</v>
       </c>
       <c r="E461">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F461" t="s">
         <v>1596</v>
@@ -24386,7 +24386,7 @@
         <v>1565</v>
       </c>
       <c r="E462">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F462" t="s">
         <v>1596</v>
@@ -24421,7 +24421,7 @@
         <v>1565</v>
       </c>
       <c r="E463">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F463" t="s">
         <v>1596</v>
@@ -24456,7 +24456,7 @@
         <v>1565</v>
       </c>
       <c r="E464">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F464" t="s">
         <v>1596</v>
@@ -24491,7 +24491,7 @@
         <v>1565</v>
       </c>
       <c r="E465">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F465" t="s">
         <v>1596</v>
@@ -24526,7 +24526,7 @@
         <v>1565</v>
       </c>
       <c r="E466">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F466" t="s">
         <v>1596</v>
@@ -24561,7 +24561,7 @@
         <v>1565</v>
       </c>
       <c r="E467">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F467" t="s">
         <v>1596</v>
@@ -24596,7 +24596,7 @@
         <v>1566</v>
       </c>
       <c r="E468">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F468" t="s">
         <v>1596</v>
@@ -24631,7 +24631,7 @@
         <v>1566</v>
       </c>
       <c r="E469">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F469" t="s">
         <v>1596</v>
@@ -24666,7 +24666,7 @@
         <v>1566</v>
       </c>
       <c r="E470">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F470" t="s">
         <v>1596</v>
@@ -24701,7 +24701,7 @@
         <v>1567</v>
       </c>
       <c r="E471">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F471" t="s">
         <v>1596</v>
@@ -24736,7 +24736,7 @@
         <v>1568</v>
       </c>
       <c r="E472">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F472" t="s">
         <v>1596</v>
@@ -24771,7 +24771,7 @@
         <v>1568</v>
       </c>
       <c r="E473">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F473" t="s">
         <v>1596</v>
@@ -24806,7 +24806,7 @@
         <v>1568</v>
       </c>
       <c r="E474">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F474" t="s">
         <v>1598</v>
@@ -24844,7 +24844,7 @@
         <v>1568</v>
       </c>
       <c r="E475">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F475" t="s">
         <v>1596</v>
@@ -24879,7 +24879,7 @@
         <v>1568</v>
       </c>
       <c r="E476">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F476" t="s">
         <v>1596</v>
@@ -24914,7 +24914,7 @@
         <v>1569</v>
       </c>
       <c r="E477">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F477" t="s">
         <v>1596</v>
@@ -24949,7 +24949,7 @@
         <v>1569</v>
       </c>
       <c r="E478">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F478" t="s">
         <v>1596</v>
@@ -24984,7 +24984,7 @@
         <v>1569</v>
       </c>
       <c r="E479">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F479" t="s">
         <v>1596</v>
@@ -25019,7 +25019,7 @@
         <v>1569</v>
       </c>
       <c r="E480">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F480" t="s">
         <v>1596</v>
@@ -25054,7 +25054,7 @@
         <v>1570</v>
       </c>
       <c r="E481">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F481" t="s">
         <v>1596</v>
@@ -25089,7 +25089,7 @@
         <v>1570</v>
       </c>
       <c r="E482">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F482" t="s">
         <v>1596</v>
@@ -25124,7 +25124,7 @@
         <v>1570</v>
       </c>
       <c r="E483">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F483" t="s">
         <v>1596</v>
@@ -25159,7 +25159,7 @@
         <v>1570</v>
       </c>
       <c r="E484">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F484" t="s">
         <v>1596</v>
@@ -25194,7 +25194,7 @@
         <v>1570</v>
       </c>
       <c r="E485">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F485" t="s">
         <v>1596</v>
@@ -25229,7 +25229,7 @@
         <v>1570</v>
       </c>
       <c r="E486">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F486" t="s">
         <v>1596</v>
@@ -25264,7 +25264,7 @@
         <v>1570</v>
       </c>
       <c r="E487">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F487" t="s">
         <v>1596</v>
@@ -25299,7 +25299,7 @@
         <v>1570</v>
       </c>
       <c r="E488">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F488" t="s">
         <v>1596</v>
@@ -25334,7 +25334,7 @@
         <v>1571</v>
       </c>
       <c r="E489">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F489" t="s">
         <v>1596</v>
@@ -25369,7 +25369,7 @@
         <v>1571</v>
       </c>
       <c r="E490">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F490" t="s">
         <v>1596</v>
@@ -25404,7 +25404,7 @@
         <v>1572</v>
       </c>
       <c r="E491">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F491" t="s">
         <v>1596</v>
@@ -25439,7 +25439,7 @@
         <v>1572</v>
       </c>
       <c r="E492">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F492" t="s">
         <v>1596</v>
@@ -25474,7 +25474,7 @@
         <v>1572</v>
       </c>
       <c r="E493">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F493" t="s">
         <v>1596</v>
@@ -25509,7 +25509,7 @@
         <v>1572</v>
       </c>
       <c r="E494">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F494" t="s">
         <v>1600</v>
@@ -25547,7 +25547,7 @@
         <v>1572</v>
       </c>
       <c r="E495">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F495" t="s">
         <v>1596</v>
@@ -25582,7 +25582,7 @@
         <v>1572</v>
       </c>
       <c r="E496">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F496" t="s">
         <v>1600</v>
@@ -25617,7 +25617,7 @@
         <v>1573</v>
       </c>
       <c r="E497">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F497" t="s">
         <v>1596</v>
@@ -25652,7 +25652,7 @@
         <v>1574</v>
       </c>
       <c r="E498">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F498" t="s">
         <v>1596</v>
@@ -25687,7 +25687,7 @@
         <v>1574</v>
       </c>
       <c r="E499">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F499" t="s">
         <v>1596</v>
@@ -25722,7 +25722,7 @@
         <v>1574</v>
       </c>
       <c r="E500">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F500" t="s">
         <v>1596</v>
@@ -25757,7 +25757,7 @@
         <v>1574</v>
       </c>
       <c r="E501">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F501" t="s">
         <v>1596</v>
@@ -25792,7 +25792,7 @@
         <v>1575</v>
       </c>
       <c r="E502">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F502" t="s">
         <v>1596</v>
@@ -25827,7 +25827,7 @@
         <v>1575</v>
       </c>
       <c r="E503">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F503" t="s">
         <v>1600</v>
@@ -25862,7 +25862,7 @@
         <v>1575</v>
       </c>
       <c r="E504">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F504" t="s">
         <v>1596</v>
@@ -25897,7 +25897,7 @@
         <v>1575</v>
       </c>
       <c r="E505">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F505" t="s">
         <v>1596</v>
@@ -25932,7 +25932,7 @@
         <v>1575</v>
       </c>
       <c r="E506">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F506" t="s">
         <v>1596</v>
@@ -25967,7 +25967,7 @@
         <v>1576</v>
       </c>
       <c r="E507">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F507" t="s">
         <v>1596</v>
@@ -26002,7 +26002,7 @@
         <v>1576</v>
       </c>
       <c r="E508">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F508" t="s">
         <v>1598</v>
@@ -26037,7 +26037,7 @@
         <v>1576</v>
       </c>
       <c r="E509">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F509" t="s">
         <v>1596</v>
@@ -26072,7 +26072,7 @@
         <v>1576</v>
       </c>
       <c r="E510">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F510" t="s">
         <v>1596</v>
@@ -26107,7 +26107,7 @@
         <v>1577</v>
       </c>
       <c r="E511">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F511" t="s">
         <v>1596</v>
@@ -26142,7 +26142,7 @@
         <v>1577</v>
       </c>
       <c r="E512">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F512" t="s">
         <v>1596</v>
@@ -26177,7 +26177,7 @@
         <v>1577</v>
       </c>
       <c r="E513">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F513" t="s">
         <v>1596</v>
@@ -26212,7 +26212,7 @@
         <v>1577</v>
       </c>
       <c r="E514">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F514" t="s">
         <v>1596</v>
@@ -26247,7 +26247,7 @@
         <v>1577</v>
       </c>
       <c r="E515">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F515" t="s">
         <v>1596</v>
@@ -26282,7 +26282,7 @@
         <v>1577</v>
       </c>
       <c r="E516">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F516" t="s">
         <v>1596</v>
@@ -26317,7 +26317,7 @@
         <v>1578</v>
       </c>
       <c r="E517">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F517" t="s">
         <v>1596</v>
@@ -26352,7 +26352,7 @@
         <v>1578</v>
       </c>
       <c r="E518">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F518" t="s">
         <v>1596</v>
@@ -26387,7 +26387,7 @@
         <v>1578</v>
       </c>
       <c r="E519">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F519" t="s">
         <v>1596</v>
@@ -26422,7 +26422,7 @@
         <v>1578</v>
       </c>
       <c r="E520">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F520" t="s">
         <v>1596</v>
@@ -26457,7 +26457,7 @@
         <v>1578</v>
       </c>
       <c r="E521">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F521" t="s">
         <v>1596</v>
@@ -26492,7 +26492,7 @@
         <v>1578</v>
       </c>
       <c r="E522">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F522" t="s">
         <v>1596</v>
@@ -26527,7 +26527,7 @@
         <v>1578</v>
       </c>
       <c r="E523">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F523" t="s">
         <v>1596</v>
@@ -26562,7 +26562,7 @@
         <v>1578</v>
       </c>
       <c r="E524">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F524" t="s">
         <v>1596</v>
@@ -26597,7 +26597,7 @@
         <v>1578</v>
       </c>
       <c r="E525">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F525" t="s">
         <v>1596</v>
@@ -26632,7 +26632,7 @@
         <v>1578</v>
       </c>
       <c r="E526">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F526" t="s">
         <v>1596</v>
@@ -26667,7 +26667,7 @@
         <v>1578</v>
       </c>
       <c r="E527">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F527" t="s">
         <v>1596</v>
@@ -26702,7 +26702,7 @@
         <v>1578</v>
       </c>
       <c r="E528">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F528" t="s">
         <v>1596</v>
@@ -26737,7 +26737,7 @@
         <v>1578</v>
       </c>
       <c r="E529">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F529" t="s">
         <v>1596</v>
@@ -26772,7 +26772,7 @@
         <v>1578</v>
       </c>
       <c r="E530">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F530" t="s">
         <v>1596</v>
@@ -26807,7 +26807,7 @@
         <v>1578</v>
       </c>
       <c r="E531">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F531" t="s">
         <v>1596</v>
@@ -26842,7 +26842,7 @@
         <v>1578</v>
       </c>
       <c r="E532">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F532" t="s">
         <v>1596</v>
@@ -26877,7 +26877,7 @@
         <v>1578</v>
       </c>
       <c r="E533">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F533" t="s">
         <v>1596</v>
@@ -26912,7 +26912,7 @@
         <v>1578</v>
       </c>
       <c r="E534">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F534" t="s">
         <v>1596</v>
@@ -26947,7 +26947,7 @@
         <v>1578</v>
       </c>
       <c r="E535">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F535" t="s">
         <v>1596</v>
@@ -26982,7 +26982,7 @@
         <v>1578</v>
       </c>
       <c r="E536">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F536" t="s">
         <v>1596</v>
@@ -27017,7 +27017,7 @@
         <v>1578</v>
       </c>
       <c r="E537">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F537" t="s">
         <v>1596</v>
@@ -27052,7 +27052,7 @@
         <v>1578</v>
       </c>
       <c r="E538">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F538" t="s">
         <v>1596</v>
@@ -27087,7 +27087,7 @@
         <v>1578</v>
       </c>
       <c r="E539">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F539" t="s">
         <v>1596</v>
@@ -27122,7 +27122,7 @@
         <v>1578</v>
       </c>
       <c r="E540">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F540" t="s">
         <v>1596</v>
@@ -27157,7 +27157,7 @@
         <v>1578</v>
       </c>
       <c r="E541">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F541" t="s">
         <v>1596</v>
@@ -27192,7 +27192,7 @@
         <v>1578</v>
       </c>
       <c r="E542">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F542" t="s">
         <v>1596</v>
@@ -27227,7 +27227,7 @@
         <v>1579</v>
       </c>
       <c r="E543">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F543" t="s">
         <v>1596</v>
@@ -27262,7 +27262,7 @@
         <v>1579</v>
       </c>
       <c r="E544">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F544" t="s">
         <v>1596</v>
@@ -27297,7 +27297,7 @@
         <v>1579</v>
       </c>
       <c r="E545">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F545" t="s">
         <v>1596</v>
@@ -27332,7 +27332,7 @@
         <v>1579</v>
       </c>
       <c r="E546">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F546" t="s">
         <v>1596</v>
@@ -27367,7 +27367,7 @@
         <v>1579</v>
       </c>
       <c r="E547">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F547" t="s">
         <v>1596</v>
@@ -27402,7 +27402,7 @@
         <v>1579</v>
       </c>
       <c r="E548">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F548" t="s">
         <v>1596</v>
@@ -27437,7 +27437,7 @@
         <v>1579</v>
       </c>
       <c r="E549">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F549" t="s">
         <v>1600</v>
@@ -27472,7 +27472,7 @@
         <v>1579</v>
       </c>
       <c r="E550">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F550" t="s">
         <v>1596</v>
@@ -27507,7 +27507,7 @@
         <v>1580</v>
       </c>
       <c r="E551">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F551" t="s">
         <v>1596</v>
@@ -27542,7 +27542,7 @@
         <v>1580</v>
       </c>
       <c r="E552">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F552" t="s">
         <v>1596</v>
@@ -27577,7 +27577,7 @@
         <v>1581</v>
       </c>
       <c r="E553">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F553" t="s">
         <v>1596</v>
@@ -27612,7 +27612,7 @@
         <v>1581</v>
       </c>
       <c r="E554">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F554" t="s">
         <v>1598</v>
@@ -27650,7 +27650,7 @@
         <v>1582</v>
       </c>
       <c r="E555">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F555" t="s">
         <v>1598</v>
@@ -27688,7 +27688,7 @@
         <v>1582</v>
       </c>
       <c r="E556">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F556" t="s">
         <v>1596</v>
@@ -27723,7 +27723,7 @@
         <v>1582</v>
       </c>
       <c r="E557">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F557" t="s">
         <v>1598</v>
@@ -27761,7 +27761,7 @@
         <v>1582</v>
       </c>
       <c r="E558">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F558" t="s">
         <v>1596</v>
@@ -27796,7 +27796,7 @@
         <v>1582</v>
       </c>
       <c r="E559">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F559" t="s">
         <v>1596</v>
@@ -27831,7 +27831,7 @@
         <v>1582</v>
       </c>
       <c r="E560">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F560" t="s">
         <v>1596</v>
@@ -27866,7 +27866,7 @@
         <v>1582</v>
       </c>
       <c r="E561">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F561" t="s">
         <v>1596</v>
@@ -27901,7 +27901,7 @@
         <v>1582</v>
       </c>
       <c r="E562">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F562" t="s">
         <v>1596</v>
@@ -27936,7 +27936,7 @@
         <v>1583</v>
       </c>
       <c r="E563">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F563" t="s">
         <v>1596</v>
@@ -27974,7 +27974,7 @@
         <v>1583</v>
       </c>
       <c r="E564">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F564" t="s">
         <v>1600</v>
@@ -28009,7 +28009,7 @@
         <v>1583</v>
       </c>
       <c r="E565">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F565" t="s">
         <v>1598</v>
@@ -28044,7 +28044,7 @@
         <v>1583</v>
       </c>
       <c r="E566">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F566" t="s">
         <v>1596</v>
@@ -28079,7 +28079,7 @@
         <v>1583</v>
       </c>
       <c r="E567">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F567" t="s">
         <v>1596</v>
@@ -28114,7 +28114,7 @@
         <v>1583</v>
       </c>
       <c r="E568">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F568" t="s">
         <v>1596</v>
@@ -28149,7 +28149,7 @@
         <v>1583</v>
       </c>
       <c r="E569">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F569" t="s">
         <v>1596</v>
@@ -28184,7 +28184,7 @@
         <v>1583</v>
       </c>
       <c r="E570">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F570" t="s">
         <v>1596</v>
@@ -28219,7 +28219,7 @@
         <v>1583</v>
       </c>
       <c r="E571">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F571" t="s">
         <v>1596</v>
@@ -28254,7 +28254,7 @@
         <v>1584</v>
       </c>
       <c r="E572">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F572" t="s">
         <v>1596</v>
@@ -28292,7 +28292,7 @@
         <v>1584</v>
       </c>
       <c r="E573">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F573" t="s">
         <v>1596</v>
@@ -28327,7 +28327,7 @@
         <v>1585</v>
       </c>
       <c r="E574">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F574" t="s">
         <v>1596</v>
@@ -28362,7 +28362,7 @@
         <v>1585</v>
       </c>
       <c r="E575">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F575" t="s">
         <v>1598</v>
@@ -28400,7 +28400,7 @@
         <v>1585</v>
       </c>
       <c r="E576">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F576" t="s">
         <v>1596</v>
@@ -28435,7 +28435,7 @@
         <v>1585</v>
       </c>
       <c r="E577">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F577" t="s">
         <v>1596</v>
@@ -28470,7 +28470,7 @@
         <v>1585</v>
       </c>
       <c r="E578">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F578" t="s">
         <v>1596</v>
@@ -28505,7 +28505,7 @@
         <v>1585</v>
       </c>
       <c r="E579">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F579" t="s">
         <v>1596</v>
@@ -28540,7 +28540,7 @@
         <v>1585</v>
       </c>
       <c r="E580">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F580" t="s">
         <v>1596</v>
@@ -28575,7 +28575,7 @@
         <v>1585</v>
       </c>
       <c r="E581">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F581" t="s">
         <v>1596</v>
@@ -28610,7 +28610,7 @@
         <v>1585</v>
       </c>
       <c r="E582">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F582" t="s">
         <v>1596</v>
@@ -28645,7 +28645,7 @@
         <v>1586</v>
       </c>
       <c r="E583">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F583" t="s">
         <v>1596</v>
@@ -28680,7 +28680,7 @@
         <v>1586</v>
       </c>
       <c r="E584">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F584" t="s">
         <v>1596</v>
@@ -28715,7 +28715,7 @@
         <v>1586</v>
       </c>
       <c r="E585">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F585" t="s">
         <v>1596</v>
@@ -28750,7 +28750,7 @@
         <v>1586</v>
       </c>
       <c r="E586">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F586" t="s">
         <v>1596</v>
@@ -28785,7 +28785,7 @@
         <v>1586</v>
       </c>
       <c r="E587">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F587" t="s">
         <v>1598</v>
@@ -28823,7 +28823,7 @@
         <v>1586</v>
       </c>
       <c r="E588">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F588" t="s">
         <v>1596</v>
@@ -28858,7 +28858,7 @@
         <v>1586</v>
       </c>
       <c r="E589">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F589" t="s">
         <v>1596</v>
@@ -28893,7 +28893,7 @@
         <v>1586</v>
       </c>
       <c r="E590">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F590" t="s">
         <v>1596</v>
@@ -28928,7 +28928,7 @@
         <v>1586</v>
       </c>
       <c r="E591">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F591" t="s">
         <v>1596</v>
@@ -28963,7 +28963,7 @@
         <v>1586</v>
       </c>
       <c r="E592">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F592" t="s">
         <v>1598</v>
@@ -28998,7 +28998,7 @@
         <v>1586</v>
       </c>
       <c r="E593">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F593" t="s">
         <v>1596</v>
@@ -29033,7 +29033,7 @@
         <v>1586</v>
       </c>
       <c r="E594">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F594" t="s">
         <v>1600</v>
@@ -29068,7 +29068,7 @@
         <v>1586</v>
       </c>
       <c r="E595">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F595" t="s">
         <v>1596</v>
@@ -29103,7 +29103,7 @@
         <v>1587</v>
       </c>
       <c r="E596">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F596" t="s">
         <v>1596</v>
@@ -29138,7 +29138,7 @@
         <v>1587</v>
       </c>
       <c r="E597">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F597" t="s">
         <v>1596</v>
@@ -29173,7 +29173,7 @@
         <v>1587</v>
       </c>
       <c r="E598">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F598" t="s">
         <v>1596</v>
@@ -29208,7 +29208,7 @@
         <v>1587</v>
       </c>
       <c r="E599">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F599" t="s">
         <v>1596</v>
@@ -29243,7 +29243,7 @@
         <v>1587</v>
       </c>
       <c r="E600">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F600" t="s">
         <v>1596</v>
@@ -29278,7 +29278,7 @@
         <v>1587</v>
       </c>
       <c r="E601">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F601" t="s">
         <v>1596</v>
@@ -29313,7 +29313,7 @@
         <v>1587</v>
       </c>
       <c r="E602">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F602" t="s">
         <v>1596</v>
@@ -29348,7 +29348,7 @@
         <v>1587</v>
       </c>
       <c r="E603">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F603" t="s">
         <v>1596</v>
@@ -29386,7 +29386,7 @@
         <v>1587</v>
       </c>
       <c r="E604">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F604" t="s">
         <v>1598</v>
@@ -29424,7 +29424,7 @@
         <v>1587</v>
       </c>
       <c r="E605">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F605" t="s">
         <v>1598</v>
@@ -29459,7 +29459,7 @@
         <v>1587</v>
       </c>
       <c r="E606">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F606" t="s">
         <v>1598</v>
@@ -29494,7 +29494,7 @@
         <v>1587</v>
       </c>
       <c r="E607">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F607" t="s">
         <v>1596</v>
@@ -29529,7 +29529,7 @@
         <v>1588</v>
       </c>
       <c r="E608">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F608" t="s">
         <v>1596</v>
@@ -29564,7 +29564,7 @@
         <v>1588</v>
       </c>
       <c r="E609">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F609" t="s">
         <v>1596</v>
@@ -29599,7 +29599,7 @@
         <v>1588</v>
       </c>
       <c r="E610">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F610" t="s">
         <v>1596</v>
@@ -29634,7 +29634,7 @@
         <v>1588</v>
       </c>
       <c r="E611">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F611" t="s">
         <v>1596</v>
@@ -29669,7 +29669,7 @@
         <v>1588</v>
       </c>
       <c r="E612">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F612" t="s">
         <v>1596</v>
@@ -29704,7 +29704,7 @@
         <v>1588</v>
       </c>
       <c r="E613">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F613" t="s">
         <v>1596</v>
@@ -29739,7 +29739,7 @@
         <v>1588</v>
       </c>
       <c r="E614">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F614" t="s">
         <v>1596</v>
@@ -29774,7 +29774,7 @@
         <v>1588</v>
       </c>
       <c r="E615">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F615" t="s">
         <v>1596</v>
@@ -29809,7 +29809,7 @@
         <v>1588</v>
       </c>
       <c r="E616">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F616" t="s">
         <v>1596</v>
@@ -29844,7 +29844,7 @@
         <v>1588</v>
       </c>
       <c r="E617">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F617" t="s">
         <v>1596</v>
@@ -29882,7 +29882,7 @@
         <v>1589</v>
       </c>
       <c r="E618">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F618" t="s">
         <v>1596</v>
@@ -29917,7 +29917,7 @@
         <v>1589</v>
       </c>
       <c r="E619">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F619" t="s">
         <v>1596</v>
@@ -29952,7 +29952,7 @@
         <v>1590</v>
       </c>
       <c r="E620">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F620" t="s">
         <v>1596</v>
@@ -29990,7 +29990,7 @@
         <v>1590</v>
       </c>
       <c r="E621">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F621" t="s">
         <v>1596</v>
@@ -30025,7 +30025,7 @@
         <v>1590</v>
       </c>
       <c r="E622">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F622" t="s">
         <v>1596</v>
@@ -30060,7 +30060,7 @@
         <v>1590</v>
       </c>
       <c r="E623">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F623" t="s">
         <v>1598</v>
@@ -30098,7 +30098,7 @@
         <v>1590</v>
       </c>
       <c r="E624">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F624" t="s">
         <v>1598</v>
@@ -30136,7 +30136,7 @@
         <v>1590</v>
       </c>
       <c r="E625">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F625" t="s">
         <v>1596</v>
@@ -30171,7 +30171,7 @@
         <v>1590</v>
       </c>
       <c r="E626">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F626" t="s">
         <v>1596</v>
@@ -30206,7 +30206,7 @@
         <v>1590</v>
       </c>
       <c r="E627">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F627" t="s">
         <v>1596</v>
@@ -30241,7 +30241,7 @@
         <v>1591</v>
       </c>
       <c r="E628">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F628" t="s">
         <v>1596</v>
@@ -30276,7 +30276,7 @@
         <v>1591</v>
       </c>
       <c r="E629">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F629" t="s">
         <v>1596</v>
@@ -30311,7 +30311,7 @@
         <v>1591</v>
       </c>
       <c r="E630">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F630" t="s">
         <v>1596</v>
@@ -30346,7 +30346,7 @@
         <v>1591</v>
       </c>
       <c r="E631">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F631" t="s">
         <v>1596</v>
@@ -30381,7 +30381,7 @@
         <v>1591</v>
       </c>
       <c r="E632">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F632" t="s">
         <v>1596</v>
@@ -30416,7 +30416,7 @@
         <v>1591</v>
       </c>
       <c r="E633">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F633" t="s">
         <v>1596</v>
@@ -30451,7 +30451,7 @@
         <v>1591</v>
       </c>
       <c r="E634">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F634" t="s">
         <v>1596</v>
@@ -30486,7 +30486,7 @@
         <v>1591</v>
       </c>
       <c r="E635">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F635" t="s">
         <v>1596</v>
@@ -30521,7 +30521,7 @@
         <v>1591</v>
       </c>
       <c r="E636">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F636" t="s">
         <v>1596</v>
@@ -30556,7 +30556,7 @@
         <v>1591</v>
       </c>
       <c r="E637">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F637" t="s">
         <v>1596</v>
@@ -30591,7 +30591,7 @@
         <v>1591</v>
       </c>
       <c r="E638">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F638" t="s">
         <v>1596</v>
@@ -30626,7 +30626,7 @@
         <v>1591</v>
       </c>
       <c r="E639">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F639" t="s">
         <v>1596</v>
@@ -30661,7 +30661,7 @@
         <v>1591</v>
       </c>
       <c r="E640">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F640" t="s">
         <v>1596</v>
@@ -30699,7 +30699,7 @@
         <v>1591</v>
       </c>
       <c r="E641">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F641" t="s">
         <v>1596</v>
@@ -30737,7 +30737,7 @@
         <v>1591</v>
       </c>
       <c r="E642">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F642" t="s">
         <v>1598</v>
@@ -30775,7 +30775,7 @@
         <v>1591</v>
       </c>
       <c r="E643">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F643" t="s">
         <v>1596</v>
@@ -30810,7 +30810,7 @@
         <v>1592</v>
       </c>
       <c r="E644">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F644" t="s">
         <v>1596</v>
@@ -30845,7 +30845,7 @@
         <v>1592</v>
       </c>
       <c r="E645">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F645" t="s">
         <v>1598</v>
@@ -30883,7 +30883,7 @@
         <v>1592</v>
       </c>
       <c r="E646">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F646" t="s">
         <v>1596</v>
@@ -30918,7 +30918,7 @@
         <v>1592</v>
       </c>
       <c r="E647">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F647" t="s">
         <v>1596</v>
@@ -30953,7 +30953,7 @@
         <v>1593</v>
       </c>
       <c r="E648">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F648" t="s">
         <v>1596</v>
@@ -30988,7 +30988,7 @@
         <v>1593</v>
       </c>
       <c r="E649">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F649" t="s">
         <v>1596</v>
@@ -31023,7 +31023,7 @@
         <v>1593</v>
       </c>
       <c r="E650">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F650" t="s">
         <v>1596</v>
@@ -31058,7 +31058,7 @@
         <v>1593</v>
       </c>
       <c r="E651">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F651" t="s">
         <v>1596</v>
@@ -31093,7 +31093,7 @@
         <v>1593</v>
       </c>
       <c r="E652">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F652" t="s">
         <v>1598</v>
@@ -31131,7 +31131,7 @@
         <v>1593</v>
       </c>
       <c r="E653">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F653" t="s">
         <v>1598</v>
@@ -31169,7 +31169,7 @@
         <v>1593</v>
       </c>
       <c r="E654">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F654" t="s">
         <v>1596</v>
@@ -31204,7 +31204,7 @@
         <v>1593</v>
       </c>
       <c r="E655">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F655" t="s">
         <v>1596</v>
@@ -31239,7 +31239,7 @@
         <v>1593</v>
       </c>
       <c r="E656">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F656" t="s">
         <v>1596</v>
@@ -31274,7 +31274,7 @@
         <v>1593</v>
       </c>
       <c r="E657">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F657" t="s">
         <v>1596</v>
@@ -31309,7 +31309,7 @@
         <v>1593</v>
       </c>
       <c r="E658">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F658" t="s">
         <v>1596</v>
@@ -31344,7 +31344,7 @@
         <v>1593</v>
       </c>
       <c r="E659">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F659" t="s">
         <v>1596</v>
@@ -31379,7 +31379,7 @@
         <v>1593</v>
       </c>
       <c r="E660">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F660" t="s">
         <v>1596</v>
@@ -31414,7 +31414,7 @@
         <v>1594</v>
       </c>
       <c r="E661">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F661" t="s">
         <v>1600</v>
@@ -31449,7 +31449,7 @@
         <v>1594</v>
       </c>
       <c r="E662">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F662" t="s">
         <v>1596</v>
@@ -31484,7 +31484,7 @@
         <v>1594</v>
       </c>
       <c r="E663">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F663" t="s">
         <v>1596</v>
@@ -31519,7 +31519,7 @@
         <v>1594</v>
       </c>
       <c r="E664">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F664" t="s">
         <v>1596</v>
@@ -31554,7 +31554,7 @@
         <v>1594</v>
       </c>
       <c r="E665">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F665" t="s">
         <v>1596</v>
@@ -31589,7 +31589,7 @@
         <v>1594</v>
       </c>
       <c r="E666">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F666" t="s">
         <v>1596</v>
@@ -31624,7 +31624,7 @@
         <v>1594</v>
       </c>
       <c r="E667">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F667" t="s">
         <v>1596</v>
@@ -31659,7 +31659,7 @@
         <v>1594</v>
       </c>
       <c r="E668">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F668" t="s">
         <v>1596</v>
@@ -31694,7 +31694,7 @@
         <v>1595</v>
       </c>
       <c r="E669">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F669" t="s">
         <v>1596</v>
@@ -31729,7 +31729,7 @@
         <v>1595</v>
       </c>
       <c r="E670">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F670" t="s">
         <v>1596</v>
@@ -31764,7 +31764,7 @@
         <v>1595</v>
       </c>
       <c r="E671">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F671" t="s">
         <v>1596</v>
@@ -31799,7 +31799,7 @@
         <v>1595</v>
       </c>
       <c r="E672">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F672" t="s">
         <v>1596</v>
@@ -31834,7 +31834,7 @@
         <v>1595</v>
       </c>
       <c r="E673">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F673" t="s">
         <v>1596</v>

--- a/BacklogGATEAutoCompleto.xlsx
+++ b/BacklogGATEAutoCompleto.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6714" uniqueCount="2598">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6714" uniqueCount="2596">
   <si>
     <t>NUCLEO</t>
   </si>
@@ -5128,12 +5128,12 @@
     <t>EDIWAN SOUSA DA SILVA,ELIANA MIRANDA ARAUJO DA SILVA SOARES</t>
   </si>
   <si>
+    <t>VANESSA DOYNSILÊ LEAL DA SILVA</t>
+  </si>
+  <si>
     <t>CHRISTIANA ROSA FERREIRA</t>
   </si>
   <si>
-    <t>VANESSA DOYNSILÊ LEAL DA SILVA</t>
-  </si>
-  <si>
     <t>RAQUEL SILVA FERNANDES LYRA</t>
   </si>
   <si>
@@ -7714,7 +7714,7 @@
     <t>BIOLOGIA,RESÍDUOS SÓLIDOS</t>
   </si>
   <si>
-    <t>ENGENHARIA CIVIL,ECONOMICIDADE OBRAS</t>
+    <t>ECONOMICIDADE OBRAS,ENGENHARIA CIVIL</t>
   </si>
   <si>
     <t>RECURSOS HÍDRICOS,URBANISMO</t>
@@ -7765,10 +7765,7 @@
     <t>MEDICINA LEGAL,SAÚDE</t>
   </si>
   <si>
-    <t>RECURSOS HÍDRICOS,ECONOMICIDADE OBRAS</t>
-  </si>
-  <si>
-    <t>ECONOMICIDADE OBRAS,ECONOMICIDADE CONTÁBIL</t>
+    <t>ECONOMICIDADE CONTÁBIL,ECONOMICIDADE OBRAS</t>
   </si>
   <si>
     <t>AVALIAÇÃO DE IMÓVEIS,GEOLOGIA</t>
@@ -7780,6 +7777,9 @@
     <t>ENGENHARIA CIVIL,ENGENHARIA QUÍMICA,FENOMENOS DE ENERGIA E INFORMAÇÃO</t>
   </si>
   <si>
+    <t>FENOMENOS DE ENERGIA E INFORMAÇÃO,ENGENHARIA CIVIL</t>
+  </si>
+  <si>
     <t>ECONOMICIDADE CONTÁBIL,ECONOMICIDADE CONTÁBIL</t>
   </si>
   <si>
@@ -7789,25 +7789,19 @@
     <t>ASSISTÊNCIA SOCIAL,EDIFICAÇÕES</t>
   </si>
   <si>
-    <t>AVALIAÇÃO DE IMÓVEIS,ECONOMICIDADE OBRAS</t>
-  </si>
-  <si>
-    <t>FENOMENOS DE ENERGIA E INFORMAÇÃO,ENGENHARIA CIVIL</t>
+    <t>ECONOMICIDADE OBRAS,AVALIAÇÃO DE IMÓVEIS</t>
   </si>
   <si>
     <t>SAÚDE,FARMÁCIA</t>
   </si>
   <si>
-    <t>SAÚDE,ORÇAMENTO</t>
-  </si>
-  <si>
     <t>URBANISMO,BIOLOGIA</t>
   </si>
   <si>
     <t>GEOTECNIA,ENGENHARIA CIVIL</t>
   </si>
   <si>
-    <t>ORÇAMENTO,PSICOLOGIA,URBANISMO,AVALIAÇÃO DE IMÓVEIS,MOBILIDADE E TRANSPORTE,ASSISTÊNCIA SOCIAL,SAÚDE,ECONOMIA,SAÚDE MENTAL,ECONOMICIDADE CONTÁBIL</t>
+    <t>ECONOMICIDADE CONTÁBIL,ORÇAMENTO,SAÚDE MENTAL,AVALIAÇÃO DE IMÓVEIS,SAÚDE,MOBILIDADE E TRANSPORTE,ECONOMIA,ASSISTÊNCIA SOCIAL,PSICOLOGIA,URBANISMO</t>
   </si>
 </sst>
 </file>
@@ -19913,7 +19907,7 @@
     </row>
     <row r="336" spans="1:12">
       <c r="A336" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="B336" t="s">
         <v>378</v>
@@ -19934,7 +19928,7 @@
         <v>1587</v>
       </c>
       <c r="I336" t="s">
-        <v>1704</v>
+        <v>1613</v>
       </c>
       <c r="J336" t="s">
         <v>2070</v>
@@ -20074,7 +20068,7 @@
         <v>1587</v>
       </c>
       <c r="I340" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
       <c r="J340" t="s">
         <v>2074</v>
@@ -20599,7 +20593,7 @@
         <v>1587</v>
       </c>
       <c r="I355" t="s">
-        <v>1704</v>
+        <v>1705</v>
       </c>
       <c r="J355" t="s">
         <v>2089</v>
@@ -22603,7 +22597,7 @@
         <v>1587</v>
       </c>
       <c r="I412" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
       <c r="J412" t="s">
         <v>2146</v>
@@ -22813,7 +22807,7 @@
         <v>1587</v>
       </c>
       <c r="I418" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
       <c r="J418" t="s">
         <v>2152</v>
@@ -23338,7 +23332,7 @@
         <v>1587</v>
       </c>
       <c r="I433" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
       <c r="J433" t="s">
         <v>2166</v>
@@ -23408,7 +23402,7 @@
         <v>1587</v>
       </c>
       <c r="I435" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
       <c r="J435" t="s">
         <v>2168</v>
@@ -23417,7 +23411,7 @@
         <v>2399</v>
       </c>
       <c r="L435" t="s">
-        <v>2569</v>
+        <v>2542</v>
       </c>
     </row>
     <row r="436" spans="1:12">
@@ -24041,7 +24035,7 @@
         <v>1587</v>
       </c>
       <c r="I453" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
       <c r="J453" t="s">
         <v>2186</v>
@@ -24225,7 +24219,7 @@
         <v>2433</v>
       </c>
       <c r="L458" t="s">
-        <v>2583</v>
+        <v>2579</v>
       </c>
     </row>
     <row r="459" spans="1:12">
@@ -24499,7 +24493,7 @@
         <v>1587</v>
       </c>
       <c r="I466" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
       <c r="J466" t="s">
         <v>2199</v>
@@ -24604,7 +24598,7 @@
         <v>1587</v>
       </c>
       <c r="I469" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
       <c r="J469" t="s">
         <v>2202</v>
@@ -24613,7 +24607,7 @@
         <v>2425</v>
       </c>
       <c r="L469" t="s">
-        <v>2569</v>
+        <v>2528</v>
       </c>
     </row>
     <row r="470" spans="1:12">
@@ -24639,7 +24633,7 @@
         <v>1587</v>
       </c>
       <c r="I470" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
       <c r="J470" t="s">
         <v>2203</v>
@@ -25094,7 +25088,7 @@
         <v>1587</v>
       </c>
       <c r="I483" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
       <c r="J483" t="s">
         <v>2215</v>
@@ -25103,7 +25097,7 @@
         <v>2401</v>
       </c>
       <c r="L483" t="s">
-        <v>2569</v>
+        <v>2519</v>
       </c>
     </row>
     <row r="484" spans="1:12">
@@ -25797,7 +25791,7 @@
         <v>1587</v>
       </c>
       <c r="I503" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
       <c r="J503" t="s">
         <v>2235</v>
@@ -25806,7 +25800,7 @@
         <v>2412</v>
       </c>
       <c r="L503" t="s">
-        <v>2569</v>
+        <v>2528</v>
       </c>
     </row>
     <row r="504" spans="1:12">
@@ -26996,7 +26990,7 @@
         <v>2489</v>
       </c>
       <c r="L537" t="s">
-        <v>2584</v>
+        <v>2583</v>
       </c>
     </row>
     <row r="538" spans="1:12">
@@ -27273,7 +27267,7 @@
         <v>1587</v>
       </c>
       <c r="I545" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
       <c r="J545" t="s">
         <v>2274</v>
@@ -27346,7 +27340,7 @@
         <v>1587</v>
       </c>
       <c r="I547" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
       <c r="J547" t="s">
         <v>2276</v>
@@ -27451,7 +27445,7 @@
         <v>1587</v>
       </c>
       <c r="I550" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
       <c r="J550" t="s">
         <v>2279</v>
@@ -27533,7 +27527,7 @@
         <v>2411</v>
       </c>
       <c r="L552" t="s">
-        <v>2585</v>
+        <v>2584</v>
       </c>
     </row>
     <row r="553" spans="1:12">
@@ -27568,7 +27562,7 @@
         <v>2461</v>
       </c>
       <c r="L553" t="s">
-        <v>2586</v>
+        <v>2585</v>
       </c>
     </row>
     <row r="554" spans="1:12">
@@ -28090,7 +28084,7 @@
         <v>1587</v>
       </c>
       <c r="I568" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
       <c r="J568" t="s">
         <v>2297</v>
@@ -28125,7 +28119,7 @@
         <v>1587</v>
       </c>
       <c r="I569" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
       <c r="J569" t="s">
         <v>2298</v>
@@ -28265,7 +28259,7 @@
         <v>1587</v>
       </c>
       <c r="I573" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
       <c r="J573" t="s">
         <v>2302</v>
@@ -28373,7 +28367,7 @@
         <v>1587</v>
       </c>
       <c r="I576" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
       <c r="J576" t="s">
         <v>2305</v>
@@ -28487,7 +28481,7 @@
         <v>2462</v>
       </c>
       <c r="L579" t="s">
-        <v>2587</v>
+        <v>2586</v>
       </c>
     </row>
     <row r="580" spans="1:12">
@@ -28522,7 +28516,7 @@
         <v>2462</v>
       </c>
       <c r="L580" t="s">
-        <v>2587</v>
+        <v>2586</v>
       </c>
     </row>
     <row r="581" spans="1:12">
@@ -28557,7 +28551,7 @@
         <v>2406</v>
       </c>
       <c r="L581" t="s">
-        <v>2586</v>
+        <v>2587</v>
       </c>
     </row>
     <row r="582" spans="1:12">
@@ -29575,7 +29569,7 @@
         <v>1587</v>
       </c>
       <c r="I610" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
       <c r="J610" t="s">
         <v>2335</v>
@@ -29791,7 +29785,7 @@
         <v>1587</v>
       </c>
       <c r="I616" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
       <c r="J616" t="s">
         <v>2341</v>
@@ -29931,7 +29925,7 @@
         <v>1587</v>
       </c>
       <c r="I620" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
       <c r="J620" t="s">
         <v>2345</v>
@@ -30080,7 +30074,7 @@
         <v>2503</v>
       </c>
       <c r="L624" t="s">
-        <v>2592</v>
+        <v>2587</v>
       </c>
     </row>
     <row r="625" spans="1:12">
@@ -30115,7 +30109,7 @@
         <v>2435</v>
       </c>
       <c r="L625" t="s">
-        <v>2593</v>
+        <v>2592</v>
       </c>
     </row>
     <row r="626" spans="1:12">
@@ -30217,7 +30211,7 @@
         <v>1606</v>
       </c>
       <c r="I628" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
       <c r="J628" t="s">
         <v>2352</v>
@@ -30325,7 +30319,7 @@
         <v>1587</v>
       </c>
       <c r="I631" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
       <c r="J631" t="s">
         <v>2355</v>
@@ -30407,7 +30401,7 @@
         <v>2467</v>
       </c>
       <c r="L633" t="s">
-        <v>2594</v>
+        <v>2575</v>
       </c>
     </row>
     <row r="634" spans="1:12">
@@ -30433,7 +30427,7 @@
         <v>1587</v>
       </c>
       <c r="I634" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
       <c r="J634" t="s">
         <v>2358</v>
@@ -30442,7 +30436,7 @@
         <v>2431</v>
       </c>
       <c r="L634" t="s">
-        <v>2569</v>
+        <v>2552</v>
       </c>
     </row>
     <row r="635" spans="1:12">
@@ -30754,7 +30748,7 @@
         <v>1587</v>
       </c>
       <c r="I643" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
       <c r="J643" t="s">
         <v>2367</v>
@@ -30789,7 +30783,7 @@
         <v>1587</v>
       </c>
       <c r="I644" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
       <c r="J644" t="s">
         <v>2368</v>
@@ -30824,7 +30818,7 @@
         <v>1587</v>
       </c>
       <c r="I645" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
       <c r="J645" t="s">
         <v>2369</v>
@@ -31069,7 +31063,7 @@
         <v>1587</v>
       </c>
       <c r="I652" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
       <c r="J652" t="s">
         <v>2375</v>
@@ -31174,7 +31168,7 @@
         <v>1587</v>
       </c>
       <c r="I655" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
       <c r="J655" t="s">
         <v>2378</v>
@@ -31510,7 +31504,7 @@
         <v>2506</v>
       </c>
       <c r="L664" t="s">
-        <v>2595</v>
+        <v>2593</v>
       </c>
     </row>
     <row r="665" spans="1:12">
@@ -31612,7 +31606,7 @@
         <v>2514</v>
       </c>
       <c r="L667" t="s">
-        <v>2596</v>
+        <v>2594</v>
       </c>
     </row>
     <row r="668" spans="1:12">
@@ -31644,7 +31638,7 @@
         <v>2514</v>
       </c>
       <c r="L668" t="s">
-        <v>2597</v>
+        <v>2595</v>
       </c>
     </row>
   </sheetData>

--- a/BacklogGATEAutoCompleto.xlsx
+++ b/BacklogGATEAutoCompleto.xlsx
@@ -8214,7 +8214,7 @@
         <v>1370</v>
       </c>
       <c r="E2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="F2" t="s">
         <v>1582</v>
@@ -8249,7 +8249,7 @@
         <v>1371</v>
       </c>
       <c r="E3">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F3" t="s">
         <v>1582</v>
@@ -8284,7 +8284,7 @@
         <v>1372</v>
       </c>
       <c r="E4">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="F4" t="s">
         <v>1582</v>
@@ -8319,7 +8319,7 @@
         <v>1373</v>
       </c>
       <c r="E5">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="F5" t="s">
         <v>1582</v>
@@ -8354,7 +8354,7 @@
         <v>1374</v>
       </c>
       <c r="E6">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="F6" t="s">
         <v>1582</v>
@@ -8389,7 +8389,7 @@
         <v>1375</v>
       </c>
       <c r="E7">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="F7" t="s">
         <v>1582</v>
@@ -8424,7 +8424,7 @@
         <v>1376</v>
       </c>
       <c r="E8">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F8" t="s">
         <v>1582</v>
@@ -8459,7 +8459,7 @@
         <v>1377</v>
       </c>
       <c r="E9">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="F9" t="s">
         <v>1582</v>
@@ -8494,7 +8494,7 @@
         <v>1378</v>
       </c>
       <c r="E10">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="F10" t="s">
         <v>1582</v>
@@ -8529,7 +8529,7 @@
         <v>1379</v>
       </c>
       <c r="E11">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="F11" t="s">
         <v>1582</v>
@@ -8564,7 +8564,7 @@
         <v>1379</v>
       </c>
       <c r="E12">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="F12" t="s">
         <v>1582</v>
@@ -8599,7 +8599,7 @@
         <v>1380</v>
       </c>
       <c r="E13">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="F13" t="s">
         <v>1582</v>
@@ -8634,7 +8634,7 @@
         <v>1381</v>
       </c>
       <c r="E14">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="F14" t="s">
         <v>1582</v>
@@ -8669,7 +8669,7 @@
         <v>1382</v>
       </c>
       <c r="E15">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="F15" t="s">
         <v>1582</v>
@@ -8704,7 +8704,7 @@
         <v>1382</v>
       </c>
       <c r="E16">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="F16" t="s">
         <v>1582</v>
@@ -8739,7 +8739,7 @@
         <v>1383</v>
       </c>
       <c r="E17">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F17" t="s">
         <v>1582</v>
@@ -8774,7 +8774,7 @@
         <v>1384</v>
       </c>
       <c r="E18">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="F18" t="s">
         <v>1582</v>
@@ -8809,7 +8809,7 @@
         <v>1384</v>
       </c>
       <c r="E19">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="F19" t="s">
         <v>1582</v>
@@ -8844,7 +8844,7 @@
         <v>1385</v>
       </c>
       <c r="E20">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="F20" t="s">
         <v>1582</v>
@@ -8879,7 +8879,7 @@
         <v>1386</v>
       </c>
       <c r="E21">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="F21" t="s">
         <v>1582</v>
@@ -8914,7 +8914,7 @@
         <v>1387</v>
       </c>
       <c r="E22">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="F22" t="s">
         <v>1582</v>
@@ -8949,7 +8949,7 @@
         <v>1388</v>
       </c>
       <c r="E23">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="F23" t="s">
         <v>1582</v>
@@ -8984,7 +8984,7 @@
         <v>1389</v>
       </c>
       <c r="E24">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="F24" t="s">
         <v>1582</v>
@@ -9022,7 +9022,7 @@
         <v>1390</v>
       </c>
       <c r="E25">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="F25" t="s">
         <v>1582</v>
@@ -9057,7 +9057,7 @@
         <v>1391</v>
       </c>
       <c r="E26">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F26" t="s">
         <v>1582</v>
@@ -9092,7 +9092,7 @@
         <v>1392</v>
       </c>
       <c r="E27">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F27" t="s">
         <v>1582</v>
@@ -9127,7 +9127,7 @@
         <v>1393</v>
       </c>
       <c r="E28">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F28" t="s">
         <v>1582</v>
@@ -9162,7 +9162,7 @@
         <v>1393</v>
       </c>
       <c r="E29">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F29" t="s">
         <v>1582</v>
@@ -9197,7 +9197,7 @@
         <v>1394</v>
       </c>
       <c r="E30">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F30" t="s">
         <v>1582</v>
@@ -9232,7 +9232,7 @@
         <v>1395</v>
       </c>
       <c r="E31">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F31" t="s">
         <v>1582</v>
@@ -9267,7 +9267,7 @@
         <v>1396</v>
       </c>
       <c r="E32">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F32" t="s">
         <v>1582</v>
@@ -9302,7 +9302,7 @@
         <v>1397</v>
       </c>
       <c r="E33">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F33" t="s">
         <v>1582</v>
@@ -9337,7 +9337,7 @@
         <v>1398</v>
       </c>
       <c r="E34">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="F34" t="s">
         <v>1582</v>
@@ -9372,7 +9372,7 @@
         <v>1399</v>
       </c>
       <c r="E35">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F35" t="s">
         <v>1582</v>
@@ -9407,7 +9407,7 @@
         <v>1400</v>
       </c>
       <c r="E36">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F36" t="s">
         <v>1582</v>
@@ -9442,7 +9442,7 @@
         <v>1401</v>
       </c>
       <c r="E37">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F37" t="s">
         <v>1582</v>
@@ -9477,7 +9477,7 @@
         <v>1401</v>
       </c>
       <c r="E38">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F38" t="s">
         <v>1582</v>
@@ -9512,7 +9512,7 @@
         <v>1402</v>
       </c>
       <c r="E39">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F39" t="s">
         <v>1582</v>
@@ -9547,7 +9547,7 @@
         <v>1403</v>
       </c>
       <c r="E40">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F40" t="s">
         <v>1582</v>
@@ -9582,7 +9582,7 @@
         <v>1404</v>
       </c>
       <c r="E41">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F41" t="s">
         <v>1582</v>
@@ -9617,7 +9617,7 @@
         <v>1405</v>
       </c>
       <c r="E42">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F42" t="s">
         <v>1582</v>
@@ -9652,7 +9652,7 @@
         <v>1406</v>
       </c>
       <c r="E43">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F43" t="s">
         <v>1582</v>
@@ -9687,7 +9687,7 @@
         <v>1406</v>
       </c>
       <c r="E44">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F44" t="s">
         <v>1582</v>
@@ -9722,7 +9722,7 @@
         <v>1407</v>
       </c>
       <c r="E45">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F45" t="s">
         <v>1582</v>
@@ -9757,7 +9757,7 @@
         <v>1408</v>
       </c>
       <c r="E46">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F46" t="s">
         <v>1582</v>
@@ -9792,7 +9792,7 @@
         <v>1408</v>
       </c>
       <c r="E47">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F47" t="s">
         <v>1582</v>
@@ -9827,7 +9827,7 @@
         <v>1409</v>
       </c>
       <c r="E48">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F48" t="s">
         <v>1582</v>
@@ -9862,7 +9862,7 @@
         <v>1409</v>
       </c>
       <c r="E49">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F49" t="s">
         <v>1582</v>
@@ -9897,7 +9897,7 @@
         <v>1410</v>
       </c>
       <c r="E50">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F50" t="s">
         <v>1582</v>
@@ -9932,7 +9932,7 @@
         <v>1411</v>
       </c>
       <c r="E51">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F51" t="s">
         <v>1582</v>
@@ -9967,7 +9967,7 @@
         <v>1412</v>
       </c>
       <c r="E52">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F52" t="s">
         <v>1582</v>
@@ -10002,7 +10002,7 @@
         <v>1413</v>
       </c>
       <c r="E53">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F53" t="s">
         <v>1582</v>
@@ -10037,7 +10037,7 @@
         <v>1414</v>
       </c>
       <c r="E54">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F54" t="s">
         <v>1582</v>
@@ -10072,7 +10072,7 @@
         <v>1415</v>
       </c>
       <c r="E55">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F55" t="s">
         <v>1582</v>
@@ -10107,7 +10107,7 @@
         <v>1416</v>
       </c>
       <c r="E56">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F56" t="s">
         <v>1582</v>
@@ -10142,7 +10142,7 @@
         <v>1417</v>
       </c>
       <c r="E57">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F57" t="s">
         <v>1582</v>
@@ -10177,7 +10177,7 @@
         <v>1418</v>
       </c>
       <c r="E58">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F58" t="s">
         <v>1582</v>
@@ -10212,7 +10212,7 @@
         <v>1419</v>
       </c>
       <c r="E59">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F59" t="s">
         <v>1582</v>
@@ -10247,7 +10247,7 @@
         <v>1420</v>
       </c>
       <c r="E60">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F60" t="s">
         <v>1582</v>
@@ -10282,7 +10282,7 @@
         <v>1421</v>
       </c>
       <c r="E61">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F61" t="s">
         <v>1582</v>
@@ -10317,7 +10317,7 @@
         <v>1422</v>
       </c>
       <c r="E62">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F62" t="s">
         <v>1582</v>
@@ -10352,7 +10352,7 @@
         <v>1422</v>
       </c>
       <c r="E63">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F63" t="s">
         <v>1582</v>
@@ -10387,7 +10387,7 @@
         <v>1422</v>
       </c>
       <c r="E64">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F64" t="s">
         <v>1582</v>
@@ -10422,7 +10422,7 @@
         <v>1423</v>
       </c>
       <c r="E65">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F65" t="s">
         <v>1582</v>
@@ -10457,7 +10457,7 @@
         <v>1424</v>
       </c>
       <c r="E66">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F66" t="s">
         <v>1582</v>
@@ -10492,7 +10492,7 @@
         <v>1425</v>
       </c>
       <c r="E67">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F67" t="s">
         <v>1582</v>
@@ -10527,7 +10527,7 @@
         <v>1425</v>
       </c>
       <c r="E68">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F68" t="s">
         <v>1582</v>
@@ -10562,7 +10562,7 @@
         <v>1425</v>
       </c>
       <c r="E69">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F69" t="s">
         <v>1582</v>
@@ -10597,7 +10597,7 @@
         <v>1426</v>
       </c>
       <c r="E70">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F70" t="s">
         <v>1582</v>
@@ -10632,7 +10632,7 @@
         <v>1427</v>
       </c>
       <c r="E71">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F71" t="s">
         <v>1582</v>
@@ -10667,7 +10667,7 @@
         <v>1428</v>
       </c>
       <c r="E72">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F72" t="s">
         <v>1582</v>
@@ -10702,7 +10702,7 @@
         <v>1428</v>
       </c>
       <c r="E73">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F73" t="s">
         <v>1582</v>
@@ -10737,7 +10737,7 @@
         <v>1428</v>
       </c>
       <c r="E74">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F74" t="s">
         <v>1582</v>
@@ -10772,7 +10772,7 @@
         <v>1429</v>
       </c>
       <c r="E75">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F75" t="s">
         <v>1582</v>
@@ -10807,7 +10807,7 @@
         <v>1430</v>
       </c>
       <c r="E76">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F76" t="s">
         <v>1582</v>
@@ -10842,7 +10842,7 @@
         <v>1430</v>
       </c>
       <c r="E77">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F77" t="s">
         <v>1582</v>
@@ -10877,7 +10877,7 @@
         <v>1430</v>
       </c>
       <c r="E78">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F78" t="s">
         <v>1583</v>
@@ -10912,7 +10912,7 @@
         <v>1430</v>
       </c>
       <c r="E79">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F79" t="s">
         <v>1582</v>
@@ -10947,7 +10947,7 @@
         <v>1431</v>
       </c>
       <c r="E80">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F80" t="s">
         <v>1582</v>
@@ -10982,7 +10982,7 @@
         <v>1432</v>
       </c>
       <c r="E81">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F81" t="s">
         <v>1582</v>
@@ -11017,7 +11017,7 @@
         <v>1432</v>
       </c>
       <c r="E82">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F82" t="s">
         <v>1582</v>
@@ -11052,7 +11052,7 @@
         <v>1433</v>
       </c>
       <c r="E83">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F83" t="s">
         <v>1582</v>
@@ -11087,7 +11087,7 @@
         <v>1434</v>
       </c>
       <c r="E84">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F84" t="s">
         <v>1582</v>
@@ -11122,7 +11122,7 @@
         <v>1435</v>
       </c>
       <c r="E85">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F85" t="s">
         <v>1582</v>
@@ -11157,7 +11157,7 @@
         <v>1436</v>
       </c>
       <c r="E86">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F86" t="s">
         <v>1582</v>
@@ -11192,7 +11192,7 @@
         <v>1437</v>
       </c>
       <c r="E87">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F87" t="s">
         <v>1582</v>
@@ -11227,7 +11227,7 @@
         <v>1437</v>
       </c>
       <c r="E88">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F88" t="s">
         <v>1582</v>
@@ -11262,7 +11262,7 @@
         <v>1437</v>
       </c>
       <c r="E89">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F89" t="s">
         <v>1582</v>
@@ -11297,7 +11297,7 @@
         <v>1437</v>
       </c>
       <c r="E90">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F90" t="s">
         <v>1582</v>
@@ -11332,7 +11332,7 @@
         <v>1437</v>
       </c>
       <c r="E91">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F91" t="s">
         <v>1582</v>
@@ -11367,7 +11367,7 @@
         <v>1437</v>
       </c>
       <c r="E92">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F92" t="s">
         <v>1582</v>
@@ -11402,7 +11402,7 @@
         <v>1437</v>
       </c>
       <c r="E93">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F93" t="s">
         <v>1582</v>
@@ -11437,7 +11437,7 @@
         <v>1438</v>
       </c>
       <c r="E94">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F94" t="s">
         <v>1582</v>
@@ -11472,7 +11472,7 @@
         <v>1438</v>
       </c>
       <c r="E95">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F95" t="s">
         <v>1582</v>
@@ -11507,7 +11507,7 @@
         <v>1439</v>
       </c>
       <c r="E96">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F96" t="s">
         <v>1582</v>
@@ -11542,7 +11542,7 @@
         <v>1440</v>
       </c>
       <c r="E97">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F97" t="s">
         <v>1582</v>
@@ -11577,7 +11577,7 @@
         <v>1440</v>
       </c>
       <c r="E98">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F98" t="s">
         <v>1582</v>
@@ -11612,7 +11612,7 @@
         <v>1441</v>
       </c>
       <c r="E99">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F99" t="s">
         <v>1582</v>
@@ -11647,7 +11647,7 @@
         <v>1441</v>
       </c>
       <c r="E100">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F100" t="s">
         <v>1584</v>
@@ -11682,7 +11682,7 @@
         <v>1442</v>
       </c>
       <c r="E101">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F101" t="s">
         <v>1582</v>
@@ -11717,7 +11717,7 @@
         <v>1443</v>
       </c>
       <c r="E102">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F102" t="s">
         <v>1582</v>
@@ -11752,7 +11752,7 @@
         <v>1444</v>
       </c>
       <c r="E103">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F103" t="s">
         <v>1582</v>
@@ -11787,7 +11787,7 @@
         <v>1444</v>
       </c>
       <c r="E104">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F104" t="s">
         <v>1582</v>
@@ -11822,7 +11822,7 @@
         <v>1445</v>
       </c>
       <c r="E105">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F105" t="s">
         <v>1582</v>
@@ -11857,7 +11857,7 @@
         <v>1446</v>
       </c>
       <c r="E106">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F106" t="s">
         <v>1582</v>
@@ -11892,7 +11892,7 @@
         <v>1447</v>
       </c>
       <c r="E107">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F107" t="s">
         <v>1582</v>
@@ -11927,7 +11927,7 @@
         <v>1448</v>
       </c>
       <c r="E108">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F108" t="s">
         <v>1582</v>
@@ -11962,7 +11962,7 @@
         <v>1449</v>
       </c>
       <c r="E109">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F109" t="s">
         <v>1582</v>
@@ -11997,7 +11997,7 @@
         <v>1449</v>
       </c>
       <c r="E110">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F110" t="s">
         <v>1582</v>
@@ -12032,7 +12032,7 @@
         <v>1450</v>
       </c>
       <c r="E111">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F111" t="s">
         <v>1582</v>
@@ -12067,7 +12067,7 @@
         <v>1450</v>
       </c>
       <c r="E112">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F112" t="s">
         <v>1582</v>
@@ -12102,7 +12102,7 @@
         <v>1450</v>
       </c>
       <c r="E113">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F113" t="s">
         <v>1582</v>
@@ -12137,7 +12137,7 @@
         <v>1451</v>
       </c>
       <c r="E114">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F114" t="s">
         <v>1582</v>
@@ -12172,7 +12172,7 @@
         <v>1451</v>
       </c>
       <c r="E115">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F115" t="s">
         <v>1582</v>
@@ -12207,7 +12207,7 @@
         <v>1451</v>
       </c>
       <c r="E116">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F116" t="s">
         <v>1582</v>
@@ -12242,7 +12242,7 @@
         <v>1451</v>
       </c>
       <c r="E117">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F117" t="s">
         <v>1582</v>
@@ -12277,7 +12277,7 @@
         <v>1451</v>
       </c>
       <c r="E118">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F118" t="s">
         <v>1582</v>
@@ -12312,7 +12312,7 @@
         <v>1452</v>
       </c>
       <c r="E119">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F119" t="s">
         <v>1582</v>
@@ -12347,7 +12347,7 @@
         <v>1453</v>
       </c>
       <c r="E120">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F120" t="s">
         <v>1582</v>
@@ -12382,7 +12382,7 @@
         <v>1453</v>
       </c>
       <c r="E121">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F121" t="s">
         <v>1582</v>
@@ -12417,7 +12417,7 @@
         <v>1454</v>
       </c>
       <c r="E122">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F122" t="s">
         <v>1582</v>
@@ -12452,7 +12452,7 @@
         <v>1455</v>
       </c>
       <c r="E123">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F123" t="s">
         <v>1582</v>
@@ -12487,7 +12487,7 @@
         <v>1455</v>
       </c>
       <c r="E124">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F124" t="s">
         <v>1582</v>
@@ -12522,7 +12522,7 @@
         <v>1455</v>
       </c>
       <c r="E125">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F125" t="s">
         <v>1582</v>
@@ -12557,7 +12557,7 @@
         <v>1456</v>
       </c>
       <c r="E126">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F126" t="s">
         <v>1582</v>
@@ -12592,7 +12592,7 @@
         <v>1456</v>
       </c>
       <c r="E127">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F127" t="s">
         <v>1582</v>
@@ -12627,7 +12627,7 @@
         <v>1456</v>
       </c>
       <c r="E128">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F128" t="s">
         <v>1582</v>
@@ -12662,7 +12662,7 @@
         <v>1457</v>
       </c>
       <c r="E129">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F129" t="s">
         <v>1582</v>
@@ -12697,7 +12697,7 @@
         <v>1457</v>
       </c>
       <c r="E130">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F130" t="s">
         <v>1582</v>
@@ -12732,7 +12732,7 @@
         <v>1457</v>
       </c>
       <c r="E131">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F131" t="s">
         <v>1582</v>
@@ -12767,7 +12767,7 @@
         <v>1458</v>
       </c>
       <c r="E132">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F132" t="s">
         <v>1582</v>
@@ -12802,7 +12802,7 @@
         <v>1458</v>
       </c>
       <c r="E133">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F133" t="s">
         <v>1582</v>
@@ -12837,7 +12837,7 @@
         <v>1459</v>
       </c>
       <c r="E134">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F134" t="s">
         <v>1582</v>
@@ -12872,7 +12872,7 @@
         <v>1460</v>
       </c>
       <c r="E135">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F135" t="s">
         <v>1582</v>
@@ -12907,7 +12907,7 @@
         <v>1460</v>
       </c>
       <c r="E136">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F136" t="s">
         <v>1582</v>
@@ -12942,7 +12942,7 @@
         <v>1460</v>
       </c>
       <c r="E137">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F137" t="s">
         <v>1582</v>
@@ -12977,7 +12977,7 @@
         <v>1461</v>
       </c>
       <c r="E138">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F138" t="s">
         <v>1582</v>
@@ -13012,7 +13012,7 @@
         <v>1461</v>
       </c>
       <c r="E139">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F139" t="s">
         <v>1582</v>
@@ -13047,7 +13047,7 @@
         <v>1462</v>
       </c>
       <c r="E140">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F140" t="s">
         <v>1582</v>
@@ -13085,7 +13085,7 @@
         <v>1462</v>
       </c>
       <c r="E141">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F141" t="s">
         <v>1582</v>
@@ -13120,7 +13120,7 @@
         <v>1462</v>
       </c>
       <c r="E142">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F142" t="s">
         <v>1582</v>
@@ -13155,7 +13155,7 @@
         <v>1462</v>
       </c>
       <c r="E143">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F143" t="s">
         <v>1582</v>
@@ -13190,7 +13190,7 @@
         <v>1462</v>
       </c>
       <c r="E144">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F144" t="s">
         <v>1582</v>
@@ -13225,7 +13225,7 @@
         <v>1463</v>
       </c>
       <c r="E145">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F145" t="s">
         <v>1582</v>
@@ -13260,7 +13260,7 @@
         <v>1464</v>
       </c>
       <c r="E146">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F146" t="s">
         <v>1583</v>
@@ -13295,7 +13295,7 @@
         <v>1465</v>
       </c>
       <c r="E147">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F147" t="s">
         <v>1582</v>
@@ -13330,7 +13330,7 @@
         <v>1465</v>
       </c>
       <c r="E148">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F148" t="s">
         <v>1582</v>
@@ -13365,7 +13365,7 @@
         <v>1465</v>
       </c>
       <c r="E149">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F149" t="s">
         <v>1582</v>
@@ -13400,7 +13400,7 @@
         <v>1465</v>
       </c>
       <c r="E150">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F150" t="s">
         <v>1582</v>
@@ -13435,7 +13435,7 @@
         <v>1466</v>
       </c>
       <c r="E151">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F151" t="s">
         <v>1582</v>
@@ -13470,7 +13470,7 @@
         <v>1466</v>
       </c>
       <c r="E152">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F152" t="s">
         <v>1582</v>
@@ -13505,7 +13505,7 @@
         <v>1466</v>
       </c>
       <c r="E153">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F153" t="s">
         <v>1582</v>
@@ -13540,7 +13540,7 @@
         <v>1466</v>
       </c>
       <c r="E154">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F154" t="s">
         <v>1582</v>
@@ -13575,7 +13575,7 @@
         <v>1466</v>
       </c>
       <c r="E155">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F155" t="s">
         <v>1582</v>
@@ -13610,7 +13610,7 @@
         <v>1466</v>
       </c>
       <c r="E156">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F156" t="s">
         <v>1582</v>
@@ -13645,7 +13645,7 @@
         <v>1466</v>
       </c>
       <c r="E157">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F157" t="s">
         <v>1582</v>
@@ -13680,7 +13680,7 @@
         <v>1467</v>
       </c>
       <c r="E158">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F158" t="s">
         <v>1582</v>
@@ -13715,7 +13715,7 @@
         <v>1467</v>
       </c>
       <c r="E159">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F159" t="s">
         <v>1582</v>
@@ -13750,7 +13750,7 @@
         <v>1468</v>
       </c>
       <c r="E160">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F160" t="s">
         <v>1582</v>
@@ -13785,7 +13785,7 @@
         <v>1468</v>
       </c>
       <c r="E161">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F161" t="s">
         <v>1582</v>
@@ -13820,7 +13820,7 @@
         <v>1469</v>
       </c>
       <c r="E162">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F162" t="s">
         <v>1582</v>
@@ -13855,7 +13855,7 @@
         <v>1469</v>
       </c>
       <c r="E163">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F163" t="s">
         <v>1582</v>
@@ -13890,7 +13890,7 @@
         <v>1469</v>
       </c>
       <c r="E164">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F164" t="s">
         <v>1582</v>
@@ -13925,7 +13925,7 @@
         <v>1469</v>
       </c>
       <c r="E165">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F165" t="s">
         <v>1582</v>
@@ -13960,7 +13960,7 @@
         <v>1470</v>
       </c>
       <c r="E166">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F166" t="s">
         <v>1582</v>
@@ -13995,7 +13995,7 @@
         <v>1470</v>
       </c>
       <c r="E167">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F167" t="s">
         <v>1582</v>
@@ -14030,7 +14030,7 @@
         <v>1470</v>
       </c>
       <c r="E168">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F168" t="s">
         <v>1582</v>
@@ -14065,7 +14065,7 @@
         <v>1470</v>
       </c>
       <c r="E169">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F169" t="s">
         <v>1582</v>
@@ -14100,7 +14100,7 @@
         <v>1470</v>
       </c>
       <c r="E170">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F170" t="s">
         <v>1582</v>
@@ -14135,7 +14135,7 @@
         <v>1470</v>
       </c>
       <c r="E171">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F171" t="s">
         <v>1582</v>
@@ -14170,7 +14170,7 @@
         <v>1470</v>
       </c>
       <c r="E172">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F172" t="s">
         <v>1582</v>
@@ -14205,7 +14205,7 @@
         <v>1470</v>
       </c>
       <c r="E173">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F173" t="s">
         <v>1582</v>
@@ -14240,7 +14240,7 @@
         <v>1470</v>
       </c>
       <c r="E174">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F174" t="s">
         <v>1582</v>
@@ -14275,7 +14275,7 @@
         <v>1470</v>
       </c>
       <c r="E175">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F175" t="s">
         <v>1582</v>
@@ -14310,7 +14310,7 @@
         <v>1471</v>
       </c>
       <c r="E176">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F176" t="s">
         <v>1582</v>
@@ -14345,7 +14345,7 @@
         <v>1471</v>
       </c>
       <c r="E177">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F177" t="s">
         <v>1582</v>
@@ -14380,7 +14380,7 @@
         <v>1471</v>
       </c>
       <c r="E178">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F178" t="s">
         <v>1582</v>
@@ -14415,7 +14415,7 @@
         <v>1472</v>
       </c>
       <c r="E179">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F179" t="s">
         <v>1582</v>
@@ -14450,7 +14450,7 @@
         <v>1472</v>
       </c>
       <c r="E180">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F180" t="s">
         <v>1583</v>
@@ -14485,7 +14485,7 @@
         <v>1472</v>
       </c>
       <c r="E181">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F181" t="s">
         <v>1582</v>
@@ -14520,7 +14520,7 @@
         <v>1473</v>
       </c>
       <c r="E182">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F182" t="s">
         <v>1582</v>
@@ -14555,7 +14555,7 @@
         <v>1473</v>
       </c>
       <c r="E183">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F183" t="s">
         <v>1582</v>
@@ -14590,7 +14590,7 @@
         <v>1474</v>
       </c>
       <c r="E184">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F184" t="s">
         <v>1582</v>
@@ -14625,7 +14625,7 @@
         <v>1474</v>
       </c>
       <c r="E185">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F185" t="s">
         <v>1582</v>
@@ -14660,7 +14660,7 @@
         <v>1475</v>
       </c>
       <c r="E186">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F186" t="s">
         <v>1582</v>
@@ -14695,7 +14695,7 @@
         <v>1475</v>
       </c>
       <c r="E187">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F187" t="s">
         <v>1582</v>
@@ -14730,7 +14730,7 @@
         <v>1476</v>
       </c>
       <c r="E188">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F188" t="s">
         <v>1582</v>
@@ -14765,7 +14765,7 @@
         <v>1476</v>
       </c>
       <c r="E189">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F189" t="s">
         <v>1582</v>
@@ -14800,7 +14800,7 @@
         <v>1476</v>
       </c>
       <c r="E190">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F190" t="s">
         <v>1582</v>
@@ -14835,7 +14835,7 @@
         <v>1476</v>
       </c>
       <c r="E191">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F191" t="s">
         <v>1582</v>
@@ -14870,7 +14870,7 @@
         <v>1476</v>
       </c>
       <c r="E192">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F192" t="s">
         <v>1582</v>
@@ -14905,7 +14905,7 @@
         <v>1477</v>
       </c>
       <c r="E193">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F193" t="s">
         <v>1582</v>
@@ -14940,7 +14940,7 @@
         <v>1477</v>
       </c>
       <c r="E194">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F194" t="s">
         <v>1582</v>
@@ -14975,7 +14975,7 @@
         <v>1478</v>
       </c>
       <c r="E195">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F195" t="s">
         <v>1582</v>
@@ -15010,7 +15010,7 @@
         <v>1479</v>
       </c>
       <c r="E196">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F196" t="s">
         <v>1582</v>
@@ -15045,7 +15045,7 @@
         <v>1479</v>
       </c>
       <c r="E197">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F197" t="s">
         <v>1582</v>
@@ -15080,7 +15080,7 @@
         <v>1479</v>
       </c>
       <c r="E198">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F198" t="s">
         <v>1582</v>
@@ -15115,7 +15115,7 @@
         <v>1479</v>
       </c>
       <c r="E199">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F199" t="s">
         <v>1582</v>
@@ -15150,7 +15150,7 @@
         <v>1480</v>
       </c>
       <c r="E200">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F200" t="s">
         <v>1582</v>
@@ -15185,7 +15185,7 @@
         <v>1481</v>
       </c>
       <c r="E201">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F201" t="s">
         <v>1582</v>
@@ -15220,7 +15220,7 @@
         <v>1481</v>
       </c>
       <c r="E202">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F202" t="s">
         <v>1582</v>
@@ -15255,7 +15255,7 @@
         <v>1481</v>
       </c>
       <c r="E203">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F203" t="s">
         <v>1582</v>
@@ -15290,7 +15290,7 @@
         <v>1481</v>
       </c>
       <c r="E204">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F204" t="s">
         <v>1582</v>
@@ -15325,7 +15325,7 @@
         <v>1481</v>
       </c>
       <c r="E205">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F205" t="s">
         <v>1582</v>
@@ -15360,7 +15360,7 @@
         <v>1482</v>
       </c>
       <c r="E206">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F206" t="s">
         <v>1582</v>
@@ -15395,7 +15395,7 @@
         <v>1482</v>
       </c>
       <c r="E207">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F207" t="s">
         <v>1582</v>
@@ -15430,7 +15430,7 @@
         <v>1482</v>
       </c>
       <c r="E208">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F208" t="s">
         <v>1582</v>
@@ -15465,7 +15465,7 @@
         <v>1482</v>
       </c>
       <c r="E209">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F209" t="s">
         <v>1582</v>
@@ -15500,7 +15500,7 @@
         <v>1482</v>
       </c>
       <c r="E210">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F210" t="s">
         <v>1582</v>
@@ -15535,7 +15535,7 @@
         <v>1482</v>
       </c>
       <c r="E211">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F211" t="s">
         <v>1582</v>
@@ -15570,7 +15570,7 @@
         <v>1482</v>
       </c>
       <c r="E212">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F212" t="s">
         <v>1582</v>
@@ -15605,7 +15605,7 @@
         <v>1483</v>
       </c>
       <c r="E213">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F213" t="s">
         <v>1582</v>
@@ -15640,7 +15640,7 @@
         <v>1483</v>
       </c>
       <c r="E214">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F214" t="s">
         <v>1582</v>
@@ -15675,7 +15675,7 @@
         <v>1483</v>
       </c>
       <c r="E215">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F215" t="s">
         <v>1582</v>
@@ -15710,7 +15710,7 @@
         <v>1483</v>
       </c>
       <c r="E216">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F216" t="s">
         <v>1582</v>
@@ -15745,7 +15745,7 @@
         <v>1484</v>
       </c>
       <c r="E217">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F217" t="s">
         <v>1582</v>
@@ -15780,7 +15780,7 @@
         <v>1484</v>
       </c>
       <c r="E218">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F218" t="s">
         <v>1582</v>
@@ -15815,7 +15815,7 @@
         <v>1484</v>
       </c>
       <c r="E219">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F219" t="s">
         <v>1582</v>
@@ -15850,7 +15850,7 @@
         <v>1485</v>
       </c>
       <c r="E220">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F220" t="s">
         <v>1582</v>
@@ -15885,7 +15885,7 @@
         <v>1485</v>
       </c>
       <c r="E221">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F221" t="s">
         <v>1582</v>
@@ -15920,7 +15920,7 @@
         <v>1486</v>
       </c>
       <c r="E222">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F222" t="s">
         <v>1582</v>
@@ -15955,7 +15955,7 @@
         <v>1486</v>
       </c>
       <c r="E223">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F223" t="s">
         <v>1582</v>
@@ -15990,7 +15990,7 @@
         <v>1487</v>
       </c>
       <c r="E224">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F224" t="s">
         <v>1582</v>
@@ -16025,7 +16025,7 @@
         <v>1487</v>
       </c>
       <c r="E225">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F225" t="s">
         <v>1582</v>
@@ -16060,7 +16060,7 @@
         <v>1488</v>
       </c>
       <c r="E226">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F226" t="s">
         <v>1582</v>
@@ -16095,7 +16095,7 @@
         <v>1488</v>
       </c>
       <c r="E227">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F227" t="s">
         <v>1582</v>
@@ -16130,7 +16130,7 @@
         <v>1489</v>
       </c>
       <c r="E228">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F228" t="s">
         <v>1582</v>
@@ -16165,7 +16165,7 @@
         <v>1489</v>
       </c>
       <c r="E229">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F229" t="s">
         <v>1582</v>
@@ -16200,7 +16200,7 @@
         <v>1490</v>
       </c>
       <c r="E230">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F230" t="s">
         <v>1582</v>
@@ -16235,7 +16235,7 @@
         <v>1491</v>
       </c>
       <c r="E231">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F231" t="s">
         <v>1582</v>
@@ -16270,7 +16270,7 @@
         <v>1491</v>
       </c>
       <c r="E232">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F232" t="s">
         <v>1582</v>
@@ -16305,7 +16305,7 @@
         <v>1491</v>
       </c>
       <c r="E233">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F233" t="s">
         <v>1582</v>
@@ -16340,7 +16340,7 @@
         <v>1492</v>
       </c>
       <c r="E234">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F234" t="s">
         <v>1582</v>
@@ -16375,7 +16375,7 @@
         <v>1492</v>
       </c>
       <c r="E235">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F235" t="s">
         <v>1582</v>
@@ -16410,7 +16410,7 @@
         <v>1493</v>
       </c>
       <c r="E236">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F236" t="s">
         <v>1582</v>
@@ -16445,7 +16445,7 @@
         <v>1494</v>
       </c>
       <c r="E237">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F237" t="s">
         <v>1582</v>
@@ -16480,7 +16480,7 @@
         <v>1494</v>
       </c>
       <c r="E238">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F238" t="s">
         <v>1582</v>
@@ -16515,7 +16515,7 @@
         <v>1494</v>
       </c>
       <c r="E239">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F239" t="s">
         <v>1582</v>
@@ -16550,7 +16550,7 @@
         <v>1495</v>
       </c>
       <c r="E240">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F240" t="s">
         <v>1582</v>
@@ -16585,7 +16585,7 @@
         <v>1495</v>
       </c>
       <c r="E241">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F241" t="s">
         <v>1582</v>
@@ -16620,7 +16620,7 @@
         <v>1496</v>
       </c>
       <c r="E242">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F242" t="s">
         <v>1582</v>
@@ -16655,7 +16655,7 @@
         <v>1496</v>
       </c>
       <c r="E243">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F243" t="s">
         <v>1582</v>
@@ -16690,7 +16690,7 @@
         <v>1496</v>
       </c>
       <c r="E244">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F244" t="s">
         <v>1584</v>
@@ -16725,7 +16725,7 @@
         <v>1496</v>
       </c>
       <c r="E245">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F245" t="s">
         <v>1582</v>
@@ -16760,7 +16760,7 @@
         <v>1497</v>
       </c>
       <c r="E246">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F246" t="s">
         <v>1582</v>
@@ -16795,7 +16795,7 @@
         <v>1497</v>
       </c>
       <c r="E247">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F247" t="s">
         <v>1582</v>
@@ -16833,7 +16833,7 @@
         <v>1497</v>
       </c>
       <c r="E248">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F248" t="s">
         <v>1582</v>
@@ -16868,7 +16868,7 @@
         <v>1497</v>
       </c>
       <c r="E249">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F249" t="s">
         <v>1582</v>
@@ -16903,7 +16903,7 @@
         <v>1497</v>
       </c>
       <c r="E250">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F250" t="s">
         <v>1582</v>
@@ -16938,7 +16938,7 @@
         <v>1497</v>
       </c>
       <c r="E251">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F251" t="s">
         <v>1582</v>
@@ -16973,7 +16973,7 @@
         <v>1498</v>
       </c>
       <c r="E252">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F252" t="s">
         <v>1582</v>
@@ -17008,7 +17008,7 @@
         <v>1498</v>
       </c>
       <c r="E253">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F253" t="s">
         <v>1582</v>
@@ -17043,7 +17043,7 @@
         <v>1498</v>
       </c>
       <c r="E254">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F254" t="s">
         <v>1582</v>
@@ -17078,7 +17078,7 @@
         <v>1499</v>
       </c>
       <c r="E255">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F255" t="s">
         <v>1582</v>
@@ -17113,7 +17113,7 @@
         <v>1499</v>
       </c>
       <c r="E256">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F256" t="s">
         <v>1582</v>
@@ -17148,7 +17148,7 @@
         <v>1499</v>
       </c>
       <c r="E257">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F257" t="s">
         <v>1582</v>
@@ -17183,7 +17183,7 @@
         <v>1499</v>
       </c>
       <c r="E258">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F258" t="s">
         <v>1582</v>
@@ -17218,7 +17218,7 @@
         <v>1500</v>
       </c>
       <c r="E259">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F259" t="s">
         <v>1582</v>
@@ -17253,7 +17253,7 @@
         <v>1500</v>
       </c>
       <c r="E260">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F260" t="s">
         <v>1582</v>
@@ -17288,7 +17288,7 @@
         <v>1500</v>
       </c>
       <c r="E261">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F261" t="s">
         <v>1582</v>
@@ -17323,7 +17323,7 @@
         <v>1500</v>
       </c>
       <c r="E262">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F262" t="s">
         <v>1582</v>
@@ -17358,7 +17358,7 @@
         <v>1500</v>
       </c>
       <c r="E263">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F263" t="s">
         <v>1582</v>
@@ -17393,7 +17393,7 @@
         <v>1501</v>
       </c>
       <c r="E264">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F264" t="s">
         <v>1582</v>
@@ -17428,7 +17428,7 @@
         <v>1501</v>
       </c>
       <c r="E265">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F265" t="s">
         <v>1582</v>
@@ -17463,7 +17463,7 @@
         <v>1501</v>
       </c>
       <c r="E266">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F266" t="s">
         <v>1582</v>
@@ -17498,7 +17498,7 @@
         <v>1501</v>
       </c>
       <c r="E267">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F267" t="s">
         <v>1582</v>
@@ -17533,7 +17533,7 @@
         <v>1501</v>
       </c>
       <c r="E268">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F268" t="s">
         <v>1582</v>
@@ -17568,7 +17568,7 @@
         <v>1501</v>
       </c>
       <c r="E269">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F269" t="s">
         <v>1582</v>
@@ -17603,7 +17603,7 @@
         <v>1502</v>
       </c>
       <c r="E270">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F270" t="s">
         <v>1582</v>
@@ -17638,7 +17638,7 @@
         <v>1503</v>
       </c>
       <c r="E271">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F271" t="s">
         <v>1583</v>
@@ -17673,7 +17673,7 @@
         <v>1503</v>
       </c>
       <c r="E272">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F272" t="s">
         <v>1582</v>
@@ -17708,7 +17708,7 @@
         <v>1503</v>
       </c>
       <c r="E273">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F273" t="s">
         <v>1585</v>
@@ -17743,7 +17743,7 @@
         <v>1503</v>
       </c>
       <c r="E274">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F274" t="s">
         <v>1582</v>
@@ -17778,7 +17778,7 @@
         <v>1503</v>
       </c>
       <c r="E275">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F275" t="s">
         <v>1582</v>
@@ -17813,7 +17813,7 @@
         <v>1503</v>
       </c>
       <c r="E276">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F276" t="s">
         <v>1582</v>
@@ -17848,7 +17848,7 @@
         <v>1504</v>
       </c>
       <c r="E277">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F277" t="s">
         <v>1582</v>
@@ -17883,7 +17883,7 @@
         <v>1504</v>
       </c>
       <c r="E278">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F278" t="s">
         <v>1582</v>
@@ -17918,7 +17918,7 @@
         <v>1504</v>
       </c>
       <c r="E279">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F279" t="s">
         <v>1582</v>
@@ -17953,7 +17953,7 @@
         <v>1504</v>
       </c>
       <c r="E280">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F280" t="s">
         <v>1582</v>
@@ -17988,7 +17988,7 @@
         <v>1505</v>
       </c>
       <c r="E281">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F281" t="s">
         <v>1582</v>
@@ -18023,7 +18023,7 @@
         <v>1505</v>
       </c>
       <c r="E282">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F282" t="s">
         <v>1582</v>
@@ -18058,7 +18058,7 @@
         <v>1506</v>
       </c>
       <c r="E283">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F283" t="s">
         <v>1582</v>
@@ -18096,7 +18096,7 @@
         <v>1506</v>
       </c>
       <c r="E284">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F284" t="s">
         <v>1582</v>
@@ -18131,7 +18131,7 @@
         <v>1507</v>
       </c>
       <c r="E285">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F285" t="s">
         <v>1582</v>
@@ -18166,7 +18166,7 @@
         <v>1507</v>
       </c>
       <c r="E286">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F286" t="s">
         <v>1582</v>
@@ -18201,7 +18201,7 @@
         <v>1507</v>
       </c>
       <c r="E287">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F287" t="s">
         <v>1582</v>
@@ -18236,7 +18236,7 @@
         <v>1507</v>
       </c>
       <c r="E288">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F288" t="s">
         <v>1582</v>
@@ -18274,7 +18274,7 @@
         <v>1507</v>
       </c>
       <c r="E289">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F289" t="s">
         <v>1582</v>
@@ -18309,7 +18309,7 @@
         <v>1507</v>
       </c>
       <c r="E290">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F290" t="s">
         <v>1582</v>
@@ -18344,7 +18344,7 @@
         <v>1508</v>
       </c>
       <c r="E291">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F291" t="s">
         <v>1582</v>
@@ -18379,7 +18379,7 @@
         <v>1508</v>
       </c>
       <c r="E292">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F292" t="s">
         <v>1582</v>
@@ -18414,7 +18414,7 @@
         <v>1509</v>
       </c>
       <c r="E293">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F293" t="s">
         <v>1582</v>
@@ -18449,7 +18449,7 @@
         <v>1509</v>
       </c>
       <c r="E294">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F294" t="s">
         <v>1582</v>
@@ -18484,7 +18484,7 @@
         <v>1510</v>
       </c>
       <c r="E295">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F295" t="s">
         <v>1582</v>
@@ -18519,7 +18519,7 @@
         <v>1510</v>
       </c>
       <c r="E296">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F296" t="s">
         <v>1582</v>
@@ -18554,7 +18554,7 @@
         <v>1510</v>
       </c>
       <c r="E297">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F297" t="s">
         <v>1582</v>
@@ -18589,7 +18589,7 @@
         <v>1510</v>
       </c>
       <c r="E298">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F298" t="s">
         <v>1582</v>
@@ -18624,7 +18624,7 @@
         <v>1511</v>
       </c>
       <c r="E299">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F299" t="s">
         <v>1582</v>
@@ -18659,7 +18659,7 @@
         <v>1511</v>
       </c>
       <c r="E300">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F300" t="s">
         <v>1582</v>
@@ -18694,7 +18694,7 @@
         <v>1511</v>
       </c>
       <c r="E301">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F301" t="s">
         <v>1582</v>
@@ -18729,7 +18729,7 @@
         <v>1511</v>
       </c>
       <c r="E302">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F302" t="s">
         <v>1582</v>
@@ -18764,7 +18764,7 @@
         <v>1512</v>
       </c>
       <c r="E303">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F303" t="s">
         <v>1582</v>
@@ -18799,7 +18799,7 @@
         <v>1512</v>
       </c>
       <c r="E304">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F304" t="s">
         <v>1582</v>
@@ -18834,7 +18834,7 @@
         <v>1513</v>
       </c>
       <c r="E305">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F305" t="s">
         <v>1582</v>
@@ -18869,7 +18869,7 @@
         <v>1513</v>
       </c>
       <c r="E306">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F306" t="s">
         <v>1582</v>
@@ -18904,7 +18904,7 @@
         <v>1513</v>
       </c>
       <c r="E307">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F307" t="s">
         <v>1582</v>
@@ -18939,7 +18939,7 @@
         <v>1513</v>
       </c>
       <c r="E308">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F308" t="s">
         <v>1582</v>
@@ -18974,7 +18974,7 @@
         <v>1513</v>
       </c>
       <c r="E309">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F309" t="s">
         <v>1582</v>
@@ -19009,7 +19009,7 @@
         <v>1514</v>
       </c>
       <c r="E310">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F310" t="s">
         <v>1582</v>
@@ -19044,7 +19044,7 @@
         <v>1514</v>
       </c>
       <c r="E311">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F311" t="s">
         <v>1582</v>
@@ -19079,7 +19079,7 @@
         <v>1514</v>
       </c>
       <c r="E312">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F312" t="s">
         <v>1582</v>
@@ -19114,7 +19114,7 @@
         <v>1515</v>
       </c>
       <c r="E313">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F313" t="s">
         <v>1582</v>
@@ -19149,7 +19149,7 @@
         <v>1515</v>
       </c>
       <c r="E314">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F314" t="s">
         <v>1582</v>
@@ -19184,7 +19184,7 @@
         <v>1516</v>
       </c>
       <c r="E315">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F315" t="s">
         <v>1582</v>
@@ -19219,7 +19219,7 @@
         <v>1516</v>
       </c>
       <c r="E316">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F316" t="s">
         <v>1582</v>
@@ -19254,7 +19254,7 @@
         <v>1516</v>
       </c>
       <c r="E317">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F317" t="s">
         <v>1582</v>
@@ -19289,7 +19289,7 @@
         <v>1516</v>
       </c>
       <c r="E318">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F318" t="s">
         <v>1582</v>
@@ -19324,7 +19324,7 @@
         <v>1516</v>
       </c>
       <c r="E319">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F319" t="s">
         <v>1582</v>
@@ -19359,7 +19359,7 @@
         <v>1516</v>
       </c>
       <c r="E320">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F320" t="s">
         <v>1582</v>
@@ -19394,7 +19394,7 @@
         <v>1516</v>
       </c>
       <c r="E321">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F321" t="s">
         <v>1582</v>
@@ -19429,7 +19429,7 @@
         <v>1516</v>
       </c>
       <c r="E322">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F322" t="s">
         <v>1582</v>
@@ -19464,7 +19464,7 @@
         <v>1517</v>
       </c>
       <c r="E323">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F323" t="s">
         <v>1582</v>
@@ -19499,7 +19499,7 @@
         <v>1517</v>
       </c>
       <c r="E324">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F324" t="s">
         <v>1582</v>
@@ -19534,7 +19534,7 @@
         <v>1517</v>
       </c>
       <c r="E325">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F325" t="s">
         <v>1582</v>
@@ -19569,7 +19569,7 @@
         <v>1518</v>
       </c>
       <c r="E326">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F326" t="s">
         <v>1582</v>
@@ -19604,7 +19604,7 @@
         <v>1519</v>
       </c>
       <c r="E327">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F327" t="s">
         <v>1582</v>
@@ -19639,7 +19639,7 @@
         <v>1520</v>
       </c>
       <c r="E328">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F328" t="s">
         <v>1584</v>
@@ -19674,7 +19674,7 @@
         <v>1520</v>
       </c>
       <c r="E329">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F329" t="s">
         <v>1582</v>
@@ -19709,7 +19709,7 @@
         <v>1520</v>
       </c>
       <c r="E330">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F330" t="s">
         <v>1582</v>
@@ -19744,7 +19744,7 @@
         <v>1520</v>
       </c>
       <c r="E331">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F331" t="s">
         <v>1582</v>
@@ -19779,7 +19779,7 @@
         <v>1520</v>
       </c>
       <c r="E332">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F332" t="s">
         <v>1582</v>
@@ -19814,7 +19814,7 @@
         <v>1520</v>
       </c>
       <c r="E333">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F333" t="s">
         <v>1582</v>
@@ -19849,7 +19849,7 @@
         <v>1521</v>
       </c>
       <c r="E334">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F334" t="s">
         <v>1582</v>
@@ -19884,7 +19884,7 @@
         <v>1521</v>
       </c>
       <c r="E335">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F335" t="s">
         <v>1582</v>
@@ -19919,7 +19919,7 @@
         <v>1522</v>
       </c>
       <c r="E336">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F336" t="s">
         <v>1582</v>
@@ -19954,7 +19954,7 @@
         <v>1522</v>
       </c>
       <c r="E337">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F337" t="s">
         <v>1582</v>
@@ -19989,7 +19989,7 @@
         <v>1522</v>
       </c>
       <c r="E338">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F338" t="s">
         <v>1582</v>
@@ -20024,7 +20024,7 @@
         <v>1523</v>
       </c>
       <c r="E339">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F339" t="s">
         <v>1582</v>
@@ -20059,7 +20059,7 @@
         <v>1524</v>
       </c>
       <c r="E340">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F340" t="s">
         <v>1582</v>
@@ -20094,7 +20094,7 @@
         <v>1525</v>
       </c>
       <c r="E341">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F341" t="s">
         <v>1582</v>
@@ -20129,7 +20129,7 @@
         <v>1525</v>
       </c>
       <c r="E342">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F342" t="s">
         <v>1582</v>
@@ -20164,7 +20164,7 @@
         <v>1526</v>
       </c>
       <c r="E343">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F343" t="s">
         <v>1582</v>
@@ -20199,7 +20199,7 @@
         <v>1526</v>
       </c>
       <c r="E344">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F344" t="s">
         <v>1582</v>
@@ -20234,7 +20234,7 @@
         <v>1526</v>
       </c>
       <c r="E345">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F345" t="s">
         <v>1582</v>
@@ -20269,7 +20269,7 @@
         <v>1527</v>
       </c>
       <c r="E346">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F346" t="s">
         <v>1582</v>
@@ -20304,7 +20304,7 @@
         <v>1527</v>
       </c>
       <c r="E347">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F347" t="s">
         <v>1582</v>
@@ -20339,7 +20339,7 @@
         <v>1527</v>
       </c>
       <c r="E348">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F348" t="s">
         <v>1582</v>
@@ -20374,7 +20374,7 @@
         <v>1527</v>
       </c>
       <c r="E349">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F349" t="s">
         <v>1582</v>
@@ -20409,7 +20409,7 @@
         <v>1527</v>
       </c>
       <c r="E350">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F350" t="s">
         <v>1582</v>
@@ -20444,7 +20444,7 @@
         <v>1527</v>
       </c>
       <c r="E351">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F351" t="s">
         <v>1582</v>
@@ -20479,7 +20479,7 @@
         <v>1527</v>
       </c>
       <c r="E352">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F352" t="s">
         <v>1582</v>
@@ -20514,7 +20514,7 @@
         <v>1527</v>
       </c>
       <c r="E353">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F353" t="s">
         <v>1582</v>
@@ -20549,7 +20549,7 @@
         <v>1527</v>
       </c>
       <c r="E354">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F354" t="s">
         <v>1582</v>
@@ -20584,7 +20584,7 @@
         <v>1528</v>
       </c>
       <c r="E355">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F355" t="s">
         <v>1582</v>
@@ -20619,7 +20619,7 @@
         <v>1528</v>
       </c>
       <c r="E356">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F356" t="s">
         <v>1582</v>
@@ -20654,7 +20654,7 @@
         <v>1528</v>
       </c>
       <c r="E357">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F357" t="s">
         <v>1582</v>
@@ -20689,7 +20689,7 @@
         <v>1528</v>
       </c>
       <c r="E358">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F358" t="s">
         <v>1582</v>
@@ -20724,7 +20724,7 @@
         <v>1529</v>
       </c>
       <c r="E359">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F359" t="s">
         <v>1582</v>
@@ -20759,7 +20759,7 @@
         <v>1530</v>
       </c>
       <c r="E360">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F360" t="s">
         <v>1582</v>
@@ -20794,7 +20794,7 @@
         <v>1530</v>
       </c>
       <c r="E361">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F361" t="s">
         <v>1582</v>
@@ -20829,7 +20829,7 @@
         <v>1530</v>
       </c>
       <c r="E362">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F362" t="s">
         <v>1582</v>
@@ -20864,7 +20864,7 @@
         <v>1530</v>
       </c>
       <c r="E363">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F363" t="s">
         <v>1582</v>
@@ -20899,7 +20899,7 @@
         <v>1530</v>
       </c>
       <c r="E364">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F364" t="s">
         <v>1586</v>
@@ -20937,7 +20937,7 @@
         <v>1530</v>
       </c>
       <c r="E365">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F365" t="s">
         <v>1582</v>
@@ -20972,7 +20972,7 @@
         <v>1530</v>
       </c>
       <c r="E366">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F366" t="s">
         <v>1582</v>
@@ -21007,7 +21007,7 @@
         <v>1531</v>
       </c>
       <c r="E367">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F367" t="s">
         <v>1582</v>
@@ -21042,7 +21042,7 @@
         <v>1531</v>
       </c>
       <c r="E368">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F368" t="s">
         <v>1582</v>
@@ -21077,7 +21077,7 @@
         <v>1531</v>
       </c>
       <c r="E369">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F369" t="s">
         <v>1582</v>
@@ -21112,7 +21112,7 @@
         <v>1531</v>
       </c>
       <c r="E370">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F370" t="s">
         <v>1582</v>
@@ -21150,7 +21150,7 @@
         <v>1531</v>
       </c>
       <c r="E371">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F371" t="s">
         <v>1582</v>
@@ -21185,7 +21185,7 @@
         <v>1531</v>
       </c>
       <c r="E372">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F372" t="s">
         <v>1582</v>
@@ -21220,7 +21220,7 @@
         <v>1531</v>
       </c>
       <c r="E373">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F373" t="s">
         <v>1582</v>
@@ -21255,7 +21255,7 @@
         <v>1531</v>
       </c>
       <c r="E374">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F374" t="s">
         <v>1582</v>
@@ -21290,7 +21290,7 @@
         <v>1531</v>
       </c>
       <c r="E375">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F375" t="s">
         <v>1582</v>
@@ -21325,7 +21325,7 @@
         <v>1532</v>
       </c>
       <c r="E376">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F376" t="s">
         <v>1583</v>
@@ -21360,7 +21360,7 @@
         <v>1533</v>
       </c>
       <c r="E377">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F377" t="s">
         <v>1586</v>
@@ -21395,7 +21395,7 @@
         <v>1534</v>
       </c>
       <c r="E378">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F378" t="s">
         <v>1582</v>
@@ -21430,7 +21430,7 @@
         <v>1535</v>
       </c>
       <c r="E379">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F379" t="s">
         <v>1582</v>
@@ -21465,7 +21465,7 @@
         <v>1535</v>
       </c>
       <c r="E380">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F380" t="s">
         <v>1582</v>
@@ -21500,7 +21500,7 @@
         <v>1536</v>
       </c>
       <c r="E381">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F381" t="s">
         <v>1582</v>
@@ -21535,7 +21535,7 @@
         <v>1537</v>
       </c>
       <c r="E382">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F382" t="s">
         <v>1585</v>
@@ -21570,7 +21570,7 @@
         <v>1537</v>
       </c>
       <c r="E383">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F383" t="s">
         <v>1582</v>
@@ -21605,7 +21605,7 @@
         <v>1537</v>
       </c>
       <c r="E384">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F384" t="s">
         <v>1582</v>
@@ -21640,7 +21640,7 @@
         <v>1537</v>
       </c>
       <c r="E385">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F385" t="s">
         <v>1582</v>
@@ -21675,7 +21675,7 @@
         <v>1537</v>
       </c>
       <c r="E386">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F386" t="s">
         <v>1582</v>
@@ -21710,7 +21710,7 @@
         <v>1537</v>
       </c>
       <c r="E387">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F387" t="s">
         <v>1582</v>
@@ -21745,7 +21745,7 @@
         <v>1538</v>
       </c>
       <c r="E388">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F388" t="s">
         <v>1582</v>
@@ -21780,7 +21780,7 @@
         <v>1538</v>
       </c>
       <c r="E389">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F389" t="s">
         <v>1582</v>
@@ -21815,7 +21815,7 @@
         <v>1538</v>
       </c>
       <c r="E390">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F390" t="s">
         <v>1582</v>
@@ -21850,7 +21850,7 @@
         <v>1539</v>
       </c>
       <c r="E391">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F391" t="s">
         <v>1582</v>
@@ -21885,7 +21885,7 @@
         <v>1539</v>
       </c>
       <c r="E392">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F392" t="s">
         <v>1582</v>
@@ -21920,7 +21920,7 @@
         <v>1539</v>
       </c>
       <c r="E393">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F393" t="s">
         <v>1582</v>
@@ -21958,7 +21958,7 @@
         <v>1539</v>
       </c>
       <c r="E394">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F394" t="s">
         <v>1582</v>
@@ -21993,7 +21993,7 @@
         <v>1540</v>
       </c>
       <c r="E395">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F395" t="s">
         <v>1582</v>
@@ -22028,7 +22028,7 @@
         <v>1540</v>
       </c>
       <c r="E396">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F396" t="s">
         <v>1582</v>
@@ -22063,7 +22063,7 @@
         <v>1540</v>
       </c>
       <c r="E397">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F397" t="s">
         <v>1582</v>
@@ -22098,7 +22098,7 @@
         <v>1540</v>
       </c>
       <c r="E398">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F398" t="s">
         <v>1582</v>
@@ -22133,7 +22133,7 @@
         <v>1540</v>
       </c>
       <c r="E399">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F399" t="s">
         <v>1582</v>
@@ -22168,7 +22168,7 @@
         <v>1541</v>
       </c>
       <c r="E400">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F400" t="s">
         <v>1582</v>
@@ -22203,7 +22203,7 @@
         <v>1541</v>
       </c>
       <c r="E401">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F401" t="s">
         <v>1582</v>
@@ -22238,7 +22238,7 @@
         <v>1542</v>
       </c>
       <c r="E402">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F402" t="s">
         <v>1582</v>
@@ -22273,7 +22273,7 @@
         <v>1542</v>
       </c>
       <c r="E403">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F403" t="s">
         <v>1582</v>
@@ -22308,7 +22308,7 @@
         <v>1542</v>
       </c>
       <c r="E404">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F404" t="s">
         <v>1582</v>
@@ -22343,7 +22343,7 @@
         <v>1542</v>
       </c>
       <c r="E405">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F405" t="s">
         <v>1582</v>
@@ -22378,7 +22378,7 @@
         <v>1542</v>
       </c>
       <c r="E406">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F406" t="s">
         <v>1582</v>
@@ -22413,7 +22413,7 @@
         <v>1542</v>
       </c>
       <c r="E407">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F407" t="s">
         <v>1582</v>
@@ -22448,7 +22448,7 @@
         <v>1542</v>
       </c>
       <c r="E408">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F408" t="s">
         <v>1582</v>
@@ -22483,7 +22483,7 @@
         <v>1542</v>
       </c>
       <c r="E409">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F409" t="s">
         <v>1582</v>
@@ -22518,7 +22518,7 @@
         <v>1542</v>
       </c>
       <c r="E410">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F410" t="s">
         <v>1582</v>
@@ -22553,7 +22553,7 @@
         <v>1542</v>
       </c>
       <c r="E411">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F411" t="s">
         <v>1582</v>
@@ -22588,7 +22588,7 @@
         <v>1543</v>
       </c>
       <c r="E412">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F412" t="s">
         <v>1582</v>
@@ -22623,7 +22623,7 @@
         <v>1543</v>
       </c>
       <c r="E413">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F413" t="s">
         <v>1582</v>
@@ -22658,7 +22658,7 @@
         <v>1543</v>
       </c>
       <c r="E414">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F414" t="s">
         <v>1583</v>
@@ -22693,7 +22693,7 @@
         <v>1544</v>
       </c>
       <c r="E415">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F415" t="s">
         <v>1582</v>
@@ -22728,7 +22728,7 @@
         <v>1544</v>
       </c>
       <c r="E416">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F416" t="s">
         <v>1582</v>
@@ -22763,7 +22763,7 @@
         <v>1544</v>
       </c>
       <c r="E417">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F417" t="s">
         <v>1582</v>
@@ -22798,7 +22798,7 @@
         <v>1544</v>
       </c>
       <c r="E418">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F418" t="s">
         <v>1582</v>
@@ -22833,7 +22833,7 @@
         <v>1544</v>
       </c>
       <c r="E419">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F419" t="s">
         <v>1582</v>
@@ -22868,7 +22868,7 @@
         <v>1544</v>
       </c>
       <c r="E420">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F420" t="s">
         <v>1582</v>
@@ -22903,7 +22903,7 @@
         <v>1544</v>
       </c>
       <c r="E421">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F421" t="s">
         <v>1585</v>
@@ -22938,7 +22938,7 @@
         <v>1545</v>
       </c>
       <c r="E422">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F422" t="s">
         <v>1582</v>
@@ -22973,7 +22973,7 @@
         <v>1545</v>
       </c>
       <c r="E423">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F423" t="s">
         <v>1582</v>
@@ -23008,7 +23008,7 @@
         <v>1545</v>
       </c>
       <c r="E424">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F424" t="s">
         <v>1582</v>
@@ -23043,7 +23043,7 @@
         <v>1545</v>
       </c>
       <c r="E425">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F425" t="s">
         <v>1582</v>
@@ -23078,7 +23078,7 @@
         <v>1546</v>
       </c>
       <c r="E426">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F426" t="s">
         <v>1582</v>
@@ -23113,7 +23113,7 @@
         <v>1546</v>
       </c>
       <c r="E427">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F427" t="s">
         <v>1585</v>
@@ -23148,7 +23148,7 @@
         <v>1546</v>
       </c>
       <c r="E428">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F428" t="s">
         <v>1582</v>
@@ -23183,7 +23183,7 @@
         <v>1546</v>
       </c>
       <c r="E429">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F429" t="s">
         <v>1582</v>
@@ -23218,7 +23218,7 @@
         <v>1546</v>
       </c>
       <c r="E430">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F430" t="s">
         <v>1582</v>
@@ -23253,7 +23253,7 @@
         <v>1546</v>
       </c>
       <c r="E431">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F431" t="s">
         <v>1582</v>
@@ -23288,7 +23288,7 @@
         <v>1546</v>
       </c>
       <c r="E432">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F432" t="s">
         <v>1586</v>
@@ -23323,7 +23323,7 @@
         <v>1546</v>
       </c>
       <c r="E433">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F433" t="s">
         <v>1582</v>
@@ -23358,7 +23358,7 @@
         <v>1546</v>
       </c>
       <c r="E434">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F434" t="s">
         <v>1582</v>
@@ -23393,7 +23393,7 @@
         <v>1547</v>
       </c>
       <c r="E435">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F435" t="s">
         <v>1582</v>
@@ -23428,7 +23428,7 @@
         <v>1547</v>
       </c>
       <c r="E436">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F436" t="s">
         <v>1582</v>
@@ -23463,7 +23463,7 @@
         <v>1547</v>
       </c>
       <c r="E437">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F437" t="s">
         <v>1582</v>
@@ -23498,7 +23498,7 @@
         <v>1547</v>
       </c>
       <c r="E438">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F438" t="s">
         <v>1582</v>
@@ -23533,7 +23533,7 @@
         <v>1547</v>
       </c>
       <c r="E439">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F439" t="s">
         <v>1584</v>
@@ -23568,7 +23568,7 @@
         <v>1547</v>
       </c>
       <c r="E440">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F440" t="s">
         <v>1582</v>
@@ -23603,7 +23603,7 @@
         <v>1547</v>
       </c>
       <c r="E441">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F441" t="s">
         <v>1582</v>
@@ -23638,7 +23638,7 @@
         <v>1548</v>
       </c>
       <c r="E442">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F442" t="s">
         <v>1582</v>
@@ -23673,7 +23673,7 @@
         <v>1548</v>
       </c>
       <c r="E443">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F443" t="s">
         <v>1582</v>
@@ -23708,7 +23708,7 @@
         <v>1548</v>
       </c>
       <c r="E444">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F444" t="s">
         <v>1582</v>
@@ -23743,7 +23743,7 @@
         <v>1548</v>
       </c>
       <c r="E445">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F445" t="s">
         <v>1582</v>
@@ -23778,7 +23778,7 @@
         <v>1548</v>
       </c>
       <c r="E446">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F446" t="s">
         <v>1582</v>
@@ -23813,7 +23813,7 @@
         <v>1549</v>
       </c>
       <c r="E447">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F447" t="s">
         <v>1582</v>
@@ -23848,7 +23848,7 @@
         <v>1549</v>
       </c>
       <c r="E448">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F448" t="s">
         <v>1582</v>
@@ -23883,7 +23883,7 @@
         <v>1549</v>
       </c>
       <c r="E449">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F449" t="s">
         <v>1582</v>
@@ -23918,7 +23918,7 @@
         <v>1549</v>
       </c>
       <c r="E450">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F450" t="s">
         <v>1582</v>
@@ -23953,7 +23953,7 @@
         <v>1549</v>
       </c>
       <c r="E451">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F451" t="s">
         <v>1582</v>
@@ -23991,7 +23991,7 @@
         <v>1550</v>
       </c>
       <c r="E452">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F452" t="s">
         <v>1582</v>
@@ -24026,7 +24026,7 @@
         <v>1550</v>
       </c>
       <c r="E453">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F453" t="s">
         <v>1582</v>
@@ -24061,7 +24061,7 @@
         <v>1550</v>
       </c>
       <c r="E454">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F454" t="s">
         <v>1582</v>
@@ -24096,7 +24096,7 @@
         <v>1550</v>
       </c>
       <c r="E455">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F455" t="s">
         <v>1582</v>
@@ -24131,7 +24131,7 @@
         <v>1550</v>
       </c>
       <c r="E456">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F456" t="s">
         <v>1582</v>
@@ -24166,7 +24166,7 @@
         <v>1550</v>
       </c>
       <c r="E457">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F457" t="s">
         <v>1582</v>
@@ -24201,7 +24201,7 @@
         <v>1551</v>
       </c>
       <c r="E458">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F458" t="s">
         <v>1582</v>
@@ -24236,7 +24236,7 @@
         <v>1551</v>
       </c>
       <c r="E459">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F459" t="s">
         <v>1582</v>
@@ -24271,7 +24271,7 @@
         <v>1551</v>
       </c>
       <c r="E460">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F460" t="s">
         <v>1582</v>
@@ -24306,7 +24306,7 @@
         <v>1552</v>
       </c>
       <c r="E461">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F461" t="s">
         <v>1582</v>
@@ -24341,7 +24341,7 @@
         <v>1553</v>
       </c>
       <c r="E462">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F462" t="s">
         <v>1582</v>
@@ -24376,7 +24376,7 @@
         <v>1553</v>
       </c>
       <c r="E463">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F463" t="s">
         <v>1582</v>
@@ -24411,7 +24411,7 @@
         <v>1553</v>
       </c>
       <c r="E464">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F464" t="s">
         <v>1584</v>
@@ -24449,7 +24449,7 @@
         <v>1553</v>
       </c>
       <c r="E465">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F465" t="s">
         <v>1582</v>
@@ -24484,7 +24484,7 @@
         <v>1553</v>
       </c>
       <c r="E466">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F466" t="s">
         <v>1582</v>
@@ -24519,7 +24519,7 @@
         <v>1554</v>
       </c>
       <c r="E467">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F467" t="s">
         <v>1582</v>
@@ -24554,7 +24554,7 @@
         <v>1554</v>
       </c>
       <c r="E468">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F468" t="s">
         <v>1582</v>
@@ -24589,7 +24589,7 @@
         <v>1554</v>
       </c>
       <c r="E469">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F469" t="s">
         <v>1582</v>
@@ -24624,7 +24624,7 @@
         <v>1554</v>
       </c>
       <c r="E470">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F470" t="s">
         <v>1582</v>
@@ -24659,7 +24659,7 @@
         <v>1555</v>
       </c>
       <c r="E471">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F471" t="s">
         <v>1582</v>
@@ -24694,7 +24694,7 @@
         <v>1555</v>
       </c>
       <c r="E472">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F472" t="s">
         <v>1582</v>
@@ -24729,7 +24729,7 @@
         <v>1555</v>
       </c>
       <c r="E473">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F473" t="s">
         <v>1582</v>
@@ -24764,7 +24764,7 @@
         <v>1555</v>
       </c>
       <c r="E474">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F474" t="s">
         <v>1582</v>
@@ -24799,7 +24799,7 @@
         <v>1555</v>
       </c>
       <c r="E475">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F475" t="s">
         <v>1582</v>
@@ -24834,7 +24834,7 @@
         <v>1555</v>
       </c>
       <c r="E476">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F476" t="s">
         <v>1582</v>
@@ -24869,7 +24869,7 @@
         <v>1555</v>
       </c>
       <c r="E477">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F477" t="s">
         <v>1582</v>
@@ -24904,7 +24904,7 @@
         <v>1555</v>
       </c>
       <c r="E478">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F478" t="s">
         <v>1582</v>
@@ -24939,7 +24939,7 @@
         <v>1556</v>
       </c>
       <c r="E479">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F479" t="s">
         <v>1582</v>
@@ -24974,7 +24974,7 @@
         <v>1556</v>
       </c>
       <c r="E480">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F480" t="s">
         <v>1582</v>
@@ -25009,7 +25009,7 @@
         <v>1557</v>
       </c>
       <c r="E481">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F481" t="s">
         <v>1582</v>
@@ -25044,7 +25044,7 @@
         <v>1557</v>
       </c>
       <c r="E482">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F482" t="s">
         <v>1582</v>
@@ -25079,7 +25079,7 @@
         <v>1557</v>
       </c>
       <c r="E483">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F483" t="s">
         <v>1582</v>
@@ -25114,7 +25114,7 @@
         <v>1557</v>
       </c>
       <c r="E484">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F484" t="s">
         <v>1586</v>
@@ -25152,7 +25152,7 @@
         <v>1557</v>
       </c>
       <c r="E485">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F485" t="s">
         <v>1582</v>
@@ -25187,7 +25187,7 @@
         <v>1557</v>
       </c>
       <c r="E486">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F486" t="s">
         <v>1586</v>
@@ -25222,7 +25222,7 @@
         <v>1558</v>
       </c>
       <c r="E487">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F487" t="s">
         <v>1582</v>
@@ -25257,7 +25257,7 @@
         <v>1559</v>
       </c>
       <c r="E488">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F488" t="s">
         <v>1582</v>
@@ -25292,7 +25292,7 @@
         <v>1559</v>
       </c>
       <c r="E489">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F489" t="s">
         <v>1582</v>
@@ -25327,7 +25327,7 @@
         <v>1559</v>
       </c>
       <c r="E490">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F490" t="s">
         <v>1582</v>
@@ -25362,7 +25362,7 @@
         <v>1559</v>
       </c>
       <c r="E491">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F491" t="s">
         <v>1582</v>
@@ -25397,7 +25397,7 @@
         <v>1560</v>
       </c>
       <c r="E492">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F492" t="s">
         <v>1582</v>
@@ -25432,7 +25432,7 @@
         <v>1560</v>
       </c>
       <c r="E493">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F493" t="s">
         <v>1586</v>
@@ -25467,7 +25467,7 @@
         <v>1560</v>
       </c>
       <c r="E494">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F494" t="s">
         <v>1582</v>
@@ -25502,7 +25502,7 @@
         <v>1560</v>
       </c>
       <c r="E495">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F495" t="s">
         <v>1582</v>
@@ -25537,7 +25537,7 @@
         <v>1560</v>
       </c>
       <c r="E496">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F496" t="s">
         <v>1582</v>
@@ -25572,7 +25572,7 @@
         <v>1561</v>
       </c>
       <c r="E497">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F497" t="s">
         <v>1582</v>
@@ -25607,7 +25607,7 @@
         <v>1561</v>
       </c>
       <c r="E498">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F498" t="s">
         <v>1584</v>
@@ -25642,7 +25642,7 @@
         <v>1561</v>
       </c>
       <c r="E499">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F499" t="s">
         <v>1582</v>
@@ -25677,7 +25677,7 @@
         <v>1561</v>
       </c>
       <c r="E500">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F500" t="s">
         <v>1582</v>
@@ -25712,7 +25712,7 @@
         <v>1562</v>
       </c>
       <c r="E501">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F501" t="s">
         <v>1582</v>
@@ -25747,7 +25747,7 @@
         <v>1562</v>
       </c>
       <c r="E502">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F502" t="s">
         <v>1582</v>
@@ -25782,7 +25782,7 @@
         <v>1562</v>
       </c>
       <c r="E503">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F503" t="s">
         <v>1582</v>
@@ -25817,7 +25817,7 @@
         <v>1562</v>
       </c>
       <c r="E504">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F504" t="s">
         <v>1582</v>
@@ -25852,7 +25852,7 @@
         <v>1562</v>
       </c>
       <c r="E505">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F505" t="s">
         <v>1582</v>
@@ -25887,7 +25887,7 @@
         <v>1562</v>
       </c>
       <c r="E506">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F506" t="s">
         <v>1582</v>
@@ -25922,7 +25922,7 @@
         <v>1563</v>
       </c>
       <c r="E507">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F507" t="s">
         <v>1582</v>
@@ -25957,7 +25957,7 @@
         <v>1563</v>
       </c>
       <c r="E508">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F508" t="s">
         <v>1582</v>
@@ -25992,7 +25992,7 @@
         <v>1563</v>
       </c>
       <c r="E509">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F509" t="s">
         <v>1582</v>
@@ -26027,7 +26027,7 @@
         <v>1563</v>
       </c>
       <c r="E510">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F510" t="s">
         <v>1582</v>
@@ -26062,7 +26062,7 @@
         <v>1563</v>
       </c>
       <c r="E511">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F511" t="s">
         <v>1582</v>
@@ -26097,7 +26097,7 @@
         <v>1563</v>
       </c>
       <c r="E512">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F512" t="s">
         <v>1582</v>
@@ -26132,7 +26132,7 @@
         <v>1563</v>
       </c>
       <c r="E513">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F513" t="s">
         <v>1582</v>
@@ -26167,7 +26167,7 @@
         <v>1563</v>
       </c>
       <c r="E514">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F514" t="s">
         <v>1582</v>
@@ -26202,7 +26202,7 @@
         <v>1563</v>
       </c>
       <c r="E515">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F515" t="s">
         <v>1582</v>
@@ -26237,7 +26237,7 @@
         <v>1563</v>
       </c>
       <c r="E516">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F516" t="s">
         <v>1582</v>
@@ -26272,7 +26272,7 @@
         <v>1563</v>
       </c>
       <c r="E517">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F517" t="s">
         <v>1582</v>
@@ -26307,7 +26307,7 @@
         <v>1563</v>
       </c>
       <c r="E518">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F518" t="s">
         <v>1582</v>
@@ -26342,7 +26342,7 @@
         <v>1563</v>
       </c>
       <c r="E519">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F519" t="s">
         <v>1582</v>
@@ -26377,7 +26377,7 @@
         <v>1563</v>
       </c>
       <c r="E520">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F520" t="s">
         <v>1582</v>
@@ -26412,7 +26412,7 @@
         <v>1563</v>
       </c>
       <c r="E521">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F521" t="s">
         <v>1582</v>
@@ -26447,7 +26447,7 @@
         <v>1563</v>
       </c>
       <c r="E522">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F522" t="s">
         <v>1582</v>
@@ -26482,7 +26482,7 @@
         <v>1563</v>
       </c>
       <c r="E523">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F523" t="s">
         <v>1582</v>
@@ -26517,7 +26517,7 @@
         <v>1563</v>
       </c>
       <c r="E524">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F524" t="s">
         <v>1582</v>
@@ -26552,7 +26552,7 @@
         <v>1563</v>
       </c>
       <c r="E525">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F525" t="s">
         <v>1582</v>
@@ -26587,7 +26587,7 @@
         <v>1563</v>
       </c>
       <c r="E526">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F526" t="s">
         <v>1582</v>
@@ -26622,7 +26622,7 @@
         <v>1563</v>
       </c>
       <c r="E527">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F527" t="s">
         <v>1582</v>
@@ -26657,7 +26657,7 @@
         <v>1563</v>
       </c>
       <c r="E528">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F528" t="s">
         <v>1582</v>
@@ -26692,7 +26692,7 @@
         <v>1563</v>
       </c>
       <c r="E529">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F529" t="s">
         <v>1582</v>
@@ -26727,7 +26727,7 @@
         <v>1563</v>
       </c>
       <c r="E530">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F530" t="s">
         <v>1582</v>
@@ -26762,7 +26762,7 @@
         <v>1563</v>
       </c>
       <c r="E531">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F531" t="s">
         <v>1582</v>
@@ -26797,7 +26797,7 @@
         <v>1563</v>
       </c>
       <c r="E532">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F532" t="s">
         <v>1582</v>
@@ -26832,7 +26832,7 @@
         <v>1564</v>
       </c>
       <c r="E533">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F533" t="s">
         <v>1582</v>
@@ -26867,7 +26867,7 @@
         <v>1564</v>
       </c>
       <c r="E534">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F534" t="s">
         <v>1582</v>
@@ -26902,7 +26902,7 @@
         <v>1564</v>
       </c>
       <c r="E535">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F535" t="s">
         <v>1582</v>
@@ -26937,7 +26937,7 @@
         <v>1564</v>
       </c>
       <c r="E536">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F536" t="s">
         <v>1582</v>
@@ -26972,7 +26972,7 @@
         <v>1564</v>
       </c>
       <c r="E537">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F537" t="s">
         <v>1582</v>
@@ -27007,7 +27007,7 @@
         <v>1564</v>
       </c>
       <c r="E538">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F538" t="s">
         <v>1582</v>
@@ -27042,7 +27042,7 @@
         <v>1564</v>
       </c>
       <c r="E539">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F539" t="s">
         <v>1586</v>
@@ -27077,7 +27077,7 @@
         <v>1564</v>
       </c>
       <c r="E540">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F540" t="s">
         <v>1582</v>
@@ -27112,7 +27112,7 @@
         <v>1565</v>
       </c>
       <c r="E541">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F541" t="s">
         <v>1582</v>
@@ -27147,7 +27147,7 @@
         <v>1566</v>
       </c>
       <c r="E542">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F542" t="s">
         <v>1582</v>
@@ -27182,7 +27182,7 @@
         <v>1566</v>
       </c>
       <c r="E543">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F543" t="s">
         <v>1584</v>
@@ -27220,7 +27220,7 @@
         <v>1567</v>
       </c>
       <c r="E544">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F544" t="s">
         <v>1584</v>
@@ -27258,7 +27258,7 @@
         <v>1567</v>
       </c>
       <c r="E545">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F545" t="s">
         <v>1582</v>
@@ -27293,7 +27293,7 @@
         <v>1567</v>
       </c>
       <c r="E546">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F546" t="s">
         <v>1584</v>
@@ -27331,7 +27331,7 @@
         <v>1567</v>
       </c>
       <c r="E547">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F547" t="s">
         <v>1582</v>
@@ -27366,7 +27366,7 @@
         <v>1567</v>
       </c>
       <c r="E548">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F548" t="s">
         <v>1582</v>
@@ -27401,7 +27401,7 @@
         <v>1567</v>
       </c>
       <c r="E549">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F549" t="s">
         <v>1582</v>
@@ -27436,7 +27436,7 @@
         <v>1567</v>
       </c>
       <c r="E550">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F550" t="s">
         <v>1582</v>
@@ -27471,7 +27471,7 @@
         <v>1567</v>
       </c>
       <c r="E551">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F551" t="s">
         <v>1582</v>
@@ -27506,7 +27506,7 @@
         <v>1568</v>
       </c>
       <c r="E552">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F552" t="s">
         <v>1582</v>
@@ -27544,7 +27544,7 @@
         <v>1568</v>
       </c>
       <c r="E553">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F553" t="s">
         <v>1586</v>
@@ -27579,7 +27579,7 @@
         <v>1568</v>
       </c>
       <c r="E554">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F554" t="s">
         <v>1584</v>
@@ -27614,7 +27614,7 @@
         <v>1568</v>
       </c>
       <c r="E555">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F555" t="s">
         <v>1582</v>
@@ -27649,7 +27649,7 @@
         <v>1568</v>
       </c>
       <c r="E556">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F556" t="s">
         <v>1582</v>
@@ -27684,7 +27684,7 @@
         <v>1568</v>
       </c>
       <c r="E557">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F557" t="s">
         <v>1582</v>
@@ -27719,7 +27719,7 @@
         <v>1568</v>
       </c>
       <c r="E558">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F558" t="s">
         <v>1582</v>
@@ -27754,7 +27754,7 @@
         <v>1568</v>
       </c>
       <c r="E559">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F559" t="s">
         <v>1582</v>
@@ -27789,7 +27789,7 @@
         <v>1568</v>
       </c>
       <c r="E560">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F560" t="s">
         <v>1582</v>
@@ -27824,7 +27824,7 @@
         <v>1569</v>
       </c>
       <c r="E561">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F561" t="s">
         <v>1582</v>
@@ -27862,7 +27862,7 @@
         <v>1569</v>
       </c>
       <c r="E562">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F562" t="s">
         <v>1582</v>
@@ -27897,7 +27897,7 @@
         <v>1570</v>
       </c>
       <c r="E563">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F563" t="s">
         <v>1582</v>
@@ -27932,7 +27932,7 @@
         <v>1570</v>
       </c>
       <c r="E564">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F564" t="s">
         <v>1584</v>
@@ -27970,7 +27970,7 @@
         <v>1570</v>
       </c>
       <c r="E565">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F565" t="s">
         <v>1582</v>
@@ -28005,7 +28005,7 @@
         <v>1570</v>
       </c>
       <c r="E566">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F566" t="s">
         <v>1582</v>
@@ -28040,7 +28040,7 @@
         <v>1570</v>
       </c>
       <c r="E567">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F567" t="s">
         <v>1582</v>
@@ -28075,7 +28075,7 @@
         <v>1570</v>
       </c>
       <c r="E568">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F568" t="s">
         <v>1582</v>
@@ -28110,7 +28110,7 @@
         <v>1570</v>
       </c>
       <c r="E569">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F569" t="s">
         <v>1582</v>
@@ -28145,7 +28145,7 @@
         <v>1570</v>
       </c>
       <c r="E570">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F570" t="s">
         <v>1582</v>
@@ -28180,7 +28180,7 @@
         <v>1571</v>
       </c>
       <c r="E571">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F571" t="s">
         <v>1582</v>
@@ -28215,7 +28215,7 @@
         <v>1571</v>
       </c>
       <c r="E572">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F572" t="s">
         <v>1582</v>
@@ -28250,7 +28250,7 @@
         <v>1571</v>
       </c>
       <c r="E573">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F573" t="s">
         <v>1582</v>
@@ -28285,7 +28285,7 @@
         <v>1571</v>
       </c>
       <c r="E574">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F574" t="s">
         <v>1582</v>
@@ -28320,7 +28320,7 @@
         <v>1571</v>
       </c>
       <c r="E575">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F575" t="s">
         <v>1584</v>
@@ -28358,7 +28358,7 @@
         <v>1571</v>
       </c>
       <c r="E576">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F576" t="s">
         <v>1582</v>
@@ -28393,7 +28393,7 @@
         <v>1571</v>
       </c>
       <c r="E577">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F577" t="s">
         <v>1582</v>
@@ -28428,7 +28428,7 @@
         <v>1571</v>
       </c>
       <c r="E578">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F578" t="s">
         <v>1582</v>
@@ -28463,7 +28463,7 @@
         <v>1571</v>
       </c>
       <c r="E579">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F579" t="s">
         <v>1582</v>
@@ -28498,7 +28498,7 @@
         <v>1571</v>
       </c>
       <c r="E580">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F580" t="s">
         <v>1584</v>
@@ -28533,7 +28533,7 @@
         <v>1571</v>
       </c>
       <c r="E581">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F581" t="s">
         <v>1582</v>
@@ -28568,7 +28568,7 @@
         <v>1571</v>
       </c>
       <c r="E582">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F582" t="s">
         <v>1586</v>
@@ -28603,7 +28603,7 @@
         <v>1571</v>
       </c>
       <c r="E583">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F583" t="s">
         <v>1582</v>
@@ -28638,7 +28638,7 @@
         <v>1572</v>
       </c>
       <c r="E584">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F584" t="s">
         <v>1582</v>
@@ -28673,7 +28673,7 @@
         <v>1572</v>
       </c>
       <c r="E585">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F585" t="s">
         <v>1582</v>
@@ -28708,7 +28708,7 @@
         <v>1572</v>
       </c>
       <c r="E586">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F586" t="s">
         <v>1582</v>
@@ -28743,7 +28743,7 @@
         <v>1572</v>
       </c>
       <c r="E587">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F587" t="s">
         <v>1582</v>
@@ -28778,7 +28778,7 @@
         <v>1572</v>
       </c>
       <c r="E588">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F588" t="s">
         <v>1582</v>
@@ -28813,7 +28813,7 @@
         <v>1572</v>
       </c>
       <c r="E589">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F589" t="s">
         <v>1582</v>
@@ -28848,7 +28848,7 @@
         <v>1572</v>
       </c>
       <c r="E590">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F590" t="s">
         <v>1582</v>
@@ -28883,7 +28883,7 @@
         <v>1572</v>
       </c>
       <c r="E591">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F591" t="s">
         <v>1582</v>
@@ -28921,7 +28921,7 @@
         <v>1572</v>
       </c>
       <c r="E592">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F592" t="s">
         <v>1584</v>
@@ -28959,7 +28959,7 @@
         <v>1572</v>
       </c>
       <c r="E593">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F593" t="s">
         <v>1584</v>
@@ -28994,7 +28994,7 @@
         <v>1572</v>
       </c>
       <c r="E594">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F594" t="s">
         <v>1584</v>
@@ -29029,7 +29029,7 @@
         <v>1572</v>
       </c>
       <c r="E595">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F595" t="s">
         <v>1582</v>
@@ -29064,7 +29064,7 @@
         <v>1573</v>
       </c>
       <c r="E596">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F596" t="s">
         <v>1582</v>
@@ -29099,7 +29099,7 @@
         <v>1573</v>
       </c>
       <c r="E597">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F597" t="s">
         <v>1582</v>
@@ -29134,7 +29134,7 @@
         <v>1573</v>
       </c>
       <c r="E598">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F598" t="s">
         <v>1582</v>
@@ -29169,7 +29169,7 @@
         <v>1573</v>
       </c>
       <c r="E599">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F599" t="s">
         <v>1582</v>
@@ -29204,7 +29204,7 @@
         <v>1573</v>
       </c>
       <c r="E600">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F600" t="s">
         <v>1582</v>
@@ -29239,7 +29239,7 @@
         <v>1573</v>
       </c>
       <c r="E601">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F601" t="s">
         <v>1582</v>
@@ -29274,7 +29274,7 @@
         <v>1573</v>
       </c>
       <c r="E602">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F602" t="s">
         <v>1582</v>
@@ -29309,7 +29309,7 @@
         <v>1573</v>
       </c>
       <c r="E603">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F603" t="s">
         <v>1582</v>
@@ -29344,7 +29344,7 @@
         <v>1573</v>
       </c>
       <c r="E604">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F604" t="s">
         <v>1582</v>
@@ -29379,7 +29379,7 @@
         <v>1573</v>
       </c>
       <c r="E605">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F605" t="s">
         <v>1582</v>
@@ -29417,7 +29417,7 @@
         <v>1574</v>
       </c>
       <c r="E606">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F606" t="s">
         <v>1582</v>
@@ -29452,7 +29452,7 @@
         <v>1574</v>
       </c>
       <c r="E607">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F607" t="s">
         <v>1582</v>
@@ -29487,7 +29487,7 @@
         <v>1575</v>
       </c>
       <c r="E608">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F608" t="s">
         <v>1582</v>
@@ -29525,7 +29525,7 @@
         <v>1575</v>
       </c>
       <c r="E609">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F609" t="s">
         <v>1582</v>
@@ -29560,7 +29560,7 @@
         <v>1575</v>
       </c>
       <c r="E610">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F610" t="s">
         <v>1582</v>
@@ -29595,7 +29595,7 @@
         <v>1575</v>
       </c>
       <c r="E611">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F611" t="s">
         <v>1584</v>
@@ -29633,7 +29633,7 @@
         <v>1575</v>
       </c>
       <c r="E612">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F612" t="s">
         <v>1584</v>
@@ -29671,7 +29671,7 @@
         <v>1575</v>
       </c>
       <c r="E613">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F613" t="s">
         <v>1582</v>
@@ -29706,7 +29706,7 @@
         <v>1575</v>
       </c>
       <c r="E614">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F614" t="s">
         <v>1582</v>
@@ -29741,7 +29741,7 @@
         <v>1575</v>
       </c>
       <c r="E615">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F615" t="s">
         <v>1582</v>
@@ -29776,7 +29776,7 @@
         <v>1576</v>
       </c>
       <c r="E616">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F616" t="s">
         <v>1582</v>
@@ -29811,7 +29811,7 @@
         <v>1576</v>
       </c>
       <c r="E617">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F617" t="s">
         <v>1582</v>
@@ -29846,7 +29846,7 @@
         <v>1576</v>
       </c>
       <c r="E618">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F618" t="s">
         <v>1582</v>
@@ -29881,7 +29881,7 @@
         <v>1576</v>
       </c>
       <c r="E619">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F619" t="s">
         <v>1582</v>
@@ -29916,7 +29916,7 @@
         <v>1576</v>
       </c>
       <c r="E620">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F620" t="s">
         <v>1582</v>
@@ -29951,7 +29951,7 @@
         <v>1576</v>
       </c>
       <c r="E621">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F621" t="s">
         <v>1582</v>
@@ -29986,7 +29986,7 @@
         <v>1576</v>
       </c>
       <c r="E622">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F622" t="s">
         <v>1582</v>
@@ -30021,7 +30021,7 @@
         <v>1576</v>
       </c>
       <c r="E623">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F623" t="s">
         <v>1582</v>
@@ -30056,7 +30056,7 @@
         <v>1576</v>
       </c>
       <c r="E624">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F624" t="s">
         <v>1582</v>
@@ -30091,7 +30091,7 @@
         <v>1576</v>
       </c>
       <c r="E625">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F625" t="s">
         <v>1582</v>
@@ -30126,7 +30126,7 @@
         <v>1576</v>
       </c>
       <c r="E626">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F626" t="s">
         <v>1582</v>
@@ -30161,7 +30161,7 @@
         <v>1576</v>
       </c>
       <c r="E627">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F627" t="s">
         <v>1582</v>
@@ -30199,7 +30199,7 @@
         <v>1576</v>
       </c>
       <c r="E628">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F628" t="s">
         <v>1582</v>
@@ -30237,7 +30237,7 @@
         <v>1576</v>
       </c>
       <c r="E629">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F629" t="s">
         <v>1584</v>
@@ -30275,7 +30275,7 @@
         <v>1576</v>
       </c>
       <c r="E630">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F630" t="s">
         <v>1582</v>
@@ -30310,7 +30310,7 @@
         <v>1577</v>
       </c>
       <c r="E631">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F631" t="s">
         <v>1582</v>
@@ -30345,7 +30345,7 @@
         <v>1577</v>
       </c>
       <c r="E632">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F632" t="s">
         <v>1584</v>
@@ -30383,7 +30383,7 @@
         <v>1577</v>
       </c>
       <c r="E633">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F633" t="s">
         <v>1582</v>
@@ -30418,7 +30418,7 @@
         <v>1577</v>
       </c>
       <c r="E634">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F634" t="s">
         <v>1582</v>
@@ -30453,7 +30453,7 @@
         <v>1578</v>
       </c>
       <c r="E635">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F635" t="s">
         <v>1582</v>
@@ -30488,7 +30488,7 @@
         <v>1578</v>
       </c>
       <c r="E636">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F636" t="s">
         <v>1582</v>
@@ -30523,7 +30523,7 @@
         <v>1578</v>
       </c>
       <c r="E637">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F637" t="s">
         <v>1582</v>
@@ -30558,7 +30558,7 @@
         <v>1578</v>
       </c>
       <c r="E638">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F638" t="s">
         <v>1582</v>
@@ -30593,7 +30593,7 @@
         <v>1578</v>
       </c>
       <c r="E639">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F639" t="s">
         <v>1584</v>
@@ -30631,7 +30631,7 @@
         <v>1578</v>
       </c>
       <c r="E640">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F640" t="s">
         <v>1584</v>
@@ -30669,7 +30669,7 @@
         <v>1578</v>
       </c>
       <c r="E641">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F641" t="s">
         <v>1582</v>
@@ -30704,7 +30704,7 @@
         <v>1578</v>
       </c>
       <c r="E642">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F642" t="s">
         <v>1582</v>
@@ -30739,7 +30739,7 @@
         <v>1578</v>
       </c>
       <c r="E643">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F643" t="s">
         <v>1582</v>
@@ -30774,7 +30774,7 @@
         <v>1578</v>
       </c>
       <c r="E644">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F644" t="s">
         <v>1582</v>
@@ -30809,7 +30809,7 @@
         <v>1578</v>
       </c>
       <c r="E645">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F645" t="s">
         <v>1582</v>
@@ -30844,7 +30844,7 @@
         <v>1578</v>
       </c>
       <c r="E646">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F646" t="s">
         <v>1582</v>
@@ -30879,7 +30879,7 @@
         <v>1578</v>
       </c>
       <c r="E647">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F647" t="s">
         <v>1582</v>
@@ -30914,7 +30914,7 @@
         <v>1579</v>
       </c>
       <c r="E648">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F648" t="s">
         <v>1586</v>
@@ -30949,7 +30949,7 @@
         <v>1579</v>
       </c>
       <c r="E649">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F649" t="s">
         <v>1582</v>
@@ -30984,7 +30984,7 @@
         <v>1579</v>
       </c>
       <c r="E650">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F650" t="s">
         <v>1582</v>
@@ -31019,7 +31019,7 @@
         <v>1579</v>
       </c>
       <c r="E651">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F651" t="s">
         <v>1582</v>
@@ -31054,7 +31054,7 @@
         <v>1579</v>
       </c>
       <c r="E652">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F652" t="s">
         <v>1582</v>
@@ -31089,7 +31089,7 @@
         <v>1579</v>
       </c>
       <c r="E653">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F653" t="s">
         <v>1582</v>
@@ -31124,7 +31124,7 @@
         <v>1579</v>
       </c>
       <c r="E654">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F654" t="s">
         <v>1582</v>
@@ -31159,7 +31159,7 @@
         <v>1579</v>
       </c>
       <c r="E655">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F655" t="s">
         <v>1582</v>
@@ -31194,7 +31194,7 @@
         <v>1580</v>
       </c>
       <c r="E656">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F656" t="s">
         <v>1582</v>
@@ -31229,7 +31229,7 @@
         <v>1580</v>
       </c>
       <c r="E657">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F657" t="s">
         <v>1582</v>
@@ -31267,7 +31267,7 @@
         <v>1580</v>
       </c>
       <c r="E658">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F658" t="s">
         <v>1582</v>
@@ -31302,7 +31302,7 @@
         <v>1580</v>
       </c>
       <c r="E659">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F659" t="s">
         <v>1582</v>
@@ -31337,7 +31337,7 @@
         <v>1580</v>
       </c>
       <c r="E660">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F660" t="s">
         <v>1582</v>
@@ -31372,7 +31372,7 @@
         <v>1580</v>
       </c>
       <c r="E661">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F661" t="s">
         <v>1582</v>
@@ -31410,7 +31410,7 @@
         <v>1581</v>
       </c>
       <c r="E662">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F662" t="s">
         <v>1582</v>
@@ -31445,7 +31445,7 @@
         <v>1581</v>
       </c>
       <c r="E663">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F663" t="s">
         <v>1582</v>
@@ -31483,7 +31483,7 @@
         <v>1581</v>
       </c>
       <c r="E664">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F664" t="s">
         <v>1582</v>
@@ -31521,7 +31521,7 @@
         <v>1581</v>
       </c>
       <c r="E665">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F665" t="s">
         <v>1582</v>
@@ -31556,7 +31556,7 @@
         <v>1581</v>
       </c>
       <c r="E666">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F666" t="s">
         <v>1582</v>

--- a/BacklogGATEAutoCompleto.xlsx
+++ b/BacklogGATEAutoCompleto.xlsx
@@ -8280,7 +8280,7 @@
         <v>1386</v>
       </c>
       <c r="E2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="F2" t="s">
         <v>1600</v>
@@ -8315,7 +8315,7 @@
         <v>1387</v>
       </c>
       <c r="E3">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="F3" t="s">
         <v>1600</v>
@@ -8350,7 +8350,7 @@
         <v>1388</v>
       </c>
       <c r="E4">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F4" t="s">
         <v>1600</v>
@@ -8385,7 +8385,7 @@
         <v>1389</v>
       </c>
       <c r="E5">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="F5" t="s">
         <v>1600</v>
@@ -8420,7 +8420,7 @@
         <v>1390</v>
       </c>
       <c r="E6">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="F6" t="s">
         <v>1600</v>
@@ -8455,7 +8455,7 @@
         <v>1391</v>
       </c>
       <c r="E7">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="F7" t="s">
         <v>1600</v>
@@ -8490,7 +8490,7 @@
         <v>1392</v>
       </c>
       <c r="E8">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="F8" t="s">
         <v>1600</v>
@@ -8525,7 +8525,7 @@
         <v>1393</v>
       </c>
       <c r="E9">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F9" t="s">
         <v>1600</v>
@@ -8560,7 +8560,7 @@
         <v>1394</v>
       </c>
       <c r="E10">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="F10" t="s">
         <v>1600</v>
@@ -8595,7 +8595,7 @@
         <v>1395</v>
       </c>
       <c r="E11">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="F11" t="s">
         <v>1600</v>
@@ -8630,7 +8630,7 @@
         <v>1395</v>
       </c>
       <c r="E12">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="F12" t="s">
         <v>1600</v>
@@ -8665,7 +8665,7 @@
         <v>1396</v>
       </c>
       <c r="E13">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="F13" t="s">
         <v>1600</v>
@@ -8700,7 +8700,7 @@
         <v>1397</v>
       </c>
       <c r="E14">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F14" t="s">
         <v>1600</v>
@@ -8735,7 +8735,7 @@
         <v>1398</v>
       </c>
       <c r="E15">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="F15" t="s">
         <v>1600</v>
@@ -8770,7 +8770,7 @@
         <v>1398</v>
       </c>
       <c r="E16">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="F16" t="s">
         <v>1600</v>
@@ -8805,7 +8805,7 @@
         <v>1399</v>
       </c>
       <c r="E17">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="F17" t="s">
         <v>1600</v>
@@ -8840,7 +8840,7 @@
         <v>1400</v>
       </c>
       <c r="E18">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="F18" t="s">
         <v>1600</v>
@@ -8875,7 +8875,7 @@
         <v>1400</v>
       </c>
       <c r="E19">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="F19" t="s">
         <v>1600</v>
@@ -8910,7 +8910,7 @@
         <v>1401</v>
       </c>
       <c r="E20">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="F20" t="s">
         <v>1600</v>
@@ -8945,7 +8945,7 @@
         <v>1402</v>
       </c>
       <c r="E21">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F21" t="s">
         <v>1600</v>
@@ -8980,7 +8980,7 @@
         <v>1403</v>
       </c>
       <c r="E22">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="F22" t="s">
         <v>1600</v>
@@ -9015,7 +9015,7 @@
         <v>1404</v>
       </c>
       <c r="E23">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="F23" t="s">
         <v>1600</v>
@@ -9050,7 +9050,7 @@
         <v>1405</v>
       </c>
       <c r="E24">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="F24" t="s">
         <v>1600</v>
@@ -9088,7 +9088,7 @@
         <v>1406</v>
       </c>
       <c r="E25">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F25" t="s">
         <v>1600</v>
@@ -9123,7 +9123,7 @@
         <v>1407</v>
       </c>
       <c r="E26">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F26" t="s">
         <v>1600</v>
@@ -9158,7 +9158,7 @@
         <v>1408</v>
       </c>
       <c r="E27">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F27" t="s">
         <v>1600</v>
@@ -9193,7 +9193,7 @@
         <v>1409</v>
       </c>
       <c r="E28">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F28" t="s">
         <v>1600</v>
@@ -9228,7 +9228,7 @@
         <v>1410</v>
       </c>
       <c r="E29">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F29" t="s">
         <v>1600</v>
@@ -9263,7 +9263,7 @@
         <v>1411</v>
       </c>
       <c r="E30">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F30" t="s">
         <v>1600</v>
@@ -9298,7 +9298,7 @@
         <v>1412</v>
       </c>
       <c r="E31">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F31" t="s">
         <v>1600</v>
@@ -9333,7 +9333,7 @@
         <v>1413</v>
       </c>
       <c r="E32">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F32" t="s">
         <v>1600</v>
@@ -9368,7 +9368,7 @@
         <v>1414</v>
       </c>
       <c r="E33">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F33" t="s">
         <v>1600</v>
@@ -9403,7 +9403,7 @@
         <v>1415</v>
       </c>
       <c r="E34">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F34" t="s">
         <v>1600</v>
@@ -9438,7 +9438,7 @@
         <v>1416</v>
       </c>
       <c r="E35">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F35" t="s">
         <v>1600</v>
@@ -9473,7 +9473,7 @@
         <v>1417</v>
       </c>
       <c r="E36">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="F36" t="s">
         <v>1600</v>
@@ -9508,7 +9508,7 @@
         <v>1417</v>
       </c>
       <c r="E37">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="F37" t="s">
         <v>1600</v>
@@ -9543,7 +9543,7 @@
         <v>1418</v>
       </c>
       <c r="E38">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F38" t="s">
         <v>1600</v>
@@ -9578,7 +9578,7 @@
         <v>1419</v>
       </c>
       <c r="E39">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F39" t="s">
         <v>1600</v>
@@ -9613,7 +9613,7 @@
         <v>1420</v>
       </c>
       <c r="E40">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F40" t="s">
         <v>1600</v>
@@ -9648,7 +9648,7 @@
         <v>1421</v>
       </c>
       <c r="E41">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F41" t="s">
         <v>1600</v>
@@ -9683,7 +9683,7 @@
         <v>1422</v>
       </c>
       <c r="E42">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F42" t="s">
         <v>1600</v>
@@ -9718,7 +9718,7 @@
         <v>1422</v>
       </c>
       <c r="E43">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F43" t="s">
         <v>1600</v>
@@ -9753,7 +9753,7 @@
         <v>1423</v>
       </c>
       <c r="E44">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F44" t="s">
         <v>1600</v>
@@ -9788,7 +9788,7 @@
         <v>1424</v>
       </c>
       <c r="E45">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F45" t="s">
         <v>1600</v>
@@ -9823,7 +9823,7 @@
         <v>1425</v>
       </c>
       <c r="E46">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F46" t="s">
         <v>1600</v>
@@ -9858,7 +9858,7 @@
         <v>1425</v>
       </c>
       <c r="E47">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F47" t="s">
         <v>1600</v>
@@ -9893,7 +9893,7 @@
         <v>1426</v>
       </c>
       <c r="E48">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F48" t="s">
         <v>1600</v>
@@ -9928,7 +9928,7 @@
         <v>1426</v>
       </c>
       <c r="E49">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F49" t="s">
         <v>1600</v>
@@ -9963,7 +9963,7 @@
         <v>1427</v>
       </c>
       <c r="E50">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F50" t="s">
         <v>1600</v>
@@ -9998,7 +9998,7 @@
         <v>1428</v>
       </c>
       <c r="E51">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F51" t="s">
         <v>1600</v>
@@ -10033,7 +10033,7 @@
         <v>1429</v>
       </c>
       <c r="E52">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F52" t="s">
         <v>1600</v>
@@ -10068,7 +10068,7 @@
         <v>1430</v>
       </c>
       <c r="E53">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F53" t="s">
         <v>1600</v>
@@ -10103,7 +10103,7 @@
         <v>1431</v>
       </c>
       <c r="E54">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F54" t="s">
         <v>1600</v>
@@ -10138,7 +10138,7 @@
         <v>1432</v>
       </c>
       <c r="E55">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F55" t="s">
         <v>1600</v>
@@ -10173,7 +10173,7 @@
         <v>1433</v>
       </c>
       <c r="E56">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F56" t="s">
         <v>1600</v>
@@ -10208,7 +10208,7 @@
         <v>1434</v>
       </c>
       <c r="E57">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F57" t="s">
         <v>1600</v>
@@ -10243,7 +10243,7 @@
         <v>1435</v>
       </c>
       <c r="E58">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F58" t="s">
         <v>1600</v>
@@ -10278,7 +10278,7 @@
         <v>1436</v>
       </c>
       <c r="E59">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F59" t="s">
         <v>1600</v>
@@ -10313,7 +10313,7 @@
         <v>1437</v>
       </c>
       <c r="E60">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F60" t="s">
         <v>1600</v>
@@ -10348,7 +10348,7 @@
         <v>1438</v>
       </c>
       <c r="E61">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F61" t="s">
         <v>1600</v>
@@ -10383,7 +10383,7 @@
         <v>1439</v>
       </c>
       <c r="E62">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F62" t="s">
         <v>1600</v>
@@ -10418,7 +10418,7 @@
         <v>1439</v>
       </c>
       <c r="E63">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F63" t="s">
         <v>1600</v>
@@ -10453,7 +10453,7 @@
         <v>1439</v>
       </c>
       <c r="E64">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F64" t="s">
         <v>1600</v>
@@ -10488,7 +10488,7 @@
         <v>1440</v>
       </c>
       <c r="E65">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F65" t="s">
         <v>1600</v>
@@ -10523,7 +10523,7 @@
         <v>1441</v>
       </c>
       <c r="E66">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F66" t="s">
         <v>1600</v>
@@ -10558,7 +10558,7 @@
         <v>1442</v>
       </c>
       <c r="E67">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F67" t="s">
         <v>1600</v>
@@ -10593,7 +10593,7 @@
         <v>1442</v>
       </c>
       <c r="E68">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F68" t="s">
         <v>1600</v>
@@ -10628,7 +10628,7 @@
         <v>1442</v>
       </c>
       <c r="E69">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F69" t="s">
         <v>1600</v>
@@ -10663,7 +10663,7 @@
         <v>1443</v>
       </c>
       <c r="E70">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F70" t="s">
         <v>1600</v>
@@ -10698,7 +10698,7 @@
         <v>1444</v>
       </c>
       <c r="E71">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F71" t="s">
         <v>1600</v>
@@ -10733,7 +10733,7 @@
         <v>1445</v>
       </c>
       <c r="E72">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F72" t="s">
         <v>1600</v>
@@ -10768,7 +10768,7 @@
         <v>1445</v>
       </c>
       <c r="E73">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F73" t="s">
         <v>1600</v>
@@ -10803,7 +10803,7 @@
         <v>1445</v>
       </c>
       <c r="E74">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F74" t="s">
         <v>1600</v>
@@ -10838,7 +10838,7 @@
         <v>1446</v>
       </c>
       <c r="E75">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F75" t="s">
         <v>1600</v>
@@ -10873,7 +10873,7 @@
         <v>1447</v>
       </c>
       <c r="E76">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F76" t="s">
         <v>1600</v>
@@ -10908,7 +10908,7 @@
         <v>1447</v>
       </c>
       <c r="E77">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F77" t="s">
         <v>1600</v>
@@ -10943,7 +10943,7 @@
         <v>1447</v>
       </c>
       <c r="E78">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F78" t="s">
         <v>1601</v>
@@ -10978,7 +10978,7 @@
         <v>1447</v>
       </c>
       <c r="E79">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F79" t="s">
         <v>1600</v>
@@ -11013,7 +11013,7 @@
         <v>1448</v>
       </c>
       <c r="E80">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F80" t="s">
         <v>1600</v>
@@ -11048,7 +11048,7 @@
         <v>1449</v>
       </c>
       <c r="E81">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F81" t="s">
         <v>1600</v>
@@ -11083,7 +11083,7 @@
         <v>1449</v>
       </c>
       <c r="E82">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F82" t="s">
         <v>1600</v>
@@ -11118,7 +11118,7 @@
         <v>1450</v>
       </c>
       <c r="E83">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F83" t="s">
         <v>1600</v>
@@ -11153,7 +11153,7 @@
         <v>1451</v>
       </c>
       <c r="E84">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F84" t="s">
         <v>1600</v>
@@ -11188,7 +11188,7 @@
         <v>1452</v>
       </c>
       <c r="E85">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F85" t="s">
         <v>1600</v>
@@ -11223,7 +11223,7 @@
         <v>1453</v>
       </c>
       <c r="E86">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F86" t="s">
         <v>1600</v>
@@ -11258,7 +11258,7 @@
         <v>1454</v>
       </c>
       <c r="E87">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F87" t="s">
         <v>1600</v>
@@ -11293,7 +11293,7 @@
         <v>1454</v>
       </c>
       <c r="E88">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F88" t="s">
         <v>1600</v>
@@ -11328,7 +11328,7 @@
         <v>1454</v>
       </c>
       <c r="E89">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F89" t="s">
         <v>1600</v>
@@ -11363,7 +11363,7 @@
         <v>1454</v>
       </c>
       <c r="E90">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F90" t="s">
         <v>1600</v>
@@ -11398,7 +11398,7 @@
         <v>1454</v>
       </c>
       <c r="E91">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F91" t="s">
         <v>1600</v>
@@ -11433,7 +11433,7 @@
         <v>1454</v>
       </c>
       <c r="E92">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F92" t="s">
         <v>1600</v>
@@ -11468,7 +11468,7 @@
         <v>1454</v>
       </c>
       <c r="E93">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F93" t="s">
         <v>1600</v>
@@ -11503,7 +11503,7 @@
         <v>1455</v>
       </c>
       <c r="E94">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F94" t="s">
         <v>1600</v>
@@ -11538,7 +11538,7 @@
         <v>1455</v>
       </c>
       <c r="E95">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F95" t="s">
         <v>1600</v>
@@ -11573,7 +11573,7 @@
         <v>1456</v>
       </c>
       <c r="E96">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F96" t="s">
         <v>1600</v>
@@ -11608,7 +11608,7 @@
         <v>1457</v>
       </c>
       <c r="E97">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F97" t="s">
         <v>1600</v>
@@ -11643,7 +11643,7 @@
         <v>1457</v>
       </c>
       <c r="E98">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F98" t="s">
         <v>1600</v>
@@ -11678,7 +11678,7 @@
         <v>1458</v>
       </c>
       <c r="E99">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F99" t="s">
         <v>1600</v>
@@ -11713,7 +11713,7 @@
         <v>1458</v>
       </c>
       <c r="E100">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F100" t="s">
         <v>1602</v>
@@ -11748,7 +11748,7 @@
         <v>1459</v>
       </c>
       <c r="E101">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F101" t="s">
         <v>1600</v>
@@ -11783,7 +11783,7 @@
         <v>1460</v>
       </c>
       <c r="E102">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F102" t="s">
         <v>1600</v>
@@ -11818,7 +11818,7 @@
         <v>1461</v>
       </c>
       <c r="E103">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F103" t="s">
         <v>1600</v>
@@ -11853,7 +11853,7 @@
         <v>1461</v>
       </c>
       <c r="E104">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F104" t="s">
         <v>1600</v>
@@ -11888,7 +11888,7 @@
         <v>1462</v>
       </c>
       <c r="E105">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F105" t="s">
         <v>1600</v>
@@ -11923,7 +11923,7 @@
         <v>1463</v>
       </c>
       <c r="E106">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F106" t="s">
         <v>1600</v>
@@ -11958,7 +11958,7 @@
         <v>1464</v>
       </c>
       <c r="E107">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F107" t="s">
         <v>1600</v>
@@ -11993,7 +11993,7 @@
         <v>1465</v>
       </c>
       <c r="E108">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F108" t="s">
         <v>1600</v>
@@ -12028,7 +12028,7 @@
         <v>1466</v>
       </c>
       <c r="E109">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F109" t="s">
         <v>1600</v>
@@ -12063,7 +12063,7 @@
         <v>1466</v>
       </c>
       <c r="E110">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F110" t="s">
         <v>1600</v>
@@ -12098,7 +12098,7 @@
         <v>1467</v>
       </c>
       <c r="E111">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F111" t="s">
         <v>1600</v>
@@ -12133,7 +12133,7 @@
         <v>1467</v>
       </c>
       <c r="E112">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F112" t="s">
         <v>1600</v>
@@ -12168,7 +12168,7 @@
         <v>1467</v>
       </c>
       <c r="E113">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F113" t="s">
         <v>1600</v>
@@ -12203,7 +12203,7 @@
         <v>1468</v>
       </c>
       <c r="E114">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F114" t="s">
         <v>1600</v>
@@ -12238,7 +12238,7 @@
         <v>1468</v>
       </c>
       <c r="E115">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F115" t="s">
         <v>1600</v>
@@ -12273,7 +12273,7 @@
         <v>1468</v>
       </c>
       <c r="E116">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F116" t="s">
         <v>1600</v>
@@ -12308,7 +12308,7 @@
         <v>1468</v>
       </c>
       <c r="E117">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F117" t="s">
         <v>1600</v>
@@ -12343,7 +12343,7 @@
         <v>1468</v>
       </c>
       <c r="E118">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F118" t="s">
         <v>1600</v>
@@ -12378,7 +12378,7 @@
         <v>1469</v>
       </c>
       <c r="E119">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F119" t="s">
         <v>1600</v>
@@ -12413,7 +12413,7 @@
         <v>1470</v>
       </c>
       <c r="E120">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F120" t="s">
         <v>1600</v>
@@ -12448,7 +12448,7 @@
         <v>1470</v>
       </c>
       <c r="E121">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F121" t="s">
         <v>1600</v>
@@ -12483,7 +12483,7 @@
         <v>1471</v>
       </c>
       <c r="E122">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F122" t="s">
         <v>1600</v>
@@ -12518,7 +12518,7 @@
         <v>1472</v>
       </c>
       <c r="E123">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F123" t="s">
         <v>1600</v>
@@ -12553,7 +12553,7 @@
         <v>1472</v>
       </c>
       <c r="E124">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F124" t="s">
         <v>1600</v>
@@ -12588,7 +12588,7 @@
         <v>1472</v>
       </c>
       <c r="E125">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F125" t="s">
         <v>1600</v>
@@ -12623,7 +12623,7 @@
         <v>1473</v>
       </c>
       <c r="E126">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F126" t="s">
         <v>1600</v>
@@ -12658,7 +12658,7 @@
         <v>1473</v>
       </c>
       <c r="E127">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F127" t="s">
         <v>1600</v>
@@ -12693,7 +12693,7 @@
         <v>1473</v>
       </c>
       <c r="E128">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F128" t="s">
         <v>1600</v>
@@ -12728,7 +12728,7 @@
         <v>1474</v>
       </c>
       <c r="E129">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F129" t="s">
         <v>1600</v>
@@ -12763,7 +12763,7 @@
         <v>1474</v>
       </c>
       <c r="E130">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F130" t="s">
         <v>1600</v>
@@ -12798,7 +12798,7 @@
         <v>1475</v>
       </c>
       <c r="E131">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F131" t="s">
         <v>1600</v>
@@ -12833,7 +12833,7 @@
         <v>1475</v>
       </c>
       <c r="E132">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F132" t="s">
         <v>1600</v>
@@ -12868,7 +12868,7 @@
         <v>1476</v>
       </c>
       <c r="E133">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F133" t="s">
         <v>1600</v>
@@ -12903,7 +12903,7 @@
         <v>1477</v>
       </c>
       <c r="E134">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F134" t="s">
         <v>1600</v>
@@ -12938,7 +12938,7 @@
         <v>1477</v>
       </c>
       <c r="E135">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F135" t="s">
         <v>1600</v>
@@ -12973,7 +12973,7 @@
         <v>1478</v>
       </c>
       <c r="E136">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F136" t="s">
         <v>1600</v>
@@ -13008,7 +13008,7 @@
         <v>1478</v>
       </c>
       <c r="E137">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F137" t="s">
         <v>1600</v>
@@ -13043,7 +13043,7 @@
         <v>1479</v>
       </c>
       <c r="E138">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F138" t="s">
         <v>1600</v>
@@ -13081,7 +13081,7 @@
         <v>1479</v>
       </c>
       <c r="E139">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F139" t="s">
         <v>1600</v>
@@ -13116,7 +13116,7 @@
         <v>1479</v>
       </c>
       <c r="E140">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F140" t="s">
         <v>1600</v>
@@ -13151,7 +13151,7 @@
         <v>1479</v>
       </c>
       <c r="E141">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F141" t="s">
         <v>1600</v>
@@ -13186,7 +13186,7 @@
         <v>1479</v>
       </c>
       <c r="E142">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F142" t="s">
         <v>1600</v>
@@ -13221,7 +13221,7 @@
         <v>1480</v>
       </c>
       <c r="E143">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F143" t="s">
         <v>1600</v>
@@ -13256,7 +13256,7 @@
         <v>1481</v>
       </c>
       <c r="E144">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F144" t="s">
         <v>1601</v>
@@ -13291,7 +13291,7 @@
         <v>1482</v>
       </c>
       <c r="E145">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F145" t="s">
         <v>1600</v>
@@ -13326,7 +13326,7 @@
         <v>1482</v>
       </c>
       <c r="E146">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F146" t="s">
         <v>1600</v>
@@ -13361,7 +13361,7 @@
         <v>1482</v>
       </c>
       <c r="E147">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F147" t="s">
         <v>1600</v>
@@ -13396,7 +13396,7 @@
         <v>1482</v>
       </c>
       <c r="E148">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F148" t="s">
         <v>1600</v>
@@ -13431,7 +13431,7 @@
         <v>1483</v>
       </c>
       <c r="E149">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F149" t="s">
         <v>1600</v>
@@ -13466,7 +13466,7 @@
         <v>1483</v>
       </c>
       <c r="E150">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F150" t="s">
         <v>1600</v>
@@ -13501,7 +13501,7 @@
         <v>1483</v>
       </c>
       <c r="E151">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F151" t="s">
         <v>1600</v>
@@ -13536,7 +13536,7 @@
         <v>1483</v>
       </c>
       <c r="E152">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F152" t="s">
         <v>1600</v>
@@ -13571,7 +13571,7 @@
         <v>1483</v>
       </c>
       <c r="E153">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F153" t="s">
         <v>1600</v>
@@ -13606,7 +13606,7 @@
         <v>1483</v>
       </c>
       <c r="E154">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F154" t="s">
         <v>1600</v>
@@ -13641,7 +13641,7 @@
         <v>1483</v>
       </c>
       <c r="E155">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F155" t="s">
         <v>1600</v>
@@ -13676,7 +13676,7 @@
         <v>1484</v>
       </c>
       <c r="E156">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F156" t="s">
         <v>1600</v>
@@ -13711,7 +13711,7 @@
         <v>1484</v>
       </c>
       <c r="E157">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F157" t="s">
         <v>1600</v>
@@ -13746,7 +13746,7 @@
         <v>1485</v>
       </c>
       <c r="E158">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F158" t="s">
         <v>1600</v>
@@ -13781,7 +13781,7 @@
         <v>1485</v>
       </c>
       <c r="E159">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F159" t="s">
         <v>1600</v>
@@ -13816,7 +13816,7 @@
         <v>1486</v>
       </c>
       <c r="E160">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F160" t="s">
         <v>1600</v>
@@ -13851,7 +13851,7 @@
         <v>1486</v>
       </c>
       <c r="E161">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F161" t="s">
         <v>1600</v>
@@ -13886,7 +13886,7 @@
         <v>1486</v>
       </c>
       <c r="E162">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F162" t="s">
         <v>1600</v>
@@ -13921,7 +13921,7 @@
         <v>1486</v>
       </c>
       <c r="E163">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F163" t="s">
         <v>1600</v>
@@ -13956,7 +13956,7 @@
         <v>1487</v>
       </c>
       <c r="E164">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F164" t="s">
         <v>1600</v>
@@ -13991,7 +13991,7 @@
         <v>1487</v>
       </c>
       <c r="E165">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F165" t="s">
         <v>1600</v>
@@ -14026,7 +14026,7 @@
         <v>1487</v>
       </c>
       <c r="E166">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F166" t="s">
         <v>1600</v>
@@ -14061,7 +14061,7 @@
         <v>1487</v>
       </c>
       <c r="E167">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F167" t="s">
         <v>1600</v>
@@ -14096,7 +14096,7 @@
         <v>1487</v>
       </c>
       <c r="E168">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F168" t="s">
         <v>1600</v>
@@ -14131,7 +14131,7 @@
         <v>1487</v>
       </c>
       <c r="E169">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F169" t="s">
         <v>1600</v>
@@ -14166,7 +14166,7 @@
         <v>1487</v>
       </c>
       <c r="E170">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F170" t="s">
         <v>1600</v>
@@ -14201,7 +14201,7 @@
         <v>1487</v>
       </c>
       <c r="E171">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F171" t="s">
         <v>1600</v>
@@ -14236,7 +14236,7 @@
         <v>1487</v>
       </c>
       <c r="E172">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F172" t="s">
         <v>1600</v>
@@ -14271,7 +14271,7 @@
         <v>1487</v>
       </c>
       <c r="E173">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F173" t="s">
         <v>1600</v>
@@ -14306,7 +14306,7 @@
         <v>1488</v>
       </c>
       <c r="E174">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F174" t="s">
         <v>1600</v>
@@ -14341,7 +14341,7 @@
         <v>1488</v>
       </c>
       <c r="E175">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F175" t="s">
         <v>1600</v>
@@ -14376,7 +14376,7 @@
         <v>1488</v>
       </c>
       <c r="E176">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F176" t="s">
         <v>1600</v>
@@ -14411,7 +14411,7 @@
         <v>1489</v>
       </c>
       <c r="E177">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F177" t="s">
         <v>1600</v>
@@ -14446,7 +14446,7 @@
         <v>1489</v>
       </c>
       <c r="E178">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F178" t="s">
         <v>1601</v>
@@ -14481,7 +14481,7 @@
         <v>1489</v>
       </c>
       <c r="E179">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F179" t="s">
         <v>1600</v>
@@ -14516,7 +14516,7 @@
         <v>1490</v>
       </c>
       <c r="E180">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F180" t="s">
         <v>1600</v>
@@ -14551,7 +14551,7 @@
         <v>1490</v>
       </c>
       <c r="E181">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F181" t="s">
         <v>1600</v>
@@ -14586,7 +14586,7 @@
         <v>1491</v>
       </c>
       <c r="E182">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F182" t="s">
         <v>1600</v>
@@ -14621,7 +14621,7 @@
         <v>1491</v>
       </c>
       <c r="E183">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F183" t="s">
         <v>1600</v>
@@ -14656,7 +14656,7 @@
         <v>1492</v>
       </c>
       <c r="E184">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F184" t="s">
         <v>1600</v>
@@ -14691,7 +14691,7 @@
         <v>1492</v>
       </c>
       <c r="E185">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F185" t="s">
         <v>1600</v>
@@ -14726,7 +14726,7 @@
         <v>1493</v>
       </c>
       <c r="E186">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F186" t="s">
         <v>1600</v>
@@ -14761,7 +14761,7 @@
         <v>1493</v>
       </c>
       <c r="E187">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F187" t="s">
         <v>1600</v>
@@ -14796,7 +14796,7 @@
         <v>1493</v>
       </c>
       <c r="E188">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F188" t="s">
         <v>1600</v>
@@ -14831,7 +14831,7 @@
         <v>1493</v>
       </c>
       <c r="E189">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F189" t="s">
         <v>1600</v>
@@ -14866,7 +14866,7 @@
         <v>1493</v>
       </c>
       <c r="E190">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F190" t="s">
         <v>1600</v>
@@ -14901,7 +14901,7 @@
         <v>1494</v>
       </c>
       <c r="E191">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F191" t="s">
         <v>1600</v>
@@ -14936,7 +14936,7 @@
         <v>1494</v>
       </c>
       <c r="E192">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F192" t="s">
         <v>1600</v>
@@ -14971,7 +14971,7 @@
         <v>1495</v>
       </c>
       <c r="E193">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F193" t="s">
         <v>1600</v>
@@ -15006,7 +15006,7 @@
         <v>1496</v>
       </c>
       <c r="E194">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F194" t="s">
         <v>1600</v>
@@ -15041,7 +15041,7 @@
         <v>1496</v>
       </c>
       <c r="E195">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F195" t="s">
         <v>1600</v>
@@ -15076,7 +15076,7 @@
         <v>1496</v>
       </c>
       <c r="E196">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F196" t="s">
         <v>1600</v>
@@ -15111,7 +15111,7 @@
         <v>1496</v>
       </c>
       <c r="E197">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F197" t="s">
         <v>1600</v>
@@ -15146,7 +15146,7 @@
         <v>1497</v>
       </c>
       <c r="E198">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F198" t="s">
         <v>1600</v>
@@ -15181,7 +15181,7 @@
         <v>1498</v>
       </c>
       <c r="E199">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F199" t="s">
         <v>1600</v>
@@ -15216,7 +15216,7 @@
         <v>1498</v>
       </c>
       <c r="E200">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F200" t="s">
         <v>1600</v>
@@ -15251,7 +15251,7 @@
         <v>1498</v>
       </c>
       <c r="E201">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F201" t="s">
         <v>1600</v>
@@ -15286,7 +15286,7 @@
         <v>1498</v>
       </c>
       <c r="E202">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F202" t="s">
         <v>1600</v>
@@ -15321,7 +15321,7 @@
         <v>1498</v>
       </c>
       <c r="E203">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F203" t="s">
         <v>1600</v>
@@ -15356,7 +15356,7 @@
         <v>1499</v>
       </c>
       <c r="E204">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F204" t="s">
         <v>1600</v>
@@ -15391,7 +15391,7 @@
         <v>1499</v>
       </c>
       <c r="E205">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F205" t="s">
         <v>1600</v>
@@ -15426,7 +15426,7 @@
         <v>1499</v>
       </c>
       <c r="E206">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F206" t="s">
         <v>1600</v>
@@ -15461,7 +15461,7 @@
         <v>1499</v>
       </c>
       <c r="E207">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F207" t="s">
         <v>1600</v>
@@ -15496,7 +15496,7 @@
         <v>1499</v>
       </c>
       <c r="E208">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F208" t="s">
         <v>1600</v>
@@ -15531,7 +15531,7 @@
         <v>1499</v>
       </c>
       <c r="E209">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F209" t="s">
         <v>1600</v>
@@ -15566,7 +15566,7 @@
         <v>1499</v>
       </c>
       <c r="E210">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F210" t="s">
         <v>1600</v>
@@ -15601,7 +15601,7 @@
         <v>1500</v>
       </c>
       <c r="E211">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F211" t="s">
         <v>1600</v>
@@ -15636,7 +15636,7 @@
         <v>1500</v>
       </c>
       <c r="E212">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F212" t="s">
         <v>1600</v>
@@ -15671,7 +15671,7 @@
         <v>1500</v>
       </c>
       <c r="E213">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F213" t="s">
         <v>1600</v>
@@ -15706,7 +15706,7 @@
         <v>1500</v>
       </c>
       <c r="E214">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F214" t="s">
         <v>1600</v>
@@ -15741,7 +15741,7 @@
         <v>1501</v>
       </c>
       <c r="E215">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F215" t="s">
         <v>1600</v>
@@ -15776,7 +15776,7 @@
         <v>1501</v>
       </c>
       <c r="E216">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F216" t="s">
         <v>1600</v>
@@ -15811,7 +15811,7 @@
         <v>1502</v>
       </c>
       <c r="E217">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F217" t="s">
         <v>1600</v>
@@ -15846,7 +15846,7 @@
         <v>1502</v>
       </c>
       <c r="E218">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F218" t="s">
         <v>1600</v>
@@ -15881,7 +15881,7 @@
         <v>1503</v>
       </c>
       <c r="E219">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F219" t="s">
         <v>1600</v>
@@ -15916,7 +15916,7 @@
         <v>1503</v>
       </c>
       <c r="E220">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F220" t="s">
         <v>1600</v>
@@ -15951,7 +15951,7 @@
         <v>1504</v>
       </c>
       <c r="E221">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F221" t="s">
         <v>1600</v>
@@ -15986,7 +15986,7 @@
         <v>1505</v>
       </c>
       <c r="E222">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F222" t="s">
         <v>1600</v>
@@ -16021,7 +16021,7 @@
         <v>1505</v>
       </c>
       <c r="E223">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F223" t="s">
         <v>1600</v>
@@ -16056,7 +16056,7 @@
         <v>1506</v>
       </c>
       <c r="E224">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F224" t="s">
         <v>1600</v>
@@ -16091,7 +16091,7 @@
         <v>1506</v>
       </c>
       <c r="E225">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F225" t="s">
         <v>1600</v>
@@ -16126,7 +16126,7 @@
         <v>1507</v>
       </c>
       <c r="E226">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F226" t="s">
         <v>1600</v>
@@ -16161,7 +16161,7 @@
         <v>1508</v>
       </c>
       <c r="E227">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F227" t="s">
         <v>1600</v>
@@ -16196,7 +16196,7 @@
         <v>1508</v>
       </c>
       <c r="E228">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F228" t="s">
         <v>1600</v>
@@ -16231,7 +16231,7 @@
         <v>1508</v>
       </c>
       <c r="E229">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F229" t="s">
         <v>1600</v>
@@ -16266,7 +16266,7 @@
         <v>1509</v>
       </c>
       <c r="E230">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F230" t="s">
         <v>1600</v>
@@ -16301,7 +16301,7 @@
         <v>1509</v>
       </c>
       <c r="E231">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F231" t="s">
         <v>1600</v>
@@ -16336,7 +16336,7 @@
         <v>1510</v>
       </c>
       <c r="E232">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F232" t="s">
         <v>1600</v>
@@ -16371,7 +16371,7 @@
         <v>1511</v>
       </c>
       <c r="E233">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F233" t="s">
         <v>1600</v>
@@ -16406,7 +16406,7 @@
         <v>1511</v>
       </c>
       <c r="E234">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F234" t="s">
         <v>1600</v>
@@ -16441,7 +16441,7 @@
         <v>1511</v>
       </c>
       <c r="E235">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F235" t="s">
         <v>1600</v>
@@ -16476,7 +16476,7 @@
         <v>1512</v>
       </c>
       <c r="E236">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F236" t="s">
         <v>1600</v>
@@ -16511,7 +16511,7 @@
         <v>1512</v>
       </c>
       <c r="E237">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F237" t="s">
         <v>1600</v>
@@ -16546,7 +16546,7 @@
         <v>1513</v>
       </c>
       <c r="E238">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F238" t="s">
         <v>1600</v>
@@ -16581,7 +16581,7 @@
         <v>1513</v>
       </c>
       <c r="E239">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F239" t="s">
         <v>1600</v>
@@ -16616,7 +16616,7 @@
         <v>1513</v>
       </c>
       <c r="E240">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F240" t="s">
         <v>1602</v>
@@ -16651,7 +16651,7 @@
         <v>1513</v>
       </c>
       <c r="E241">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F241" t="s">
         <v>1600</v>
@@ -16686,7 +16686,7 @@
         <v>1514</v>
       </c>
       <c r="E242">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F242" t="s">
         <v>1600</v>
@@ -16721,7 +16721,7 @@
         <v>1514</v>
       </c>
       <c r="E243">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F243" t="s">
         <v>1600</v>
@@ -16759,7 +16759,7 @@
         <v>1514</v>
       </c>
       <c r="E244">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F244" t="s">
         <v>1600</v>
@@ -16794,7 +16794,7 @@
         <v>1514</v>
       </c>
       <c r="E245">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F245" t="s">
         <v>1600</v>
@@ -16829,7 +16829,7 @@
         <v>1514</v>
       </c>
       <c r="E246">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F246" t="s">
         <v>1600</v>
@@ -16864,7 +16864,7 @@
         <v>1514</v>
       </c>
       <c r="E247">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F247" t="s">
         <v>1600</v>
@@ -16899,7 +16899,7 @@
         <v>1515</v>
       </c>
       <c r="E248">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F248" t="s">
         <v>1600</v>
@@ -16934,7 +16934,7 @@
         <v>1515</v>
       </c>
       <c r="E249">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F249" t="s">
         <v>1600</v>
@@ -16969,7 +16969,7 @@
         <v>1515</v>
       </c>
       <c r="E250">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F250" t="s">
         <v>1600</v>
@@ -17004,7 +17004,7 @@
         <v>1516</v>
       </c>
       <c r="E251">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F251" t="s">
         <v>1600</v>
@@ -17039,7 +17039,7 @@
         <v>1516</v>
       </c>
       <c r="E252">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F252" t="s">
         <v>1600</v>
@@ -17074,7 +17074,7 @@
         <v>1516</v>
       </c>
       <c r="E253">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F253" t="s">
         <v>1600</v>
@@ -17109,7 +17109,7 @@
         <v>1516</v>
       </c>
       <c r="E254">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F254" t="s">
         <v>1600</v>
@@ -17144,7 +17144,7 @@
         <v>1517</v>
       </c>
       <c r="E255">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F255" t="s">
         <v>1600</v>
@@ -17179,7 +17179,7 @@
         <v>1517</v>
       </c>
       <c r="E256">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F256" t="s">
         <v>1600</v>
@@ -17214,7 +17214,7 @@
         <v>1517</v>
       </c>
       <c r="E257">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F257" t="s">
         <v>1600</v>
@@ -17249,7 +17249,7 @@
         <v>1517</v>
       </c>
       <c r="E258">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F258" t="s">
         <v>1600</v>
@@ -17284,7 +17284,7 @@
         <v>1517</v>
       </c>
       <c r="E259">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F259" t="s">
         <v>1600</v>
@@ -17319,7 +17319,7 @@
         <v>1518</v>
       </c>
       <c r="E260">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F260" t="s">
         <v>1600</v>
@@ -17354,7 +17354,7 @@
         <v>1518</v>
       </c>
       <c r="E261">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F261" t="s">
         <v>1600</v>
@@ -17389,7 +17389,7 @@
         <v>1518</v>
       </c>
       <c r="E262">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F262" t="s">
         <v>1600</v>
@@ -17424,7 +17424,7 @@
         <v>1518</v>
       </c>
       <c r="E263">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F263" t="s">
         <v>1600</v>
@@ -17459,7 +17459,7 @@
         <v>1518</v>
       </c>
       <c r="E264">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F264" t="s">
         <v>1600</v>
@@ -17494,7 +17494,7 @@
         <v>1518</v>
       </c>
       <c r="E265">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F265" t="s">
         <v>1600</v>
@@ -17529,7 +17529,7 @@
         <v>1519</v>
       </c>
       <c r="E266">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F266" t="s">
         <v>1600</v>
@@ -17564,7 +17564,7 @@
         <v>1520</v>
       </c>
       <c r="E267">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F267" t="s">
         <v>1601</v>
@@ -17599,7 +17599,7 @@
         <v>1520</v>
       </c>
       <c r="E268">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F268" t="s">
         <v>1600</v>
@@ -17634,7 +17634,7 @@
         <v>1520</v>
       </c>
       <c r="E269">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F269" t="s">
         <v>1603</v>
@@ -17669,7 +17669,7 @@
         <v>1520</v>
       </c>
       <c r="E270">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F270" t="s">
         <v>1600</v>
@@ -17704,7 +17704,7 @@
         <v>1520</v>
       </c>
       <c r="E271">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F271" t="s">
         <v>1600</v>
@@ -17739,7 +17739,7 @@
         <v>1520</v>
       </c>
       <c r="E272">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F272" t="s">
         <v>1600</v>
@@ -17774,7 +17774,7 @@
         <v>1521</v>
       </c>
       <c r="E273">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F273" t="s">
         <v>1600</v>
@@ -17809,7 +17809,7 @@
         <v>1521</v>
       </c>
       <c r="E274">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F274" t="s">
         <v>1600</v>
@@ -17844,7 +17844,7 @@
         <v>1521</v>
       </c>
       <c r="E275">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F275" t="s">
         <v>1600</v>
@@ -17879,7 +17879,7 @@
         <v>1521</v>
       </c>
       <c r="E276">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F276" t="s">
         <v>1600</v>
@@ -17914,7 +17914,7 @@
         <v>1522</v>
       </c>
       <c r="E277">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F277" t="s">
         <v>1600</v>
@@ -17949,7 +17949,7 @@
         <v>1522</v>
       </c>
       <c r="E278">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F278" t="s">
         <v>1600</v>
@@ -17984,7 +17984,7 @@
         <v>1523</v>
       </c>
       <c r="E279">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F279" t="s">
         <v>1600</v>
@@ -18022,7 +18022,7 @@
         <v>1523</v>
       </c>
       <c r="E280">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F280" t="s">
         <v>1600</v>
@@ -18057,7 +18057,7 @@
         <v>1524</v>
       </c>
       <c r="E281">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F281" t="s">
         <v>1600</v>
@@ -18092,7 +18092,7 @@
         <v>1524</v>
       </c>
       <c r="E282">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F282" t="s">
         <v>1600</v>
@@ -18127,7 +18127,7 @@
         <v>1524</v>
       </c>
       <c r="E283">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F283" t="s">
         <v>1600</v>
@@ -18162,7 +18162,7 @@
         <v>1524</v>
       </c>
       <c r="E284">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F284" t="s">
         <v>1600</v>
@@ -18200,7 +18200,7 @@
         <v>1524</v>
       </c>
       <c r="E285">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F285" t="s">
         <v>1600</v>
@@ -18235,7 +18235,7 @@
         <v>1524</v>
       </c>
       <c r="E286">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F286" t="s">
         <v>1600</v>
@@ -18270,7 +18270,7 @@
         <v>1525</v>
       </c>
       <c r="E287">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F287" t="s">
         <v>1600</v>
@@ -18305,7 +18305,7 @@
         <v>1525</v>
       </c>
       <c r="E288">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F288" t="s">
         <v>1600</v>
@@ -18340,7 +18340,7 @@
         <v>1526</v>
       </c>
       <c r="E289">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F289" t="s">
         <v>1600</v>
@@ -18375,7 +18375,7 @@
         <v>1526</v>
       </c>
       <c r="E290">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F290" t="s">
         <v>1600</v>
@@ -18410,7 +18410,7 @@
         <v>1527</v>
       </c>
       <c r="E291">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F291" t="s">
         <v>1600</v>
@@ -18445,7 +18445,7 @@
         <v>1527</v>
       </c>
       <c r="E292">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F292" t="s">
         <v>1600</v>
@@ -18480,7 +18480,7 @@
         <v>1527</v>
       </c>
       <c r="E293">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F293" t="s">
         <v>1600</v>
@@ -18515,7 +18515,7 @@
         <v>1527</v>
       </c>
       <c r="E294">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F294" t="s">
         <v>1600</v>
@@ -18550,7 +18550,7 @@
         <v>1528</v>
       </c>
       <c r="E295">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F295" t="s">
         <v>1600</v>
@@ -18585,7 +18585,7 @@
         <v>1528</v>
       </c>
       <c r="E296">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F296" t="s">
         <v>1600</v>
@@ -18620,7 +18620,7 @@
         <v>1528</v>
       </c>
       <c r="E297">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F297" t="s">
         <v>1600</v>
@@ -18655,7 +18655,7 @@
         <v>1528</v>
       </c>
       <c r="E298">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F298" t="s">
         <v>1600</v>
@@ -18690,7 +18690,7 @@
         <v>1529</v>
       </c>
       <c r="E299">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F299" t="s">
         <v>1600</v>
@@ -18725,7 +18725,7 @@
         <v>1529</v>
       </c>
       <c r="E300">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F300" t="s">
         <v>1600</v>
@@ -18760,7 +18760,7 @@
         <v>1530</v>
       </c>
       <c r="E301">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F301" t="s">
         <v>1600</v>
@@ -18795,7 +18795,7 @@
         <v>1530</v>
       </c>
       <c r="E302">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F302" t="s">
         <v>1600</v>
@@ -18830,7 +18830,7 @@
         <v>1530</v>
       </c>
       <c r="E303">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F303" t="s">
         <v>1600</v>
@@ -18865,7 +18865,7 @@
         <v>1530</v>
       </c>
       <c r="E304">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F304" t="s">
         <v>1600</v>
@@ -18900,7 +18900,7 @@
         <v>1530</v>
       </c>
       <c r="E305">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F305" t="s">
         <v>1600</v>
@@ -18935,7 +18935,7 @@
         <v>1531</v>
       </c>
       <c r="E306">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F306" t="s">
         <v>1600</v>
@@ -18970,7 +18970,7 @@
         <v>1531</v>
       </c>
       <c r="E307">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F307" t="s">
         <v>1600</v>
@@ -19005,7 +19005,7 @@
         <v>1531</v>
       </c>
       <c r="E308">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F308" t="s">
         <v>1600</v>
@@ -19040,7 +19040,7 @@
         <v>1532</v>
       </c>
       <c r="E309">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F309" t="s">
         <v>1600</v>
@@ -19075,7 +19075,7 @@
         <v>1532</v>
       </c>
       <c r="E310">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F310" t="s">
         <v>1600</v>
@@ -19110,7 +19110,7 @@
         <v>1533</v>
       </c>
       <c r="E311">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F311" t="s">
         <v>1600</v>
@@ -19145,7 +19145,7 @@
         <v>1533</v>
       </c>
       <c r="E312">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F312" t="s">
         <v>1600</v>
@@ -19180,7 +19180,7 @@
         <v>1533</v>
       </c>
       <c r="E313">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F313" t="s">
         <v>1600</v>
@@ -19215,7 +19215,7 @@
         <v>1533</v>
       </c>
       <c r="E314">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F314" t="s">
         <v>1600</v>
@@ -19250,7 +19250,7 @@
         <v>1533</v>
       </c>
       <c r="E315">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F315" t="s">
         <v>1600</v>
@@ -19285,7 +19285,7 @@
         <v>1533</v>
       </c>
       <c r="E316">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F316" t="s">
         <v>1600</v>
@@ -19320,7 +19320,7 @@
         <v>1533</v>
       </c>
       <c r="E317">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F317" t="s">
         <v>1600</v>
@@ -19355,7 +19355,7 @@
         <v>1533</v>
       </c>
       <c r="E318">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F318" t="s">
         <v>1600</v>
@@ -19390,7 +19390,7 @@
         <v>1534</v>
       </c>
       <c r="E319">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F319" t="s">
         <v>1600</v>
@@ -19425,7 +19425,7 @@
         <v>1534</v>
       </c>
       <c r="E320">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F320" t="s">
         <v>1600</v>
@@ -19460,7 +19460,7 @@
         <v>1534</v>
       </c>
       <c r="E321">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F321" t="s">
         <v>1600</v>
@@ -19495,7 +19495,7 @@
         <v>1535</v>
       </c>
       <c r="E322">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F322" t="s">
         <v>1600</v>
@@ -19530,7 +19530,7 @@
         <v>1536</v>
       </c>
       <c r="E323">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F323" t="s">
         <v>1600</v>
@@ -19565,7 +19565,7 @@
         <v>1537</v>
       </c>
       <c r="E324">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F324" t="s">
         <v>1602</v>
@@ -19600,7 +19600,7 @@
         <v>1537</v>
       </c>
       <c r="E325">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F325" t="s">
         <v>1600</v>
@@ -19635,7 +19635,7 @@
         <v>1537</v>
       </c>
       <c r="E326">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F326" t="s">
         <v>1600</v>
@@ -19670,7 +19670,7 @@
         <v>1537</v>
       </c>
       <c r="E327">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F327" t="s">
         <v>1600</v>
@@ -19705,7 +19705,7 @@
         <v>1537</v>
       </c>
       <c r="E328">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F328" t="s">
         <v>1600</v>
@@ -19740,7 +19740,7 @@
         <v>1537</v>
       </c>
       <c r="E329">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F329" t="s">
         <v>1600</v>
@@ -19775,7 +19775,7 @@
         <v>1538</v>
       </c>
       <c r="E330">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F330" t="s">
         <v>1600</v>
@@ -19810,7 +19810,7 @@
         <v>1538</v>
       </c>
       <c r="E331">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F331" t="s">
         <v>1600</v>
@@ -19845,7 +19845,7 @@
         <v>1539</v>
       </c>
       <c r="E332">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F332" t="s">
         <v>1600</v>
@@ -19880,7 +19880,7 @@
         <v>1539</v>
       </c>
       <c r="E333">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F333" t="s">
         <v>1600</v>
@@ -19915,7 +19915,7 @@
         <v>1539</v>
       </c>
       <c r="E334">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F334" t="s">
         <v>1600</v>
@@ -19950,7 +19950,7 @@
         <v>1540</v>
       </c>
       <c r="E335">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F335" t="s">
         <v>1600</v>
@@ -19985,7 +19985,7 @@
         <v>1541</v>
       </c>
       <c r="E336">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F336" t="s">
         <v>1600</v>
@@ -20020,7 +20020,7 @@
         <v>1542</v>
       </c>
       <c r="E337">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F337" t="s">
         <v>1600</v>
@@ -20055,7 +20055,7 @@
         <v>1542</v>
       </c>
       <c r="E338">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F338" t="s">
         <v>1600</v>
@@ -20090,7 +20090,7 @@
         <v>1543</v>
       </c>
       <c r="E339">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F339" t="s">
         <v>1600</v>
@@ -20125,7 +20125,7 @@
         <v>1543</v>
       </c>
       <c r="E340">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F340" t="s">
         <v>1600</v>
@@ -20160,7 +20160,7 @@
         <v>1543</v>
       </c>
       <c r="E341">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F341" t="s">
         <v>1600</v>
@@ -20195,7 +20195,7 @@
         <v>1544</v>
       </c>
       <c r="E342">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F342" t="s">
         <v>1600</v>
@@ -20230,7 +20230,7 @@
         <v>1544</v>
       </c>
       <c r="E343">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F343" t="s">
         <v>1600</v>
@@ -20265,7 +20265,7 @@
         <v>1544</v>
       </c>
       <c r="E344">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F344" t="s">
         <v>1600</v>
@@ -20300,7 +20300,7 @@
         <v>1544</v>
       </c>
       <c r="E345">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F345" t="s">
         <v>1600</v>
@@ -20335,7 +20335,7 @@
         <v>1544</v>
       </c>
       <c r="E346">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F346" t="s">
         <v>1600</v>
@@ -20370,7 +20370,7 @@
         <v>1544</v>
       </c>
       <c r="E347">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F347" t="s">
         <v>1600</v>
@@ -20405,7 +20405,7 @@
         <v>1544</v>
       </c>
       <c r="E348">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F348" t="s">
         <v>1600</v>
@@ -20440,7 +20440,7 @@
         <v>1544</v>
       </c>
       <c r="E349">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F349" t="s">
         <v>1600</v>
@@ -20475,7 +20475,7 @@
         <v>1544</v>
       </c>
       <c r="E350">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F350" t="s">
         <v>1600</v>
@@ -20510,7 +20510,7 @@
         <v>1545</v>
       </c>
       <c r="E351">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F351" t="s">
         <v>1600</v>
@@ -20545,7 +20545,7 @@
         <v>1545</v>
       </c>
       <c r="E352">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F352" t="s">
         <v>1600</v>
@@ -20580,7 +20580,7 @@
         <v>1545</v>
       </c>
       <c r="E353">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F353" t="s">
         <v>1600</v>
@@ -20615,7 +20615,7 @@
         <v>1545</v>
       </c>
       <c r="E354">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F354" t="s">
         <v>1600</v>
@@ -20650,7 +20650,7 @@
         <v>1546</v>
       </c>
       <c r="E355">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F355" t="s">
         <v>1600</v>
@@ -20685,7 +20685,7 @@
         <v>1547</v>
       </c>
       <c r="E356">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F356" t="s">
         <v>1600</v>
@@ -20720,7 +20720,7 @@
         <v>1547</v>
       </c>
       <c r="E357">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F357" t="s">
         <v>1600</v>
@@ -20755,7 +20755,7 @@
         <v>1547</v>
       </c>
       <c r="E358">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F358" t="s">
         <v>1600</v>
@@ -20790,7 +20790,7 @@
         <v>1547</v>
       </c>
       <c r="E359">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F359" t="s">
         <v>1600</v>
@@ -20825,7 +20825,7 @@
         <v>1547</v>
       </c>
       <c r="E360">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F360" t="s">
         <v>1604</v>
@@ -20863,7 +20863,7 @@
         <v>1547</v>
       </c>
       <c r="E361">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F361" t="s">
         <v>1600</v>
@@ -20898,7 +20898,7 @@
         <v>1547</v>
       </c>
       <c r="E362">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F362" t="s">
         <v>1600</v>
@@ -20933,7 +20933,7 @@
         <v>1548</v>
       </c>
       <c r="E363">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F363" t="s">
         <v>1600</v>
@@ -20968,7 +20968,7 @@
         <v>1548</v>
       </c>
       <c r="E364">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F364" t="s">
         <v>1600</v>
@@ -21003,7 +21003,7 @@
         <v>1548</v>
       </c>
       <c r="E365">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F365" t="s">
         <v>1600</v>
@@ -21038,7 +21038,7 @@
         <v>1548</v>
       </c>
       <c r="E366">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F366" t="s">
         <v>1600</v>
@@ -21076,7 +21076,7 @@
         <v>1548</v>
       </c>
       <c r="E367">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F367" t="s">
         <v>1600</v>
@@ -21111,7 +21111,7 @@
         <v>1548</v>
       </c>
       <c r="E368">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F368" t="s">
         <v>1600</v>
@@ -21146,7 +21146,7 @@
         <v>1548</v>
       </c>
       <c r="E369">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F369" t="s">
         <v>1600</v>
@@ -21181,7 +21181,7 @@
         <v>1548</v>
       </c>
       <c r="E370">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F370" t="s">
         <v>1600</v>
@@ -21216,7 +21216,7 @@
         <v>1548</v>
       </c>
       <c r="E371">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F371" t="s">
         <v>1600</v>
@@ -21251,7 +21251,7 @@
         <v>1549</v>
       </c>
       <c r="E372">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F372" t="s">
         <v>1601</v>
@@ -21286,7 +21286,7 @@
         <v>1550</v>
       </c>
       <c r="E373">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F373" t="s">
         <v>1604</v>
@@ -21321,7 +21321,7 @@
         <v>1551</v>
       </c>
       <c r="E374">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F374" t="s">
         <v>1600</v>
@@ -21356,7 +21356,7 @@
         <v>1552</v>
       </c>
       <c r="E375">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F375" t="s">
         <v>1600</v>
@@ -21391,7 +21391,7 @@
         <v>1552</v>
       </c>
       <c r="E376">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F376" t="s">
         <v>1600</v>
@@ -21426,7 +21426,7 @@
         <v>1553</v>
       </c>
       <c r="E377">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F377" t="s">
         <v>1600</v>
@@ -21461,7 +21461,7 @@
         <v>1554</v>
       </c>
       <c r="E378">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F378" t="s">
         <v>1603</v>
@@ -21496,7 +21496,7 @@
         <v>1554</v>
       </c>
       <c r="E379">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F379" t="s">
         <v>1600</v>
@@ -21531,7 +21531,7 @@
         <v>1554</v>
       </c>
       <c r="E380">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F380" t="s">
         <v>1600</v>
@@ -21566,7 +21566,7 @@
         <v>1554</v>
       </c>
       <c r="E381">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F381" t="s">
         <v>1600</v>
@@ -21601,7 +21601,7 @@
         <v>1554</v>
       </c>
       <c r="E382">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F382" t="s">
         <v>1600</v>
@@ -21636,7 +21636,7 @@
         <v>1554</v>
       </c>
       <c r="E383">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F383" t="s">
         <v>1600</v>
@@ -21671,7 +21671,7 @@
         <v>1555</v>
       </c>
       <c r="E384">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F384" t="s">
         <v>1600</v>
@@ -21706,7 +21706,7 @@
         <v>1555</v>
       </c>
       <c r="E385">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F385" t="s">
         <v>1600</v>
@@ -21741,7 +21741,7 @@
         <v>1555</v>
       </c>
       <c r="E386">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F386" t="s">
         <v>1600</v>
@@ -21776,7 +21776,7 @@
         <v>1556</v>
       </c>
       <c r="E387">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F387" t="s">
         <v>1600</v>
@@ -21811,7 +21811,7 @@
         <v>1556</v>
       </c>
       <c r="E388">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F388" t="s">
         <v>1600</v>
@@ -21846,7 +21846,7 @@
         <v>1556</v>
       </c>
       <c r="E389">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F389" t="s">
         <v>1600</v>
@@ -21884,7 +21884,7 @@
         <v>1556</v>
       </c>
       <c r="E390">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F390" t="s">
         <v>1600</v>
@@ -21919,7 +21919,7 @@
         <v>1557</v>
       </c>
       <c r="E391">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F391" t="s">
         <v>1600</v>
@@ -21954,7 +21954,7 @@
         <v>1557</v>
       </c>
       <c r="E392">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F392" t="s">
         <v>1600</v>
@@ -21989,7 +21989,7 @@
         <v>1557</v>
       </c>
       <c r="E393">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F393" t="s">
         <v>1600</v>
@@ -22024,7 +22024,7 @@
         <v>1557</v>
       </c>
       <c r="E394">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F394" t="s">
         <v>1600</v>
@@ -22059,7 +22059,7 @@
         <v>1557</v>
       </c>
       <c r="E395">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F395" t="s">
         <v>1600</v>
@@ -22094,7 +22094,7 @@
         <v>1558</v>
       </c>
       <c r="E396">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F396" t="s">
         <v>1600</v>
@@ -22129,7 +22129,7 @@
         <v>1558</v>
       </c>
       <c r="E397">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F397" t="s">
         <v>1600</v>
@@ -22164,7 +22164,7 @@
         <v>1559</v>
       </c>
       <c r="E398">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F398" t="s">
         <v>1600</v>
@@ -22199,7 +22199,7 @@
         <v>1559</v>
       </c>
       <c r="E399">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F399" t="s">
         <v>1600</v>
@@ -22234,7 +22234,7 @@
         <v>1559</v>
       </c>
       <c r="E400">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F400" t="s">
         <v>1600</v>
@@ -22269,7 +22269,7 @@
         <v>1559</v>
       </c>
       <c r="E401">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F401" t="s">
         <v>1600</v>
@@ -22304,7 +22304,7 @@
         <v>1559</v>
       </c>
       <c r="E402">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F402" t="s">
         <v>1600</v>
@@ -22339,7 +22339,7 @@
         <v>1559</v>
       </c>
       <c r="E403">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F403" t="s">
         <v>1600</v>
@@ -22374,7 +22374,7 @@
         <v>1559</v>
       </c>
       <c r="E404">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F404" t="s">
         <v>1600</v>
@@ -22409,7 +22409,7 @@
         <v>1559</v>
       </c>
       <c r="E405">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F405" t="s">
         <v>1600</v>
@@ -22444,7 +22444,7 @@
         <v>1559</v>
       </c>
       <c r="E406">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F406" t="s">
         <v>1600</v>
@@ -22479,7 +22479,7 @@
         <v>1559</v>
       </c>
       <c r="E407">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F407" t="s">
         <v>1600</v>
@@ -22514,7 +22514,7 @@
         <v>1560</v>
       </c>
       <c r="E408">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F408" t="s">
         <v>1600</v>
@@ -22549,7 +22549,7 @@
         <v>1560</v>
       </c>
       <c r="E409">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F409" t="s">
         <v>1600</v>
@@ -22584,7 +22584,7 @@
         <v>1560</v>
       </c>
       <c r="E410">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F410" t="s">
         <v>1601</v>
@@ -22619,7 +22619,7 @@
         <v>1561</v>
       </c>
       <c r="E411">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F411" t="s">
         <v>1600</v>
@@ -22654,7 +22654,7 @@
         <v>1561</v>
       </c>
       <c r="E412">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F412" t="s">
         <v>1600</v>
@@ -22689,7 +22689,7 @@
         <v>1561</v>
       </c>
       <c r="E413">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F413" t="s">
         <v>1600</v>
@@ -22724,7 +22724,7 @@
         <v>1561</v>
       </c>
       <c r="E414">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F414" t="s">
         <v>1600</v>
@@ -22759,7 +22759,7 @@
         <v>1561</v>
       </c>
       <c r="E415">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F415" t="s">
         <v>1600</v>
@@ -22794,7 +22794,7 @@
         <v>1561</v>
       </c>
       <c r="E416">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F416" t="s">
         <v>1600</v>
@@ -22829,7 +22829,7 @@
         <v>1561</v>
       </c>
       <c r="E417">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F417" t="s">
         <v>1603</v>
@@ -22864,7 +22864,7 @@
         <v>1562</v>
       </c>
       <c r="E418">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F418" t="s">
         <v>1600</v>
@@ -22899,7 +22899,7 @@
         <v>1562</v>
       </c>
       <c r="E419">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F419" t="s">
         <v>1600</v>
@@ -22934,7 +22934,7 @@
         <v>1562</v>
       </c>
       <c r="E420">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F420" t="s">
         <v>1600</v>
@@ -22969,7 +22969,7 @@
         <v>1562</v>
       </c>
       <c r="E421">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F421" t="s">
         <v>1600</v>
@@ -23004,7 +23004,7 @@
         <v>1563</v>
       </c>
       <c r="E422">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F422" t="s">
         <v>1600</v>
@@ -23039,7 +23039,7 @@
         <v>1563</v>
       </c>
       <c r="E423">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F423" t="s">
         <v>1603</v>
@@ -23074,7 +23074,7 @@
         <v>1563</v>
       </c>
       <c r="E424">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F424" t="s">
         <v>1600</v>
@@ -23109,7 +23109,7 @@
         <v>1563</v>
       </c>
       <c r="E425">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F425" t="s">
         <v>1600</v>
@@ -23144,7 +23144,7 @@
         <v>1563</v>
       </c>
       <c r="E426">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F426" t="s">
         <v>1600</v>
@@ -23179,7 +23179,7 @@
         <v>1563</v>
       </c>
       <c r="E427">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F427" t="s">
         <v>1600</v>
@@ -23214,7 +23214,7 @@
         <v>1563</v>
       </c>
       <c r="E428">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F428" t="s">
         <v>1604</v>
@@ -23249,7 +23249,7 @@
         <v>1563</v>
       </c>
       <c r="E429">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F429" t="s">
         <v>1600</v>
@@ -23284,7 +23284,7 @@
         <v>1563</v>
       </c>
       <c r="E430">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F430" t="s">
         <v>1600</v>
@@ -23319,7 +23319,7 @@
         <v>1564</v>
       </c>
       <c r="E431">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F431" t="s">
         <v>1600</v>
@@ -23354,7 +23354,7 @@
         <v>1564</v>
       </c>
       <c r="E432">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F432" t="s">
         <v>1600</v>
@@ -23389,7 +23389,7 @@
         <v>1564</v>
       </c>
       <c r="E433">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F433" t="s">
         <v>1600</v>
@@ -23424,7 +23424,7 @@
         <v>1564</v>
       </c>
       <c r="E434">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F434" t="s">
         <v>1600</v>
@@ -23459,7 +23459,7 @@
         <v>1564</v>
       </c>
       <c r="E435">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F435" t="s">
         <v>1602</v>
@@ -23494,7 +23494,7 @@
         <v>1564</v>
       </c>
       <c r="E436">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F436" t="s">
         <v>1600</v>
@@ -23529,7 +23529,7 @@
         <v>1564</v>
       </c>
       <c r="E437">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F437" t="s">
         <v>1600</v>
@@ -23564,7 +23564,7 @@
         <v>1565</v>
       </c>
       <c r="E438">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F438" t="s">
         <v>1600</v>
@@ -23599,7 +23599,7 @@
         <v>1565</v>
       </c>
       <c r="E439">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F439" t="s">
         <v>1600</v>
@@ -23634,7 +23634,7 @@
         <v>1565</v>
       </c>
       <c r="E440">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F440" t="s">
         <v>1600</v>
@@ -23669,7 +23669,7 @@
         <v>1565</v>
       </c>
       <c r="E441">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F441" t="s">
         <v>1600</v>
@@ -23704,7 +23704,7 @@
         <v>1565</v>
       </c>
       <c r="E442">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F442" t="s">
         <v>1600</v>
@@ -23739,7 +23739,7 @@
         <v>1566</v>
       </c>
       <c r="E443">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F443" t="s">
         <v>1600</v>
@@ -23774,7 +23774,7 @@
         <v>1566</v>
       </c>
       <c r="E444">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F444" t="s">
         <v>1600</v>
@@ -23809,7 +23809,7 @@
         <v>1566</v>
       </c>
       <c r="E445">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F445" t="s">
         <v>1600</v>
@@ -23844,7 +23844,7 @@
         <v>1566</v>
       </c>
       <c r="E446">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F446" t="s">
         <v>1600</v>
@@ -23879,7 +23879,7 @@
         <v>1566</v>
       </c>
       <c r="E447">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F447" t="s">
         <v>1600</v>
@@ -23917,7 +23917,7 @@
         <v>1567</v>
       </c>
       <c r="E448">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F448" t="s">
         <v>1600</v>
@@ -23952,7 +23952,7 @@
         <v>1567</v>
       </c>
       <c r="E449">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F449" t="s">
         <v>1600</v>
@@ -23987,7 +23987,7 @@
         <v>1567</v>
       </c>
       <c r="E450">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F450" t="s">
         <v>1600</v>
@@ -24022,7 +24022,7 @@
         <v>1567</v>
       </c>
       <c r="E451">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F451" t="s">
         <v>1600</v>
@@ -24057,7 +24057,7 @@
         <v>1567</v>
       </c>
       <c r="E452">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F452" t="s">
         <v>1600</v>
@@ -24092,7 +24092,7 @@
         <v>1567</v>
       </c>
       <c r="E453">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F453" t="s">
         <v>1600</v>
@@ -24127,7 +24127,7 @@
         <v>1568</v>
       </c>
       <c r="E454">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F454" t="s">
         <v>1600</v>
@@ -24162,7 +24162,7 @@
         <v>1568</v>
       </c>
       <c r="E455">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F455" t="s">
         <v>1600</v>
@@ -24197,7 +24197,7 @@
         <v>1568</v>
       </c>
       <c r="E456">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F456" t="s">
         <v>1600</v>
@@ -24232,7 +24232,7 @@
         <v>1569</v>
       </c>
       <c r="E457">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F457" t="s">
         <v>1600</v>
@@ -24267,7 +24267,7 @@
         <v>1570</v>
       </c>
       <c r="E458">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F458" t="s">
         <v>1600</v>
@@ -24302,7 +24302,7 @@
         <v>1570</v>
       </c>
       <c r="E459">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F459" t="s">
         <v>1600</v>
@@ -24337,7 +24337,7 @@
         <v>1570</v>
       </c>
       <c r="E460">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F460" t="s">
         <v>1602</v>
@@ -24375,7 +24375,7 @@
         <v>1570</v>
       </c>
       <c r="E461">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F461" t="s">
         <v>1600</v>
@@ -24410,7 +24410,7 @@
         <v>1570</v>
       </c>
       <c r="E462">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F462" t="s">
         <v>1600</v>
@@ -24445,7 +24445,7 @@
         <v>1571</v>
       </c>
       <c r="E463">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F463" t="s">
         <v>1600</v>
@@ -24480,7 +24480,7 @@
         <v>1571</v>
       </c>
       <c r="E464">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F464" t="s">
         <v>1600</v>
@@ -24515,7 +24515,7 @@
         <v>1571</v>
       </c>
       <c r="E465">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F465" t="s">
         <v>1600</v>
@@ -24550,7 +24550,7 @@
         <v>1571</v>
       </c>
       <c r="E466">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F466" t="s">
         <v>1600</v>
@@ -24585,7 +24585,7 @@
         <v>1572</v>
       </c>
       <c r="E467">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F467" t="s">
         <v>1600</v>
@@ -24620,7 +24620,7 @@
         <v>1572</v>
       </c>
       <c r="E468">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F468" t="s">
         <v>1600</v>
@@ -24655,7 +24655,7 @@
         <v>1572</v>
       </c>
       <c r="E469">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F469" t="s">
         <v>1600</v>
@@ -24690,7 +24690,7 @@
         <v>1572</v>
       </c>
       <c r="E470">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F470" t="s">
         <v>1600</v>
@@ -24725,7 +24725,7 @@
         <v>1572</v>
       </c>
       <c r="E471">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F471" t="s">
         <v>1600</v>
@@ -24760,7 +24760,7 @@
         <v>1572</v>
       </c>
       <c r="E472">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F472" t="s">
         <v>1600</v>
@@ -24795,7 +24795,7 @@
         <v>1572</v>
       </c>
       <c r="E473">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F473" t="s">
         <v>1600</v>
@@ -24830,7 +24830,7 @@
         <v>1572</v>
       </c>
       <c r="E474">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F474" t="s">
         <v>1600</v>
@@ -24865,7 +24865,7 @@
         <v>1573</v>
       </c>
       <c r="E475">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F475" t="s">
         <v>1600</v>
@@ -24900,7 +24900,7 @@
         <v>1573</v>
       </c>
       <c r="E476">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F476" t="s">
         <v>1600</v>
@@ -24935,7 +24935,7 @@
         <v>1574</v>
       </c>
       <c r="E477">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F477" t="s">
         <v>1600</v>
@@ -24970,7 +24970,7 @@
         <v>1574</v>
       </c>
       <c r="E478">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F478" t="s">
         <v>1600</v>
@@ -25005,7 +25005,7 @@
         <v>1574</v>
       </c>
       <c r="E479">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F479" t="s">
         <v>1600</v>
@@ -25040,7 +25040,7 @@
         <v>1574</v>
       </c>
       <c r="E480">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F480" t="s">
         <v>1604</v>
@@ -25078,7 +25078,7 @@
         <v>1574</v>
       </c>
       <c r="E481">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F481" t="s">
         <v>1600</v>
@@ -25113,7 +25113,7 @@
         <v>1574</v>
       </c>
       <c r="E482">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F482" t="s">
         <v>1604</v>
@@ -25148,7 +25148,7 @@
         <v>1575</v>
       </c>
       <c r="E483">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F483" t="s">
         <v>1600</v>
@@ -25183,7 +25183,7 @@
         <v>1576</v>
       </c>
       <c r="E484">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F484" t="s">
         <v>1600</v>
@@ -25218,7 +25218,7 @@
         <v>1576</v>
       </c>
       <c r="E485">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F485" t="s">
         <v>1600</v>
@@ -25253,7 +25253,7 @@
         <v>1576</v>
       </c>
       <c r="E486">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F486" t="s">
         <v>1600</v>
@@ -25288,7 +25288,7 @@
         <v>1576</v>
       </c>
       <c r="E487">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F487" t="s">
         <v>1600</v>
@@ -25323,7 +25323,7 @@
         <v>1577</v>
       </c>
       <c r="E488">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F488" t="s">
         <v>1600</v>
@@ -25358,7 +25358,7 @@
         <v>1577</v>
       </c>
       <c r="E489">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F489" t="s">
         <v>1604</v>
@@ -25393,7 +25393,7 @@
         <v>1577</v>
       </c>
       <c r="E490">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F490" t="s">
         <v>1600</v>
@@ -25428,7 +25428,7 @@
         <v>1577</v>
       </c>
       <c r="E491">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F491" t="s">
         <v>1600</v>
@@ -25463,7 +25463,7 @@
         <v>1577</v>
       </c>
       <c r="E492">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F492" t="s">
         <v>1600</v>
@@ -25498,7 +25498,7 @@
         <v>1578</v>
       </c>
       <c r="E493">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F493" t="s">
         <v>1600</v>
@@ -25533,7 +25533,7 @@
         <v>1578</v>
       </c>
       <c r="E494">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F494" t="s">
         <v>1602</v>
@@ -25568,7 +25568,7 @@
         <v>1578</v>
       </c>
       <c r="E495">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F495" t="s">
         <v>1600</v>
@@ -25603,7 +25603,7 @@
         <v>1578</v>
       </c>
       <c r="E496">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F496" t="s">
         <v>1600</v>
@@ -25638,7 +25638,7 @@
         <v>1579</v>
       </c>
       <c r="E497">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F497" t="s">
         <v>1600</v>
@@ -25673,7 +25673,7 @@
         <v>1579</v>
       </c>
       <c r="E498">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F498" t="s">
         <v>1600</v>
@@ -25708,7 +25708,7 @@
         <v>1579</v>
       </c>
       <c r="E499">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F499" t="s">
         <v>1600</v>
@@ -25743,7 +25743,7 @@
         <v>1579</v>
       </c>
       <c r="E500">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F500" t="s">
         <v>1600</v>
@@ -25778,7 +25778,7 @@
         <v>1579</v>
       </c>
       <c r="E501">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F501" t="s">
         <v>1600</v>
@@ -25813,7 +25813,7 @@
         <v>1579</v>
       </c>
       <c r="E502">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F502" t="s">
         <v>1600</v>
@@ -25848,7 +25848,7 @@
         <v>1580</v>
       </c>
       <c r="E503">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F503" t="s">
         <v>1600</v>
@@ -25883,7 +25883,7 @@
         <v>1580</v>
       </c>
       <c r="E504">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F504" t="s">
         <v>1600</v>
@@ -25918,7 +25918,7 @@
         <v>1580</v>
       </c>
       <c r="E505">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F505" t="s">
         <v>1600</v>
@@ -25953,7 +25953,7 @@
         <v>1580</v>
       </c>
       <c r="E506">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F506" t="s">
         <v>1600</v>
@@ -25988,7 +25988,7 @@
         <v>1580</v>
       </c>
       <c r="E507">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F507" t="s">
         <v>1600</v>
@@ -26023,7 +26023,7 @@
         <v>1580</v>
       </c>
       <c r="E508">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F508" t="s">
         <v>1600</v>
@@ -26058,7 +26058,7 @@
         <v>1580</v>
       </c>
       <c r="E509">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F509" t="s">
         <v>1600</v>
@@ -26093,7 +26093,7 @@
         <v>1580</v>
       </c>
       <c r="E510">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F510" t="s">
         <v>1600</v>
@@ -26128,7 +26128,7 @@
         <v>1580</v>
       </c>
       <c r="E511">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F511" t="s">
         <v>1600</v>
@@ -26163,7 +26163,7 @@
         <v>1580</v>
       </c>
       <c r="E512">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F512" t="s">
         <v>1600</v>
@@ -26198,7 +26198,7 @@
         <v>1580</v>
       </c>
       <c r="E513">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F513" t="s">
         <v>1600</v>
@@ -26233,7 +26233,7 @@
         <v>1580</v>
       </c>
       <c r="E514">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F514" t="s">
         <v>1600</v>
@@ -26268,7 +26268,7 @@
         <v>1580</v>
       </c>
       <c r="E515">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F515" t="s">
         <v>1600</v>
@@ -26303,7 +26303,7 @@
         <v>1580</v>
       </c>
       <c r="E516">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F516" t="s">
         <v>1600</v>
@@ -26338,7 +26338,7 @@
         <v>1580</v>
       </c>
       <c r="E517">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F517" t="s">
         <v>1600</v>
@@ -26373,7 +26373,7 @@
         <v>1580</v>
       </c>
       <c r="E518">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F518" t="s">
         <v>1600</v>
@@ -26408,7 +26408,7 @@
         <v>1580</v>
       </c>
       <c r="E519">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F519" t="s">
         <v>1600</v>
@@ -26443,7 +26443,7 @@
         <v>1580</v>
       </c>
       <c r="E520">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F520" t="s">
         <v>1600</v>
@@ -26478,7 +26478,7 @@
         <v>1580</v>
       </c>
       <c r="E521">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F521" t="s">
         <v>1600</v>
@@ -26513,7 +26513,7 @@
         <v>1580</v>
       </c>
       <c r="E522">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F522" t="s">
         <v>1600</v>
@@ -26548,7 +26548,7 @@
         <v>1580</v>
       </c>
       <c r="E523">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F523" t="s">
         <v>1600</v>
@@ -26583,7 +26583,7 @@
         <v>1580</v>
       </c>
       <c r="E524">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F524" t="s">
         <v>1600</v>
@@ -26618,7 +26618,7 @@
         <v>1580</v>
       </c>
       <c r="E525">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F525" t="s">
         <v>1600</v>
@@ -26653,7 +26653,7 @@
         <v>1580</v>
       </c>
       <c r="E526">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F526" t="s">
         <v>1600</v>
@@ -26688,7 +26688,7 @@
         <v>1580</v>
       </c>
       <c r="E527">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F527" t="s">
         <v>1600</v>
@@ -26723,7 +26723,7 @@
         <v>1580</v>
       </c>
       <c r="E528">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F528" t="s">
         <v>1600</v>
@@ -26758,7 +26758,7 @@
         <v>1581</v>
       </c>
       <c r="E529">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F529" t="s">
         <v>1600</v>
@@ -26793,7 +26793,7 @@
         <v>1581</v>
       </c>
       <c r="E530">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F530" t="s">
         <v>1600</v>
@@ -26828,7 +26828,7 @@
         <v>1581</v>
       </c>
       <c r="E531">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F531" t="s">
         <v>1600</v>
@@ -26863,7 +26863,7 @@
         <v>1581</v>
       </c>
       <c r="E532">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F532" t="s">
         <v>1600</v>
@@ -26898,7 +26898,7 @@
         <v>1581</v>
       </c>
       <c r="E533">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F533" t="s">
         <v>1600</v>
@@ -26933,7 +26933,7 @@
         <v>1581</v>
       </c>
       <c r="E534">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F534" t="s">
         <v>1600</v>
@@ -26968,7 +26968,7 @@
         <v>1581</v>
       </c>
       <c r="E535">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F535" t="s">
         <v>1604</v>
@@ -27003,7 +27003,7 @@
         <v>1581</v>
       </c>
       <c r="E536">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F536" t="s">
         <v>1600</v>
@@ -27038,7 +27038,7 @@
         <v>1582</v>
       </c>
       <c r="E537">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F537" t="s">
         <v>1600</v>
@@ -27073,7 +27073,7 @@
         <v>1583</v>
       </c>
       <c r="E538">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F538" t="s">
         <v>1600</v>
@@ -27108,7 +27108,7 @@
         <v>1583</v>
       </c>
       <c r="E539">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F539" t="s">
         <v>1602</v>
@@ -27146,7 +27146,7 @@
         <v>1584</v>
       </c>
       <c r="E540">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F540" t="s">
         <v>1602</v>
@@ -27184,7 +27184,7 @@
         <v>1584</v>
       </c>
       <c r="E541">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F541" t="s">
         <v>1600</v>
@@ -27219,7 +27219,7 @@
         <v>1584</v>
       </c>
       <c r="E542">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F542" t="s">
         <v>1602</v>
@@ -27257,7 +27257,7 @@
         <v>1584</v>
       </c>
       <c r="E543">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F543" t="s">
         <v>1600</v>
@@ -27292,7 +27292,7 @@
         <v>1584</v>
       </c>
       <c r="E544">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F544" t="s">
         <v>1600</v>
@@ -27327,7 +27327,7 @@
         <v>1584</v>
       </c>
       <c r="E545">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F545" t="s">
         <v>1600</v>
@@ -27362,7 +27362,7 @@
         <v>1584</v>
       </c>
       <c r="E546">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F546" t="s">
         <v>1600</v>
@@ -27397,7 +27397,7 @@
         <v>1584</v>
       </c>
       <c r="E547">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F547" t="s">
         <v>1600</v>
@@ -27432,7 +27432,7 @@
         <v>1585</v>
       </c>
       <c r="E548">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F548" t="s">
         <v>1600</v>
@@ -27470,7 +27470,7 @@
         <v>1585</v>
       </c>
       <c r="E549">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F549" t="s">
         <v>1604</v>
@@ -27505,7 +27505,7 @@
         <v>1585</v>
       </c>
       <c r="E550">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F550" t="s">
         <v>1602</v>
@@ -27540,7 +27540,7 @@
         <v>1585</v>
       </c>
       <c r="E551">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F551" t="s">
         <v>1600</v>
@@ -27575,7 +27575,7 @@
         <v>1585</v>
       </c>
       <c r="E552">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F552" t="s">
         <v>1600</v>
@@ -27610,7 +27610,7 @@
         <v>1585</v>
       </c>
       <c r="E553">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F553" t="s">
         <v>1600</v>
@@ -27645,7 +27645,7 @@
         <v>1585</v>
       </c>
       <c r="E554">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F554" t="s">
         <v>1600</v>
@@ -27680,7 +27680,7 @@
         <v>1585</v>
       </c>
       <c r="E555">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F555" t="s">
         <v>1600</v>
@@ -27715,7 +27715,7 @@
         <v>1585</v>
       </c>
       <c r="E556">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F556" t="s">
         <v>1600</v>
@@ -27750,7 +27750,7 @@
         <v>1586</v>
       </c>
       <c r="E557">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F557" t="s">
         <v>1600</v>
@@ -27788,7 +27788,7 @@
         <v>1586</v>
       </c>
       <c r="E558">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F558" t="s">
         <v>1600</v>
@@ -27823,7 +27823,7 @@
         <v>1587</v>
       </c>
       <c r="E559">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F559" t="s">
         <v>1600</v>
@@ -27858,7 +27858,7 @@
         <v>1587</v>
       </c>
       <c r="E560">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F560" t="s">
         <v>1602</v>
@@ -27896,7 +27896,7 @@
         <v>1587</v>
       </c>
       <c r="E561">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F561" t="s">
         <v>1600</v>
@@ -27931,7 +27931,7 @@
         <v>1587</v>
       </c>
       <c r="E562">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F562" t="s">
         <v>1600</v>
@@ -27966,7 +27966,7 @@
         <v>1587</v>
       </c>
       <c r="E563">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F563" t="s">
         <v>1600</v>
@@ -28001,7 +28001,7 @@
         <v>1587</v>
       </c>
       <c r="E564">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F564" t="s">
         <v>1600</v>
@@ -28036,7 +28036,7 @@
         <v>1587</v>
       </c>
       <c r="E565">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F565" t="s">
         <v>1600</v>
@@ -28071,7 +28071,7 @@
         <v>1587</v>
       </c>
       <c r="E566">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F566" t="s">
         <v>1600</v>
@@ -28106,7 +28106,7 @@
         <v>1588</v>
       </c>
       <c r="E567">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F567" t="s">
         <v>1600</v>
@@ -28141,7 +28141,7 @@
         <v>1588</v>
       </c>
       <c r="E568">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F568" t="s">
         <v>1600</v>
@@ -28176,7 +28176,7 @@
         <v>1588</v>
       </c>
       <c r="E569">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F569" t="s">
         <v>1600</v>
@@ -28211,7 +28211,7 @@
         <v>1588</v>
       </c>
       <c r="E570">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F570" t="s">
         <v>1600</v>
@@ -28246,7 +28246,7 @@
         <v>1588</v>
       </c>
       <c r="E571">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F571" t="s">
         <v>1602</v>
@@ -28284,7 +28284,7 @@
         <v>1588</v>
       </c>
       <c r="E572">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F572" t="s">
         <v>1600</v>
@@ -28319,7 +28319,7 @@
         <v>1588</v>
       </c>
       <c r="E573">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F573" t="s">
         <v>1600</v>
@@ -28354,7 +28354,7 @@
         <v>1588</v>
       </c>
       <c r="E574">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F574" t="s">
         <v>1600</v>
@@ -28389,7 +28389,7 @@
         <v>1588</v>
       </c>
       <c r="E575">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F575" t="s">
         <v>1600</v>
@@ -28424,7 +28424,7 @@
         <v>1588</v>
       </c>
       <c r="E576">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F576" t="s">
         <v>1602</v>
@@ -28459,7 +28459,7 @@
         <v>1588</v>
       </c>
       <c r="E577">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F577" t="s">
         <v>1600</v>
@@ -28494,7 +28494,7 @@
         <v>1588</v>
       </c>
       <c r="E578">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F578" t="s">
         <v>1604</v>
@@ -28529,7 +28529,7 @@
         <v>1588</v>
       </c>
       <c r="E579">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F579" t="s">
         <v>1600</v>
@@ -28564,7 +28564,7 @@
         <v>1589</v>
       </c>
       <c r="E580">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F580" t="s">
         <v>1600</v>
@@ -28599,7 +28599,7 @@
         <v>1589</v>
       </c>
       <c r="E581">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F581" t="s">
         <v>1600</v>
@@ -28634,7 +28634,7 @@
         <v>1589</v>
       </c>
       <c r="E582">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F582" t="s">
         <v>1600</v>
@@ -28669,7 +28669,7 @@
         <v>1589</v>
       </c>
       <c r="E583">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F583" t="s">
         <v>1600</v>
@@ -28704,7 +28704,7 @@
         <v>1589</v>
       </c>
       <c r="E584">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F584" t="s">
         <v>1600</v>
@@ -28739,7 +28739,7 @@
         <v>1589</v>
       </c>
       <c r="E585">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F585" t="s">
         <v>1600</v>
@@ -28774,7 +28774,7 @@
         <v>1589</v>
       </c>
       <c r="E586">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F586" t="s">
         <v>1600</v>
@@ -28809,7 +28809,7 @@
         <v>1589</v>
       </c>
       <c r="E587">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F587" t="s">
         <v>1600</v>
@@ -28847,7 +28847,7 @@
         <v>1589</v>
       </c>
       <c r="E588">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F588" t="s">
         <v>1602</v>
@@ -28885,7 +28885,7 @@
         <v>1589</v>
       </c>
       <c r="E589">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F589" t="s">
         <v>1602</v>
@@ -28920,7 +28920,7 @@
         <v>1589</v>
       </c>
       <c r="E590">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F590" t="s">
         <v>1602</v>
@@ -28955,7 +28955,7 @@
         <v>1589</v>
       </c>
       <c r="E591">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F591" t="s">
         <v>1600</v>
@@ -28990,7 +28990,7 @@
         <v>1590</v>
       </c>
       <c r="E592">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F592" t="s">
         <v>1600</v>
@@ -29025,7 +29025,7 @@
         <v>1590</v>
       </c>
       <c r="E593">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F593" t="s">
         <v>1600</v>
@@ -29060,7 +29060,7 @@
         <v>1590</v>
       </c>
       <c r="E594">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F594" t="s">
         <v>1600</v>
@@ -29095,7 +29095,7 @@
         <v>1590</v>
       </c>
       <c r="E595">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F595" t="s">
         <v>1600</v>
@@ -29130,7 +29130,7 @@
         <v>1590</v>
       </c>
       <c r="E596">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F596" t="s">
         <v>1600</v>
@@ -29165,7 +29165,7 @@
         <v>1590</v>
       </c>
       <c r="E597">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F597" t="s">
         <v>1600</v>
@@ -29200,7 +29200,7 @@
         <v>1590</v>
       </c>
       <c r="E598">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F598" t="s">
         <v>1600</v>
@@ -29235,7 +29235,7 @@
         <v>1590</v>
       </c>
       <c r="E599">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F599" t="s">
         <v>1600</v>
@@ -29270,7 +29270,7 @@
         <v>1590</v>
       </c>
       <c r="E600">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F600" t="s">
         <v>1600</v>
@@ -29305,7 +29305,7 @@
         <v>1590</v>
       </c>
       <c r="E601">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F601" t="s">
         <v>1600</v>
@@ -29343,7 +29343,7 @@
         <v>1591</v>
       </c>
       <c r="E602">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F602" t="s">
         <v>1600</v>
@@ -29378,7 +29378,7 @@
         <v>1591</v>
       </c>
       <c r="E603">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F603" t="s">
         <v>1600</v>
@@ -29413,7 +29413,7 @@
         <v>1592</v>
       </c>
       <c r="E604">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F604" t="s">
         <v>1600</v>
@@ -29451,7 +29451,7 @@
         <v>1592</v>
       </c>
       <c r="E605">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F605" t="s">
         <v>1600</v>
@@ -29486,7 +29486,7 @@
         <v>1592</v>
       </c>
       <c r="E606">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F606" t="s">
         <v>1600</v>
@@ -29521,7 +29521,7 @@
         <v>1592</v>
       </c>
       <c r="E607">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F607" t="s">
         <v>1602</v>
@@ -29559,7 +29559,7 @@
         <v>1592</v>
       </c>
       <c r="E608">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F608" t="s">
         <v>1602</v>
@@ -29597,7 +29597,7 @@
         <v>1592</v>
       </c>
       <c r="E609">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F609" t="s">
         <v>1600</v>
@@ -29632,7 +29632,7 @@
         <v>1592</v>
       </c>
       <c r="E610">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F610" t="s">
         <v>1600</v>
@@ -29667,7 +29667,7 @@
         <v>1592</v>
       </c>
       <c r="E611">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F611" t="s">
         <v>1600</v>
@@ -29702,7 +29702,7 @@
         <v>1593</v>
       </c>
       <c r="E612">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F612" t="s">
         <v>1600</v>
@@ -29737,7 +29737,7 @@
         <v>1593</v>
       </c>
       <c r="E613">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F613" t="s">
         <v>1600</v>
@@ -29772,7 +29772,7 @@
         <v>1593</v>
       </c>
       <c r="E614">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F614" t="s">
         <v>1600</v>
@@ -29807,7 +29807,7 @@
         <v>1593</v>
       </c>
       <c r="E615">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F615" t="s">
         <v>1600</v>
@@ -29842,7 +29842,7 @@
         <v>1593</v>
       </c>
       <c r="E616">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F616" t="s">
         <v>1600</v>
@@ -29877,7 +29877,7 @@
         <v>1593</v>
       </c>
       <c r="E617">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F617" t="s">
         <v>1600</v>
@@ -29912,7 +29912,7 @@
         <v>1593</v>
       </c>
       <c r="E618">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F618" t="s">
         <v>1600</v>
@@ -29947,7 +29947,7 @@
         <v>1593</v>
       </c>
       <c r="E619">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F619" t="s">
         <v>1600</v>
@@ -29982,7 +29982,7 @@
         <v>1593</v>
       </c>
       <c r="E620">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F620" t="s">
         <v>1600</v>
@@ -30017,7 +30017,7 @@
         <v>1593</v>
       </c>
       <c r="E621">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F621" t="s">
         <v>1600</v>
@@ -30052,7 +30052,7 @@
         <v>1593</v>
       </c>
       <c r="E622">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F622" t="s">
         <v>1600</v>
@@ -30087,7 +30087,7 @@
         <v>1593</v>
       </c>
       <c r="E623">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F623" t="s">
         <v>1602</v>
@@ -30125,7 +30125,7 @@
         <v>1593</v>
       </c>
       <c r="E624">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F624" t="s">
         <v>1600</v>
@@ -30163,7 +30163,7 @@
         <v>1593</v>
       </c>
       <c r="E625">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F625" t="s">
         <v>1602</v>
@@ -30201,7 +30201,7 @@
         <v>1593</v>
       </c>
       <c r="E626">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F626" t="s">
         <v>1600</v>
@@ -30236,7 +30236,7 @@
         <v>1594</v>
       </c>
       <c r="E627">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F627" t="s">
         <v>1600</v>
@@ -30271,7 +30271,7 @@
         <v>1594</v>
       </c>
       <c r="E628">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F628" t="s">
         <v>1602</v>
@@ -30309,7 +30309,7 @@
         <v>1594</v>
       </c>
       <c r="E629">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F629" t="s">
         <v>1600</v>
@@ -30344,7 +30344,7 @@
         <v>1594</v>
       </c>
       <c r="E630">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F630" t="s">
         <v>1600</v>
@@ -30379,7 +30379,7 @@
         <v>1595</v>
       </c>
       <c r="E631">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F631" t="s">
         <v>1600</v>
@@ -30414,7 +30414,7 @@
         <v>1595</v>
       </c>
       <c r="E632">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F632" t="s">
         <v>1600</v>
@@ -30449,7 +30449,7 @@
         <v>1595</v>
       </c>
       <c r="E633">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F633" t="s">
         <v>1600</v>
@@ -30484,7 +30484,7 @@
         <v>1595</v>
       </c>
       <c r="E634">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F634" t="s">
         <v>1600</v>
@@ -30519,7 +30519,7 @@
         <v>1595</v>
       </c>
       <c r="E635">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F635" t="s">
         <v>1602</v>
@@ -30557,7 +30557,7 @@
         <v>1595</v>
       </c>
       <c r="E636">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F636" t="s">
         <v>1602</v>
@@ -30595,7 +30595,7 @@
         <v>1595</v>
       </c>
       <c r="E637">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F637" t="s">
         <v>1600</v>
@@ -30630,7 +30630,7 @@
         <v>1595</v>
       </c>
       <c r="E638">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F638" t="s">
         <v>1600</v>
@@ -30665,7 +30665,7 @@
         <v>1595</v>
       </c>
       <c r="E639">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F639" t="s">
         <v>1600</v>
@@ -30700,7 +30700,7 @@
         <v>1595</v>
       </c>
       <c r="E640">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F640" t="s">
         <v>1600</v>
@@ -30735,7 +30735,7 @@
         <v>1595</v>
       </c>
       <c r="E641">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F641" t="s">
         <v>1600</v>
@@ -30770,7 +30770,7 @@
         <v>1595</v>
       </c>
       <c r="E642">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F642" t="s">
         <v>1600</v>
@@ -30805,7 +30805,7 @@
         <v>1595</v>
       </c>
       <c r="E643">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F643" t="s">
         <v>1600</v>
@@ -30840,7 +30840,7 @@
         <v>1596</v>
       </c>
       <c r="E644">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F644" t="s">
         <v>1604</v>
@@ -30875,7 +30875,7 @@
         <v>1596</v>
       </c>
       <c r="E645">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F645" t="s">
         <v>1600</v>
@@ -30910,7 +30910,7 @@
         <v>1596</v>
       </c>
       <c r="E646">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F646" t="s">
         <v>1600</v>
@@ -30945,7 +30945,7 @@
         <v>1596</v>
       </c>
       <c r="E647">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F647" t="s">
         <v>1600</v>
@@ -30980,7 +30980,7 @@
         <v>1596</v>
       </c>
       <c r="E648">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F648" t="s">
         <v>1600</v>
@@ -31015,7 +31015,7 @@
         <v>1596</v>
       </c>
       <c r="E649">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F649" t="s">
         <v>1602</v>
@@ -31050,7 +31050,7 @@
         <v>1596</v>
       </c>
       <c r="E650">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F650" t="s">
         <v>1600</v>
@@ -31085,7 +31085,7 @@
         <v>1596</v>
       </c>
       <c r="E651">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F651" t="s">
         <v>1600</v>
@@ -31120,7 +31120,7 @@
         <v>1597</v>
       </c>
       <c r="E652">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F652" t="s">
         <v>1600</v>
@@ -31155,7 +31155,7 @@
         <v>1597</v>
       </c>
       <c r="E653">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F653" t="s">
         <v>1600</v>
@@ -31193,7 +31193,7 @@
         <v>1597</v>
       </c>
       <c r="E654">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F654" t="s">
         <v>1600</v>
@@ -31228,7 +31228,7 @@
         <v>1597</v>
       </c>
       <c r="E655">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F655" t="s">
         <v>1600</v>
@@ -31263,7 +31263,7 @@
         <v>1597</v>
       </c>
       <c r="E656">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F656" t="s">
         <v>1600</v>
@@ -31298,7 +31298,7 @@
         <v>1597</v>
       </c>
       <c r="E657">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F657" t="s">
         <v>1602</v>
@@ -31336,7 +31336,7 @@
         <v>1598</v>
       </c>
       <c r="E658">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F658" t="s">
         <v>1600</v>
@@ -31371,7 +31371,7 @@
         <v>1598</v>
       </c>
       <c r="E659">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F659" t="s">
         <v>1600</v>
@@ -31409,7 +31409,7 @@
         <v>1598</v>
       </c>
       <c r="E660">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F660" t="s">
         <v>1600</v>
@@ -31447,7 +31447,7 @@
         <v>1598</v>
       </c>
       <c r="E661">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F661" t="s">
         <v>1600</v>
@@ -31482,7 +31482,7 @@
         <v>1598</v>
       </c>
       <c r="E662">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F662" t="s">
         <v>1600</v>
@@ -31517,7 +31517,7 @@
         <v>1599</v>
       </c>
       <c r="E663">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F663" t="s">
         <v>1602</v>
@@ -31555,7 +31555,7 @@
         <v>1599</v>
       </c>
       <c r="E664">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F664" t="s">
         <v>1600</v>
@@ -31590,7 +31590,7 @@
         <v>1599</v>
       </c>
       <c r="E665">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F665" t="s">
         <v>1600</v>
@@ -31625,7 +31625,7 @@
         <v>1599</v>
       </c>
       <c r="E666">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F666" t="s">
         <v>1600</v>
@@ -31660,7 +31660,7 @@
         <v>1599</v>
       </c>
       <c r="E667">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F667" t="s">
         <v>1600</v>
@@ -31695,7 +31695,7 @@
         <v>1599</v>
       </c>
       <c r="E668">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F668" t="s">
         <v>1600</v>
@@ -31730,7 +31730,7 @@
         <v>1599</v>
       </c>
       <c r="E669">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F669" t="s">
         <v>1600</v>
@@ -31765,7 +31765,7 @@
         <v>1599</v>
       </c>
       <c r="E670">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F670" t="s">
         <v>1600</v>
@@ -31800,7 +31800,7 @@
         <v>1599</v>
       </c>
       <c r="E671">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F671" t="s">
         <v>1600</v>
@@ -31835,7 +31835,7 @@
         <v>1599</v>
       </c>
       <c r="E672">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F672" t="s">
         <v>1600</v>
@@ -31873,7 +31873,7 @@
         <v>1599</v>
       </c>
       <c r="E673">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F673" t="s">
         <v>1600</v>
@@ -31908,7 +31908,7 @@
         <v>1599</v>
       </c>
       <c r="E674">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F674" t="s">
         <v>1600</v>
@@ -31943,7 +31943,7 @@
         <v>1599</v>
       </c>
       <c r="E675">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F675" t="s">
         <v>1600</v>

--- a/BacklogGATEAutoCompleto.xlsx
+++ b/BacklogGATEAutoCompleto.xlsx
@@ -7789,7 +7789,7 @@
     <t>ENGENHARIA CIVIL,GEOTECNIA</t>
   </si>
   <si>
-    <t>ECONOMICIDADE CONTÁBIL,ECONOMICIDADE OBRAS</t>
+    <t>ECONOMICIDADE OBRAS,ECONOMICIDADE CONTÁBIL</t>
   </si>
   <si>
     <t>ENGENHARIA CIVIL,FENOMENOS DE ENERGIA E INFORMAÇÃO,MEDICINA LEGAL</t>
@@ -7810,7 +7810,7 @@
     <t>ECONOMICIDADE CONTÁBIL,RECURSOS HÍDRICOS</t>
   </si>
   <si>
-    <t>MOBILIDADE E TRANSPORTE,ECONOMICIDADE OBRAS</t>
+    <t>ECONOMICIDADE OBRAS,MOBILIDADE E TRANSPORTE</t>
   </si>
   <si>
     <t>ECONOMICIDADE OBRAS,RECURSOS HÍDRICOS</t>
@@ -7825,6 +7825,9 @@
     <t>MEDICINA LEGAL,SAÚDE</t>
   </si>
   <si>
+    <t>RECURSOS HÍDRICOS,ECONOMICIDADE OBRAS</t>
+  </si>
+  <si>
     <t>AVALIAÇÃO DE IMÓVEIS,GEOLOGIA</t>
   </si>
   <si>
@@ -7834,19 +7837,19 @@
     <t>ENGENHARIA CIVIL,ENGENHARIA QUÍMICA,FENOMENOS DE ENERGIA E INFORMAÇÃO</t>
   </si>
   <si>
+    <t>FENOMENOS DE ENERGIA E INFORMAÇÃO,ENGENHARIA CIVIL</t>
+  </si>
+  <si>
     <t>ECONOMICIDADE CONTÁBIL,ECONOMICIDADE CONTÁBIL</t>
   </si>
   <si>
     <t>RECURSOS HÍDRICOS,VALORAÇÃO DANOS AMBIENTAIS</t>
   </si>
   <si>
-    <t>EDIFICAÇÕES,ASSISTÊNCIA SOCIAL</t>
-  </si>
-  <si>
-    <t>AVALIAÇÃO DE IMÓVEIS,ECONOMICIDADE OBRAS</t>
-  </si>
-  <si>
-    <t>FENOMENOS DE ENERGIA E INFORMAÇÃO,ENGENHARIA CIVIL</t>
+    <t>ASSISTÊNCIA SOCIAL,EDIFICAÇÕES</t>
+  </si>
+  <si>
+    <t>ECONOMICIDADE OBRAS,AVALIAÇÃO DE IMÓVEIS</t>
   </si>
   <si>
     <t>FARMÁCIA,SAÚDE</t>
@@ -7855,10 +7858,7 @@
     <t>SAÚDE,ORÇAMENTO</t>
   </si>
   <si>
-    <t>URBANISMO,BIOLOGIA</t>
-  </si>
-  <si>
-    <t>ORÇAMENTO,ASSISTÊNCIA SOCIAL,AVALIAÇÃO DE IMÓVEIS,PSICOLOGIA,ECONOMIA,URBANISMO,SAÚDE MENTAL,ECONOMICIDADE CONTÁBIL,MOBILIDADE E TRANSPORTE,SAÚDE</t>
+    <t>SAÚDE MENTAL,PSICOLOGIA,ECONOMICIDADE CONTÁBIL,ASSISTÊNCIA SOCIAL,ECONOMIA,SAÚDE,AVALIAÇÃO DE IMÓVEIS,MOBILIDADE E TRANSPORTE,URBANISMO,ORÇAMENTO</t>
   </si>
 </sst>
 </file>
@@ -24101,7 +24101,7 @@
         <v>2453</v>
       </c>
       <c r="L453" t="s">
-        <v>2599</v>
+        <v>2603</v>
       </c>
     </row>
     <row r="454" spans="1:12">
@@ -27409,7 +27409,7 @@
         <v>2430</v>
       </c>
       <c r="L547" t="s">
-        <v>2603</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="548" spans="1:12">
@@ -27444,7 +27444,7 @@
         <v>2479</v>
       </c>
       <c r="L548" t="s">
-        <v>2604</v>
+        <v>2605</v>
       </c>
     </row>
     <row r="549" spans="1:12">
@@ -28363,7 +28363,7 @@
         <v>2480</v>
       </c>
       <c r="L574" t="s">
-        <v>2605</v>
+        <v>2606</v>
       </c>
     </row>
     <row r="575" spans="1:12">
@@ -28398,7 +28398,7 @@
         <v>2480</v>
       </c>
       <c r="L575" t="s">
-        <v>2605</v>
+        <v>2606</v>
       </c>
     </row>
     <row r="576" spans="1:12">
@@ -28433,7 +28433,7 @@
         <v>2425</v>
       </c>
       <c r="L576" t="s">
-        <v>2604</v>
+        <v>2607</v>
       </c>
     </row>
     <row r="577" spans="1:12">
@@ -28468,7 +28468,7 @@
         <v>2521</v>
       </c>
       <c r="L577" t="s">
-        <v>2606</v>
+        <v>2608</v>
       </c>
     </row>
     <row r="578" spans="1:12">
@@ -28859,7 +28859,7 @@
         <v>2420</v>
       </c>
       <c r="L588" t="s">
-        <v>2607</v>
+        <v>2609</v>
       </c>
     </row>
     <row r="589" spans="1:12">
@@ -29282,7 +29282,7 @@
         <v>2525</v>
       </c>
       <c r="L600" t="s">
-        <v>2608</v>
+        <v>2610</v>
       </c>
     </row>
     <row r="601" spans="1:12">
@@ -29425,7 +29425,7 @@
         <v>2448</v>
       </c>
       <c r="L604" t="s">
-        <v>2609</v>
+        <v>2611</v>
       </c>
     </row>
     <row r="605" spans="1:12">
@@ -29956,7 +29956,7 @@
         <v>2520</v>
       </c>
       <c r="L619" t="s">
-        <v>2610</v>
+        <v>2605</v>
       </c>
     </row>
     <row r="620" spans="1:12">
@@ -29991,7 +29991,7 @@
         <v>2455</v>
       </c>
       <c r="L620" t="s">
-        <v>2611</v>
+        <v>2612</v>
       </c>
     </row>
     <row r="621" spans="1:12">
@@ -30283,7 +30283,7 @@
         <v>2484</v>
       </c>
       <c r="L628" t="s">
-        <v>2612</v>
+        <v>2613</v>
       </c>
     </row>
     <row r="629" spans="1:12">
@@ -31386,7 +31386,7 @@
         <v>2523</v>
       </c>
       <c r="L659" t="s">
-        <v>2613</v>
+        <v>2549</v>
       </c>
     </row>
     <row r="660" spans="1:12">
@@ -31499,7 +31499,7 @@
     </row>
     <row r="663" spans="1:12">
       <c r="A663" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="B663" t="s">
         <v>699</v>
@@ -31520,7 +31520,7 @@
         <v>1603</v>
       </c>
       <c r="I663" t="s">
-        <v>1630</v>
+        <v>1748</v>
       </c>
       <c r="J663" t="s">
         <v>2397</v>
@@ -31529,7 +31529,7 @@
         <v>2419</v>
       </c>
       <c r="L663" t="s">
-        <v>2588</v>
+        <v>2534</v>
       </c>
     </row>
     <row r="664" spans="1:12">
@@ -31774,7 +31774,7 @@
         <v>2492</v>
       </c>
       <c r="L670" t="s">
-        <v>2588</v>
+        <v>2564</v>
       </c>
     </row>
     <row r="671" spans="1:12">

--- a/BacklogGATEAutoCompleto.xlsx
+++ b/BacklogGATEAutoCompleto.xlsx
@@ -8187,7 +8187,7 @@
         <v>1365</v>
       </c>
       <c r="E2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="F2" t="s">
         <v>1578</v>
@@ -8222,7 +8222,7 @@
         <v>1366</v>
       </c>
       <c r="E3">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="F3" t="s">
         <v>1578</v>
@@ -8257,7 +8257,7 @@
         <v>1367</v>
       </c>
       <c r="E4">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="F4" t="s">
         <v>1578</v>
@@ -8292,7 +8292,7 @@
         <v>1368</v>
       </c>
       <c r="E5">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="F5" t="s">
         <v>1578</v>
@@ -8327,7 +8327,7 @@
         <v>1369</v>
       </c>
       <c r="E6">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="F6" t="s">
         <v>1578</v>
@@ -8362,7 +8362,7 @@
         <v>1370</v>
       </c>
       <c r="E7">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="F7" t="s">
         <v>1578</v>
@@ -8397,7 +8397,7 @@
         <v>1371</v>
       </c>
       <c r="E8">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="F8" t="s">
         <v>1578</v>
@@ -8432,7 +8432,7 @@
         <v>1372</v>
       </c>
       <c r="E9">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F9" t="s">
         <v>1578</v>
@@ -8467,7 +8467,7 @@
         <v>1373</v>
       </c>
       <c r="E10">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F10" t="s">
         <v>1578</v>
@@ -8502,7 +8502,7 @@
         <v>1374</v>
       </c>
       <c r="E11">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="F11" t="s">
         <v>1578</v>
@@ -8537,7 +8537,7 @@
         <v>1374</v>
       </c>
       <c r="E12">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="F12" t="s">
         <v>1578</v>
@@ -8572,7 +8572,7 @@
         <v>1375</v>
       </c>
       <c r="E13">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="F13" t="s">
         <v>1578</v>
@@ -8607,7 +8607,7 @@
         <v>1376</v>
       </c>
       <c r="E14">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="F14" t="s">
         <v>1578</v>
@@ -8642,7 +8642,7 @@
         <v>1377</v>
       </c>
       <c r="E15">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="F15" t="s">
         <v>1578</v>
@@ -8677,7 +8677,7 @@
         <v>1377</v>
       </c>
       <c r="E16">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="F16" t="s">
         <v>1578</v>
@@ -8712,7 +8712,7 @@
         <v>1378</v>
       </c>
       <c r="E17">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="F17" t="s">
         <v>1578</v>
@@ -8747,7 +8747,7 @@
         <v>1379</v>
       </c>
       <c r="E18">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="F18" t="s">
         <v>1578</v>
@@ -8782,7 +8782,7 @@
         <v>1379</v>
       </c>
       <c r="E19">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="F19" t="s">
         <v>1578</v>
@@ -8817,7 +8817,7 @@
         <v>1380</v>
       </c>
       <c r="E20">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="F20" t="s">
         <v>1578</v>
@@ -8852,7 +8852,7 @@
         <v>1381</v>
       </c>
       <c r="E21">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="F21" t="s">
         <v>1578</v>
@@ -8887,7 +8887,7 @@
         <v>1382</v>
       </c>
       <c r="E22">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F22" t="s">
         <v>1578</v>
@@ -8922,7 +8922,7 @@
         <v>1383</v>
       </c>
       <c r="E23">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F23" t="s">
         <v>1578</v>
@@ -8957,7 +8957,7 @@
         <v>1384</v>
       </c>
       <c r="E24">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="F24" t="s">
         <v>1578</v>
@@ -8995,7 +8995,7 @@
         <v>1385</v>
       </c>
       <c r="E25">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F25" t="s">
         <v>1578</v>
@@ -9030,7 +9030,7 @@
         <v>1386</v>
       </c>
       <c r="E26">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="F26" t="s">
         <v>1578</v>
@@ -9065,7 +9065,7 @@
         <v>1387</v>
       </c>
       <c r="E27">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="F27" t="s">
         <v>1578</v>
@@ -9100,7 +9100,7 @@
         <v>1388</v>
       </c>
       <c r="E28">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F28" t="s">
         <v>1578</v>
@@ -9135,7 +9135,7 @@
         <v>1389</v>
       </c>
       <c r="E29">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F29" t="s">
         <v>1578</v>
@@ -9170,7 +9170,7 @@
         <v>1390</v>
       </c>
       <c r="E30">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F30" t="s">
         <v>1578</v>
@@ -9205,7 +9205,7 @@
         <v>1391</v>
       </c>
       <c r="E31">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F31" t="s">
         <v>1578</v>
@@ -9240,7 +9240,7 @@
         <v>1392</v>
       </c>
       <c r="E32">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F32" t="s">
         <v>1578</v>
@@ -9275,7 +9275,7 @@
         <v>1393</v>
       </c>
       <c r="E33">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F33" t="s">
         <v>1578</v>
@@ -9310,7 +9310,7 @@
         <v>1394</v>
       </c>
       <c r="E34">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="F34" t="s">
         <v>1578</v>
@@ -9345,7 +9345,7 @@
         <v>1395</v>
       </c>
       <c r="E35">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F35" t="s">
         <v>1578</v>
@@ -9380,7 +9380,7 @@
         <v>1396</v>
       </c>
       <c r="E36">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F36" t="s">
         <v>1578</v>
@@ -9415,7 +9415,7 @@
         <v>1396</v>
       </c>
       <c r="E37">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F37" t="s">
         <v>1578</v>
@@ -9450,7 +9450,7 @@
         <v>1397</v>
       </c>
       <c r="E38">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F38" t="s">
         <v>1578</v>
@@ -9485,7 +9485,7 @@
         <v>1398</v>
       </c>
       <c r="E39">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F39" t="s">
         <v>1578</v>
@@ -9520,7 +9520,7 @@
         <v>1399</v>
       </c>
       <c r="E40">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F40" t="s">
         <v>1578</v>
@@ -9555,7 +9555,7 @@
         <v>1400</v>
       </c>
       <c r="E41">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F41" t="s">
         <v>1578</v>
@@ -9590,7 +9590,7 @@
         <v>1401</v>
       </c>
       <c r="E42">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F42" t="s">
         <v>1578</v>
@@ -9625,7 +9625,7 @@
         <v>1401</v>
       </c>
       <c r="E43">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F43" t="s">
         <v>1578</v>
@@ -9660,7 +9660,7 @@
         <v>1402</v>
       </c>
       <c r="E44">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F44" t="s">
         <v>1578</v>
@@ -9695,7 +9695,7 @@
         <v>1403</v>
       </c>
       <c r="E45">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F45" t="s">
         <v>1578</v>
@@ -9730,7 +9730,7 @@
         <v>1404</v>
       </c>
       <c r="E46">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F46" t="s">
         <v>1578</v>
@@ -9765,7 +9765,7 @@
         <v>1404</v>
       </c>
       <c r="E47">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F47" t="s">
         <v>1578</v>
@@ -9800,7 +9800,7 @@
         <v>1405</v>
       </c>
       <c r="E48">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F48" t="s">
         <v>1578</v>
@@ -9835,7 +9835,7 @@
         <v>1405</v>
       </c>
       <c r="E49">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F49" t="s">
         <v>1578</v>
@@ -9870,7 +9870,7 @@
         <v>1406</v>
       </c>
       <c r="E50">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F50" t="s">
         <v>1578</v>
@@ -9905,7 +9905,7 @@
         <v>1407</v>
       </c>
       <c r="E51">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F51" t="s">
         <v>1578</v>
@@ -9940,7 +9940,7 @@
         <v>1408</v>
       </c>
       <c r="E52">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F52" t="s">
         <v>1578</v>
@@ -9975,7 +9975,7 @@
         <v>1409</v>
       </c>
       <c r="E53">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F53" t="s">
         <v>1578</v>
@@ -10010,7 +10010,7 @@
         <v>1410</v>
       </c>
       <c r="E54">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F54" t="s">
         <v>1578</v>
@@ -10045,7 +10045,7 @@
         <v>1411</v>
       </c>
       <c r="E55">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F55" t="s">
         <v>1578</v>
@@ -10080,7 +10080,7 @@
         <v>1412</v>
       </c>
       <c r="E56">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F56" t="s">
         <v>1578</v>
@@ -10115,7 +10115,7 @@
         <v>1413</v>
       </c>
       <c r="E57">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F57" t="s">
         <v>1578</v>
@@ -10150,7 +10150,7 @@
         <v>1414</v>
       </c>
       <c r="E58">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F58" t="s">
         <v>1578</v>
@@ -10185,7 +10185,7 @@
         <v>1415</v>
       </c>
       <c r="E59">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F59" t="s">
         <v>1578</v>
@@ -10220,7 +10220,7 @@
         <v>1416</v>
       </c>
       <c r="E60">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F60" t="s">
         <v>1578</v>
@@ -10255,7 +10255,7 @@
         <v>1417</v>
       </c>
       <c r="E61">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F61" t="s">
         <v>1578</v>
@@ -10290,7 +10290,7 @@
         <v>1417</v>
       </c>
       <c r="E62">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F62" t="s">
         <v>1578</v>
@@ -10325,7 +10325,7 @@
         <v>1417</v>
       </c>
       <c r="E63">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F63" t="s">
         <v>1578</v>
@@ -10360,7 +10360,7 @@
         <v>1418</v>
       </c>
       <c r="E64">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F64" t="s">
         <v>1578</v>
@@ -10395,7 +10395,7 @@
         <v>1419</v>
       </c>
       <c r="E65">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F65" t="s">
         <v>1578</v>
@@ -10430,7 +10430,7 @@
         <v>1420</v>
       </c>
       <c r="E66">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F66" t="s">
         <v>1578</v>
@@ -10465,7 +10465,7 @@
         <v>1420</v>
       </c>
       <c r="E67">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F67" t="s">
         <v>1578</v>
@@ -10500,7 +10500,7 @@
         <v>1420</v>
       </c>
       <c r="E68">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F68" t="s">
         <v>1578</v>
@@ -10535,7 +10535,7 @@
         <v>1421</v>
       </c>
       <c r="E69">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F69" t="s">
         <v>1578</v>
@@ -10570,7 +10570,7 @@
         <v>1422</v>
       </c>
       <c r="E70">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F70" t="s">
         <v>1578</v>
@@ -10605,7 +10605,7 @@
         <v>1423</v>
       </c>
       <c r="E71">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F71" t="s">
         <v>1578</v>
@@ -10640,7 +10640,7 @@
         <v>1423</v>
       </c>
       <c r="E72">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F72" t="s">
         <v>1578</v>
@@ -10675,7 +10675,7 @@
         <v>1423</v>
       </c>
       <c r="E73">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F73" t="s">
         <v>1578</v>
@@ -10710,7 +10710,7 @@
         <v>1424</v>
       </c>
       <c r="E74">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F74" t="s">
         <v>1578</v>
@@ -10745,7 +10745,7 @@
         <v>1425</v>
       </c>
       <c r="E75">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F75" t="s">
         <v>1578</v>
@@ -10780,7 +10780,7 @@
         <v>1425</v>
       </c>
       <c r="E76">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F76" t="s">
         <v>1578</v>
@@ -10815,7 +10815,7 @@
         <v>1425</v>
       </c>
       <c r="E77">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F77" t="s">
         <v>1579</v>
@@ -10850,7 +10850,7 @@
         <v>1425</v>
       </c>
       <c r="E78">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F78" t="s">
         <v>1578</v>
@@ -10885,7 +10885,7 @@
         <v>1426</v>
       </c>
       <c r="E79">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F79" t="s">
         <v>1578</v>
@@ -10920,7 +10920,7 @@
         <v>1427</v>
       </c>
       <c r="E80">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F80" t="s">
         <v>1578</v>
@@ -10955,7 +10955,7 @@
         <v>1427</v>
       </c>
       <c r="E81">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F81" t="s">
         <v>1578</v>
@@ -10990,7 +10990,7 @@
         <v>1428</v>
       </c>
       <c r="E82">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F82" t="s">
         <v>1578</v>
@@ -11025,7 +11025,7 @@
         <v>1429</v>
       </c>
       <c r="E83">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F83" t="s">
         <v>1578</v>
@@ -11060,7 +11060,7 @@
         <v>1430</v>
       </c>
       <c r="E84">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F84" t="s">
         <v>1578</v>
@@ -11095,7 +11095,7 @@
         <v>1431</v>
       </c>
       <c r="E85">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F85" t="s">
         <v>1578</v>
@@ -11130,7 +11130,7 @@
         <v>1431</v>
       </c>
       <c r="E86">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F86" t="s">
         <v>1578</v>
@@ -11165,7 +11165,7 @@
         <v>1431</v>
       </c>
       <c r="E87">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F87" t="s">
         <v>1578</v>
@@ -11200,7 +11200,7 @@
         <v>1431</v>
       </c>
       <c r="E88">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F88" t="s">
         <v>1578</v>
@@ -11235,7 +11235,7 @@
         <v>1431</v>
       </c>
       <c r="E89">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F89" t="s">
         <v>1578</v>
@@ -11270,7 +11270,7 @@
         <v>1431</v>
       </c>
       <c r="E90">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F90" t="s">
         <v>1578</v>
@@ -11305,7 +11305,7 @@
         <v>1432</v>
       </c>
       <c r="E91">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F91" t="s">
         <v>1578</v>
@@ -11340,7 +11340,7 @@
         <v>1432</v>
       </c>
       <c r="E92">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F92" t="s">
         <v>1578</v>
@@ -11375,7 +11375,7 @@
         <v>1433</v>
       </c>
       <c r="E93">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F93" t="s">
         <v>1578</v>
@@ -11410,7 +11410,7 @@
         <v>1434</v>
       </c>
       <c r="E94">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F94" t="s">
         <v>1578</v>
@@ -11445,7 +11445,7 @@
         <v>1434</v>
       </c>
       <c r="E95">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F95" t="s">
         <v>1578</v>
@@ -11480,7 +11480,7 @@
         <v>1435</v>
       </c>
       <c r="E96">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F96" t="s">
         <v>1578</v>
@@ -11515,7 +11515,7 @@
         <v>1435</v>
       </c>
       <c r="E97">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F97" t="s">
         <v>1580</v>
@@ -11550,7 +11550,7 @@
         <v>1436</v>
       </c>
       <c r="E98">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F98" t="s">
         <v>1578</v>
@@ -11585,7 +11585,7 @@
         <v>1437</v>
       </c>
       <c r="E99">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F99" t="s">
         <v>1578</v>
@@ -11620,7 +11620,7 @@
         <v>1438</v>
       </c>
       <c r="E100">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F100" t="s">
         <v>1578</v>
@@ -11655,7 +11655,7 @@
         <v>1438</v>
       </c>
       <c r="E101">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F101" t="s">
         <v>1578</v>
@@ -11690,7 +11690,7 @@
         <v>1439</v>
       </c>
       <c r="E102">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F102" t="s">
         <v>1578</v>
@@ -11725,7 +11725,7 @@
         <v>1440</v>
       </c>
       <c r="E103">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F103" t="s">
         <v>1578</v>
@@ -11760,7 +11760,7 @@
         <v>1441</v>
       </c>
       <c r="E104">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F104" t="s">
         <v>1578</v>
@@ -11795,7 +11795,7 @@
         <v>1442</v>
       </c>
       <c r="E105">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F105" t="s">
         <v>1578</v>
@@ -11830,7 +11830,7 @@
         <v>1443</v>
       </c>
       <c r="E106">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F106" t="s">
         <v>1578</v>
@@ -11865,7 +11865,7 @@
         <v>1443</v>
       </c>
       <c r="E107">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F107" t="s">
         <v>1578</v>
@@ -11900,7 +11900,7 @@
         <v>1444</v>
       </c>
       <c r="E108">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F108" t="s">
         <v>1578</v>
@@ -11935,7 +11935,7 @@
         <v>1444</v>
       </c>
       <c r="E109">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F109" t="s">
         <v>1578</v>
@@ -11970,7 +11970,7 @@
         <v>1444</v>
       </c>
       <c r="E110">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F110" t="s">
         <v>1578</v>
@@ -12005,7 +12005,7 @@
         <v>1445</v>
       </c>
       <c r="E111">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F111" t="s">
         <v>1578</v>
@@ -12040,7 +12040,7 @@
         <v>1445</v>
       </c>
       <c r="E112">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F112" t="s">
         <v>1578</v>
@@ -12075,7 +12075,7 @@
         <v>1445</v>
       </c>
       <c r="E113">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F113" t="s">
         <v>1578</v>
@@ -12110,7 +12110,7 @@
         <v>1445</v>
       </c>
       <c r="E114">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F114" t="s">
         <v>1578</v>
@@ -12145,7 +12145,7 @@
         <v>1445</v>
       </c>
       <c r="E115">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F115" t="s">
         <v>1578</v>
@@ -12180,7 +12180,7 @@
         <v>1446</v>
       </c>
       <c r="E116">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F116" t="s">
         <v>1578</v>
@@ -12215,7 +12215,7 @@
         <v>1447</v>
       </c>
       <c r="E117">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F117" t="s">
         <v>1578</v>
@@ -12250,7 +12250,7 @@
         <v>1447</v>
       </c>
       <c r="E118">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F118" t="s">
         <v>1578</v>
@@ -12285,7 +12285,7 @@
         <v>1448</v>
       </c>
       <c r="E119">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F119" t="s">
         <v>1578</v>
@@ -12320,7 +12320,7 @@
         <v>1449</v>
       </c>
       <c r="E120">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F120" t="s">
         <v>1578</v>
@@ -12355,7 +12355,7 @@
         <v>1449</v>
       </c>
       <c r="E121">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F121" t="s">
         <v>1578</v>
@@ -12390,7 +12390,7 @@
         <v>1449</v>
       </c>
       <c r="E122">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F122" t="s">
         <v>1578</v>
@@ -12425,7 +12425,7 @@
         <v>1450</v>
       </c>
       <c r="E123">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F123" t="s">
         <v>1578</v>
@@ -12460,7 +12460,7 @@
         <v>1450</v>
       </c>
       <c r="E124">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F124" t="s">
         <v>1578</v>
@@ -12495,7 +12495,7 @@
         <v>1450</v>
       </c>
       <c r="E125">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F125" t="s">
         <v>1578</v>
@@ -12530,7 +12530,7 @@
         <v>1451</v>
       </c>
       <c r="E126">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F126" t="s">
         <v>1578</v>
@@ -12565,7 +12565,7 @@
         <v>1451</v>
       </c>
       <c r="E127">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F127" t="s">
         <v>1578</v>
@@ -12600,7 +12600,7 @@
         <v>1452</v>
       </c>
       <c r="E128">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F128" t="s">
         <v>1578</v>
@@ -12635,7 +12635,7 @@
         <v>1452</v>
       </c>
       <c r="E129">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F129" t="s">
         <v>1578</v>
@@ -12670,7 +12670,7 @@
         <v>1453</v>
       </c>
       <c r="E130">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F130" t="s">
         <v>1578</v>
@@ -12705,7 +12705,7 @@
         <v>1454</v>
       </c>
       <c r="E131">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F131" t="s">
         <v>1578</v>
@@ -12740,7 +12740,7 @@
         <v>1454</v>
       </c>
       <c r="E132">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F132" t="s">
         <v>1578</v>
@@ -12775,7 +12775,7 @@
         <v>1455</v>
       </c>
       <c r="E133">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F133" t="s">
         <v>1578</v>
@@ -12810,7 +12810,7 @@
         <v>1455</v>
       </c>
       <c r="E134">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F134" t="s">
         <v>1578</v>
@@ -12845,7 +12845,7 @@
         <v>1456</v>
       </c>
       <c r="E135">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F135" t="s">
         <v>1578</v>
@@ -12883,7 +12883,7 @@
         <v>1456</v>
       </c>
       <c r="E136">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F136" t="s">
         <v>1578</v>
@@ -12918,7 +12918,7 @@
         <v>1456</v>
       </c>
       <c r="E137">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F137" t="s">
         <v>1578</v>
@@ -12953,7 +12953,7 @@
         <v>1456</v>
       </c>
       <c r="E138">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F138" t="s">
         <v>1578</v>
@@ -12988,7 +12988,7 @@
         <v>1456</v>
       </c>
       <c r="E139">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F139" t="s">
         <v>1578</v>
@@ -13023,7 +13023,7 @@
         <v>1457</v>
       </c>
       <c r="E140">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F140" t="s">
         <v>1578</v>
@@ -13058,7 +13058,7 @@
         <v>1458</v>
       </c>
       <c r="E141">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F141" t="s">
         <v>1579</v>
@@ -13093,7 +13093,7 @@
         <v>1459</v>
       </c>
       <c r="E142">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F142" t="s">
         <v>1578</v>
@@ -13128,7 +13128,7 @@
         <v>1459</v>
       </c>
       <c r="E143">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F143" t="s">
         <v>1578</v>
@@ -13163,7 +13163,7 @@
         <v>1459</v>
       </c>
       <c r="E144">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F144" t="s">
         <v>1578</v>
@@ -13198,7 +13198,7 @@
         <v>1459</v>
       </c>
       <c r="E145">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F145" t="s">
         <v>1578</v>
@@ -13233,7 +13233,7 @@
         <v>1460</v>
       </c>
       <c r="E146">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F146" t="s">
         <v>1578</v>
@@ -13268,7 +13268,7 @@
         <v>1460</v>
       </c>
       <c r="E147">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F147" t="s">
         <v>1578</v>
@@ -13303,7 +13303,7 @@
         <v>1460</v>
       </c>
       <c r="E148">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F148" t="s">
         <v>1578</v>
@@ -13338,7 +13338,7 @@
         <v>1460</v>
       </c>
       <c r="E149">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F149" t="s">
         <v>1578</v>
@@ -13373,7 +13373,7 @@
         <v>1460</v>
       </c>
       <c r="E150">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F150" t="s">
         <v>1578</v>
@@ -13408,7 +13408,7 @@
         <v>1460</v>
       </c>
       <c r="E151">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F151" t="s">
         <v>1578</v>
@@ -13443,7 +13443,7 @@
         <v>1460</v>
       </c>
       <c r="E152">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F152" t="s">
         <v>1578</v>
@@ -13478,7 +13478,7 @@
         <v>1461</v>
       </c>
       <c r="E153">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F153" t="s">
         <v>1578</v>
@@ -13513,7 +13513,7 @@
         <v>1461</v>
       </c>
       <c r="E154">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F154" t="s">
         <v>1578</v>
@@ -13548,7 +13548,7 @@
         <v>1462</v>
       </c>
       <c r="E155">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F155" t="s">
         <v>1578</v>
@@ -13583,7 +13583,7 @@
         <v>1462</v>
       </c>
       <c r="E156">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F156" t="s">
         <v>1578</v>
@@ -13618,7 +13618,7 @@
         <v>1463</v>
       </c>
       <c r="E157">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F157" t="s">
         <v>1578</v>
@@ -13653,7 +13653,7 @@
         <v>1463</v>
       </c>
       <c r="E158">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F158" t="s">
         <v>1578</v>
@@ -13688,7 +13688,7 @@
         <v>1463</v>
       </c>
       <c r="E159">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F159" t="s">
         <v>1578</v>
@@ -13723,7 +13723,7 @@
         <v>1464</v>
       </c>
       <c r="E160">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F160" t="s">
         <v>1578</v>
@@ -13758,7 +13758,7 @@
         <v>1464</v>
       </c>
       <c r="E161">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F161" t="s">
         <v>1578</v>
@@ -13793,7 +13793,7 @@
         <v>1464</v>
       </c>
       <c r="E162">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F162" t="s">
         <v>1578</v>
@@ -13828,7 +13828,7 @@
         <v>1464</v>
       </c>
       <c r="E163">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F163" t="s">
         <v>1578</v>
@@ -13863,7 +13863,7 @@
         <v>1464</v>
       </c>
       <c r="E164">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F164" t="s">
         <v>1578</v>
@@ -13898,7 +13898,7 @@
         <v>1464</v>
       </c>
       <c r="E165">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F165" t="s">
         <v>1578</v>
@@ -13933,7 +13933,7 @@
         <v>1464</v>
       </c>
       <c r="E166">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F166" t="s">
         <v>1578</v>
@@ -13968,7 +13968,7 @@
         <v>1464</v>
       </c>
       <c r="E167">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F167" t="s">
         <v>1578</v>
@@ -14003,7 +14003,7 @@
         <v>1464</v>
       </c>
       <c r="E168">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F168" t="s">
         <v>1578</v>
@@ -14038,7 +14038,7 @@
         <v>1464</v>
       </c>
       <c r="E169">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F169" t="s">
         <v>1578</v>
@@ -14073,7 +14073,7 @@
         <v>1465</v>
       </c>
       <c r="E170">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F170" t="s">
         <v>1578</v>
@@ -14108,7 +14108,7 @@
         <v>1465</v>
       </c>
       <c r="E171">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F171" t="s">
         <v>1578</v>
@@ -14143,7 +14143,7 @@
         <v>1465</v>
       </c>
       <c r="E172">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F172" t="s">
         <v>1578</v>
@@ -14178,7 +14178,7 @@
         <v>1466</v>
       </c>
       <c r="E173">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F173" t="s">
         <v>1578</v>
@@ -14213,7 +14213,7 @@
         <v>1466</v>
       </c>
       <c r="E174">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F174" t="s">
         <v>1579</v>
@@ -14248,7 +14248,7 @@
         <v>1466</v>
       </c>
       <c r="E175">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F175" t="s">
         <v>1578</v>
@@ -14283,7 +14283,7 @@
         <v>1467</v>
       </c>
       <c r="E176">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F176" t="s">
         <v>1578</v>
@@ -14318,7 +14318,7 @@
         <v>1467</v>
       </c>
       <c r="E177">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F177" t="s">
         <v>1578</v>
@@ -14353,7 +14353,7 @@
         <v>1468</v>
       </c>
       <c r="E178">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F178" t="s">
         <v>1578</v>
@@ -14388,7 +14388,7 @@
         <v>1468</v>
       </c>
       <c r="E179">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F179" t="s">
         <v>1578</v>
@@ -14423,7 +14423,7 @@
         <v>1469</v>
       </c>
       <c r="E180">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F180" t="s">
         <v>1578</v>
@@ -14458,7 +14458,7 @@
         <v>1469</v>
       </c>
       <c r="E181">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F181" t="s">
         <v>1578</v>
@@ -14493,7 +14493,7 @@
         <v>1470</v>
       </c>
       <c r="E182">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F182" t="s">
         <v>1578</v>
@@ -14528,7 +14528,7 @@
         <v>1470</v>
       </c>
       <c r="E183">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F183" t="s">
         <v>1578</v>
@@ -14563,7 +14563,7 @@
         <v>1470</v>
       </c>
       <c r="E184">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F184" t="s">
         <v>1578</v>
@@ -14598,7 +14598,7 @@
         <v>1470</v>
       </c>
       <c r="E185">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F185" t="s">
         <v>1578</v>
@@ -14633,7 +14633,7 @@
         <v>1470</v>
       </c>
       <c r="E186">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F186" t="s">
         <v>1578</v>
@@ -14668,7 +14668,7 @@
         <v>1471</v>
       </c>
       <c r="E187">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F187" t="s">
         <v>1578</v>
@@ -14703,7 +14703,7 @@
         <v>1471</v>
       </c>
       <c r="E188">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F188" t="s">
         <v>1578</v>
@@ -14738,7 +14738,7 @@
         <v>1472</v>
       </c>
       <c r="E189">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F189" t="s">
         <v>1578</v>
@@ -14773,7 +14773,7 @@
         <v>1473</v>
       </c>
       <c r="E190">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F190" t="s">
         <v>1578</v>
@@ -14808,7 +14808,7 @@
         <v>1473</v>
       </c>
       <c r="E191">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F191" t="s">
         <v>1578</v>
@@ -14843,7 +14843,7 @@
         <v>1473</v>
       </c>
       <c r="E192">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F192" t="s">
         <v>1578</v>
@@ -14878,7 +14878,7 @@
         <v>1473</v>
       </c>
       <c r="E193">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F193" t="s">
         <v>1578</v>
@@ -14913,7 +14913,7 @@
         <v>1474</v>
       </c>
       <c r="E194">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F194" t="s">
         <v>1578</v>
@@ -14948,7 +14948,7 @@
         <v>1475</v>
       </c>
       <c r="E195">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F195" t="s">
         <v>1578</v>
@@ -14983,7 +14983,7 @@
         <v>1475</v>
       </c>
       <c r="E196">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F196" t="s">
         <v>1578</v>
@@ -15018,7 +15018,7 @@
         <v>1475</v>
       </c>
       <c r="E197">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F197" t="s">
         <v>1578</v>
@@ -15053,7 +15053,7 @@
         <v>1475</v>
       </c>
       <c r="E198">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F198" t="s">
         <v>1578</v>
@@ -15088,7 +15088,7 @@
         <v>1475</v>
       </c>
       <c r="E199">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F199" t="s">
         <v>1578</v>
@@ -15123,7 +15123,7 @@
         <v>1476</v>
       </c>
       <c r="E200">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F200" t="s">
         <v>1578</v>
@@ -15158,7 +15158,7 @@
         <v>1476</v>
       </c>
       <c r="E201">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F201" t="s">
         <v>1578</v>
@@ -15193,7 +15193,7 @@
         <v>1476</v>
       </c>
       <c r="E202">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F202" t="s">
         <v>1578</v>
@@ -15228,7 +15228,7 @@
         <v>1476</v>
       </c>
       <c r="E203">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F203" t="s">
         <v>1578</v>
@@ -15263,7 +15263,7 @@
         <v>1476</v>
       </c>
       <c r="E204">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F204" t="s">
         <v>1578</v>
@@ -15298,7 +15298,7 @@
         <v>1476</v>
       </c>
       <c r="E205">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F205" t="s">
         <v>1578</v>
@@ -15333,7 +15333,7 @@
         <v>1476</v>
       </c>
       <c r="E206">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F206" t="s">
         <v>1578</v>
@@ -15368,7 +15368,7 @@
         <v>1477</v>
       </c>
       <c r="E207">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F207" t="s">
         <v>1578</v>
@@ -15403,7 +15403,7 @@
         <v>1477</v>
       </c>
       <c r="E208">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F208" t="s">
         <v>1578</v>
@@ -15438,7 +15438,7 @@
         <v>1477</v>
       </c>
       <c r="E209">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F209" t="s">
         <v>1578</v>
@@ -15473,7 +15473,7 @@
         <v>1477</v>
       </c>
       <c r="E210">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F210" t="s">
         <v>1578</v>
@@ -15508,7 +15508,7 @@
         <v>1478</v>
       </c>
       <c r="E211">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F211" t="s">
         <v>1578</v>
@@ -15543,7 +15543,7 @@
         <v>1478</v>
       </c>
       <c r="E212">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F212" t="s">
         <v>1578</v>
@@ -15578,7 +15578,7 @@
         <v>1479</v>
       </c>
       <c r="E213">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F213" t="s">
         <v>1578</v>
@@ -15613,7 +15613,7 @@
         <v>1479</v>
       </c>
       <c r="E214">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F214" t="s">
         <v>1578</v>
@@ -15648,7 +15648,7 @@
         <v>1480</v>
       </c>
       <c r="E215">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F215" t="s">
         <v>1578</v>
@@ -15683,7 +15683,7 @@
         <v>1480</v>
       </c>
       <c r="E216">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F216" t="s">
         <v>1578</v>
@@ -15718,7 +15718,7 @@
         <v>1481</v>
       </c>
       <c r="E217">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F217" t="s">
         <v>1578</v>
@@ -15753,7 +15753,7 @@
         <v>1482</v>
       </c>
       <c r="E218">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F218" t="s">
         <v>1578</v>
@@ -15788,7 +15788,7 @@
         <v>1482</v>
       </c>
       <c r="E219">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F219" t="s">
         <v>1578</v>
@@ -15823,7 +15823,7 @@
         <v>1483</v>
       </c>
       <c r="E220">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F220" t="s">
         <v>1578</v>
@@ -15858,7 +15858,7 @@
         <v>1483</v>
       </c>
       <c r="E221">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F221" t="s">
         <v>1578</v>
@@ -15893,7 +15893,7 @@
         <v>1484</v>
       </c>
       <c r="E222">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F222" t="s">
         <v>1578</v>
@@ -15928,7 +15928,7 @@
         <v>1485</v>
       </c>
       <c r="E223">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F223" t="s">
         <v>1578</v>
@@ -15963,7 +15963,7 @@
         <v>1485</v>
       </c>
       <c r="E224">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F224" t="s">
         <v>1578</v>
@@ -15998,7 +15998,7 @@
         <v>1485</v>
       </c>
       <c r="E225">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F225" t="s">
         <v>1578</v>
@@ -16033,7 +16033,7 @@
         <v>1486</v>
       </c>
       <c r="E226">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F226" t="s">
         <v>1578</v>
@@ -16068,7 +16068,7 @@
         <v>1486</v>
       </c>
       <c r="E227">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F227" t="s">
         <v>1578</v>
@@ -16103,7 +16103,7 @@
         <v>1487</v>
       </c>
       <c r="E228">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F228" t="s">
         <v>1578</v>
@@ -16138,7 +16138,7 @@
         <v>1488</v>
       </c>
       <c r="E229">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F229" t="s">
         <v>1578</v>
@@ -16173,7 +16173,7 @@
         <v>1488</v>
       </c>
       <c r="E230">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F230" t="s">
         <v>1578</v>
@@ -16208,7 +16208,7 @@
         <v>1488</v>
       </c>
       <c r="E231">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F231" t="s">
         <v>1578</v>
@@ -16243,7 +16243,7 @@
         <v>1489</v>
       </c>
       <c r="E232">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F232" t="s">
         <v>1578</v>
@@ -16278,7 +16278,7 @@
         <v>1489</v>
       </c>
       <c r="E233">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F233" t="s">
         <v>1578</v>
@@ -16313,7 +16313,7 @@
         <v>1490</v>
       </c>
       <c r="E234">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F234" t="s">
         <v>1578</v>
@@ -16348,7 +16348,7 @@
         <v>1490</v>
       </c>
       <c r="E235">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F235" t="s">
         <v>1578</v>
@@ -16383,7 +16383,7 @@
         <v>1490</v>
       </c>
       <c r="E236">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F236" t="s">
         <v>1580</v>
@@ -16418,7 +16418,7 @@
         <v>1490</v>
       </c>
       <c r="E237">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F237" t="s">
         <v>1578</v>
@@ -16453,7 +16453,7 @@
         <v>1491</v>
       </c>
       <c r="E238">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F238" t="s">
         <v>1578</v>
@@ -16488,7 +16488,7 @@
         <v>1491</v>
       </c>
       <c r="E239">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F239" t="s">
         <v>1578</v>
@@ -16526,7 +16526,7 @@
         <v>1491</v>
       </c>
       <c r="E240">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F240" t="s">
         <v>1578</v>
@@ -16561,7 +16561,7 @@
         <v>1491</v>
       </c>
       <c r="E241">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F241" t="s">
         <v>1578</v>
@@ -16596,7 +16596,7 @@
         <v>1491</v>
       </c>
       <c r="E242">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F242" t="s">
         <v>1578</v>
@@ -16631,7 +16631,7 @@
         <v>1491</v>
       </c>
       <c r="E243">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F243" t="s">
         <v>1578</v>
@@ -16666,7 +16666,7 @@
         <v>1492</v>
       </c>
       <c r="E244">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F244" t="s">
         <v>1578</v>
@@ -16701,7 +16701,7 @@
         <v>1492</v>
       </c>
       <c r="E245">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F245" t="s">
         <v>1578</v>
@@ -16736,7 +16736,7 @@
         <v>1492</v>
       </c>
       <c r="E246">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F246" t="s">
         <v>1578</v>
@@ -16771,7 +16771,7 @@
         <v>1493</v>
       </c>
       <c r="E247">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F247" t="s">
         <v>1578</v>
@@ -16806,7 +16806,7 @@
         <v>1493</v>
       </c>
       <c r="E248">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F248" t="s">
         <v>1578</v>
@@ -16841,7 +16841,7 @@
         <v>1493</v>
       </c>
       <c r="E249">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F249" t="s">
         <v>1578</v>
@@ -16876,7 +16876,7 @@
         <v>1493</v>
       </c>
       <c r="E250">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F250" t="s">
         <v>1578</v>
@@ -16911,7 +16911,7 @@
         <v>1494</v>
       </c>
       <c r="E251">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F251" t="s">
         <v>1578</v>
@@ -16946,7 +16946,7 @@
         <v>1494</v>
       </c>
       <c r="E252">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F252" t="s">
         <v>1578</v>
@@ -16981,7 +16981,7 @@
         <v>1494</v>
       </c>
       <c r="E253">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F253" t="s">
         <v>1578</v>
@@ -17016,7 +17016,7 @@
         <v>1494</v>
       </c>
       <c r="E254">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F254" t="s">
         <v>1578</v>
@@ -17051,7 +17051,7 @@
         <v>1494</v>
       </c>
       <c r="E255">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F255" t="s">
         <v>1578</v>
@@ -17086,7 +17086,7 @@
         <v>1495</v>
       </c>
       <c r="E256">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F256" t="s">
         <v>1578</v>
@@ -17121,7 +17121,7 @@
         <v>1495</v>
       </c>
       <c r="E257">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F257" t="s">
         <v>1578</v>
@@ -17156,7 +17156,7 @@
         <v>1495</v>
       </c>
       <c r="E258">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F258" t="s">
         <v>1578</v>
@@ -17191,7 +17191,7 @@
         <v>1495</v>
       </c>
       <c r="E259">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F259" t="s">
         <v>1578</v>
@@ -17226,7 +17226,7 @@
         <v>1495</v>
       </c>
       <c r="E260">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F260" t="s">
         <v>1578</v>
@@ -17261,7 +17261,7 @@
         <v>1495</v>
       </c>
       <c r="E261">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F261" t="s">
         <v>1578</v>
@@ -17296,7 +17296,7 @@
         <v>1496</v>
       </c>
       <c r="E262">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F262" t="s">
         <v>1578</v>
@@ -17331,7 +17331,7 @@
         <v>1497</v>
       </c>
       <c r="E263">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F263" t="s">
         <v>1579</v>
@@ -17366,7 +17366,7 @@
         <v>1497</v>
       </c>
       <c r="E264">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F264" t="s">
         <v>1578</v>
@@ -17401,7 +17401,7 @@
         <v>1497</v>
       </c>
       <c r="E265">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F265" t="s">
         <v>1581</v>
@@ -17436,7 +17436,7 @@
         <v>1497</v>
       </c>
       <c r="E266">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F266" t="s">
         <v>1578</v>
@@ -17471,7 +17471,7 @@
         <v>1497</v>
       </c>
       <c r="E267">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F267" t="s">
         <v>1578</v>
@@ -17506,7 +17506,7 @@
         <v>1497</v>
       </c>
       <c r="E268">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F268" t="s">
         <v>1578</v>
@@ -17541,7 +17541,7 @@
         <v>1498</v>
       </c>
       <c r="E269">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F269" t="s">
         <v>1578</v>
@@ -17576,7 +17576,7 @@
         <v>1498</v>
       </c>
       <c r="E270">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F270" t="s">
         <v>1578</v>
@@ -17611,7 +17611,7 @@
         <v>1498</v>
       </c>
       <c r="E271">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F271" t="s">
         <v>1578</v>
@@ -17646,7 +17646,7 @@
         <v>1498</v>
       </c>
       <c r="E272">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F272" t="s">
         <v>1578</v>
@@ -17681,7 +17681,7 @@
         <v>1499</v>
       </c>
       <c r="E273">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F273" t="s">
         <v>1578</v>
@@ -17716,7 +17716,7 @@
         <v>1500</v>
       </c>
       <c r="E274">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F274" t="s">
         <v>1578</v>
@@ -17754,7 +17754,7 @@
         <v>1500</v>
       </c>
       <c r="E275">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F275" t="s">
         <v>1578</v>
@@ -17789,7 +17789,7 @@
         <v>1501</v>
       </c>
       <c r="E276">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F276" t="s">
         <v>1578</v>
@@ -17824,7 +17824,7 @@
         <v>1501</v>
       </c>
       <c r="E277">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F277" t="s">
         <v>1578</v>
@@ -17859,7 +17859,7 @@
         <v>1501</v>
       </c>
       <c r="E278">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F278" t="s">
         <v>1578</v>
@@ -17894,7 +17894,7 @@
         <v>1501</v>
       </c>
       <c r="E279">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F279" t="s">
         <v>1578</v>
@@ -17932,7 +17932,7 @@
         <v>1501</v>
       </c>
       <c r="E280">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F280" t="s">
         <v>1578</v>
@@ -17967,7 +17967,7 @@
         <v>1501</v>
       </c>
       <c r="E281">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F281" t="s">
         <v>1578</v>
@@ -18002,7 +18002,7 @@
         <v>1502</v>
       </c>
       <c r="E282">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F282" t="s">
         <v>1578</v>
@@ -18037,7 +18037,7 @@
         <v>1502</v>
       </c>
       <c r="E283">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F283" t="s">
         <v>1578</v>
@@ -18072,7 +18072,7 @@
         <v>1503</v>
       </c>
       <c r="E284">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F284" t="s">
         <v>1578</v>
@@ -18107,7 +18107,7 @@
         <v>1503</v>
       </c>
       <c r="E285">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F285" t="s">
         <v>1578</v>
@@ -18142,7 +18142,7 @@
         <v>1504</v>
       </c>
       <c r="E286">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F286" t="s">
         <v>1578</v>
@@ -18177,7 +18177,7 @@
         <v>1504</v>
       </c>
       <c r="E287">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F287" t="s">
         <v>1578</v>
@@ -18212,7 +18212,7 @@
         <v>1504</v>
       </c>
       <c r="E288">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F288" t="s">
         <v>1578</v>
@@ -18247,7 +18247,7 @@
         <v>1504</v>
       </c>
       <c r="E289">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F289" t="s">
         <v>1578</v>
@@ -18282,7 +18282,7 @@
         <v>1505</v>
       </c>
       <c r="E290">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F290" t="s">
         <v>1578</v>
@@ -18317,7 +18317,7 @@
         <v>1505</v>
       </c>
       <c r="E291">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F291" t="s">
         <v>1578</v>
@@ -18352,7 +18352,7 @@
         <v>1505</v>
       </c>
       <c r="E292">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F292" t="s">
         <v>1578</v>
@@ -18387,7 +18387,7 @@
         <v>1505</v>
       </c>
       <c r="E293">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F293" t="s">
         <v>1578</v>
@@ -18422,7 +18422,7 @@
         <v>1506</v>
       </c>
       <c r="E294">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F294" t="s">
         <v>1578</v>
@@ -18457,7 +18457,7 @@
         <v>1506</v>
       </c>
       <c r="E295">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F295" t="s">
         <v>1578</v>
@@ -18492,7 +18492,7 @@
         <v>1507</v>
       </c>
       <c r="E296">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F296" t="s">
         <v>1578</v>
@@ -18527,7 +18527,7 @@
         <v>1507</v>
       </c>
       <c r="E297">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F297" t="s">
         <v>1578</v>
@@ -18562,7 +18562,7 @@
         <v>1507</v>
       </c>
       <c r="E298">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F298" t="s">
         <v>1578</v>
@@ -18597,7 +18597,7 @@
         <v>1507</v>
       </c>
       <c r="E299">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F299" t="s">
         <v>1578</v>
@@ -18632,7 +18632,7 @@
         <v>1507</v>
       </c>
       <c r="E300">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F300" t="s">
         <v>1578</v>
@@ -18667,7 +18667,7 @@
         <v>1508</v>
       </c>
       <c r="E301">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F301" t="s">
         <v>1578</v>
@@ -18702,7 +18702,7 @@
         <v>1508</v>
       </c>
       <c r="E302">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F302" t="s">
         <v>1578</v>
@@ -18737,7 +18737,7 @@
         <v>1508</v>
       </c>
       <c r="E303">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F303" t="s">
         <v>1578</v>
@@ -18772,7 +18772,7 @@
         <v>1509</v>
       </c>
       <c r="E304">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F304" t="s">
         <v>1578</v>
@@ -18807,7 +18807,7 @@
         <v>1509</v>
       </c>
       <c r="E305">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F305" t="s">
         <v>1578</v>
@@ -18842,7 +18842,7 @@
         <v>1510</v>
       </c>
       <c r="E306">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F306" t="s">
         <v>1578</v>
@@ -18877,7 +18877,7 @@
         <v>1510</v>
       </c>
       <c r="E307">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F307" t="s">
         <v>1578</v>
@@ -18912,7 +18912,7 @@
         <v>1510</v>
       </c>
       <c r="E308">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F308" t="s">
         <v>1578</v>
@@ -18947,7 +18947,7 @@
         <v>1510</v>
       </c>
       <c r="E309">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F309" t="s">
         <v>1578</v>
@@ -18982,7 +18982,7 @@
         <v>1510</v>
       </c>
       <c r="E310">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F310" t="s">
         <v>1578</v>
@@ -19017,7 +19017,7 @@
         <v>1510</v>
       </c>
       <c r="E311">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F311" t="s">
         <v>1578</v>
@@ -19052,7 +19052,7 @@
         <v>1510</v>
       </c>
       <c r="E312">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F312" t="s">
         <v>1578</v>
@@ -19087,7 +19087,7 @@
         <v>1510</v>
       </c>
       <c r="E313">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F313" t="s">
         <v>1578</v>
@@ -19122,7 +19122,7 @@
         <v>1511</v>
       </c>
       <c r="E314">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F314" t="s">
         <v>1578</v>
@@ -19157,7 +19157,7 @@
         <v>1511</v>
       </c>
       <c r="E315">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F315" t="s">
         <v>1578</v>
@@ -19192,7 +19192,7 @@
         <v>1511</v>
       </c>
       <c r="E316">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F316" t="s">
         <v>1578</v>
@@ -19227,7 +19227,7 @@
         <v>1512</v>
       </c>
       <c r="E317">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F317" t="s">
         <v>1578</v>
@@ -19262,7 +19262,7 @@
         <v>1513</v>
       </c>
       <c r="E318">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F318" t="s">
         <v>1578</v>
@@ -19297,7 +19297,7 @@
         <v>1514</v>
       </c>
       <c r="E319">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F319" t="s">
         <v>1580</v>
@@ -19332,7 +19332,7 @@
         <v>1514</v>
       </c>
       <c r="E320">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F320" t="s">
         <v>1578</v>
@@ -19367,7 +19367,7 @@
         <v>1514</v>
       </c>
       <c r="E321">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F321" t="s">
         <v>1578</v>
@@ -19402,7 +19402,7 @@
         <v>1514</v>
       </c>
       <c r="E322">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F322" t="s">
         <v>1578</v>
@@ -19437,7 +19437,7 @@
         <v>1514</v>
       </c>
       <c r="E323">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F323" t="s">
         <v>1578</v>
@@ -19472,7 +19472,7 @@
         <v>1514</v>
       </c>
       <c r="E324">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F324" t="s">
         <v>1578</v>
@@ -19507,7 +19507,7 @@
         <v>1515</v>
       </c>
       <c r="E325">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F325" t="s">
         <v>1578</v>
@@ -19542,7 +19542,7 @@
         <v>1515</v>
       </c>
       <c r="E326">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F326" t="s">
         <v>1578</v>
@@ -19577,7 +19577,7 @@
         <v>1516</v>
       </c>
       <c r="E327">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F327" t="s">
         <v>1578</v>
@@ -19612,7 +19612,7 @@
         <v>1516</v>
       </c>
       <c r="E328">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F328" t="s">
         <v>1578</v>
@@ -19647,7 +19647,7 @@
         <v>1517</v>
       </c>
       <c r="E329">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F329" t="s">
         <v>1578</v>
@@ -19682,7 +19682,7 @@
         <v>1518</v>
       </c>
       <c r="E330">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F330" t="s">
         <v>1578</v>
@@ -19717,7 +19717,7 @@
         <v>1519</v>
       </c>
       <c r="E331">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F331" t="s">
         <v>1578</v>
@@ -19752,7 +19752,7 @@
         <v>1519</v>
       </c>
       <c r="E332">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F332" t="s">
         <v>1578</v>
@@ -19787,7 +19787,7 @@
         <v>1520</v>
       </c>
       <c r="E333">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F333" t="s">
         <v>1578</v>
@@ -19822,7 +19822,7 @@
         <v>1520</v>
       </c>
       <c r="E334">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F334" t="s">
         <v>1578</v>
@@ -19857,7 +19857,7 @@
         <v>1520</v>
       </c>
       <c r="E335">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F335" t="s">
         <v>1578</v>
@@ -19892,7 +19892,7 @@
         <v>1521</v>
       </c>
       <c r="E336">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F336" t="s">
         <v>1578</v>
@@ -19927,7 +19927,7 @@
         <v>1521</v>
       </c>
       <c r="E337">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F337" t="s">
         <v>1578</v>
@@ -19962,7 +19962,7 @@
         <v>1521</v>
       </c>
       <c r="E338">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F338" t="s">
         <v>1578</v>
@@ -19997,7 +19997,7 @@
         <v>1521</v>
       </c>
       <c r="E339">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F339" t="s">
         <v>1578</v>
@@ -20032,7 +20032,7 @@
         <v>1521</v>
       </c>
       <c r="E340">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F340" t="s">
         <v>1578</v>
@@ -20067,7 +20067,7 @@
         <v>1521</v>
       </c>
       <c r="E341">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F341" t="s">
         <v>1578</v>
@@ -20102,7 +20102,7 @@
         <v>1521</v>
       </c>
       <c r="E342">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F342" t="s">
         <v>1578</v>
@@ -20137,7 +20137,7 @@
         <v>1521</v>
       </c>
       <c r="E343">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F343" t="s">
         <v>1578</v>
@@ -20172,7 +20172,7 @@
         <v>1521</v>
       </c>
       <c r="E344">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F344" t="s">
         <v>1578</v>
@@ -20207,7 +20207,7 @@
         <v>1522</v>
       </c>
       <c r="E345">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F345" t="s">
         <v>1578</v>
@@ -20242,7 +20242,7 @@
         <v>1522</v>
       </c>
       <c r="E346">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F346" t="s">
         <v>1578</v>
@@ -20277,7 +20277,7 @@
         <v>1522</v>
       </c>
       <c r="E347">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F347" t="s">
         <v>1578</v>
@@ -20312,7 +20312,7 @@
         <v>1523</v>
       </c>
       <c r="E348">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F348" t="s">
         <v>1578</v>
@@ -20347,7 +20347,7 @@
         <v>1524</v>
       </c>
       <c r="E349">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F349" t="s">
         <v>1578</v>
@@ -20382,7 +20382,7 @@
         <v>1524</v>
       </c>
       <c r="E350">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F350" t="s">
         <v>1578</v>
@@ -20417,7 +20417,7 @@
         <v>1524</v>
       </c>
       <c r="E351">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F351" t="s">
         <v>1578</v>
@@ -20452,7 +20452,7 @@
         <v>1524</v>
       </c>
       <c r="E352">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F352" t="s">
         <v>1578</v>
@@ -20487,7 +20487,7 @@
         <v>1524</v>
       </c>
       <c r="E353">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F353" t="s">
         <v>1582</v>
@@ -20525,7 +20525,7 @@
         <v>1524</v>
       </c>
       <c r="E354">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F354" t="s">
         <v>1578</v>
@@ -20560,7 +20560,7 @@
         <v>1524</v>
       </c>
       <c r="E355">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F355" t="s">
         <v>1578</v>
@@ -20595,7 +20595,7 @@
         <v>1525</v>
       </c>
       <c r="E356">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F356" t="s">
         <v>1578</v>
@@ -20630,7 +20630,7 @@
         <v>1525</v>
       </c>
       <c r="E357">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F357" t="s">
         <v>1578</v>
@@ -20665,7 +20665,7 @@
         <v>1525</v>
       </c>
       <c r="E358">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F358" t="s">
         <v>1578</v>
@@ -20700,7 +20700,7 @@
         <v>1525</v>
       </c>
       <c r="E359">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F359" t="s">
         <v>1578</v>
@@ -20738,7 +20738,7 @@
         <v>1525</v>
       </c>
       <c r="E360">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F360" t="s">
         <v>1578</v>
@@ -20773,7 +20773,7 @@
         <v>1525</v>
       </c>
       <c r="E361">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F361" t="s">
         <v>1578</v>
@@ -20808,7 +20808,7 @@
         <v>1525</v>
       </c>
       <c r="E362">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F362" t="s">
         <v>1578</v>
@@ -20843,7 +20843,7 @@
         <v>1525</v>
       </c>
       <c r="E363">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F363" t="s">
         <v>1578</v>
@@ -20878,7 +20878,7 @@
         <v>1525</v>
       </c>
       <c r="E364">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F364" t="s">
         <v>1578</v>
@@ -20913,7 +20913,7 @@
         <v>1526</v>
       </c>
       <c r="E365">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F365" t="s">
         <v>1579</v>
@@ -20948,7 +20948,7 @@
         <v>1527</v>
       </c>
       <c r="E366">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F366" t="s">
         <v>1582</v>
@@ -20983,7 +20983,7 @@
         <v>1528</v>
       </c>
       <c r="E367">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F367" t="s">
         <v>1578</v>
@@ -21018,7 +21018,7 @@
         <v>1529</v>
       </c>
       <c r="E368">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F368" t="s">
         <v>1578</v>
@@ -21053,7 +21053,7 @@
         <v>1529</v>
       </c>
       <c r="E369">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F369" t="s">
         <v>1578</v>
@@ -21088,7 +21088,7 @@
         <v>1530</v>
       </c>
       <c r="E370">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F370" t="s">
         <v>1578</v>
@@ -21123,7 +21123,7 @@
         <v>1531</v>
       </c>
       <c r="E371">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F371" t="s">
         <v>1581</v>
@@ -21158,7 +21158,7 @@
         <v>1531</v>
       </c>
       <c r="E372">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F372" t="s">
         <v>1578</v>
@@ -21193,7 +21193,7 @@
         <v>1531</v>
       </c>
       <c r="E373">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F373" t="s">
         <v>1578</v>
@@ -21228,7 +21228,7 @@
         <v>1531</v>
       </c>
       <c r="E374">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F374" t="s">
         <v>1578</v>
@@ -21263,7 +21263,7 @@
         <v>1531</v>
       </c>
       <c r="E375">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F375" t="s">
         <v>1578</v>
@@ -21298,7 +21298,7 @@
         <v>1531</v>
       </c>
       <c r="E376">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F376" t="s">
         <v>1578</v>
@@ -21333,7 +21333,7 @@
         <v>1532</v>
       </c>
       <c r="E377">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F377" t="s">
         <v>1578</v>
@@ -21368,7 +21368,7 @@
         <v>1532</v>
       </c>
       <c r="E378">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F378" t="s">
         <v>1578</v>
@@ -21403,7 +21403,7 @@
         <v>1532</v>
       </c>
       <c r="E379">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F379" t="s">
         <v>1578</v>
@@ -21438,7 +21438,7 @@
         <v>1533</v>
       </c>
       <c r="E380">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F380" t="s">
         <v>1578</v>
@@ -21473,7 +21473,7 @@
         <v>1533</v>
       </c>
       <c r="E381">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F381" t="s">
         <v>1578</v>
@@ -21508,7 +21508,7 @@
         <v>1533</v>
       </c>
       <c r="E382">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F382" t="s">
         <v>1578</v>
@@ -21546,7 +21546,7 @@
         <v>1533</v>
       </c>
       <c r="E383">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F383" t="s">
         <v>1578</v>
@@ -21581,7 +21581,7 @@
         <v>1534</v>
       </c>
       <c r="E384">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F384" t="s">
         <v>1578</v>
@@ -21616,7 +21616,7 @@
         <v>1534</v>
       </c>
       <c r="E385">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F385" t="s">
         <v>1578</v>
@@ -21651,7 +21651,7 @@
         <v>1534</v>
       </c>
       <c r="E386">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F386" t="s">
         <v>1578</v>
@@ -21686,7 +21686,7 @@
         <v>1534</v>
       </c>
       <c r="E387">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F387" t="s">
         <v>1578</v>
@@ -21721,7 +21721,7 @@
         <v>1534</v>
       </c>
       <c r="E388">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F388" t="s">
         <v>1578</v>
@@ -21756,7 +21756,7 @@
         <v>1535</v>
       </c>
       <c r="E389">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F389" t="s">
         <v>1578</v>
@@ -21791,7 +21791,7 @@
         <v>1535</v>
       </c>
       <c r="E390">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F390" t="s">
         <v>1578</v>
@@ -21826,7 +21826,7 @@
         <v>1536</v>
       </c>
       <c r="E391">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F391" t="s">
         <v>1578</v>
@@ -21861,7 +21861,7 @@
         <v>1536</v>
       </c>
       <c r="E392">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F392" t="s">
         <v>1578</v>
@@ -21896,7 +21896,7 @@
         <v>1536</v>
       </c>
       <c r="E393">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F393" t="s">
         <v>1578</v>
@@ -21931,7 +21931,7 @@
         <v>1536</v>
       </c>
       <c r="E394">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F394" t="s">
         <v>1578</v>
@@ -21966,7 +21966,7 @@
         <v>1536</v>
       </c>
       <c r="E395">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F395" t="s">
         <v>1578</v>
@@ -22001,7 +22001,7 @@
         <v>1536</v>
       </c>
       <c r="E396">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F396" t="s">
         <v>1578</v>
@@ -22036,7 +22036,7 @@
         <v>1536</v>
       </c>
       <c r="E397">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F397" t="s">
         <v>1578</v>
@@ -22071,7 +22071,7 @@
         <v>1536</v>
       </c>
       <c r="E398">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F398" t="s">
         <v>1578</v>
@@ -22106,7 +22106,7 @@
         <v>1536</v>
       </c>
       <c r="E399">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F399" t="s">
         <v>1578</v>
@@ -22141,7 +22141,7 @@
         <v>1536</v>
       </c>
       <c r="E400">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F400" t="s">
         <v>1578</v>
@@ -22176,7 +22176,7 @@
         <v>1537</v>
       </c>
       <c r="E401">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F401" t="s">
         <v>1578</v>
@@ -22211,7 +22211,7 @@
         <v>1537</v>
       </c>
       <c r="E402">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F402" t="s">
         <v>1578</v>
@@ -22246,7 +22246,7 @@
         <v>1537</v>
       </c>
       <c r="E403">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F403" t="s">
         <v>1579</v>
@@ -22281,7 +22281,7 @@
         <v>1538</v>
       </c>
       <c r="E404">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F404" t="s">
         <v>1578</v>
@@ -22316,7 +22316,7 @@
         <v>1538</v>
       </c>
       <c r="E405">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F405" t="s">
         <v>1578</v>
@@ -22351,7 +22351,7 @@
         <v>1538</v>
       </c>
       <c r="E406">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F406" t="s">
         <v>1578</v>
@@ -22386,7 +22386,7 @@
         <v>1538</v>
       </c>
       <c r="E407">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F407" t="s">
         <v>1578</v>
@@ -22421,7 +22421,7 @@
         <v>1538</v>
       </c>
       <c r="E408">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F408" t="s">
         <v>1578</v>
@@ -22456,7 +22456,7 @@
         <v>1538</v>
       </c>
       <c r="E409">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F409" t="s">
         <v>1578</v>
@@ -22491,7 +22491,7 @@
         <v>1538</v>
       </c>
       <c r="E410">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F410" t="s">
         <v>1581</v>
@@ -22526,7 +22526,7 @@
         <v>1539</v>
       </c>
       <c r="E411">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F411" t="s">
         <v>1578</v>
@@ -22561,7 +22561,7 @@
         <v>1539</v>
       </c>
       <c r="E412">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F412" t="s">
         <v>1578</v>
@@ -22596,7 +22596,7 @@
         <v>1539</v>
       </c>
       <c r="E413">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F413" t="s">
         <v>1578</v>
@@ -22631,7 +22631,7 @@
         <v>1539</v>
       </c>
       <c r="E414">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F414" t="s">
         <v>1578</v>
@@ -22666,7 +22666,7 @@
         <v>1540</v>
       </c>
       <c r="E415">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F415" t="s">
         <v>1581</v>
@@ -22701,7 +22701,7 @@
         <v>1540</v>
       </c>
       <c r="E416">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F416" t="s">
         <v>1578</v>
@@ -22736,7 +22736,7 @@
         <v>1540</v>
       </c>
       <c r="E417">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F417" t="s">
         <v>1578</v>
@@ -22771,7 +22771,7 @@
         <v>1540</v>
       </c>
       <c r="E418">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F418" t="s">
         <v>1578</v>
@@ -22806,7 +22806,7 @@
         <v>1540</v>
       </c>
       <c r="E419">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F419" t="s">
         <v>1578</v>
@@ -22841,7 +22841,7 @@
         <v>1540</v>
       </c>
       <c r="E420">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F420" t="s">
         <v>1582</v>
@@ -22876,7 +22876,7 @@
         <v>1540</v>
       </c>
       <c r="E421">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F421" t="s">
         <v>1578</v>
@@ -22911,7 +22911,7 @@
         <v>1540</v>
       </c>
       <c r="E422">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F422" t="s">
         <v>1578</v>
@@ -22946,7 +22946,7 @@
         <v>1541</v>
       </c>
       <c r="E423">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F423" t="s">
         <v>1578</v>
@@ -22981,7 +22981,7 @@
         <v>1541</v>
       </c>
       <c r="E424">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F424" t="s">
         <v>1578</v>
@@ -23016,7 +23016,7 @@
         <v>1541</v>
       </c>
       <c r="E425">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F425" t="s">
         <v>1578</v>
@@ -23051,7 +23051,7 @@
         <v>1541</v>
       </c>
       <c r="E426">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F426" t="s">
         <v>1578</v>
@@ -23086,7 +23086,7 @@
         <v>1541</v>
       </c>
       <c r="E427">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F427" t="s">
         <v>1580</v>
@@ -23121,7 +23121,7 @@
         <v>1541</v>
       </c>
       <c r="E428">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F428" t="s">
         <v>1578</v>
@@ -23156,7 +23156,7 @@
         <v>1541</v>
       </c>
       <c r="E429">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F429" t="s">
         <v>1578</v>
@@ -23191,7 +23191,7 @@
         <v>1542</v>
       </c>
       <c r="E430">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F430" t="s">
         <v>1578</v>
@@ -23226,7 +23226,7 @@
         <v>1542</v>
       </c>
       <c r="E431">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F431" t="s">
         <v>1578</v>
@@ -23261,7 +23261,7 @@
         <v>1542</v>
       </c>
       <c r="E432">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F432" t="s">
         <v>1578</v>
@@ -23296,7 +23296,7 @@
         <v>1542</v>
       </c>
       <c r="E433">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F433" t="s">
         <v>1578</v>
@@ -23331,7 +23331,7 @@
         <v>1542</v>
       </c>
       <c r="E434">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F434" t="s">
         <v>1578</v>
@@ -23366,7 +23366,7 @@
         <v>1543</v>
       </c>
       <c r="E435">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F435" t="s">
         <v>1578</v>
@@ -23401,7 +23401,7 @@
         <v>1543</v>
       </c>
       <c r="E436">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F436" t="s">
         <v>1578</v>
@@ -23436,7 +23436,7 @@
         <v>1543</v>
       </c>
       <c r="E437">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F437" t="s">
         <v>1578</v>
@@ -23471,7 +23471,7 @@
         <v>1543</v>
       </c>
       <c r="E438">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F438" t="s">
         <v>1578</v>
@@ -23506,7 +23506,7 @@
         <v>1543</v>
       </c>
       <c r="E439">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F439" t="s">
         <v>1578</v>
@@ -23544,7 +23544,7 @@
         <v>1544</v>
       </c>
       <c r="E440">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F440" t="s">
         <v>1578</v>
@@ -23579,7 +23579,7 @@
         <v>1544</v>
       </c>
       <c r="E441">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F441" t="s">
         <v>1578</v>
@@ -23614,7 +23614,7 @@
         <v>1544</v>
       </c>
       <c r="E442">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F442" t="s">
         <v>1578</v>
@@ -23649,7 +23649,7 @@
         <v>1544</v>
       </c>
       <c r="E443">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F443" t="s">
         <v>1578</v>
@@ -23684,7 +23684,7 @@
         <v>1544</v>
       </c>
       <c r="E444">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F444" t="s">
         <v>1578</v>
@@ -23719,7 +23719,7 @@
         <v>1544</v>
       </c>
       <c r="E445">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F445" t="s">
         <v>1578</v>
@@ -23754,7 +23754,7 @@
         <v>1545</v>
       </c>
       <c r="E446">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F446" t="s">
         <v>1578</v>
@@ -23789,7 +23789,7 @@
         <v>1545</v>
       </c>
       <c r="E447">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F447" t="s">
         <v>1578</v>
@@ -23824,7 +23824,7 @@
         <v>1545</v>
       </c>
       <c r="E448">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F448" t="s">
         <v>1578</v>
@@ -23859,7 +23859,7 @@
         <v>1546</v>
       </c>
       <c r="E449">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F449" t="s">
         <v>1578</v>
@@ -23894,7 +23894,7 @@
         <v>1547</v>
       </c>
       <c r="E450">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F450" t="s">
         <v>1578</v>
@@ -23929,7 +23929,7 @@
         <v>1547</v>
       </c>
       <c r="E451">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F451" t="s">
         <v>1578</v>
@@ -23964,7 +23964,7 @@
         <v>1547</v>
       </c>
       <c r="E452">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F452" t="s">
         <v>1580</v>
@@ -24002,7 +24002,7 @@
         <v>1547</v>
       </c>
       <c r="E453">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F453" t="s">
         <v>1578</v>
@@ -24037,7 +24037,7 @@
         <v>1547</v>
       </c>
       <c r="E454">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F454" t="s">
         <v>1578</v>
@@ -24072,7 +24072,7 @@
         <v>1548</v>
       </c>
       <c r="E455">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F455" t="s">
         <v>1578</v>
@@ -24107,7 +24107,7 @@
         <v>1548</v>
       </c>
       <c r="E456">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F456" t="s">
         <v>1578</v>
@@ -24142,7 +24142,7 @@
         <v>1548</v>
       </c>
       <c r="E457">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F457" t="s">
         <v>1578</v>
@@ -24177,7 +24177,7 @@
         <v>1548</v>
       </c>
       <c r="E458">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F458" t="s">
         <v>1578</v>
@@ -24212,7 +24212,7 @@
         <v>1549</v>
       </c>
       <c r="E459">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F459" t="s">
         <v>1578</v>
@@ -24247,7 +24247,7 @@
         <v>1549</v>
       </c>
       <c r="E460">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F460" t="s">
         <v>1578</v>
@@ -24282,7 +24282,7 @@
         <v>1549</v>
       </c>
       <c r="E461">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F461" t="s">
         <v>1578</v>
@@ -24317,7 +24317,7 @@
         <v>1549</v>
       </c>
       <c r="E462">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F462" t="s">
         <v>1578</v>
@@ -24352,7 +24352,7 @@
         <v>1549</v>
       </c>
       <c r="E463">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F463" t="s">
         <v>1578</v>
@@ -24387,7 +24387,7 @@
         <v>1549</v>
       </c>
       <c r="E464">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F464" t="s">
         <v>1578</v>
@@ -24422,7 +24422,7 @@
         <v>1549</v>
       </c>
       <c r="E465">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F465" t="s">
         <v>1578</v>
@@ -24457,7 +24457,7 @@
         <v>1549</v>
       </c>
       <c r="E466">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F466" t="s">
         <v>1578</v>
@@ -24492,7 +24492,7 @@
         <v>1550</v>
       </c>
       <c r="E467">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F467" t="s">
         <v>1578</v>
@@ -24527,7 +24527,7 @@
         <v>1550</v>
       </c>
       <c r="E468">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F468" t="s">
         <v>1578</v>
@@ -24562,7 +24562,7 @@
         <v>1551</v>
       </c>
       <c r="E469">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F469" t="s">
         <v>1578</v>
@@ -24597,7 +24597,7 @@
         <v>1551</v>
       </c>
       <c r="E470">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F470" t="s">
         <v>1578</v>
@@ -24632,7 +24632,7 @@
         <v>1551</v>
       </c>
       <c r="E471">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F471" t="s">
         <v>1578</v>
@@ -24667,7 +24667,7 @@
         <v>1551</v>
       </c>
       <c r="E472">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F472" t="s">
         <v>1582</v>
@@ -24705,7 +24705,7 @@
         <v>1551</v>
       </c>
       <c r="E473">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F473" t="s">
         <v>1578</v>
@@ -24740,7 +24740,7 @@
         <v>1551</v>
       </c>
       <c r="E474">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F474" t="s">
         <v>1582</v>
@@ -24775,7 +24775,7 @@
         <v>1552</v>
       </c>
       <c r="E475">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F475" t="s">
         <v>1578</v>
@@ -24810,7 +24810,7 @@
         <v>1553</v>
       </c>
       <c r="E476">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F476" t="s">
         <v>1578</v>
@@ -24845,7 +24845,7 @@
         <v>1553</v>
       </c>
       <c r="E477">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F477" t="s">
         <v>1578</v>
@@ -24880,7 +24880,7 @@
         <v>1553</v>
       </c>
       <c r="E478">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F478" t="s">
         <v>1578</v>
@@ -24915,7 +24915,7 @@
         <v>1553</v>
       </c>
       <c r="E479">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F479" t="s">
         <v>1578</v>
@@ -24950,7 +24950,7 @@
         <v>1554</v>
       </c>
       <c r="E480">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F480" t="s">
         <v>1578</v>
@@ -24985,7 +24985,7 @@
         <v>1554</v>
       </c>
       <c r="E481">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F481" t="s">
         <v>1582</v>
@@ -25020,7 +25020,7 @@
         <v>1554</v>
       </c>
       <c r="E482">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F482" t="s">
         <v>1578</v>
@@ -25055,7 +25055,7 @@
         <v>1554</v>
       </c>
       <c r="E483">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F483" t="s">
         <v>1578</v>
@@ -25090,7 +25090,7 @@
         <v>1554</v>
       </c>
       <c r="E484">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F484" t="s">
         <v>1578</v>
@@ -25125,7 +25125,7 @@
         <v>1555</v>
       </c>
       <c r="E485">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F485" t="s">
         <v>1578</v>
@@ -25160,7 +25160,7 @@
         <v>1555</v>
       </c>
       <c r="E486">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F486" t="s">
         <v>1578</v>
@@ -25195,7 +25195,7 @@
         <v>1555</v>
       </c>
       <c r="E487">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F487" t="s">
         <v>1578</v>
@@ -25230,7 +25230,7 @@
         <v>1556</v>
       </c>
       <c r="E488">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F488" t="s">
         <v>1578</v>
@@ -25265,7 +25265,7 @@
         <v>1556</v>
       </c>
       <c r="E489">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F489" t="s">
         <v>1578</v>
@@ -25300,7 +25300,7 @@
         <v>1556</v>
       </c>
       <c r="E490">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F490" t="s">
         <v>1578</v>
@@ -25335,7 +25335,7 @@
         <v>1556</v>
       </c>
       <c r="E491">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F491" t="s">
         <v>1578</v>
@@ -25370,7 +25370,7 @@
         <v>1556</v>
       </c>
       <c r="E492">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F492" t="s">
         <v>1578</v>
@@ -25405,7 +25405,7 @@
         <v>1556</v>
       </c>
       <c r="E493">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F493" t="s">
         <v>1578</v>
@@ -25440,7 +25440,7 @@
         <v>1557</v>
       </c>
       <c r="E494">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F494" t="s">
         <v>1578</v>
@@ -25475,7 +25475,7 @@
         <v>1557</v>
       </c>
       <c r="E495">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F495" t="s">
         <v>1578</v>
@@ -25510,7 +25510,7 @@
         <v>1557</v>
       </c>
       <c r="E496">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F496" t="s">
         <v>1578</v>
@@ -25545,7 +25545,7 @@
         <v>1557</v>
       </c>
       <c r="E497">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F497" t="s">
         <v>1578</v>
@@ -25580,7 +25580,7 @@
         <v>1557</v>
       </c>
       <c r="E498">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F498" t="s">
         <v>1578</v>
@@ -25615,7 +25615,7 @@
         <v>1557</v>
       </c>
       <c r="E499">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F499" t="s">
         <v>1578</v>
@@ -25650,7 +25650,7 @@
         <v>1557</v>
       </c>
       <c r="E500">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F500" t="s">
         <v>1578</v>
@@ -25685,7 +25685,7 @@
         <v>1557</v>
       </c>
       <c r="E501">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F501" t="s">
         <v>1578</v>
@@ -25720,7 +25720,7 @@
         <v>1557</v>
       </c>
       <c r="E502">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F502" t="s">
         <v>1578</v>
@@ -25755,7 +25755,7 @@
         <v>1557</v>
       </c>
       <c r="E503">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F503" t="s">
         <v>1578</v>
@@ -25790,7 +25790,7 @@
         <v>1557</v>
       </c>
       <c r="E504">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F504" t="s">
         <v>1578</v>
@@ -25825,7 +25825,7 @@
         <v>1557</v>
       </c>
       <c r="E505">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F505" t="s">
         <v>1578</v>
@@ -25860,7 +25860,7 @@
         <v>1557</v>
       </c>
       <c r="E506">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F506" t="s">
         <v>1578</v>
@@ -25895,7 +25895,7 @@
         <v>1557</v>
       </c>
       <c r="E507">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F507" t="s">
         <v>1578</v>
@@ -25930,7 +25930,7 @@
         <v>1557</v>
       </c>
       <c r="E508">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F508" t="s">
         <v>1578</v>
@@ -25965,7 +25965,7 @@
         <v>1557</v>
       </c>
       <c r="E509">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F509" t="s">
         <v>1578</v>
@@ -26000,7 +26000,7 @@
         <v>1557</v>
       </c>
       <c r="E510">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F510" t="s">
         <v>1578</v>
@@ -26035,7 +26035,7 @@
         <v>1557</v>
       </c>
       <c r="E511">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F511" t="s">
         <v>1578</v>
@@ -26070,7 +26070,7 @@
         <v>1557</v>
       </c>
       <c r="E512">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F512" t="s">
         <v>1578</v>
@@ -26105,7 +26105,7 @@
         <v>1557</v>
       </c>
       <c r="E513">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F513" t="s">
         <v>1578</v>
@@ -26140,7 +26140,7 @@
         <v>1557</v>
       </c>
       <c r="E514">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F514" t="s">
         <v>1578</v>
@@ -26175,7 +26175,7 @@
         <v>1557</v>
       </c>
       <c r="E515">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F515" t="s">
         <v>1578</v>
@@ -26210,7 +26210,7 @@
         <v>1557</v>
       </c>
       <c r="E516">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F516" t="s">
         <v>1578</v>
@@ -26245,7 +26245,7 @@
         <v>1557</v>
       </c>
       <c r="E517">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F517" t="s">
         <v>1578</v>
@@ -26280,7 +26280,7 @@
         <v>1557</v>
       </c>
       <c r="E518">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F518" t="s">
         <v>1578</v>
@@ -26315,7 +26315,7 @@
         <v>1558</v>
       </c>
       <c r="E519">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F519" t="s">
         <v>1578</v>
@@ -26350,7 +26350,7 @@
         <v>1558</v>
       </c>
       <c r="E520">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F520" t="s">
         <v>1578</v>
@@ -26385,7 +26385,7 @@
         <v>1558</v>
       </c>
       <c r="E521">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F521" t="s">
         <v>1578</v>
@@ -26420,7 +26420,7 @@
         <v>1558</v>
       </c>
       <c r="E522">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F522" t="s">
         <v>1578</v>
@@ -26455,7 +26455,7 @@
         <v>1558</v>
       </c>
       <c r="E523">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F523" t="s">
         <v>1578</v>
@@ -26490,7 +26490,7 @@
         <v>1558</v>
       </c>
       <c r="E524">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F524" t="s">
         <v>1578</v>
@@ -26525,7 +26525,7 @@
         <v>1558</v>
       </c>
       <c r="E525">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F525" t="s">
         <v>1582</v>
@@ -26560,7 +26560,7 @@
         <v>1558</v>
       </c>
       <c r="E526">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F526" t="s">
         <v>1578</v>
@@ -26595,7 +26595,7 @@
         <v>1559</v>
       </c>
       <c r="E527">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F527" t="s">
         <v>1578</v>
@@ -26630,7 +26630,7 @@
         <v>1560</v>
       </c>
       <c r="E528">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F528" t="s">
         <v>1578</v>
@@ -26665,7 +26665,7 @@
         <v>1560</v>
       </c>
       <c r="E529">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F529" t="s">
         <v>1580</v>
@@ -26703,7 +26703,7 @@
         <v>1561</v>
       </c>
       <c r="E530">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F530" t="s">
         <v>1580</v>
@@ -26741,7 +26741,7 @@
         <v>1561</v>
       </c>
       <c r="E531">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F531" t="s">
         <v>1578</v>
@@ -26776,7 +26776,7 @@
         <v>1561</v>
       </c>
       <c r="E532">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F532" t="s">
         <v>1580</v>
@@ -26814,7 +26814,7 @@
         <v>1561</v>
       </c>
       <c r="E533">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F533" t="s">
         <v>1578</v>
@@ -26849,7 +26849,7 @@
         <v>1561</v>
       </c>
       <c r="E534">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F534" t="s">
         <v>1578</v>
@@ -26884,7 +26884,7 @@
         <v>1561</v>
       </c>
       <c r="E535">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F535" t="s">
         <v>1578</v>
@@ -26919,7 +26919,7 @@
         <v>1561</v>
       </c>
       <c r="E536">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F536" t="s">
         <v>1578</v>
@@ -26954,7 +26954,7 @@
         <v>1561</v>
       </c>
       <c r="E537">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F537" t="s">
         <v>1578</v>
@@ -26989,7 +26989,7 @@
         <v>1562</v>
       </c>
       <c r="E538">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F538" t="s">
         <v>1578</v>
@@ -27027,7 +27027,7 @@
         <v>1562</v>
       </c>
       <c r="E539">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F539" t="s">
         <v>1582</v>
@@ -27062,7 +27062,7 @@
         <v>1562</v>
       </c>
       <c r="E540">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F540" t="s">
         <v>1580</v>
@@ -27097,7 +27097,7 @@
         <v>1562</v>
       </c>
       <c r="E541">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F541" t="s">
         <v>1578</v>
@@ -27132,7 +27132,7 @@
         <v>1562</v>
       </c>
       <c r="E542">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F542" t="s">
         <v>1578</v>
@@ -27167,7 +27167,7 @@
         <v>1562</v>
       </c>
       <c r="E543">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F543" t="s">
         <v>1578</v>
@@ -27202,7 +27202,7 @@
         <v>1562</v>
       </c>
       <c r="E544">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F544" t="s">
         <v>1578</v>
@@ -27237,7 +27237,7 @@
         <v>1562</v>
       </c>
       <c r="E545">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F545" t="s">
         <v>1578</v>
@@ -27272,7 +27272,7 @@
         <v>1562</v>
       </c>
       <c r="E546">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F546" t="s">
         <v>1578</v>
@@ -27307,7 +27307,7 @@
         <v>1563</v>
       </c>
       <c r="E547">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F547" t="s">
         <v>1578</v>
@@ -27345,7 +27345,7 @@
         <v>1563</v>
       </c>
       <c r="E548">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F548" t="s">
         <v>1578</v>
@@ -27380,7 +27380,7 @@
         <v>1564</v>
       </c>
       <c r="E549">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F549" t="s">
         <v>1578</v>
@@ -27415,7 +27415,7 @@
         <v>1564</v>
       </c>
       <c r="E550">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F550" t="s">
         <v>1580</v>
@@ -27453,7 +27453,7 @@
         <v>1564</v>
       </c>
       <c r="E551">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F551" t="s">
         <v>1578</v>
@@ -27488,7 +27488,7 @@
         <v>1564</v>
       </c>
       <c r="E552">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F552" t="s">
         <v>1578</v>
@@ -27523,7 +27523,7 @@
         <v>1564</v>
       </c>
       <c r="E553">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F553" t="s">
         <v>1578</v>
@@ -27558,7 +27558,7 @@
         <v>1564</v>
       </c>
       <c r="E554">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F554" t="s">
         <v>1578</v>
@@ -27593,7 +27593,7 @@
         <v>1564</v>
       </c>
       <c r="E555">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F555" t="s">
         <v>1578</v>
@@ -27628,7 +27628,7 @@
         <v>1564</v>
       </c>
       <c r="E556">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F556" t="s">
         <v>1578</v>
@@ -27663,7 +27663,7 @@
         <v>1565</v>
       </c>
       <c r="E557">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F557" t="s">
         <v>1578</v>
@@ -27698,7 +27698,7 @@
         <v>1565</v>
       </c>
       <c r="E558">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F558" t="s">
         <v>1578</v>
@@ -27733,7 +27733,7 @@
         <v>1565</v>
       </c>
       <c r="E559">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F559" t="s">
         <v>1578</v>
@@ -27768,7 +27768,7 @@
         <v>1565</v>
       </c>
       <c r="E560">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F560" t="s">
         <v>1578</v>
@@ -27803,7 +27803,7 @@
         <v>1565</v>
       </c>
       <c r="E561">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F561" t="s">
         <v>1578</v>
@@ -27838,7 +27838,7 @@
         <v>1565</v>
       </c>
       <c r="E562">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F562" t="s">
         <v>1578</v>
@@ -27873,7 +27873,7 @@
         <v>1565</v>
       </c>
       <c r="E563">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F563" t="s">
         <v>1578</v>
@@ -27908,7 +27908,7 @@
         <v>1565</v>
       </c>
       <c r="E564">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F564" t="s">
         <v>1578</v>
@@ -27943,7 +27943,7 @@
         <v>1565</v>
       </c>
       <c r="E565">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F565" t="s">
         <v>1580</v>
@@ -27978,7 +27978,7 @@
         <v>1565</v>
       </c>
       <c r="E566">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F566" t="s">
         <v>1578</v>
@@ -28013,7 +28013,7 @@
         <v>1565</v>
       </c>
       <c r="E567">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F567" t="s">
         <v>1582</v>
@@ -28048,7 +28048,7 @@
         <v>1565</v>
       </c>
       <c r="E568">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F568" t="s">
         <v>1578</v>
@@ -28083,7 +28083,7 @@
         <v>1566</v>
       </c>
       <c r="E569">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F569" t="s">
         <v>1578</v>
@@ -28118,7 +28118,7 @@
         <v>1566</v>
       </c>
       <c r="E570">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F570" t="s">
         <v>1578</v>
@@ -28153,7 +28153,7 @@
         <v>1566</v>
       </c>
       <c r="E571">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F571" t="s">
         <v>1578</v>
@@ -28188,7 +28188,7 @@
         <v>1566</v>
       </c>
       <c r="E572">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F572" t="s">
         <v>1578</v>
@@ -28223,7 +28223,7 @@
         <v>1566</v>
       </c>
       <c r="E573">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F573" t="s">
         <v>1578</v>
@@ -28258,7 +28258,7 @@
         <v>1566</v>
       </c>
       <c r="E574">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F574" t="s">
         <v>1578</v>
@@ -28293,7 +28293,7 @@
         <v>1566</v>
       </c>
       <c r="E575">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F575" t="s">
         <v>1578</v>
@@ -28328,7 +28328,7 @@
         <v>1566</v>
       </c>
       <c r="E576">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F576" t="s">
         <v>1578</v>
@@ -28366,7 +28366,7 @@
         <v>1566</v>
       </c>
       <c r="E577">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F577" t="s">
         <v>1580</v>
@@ -28404,7 +28404,7 @@
         <v>1566</v>
       </c>
       <c r="E578">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F578" t="s">
         <v>1580</v>
@@ -28439,7 +28439,7 @@
         <v>1566</v>
       </c>
       <c r="E579">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F579" t="s">
         <v>1580</v>
@@ -28474,7 +28474,7 @@
         <v>1566</v>
       </c>
       <c r="E580">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F580" t="s">
         <v>1578</v>
@@ -28509,7 +28509,7 @@
         <v>1567</v>
       </c>
       <c r="E581">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F581" t="s">
         <v>1578</v>
@@ -28544,7 +28544,7 @@
         <v>1567</v>
       </c>
       <c r="E582">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F582" t="s">
         <v>1578</v>
@@ -28579,7 +28579,7 @@
         <v>1567</v>
       </c>
       <c r="E583">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F583" t="s">
         <v>1578</v>
@@ -28614,7 +28614,7 @@
         <v>1567</v>
       </c>
       <c r="E584">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F584" t="s">
         <v>1578</v>
@@ -28649,7 +28649,7 @@
         <v>1567</v>
       </c>
       <c r="E585">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F585" t="s">
         <v>1578</v>
@@ -28684,7 +28684,7 @@
         <v>1567</v>
       </c>
       <c r="E586">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F586" t="s">
         <v>1578</v>
@@ -28719,7 +28719,7 @@
         <v>1567</v>
       </c>
       <c r="E587">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F587" t="s">
         <v>1578</v>
@@ -28754,7 +28754,7 @@
         <v>1567</v>
       </c>
       <c r="E588">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F588" t="s">
         <v>1578</v>
@@ -28789,7 +28789,7 @@
         <v>1567</v>
       </c>
       <c r="E589">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F589" t="s">
         <v>1578</v>
@@ -28827,7 +28827,7 @@
         <v>1568</v>
       </c>
       <c r="E590">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F590" t="s">
         <v>1578</v>
@@ -28862,7 +28862,7 @@
         <v>1568</v>
       </c>
       <c r="E591">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F591" t="s">
         <v>1578</v>
@@ -28897,7 +28897,7 @@
         <v>1569</v>
       </c>
       <c r="E592">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F592" t="s">
         <v>1578</v>
@@ -28935,7 +28935,7 @@
         <v>1569</v>
       </c>
       <c r="E593">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F593" t="s">
         <v>1578</v>
@@ -28970,7 +28970,7 @@
         <v>1569</v>
       </c>
       <c r="E594">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F594" t="s">
         <v>1578</v>
@@ -29005,7 +29005,7 @@
         <v>1569</v>
       </c>
       <c r="E595">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F595" t="s">
         <v>1580</v>
@@ -29043,7 +29043,7 @@
         <v>1569</v>
       </c>
       <c r="E596">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F596" t="s">
         <v>1580</v>
@@ -29081,7 +29081,7 @@
         <v>1569</v>
       </c>
       <c r="E597">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F597" t="s">
         <v>1578</v>
@@ -29116,7 +29116,7 @@
         <v>1569</v>
       </c>
       <c r="E598">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F598" t="s">
         <v>1578</v>
@@ -29151,7 +29151,7 @@
         <v>1569</v>
       </c>
       <c r="E599">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F599" t="s">
         <v>1578</v>
@@ -29186,7 +29186,7 @@
         <v>1570</v>
       </c>
       <c r="E600">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F600" t="s">
         <v>1578</v>
@@ -29221,7 +29221,7 @@
         <v>1570</v>
       </c>
       <c r="E601">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F601" t="s">
         <v>1578</v>
@@ -29256,7 +29256,7 @@
         <v>1570</v>
       </c>
       <c r="E602">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F602" t="s">
         <v>1578</v>
@@ -29291,7 +29291,7 @@
         <v>1570</v>
       </c>
       <c r="E603">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F603" t="s">
         <v>1578</v>
@@ -29326,7 +29326,7 @@
         <v>1570</v>
       </c>
       <c r="E604">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F604" t="s">
         <v>1578</v>
@@ -29361,7 +29361,7 @@
         <v>1570</v>
       </c>
       <c r="E605">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F605" t="s">
         <v>1578</v>
@@ -29396,7 +29396,7 @@
         <v>1570</v>
       </c>
       <c r="E606">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F606" t="s">
         <v>1578</v>
@@ -29431,7 +29431,7 @@
         <v>1570</v>
       </c>
       <c r="E607">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F607" t="s">
         <v>1578</v>
@@ -29466,7 +29466,7 @@
         <v>1570</v>
       </c>
       <c r="E608">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F608" t="s">
         <v>1578</v>
@@ -29501,7 +29501,7 @@
         <v>1570</v>
       </c>
       <c r="E609">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F609" t="s">
         <v>1580</v>
@@ -29539,7 +29539,7 @@
         <v>1570</v>
       </c>
       <c r="E610">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F610" t="s">
         <v>1578</v>
@@ -29577,7 +29577,7 @@
         <v>1570</v>
       </c>
       <c r="E611">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F611" t="s">
         <v>1580</v>
@@ -29615,7 +29615,7 @@
         <v>1570</v>
       </c>
       <c r="E612">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F612" t="s">
         <v>1578</v>
@@ -29650,7 +29650,7 @@
         <v>1571</v>
       </c>
       <c r="E613">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F613" t="s">
         <v>1578</v>
@@ -29685,7 +29685,7 @@
         <v>1571</v>
       </c>
       <c r="E614">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F614" t="s">
         <v>1580</v>
@@ -29723,7 +29723,7 @@
         <v>1571</v>
       </c>
       <c r="E615">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F615" t="s">
         <v>1578</v>
@@ -29758,7 +29758,7 @@
         <v>1571</v>
       </c>
       <c r="E616">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F616" t="s">
         <v>1578</v>
@@ -29793,7 +29793,7 @@
         <v>1572</v>
       </c>
       <c r="E617">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F617" t="s">
         <v>1578</v>
@@ -29828,7 +29828,7 @@
         <v>1572</v>
       </c>
       <c r="E618">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F618" t="s">
         <v>1578</v>
@@ -29863,7 +29863,7 @@
         <v>1572</v>
       </c>
       <c r="E619">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F619" t="s">
         <v>1578</v>
@@ -29898,7 +29898,7 @@
         <v>1572</v>
       </c>
       <c r="E620">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F620" t="s">
         <v>1578</v>
@@ -29933,7 +29933,7 @@
         <v>1572</v>
       </c>
       <c r="E621">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F621" t="s">
         <v>1580</v>
@@ -29971,7 +29971,7 @@
         <v>1572</v>
       </c>
       <c r="E622">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F622" t="s">
         <v>1580</v>
@@ -30009,7 +30009,7 @@
         <v>1572</v>
       </c>
       <c r="E623">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F623" t="s">
         <v>1578</v>
@@ -30044,7 +30044,7 @@
         <v>1572</v>
       </c>
       <c r="E624">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F624" t="s">
         <v>1578</v>
@@ -30079,7 +30079,7 @@
         <v>1572</v>
       </c>
       <c r="E625">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F625" t="s">
         <v>1578</v>
@@ -30114,7 +30114,7 @@
         <v>1572</v>
       </c>
       <c r="E626">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F626" t="s">
         <v>1578</v>
@@ -30149,7 +30149,7 @@
         <v>1572</v>
       </c>
       <c r="E627">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F627" t="s">
         <v>1578</v>
@@ -30184,7 +30184,7 @@
         <v>1572</v>
       </c>
       <c r="E628">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F628" t="s">
         <v>1578</v>
@@ -30219,7 +30219,7 @@
         <v>1572</v>
       </c>
       <c r="E629">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F629" t="s">
         <v>1578</v>
@@ -30254,7 +30254,7 @@
         <v>1573</v>
       </c>
       <c r="E630">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F630" t="s">
         <v>1582</v>
@@ -30289,7 +30289,7 @@
         <v>1573</v>
       </c>
       <c r="E631">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F631" t="s">
         <v>1578</v>
@@ -30324,7 +30324,7 @@
         <v>1573</v>
       </c>
       <c r="E632">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F632" t="s">
         <v>1578</v>
@@ -30359,7 +30359,7 @@
         <v>1573</v>
       </c>
       <c r="E633">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F633" t="s">
         <v>1578</v>
@@ -30394,7 +30394,7 @@
         <v>1573</v>
       </c>
       <c r="E634">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F634" t="s">
         <v>1578</v>
@@ -30429,7 +30429,7 @@
         <v>1573</v>
       </c>
       <c r="E635">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F635" t="s">
         <v>1580</v>
@@ -30464,7 +30464,7 @@
         <v>1573</v>
       </c>
       <c r="E636">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F636" t="s">
         <v>1578</v>
@@ -30499,7 +30499,7 @@
         <v>1573</v>
       </c>
       <c r="E637">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F637" t="s">
         <v>1578</v>
@@ -30534,7 +30534,7 @@
         <v>1574</v>
       </c>
       <c r="E638">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F638" t="s">
         <v>1578</v>
@@ -30569,7 +30569,7 @@
         <v>1574</v>
       </c>
       <c r="E639">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F639" t="s">
         <v>1578</v>
@@ -30607,7 +30607,7 @@
         <v>1574</v>
       </c>
       <c r="E640">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F640" t="s">
         <v>1578</v>
@@ -30642,7 +30642,7 @@
         <v>1574</v>
       </c>
       <c r="E641">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F641" t="s">
         <v>1578</v>
@@ -30677,7 +30677,7 @@
         <v>1574</v>
       </c>
       <c r="E642">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F642" t="s">
         <v>1578</v>
@@ -30712,7 +30712,7 @@
         <v>1574</v>
       </c>
       <c r="E643">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F643" t="s">
         <v>1580</v>
@@ -30750,7 +30750,7 @@
         <v>1575</v>
       </c>
       <c r="E644">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F644" t="s">
         <v>1578</v>
@@ -30785,7 +30785,7 @@
         <v>1575</v>
       </c>
       <c r="E645">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F645" t="s">
         <v>1578</v>
@@ -30823,7 +30823,7 @@
         <v>1575</v>
       </c>
       <c r="E646">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F646" t="s">
         <v>1578</v>
@@ -30861,7 +30861,7 @@
         <v>1575</v>
       </c>
       <c r="E647">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F647" t="s">
         <v>1578</v>
@@ -30896,7 +30896,7 @@
         <v>1575</v>
       </c>
       <c r="E648">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F648" t="s">
         <v>1578</v>
@@ -30931,7 +30931,7 @@
         <v>1576</v>
       </c>
       <c r="E649">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F649" t="s">
         <v>1580</v>
@@ -30969,7 +30969,7 @@
         <v>1576</v>
       </c>
       <c r="E650">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F650" t="s">
         <v>1578</v>
@@ -31004,7 +31004,7 @@
         <v>1576</v>
       </c>
       <c r="E651">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F651" t="s">
         <v>1578</v>
@@ -31039,7 +31039,7 @@
         <v>1576</v>
       </c>
       <c r="E652">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F652" t="s">
         <v>1578</v>
@@ -31074,7 +31074,7 @@
         <v>1576</v>
       </c>
       <c r="E653">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F653" t="s">
         <v>1578</v>
@@ -31109,7 +31109,7 @@
         <v>1576</v>
       </c>
       <c r="E654">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F654" t="s">
         <v>1578</v>
@@ -31144,7 +31144,7 @@
         <v>1576</v>
       </c>
       <c r="E655">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F655" t="s">
         <v>1578</v>
@@ -31179,7 +31179,7 @@
         <v>1576</v>
       </c>
       <c r="E656">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F656" t="s">
         <v>1578</v>
@@ -31214,7 +31214,7 @@
         <v>1576</v>
       </c>
       <c r="E657">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F657" t="s">
         <v>1578</v>
@@ -31249,7 +31249,7 @@
         <v>1576</v>
       </c>
       <c r="E658">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F658" t="s">
         <v>1578</v>
@@ -31287,7 +31287,7 @@
         <v>1576</v>
       </c>
       <c r="E659">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F659" t="s">
         <v>1578</v>
@@ -31322,7 +31322,7 @@
         <v>1576</v>
       </c>
       <c r="E660">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F660" t="s">
         <v>1578</v>
@@ -31357,7 +31357,7 @@
         <v>1576</v>
       </c>
       <c r="E661">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F661" t="s">
         <v>1578</v>
@@ -31392,7 +31392,7 @@
         <v>1577</v>
       </c>
       <c r="E662">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F662" t="s">
         <v>1578</v>
@@ -31427,7 +31427,7 @@
         <v>1577</v>
       </c>
       <c r="E663">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F663" t="s">
         <v>1578</v>
@@ -31465,7 +31465,7 @@
         <v>1577</v>
       </c>
       <c r="E664">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F664" t="s">
         <v>1578</v>
@@ -31500,7 +31500,7 @@
         <v>1577</v>
       </c>
       <c r="E665">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F665" t="s">
         <v>1578</v>

--- a/BacklogGATEAutoCompleto.xlsx
+++ b/BacklogGATEAutoCompleto.xlsx
@@ -27635,7 +27635,7 @@
         <v>1585</v>
       </c>
       <c r="I555" t="s">
-        <v>1675</v>
+        <v>1618</v>
       </c>
       <c r="J555" t="s">
         <v>2281</v>

--- a/BacklogGATEAutoCompleto.xlsx
+++ b/BacklogGATEAutoCompleto.xlsx
@@ -8220,7 +8220,7 @@
         <v>1368</v>
       </c>
       <c r="E2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="F2" t="s">
         <v>1580</v>
@@ -8255,7 +8255,7 @@
         <v>1369</v>
       </c>
       <c r="E3">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="F3" t="s">
         <v>1580</v>
@@ -8290,7 +8290,7 @@
         <v>1370</v>
       </c>
       <c r="E4">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="F4" t="s">
         <v>1580</v>
@@ -8325,7 +8325,7 @@
         <v>1371</v>
       </c>
       <c r="E5">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="F5" t="s">
         <v>1580</v>
@@ -8360,7 +8360,7 @@
         <v>1372</v>
       </c>
       <c r="E6">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="F6" t="s">
         <v>1580</v>
@@ -8395,7 +8395,7 @@
         <v>1373</v>
       </c>
       <c r="E7">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="F7" t="s">
         <v>1580</v>
@@ -8430,7 +8430,7 @@
         <v>1374</v>
       </c>
       <c r="E8">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="F8" t="s">
         <v>1580</v>
@@ -8465,7 +8465,7 @@
         <v>1375</v>
       </c>
       <c r="E9">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F9" t="s">
         <v>1580</v>
@@ -8500,7 +8500,7 @@
         <v>1376</v>
       </c>
       <c r="E10">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F10" t="s">
         <v>1580</v>
@@ -8535,7 +8535,7 @@
         <v>1376</v>
       </c>
       <c r="E11">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F11" t="s">
         <v>1580</v>
@@ -8570,7 +8570,7 @@
         <v>1377</v>
       </c>
       <c r="E12">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="F12" t="s">
         <v>1580</v>
@@ -8605,7 +8605,7 @@
         <v>1378</v>
       </c>
       <c r="E13">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="F13" t="s">
         <v>1580</v>
@@ -8640,7 +8640,7 @@
         <v>1379</v>
       </c>
       <c r="E14">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="F14" t="s">
         <v>1580</v>
@@ -8675,7 +8675,7 @@
         <v>1379</v>
       </c>
       <c r="E15">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="F15" t="s">
         <v>1580</v>
@@ -8710,7 +8710,7 @@
         <v>1380</v>
       </c>
       <c r="E16">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="F16" t="s">
         <v>1580</v>
@@ -8745,7 +8745,7 @@
         <v>1381</v>
       </c>
       <c r="E17">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="F17" t="s">
         <v>1580</v>
@@ -8780,7 +8780,7 @@
         <v>1381</v>
       </c>
       <c r="E18">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="F18" t="s">
         <v>1580</v>
@@ -8815,7 +8815,7 @@
         <v>1382</v>
       </c>
       <c r="E19">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="F19" t="s">
         <v>1580</v>
@@ -8850,7 +8850,7 @@
         <v>1383</v>
       </c>
       <c r="E20">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="F20" t="s">
         <v>1580</v>
@@ -8885,7 +8885,7 @@
         <v>1384</v>
       </c>
       <c r="E21">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="F21" t="s">
         <v>1580</v>
@@ -8920,7 +8920,7 @@
         <v>1385</v>
       </c>
       <c r="E22">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F22" t="s">
         <v>1580</v>
@@ -8955,7 +8955,7 @@
         <v>1386</v>
       </c>
       <c r="E23">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F23" t="s">
         <v>1580</v>
@@ -8993,7 +8993,7 @@
         <v>1387</v>
       </c>
       <c r="E24">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="F24" t="s">
         <v>1580</v>
@@ -9028,7 +9028,7 @@
         <v>1388</v>
       </c>
       <c r="E25">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F25" t="s">
         <v>1580</v>
@@ -9063,7 +9063,7 @@
         <v>1389</v>
       </c>
       <c r="E26">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F26" t="s">
         <v>1580</v>
@@ -9098,7 +9098,7 @@
         <v>1390</v>
       </c>
       <c r="E27">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="F27" t="s">
         <v>1580</v>
@@ -9133,7 +9133,7 @@
         <v>1391</v>
       </c>
       <c r="E28">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F28" t="s">
         <v>1580</v>
@@ -9168,7 +9168,7 @@
         <v>1392</v>
       </c>
       <c r="E29">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F29" t="s">
         <v>1580</v>
@@ -9203,7 +9203,7 @@
         <v>1393</v>
       </c>
       <c r="E30">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F30" t="s">
         <v>1580</v>
@@ -9238,7 +9238,7 @@
         <v>1394</v>
       </c>
       <c r="E31">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F31" t="s">
         <v>1580</v>
@@ -9273,7 +9273,7 @@
         <v>1395</v>
       </c>
       <c r="E32">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F32" t="s">
         <v>1580</v>
@@ -9308,7 +9308,7 @@
         <v>1396</v>
       </c>
       <c r="E33">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F33" t="s">
         <v>1580</v>
@@ -9343,7 +9343,7 @@
         <v>1397</v>
       </c>
       <c r="E34">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="F34" t="s">
         <v>1580</v>
@@ -9378,7 +9378,7 @@
         <v>1398</v>
       </c>
       <c r="E35">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F35" t="s">
         <v>1580</v>
@@ -9413,7 +9413,7 @@
         <v>1398</v>
       </c>
       <c r="E36">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F36" t="s">
         <v>1580</v>
@@ -9448,7 +9448,7 @@
         <v>1399</v>
       </c>
       <c r="E37">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F37" t="s">
         <v>1580</v>
@@ -9483,7 +9483,7 @@
         <v>1400</v>
       </c>
       <c r="E38">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F38" t="s">
         <v>1580</v>
@@ -9518,7 +9518,7 @@
         <v>1401</v>
       </c>
       <c r="E39">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F39" t="s">
         <v>1580</v>
@@ -9553,7 +9553,7 @@
         <v>1402</v>
       </c>
       <c r="E40">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F40" t="s">
         <v>1580</v>
@@ -9588,7 +9588,7 @@
         <v>1403</v>
       </c>
       <c r="E41">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F41" t="s">
         <v>1580</v>
@@ -9623,7 +9623,7 @@
         <v>1403</v>
       </c>
       <c r="E42">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F42" t="s">
         <v>1580</v>
@@ -9658,7 +9658,7 @@
         <v>1404</v>
       </c>
       <c r="E43">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F43" t="s">
         <v>1580</v>
@@ -9693,7 +9693,7 @@
         <v>1405</v>
       </c>
       <c r="E44">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F44" t="s">
         <v>1580</v>
@@ -9728,7 +9728,7 @@
         <v>1406</v>
       </c>
       <c r="E45">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F45" t="s">
         <v>1580</v>
@@ -9763,7 +9763,7 @@
         <v>1406</v>
       </c>
       <c r="E46">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F46" t="s">
         <v>1580</v>
@@ -9798,7 +9798,7 @@
         <v>1407</v>
       </c>
       <c r="E47">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F47" t="s">
         <v>1580</v>
@@ -9833,7 +9833,7 @@
         <v>1407</v>
       </c>
       <c r="E48">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F48" t="s">
         <v>1580</v>
@@ -9868,7 +9868,7 @@
         <v>1408</v>
       </c>
       <c r="E49">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F49" t="s">
         <v>1580</v>
@@ -9903,7 +9903,7 @@
         <v>1409</v>
       </c>
       <c r="E50">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F50" t="s">
         <v>1580</v>
@@ -9938,7 +9938,7 @@
         <v>1410</v>
       </c>
       <c r="E51">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F51" t="s">
         <v>1580</v>
@@ -9973,7 +9973,7 @@
         <v>1411</v>
       </c>
       <c r="E52">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F52" t="s">
         <v>1580</v>
@@ -10008,7 +10008,7 @@
         <v>1412</v>
       </c>
       <c r="E53">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F53" t="s">
         <v>1580</v>
@@ -10043,7 +10043,7 @@
         <v>1413</v>
       </c>
       <c r="E54">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F54" t="s">
         <v>1580</v>
@@ -10078,7 +10078,7 @@
         <v>1414</v>
       </c>
       <c r="E55">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F55" t="s">
         <v>1580</v>
@@ -10113,7 +10113,7 @@
         <v>1415</v>
       </c>
       <c r="E56">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F56" t="s">
         <v>1580</v>
@@ -10148,7 +10148,7 @@
         <v>1416</v>
       </c>
       <c r="E57">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F57" t="s">
         <v>1580</v>
@@ -10183,7 +10183,7 @@
         <v>1417</v>
       </c>
       <c r="E58">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F58" t="s">
         <v>1580</v>
@@ -10218,7 +10218,7 @@
         <v>1418</v>
       </c>
       <c r="E59">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F59" t="s">
         <v>1580</v>
@@ -10253,7 +10253,7 @@
         <v>1419</v>
       </c>
       <c r="E60">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F60" t="s">
         <v>1580</v>
@@ -10288,7 +10288,7 @@
         <v>1419</v>
       </c>
       <c r="E61">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F61" t="s">
         <v>1580</v>
@@ -10323,7 +10323,7 @@
         <v>1419</v>
       </c>
       <c r="E62">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F62" t="s">
         <v>1580</v>
@@ -10358,7 +10358,7 @@
         <v>1420</v>
       </c>
       <c r="E63">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F63" t="s">
         <v>1580</v>
@@ -10393,7 +10393,7 @@
         <v>1421</v>
       </c>
       <c r="E64">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F64" t="s">
         <v>1580</v>
@@ -10428,7 +10428,7 @@
         <v>1422</v>
       </c>
       <c r="E65">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F65" t="s">
         <v>1580</v>
@@ -10463,7 +10463,7 @@
         <v>1422</v>
       </c>
       <c r="E66">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F66" t="s">
         <v>1580</v>
@@ -10498,7 +10498,7 @@
         <v>1422</v>
       </c>
       <c r="E67">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F67" t="s">
         <v>1580</v>
@@ -10533,7 +10533,7 @@
         <v>1423</v>
       </c>
       <c r="E68">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F68" t="s">
         <v>1580</v>
@@ -10568,7 +10568,7 @@
         <v>1424</v>
       </c>
       <c r="E69">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F69" t="s">
         <v>1580</v>
@@ -10603,7 +10603,7 @@
         <v>1425</v>
       </c>
       <c r="E70">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F70" t="s">
         <v>1580</v>
@@ -10638,7 +10638,7 @@
         <v>1425</v>
       </c>
       <c r="E71">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F71" t="s">
         <v>1580</v>
@@ -10673,7 +10673,7 @@
         <v>1425</v>
       </c>
       <c r="E72">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F72" t="s">
         <v>1580</v>
@@ -10708,7 +10708,7 @@
         <v>1426</v>
       </c>
       <c r="E73">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F73" t="s">
         <v>1580</v>
@@ -10743,7 +10743,7 @@
         <v>1427</v>
       </c>
       <c r="E74">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F74" t="s">
         <v>1580</v>
@@ -10778,7 +10778,7 @@
         <v>1427</v>
       </c>
       <c r="E75">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F75" t="s">
         <v>1580</v>
@@ -10813,7 +10813,7 @@
         <v>1427</v>
       </c>
       <c r="E76">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F76" t="s">
         <v>1581</v>
@@ -10848,7 +10848,7 @@
         <v>1427</v>
       </c>
       <c r="E77">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F77" t="s">
         <v>1580</v>
@@ -10883,7 +10883,7 @@
         <v>1428</v>
       </c>
       <c r="E78">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F78" t="s">
         <v>1580</v>
@@ -10918,7 +10918,7 @@
         <v>1429</v>
       </c>
       <c r="E79">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F79" t="s">
         <v>1580</v>
@@ -10953,7 +10953,7 @@
         <v>1429</v>
       </c>
       <c r="E80">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F80" t="s">
         <v>1580</v>
@@ -10988,7 +10988,7 @@
         <v>1430</v>
       </c>
       <c r="E81">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F81" t="s">
         <v>1580</v>
@@ -11023,7 +11023,7 @@
         <v>1431</v>
       </c>
       <c r="E82">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F82" t="s">
         <v>1580</v>
@@ -11058,7 +11058,7 @@
         <v>1432</v>
       </c>
       <c r="E83">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F83" t="s">
         <v>1580</v>
@@ -11093,7 +11093,7 @@
         <v>1433</v>
       </c>
       <c r="E84">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F84" t="s">
         <v>1580</v>
@@ -11128,7 +11128,7 @@
         <v>1433</v>
       </c>
       <c r="E85">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F85" t="s">
         <v>1580</v>
@@ -11163,7 +11163,7 @@
         <v>1433</v>
       </c>
       <c r="E86">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F86" t="s">
         <v>1580</v>
@@ -11198,7 +11198,7 @@
         <v>1433</v>
       </c>
       <c r="E87">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F87" t="s">
         <v>1580</v>
@@ -11233,7 +11233,7 @@
         <v>1433</v>
       </c>
       <c r="E88">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F88" t="s">
         <v>1580</v>
@@ -11268,7 +11268,7 @@
         <v>1433</v>
       </c>
       <c r="E89">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F89" t="s">
         <v>1580</v>
@@ -11303,7 +11303,7 @@
         <v>1434</v>
       </c>
       <c r="E90">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F90" t="s">
         <v>1580</v>
@@ -11338,7 +11338,7 @@
         <v>1434</v>
       </c>
       <c r="E91">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F91" t="s">
         <v>1580</v>
@@ -11373,7 +11373,7 @@
         <v>1435</v>
       </c>
       <c r="E92">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F92" t="s">
         <v>1580</v>
@@ -11408,7 +11408,7 @@
         <v>1436</v>
       </c>
       <c r="E93">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F93" t="s">
         <v>1580</v>
@@ -11443,7 +11443,7 @@
         <v>1436</v>
       </c>
       <c r="E94">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F94" t="s">
         <v>1580</v>
@@ -11478,7 +11478,7 @@
         <v>1437</v>
       </c>
       <c r="E95">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F95" t="s">
         <v>1580</v>
@@ -11513,7 +11513,7 @@
         <v>1437</v>
       </c>
       <c r="E96">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F96" t="s">
         <v>1582</v>
@@ -11548,7 +11548,7 @@
         <v>1438</v>
       </c>
       <c r="E97">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F97" t="s">
         <v>1580</v>
@@ -11583,7 +11583,7 @@
         <v>1439</v>
       </c>
       <c r="E98">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F98" t="s">
         <v>1580</v>
@@ -11618,7 +11618,7 @@
         <v>1440</v>
       </c>
       <c r="E99">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F99" t="s">
         <v>1580</v>
@@ -11653,7 +11653,7 @@
         <v>1440</v>
       </c>
       <c r="E100">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F100" t="s">
         <v>1580</v>
@@ -11688,7 +11688,7 @@
         <v>1441</v>
       </c>
       <c r="E101">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F101" t="s">
         <v>1580</v>
@@ -11723,7 +11723,7 @@
         <v>1442</v>
       </c>
       <c r="E102">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F102" t="s">
         <v>1580</v>
@@ -11758,7 +11758,7 @@
         <v>1443</v>
       </c>
       <c r="E103">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F103" t="s">
         <v>1580</v>
@@ -11793,7 +11793,7 @@
         <v>1444</v>
       </c>
       <c r="E104">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F104" t="s">
         <v>1580</v>
@@ -11828,7 +11828,7 @@
         <v>1445</v>
       </c>
       <c r="E105">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F105" t="s">
         <v>1580</v>
@@ -11863,7 +11863,7 @@
         <v>1445</v>
       </c>
       <c r="E106">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F106" t="s">
         <v>1580</v>
@@ -11898,7 +11898,7 @@
         <v>1446</v>
       </c>
       <c r="E107">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F107" t="s">
         <v>1580</v>
@@ -11933,7 +11933,7 @@
         <v>1446</v>
       </c>
       <c r="E108">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F108" t="s">
         <v>1580</v>
@@ -11968,7 +11968,7 @@
         <v>1446</v>
       </c>
       <c r="E109">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F109" t="s">
         <v>1580</v>
@@ -12003,7 +12003,7 @@
         <v>1447</v>
       </c>
       <c r="E110">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F110" t="s">
         <v>1580</v>
@@ -12038,7 +12038,7 @@
         <v>1447</v>
       </c>
       <c r="E111">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F111" t="s">
         <v>1580</v>
@@ -12073,7 +12073,7 @@
         <v>1447</v>
       </c>
       <c r="E112">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F112" t="s">
         <v>1580</v>
@@ -12108,7 +12108,7 @@
         <v>1447</v>
       </c>
       <c r="E113">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F113" t="s">
         <v>1580</v>
@@ -12143,7 +12143,7 @@
         <v>1448</v>
       </c>
       <c r="E114">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F114" t="s">
         <v>1580</v>
@@ -12178,7 +12178,7 @@
         <v>1449</v>
       </c>
       <c r="E115">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F115" t="s">
         <v>1580</v>
@@ -12213,7 +12213,7 @@
         <v>1449</v>
       </c>
       <c r="E116">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F116" t="s">
         <v>1580</v>
@@ -12248,7 +12248,7 @@
         <v>1450</v>
       </c>
       <c r="E117">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F117" t="s">
         <v>1580</v>
@@ -12283,7 +12283,7 @@
         <v>1451</v>
       </c>
       <c r="E118">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F118" t="s">
         <v>1580</v>
@@ -12318,7 +12318,7 @@
         <v>1451</v>
       </c>
       <c r="E119">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F119" t="s">
         <v>1580</v>
@@ -12353,7 +12353,7 @@
         <v>1451</v>
       </c>
       <c r="E120">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F120" t="s">
         <v>1580</v>
@@ -12388,7 +12388,7 @@
         <v>1452</v>
       </c>
       <c r="E121">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F121" t="s">
         <v>1580</v>
@@ -12423,7 +12423,7 @@
         <v>1452</v>
       </c>
       <c r="E122">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F122" t="s">
         <v>1580</v>
@@ -12458,7 +12458,7 @@
         <v>1452</v>
       </c>
       <c r="E123">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F123" t="s">
         <v>1580</v>
@@ -12493,7 +12493,7 @@
         <v>1453</v>
       </c>
       <c r="E124">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F124" t="s">
         <v>1580</v>
@@ -12528,7 +12528,7 @@
         <v>1453</v>
       </c>
       <c r="E125">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F125" t="s">
         <v>1580</v>
@@ -12563,7 +12563,7 @@
         <v>1454</v>
       </c>
       <c r="E126">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F126" t="s">
         <v>1580</v>
@@ -12598,7 +12598,7 @@
         <v>1454</v>
       </c>
       <c r="E127">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F127" t="s">
         <v>1580</v>
@@ -12633,7 +12633,7 @@
         <v>1455</v>
       </c>
       <c r="E128">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F128" t="s">
         <v>1580</v>
@@ -12668,7 +12668,7 @@
         <v>1456</v>
       </c>
       <c r="E129">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F129" t="s">
         <v>1580</v>
@@ -12703,7 +12703,7 @@
         <v>1456</v>
       </c>
       <c r="E130">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F130" t="s">
         <v>1580</v>
@@ -12738,7 +12738,7 @@
         <v>1457</v>
       </c>
       <c r="E131">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F131" t="s">
         <v>1580</v>
@@ -12773,7 +12773,7 @@
         <v>1457</v>
       </c>
       <c r="E132">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F132" t="s">
         <v>1580</v>
@@ -12808,7 +12808,7 @@
         <v>1458</v>
       </c>
       <c r="E133">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F133" t="s">
         <v>1580</v>
@@ -12846,7 +12846,7 @@
         <v>1458</v>
       </c>
       <c r="E134">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F134" t="s">
         <v>1580</v>
@@ -12881,7 +12881,7 @@
         <v>1458</v>
       </c>
       <c r="E135">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F135" t="s">
         <v>1580</v>
@@ -12916,7 +12916,7 @@
         <v>1458</v>
       </c>
       <c r="E136">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F136" t="s">
         <v>1580</v>
@@ -12951,7 +12951,7 @@
         <v>1458</v>
       </c>
       <c r="E137">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F137" t="s">
         <v>1580</v>
@@ -12986,7 +12986,7 @@
         <v>1459</v>
       </c>
       <c r="E138">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F138" t="s">
         <v>1580</v>
@@ -13021,7 +13021,7 @@
         <v>1460</v>
       </c>
       <c r="E139">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F139" t="s">
         <v>1581</v>
@@ -13056,7 +13056,7 @@
         <v>1461</v>
       </c>
       <c r="E140">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F140" t="s">
         <v>1580</v>
@@ -13091,7 +13091,7 @@
         <v>1461</v>
       </c>
       <c r="E141">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F141" t="s">
         <v>1580</v>
@@ -13126,7 +13126,7 @@
         <v>1461</v>
       </c>
       <c r="E142">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F142" t="s">
         <v>1580</v>
@@ -13161,7 +13161,7 @@
         <v>1461</v>
       </c>
       <c r="E143">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F143" t="s">
         <v>1580</v>
@@ -13196,7 +13196,7 @@
         <v>1462</v>
       </c>
       <c r="E144">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F144" t="s">
         <v>1580</v>
@@ -13231,7 +13231,7 @@
         <v>1462</v>
       </c>
       <c r="E145">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F145" t="s">
         <v>1580</v>
@@ -13266,7 +13266,7 @@
         <v>1462</v>
       </c>
       <c r="E146">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F146" t="s">
         <v>1580</v>
@@ -13301,7 +13301,7 @@
         <v>1462</v>
       </c>
       <c r="E147">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F147" t="s">
         <v>1580</v>
@@ -13336,7 +13336,7 @@
         <v>1462</v>
       </c>
       <c r="E148">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F148" t="s">
         <v>1580</v>
@@ -13371,7 +13371,7 @@
         <v>1462</v>
       </c>
       <c r="E149">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F149" t="s">
         <v>1580</v>
@@ -13406,7 +13406,7 @@
         <v>1462</v>
       </c>
       <c r="E150">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F150" t="s">
         <v>1580</v>
@@ -13441,7 +13441,7 @@
         <v>1463</v>
       </c>
       <c r="E151">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F151" t="s">
         <v>1580</v>
@@ -13476,7 +13476,7 @@
         <v>1463</v>
       </c>
       <c r="E152">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F152" t="s">
         <v>1580</v>
@@ -13511,7 +13511,7 @@
         <v>1464</v>
       </c>
       <c r="E153">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F153" t="s">
         <v>1580</v>
@@ -13546,7 +13546,7 @@
         <v>1464</v>
       </c>
       <c r="E154">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F154" t="s">
         <v>1580</v>
@@ -13581,7 +13581,7 @@
         <v>1465</v>
       </c>
       <c r="E155">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F155" t="s">
         <v>1580</v>
@@ -13616,7 +13616,7 @@
         <v>1465</v>
       </c>
       <c r="E156">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F156" t="s">
         <v>1580</v>
@@ -13651,7 +13651,7 @@
         <v>1465</v>
       </c>
       <c r="E157">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F157" t="s">
         <v>1580</v>
@@ -13686,7 +13686,7 @@
         <v>1466</v>
       </c>
       <c r="E158">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F158" t="s">
         <v>1580</v>
@@ -13721,7 +13721,7 @@
         <v>1466</v>
       </c>
       <c r="E159">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F159" t="s">
         <v>1580</v>
@@ -13756,7 +13756,7 @@
         <v>1466</v>
       </c>
       <c r="E160">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F160" t="s">
         <v>1580</v>
@@ -13791,7 +13791,7 @@
         <v>1466</v>
       </c>
       <c r="E161">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F161" t="s">
         <v>1580</v>
@@ -13826,7 +13826,7 @@
         <v>1466</v>
       </c>
       <c r="E162">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F162" t="s">
         <v>1580</v>
@@ -13861,7 +13861,7 @@
         <v>1466</v>
       </c>
       <c r="E163">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F163" t="s">
         <v>1580</v>
@@ -13896,7 +13896,7 @@
         <v>1466</v>
       </c>
       <c r="E164">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F164" t="s">
         <v>1580</v>
@@ -13931,7 +13931,7 @@
         <v>1466</v>
       </c>
       <c r="E165">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F165" t="s">
         <v>1580</v>
@@ -13966,7 +13966,7 @@
         <v>1466</v>
       </c>
       <c r="E166">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F166" t="s">
         <v>1580</v>
@@ -14001,7 +14001,7 @@
         <v>1466</v>
       </c>
       <c r="E167">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F167" t="s">
         <v>1580</v>
@@ -14036,7 +14036,7 @@
         <v>1467</v>
       </c>
       <c r="E168">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F168" t="s">
         <v>1580</v>
@@ -14071,7 +14071,7 @@
         <v>1467</v>
       </c>
       <c r="E169">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F169" t="s">
         <v>1580</v>
@@ -14106,7 +14106,7 @@
         <v>1467</v>
       </c>
       <c r="E170">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F170" t="s">
         <v>1580</v>
@@ -14141,7 +14141,7 @@
         <v>1468</v>
       </c>
       <c r="E171">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F171" t="s">
         <v>1580</v>
@@ -14176,7 +14176,7 @@
         <v>1468</v>
       </c>
       <c r="E172">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F172" t="s">
         <v>1581</v>
@@ -14211,7 +14211,7 @@
         <v>1468</v>
       </c>
       <c r="E173">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F173" t="s">
         <v>1580</v>
@@ -14246,7 +14246,7 @@
         <v>1469</v>
       </c>
       <c r="E174">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F174" t="s">
         <v>1580</v>
@@ -14281,7 +14281,7 @@
         <v>1469</v>
       </c>
       <c r="E175">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F175" t="s">
         <v>1580</v>
@@ -14316,7 +14316,7 @@
         <v>1470</v>
       </c>
       <c r="E176">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F176" t="s">
         <v>1580</v>
@@ -14351,7 +14351,7 @@
         <v>1470</v>
       </c>
       <c r="E177">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F177" t="s">
         <v>1580</v>
@@ -14386,7 +14386,7 @@
         <v>1471</v>
       </c>
       <c r="E178">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F178" t="s">
         <v>1580</v>
@@ -14421,7 +14421,7 @@
         <v>1471</v>
       </c>
       <c r="E179">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F179" t="s">
         <v>1580</v>
@@ -14456,7 +14456,7 @@
         <v>1472</v>
       </c>
       <c r="E180">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F180" t="s">
         <v>1580</v>
@@ -14491,7 +14491,7 @@
         <v>1472</v>
       </c>
       <c r="E181">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F181" t="s">
         <v>1580</v>
@@ -14526,7 +14526,7 @@
         <v>1472</v>
       </c>
       <c r="E182">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F182" t="s">
         <v>1580</v>
@@ -14561,7 +14561,7 @@
         <v>1472</v>
       </c>
       <c r="E183">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F183" t="s">
         <v>1580</v>
@@ -14596,7 +14596,7 @@
         <v>1472</v>
       </c>
       <c r="E184">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F184" t="s">
         <v>1580</v>
@@ -14631,7 +14631,7 @@
         <v>1473</v>
       </c>
       <c r="E185">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F185" t="s">
         <v>1580</v>
@@ -14666,7 +14666,7 @@
         <v>1473</v>
       </c>
       <c r="E186">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F186" t="s">
         <v>1580</v>
@@ -14701,7 +14701,7 @@
         <v>1474</v>
       </c>
       <c r="E187">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F187" t="s">
         <v>1580</v>
@@ -14736,7 +14736,7 @@
         <v>1475</v>
       </c>
       <c r="E188">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F188" t="s">
         <v>1580</v>
@@ -14771,7 +14771,7 @@
         <v>1475</v>
       </c>
       <c r="E189">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F189" t="s">
         <v>1580</v>
@@ -14806,7 +14806,7 @@
         <v>1475</v>
       </c>
       <c r="E190">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F190" t="s">
         <v>1580</v>
@@ -14841,7 +14841,7 @@
         <v>1475</v>
       </c>
       <c r="E191">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F191" t="s">
         <v>1580</v>
@@ -14876,7 +14876,7 @@
         <v>1476</v>
       </c>
       <c r="E192">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F192" t="s">
         <v>1580</v>
@@ -14911,7 +14911,7 @@
         <v>1477</v>
       </c>
       <c r="E193">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F193" t="s">
         <v>1580</v>
@@ -14946,7 +14946,7 @@
         <v>1477</v>
       </c>
       <c r="E194">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F194" t="s">
         <v>1580</v>
@@ -14981,7 +14981,7 @@
         <v>1477</v>
       </c>
       <c r="E195">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F195" t="s">
         <v>1580</v>
@@ -15016,7 +15016,7 @@
         <v>1477</v>
       </c>
       <c r="E196">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F196" t="s">
         <v>1580</v>
@@ -15051,7 +15051,7 @@
         <v>1477</v>
       </c>
       <c r="E197">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F197" t="s">
         <v>1580</v>
@@ -15086,7 +15086,7 @@
         <v>1478</v>
       </c>
       <c r="E198">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F198" t="s">
         <v>1580</v>
@@ -15121,7 +15121,7 @@
         <v>1478</v>
       </c>
       <c r="E199">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F199" t="s">
         <v>1580</v>
@@ -15156,7 +15156,7 @@
         <v>1478</v>
       </c>
       <c r="E200">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F200" t="s">
         <v>1580</v>
@@ -15191,7 +15191,7 @@
         <v>1478</v>
       </c>
       <c r="E201">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F201" t="s">
         <v>1580</v>
@@ -15226,7 +15226,7 @@
         <v>1478</v>
       </c>
       <c r="E202">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F202" t="s">
         <v>1580</v>
@@ -15261,7 +15261,7 @@
         <v>1478</v>
       </c>
       <c r="E203">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F203" t="s">
         <v>1580</v>
@@ -15296,7 +15296,7 @@
         <v>1478</v>
       </c>
       <c r="E204">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F204" t="s">
         <v>1580</v>
@@ -15331,7 +15331,7 @@
         <v>1479</v>
       </c>
       <c r="E205">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F205" t="s">
         <v>1580</v>
@@ -15366,7 +15366,7 @@
         <v>1479</v>
       </c>
       <c r="E206">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F206" t="s">
         <v>1580</v>
@@ -15401,7 +15401,7 @@
         <v>1479</v>
       </c>
       <c r="E207">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F207" t="s">
         <v>1580</v>
@@ -15436,7 +15436,7 @@
         <v>1479</v>
       </c>
       <c r="E208">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F208" t="s">
         <v>1580</v>
@@ -15471,7 +15471,7 @@
         <v>1480</v>
       </c>
       <c r="E209">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F209" t="s">
         <v>1580</v>
@@ -15506,7 +15506,7 @@
         <v>1480</v>
       </c>
       <c r="E210">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F210" t="s">
         <v>1580</v>
@@ -15541,7 +15541,7 @@
         <v>1481</v>
       </c>
       <c r="E211">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F211" t="s">
         <v>1580</v>
@@ -15576,7 +15576,7 @@
         <v>1481</v>
       </c>
       <c r="E212">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F212" t="s">
         <v>1580</v>
@@ -15611,7 +15611,7 @@
         <v>1482</v>
       </c>
       <c r="E213">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F213" t="s">
         <v>1580</v>
@@ -15646,7 +15646,7 @@
         <v>1482</v>
       </c>
       <c r="E214">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F214" t="s">
         <v>1580</v>
@@ -15681,7 +15681,7 @@
         <v>1483</v>
       </c>
       <c r="E215">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F215" t="s">
         <v>1580</v>
@@ -15716,7 +15716,7 @@
         <v>1484</v>
       </c>
       <c r="E216">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F216" t="s">
         <v>1580</v>
@@ -15751,7 +15751,7 @@
         <v>1484</v>
       </c>
       <c r="E217">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F217" t="s">
         <v>1580</v>
@@ -15786,7 +15786,7 @@
         <v>1485</v>
       </c>
       <c r="E218">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F218" t="s">
         <v>1580</v>
@@ -15821,7 +15821,7 @@
         <v>1485</v>
       </c>
       <c r="E219">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F219" t="s">
         <v>1580</v>
@@ -15856,7 +15856,7 @@
         <v>1486</v>
       </c>
       <c r="E220">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F220" t="s">
         <v>1580</v>
@@ -15891,7 +15891,7 @@
         <v>1487</v>
       </c>
       <c r="E221">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F221" t="s">
         <v>1580</v>
@@ -15926,7 +15926,7 @@
         <v>1487</v>
       </c>
       <c r="E222">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F222" t="s">
         <v>1580</v>
@@ -15961,7 +15961,7 @@
         <v>1487</v>
       </c>
       <c r="E223">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F223" t="s">
         <v>1580</v>
@@ -15996,7 +15996,7 @@
         <v>1488</v>
       </c>
       <c r="E224">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F224" t="s">
         <v>1580</v>
@@ -16031,7 +16031,7 @@
         <v>1488</v>
       </c>
       <c r="E225">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F225" t="s">
         <v>1580</v>
@@ -16066,7 +16066,7 @@
         <v>1489</v>
       </c>
       <c r="E226">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F226" t="s">
         <v>1580</v>
@@ -16101,7 +16101,7 @@
         <v>1490</v>
       </c>
       <c r="E227">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F227" t="s">
         <v>1580</v>
@@ -16136,7 +16136,7 @@
         <v>1490</v>
       </c>
       <c r="E228">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F228" t="s">
         <v>1580</v>
@@ -16171,7 +16171,7 @@
         <v>1490</v>
       </c>
       <c r="E229">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F229" t="s">
         <v>1580</v>
@@ -16206,7 +16206,7 @@
         <v>1491</v>
       </c>
       <c r="E230">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F230" t="s">
         <v>1580</v>
@@ -16241,7 +16241,7 @@
         <v>1491</v>
       </c>
       <c r="E231">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F231" t="s">
         <v>1580</v>
@@ -16276,7 +16276,7 @@
         <v>1492</v>
       </c>
       <c r="E232">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F232" t="s">
         <v>1580</v>
@@ -16311,7 +16311,7 @@
         <v>1492</v>
       </c>
       <c r="E233">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F233" t="s">
         <v>1580</v>
@@ -16346,7 +16346,7 @@
         <v>1492</v>
       </c>
       <c r="E234">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F234" t="s">
         <v>1582</v>
@@ -16381,7 +16381,7 @@
         <v>1492</v>
       </c>
       <c r="E235">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F235" t="s">
         <v>1580</v>
@@ -16416,7 +16416,7 @@
         <v>1493</v>
       </c>
       <c r="E236">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F236" t="s">
         <v>1580</v>
@@ -16451,7 +16451,7 @@
         <v>1493</v>
       </c>
       <c r="E237">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F237" t="s">
         <v>1580</v>
@@ -16489,7 +16489,7 @@
         <v>1493</v>
       </c>
       <c r="E238">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F238" t="s">
         <v>1580</v>
@@ -16524,7 +16524,7 @@
         <v>1493</v>
       </c>
       <c r="E239">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F239" t="s">
         <v>1580</v>
@@ -16559,7 +16559,7 @@
         <v>1493</v>
       </c>
       <c r="E240">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F240" t="s">
         <v>1580</v>
@@ -16594,7 +16594,7 @@
         <v>1493</v>
       </c>
       <c r="E241">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F241" t="s">
         <v>1580</v>
@@ -16629,7 +16629,7 @@
         <v>1494</v>
       </c>
       <c r="E242">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F242" t="s">
         <v>1580</v>
@@ -16664,7 +16664,7 @@
         <v>1494</v>
       </c>
       <c r="E243">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F243" t="s">
         <v>1580</v>
@@ -16699,7 +16699,7 @@
         <v>1494</v>
       </c>
       <c r="E244">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F244" t="s">
         <v>1580</v>
@@ -16734,7 +16734,7 @@
         <v>1495</v>
       </c>
       <c r="E245">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F245" t="s">
         <v>1580</v>
@@ -16769,7 +16769,7 @@
         <v>1495</v>
       </c>
       <c r="E246">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F246" t="s">
         <v>1580</v>
@@ -16804,7 +16804,7 @@
         <v>1495</v>
       </c>
       <c r="E247">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F247" t="s">
         <v>1580</v>
@@ -16839,7 +16839,7 @@
         <v>1495</v>
       </c>
       <c r="E248">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F248" t="s">
         <v>1580</v>
@@ -16874,7 +16874,7 @@
         <v>1496</v>
       </c>
       <c r="E249">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F249" t="s">
         <v>1580</v>
@@ -16909,7 +16909,7 @@
         <v>1496</v>
       </c>
       <c r="E250">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F250" t="s">
         <v>1580</v>
@@ -16944,7 +16944,7 @@
         <v>1496</v>
       </c>
       <c r="E251">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F251" t="s">
         <v>1580</v>
@@ -16979,7 +16979,7 @@
         <v>1496</v>
       </c>
       <c r="E252">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F252" t="s">
         <v>1580</v>
@@ -17014,7 +17014,7 @@
         <v>1497</v>
       </c>
       <c r="E253">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F253" t="s">
         <v>1580</v>
@@ -17049,7 +17049,7 @@
         <v>1497</v>
       </c>
       <c r="E254">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F254" t="s">
         <v>1580</v>
@@ -17084,7 +17084,7 @@
         <v>1497</v>
       </c>
       <c r="E255">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F255" t="s">
         <v>1580</v>
@@ -17119,7 +17119,7 @@
         <v>1497</v>
       </c>
       <c r="E256">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F256" t="s">
         <v>1580</v>
@@ -17154,7 +17154,7 @@
         <v>1497</v>
       </c>
       <c r="E257">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F257" t="s">
         <v>1580</v>
@@ -17189,7 +17189,7 @@
         <v>1497</v>
       </c>
       <c r="E258">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F258" t="s">
         <v>1580</v>
@@ -17224,7 +17224,7 @@
         <v>1498</v>
       </c>
       <c r="E259">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F259" t="s">
         <v>1580</v>
@@ -17259,7 +17259,7 @@
         <v>1499</v>
       </c>
       <c r="E260">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F260" t="s">
         <v>1581</v>
@@ -17294,7 +17294,7 @@
         <v>1499</v>
       </c>
       <c r="E261">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F261" t="s">
         <v>1580</v>
@@ -17329,7 +17329,7 @@
         <v>1499</v>
       </c>
       <c r="E262">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F262" t="s">
         <v>1583</v>
@@ -17364,7 +17364,7 @@
         <v>1499</v>
       </c>
       <c r="E263">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F263" t="s">
         <v>1580</v>
@@ -17399,7 +17399,7 @@
         <v>1499</v>
       </c>
       <c r="E264">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F264" t="s">
         <v>1580</v>
@@ -17434,7 +17434,7 @@
         <v>1499</v>
       </c>
       <c r="E265">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F265" t="s">
         <v>1580</v>
@@ -17469,7 +17469,7 @@
         <v>1500</v>
       </c>
       <c r="E266">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F266" t="s">
         <v>1580</v>
@@ -17504,7 +17504,7 @@
         <v>1500</v>
       </c>
       <c r="E267">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F267" t="s">
         <v>1580</v>
@@ -17539,7 +17539,7 @@
         <v>1500</v>
       </c>
       <c r="E268">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F268" t="s">
         <v>1580</v>
@@ -17574,7 +17574,7 @@
         <v>1500</v>
       </c>
       <c r="E269">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F269" t="s">
         <v>1580</v>
@@ -17609,7 +17609,7 @@
         <v>1501</v>
       </c>
       <c r="E270">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F270" t="s">
         <v>1580</v>
@@ -17644,7 +17644,7 @@
         <v>1502</v>
       </c>
       <c r="E271">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F271" t="s">
         <v>1580</v>
@@ -17682,7 +17682,7 @@
         <v>1502</v>
       </c>
       <c r="E272">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F272" t="s">
         <v>1580</v>
@@ -17717,7 +17717,7 @@
         <v>1503</v>
       </c>
       <c r="E273">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F273" t="s">
         <v>1580</v>
@@ -17752,7 +17752,7 @@
         <v>1503</v>
       </c>
       <c r="E274">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F274" t="s">
         <v>1580</v>
@@ -17787,7 +17787,7 @@
         <v>1503</v>
       </c>
       <c r="E275">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F275" t="s">
         <v>1580</v>
@@ -17822,7 +17822,7 @@
         <v>1503</v>
       </c>
       <c r="E276">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F276" t="s">
         <v>1580</v>
@@ -17860,7 +17860,7 @@
         <v>1503</v>
       </c>
       <c r="E277">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F277" t="s">
         <v>1580</v>
@@ -17895,7 +17895,7 @@
         <v>1503</v>
       </c>
       <c r="E278">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F278" t="s">
         <v>1580</v>
@@ -17930,7 +17930,7 @@
         <v>1504</v>
       </c>
       <c r="E279">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F279" t="s">
         <v>1580</v>
@@ -17965,7 +17965,7 @@
         <v>1504</v>
       </c>
       <c r="E280">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F280" t="s">
         <v>1580</v>
@@ -18000,7 +18000,7 @@
         <v>1505</v>
       </c>
       <c r="E281">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F281" t="s">
         <v>1580</v>
@@ -18035,7 +18035,7 @@
         <v>1505</v>
       </c>
       <c r="E282">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F282" t="s">
         <v>1580</v>
@@ -18070,7 +18070,7 @@
         <v>1506</v>
       </c>
       <c r="E283">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F283" t="s">
         <v>1580</v>
@@ -18105,7 +18105,7 @@
         <v>1506</v>
       </c>
       <c r="E284">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F284" t="s">
         <v>1580</v>
@@ -18140,7 +18140,7 @@
         <v>1506</v>
       </c>
       <c r="E285">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F285" t="s">
         <v>1580</v>
@@ -18175,7 +18175,7 @@
         <v>1507</v>
       </c>
       <c r="E286">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F286" t="s">
         <v>1580</v>
@@ -18210,7 +18210,7 @@
         <v>1507</v>
       </c>
       <c r="E287">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F287" t="s">
         <v>1580</v>
@@ -18245,7 +18245,7 @@
         <v>1507</v>
       </c>
       <c r="E288">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F288" t="s">
         <v>1580</v>
@@ -18280,7 +18280,7 @@
         <v>1507</v>
       </c>
       <c r="E289">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F289" t="s">
         <v>1580</v>
@@ -18315,7 +18315,7 @@
         <v>1508</v>
       </c>
       <c r="E290">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F290" t="s">
         <v>1580</v>
@@ -18350,7 +18350,7 @@
         <v>1508</v>
       </c>
       <c r="E291">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F291" t="s">
         <v>1580</v>
@@ -18385,7 +18385,7 @@
         <v>1509</v>
       </c>
       <c r="E292">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F292" t="s">
         <v>1580</v>
@@ -18420,7 +18420,7 @@
         <v>1509</v>
       </c>
       <c r="E293">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F293" t="s">
         <v>1580</v>
@@ -18455,7 +18455,7 @@
         <v>1509</v>
       </c>
       <c r="E294">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F294" t="s">
         <v>1580</v>
@@ -18490,7 +18490,7 @@
         <v>1509</v>
       </c>
       <c r="E295">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F295" t="s">
         <v>1580</v>
@@ -18525,7 +18525,7 @@
         <v>1509</v>
       </c>
       <c r="E296">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F296" t="s">
         <v>1580</v>
@@ -18560,7 +18560,7 @@
         <v>1510</v>
       </c>
       <c r="E297">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F297" t="s">
         <v>1580</v>
@@ -18595,7 +18595,7 @@
         <v>1510</v>
       </c>
       <c r="E298">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F298" t="s">
         <v>1580</v>
@@ -18630,7 +18630,7 @@
         <v>1510</v>
       </c>
       <c r="E299">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F299" t="s">
         <v>1580</v>
@@ -18665,7 +18665,7 @@
         <v>1511</v>
       </c>
       <c r="E300">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F300" t="s">
         <v>1580</v>
@@ -18700,7 +18700,7 @@
         <v>1511</v>
       </c>
       <c r="E301">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F301" t="s">
         <v>1580</v>
@@ -18735,7 +18735,7 @@
         <v>1512</v>
       </c>
       <c r="E302">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F302" t="s">
         <v>1580</v>
@@ -18770,7 +18770,7 @@
         <v>1512</v>
       </c>
       <c r="E303">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F303" t="s">
         <v>1580</v>
@@ -18805,7 +18805,7 @@
         <v>1512</v>
       </c>
       <c r="E304">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F304" t="s">
         <v>1580</v>
@@ -18840,7 +18840,7 @@
         <v>1512</v>
       </c>
       <c r="E305">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F305" t="s">
         <v>1580</v>
@@ -18875,7 +18875,7 @@
         <v>1512</v>
       </c>
       <c r="E306">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F306" t="s">
         <v>1580</v>
@@ -18910,7 +18910,7 @@
         <v>1512</v>
       </c>
       <c r="E307">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F307" t="s">
         <v>1580</v>
@@ -18945,7 +18945,7 @@
         <v>1513</v>
       </c>
       <c r="E308">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F308" t="s">
         <v>1580</v>
@@ -18980,7 +18980,7 @@
         <v>1513</v>
       </c>
       <c r="E309">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F309" t="s">
         <v>1580</v>
@@ -19015,7 +19015,7 @@
         <v>1513</v>
       </c>
       <c r="E310">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F310" t="s">
         <v>1580</v>
@@ -19050,7 +19050,7 @@
         <v>1514</v>
       </c>
       <c r="E311">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F311" t="s">
         <v>1580</v>
@@ -19085,7 +19085,7 @@
         <v>1515</v>
       </c>
       <c r="E312">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F312" t="s">
         <v>1580</v>
@@ -19120,7 +19120,7 @@
         <v>1516</v>
       </c>
       <c r="E313">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F313" t="s">
         <v>1582</v>
@@ -19155,7 +19155,7 @@
         <v>1516</v>
       </c>
       <c r="E314">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F314" t="s">
         <v>1580</v>
@@ -19190,7 +19190,7 @@
         <v>1516</v>
       </c>
       <c r="E315">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F315" t="s">
         <v>1580</v>
@@ -19225,7 +19225,7 @@
         <v>1516</v>
       </c>
       <c r="E316">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F316" t="s">
         <v>1580</v>
@@ -19260,7 +19260,7 @@
         <v>1516</v>
       </c>
       <c r="E317">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F317" t="s">
         <v>1580</v>
@@ -19295,7 +19295,7 @@
         <v>1516</v>
       </c>
       <c r="E318">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F318" t="s">
         <v>1580</v>
@@ -19330,7 +19330,7 @@
         <v>1517</v>
       </c>
       <c r="E319">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F319" t="s">
         <v>1580</v>
@@ -19365,7 +19365,7 @@
         <v>1517</v>
       </c>
       <c r="E320">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F320" t="s">
         <v>1580</v>
@@ -19400,7 +19400,7 @@
         <v>1518</v>
       </c>
       <c r="E321">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F321" t="s">
         <v>1580</v>
@@ -19435,7 +19435,7 @@
         <v>1518</v>
       </c>
       <c r="E322">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F322" t="s">
         <v>1580</v>
@@ -19470,7 +19470,7 @@
         <v>1519</v>
       </c>
       <c r="E323">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F323" t="s">
         <v>1580</v>
@@ -19505,7 +19505,7 @@
         <v>1520</v>
       </c>
       <c r="E324">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F324" t="s">
         <v>1580</v>
@@ -19540,7 +19540,7 @@
         <v>1521</v>
       </c>
       <c r="E325">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F325" t="s">
         <v>1580</v>
@@ -19575,7 +19575,7 @@
         <v>1521</v>
       </c>
       <c r="E326">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F326" t="s">
         <v>1580</v>
@@ -19610,7 +19610,7 @@
         <v>1522</v>
       </c>
       <c r="E327">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F327" t="s">
         <v>1580</v>
@@ -19645,7 +19645,7 @@
         <v>1522</v>
       </c>
       <c r="E328">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F328" t="s">
         <v>1580</v>
@@ -19680,7 +19680,7 @@
         <v>1522</v>
       </c>
       <c r="E329">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F329" t="s">
         <v>1580</v>
@@ -19715,7 +19715,7 @@
         <v>1523</v>
       </c>
       <c r="E330">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F330" t="s">
         <v>1580</v>
@@ -19750,7 +19750,7 @@
         <v>1523</v>
       </c>
       <c r="E331">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F331" t="s">
         <v>1580</v>
@@ -19785,7 +19785,7 @@
         <v>1523</v>
       </c>
       <c r="E332">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F332" t="s">
         <v>1580</v>
@@ -19820,7 +19820,7 @@
         <v>1523</v>
       </c>
       <c r="E333">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F333" t="s">
         <v>1580</v>
@@ -19855,7 +19855,7 @@
         <v>1523</v>
       </c>
       <c r="E334">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F334" t="s">
         <v>1580</v>
@@ -19890,7 +19890,7 @@
         <v>1523</v>
       </c>
       <c r="E335">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F335" t="s">
         <v>1580</v>
@@ -19925,7 +19925,7 @@
         <v>1523</v>
       </c>
       <c r="E336">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F336" t="s">
         <v>1580</v>
@@ -19960,7 +19960,7 @@
         <v>1523</v>
       </c>
       <c r="E337">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F337" t="s">
         <v>1580</v>
@@ -19995,7 +19995,7 @@
         <v>1523</v>
       </c>
       <c r="E338">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F338" t="s">
         <v>1580</v>
@@ -20030,7 +20030,7 @@
         <v>1524</v>
       </c>
       <c r="E339">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F339" t="s">
         <v>1580</v>
@@ -20065,7 +20065,7 @@
         <v>1524</v>
       </c>
       <c r="E340">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F340" t="s">
         <v>1580</v>
@@ -20100,7 +20100,7 @@
         <v>1524</v>
       </c>
       <c r="E341">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F341" t="s">
         <v>1580</v>
@@ -20135,7 +20135,7 @@
         <v>1525</v>
       </c>
       <c r="E342">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F342" t="s">
         <v>1580</v>
@@ -20170,7 +20170,7 @@
         <v>1526</v>
       </c>
       <c r="E343">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F343" t="s">
         <v>1580</v>
@@ -20205,7 +20205,7 @@
         <v>1526</v>
       </c>
       <c r="E344">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F344" t="s">
         <v>1580</v>
@@ -20240,7 +20240,7 @@
         <v>1526</v>
       </c>
       <c r="E345">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F345" t="s">
         <v>1580</v>
@@ -20275,7 +20275,7 @@
         <v>1526</v>
       </c>
       <c r="E346">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F346" t="s">
         <v>1580</v>
@@ -20310,7 +20310,7 @@
         <v>1526</v>
       </c>
       <c r="E347">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F347" t="s">
         <v>1584</v>
@@ -20348,7 +20348,7 @@
         <v>1526</v>
       </c>
       <c r="E348">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F348" t="s">
         <v>1580</v>
@@ -20383,7 +20383,7 @@
         <v>1526</v>
       </c>
       <c r="E349">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F349" t="s">
         <v>1580</v>
@@ -20418,7 +20418,7 @@
         <v>1527</v>
       </c>
       <c r="E350">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F350" t="s">
         <v>1580</v>
@@ -20453,7 +20453,7 @@
         <v>1527</v>
       </c>
       <c r="E351">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F351" t="s">
         <v>1580</v>
@@ -20488,7 +20488,7 @@
         <v>1527</v>
       </c>
       <c r="E352">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F352" t="s">
         <v>1580</v>
@@ -20523,7 +20523,7 @@
         <v>1527</v>
       </c>
       <c r="E353">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F353" t="s">
         <v>1580</v>
@@ -20561,7 +20561,7 @@
         <v>1527</v>
       </c>
       <c r="E354">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F354" t="s">
         <v>1580</v>
@@ -20596,7 +20596,7 @@
         <v>1527</v>
       </c>
       <c r="E355">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F355" t="s">
         <v>1580</v>
@@ -20631,7 +20631,7 @@
         <v>1527</v>
       </c>
       <c r="E356">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F356" t="s">
         <v>1580</v>
@@ -20666,7 +20666,7 @@
         <v>1527</v>
       </c>
       <c r="E357">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F357" t="s">
         <v>1580</v>
@@ -20701,7 +20701,7 @@
         <v>1527</v>
       </c>
       <c r="E358">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F358" t="s">
         <v>1580</v>
@@ -20736,7 +20736,7 @@
         <v>1528</v>
       </c>
       <c r="E359">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F359" t="s">
         <v>1581</v>
@@ -20771,7 +20771,7 @@
         <v>1529</v>
       </c>
       <c r="E360">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F360" t="s">
         <v>1584</v>
@@ -20806,7 +20806,7 @@
         <v>1530</v>
       </c>
       <c r="E361">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F361" t="s">
         <v>1580</v>
@@ -20841,7 +20841,7 @@
         <v>1531</v>
       </c>
       <c r="E362">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F362" t="s">
         <v>1580</v>
@@ -20876,7 +20876,7 @@
         <v>1531</v>
       </c>
       <c r="E363">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F363" t="s">
         <v>1580</v>
@@ -20911,7 +20911,7 @@
         <v>1532</v>
       </c>
       <c r="E364">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F364" t="s">
         <v>1580</v>
@@ -20946,7 +20946,7 @@
         <v>1533</v>
       </c>
       <c r="E365">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F365" t="s">
         <v>1583</v>
@@ -20981,7 +20981,7 @@
         <v>1533</v>
       </c>
       <c r="E366">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F366" t="s">
         <v>1580</v>
@@ -21016,7 +21016,7 @@
         <v>1533</v>
       </c>
       <c r="E367">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F367" t="s">
         <v>1580</v>
@@ -21051,7 +21051,7 @@
         <v>1533</v>
       </c>
       <c r="E368">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F368" t="s">
         <v>1580</v>
@@ -21086,7 +21086,7 @@
         <v>1533</v>
       </c>
       <c r="E369">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F369" t="s">
         <v>1580</v>
@@ -21121,7 +21121,7 @@
         <v>1533</v>
       </c>
       <c r="E370">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F370" t="s">
         <v>1580</v>
@@ -21156,7 +21156,7 @@
         <v>1534</v>
       </c>
       <c r="E371">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F371" t="s">
         <v>1580</v>
@@ -21191,7 +21191,7 @@
         <v>1534</v>
       </c>
       <c r="E372">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F372" t="s">
         <v>1580</v>
@@ -21226,7 +21226,7 @@
         <v>1534</v>
       </c>
       <c r="E373">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F373" t="s">
         <v>1580</v>
@@ -21261,7 +21261,7 @@
         <v>1535</v>
       </c>
       <c r="E374">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F374" t="s">
         <v>1580</v>
@@ -21296,7 +21296,7 @@
         <v>1535</v>
       </c>
       <c r="E375">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F375" t="s">
         <v>1580</v>
@@ -21331,7 +21331,7 @@
         <v>1535</v>
       </c>
       <c r="E376">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F376" t="s">
         <v>1580</v>
@@ -21369,7 +21369,7 @@
         <v>1535</v>
       </c>
       <c r="E377">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F377" t="s">
         <v>1580</v>
@@ -21404,7 +21404,7 @@
         <v>1536</v>
       </c>
       <c r="E378">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F378" t="s">
         <v>1580</v>
@@ -21439,7 +21439,7 @@
         <v>1536</v>
       </c>
       <c r="E379">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F379" t="s">
         <v>1580</v>
@@ -21474,7 +21474,7 @@
         <v>1536</v>
       </c>
       <c r="E380">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F380" t="s">
         <v>1580</v>
@@ -21509,7 +21509,7 @@
         <v>1536</v>
       </c>
       <c r="E381">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F381" t="s">
         <v>1580</v>
@@ -21544,7 +21544,7 @@
         <v>1536</v>
       </c>
       <c r="E382">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F382" t="s">
         <v>1580</v>
@@ -21579,7 +21579,7 @@
         <v>1537</v>
       </c>
       <c r="E383">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F383" t="s">
         <v>1580</v>
@@ -21614,7 +21614,7 @@
         <v>1537</v>
       </c>
       <c r="E384">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F384" t="s">
         <v>1580</v>
@@ -21649,7 +21649,7 @@
         <v>1538</v>
       </c>
       <c r="E385">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F385" t="s">
         <v>1580</v>
@@ -21684,7 +21684,7 @@
         <v>1538</v>
       </c>
       <c r="E386">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F386" t="s">
         <v>1580</v>
@@ -21719,7 +21719,7 @@
         <v>1538</v>
       </c>
       <c r="E387">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F387" t="s">
         <v>1580</v>
@@ -21754,7 +21754,7 @@
         <v>1538</v>
       </c>
       <c r="E388">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F388" t="s">
         <v>1580</v>
@@ -21789,7 +21789,7 @@
         <v>1538</v>
       </c>
       <c r="E389">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F389" t="s">
         <v>1580</v>
@@ -21824,7 +21824,7 @@
         <v>1538</v>
       </c>
       <c r="E390">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F390" t="s">
         <v>1580</v>
@@ -21859,7 +21859,7 @@
         <v>1538</v>
       </c>
       <c r="E391">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F391" t="s">
         <v>1580</v>
@@ -21894,7 +21894,7 @@
         <v>1538</v>
       </c>
       <c r="E392">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F392" t="s">
         <v>1580</v>
@@ -21929,7 +21929,7 @@
         <v>1538</v>
       </c>
       <c r="E393">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F393" t="s">
         <v>1580</v>
@@ -21964,7 +21964,7 @@
         <v>1538</v>
       </c>
       <c r="E394">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F394" t="s">
         <v>1580</v>
@@ -21999,7 +21999,7 @@
         <v>1539</v>
       </c>
       <c r="E395">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F395" t="s">
         <v>1580</v>
@@ -22034,7 +22034,7 @@
         <v>1539</v>
       </c>
       <c r="E396">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F396" t="s">
         <v>1580</v>
@@ -22069,7 +22069,7 @@
         <v>1539</v>
       </c>
       <c r="E397">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F397" t="s">
         <v>1581</v>
@@ -22104,7 +22104,7 @@
         <v>1540</v>
       </c>
       <c r="E398">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F398" t="s">
         <v>1580</v>
@@ -22139,7 +22139,7 @@
         <v>1540</v>
       </c>
       <c r="E399">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F399" t="s">
         <v>1580</v>
@@ -22174,7 +22174,7 @@
         <v>1540</v>
       </c>
       <c r="E400">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F400" t="s">
         <v>1580</v>
@@ -22209,7 +22209,7 @@
         <v>1540</v>
       </c>
       <c r="E401">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F401" t="s">
         <v>1580</v>
@@ -22244,7 +22244,7 @@
         <v>1540</v>
       </c>
       <c r="E402">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F402" t="s">
         <v>1580</v>
@@ -22279,7 +22279,7 @@
         <v>1540</v>
       </c>
       <c r="E403">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F403" t="s">
         <v>1580</v>
@@ -22314,7 +22314,7 @@
         <v>1540</v>
       </c>
       <c r="E404">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F404" t="s">
         <v>1583</v>
@@ -22349,7 +22349,7 @@
         <v>1541</v>
       </c>
       <c r="E405">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F405" t="s">
         <v>1580</v>
@@ -22384,7 +22384,7 @@
         <v>1541</v>
       </c>
       <c r="E406">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F406" t="s">
         <v>1580</v>
@@ -22419,7 +22419,7 @@
         <v>1541</v>
       </c>
       <c r="E407">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F407" t="s">
         <v>1580</v>
@@ -22454,7 +22454,7 @@
         <v>1541</v>
       </c>
       <c r="E408">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F408" t="s">
         <v>1580</v>
@@ -22489,7 +22489,7 @@
         <v>1542</v>
       </c>
       <c r="E409">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F409" t="s">
         <v>1583</v>
@@ -22524,7 +22524,7 @@
         <v>1542</v>
       </c>
       <c r="E410">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F410" t="s">
         <v>1580</v>
@@ -22559,7 +22559,7 @@
         <v>1542</v>
       </c>
       <c r="E411">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F411" t="s">
         <v>1580</v>
@@ -22594,7 +22594,7 @@
         <v>1542</v>
       </c>
       <c r="E412">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F412" t="s">
         <v>1580</v>
@@ -22629,7 +22629,7 @@
         <v>1542</v>
       </c>
       <c r="E413">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F413" t="s">
         <v>1580</v>
@@ -22664,7 +22664,7 @@
         <v>1542</v>
       </c>
       <c r="E414">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F414" t="s">
         <v>1584</v>
@@ -22699,7 +22699,7 @@
         <v>1542</v>
       </c>
       <c r="E415">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F415" t="s">
         <v>1580</v>
@@ -22734,7 +22734,7 @@
         <v>1542</v>
       </c>
       <c r="E416">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F416" t="s">
         <v>1580</v>
@@ -22769,7 +22769,7 @@
         <v>1543</v>
       </c>
       <c r="E417">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F417" t="s">
         <v>1580</v>
@@ -22804,7 +22804,7 @@
         <v>1543</v>
       </c>
       <c r="E418">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F418" t="s">
         <v>1580</v>
@@ -22839,7 +22839,7 @@
         <v>1543</v>
       </c>
       <c r="E419">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F419" t="s">
         <v>1580</v>
@@ -22874,7 +22874,7 @@
         <v>1543</v>
       </c>
       <c r="E420">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F420" t="s">
         <v>1580</v>
@@ -22909,7 +22909,7 @@
         <v>1543</v>
       </c>
       <c r="E421">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F421" t="s">
         <v>1582</v>
@@ -22944,7 +22944,7 @@
         <v>1543</v>
       </c>
       <c r="E422">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F422" t="s">
         <v>1580</v>
@@ -22979,7 +22979,7 @@
         <v>1543</v>
       </c>
       <c r="E423">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F423" t="s">
         <v>1580</v>
@@ -23014,7 +23014,7 @@
         <v>1544</v>
       </c>
       <c r="E424">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F424" t="s">
         <v>1580</v>
@@ -23049,7 +23049,7 @@
         <v>1544</v>
       </c>
       <c r="E425">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F425" t="s">
         <v>1580</v>
@@ -23084,7 +23084,7 @@
         <v>1544</v>
       </c>
       <c r="E426">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F426" t="s">
         <v>1580</v>
@@ -23119,7 +23119,7 @@
         <v>1544</v>
       </c>
       <c r="E427">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F427" t="s">
         <v>1580</v>
@@ -23154,7 +23154,7 @@
         <v>1544</v>
       </c>
       <c r="E428">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F428" t="s">
         <v>1580</v>
@@ -23189,7 +23189,7 @@
         <v>1545</v>
       </c>
       <c r="E429">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F429" t="s">
         <v>1580</v>
@@ -23224,7 +23224,7 @@
         <v>1545</v>
       </c>
       <c r="E430">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F430" t="s">
         <v>1580</v>
@@ -23259,7 +23259,7 @@
         <v>1545</v>
       </c>
       <c r="E431">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F431" t="s">
         <v>1580</v>
@@ -23294,7 +23294,7 @@
         <v>1545</v>
       </c>
       <c r="E432">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F432" t="s">
         <v>1580</v>
@@ -23329,7 +23329,7 @@
         <v>1545</v>
       </c>
       <c r="E433">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F433" t="s">
         <v>1580</v>
@@ -23367,7 +23367,7 @@
         <v>1546</v>
       </c>
       <c r="E434">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F434" t="s">
         <v>1580</v>
@@ -23402,7 +23402,7 @@
         <v>1546</v>
       </c>
       <c r="E435">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F435" t="s">
         <v>1580</v>
@@ -23437,7 +23437,7 @@
         <v>1546</v>
       </c>
       <c r="E436">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F436" t="s">
         <v>1580</v>
@@ -23472,7 +23472,7 @@
         <v>1546</v>
       </c>
       <c r="E437">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F437" t="s">
         <v>1580</v>
@@ -23507,7 +23507,7 @@
         <v>1546</v>
       </c>
       <c r="E438">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F438" t="s">
         <v>1580</v>
@@ -23542,7 +23542,7 @@
         <v>1546</v>
       </c>
       <c r="E439">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F439" t="s">
         <v>1580</v>
@@ -23577,7 +23577,7 @@
         <v>1547</v>
       </c>
       <c r="E440">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F440" t="s">
         <v>1580</v>
@@ -23612,7 +23612,7 @@
         <v>1547</v>
       </c>
       <c r="E441">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F441" t="s">
         <v>1580</v>
@@ -23647,7 +23647,7 @@
         <v>1547</v>
       </c>
       <c r="E442">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F442" t="s">
         <v>1580</v>
@@ -23682,7 +23682,7 @@
         <v>1548</v>
       </c>
       <c r="E443">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F443" t="s">
         <v>1580</v>
@@ -23717,7 +23717,7 @@
         <v>1549</v>
       </c>
       <c r="E444">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F444" t="s">
         <v>1580</v>
@@ -23752,7 +23752,7 @@
         <v>1549</v>
       </c>
       <c r="E445">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F445" t="s">
         <v>1580</v>
@@ -23787,7 +23787,7 @@
         <v>1549</v>
       </c>
       <c r="E446">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F446" t="s">
         <v>1582</v>
@@ -23825,7 +23825,7 @@
         <v>1549</v>
       </c>
       <c r="E447">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F447" t="s">
         <v>1580</v>
@@ -23860,7 +23860,7 @@
         <v>1549</v>
       </c>
       <c r="E448">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F448" t="s">
         <v>1580</v>
@@ -23895,7 +23895,7 @@
         <v>1550</v>
       </c>
       <c r="E449">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F449" t="s">
         <v>1580</v>
@@ -23930,7 +23930,7 @@
         <v>1550</v>
       </c>
       <c r="E450">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F450" t="s">
         <v>1580</v>
@@ -23965,7 +23965,7 @@
         <v>1550</v>
       </c>
       <c r="E451">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F451" t="s">
         <v>1580</v>
@@ -24000,7 +24000,7 @@
         <v>1550</v>
       </c>
       <c r="E452">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F452" t="s">
         <v>1580</v>
@@ -24035,7 +24035,7 @@
         <v>1551</v>
       </c>
       <c r="E453">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F453" t="s">
         <v>1580</v>
@@ -24070,7 +24070,7 @@
         <v>1551</v>
       </c>
       <c r="E454">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F454" t="s">
         <v>1580</v>
@@ -24105,7 +24105,7 @@
         <v>1551</v>
       </c>
       <c r="E455">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F455" t="s">
         <v>1580</v>
@@ -24140,7 +24140,7 @@
         <v>1551</v>
       </c>
       <c r="E456">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F456" t="s">
         <v>1580</v>
@@ -24175,7 +24175,7 @@
         <v>1551</v>
       </c>
       <c r="E457">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F457" t="s">
         <v>1580</v>
@@ -24210,7 +24210,7 @@
         <v>1551</v>
       </c>
       <c r="E458">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F458" t="s">
         <v>1580</v>
@@ -24245,7 +24245,7 @@
         <v>1551</v>
       </c>
       <c r="E459">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F459" t="s">
         <v>1580</v>
@@ -24280,7 +24280,7 @@
         <v>1551</v>
       </c>
       <c r="E460">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F460" t="s">
         <v>1580</v>
@@ -24315,7 +24315,7 @@
         <v>1552</v>
       </c>
       <c r="E461">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F461" t="s">
         <v>1580</v>
@@ -24350,7 +24350,7 @@
         <v>1552</v>
       </c>
       <c r="E462">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F462" t="s">
         <v>1580</v>
@@ -24385,7 +24385,7 @@
         <v>1553</v>
       </c>
       <c r="E463">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F463" t="s">
         <v>1580</v>
@@ -24420,7 +24420,7 @@
         <v>1553</v>
       </c>
       <c r="E464">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F464" t="s">
         <v>1580</v>
@@ -24455,7 +24455,7 @@
         <v>1553</v>
       </c>
       <c r="E465">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F465" t="s">
         <v>1580</v>
@@ -24490,7 +24490,7 @@
         <v>1553</v>
       </c>
       <c r="E466">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F466" t="s">
         <v>1584</v>
@@ -24528,7 +24528,7 @@
         <v>1553</v>
       </c>
       <c r="E467">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F467" t="s">
         <v>1580</v>
@@ -24563,7 +24563,7 @@
         <v>1553</v>
       </c>
       <c r="E468">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F468" t="s">
         <v>1584</v>
@@ -24598,7 +24598,7 @@
         <v>1554</v>
       </c>
       <c r="E469">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F469" t="s">
         <v>1580</v>
@@ -24633,7 +24633,7 @@
         <v>1555</v>
       </c>
       <c r="E470">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F470" t="s">
         <v>1580</v>
@@ -24668,7 +24668,7 @@
         <v>1555</v>
       </c>
       <c r="E471">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F471" t="s">
         <v>1580</v>
@@ -24703,7 +24703,7 @@
         <v>1555</v>
       </c>
       <c r="E472">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F472" t="s">
         <v>1580</v>
@@ -24738,7 +24738,7 @@
         <v>1555</v>
       </c>
       <c r="E473">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F473" t="s">
         <v>1580</v>
@@ -24773,7 +24773,7 @@
         <v>1556</v>
       </c>
       <c r="E474">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F474" t="s">
         <v>1580</v>
@@ -24808,7 +24808,7 @@
         <v>1556</v>
       </c>
       <c r="E475">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F475" t="s">
         <v>1584</v>
@@ -24843,7 +24843,7 @@
         <v>1556</v>
       </c>
       <c r="E476">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F476" t="s">
         <v>1580</v>
@@ -24878,7 +24878,7 @@
         <v>1556</v>
       </c>
       <c r="E477">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F477" t="s">
         <v>1580</v>
@@ -24913,7 +24913,7 @@
         <v>1556</v>
       </c>
       <c r="E478">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F478" t="s">
         <v>1580</v>
@@ -24948,7 +24948,7 @@
         <v>1557</v>
       </c>
       <c r="E479">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F479" t="s">
         <v>1580</v>
@@ -24983,7 +24983,7 @@
         <v>1557</v>
       </c>
       <c r="E480">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F480" t="s">
         <v>1580</v>
@@ -25018,7 +25018,7 @@
         <v>1557</v>
       </c>
       <c r="E481">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F481" t="s">
         <v>1580</v>
@@ -25053,7 +25053,7 @@
         <v>1558</v>
       </c>
       <c r="E482">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F482" t="s">
         <v>1580</v>
@@ -25088,7 +25088,7 @@
         <v>1558</v>
       </c>
       <c r="E483">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F483" t="s">
         <v>1580</v>
@@ -25123,7 +25123,7 @@
         <v>1558</v>
       </c>
       <c r="E484">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F484" t="s">
         <v>1580</v>
@@ -25158,7 +25158,7 @@
         <v>1558</v>
       </c>
       <c r="E485">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F485" t="s">
         <v>1580</v>
@@ -25193,7 +25193,7 @@
         <v>1558</v>
       </c>
       <c r="E486">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F486" t="s">
         <v>1580</v>
@@ -25228,7 +25228,7 @@
         <v>1558</v>
       </c>
       <c r="E487">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F487" t="s">
         <v>1580</v>
@@ -25263,7 +25263,7 @@
         <v>1559</v>
       </c>
       <c r="E488">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F488" t="s">
         <v>1580</v>
@@ -25298,7 +25298,7 @@
         <v>1559</v>
       </c>
       <c r="E489">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F489" t="s">
         <v>1580</v>
@@ -25333,7 +25333,7 @@
         <v>1559</v>
       </c>
       <c r="E490">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F490" t="s">
         <v>1580</v>
@@ -25368,7 +25368,7 @@
         <v>1559</v>
       </c>
       <c r="E491">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F491" t="s">
         <v>1580</v>
@@ -25403,7 +25403,7 @@
         <v>1559</v>
       </c>
       <c r="E492">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F492" t="s">
         <v>1580</v>
@@ -25438,7 +25438,7 @@
         <v>1559</v>
       </c>
       <c r="E493">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F493" t="s">
         <v>1580</v>
@@ -25473,7 +25473,7 @@
         <v>1559</v>
       </c>
       <c r="E494">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F494" t="s">
         <v>1580</v>
@@ -25508,7 +25508,7 @@
         <v>1559</v>
       </c>
       <c r="E495">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F495" t="s">
         <v>1580</v>
@@ -25543,7 +25543,7 @@
         <v>1559</v>
       </c>
       <c r="E496">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F496" t="s">
         <v>1580</v>
@@ -25578,7 +25578,7 @@
         <v>1559</v>
       </c>
       <c r="E497">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F497" t="s">
         <v>1580</v>
@@ -25613,7 +25613,7 @@
         <v>1559</v>
       </c>
       <c r="E498">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F498" t="s">
         <v>1580</v>
@@ -25648,7 +25648,7 @@
         <v>1559</v>
       </c>
       <c r="E499">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F499" t="s">
         <v>1580</v>
@@ -25683,7 +25683,7 @@
         <v>1559</v>
       </c>
       <c r="E500">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F500" t="s">
         <v>1580</v>
@@ -25718,7 +25718,7 @@
         <v>1559</v>
       </c>
       <c r="E501">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F501" t="s">
         <v>1580</v>
@@ -25753,7 +25753,7 @@
         <v>1559</v>
       </c>
       <c r="E502">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F502" t="s">
         <v>1580</v>
@@ -25788,7 +25788,7 @@
         <v>1559</v>
       </c>
       <c r="E503">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F503" t="s">
         <v>1580</v>
@@ -25823,7 +25823,7 @@
         <v>1559</v>
       </c>
       <c r="E504">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F504" t="s">
         <v>1580</v>
@@ -25858,7 +25858,7 @@
         <v>1559</v>
       </c>
       <c r="E505">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F505" t="s">
         <v>1580</v>
@@ -25893,7 +25893,7 @@
         <v>1559</v>
       </c>
       <c r="E506">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F506" t="s">
         <v>1580</v>
@@ -25928,7 +25928,7 @@
         <v>1559</v>
       </c>
       <c r="E507">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F507" t="s">
         <v>1580</v>
@@ -25963,7 +25963,7 @@
         <v>1559</v>
       </c>
       <c r="E508">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F508" t="s">
         <v>1580</v>
@@ -25998,7 +25998,7 @@
         <v>1559</v>
       </c>
       <c r="E509">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F509" t="s">
         <v>1580</v>
@@ -26033,7 +26033,7 @@
         <v>1559</v>
       </c>
       <c r="E510">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F510" t="s">
         <v>1580</v>
@@ -26068,7 +26068,7 @@
         <v>1559</v>
       </c>
       <c r="E511">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F511" t="s">
         <v>1580</v>
@@ -26103,7 +26103,7 @@
         <v>1559</v>
       </c>
       <c r="E512">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F512" t="s">
         <v>1580</v>
@@ -26138,7 +26138,7 @@
         <v>1560</v>
       </c>
       <c r="E513">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F513" t="s">
         <v>1580</v>
@@ -26173,7 +26173,7 @@
         <v>1560</v>
       </c>
       <c r="E514">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F514" t="s">
         <v>1580</v>
@@ -26208,7 +26208,7 @@
         <v>1560</v>
       </c>
       <c r="E515">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F515" t="s">
         <v>1580</v>
@@ -26243,7 +26243,7 @@
         <v>1560</v>
       </c>
       <c r="E516">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F516" t="s">
         <v>1580</v>
@@ -26278,7 +26278,7 @@
         <v>1560</v>
       </c>
       <c r="E517">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F517" t="s">
         <v>1580</v>
@@ -26313,7 +26313,7 @@
         <v>1560</v>
       </c>
       <c r="E518">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F518" t="s">
         <v>1580</v>
@@ -26348,7 +26348,7 @@
         <v>1560</v>
       </c>
       <c r="E519">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F519" t="s">
         <v>1584</v>
@@ -26383,7 +26383,7 @@
         <v>1560</v>
       </c>
       <c r="E520">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F520" t="s">
         <v>1580</v>
@@ -26418,7 +26418,7 @@
         <v>1561</v>
       </c>
       <c r="E521">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F521" t="s">
         <v>1580</v>
@@ -26453,7 +26453,7 @@
         <v>1561</v>
       </c>
       <c r="E522">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F522" t="s">
         <v>1582</v>
@@ -26491,7 +26491,7 @@
         <v>1562</v>
       </c>
       <c r="E523">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F523" t="s">
         <v>1582</v>
@@ -26529,7 +26529,7 @@
         <v>1562</v>
       </c>
       <c r="E524">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F524" t="s">
         <v>1580</v>
@@ -26564,7 +26564,7 @@
         <v>1562</v>
       </c>
       <c r="E525">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F525" t="s">
         <v>1582</v>
@@ -26602,7 +26602,7 @@
         <v>1562</v>
       </c>
       <c r="E526">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F526" t="s">
         <v>1580</v>
@@ -26637,7 +26637,7 @@
         <v>1562</v>
       </c>
       <c r="E527">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F527" t="s">
         <v>1580</v>
@@ -26672,7 +26672,7 @@
         <v>1562</v>
       </c>
       <c r="E528">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F528" t="s">
         <v>1580</v>
@@ -26707,7 +26707,7 @@
         <v>1562</v>
       </c>
       <c r="E529">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F529" t="s">
         <v>1580</v>
@@ -26742,7 +26742,7 @@
         <v>1562</v>
       </c>
       <c r="E530">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F530" t="s">
         <v>1580</v>
@@ -26777,7 +26777,7 @@
         <v>1563</v>
       </c>
       <c r="E531">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F531" t="s">
         <v>1580</v>
@@ -26815,7 +26815,7 @@
         <v>1563</v>
       </c>
       <c r="E532">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F532" t="s">
         <v>1584</v>
@@ -26850,7 +26850,7 @@
         <v>1563</v>
       </c>
       <c r="E533">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F533" t="s">
         <v>1582</v>
@@ -26885,7 +26885,7 @@
         <v>1563</v>
       </c>
       <c r="E534">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F534" t="s">
         <v>1580</v>
@@ -26920,7 +26920,7 @@
         <v>1563</v>
       </c>
       <c r="E535">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F535" t="s">
         <v>1580</v>
@@ -26955,7 +26955,7 @@
         <v>1563</v>
       </c>
       <c r="E536">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F536" t="s">
         <v>1580</v>
@@ -26990,7 +26990,7 @@
         <v>1563</v>
       </c>
       <c r="E537">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F537" t="s">
         <v>1580</v>
@@ -27025,7 +27025,7 @@
         <v>1563</v>
       </c>
       <c r="E538">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F538" t="s">
         <v>1580</v>
@@ -27060,7 +27060,7 @@
         <v>1563</v>
       </c>
       <c r="E539">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F539" t="s">
         <v>1580</v>
@@ -27095,7 +27095,7 @@
         <v>1564</v>
       </c>
       <c r="E540">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F540" t="s">
         <v>1580</v>
@@ -27133,7 +27133,7 @@
         <v>1564</v>
       </c>
       <c r="E541">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F541" t="s">
         <v>1580</v>
@@ -27168,7 +27168,7 @@
         <v>1565</v>
       </c>
       <c r="E542">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F542" t="s">
         <v>1580</v>
@@ -27203,7 +27203,7 @@
         <v>1565</v>
       </c>
       <c r="E543">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F543" t="s">
         <v>1582</v>
@@ -27241,7 +27241,7 @@
         <v>1565</v>
       </c>
       <c r="E544">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F544" t="s">
         <v>1580</v>
@@ -27276,7 +27276,7 @@
         <v>1565</v>
       </c>
       <c r="E545">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F545" t="s">
         <v>1580</v>
@@ -27311,7 +27311,7 @@
         <v>1565</v>
       </c>
       <c r="E546">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F546" t="s">
         <v>1580</v>
@@ -27346,7 +27346,7 @@
         <v>1565</v>
       </c>
       <c r="E547">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F547" t="s">
         <v>1580</v>
@@ -27381,7 +27381,7 @@
         <v>1565</v>
       </c>
       <c r="E548">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F548" t="s">
         <v>1580</v>
@@ -27416,7 +27416,7 @@
         <v>1565</v>
       </c>
       <c r="E549">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F549" t="s">
         <v>1580</v>
@@ -27451,7 +27451,7 @@
         <v>1566</v>
       </c>
       <c r="E550">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F550" t="s">
         <v>1580</v>
@@ -27486,7 +27486,7 @@
         <v>1566</v>
       </c>
       <c r="E551">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F551" t="s">
         <v>1580</v>
@@ -27521,7 +27521,7 @@
         <v>1566</v>
       </c>
       <c r="E552">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F552" t="s">
         <v>1580</v>
@@ -27556,7 +27556,7 @@
         <v>1566</v>
       </c>
       <c r="E553">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F553" t="s">
         <v>1580</v>
@@ -27591,7 +27591,7 @@
         <v>1566</v>
       </c>
       <c r="E554">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F554" t="s">
         <v>1580</v>
@@ -27626,7 +27626,7 @@
         <v>1566</v>
       </c>
       <c r="E555">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F555" t="s">
         <v>1580</v>
@@ -27661,7 +27661,7 @@
         <v>1566</v>
       </c>
       <c r="E556">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F556" t="s">
         <v>1580</v>
@@ -27696,7 +27696,7 @@
         <v>1566</v>
       </c>
       <c r="E557">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F557" t="s">
         <v>1580</v>
@@ -27731,7 +27731,7 @@
         <v>1566</v>
       </c>
       <c r="E558">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F558" t="s">
         <v>1582</v>
@@ -27766,7 +27766,7 @@
         <v>1566</v>
       </c>
       <c r="E559">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F559" t="s">
         <v>1580</v>
@@ -27801,7 +27801,7 @@
         <v>1566</v>
       </c>
       <c r="E560">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F560" t="s">
         <v>1584</v>
@@ -27836,7 +27836,7 @@
         <v>1566</v>
       </c>
       <c r="E561">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F561" t="s">
         <v>1580</v>
@@ -27871,7 +27871,7 @@
         <v>1567</v>
       </c>
       <c r="E562">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F562" t="s">
         <v>1580</v>
@@ -27906,7 +27906,7 @@
         <v>1567</v>
       </c>
       <c r="E563">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F563" t="s">
         <v>1580</v>
@@ -27941,7 +27941,7 @@
         <v>1567</v>
       </c>
       <c r="E564">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F564" t="s">
         <v>1580</v>
@@ -27976,7 +27976,7 @@
         <v>1567</v>
       </c>
       <c r="E565">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F565" t="s">
         <v>1580</v>
@@ -28011,7 +28011,7 @@
         <v>1567</v>
       </c>
       <c r="E566">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F566" t="s">
         <v>1580</v>
@@ -28046,7 +28046,7 @@
         <v>1567</v>
       </c>
       <c r="E567">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F567" t="s">
         <v>1580</v>
@@ -28081,7 +28081,7 @@
         <v>1567</v>
       </c>
       <c r="E568">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F568" t="s">
         <v>1580</v>
@@ -28116,7 +28116,7 @@
         <v>1567</v>
       </c>
       <c r="E569">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F569" t="s">
         <v>1580</v>
@@ -28154,7 +28154,7 @@
         <v>1567</v>
       </c>
       <c r="E570">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F570" t="s">
         <v>1582</v>
@@ -28192,7 +28192,7 @@
         <v>1567</v>
       </c>
       <c r="E571">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F571" t="s">
         <v>1582</v>
@@ -28227,7 +28227,7 @@
         <v>1567</v>
       </c>
       <c r="E572">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F572" t="s">
         <v>1582</v>
@@ -28262,7 +28262,7 @@
         <v>1567</v>
       </c>
       <c r="E573">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F573" t="s">
         <v>1580</v>
@@ -28297,7 +28297,7 @@
         <v>1568</v>
       </c>
       <c r="E574">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F574" t="s">
         <v>1580</v>
@@ -28332,7 +28332,7 @@
         <v>1568</v>
       </c>
       <c r="E575">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F575" t="s">
         <v>1580</v>
@@ -28367,7 +28367,7 @@
         <v>1568</v>
       </c>
       <c r="E576">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F576" t="s">
         <v>1580</v>
@@ -28402,7 +28402,7 @@
         <v>1568</v>
       </c>
       <c r="E577">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F577" t="s">
         <v>1580</v>
@@ -28437,7 +28437,7 @@
         <v>1568</v>
       </c>
       <c r="E578">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F578" t="s">
         <v>1580</v>
@@ -28472,7 +28472,7 @@
         <v>1568</v>
       </c>
       <c r="E579">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F579" t="s">
         <v>1580</v>
@@ -28507,7 +28507,7 @@
         <v>1568</v>
       </c>
       <c r="E580">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F580" t="s">
         <v>1580</v>
@@ -28542,7 +28542,7 @@
         <v>1568</v>
       </c>
       <c r="E581">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F581" t="s">
         <v>1580</v>
@@ -28577,7 +28577,7 @@
         <v>1568</v>
       </c>
       <c r="E582">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F582" t="s">
         <v>1580</v>
@@ -28615,7 +28615,7 @@
         <v>1569</v>
       </c>
       <c r="E583">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F583" t="s">
         <v>1580</v>
@@ -28650,7 +28650,7 @@
         <v>1569</v>
       </c>
       <c r="E584">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F584" t="s">
         <v>1580</v>
@@ -28685,7 +28685,7 @@
         <v>1570</v>
       </c>
       <c r="E585">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F585" t="s">
         <v>1580</v>
@@ -28723,7 +28723,7 @@
         <v>1570</v>
       </c>
       <c r="E586">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F586" t="s">
         <v>1580</v>
@@ -28758,7 +28758,7 @@
         <v>1570</v>
       </c>
       <c r="E587">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F587" t="s">
         <v>1580</v>
@@ -28793,7 +28793,7 @@
         <v>1570</v>
       </c>
       <c r="E588">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F588" t="s">
         <v>1582</v>
@@ -28831,7 +28831,7 @@
         <v>1570</v>
       </c>
       <c r="E589">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F589" t="s">
         <v>1582</v>
@@ -28869,7 +28869,7 @@
         <v>1570</v>
       </c>
       <c r="E590">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F590" t="s">
         <v>1580</v>
@@ -28904,7 +28904,7 @@
         <v>1570</v>
       </c>
       <c r="E591">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F591" t="s">
         <v>1580</v>
@@ -28939,7 +28939,7 @@
         <v>1570</v>
       </c>
       <c r="E592">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F592" t="s">
         <v>1580</v>
@@ -28974,7 +28974,7 @@
         <v>1571</v>
       </c>
       <c r="E593">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F593" t="s">
         <v>1580</v>
@@ -29009,7 +29009,7 @@
         <v>1571</v>
       </c>
       <c r="E594">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F594" t="s">
         <v>1580</v>
@@ -29044,7 +29044,7 @@
         <v>1571</v>
       </c>
       <c r="E595">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F595" t="s">
         <v>1580</v>
@@ -29079,7 +29079,7 @@
         <v>1571</v>
       </c>
       <c r="E596">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F596" t="s">
         <v>1580</v>
@@ -29114,7 +29114,7 @@
         <v>1571</v>
       </c>
       <c r="E597">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F597" t="s">
         <v>1580</v>
@@ -29149,7 +29149,7 @@
         <v>1571</v>
       </c>
       <c r="E598">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F598" t="s">
         <v>1580</v>
@@ -29184,7 +29184,7 @@
         <v>1571</v>
       </c>
       <c r="E599">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F599" t="s">
         <v>1580</v>
@@ -29219,7 +29219,7 @@
         <v>1571</v>
       </c>
       <c r="E600">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F600" t="s">
         <v>1580</v>
@@ -29254,7 +29254,7 @@
         <v>1571</v>
       </c>
       <c r="E601">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F601" t="s">
         <v>1580</v>
@@ -29289,7 +29289,7 @@
         <v>1571</v>
       </c>
       <c r="E602">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F602" t="s">
         <v>1580</v>
@@ -29327,7 +29327,7 @@
         <v>1571</v>
       </c>
       <c r="E603">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F603" t="s">
         <v>1580</v>
@@ -29362,7 +29362,7 @@
         <v>1572</v>
       </c>
       <c r="E604">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F604" t="s">
         <v>1580</v>
@@ -29397,7 +29397,7 @@
         <v>1572</v>
       </c>
       <c r="E605">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F605" t="s">
         <v>1582</v>
@@ -29435,7 +29435,7 @@
         <v>1572</v>
       </c>
       <c r="E606">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F606" t="s">
         <v>1580</v>
@@ -29470,7 +29470,7 @@
         <v>1572</v>
       </c>
       <c r="E607">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F607" t="s">
         <v>1580</v>
@@ -29505,7 +29505,7 @@
         <v>1573</v>
       </c>
       <c r="E608">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F608" t="s">
         <v>1580</v>
@@ -29540,7 +29540,7 @@
         <v>1573</v>
       </c>
       <c r="E609">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F609" t="s">
         <v>1580</v>
@@ -29575,7 +29575,7 @@
         <v>1573</v>
       </c>
       <c r="E610">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F610" t="s">
         <v>1580</v>
@@ -29610,7 +29610,7 @@
         <v>1573</v>
       </c>
       <c r="E611">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F611" t="s">
         <v>1580</v>
@@ -29645,7 +29645,7 @@
         <v>1573</v>
       </c>
       <c r="E612">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F612" t="s">
         <v>1582</v>
@@ -29683,7 +29683,7 @@
         <v>1573</v>
       </c>
       <c r="E613">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F613" t="s">
         <v>1582</v>
@@ -29721,7 +29721,7 @@
         <v>1573</v>
       </c>
       <c r="E614">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F614" t="s">
         <v>1580</v>
@@ -29756,7 +29756,7 @@
         <v>1573</v>
       </c>
       <c r="E615">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F615" t="s">
         <v>1580</v>
@@ -29791,7 +29791,7 @@
         <v>1573</v>
       </c>
       <c r="E616">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F616" t="s">
         <v>1580</v>
@@ -29826,7 +29826,7 @@
         <v>1573</v>
       </c>
       <c r="E617">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F617" t="s">
         <v>1580</v>
@@ -29861,7 +29861,7 @@
         <v>1573</v>
       </c>
       <c r="E618">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F618" t="s">
         <v>1580</v>
@@ -29896,7 +29896,7 @@
         <v>1573</v>
       </c>
       <c r="E619">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F619" t="s">
         <v>1580</v>
@@ -29931,7 +29931,7 @@
         <v>1573</v>
       </c>
       <c r="E620">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F620" t="s">
         <v>1580</v>
@@ -29966,7 +29966,7 @@
         <v>1574</v>
       </c>
       <c r="E621">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F621" t="s">
         <v>1584</v>
@@ -30001,7 +30001,7 @@
         <v>1574</v>
       </c>
       <c r="E622">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F622" t="s">
         <v>1580</v>
@@ -30036,7 +30036,7 @@
         <v>1574</v>
       </c>
       <c r="E623">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F623" t="s">
         <v>1580</v>
@@ -30071,7 +30071,7 @@
         <v>1574</v>
       </c>
       <c r="E624">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F624" t="s">
         <v>1580</v>
@@ -30106,7 +30106,7 @@
         <v>1574</v>
       </c>
       <c r="E625">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F625" t="s">
         <v>1580</v>
@@ -30141,7 +30141,7 @@
         <v>1574</v>
       </c>
       <c r="E626">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F626" t="s">
         <v>1582</v>
@@ -30176,7 +30176,7 @@
         <v>1574</v>
       </c>
       <c r="E627">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F627" t="s">
         <v>1580</v>
@@ -30211,7 +30211,7 @@
         <v>1574</v>
       </c>
       <c r="E628">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F628" t="s">
         <v>1580</v>
@@ -30246,7 +30246,7 @@
         <v>1575</v>
       </c>
       <c r="E629">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F629" t="s">
         <v>1580</v>
@@ -30281,7 +30281,7 @@
         <v>1575</v>
       </c>
       <c r="E630">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F630" t="s">
         <v>1580</v>
@@ -30319,7 +30319,7 @@
         <v>1575</v>
       </c>
       <c r="E631">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F631" t="s">
         <v>1580</v>
@@ -30354,7 +30354,7 @@
         <v>1575</v>
       </c>
       <c r="E632">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F632" t="s">
         <v>1580</v>
@@ -30389,7 +30389,7 @@
         <v>1575</v>
       </c>
       <c r="E633">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F633" t="s">
         <v>1580</v>
@@ -30424,7 +30424,7 @@
         <v>1575</v>
       </c>
       <c r="E634">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F634" t="s">
         <v>1582</v>
@@ -30462,7 +30462,7 @@
         <v>1576</v>
       </c>
       <c r="E635">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F635" t="s">
         <v>1580</v>
@@ -30497,7 +30497,7 @@
         <v>1576</v>
       </c>
       <c r="E636">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F636" t="s">
         <v>1580</v>
@@ -30535,7 +30535,7 @@
         <v>1576</v>
       </c>
       <c r="E637">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F637" t="s">
         <v>1582</v>
@@ -30573,7 +30573,7 @@
         <v>1576</v>
       </c>
       <c r="E638">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F638" t="s">
         <v>1582</v>
@@ -30611,7 +30611,7 @@
         <v>1576</v>
       </c>
       <c r="E639">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F639" t="s">
         <v>1580</v>
@@ -30646,7 +30646,7 @@
         <v>1576</v>
       </c>
       <c r="E640">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F640" t="s">
         <v>1580</v>
@@ -30681,7 +30681,7 @@
         <v>1577</v>
       </c>
       <c r="E641">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F641" t="s">
         <v>1582</v>
@@ -30719,7 +30719,7 @@
         <v>1577</v>
       </c>
       <c r="E642">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F642" t="s">
         <v>1580</v>
@@ -30754,7 +30754,7 @@
         <v>1577</v>
       </c>
       <c r="E643">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F643" t="s">
         <v>1580</v>
@@ -30789,7 +30789,7 @@
         <v>1577</v>
       </c>
       <c r="E644">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F644" t="s">
         <v>1580</v>
@@ -30824,7 +30824,7 @@
         <v>1577</v>
       </c>
       <c r="E645">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F645" t="s">
         <v>1580</v>
@@ -30859,7 +30859,7 @@
         <v>1577</v>
       </c>
       <c r="E646">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F646" t="s">
         <v>1580</v>
@@ -30894,7 +30894,7 @@
         <v>1577</v>
       </c>
       <c r="E647">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F647" t="s">
         <v>1580</v>
@@ -30929,7 +30929,7 @@
         <v>1577</v>
       </c>
       <c r="E648">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F648" t="s">
         <v>1580</v>
@@ -30964,7 +30964,7 @@
         <v>1577</v>
       </c>
       <c r="E649">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F649" t="s">
         <v>1580</v>
@@ -31002,7 +31002,7 @@
         <v>1577</v>
       </c>
       <c r="E650">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F650" t="s">
         <v>1580</v>
@@ -31037,7 +31037,7 @@
         <v>1577</v>
       </c>
       <c r="E651">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F651" t="s">
         <v>1580</v>
@@ -31072,7 +31072,7 @@
         <v>1577</v>
       </c>
       <c r="E652">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F652" t="s">
         <v>1580</v>
@@ -31107,7 +31107,7 @@
         <v>1578</v>
       </c>
       <c r="E653">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F653" t="s">
         <v>1580</v>
@@ -31142,7 +31142,7 @@
         <v>1578</v>
       </c>
       <c r="E654">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F654" t="s">
         <v>1580</v>
@@ -31180,7 +31180,7 @@
         <v>1578</v>
       </c>
       <c r="E655">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F655" t="s">
         <v>1580</v>
@@ -31215,7 +31215,7 @@
         <v>1578</v>
       </c>
       <c r="E656">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F656" t="s">
         <v>1580</v>
@@ -31250,7 +31250,7 @@
         <v>1578</v>
       </c>
       <c r="E657">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F657" t="s">
         <v>1580</v>
@@ -31285,7 +31285,7 @@
         <v>1579</v>
       </c>
       <c r="E658">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F658" t="s">
         <v>1580</v>
@@ -31323,7 +31323,7 @@
         <v>1579</v>
       </c>
       <c r="E659">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F659" t="s">
         <v>1580</v>
@@ -31361,7 +31361,7 @@
         <v>1579</v>
       </c>
       <c r="E660">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F660" t="s">
         <v>1580</v>
@@ -31399,7 +31399,7 @@
         <v>1579</v>
       </c>
       <c r="E661">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F661" t="s">
         <v>1580</v>
@@ -31437,7 +31437,7 @@
         <v>1579</v>
       </c>
       <c r="E662">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F662" t="s">
         <v>1580</v>
@@ -31475,7 +31475,7 @@
         <v>1579</v>
       </c>
       <c r="E663">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F663" t="s">
         <v>1582</v>
@@ -31510,7 +31510,7 @@
         <v>1579</v>
       </c>
       <c r="E664">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F664" t="s">
         <v>1580</v>
@@ -31545,7 +31545,7 @@
         <v>1579</v>
       </c>
       <c r="E665">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F665" t="s">
         <v>1580</v>
@@ -31580,7 +31580,7 @@
         <v>1579</v>
       </c>
       <c r="E666">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F666" t="s">
         <v>1580</v>
@@ -31615,7 +31615,7 @@
         <v>1579</v>
       </c>
       <c r="E667">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F667" t="s">
         <v>1580</v>

--- a/BacklogGATEAutoCompleto.xlsx
+++ b/BacklogGATEAutoCompleto.xlsx
@@ -8220,7 +8220,7 @@
         <v>1368</v>
       </c>
       <c r="E2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="F2" t="s">
         <v>1580</v>
@@ -8255,7 +8255,7 @@
         <v>1369</v>
       </c>
       <c r="E3">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="F3" t="s">
         <v>1580</v>
@@ -8290,7 +8290,7 @@
         <v>1370</v>
       </c>
       <c r="E4">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="F4" t="s">
         <v>1580</v>
@@ -8325,7 +8325,7 @@
         <v>1371</v>
       </c>
       <c r="E5">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="F5" t="s">
         <v>1580</v>
@@ -8360,7 +8360,7 @@
         <v>1372</v>
       </c>
       <c r="E6">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="F6" t="s">
         <v>1580</v>
@@ -8395,7 +8395,7 @@
         <v>1373</v>
       </c>
       <c r="E7">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="F7" t="s">
         <v>1580</v>
@@ -8430,7 +8430,7 @@
         <v>1374</v>
       </c>
       <c r="E8">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="F8" t="s">
         <v>1580</v>
@@ -8465,7 +8465,7 @@
         <v>1375</v>
       </c>
       <c r="E9">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="F9" t="s">
         <v>1580</v>
@@ -8500,7 +8500,7 @@
         <v>1376</v>
       </c>
       <c r="E10">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F10" t="s">
         <v>1580</v>
@@ -8535,7 +8535,7 @@
         <v>1376</v>
       </c>
       <c r="E11">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F11" t="s">
         <v>1580</v>
@@ -8570,7 +8570,7 @@
         <v>1377</v>
       </c>
       <c r="E12">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="F12" t="s">
         <v>1580</v>
@@ -8605,7 +8605,7 @@
         <v>1378</v>
       </c>
       <c r="E13">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F13" t="s">
         <v>1580</v>
@@ -8640,7 +8640,7 @@
         <v>1379</v>
       </c>
       <c r="E14">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="F14" t="s">
         <v>1580</v>
@@ -8675,7 +8675,7 @@
         <v>1379</v>
       </c>
       <c r="E15">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="F15" t="s">
         <v>1580</v>
@@ -8710,7 +8710,7 @@
         <v>1380</v>
       </c>
       <c r="E16">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F16" t="s">
         <v>1580</v>
@@ -8745,7 +8745,7 @@
         <v>1381</v>
       </c>
       <c r="E17">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="F17" t="s">
         <v>1580</v>
@@ -8780,7 +8780,7 @@
         <v>1381</v>
       </c>
       <c r="E18">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="F18" t="s">
         <v>1580</v>
@@ -8815,7 +8815,7 @@
         <v>1382</v>
       </c>
       <c r="E19">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="F19" t="s">
         <v>1580</v>
@@ -8850,7 +8850,7 @@
         <v>1383</v>
       </c>
       <c r="E20">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="F20" t="s">
         <v>1580</v>
@@ -8885,7 +8885,7 @@
         <v>1384</v>
       </c>
       <c r="E21">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="F21" t="s">
         <v>1580</v>
@@ -8920,7 +8920,7 @@
         <v>1385</v>
       </c>
       <c r="E22">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="F22" t="s">
         <v>1580</v>
@@ -8955,7 +8955,7 @@
         <v>1386</v>
       </c>
       <c r="E23">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F23" t="s">
         <v>1580</v>
@@ -8993,7 +8993,7 @@
         <v>1387</v>
       </c>
       <c r="E24">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="F24" t="s">
         <v>1580</v>
@@ -9028,7 +9028,7 @@
         <v>1388</v>
       </c>
       <c r="E25">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F25" t="s">
         <v>1580</v>
@@ -9063,7 +9063,7 @@
         <v>1389</v>
       </c>
       <c r="E26">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F26" t="s">
         <v>1580</v>
@@ -9098,7 +9098,7 @@
         <v>1390</v>
       </c>
       <c r="E27">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F27" t="s">
         <v>1580</v>
@@ -9133,7 +9133,7 @@
         <v>1391</v>
       </c>
       <c r="E28">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F28" t="s">
         <v>1580</v>
@@ -9168,7 +9168,7 @@
         <v>1392</v>
       </c>
       <c r="E29">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F29" t="s">
         <v>1580</v>
@@ -9203,7 +9203,7 @@
         <v>1393</v>
       </c>
       <c r="E30">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F30" t="s">
         <v>1580</v>
@@ -9238,7 +9238,7 @@
         <v>1394</v>
       </c>
       <c r="E31">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F31" t="s">
         <v>1580</v>
@@ -9273,7 +9273,7 @@
         <v>1395</v>
       </c>
       <c r="E32">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F32" t="s">
         <v>1580</v>
@@ -9308,7 +9308,7 @@
         <v>1396</v>
       </c>
  